--- a/data/ventas.xlsx
+++ b/data/ventas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cesar\Desktop\Reportes Ventas Rap\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{349C1206-A2E4-4AA5-898B-16F0DAD2F070}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1ED77F2B-C804-4A4C-B2B1-B2CB88BD6181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2534,22 +2534,22 @@
         <v>0</v>
       </c>
       <c r="C2" s="96">
-        <v>17146.3661547753</v>
+        <v>20239.264746040899</v>
       </c>
       <c r="D2" s="96">
-        <v>85454.712087362597</v>
+        <v>97497.216435570401</v>
       </c>
       <c r="E2" s="96">
-        <v>298472871.26286787</v>
+        <v>347488527.93282223</v>
       </c>
       <c r="F2" s="96">
         <v>0</v>
       </c>
       <c r="G2" s="96">
-        <v>185038.5097417341</v>
+        <v>208601.67291691661</v>
       </c>
       <c r="H2" s="96">
-        <v>185038.5</v>
+        <v>208601.74</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -2560,22 +2560,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="96">
-        <v>250.12620409120001</v>
+        <v>287.35735488500001</v>
       </c>
       <c r="D3" s="96">
-        <v>592.11105820729995</v>
+        <v>636.38716535089998</v>
       </c>
       <c r="E3" s="96">
-        <v>6167950.3247244535</v>
+        <v>6953389.0972305397</v>
       </c>
       <c r="F3" s="96">
         <v>0</v>
       </c>
       <c r="G3" s="96">
-        <v>185038.5097417341</v>
+        <v>208601.67291691661</v>
       </c>
       <c r="H3" s="96">
-        <v>185038.5</v>
+        <v>208601.74</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2586,13 +2586,13 @@
         <v>1</v>
       </c>
       <c r="C4" s="96">
-        <v>104.8786706344</v>
+        <v>155.42341269729999</v>
       </c>
       <c r="D4" s="96">
-        <v>236.1575000002</v>
+        <v>326.98499999799998</v>
       </c>
       <c r="E4" s="96">
-        <v>3831780.4656781647</v>
+        <v>4842984.6712837927</v>
       </c>
       <c r="F4" s="96">
         <v>0</v>
@@ -2612,13 +2612,13 @@
         <v>1</v>
       </c>
       <c r="C5" s="96">
-        <v>160.9195238085</v>
+        <v>200.08797618950001</v>
       </c>
       <c r="D5" s="96">
-        <v>612.02249999640003</v>
+        <v>776.02249999560001</v>
       </c>
       <c r="E5" s="96">
-        <v>3383340.6159000443</v>
+        <v>4538116.0675083203</v>
       </c>
       <c r="F5" s="96">
         <v>0</v>
@@ -2638,13 +2638,13 @@
         <v>1</v>
       </c>
       <c r="C6" s="96">
-        <v>361.47559523759998</v>
+        <v>397.30575396749998</v>
       </c>
       <c r="D6" s="96">
-        <v>1048.2891785794</v>
+        <v>1116.1477142923</v>
       </c>
       <c r="E6" s="96">
-        <v>6899879.8473196756</v>
+        <v>7971555.33420307</v>
       </c>
       <c r="F6" s="96">
         <v>0</v>
@@ -2664,13 +2664,13 @@
         <v>1</v>
       </c>
       <c r="C7" s="96">
-        <v>327.00688491969998</v>
+        <v>418.16251984000002</v>
       </c>
       <c r="D7" s="96">
-        <v>1128.9845000005</v>
+        <v>1324.0909999978001</v>
       </c>
       <c r="E7" s="96">
-        <v>6168952.3513542237</v>
+        <v>8068882.1386908181</v>
       </c>
       <c r="F7" s="96">
         <v>0</v>
@@ -2690,13 +2690,13 @@
         <v>1</v>
       </c>
       <c r="C8" s="96">
-        <v>1635.1449074075001</v>
+        <v>1635.1115740742</v>
       </c>
       <c r="D8" s="96">
-        <v>1871.1244768535</v>
+        <v>1870.3864768542001</v>
       </c>
       <c r="E8" s="96">
-        <v>17081843.43377829</v>
+        <v>17061083.040882383</v>
       </c>
       <c r="F8" s="96">
         <v>0</v>
@@ -2716,13 +2716,13 @@
         <v>1</v>
       </c>
       <c r="C9" s="96">
-        <v>151.30611111069999</v>
+        <v>198.23150793619999</v>
       </c>
       <c r="D9" s="96">
-        <v>844.06249999780005</v>
+        <v>911.56750000140005</v>
       </c>
       <c r="E9" s="96">
-        <v>2938195.7767915935</v>
+        <v>3586477.5079781078</v>
       </c>
       <c r="F9" s="96">
         <v>0</v>
@@ -2742,13 +2742,13 @@
         <v>1</v>
       </c>
       <c r="C10" s="96">
-        <v>97.588759920800001</v>
+        <v>151.87760912690001</v>
       </c>
       <c r="D10" s="96">
-        <v>283.49911458560001</v>
+        <v>538.00411458880001</v>
       </c>
       <c r="E10" s="96">
-        <v>2863924.6281832345</v>
+        <v>3996158.8131728824</v>
       </c>
       <c r="F10" s="96">
         <v>0</v>
@@ -2768,13 +2768,13 @@
         <v>1</v>
       </c>
       <c r="C11" s="96">
-        <v>115.3075396819</v>
+        <v>157.76408730060001</v>
       </c>
       <c r="D11" s="96">
-        <v>293.55459523730002</v>
+        <v>362.56459523730001</v>
       </c>
       <c r="E11" s="96">
-        <v>2292259.0263364343</v>
+        <v>2958594.3353685732</v>
       </c>
       <c r="F11" s="96">
         <v>0</v>
@@ -2794,13 +2794,13 @@
         <v>1</v>
       </c>
       <c r="C12" s="96">
-        <v>345.86944444289998</v>
+        <v>376.22777777610003</v>
       </c>
       <c r="D12" s="96">
-        <v>2278.2034523770999</v>
+        <v>2353.8501190427</v>
       </c>
       <c r="E12" s="96">
-        <v>5810906.7980635744</v>
+        <v>6404448.8053096188</v>
       </c>
       <c r="F12" s="96">
         <v>0</v>
@@ -2820,13 +2820,13 @@
         <v>1</v>
       </c>
       <c r="C13" s="96">
-        <v>276.10170634870002</v>
+        <v>340.59277777739999</v>
       </c>
       <c r="D13" s="96">
-        <v>940.33651190850003</v>
+        <v>1049.3365119081</v>
       </c>
       <c r="E13" s="96">
-        <v>5672001.5032034451</v>
+        <v>6622431.8650625329</v>
       </c>
       <c r="F13" s="96">
         <v>0</v>
@@ -2846,13 +2846,13 @@
         <v>1</v>
       </c>
       <c r="C14" s="96">
-        <v>1609.1910714287001</v>
+        <v>1689.6688492064</v>
       </c>
       <c r="D14" s="96">
-        <v>14799.4800000014</v>
+        <v>14984.7324999998</v>
       </c>
       <c r="E14" s="96">
-        <v>38609317.055148289</v>
+        <v>39689592.681744099</v>
       </c>
       <c r="F14" s="96">
         <v>0</v>
@@ -2872,13 +2872,13 @@
         <v>1</v>
       </c>
       <c r="C15" s="96">
-        <v>247.15327380900001</v>
+        <v>322.91230158680003</v>
       </c>
       <c r="D15" s="96">
-        <v>974.77749999800005</v>
+        <v>1065.8074999979999</v>
       </c>
       <c r="E15" s="96">
-        <v>4655359.4802594241</v>
+        <v>6197917.8190731332</v>
       </c>
       <c r="F15" s="96">
         <v>0</v>
@@ -2898,13 +2898,13 @@
         <v>1</v>
       </c>
       <c r="C16" s="96">
-        <v>178.4678174595</v>
+        <v>214.65501984030001</v>
       </c>
       <c r="D16" s="96">
-        <v>966.66851190839998</v>
+        <v>1133.6685119097999</v>
       </c>
       <c r="E16" s="96">
-        <v>4172472.7522102422</v>
+        <v>5255755.4759214995</v>
       </c>
       <c r="F16" s="96">
         <v>0</v>
@@ -2924,13 +2924,13 @@
         <v>1</v>
       </c>
       <c r="C17" s="96">
-        <v>300.13720237960001</v>
+        <v>480.26246031580001</v>
       </c>
       <c r="D17" s="96">
-        <v>957.02602381810004</v>
+        <v>1416.7735238169</v>
       </c>
       <c r="E17" s="96">
-        <v>6362623.1530077159</v>
+        <v>9288875.7683896385</v>
       </c>
       <c r="F17" s="96">
         <v>0</v>
@@ -2950,13 +2950,13 @@
         <v>1</v>
       </c>
       <c r="C18" s="96">
-        <v>484.40908730130002</v>
+        <v>588.94634920609997</v>
       </c>
       <c r="D18" s="96">
-        <v>2532.7421785693</v>
+        <v>2848.4188452368999</v>
       </c>
       <c r="E18" s="96">
-        <v>10180781.322442733</v>
+        <v>12202147.531287048</v>
       </c>
       <c r="F18" s="96">
         <v>0</v>
@@ -2976,13 +2976,13 @@
         <v>1</v>
       </c>
       <c r="C19" s="96">
-        <v>381.46455026360002</v>
+        <v>441.94708994609999</v>
       </c>
       <c r="D19" s="96">
-        <v>1583.1667142941999</v>
+        <v>1784.6717142952</v>
       </c>
       <c r="E19" s="96">
-        <v>8068602.606727235</v>
+        <v>9037854.5756811257</v>
       </c>
       <c r="F19" s="96">
         <v>0</v>
@@ -3002,13 +3002,13 @@
         <v>1</v>
       </c>
       <c r="C20" s="96">
-        <v>1502.1562896826999</v>
+        <v>1691.1757341268999</v>
       </c>
       <c r="D20" s="96">
-        <v>8207.8199999985009</v>
+        <v>8709.6164999951998</v>
       </c>
       <c r="E20" s="96">
-        <v>21714287.032106198</v>
+        <v>25307057.946538661</v>
       </c>
       <c r="F20" s="96">
         <v>0</v>
@@ -3028,13 +3028,13 @@
         <v>1</v>
       </c>
       <c r="C21" s="96">
-        <v>211.5864484121</v>
+        <v>264.46081349069999</v>
       </c>
       <c r="D21" s="96">
-        <v>833.7746071478</v>
+        <v>939.2292142901</v>
       </c>
       <c r="E21" s="96">
-        <v>4521737.6382463202</v>
+        <v>5595341.8938343767</v>
       </c>
       <c r="F21" s="96">
         <v>0</v>
@@ -3054,13 +3054,13 @@
         <v>1</v>
       </c>
       <c r="C22" s="96">
-        <v>165.08382936460001</v>
+        <v>197.9982142849</v>
       </c>
       <c r="D22" s="96">
-        <v>427.67851190099998</v>
+        <v>505.67851190179999</v>
       </c>
       <c r="E22" s="96">
-        <v>2633216.6305364068</v>
+        <v>3109025.2196221473</v>
       </c>
       <c r="F22" s="96">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         <v>1</v>
       </c>
       <c r="C23" s="96">
-        <v>790.79180555489995</v>
+        <v>781.37513888820001</v>
       </c>
       <c r="D23" s="96">
         <v>4836.2267976160001</v>
       </c>
       <c r="E23" s="96">
-        <v>17286368.69822238</v>
+        <v>16984006.336814482</v>
       </c>
       <c r="F23" s="96">
         <v>0</v>
@@ -3132,13 +3132,13 @@
         <v>1</v>
       </c>
       <c r="C25" s="96">
-        <v>266.02386904759999</v>
+        <v>298.05575396820001</v>
       </c>
       <c r="D25" s="96">
-        <v>745.76000000479996</v>
+        <v>850.76000000500005</v>
       </c>
       <c r="E25" s="96">
-        <v>4425690.3579718489</v>
+        <v>4865926.9418352479</v>
       </c>
       <c r="F25" s="96">
         <v>0</v>
@@ -3158,13 +3158,13 @@
         <v>1</v>
       </c>
       <c r="C26" s="96">
-        <v>116.358075396</v>
+        <v>200.69081349109999</v>
       </c>
       <c r="D26" s="96">
-        <v>329.2370833343</v>
+        <v>459.23708333330001</v>
       </c>
       <c r="E26" s="96">
-        <v>2299134.4748592312</v>
+        <v>3089173.5689832573</v>
       </c>
       <c r="F26" s="96">
         <v>0</v>
@@ -3184,13 +3184,13 @@
         <v>1</v>
       </c>
       <c r="C27" s="96">
-        <v>1858.5</v>
+        <v>1888.5</v>
       </c>
       <c r="D27" s="96">
-        <v>9370.84</v>
+        <v>9736.84</v>
       </c>
       <c r="E27" s="96">
-        <v>22612109.009</v>
+        <v>23468686.842</v>
       </c>
       <c r="F27" s="96">
         <v>0</v>
@@ -3210,13 +3210,13 @@
         <v>1</v>
       </c>
       <c r="C28" s="96">
-        <v>335.03509589909999</v>
+        <v>424.6578339939</v>
       </c>
       <c r="D28" s="96">
-        <v>1431.6175520900999</v>
+        <v>1810.8346354224</v>
       </c>
       <c r="E28" s="96">
-        <v>6604601.1312453747</v>
+        <v>8516814.03087065</v>
       </c>
       <c r="F28" s="96">
         <v>0</v>
@@ -3236,13 +3236,13 @@
         <v>1</v>
       </c>
       <c r="C29" s="96">
-        <v>1070.0341666667</v>
+        <v>1351.4300000001001</v>
       </c>
       <c r="D29" s="96">
-        <v>2070.5600000021</v>
+        <v>2346.2820833356</v>
       </c>
       <c r="E29" s="96">
-        <v>14993819.966923174</v>
+        <v>17555809.912466466</v>
       </c>
       <c r="F29" s="96">
         <v>0</v>
@@ -3262,13 +3262,13 @@
         <v>1</v>
       </c>
       <c r="C30" s="96">
-        <v>94.954265873200001</v>
+        <v>111.48898809560001</v>
       </c>
       <c r="D30" s="96">
-        <v>328.6716666758</v>
+        <v>371.92416667719999</v>
       </c>
       <c r="E30" s="96">
-        <v>1808557.8257932956</v>
+        <v>2098536.1960838647</v>
       </c>
       <c r="F30" s="96">
         <v>0</v>
@@ -3288,13 +3288,13 @@
         <v>1</v>
       </c>
       <c r="C31" s="96">
-        <v>129.67519841169999</v>
+        <v>172.14345238000001</v>
       </c>
       <c r="D31" s="96">
-        <v>329.79500000109999</v>
+        <v>351.31749999890002</v>
       </c>
       <c r="E31" s="96">
-        <v>2246997.9859188953</v>
+        <v>2883607.9842428509</v>
       </c>
       <c r="F31" s="96">
         <v>0</v>
@@ -3314,13 +3314,13 @@
         <v>1</v>
       </c>
       <c r="C32" s="96">
-        <v>35.690277778000002</v>
+        <v>55.931944444599999</v>
       </c>
       <c r="D32" s="96">
-        <v>226.89916666760001</v>
+        <v>392.40416666760001</v>
       </c>
       <c r="E32" s="96">
-        <v>1134886.8601273343</v>
+        <v>1626463.4655310514</v>
       </c>
       <c r="F32" s="96">
         <v>0</v>
@@ -3340,13 +3340,13 @@
         <v>1</v>
       </c>
       <c r="C33" s="96">
-        <v>295.61113095220003</v>
+        <v>308.6682738092</v>
       </c>
       <c r="D33" s="96">
-        <v>667.99600000179998</v>
+        <v>704.99600000179998</v>
       </c>
       <c r="E33" s="96">
-        <v>4669958.7290065279</v>
+        <v>4975553.6144345868</v>
       </c>
       <c r="F33" s="96">
         <v>0</v>
@@ -3418,13 +3418,13 @@
         <v>1</v>
       </c>
       <c r="C36" s="96">
-        <v>249.8000992058</v>
+        <v>285.49811507840002</v>
       </c>
       <c r="D36" s="96">
-        <v>1087.4160119085</v>
+        <v>1243.7466071438</v>
       </c>
       <c r="E36" s="96">
-        <v>5027241.122842595</v>
+        <v>5822405.6030015703</v>
       </c>
       <c r="F36" s="96">
         <v>0</v>
@@ -3470,13 +3470,13 @@
         <v>1</v>
       </c>
       <c r="C38" s="96">
-        <v>259.89242424230002</v>
+        <v>308.39242424230002</v>
       </c>
       <c r="D38" s="96">
-        <v>2636.4299999988998</v>
+        <v>3260.7299999989</v>
       </c>
       <c r="E38" s="96">
-        <v>5554944.6639294196</v>
+        <v>6663134.8062294191</v>
       </c>
       <c r="F38" s="96">
         <v>0</v>
@@ -3496,13 +3496,13 @@
         <v>1</v>
       </c>
       <c r="C39" s="96">
-        <v>403.9166666667</v>
+        <v>471.4166666667</v>
       </c>
       <c r="D39" s="96">
-        <v>4611.43</v>
+        <v>5734.2</v>
       </c>
       <c r="E39" s="96">
-        <v>8252554.4917521486</v>
+        <v>10196205.867152149</v>
       </c>
       <c r="F39" s="96">
         <v>0</v>
@@ -3522,13 +3522,13 @@
         <v>1</v>
       </c>
       <c r="C40" s="96">
-        <v>319.48347883600002</v>
+        <v>757.61760582019997</v>
       </c>
       <c r="D40" s="96">
-        <v>1582.4444986829001</v>
+        <v>4224.4444986853996</v>
       </c>
       <c r="E40" s="96">
-        <v>4507114.506957056</v>
+        <v>6909391.5039921645</v>
       </c>
       <c r="F40" s="96">
         <v>0</v>
@@ -3548,13 +3548,13 @@
         <v>1</v>
       </c>
       <c r="C41" s="96">
-        <v>548.18968253950004</v>
+        <v>679.35634920610005</v>
       </c>
       <c r="D41" s="96">
-        <v>4043.0241666669999</v>
+        <v>4883.0241666669999</v>
       </c>
       <c r="E41" s="96">
-        <v>7398936.6723073218</v>
+        <v>8825883.2392010316</v>
       </c>
       <c r="F41" s="96">
         <v>0</v>
@@ -3574,13 +3574,13 @@
         <v>1</v>
       </c>
       <c r="C42" s="96">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="D42" s="96">
-        <v>126.04</v>
+        <v>424.04</v>
       </c>
       <c r="E42" s="96">
-        <v>280769.63740000001</v>
+        <v>746511.00490000006</v>
       </c>
       <c r="F42" s="96">
         <v>0</v>
@@ -3600,13 +3600,13 @@
         <v>1</v>
       </c>
       <c r="C43" s="96">
-        <v>-6.2142857142999999</v>
+        <v>74.818551587300007</v>
       </c>
       <c r="D43" s="96">
-        <v>-6.2810714286999998</v>
+        <v>229.00349106979999</v>
       </c>
       <c r="E43" s="96">
-        <v>-275260.76904147147</v>
+        <v>3760393.1741207056</v>
       </c>
       <c r="F43" s="96">
         <v>0</v>
@@ -3626,13 +3626,13 @@
         <v>1</v>
       </c>
       <c r="C44" s="96">
-        <v>-3.2847222223000001</v>
+        <v>123.917063492</v>
       </c>
       <c r="D44" s="96">
-        <v>-20.505000001599999</v>
+        <v>1239.6349404736</v>
       </c>
       <c r="E44" s="96">
-        <v>-402349.89063324447</v>
+        <v>1913900.6624423866</v>
       </c>
       <c r="F44" s="96">
         <v>0</v>
@@ -3652,13 +3652,13 @@
         <v>1</v>
       </c>
       <c r="C45" s="96">
-        <v>217.31500000029999</v>
+        <v>234.9175793654</v>
       </c>
       <c r="D45" s="96">
-        <v>2178.0000000025002</v>
+        <v>2276.0000000041</v>
       </c>
       <c r="E45" s="96">
-        <v>4246358.1772271991</v>
+        <v>4664188.216696891</v>
       </c>
       <c r="F45" s="96">
         <v>0</v>
@@ -3678,13 +3678,13 @@
         <v>1</v>
       </c>
       <c r="C46" s="96">
-        <v>101.875</v>
+        <v>321.875</v>
       </c>
       <c r="D46" s="96">
         <v>-24.9999999996</v>
       </c>
       <c r="E46" s="96">
-        <v>136464.048396092</v>
+        <v>1599703.2523960921</v>
       </c>
       <c r="F46" s="96">
         <v>0</v>
@@ -3773,44 +3773,44 @@
       </c>
       <c r="D2" s="59">
         <f>IFERROR(+VLOOKUP(B2,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>12202147.531287048</v>
+      </c>
+      <c r="E2" s="59">
         <v>10180781.322442733</v>
-      </c>
-      <c r="E2" s="59">
-        <v>6538018.3834050605</v>
       </c>
       <c r="F2" s="59">
         <f t="shared" ref="F2:F9" si="0">+D2-E2</f>
-        <v>3642762.9390376722</v>
+        <v>2021366.2088443153</v>
       </c>
       <c r="G2" s="60">
         <f t="shared" ref="G2:G41" si="1">+D2/C2</f>
-        <v>0.31539877786895837</v>
+        <v>0.3780203401737795</v>
       </c>
       <c r="H2" s="59">
         <f>+D2/$N$3*$N$4</f>
-        <v>61084687.934656397</v>
+        <v>58570308.150177836</v>
       </c>
       <c r="I2" s="60">
         <f t="shared" ref="I2:I41" si="2">+H2/C2</f>
-        <v>1.8923926672137501</v>
+        <v>1.8144976328341418</v>
       </c>
       <c r="J2" s="59">
         <f>+D2/$N$3</f>
-        <v>2545195.3306106832</v>
+        <v>2440429.5062574097</v>
       </c>
       <c r="K2" s="59">
         <f t="shared" ref="K2:K41" si="3">+(C2-D2)/$N$2</f>
-        <v>1104914.765790401</v>
+        <v>1056680.4793138793</v>
       </c>
       <c r="L2" s="61" cm="1">
         <f t="array" ref="L2">+_xlfn.IFS(I2&gt;114%,H2*0.02,I2&gt;109%,H2*0.015,I2&gt;104%,H2*0.0125,I2&gt;99%,H2*0.01,I2&lt;99%,H2*0)</f>
-        <v>1221693.7586931279</v>
+        <v>1171406.1630035567</v>
       </c>
       <c r="M2" s="53" t="s">
         <v>36</v>
       </c>
       <c r="N2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -3823,45 +3823,45 @@
       </c>
       <c r="D3" s="4">
         <f>IFERROR(+VLOOKUP(B3,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>9288875.7683896385</v>
+      </c>
+      <c r="E3" s="4">
         <v>6362623.1530077159</v>
-      </c>
-      <c r="E3" s="4">
-        <v>5092283.3348378455</v>
       </c>
       <c r="F3" s="4">
         <f t="shared" si="0"/>
-        <v>1270339.8181698704</v>
+        <v>2926252.6153819226</v>
       </c>
       <c r="G3" s="5">
         <f t="shared" si="1"/>
-        <v>0.20536032580062649</v>
+        <v>0.29980819360899963</v>
       </c>
       <c r="H3" s="4">
         <f t="shared" ref="H3:H41" si="4">+D3/$N$3*$N$4</f>
-        <v>38175738.918046296</v>
+        <v>44586603.688270271</v>
       </c>
       <c r="I3" s="5">
         <f t="shared" si="2"/>
-        <v>1.2321619548037588</v>
+        <v>1.4390793293231983</v>
       </c>
       <c r="J3" s="4">
         <f t="shared" ref="J3:J41" si="5">+D3/$N$3</f>
-        <v>1590655.788251929</v>
+        <v>1857775.1536779278</v>
       </c>
       <c r="K3" s="4">
         <f t="shared" si="3"/>
-        <v>1231005.251293777</v>
+        <v>1141781.7058154535</v>
       </c>
       <c r="L3" s="63" cm="1">
         <f t="array" ref="L3">+_xlfn.IFS(I3&gt;114%,H3*0.02,I3&gt;109%,H3*0.015,I3&gt;104%,H3*0.0125,I3&gt;99%,H3*0.01,I3&lt;99%,H3*0)</f>
-        <v>763514.77836092596</v>
+        <v>891732.07376540545</v>
       </c>
       <c r="M3" s="53" t="s">
         <v>40</v>
       </c>
       <c r="N3">
         <f>N4-N2</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -3874,38 +3874,38 @@
       </c>
       <c r="D4" s="4">
         <f>IFERROR(+VLOOKUP(B4,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>6197917.8190731332</v>
+      </c>
+      <c r="E4" s="4">
         <v>4655359.4802594241</v>
-      </c>
-      <c r="E4" s="4">
-        <v>3799689.1529486589</v>
       </c>
       <c r="F4" s="4">
         <f t="shared" si="0"/>
-        <v>855670.32731076516</v>
+        <v>1542558.3388137091</v>
       </c>
       <c r="G4" s="5">
         <f t="shared" si="1"/>
-        <v>0.16397866693420166</v>
+        <v>0.21831317346146409</v>
       </c>
       <c r="H4" s="4">
         <f t="shared" si="4"/>
-        <v>27932156.881556544</v>
+        <v>29750005.531551037</v>
       </c>
       <c r="I4" s="5">
         <f t="shared" si="2"/>
-        <v>0.98387200160521004</v>
+        <v>1.0479032326150275</v>
       </c>
       <c r="J4" s="4">
         <f t="shared" si="5"/>
-        <v>1163839.870064856</v>
+        <v>1239583.5638146265</v>
       </c>
       <c r="K4" s="4">
         <f t="shared" si="3"/>
-        <v>1186733.5889944416</v>
+        <v>1168005.970582901</v>
       </c>
       <c r="L4" s="63" cm="1">
         <f t="array" ref="L4">+_xlfn.IFS(I4&gt;114%,H4*0.02,I4&gt;109%,H4*0.015,I4&gt;104%,H4*0.0125,I4&gt;99%,H4*0.01,I4&lt;99%,H4*0)</f>
-        <v>0</v>
+        <v>371875.06914438796</v>
       </c>
       <c r="M4" s="53" t="s">
         <v>47</v>
@@ -3924,38 +3924,38 @@
       </c>
       <c r="D5" s="4">
         <f>IFERROR(+VLOOKUP(B5,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>6622431.8650625329</v>
+      </c>
+      <c r="E5" s="4">
         <v>5672001.5032034451</v>
-      </c>
-      <c r="E5" s="4">
-        <v>4650179.1579327742</v>
       </c>
       <c r="F5" s="4">
         <f t="shared" si="0"/>
-        <v>1021822.345270671</v>
+        <v>950430.36185908783</v>
       </c>
       <c r="G5" s="5">
         <f t="shared" si="1"/>
-        <v>0.19978849093996473</v>
+        <v>0.23326609979322546</v>
       </c>
       <c r="H5" s="4">
         <f t="shared" si="4"/>
-        <v>34032009.019220673</v>
+        <v>31787672.952300161</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" si="2"/>
-        <v>1.1987309456397885</v>
+        <v>1.1196772790074823</v>
       </c>
       <c r="J5" s="4">
         <f t="shared" si="5"/>
-        <v>1418000.3758008613</v>
+        <v>1324486.3730125066</v>
       </c>
       <c r="K5" s="4">
         <f t="shared" si="3"/>
-        <v>1135901.4878472404</v>
+        <v>1145663.1260571433</v>
       </c>
       <c r="L5" s="63" cm="1">
         <f t="array" ref="L5">+_xlfn.IFS(I5&gt;114%,H5*0.02,I5&gt;109%,H5*0.015,I5&gt;104%,H5*0.0125,I5&gt;99%,H5*0.01,I5&lt;99%,H5*0)</f>
-        <v>680640.18038441346</v>
+        <v>476815.09428450238</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
@@ -3968,38 +3968,38 @@
       </c>
       <c r="D6" s="4">
         <f>IFERROR(+VLOOKUP(B6,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>6404448.8053096188</v>
+      </c>
+      <c r="E6" s="4">
         <v>5810906.7980635744</v>
-      </c>
-      <c r="E6" s="4">
-        <v>3454829.7358999122</v>
       </c>
       <c r="F6" s="4">
         <f t="shared" si="0"/>
-        <v>2356077.0621636622</v>
+        <v>593542.00724604446</v>
       </c>
       <c r="G6" s="5">
         <f t="shared" si="1"/>
-        <v>0.24697075223084025</v>
+        <v>0.27219702432644627</v>
       </c>
       <c r="H6" s="4">
         <f t="shared" si="4"/>
-        <v>34865440.788381442</v>
+        <v>30741354.265486173</v>
       </c>
       <c r="I6" s="5">
         <f t="shared" si="2"/>
-        <v>1.4818245133850414</v>
+        <v>1.3065457167669423</v>
       </c>
       <c r="J6" s="4">
         <f t="shared" si="5"/>
-        <v>1452726.6995158936</v>
+        <v>1280889.7610619238</v>
       </c>
       <c r="K6" s="4">
         <f t="shared" si="3"/>
-        <v>885890.88697282749</v>
+        <v>901277.67011634237</v>
       </c>
       <c r="L6" s="63" cm="1">
         <f t="array" ref="L6">+_xlfn.IFS(I6&gt;114%,H6*0.02,I6&gt;109%,H6*0.015,I6&gt;104%,H6*0.0125,I6&gt;99%,H6*0.01,I6&lt;99%,H6*0)</f>
-        <v>697308.81576762884</v>
+        <v>614827.08530972351</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
@@ -4012,34 +4012,34 @@
       </c>
       <c r="D7" s="4">
         <f>IFERROR(+VLOOKUP(B7,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>3586477.5079781078</v>
+      </c>
+      <c r="E7" s="4">
         <v>2938195.7767915935</v>
-      </c>
-      <c r="E7" s="4">
-        <v>2229458.8498637299</v>
       </c>
       <c r="F7" s="4">
         <f t="shared" ref="F7:F8" si="6">+D7-E7</f>
-        <v>708736.92692786362</v>
+        <v>648281.73118651425</v>
       </c>
       <c r="G7" s="5">
         <f t="shared" si="1"/>
-        <v>0.10591200774933836</v>
+        <v>0.12928036879577476</v>
       </c>
       <c r="H7" s="4">
         <f t="shared" si="4"/>
-        <v>17629174.660749562</v>
+        <v>17215092.038294919</v>
       </c>
       <c r="I7" s="5">
         <f t="shared" si="2"/>
-        <v>0.63547204649603017</v>
+        <v>0.62054577021971891</v>
       </c>
       <c r="J7" s="4">
         <f t="shared" si="5"/>
-        <v>734548.94419789838</v>
+        <v>717295.50159562158</v>
       </c>
       <c r="K7" s="4">
         <f t="shared" si="3"/>
-        <v>1240183.0626836454</v>
+        <v>1271335.7643413893</v>
       </c>
       <c r="L7" s="63" cm="1">
         <f t="array" ref="L7">+_xlfn.IFS(I7&gt;114%,H7*0.02,I7&gt;109%,H7*0.015,I7&gt;104%,H7*0.0125,I7&gt;99%,H7*0.01,I7&lt;99%,H7*0)</f>
@@ -4056,38 +4056,38 @@
       </c>
       <c r="D8" s="4">
         <f>IFERROR(+VLOOKUP(B8,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>8068882.1386908181</v>
+      </c>
+      <c r="E8" s="4">
         <v>6168952.3513542237</v>
-      </c>
-      <c r="E8" s="4">
-        <v>4232380.5042614806</v>
       </c>
       <c r="F8" s="4">
         <f t="shared" si="6"/>
-        <v>1936571.847092743</v>
+        <v>1899929.7873365944</v>
       </c>
       <c r="G8" s="5">
         <f t="shared" si="1"/>
-        <v>0.17216767758838331</v>
+        <v>0.22519232106693524</v>
       </c>
       <c r="H8" s="4">
         <f t="shared" si="4"/>
-        <v>37013714.108125344</v>
+        <v>38730634.265715927</v>
       </c>
       <c r="I8" s="5">
         <f t="shared" si="2"/>
-        <v>1.0330060655302999</v>
+        <v>1.0809231411212892</v>
       </c>
       <c r="J8" s="4">
         <f t="shared" si="5"/>
-        <v>1542238.0878385559</v>
+        <v>1613776.4277381636</v>
       </c>
       <c r="K8" s="4">
         <f t="shared" si="3"/>
-        <v>1483105.9532781742</v>
+        <v>1461167.8567487835</v>
       </c>
       <c r="L8" s="63" cm="1">
         <f t="array" ref="L8">+_xlfn.IFS(I8&gt;114%,H8*0.02,I8&gt;109%,H8*0.015,I8&gt;104%,H8*0.0125,I8&gt;99%,H8*0.01,I8&lt;99%,H8*0)</f>
-        <v>370137.14108125347</v>
+        <v>484132.92832144909</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
@@ -4100,38 +4100,38 @@
       </c>
       <c r="D9" s="4">
         <f>IFERROR(+VLOOKUP(B9,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>7971555.33420307</v>
+      </c>
+      <c r="E9" s="4">
         <v>6899879.8473196756</v>
-      </c>
-      <c r="E9" s="4">
-        <v>5960130.3637676956</v>
       </c>
       <c r="F9" s="4">
         <f t="shared" si="0"/>
-        <v>939749.48355198</v>
+        <v>1071675.4868833944</v>
       </c>
       <c r="G9" s="5">
         <f t="shared" si="1"/>
-        <v>0.19256694188781318</v>
+        <v>0.22247605273782814</v>
       </c>
       <c r="H9" s="4">
         <f t="shared" si="4"/>
-        <v>41399279.08391805</v>
+        <v>38263465.604174733</v>
       </c>
       <c r="I9" s="5">
         <f t="shared" si="2"/>
-        <v>1.155401651326879</v>
+        <v>1.0678850531415751</v>
       </c>
       <c r="J9" s="4">
         <f t="shared" si="5"/>
-        <v>1724969.9618299189</v>
+        <v>1594311.066840614</v>
       </c>
       <c r="K9" s="4">
         <f t="shared" si="3"/>
-        <v>1446559.5784799014</v>
+        <v>1466290.3201428754</v>
       </c>
       <c r="L9" s="63" cm="1">
         <f t="array" ref="L9">+_xlfn.IFS(I9&gt;114%,H9*0.02,I9&gt;109%,H9*0.015,I9&gt;104%,H9*0.0125,I9&gt;99%,H9*0.01,I9&lt;99%,H9*0)</f>
-        <v>827985.58167836105</v>
+        <v>478293.32005218416</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4142,34 +4142,34 @@
       </c>
       <c r="D10" s="64">
         <f>+SUM(D2:D9)</f>
+        <v>60342736.769993968</v>
+      </c>
+      <c r="E10" s="65">
         <v>48688700.232442394</v>
-      </c>
-      <c r="E10" s="65">
-        <v>35956969.48291716</v>
       </c>
       <c r="F10" s="64">
         <f>+SUM(F2:F9)</f>
-        <v>12731730.749525227</v>
+        <v>11654036.537551582</v>
       </c>
       <c r="G10" s="66">
         <f t="shared" si="1"/>
-        <v>0.2003859740391824</v>
+        <v>0.2483499872890047</v>
       </c>
       <c r="H10" s="64">
         <f t="shared" si="4"/>
-        <v>292132201.39465439</v>
+        <v>289645136.49597102</v>
       </c>
       <c r="I10" s="66">
         <f t="shared" si="2"/>
-        <v>1.2023158442350945</v>
+        <v>1.1920799389872223</v>
       </c>
       <c r="J10" s="64">
         <f t="shared" si="5"/>
-        <v>12172175.058110598</v>
+        <v>12068547.353998793</v>
       </c>
       <c r="K10" s="67">
         <f t="shared" si="3"/>
-        <v>9714294.5753404051</v>
+        <v>9612202.8931187652</v>
       </c>
       <c r="L10" s="68"/>
     </row>
@@ -4185,38 +4185,38 @@
       </c>
       <c r="D11" s="59">
         <f>IFERROR(+VLOOKUP(B11,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>25307057.946538661</v>
+      </c>
+      <c r="E11" s="59">
         <v>21714287.032106198</v>
-      </c>
-      <c r="E11" s="59">
-        <v>18543635.055367131</v>
       </c>
       <c r="F11" s="59">
         <f t="shared" ref="F11:F16" si="7">+D11-E11</f>
-        <v>3170651.9767390676</v>
+        <v>3592770.9144324623</v>
       </c>
       <c r="G11" s="60">
         <f t="shared" si="1"/>
-        <v>0.22392338580835955</v>
+        <v>0.26097297562008082</v>
       </c>
       <c r="H11" s="59">
         <f t="shared" si="4"/>
-        <v>130285722.19263719</v>
+        <v>121473878.14338556</v>
       </c>
       <c r="I11" s="60">
         <f t="shared" si="2"/>
-        <v>1.3435403148501575</v>
+        <v>1.2526702829763878</v>
       </c>
       <c r="J11" s="59">
         <f t="shared" si="5"/>
-        <v>5428571.7580265496</v>
+        <v>5061411.5893077319</v>
       </c>
       <c r="K11" s="59">
         <f t="shared" si="3"/>
-        <v>3762883.0724015655</v>
+        <v>3771836.3438736238</v>
       </c>
       <c r="L11" s="61" cm="1">
         <f t="array" ref="L11">+_xlfn.IFS(I11&gt;114%,H11*0.0125,I11&gt;109%,H11*0.01,I11&gt;104%,H11*0.0075,I11&gt;99%,H11*0.005,I11&lt;99%,H11*0)</f>
-        <v>1628571.5274079649</v>
+        <v>1518423.4767923197</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4244,23 +4244,23 @@
       </c>
       <c r="H12" s="4">
         <f t="shared" si="4"/>
-        <v>44054155.646617025</v>
+        <v>35243324.517293625</v>
       </c>
       <c r="I12" s="5">
         <f t="shared" si="2"/>
-        <v>1.3927568387895652</v>
+        <v>1.1142054710316522</v>
       </c>
       <c r="J12" s="4">
         <f t="shared" si="5"/>
-        <v>1835589.8186090428</v>
+        <v>1468471.8548872343</v>
       </c>
       <c r="K12" s="4">
         <f t="shared" si="3"/>
-        <v>1214427.1567065415</v>
+        <v>1278344.3754805701</v>
       </c>
       <c r="L12" s="63" cm="1">
         <f t="array" ref="L12">+_xlfn.IFS(I12&gt;114%,H12*0.02,I12&gt;109%,H12*0.015,I12&gt;104%,H12*0.0125,I12&gt;99%,H12*0.01,I12&lt;99%,H12*0)</f>
-        <v>881083.11293234047</v>
+        <v>528649.86775940435</v>
       </c>
       <c r="M12" s="27"/>
     </row>
@@ -4274,38 +4274,38 @@
       </c>
       <c r="D13" s="4">
         <f>IFERROR(+VLOOKUP(B13,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>39689592.681744099</v>
+      </c>
+      <c r="E13" s="4">
         <v>38609317.055148289</v>
-      </c>
-      <c r="E13" s="4">
-        <v>35677866.984969728</v>
       </c>
       <c r="F13" s="4">
         <f t="shared" si="7"/>
-        <v>2931450.0701785609</v>
+        <v>1080275.6265958101</v>
       </c>
       <c r="G13" s="5">
         <f t="shared" si="1"/>
-        <v>0.30078014317281015</v>
+        <v>0.30919586980090541</v>
       </c>
       <c r="H13" s="4">
         <f t="shared" si="4"/>
-        <v>231655902.33088973</v>
+        <v>190510044.87237167</v>
       </c>
       <c r="I13" s="5">
         <f t="shared" si="2"/>
-        <v>1.8046808590368608</v>
+        <v>1.4841401750443461</v>
       </c>
       <c r="J13" s="4">
         <f t="shared" si="5"/>
-        <v>9652329.2637870722</v>
+        <v>7937918.5363488197</v>
       </c>
       <c r="K13" s="4">
         <f t="shared" si="3"/>
-        <v>4487729.9509738348</v>
+        <v>4667069.6522568883</v>
       </c>
       <c r="L13" s="63" cm="1">
         <f t="array" ref="L13">+_xlfn.IFS(I13&gt;114%,H13*0.0125,I13&gt;109%,H13*0.01,I13&gt;104%,H13*0.0075,I13&gt;99%,H13*0.005,I13&lt;99%,H13*0)</f>
-        <v>2895698.7791361217</v>
+        <v>2381375.5609046458</v>
       </c>
       <c r="M13" s="53" t="s">
         <v>61</v>
@@ -4324,34 +4324,34 @@
       </c>
       <c r="D14" s="4">
         <f>IFERROR(+VLOOKUP(B14,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>6663134.8062294191</v>
+      </c>
+      <c r="E14" s="4">
         <v>5554944.6639294196</v>
-      </c>
-      <c r="E14" s="4">
-        <v>4699575.8856638623</v>
       </c>
       <c r="F14" s="4">
         <f t="shared" si="7"/>
-        <v>855368.77826555725</v>
+        <v>1108190.1422999995</v>
       </c>
       <c r="G14" s="5">
         <f t="shared" si="1"/>
-        <v>0.13086143732809949</v>
+        <v>0.15696779186946522</v>
       </c>
       <c r="H14" s="4">
         <f t="shared" si="4"/>
-        <v>33329667.983576518</v>
+        <v>31983047.069901209</v>
       </c>
       <c r="I14" s="5">
         <f t="shared" si="2"/>
-        <v>0.78516862396859699</v>
+        <v>0.75344540097343304</v>
       </c>
       <c r="J14" s="4">
         <f t="shared" si="5"/>
-        <v>1388736.1659823549</v>
+        <v>1332626.9612458837</v>
       </c>
       <c r="K14" s="4">
         <f t="shared" si="3"/>
-        <v>1844705.6365522791</v>
+        <v>1883469.6099339779</v>
       </c>
       <c r="L14" s="63" cm="1">
         <f t="array" ref="L14">+_xlfn.IFS(I14&gt;109%,H14*0.015,I14&gt;104%,H14*0.0125,I14&gt;99%,H14*0.01,I14&lt;99%,H14*0)</f>
@@ -4369,38 +4369,38 @@
       </c>
       <c r="D15" s="4">
         <f>IFERROR(+VLOOKUP(B15,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>10196205.867152149</v>
+      </c>
+      <c r="E15" s="4">
         <v>8252554.4917521486</v>
-      </c>
-      <c r="E15" s="4">
-        <v>5825319.4707523696</v>
       </c>
       <c r="F15" s="4">
         <f t="shared" si="7"/>
-        <v>2427235.020999779</v>
+        <v>1943651.3754000003</v>
       </c>
       <c r="G15" s="5">
         <f t="shared" si="1"/>
-        <v>0.1944107831409482</v>
+        <v>0.24019864027320303</v>
       </c>
       <c r="H15" s="4">
         <f t="shared" si="4"/>
-        <v>49515326.950512893</v>
+        <v>48941788.162330315</v>
       </c>
       <c r="I15" s="5">
         <f t="shared" si="2"/>
-        <v>1.1664646988456893</v>
+        <v>1.1529534733113747</v>
       </c>
       <c r="J15" s="4">
         <f t="shared" si="5"/>
-        <v>2063138.6229380372</v>
+        <v>2039241.1734304298</v>
       </c>
       <c r="K15" s="4">
         <f t="shared" si="3"/>
-        <v>1709825.1451611426</v>
+        <v>1697518.5014643606</v>
       </c>
       <c r="L15" s="63" cm="1">
         <f t="array" ref="L15">+_xlfn.IFS(I15&gt;109%,H15*0.015,I15&gt;104%,H15*0.0125,I15&gt;99%,H15*0.01,I15&lt;99%,H15*0)</f>
-        <v>742729.90425769333</v>
+        <v>734126.82243495469</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4411,34 +4411,34 @@
       </c>
       <c r="D16" s="64">
         <f>+SUM(D11:D15)</f>
+        <v>89198350.576100498</v>
+      </c>
+      <c r="E16" s="65">
         <v>81473462.517372221</v>
-      </c>
-      <c r="E16" s="65">
-        <v>72088756.671189263</v>
       </c>
       <c r="F16" s="64">
         <f t="shared" si="7"/>
-        <v>9384705.8461829573</v>
+        <v>7724888.0587282777</v>
       </c>
       <c r="G16" s="66">
         <f t="shared" si="1"/>
-        <v>0.23832065493106369</v>
+        <v>0.26091697432810329</v>
       </c>
       <c r="H16" s="64">
         <f t="shared" si="4"/>
-        <v>488840775.10423332</v>
+        <v>428152082.76528239</v>
       </c>
       <c r="I16" s="66">
         <f t="shared" si="2"/>
-        <v>1.4299239295863821</v>
+        <v>1.2524014767748959</v>
       </c>
       <c r="J16" s="64">
         <f t="shared" si="5"/>
-        <v>20368365.629343055</v>
+        <v>17839670.1152201</v>
       </c>
       <c r="K16" s="67">
         <f t="shared" si="3"/>
-        <v>13019570.961795364</v>
+        <v>13298238.483009422</v>
       </c>
       <c r="L16" s="68"/>
     </row>
@@ -4454,34 +4454,34 @@
       </c>
       <c r="D17" s="59">
         <f>IFERROR(+VLOOKUP(B17,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>4842984.6712837927</v>
+      </c>
+      <c r="E17" s="59">
         <v>3831780.4656781647</v>
-      </c>
-      <c r="E17" s="59">
-        <v>3490474.4748070529</v>
       </c>
       <c r="F17" s="59">
         <f t="shared" ref="F17:F40" si="8">+D17-E17</f>
-        <v>341305.99087111186</v>
+        <v>1011204.205605628</v>
       </c>
       <c r="G17" s="60">
         <f t="shared" si="1"/>
-        <v>0.13060802022729012</v>
+        <v>0.1650753861222426</v>
       </c>
       <c r="H17" s="59">
         <f t="shared" si="4"/>
-        <v>22990682.794068988</v>
+        <v>23246326.422162205</v>
       </c>
       <c r="I17" s="60">
         <f t="shared" si="2"/>
-        <v>0.78364812136374074</v>
+        <v>0.79236185338676446</v>
       </c>
       <c r="J17" s="59">
         <f t="shared" si="5"/>
-        <v>957945.11641954118</v>
+        <v>968596.93425675854</v>
       </c>
       <c r="K17" s="59">
         <f t="shared" si="3"/>
-        <v>1275311.8833410919</v>
+        <v>1289212.2874324322</v>
       </c>
       <c r="L17" s="61" cm="1">
         <f t="array" ref="L17">+_xlfn.IFS(I17&gt;114%,H17*0.02,I17&gt;109%,H17*0.015,I17&gt;104%,H17*0.0125,I17&gt;99%,H17*0.01,I17&lt;99%,H17*0)</f>
@@ -4498,34 +4498,34 @@
       </c>
       <c r="D18" s="4">
         <f>IFERROR(+VLOOKUP(B18,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>4538116.0675083203</v>
+      </c>
+      <c r="E18" s="4">
         <v>3383340.6159000443</v>
-      </c>
-      <c r="E18" s="4">
-        <v>2539362.2668490014</v>
       </c>
       <c r="F18" s="4">
         <f t="shared" si="8"/>
-        <v>843978.34905104293</v>
+        <v>1154775.451608276</v>
       </c>
       <c r="G18" s="5">
         <f t="shared" si="1"/>
-        <v>0.13555318881132356</v>
+        <v>0.18181914680884448</v>
       </c>
       <c r="H18" s="4">
         <f t="shared" si="4"/>
-        <v>20300043.695400268</v>
+        <v>21782957.124039941</v>
       </c>
       <c r="I18" s="5">
         <f t="shared" si="2"/>
-        <v>0.81331913286794133</v>
+        <v>0.87273190468245365</v>
       </c>
       <c r="J18" s="4">
         <f t="shared" si="5"/>
-        <v>845835.15397501108</v>
+        <v>907623.21350166411</v>
       </c>
       <c r="K18" s="4">
         <f t="shared" si="3"/>
-        <v>1078808.264204998</v>
+        <v>1074809.9911837727</v>
       </c>
       <c r="L18" s="63" cm="1">
         <f t="array" ref="L18">+_xlfn.IFS(I18&gt;114%,H18*0.02,I18&gt;109%,H18*0.015,I18&gt;104%,H18*0.0125,I18&gt;99%,H18*0.01,I18&lt;99%,H18*0)</f>
@@ -4542,34 +4542,34 @@
       </c>
       <c r="D19" s="4">
         <f>IFERROR(+VLOOKUP(B19,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>5255755.4759214995</v>
+      </c>
+      <c r="E19" s="4">
         <v>4172472.7522102422</v>
-      </c>
-      <c r="E19" s="4">
-        <v>3126324.9965506792</v>
       </c>
       <c r="F19" s="4">
         <f t="shared" si="8"/>
-        <v>1046147.755659563</v>
+        <v>1083282.7237112573</v>
       </c>
       <c r="G19" s="5">
         <f t="shared" si="1"/>
-        <v>0.16136942432618312</v>
+        <v>0.20326513458940426</v>
       </c>
       <c r="H19" s="4">
         <f t="shared" si="4"/>
-        <v>25034836.513261452</v>
+        <v>25227626.284423195</v>
       </c>
       <c r="I19" s="5">
         <f t="shared" si="2"/>
-        <v>0.96821654595709861</v>
+        <v>0.97567264602914039</v>
       </c>
       <c r="J19" s="4">
         <f t="shared" si="5"/>
-        <v>1043118.1880525606</v>
+        <v>1051151.0951842999</v>
       </c>
       <c r="K19" s="4">
         <f t="shared" si="3"/>
-        <v>1084208.8706644881</v>
+        <v>1084257.6152409737</v>
       </c>
       <c r="L19" s="63" cm="1">
         <f t="array" ref="L19">+_xlfn.IFS(I19&gt;114%,H19*0.02,I19&gt;109%,H19*0.015,I19&gt;104%,H19*0.0125,I19&gt;99%,H19*0.01,I19&lt;99%,H19*0)</f>
@@ -4586,38 +4586,38 @@
       </c>
       <c r="D20" s="4">
         <f>IFERROR(+VLOOKUP(B20,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>9037854.5756811257</v>
+      </c>
+      <c r="E20" s="4">
         <v>8068602.606727235</v>
-      </c>
-      <c r="E20" s="4">
-        <v>5313079.7996425815</v>
       </c>
       <c r="F20" s="4">
         <f t="shared" si="8"/>
-        <v>2755522.8070846535</v>
+        <v>969251.96895389073</v>
       </c>
       <c r="G20" s="5">
         <f t="shared" si="1"/>
-        <v>0.24050826698022318</v>
+        <v>0.2693996528474501</v>
       </c>
       <c r="H20" s="4">
         <f t="shared" si="4"/>
-        <v>48411615.64036341</v>
+        <v>43381701.963269398</v>
       </c>
       <c r="I20" s="5">
         <f t="shared" si="2"/>
-        <v>1.4430496018813392</v>
+        <v>1.2931183336677603</v>
       </c>
       <c r="J20" s="4">
         <f t="shared" si="5"/>
-        <v>2017150.6516818088</v>
+        <v>1807570.9151362251</v>
       </c>
       <c r="K20" s="4">
         <f t="shared" si="3"/>
-        <v>1273976.3696636383</v>
+        <v>1290014.4960167827</v>
       </c>
       <c r="L20" s="63" cm="1">
         <f t="array" ref="L20">+_xlfn.IFS(I20&gt;114%,H20*0.02,I20&gt;109%,H20*0.015,I20&gt;104%,H20*0.0125,I20&gt;99%,H20*0.01,I20&lt;99%,H20*0)</f>
-        <v>968232.31280726823</v>
+        <v>867634.03926538792</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4630,38 +4630,38 @@
       </c>
       <c r="D21" s="4">
         <f>IFERROR(+VLOOKUP(B21,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>5595341.8938343767</v>
+      </c>
+      <c r="E21" s="4">
         <v>4521737.6382463202</v>
-      </c>
-      <c r="E21" s="4">
-        <v>3621062.6775038806</v>
       </c>
       <c r="F21" s="4">
         <f t="shared" ref="F21:F23" si="9">+D21-E21</f>
-        <v>900674.96074243961</v>
+        <v>1073604.2555880565</v>
       </c>
       <c r="G21" s="5">
         <f t="shared" si="1"/>
-        <v>0.17761202985745514</v>
+        <v>0.2197827718053561</v>
       </c>
       <c r="H21" s="4">
         <f t="shared" si="4"/>
-        <v>27130425.829477921</v>
+        <v>26857641.090405006</v>
       </c>
       <c r="I21" s="5">
         <f t="shared" si="2"/>
-        <v>1.0656721791447308</v>
+        <v>1.0549573046657093</v>
       </c>
       <c r="J21" s="4">
         <f t="shared" si="5"/>
-        <v>1130434.40956158</v>
+        <v>1119068.3787668752</v>
       </c>
       <c r="K21" s="4">
         <f t="shared" si="3"/>
-        <v>1046838.618087684</v>
+        <v>1045429.9003245066</v>
       </c>
       <c r="L21" s="63" cm="1">
         <f t="array" ref="L21">+_xlfn.IFS(I21&gt;114%,H21*0.02,I21&gt;109%,H21*0.015,I21&gt;104%,H21*0.0125,I21&gt;99%,H21*0.01,I21&lt;99%,H21*0)</f>
-        <v>339130.32286847406</v>
+        <v>335720.51363006257</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4674,38 +4674,38 @@
       </c>
       <c r="D22" s="4">
         <f>IFERROR(+VLOOKUP(B22,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>8516814.03087065</v>
+      </c>
+      <c r="E22" s="4">
         <v>6604601.1312453747</v>
-      </c>
-      <c r="E22" s="4">
-        <v>4525419.7648018571</v>
       </c>
       <c r="F22" s="4">
         <f t="shared" si="9"/>
-        <v>2079181.3664435176</v>
+        <v>1912212.8996252753</v>
       </c>
       <c r="G22" s="5">
         <f t="shared" si="1"/>
-        <v>0.20806552552815036</v>
+        <v>0.26830619320450694</v>
       </c>
       <c r="H22" s="4">
         <f t="shared" si="4"/>
-        <v>39627606.787472248</v>
+        <v>40880707.348179117</v>
       </c>
       <c r="I22" s="5">
         <f t="shared" si="2"/>
-        <v>1.2483931531689021</v>
+        <v>1.2878697273816331</v>
       </c>
       <c r="J22" s="4">
         <f t="shared" si="5"/>
-        <v>1651150.2828113437</v>
+        <v>1703362.8061741299</v>
       </c>
       <c r="K22" s="4">
         <f t="shared" si="3"/>
-        <v>1256914.4534377314</v>
+        <v>1222425.061533124</v>
       </c>
       <c r="L22" s="63" cm="1">
         <f t="array" ref="L22">+_xlfn.IFS(I22&gt;114%,H22*0.02,I22&gt;109%,H22*0.015,I22&gt;104%,H22*0.0125,I22&gt;99%,H22*0.01,I22&lt;99%,H22*0)</f>
-        <v>792552.13574944495</v>
+        <v>817614.14696358237</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4718,38 +4718,38 @@
       </c>
       <c r="D23" s="4">
         <f>IFERROR(+VLOOKUP(B23,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>5822405.6030015703</v>
+      </c>
+      <c r="E23" s="4">
         <v>5027241.122842595</v>
-      </c>
-      <c r="E23" s="4">
-        <v>3880349.2779353959</v>
       </c>
       <c r="F23" s="4">
         <f t="shared" si="9"/>
-        <v>1146891.844907199</v>
+        <v>795164.48015897535</v>
       </c>
       <c r="G23" s="5">
         <f t="shared" si="1"/>
-        <v>0.18323556551315615</v>
+        <v>0.21221814455355015</v>
       </c>
       <c r="H23" s="4">
         <f t="shared" si="4"/>
-        <v>30163446.73705557</v>
+        <v>27947546.894407541</v>
       </c>
       <c r="I23" s="5">
         <f t="shared" si="2"/>
-        <v>1.0994133930789369</v>
+        <v>1.0186470938570409</v>
       </c>
       <c r="J23" s="4">
         <f t="shared" si="5"/>
-        <v>1256810.2807106487</v>
+        <v>1164481.1206003141</v>
       </c>
       <c r="K23" s="4">
         <f t="shared" si="3"/>
-        <v>1120435.2553578704</v>
+        <v>1137554.7698420228</v>
       </c>
       <c r="L23" s="63" cm="1">
         <f t="array" ref="L23">+_xlfn.IFS(I23&gt;114%,H23*0.02,I23&gt;109%,H23*0.015,I23&gt;104%,H23*0.0125,I23&gt;99%,H23*0.01,I23&lt;99%,H23*0)</f>
-        <v>452451.70105583355</v>
+        <v>279475.4689440754</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4762,38 +4762,38 @@
       </c>
       <c r="D24" s="4">
         <f>IFERROR(+VLOOKUP(B24,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>6909391.5039921645</v>
+      </c>
+      <c r="E24" s="4">
         <v>4507114.506957056</v>
-      </c>
-      <c r="E24" s="4">
-        <v>3150944.560423614</v>
       </c>
       <c r="F24" s="4">
         <f t="shared" si="8"/>
-        <v>1356169.946533442</v>
+        <v>2402276.9970351085</v>
       </c>
       <c r="G24" s="5">
         <f t="shared" si="1"/>
-        <v>0.13456461174847464</v>
+        <v>0.20628710091961586</v>
       </c>
       <c r="H24" s="4">
         <f t="shared" si="4"/>
-        <v>27042687.041742336</v>
+        <v>33165079.21916239</v>
       </c>
       <c r="I24" s="5">
         <f t="shared" si="2"/>
-        <v>0.80738767049084792</v>
+        <v>0.99017808441415622</v>
       </c>
       <c r="J24" s="4">
         <f t="shared" si="5"/>
-        <v>1126778.626739264</v>
+        <v>1381878.3007984329</v>
       </c>
       <c r="K24" s="4">
         <f t="shared" si="3"/>
-        <v>1449347.0246521472</v>
+        <v>1399192.8155793599</v>
       </c>
       <c r="L24" s="63" cm="1">
         <f t="array" ref="L24">+_xlfn.IFS(I24&gt;114%,H24*0.02,I24&gt;109%,H24*0.015,I24&gt;104%,H24*0.0125,I24&gt;99%,H24*0.01,I24&lt;99%,H24*0)</f>
-        <v>0</v>
+        <v>331650.79219162388</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4806,34 +4806,34 @@
       </c>
       <c r="D25" s="4">
         <f>IFERROR(+VLOOKUP(B25,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>8825883.2392010316</v>
+      </c>
+      <c r="E25" s="4">
         <v>7398936.6723073218</v>
-      </c>
-      <c r="E25" s="4">
-        <v>7402539.5016198214</v>
       </c>
       <c r="F25" s="4">
         <f t="shared" si="8"/>
-        <v>-3602.8293124996126</v>
+        <v>1426946.5668937098</v>
       </c>
       <c r="G25" s="5">
         <f t="shared" si="1"/>
-        <v>0.13685273509407175</v>
+        <v>0.16324592497544999</v>
       </c>
       <c r="H25" s="4">
         <f t="shared" si="4"/>
-        <v>44393620.033843935</v>
+        <v>42364239.548164949</v>
       </c>
       <c r="I25" s="5">
         <f t="shared" si="2"/>
-        <v>0.82111641056443052</v>
+        <v>0.78358043988215986</v>
       </c>
       <c r="J25" s="4">
         <f t="shared" si="5"/>
-        <v>1849734.1680768305</v>
+        <v>1765176.6478402063</v>
       </c>
       <c r="K25" s="4">
         <f t="shared" si="3"/>
-        <v>2333300.8096346343</v>
+        <v>2381003.6645157356</v>
       </c>
       <c r="L25" s="63" cm="1">
         <f t="array" ref="L25">+_xlfn.IFS(I25&gt;109%,H25*0.015,I25&gt;104%,H25*0.0125,I25&gt;99%,H25*0.01,I25&lt;99%,H25*0)</f>
@@ -4848,34 +4848,34 @@
       </c>
       <c r="D26" s="67">
         <f>+SUM(D17:D25)</f>
+        <v>59344547.061294533</v>
+      </c>
+      <c r="E26" s="65">
         <v>47515827.512114353</v>
-      </c>
-      <c r="E26" s="65">
-        <v>37049557.32013388</v>
       </c>
       <c r="F26" s="67">
         <f>+D26-E26</f>
-        <v>10466270.191980474</v>
+        <v>11828719.54918018</v>
       </c>
       <c r="G26" s="66">
         <f t="shared" si="1"/>
-        <v>0.16619814784222828</v>
+        <v>0.20757196754299401</v>
       </c>
       <c r="H26" s="64">
         <f t="shared" si="4"/>
-        <v>285094965.07268614</v>
+        <v>284853825.89421374</v>
       </c>
       <c r="I26" s="66">
         <f t="shared" si="2"/>
-        <v>0.99718888705336972</v>
+        <v>0.99634544420637117</v>
       </c>
       <c r="J26" s="64">
         <f t="shared" si="5"/>
-        <v>11878956.878028588</v>
+        <v>11868909.412258906</v>
       </c>
       <c r="K26" s="67">
         <f t="shared" si="3"/>
-        <v>11919141.549044285</v>
+        <v>11923900.60166871</v>
       </c>
       <c r="L26" s="68"/>
     </row>
@@ -4891,38 +4891,38 @@
       </c>
       <c r="D27" s="59">
         <f>IFERROR(+VLOOKUP(B27,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>17555809.912466466</v>
+      </c>
+      <c r="E27" s="59">
         <v>14993819.966923174</v>
-      </c>
-      <c r="E27" s="59">
-        <v>7197381.3632933144</v>
       </c>
       <c r="F27" s="59">
         <f t="shared" si="8"/>
-        <v>7796438.6036298592</v>
+        <v>2561989.9455432929</v>
       </c>
       <c r="G27" s="60">
         <f t="shared" si="1"/>
-        <v>0.1829012032165232</v>
+        <v>0.21415348213558646</v>
       </c>
       <c r="H27" s="59">
         <f t="shared" si="4"/>
-        <v>89962919.801539034</v>
+        <v>84267887.579839051</v>
       </c>
       <c r="I27" s="60">
         <f t="shared" si="2"/>
-        <v>1.0974072192991391</v>
+        <v>1.0279367142508151</v>
       </c>
       <c r="J27" s="59">
         <f t="shared" si="5"/>
-        <v>3748454.9917307934</v>
+        <v>3511161.9824932935</v>
       </c>
       <c r="K27" s="59">
         <f t="shared" si="3"/>
-        <v>3349194.0016538412</v>
+        <v>3390625.7940807124</v>
       </c>
       <c r="L27" s="61" cm="1">
         <f t="array" ref="L27">+_xlfn.IFS(I27&gt;114%,H27*0.0125,I27&gt;109%,H27*0.01,I27&gt;104%,H27*0.0075,I27&gt;99%,H27*0.005,I27&lt;99%,H27*0)</f>
-        <v>899629.19801539031</v>
+        <v>421339.43789919524</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4935,34 +4935,34 @@
       </c>
       <c r="D28" s="4">
         <f>IFERROR(+VLOOKUP(B28,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>2883607.9842428509</v>
+      </c>
+      <c r="E28" s="4">
         <v>2246997.9859188953</v>
-      </c>
-      <c r="E28" s="4">
-        <v>1662817.6962441357</v>
       </c>
       <c r="F28" s="4">
         <f t="shared" si="8"/>
-        <v>584180.28967475961</v>
+        <v>636609.99832395557</v>
       </c>
       <c r="G28" s="5">
         <f t="shared" si="1"/>
-        <v>0.10699990409137597</v>
+        <v>0.13731466591632624</v>
       </c>
       <c r="H28" s="4">
         <f t="shared" si="4"/>
-        <v>13481987.915513372</v>
+        <v>13841318.324365683</v>
       </c>
       <c r="I28" s="5">
         <f t="shared" si="2"/>
-        <v>0.64199942454825576</v>
+        <v>0.65911039639836588</v>
       </c>
       <c r="J28" s="4">
         <f t="shared" si="5"/>
-        <v>561749.49647972384</v>
+        <v>576721.59684857016</v>
       </c>
       <c r="K28" s="4">
         <f t="shared" si="3"/>
-        <v>937650.10070405528</v>
+        <v>953494.31661879737</v>
       </c>
       <c r="L28" s="63" cm="1">
         <f t="array" ref="L28">+_xlfn.IFS(I28&gt;114%,H28*0.02,I28&gt;109%,H28*0.015,I28&gt;104%,H28*0.0125,I28&gt;99%,H28*0.01,I28&lt;99%,H28*0)</f>
@@ -4979,34 +4979,34 @@
       </c>
       <c r="D29" s="4">
         <f>IFERROR(+VLOOKUP(B29,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>3996158.8131728824</v>
+      </c>
+      <c r="E29" s="4">
         <v>2863924.6281832345</v>
-      </c>
-      <c r="E29" s="4">
-        <v>2237337.654012111</v>
       </c>
       <c r="F29" s="4">
         <f t="shared" si="8"/>
-        <v>626586.97417112347</v>
+        <v>1132234.1849896479</v>
       </c>
       <c r="G29" s="5">
         <f t="shared" si="1"/>
-        <v>0.11126487986197331</v>
+        <v>0.15525273461512304</v>
       </c>
       <c r="H29" s="4">
         <f t="shared" si="4"/>
-        <v>17183547.769099407</v>
+        <v>19181562.303229839</v>
       </c>
       <c r="I29" s="5">
         <f t="shared" si="2"/>
-        <v>0.66758927917183986</v>
+        <v>0.74521312615259072</v>
       </c>
       <c r="J29" s="4">
         <f t="shared" si="5"/>
-        <v>715981.15704580862</v>
+        <v>799231.76263457653</v>
       </c>
       <c r="K29" s="4">
         <f t="shared" si="3"/>
-        <v>1143788.7685908382</v>
+        <v>1144396.9045698482</v>
       </c>
       <c r="L29" s="63" cm="1">
         <f t="array" ref="L29">+_xlfn.IFS(I29&gt;114%,H29*0.02,I29&gt;109%,H29*0.015,I29&gt;104%,H29*0.0125,I29&gt;99%,H29*0.01,I29&lt;99%,H29*0)</f>
@@ -5024,34 +5024,34 @@
       </c>
       <c r="D30" s="4">
         <f>IFERROR(+VLOOKUP(B30,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>4975553.6144345868</v>
+      </c>
+      <c r="E30" s="4">
         <v>4669958.7290065279</v>
-      </c>
-      <c r="E30" s="4">
-        <v>2806120.8392654946</v>
       </c>
       <c r="F30" s="4">
         <f t="shared" si="8"/>
-        <v>1863837.8897410333</v>
+        <v>305594.88542805891</v>
       </c>
       <c r="G30" s="5">
         <f t="shared" si="1"/>
-        <v>0.12214405554833929</v>
+        <v>0.13013697386454762</v>
       </c>
       <c r="H30" s="4">
         <f t="shared" si="4"/>
-        <v>28019752.374039166</v>
+        <v>23882657.34928602</v>
       </c>
       <c r="I30" s="5">
         <f t="shared" si="2"/>
-        <v>0.73286433329003575</v>
+        <v>0.62465747454982867</v>
       </c>
       <c r="J30" s="4">
         <f t="shared" si="5"/>
-        <v>1167489.682251632</v>
+        <v>995110.72288691741</v>
       </c>
       <c r="K30" s="4">
         <f t="shared" si="3"/>
-        <v>1678162.3191559571</v>
+        <v>1750402.710404794</v>
       </c>
       <c r="L30" s="63" cm="1">
         <f t="array" ref="L30">+_xlfn.IFS(I30&gt;114%,H30*0.02,I30&gt;109%,H30*0.015,I30&gt;104%,H30*0.0125,I30&gt;99%,H30*0.01,I30&lt;99%,H30*0)</f>
@@ -5069,38 +5069,38 @@
       </c>
       <c r="D31" s="4">
         <f>IFERROR(+VLOOKUP(B31,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>4865926.9418352479</v>
+      </c>
+      <c r="E31" s="4">
         <v>4425690.3579718489</v>
-      </c>
-      <c r="E31" s="4">
-        <v>3265458.2459612871</v>
       </c>
       <c r="F31" s="4">
         <f t="shared" si="8"/>
-        <v>1160232.1120105619</v>
+        <v>440236.58386339899</v>
       </c>
       <c r="G31" s="5">
         <f t="shared" si="1"/>
-        <v>0.17413522817882371</v>
+        <v>0.19145697728077624</v>
       </c>
       <c r="H31" s="4">
         <f t="shared" si="4"/>
-        <v>26554142.147831094</v>
+        <v>23356449.320809193</v>
       </c>
       <c r="I31" s="5">
         <f t="shared" si="2"/>
-        <v>1.0448113690729421</v>
+        <v>0.91899349094772598</v>
       </c>
       <c r="J31" s="4">
         <f t="shared" si="5"/>
-        <v>1106422.5894929622</v>
+        <v>973185.38836704963</v>
       </c>
       <c r="K31" s="4">
         <f t="shared" si="3"/>
-        <v>1049477.9821014076</v>
+        <v>1081543.3188507764</v>
       </c>
       <c r="L31" s="63" cm="1">
         <f t="array" ref="L31">+_xlfn.IFS(I31&gt;114%,H31*0.02,I31&gt;109%,H31*0.015,I31&gt;104%,H31*0.0125,I31&gt;99%,H31*0.01,I31&lt;99%,H31*0)</f>
-        <v>331926.77684788872</v>
+        <v>0</v>
       </c>
       <c r="M31" s="27"/>
     </row>
@@ -5114,34 +5114,34 @@
       </c>
       <c r="D32" s="4">
         <f>IFERROR(+VLOOKUP(B32,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>2958594.3353685732</v>
+      </c>
+      <c r="E32" s="4">
         <v>2292259.0263364343</v>
-      </c>
-      <c r="E32" s="4">
-        <v>1556471.8667402903</v>
       </c>
       <c r="F32" s="4">
         <f t="shared" si="8"/>
-        <v>735787.15959614399</v>
+        <v>666335.3090321389</v>
       </c>
       <c r="G32" s="5">
         <f t="shared" si="1"/>
-        <v>9.0962659775255333E-2</v>
+        <v>0.11740453711780052</v>
       </c>
       <c r="H32" s="4">
         <f t="shared" si="4"/>
-        <v>13753554.158018606</v>
+        <v>14201252.80976915</v>
       </c>
       <c r="I32" s="5">
         <f t="shared" si="2"/>
-        <v>0.54577595865153194</v>
+        <v>0.56354177816544249</v>
       </c>
       <c r="J32" s="4">
         <f t="shared" si="5"/>
-        <v>573064.75658410857</v>
+        <v>591718.86707371462</v>
       </c>
       <c r="K32" s="4">
         <f t="shared" si="3"/>
-        <v>1145387.0486831781</v>
+        <v>1170600.2981384962</v>
       </c>
       <c r="L32" s="63" cm="1">
         <f t="array" ref="L32">+_xlfn.IFS(I32&gt;114%,H32*0.02,I32&gt;109%,H32*0.015,I32&gt;104%,H32*0.0125,I32&gt;99%,H32*0.01,I32&lt;99%,H32*0)</f>
@@ -5159,34 +5159,34 @@
       </c>
       <c r="D33" s="4">
         <f>IFERROR(+VLOOKUP(B33,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>3089173.5689832573</v>
+      </c>
+      <c r="E33" s="4">
         <v>2299134.4748592312</v>
-      </c>
-      <c r="E33" s="4">
-        <v>1905347.2963424551</v>
       </c>
       <c r="F33" s="4">
         <f t="shared" si="8"/>
-        <v>393787.17851677607</v>
+        <v>790039.09412402613</v>
       </c>
       <c r="G33" s="5">
         <f t="shared" si="1"/>
-        <v>8.6770433161019039E-2</v>
+        <v>0.1165868859004692</v>
       </c>
       <c r="H33" s="4">
         <f t="shared" si="4"/>
-        <v>13794806.849155387</v>
+        <v>14828033.131119635</v>
       </c>
       <c r="I33" s="5">
         <f t="shared" si="2"/>
-        <v>0.52062259896611418</v>
+        <v>0.55961705232225212</v>
       </c>
       <c r="J33" s="4">
         <f t="shared" si="5"/>
-        <v>574783.61871480779</v>
+        <v>617834.71379665146</v>
       </c>
       <c r="K33" s="4">
         <f t="shared" si="3"/>
-        <v>1209880.7762570386</v>
+        <v>1231977.706895618</v>
       </c>
       <c r="L33" s="63" cm="1">
         <f t="array" ref="L33">+_xlfn.IFS(I33&gt;114%,H33*0.02,I33&gt;109%,H33*0.015,I33&gt;104%,H33*0.0125,I33&gt;99%,H33*0.01,I33&lt;99%,H33*0)</f>
@@ -5203,34 +5203,34 @@
       </c>
       <c r="D34" s="4">
         <f>IFERROR(+VLOOKUP(B34,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>2098536.1960838647</v>
+      </c>
+      <c r="E34" s="4">
         <v>1808557.8257932956</v>
-      </c>
-      <c r="E34" s="4">
-        <v>1342266.2312651528</v>
       </c>
       <c r="F34" s="4">
         <f t="shared" si="8"/>
-        <v>466291.59452814283</v>
+        <v>289978.37029056903</v>
       </c>
       <c r="G34" s="5">
         <f t="shared" si="1"/>
-        <v>8.6121801228252179E-2</v>
+        <v>9.9930295051612605E-2</v>
       </c>
       <c r="H34" s="4">
         <f t="shared" si="4"/>
-        <v>10851346.954759773</v>
+        <v>10072973.741202552</v>
       </c>
       <c r="I34" s="5">
         <f t="shared" si="2"/>
-        <v>0.51673080736951305</v>
+        <v>0.47966541624774056</v>
       </c>
       <c r="J34" s="4">
         <f t="shared" si="5"/>
-        <v>452139.45644832391</v>
+        <v>419707.23921677296</v>
       </c>
       <c r="K34" s="4">
         <f t="shared" si="3"/>
-        <v>959572.10871033522</v>
+        <v>994813.88441663864</v>
       </c>
       <c r="L34" s="63" cm="1">
         <f t="array" ref="L34">+_xlfn.IFS(I34&gt;114%,H34*0.02,I34&gt;109%,H34*0.015,I34&gt;104%,H34*0.0125,I34&gt;99%,H34*0.01,I34&lt;99%,H34*0)</f>
@@ -5247,34 +5247,34 @@
       </c>
       <c r="D35" s="4">
         <f>IFERROR(+VLOOKUP(B35,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>1626463.4655310514</v>
+      </c>
+      <c r="E35" s="4">
         <v>1134886.8601273343</v>
-      </c>
-      <c r="E35" s="4">
-        <v>920475.59202497394</v>
       </c>
       <c r="F35" s="4">
         <f t="shared" si="8"/>
-        <v>214411.26810236031</v>
+        <v>491576.60540371714</v>
       </c>
       <c r="G35" s="5">
         <f t="shared" si="1"/>
-        <v>4.6024724437604296E-2</v>
+        <v>6.5960348506016314E-2</v>
       </c>
       <c r="H35" s="4">
         <f t="shared" si="4"/>
-        <v>6809321.160764005</v>
+        <v>7807024.6345490459</v>
       </c>
       <c r="I35" s="5">
         <f t="shared" si="2"/>
-        <v>0.27614834662562576</v>
+        <v>0.31660967282887825</v>
       </c>
       <c r="J35" s="4">
         <f t="shared" si="5"/>
-        <v>283721.71503183356</v>
+        <v>325292.69310621027</v>
       </c>
       <c r="K35" s="4">
         <f t="shared" si="3"/>
-        <v>1176165.6569936334</v>
+        <v>1212196.659708892</v>
       </c>
       <c r="L35" s="63" cm="1">
         <f t="array" ref="L35">+_xlfn.IFS(I35&gt;114%,H35*0.02,I35&gt;109%,H35*0.015,I35&gt;104%,H35*0.0125,I35&gt;99%,H35*0.01,I35&lt;99%,H35*0)</f>
@@ -5291,34 +5291,34 @@
       </c>
       <c r="D36" s="4">
         <f>IFERROR(+VLOOKUP(B36,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>3109025.2196221473</v>
+      </c>
+      <c r="E36" s="4">
         <v>2633216.6305364068</v>
-      </c>
-      <c r="E36" s="4">
-        <v>1931060.2247250369</v>
       </c>
       <c r="F36" s="4">
         <f t="shared" si="8"/>
-        <v>702156.40581136988</v>
+        <v>475808.5890857405</v>
       </c>
       <c r="G36" s="5">
         <f t="shared" si="1"/>
-        <v>0.1043477959396238</v>
+        <v>0.12320290151068544</v>
       </c>
       <c r="H36" s="4">
         <f t="shared" si="4"/>
-        <v>15799299.78321844</v>
+        <v>14923321.054186307</v>
       </c>
       <c r="I36" s="5">
         <f t="shared" si="2"/>
-        <v>0.62608677563774284</v>
+        <v>0.59137392725129012</v>
       </c>
       <c r="J36" s="4">
         <f t="shared" si="5"/>
-        <v>658304.15763410169</v>
+        <v>621805.04392442945</v>
       </c>
       <c r="K36" s="4">
         <f t="shared" si="3"/>
-        <v>1130089.1684731797</v>
+        <v>1164524.9884409397</v>
       </c>
       <c r="L36" s="63" cm="1">
         <f t="array" ref="L36">+_xlfn.IFS(I36&gt;114%,H36*0.02,I36&gt;109%,H36*0.015,I36&gt;104%,H36*0.0125,I36&gt;99%,H36*0.01,I36&lt;99%,H36*0)</f>
@@ -5335,34 +5335,34 @@
       </c>
       <c r="D37" s="4">
         <f>IFERROR(+VLOOKUP(B37,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>17061083.040882383</v>
+      </c>
+      <c r="E37" s="4">
         <v>17081843.43377829</v>
-      </c>
-      <c r="E37" s="4">
-        <v>16463801.298558187</v>
       </c>
       <c r="F37" s="4">
         <f t="shared" si="8"/>
-        <v>618042.13522010297</v>
+        <v>-20760.392895907164</v>
       </c>
       <c r="G37" s="5">
         <f t="shared" si="1"/>
-        <v>0.14000162634974328</v>
+        <v>0.13983147558233025</v>
       </c>
       <c r="H37" s="4">
         <f t="shared" si="4"/>
-        <v>102491060.60266975</v>
+        <v>81893198.596235424</v>
       </c>
       <c r="I37" s="5">
         <f t="shared" si="2"/>
-        <v>0.84000975809845979</v>
+        <v>0.67119108279518513</v>
       </c>
       <c r="J37" s="4">
         <f t="shared" si="5"/>
-        <v>4270460.8584445724</v>
+        <v>3412216.6081764763</v>
       </c>
       <c r="K37" s="4">
         <f t="shared" si="3"/>
-        <v>5246495.3283110857</v>
+        <v>5523719.3136377698</v>
       </c>
       <c r="L37" s="63" cm="1">
         <f t="array" ref="L37">+_xlfn.IFS(I37&gt;114%,H37*0.0125,I37&gt;109%,H37*0.01,I37&gt;104%,H37*0.0075,I37&gt;99%,H37*0.005,I37&lt;99%,H37*0)</f>
@@ -5379,34 +5379,34 @@
       </c>
       <c r="D38" s="4">
         <f>IFERROR(+VLOOKUP(B38,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>746511.00490000006</v>
+      </c>
+      <c r="E38" s="4">
         <v>280769.63740000001</v>
-      </c>
-      <c r="E38" s="4">
-        <v>149294.68419999999</v>
       </c>
       <c r="F38" s="4">
         <f t="shared" ref="F38" si="10">+D38-E38</f>
-        <v>131474.95320000002</v>
+        <v>465741.36750000005</v>
       </c>
       <c r="G38" s="5">
         <f t="shared" si="1"/>
-        <v>7.8646957254901971E-3</v>
+        <v>2.0910672406162466E-2</v>
       </c>
       <c r="H38" s="4">
         <f t="shared" si="4"/>
-        <v>1684617.8244</v>
+        <v>3583252.8235200006</v>
       </c>
       <c r="I38" s="5">
         <f t="shared" si="2"/>
-        <v>4.7188174352941176E-2</v>
+        <v>0.10037122754957985</v>
       </c>
       <c r="J38" s="4">
         <f t="shared" si="5"/>
-        <v>70192.409350000002</v>
+        <v>149302.20098000002</v>
       </c>
       <c r="K38" s="4">
         <f t="shared" si="3"/>
-        <v>1770961.51813</v>
+        <v>1839657.3155315788</v>
       </c>
       <c r="L38" s="63" cm="1">
         <f t="array" ref="L38">+_xlfn.IFS(I38&gt;109%,H38*0.015,I38&gt;104%,H38*0.0125,I38&gt;99%,H38*0.01,I38&lt;99%,H38*0)</f>
@@ -5423,38 +5423,38 @@
       </c>
       <c r="D39" s="4">
         <f>IFERROR(+VLOOKUP(B39,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>6953389.0972305397</v>
+      </c>
+      <c r="E39" s="4">
         <v>6167950.3247244535</v>
-      </c>
-      <c r="E39" s="4">
-        <v>4713478.3902184051</v>
       </c>
       <c r="F39" s="4">
         <f t="shared" si="8"/>
-        <v>1454471.9345060484</v>
+        <v>785438.77250608616</v>
       </c>
       <c r="G39" s="5">
         <f t="shared" si="1"/>
-        <v>0.16962893671276072</v>
+        <v>0.19122981493305272</v>
       </c>
       <c r="H39" s="4">
         <f t="shared" si="4"/>
-        <v>37007701.948346719</v>
+        <v>33376267.666706588</v>
       </c>
       <c r="I39" s="5">
         <f t="shared" si="2"/>
-        <v>1.0177736202765644</v>
+        <v>0.91790311167865302</v>
       </c>
       <c r="J39" s="4">
         <f t="shared" si="5"/>
-        <v>1541987.5811811134</v>
+        <v>1390677.8194461078</v>
       </c>
       <c r="K39" s="4">
         <f t="shared" si="3"/>
-        <v>1509673.8707137774</v>
+        <v>1547791.5074615506</v>
       </c>
       <c r="L39" s="63" cm="1">
         <f t="array" ref="L39">+_xlfn.IFS(I39&gt;114%,H39*0.02,I39&gt;109%,H39*0.015,I39&gt;104%,H39*0.0125,I39&gt;99%,H39*0.01,I39&lt;99%,H39*0)</f>
-        <v>370077.01948346721</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -5465,34 +5465,34 @@
       </c>
       <c r="D40" s="67">
         <f>+SUM(D27:D39)</f>
+        <v>71919833.194753855</v>
+      </c>
+      <c r="E40" s="65">
         <v>62899009.881559134</v>
-      </c>
-      <c r="E40" s="65">
-        <v>46151311.382850848</v>
       </c>
       <c r="F40" s="67">
         <f t="shared" si="8"/>
-        <v>16747698.498708285</v>
+        <v>9020823.3131947219</v>
       </c>
       <c r="G40" s="66">
         <f t="shared" si="1"/>
-        <v>0.12356665730358822</v>
+        <v>0.14128828734254617</v>
       </c>
       <c r="H40" s="64">
         <f t="shared" si="4"/>
-        <v>377394059.2893548</v>
+        <v>345215199.33481848</v>
       </c>
       <c r="I40" s="66">
         <f t="shared" si="2"/>
-        <v>0.74139994382152929</v>
+        <v>0.67818377924422157</v>
       </c>
       <c r="J40" s="64">
         <f t="shared" si="5"/>
-        <v>15724752.470389783</v>
+        <v>14383966.638950771</v>
       </c>
       <c r="K40" s="67">
         <f t="shared" si="3"/>
-        <v>22306498.648478329</v>
+        <v>23005744.718756411</v>
       </c>
       <c r="L40" s="68"/>
     </row>
@@ -5506,34 +5506,34 @@
       </c>
       <c r="D41" s="81">
         <f>+D40+D26+D10+D16</f>
+        <v>280805467.60214281</v>
+      </c>
+      <c r="E41" s="82">
         <v>240577000.14348808</v>
-      </c>
-      <c r="E41" s="82">
-        <v>191246594.85709113</v>
       </c>
       <c r="F41" s="81">
         <f>+D41-E41</f>
-        <v>49330405.28639695</v>
+        <v>40228467.458654732</v>
       </c>
       <c r="G41" s="83">
         <f t="shared" si="1"/>
-        <v>0.17436058008072636</v>
+        <v>0.20351656306191793</v>
       </c>
       <c r="H41" s="81">
         <f t="shared" si="4"/>
-        <v>1443462000.8609285</v>
+        <v>1347866244.4902854</v>
       </c>
       <c r="I41" s="83">
         <f t="shared" si="2"/>
-        <v>1.046163480484358</v>
+        <v>0.97687950269720591</v>
       </c>
       <c r="J41" s="81">
         <f t="shared" si="5"/>
-        <v>60144250.03587202</v>
+        <v>56161093.520428561</v>
       </c>
       <c r="K41" s="81">
         <f t="shared" si="3"/>
-        <v>56959507.347482398</v>
+        <v>57840088.394262806</v>
       </c>
       <c r="L41" s="84"/>
     </row>
@@ -5581,34 +5581,34 @@
       </c>
       <c r="D43" s="4">
         <f>IFERROR(+VLOOKUP(B43,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>-275260.76904147147</v>
+        <v>3760393.1741207056</v>
       </c>
       <c r="E43" s="4">
         <v>-275260.76904147147</v>
       </c>
       <c r="F43" s="4">
         <f t="shared" ref="F43" si="11">+D43-E43</f>
-        <v>0</v>
+        <v>4035653.9431621772</v>
       </c>
       <c r="G43" s="5">
         <f>+D43/C43</f>
-        <v>-6.8815192260367865E-3</v>
+        <v>9.4009829353017646E-2</v>
       </c>
       <c r="H43" s="4">
         <f t="shared" ref="H43" si="12">+D43/$N$3*$N$4</f>
-        <v>-1651564.614248829</v>
+        <v>18049887.23577939</v>
       </c>
       <c r="I43" s="5">
         <f>+H43/C43</f>
-        <v>-4.1289115356220721E-2</v>
+        <v>0.45124718089448473</v>
       </c>
       <c r="J43" s="4">
         <f t="shared" ref="J43" si="13">+D43/$N$3</f>
-        <v>-68815.192260367869</v>
+        <v>752078.63482414116</v>
       </c>
       <c r="K43" s="4">
         <f>+(C43-D43)/$N$2</f>
-        <v>2013763.0384520735</v>
+        <v>1907347.7276778575</v>
       </c>
       <c r="L43" s="4" cm="1">
         <f t="array" ref="L43">+_xlfn.IFS(I43&gt;114%,H43*0.02,I43&gt;109%,H43*0.015,I43&gt;104%,H43*0.0125,I43&gt;99%,H43*0.01,I43&lt;99%,H43*0)</f>
@@ -5624,34 +5624,34 @@
       </c>
       <c r="D44" s="4">
         <f>IFERROR(+VLOOKUP(B44,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>-402349.89063324447</v>
+        <v>1913900.6624423866</v>
       </c>
       <c r="E44" s="4">
         <v>-402349.89063324447</v>
       </c>
       <c r="F44" s="4">
         <f t="shared" ref="F44" si="14">+D44-E44</f>
-        <v>0</v>
+        <v>2316250.5530756311</v>
       </c>
       <c r="G44" s="5">
         <f>+D44/C44</f>
-        <v>-1.3411663021108149E-2</v>
+        <v>6.3796688748079561E-2</v>
       </c>
       <c r="H44" s="4">
         <f t="shared" ref="H44" si="15">+D44/$N$3*$N$4</f>
-        <v>-2414099.3437994667</v>
+        <v>9186723.1797234565</v>
       </c>
       <c r="I44" s="5">
         <f>+H44/C44</f>
-        <v>-8.0469978126648897E-2</v>
+        <v>0.30622410599078187</v>
       </c>
       <c r="J44" s="4">
         <f t="shared" ref="J44" si="16">+D44/$N$3</f>
-        <v>-100587.47265831112</v>
+        <v>382780.13248847733</v>
       </c>
       <c r="K44" s="4">
         <f>+(C44-D44)/$N$2</f>
-        <v>1520117.4945316622</v>
+        <v>1478215.7546082954</v>
       </c>
       <c r="L44" s="4" cm="1">
         <f t="array" ref="L44">+_xlfn.IFS(I44&gt;114%,H44*0.02,I44&gt;109%,H44*0.015,I44&gt;104%,H44*0.0125,I44&gt;99%,H44*0.01,I44&lt;99%,H44*0)</f>
@@ -5793,14 +5793,14 @@
       </c>
       <c r="D2" s="22">
         <f>H2/G2</f>
-        <v>0.40277777777777779</v>
+        <v>0.51388888888888884</v>
       </c>
       <c r="E2" s="13">
         <v>33</v>
       </c>
       <c r="F2" s="12">
         <f>+H2-E2</f>
-        <v>-4</v>
+        <v>4</v>
       </c>
       <c r="G2" s="13">
         <f>VLOOKUP(B2,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -5808,11 +5808,11 @@
       </c>
       <c r="H2" s="13">
         <f>VLOOKUP(B2,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="I2" s="17">
         <f>(+G2*$M$2)-H2</f>
-        <v>32.199999999999996</v>
+        <v>24.199999999999996</v>
       </c>
       <c r="J2" t="s">
         <v>55</v>
@@ -5896,14 +5896,14 @@
         <v>145 - ALMACEN</v>
       </c>
       <c r="S3" s="12">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="T3" s="12">
         <v>214</v>
       </c>
       <c r="U3" s="41">
         <f>+S3/T3</f>
-        <v>7.476635514018691E-2</v>
+        <v>8.4112149532710276E-2</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
@@ -5917,14 +5917,14 @@
       </c>
       <c r="D4" s="22">
         <f t="shared" si="0"/>
-        <v>0.42290748898678415</v>
+        <v>0.52422907488986781</v>
       </c>
       <c r="E4" s="13">
         <v>126</v>
       </c>
       <c r="F4" s="12">
         <f t="shared" si="1"/>
-        <v>-30</v>
+        <v>-7</v>
       </c>
       <c r="G4" s="13">
         <f>VLOOKUP(B4,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -5932,11 +5932,11 @@
       </c>
       <c r="H4" s="13">
         <f>VLOOKUP(B4,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="I4" s="17">
         <f t="shared" si="2"/>
-        <v>96.949999999999989</v>
+        <v>73.949999999999989</v>
       </c>
       <c r="J4" t="s">
         <v>57</v>
@@ -5954,14 +5954,14 @@
         <v>145 - Articulos Sin Asociar Agrupacion</v>
       </c>
       <c r="S4" s="13">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T4" s="13">
         <v>214</v>
       </c>
       <c r="U4" s="5">
         <f t="shared" ref="U4:U11" si="3">+S4/T4</f>
-        <v>5.6074766355140186E-2</v>
+        <v>7.0093457943925228E-2</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
@@ -5975,14 +5975,14 @@
       </c>
       <c r="D5" s="22">
         <f t="shared" si="0"/>
-        <v>0.29230769230769232</v>
+        <v>0.41538461538461541</v>
       </c>
       <c r="E5" s="13">
         <v>21</v>
       </c>
       <c r="F5" s="12">
         <f t="shared" si="1"/>
-        <v>-2</v>
+        <v>6</v>
       </c>
       <c r="G5" s="13">
         <f>VLOOKUP(B5,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -5990,11 +5990,11 @@
       </c>
       <c r="H5" s="13">
         <f>VLOOKUP(B5,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="I5" s="17">
         <f t="shared" si="2"/>
-        <v>36.25</v>
+        <v>28.25</v>
       </c>
       <c r="K5" t="s">
         <v>64</v>
@@ -6009,14 +6009,14 @@
         <v>145 - BEBIDAS</v>
       </c>
       <c r="S5" s="13">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="T5" s="13">
         <v>214</v>
       </c>
       <c r="U5" s="5">
         <f t="shared" si="3"/>
-        <v>7.9439252336448593E-2</v>
+        <v>0.13084112149532709</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
@@ -6030,14 +6030,14 @@
       </c>
       <c r="D6" s="22">
         <f t="shared" si="0"/>
-        <v>0.42995169082125606</v>
+        <v>0.50724637681159424</v>
       </c>
       <c r="E6" s="13">
         <v>100</v>
       </c>
       <c r="F6" s="12">
         <f t="shared" si="1"/>
-        <v>-11</v>
+        <v>5</v>
       </c>
       <c r="G6" s="13">
         <f>VLOOKUP(B6,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6045,11 +6045,11 @@
       </c>
       <c r="H6" s="13">
         <f>VLOOKUP(B6,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="I6" s="17">
         <f t="shared" si="2"/>
-        <v>86.949999999999989</v>
+        <v>70.949999999999989</v>
       </c>
       <c r="J6" t="s">
         <v>58</v>
@@ -6067,14 +6067,14 @@
         <v>145 - CHOCOLATE</v>
       </c>
       <c r="S6" s="13">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T6" s="13">
         <v>214</v>
       </c>
       <c r="U6" s="5">
         <f t="shared" si="3"/>
-        <v>5.1401869158878503E-2</v>
+        <v>6.0747663551401869E-2</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
@@ -6088,14 +6088,14 @@
       </c>
       <c r="D7" s="22">
         <f t="shared" si="0"/>
-        <v>0.27777777777777779</v>
+        <v>0.32323232323232326</v>
       </c>
       <c r="E7" s="13">
         <v>81</v>
       </c>
       <c r="F7" s="12">
         <f t="shared" si="1"/>
-        <v>-26</v>
+        <v>-17</v>
       </c>
       <c r="G7" s="13">
         <f>VLOOKUP(B7,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6103,11 +6103,11 @@
       </c>
       <c r="H7" s="13">
         <f>VLOOKUP(B7,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="I7" s="17">
         <f t="shared" si="2"/>
-        <v>113.29999999999998</v>
+        <v>104.29999999999998</v>
       </c>
       <c r="J7" t="s">
         <v>58</v>
@@ -6125,14 +6125,14 @@
         <v>145 - GALLETITAS</v>
       </c>
       <c r="S7" s="13">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="T7" s="13">
         <v>214</v>
       </c>
       <c r="U7" s="5">
         <f t="shared" si="3"/>
-        <v>0.13551401869158877</v>
+        <v>0.17289719626168223</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
@@ -6146,14 +6146,14 @@
       </c>
       <c r="D8" s="22">
         <f t="shared" si="0"/>
-        <v>0.32242990654205606</v>
+        <v>0.43457943925233644</v>
       </c>
       <c r="E8" s="13">
         <v>89</v>
       </c>
       <c r="F8" s="12">
         <f t="shared" si="1"/>
-        <v>-20</v>
+        <v>4</v>
       </c>
       <c r="G8" s="13">
         <f>VLOOKUP(B8,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6161,11 +6161,11 @@
       </c>
       <c r="H8" s="13">
         <f>VLOOKUP(B8,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="I8" s="17">
         <f t="shared" si="2"/>
-        <v>112.9</v>
+        <v>88.9</v>
       </c>
       <c r="J8" t="s">
         <v>55</v>
@@ -6184,14 +6184,14 @@
         <v>145 - GOLOSINAS</v>
       </c>
       <c r="S8" s="13">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="T8" s="13">
         <v>214</v>
       </c>
       <c r="U8" s="5">
         <f t="shared" si="3"/>
-        <v>0.12149532710280374</v>
+        <v>0.1822429906542056</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
@@ -6205,26 +6205,26 @@
       </c>
       <c r="D9" s="22">
         <f>H9/G9</f>
-        <v>0.3592814371257485</v>
+        <v>0.42603550295857989</v>
       </c>
       <c r="E9" s="13">
         <v>92</v>
       </c>
       <c r="F9" s="12">
         <f t="shared" si="1"/>
-        <v>-32</v>
+        <v>-20</v>
       </c>
       <c r="G9" s="13">
         <f>VLOOKUP(B9,'Base Cobertura'!$A:$C,3,FALSE)</f>
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H9" s="13">
         <f>VLOOKUP(B9,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="I9" s="17">
         <f t="shared" si="2"/>
-        <v>81.949999999999989</v>
+        <v>71.650000000000006</v>
       </c>
       <c r="J9" t="s">
         <v>55</v>
@@ -6242,14 +6242,14 @@
         <v>145 - MASCOTAS</v>
       </c>
       <c r="S9" s="13">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T9" s="13">
         <v>214</v>
       </c>
       <c r="U9" s="5">
         <f t="shared" si="3"/>
-        <v>3.2710280373831772E-2</v>
+        <v>4.2056074766355138E-2</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
@@ -6263,14 +6263,14 @@
       </c>
       <c r="D10" s="22">
         <f t="shared" si="0"/>
-        <v>0.28205128205128205</v>
+        <v>0.3487179487179487</v>
       </c>
       <c r="E10" s="13">
         <v>64</v>
       </c>
       <c r="F10" s="12">
         <f t="shared" si="1"/>
-        <v>-9</v>
+        <v>4</v>
       </c>
       <c r="G10" s="13">
         <f>VLOOKUP(B10,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6278,11 +6278,11 @@
       </c>
       <c r="H10" s="13">
         <f>VLOOKUP(B10,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="I10" s="17">
         <f t="shared" si="2"/>
-        <v>110.75</v>
+        <v>97.75</v>
       </c>
       <c r="J10" t="s">
         <v>58</v>
@@ -6300,14 +6300,14 @@
         <v>145 - NO PERECEDEROS</v>
       </c>
       <c r="S10" s="13">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T10" s="13">
         <v>214</v>
       </c>
       <c r="U10" s="5">
         <f t="shared" si="3"/>
-        <v>1.4018691588785047E-2</v>
+        <v>2.336448598130841E-2</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
@@ -6321,14 +6321,14 @@
       </c>
       <c r="D11" s="32">
         <f t="shared" si="0"/>
-        <v>0.13861386138613863</v>
+        <v>0.16831683168316833</v>
       </c>
       <c r="E11" s="31">
         <v>19</v>
       </c>
       <c r="F11" s="33">
         <f t="shared" si="1"/>
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="G11" s="13">
         <f>VLOOKUP(B11,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6336,11 +6336,11 @@
       </c>
       <c r="H11" s="13">
         <f>VLOOKUP(B11,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I11" s="34">
         <f t="shared" si="2"/>
-        <v>71.849999999999994</v>
+        <v>68.849999999999994</v>
       </c>
       <c r="J11" t="s">
         <v>59</v>
@@ -6355,14 +6355,14 @@
         <v>145 - PILAS</v>
       </c>
       <c r="S11" s="13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T11" s="13">
         <v>214</v>
       </c>
       <c r="U11" s="5">
         <f t="shared" si="3"/>
-        <v>1.8691588785046728E-2</v>
+        <v>2.336448598130841E-2</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
@@ -6376,14 +6376,14 @@
       </c>
       <c r="D12" s="32">
         <f t="shared" si="0"/>
-        <v>0.13333333333333333</v>
+        <v>0.19047619047619047</v>
       </c>
       <c r="E12" s="31">
         <v>24</v>
       </c>
       <c r="F12" s="33">
         <f t="shared" si="1"/>
-        <v>-10</v>
+        <v>-4</v>
       </c>
       <c r="G12" s="13">
         <f>VLOOKUP(B12,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6391,11 +6391,11 @@
       </c>
       <c r="H12" s="13">
         <f>VLOOKUP(B12,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I12" s="34">
         <f t="shared" si="2"/>
-        <v>75.25</v>
+        <v>69.25</v>
       </c>
       <c r="J12" t="s">
         <v>59</v>
@@ -6412,14 +6412,14 @@
       </c>
       <c r="D13" s="22">
         <f t="shared" si="0"/>
-        <v>0.35</v>
+        <v>0.41153846153846152</v>
       </c>
       <c r="E13" s="13">
         <v>144</v>
       </c>
       <c r="F13" s="12">
         <f t="shared" si="1"/>
-        <v>-53</v>
+        <v>-37</v>
       </c>
       <c r="G13" s="13">
         <f>VLOOKUP(B13,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6427,11 +6427,11 @@
       </c>
       <c r="H13" s="13">
         <f>VLOOKUP(B13,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="I13" s="17">
         <f t="shared" si="2"/>
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="J13" t="s">
         <v>57</v>
@@ -6451,14 +6451,14 @@
       </c>
       <c r="D14" s="22">
         <f t="shared" si="0"/>
-        <v>0.31868131868131866</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="E14" s="13">
         <v>85</v>
       </c>
       <c r="F14" s="12">
         <f t="shared" si="1"/>
-        <v>-27</v>
+        <v>-15</v>
       </c>
       <c r="G14" s="13">
         <f>VLOOKUP(B14,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6466,11 +6466,11 @@
       </c>
       <c r="H14" s="13">
         <f>VLOOKUP(B14,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="I14" s="17">
         <f t="shared" si="2"/>
-        <v>96.699999999999989</v>
+        <v>84.699999999999989</v>
       </c>
       <c r="J14" t="s">
         <v>55</v>
@@ -6486,15 +6486,15 @@
       <c r="E15" s="14"/>
       <c r="F15" s="16">
         <f>+SUM(F2:F14)</f>
-        <v>-177</v>
+        <v>-27</v>
       </c>
       <c r="G15" s="8">
         <f>+SUM(G2:G14)</f>
-        <v>2232</v>
+        <v>2234</v>
       </c>
       <c r="H15" s="8">
         <f>+SUM(H2:H14)</f>
-        <v>702</v>
+        <v>852</v>
       </c>
       <c r="I15" s="8"/>
     </row>
@@ -6511,14 +6511,14 @@
       </c>
       <c r="D16" s="22">
         <f t="shared" si="0"/>
-        <v>0.40993788819875776</v>
+        <v>0.49689440993788819</v>
       </c>
       <c r="E16" s="13">
         <v>90</v>
       </c>
       <c r="F16" s="12">
         <f t="shared" si="1"/>
-        <v>-24</v>
+        <v>-10</v>
       </c>
       <c r="G16" s="13">
         <f>VLOOKUP(B16,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6526,11 +6526,11 @@
       </c>
       <c r="H16" s="13">
         <f>VLOOKUP(B16,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="I16" s="17">
         <f t="shared" si="2"/>
-        <v>70.849999999999994</v>
+        <v>56.849999999999994</v>
       </c>
       <c r="J16" t="s">
         <v>55</v>
@@ -6550,14 +6550,14 @@
       </c>
       <c r="D17" s="22">
         <f t="shared" si="0"/>
-        <v>0.28712871287128711</v>
+        <v>0.33663366336633666</v>
       </c>
       <c r="E17" s="13">
         <v>92</v>
       </c>
       <c r="F17" s="12">
         <f t="shared" si="1"/>
-        <v>-34</v>
+        <v>-24</v>
       </c>
       <c r="G17" s="13">
         <f>VLOOKUP(B17,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6565,11 +6565,11 @@
       </c>
       <c r="H17" s="13">
         <f>VLOOKUP(B17,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="I17" s="17">
         <f t="shared" si="2"/>
-        <v>113.69999999999999</v>
+        <v>103.69999999999999</v>
       </c>
       <c r="J17" t="s">
         <v>55</v>
@@ -6589,14 +6589,14 @@
       </c>
       <c r="D18" s="22">
         <f t="shared" si="0"/>
-        <v>0.44117647058823528</v>
+        <v>0.53529411764705881</v>
       </c>
       <c r="E18" s="13">
         <v>88</v>
       </c>
       <c r="F18" s="12">
         <f t="shared" si="1"/>
-        <v>-13</v>
+        <v>3</v>
       </c>
       <c r="G18" s="13">
         <f>VLOOKUP(B18,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6604,11 +6604,11 @@
       </c>
       <c r="H18" s="13">
         <f>VLOOKUP(B18,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="I18" s="17">
         <f t="shared" si="2"/>
-        <v>69.5</v>
+        <v>53.5</v>
       </c>
       <c r="J18" t="s">
         <v>58</v>
@@ -6628,14 +6628,14 @@
       </c>
       <c r="D19" s="22">
         <f t="shared" si="0"/>
-        <v>0.51249999999999996</v>
+        <v>0.55625000000000002</v>
       </c>
       <c r="E19" s="13">
         <v>95</v>
       </c>
       <c r="F19" s="12">
         <f t="shared" si="1"/>
-        <v>-13</v>
+        <v>-6</v>
       </c>
       <c r="G19" s="13">
         <f>VLOOKUP(B19,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6643,11 +6643,11 @@
       </c>
       <c r="H19" s="13">
         <f>VLOOKUP(B19,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="I19" s="17">
         <f t="shared" si="2"/>
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="J19" t="s">
         <v>58</v>
@@ -6667,14 +6667,14 @@
       </c>
       <c r="D20" s="22">
         <f t="shared" si="0"/>
-        <v>0.43502824858757061</v>
+        <v>0.50847457627118642</v>
       </c>
       <c r="E20" s="13">
         <v>83</v>
       </c>
       <c r="F20" s="12">
         <f t="shared" si="1"/>
-        <v>-6</v>
+        <v>7</v>
       </c>
       <c r="G20" s="13">
         <f>VLOOKUP(B20,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6682,11 +6682,11 @@
       </c>
       <c r="H20" s="13">
         <f>VLOOKUP(B20,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="I20" s="17">
         <f t="shared" si="2"/>
-        <v>73.449999999999989</v>
+        <v>60.449999999999989</v>
       </c>
       <c r="J20" t="s">
         <v>55</v>
@@ -6706,14 +6706,14 @@
       </c>
       <c r="D21" s="22">
         <f t="shared" si="0"/>
-        <v>0.42011834319526625</v>
+        <v>0.47928994082840237</v>
       </c>
       <c r="E21" s="13">
         <v>64</v>
       </c>
       <c r="F21" s="12">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G21" s="13">
         <f>VLOOKUP(B21,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6721,11 +6721,11 @@
       </c>
       <c r="H21" s="13">
         <f>VLOOKUP(B21,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="I21" s="17">
         <f t="shared" si="2"/>
-        <v>72.650000000000006</v>
+        <v>62.650000000000006</v>
       </c>
       <c r="J21" t="s">
         <v>58</v>
@@ -6784,14 +6784,14 @@
       </c>
       <c r="D23" s="22">
         <f t="shared" si="0"/>
-        <v>0.39130434782608697</v>
+        <v>0.43478260869565216</v>
       </c>
       <c r="E23" s="13">
         <v>70</v>
       </c>
       <c r="F23" s="12">
         <f t="shared" si="1"/>
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="G23" s="13">
         <f>VLOOKUP(B23,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6799,11 +6799,11 @@
       </c>
       <c r="H23" s="13">
         <f>VLOOKUP(B23,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="I23" s="17">
         <f t="shared" si="2"/>
-        <v>63.3</v>
+        <v>57.3</v>
       </c>
       <c r="J23" t="s">
         <v>58</v>
@@ -6823,14 +6823,14 @@
       </c>
       <c r="D24" s="22">
         <f t="shared" si="0"/>
-        <v>0.41764705882352943</v>
+        <v>0.48823529411764705</v>
       </c>
       <c r="E24" s="13">
         <v>79</v>
       </c>
       <c r="F24" s="12">
         <f t="shared" si="1"/>
-        <v>-8</v>
+        <v>4</v>
       </c>
       <c r="G24" s="13">
         <f>VLOOKUP(B24,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6838,11 +6838,11 @@
       </c>
       <c r="H24" s="13">
         <f>VLOOKUP(B24,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="I24" s="17">
         <f t="shared" si="2"/>
-        <v>73.5</v>
+        <v>61.5</v>
       </c>
       <c r="J24" t="s">
         <v>60</v>
@@ -6858,7 +6858,7 @@
       <c r="E25" s="14"/>
       <c r="F25" s="16">
         <f>+SUM(F16:F24)</f>
-        <v>-132</v>
+        <v>-44</v>
       </c>
       <c r="G25" s="8">
         <f>+SUM(G16:G24)</f>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="H25" s="8">
         <f>+SUM(H16:H24)</f>
-        <v>595</v>
+        <v>683</v>
       </c>
       <c r="I25" s="8"/>
     </row>
@@ -6883,14 +6883,14 @@
       </c>
       <c r="D26" s="22">
         <f t="shared" si="0"/>
-        <v>0.23214285714285715</v>
+        <v>0.30357142857142855</v>
       </c>
       <c r="E26" s="13">
         <v>20</v>
       </c>
       <c r="F26" s="12">
         <f>+H26-E26</f>
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="G26" s="13">
         <f>VLOOKUP(B26,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6898,11 +6898,11 @@
       </c>
       <c r="H26" s="13">
         <f>VLOOKUP(B26,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I26" s="17">
         <f t="shared" si="2"/>
-        <v>34.6</v>
+        <v>30.6</v>
       </c>
       <c r="J26" t="s">
         <v>55</v>
@@ -6922,14 +6922,14 @@
       </c>
       <c r="D27" s="22">
         <f t="shared" si="0"/>
-        <v>0.35256410256410259</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="E27" s="13">
         <v>68</v>
       </c>
       <c r="F27" s="12">
         <f t="shared" si="1"/>
-        <v>-13</v>
+        <v>-3</v>
       </c>
       <c r="G27" s="13">
         <f>VLOOKUP(B27,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6937,11 +6937,11 @@
       </c>
       <c r="H27" s="13">
         <f>VLOOKUP(B27,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="I27" s="17">
         <f t="shared" si="2"/>
-        <v>77.599999999999994</v>
+        <v>67.599999999999994</v>
       </c>
       <c r="J27" t="s">
         <v>58</v>
@@ -6961,14 +6961,14 @@
       </c>
       <c r="D28" s="22">
         <f t="shared" si="0"/>
-        <v>0.29813664596273293</v>
+        <v>0.36645962732919257</v>
       </c>
       <c r="E28" s="13">
         <v>80</v>
       </c>
       <c r="F28" s="12">
         <f t="shared" si="1"/>
-        <v>-32</v>
+        <v>-21</v>
       </c>
       <c r="G28" s="13">
         <f>VLOOKUP(B28,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6976,11 +6976,11 @@
       </c>
       <c r="H28" s="13">
         <f>VLOOKUP(B28,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="I28" s="17">
         <f t="shared" si="2"/>
-        <v>88.85</v>
+        <v>77.849999999999994</v>
       </c>
       <c r="J28" t="s">
         <v>58</v>
@@ -7000,14 +7000,14 @@
       </c>
       <c r="D29" s="22">
         <f t="shared" si="0"/>
-        <v>0.1606425702811245</v>
+        <v>0.20481927710843373</v>
       </c>
       <c r="E29" s="13">
         <v>68</v>
       </c>
       <c r="F29" s="12">
         <f t="shared" si="1"/>
-        <v>-28</v>
+        <v>-17</v>
       </c>
       <c r="G29" s="13">
         <f>VLOOKUP(B29,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7015,11 +7015,11 @@
       </c>
       <c r="H29" s="13">
         <f>VLOOKUP(B29,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="I29" s="17">
         <f t="shared" si="2"/>
-        <v>171.65</v>
+        <v>160.65</v>
       </c>
       <c r="J29" t="s">
         <v>58</v>
@@ -7039,14 +7039,14 @@
       </c>
       <c r="D30" s="22">
         <f t="shared" si="0"/>
-        <v>0.42857142857142855</v>
+        <v>0.51428571428571423</v>
       </c>
       <c r="E30" s="13">
         <v>73</v>
       </c>
       <c r="F30" s="12">
         <f t="shared" si="1"/>
-        <v>-13</v>
+        <v>-1</v>
       </c>
       <c r="G30" s="13">
         <f>VLOOKUP(B30,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7054,11 +7054,11 @@
       </c>
       <c r="H30" s="13">
         <f>VLOOKUP(B30,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="I30" s="17">
         <f t="shared" si="2"/>
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="J30" t="s">
         <v>55</v>
@@ -7078,14 +7078,14 @@
       </c>
       <c r="D31" s="22">
         <f t="shared" si="0"/>
-        <v>0.25966850828729282</v>
+        <v>0.2983425414364641</v>
       </c>
       <c r="E31" s="13">
         <v>40</v>
       </c>
       <c r="F31" s="12">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G31" s="13">
         <f>VLOOKUP(B31,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7093,11 +7093,11 @@
       </c>
       <c r="H31" s="13">
         <f>VLOOKUP(B31,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="I31" s="17">
         <f t="shared" si="2"/>
-        <v>106.85</v>
+        <v>99.85</v>
       </c>
       <c r="J31" t="s">
         <v>58</v>
@@ -7117,14 +7117,14 @@
       </c>
       <c r="D32" s="22">
         <f t="shared" si="0"/>
-        <v>0.30357142857142855</v>
+        <v>0.35119047619047616</v>
       </c>
       <c r="E32" s="13">
         <v>67</v>
       </c>
       <c r="F32" s="12">
         <f t="shared" si="1"/>
-        <v>-16</v>
+        <v>-8</v>
       </c>
       <c r="G32" s="13">
         <f>VLOOKUP(B32,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7132,11 +7132,11 @@
       </c>
       <c r="H32" s="13">
         <f>VLOOKUP(B32,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="I32" s="17">
         <f t="shared" si="2"/>
-        <v>91.799999999999983</v>
+        <v>83.799999999999983</v>
       </c>
       <c r="J32" t="s">
         <v>58</v>
@@ -7156,14 +7156,14 @@
       </c>
       <c r="D33" s="22">
         <f t="shared" si="0"/>
-        <v>0.34883720930232559</v>
+        <v>0.39534883720930231</v>
       </c>
       <c r="E33" s="13">
         <v>66</v>
       </c>
       <c r="F33" s="12">
         <f t="shared" si="1"/>
-        <v>-6</v>
+        <v>2</v>
       </c>
       <c r="G33" s="13">
         <f>VLOOKUP(B33,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7171,11 +7171,11 @@
       </c>
       <c r="H33" s="13">
         <f>VLOOKUP(B33,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="I33" s="17">
         <f t="shared" si="2"/>
-        <v>86.199999999999989</v>
+        <v>78.199999999999989</v>
       </c>
       <c r="J33" t="s">
         <v>58</v>
@@ -7195,14 +7195,14 @@
       </c>
       <c r="D34" s="22">
         <f t="shared" si="0"/>
-        <v>0.14788732394366197</v>
+        <v>0.19718309859154928</v>
       </c>
       <c r="E34" s="13">
         <v>82</v>
       </c>
       <c r="F34" s="12">
         <f t="shared" si="1"/>
-        <v>-61</v>
+        <v>-54</v>
       </c>
       <c r="G34" s="13">
         <f>VLOOKUP(B34,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7210,11 +7210,11 @@
       </c>
       <c r="H34" s="13">
         <f>VLOOKUP(B34,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="I34" s="17">
         <f t="shared" si="2"/>
-        <v>99.7</v>
+        <v>92.7</v>
       </c>
       <c r="J34" t="s">
         <v>55</v>
@@ -7234,14 +7234,14 @@
       </c>
       <c r="D35" s="22">
         <f t="shared" si="0"/>
-        <v>0.2808988764044944</v>
+        <v>0.398876404494382</v>
       </c>
       <c r="E35" s="13">
         <v>81</v>
       </c>
       <c r="F35" s="12">
         <f t="shared" si="1"/>
-        <v>-31</v>
+        <v>-10</v>
       </c>
       <c r="G35" s="13">
         <f>VLOOKUP(B35,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7249,11 +7249,11 @@
       </c>
       <c r="H35" s="13">
         <f>VLOOKUP(B35,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="I35" s="17">
         <f t="shared" si="2"/>
-        <v>101.29999999999998</v>
+        <v>80.299999999999983</v>
       </c>
       <c r="J35" t="s">
         <v>58</v>
@@ -7273,14 +7273,14 @@
       </c>
       <c r="D36" s="22">
         <f t="shared" si="0"/>
-        <v>8.8495575221238937E-3</v>
+        <v>2.6548672566371681E-2</v>
       </c>
       <c r="E36" s="13">
         <v>0</v>
       </c>
       <c r="F36" s="12">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G36" s="13">
         <f>VLOOKUP(B36,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7288,11 +7288,11 @@
       </c>
       <c r="H36" s="13">
         <f>VLOOKUP(B36,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I36" s="17">
         <f t="shared" si="2"/>
-        <v>95.05</v>
+        <v>93.05</v>
       </c>
       <c r="J36" t="s">
         <v>58</v>
@@ -7309,26 +7309,26 @@
       </c>
       <c r="D37" s="22">
         <f t="shared" si="0"/>
-        <v>1.9417475728155338E-2</v>
+        <v>3.8461538461538464E-2</v>
       </c>
       <c r="E37" s="13">
         <v>17</v>
       </c>
       <c r="F37" s="12">
         <f t="shared" si="1"/>
-        <v>-15</v>
+        <v>-13</v>
       </c>
       <c r="G37" s="13">
         <f>VLOOKUP(B37,'Base Cobertura'!$A:$C,3,FALSE)</f>
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H37" s="13">
         <f>VLOOKUP(B37,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I37" s="17">
         <f t="shared" si="2"/>
-        <v>85.55</v>
+        <v>84.399999999999991</v>
       </c>
       <c r="J37" t="s">
         <v>59</v>
@@ -7345,14 +7345,14 @@
       </c>
       <c r="D38" s="22">
         <f t="shared" si="0"/>
-        <v>0.40157480314960631</v>
+        <v>0.47244094488188976</v>
       </c>
       <c r="E38" s="13">
         <v>60</v>
       </c>
       <c r="F38" s="12">
         <f t="shared" si="1"/>
-        <v>-9</v>
+        <v>0</v>
       </c>
       <c r="G38" s="13">
         <f>VLOOKUP(B38,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7360,11 +7360,11 @@
       </c>
       <c r="H38" s="13">
         <f>VLOOKUP(B38,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="I38" s="17">
         <f t="shared" si="2"/>
-        <v>56.95</v>
+        <v>47.95</v>
       </c>
       <c r="J38" t="s">
         <v>55</v>
@@ -7380,15 +7380,15 @@
       <c r="E39" s="14"/>
       <c r="F39" s="8">
         <f>+SUM(F26:F38)</f>
-        <v>-223</v>
+        <v>-111</v>
       </c>
       <c r="G39" s="8">
         <f>+SUM(G26:G38)</f>
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="H39" s="8">
         <f>+SUM(H26:H38)</f>
-        <v>499</v>
+        <v>611</v>
       </c>
       <c r="I39" s="8"/>
       <c r="L39" t="s">
@@ -7404,20 +7404,20 @@
       <c r="E40" s="6"/>
       <c r="F40" s="8">
         <f>+SUM(F39+F25+F15)</f>
-        <v>-532</v>
+        <v>-182</v>
       </c>
       <c r="G40" s="8">
         <f>+G15+G25+G39</f>
-        <v>5723</v>
+        <v>5726</v>
       </c>
       <c r="H40" s="8">
         <f>+H15+H25+H39</f>
-        <v>1796</v>
+        <v>2146</v>
       </c>
       <c r="I40" s="8"/>
       <c r="L40" s="1">
         <f>+H40/G40</f>
-        <v>0.31382142233094529</v>
+        <v>0.37478169752008383</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
@@ -7462,7 +7462,7 @@
       </c>
       <c r="D42" s="22">
         <f t="shared" si="4"/>
-        <v>8.4033613445378148E-3</v>
+        <v>8.3333333333333332E-3</v>
       </c>
       <c r="E42" s="13">
         <v>60</v>
@@ -7473,7 +7473,7 @@
       </c>
       <c r="G42" s="13">
         <f>VLOOKUP(B42,'Base Cobertura'!$A:$C,3,FALSE)</f>
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H42" s="13">
         <f>VLOOKUP(B42,'Base Cobertura'!$A:$C,2,FALSE)</f>
@@ -7481,7 +7481,7 @@
       </c>
       <c r="I42" s="17">
         <f t="shared" si="6"/>
-        <v>100.14999999999999</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -8075,7 +8075,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="51">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C4" s="51">
         <v>127</v>
@@ -8095,7 +8095,7 @@
         <v>10</v>
       </c>
       <c r="B5" s="51">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C5" s="51">
         <v>181</v>
@@ -8113,10 +8113,10 @@
         <v>100</v>
       </c>
       <c r="B6" s="51">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C6" s="51">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G6" t="s">
         <v>225</v>
@@ -8131,10 +8131,10 @@
         <v>11</v>
       </c>
       <c r="B7" s="51">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="C7" s="51">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G7" t="s">
         <v>226</v>
@@ -8151,7 +8151,7 @@
         <v>12</v>
       </c>
       <c r="B8" s="51">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="C8" s="51">
         <v>214</v>
@@ -8171,7 +8171,7 @@
         <v>123</v>
       </c>
       <c r="B9" s="51">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C9" s="51">
         <v>489</v>
@@ -8191,7 +8191,7 @@
         <v>15</v>
       </c>
       <c r="B10" s="51">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C10" s="51">
         <v>65</v>
@@ -8211,7 +8211,7 @@
         <v>16</v>
       </c>
       <c r="B11" s="51">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="C11" s="51">
         <v>198</v>
@@ -8229,7 +8229,7 @@
         <v>18</v>
       </c>
       <c r="B12" s="51">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="C12" s="51">
         <v>177</v>
@@ -8245,7 +8245,7 @@
         <v>222</v>
       </c>
       <c r="H12">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="I12" s="51">
         <v>127</v>
@@ -8256,7 +8256,7 @@
         <v>19</v>
       </c>
       <c r="B13" s="51">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="C13" s="51">
         <v>207</v>
@@ -8269,7 +8269,7 @@
         <v>223</v>
       </c>
       <c r="H13" s="51">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I13" s="51">
         <v>127</v>
@@ -8280,7 +8280,7 @@
         <v>2</v>
       </c>
       <c r="B14" s="51">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C14" s="51">
         <v>138</v>
@@ -8293,7 +8293,7 @@
         <v>224</v>
       </c>
       <c r="H14" s="51">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I14" s="51">
         <v>127</v>
@@ -8304,7 +8304,7 @@
         <v>20</v>
       </c>
       <c r="B15" s="51">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="C15" s="51">
         <v>227</v>
@@ -8317,7 +8317,7 @@
         <v>225</v>
       </c>
       <c r="H15" s="51">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I15" s="51">
         <v>127</v>
@@ -8328,7 +8328,7 @@
         <v>21</v>
       </c>
       <c r="B16" s="51">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="C16" s="51">
         <v>170</v>
@@ -8341,7 +8341,7 @@
         <v>226</v>
       </c>
       <c r="H16" s="51">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="I16" s="51">
         <v>127</v>
@@ -8352,7 +8352,7 @@
         <v>22</v>
       </c>
       <c r="B17" s="51">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C17" s="51">
         <v>72</v>
@@ -8365,7 +8365,7 @@
         <v>227</v>
       </c>
       <c r="H17" s="51">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="I17" s="51">
         <v>127</v>
@@ -8376,7 +8376,7 @@
         <v>23</v>
       </c>
       <c r="B18" s="51">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C18" s="51">
         <v>160</v>
@@ -8389,7 +8389,7 @@
         <v>228</v>
       </c>
       <c r="H18" s="51">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I18" s="51">
         <v>127</v>
@@ -8400,7 +8400,7 @@
         <v>24</v>
       </c>
       <c r="B19" s="51">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="C19" s="51">
         <v>178</v>
@@ -8413,7 +8413,7 @@
         <v>229</v>
       </c>
       <c r="H19" s="51">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I19" s="51">
         <v>127</v>
@@ -8424,7 +8424,7 @@
         <v>25</v>
       </c>
       <c r="B20" s="51">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="C20" s="51">
         <v>172</v>
@@ -8437,7 +8437,7 @@
         <v>230</v>
       </c>
       <c r="H20">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I20" s="51">
         <v>127</v>
@@ -8451,7 +8451,7 @@
         <v>31</v>
       </c>
       <c r="C21" s="51">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E21">
         <f>+$F$21</f>
@@ -8475,7 +8475,7 @@
         <v>27</v>
       </c>
       <c r="B22" s="51">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="C22" s="51">
         <v>140</v>
@@ -8487,7 +8487,9 @@
       <c r="G22" t="s">
         <v>223</v>
       </c>
-      <c r="H22" s="51"/>
+      <c r="H22" s="51">
+        <v>1</v>
+      </c>
       <c r="I22" s="51">
         <v>181</v>
       </c>
@@ -8497,7 +8499,7 @@
         <v>28</v>
       </c>
       <c r="B23" s="51">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="C23" s="51">
         <v>168</v>
@@ -8510,7 +8512,7 @@
         <v>224</v>
       </c>
       <c r="H23" s="51">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I23" s="51">
         <v>181</v>
@@ -8521,7 +8523,7 @@
         <v>3</v>
       </c>
       <c r="B24" s="51">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="C24" s="51">
         <v>170</v>
@@ -8534,7 +8536,7 @@
         <v>225</v>
       </c>
       <c r="H24" s="51">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I24" s="51">
         <v>181</v>
@@ -8545,10 +8547,10 @@
         <v>30</v>
       </c>
       <c r="B25" s="51">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C25" s="51">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E25">
         <f t="shared" si="1"/>
@@ -8558,7 +8560,7 @@
         <v>226</v>
       </c>
       <c r="H25" s="51">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I25" s="51">
         <v>181</v>
@@ -8569,7 +8571,7 @@
         <v>31</v>
       </c>
       <c r="B26" s="51">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="C26" s="51">
         <v>161</v>
@@ -8582,7 +8584,7 @@
         <v>227</v>
       </c>
       <c r="H26" s="51">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I26" s="51">
         <v>181</v>
@@ -8593,7 +8595,7 @@
         <v>32</v>
       </c>
       <c r="B27" s="51">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C27" s="51">
         <v>56</v>
@@ -8617,7 +8619,7 @@
         <v>33</v>
       </c>
       <c r="B28" s="51">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="C28" s="51">
         <v>172</v>
@@ -8630,7 +8632,7 @@
         <v>229</v>
       </c>
       <c r="H28" s="51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I28" s="51">
         <v>181</v>
@@ -8641,7 +8643,7 @@
         <v>36</v>
       </c>
       <c r="B29" s="51">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="C29" s="51">
         <v>156</v>
@@ -8665,7 +8667,7 @@
         <v>37</v>
       </c>
       <c r="B30" s="51">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="C30" s="51">
         <v>142</v>
@@ -8681,10 +8683,10 @@
         <v>222</v>
       </c>
       <c r="H30" s="51">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I30" s="51">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
@@ -8692,7 +8694,7 @@
         <v>4</v>
       </c>
       <c r="B31" s="51">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="C31" s="51">
         <v>182</v>
@@ -8705,10 +8707,10 @@
         <v>223</v>
       </c>
       <c r="H31" s="51">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I31" s="51">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
@@ -8716,7 +8718,7 @@
         <v>40</v>
       </c>
       <c r="B32" s="51">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="C32" s="51">
         <v>249</v>
@@ -8729,17 +8731,19 @@
         <v>224</v>
       </c>
       <c r="H32" s="51">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I32" s="51">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>42</v>
       </c>
-      <c r="B33" s="51"/>
+      <c r="B33" s="51">
+        <v>4</v>
+      </c>
       <c r="C33" s="51">
         <v>52</v>
       </c>
@@ -8751,10 +8755,10 @@
         <v>225</v>
       </c>
       <c r="H33" s="51">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I33" s="51">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
@@ -8773,10 +8777,10 @@
         <v>226</v>
       </c>
       <c r="H34" s="51">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I34" s="51">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
@@ -8784,7 +8788,7 @@
         <v>44</v>
       </c>
       <c r="B35" s="51">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="C35" s="51">
         <v>169</v>
@@ -8797,10 +8801,10 @@
         <v>227</v>
       </c>
       <c r="H35" s="51">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I35" s="51">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
@@ -8821,10 +8825,10 @@
         <v>228</v>
       </c>
       <c r="H36" s="51">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I36" s="51">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
@@ -8832,7 +8836,7 @@
         <v>5</v>
       </c>
       <c r="B37" s="51">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="C37" s="51">
         <v>260</v>
@@ -8845,10 +8849,10 @@
         <v>229</v>
       </c>
       <c r="H37" s="51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I37" s="51">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
@@ -8856,7 +8860,7 @@
         <v>52</v>
       </c>
       <c r="B38" s="51">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C38" s="51">
         <v>101</v>
@@ -8870,7 +8874,7 @@
       </c>
       <c r="H38" s="51"/>
       <c r="I38" s="51">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
@@ -8878,7 +8882,7 @@
         <v>53</v>
       </c>
       <c r="B39" s="51">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C39" s="51">
         <v>105</v>
@@ -8897,7 +8901,7 @@
         <v>8</v>
       </c>
       <c r="I39" s="51">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
@@ -8905,7 +8909,7 @@
         <v>54</v>
       </c>
       <c r="B40" s="51">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C40" s="51">
         <v>202</v>
@@ -8918,10 +8922,10 @@
         <v>223</v>
       </c>
       <c r="H40" s="51">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I40" s="51">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
@@ -8942,10 +8946,10 @@
         <v>224</v>
       </c>
       <c r="H41" s="51">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I41" s="51">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
@@ -8953,10 +8957,10 @@
         <v>57</v>
       </c>
       <c r="B42" s="51">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C42" s="51">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E42">
         <f t="shared" si="3"/>
@@ -8966,10 +8970,10 @@
         <v>225</v>
       </c>
       <c r="H42" s="51">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I42" s="51">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
@@ -8988,10 +8992,10 @@
         <v>226</v>
       </c>
       <c r="H43" s="51">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I43" s="51">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
@@ -9002,7 +9006,7 @@
         <v>1</v>
       </c>
       <c r="C44" s="51">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E44">
         <f t="shared" si="3"/>
@@ -9012,10 +9016,10 @@
         <v>227</v>
       </c>
       <c r="H44" s="51">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="I44" s="51">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
@@ -9023,7 +9027,7 @@
         <v>7</v>
       </c>
       <c r="B45" s="51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C45" s="51">
         <v>113</v>
@@ -9036,10 +9040,10 @@
         <v>228</v>
       </c>
       <c r="H45" s="51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I45" s="51">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
@@ -9047,7 +9051,7 @@
         <v>8</v>
       </c>
       <c r="B46" s="51">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="C46" s="51">
         <v>195</v>
@@ -9060,10 +9064,10 @@
         <v>229</v>
       </c>
       <c r="H46" s="51">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I46" s="51">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
@@ -9071,7 +9075,7 @@
         <v>9</v>
       </c>
       <c r="B47" s="51">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="C47" s="51">
         <v>161</v>
@@ -9087,7 +9091,7 @@
         <v>5</v>
       </c>
       <c r="I47" s="51">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
@@ -9104,7 +9108,7 @@
         <v>222</v>
       </c>
       <c r="H48" s="51">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I48" s="51">
         <v>214</v>
@@ -9121,7 +9125,7 @@
         <v>223</v>
       </c>
       <c r="H49" s="51">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I49" s="51">
         <v>214</v>
@@ -9136,7 +9140,7 @@
         <v>224</v>
       </c>
       <c r="H50" s="51">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="I50" s="51">
         <v>214</v>
@@ -9151,7 +9155,7 @@
         <v>225</v>
       </c>
       <c r="H51" s="51">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I51" s="51">
         <v>214</v>
@@ -9166,7 +9170,7 @@
         <v>226</v>
       </c>
       <c r="H52" s="51">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="I52" s="51">
         <v>214</v>
@@ -9181,7 +9185,7 @@
         <v>227</v>
       </c>
       <c r="H53" s="51">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="I53" s="51">
         <v>214</v>
@@ -9196,7 +9200,7 @@
         <v>228</v>
       </c>
       <c r="H54" s="51">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I54" s="51">
         <v>214</v>
@@ -9211,7 +9215,7 @@
         <v>229</v>
       </c>
       <c r="H55" s="51">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I55" s="51">
         <v>214</v>
@@ -9226,7 +9230,7 @@
         <v>230</v>
       </c>
       <c r="H56" s="51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I56" s="51">
         <v>214</v>
@@ -9244,7 +9248,7 @@
         <v>222</v>
       </c>
       <c r="H57" s="51">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I57" s="51">
         <v>489</v>
@@ -9259,7 +9263,7 @@
         <v>223</v>
       </c>
       <c r="H58" s="51">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I58" s="51">
         <v>489</v>
@@ -9274,7 +9278,7 @@
         <v>224</v>
       </c>
       <c r="H59" s="51">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I59" s="51">
         <v>489</v>
@@ -9288,7 +9292,9 @@
       <c r="G60" t="s">
         <v>225</v>
       </c>
-      <c r="H60" s="51"/>
+      <c r="H60" s="51">
+        <v>1</v>
+      </c>
       <c r="I60" s="51">
         <v>489</v>
       </c>
@@ -9302,7 +9308,7 @@
         <v>226</v>
       </c>
       <c r="H61" s="51">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I61" s="51">
         <v>489</v>
@@ -9330,7 +9336,7 @@
         <v>228</v>
       </c>
       <c r="H63" s="51">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I63" s="51">
         <v>489</v>
@@ -9345,7 +9351,7 @@
         <v>229</v>
       </c>
       <c r="H64" s="51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I64" s="51">
         <v>489</v>
@@ -9376,7 +9382,7 @@
         <v>222</v>
       </c>
       <c r="H66" s="51">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I66" s="51">
         <v>65</v>
@@ -9391,7 +9397,7 @@
         <v>223</v>
       </c>
       <c r="H67" s="51">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I67" s="51">
         <v>65</v>
@@ -9406,7 +9412,7 @@
         <v>224</v>
       </c>
       <c r="H68" s="51">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I68" s="51">
         <v>65</v>
@@ -9421,7 +9427,7 @@
         <v>225</v>
       </c>
       <c r="H69" s="51">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I69" s="51">
         <v>65</v>
@@ -9436,7 +9442,7 @@
         <v>226</v>
       </c>
       <c r="H70" s="51">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I70" s="51">
         <v>65</v>
@@ -9451,7 +9457,7 @@
         <v>227</v>
       </c>
       <c r="H71" s="51">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I71" s="51">
         <v>65</v>
@@ -9466,7 +9472,7 @@
         <v>228</v>
       </c>
       <c r="H72" s="51">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I72" s="51">
         <v>65</v>
@@ -9481,7 +9487,7 @@
         <v>229</v>
       </c>
       <c r="H73" s="51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I73" s="51">
         <v>65</v>
@@ -9514,7 +9520,7 @@
         <v>222</v>
       </c>
       <c r="H75" s="51">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I75" s="51">
         <v>198</v>
@@ -9529,7 +9535,7 @@
         <v>223</v>
       </c>
       <c r="H76">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I76" s="51">
         <v>198</v>
@@ -9544,7 +9550,7 @@
         <v>224</v>
       </c>
       <c r="H77" s="51">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="I77" s="51">
         <v>198</v>
@@ -9559,7 +9565,7 @@
         <v>225</v>
       </c>
       <c r="H78" s="51">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I78" s="51">
         <v>198</v>
@@ -9574,7 +9580,7 @@
         <v>226</v>
       </c>
       <c r="H79" s="51">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="I79" s="51">
         <v>198</v>
@@ -9589,7 +9595,7 @@
         <v>227</v>
       </c>
       <c r="H80" s="51">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I80" s="51">
         <v>198</v>
@@ -9604,7 +9610,7 @@
         <v>228</v>
       </c>
       <c r="H81" s="51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I81" s="51">
         <v>198</v>
@@ -9619,7 +9625,7 @@
         <v>229</v>
       </c>
       <c r="H82" s="51">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I82" s="51">
         <v>198</v>
@@ -9634,7 +9640,7 @@
         <v>230</v>
       </c>
       <c r="H83" s="51">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I83" s="51">
         <v>198</v>
@@ -9652,7 +9658,7 @@
         <v>222</v>
       </c>
       <c r="H84" s="51">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I84" s="51">
         <v>177</v>
@@ -9667,7 +9673,7 @@
         <v>223</v>
       </c>
       <c r="H85" s="51">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I85" s="51">
         <v>177</v>
@@ -9682,7 +9688,7 @@
         <v>224</v>
       </c>
       <c r="H86" s="51">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I86" s="51">
         <v>177</v>
@@ -9697,7 +9703,7 @@
         <v>225</v>
       </c>
       <c r="H87" s="51">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I87" s="51">
         <v>177</v>
@@ -9712,7 +9718,7 @@
         <v>226</v>
       </c>
       <c r="H88" s="51">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="I88" s="51">
         <v>177</v>
@@ -9727,7 +9733,7 @@
         <v>227</v>
       </c>
       <c r="H89" s="51">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I89" s="51">
         <v>177</v>
@@ -9742,7 +9748,7 @@
         <v>228</v>
       </c>
       <c r="H90" s="51">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I90" s="51">
         <v>177</v>
@@ -9757,7 +9763,7 @@
         <v>229</v>
       </c>
       <c r="H91" s="51">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I91" s="51">
         <v>177</v>
@@ -9772,7 +9778,7 @@
         <v>230</v>
       </c>
       <c r="H92" s="51">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I92" s="51">
         <v>177</v>
@@ -9790,7 +9796,7 @@
         <v>222</v>
       </c>
       <c r="H93" s="51">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I93" s="51">
         <v>207</v>
@@ -9805,7 +9811,7 @@
         <v>223</v>
       </c>
       <c r="H94" s="51">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I94" s="51">
         <v>207</v>
@@ -9820,7 +9826,7 @@
         <v>224</v>
       </c>
       <c r="H95" s="51">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="I95" s="51">
         <v>207</v>
@@ -9835,7 +9841,7 @@
         <v>225</v>
       </c>
       <c r="H96" s="51">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I96" s="51">
         <v>207</v>
@@ -9850,7 +9856,7 @@
         <v>226</v>
       </c>
       <c r="H97" s="51">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="I97" s="51">
         <v>207</v>
@@ -9865,7 +9871,7 @@
         <v>227</v>
       </c>
       <c r="H98" s="51">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="I98" s="51">
         <v>207</v>
@@ -9895,7 +9901,7 @@
         <v>229</v>
       </c>
       <c r="H100" s="51">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I100" s="51">
         <v>207</v>
@@ -9910,7 +9916,7 @@
         <v>230</v>
       </c>
       <c r="H101" s="51">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I101" s="51">
         <v>207</v>
@@ -9928,7 +9934,7 @@
         <v>222</v>
       </c>
       <c r="H102" s="51">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I102" s="51">
         <v>138</v>
@@ -9943,7 +9949,7 @@
         <v>223</v>
       </c>
       <c r="H103" s="51">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I103" s="51">
         <v>138</v>
@@ -9958,7 +9964,7 @@
         <v>224</v>
       </c>
       <c r="H104" s="51">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I104" s="51">
         <v>138</v>
@@ -9988,7 +9994,7 @@
         <v>226</v>
       </c>
       <c r="H106" s="51">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="I106" s="51">
         <v>138</v>
@@ -10003,7 +10009,7 @@
         <v>227</v>
       </c>
       <c r="H107" s="51">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I107" s="51">
         <v>138</v>
@@ -10048,7 +10054,7 @@
         <v>230</v>
       </c>
       <c r="H110" s="51">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I110" s="51">
         <v>138</v>
@@ -10066,7 +10072,7 @@
         <v>222</v>
       </c>
       <c r="H111" s="51">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I111" s="51">
         <v>227</v>
@@ -10081,7 +10087,7 @@
         <v>223</v>
       </c>
       <c r="H112" s="51">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I112" s="51">
         <v>227</v>
@@ -10096,7 +10102,7 @@
         <v>224</v>
       </c>
       <c r="H113" s="51">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="I113" s="51">
         <v>227</v>
@@ -10111,7 +10117,7 @@
         <v>225</v>
       </c>
       <c r="H114" s="51">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="I114" s="51">
         <v>227</v>
@@ -10126,7 +10132,7 @@
         <v>226</v>
       </c>
       <c r="H115" s="51">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="I115" s="51">
         <v>227</v>
@@ -10141,7 +10147,7 @@
         <v>227</v>
       </c>
       <c r="H116">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="I116" s="51">
         <v>227</v>
@@ -10156,7 +10162,7 @@
         <v>228</v>
       </c>
       <c r="H117" s="51">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I117" s="51">
         <v>227</v>
@@ -10171,7 +10177,7 @@
         <v>229</v>
       </c>
       <c r="H118" s="51">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I118" s="51">
         <v>227</v>
@@ -10186,7 +10192,7 @@
         <v>230</v>
       </c>
       <c r="H119" s="51">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I119" s="51">
         <v>227</v>
@@ -10204,7 +10210,7 @@
         <v>222</v>
       </c>
       <c r="H120" s="51">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I120" s="51">
         <v>170</v>
@@ -10219,7 +10225,7 @@
         <v>223</v>
       </c>
       <c r="H121" s="51">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I121" s="51">
         <v>170</v>
@@ -10234,7 +10240,7 @@
         <v>224</v>
       </c>
       <c r="H122" s="51">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="I122" s="51">
         <v>170</v>
@@ -10249,7 +10255,7 @@
         <v>225</v>
       </c>
       <c r="H123" s="51">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I123" s="51">
         <v>170</v>
@@ -10264,7 +10270,7 @@
         <v>226</v>
       </c>
       <c r="H124">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="I124" s="51">
         <v>170</v>
@@ -10279,7 +10285,7 @@
         <v>227</v>
       </c>
       <c r="H125" s="51">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="I125" s="51">
         <v>170</v>
@@ -10294,7 +10300,7 @@
         <v>228</v>
       </c>
       <c r="H126" s="51">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I126" s="51">
         <v>170</v>
@@ -10309,7 +10315,7 @@
         <v>229</v>
       </c>
       <c r="H127" s="51">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I127" s="51">
         <v>170</v>
@@ -10324,7 +10330,7 @@
         <v>230</v>
       </c>
       <c r="H128" s="51">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I128" s="51">
         <v>170</v>
@@ -10342,7 +10348,7 @@
         <v>222</v>
       </c>
       <c r="H129" s="51">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I129" s="51">
         <v>72</v>
@@ -10357,7 +10363,7 @@
         <v>223</v>
       </c>
       <c r="H130" s="51">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I130" s="51">
         <v>72</v>
@@ -10372,7 +10378,7 @@
         <v>224</v>
       </c>
       <c r="H131" s="51">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="I131" s="51">
         <v>72</v>
@@ -10387,7 +10393,7 @@
         <v>225</v>
       </c>
       <c r="H132" s="51">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I132" s="51">
         <v>72</v>
@@ -10402,7 +10408,7 @@
         <v>226</v>
       </c>
       <c r="H133" s="51">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I133" s="51">
         <v>72</v>
@@ -10417,7 +10423,7 @@
         <v>227</v>
       </c>
       <c r="H134" s="51">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I134" s="51">
         <v>72</v>
@@ -10432,7 +10438,7 @@
         <v>228</v>
       </c>
       <c r="H135" s="51">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I135" s="51">
         <v>72</v>
@@ -10447,7 +10453,7 @@
         <v>229</v>
       </c>
       <c r="H136" s="51">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I136" s="51">
         <v>72</v>
@@ -10462,7 +10468,7 @@
         <v>230</v>
       </c>
       <c r="H137" s="51">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I137" s="51">
         <v>72</v>
@@ -10480,7 +10486,7 @@
         <v>222</v>
       </c>
       <c r="H138" s="51">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I138" s="51">
         <v>160</v>
@@ -10495,7 +10501,7 @@
         <v>223</v>
       </c>
       <c r="H139" s="51">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I139" s="51">
         <v>160</v>
@@ -10510,7 +10516,7 @@
         <v>224</v>
       </c>
       <c r="H140">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="I140" s="51">
         <v>160</v>
@@ -10525,7 +10531,7 @@
         <v>225</v>
       </c>
       <c r="H141" s="51">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I141" s="51">
         <v>160</v>
@@ -10540,7 +10546,7 @@
         <v>226</v>
       </c>
       <c r="H142" s="51">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="I142" s="51">
         <v>160</v>
@@ -10555,7 +10561,7 @@
         <v>227</v>
       </c>
       <c r="H143" s="51">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I143" s="51">
         <v>160</v>
@@ -10570,7 +10576,7 @@
         <v>228</v>
       </c>
       <c r="H144" s="51">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I144" s="51">
         <v>160</v>
@@ -10585,7 +10591,7 @@
         <v>229</v>
       </c>
       <c r="H145" s="51">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I145" s="51">
         <v>160</v>
@@ -10618,7 +10624,7 @@
         <v>222</v>
       </c>
       <c r="H147" s="51">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I147" s="51">
         <v>178</v>
@@ -10648,7 +10654,7 @@
         <v>224</v>
       </c>
       <c r="H149" s="51">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="I149" s="51">
         <v>178</v>
@@ -10663,7 +10669,7 @@
         <v>225</v>
       </c>
       <c r="H150" s="51">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I150" s="51">
         <v>178</v>
@@ -10678,7 +10684,7 @@
         <v>226</v>
       </c>
       <c r="H151" s="51">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="I151" s="51">
         <v>178</v>
@@ -10693,7 +10699,7 @@
         <v>227</v>
       </c>
       <c r="H152" s="51">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I152" s="51">
         <v>178</v>
@@ -10708,7 +10714,7 @@
         <v>228</v>
       </c>
       <c r="H153" s="51">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I153" s="51">
         <v>178</v>
@@ -10756,7 +10762,7 @@
         <v>222</v>
       </c>
       <c r="H156" s="51">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="I156" s="51">
         <v>172</v>
@@ -10771,7 +10777,7 @@
         <v>223</v>
       </c>
       <c r="H157" s="51">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="I157" s="51">
         <v>172</v>
@@ -10786,7 +10792,7 @@
         <v>224</v>
       </c>
       <c r="H158" s="51">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="I158" s="51">
         <v>172</v>
@@ -10801,7 +10807,7 @@
         <v>225</v>
       </c>
       <c r="H159" s="51">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="I159" s="51">
         <v>172</v>
@@ -10816,7 +10822,7 @@
         <v>226</v>
       </c>
       <c r="H160" s="51">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="I160" s="51">
         <v>172</v>
@@ -10831,7 +10837,7 @@
         <v>227</v>
       </c>
       <c r="H161" s="51">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="I161" s="51">
         <v>172</v>
@@ -10846,7 +10852,7 @@
         <v>228</v>
       </c>
       <c r="H162" s="51">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="I162" s="51">
         <v>172</v>
@@ -10861,7 +10867,7 @@
         <v>229</v>
       </c>
       <c r="H163" s="51">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I163" s="51">
         <v>172</v>
@@ -10876,7 +10882,7 @@
         <v>230</v>
       </c>
       <c r="H164">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I164" s="51">
         <v>172</v>
@@ -10897,7 +10903,7 @@
         <v>12</v>
       </c>
       <c r="I165" s="51">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="166" spans="5:9" x14ac:dyDescent="0.25">
@@ -10912,7 +10918,7 @@
         <v>6</v>
       </c>
       <c r="I166" s="51">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="167" spans="5:9" x14ac:dyDescent="0.25">
@@ -10927,7 +10933,7 @@
         <v>3</v>
       </c>
       <c r="I167" s="51">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="168" spans="5:9" x14ac:dyDescent="0.25">
@@ -10942,7 +10948,7 @@
         <v>15</v>
       </c>
       <c r="I168" s="51">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="169" spans="5:9" x14ac:dyDescent="0.25">
@@ -10957,7 +10963,7 @@
         <v>11</v>
       </c>
       <c r="I169" s="51">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="170" spans="5:9" x14ac:dyDescent="0.25">
@@ -10972,7 +10978,7 @@
         <v>12</v>
       </c>
       <c r="I170" s="51">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="171" spans="5:9" x14ac:dyDescent="0.25">
@@ -10987,7 +10993,7 @@
         <v>16</v>
       </c>
       <c r="I171" s="51">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="172" spans="5:9" x14ac:dyDescent="0.25">
@@ -11002,7 +11008,7 @@
         <v>6</v>
       </c>
       <c r="I172" s="51">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="173" spans="5:9" x14ac:dyDescent="0.25">
@@ -11017,7 +11023,7 @@
         <v>11</v>
       </c>
       <c r="I173" s="51">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="174" spans="5:9" x14ac:dyDescent="0.25">
@@ -11032,7 +11038,7 @@
         <v>222</v>
       </c>
       <c r="H174" s="51">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I174" s="51">
         <v>140</v>
@@ -11047,7 +11053,7 @@
         <v>223</v>
       </c>
       <c r="H175" s="51">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I175" s="51">
         <v>140</v>
@@ -11062,7 +11068,7 @@
         <v>224</v>
       </c>
       <c r="H176" s="51">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I176" s="51">
         <v>140</v>
@@ -11077,7 +11083,7 @@
         <v>225</v>
       </c>
       <c r="H177" s="51">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I177" s="51">
         <v>140</v>
@@ -11092,7 +11098,7 @@
         <v>226</v>
       </c>
       <c r="H178" s="51">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="I178" s="51">
         <v>140</v>
@@ -11107,7 +11113,7 @@
         <v>227</v>
       </c>
       <c r="H179" s="51">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="I179" s="51">
         <v>140</v>
@@ -11122,7 +11128,7 @@
         <v>228</v>
       </c>
       <c r="H180">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I180" s="51">
         <v>140</v>
@@ -11137,7 +11143,7 @@
         <v>229</v>
       </c>
       <c r="H181" s="51">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I181" s="51">
         <v>140</v>
@@ -11152,7 +11158,7 @@
         <v>230</v>
       </c>
       <c r="H182" s="51">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I182" s="51">
         <v>140</v>
@@ -11170,7 +11176,7 @@
         <v>222</v>
       </c>
       <c r="H183" s="51">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I183" s="51">
         <v>168</v>
@@ -11185,7 +11191,7 @@
         <v>223</v>
       </c>
       <c r="H184" s="51">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I184" s="51">
         <v>168</v>
@@ -11200,7 +11206,7 @@
         <v>224</v>
       </c>
       <c r="H185" s="51">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I185" s="51">
         <v>168</v>
@@ -11215,7 +11221,7 @@
         <v>225</v>
       </c>
       <c r="H186">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I186" s="51">
         <v>168</v>
@@ -11230,7 +11236,7 @@
         <v>226</v>
       </c>
       <c r="H187" s="51">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I187" s="51">
         <v>168</v>
@@ -11245,7 +11251,7 @@
         <v>227</v>
       </c>
       <c r="H188" s="51">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="I188" s="51">
         <v>168</v>
@@ -11275,7 +11281,7 @@
         <v>229</v>
       </c>
       <c r="H190" s="51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I190" s="51">
         <v>168</v>
@@ -11290,7 +11296,7 @@
         <v>230</v>
       </c>
       <c r="H191" s="51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I191" s="51">
         <v>168</v>
@@ -11308,7 +11314,7 @@
         <v>222</v>
       </c>
       <c r="H192" s="51">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I192" s="51">
         <v>170</v>
@@ -11338,7 +11344,7 @@
         <v>224</v>
       </c>
       <c r="H194" s="51">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="I194" s="51">
         <v>170</v>
@@ -11353,7 +11359,7 @@
         <v>225</v>
       </c>
       <c r="H195" s="51">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I195" s="51">
         <v>170</v>
@@ -11368,7 +11374,7 @@
         <v>226</v>
       </c>
       <c r="H196">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I196" s="51">
         <v>170</v>
@@ -11383,7 +11389,7 @@
         <v>227</v>
       </c>
       <c r="H197" s="51">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I197" s="51">
         <v>170</v>
@@ -11398,7 +11404,7 @@
         <v>228</v>
       </c>
       <c r="H198" s="51">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I198" s="51">
         <v>170</v>
@@ -11413,7 +11419,7 @@
         <v>229</v>
       </c>
       <c r="H199" s="51">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I199" s="51">
         <v>170</v>
@@ -11428,7 +11434,7 @@
         <v>230</v>
       </c>
       <c r="H200" s="51">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I200" s="51">
         <v>170</v>
@@ -11446,10 +11452,10 @@
         <v>222</v>
       </c>
       <c r="H201" s="51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I201" s="51">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="202" spans="5:9" x14ac:dyDescent="0.25">
@@ -11460,9 +11466,11 @@
       <c r="G202" t="s">
         <v>223</v>
       </c>
-      <c r="H202" s="51"/>
+      <c r="H202" s="51">
+        <v>1</v>
+      </c>
       <c r="I202" s="51">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="203" spans="5:9" x14ac:dyDescent="0.25">
@@ -11474,10 +11482,10 @@
         <v>224</v>
       </c>
       <c r="H203" s="51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I203" s="51">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="204" spans="5:9" x14ac:dyDescent="0.25">
@@ -11490,7 +11498,7 @@
       </c>
       <c r="H204" s="51"/>
       <c r="I204" s="51">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="205" spans="5:9" x14ac:dyDescent="0.25">
@@ -11505,7 +11513,7 @@
         <v>3</v>
       </c>
       <c r="I205" s="51">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="206" spans="5:9" x14ac:dyDescent="0.25">
@@ -11518,7 +11526,7 @@
       </c>
       <c r="H206" s="51"/>
       <c r="I206" s="51">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="207" spans="5:9" x14ac:dyDescent="0.25">
@@ -11530,10 +11538,10 @@
         <v>228</v>
       </c>
       <c r="H207" s="51">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I207" s="51">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="208" spans="5:9" x14ac:dyDescent="0.25">
@@ -11546,7 +11554,7 @@
       </c>
       <c r="H208" s="51"/>
       <c r="I208" s="51">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="209" spans="5:9" x14ac:dyDescent="0.25">
@@ -11559,7 +11567,7 @@
       </c>
       <c r="H209" s="51"/>
       <c r="I209" s="51">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="210" spans="5:9" x14ac:dyDescent="0.25">
@@ -11574,7 +11582,7 @@
         <v>222</v>
       </c>
       <c r="H210" s="51">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I210" s="51">
         <v>161</v>
@@ -11589,7 +11597,7 @@
         <v>223</v>
       </c>
       <c r="H211" s="51">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I211" s="51">
         <v>161</v>
@@ -11604,7 +11612,7 @@
         <v>224</v>
       </c>
       <c r="H212">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="I212" s="51">
         <v>161</v>
@@ -11619,7 +11627,7 @@
         <v>225</v>
       </c>
       <c r="H213" s="51">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I213" s="51">
         <v>161</v>
@@ -11634,7 +11642,7 @@
         <v>226</v>
       </c>
       <c r="H214" s="51">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="I214" s="51">
         <v>161</v>
@@ -11649,7 +11657,7 @@
         <v>227</v>
       </c>
       <c r="H215" s="51">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="I215" s="51">
         <v>161</v>
@@ -11664,7 +11672,7 @@
         <v>228</v>
       </c>
       <c r="H216" s="51">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I216" s="51">
         <v>161</v>
@@ -11679,7 +11687,7 @@
         <v>229</v>
       </c>
       <c r="H217" s="51">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I217" s="51">
         <v>161</v>
@@ -11712,7 +11720,7 @@
         <v>222</v>
       </c>
       <c r="H219" s="51">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I219" s="51">
         <v>56</v>
@@ -11727,7 +11735,7 @@
         <v>223</v>
       </c>
       <c r="H220" s="51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I220" s="51">
         <v>56</v>
@@ -11742,7 +11750,7 @@
         <v>224</v>
       </c>
       <c r="H221" s="51">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I221" s="51">
         <v>56</v>
@@ -11757,7 +11765,7 @@
         <v>225</v>
       </c>
       <c r="H222" s="51">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I222" s="51">
         <v>56</v>
@@ -11772,7 +11780,7 @@
         <v>226</v>
       </c>
       <c r="H223" s="51">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I223" s="51">
         <v>56</v>
@@ -11787,7 +11795,7 @@
         <v>227</v>
       </c>
       <c r="H224" s="51">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I224" s="51">
         <v>56</v>
@@ -11802,7 +11810,7 @@
         <v>228</v>
       </c>
       <c r="H225" s="51">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I225" s="51">
         <v>56</v>
@@ -11817,7 +11825,7 @@
         <v>229</v>
       </c>
       <c r="H226" s="51">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I226" s="51">
         <v>56</v>
@@ -11832,7 +11840,7 @@
         <v>230</v>
       </c>
       <c r="H227" s="51">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I227" s="51">
         <v>56</v>
@@ -11850,7 +11858,7 @@
         <v>222</v>
       </c>
       <c r="H228" s="51">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I228" s="51">
         <v>172</v>
@@ -11865,7 +11873,7 @@
         <v>223</v>
       </c>
       <c r="H229" s="51">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I229" s="51">
         <v>172</v>
@@ -11880,7 +11888,7 @@
         <v>224</v>
       </c>
       <c r="H230" s="51">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I230" s="51">
         <v>172</v>
@@ -11895,7 +11903,7 @@
         <v>225</v>
       </c>
       <c r="H231" s="51">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I231" s="51">
         <v>172</v>
@@ -11910,7 +11918,7 @@
         <v>226</v>
       </c>
       <c r="H232" s="51">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I232" s="51">
         <v>172</v>
@@ -11925,7 +11933,7 @@
         <v>227</v>
       </c>
       <c r="H233" s="51">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I233" s="51">
         <v>172</v>
@@ -11955,7 +11963,7 @@
         <v>229</v>
       </c>
       <c r="H235" s="51">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I235" s="51">
         <v>172</v>
@@ -11970,7 +11978,7 @@
         <v>230</v>
       </c>
       <c r="H236">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I236" s="51">
         <v>172</v>
@@ -11988,7 +11996,7 @@
         <v>222</v>
       </c>
       <c r="H237" s="51">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I237" s="51">
         <v>156</v>
@@ -12003,7 +12011,7 @@
         <v>223</v>
       </c>
       <c r="H238" s="51">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I238" s="51">
         <v>156</v>
@@ -12018,7 +12026,7 @@
         <v>224</v>
       </c>
       <c r="H239" s="51">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I239" s="51">
         <v>156</v>
@@ -12033,7 +12041,7 @@
         <v>225</v>
       </c>
       <c r="H240" s="51">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I240" s="51">
         <v>156</v>
@@ -12048,7 +12056,7 @@
         <v>226</v>
       </c>
       <c r="H241" s="51">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="I241" s="51">
         <v>156</v>
@@ -12063,7 +12071,7 @@
         <v>227</v>
       </c>
       <c r="H242" s="51">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="I242" s="51">
         <v>156</v>
@@ -12078,7 +12086,7 @@
         <v>228</v>
       </c>
       <c r="H243" s="51">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I243" s="51">
         <v>156</v>
@@ -12093,7 +12101,7 @@
         <v>229</v>
       </c>
       <c r="H244">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I244" s="51">
         <v>156</v>
@@ -12108,7 +12116,7 @@
         <v>230</v>
       </c>
       <c r="H245" s="51">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I245" s="51">
         <v>156</v>
@@ -12141,7 +12149,7 @@
         <v>223</v>
       </c>
       <c r="H247" s="51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I247" s="51">
         <v>142</v>
@@ -12156,7 +12164,7 @@
         <v>224</v>
       </c>
       <c r="H248" s="51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I248" s="51">
         <v>142</v>
@@ -12171,7 +12179,7 @@
         <v>225</v>
       </c>
       <c r="H249" s="51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I249" s="51">
         <v>142</v>
@@ -12186,7 +12194,7 @@
         <v>226</v>
       </c>
       <c r="H250" s="51">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I250" s="51">
         <v>142</v>
@@ -12201,7 +12209,7 @@
         <v>227</v>
       </c>
       <c r="H251" s="51">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I251" s="51">
         <v>142</v>
@@ -12216,7 +12224,7 @@
         <v>228</v>
       </c>
       <c r="H252">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I252" s="51">
         <v>142</v>
@@ -12231,7 +12239,7 @@
         <v>229</v>
       </c>
       <c r="H253" s="51">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I253" s="51">
         <v>142</v>
@@ -12246,7 +12254,7 @@
         <v>230</v>
       </c>
       <c r="H254" s="51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I254" s="51">
         <v>142</v>
@@ -12264,7 +12272,7 @@
         <v>222</v>
       </c>
       <c r="H255" s="51">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I255" s="51">
         <v>182</v>
@@ -12279,7 +12287,7 @@
         <v>223</v>
       </c>
       <c r="H256" s="51">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I256" s="51">
         <v>182</v>
@@ -12294,7 +12302,7 @@
         <v>224</v>
       </c>
       <c r="H257" s="51">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I257" s="51">
         <v>182</v>
@@ -12309,7 +12317,7 @@
         <v>225</v>
       </c>
       <c r="H258">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I258" s="51">
         <v>182</v>
@@ -12324,7 +12332,7 @@
         <v>226</v>
       </c>
       <c r="H259" s="51">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="I259" s="51">
         <v>182</v>
@@ -12339,7 +12347,7 @@
         <v>227</v>
       </c>
       <c r="H260">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="I260" s="51">
         <v>182</v>
@@ -12354,7 +12362,7 @@
         <v>228</v>
       </c>
       <c r="H261" s="51">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I261" s="51">
         <v>182</v>
@@ -12369,7 +12377,7 @@
         <v>229</v>
       </c>
       <c r="H262" s="51">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I262" s="51">
         <v>182</v>
@@ -12384,7 +12392,7 @@
         <v>230</v>
       </c>
       <c r="H263" s="51">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I263" s="51">
         <v>182</v>
@@ -12402,7 +12410,7 @@
         <v>222</v>
       </c>
       <c r="H264" s="51">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I264" s="51">
         <v>249</v>
@@ -12417,7 +12425,7 @@
         <v>223</v>
       </c>
       <c r="H265">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I265" s="51">
         <v>249</v>
@@ -12432,7 +12440,7 @@
         <v>224</v>
       </c>
       <c r="H266" s="51">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I266" s="51">
         <v>249</v>
@@ -12447,7 +12455,7 @@
         <v>225</v>
       </c>
       <c r="H267" s="51">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I267" s="51">
         <v>249</v>
@@ -12462,7 +12470,7 @@
         <v>226</v>
       </c>
       <c r="H268">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="I268" s="51">
         <v>249</v>
@@ -12477,7 +12485,7 @@
         <v>227</v>
       </c>
       <c r="H269" s="51">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I269" s="51">
         <v>249</v>
@@ -12492,7 +12500,7 @@
         <v>228</v>
       </c>
       <c r="H270" s="51">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I270" s="51">
         <v>249</v>
@@ -12507,7 +12515,7 @@
         <v>229</v>
       </c>
       <c r="H271" s="51">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I271" s="51">
         <v>249</v>
@@ -12522,7 +12530,7 @@
         <v>230</v>
       </c>
       <c r="H272" s="51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I272" s="51">
         <v>249</v>
@@ -12590,7 +12598,9 @@
       <c r="G277" t="s">
         <v>226</v>
       </c>
-      <c r="H277" s="51"/>
+      <c r="H277" s="51">
+        <v>3</v>
+      </c>
       <c r="I277" s="51">
         <v>52</v>
       </c>
@@ -12603,7 +12613,9 @@
       <c r="G278" t="s">
         <v>227</v>
       </c>
-      <c r="H278" s="51"/>
+      <c r="H278" s="51">
+        <v>2</v>
+      </c>
       <c r="I278" s="51">
         <v>52</v>
       </c>
@@ -12616,7 +12628,9 @@
       <c r="G279" t="s">
         <v>228</v>
       </c>
-      <c r="H279" s="51"/>
+      <c r="H279" s="51">
+        <v>4</v>
+      </c>
       <c r="I279" s="51">
         <v>52</v>
       </c>
@@ -12629,7 +12643,9 @@
       <c r="G280" t="s">
         <v>229</v>
       </c>
-      <c r="H280" s="51"/>
+      <c r="H280" s="51">
+        <v>1</v>
+      </c>
       <c r="I280" s="51">
         <v>52</v>
       </c>
@@ -12642,7 +12658,9 @@
       <c r="G281" t="s">
         <v>230</v>
       </c>
-      <c r="H281" s="51"/>
+      <c r="H281" s="51">
+        <v>2</v>
+      </c>
       <c r="I281" s="51">
         <v>52</v>
       </c>
@@ -12773,7 +12791,7 @@
         <v>222</v>
       </c>
       <c r="H291">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I291" s="51">
         <v>169</v>
@@ -12788,7 +12806,7 @@
         <v>223</v>
       </c>
       <c r="H292">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I292" s="51">
         <v>169</v>
@@ -12803,7 +12821,7 @@
         <v>224</v>
       </c>
       <c r="H293">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I293" s="51">
         <v>169</v>
@@ -12818,7 +12836,7 @@
         <v>225</v>
       </c>
       <c r="H294">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I294" s="51">
         <v>169</v>
@@ -12833,7 +12851,7 @@
         <v>226</v>
       </c>
       <c r="H295">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="I295" s="51">
         <v>169</v>
@@ -12848,7 +12866,7 @@
         <v>227</v>
       </c>
       <c r="H296">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="I296" s="51">
         <v>169</v>
@@ -12863,7 +12881,7 @@
         <v>228</v>
       </c>
       <c r="H297" s="51">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I297" s="51">
         <v>169</v>
@@ -12878,7 +12896,7 @@
         <v>229</v>
       </c>
       <c r="H298">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I298" s="51">
         <v>169</v>
@@ -12893,7 +12911,7 @@
         <v>230</v>
       </c>
       <c r="H299" s="51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I299" s="51">
         <v>169</v>
@@ -13049,7 +13067,7 @@
         <v>222</v>
       </c>
       <c r="H309">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="I309" s="51">
         <v>260</v>
@@ -13064,7 +13082,7 @@
         <v>223</v>
       </c>
       <c r="H310">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I310" s="51">
         <v>260</v>
@@ -13079,7 +13097,7 @@
         <v>224</v>
       </c>
       <c r="H311">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="I311" s="51">
         <v>260</v>
@@ -13094,7 +13112,7 @@
         <v>225</v>
       </c>
       <c r="H312">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I312" s="51">
         <v>260</v>
@@ -13109,7 +13127,7 @@
         <v>226</v>
       </c>
       <c r="H313">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="I313" s="51">
         <v>260</v>
@@ -13124,7 +13142,7 @@
         <v>227</v>
       </c>
       <c r="H314">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="I314" s="51">
         <v>260</v>
@@ -13139,7 +13157,7 @@
         <v>228</v>
       </c>
       <c r="H315" s="51">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I315" s="51">
         <v>260</v>
@@ -13154,7 +13172,7 @@
         <v>229</v>
       </c>
       <c r="H316">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I316" s="51">
         <v>260</v>
@@ -13169,7 +13187,7 @@
         <v>230</v>
       </c>
       <c r="H317" s="51">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I317" s="51">
         <v>260</v>
@@ -13202,7 +13220,7 @@
         <v>223</v>
       </c>
       <c r="H319" s="51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I319" s="51">
         <v>101</v>
@@ -13268,7 +13286,7 @@
         <v>228</v>
       </c>
       <c r="H324" s="51">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I324" s="51">
         <v>101</v>
@@ -13323,6 +13341,9 @@
       <c r="G328" t="s">
         <v>223</v>
       </c>
+      <c r="H328">
+        <v>1</v>
+      </c>
       <c r="I328" s="51">
         <v>105</v>
       </c>
@@ -13386,7 +13407,7 @@
         <v>228</v>
       </c>
       <c r="H333" s="51">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I333" s="51">
         <v>105</v>
@@ -13445,7 +13466,7 @@
         <v>223</v>
       </c>
       <c r="H337" s="51">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I337" s="51">
         <v>202</v>
@@ -13460,7 +13481,7 @@
         <v>224</v>
       </c>
       <c r="H338" s="51">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="I338" s="51">
         <v>202</v>
@@ -13475,7 +13496,7 @@
         <v>225</v>
       </c>
       <c r="H339" s="51">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I339" s="51">
         <v>202</v>
@@ -13490,7 +13511,7 @@
         <v>226</v>
       </c>
       <c r="H340">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="I340" s="51">
         <v>202</v>
@@ -13505,7 +13526,7 @@
         <v>227</v>
       </c>
       <c r="H341" s="51">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I341" s="51">
         <v>202</v>
@@ -13520,7 +13541,7 @@
         <v>228</v>
       </c>
       <c r="H342" s="51">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I342" s="51">
         <v>202</v>
@@ -13535,7 +13556,7 @@
         <v>229</v>
       </c>
       <c r="H343" s="51">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I343" s="51">
         <v>202</v>
@@ -13550,7 +13571,7 @@
         <v>230</v>
       </c>
       <c r="H344" s="51">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I344" s="51">
         <v>202</v>
@@ -13707,7 +13728,7 @@
       </c>
       <c r="H354" s="51"/>
       <c r="I354" s="51">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="355" spans="5:9" x14ac:dyDescent="0.25">
@@ -13720,7 +13741,7 @@
       </c>
       <c r="H355" s="51"/>
       <c r="I355" s="51">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="356" spans="5:9" x14ac:dyDescent="0.25">
@@ -13733,7 +13754,7 @@
       </c>
       <c r="H356" s="51"/>
       <c r="I356" s="51">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="357" spans="5:9" x14ac:dyDescent="0.25">
@@ -13746,7 +13767,7 @@
       </c>
       <c r="H357" s="51"/>
       <c r="I357" s="51">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="358" spans="5:9" x14ac:dyDescent="0.25">
@@ -13759,7 +13780,7 @@
       </c>
       <c r="H358" s="51"/>
       <c r="I358" s="51">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="359" spans="5:9" x14ac:dyDescent="0.25">
@@ -13772,7 +13793,7 @@
       </c>
       <c r="H359" s="51"/>
       <c r="I359" s="51">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="360" spans="5:9" x14ac:dyDescent="0.25">
@@ -13784,10 +13805,10 @@
         <v>228</v>
       </c>
       <c r="H360" s="51">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I360" s="51">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="361" spans="5:9" x14ac:dyDescent="0.25">
@@ -13800,7 +13821,7 @@
       </c>
       <c r="H361" s="51"/>
       <c r="I361" s="51">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="362" spans="5:9" x14ac:dyDescent="0.25">
@@ -13813,7 +13834,7 @@
       </c>
       <c r="H362" s="51"/>
       <c r="I362" s="51">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="363" spans="5:9" x14ac:dyDescent="0.25">
@@ -13947,8 +13968,11 @@
       <c r="G372" t="s">
         <v>222</v>
       </c>
+      <c r="H372">
+        <v>1</v>
+      </c>
       <c r="I372">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="373" spans="5:9" x14ac:dyDescent="0.25">
@@ -13959,11 +13983,8 @@
       <c r="G373" t="s">
         <v>223</v>
       </c>
-      <c r="H373">
-        <v>1</v>
-      </c>
       <c r="I373">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="374" spans="5:9" x14ac:dyDescent="0.25">
@@ -13975,7 +13996,7 @@
         <v>224</v>
       </c>
       <c r="I374">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="375" spans="5:9" x14ac:dyDescent="0.25">
@@ -13987,7 +14008,7 @@
         <v>225</v>
       </c>
       <c r="I375">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="376" spans="5:9" x14ac:dyDescent="0.25">
@@ -13999,7 +14020,7 @@
         <v>226</v>
       </c>
       <c r="I376">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="377" spans="5:9" x14ac:dyDescent="0.25">
@@ -14011,7 +14032,7 @@
         <v>227</v>
       </c>
       <c r="I377">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="378" spans="5:9" x14ac:dyDescent="0.25">
@@ -14023,7 +14044,7 @@
         <v>228</v>
       </c>
       <c r="I378">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="379" spans="5:9" x14ac:dyDescent="0.25">
@@ -14035,7 +14056,7 @@
         <v>229</v>
       </c>
       <c r="I379">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="380" spans="5:9" x14ac:dyDescent="0.25">
@@ -14047,7 +14068,7 @@
         <v>230</v>
       </c>
       <c r="I380">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="381" spans="5:9" x14ac:dyDescent="0.25">
@@ -14089,7 +14110,7 @@
         <v>224</v>
       </c>
       <c r="H383">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I383">
         <v>113</v>
@@ -14130,6 +14151,9 @@
       <c r="G386" t="s">
         <v>227</v>
       </c>
+      <c r="H386">
+        <v>1</v>
+      </c>
       <c r="I386">
         <v>113</v>
       </c>
@@ -14185,7 +14209,7 @@
         <v>222</v>
       </c>
       <c r="H390">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I390">
         <v>195</v>
@@ -14200,7 +14224,7 @@
         <v>223</v>
       </c>
       <c r="H391">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I391">
         <v>195</v>
@@ -14215,7 +14239,7 @@
         <v>224</v>
       </c>
       <c r="H392">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I392">
         <v>195</v>
@@ -14230,7 +14254,7 @@
         <v>225</v>
       </c>
       <c r="H393">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I393">
         <v>195</v>
@@ -14245,7 +14269,7 @@
         <v>226</v>
       </c>
       <c r="H394">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="I394">
         <v>195</v>
@@ -14260,7 +14284,7 @@
         <v>227</v>
       </c>
       <c r="H395">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="I395">
         <v>195</v>
@@ -14275,7 +14299,7 @@
         <v>228</v>
       </c>
       <c r="H396">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I396">
         <v>195</v>
@@ -14290,7 +14314,7 @@
         <v>229</v>
       </c>
       <c r="H397">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I397">
         <v>195</v>
@@ -14305,7 +14329,7 @@
         <v>230</v>
       </c>
       <c r="H398">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I398">
         <v>195</v>
@@ -14323,7 +14347,7 @@
         <v>222</v>
       </c>
       <c r="H399">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I399">
         <v>161</v>
@@ -14338,7 +14362,7 @@
         <v>223</v>
       </c>
       <c r="H400">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I400">
         <v>161</v>
@@ -14353,7 +14377,7 @@
         <v>224</v>
       </c>
       <c r="H401">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I401">
         <v>161</v>
@@ -14368,7 +14392,7 @@
         <v>225</v>
       </c>
       <c r="H402">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I402">
         <v>161</v>
@@ -14383,7 +14407,7 @@
         <v>226</v>
       </c>
       <c r="H403">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I403">
         <v>161</v>
@@ -14398,7 +14422,7 @@
         <v>227</v>
       </c>
       <c r="H404">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="I404">
         <v>161</v>
@@ -14428,7 +14452,7 @@
         <v>229</v>
       </c>
       <c r="H406">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I406">
         <v>161</v>
@@ -14443,7 +14467,7 @@
         <v>230</v>
       </c>
       <c r="H407">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I407">
         <v>161</v>

--- a/data/ventas.xlsx
+++ b/data/ventas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cesar\Desktop\Reportes Ventas Rap\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1ED77F2B-C804-4A4C-B2B1-B2CB88BD6181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{349C1206-A2E4-4AA5-898B-16F0DAD2F070}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2534,22 +2534,22 @@
         <v>0</v>
       </c>
       <c r="C2" s="96">
-        <v>20239.264746040899</v>
+        <v>17146.3661547753</v>
       </c>
       <c r="D2" s="96">
-        <v>97497.216435570401</v>
+        <v>85454.712087362597</v>
       </c>
       <c r="E2" s="96">
-        <v>347488527.93282223</v>
+        <v>298472871.26286787</v>
       </c>
       <c r="F2" s="96">
         <v>0</v>
       </c>
       <c r="G2" s="96">
-        <v>208601.67291691661</v>
+        <v>185038.5097417341</v>
       </c>
       <c r="H2" s="96">
-        <v>208601.74</v>
+        <v>185038.5</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -2560,22 +2560,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="96">
-        <v>287.35735488500001</v>
+        <v>250.12620409120001</v>
       </c>
       <c r="D3" s="96">
-        <v>636.38716535089998</v>
+        <v>592.11105820729995</v>
       </c>
       <c r="E3" s="96">
-        <v>6953389.0972305397</v>
+        <v>6167950.3247244535</v>
       </c>
       <c r="F3" s="96">
         <v>0</v>
       </c>
       <c r="G3" s="96">
-        <v>208601.67291691661</v>
+        <v>185038.5097417341</v>
       </c>
       <c r="H3" s="96">
-        <v>208601.74</v>
+        <v>185038.5</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2586,13 +2586,13 @@
         <v>1</v>
       </c>
       <c r="C4" s="96">
-        <v>155.42341269729999</v>
+        <v>104.8786706344</v>
       </c>
       <c r="D4" s="96">
-        <v>326.98499999799998</v>
+        <v>236.1575000002</v>
       </c>
       <c r="E4" s="96">
-        <v>4842984.6712837927</v>
+        <v>3831780.4656781647</v>
       </c>
       <c r="F4" s="96">
         <v>0</v>
@@ -2612,13 +2612,13 @@
         <v>1</v>
       </c>
       <c r="C5" s="96">
-        <v>200.08797618950001</v>
+        <v>160.9195238085</v>
       </c>
       <c r="D5" s="96">
-        <v>776.02249999560001</v>
+        <v>612.02249999640003</v>
       </c>
       <c r="E5" s="96">
-        <v>4538116.0675083203</v>
+        <v>3383340.6159000443</v>
       </c>
       <c r="F5" s="96">
         <v>0</v>
@@ -2638,13 +2638,13 @@
         <v>1</v>
       </c>
       <c r="C6" s="96">
-        <v>397.30575396749998</v>
+        <v>361.47559523759998</v>
       </c>
       <c r="D6" s="96">
-        <v>1116.1477142923</v>
+        <v>1048.2891785794</v>
       </c>
       <c r="E6" s="96">
-        <v>7971555.33420307</v>
+        <v>6899879.8473196756</v>
       </c>
       <c r="F6" s="96">
         <v>0</v>
@@ -2664,13 +2664,13 @@
         <v>1</v>
       </c>
       <c r="C7" s="96">
-        <v>418.16251984000002</v>
+        <v>327.00688491969998</v>
       </c>
       <c r="D7" s="96">
-        <v>1324.0909999978001</v>
+        <v>1128.9845000005</v>
       </c>
       <c r="E7" s="96">
-        <v>8068882.1386908181</v>
+        <v>6168952.3513542237</v>
       </c>
       <c r="F7" s="96">
         <v>0</v>
@@ -2690,13 +2690,13 @@
         <v>1</v>
       </c>
       <c r="C8" s="96">
-        <v>1635.1115740742</v>
+        <v>1635.1449074075001</v>
       </c>
       <c r="D8" s="96">
-        <v>1870.3864768542001</v>
+        <v>1871.1244768535</v>
       </c>
       <c r="E8" s="96">
-        <v>17061083.040882383</v>
+        <v>17081843.43377829</v>
       </c>
       <c r="F8" s="96">
         <v>0</v>
@@ -2716,13 +2716,13 @@
         <v>1</v>
       </c>
       <c r="C9" s="96">
-        <v>198.23150793619999</v>
+        <v>151.30611111069999</v>
       </c>
       <c r="D9" s="96">
-        <v>911.56750000140005</v>
+        <v>844.06249999780005</v>
       </c>
       <c r="E9" s="96">
-        <v>3586477.5079781078</v>
+        <v>2938195.7767915935</v>
       </c>
       <c r="F9" s="96">
         <v>0</v>
@@ -2742,13 +2742,13 @@
         <v>1</v>
       </c>
       <c r="C10" s="96">
-        <v>151.87760912690001</v>
+        <v>97.588759920800001</v>
       </c>
       <c r="D10" s="96">
-        <v>538.00411458880001</v>
+        <v>283.49911458560001</v>
       </c>
       <c r="E10" s="96">
-        <v>3996158.8131728824</v>
+        <v>2863924.6281832345</v>
       </c>
       <c r="F10" s="96">
         <v>0</v>
@@ -2768,13 +2768,13 @@
         <v>1</v>
       </c>
       <c r="C11" s="96">
-        <v>157.76408730060001</v>
+        <v>115.3075396819</v>
       </c>
       <c r="D11" s="96">
-        <v>362.56459523730001</v>
+        <v>293.55459523730002</v>
       </c>
       <c r="E11" s="96">
-        <v>2958594.3353685732</v>
+        <v>2292259.0263364343</v>
       </c>
       <c r="F11" s="96">
         <v>0</v>
@@ -2794,13 +2794,13 @@
         <v>1</v>
       </c>
       <c r="C12" s="96">
-        <v>376.22777777610003</v>
+        <v>345.86944444289998</v>
       </c>
       <c r="D12" s="96">
-        <v>2353.8501190427</v>
+        <v>2278.2034523770999</v>
       </c>
       <c r="E12" s="96">
-        <v>6404448.8053096188</v>
+        <v>5810906.7980635744</v>
       </c>
       <c r="F12" s="96">
         <v>0</v>
@@ -2820,13 +2820,13 @@
         <v>1</v>
       </c>
       <c r="C13" s="96">
-        <v>340.59277777739999</v>
+        <v>276.10170634870002</v>
       </c>
       <c r="D13" s="96">
-        <v>1049.3365119081</v>
+        <v>940.33651190850003</v>
       </c>
       <c r="E13" s="96">
-        <v>6622431.8650625329</v>
+        <v>5672001.5032034451</v>
       </c>
       <c r="F13" s="96">
         <v>0</v>
@@ -2846,13 +2846,13 @@
         <v>1</v>
       </c>
       <c r="C14" s="96">
-        <v>1689.6688492064</v>
+        <v>1609.1910714287001</v>
       </c>
       <c r="D14" s="96">
-        <v>14984.7324999998</v>
+        <v>14799.4800000014</v>
       </c>
       <c r="E14" s="96">
-        <v>39689592.681744099</v>
+        <v>38609317.055148289</v>
       </c>
       <c r="F14" s="96">
         <v>0</v>
@@ -2872,13 +2872,13 @@
         <v>1</v>
       </c>
       <c r="C15" s="96">
-        <v>322.91230158680003</v>
+        <v>247.15327380900001</v>
       </c>
       <c r="D15" s="96">
-        <v>1065.8074999979999</v>
+        <v>974.77749999800005</v>
       </c>
       <c r="E15" s="96">
-        <v>6197917.8190731332</v>
+        <v>4655359.4802594241</v>
       </c>
       <c r="F15" s="96">
         <v>0</v>
@@ -2898,13 +2898,13 @@
         <v>1</v>
       </c>
       <c r="C16" s="96">
-        <v>214.65501984030001</v>
+        <v>178.4678174595</v>
       </c>
       <c r="D16" s="96">
-        <v>1133.6685119097999</v>
+        <v>966.66851190839998</v>
       </c>
       <c r="E16" s="96">
-        <v>5255755.4759214995</v>
+        <v>4172472.7522102422</v>
       </c>
       <c r="F16" s="96">
         <v>0</v>
@@ -2924,13 +2924,13 @@
         <v>1</v>
       </c>
       <c r="C17" s="96">
-        <v>480.26246031580001</v>
+        <v>300.13720237960001</v>
       </c>
       <c r="D17" s="96">
-        <v>1416.7735238169</v>
+        <v>957.02602381810004</v>
       </c>
       <c r="E17" s="96">
-        <v>9288875.7683896385</v>
+        <v>6362623.1530077159</v>
       </c>
       <c r="F17" s="96">
         <v>0</v>
@@ -2950,13 +2950,13 @@
         <v>1</v>
       </c>
       <c r="C18" s="96">
-        <v>588.94634920609997</v>
+        <v>484.40908730130002</v>
       </c>
       <c r="D18" s="96">
-        <v>2848.4188452368999</v>
+        <v>2532.7421785693</v>
       </c>
       <c r="E18" s="96">
-        <v>12202147.531287048</v>
+        <v>10180781.322442733</v>
       </c>
       <c r="F18" s="96">
         <v>0</v>
@@ -2976,13 +2976,13 @@
         <v>1</v>
       </c>
       <c r="C19" s="96">
-        <v>441.94708994609999</v>
+        <v>381.46455026360002</v>
       </c>
       <c r="D19" s="96">
-        <v>1784.6717142952</v>
+        <v>1583.1667142941999</v>
       </c>
       <c r="E19" s="96">
-        <v>9037854.5756811257</v>
+        <v>8068602.606727235</v>
       </c>
       <c r="F19" s="96">
         <v>0</v>
@@ -3002,13 +3002,13 @@
         <v>1</v>
       </c>
       <c r="C20" s="96">
-        <v>1691.1757341268999</v>
+        <v>1502.1562896826999</v>
       </c>
       <c r="D20" s="96">
-        <v>8709.6164999951998</v>
+        <v>8207.8199999985009</v>
       </c>
       <c r="E20" s="96">
-        <v>25307057.946538661</v>
+        <v>21714287.032106198</v>
       </c>
       <c r="F20" s="96">
         <v>0</v>
@@ -3028,13 +3028,13 @@
         <v>1</v>
       </c>
       <c r="C21" s="96">
-        <v>264.46081349069999</v>
+        <v>211.5864484121</v>
       </c>
       <c r="D21" s="96">
-        <v>939.2292142901</v>
+        <v>833.7746071478</v>
       </c>
       <c r="E21" s="96">
-        <v>5595341.8938343767</v>
+        <v>4521737.6382463202</v>
       </c>
       <c r="F21" s="96">
         <v>0</v>
@@ -3054,13 +3054,13 @@
         <v>1</v>
       </c>
       <c r="C22" s="96">
-        <v>197.9982142849</v>
+        <v>165.08382936460001</v>
       </c>
       <c r="D22" s="96">
-        <v>505.67851190179999</v>
+        <v>427.67851190099998</v>
       </c>
       <c r="E22" s="96">
-        <v>3109025.2196221473</v>
+        <v>2633216.6305364068</v>
       </c>
       <c r="F22" s="96">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         <v>1</v>
       </c>
       <c r="C23" s="96">
-        <v>781.37513888820001</v>
+        <v>790.79180555489995</v>
       </c>
       <c r="D23" s="96">
         <v>4836.2267976160001</v>
       </c>
       <c r="E23" s="96">
-        <v>16984006.336814482</v>
+        <v>17286368.69822238</v>
       </c>
       <c r="F23" s="96">
         <v>0</v>
@@ -3132,13 +3132,13 @@
         <v>1</v>
       </c>
       <c r="C25" s="96">
-        <v>298.05575396820001</v>
+        <v>266.02386904759999</v>
       </c>
       <c r="D25" s="96">
-        <v>850.76000000500005</v>
+        <v>745.76000000479996</v>
       </c>
       <c r="E25" s="96">
-        <v>4865926.9418352479</v>
+        <v>4425690.3579718489</v>
       </c>
       <c r="F25" s="96">
         <v>0</v>
@@ -3158,13 +3158,13 @@
         <v>1</v>
       </c>
       <c r="C26" s="96">
-        <v>200.69081349109999</v>
+        <v>116.358075396</v>
       </c>
       <c r="D26" s="96">
-        <v>459.23708333330001</v>
+        <v>329.2370833343</v>
       </c>
       <c r="E26" s="96">
-        <v>3089173.5689832573</v>
+        <v>2299134.4748592312</v>
       </c>
       <c r="F26" s="96">
         <v>0</v>
@@ -3184,13 +3184,13 @@
         <v>1</v>
       </c>
       <c r="C27" s="96">
-        <v>1888.5</v>
+        <v>1858.5</v>
       </c>
       <c r="D27" s="96">
-        <v>9736.84</v>
+        <v>9370.84</v>
       </c>
       <c r="E27" s="96">
-        <v>23468686.842</v>
+        <v>22612109.009</v>
       </c>
       <c r="F27" s="96">
         <v>0</v>
@@ -3210,13 +3210,13 @@
         <v>1</v>
       </c>
       <c r="C28" s="96">
-        <v>424.6578339939</v>
+        <v>335.03509589909999</v>
       </c>
       <c r="D28" s="96">
-        <v>1810.8346354224</v>
+        <v>1431.6175520900999</v>
       </c>
       <c r="E28" s="96">
-        <v>8516814.03087065</v>
+        <v>6604601.1312453747</v>
       </c>
       <c r="F28" s="96">
         <v>0</v>
@@ -3236,13 +3236,13 @@
         <v>1</v>
       </c>
       <c r="C29" s="96">
-        <v>1351.4300000001001</v>
+        <v>1070.0341666667</v>
       </c>
       <c r="D29" s="96">
-        <v>2346.2820833356</v>
+        <v>2070.5600000021</v>
       </c>
       <c r="E29" s="96">
-        <v>17555809.912466466</v>
+        <v>14993819.966923174</v>
       </c>
       <c r="F29" s="96">
         <v>0</v>
@@ -3262,13 +3262,13 @@
         <v>1</v>
       </c>
       <c r="C30" s="96">
-        <v>111.48898809560001</v>
+        <v>94.954265873200001</v>
       </c>
       <c r="D30" s="96">
-        <v>371.92416667719999</v>
+        <v>328.6716666758</v>
       </c>
       <c r="E30" s="96">
-        <v>2098536.1960838647</v>
+        <v>1808557.8257932956</v>
       </c>
       <c r="F30" s="96">
         <v>0</v>
@@ -3288,13 +3288,13 @@
         <v>1</v>
       </c>
       <c r="C31" s="96">
-        <v>172.14345238000001</v>
+        <v>129.67519841169999</v>
       </c>
       <c r="D31" s="96">
-        <v>351.31749999890002</v>
+        <v>329.79500000109999</v>
       </c>
       <c r="E31" s="96">
-        <v>2883607.9842428509</v>
+        <v>2246997.9859188953</v>
       </c>
       <c r="F31" s="96">
         <v>0</v>
@@ -3314,13 +3314,13 @@
         <v>1</v>
       </c>
       <c r="C32" s="96">
-        <v>55.931944444599999</v>
+        <v>35.690277778000002</v>
       </c>
       <c r="D32" s="96">
-        <v>392.40416666760001</v>
+        <v>226.89916666760001</v>
       </c>
       <c r="E32" s="96">
-        <v>1626463.4655310514</v>
+        <v>1134886.8601273343</v>
       </c>
       <c r="F32" s="96">
         <v>0</v>
@@ -3340,13 +3340,13 @@
         <v>1</v>
       </c>
       <c r="C33" s="96">
-        <v>308.6682738092</v>
+        <v>295.61113095220003</v>
       </c>
       <c r="D33" s="96">
-        <v>704.99600000179998</v>
+        <v>667.99600000179998</v>
       </c>
       <c r="E33" s="96">
-        <v>4975553.6144345868</v>
+        <v>4669958.7290065279</v>
       </c>
       <c r="F33" s="96">
         <v>0</v>
@@ -3418,13 +3418,13 @@
         <v>1</v>
       </c>
       <c r="C36" s="96">
-        <v>285.49811507840002</v>
+        <v>249.8000992058</v>
       </c>
       <c r="D36" s="96">
-        <v>1243.7466071438</v>
+        <v>1087.4160119085</v>
       </c>
       <c r="E36" s="96">
-        <v>5822405.6030015703</v>
+        <v>5027241.122842595</v>
       </c>
       <c r="F36" s="96">
         <v>0</v>
@@ -3470,13 +3470,13 @@
         <v>1</v>
       </c>
       <c r="C38" s="96">
-        <v>308.39242424230002</v>
+        <v>259.89242424230002</v>
       </c>
       <c r="D38" s="96">
-        <v>3260.7299999989</v>
+        <v>2636.4299999988998</v>
       </c>
       <c r="E38" s="96">
-        <v>6663134.8062294191</v>
+        <v>5554944.6639294196</v>
       </c>
       <c r="F38" s="96">
         <v>0</v>
@@ -3496,13 +3496,13 @@
         <v>1</v>
       </c>
       <c r="C39" s="96">
-        <v>471.4166666667</v>
+        <v>403.9166666667</v>
       </c>
       <c r="D39" s="96">
-        <v>5734.2</v>
+        <v>4611.43</v>
       </c>
       <c r="E39" s="96">
-        <v>10196205.867152149</v>
+        <v>8252554.4917521486</v>
       </c>
       <c r="F39" s="96">
         <v>0</v>
@@ -3522,13 +3522,13 @@
         <v>1</v>
       </c>
       <c r="C40" s="96">
-        <v>757.61760582019997</v>
+        <v>319.48347883600002</v>
       </c>
       <c r="D40" s="96">
-        <v>4224.4444986853996</v>
+        <v>1582.4444986829001</v>
       </c>
       <c r="E40" s="96">
-        <v>6909391.5039921645</v>
+        <v>4507114.506957056</v>
       </c>
       <c r="F40" s="96">
         <v>0</v>
@@ -3548,13 +3548,13 @@
         <v>1</v>
       </c>
       <c r="C41" s="96">
-        <v>679.35634920610005</v>
+        <v>548.18968253950004</v>
       </c>
       <c r="D41" s="96">
-        <v>4883.0241666669999</v>
+        <v>4043.0241666669999</v>
       </c>
       <c r="E41" s="96">
-        <v>8825883.2392010316</v>
+        <v>7398936.6723073218</v>
       </c>
       <c r="F41" s="96">
         <v>0</v>
@@ -3574,13 +3574,13 @@
         <v>1</v>
       </c>
       <c r="C42" s="96">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="D42" s="96">
-        <v>424.04</v>
+        <v>126.04</v>
       </c>
       <c r="E42" s="96">
-        <v>746511.00490000006</v>
+        <v>280769.63740000001</v>
       </c>
       <c r="F42" s="96">
         <v>0</v>
@@ -3600,13 +3600,13 @@
         <v>1</v>
       </c>
       <c r="C43" s="96">
-        <v>74.818551587300007</v>
+        <v>-6.2142857142999999</v>
       </c>
       <c r="D43" s="96">
-        <v>229.00349106979999</v>
+        <v>-6.2810714286999998</v>
       </c>
       <c r="E43" s="96">
-        <v>3760393.1741207056</v>
+        <v>-275260.76904147147</v>
       </c>
       <c r="F43" s="96">
         <v>0</v>
@@ -3626,13 +3626,13 @@
         <v>1</v>
       </c>
       <c r="C44" s="96">
-        <v>123.917063492</v>
+        <v>-3.2847222223000001</v>
       </c>
       <c r="D44" s="96">
-        <v>1239.6349404736</v>
+        <v>-20.505000001599999</v>
       </c>
       <c r="E44" s="96">
-        <v>1913900.6624423866</v>
+        <v>-402349.89063324447</v>
       </c>
       <c r="F44" s="96">
         <v>0</v>
@@ -3652,13 +3652,13 @@
         <v>1</v>
       </c>
       <c r="C45" s="96">
-        <v>234.9175793654</v>
+        <v>217.31500000029999</v>
       </c>
       <c r="D45" s="96">
-        <v>2276.0000000041</v>
+        <v>2178.0000000025002</v>
       </c>
       <c r="E45" s="96">
-        <v>4664188.216696891</v>
+        <v>4246358.1772271991</v>
       </c>
       <c r="F45" s="96">
         <v>0</v>
@@ -3678,13 +3678,13 @@
         <v>1</v>
       </c>
       <c r="C46" s="96">
-        <v>321.875</v>
+        <v>101.875</v>
       </c>
       <c r="D46" s="96">
         <v>-24.9999999996</v>
       </c>
       <c r="E46" s="96">
-        <v>1599703.2523960921</v>
+        <v>136464.048396092</v>
       </c>
       <c r="F46" s="96">
         <v>0</v>
@@ -3773,44 +3773,44 @@
       </c>
       <c r="D2" s="59">
         <f>IFERROR(+VLOOKUP(B2,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>12202147.531287048</v>
+        <v>10180781.322442733</v>
       </c>
       <c r="E2" s="59">
-        <v>10180781.322442733</v>
+        <v>6538018.3834050605</v>
       </c>
       <c r="F2" s="59">
         <f t="shared" ref="F2:F9" si="0">+D2-E2</f>
-        <v>2021366.2088443153</v>
+        <v>3642762.9390376722</v>
       </c>
       <c r="G2" s="60">
         <f t="shared" ref="G2:G41" si="1">+D2/C2</f>
-        <v>0.3780203401737795</v>
+        <v>0.31539877786895837</v>
       </c>
       <c r="H2" s="59">
         <f>+D2/$N$3*$N$4</f>
-        <v>58570308.150177836</v>
+        <v>61084687.934656397</v>
       </c>
       <c r="I2" s="60">
         <f t="shared" ref="I2:I41" si="2">+H2/C2</f>
-        <v>1.8144976328341418</v>
+        <v>1.8923926672137501</v>
       </c>
       <c r="J2" s="59">
         <f>+D2/$N$3</f>
-        <v>2440429.5062574097</v>
+        <v>2545195.3306106832</v>
       </c>
       <c r="K2" s="59">
         <f t="shared" ref="K2:K41" si="3">+(C2-D2)/$N$2</f>
-        <v>1056680.4793138793</v>
+        <v>1104914.765790401</v>
       </c>
       <c r="L2" s="61" cm="1">
         <f t="array" ref="L2">+_xlfn.IFS(I2&gt;114%,H2*0.02,I2&gt;109%,H2*0.015,I2&gt;104%,H2*0.0125,I2&gt;99%,H2*0.01,I2&lt;99%,H2*0)</f>
-        <v>1171406.1630035567</v>
+        <v>1221693.7586931279</v>
       </c>
       <c r="M2" s="53" t="s">
         <v>36</v>
       </c>
       <c r="N2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -3823,45 +3823,45 @@
       </c>
       <c r="D3" s="4">
         <f>IFERROR(+VLOOKUP(B3,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>9288875.7683896385</v>
+        <v>6362623.1530077159</v>
       </c>
       <c r="E3" s="4">
-        <v>6362623.1530077159</v>
+        <v>5092283.3348378455</v>
       </c>
       <c r="F3" s="4">
         <f t="shared" si="0"/>
-        <v>2926252.6153819226</v>
+        <v>1270339.8181698704</v>
       </c>
       <c r="G3" s="5">
         <f t="shared" si="1"/>
-        <v>0.29980819360899963</v>
+        <v>0.20536032580062649</v>
       </c>
       <c r="H3" s="4">
         <f t="shared" ref="H3:H41" si="4">+D3/$N$3*$N$4</f>
-        <v>44586603.688270271</v>
+        <v>38175738.918046296</v>
       </c>
       <c r="I3" s="5">
         <f t="shared" si="2"/>
-        <v>1.4390793293231983</v>
+        <v>1.2321619548037588</v>
       </c>
       <c r="J3" s="4">
         <f t="shared" ref="J3:J41" si="5">+D3/$N$3</f>
-        <v>1857775.1536779278</v>
+        <v>1590655.788251929</v>
       </c>
       <c r="K3" s="4">
         <f t="shared" si="3"/>
-        <v>1141781.7058154535</v>
+        <v>1231005.251293777</v>
       </c>
       <c r="L3" s="63" cm="1">
         <f t="array" ref="L3">+_xlfn.IFS(I3&gt;114%,H3*0.02,I3&gt;109%,H3*0.015,I3&gt;104%,H3*0.0125,I3&gt;99%,H3*0.01,I3&lt;99%,H3*0)</f>
-        <v>891732.07376540545</v>
+        <v>763514.77836092596</v>
       </c>
       <c r="M3" s="53" t="s">
         <v>40</v>
       </c>
       <c r="N3">
         <f>N4-N2</f>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -3874,38 +3874,38 @@
       </c>
       <c r="D4" s="4">
         <f>IFERROR(+VLOOKUP(B4,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>6197917.8190731332</v>
+        <v>4655359.4802594241</v>
       </c>
       <c r="E4" s="4">
-        <v>4655359.4802594241</v>
+        <v>3799689.1529486589</v>
       </c>
       <c r="F4" s="4">
         <f t="shared" si="0"/>
-        <v>1542558.3388137091</v>
+        <v>855670.32731076516</v>
       </c>
       <c r="G4" s="5">
         <f t="shared" si="1"/>
-        <v>0.21831317346146409</v>
+        <v>0.16397866693420166</v>
       </c>
       <c r="H4" s="4">
         <f t="shared" si="4"/>
-        <v>29750005.531551037</v>
+        <v>27932156.881556544</v>
       </c>
       <c r="I4" s="5">
         <f t="shared" si="2"/>
-        <v>1.0479032326150275</v>
+        <v>0.98387200160521004</v>
       </c>
       <c r="J4" s="4">
         <f t="shared" si="5"/>
-        <v>1239583.5638146265</v>
+        <v>1163839.870064856</v>
       </c>
       <c r="K4" s="4">
         <f t="shared" si="3"/>
-        <v>1168005.970582901</v>
+        <v>1186733.5889944416</v>
       </c>
       <c r="L4" s="63" cm="1">
         <f t="array" ref="L4">+_xlfn.IFS(I4&gt;114%,H4*0.02,I4&gt;109%,H4*0.015,I4&gt;104%,H4*0.0125,I4&gt;99%,H4*0.01,I4&lt;99%,H4*0)</f>
-        <v>371875.06914438796</v>
+        <v>0</v>
       </c>
       <c r="M4" s="53" t="s">
         <v>47</v>
@@ -3924,38 +3924,38 @@
       </c>
       <c r="D5" s="4">
         <f>IFERROR(+VLOOKUP(B5,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>6622431.8650625329</v>
+        <v>5672001.5032034451</v>
       </c>
       <c r="E5" s="4">
-        <v>5672001.5032034451</v>
+        <v>4650179.1579327742</v>
       </c>
       <c r="F5" s="4">
         <f t="shared" si="0"/>
-        <v>950430.36185908783</v>
+        <v>1021822.345270671</v>
       </c>
       <c r="G5" s="5">
         <f t="shared" si="1"/>
-        <v>0.23326609979322546</v>
+        <v>0.19978849093996473</v>
       </c>
       <c r="H5" s="4">
         <f t="shared" si="4"/>
-        <v>31787672.952300161</v>
+        <v>34032009.019220673</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" si="2"/>
-        <v>1.1196772790074823</v>
+        <v>1.1987309456397885</v>
       </c>
       <c r="J5" s="4">
         <f t="shared" si="5"/>
-        <v>1324486.3730125066</v>
+        <v>1418000.3758008613</v>
       </c>
       <c r="K5" s="4">
         <f t="shared" si="3"/>
-        <v>1145663.1260571433</v>
+        <v>1135901.4878472404</v>
       </c>
       <c r="L5" s="63" cm="1">
         <f t="array" ref="L5">+_xlfn.IFS(I5&gt;114%,H5*0.02,I5&gt;109%,H5*0.015,I5&gt;104%,H5*0.0125,I5&gt;99%,H5*0.01,I5&lt;99%,H5*0)</f>
-        <v>476815.09428450238</v>
+        <v>680640.18038441346</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
@@ -3968,38 +3968,38 @@
       </c>
       <c r="D6" s="4">
         <f>IFERROR(+VLOOKUP(B6,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>6404448.8053096188</v>
+        <v>5810906.7980635744</v>
       </c>
       <c r="E6" s="4">
-        <v>5810906.7980635744</v>
+        <v>3454829.7358999122</v>
       </c>
       <c r="F6" s="4">
         <f t="shared" si="0"/>
-        <v>593542.00724604446</v>
+        <v>2356077.0621636622</v>
       </c>
       <c r="G6" s="5">
         <f t="shared" si="1"/>
-        <v>0.27219702432644627</v>
+        <v>0.24697075223084025</v>
       </c>
       <c r="H6" s="4">
         <f t="shared" si="4"/>
-        <v>30741354.265486173</v>
+        <v>34865440.788381442</v>
       </c>
       <c r="I6" s="5">
         <f t="shared" si="2"/>
-        <v>1.3065457167669423</v>
+        <v>1.4818245133850414</v>
       </c>
       <c r="J6" s="4">
         <f t="shared" si="5"/>
-        <v>1280889.7610619238</v>
+        <v>1452726.6995158936</v>
       </c>
       <c r="K6" s="4">
         <f t="shared" si="3"/>
-        <v>901277.67011634237</v>
+        <v>885890.88697282749</v>
       </c>
       <c r="L6" s="63" cm="1">
         <f t="array" ref="L6">+_xlfn.IFS(I6&gt;114%,H6*0.02,I6&gt;109%,H6*0.015,I6&gt;104%,H6*0.0125,I6&gt;99%,H6*0.01,I6&lt;99%,H6*0)</f>
-        <v>614827.08530972351</v>
+        <v>697308.81576762884</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
@@ -4012,34 +4012,34 @@
       </c>
       <c r="D7" s="4">
         <f>IFERROR(+VLOOKUP(B7,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>3586477.5079781078</v>
+        <v>2938195.7767915935</v>
       </c>
       <c r="E7" s="4">
-        <v>2938195.7767915935</v>
+        <v>2229458.8498637299</v>
       </c>
       <c r="F7" s="4">
         <f t="shared" ref="F7:F8" si="6">+D7-E7</f>
-        <v>648281.73118651425</v>
+        <v>708736.92692786362</v>
       </c>
       <c r="G7" s="5">
         <f t="shared" si="1"/>
-        <v>0.12928036879577476</v>
+        <v>0.10591200774933836</v>
       </c>
       <c r="H7" s="4">
         <f t="shared" si="4"/>
-        <v>17215092.038294919</v>
+        <v>17629174.660749562</v>
       </c>
       <c r="I7" s="5">
         <f t="shared" si="2"/>
-        <v>0.62054577021971891</v>
+        <v>0.63547204649603017</v>
       </c>
       <c r="J7" s="4">
         <f t="shared" si="5"/>
-        <v>717295.50159562158</v>
+        <v>734548.94419789838</v>
       </c>
       <c r="K7" s="4">
         <f t="shared" si="3"/>
-        <v>1271335.7643413893</v>
+        <v>1240183.0626836454</v>
       </c>
       <c r="L7" s="63" cm="1">
         <f t="array" ref="L7">+_xlfn.IFS(I7&gt;114%,H7*0.02,I7&gt;109%,H7*0.015,I7&gt;104%,H7*0.0125,I7&gt;99%,H7*0.01,I7&lt;99%,H7*0)</f>
@@ -4056,38 +4056,38 @@
       </c>
       <c r="D8" s="4">
         <f>IFERROR(+VLOOKUP(B8,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>8068882.1386908181</v>
+        <v>6168952.3513542237</v>
       </c>
       <c r="E8" s="4">
-        <v>6168952.3513542237</v>
+        <v>4232380.5042614806</v>
       </c>
       <c r="F8" s="4">
         <f t="shared" si="6"/>
-        <v>1899929.7873365944</v>
+        <v>1936571.847092743</v>
       </c>
       <c r="G8" s="5">
         <f t="shared" si="1"/>
-        <v>0.22519232106693524</v>
+        <v>0.17216767758838331</v>
       </c>
       <c r="H8" s="4">
         <f t="shared" si="4"/>
-        <v>38730634.265715927</v>
+        <v>37013714.108125344</v>
       </c>
       <c r="I8" s="5">
         <f t="shared" si="2"/>
-        <v>1.0809231411212892</v>
+        <v>1.0330060655302999</v>
       </c>
       <c r="J8" s="4">
         <f t="shared" si="5"/>
-        <v>1613776.4277381636</v>
+        <v>1542238.0878385559</v>
       </c>
       <c r="K8" s="4">
         <f t="shared" si="3"/>
-        <v>1461167.8567487835</v>
+        <v>1483105.9532781742</v>
       </c>
       <c r="L8" s="63" cm="1">
         <f t="array" ref="L8">+_xlfn.IFS(I8&gt;114%,H8*0.02,I8&gt;109%,H8*0.015,I8&gt;104%,H8*0.0125,I8&gt;99%,H8*0.01,I8&lt;99%,H8*0)</f>
-        <v>484132.92832144909</v>
+        <v>370137.14108125347</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
@@ -4100,38 +4100,38 @@
       </c>
       <c r="D9" s="4">
         <f>IFERROR(+VLOOKUP(B9,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>7971555.33420307</v>
+        <v>6899879.8473196756</v>
       </c>
       <c r="E9" s="4">
-        <v>6899879.8473196756</v>
+        <v>5960130.3637676956</v>
       </c>
       <c r="F9" s="4">
         <f t="shared" si="0"/>
-        <v>1071675.4868833944</v>
+        <v>939749.48355198</v>
       </c>
       <c r="G9" s="5">
         <f t="shared" si="1"/>
-        <v>0.22247605273782814</v>
+        <v>0.19256694188781318</v>
       </c>
       <c r="H9" s="4">
         <f t="shared" si="4"/>
-        <v>38263465.604174733</v>
+        <v>41399279.08391805</v>
       </c>
       <c r="I9" s="5">
         <f t="shared" si="2"/>
-        <v>1.0678850531415751</v>
+        <v>1.155401651326879</v>
       </c>
       <c r="J9" s="4">
         <f t="shared" si="5"/>
-        <v>1594311.066840614</v>
+        <v>1724969.9618299189</v>
       </c>
       <c r="K9" s="4">
         <f t="shared" si="3"/>
-        <v>1466290.3201428754</v>
+        <v>1446559.5784799014</v>
       </c>
       <c r="L9" s="63" cm="1">
         <f t="array" ref="L9">+_xlfn.IFS(I9&gt;114%,H9*0.02,I9&gt;109%,H9*0.015,I9&gt;104%,H9*0.0125,I9&gt;99%,H9*0.01,I9&lt;99%,H9*0)</f>
-        <v>478293.32005218416</v>
+        <v>827985.58167836105</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4142,34 +4142,34 @@
       </c>
       <c r="D10" s="64">
         <f>+SUM(D2:D9)</f>
-        <v>60342736.769993968</v>
+        <v>48688700.232442394</v>
       </c>
       <c r="E10" s="65">
-        <v>48688700.232442394</v>
+        <v>35956969.48291716</v>
       </c>
       <c r="F10" s="64">
         <f>+SUM(F2:F9)</f>
-        <v>11654036.537551582</v>
+        <v>12731730.749525227</v>
       </c>
       <c r="G10" s="66">
         <f t="shared" si="1"/>
-        <v>0.2483499872890047</v>
+        <v>0.2003859740391824</v>
       </c>
       <c r="H10" s="64">
         <f t="shared" si="4"/>
-        <v>289645136.49597102</v>
+        <v>292132201.39465439</v>
       </c>
       <c r="I10" s="66">
         <f t="shared" si="2"/>
-        <v>1.1920799389872223</v>
+        <v>1.2023158442350945</v>
       </c>
       <c r="J10" s="64">
         <f t="shared" si="5"/>
-        <v>12068547.353998793</v>
+        <v>12172175.058110598</v>
       </c>
       <c r="K10" s="67">
         <f t="shared" si="3"/>
-        <v>9612202.8931187652</v>
+        <v>9714294.5753404051</v>
       </c>
       <c r="L10" s="68"/>
     </row>
@@ -4185,38 +4185,38 @@
       </c>
       <c r="D11" s="59">
         <f>IFERROR(+VLOOKUP(B11,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>25307057.946538661</v>
+        <v>21714287.032106198</v>
       </c>
       <c r="E11" s="59">
-        <v>21714287.032106198</v>
+        <v>18543635.055367131</v>
       </c>
       <c r="F11" s="59">
         <f t="shared" ref="F11:F16" si="7">+D11-E11</f>
-        <v>3592770.9144324623</v>
+        <v>3170651.9767390676</v>
       </c>
       <c r="G11" s="60">
         <f t="shared" si="1"/>
-        <v>0.26097297562008082</v>
+        <v>0.22392338580835955</v>
       </c>
       <c r="H11" s="59">
         <f t="shared" si="4"/>
-        <v>121473878.14338556</v>
+        <v>130285722.19263719</v>
       </c>
       <c r="I11" s="60">
         <f t="shared" si="2"/>
-        <v>1.2526702829763878</v>
+        <v>1.3435403148501575</v>
       </c>
       <c r="J11" s="59">
         <f t="shared" si="5"/>
-        <v>5061411.5893077319</v>
+        <v>5428571.7580265496</v>
       </c>
       <c r="K11" s="59">
         <f t="shared" si="3"/>
-        <v>3771836.3438736238</v>
+        <v>3762883.0724015655</v>
       </c>
       <c r="L11" s="61" cm="1">
         <f t="array" ref="L11">+_xlfn.IFS(I11&gt;114%,H11*0.0125,I11&gt;109%,H11*0.01,I11&gt;104%,H11*0.0075,I11&gt;99%,H11*0.005,I11&lt;99%,H11*0)</f>
-        <v>1518423.4767923197</v>
+        <v>1628571.5274079649</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4244,23 +4244,23 @@
       </c>
       <c r="H12" s="4">
         <f t="shared" si="4"/>
-        <v>35243324.517293625</v>
+        <v>44054155.646617025</v>
       </c>
       <c r="I12" s="5">
         <f t="shared" si="2"/>
-        <v>1.1142054710316522</v>
+        <v>1.3927568387895652</v>
       </c>
       <c r="J12" s="4">
         <f t="shared" si="5"/>
-        <v>1468471.8548872343</v>
+        <v>1835589.8186090428</v>
       </c>
       <c r="K12" s="4">
         <f t="shared" si="3"/>
-        <v>1278344.3754805701</v>
+        <v>1214427.1567065415</v>
       </c>
       <c r="L12" s="63" cm="1">
         <f t="array" ref="L12">+_xlfn.IFS(I12&gt;114%,H12*0.02,I12&gt;109%,H12*0.015,I12&gt;104%,H12*0.0125,I12&gt;99%,H12*0.01,I12&lt;99%,H12*0)</f>
-        <v>528649.86775940435</v>
+        <v>881083.11293234047</v>
       </c>
       <c r="M12" s="27"/>
     </row>
@@ -4274,38 +4274,38 @@
       </c>
       <c r="D13" s="4">
         <f>IFERROR(+VLOOKUP(B13,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>39689592.681744099</v>
+        <v>38609317.055148289</v>
       </c>
       <c r="E13" s="4">
-        <v>38609317.055148289</v>
+        <v>35677866.984969728</v>
       </c>
       <c r="F13" s="4">
         <f t="shared" si="7"/>
-        <v>1080275.6265958101</v>
+        <v>2931450.0701785609</v>
       </c>
       <c r="G13" s="5">
         <f t="shared" si="1"/>
-        <v>0.30919586980090541</v>
+        <v>0.30078014317281015</v>
       </c>
       <c r="H13" s="4">
         <f t="shared" si="4"/>
-        <v>190510044.87237167</v>
+        <v>231655902.33088973</v>
       </c>
       <c r="I13" s="5">
         <f t="shared" si="2"/>
-        <v>1.4841401750443461</v>
+        <v>1.8046808590368608</v>
       </c>
       <c r="J13" s="4">
         <f t="shared" si="5"/>
-        <v>7937918.5363488197</v>
+        <v>9652329.2637870722</v>
       </c>
       <c r="K13" s="4">
         <f t="shared" si="3"/>
-        <v>4667069.6522568883</v>
+        <v>4487729.9509738348</v>
       </c>
       <c r="L13" s="63" cm="1">
         <f t="array" ref="L13">+_xlfn.IFS(I13&gt;114%,H13*0.0125,I13&gt;109%,H13*0.01,I13&gt;104%,H13*0.0075,I13&gt;99%,H13*0.005,I13&lt;99%,H13*0)</f>
-        <v>2381375.5609046458</v>
+        <v>2895698.7791361217</v>
       </c>
       <c r="M13" s="53" t="s">
         <v>61</v>
@@ -4324,34 +4324,34 @@
       </c>
       <c r="D14" s="4">
         <f>IFERROR(+VLOOKUP(B14,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>6663134.8062294191</v>
+        <v>5554944.6639294196</v>
       </c>
       <c r="E14" s="4">
-        <v>5554944.6639294196</v>
+        <v>4699575.8856638623</v>
       </c>
       <c r="F14" s="4">
         <f t="shared" si="7"/>
-        <v>1108190.1422999995</v>
+        <v>855368.77826555725</v>
       </c>
       <c r="G14" s="5">
         <f t="shared" si="1"/>
-        <v>0.15696779186946522</v>
+        <v>0.13086143732809949</v>
       </c>
       <c r="H14" s="4">
         <f t="shared" si="4"/>
-        <v>31983047.069901209</v>
+        <v>33329667.983576518</v>
       </c>
       <c r="I14" s="5">
         <f t="shared" si="2"/>
-        <v>0.75344540097343304</v>
+        <v>0.78516862396859699</v>
       </c>
       <c r="J14" s="4">
         <f t="shared" si="5"/>
-        <v>1332626.9612458837</v>
+        <v>1388736.1659823549</v>
       </c>
       <c r="K14" s="4">
         <f t="shared" si="3"/>
-        <v>1883469.6099339779</v>
+        <v>1844705.6365522791</v>
       </c>
       <c r="L14" s="63" cm="1">
         <f t="array" ref="L14">+_xlfn.IFS(I14&gt;109%,H14*0.015,I14&gt;104%,H14*0.0125,I14&gt;99%,H14*0.01,I14&lt;99%,H14*0)</f>
@@ -4369,38 +4369,38 @@
       </c>
       <c r="D15" s="4">
         <f>IFERROR(+VLOOKUP(B15,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>10196205.867152149</v>
+        <v>8252554.4917521486</v>
       </c>
       <c r="E15" s="4">
-        <v>8252554.4917521486</v>
+        <v>5825319.4707523696</v>
       </c>
       <c r="F15" s="4">
         <f t="shared" si="7"/>
-        <v>1943651.3754000003</v>
+        <v>2427235.020999779</v>
       </c>
       <c r="G15" s="5">
         <f t="shared" si="1"/>
-        <v>0.24019864027320303</v>
+        <v>0.1944107831409482</v>
       </c>
       <c r="H15" s="4">
         <f t="shared" si="4"/>
-        <v>48941788.162330315</v>
+        <v>49515326.950512893</v>
       </c>
       <c r="I15" s="5">
         <f t="shared" si="2"/>
-        <v>1.1529534733113747</v>
+        <v>1.1664646988456893</v>
       </c>
       <c r="J15" s="4">
         <f t="shared" si="5"/>
-        <v>2039241.1734304298</v>
+        <v>2063138.6229380372</v>
       </c>
       <c r="K15" s="4">
         <f t="shared" si="3"/>
-        <v>1697518.5014643606</v>
+        <v>1709825.1451611426</v>
       </c>
       <c r="L15" s="63" cm="1">
         <f t="array" ref="L15">+_xlfn.IFS(I15&gt;109%,H15*0.015,I15&gt;104%,H15*0.0125,I15&gt;99%,H15*0.01,I15&lt;99%,H15*0)</f>
-        <v>734126.82243495469</v>
+        <v>742729.90425769333</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4411,34 +4411,34 @@
       </c>
       <c r="D16" s="64">
         <f>+SUM(D11:D15)</f>
-        <v>89198350.576100498</v>
+        <v>81473462.517372221</v>
       </c>
       <c r="E16" s="65">
-        <v>81473462.517372221</v>
+        <v>72088756.671189263</v>
       </c>
       <c r="F16" s="64">
         <f t="shared" si="7"/>
-        <v>7724888.0587282777</v>
+        <v>9384705.8461829573</v>
       </c>
       <c r="G16" s="66">
         <f t="shared" si="1"/>
-        <v>0.26091697432810329</v>
+        <v>0.23832065493106369</v>
       </c>
       <c r="H16" s="64">
         <f t="shared" si="4"/>
-        <v>428152082.76528239</v>
+        <v>488840775.10423332</v>
       </c>
       <c r="I16" s="66">
         <f t="shared" si="2"/>
-        <v>1.2524014767748959</v>
+        <v>1.4299239295863821</v>
       </c>
       <c r="J16" s="64">
         <f t="shared" si="5"/>
-        <v>17839670.1152201</v>
+        <v>20368365.629343055</v>
       </c>
       <c r="K16" s="67">
         <f t="shared" si="3"/>
-        <v>13298238.483009422</v>
+        <v>13019570.961795364</v>
       </c>
       <c r="L16" s="68"/>
     </row>
@@ -4454,34 +4454,34 @@
       </c>
       <c r="D17" s="59">
         <f>IFERROR(+VLOOKUP(B17,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>4842984.6712837927</v>
+        <v>3831780.4656781647</v>
       </c>
       <c r="E17" s="59">
-        <v>3831780.4656781647</v>
+        <v>3490474.4748070529</v>
       </c>
       <c r="F17" s="59">
         <f t="shared" ref="F17:F40" si="8">+D17-E17</f>
-        <v>1011204.205605628</v>
+        <v>341305.99087111186</v>
       </c>
       <c r="G17" s="60">
         <f t="shared" si="1"/>
-        <v>0.1650753861222426</v>
+        <v>0.13060802022729012</v>
       </c>
       <c r="H17" s="59">
         <f t="shared" si="4"/>
-        <v>23246326.422162205</v>
+        <v>22990682.794068988</v>
       </c>
       <c r="I17" s="60">
         <f t="shared" si="2"/>
-        <v>0.79236185338676446</v>
+        <v>0.78364812136374074</v>
       </c>
       <c r="J17" s="59">
         <f t="shared" si="5"/>
-        <v>968596.93425675854</v>
+        <v>957945.11641954118</v>
       </c>
       <c r="K17" s="59">
         <f t="shared" si="3"/>
-        <v>1289212.2874324322</v>
+        <v>1275311.8833410919</v>
       </c>
       <c r="L17" s="61" cm="1">
         <f t="array" ref="L17">+_xlfn.IFS(I17&gt;114%,H17*0.02,I17&gt;109%,H17*0.015,I17&gt;104%,H17*0.0125,I17&gt;99%,H17*0.01,I17&lt;99%,H17*0)</f>
@@ -4498,34 +4498,34 @@
       </c>
       <c r="D18" s="4">
         <f>IFERROR(+VLOOKUP(B18,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>4538116.0675083203</v>
+        <v>3383340.6159000443</v>
       </c>
       <c r="E18" s="4">
-        <v>3383340.6159000443</v>
+        <v>2539362.2668490014</v>
       </c>
       <c r="F18" s="4">
         <f t="shared" si="8"/>
-        <v>1154775.451608276</v>
+        <v>843978.34905104293</v>
       </c>
       <c r="G18" s="5">
         <f t="shared" si="1"/>
-        <v>0.18181914680884448</v>
+        <v>0.13555318881132356</v>
       </c>
       <c r="H18" s="4">
         <f t="shared" si="4"/>
-        <v>21782957.124039941</v>
+        <v>20300043.695400268</v>
       </c>
       <c r="I18" s="5">
         <f t="shared" si="2"/>
-        <v>0.87273190468245365</v>
+        <v>0.81331913286794133</v>
       </c>
       <c r="J18" s="4">
         <f t="shared" si="5"/>
-        <v>907623.21350166411</v>
+        <v>845835.15397501108</v>
       </c>
       <c r="K18" s="4">
         <f t="shared" si="3"/>
-        <v>1074809.9911837727</v>
+        <v>1078808.264204998</v>
       </c>
       <c r="L18" s="63" cm="1">
         <f t="array" ref="L18">+_xlfn.IFS(I18&gt;114%,H18*0.02,I18&gt;109%,H18*0.015,I18&gt;104%,H18*0.0125,I18&gt;99%,H18*0.01,I18&lt;99%,H18*0)</f>
@@ -4542,34 +4542,34 @@
       </c>
       <c r="D19" s="4">
         <f>IFERROR(+VLOOKUP(B19,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>5255755.4759214995</v>
+        <v>4172472.7522102422</v>
       </c>
       <c r="E19" s="4">
-        <v>4172472.7522102422</v>
+        <v>3126324.9965506792</v>
       </c>
       <c r="F19" s="4">
         <f t="shared" si="8"/>
-        <v>1083282.7237112573</v>
+        <v>1046147.755659563</v>
       </c>
       <c r="G19" s="5">
         <f t="shared" si="1"/>
-        <v>0.20326513458940426</v>
+        <v>0.16136942432618312</v>
       </c>
       <c r="H19" s="4">
         <f t="shared" si="4"/>
-        <v>25227626.284423195</v>
+        <v>25034836.513261452</v>
       </c>
       <c r="I19" s="5">
         <f t="shared" si="2"/>
-        <v>0.97567264602914039</v>
+        <v>0.96821654595709861</v>
       </c>
       <c r="J19" s="4">
         <f t="shared" si="5"/>
-        <v>1051151.0951842999</v>
+        <v>1043118.1880525606</v>
       </c>
       <c r="K19" s="4">
         <f t="shared" si="3"/>
-        <v>1084257.6152409737</v>
+        <v>1084208.8706644881</v>
       </c>
       <c r="L19" s="63" cm="1">
         <f t="array" ref="L19">+_xlfn.IFS(I19&gt;114%,H19*0.02,I19&gt;109%,H19*0.015,I19&gt;104%,H19*0.0125,I19&gt;99%,H19*0.01,I19&lt;99%,H19*0)</f>
@@ -4586,38 +4586,38 @@
       </c>
       <c r="D20" s="4">
         <f>IFERROR(+VLOOKUP(B20,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>9037854.5756811257</v>
+        <v>8068602.606727235</v>
       </c>
       <c r="E20" s="4">
-        <v>8068602.606727235</v>
+        <v>5313079.7996425815</v>
       </c>
       <c r="F20" s="4">
         <f t="shared" si="8"/>
-        <v>969251.96895389073</v>
+        <v>2755522.8070846535</v>
       </c>
       <c r="G20" s="5">
         <f t="shared" si="1"/>
-        <v>0.2693996528474501</v>
+        <v>0.24050826698022318</v>
       </c>
       <c r="H20" s="4">
         <f t="shared" si="4"/>
-        <v>43381701.963269398</v>
+        <v>48411615.64036341</v>
       </c>
       <c r="I20" s="5">
         <f t="shared" si="2"/>
-        <v>1.2931183336677603</v>
+        <v>1.4430496018813392</v>
       </c>
       <c r="J20" s="4">
         <f t="shared" si="5"/>
-        <v>1807570.9151362251</v>
+        <v>2017150.6516818088</v>
       </c>
       <c r="K20" s="4">
         <f t="shared" si="3"/>
-        <v>1290014.4960167827</v>
+        <v>1273976.3696636383</v>
       </c>
       <c r="L20" s="63" cm="1">
         <f t="array" ref="L20">+_xlfn.IFS(I20&gt;114%,H20*0.02,I20&gt;109%,H20*0.015,I20&gt;104%,H20*0.0125,I20&gt;99%,H20*0.01,I20&lt;99%,H20*0)</f>
-        <v>867634.03926538792</v>
+        <v>968232.31280726823</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4630,38 +4630,38 @@
       </c>
       <c r="D21" s="4">
         <f>IFERROR(+VLOOKUP(B21,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>5595341.8938343767</v>
+        <v>4521737.6382463202</v>
       </c>
       <c r="E21" s="4">
-        <v>4521737.6382463202</v>
+        <v>3621062.6775038806</v>
       </c>
       <c r="F21" s="4">
         <f t="shared" ref="F21:F23" si="9">+D21-E21</f>
-        <v>1073604.2555880565</v>
+        <v>900674.96074243961</v>
       </c>
       <c r="G21" s="5">
         <f t="shared" si="1"/>
-        <v>0.2197827718053561</v>
+        <v>0.17761202985745514</v>
       </c>
       <c r="H21" s="4">
         <f t="shared" si="4"/>
-        <v>26857641.090405006</v>
+        <v>27130425.829477921</v>
       </c>
       <c r="I21" s="5">
         <f t="shared" si="2"/>
-        <v>1.0549573046657093</v>
+        <v>1.0656721791447308</v>
       </c>
       <c r="J21" s="4">
         <f t="shared" si="5"/>
-        <v>1119068.3787668752</v>
+        <v>1130434.40956158</v>
       </c>
       <c r="K21" s="4">
         <f t="shared" si="3"/>
-        <v>1045429.9003245066</v>
+        <v>1046838.618087684</v>
       </c>
       <c r="L21" s="63" cm="1">
         <f t="array" ref="L21">+_xlfn.IFS(I21&gt;114%,H21*0.02,I21&gt;109%,H21*0.015,I21&gt;104%,H21*0.0125,I21&gt;99%,H21*0.01,I21&lt;99%,H21*0)</f>
-        <v>335720.51363006257</v>
+        <v>339130.32286847406</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4674,38 +4674,38 @@
       </c>
       <c r="D22" s="4">
         <f>IFERROR(+VLOOKUP(B22,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>8516814.03087065</v>
+        <v>6604601.1312453747</v>
       </c>
       <c r="E22" s="4">
-        <v>6604601.1312453747</v>
+        <v>4525419.7648018571</v>
       </c>
       <c r="F22" s="4">
         <f t="shared" si="9"/>
-        <v>1912212.8996252753</v>
+        <v>2079181.3664435176</v>
       </c>
       <c r="G22" s="5">
         <f t="shared" si="1"/>
-        <v>0.26830619320450694</v>
+        <v>0.20806552552815036</v>
       </c>
       <c r="H22" s="4">
         <f t="shared" si="4"/>
-        <v>40880707.348179117</v>
+        <v>39627606.787472248</v>
       </c>
       <c r="I22" s="5">
         <f t="shared" si="2"/>
-        <v>1.2878697273816331</v>
+        <v>1.2483931531689021</v>
       </c>
       <c r="J22" s="4">
         <f t="shared" si="5"/>
-        <v>1703362.8061741299</v>
+        <v>1651150.2828113437</v>
       </c>
       <c r="K22" s="4">
         <f t="shared" si="3"/>
-        <v>1222425.061533124</v>
+        <v>1256914.4534377314</v>
       </c>
       <c r="L22" s="63" cm="1">
         <f t="array" ref="L22">+_xlfn.IFS(I22&gt;114%,H22*0.02,I22&gt;109%,H22*0.015,I22&gt;104%,H22*0.0125,I22&gt;99%,H22*0.01,I22&lt;99%,H22*0)</f>
-        <v>817614.14696358237</v>
+        <v>792552.13574944495</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4718,38 +4718,38 @@
       </c>
       <c r="D23" s="4">
         <f>IFERROR(+VLOOKUP(B23,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>5822405.6030015703</v>
+        <v>5027241.122842595</v>
       </c>
       <c r="E23" s="4">
-        <v>5027241.122842595</v>
+        <v>3880349.2779353959</v>
       </c>
       <c r="F23" s="4">
         <f t="shared" si="9"/>
-        <v>795164.48015897535</v>
+        <v>1146891.844907199</v>
       </c>
       <c r="G23" s="5">
         <f t="shared" si="1"/>
-        <v>0.21221814455355015</v>
+        <v>0.18323556551315615</v>
       </c>
       <c r="H23" s="4">
         <f t="shared" si="4"/>
-        <v>27947546.894407541</v>
+        <v>30163446.73705557</v>
       </c>
       <c r="I23" s="5">
         <f t="shared" si="2"/>
-        <v>1.0186470938570409</v>
+        <v>1.0994133930789369</v>
       </c>
       <c r="J23" s="4">
         <f t="shared" si="5"/>
-        <v>1164481.1206003141</v>
+        <v>1256810.2807106487</v>
       </c>
       <c r="K23" s="4">
         <f t="shared" si="3"/>
-        <v>1137554.7698420228</v>
+        <v>1120435.2553578704</v>
       </c>
       <c r="L23" s="63" cm="1">
         <f t="array" ref="L23">+_xlfn.IFS(I23&gt;114%,H23*0.02,I23&gt;109%,H23*0.015,I23&gt;104%,H23*0.0125,I23&gt;99%,H23*0.01,I23&lt;99%,H23*0)</f>
-        <v>279475.4689440754</v>
+        <v>452451.70105583355</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4762,38 +4762,38 @@
       </c>
       <c r="D24" s="4">
         <f>IFERROR(+VLOOKUP(B24,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>6909391.5039921645</v>
+        <v>4507114.506957056</v>
       </c>
       <c r="E24" s="4">
-        <v>4507114.506957056</v>
+        <v>3150944.560423614</v>
       </c>
       <c r="F24" s="4">
         <f t="shared" si="8"/>
-        <v>2402276.9970351085</v>
+        <v>1356169.946533442</v>
       </c>
       <c r="G24" s="5">
         <f t="shared" si="1"/>
-        <v>0.20628710091961586</v>
+        <v>0.13456461174847464</v>
       </c>
       <c r="H24" s="4">
         <f t="shared" si="4"/>
-        <v>33165079.21916239</v>
+        <v>27042687.041742336</v>
       </c>
       <c r="I24" s="5">
         <f t="shared" si="2"/>
-        <v>0.99017808441415622</v>
+        <v>0.80738767049084792</v>
       </c>
       <c r="J24" s="4">
         <f t="shared" si="5"/>
-        <v>1381878.3007984329</v>
+        <v>1126778.626739264</v>
       </c>
       <c r="K24" s="4">
         <f t="shared" si="3"/>
-        <v>1399192.8155793599</v>
+        <v>1449347.0246521472</v>
       </c>
       <c r="L24" s="63" cm="1">
         <f t="array" ref="L24">+_xlfn.IFS(I24&gt;114%,H24*0.02,I24&gt;109%,H24*0.015,I24&gt;104%,H24*0.0125,I24&gt;99%,H24*0.01,I24&lt;99%,H24*0)</f>
-        <v>331650.79219162388</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4806,34 +4806,34 @@
       </c>
       <c r="D25" s="4">
         <f>IFERROR(+VLOOKUP(B25,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>8825883.2392010316</v>
+        <v>7398936.6723073218</v>
       </c>
       <c r="E25" s="4">
-        <v>7398936.6723073218</v>
+        <v>7402539.5016198214</v>
       </c>
       <c r="F25" s="4">
         <f t="shared" si="8"/>
-        <v>1426946.5668937098</v>
+        <v>-3602.8293124996126</v>
       </c>
       <c r="G25" s="5">
         <f t="shared" si="1"/>
-        <v>0.16324592497544999</v>
+        <v>0.13685273509407175</v>
       </c>
       <c r="H25" s="4">
         <f t="shared" si="4"/>
-        <v>42364239.548164949</v>
+        <v>44393620.033843935</v>
       </c>
       <c r="I25" s="5">
         <f t="shared" si="2"/>
-        <v>0.78358043988215986</v>
+        <v>0.82111641056443052</v>
       </c>
       <c r="J25" s="4">
         <f t="shared" si="5"/>
-        <v>1765176.6478402063</v>
+        <v>1849734.1680768305</v>
       </c>
       <c r="K25" s="4">
         <f t="shared" si="3"/>
-        <v>2381003.6645157356</v>
+        <v>2333300.8096346343</v>
       </c>
       <c r="L25" s="63" cm="1">
         <f t="array" ref="L25">+_xlfn.IFS(I25&gt;109%,H25*0.015,I25&gt;104%,H25*0.0125,I25&gt;99%,H25*0.01,I25&lt;99%,H25*0)</f>
@@ -4848,34 +4848,34 @@
       </c>
       <c r="D26" s="67">
         <f>+SUM(D17:D25)</f>
-        <v>59344547.061294533</v>
+        <v>47515827.512114353</v>
       </c>
       <c r="E26" s="65">
-        <v>47515827.512114353</v>
+        <v>37049557.32013388</v>
       </c>
       <c r="F26" s="67">
         <f>+D26-E26</f>
-        <v>11828719.54918018</v>
+        <v>10466270.191980474</v>
       </c>
       <c r="G26" s="66">
         <f t="shared" si="1"/>
-        <v>0.20757196754299401</v>
+        <v>0.16619814784222828</v>
       </c>
       <c r="H26" s="64">
         <f t="shared" si="4"/>
-        <v>284853825.89421374</v>
+        <v>285094965.07268614</v>
       </c>
       <c r="I26" s="66">
         <f t="shared" si="2"/>
-        <v>0.99634544420637117</v>
+        <v>0.99718888705336972</v>
       </c>
       <c r="J26" s="64">
         <f t="shared" si="5"/>
-        <v>11868909.412258906</v>
+        <v>11878956.878028588</v>
       </c>
       <c r="K26" s="67">
         <f t="shared" si="3"/>
-        <v>11923900.60166871</v>
+        <v>11919141.549044285</v>
       </c>
       <c r="L26" s="68"/>
     </row>
@@ -4891,38 +4891,38 @@
       </c>
       <c r="D27" s="59">
         <f>IFERROR(+VLOOKUP(B27,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>17555809.912466466</v>
+        <v>14993819.966923174</v>
       </c>
       <c r="E27" s="59">
-        <v>14993819.966923174</v>
+        <v>7197381.3632933144</v>
       </c>
       <c r="F27" s="59">
         <f t="shared" si="8"/>
-        <v>2561989.9455432929</v>
+        <v>7796438.6036298592</v>
       </c>
       <c r="G27" s="60">
         <f t="shared" si="1"/>
-        <v>0.21415348213558646</v>
+        <v>0.1829012032165232</v>
       </c>
       <c r="H27" s="59">
         <f t="shared" si="4"/>
-        <v>84267887.579839051</v>
+        <v>89962919.801539034</v>
       </c>
       <c r="I27" s="60">
         <f t="shared" si="2"/>
-        <v>1.0279367142508151</v>
+        <v>1.0974072192991391</v>
       </c>
       <c r="J27" s="59">
         <f t="shared" si="5"/>
-        <v>3511161.9824932935</v>
+        <v>3748454.9917307934</v>
       </c>
       <c r="K27" s="59">
         <f t="shared" si="3"/>
-        <v>3390625.7940807124</v>
+        <v>3349194.0016538412</v>
       </c>
       <c r="L27" s="61" cm="1">
         <f t="array" ref="L27">+_xlfn.IFS(I27&gt;114%,H27*0.0125,I27&gt;109%,H27*0.01,I27&gt;104%,H27*0.0075,I27&gt;99%,H27*0.005,I27&lt;99%,H27*0)</f>
-        <v>421339.43789919524</v>
+        <v>899629.19801539031</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4935,34 +4935,34 @@
       </c>
       <c r="D28" s="4">
         <f>IFERROR(+VLOOKUP(B28,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>2883607.9842428509</v>
+        <v>2246997.9859188953</v>
       </c>
       <c r="E28" s="4">
-        <v>2246997.9859188953</v>
+        <v>1662817.6962441357</v>
       </c>
       <c r="F28" s="4">
         <f t="shared" si="8"/>
-        <v>636609.99832395557</v>
+        <v>584180.28967475961</v>
       </c>
       <c r="G28" s="5">
         <f t="shared" si="1"/>
-        <v>0.13731466591632624</v>
+        <v>0.10699990409137597</v>
       </c>
       <c r="H28" s="4">
         <f t="shared" si="4"/>
-        <v>13841318.324365683</v>
+        <v>13481987.915513372</v>
       </c>
       <c r="I28" s="5">
         <f t="shared" si="2"/>
-        <v>0.65911039639836588</v>
+        <v>0.64199942454825576</v>
       </c>
       <c r="J28" s="4">
         <f t="shared" si="5"/>
-        <v>576721.59684857016</v>
+        <v>561749.49647972384</v>
       </c>
       <c r="K28" s="4">
         <f t="shared" si="3"/>
-        <v>953494.31661879737</v>
+        <v>937650.10070405528</v>
       </c>
       <c r="L28" s="63" cm="1">
         <f t="array" ref="L28">+_xlfn.IFS(I28&gt;114%,H28*0.02,I28&gt;109%,H28*0.015,I28&gt;104%,H28*0.0125,I28&gt;99%,H28*0.01,I28&lt;99%,H28*0)</f>
@@ -4979,34 +4979,34 @@
       </c>
       <c r="D29" s="4">
         <f>IFERROR(+VLOOKUP(B29,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>3996158.8131728824</v>
+        <v>2863924.6281832345</v>
       </c>
       <c r="E29" s="4">
-        <v>2863924.6281832345</v>
+        <v>2237337.654012111</v>
       </c>
       <c r="F29" s="4">
         <f t="shared" si="8"/>
-        <v>1132234.1849896479</v>
+        <v>626586.97417112347</v>
       </c>
       <c r="G29" s="5">
         <f t="shared" si="1"/>
-        <v>0.15525273461512304</v>
+        <v>0.11126487986197331</v>
       </c>
       <c r="H29" s="4">
         <f t="shared" si="4"/>
-        <v>19181562.303229839</v>
+        <v>17183547.769099407</v>
       </c>
       <c r="I29" s="5">
         <f t="shared" si="2"/>
-        <v>0.74521312615259072</v>
+        <v>0.66758927917183986</v>
       </c>
       <c r="J29" s="4">
         <f t="shared" si="5"/>
-        <v>799231.76263457653</v>
+        <v>715981.15704580862</v>
       </c>
       <c r="K29" s="4">
         <f t="shared" si="3"/>
-        <v>1144396.9045698482</v>
+        <v>1143788.7685908382</v>
       </c>
       <c r="L29" s="63" cm="1">
         <f t="array" ref="L29">+_xlfn.IFS(I29&gt;114%,H29*0.02,I29&gt;109%,H29*0.015,I29&gt;104%,H29*0.0125,I29&gt;99%,H29*0.01,I29&lt;99%,H29*0)</f>
@@ -5024,34 +5024,34 @@
       </c>
       <c r="D30" s="4">
         <f>IFERROR(+VLOOKUP(B30,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>4975553.6144345868</v>
+        <v>4669958.7290065279</v>
       </c>
       <c r="E30" s="4">
-        <v>4669958.7290065279</v>
+        <v>2806120.8392654946</v>
       </c>
       <c r="F30" s="4">
         <f t="shared" si="8"/>
-        <v>305594.88542805891</v>
+        <v>1863837.8897410333</v>
       </c>
       <c r="G30" s="5">
         <f t="shared" si="1"/>
-        <v>0.13013697386454762</v>
+        <v>0.12214405554833929</v>
       </c>
       <c r="H30" s="4">
         <f t="shared" si="4"/>
-        <v>23882657.34928602</v>
+        <v>28019752.374039166</v>
       </c>
       <c r="I30" s="5">
         <f t="shared" si="2"/>
-        <v>0.62465747454982867</v>
+        <v>0.73286433329003575</v>
       </c>
       <c r="J30" s="4">
         <f t="shared" si="5"/>
-        <v>995110.72288691741</v>
+        <v>1167489.682251632</v>
       </c>
       <c r="K30" s="4">
         <f t="shared" si="3"/>
-        <v>1750402.710404794</v>
+        <v>1678162.3191559571</v>
       </c>
       <c r="L30" s="63" cm="1">
         <f t="array" ref="L30">+_xlfn.IFS(I30&gt;114%,H30*0.02,I30&gt;109%,H30*0.015,I30&gt;104%,H30*0.0125,I30&gt;99%,H30*0.01,I30&lt;99%,H30*0)</f>
@@ -5069,38 +5069,38 @@
       </c>
       <c r="D31" s="4">
         <f>IFERROR(+VLOOKUP(B31,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>4865926.9418352479</v>
+        <v>4425690.3579718489</v>
       </c>
       <c r="E31" s="4">
-        <v>4425690.3579718489</v>
+        <v>3265458.2459612871</v>
       </c>
       <c r="F31" s="4">
         <f t="shared" si="8"/>
-        <v>440236.58386339899</v>
+        <v>1160232.1120105619</v>
       </c>
       <c r="G31" s="5">
         <f t="shared" si="1"/>
-        <v>0.19145697728077624</v>
+        <v>0.17413522817882371</v>
       </c>
       <c r="H31" s="4">
         <f t="shared" si="4"/>
-        <v>23356449.320809193</v>
+        <v>26554142.147831094</v>
       </c>
       <c r="I31" s="5">
         <f t="shared" si="2"/>
-        <v>0.91899349094772598</v>
+        <v>1.0448113690729421</v>
       </c>
       <c r="J31" s="4">
         <f t="shared" si="5"/>
-        <v>973185.38836704963</v>
+        <v>1106422.5894929622</v>
       </c>
       <c r="K31" s="4">
         <f t="shared" si="3"/>
-        <v>1081543.3188507764</v>
+        <v>1049477.9821014076</v>
       </c>
       <c r="L31" s="63" cm="1">
         <f t="array" ref="L31">+_xlfn.IFS(I31&gt;114%,H31*0.02,I31&gt;109%,H31*0.015,I31&gt;104%,H31*0.0125,I31&gt;99%,H31*0.01,I31&lt;99%,H31*0)</f>
-        <v>0</v>
+        <v>331926.77684788872</v>
       </c>
       <c r="M31" s="27"/>
     </row>
@@ -5114,34 +5114,34 @@
       </c>
       <c r="D32" s="4">
         <f>IFERROR(+VLOOKUP(B32,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>2958594.3353685732</v>
+        <v>2292259.0263364343</v>
       </c>
       <c r="E32" s="4">
-        <v>2292259.0263364343</v>
+        <v>1556471.8667402903</v>
       </c>
       <c r="F32" s="4">
         <f t="shared" si="8"/>
-        <v>666335.3090321389</v>
+        <v>735787.15959614399</v>
       </c>
       <c r="G32" s="5">
         <f t="shared" si="1"/>
-        <v>0.11740453711780052</v>
+        <v>9.0962659775255333E-2</v>
       </c>
       <c r="H32" s="4">
         <f t="shared" si="4"/>
-        <v>14201252.80976915</v>
+        <v>13753554.158018606</v>
       </c>
       <c r="I32" s="5">
         <f t="shared" si="2"/>
-        <v>0.56354177816544249</v>
+        <v>0.54577595865153194</v>
       </c>
       <c r="J32" s="4">
         <f t="shared" si="5"/>
-        <v>591718.86707371462</v>
+        <v>573064.75658410857</v>
       </c>
       <c r="K32" s="4">
         <f t="shared" si="3"/>
-        <v>1170600.2981384962</v>
+        <v>1145387.0486831781</v>
       </c>
       <c r="L32" s="63" cm="1">
         <f t="array" ref="L32">+_xlfn.IFS(I32&gt;114%,H32*0.02,I32&gt;109%,H32*0.015,I32&gt;104%,H32*0.0125,I32&gt;99%,H32*0.01,I32&lt;99%,H32*0)</f>
@@ -5159,34 +5159,34 @@
       </c>
       <c r="D33" s="4">
         <f>IFERROR(+VLOOKUP(B33,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>3089173.5689832573</v>
+        <v>2299134.4748592312</v>
       </c>
       <c r="E33" s="4">
-        <v>2299134.4748592312</v>
+        <v>1905347.2963424551</v>
       </c>
       <c r="F33" s="4">
         <f t="shared" si="8"/>
-        <v>790039.09412402613</v>
+        <v>393787.17851677607</v>
       </c>
       <c r="G33" s="5">
         <f t="shared" si="1"/>
-        <v>0.1165868859004692</v>
+        <v>8.6770433161019039E-2</v>
       </c>
       <c r="H33" s="4">
         <f t="shared" si="4"/>
-        <v>14828033.131119635</v>
+        <v>13794806.849155387</v>
       </c>
       <c r="I33" s="5">
         <f t="shared" si="2"/>
-        <v>0.55961705232225212</v>
+        <v>0.52062259896611418</v>
       </c>
       <c r="J33" s="4">
         <f t="shared" si="5"/>
-        <v>617834.71379665146</v>
+        <v>574783.61871480779</v>
       </c>
       <c r="K33" s="4">
         <f t="shared" si="3"/>
-        <v>1231977.706895618</v>
+        <v>1209880.7762570386</v>
       </c>
       <c r="L33" s="63" cm="1">
         <f t="array" ref="L33">+_xlfn.IFS(I33&gt;114%,H33*0.02,I33&gt;109%,H33*0.015,I33&gt;104%,H33*0.0125,I33&gt;99%,H33*0.01,I33&lt;99%,H33*0)</f>
@@ -5203,34 +5203,34 @@
       </c>
       <c r="D34" s="4">
         <f>IFERROR(+VLOOKUP(B34,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>2098536.1960838647</v>
+        <v>1808557.8257932956</v>
       </c>
       <c r="E34" s="4">
-        <v>1808557.8257932956</v>
+        <v>1342266.2312651528</v>
       </c>
       <c r="F34" s="4">
         <f t="shared" si="8"/>
-        <v>289978.37029056903</v>
+        <v>466291.59452814283</v>
       </c>
       <c r="G34" s="5">
         <f t="shared" si="1"/>
-        <v>9.9930295051612605E-2</v>
+        <v>8.6121801228252179E-2</v>
       </c>
       <c r="H34" s="4">
         <f t="shared" si="4"/>
-        <v>10072973.741202552</v>
+        <v>10851346.954759773</v>
       </c>
       <c r="I34" s="5">
         <f t="shared" si="2"/>
-        <v>0.47966541624774056</v>
+        <v>0.51673080736951305</v>
       </c>
       <c r="J34" s="4">
         <f t="shared" si="5"/>
-        <v>419707.23921677296</v>
+        <v>452139.45644832391</v>
       </c>
       <c r="K34" s="4">
         <f t="shared" si="3"/>
-        <v>994813.88441663864</v>
+        <v>959572.10871033522</v>
       </c>
       <c r="L34" s="63" cm="1">
         <f t="array" ref="L34">+_xlfn.IFS(I34&gt;114%,H34*0.02,I34&gt;109%,H34*0.015,I34&gt;104%,H34*0.0125,I34&gt;99%,H34*0.01,I34&lt;99%,H34*0)</f>
@@ -5247,34 +5247,34 @@
       </c>
       <c r="D35" s="4">
         <f>IFERROR(+VLOOKUP(B35,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>1626463.4655310514</v>
+        <v>1134886.8601273343</v>
       </c>
       <c r="E35" s="4">
-        <v>1134886.8601273343</v>
+        <v>920475.59202497394</v>
       </c>
       <c r="F35" s="4">
         <f t="shared" si="8"/>
-        <v>491576.60540371714</v>
+        <v>214411.26810236031</v>
       </c>
       <c r="G35" s="5">
         <f t="shared" si="1"/>
-        <v>6.5960348506016314E-2</v>
+        <v>4.6024724437604296E-2</v>
       </c>
       <c r="H35" s="4">
         <f t="shared" si="4"/>
-        <v>7807024.6345490459</v>
+        <v>6809321.160764005</v>
       </c>
       <c r="I35" s="5">
         <f t="shared" si="2"/>
-        <v>0.31660967282887825</v>
+        <v>0.27614834662562576</v>
       </c>
       <c r="J35" s="4">
         <f t="shared" si="5"/>
-        <v>325292.69310621027</v>
+        <v>283721.71503183356</v>
       </c>
       <c r="K35" s="4">
         <f t="shared" si="3"/>
-        <v>1212196.659708892</v>
+        <v>1176165.6569936334</v>
       </c>
       <c r="L35" s="63" cm="1">
         <f t="array" ref="L35">+_xlfn.IFS(I35&gt;114%,H35*0.02,I35&gt;109%,H35*0.015,I35&gt;104%,H35*0.0125,I35&gt;99%,H35*0.01,I35&lt;99%,H35*0)</f>
@@ -5291,34 +5291,34 @@
       </c>
       <c r="D36" s="4">
         <f>IFERROR(+VLOOKUP(B36,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>3109025.2196221473</v>
+        <v>2633216.6305364068</v>
       </c>
       <c r="E36" s="4">
-        <v>2633216.6305364068</v>
+        <v>1931060.2247250369</v>
       </c>
       <c r="F36" s="4">
         <f t="shared" si="8"/>
-        <v>475808.5890857405</v>
+        <v>702156.40581136988</v>
       </c>
       <c r="G36" s="5">
         <f t="shared" si="1"/>
-        <v>0.12320290151068544</v>
+        <v>0.1043477959396238</v>
       </c>
       <c r="H36" s="4">
         <f t="shared" si="4"/>
-        <v>14923321.054186307</v>
+        <v>15799299.78321844</v>
       </c>
       <c r="I36" s="5">
         <f t="shared" si="2"/>
-        <v>0.59137392725129012</v>
+        <v>0.62608677563774284</v>
       </c>
       <c r="J36" s="4">
         <f t="shared" si="5"/>
-        <v>621805.04392442945</v>
+        <v>658304.15763410169</v>
       </c>
       <c r="K36" s="4">
         <f t="shared" si="3"/>
-        <v>1164524.9884409397</v>
+        <v>1130089.1684731797</v>
       </c>
       <c r="L36" s="63" cm="1">
         <f t="array" ref="L36">+_xlfn.IFS(I36&gt;114%,H36*0.02,I36&gt;109%,H36*0.015,I36&gt;104%,H36*0.0125,I36&gt;99%,H36*0.01,I36&lt;99%,H36*0)</f>
@@ -5335,34 +5335,34 @@
       </c>
       <c r="D37" s="4">
         <f>IFERROR(+VLOOKUP(B37,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>17061083.040882383</v>
+        <v>17081843.43377829</v>
       </c>
       <c r="E37" s="4">
-        <v>17081843.43377829</v>
+        <v>16463801.298558187</v>
       </c>
       <c r="F37" s="4">
         <f t="shared" si="8"/>
-        <v>-20760.392895907164</v>
+        <v>618042.13522010297</v>
       </c>
       <c r="G37" s="5">
         <f t="shared" si="1"/>
-        <v>0.13983147558233025</v>
+        <v>0.14000162634974328</v>
       </c>
       <c r="H37" s="4">
         <f t="shared" si="4"/>
-        <v>81893198.596235424</v>
+        <v>102491060.60266975</v>
       </c>
       <c r="I37" s="5">
         <f t="shared" si="2"/>
-        <v>0.67119108279518513</v>
+        <v>0.84000975809845979</v>
       </c>
       <c r="J37" s="4">
         <f t="shared" si="5"/>
-        <v>3412216.6081764763</v>
+        <v>4270460.8584445724</v>
       </c>
       <c r="K37" s="4">
         <f t="shared" si="3"/>
-        <v>5523719.3136377698</v>
+        <v>5246495.3283110857</v>
       </c>
       <c r="L37" s="63" cm="1">
         <f t="array" ref="L37">+_xlfn.IFS(I37&gt;114%,H37*0.0125,I37&gt;109%,H37*0.01,I37&gt;104%,H37*0.0075,I37&gt;99%,H37*0.005,I37&lt;99%,H37*0)</f>
@@ -5379,34 +5379,34 @@
       </c>
       <c r="D38" s="4">
         <f>IFERROR(+VLOOKUP(B38,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>746511.00490000006</v>
+        <v>280769.63740000001</v>
       </c>
       <c r="E38" s="4">
-        <v>280769.63740000001</v>
+        <v>149294.68419999999</v>
       </c>
       <c r="F38" s="4">
         <f t="shared" ref="F38" si="10">+D38-E38</f>
-        <v>465741.36750000005</v>
+        <v>131474.95320000002</v>
       </c>
       <c r="G38" s="5">
         <f t="shared" si="1"/>
-        <v>2.0910672406162466E-2</v>
+        <v>7.8646957254901971E-3</v>
       </c>
       <c r="H38" s="4">
         <f t="shared" si="4"/>
-        <v>3583252.8235200006</v>
+        <v>1684617.8244</v>
       </c>
       <c r="I38" s="5">
         <f t="shared" si="2"/>
-        <v>0.10037122754957985</v>
+        <v>4.7188174352941176E-2</v>
       </c>
       <c r="J38" s="4">
         <f t="shared" si="5"/>
-        <v>149302.20098000002</v>
+        <v>70192.409350000002</v>
       </c>
       <c r="K38" s="4">
         <f t="shared" si="3"/>
-        <v>1839657.3155315788</v>
+        <v>1770961.51813</v>
       </c>
       <c r="L38" s="63" cm="1">
         <f t="array" ref="L38">+_xlfn.IFS(I38&gt;109%,H38*0.015,I38&gt;104%,H38*0.0125,I38&gt;99%,H38*0.01,I38&lt;99%,H38*0)</f>
@@ -5423,38 +5423,38 @@
       </c>
       <c r="D39" s="4">
         <f>IFERROR(+VLOOKUP(B39,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>6953389.0972305397</v>
+        <v>6167950.3247244535</v>
       </c>
       <c r="E39" s="4">
-        <v>6167950.3247244535</v>
+        <v>4713478.3902184051</v>
       </c>
       <c r="F39" s="4">
         <f t="shared" si="8"/>
-        <v>785438.77250608616</v>
+        <v>1454471.9345060484</v>
       </c>
       <c r="G39" s="5">
         <f t="shared" si="1"/>
-        <v>0.19122981493305272</v>
+        <v>0.16962893671276072</v>
       </c>
       <c r="H39" s="4">
         <f t="shared" si="4"/>
-        <v>33376267.666706588</v>
+        <v>37007701.948346719</v>
       </c>
       <c r="I39" s="5">
         <f t="shared" si="2"/>
-        <v>0.91790311167865302</v>
+        <v>1.0177736202765644</v>
       </c>
       <c r="J39" s="4">
         <f t="shared" si="5"/>
-        <v>1390677.8194461078</v>
+        <v>1541987.5811811134</v>
       </c>
       <c r="K39" s="4">
         <f t="shared" si="3"/>
-        <v>1547791.5074615506</v>
+        <v>1509673.8707137774</v>
       </c>
       <c r="L39" s="63" cm="1">
         <f t="array" ref="L39">+_xlfn.IFS(I39&gt;114%,H39*0.02,I39&gt;109%,H39*0.015,I39&gt;104%,H39*0.0125,I39&gt;99%,H39*0.01,I39&lt;99%,H39*0)</f>
-        <v>0</v>
+        <v>370077.01948346721</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -5465,34 +5465,34 @@
       </c>
       <c r="D40" s="67">
         <f>+SUM(D27:D39)</f>
-        <v>71919833.194753855</v>
+        <v>62899009.881559134</v>
       </c>
       <c r="E40" s="65">
-        <v>62899009.881559134</v>
+        <v>46151311.382850848</v>
       </c>
       <c r="F40" s="67">
         <f t="shared" si="8"/>
-        <v>9020823.3131947219</v>
+        <v>16747698.498708285</v>
       </c>
       <c r="G40" s="66">
         <f t="shared" si="1"/>
-        <v>0.14128828734254617</v>
+        <v>0.12356665730358822</v>
       </c>
       <c r="H40" s="64">
         <f t="shared" si="4"/>
-        <v>345215199.33481848</v>
+        <v>377394059.2893548</v>
       </c>
       <c r="I40" s="66">
         <f t="shared" si="2"/>
-        <v>0.67818377924422157</v>
+        <v>0.74139994382152929</v>
       </c>
       <c r="J40" s="64">
         <f t="shared" si="5"/>
-        <v>14383966.638950771</v>
+        <v>15724752.470389783</v>
       </c>
       <c r="K40" s="67">
         <f t="shared" si="3"/>
-        <v>23005744.718756411</v>
+        <v>22306498.648478329</v>
       </c>
       <c r="L40" s="68"/>
     </row>
@@ -5506,34 +5506,34 @@
       </c>
       <c r="D41" s="81">
         <f>+D40+D26+D10+D16</f>
-        <v>280805467.60214281</v>
+        <v>240577000.14348808</v>
       </c>
       <c r="E41" s="82">
-        <v>240577000.14348808</v>
+        <v>191246594.85709113</v>
       </c>
       <c r="F41" s="81">
         <f>+D41-E41</f>
-        <v>40228467.458654732</v>
+        <v>49330405.28639695</v>
       </c>
       <c r="G41" s="83">
         <f t="shared" si="1"/>
-        <v>0.20351656306191793</v>
+        <v>0.17436058008072636</v>
       </c>
       <c r="H41" s="81">
         <f t="shared" si="4"/>
-        <v>1347866244.4902854</v>
+        <v>1443462000.8609285</v>
       </c>
       <c r="I41" s="83">
         <f t="shared" si="2"/>
-        <v>0.97687950269720591</v>
+        <v>1.046163480484358</v>
       </c>
       <c r="J41" s="81">
         <f t="shared" si="5"/>
-        <v>56161093.520428561</v>
+        <v>60144250.03587202</v>
       </c>
       <c r="K41" s="81">
         <f t="shared" si="3"/>
-        <v>57840088.394262806</v>
+        <v>56959507.347482398</v>
       </c>
       <c r="L41" s="84"/>
     </row>
@@ -5581,34 +5581,34 @@
       </c>
       <c r="D43" s="4">
         <f>IFERROR(+VLOOKUP(B43,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>3760393.1741207056</v>
+        <v>-275260.76904147147</v>
       </c>
       <c r="E43" s="4">
         <v>-275260.76904147147</v>
       </c>
       <c r="F43" s="4">
         <f t="shared" ref="F43" si="11">+D43-E43</f>
-        <v>4035653.9431621772</v>
+        <v>0</v>
       </c>
       <c r="G43" s="5">
         <f>+D43/C43</f>
-        <v>9.4009829353017646E-2</v>
+        <v>-6.8815192260367865E-3</v>
       </c>
       <c r="H43" s="4">
         <f t="shared" ref="H43" si="12">+D43/$N$3*$N$4</f>
-        <v>18049887.23577939</v>
+        <v>-1651564.614248829</v>
       </c>
       <c r="I43" s="5">
         <f>+H43/C43</f>
-        <v>0.45124718089448473</v>
+        <v>-4.1289115356220721E-2</v>
       </c>
       <c r="J43" s="4">
         <f t="shared" ref="J43" si="13">+D43/$N$3</f>
-        <v>752078.63482414116</v>
+        <v>-68815.192260367869</v>
       </c>
       <c r="K43" s="4">
         <f>+(C43-D43)/$N$2</f>
-        <v>1907347.7276778575</v>
+        <v>2013763.0384520735</v>
       </c>
       <c r="L43" s="4" cm="1">
         <f t="array" ref="L43">+_xlfn.IFS(I43&gt;114%,H43*0.02,I43&gt;109%,H43*0.015,I43&gt;104%,H43*0.0125,I43&gt;99%,H43*0.01,I43&lt;99%,H43*0)</f>
@@ -5624,34 +5624,34 @@
       </c>
       <c r="D44" s="4">
         <f>IFERROR(+VLOOKUP(B44,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>1913900.6624423866</v>
+        <v>-402349.89063324447</v>
       </c>
       <c r="E44" s="4">
         <v>-402349.89063324447</v>
       </c>
       <c r="F44" s="4">
         <f t="shared" ref="F44" si="14">+D44-E44</f>
-        <v>2316250.5530756311</v>
+        <v>0</v>
       </c>
       <c r="G44" s="5">
         <f>+D44/C44</f>
-        <v>6.3796688748079561E-2</v>
+        <v>-1.3411663021108149E-2</v>
       </c>
       <c r="H44" s="4">
         <f t="shared" ref="H44" si="15">+D44/$N$3*$N$4</f>
-        <v>9186723.1797234565</v>
+        <v>-2414099.3437994667</v>
       </c>
       <c r="I44" s="5">
         <f>+H44/C44</f>
-        <v>0.30622410599078187</v>
+        <v>-8.0469978126648897E-2</v>
       </c>
       <c r="J44" s="4">
         <f t="shared" ref="J44" si="16">+D44/$N$3</f>
-        <v>382780.13248847733</v>
+        <v>-100587.47265831112</v>
       </c>
       <c r="K44" s="4">
         <f>+(C44-D44)/$N$2</f>
-        <v>1478215.7546082954</v>
+        <v>1520117.4945316622</v>
       </c>
       <c r="L44" s="4" cm="1">
         <f t="array" ref="L44">+_xlfn.IFS(I44&gt;114%,H44*0.02,I44&gt;109%,H44*0.015,I44&gt;104%,H44*0.0125,I44&gt;99%,H44*0.01,I44&lt;99%,H44*0)</f>
@@ -5793,14 +5793,14 @@
       </c>
       <c r="D2" s="22">
         <f>H2/G2</f>
-        <v>0.51388888888888884</v>
+        <v>0.40277777777777779</v>
       </c>
       <c r="E2" s="13">
         <v>33</v>
       </c>
       <c r="F2" s="12">
         <f>+H2-E2</f>
-        <v>4</v>
+        <v>-4</v>
       </c>
       <c r="G2" s="13">
         <f>VLOOKUP(B2,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -5808,11 +5808,11 @@
       </c>
       <c r="H2" s="13">
         <f>VLOOKUP(B2,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="I2" s="17">
         <f>(+G2*$M$2)-H2</f>
-        <v>24.199999999999996</v>
+        <v>32.199999999999996</v>
       </c>
       <c r="J2" t="s">
         <v>55</v>
@@ -5896,14 +5896,14 @@
         <v>145 - ALMACEN</v>
       </c>
       <c r="S3" s="12">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="T3" s="12">
         <v>214</v>
       </c>
       <c r="U3" s="41">
         <f>+S3/T3</f>
-        <v>8.4112149532710276E-2</v>
+        <v>7.476635514018691E-2</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
@@ -5917,14 +5917,14 @@
       </c>
       <c r="D4" s="22">
         <f t="shared" si="0"/>
-        <v>0.52422907488986781</v>
+        <v>0.42290748898678415</v>
       </c>
       <c r="E4" s="13">
         <v>126</v>
       </c>
       <c r="F4" s="12">
         <f t="shared" si="1"/>
-        <v>-7</v>
+        <v>-30</v>
       </c>
       <c r="G4" s="13">
         <f>VLOOKUP(B4,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -5932,11 +5932,11 @@
       </c>
       <c r="H4" s="13">
         <f>VLOOKUP(B4,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="I4" s="17">
         <f t="shared" si="2"/>
-        <v>73.949999999999989</v>
+        <v>96.949999999999989</v>
       </c>
       <c r="J4" t="s">
         <v>57</v>
@@ -5954,14 +5954,14 @@
         <v>145 - Articulos Sin Asociar Agrupacion</v>
       </c>
       <c r="S4" s="13">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T4" s="13">
         <v>214</v>
       </c>
       <c r="U4" s="5">
         <f t="shared" ref="U4:U11" si="3">+S4/T4</f>
-        <v>7.0093457943925228E-2</v>
+        <v>5.6074766355140186E-2</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
@@ -5975,14 +5975,14 @@
       </c>
       <c r="D5" s="22">
         <f t="shared" si="0"/>
-        <v>0.41538461538461541</v>
+        <v>0.29230769230769232</v>
       </c>
       <c r="E5" s="13">
         <v>21</v>
       </c>
       <c r="F5" s="12">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>-2</v>
       </c>
       <c r="G5" s="13">
         <f>VLOOKUP(B5,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -5990,11 +5990,11 @@
       </c>
       <c r="H5" s="13">
         <f>VLOOKUP(B5,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I5" s="17">
         <f t="shared" si="2"/>
-        <v>28.25</v>
+        <v>36.25</v>
       </c>
       <c r="K5" t="s">
         <v>64</v>
@@ -6009,14 +6009,14 @@
         <v>145 - BEBIDAS</v>
       </c>
       <c r="S5" s="13">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="T5" s="13">
         <v>214</v>
       </c>
       <c r="U5" s="5">
         <f t="shared" si="3"/>
-        <v>0.13084112149532709</v>
+        <v>7.9439252336448593E-2</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
@@ -6030,14 +6030,14 @@
       </c>
       <c r="D6" s="22">
         <f t="shared" si="0"/>
-        <v>0.50724637681159424</v>
+        <v>0.42995169082125606</v>
       </c>
       <c r="E6" s="13">
         <v>100</v>
       </c>
       <c r="F6" s="12">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>-11</v>
       </c>
       <c r="G6" s="13">
         <f>VLOOKUP(B6,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6045,11 +6045,11 @@
       </c>
       <c r="H6" s="13">
         <f>VLOOKUP(B6,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="I6" s="17">
         <f t="shared" si="2"/>
-        <v>70.949999999999989</v>
+        <v>86.949999999999989</v>
       </c>
       <c r="J6" t="s">
         <v>58</v>
@@ -6067,14 +6067,14 @@
         <v>145 - CHOCOLATE</v>
       </c>
       <c r="S6" s="13">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T6" s="13">
         <v>214</v>
       </c>
       <c r="U6" s="5">
         <f t="shared" si="3"/>
-        <v>6.0747663551401869E-2</v>
+        <v>5.1401869158878503E-2</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
@@ -6088,14 +6088,14 @@
       </c>
       <c r="D7" s="22">
         <f t="shared" si="0"/>
-        <v>0.32323232323232326</v>
+        <v>0.27777777777777779</v>
       </c>
       <c r="E7" s="13">
         <v>81</v>
       </c>
       <c r="F7" s="12">
         <f t="shared" si="1"/>
-        <v>-17</v>
+        <v>-26</v>
       </c>
       <c r="G7" s="13">
         <f>VLOOKUP(B7,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6103,11 +6103,11 @@
       </c>
       <c r="H7" s="13">
         <f>VLOOKUP(B7,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="I7" s="17">
         <f t="shared" si="2"/>
-        <v>104.29999999999998</v>
+        <v>113.29999999999998</v>
       </c>
       <c r="J7" t="s">
         <v>58</v>
@@ -6125,14 +6125,14 @@
         <v>145 - GALLETITAS</v>
       </c>
       <c r="S7" s="13">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="T7" s="13">
         <v>214</v>
       </c>
       <c r="U7" s="5">
         <f t="shared" si="3"/>
-        <v>0.17289719626168223</v>
+        <v>0.13551401869158877</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
@@ -6146,14 +6146,14 @@
       </c>
       <c r="D8" s="22">
         <f t="shared" si="0"/>
-        <v>0.43457943925233644</v>
+        <v>0.32242990654205606</v>
       </c>
       <c r="E8" s="13">
         <v>89</v>
       </c>
       <c r="F8" s="12">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>-20</v>
       </c>
       <c r="G8" s="13">
         <f>VLOOKUP(B8,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6161,11 +6161,11 @@
       </c>
       <c r="H8" s="13">
         <f>VLOOKUP(B8,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="I8" s="17">
         <f t="shared" si="2"/>
-        <v>88.9</v>
+        <v>112.9</v>
       </c>
       <c r="J8" t="s">
         <v>55</v>
@@ -6184,14 +6184,14 @@
         <v>145 - GOLOSINAS</v>
       </c>
       <c r="S8" s="13">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="T8" s="13">
         <v>214</v>
       </c>
       <c r="U8" s="5">
         <f t="shared" si="3"/>
-        <v>0.1822429906542056</v>
+        <v>0.12149532710280374</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
@@ -6205,26 +6205,26 @@
       </c>
       <c r="D9" s="22">
         <f>H9/G9</f>
-        <v>0.42603550295857989</v>
+        <v>0.3592814371257485</v>
       </c>
       <c r="E9" s="13">
         <v>92</v>
       </c>
       <c r="F9" s="12">
         <f t="shared" si="1"/>
-        <v>-20</v>
+        <v>-32</v>
       </c>
       <c r="G9" s="13">
         <f>VLOOKUP(B9,'Base Cobertura'!$A:$C,3,FALSE)</f>
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H9" s="13">
         <f>VLOOKUP(B9,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="I9" s="17">
         <f t="shared" si="2"/>
-        <v>71.650000000000006</v>
+        <v>81.949999999999989</v>
       </c>
       <c r="J9" t="s">
         <v>55</v>
@@ -6242,14 +6242,14 @@
         <v>145 - MASCOTAS</v>
       </c>
       <c r="S9" s="13">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T9" s="13">
         <v>214</v>
       </c>
       <c r="U9" s="5">
         <f t="shared" si="3"/>
-        <v>4.2056074766355138E-2</v>
+        <v>3.2710280373831772E-2</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
@@ -6263,14 +6263,14 @@
       </c>
       <c r="D10" s="22">
         <f t="shared" si="0"/>
-        <v>0.3487179487179487</v>
+        <v>0.28205128205128205</v>
       </c>
       <c r="E10" s="13">
         <v>64</v>
       </c>
       <c r="F10" s="12">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>-9</v>
       </c>
       <c r="G10" s="13">
         <f>VLOOKUP(B10,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6278,11 +6278,11 @@
       </c>
       <c r="H10" s="13">
         <f>VLOOKUP(B10,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="I10" s="17">
         <f t="shared" si="2"/>
-        <v>97.75</v>
+        <v>110.75</v>
       </c>
       <c r="J10" t="s">
         <v>58</v>
@@ -6300,14 +6300,14 @@
         <v>145 - NO PERECEDEROS</v>
       </c>
       <c r="S10" s="13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T10" s="13">
         <v>214</v>
       </c>
       <c r="U10" s="5">
         <f t="shared" si="3"/>
-        <v>2.336448598130841E-2</v>
+        <v>1.4018691588785047E-2</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
@@ -6321,14 +6321,14 @@
       </c>
       <c r="D11" s="32">
         <f t="shared" si="0"/>
-        <v>0.16831683168316833</v>
+        <v>0.13861386138613863</v>
       </c>
       <c r="E11" s="31">
         <v>19</v>
       </c>
       <c r="F11" s="33">
         <f t="shared" si="1"/>
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="G11" s="13">
         <f>VLOOKUP(B11,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6336,11 +6336,11 @@
       </c>
       <c r="H11" s="13">
         <f>VLOOKUP(B11,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I11" s="34">
         <f t="shared" si="2"/>
-        <v>68.849999999999994</v>
+        <v>71.849999999999994</v>
       </c>
       <c r="J11" t="s">
         <v>59</v>
@@ -6355,14 +6355,14 @@
         <v>145 - PILAS</v>
       </c>
       <c r="S11" s="13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T11" s="13">
         <v>214</v>
       </c>
       <c r="U11" s="5">
         <f t="shared" si="3"/>
-        <v>2.336448598130841E-2</v>
+        <v>1.8691588785046728E-2</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
@@ -6376,14 +6376,14 @@
       </c>
       <c r="D12" s="32">
         <f t="shared" si="0"/>
-        <v>0.19047619047619047</v>
+        <v>0.13333333333333333</v>
       </c>
       <c r="E12" s="31">
         <v>24</v>
       </c>
       <c r="F12" s="33">
         <f t="shared" si="1"/>
-        <v>-4</v>
+        <v>-10</v>
       </c>
       <c r="G12" s="13">
         <f>VLOOKUP(B12,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6391,11 +6391,11 @@
       </c>
       <c r="H12" s="13">
         <f>VLOOKUP(B12,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I12" s="34">
         <f t="shared" si="2"/>
-        <v>69.25</v>
+        <v>75.25</v>
       </c>
       <c r="J12" t="s">
         <v>59</v>
@@ -6412,14 +6412,14 @@
       </c>
       <c r="D13" s="22">
         <f t="shared" si="0"/>
-        <v>0.41153846153846152</v>
+        <v>0.35</v>
       </c>
       <c r="E13" s="13">
         <v>144</v>
       </c>
       <c r="F13" s="12">
         <f t="shared" si="1"/>
-        <v>-37</v>
+        <v>-53</v>
       </c>
       <c r="G13" s="13">
         <f>VLOOKUP(B13,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6427,11 +6427,11 @@
       </c>
       <c r="H13" s="13">
         <f>VLOOKUP(B13,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="I13" s="17">
         <f t="shared" si="2"/>
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="J13" t="s">
         <v>57</v>
@@ -6451,14 +6451,14 @@
       </c>
       <c r="D14" s="22">
         <f t="shared" si="0"/>
-        <v>0.38461538461538464</v>
+        <v>0.31868131868131866</v>
       </c>
       <c r="E14" s="13">
         <v>85</v>
       </c>
       <c r="F14" s="12">
         <f t="shared" si="1"/>
-        <v>-15</v>
+        <v>-27</v>
       </c>
       <c r="G14" s="13">
         <f>VLOOKUP(B14,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6466,11 +6466,11 @@
       </c>
       <c r="H14" s="13">
         <f>VLOOKUP(B14,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="I14" s="17">
         <f t="shared" si="2"/>
-        <v>84.699999999999989</v>
+        <v>96.699999999999989</v>
       </c>
       <c r="J14" t="s">
         <v>55</v>
@@ -6486,15 +6486,15 @@
       <c r="E15" s="14"/>
       <c r="F15" s="16">
         <f>+SUM(F2:F14)</f>
-        <v>-27</v>
+        <v>-177</v>
       </c>
       <c r="G15" s="8">
         <f>+SUM(G2:G14)</f>
-        <v>2234</v>
+        <v>2232</v>
       </c>
       <c r="H15" s="8">
         <f>+SUM(H2:H14)</f>
-        <v>852</v>
+        <v>702</v>
       </c>
       <c r="I15" s="8"/>
     </row>
@@ -6511,14 +6511,14 @@
       </c>
       <c r="D16" s="22">
         <f t="shared" si="0"/>
-        <v>0.49689440993788819</v>
+        <v>0.40993788819875776</v>
       </c>
       <c r="E16" s="13">
         <v>90</v>
       </c>
       <c r="F16" s="12">
         <f t="shared" si="1"/>
-        <v>-10</v>
+        <v>-24</v>
       </c>
       <c r="G16" s="13">
         <f>VLOOKUP(B16,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6526,11 +6526,11 @@
       </c>
       <c r="H16" s="13">
         <f>VLOOKUP(B16,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="I16" s="17">
         <f t="shared" si="2"/>
-        <v>56.849999999999994</v>
+        <v>70.849999999999994</v>
       </c>
       <c r="J16" t="s">
         <v>55</v>
@@ -6550,14 +6550,14 @@
       </c>
       <c r="D17" s="22">
         <f t="shared" si="0"/>
-        <v>0.33663366336633666</v>
+        <v>0.28712871287128711</v>
       </c>
       <c r="E17" s="13">
         <v>92</v>
       </c>
       <c r="F17" s="12">
         <f t="shared" si="1"/>
-        <v>-24</v>
+        <v>-34</v>
       </c>
       <c r="G17" s="13">
         <f>VLOOKUP(B17,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6565,11 +6565,11 @@
       </c>
       <c r="H17" s="13">
         <f>VLOOKUP(B17,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="I17" s="17">
         <f t="shared" si="2"/>
-        <v>103.69999999999999</v>
+        <v>113.69999999999999</v>
       </c>
       <c r="J17" t="s">
         <v>55</v>
@@ -6589,14 +6589,14 @@
       </c>
       <c r="D18" s="22">
         <f t="shared" si="0"/>
-        <v>0.53529411764705881</v>
+        <v>0.44117647058823528</v>
       </c>
       <c r="E18" s="13">
         <v>88</v>
       </c>
       <c r="F18" s="12">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>-13</v>
       </c>
       <c r="G18" s="13">
         <f>VLOOKUP(B18,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6604,11 +6604,11 @@
       </c>
       <c r="H18" s="13">
         <f>VLOOKUP(B18,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="I18" s="17">
         <f t="shared" si="2"/>
-        <v>53.5</v>
+        <v>69.5</v>
       </c>
       <c r="J18" t="s">
         <v>58</v>
@@ -6628,14 +6628,14 @@
       </c>
       <c r="D19" s="22">
         <f t="shared" si="0"/>
-        <v>0.55625000000000002</v>
+        <v>0.51249999999999996</v>
       </c>
       <c r="E19" s="13">
         <v>95</v>
       </c>
       <c r="F19" s="12">
         <f t="shared" si="1"/>
-        <v>-6</v>
+        <v>-13</v>
       </c>
       <c r="G19" s="13">
         <f>VLOOKUP(B19,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6643,11 +6643,11 @@
       </c>
       <c r="H19" s="13">
         <f>VLOOKUP(B19,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="I19" s="17">
         <f t="shared" si="2"/>
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="J19" t="s">
         <v>58</v>
@@ -6667,14 +6667,14 @@
       </c>
       <c r="D20" s="22">
         <f t="shared" si="0"/>
-        <v>0.50847457627118642</v>
+        <v>0.43502824858757061</v>
       </c>
       <c r="E20" s="13">
         <v>83</v>
       </c>
       <c r="F20" s="12">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>-6</v>
       </c>
       <c r="G20" s="13">
         <f>VLOOKUP(B20,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6682,11 +6682,11 @@
       </c>
       <c r="H20" s="13">
         <f>VLOOKUP(B20,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="I20" s="17">
         <f t="shared" si="2"/>
-        <v>60.449999999999989</v>
+        <v>73.449999999999989</v>
       </c>
       <c r="J20" t="s">
         <v>55</v>
@@ -6706,14 +6706,14 @@
       </c>
       <c r="D21" s="22">
         <f t="shared" si="0"/>
-        <v>0.47928994082840237</v>
+        <v>0.42011834319526625</v>
       </c>
       <c r="E21" s="13">
         <v>64</v>
       </c>
       <c r="F21" s="12">
         <f t="shared" si="1"/>
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G21" s="13">
         <f>VLOOKUP(B21,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6721,11 +6721,11 @@
       </c>
       <c r="H21" s="13">
         <f>VLOOKUP(B21,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="I21" s="17">
         <f t="shared" si="2"/>
-        <v>62.650000000000006</v>
+        <v>72.650000000000006</v>
       </c>
       <c r="J21" t="s">
         <v>58</v>
@@ -6784,14 +6784,14 @@
       </c>
       <c r="D23" s="22">
         <f t="shared" si="0"/>
-        <v>0.43478260869565216</v>
+        <v>0.39130434782608697</v>
       </c>
       <c r="E23" s="13">
         <v>70</v>
       </c>
       <c r="F23" s="12">
         <f t="shared" si="1"/>
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="G23" s="13">
         <f>VLOOKUP(B23,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6799,11 +6799,11 @@
       </c>
       <c r="H23" s="13">
         <f>VLOOKUP(B23,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="I23" s="17">
         <f t="shared" si="2"/>
-        <v>57.3</v>
+        <v>63.3</v>
       </c>
       <c r="J23" t="s">
         <v>58</v>
@@ -6823,14 +6823,14 @@
       </c>
       <c r="D24" s="22">
         <f t="shared" si="0"/>
-        <v>0.48823529411764705</v>
+        <v>0.41764705882352943</v>
       </c>
       <c r="E24" s="13">
         <v>79</v>
       </c>
       <c r="F24" s="12">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>-8</v>
       </c>
       <c r="G24" s="13">
         <f>VLOOKUP(B24,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6838,11 +6838,11 @@
       </c>
       <c r="H24" s="13">
         <f>VLOOKUP(B24,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="I24" s="17">
         <f t="shared" si="2"/>
-        <v>61.5</v>
+        <v>73.5</v>
       </c>
       <c r="J24" t="s">
         <v>60</v>
@@ -6858,7 +6858,7 @@
       <c r="E25" s="14"/>
       <c r="F25" s="16">
         <f>+SUM(F16:F24)</f>
-        <v>-44</v>
+        <v>-132</v>
       </c>
       <c r="G25" s="8">
         <f>+SUM(G16:G24)</f>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="H25" s="8">
         <f>+SUM(H16:H24)</f>
-        <v>683</v>
+        <v>595</v>
       </c>
       <c r="I25" s="8"/>
     </row>
@@ -6883,14 +6883,14 @@
       </c>
       <c r="D26" s="22">
         <f t="shared" si="0"/>
-        <v>0.30357142857142855</v>
+        <v>0.23214285714285715</v>
       </c>
       <c r="E26" s="13">
         <v>20</v>
       </c>
       <c r="F26" s="12">
         <f>+H26-E26</f>
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="G26" s="13">
         <f>VLOOKUP(B26,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6898,11 +6898,11 @@
       </c>
       <c r="H26" s="13">
         <f>VLOOKUP(B26,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I26" s="17">
         <f t="shared" si="2"/>
-        <v>30.6</v>
+        <v>34.6</v>
       </c>
       <c r="J26" t="s">
         <v>55</v>
@@ -6922,14 +6922,14 @@
       </c>
       <c r="D27" s="22">
         <f t="shared" si="0"/>
-        <v>0.41666666666666669</v>
+        <v>0.35256410256410259</v>
       </c>
       <c r="E27" s="13">
         <v>68</v>
       </c>
       <c r="F27" s="12">
         <f t="shared" si="1"/>
-        <v>-3</v>
+        <v>-13</v>
       </c>
       <c r="G27" s="13">
         <f>VLOOKUP(B27,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6937,11 +6937,11 @@
       </c>
       <c r="H27" s="13">
         <f>VLOOKUP(B27,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I27" s="17">
         <f t="shared" si="2"/>
-        <v>67.599999999999994</v>
+        <v>77.599999999999994</v>
       </c>
       <c r="J27" t="s">
         <v>58</v>
@@ -6961,14 +6961,14 @@
       </c>
       <c r="D28" s="22">
         <f t="shared" si="0"/>
-        <v>0.36645962732919257</v>
+        <v>0.29813664596273293</v>
       </c>
       <c r="E28" s="13">
         <v>80</v>
       </c>
       <c r="F28" s="12">
         <f t="shared" si="1"/>
-        <v>-21</v>
+        <v>-32</v>
       </c>
       <c r="G28" s="13">
         <f>VLOOKUP(B28,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6976,11 +6976,11 @@
       </c>
       <c r="H28" s="13">
         <f>VLOOKUP(B28,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="I28" s="17">
         <f t="shared" si="2"/>
-        <v>77.849999999999994</v>
+        <v>88.85</v>
       </c>
       <c r="J28" t="s">
         <v>58</v>
@@ -7000,14 +7000,14 @@
       </c>
       <c r="D29" s="22">
         <f t="shared" si="0"/>
-        <v>0.20481927710843373</v>
+        <v>0.1606425702811245</v>
       </c>
       <c r="E29" s="13">
         <v>68</v>
       </c>
       <c r="F29" s="12">
         <f t="shared" si="1"/>
-        <v>-17</v>
+        <v>-28</v>
       </c>
       <c r="G29" s="13">
         <f>VLOOKUP(B29,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7015,11 +7015,11 @@
       </c>
       <c r="H29" s="13">
         <f>VLOOKUP(B29,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="I29" s="17">
         <f t="shared" si="2"/>
-        <v>160.65</v>
+        <v>171.65</v>
       </c>
       <c r="J29" t="s">
         <v>58</v>
@@ -7039,14 +7039,14 @@
       </c>
       <c r="D30" s="22">
         <f t="shared" si="0"/>
-        <v>0.51428571428571423</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="E30" s="13">
         <v>73</v>
       </c>
       <c r="F30" s="12">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-13</v>
       </c>
       <c r="G30" s="13">
         <f>VLOOKUP(B30,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7054,11 +7054,11 @@
       </c>
       <c r="H30" s="13">
         <f>VLOOKUP(B30,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="I30" s="17">
         <f t="shared" si="2"/>
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="J30" t="s">
         <v>55</v>
@@ -7078,14 +7078,14 @@
       </c>
       <c r="D31" s="22">
         <f t="shared" si="0"/>
-        <v>0.2983425414364641</v>
+        <v>0.25966850828729282</v>
       </c>
       <c r="E31" s="13">
         <v>40</v>
       </c>
       <c r="F31" s="12">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="G31" s="13">
         <f>VLOOKUP(B31,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7093,11 +7093,11 @@
       </c>
       <c r="H31" s="13">
         <f>VLOOKUP(B31,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="I31" s="17">
         <f t="shared" si="2"/>
-        <v>99.85</v>
+        <v>106.85</v>
       </c>
       <c r="J31" t="s">
         <v>58</v>
@@ -7117,14 +7117,14 @@
       </c>
       <c r="D32" s="22">
         <f t="shared" si="0"/>
-        <v>0.35119047619047616</v>
+        <v>0.30357142857142855</v>
       </c>
       <c r="E32" s="13">
         <v>67</v>
       </c>
       <c r="F32" s="12">
         <f t="shared" si="1"/>
-        <v>-8</v>
+        <v>-16</v>
       </c>
       <c r="G32" s="13">
         <f>VLOOKUP(B32,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7132,11 +7132,11 @@
       </c>
       <c r="H32" s="13">
         <f>VLOOKUP(B32,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="I32" s="17">
         <f t="shared" si="2"/>
-        <v>83.799999999999983</v>
+        <v>91.799999999999983</v>
       </c>
       <c r="J32" t="s">
         <v>58</v>
@@ -7156,14 +7156,14 @@
       </c>
       <c r="D33" s="22">
         <f t="shared" si="0"/>
-        <v>0.39534883720930231</v>
+        <v>0.34883720930232559</v>
       </c>
       <c r="E33" s="13">
         <v>66</v>
       </c>
       <c r="F33" s="12">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="G33" s="13">
         <f>VLOOKUP(B33,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7171,11 +7171,11 @@
       </c>
       <c r="H33" s="13">
         <f>VLOOKUP(B33,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="I33" s="17">
         <f t="shared" si="2"/>
-        <v>78.199999999999989</v>
+        <v>86.199999999999989</v>
       </c>
       <c r="J33" t="s">
         <v>58</v>
@@ -7195,14 +7195,14 @@
       </c>
       <c r="D34" s="22">
         <f t="shared" si="0"/>
-        <v>0.19718309859154928</v>
+        <v>0.14788732394366197</v>
       </c>
       <c r="E34" s="13">
         <v>82</v>
       </c>
       <c r="F34" s="12">
         <f t="shared" si="1"/>
-        <v>-54</v>
+        <v>-61</v>
       </c>
       <c r="G34" s="13">
         <f>VLOOKUP(B34,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7210,11 +7210,11 @@
       </c>
       <c r="H34" s="13">
         <f>VLOOKUP(B34,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="I34" s="17">
         <f t="shared" si="2"/>
-        <v>92.7</v>
+        <v>99.7</v>
       </c>
       <c r="J34" t="s">
         <v>55</v>
@@ -7234,14 +7234,14 @@
       </c>
       <c r="D35" s="22">
         <f t="shared" si="0"/>
-        <v>0.398876404494382</v>
+        <v>0.2808988764044944</v>
       </c>
       <c r="E35" s="13">
         <v>81</v>
       </c>
       <c r="F35" s="12">
         <f t="shared" si="1"/>
-        <v>-10</v>
+        <v>-31</v>
       </c>
       <c r="G35" s="13">
         <f>VLOOKUP(B35,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7249,11 +7249,11 @@
       </c>
       <c r="H35" s="13">
         <f>VLOOKUP(B35,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="I35" s="17">
         <f t="shared" si="2"/>
-        <v>80.299999999999983</v>
+        <v>101.29999999999998</v>
       </c>
       <c r="J35" t="s">
         <v>58</v>
@@ -7273,14 +7273,14 @@
       </c>
       <c r="D36" s="22">
         <f t="shared" si="0"/>
-        <v>2.6548672566371681E-2</v>
+        <v>8.8495575221238937E-3</v>
       </c>
       <c r="E36" s="13">
         <v>0</v>
       </c>
       <c r="F36" s="12">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G36" s="13">
         <f>VLOOKUP(B36,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7288,11 +7288,11 @@
       </c>
       <c r="H36" s="13">
         <f>VLOOKUP(B36,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I36" s="17">
         <f t="shared" si="2"/>
-        <v>93.05</v>
+        <v>95.05</v>
       </c>
       <c r="J36" t="s">
         <v>58</v>
@@ -7309,26 +7309,26 @@
       </c>
       <c r="D37" s="22">
         <f t="shared" si="0"/>
-        <v>3.8461538461538464E-2</v>
+        <v>1.9417475728155338E-2</v>
       </c>
       <c r="E37" s="13">
         <v>17</v>
       </c>
       <c r="F37" s="12">
         <f t="shared" si="1"/>
-        <v>-13</v>
+        <v>-15</v>
       </c>
       <c r="G37" s="13">
         <f>VLOOKUP(B37,'Base Cobertura'!$A:$C,3,FALSE)</f>
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H37" s="13">
         <f>VLOOKUP(B37,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I37" s="17">
         <f t="shared" si="2"/>
-        <v>84.399999999999991</v>
+        <v>85.55</v>
       </c>
       <c r="J37" t="s">
         <v>59</v>
@@ -7345,14 +7345,14 @@
       </c>
       <c r="D38" s="22">
         <f t="shared" si="0"/>
-        <v>0.47244094488188976</v>
+        <v>0.40157480314960631</v>
       </c>
       <c r="E38" s="13">
         <v>60</v>
       </c>
       <c r="F38" s="12">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="G38" s="13">
         <f>VLOOKUP(B38,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7360,11 +7360,11 @@
       </c>
       <c r="H38" s="13">
         <f>VLOOKUP(B38,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="I38" s="17">
         <f t="shared" si="2"/>
-        <v>47.95</v>
+        <v>56.95</v>
       </c>
       <c r="J38" t="s">
         <v>55</v>
@@ -7380,15 +7380,15 @@
       <c r="E39" s="14"/>
       <c r="F39" s="8">
         <f>+SUM(F26:F38)</f>
-        <v>-111</v>
+        <v>-223</v>
       </c>
       <c r="G39" s="8">
         <f>+SUM(G26:G38)</f>
-        <v>1947</v>
+        <v>1946</v>
       </c>
       <c r="H39" s="8">
         <f>+SUM(H26:H38)</f>
-        <v>611</v>
+        <v>499</v>
       </c>
       <c r="I39" s="8"/>
       <c r="L39" t="s">
@@ -7404,20 +7404,20 @@
       <c r="E40" s="6"/>
       <c r="F40" s="8">
         <f>+SUM(F39+F25+F15)</f>
-        <v>-182</v>
+        <v>-532</v>
       </c>
       <c r="G40" s="8">
         <f>+G15+G25+G39</f>
-        <v>5726</v>
+        <v>5723</v>
       </c>
       <c r="H40" s="8">
         <f>+H15+H25+H39</f>
-        <v>2146</v>
+        <v>1796</v>
       </c>
       <c r="I40" s="8"/>
       <c r="L40" s="1">
         <f>+H40/G40</f>
-        <v>0.37478169752008383</v>
+        <v>0.31382142233094529</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
@@ -7462,7 +7462,7 @@
       </c>
       <c r="D42" s="22">
         <f t="shared" si="4"/>
-        <v>8.3333333333333332E-3</v>
+        <v>8.4033613445378148E-3</v>
       </c>
       <c r="E42" s="13">
         <v>60</v>
@@ -7473,7 +7473,7 @@
       </c>
       <c r="G42" s="13">
         <f>VLOOKUP(B42,'Base Cobertura'!$A:$C,3,FALSE)</f>
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H42" s="13">
         <f>VLOOKUP(B42,'Base Cobertura'!$A:$C,2,FALSE)</f>
@@ -7481,7 +7481,7 @@
       </c>
       <c r="I42" s="17">
         <f t="shared" si="6"/>
-        <v>101</v>
+        <v>100.14999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -8075,7 +8075,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="51">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="C4" s="51">
         <v>127</v>
@@ -8095,7 +8095,7 @@
         <v>10</v>
       </c>
       <c r="B5" s="51">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C5" s="51">
         <v>181</v>
@@ -8113,10 +8113,10 @@
         <v>100</v>
       </c>
       <c r="B6" s="51">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C6" s="51">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="G6" t="s">
         <v>225</v>
@@ -8131,10 +8131,10 @@
         <v>11</v>
       </c>
       <c r="B7" s="51">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="C7" s="51">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G7" t="s">
         <v>226</v>
@@ -8151,7 +8151,7 @@
         <v>12</v>
       </c>
       <c r="B8" s="51">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="C8" s="51">
         <v>214</v>
@@ -8171,7 +8171,7 @@
         <v>123</v>
       </c>
       <c r="B9" s="51">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C9" s="51">
         <v>489</v>
@@ -8191,7 +8191,7 @@
         <v>15</v>
       </c>
       <c r="B10" s="51">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C10" s="51">
         <v>65</v>
@@ -8211,7 +8211,7 @@
         <v>16</v>
       </c>
       <c r="B11" s="51">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C11" s="51">
         <v>198</v>
@@ -8229,7 +8229,7 @@
         <v>18</v>
       </c>
       <c r="B12" s="51">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="C12" s="51">
         <v>177</v>
@@ -8245,7 +8245,7 @@
         <v>222</v>
       </c>
       <c r="H12">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="I12" s="51">
         <v>127</v>
@@ -8256,7 +8256,7 @@
         <v>19</v>
       </c>
       <c r="B13" s="51">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="C13" s="51">
         <v>207</v>
@@ -8269,7 +8269,7 @@
         <v>223</v>
       </c>
       <c r="H13" s="51">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I13" s="51">
         <v>127</v>
@@ -8280,7 +8280,7 @@
         <v>2</v>
       </c>
       <c r="B14" s="51">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C14" s="51">
         <v>138</v>
@@ -8293,7 +8293,7 @@
         <v>224</v>
       </c>
       <c r="H14" s="51">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="I14" s="51">
         <v>127</v>
@@ -8304,7 +8304,7 @@
         <v>20</v>
       </c>
       <c r="B15" s="51">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="C15" s="51">
         <v>227</v>
@@ -8317,7 +8317,7 @@
         <v>225</v>
       </c>
       <c r="H15" s="51">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I15" s="51">
         <v>127</v>
@@ -8328,7 +8328,7 @@
         <v>21</v>
       </c>
       <c r="B16" s="51">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="C16" s="51">
         <v>170</v>
@@ -8341,7 +8341,7 @@
         <v>226</v>
       </c>
       <c r="H16" s="51">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="I16" s="51">
         <v>127</v>
@@ -8352,7 +8352,7 @@
         <v>22</v>
       </c>
       <c r="B17" s="51">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C17" s="51">
         <v>72</v>
@@ -8365,7 +8365,7 @@
         <v>227</v>
       </c>
       <c r="H17" s="51">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I17" s="51">
         <v>127</v>
@@ -8376,7 +8376,7 @@
         <v>23</v>
       </c>
       <c r="B18" s="51">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C18" s="51">
         <v>160</v>
@@ -8389,7 +8389,7 @@
         <v>228</v>
       </c>
       <c r="H18" s="51">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I18" s="51">
         <v>127</v>
@@ -8400,7 +8400,7 @@
         <v>24</v>
       </c>
       <c r="B19" s="51">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="C19" s="51">
         <v>178</v>
@@ -8413,7 +8413,7 @@
         <v>229</v>
       </c>
       <c r="H19" s="51">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I19" s="51">
         <v>127</v>
@@ -8424,7 +8424,7 @@
         <v>25</v>
       </c>
       <c r="B20" s="51">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="C20" s="51">
         <v>172</v>
@@ -8437,7 +8437,7 @@
         <v>230</v>
       </c>
       <c r="H20">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I20" s="51">
         <v>127</v>
@@ -8451,7 +8451,7 @@
         <v>31</v>
       </c>
       <c r="C21" s="51">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E21">
         <f>+$F$21</f>
@@ -8475,7 +8475,7 @@
         <v>27</v>
       </c>
       <c r="B22" s="51">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="C22" s="51">
         <v>140</v>
@@ -8487,9 +8487,7 @@
       <c r="G22" t="s">
         <v>223</v>
       </c>
-      <c r="H22" s="51">
-        <v>1</v>
-      </c>
+      <c r="H22" s="51"/>
       <c r="I22" s="51">
         <v>181</v>
       </c>
@@ -8499,7 +8497,7 @@
         <v>28</v>
       </c>
       <c r="B23" s="51">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="C23" s="51">
         <v>168</v>
@@ -8512,7 +8510,7 @@
         <v>224</v>
       </c>
       <c r="H23" s="51">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I23" s="51">
         <v>181</v>
@@ -8523,7 +8521,7 @@
         <v>3</v>
       </c>
       <c r="B24" s="51">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C24" s="51">
         <v>170</v>
@@ -8536,7 +8534,7 @@
         <v>225</v>
       </c>
       <c r="H24" s="51">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I24" s="51">
         <v>181</v>
@@ -8547,10 +8545,10 @@
         <v>30</v>
       </c>
       <c r="B25" s="51">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C25" s="51">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E25">
         <f t="shared" si="1"/>
@@ -8560,7 +8558,7 @@
         <v>226</v>
       </c>
       <c r="H25" s="51">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I25" s="51">
         <v>181</v>
@@ -8571,7 +8569,7 @@
         <v>31</v>
       </c>
       <c r="B26" s="51">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="C26" s="51">
         <v>161</v>
@@ -8584,7 +8582,7 @@
         <v>227</v>
       </c>
       <c r="H26" s="51">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I26" s="51">
         <v>181</v>
@@ -8595,7 +8593,7 @@
         <v>32</v>
       </c>
       <c r="B27" s="51">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C27" s="51">
         <v>56</v>
@@ -8619,7 +8617,7 @@
         <v>33</v>
       </c>
       <c r="B28" s="51">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="C28" s="51">
         <v>172</v>
@@ -8632,7 +8630,7 @@
         <v>229</v>
       </c>
       <c r="H28" s="51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I28" s="51">
         <v>181</v>
@@ -8643,7 +8641,7 @@
         <v>36</v>
       </c>
       <c r="B29" s="51">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C29" s="51">
         <v>156</v>
@@ -8667,7 +8665,7 @@
         <v>37</v>
       </c>
       <c r="B30" s="51">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C30" s="51">
         <v>142</v>
@@ -8683,10 +8681,10 @@
         <v>222</v>
       </c>
       <c r="H30" s="51">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I30" s="51">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
@@ -8694,7 +8692,7 @@
         <v>4</v>
       </c>
       <c r="B31" s="51">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="C31" s="51">
         <v>182</v>
@@ -8707,10 +8705,10 @@
         <v>223</v>
       </c>
       <c r="H31" s="51">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I31" s="51">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
@@ -8718,7 +8716,7 @@
         <v>40</v>
       </c>
       <c r="B32" s="51">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="C32" s="51">
         <v>249</v>
@@ -8731,19 +8729,17 @@
         <v>224</v>
       </c>
       <c r="H32" s="51">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I32" s="51">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>42</v>
       </c>
-      <c r="B33" s="51">
-        <v>4</v>
-      </c>
+      <c r="B33" s="51"/>
       <c r="C33" s="51">
         <v>52</v>
       </c>
@@ -8755,10 +8751,10 @@
         <v>225</v>
       </c>
       <c r="H33" s="51">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I33" s="51">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
@@ -8777,10 +8773,10 @@
         <v>226</v>
       </c>
       <c r="H34" s="51">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I34" s="51">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
@@ -8788,7 +8784,7 @@
         <v>44</v>
       </c>
       <c r="B35" s="51">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="C35" s="51">
         <v>169</v>
@@ -8801,10 +8797,10 @@
         <v>227</v>
       </c>
       <c r="H35" s="51">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I35" s="51">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
@@ -8825,10 +8821,10 @@
         <v>228</v>
       </c>
       <c r="H36" s="51">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I36" s="51">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
@@ -8836,7 +8832,7 @@
         <v>5</v>
       </c>
       <c r="B37" s="51">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="C37" s="51">
         <v>260</v>
@@ -8849,10 +8845,10 @@
         <v>229</v>
       </c>
       <c r="H37" s="51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I37" s="51">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
@@ -8860,7 +8856,7 @@
         <v>52</v>
       </c>
       <c r="B38" s="51">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C38" s="51">
         <v>101</v>
@@ -8874,7 +8870,7 @@
       </c>
       <c r="H38" s="51"/>
       <c r="I38" s="51">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
@@ -8882,7 +8878,7 @@
         <v>53</v>
       </c>
       <c r="B39" s="51">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C39" s="51">
         <v>105</v>
@@ -8901,7 +8897,7 @@
         <v>8</v>
       </c>
       <c r="I39" s="51">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
@@ -8909,7 +8905,7 @@
         <v>54</v>
       </c>
       <c r="B40" s="51">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C40" s="51">
         <v>202</v>
@@ -8922,10 +8918,10 @@
         <v>223</v>
       </c>
       <c r="H40" s="51">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I40" s="51">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
@@ -8946,10 +8942,10 @@
         <v>224</v>
       </c>
       <c r="H41" s="51">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="I41" s="51">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
@@ -8957,10 +8953,10 @@
         <v>57</v>
       </c>
       <c r="B42" s="51">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C42" s="51">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E42">
         <f t="shared" si="3"/>
@@ -8970,10 +8966,10 @@
         <v>225</v>
       </c>
       <c r="H42" s="51">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I42" s="51">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
@@ -8992,10 +8988,10 @@
         <v>226</v>
       </c>
       <c r="H43" s="51">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="I43" s="51">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
@@ -9006,7 +9002,7 @@
         <v>1</v>
       </c>
       <c r="C44" s="51">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E44">
         <f t="shared" si="3"/>
@@ -9016,10 +9012,10 @@
         <v>227</v>
       </c>
       <c r="H44" s="51">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="I44" s="51">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
@@ -9027,7 +9023,7 @@
         <v>7</v>
       </c>
       <c r="B45" s="51">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C45" s="51">
         <v>113</v>
@@ -9040,10 +9036,10 @@
         <v>228</v>
       </c>
       <c r="H45" s="51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I45" s="51">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
@@ -9051,7 +9047,7 @@
         <v>8</v>
       </c>
       <c r="B46" s="51">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="C46" s="51">
         <v>195</v>
@@ -9064,10 +9060,10 @@
         <v>229</v>
       </c>
       <c r="H46" s="51">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I46" s="51">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
@@ -9075,7 +9071,7 @@
         <v>9</v>
       </c>
       <c r="B47" s="51">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="C47" s="51">
         <v>161</v>
@@ -9091,7 +9087,7 @@
         <v>5</v>
       </c>
       <c r="I47" s="51">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
@@ -9108,7 +9104,7 @@
         <v>222</v>
       </c>
       <c r="H48" s="51">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I48" s="51">
         <v>214</v>
@@ -9125,7 +9121,7 @@
         <v>223</v>
       </c>
       <c r="H49" s="51">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I49" s="51">
         <v>214</v>
@@ -9140,7 +9136,7 @@
         <v>224</v>
       </c>
       <c r="H50" s="51">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I50" s="51">
         <v>214</v>
@@ -9155,7 +9151,7 @@
         <v>225</v>
       </c>
       <c r="H51" s="51">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I51" s="51">
         <v>214</v>
@@ -9170,7 +9166,7 @@
         <v>226</v>
       </c>
       <c r="H52" s="51">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="I52" s="51">
         <v>214</v>
@@ -9185,7 +9181,7 @@
         <v>227</v>
       </c>
       <c r="H53" s="51">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="I53" s="51">
         <v>214</v>
@@ -9200,7 +9196,7 @@
         <v>228</v>
       </c>
       <c r="H54" s="51">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I54" s="51">
         <v>214</v>
@@ -9215,7 +9211,7 @@
         <v>229</v>
       </c>
       <c r="H55" s="51">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I55" s="51">
         <v>214</v>
@@ -9230,7 +9226,7 @@
         <v>230</v>
       </c>
       <c r="H56" s="51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I56" s="51">
         <v>214</v>
@@ -9248,7 +9244,7 @@
         <v>222</v>
       </c>
       <c r="H57" s="51">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I57" s="51">
         <v>489</v>
@@ -9263,7 +9259,7 @@
         <v>223</v>
       </c>
       <c r="H58" s="51">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I58" s="51">
         <v>489</v>
@@ -9278,7 +9274,7 @@
         <v>224</v>
       </c>
       <c r="H59" s="51">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I59" s="51">
         <v>489</v>
@@ -9292,9 +9288,7 @@
       <c r="G60" t="s">
         <v>225</v>
       </c>
-      <c r="H60" s="51">
-        <v>1</v>
-      </c>
+      <c r="H60" s="51"/>
       <c r="I60" s="51">
         <v>489</v>
       </c>
@@ -9308,7 +9302,7 @@
         <v>226</v>
       </c>
       <c r="H61" s="51">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I61" s="51">
         <v>489</v>
@@ -9336,7 +9330,7 @@
         <v>228</v>
       </c>
       <c r="H63" s="51">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I63" s="51">
         <v>489</v>
@@ -9351,7 +9345,7 @@
         <v>229</v>
       </c>
       <c r="H64" s="51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I64" s="51">
         <v>489</v>
@@ -9382,7 +9376,7 @@
         <v>222</v>
       </c>
       <c r="H66" s="51">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I66" s="51">
         <v>65</v>
@@ -9397,7 +9391,7 @@
         <v>223</v>
       </c>
       <c r="H67" s="51">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I67" s="51">
         <v>65</v>
@@ -9412,7 +9406,7 @@
         <v>224</v>
       </c>
       <c r="H68" s="51">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I68" s="51">
         <v>65</v>
@@ -9427,7 +9421,7 @@
         <v>225</v>
       </c>
       <c r="H69" s="51">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I69" s="51">
         <v>65</v>
@@ -9442,7 +9436,7 @@
         <v>226</v>
       </c>
       <c r="H70" s="51">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I70" s="51">
         <v>65</v>
@@ -9457,7 +9451,7 @@
         <v>227</v>
       </c>
       <c r="H71" s="51">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I71" s="51">
         <v>65</v>
@@ -9472,7 +9466,7 @@
         <v>228</v>
       </c>
       <c r="H72" s="51">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I72" s="51">
         <v>65</v>
@@ -9487,7 +9481,7 @@
         <v>229</v>
       </c>
       <c r="H73" s="51">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I73" s="51">
         <v>65</v>
@@ -9520,7 +9514,7 @@
         <v>222</v>
       </c>
       <c r="H75" s="51">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I75" s="51">
         <v>198</v>
@@ -9535,7 +9529,7 @@
         <v>223</v>
       </c>
       <c r="H76">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I76" s="51">
         <v>198</v>
@@ -9550,7 +9544,7 @@
         <v>224</v>
       </c>
       <c r="H77" s="51">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I77" s="51">
         <v>198</v>
@@ -9565,7 +9559,7 @@
         <v>225</v>
       </c>
       <c r="H78" s="51">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I78" s="51">
         <v>198</v>
@@ -9580,7 +9574,7 @@
         <v>226</v>
       </c>
       <c r="H79" s="51">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="I79" s="51">
         <v>198</v>
@@ -9595,7 +9589,7 @@
         <v>227</v>
       </c>
       <c r="H80" s="51">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="I80" s="51">
         <v>198</v>
@@ -9610,7 +9604,7 @@
         <v>228</v>
       </c>
       <c r="H81" s="51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I81" s="51">
         <v>198</v>
@@ -9625,7 +9619,7 @@
         <v>229</v>
       </c>
       <c r="H82" s="51">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I82" s="51">
         <v>198</v>
@@ -9640,7 +9634,7 @@
         <v>230</v>
       </c>
       <c r="H83" s="51">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I83" s="51">
         <v>198</v>
@@ -9658,7 +9652,7 @@
         <v>222</v>
       </c>
       <c r="H84" s="51">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I84" s="51">
         <v>177</v>
@@ -9673,7 +9667,7 @@
         <v>223</v>
       </c>
       <c r="H85" s="51">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I85" s="51">
         <v>177</v>
@@ -9688,7 +9682,7 @@
         <v>224</v>
       </c>
       <c r="H86" s="51">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I86" s="51">
         <v>177</v>
@@ -9703,7 +9697,7 @@
         <v>225</v>
       </c>
       <c r="H87" s="51">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I87" s="51">
         <v>177</v>
@@ -9718,7 +9712,7 @@
         <v>226</v>
       </c>
       <c r="H88" s="51">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="I88" s="51">
         <v>177</v>
@@ -9733,7 +9727,7 @@
         <v>227</v>
       </c>
       <c r="H89" s="51">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="I89" s="51">
         <v>177</v>
@@ -9748,7 +9742,7 @@
         <v>228</v>
       </c>
       <c r="H90" s="51">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I90" s="51">
         <v>177</v>
@@ -9763,7 +9757,7 @@
         <v>229</v>
       </c>
       <c r="H91" s="51">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I91" s="51">
         <v>177</v>
@@ -9778,7 +9772,7 @@
         <v>230</v>
       </c>
       <c r="H92" s="51">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I92" s="51">
         <v>177</v>
@@ -9796,7 +9790,7 @@
         <v>222</v>
       </c>
       <c r="H93" s="51">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I93" s="51">
         <v>207</v>
@@ -9811,7 +9805,7 @@
         <v>223</v>
       </c>
       <c r="H94" s="51">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I94" s="51">
         <v>207</v>
@@ -9826,7 +9820,7 @@
         <v>224</v>
       </c>
       <c r="H95" s="51">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I95" s="51">
         <v>207</v>
@@ -9841,7 +9835,7 @@
         <v>225</v>
       </c>
       <c r="H96" s="51">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="I96" s="51">
         <v>207</v>
@@ -9856,7 +9850,7 @@
         <v>226</v>
       </c>
       <c r="H97" s="51">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="I97" s="51">
         <v>207</v>
@@ -9871,7 +9865,7 @@
         <v>227</v>
       </c>
       <c r="H98" s="51">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="I98" s="51">
         <v>207</v>
@@ -9901,7 +9895,7 @@
         <v>229</v>
       </c>
       <c r="H100" s="51">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I100" s="51">
         <v>207</v>
@@ -9916,7 +9910,7 @@
         <v>230</v>
       </c>
       <c r="H101" s="51">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I101" s="51">
         <v>207</v>
@@ -9934,7 +9928,7 @@
         <v>222</v>
       </c>
       <c r="H102" s="51">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I102" s="51">
         <v>138</v>
@@ -9949,7 +9943,7 @@
         <v>223</v>
       </c>
       <c r="H103" s="51">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="I103" s="51">
         <v>138</v>
@@ -9964,7 +9958,7 @@
         <v>224</v>
       </c>
       <c r="H104" s="51">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I104" s="51">
         <v>138</v>
@@ -9994,7 +9988,7 @@
         <v>226</v>
       </c>
       <c r="H106" s="51">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="I106" s="51">
         <v>138</v>
@@ -10009,7 +10003,7 @@
         <v>227</v>
       </c>
       <c r="H107" s="51">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I107" s="51">
         <v>138</v>
@@ -10054,7 +10048,7 @@
         <v>230</v>
       </c>
       <c r="H110" s="51">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I110" s="51">
         <v>138</v>
@@ -10072,7 +10066,7 @@
         <v>222</v>
       </c>
       <c r="H111" s="51">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="I111" s="51">
         <v>227</v>
@@ -10087,7 +10081,7 @@
         <v>223</v>
       </c>
       <c r="H112" s="51">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I112" s="51">
         <v>227</v>
@@ -10102,7 +10096,7 @@
         <v>224</v>
       </c>
       <c r="H113" s="51">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="I113" s="51">
         <v>227</v>
@@ -10117,7 +10111,7 @@
         <v>225</v>
       </c>
       <c r="H114" s="51">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I114" s="51">
         <v>227</v>
@@ -10132,7 +10126,7 @@
         <v>226</v>
       </c>
       <c r="H115" s="51">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="I115" s="51">
         <v>227</v>
@@ -10147,7 +10141,7 @@
         <v>227</v>
       </c>
       <c r="H116">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="I116" s="51">
         <v>227</v>
@@ -10162,7 +10156,7 @@
         <v>228</v>
       </c>
       <c r="H117" s="51">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I117" s="51">
         <v>227</v>
@@ -10177,7 +10171,7 @@
         <v>229</v>
       </c>
       <c r="H118" s="51">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I118" s="51">
         <v>227</v>
@@ -10192,7 +10186,7 @@
         <v>230</v>
       </c>
       <c r="H119" s="51">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I119" s="51">
         <v>227</v>
@@ -10210,7 +10204,7 @@
         <v>222</v>
       </c>
       <c r="H120" s="51">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I120" s="51">
         <v>170</v>
@@ -10225,7 +10219,7 @@
         <v>223</v>
       </c>
       <c r="H121" s="51">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I121" s="51">
         <v>170</v>
@@ -10240,7 +10234,7 @@
         <v>224</v>
       </c>
       <c r="H122" s="51">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="I122" s="51">
         <v>170</v>
@@ -10255,7 +10249,7 @@
         <v>225</v>
       </c>
       <c r="H123" s="51">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="I123" s="51">
         <v>170</v>
@@ -10270,7 +10264,7 @@
         <v>226</v>
       </c>
       <c r="H124">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="I124" s="51">
         <v>170</v>
@@ -10285,7 +10279,7 @@
         <v>227</v>
       </c>
       <c r="H125" s="51">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="I125" s="51">
         <v>170</v>
@@ -10300,7 +10294,7 @@
         <v>228</v>
       </c>
       <c r="H126" s="51">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I126" s="51">
         <v>170</v>
@@ -10315,7 +10309,7 @@
         <v>229</v>
       </c>
       <c r="H127" s="51">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I127" s="51">
         <v>170</v>
@@ -10330,7 +10324,7 @@
         <v>230</v>
       </c>
       <c r="H128" s="51">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I128" s="51">
         <v>170</v>
@@ -10348,7 +10342,7 @@
         <v>222</v>
       </c>
       <c r="H129" s="51">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I129" s="51">
         <v>72</v>
@@ -10363,7 +10357,7 @@
         <v>223</v>
       </c>
       <c r="H130" s="51">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I130" s="51">
         <v>72</v>
@@ -10378,7 +10372,7 @@
         <v>224</v>
       </c>
       <c r="H131" s="51">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="I131" s="51">
         <v>72</v>
@@ -10393,7 +10387,7 @@
         <v>225</v>
       </c>
       <c r="H132" s="51">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I132" s="51">
         <v>72</v>
@@ -10408,7 +10402,7 @@
         <v>226</v>
       </c>
       <c r="H133" s="51">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="I133" s="51">
         <v>72</v>
@@ -10423,7 +10417,7 @@
         <v>227</v>
       </c>
       <c r="H134" s="51">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I134" s="51">
         <v>72</v>
@@ -10438,7 +10432,7 @@
         <v>228</v>
       </c>
       <c r="H135" s="51">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="I135" s="51">
         <v>72</v>
@@ -10453,7 +10447,7 @@
         <v>229</v>
       </c>
       <c r="H136" s="51">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I136" s="51">
         <v>72</v>
@@ -10468,7 +10462,7 @@
         <v>230</v>
       </c>
       <c r="H137" s="51">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I137" s="51">
         <v>72</v>
@@ -10486,7 +10480,7 @@
         <v>222</v>
       </c>
       <c r="H138" s="51">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I138" s="51">
         <v>160</v>
@@ -10501,7 +10495,7 @@
         <v>223</v>
       </c>
       <c r="H139" s="51">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I139" s="51">
         <v>160</v>
@@ -10516,7 +10510,7 @@
         <v>224</v>
       </c>
       <c r="H140">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="I140" s="51">
         <v>160</v>
@@ -10531,7 +10525,7 @@
         <v>225</v>
       </c>
       <c r="H141" s="51">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I141" s="51">
         <v>160</v>
@@ -10546,7 +10540,7 @@
         <v>226</v>
       </c>
       <c r="H142" s="51">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="I142" s="51">
         <v>160</v>
@@ -10561,7 +10555,7 @@
         <v>227</v>
       </c>
       <c r="H143" s="51">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="I143" s="51">
         <v>160</v>
@@ -10576,7 +10570,7 @@
         <v>228</v>
       </c>
       <c r="H144" s="51">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I144" s="51">
         <v>160</v>
@@ -10591,7 +10585,7 @@
         <v>229</v>
       </c>
       <c r="H145" s="51">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I145" s="51">
         <v>160</v>
@@ -10624,7 +10618,7 @@
         <v>222</v>
       </c>
       <c r="H147" s="51">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I147" s="51">
         <v>178</v>
@@ -10654,7 +10648,7 @@
         <v>224</v>
       </c>
       <c r="H149" s="51">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="I149" s="51">
         <v>178</v>
@@ -10669,7 +10663,7 @@
         <v>225</v>
       </c>
       <c r="H150" s="51">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I150" s="51">
         <v>178</v>
@@ -10684,7 +10678,7 @@
         <v>226</v>
       </c>
       <c r="H151" s="51">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I151" s="51">
         <v>178</v>
@@ -10699,7 +10693,7 @@
         <v>227</v>
       </c>
       <c r="H152" s="51">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I152" s="51">
         <v>178</v>
@@ -10714,7 +10708,7 @@
         <v>228</v>
       </c>
       <c r="H153" s="51">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I153" s="51">
         <v>178</v>
@@ -10762,7 +10756,7 @@
         <v>222</v>
       </c>
       <c r="H156" s="51">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="I156" s="51">
         <v>172</v>
@@ -10777,7 +10771,7 @@
         <v>223</v>
       </c>
       <c r="H157" s="51">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="I157" s="51">
         <v>172</v>
@@ -10792,7 +10786,7 @@
         <v>224</v>
       </c>
       <c r="H158" s="51">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="I158" s="51">
         <v>172</v>
@@ -10807,7 +10801,7 @@
         <v>225</v>
       </c>
       <c r="H159" s="51">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="I159" s="51">
         <v>172</v>
@@ -10822,7 +10816,7 @@
         <v>226</v>
       </c>
       <c r="H160" s="51">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="I160" s="51">
         <v>172</v>
@@ -10837,7 +10831,7 @@
         <v>227</v>
       </c>
       <c r="H161" s="51">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="I161" s="51">
         <v>172</v>
@@ -10852,7 +10846,7 @@
         <v>228</v>
       </c>
       <c r="H162" s="51">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="I162" s="51">
         <v>172</v>
@@ -10867,7 +10861,7 @@
         <v>229</v>
       </c>
       <c r="H163" s="51">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I163" s="51">
         <v>172</v>
@@ -10882,7 +10876,7 @@
         <v>230</v>
       </c>
       <c r="H164">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I164" s="51">
         <v>172</v>
@@ -10903,7 +10897,7 @@
         <v>12</v>
       </c>
       <c r="I165" s="51">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="166" spans="5:9" x14ac:dyDescent="0.25">
@@ -10918,7 +10912,7 @@
         <v>6</v>
       </c>
       <c r="I166" s="51">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="167" spans="5:9" x14ac:dyDescent="0.25">
@@ -10933,7 +10927,7 @@
         <v>3</v>
       </c>
       <c r="I167" s="51">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="168" spans="5:9" x14ac:dyDescent="0.25">
@@ -10948,7 +10942,7 @@
         <v>15</v>
       </c>
       <c r="I168" s="51">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="169" spans="5:9" x14ac:dyDescent="0.25">
@@ -10963,7 +10957,7 @@
         <v>11</v>
       </c>
       <c r="I169" s="51">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="170" spans="5:9" x14ac:dyDescent="0.25">
@@ -10978,7 +10972,7 @@
         <v>12</v>
       </c>
       <c r="I170" s="51">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="171" spans="5:9" x14ac:dyDescent="0.25">
@@ -10993,7 +10987,7 @@
         <v>16</v>
       </c>
       <c r="I171" s="51">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="172" spans="5:9" x14ac:dyDescent="0.25">
@@ -11008,7 +11002,7 @@
         <v>6</v>
       </c>
       <c r="I172" s="51">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="173" spans="5:9" x14ac:dyDescent="0.25">
@@ -11023,7 +11017,7 @@
         <v>11</v>
       </c>
       <c r="I173" s="51">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="174" spans="5:9" x14ac:dyDescent="0.25">
@@ -11038,7 +11032,7 @@
         <v>222</v>
       </c>
       <c r="H174" s="51">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I174" s="51">
         <v>140</v>
@@ -11053,7 +11047,7 @@
         <v>223</v>
       </c>
       <c r="H175" s="51">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I175" s="51">
         <v>140</v>
@@ -11068,7 +11062,7 @@
         <v>224</v>
       </c>
       <c r="H176" s="51">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I176" s="51">
         <v>140</v>
@@ -11083,7 +11077,7 @@
         <v>225</v>
       </c>
       <c r="H177" s="51">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I177" s="51">
         <v>140</v>
@@ -11098,7 +11092,7 @@
         <v>226</v>
       </c>
       <c r="H178" s="51">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="I178" s="51">
         <v>140</v>
@@ -11113,7 +11107,7 @@
         <v>227</v>
       </c>
       <c r="H179" s="51">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I179" s="51">
         <v>140</v>
@@ -11128,7 +11122,7 @@
         <v>228</v>
       </c>
       <c r="H180">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I180" s="51">
         <v>140</v>
@@ -11143,7 +11137,7 @@
         <v>229</v>
       </c>
       <c r="H181" s="51">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I181" s="51">
         <v>140</v>
@@ -11158,7 +11152,7 @@
         <v>230</v>
       </c>
       <c r="H182" s="51">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I182" s="51">
         <v>140</v>
@@ -11176,7 +11170,7 @@
         <v>222</v>
       </c>
       <c r="H183" s="51">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I183" s="51">
         <v>168</v>
@@ -11191,7 +11185,7 @@
         <v>223</v>
       </c>
       <c r="H184" s="51">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I184" s="51">
         <v>168</v>
@@ -11206,7 +11200,7 @@
         <v>224</v>
       </c>
       <c r="H185" s="51">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I185" s="51">
         <v>168</v>
@@ -11221,7 +11215,7 @@
         <v>225</v>
       </c>
       <c r="H186">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I186" s="51">
         <v>168</v>
@@ -11236,7 +11230,7 @@
         <v>226</v>
       </c>
       <c r="H187" s="51">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I187" s="51">
         <v>168</v>
@@ -11251,7 +11245,7 @@
         <v>227</v>
       </c>
       <c r="H188" s="51">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="I188" s="51">
         <v>168</v>
@@ -11281,7 +11275,7 @@
         <v>229</v>
       </c>
       <c r="H190" s="51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I190" s="51">
         <v>168</v>
@@ -11296,7 +11290,7 @@
         <v>230</v>
       </c>
       <c r="H191" s="51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I191" s="51">
         <v>168</v>
@@ -11314,7 +11308,7 @@
         <v>222</v>
       </c>
       <c r="H192" s="51">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I192" s="51">
         <v>170</v>
@@ -11344,7 +11338,7 @@
         <v>224</v>
       </c>
       <c r="H194" s="51">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="I194" s="51">
         <v>170</v>
@@ -11359,7 +11353,7 @@
         <v>225</v>
       </c>
       <c r="H195" s="51">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I195" s="51">
         <v>170</v>
@@ -11374,7 +11368,7 @@
         <v>226</v>
       </c>
       <c r="H196">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="I196" s="51">
         <v>170</v>
@@ -11389,7 +11383,7 @@
         <v>227</v>
       </c>
       <c r="H197" s="51">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I197" s="51">
         <v>170</v>
@@ -11404,7 +11398,7 @@
         <v>228</v>
       </c>
       <c r="H198" s="51">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I198" s="51">
         <v>170</v>
@@ -11419,7 +11413,7 @@
         <v>229</v>
       </c>
       <c r="H199" s="51">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I199" s="51">
         <v>170</v>
@@ -11434,7 +11428,7 @@
         <v>230</v>
       </c>
       <c r="H200" s="51">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I200" s="51">
         <v>170</v>
@@ -11452,10 +11446,10 @@
         <v>222</v>
       </c>
       <c r="H201" s="51">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I201" s="51">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="202" spans="5:9" x14ac:dyDescent="0.25">
@@ -11466,11 +11460,9 @@
       <c r="G202" t="s">
         <v>223</v>
       </c>
-      <c r="H202" s="51">
-        <v>1</v>
-      </c>
+      <c r="H202" s="51"/>
       <c r="I202" s="51">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="203" spans="5:9" x14ac:dyDescent="0.25">
@@ -11482,10 +11474,10 @@
         <v>224</v>
       </c>
       <c r="H203" s="51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I203" s="51">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="204" spans="5:9" x14ac:dyDescent="0.25">
@@ -11498,7 +11490,7 @@
       </c>
       <c r="H204" s="51"/>
       <c r="I204" s="51">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="205" spans="5:9" x14ac:dyDescent="0.25">
@@ -11513,7 +11505,7 @@
         <v>3</v>
       </c>
       <c r="I205" s="51">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="206" spans="5:9" x14ac:dyDescent="0.25">
@@ -11526,7 +11518,7 @@
       </c>
       <c r="H206" s="51"/>
       <c r="I206" s="51">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="207" spans="5:9" x14ac:dyDescent="0.25">
@@ -11538,10 +11530,10 @@
         <v>228</v>
       </c>
       <c r="H207" s="51">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I207" s="51">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="208" spans="5:9" x14ac:dyDescent="0.25">
@@ -11554,7 +11546,7 @@
       </c>
       <c r="H208" s="51"/>
       <c r="I208" s="51">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="209" spans="5:9" x14ac:dyDescent="0.25">
@@ -11567,7 +11559,7 @@
       </c>
       <c r="H209" s="51"/>
       <c r="I209" s="51">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="210" spans="5:9" x14ac:dyDescent="0.25">
@@ -11582,7 +11574,7 @@
         <v>222</v>
       </c>
       <c r="H210" s="51">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I210" s="51">
         <v>161</v>
@@ -11597,7 +11589,7 @@
         <v>223</v>
       </c>
       <c r="H211" s="51">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I211" s="51">
         <v>161</v>
@@ -11612,7 +11604,7 @@
         <v>224</v>
       </c>
       <c r="H212">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="I212" s="51">
         <v>161</v>
@@ -11627,7 +11619,7 @@
         <v>225</v>
       </c>
       <c r="H213" s="51">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I213" s="51">
         <v>161</v>
@@ -11642,7 +11634,7 @@
         <v>226</v>
       </c>
       <c r="H214" s="51">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="I214" s="51">
         <v>161</v>
@@ -11657,7 +11649,7 @@
         <v>227</v>
       </c>
       <c r="H215" s="51">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I215" s="51">
         <v>161</v>
@@ -11672,7 +11664,7 @@
         <v>228</v>
       </c>
       <c r="H216" s="51">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I216" s="51">
         <v>161</v>
@@ -11687,7 +11679,7 @@
         <v>229</v>
       </c>
       <c r="H217" s="51">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I217" s="51">
         <v>161</v>
@@ -11720,7 +11712,7 @@
         <v>222</v>
       </c>
       <c r="H219" s="51">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I219" s="51">
         <v>56</v>
@@ -11735,7 +11727,7 @@
         <v>223</v>
       </c>
       <c r="H220" s="51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I220" s="51">
         <v>56</v>
@@ -11750,7 +11742,7 @@
         <v>224</v>
       </c>
       <c r="H221" s="51">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I221" s="51">
         <v>56</v>
@@ -11765,7 +11757,7 @@
         <v>225</v>
       </c>
       <c r="H222" s="51">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I222" s="51">
         <v>56</v>
@@ -11780,7 +11772,7 @@
         <v>226</v>
       </c>
       <c r="H223" s="51">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I223" s="51">
         <v>56</v>
@@ -11795,7 +11787,7 @@
         <v>227</v>
       </c>
       <c r="H224" s="51">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I224" s="51">
         <v>56</v>
@@ -11810,7 +11802,7 @@
         <v>228</v>
       </c>
       <c r="H225" s="51">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I225" s="51">
         <v>56</v>
@@ -11825,7 +11817,7 @@
         <v>229</v>
       </c>
       <c r="H226" s="51">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I226" s="51">
         <v>56</v>
@@ -11840,7 +11832,7 @@
         <v>230</v>
       </c>
       <c r="H227" s="51">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I227" s="51">
         <v>56</v>
@@ -11858,7 +11850,7 @@
         <v>222</v>
       </c>
       <c r="H228" s="51">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I228" s="51">
         <v>172</v>
@@ -11873,7 +11865,7 @@
         <v>223</v>
       </c>
       <c r="H229" s="51">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I229" s="51">
         <v>172</v>
@@ -11888,7 +11880,7 @@
         <v>224</v>
       </c>
       <c r="H230" s="51">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I230" s="51">
         <v>172</v>
@@ -11903,7 +11895,7 @@
         <v>225</v>
       </c>
       <c r="H231" s="51">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I231" s="51">
         <v>172</v>
@@ -11918,7 +11910,7 @@
         <v>226</v>
       </c>
       <c r="H232" s="51">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="I232" s="51">
         <v>172</v>
@@ -11933,7 +11925,7 @@
         <v>227</v>
       </c>
       <c r="H233" s="51">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I233" s="51">
         <v>172</v>
@@ -11963,7 +11955,7 @@
         <v>229</v>
       </c>
       <c r="H235" s="51">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I235" s="51">
         <v>172</v>
@@ -11978,7 +11970,7 @@
         <v>230</v>
       </c>
       <c r="H236">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I236" s="51">
         <v>172</v>
@@ -11996,7 +11988,7 @@
         <v>222</v>
       </c>
       <c r="H237" s="51">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I237" s="51">
         <v>156</v>
@@ -12011,7 +12003,7 @@
         <v>223</v>
       </c>
       <c r="H238" s="51">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I238" s="51">
         <v>156</v>
@@ -12026,7 +12018,7 @@
         <v>224</v>
       </c>
       <c r="H239" s="51">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I239" s="51">
         <v>156</v>
@@ -12041,7 +12033,7 @@
         <v>225</v>
       </c>
       <c r="H240" s="51">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I240" s="51">
         <v>156</v>
@@ -12056,7 +12048,7 @@
         <v>226</v>
       </c>
       <c r="H241" s="51">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="I241" s="51">
         <v>156</v>
@@ -12071,7 +12063,7 @@
         <v>227</v>
       </c>
       <c r="H242" s="51">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="I242" s="51">
         <v>156</v>
@@ -12086,7 +12078,7 @@
         <v>228</v>
       </c>
       <c r="H243" s="51">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I243" s="51">
         <v>156</v>
@@ -12101,7 +12093,7 @@
         <v>229</v>
       </c>
       <c r="H244">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I244" s="51">
         <v>156</v>
@@ -12116,7 +12108,7 @@
         <v>230</v>
       </c>
       <c r="H245" s="51">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I245" s="51">
         <v>156</v>
@@ -12149,7 +12141,7 @@
         <v>223</v>
       </c>
       <c r="H247" s="51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I247" s="51">
         <v>142</v>
@@ -12164,7 +12156,7 @@
         <v>224</v>
       </c>
       <c r="H248" s="51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I248" s="51">
         <v>142</v>
@@ -12179,7 +12171,7 @@
         <v>225</v>
       </c>
       <c r="H249" s="51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I249" s="51">
         <v>142</v>
@@ -12194,7 +12186,7 @@
         <v>226</v>
       </c>
       <c r="H250" s="51">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I250" s="51">
         <v>142</v>
@@ -12209,7 +12201,7 @@
         <v>227</v>
       </c>
       <c r="H251" s="51">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I251" s="51">
         <v>142</v>
@@ -12224,7 +12216,7 @@
         <v>228</v>
       </c>
       <c r="H252">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I252" s="51">
         <v>142</v>
@@ -12239,7 +12231,7 @@
         <v>229</v>
       </c>
       <c r="H253" s="51">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I253" s="51">
         <v>142</v>
@@ -12254,7 +12246,7 @@
         <v>230</v>
       </c>
       <c r="H254" s="51">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I254" s="51">
         <v>142</v>
@@ -12272,7 +12264,7 @@
         <v>222</v>
       </c>
       <c r="H255" s="51">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I255" s="51">
         <v>182</v>
@@ -12287,7 +12279,7 @@
         <v>223</v>
       </c>
       <c r="H256" s="51">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I256" s="51">
         <v>182</v>
@@ -12302,7 +12294,7 @@
         <v>224</v>
       </c>
       <c r="H257" s="51">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I257" s="51">
         <v>182</v>
@@ -12317,7 +12309,7 @@
         <v>225</v>
       </c>
       <c r="H258">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I258" s="51">
         <v>182</v>
@@ -12332,7 +12324,7 @@
         <v>226</v>
       </c>
       <c r="H259" s="51">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="I259" s="51">
         <v>182</v>
@@ -12347,7 +12339,7 @@
         <v>227</v>
       </c>
       <c r="H260">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I260" s="51">
         <v>182</v>
@@ -12362,7 +12354,7 @@
         <v>228</v>
       </c>
       <c r="H261" s="51">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I261" s="51">
         <v>182</v>
@@ -12377,7 +12369,7 @@
         <v>229</v>
       </c>
       <c r="H262" s="51">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I262" s="51">
         <v>182</v>
@@ -12392,7 +12384,7 @@
         <v>230</v>
       </c>
       <c r="H263" s="51">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I263" s="51">
         <v>182</v>
@@ -12410,7 +12402,7 @@
         <v>222</v>
       </c>
       <c r="H264" s="51">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I264" s="51">
         <v>249</v>
@@ -12425,7 +12417,7 @@
         <v>223</v>
       </c>
       <c r="H265">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I265" s="51">
         <v>249</v>
@@ -12440,7 +12432,7 @@
         <v>224</v>
       </c>
       <c r="H266" s="51">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I266" s="51">
         <v>249</v>
@@ -12455,7 +12447,7 @@
         <v>225</v>
       </c>
       <c r="H267" s="51">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I267" s="51">
         <v>249</v>
@@ -12470,7 +12462,7 @@
         <v>226</v>
       </c>
       <c r="H268">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I268" s="51">
         <v>249</v>
@@ -12485,7 +12477,7 @@
         <v>227</v>
       </c>
       <c r="H269" s="51">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="I269" s="51">
         <v>249</v>
@@ -12500,7 +12492,7 @@
         <v>228</v>
       </c>
       <c r="H270" s="51">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I270" s="51">
         <v>249</v>
@@ -12515,7 +12507,7 @@
         <v>229</v>
       </c>
       <c r="H271" s="51">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I271" s="51">
         <v>249</v>
@@ -12530,7 +12522,7 @@
         <v>230</v>
       </c>
       <c r="H272" s="51">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I272" s="51">
         <v>249</v>
@@ -12598,9 +12590,7 @@
       <c r="G277" t="s">
         <v>226</v>
       </c>
-      <c r="H277" s="51">
-        <v>3</v>
-      </c>
+      <c r="H277" s="51"/>
       <c r="I277" s="51">
         <v>52</v>
       </c>
@@ -12613,9 +12603,7 @@
       <c r="G278" t="s">
         <v>227</v>
       </c>
-      <c r="H278" s="51">
-        <v>2</v>
-      </c>
+      <c r="H278" s="51"/>
       <c r="I278" s="51">
         <v>52</v>
       </c>
@@ -12628,9 +12616,7 @@
       <c r="G279" t="s">
         <v>228</v>
       </c>
-      <c r="H279" s="51">
-        <v>4</v>
-      </c>
+      <c r="H279" s="51"/>
       <c r="I279" s="51">
         <v>52</v>
       </c>
@@ -12643,9 +12629,7 @@
       <c r="G280" t="s">
         <v>229</v>
       </c>
-      <c r="H280" s="51">
-        <v>1</v>
-      </c>
+      <c r="H280" s="51"/>
       <c r="I280" s="51">
         <v>52</v>
       </c>
@@ -12658,9 +12642,7 @@
       <c r="G281" t="s">
         <v>230</v>
       </c>
-      <c r="H281" s="51">
-        <v>2</v>
-      </c>
+      <c r="H281" s="51"/>
       <c r="I281" s="51">
         <v>52</v>
       </c>
@@ -12791,7 +12773,7 @@
         <v>222</v>
       </c>
       <c r="H291">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I291" s="51">
         <v>169</v>
@@ -12806,7 +12788,7 @@
         <v>223</v>
       </c>
       <c r="H292">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I292" s="51">
         <v>169</v>
@@ -12821,7 +12803,7 @@
         <v>224</v>
       </c>
       <c r="H293">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I293" s="51">
         <v>169</v>
@@ -12836,7 +12818,7 @@
         <v>225</v>
       </c>
       <c r="H294">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I294" s="51">
         <v>169</v>
@@ -12851,7 +12833,7 @@
         <v>226</v>
       </c>
       <c r="H295">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="I295" s="51">
         <v>169</v>
@@ -12866,7 +12848,7 @@
         <v>227</v>
       </c>
       <c r="H296">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I296" s="51">
         <v>169</v>
@@ -12881,7 +12863,7 @@
         <v>228</v>
       </c>
       <c r="H297" s="51">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I297" s="51">
         <v>169</v>
@@ -12896,7 +12878,7 @@
         <v>229</v>
       </c>
       <c r="H298">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I298" s="51">
         <v>169</v>
@@ -12911,7 +12893,7 @@
         <v>230</v>
       </c>
       <c r="H299" s="51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I299" s="51">
         <v>169</v>
@@ -13067,7 +13049,7 @@
         <v>222</v>
       </c>
       <c r="H309">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I309" s="51">
         <v>260</v>
@@ -13082,7 +13064,7 @@
         <v>223</v>
       </c>
       <c r="H310">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I310" s="51">
         <v>260</v>
@@ -13097,7 +13079,7 @@
         <v>224</v>
       </c>
       <c r="H311">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="I311" s="51">
         <v>260</v>
@@ -13112,7 +13094,7 @@
         <v>225</v>
       </c>
       <c r="H312">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I312" s="51">
         <v>260</v>
@@ -13127,7 +13109,7 @@
         <v>226</v>
       </c>
       <c r="H313">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="I313" s="51">
         <v>260</v>
@@ -13142,7 +13124,7 @@
         <v>227</v>
       </c>
       <c r="H314">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I314" s="51">
         <v>260</v>
@@ -13157,7 +13139,7 @@
         <v>228</v>
       </c>
       <c r="H315" s="51">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I315" s="51">
         <v>260</v>
@@ -13172,7 +13154,7 @@
         <v>229</v>
       </c>
       <c r="H316">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I316" s="51">
         <v>260</v>
@@ -13187,7 +13169,7 @@
         <v>230</v>
       </c>
       <c r="H317" s="51">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I317" s="51">
         <v>260</v>
@@ -13220,7 +13202,7 @@
         <v>223</v>
       </c>
       <c r="H319" s="51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I319" s="51">
         <v>101</v>
@@ -13286,7 +13268,7 @@
         <v>228</v>
       </c>
       <c r="H324" s="51">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I324" s="51">
         <v>101</v>
@@ -13341,9 +13323,6 @@
       <c r="G328" t="s">
         <v>223</v>
       </c>
-      <c r="H328">
-        <v>1</v>
-      </c>
       <c r="I328" s="51">
         <v>105</v>
       </c>
@@ -13407,7 +13386,7 @@
         <v>228</v>
       </c>
       <c r="H333" s="51">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I333" s="51">
         <v>105</v>
@@ -13466,7 +13445,7 @@
         <v>223</v>
       </c>
       <c r="H337" s="51">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I337" s="51">
         <v>202</v>
@@ -13481,7 +13460,7 @@
         <v>224</v>
       </c>
       <c r="H338" s="51">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="I338" s="51">
         <v>202</v>
@@ -13496,7 +13475,7 @@
         <v>225</v>
       </c>
       <c r="H339" s="51">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I339" s="51">
         <v>202</v>
@@ -13511,7 +13490,7 @@
         <v>226</v>
       </c>
       <c r="H340">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="I340" s="51">
         <v>202</v>
@@ -13526,7 +13505,7 @@
         <v>227</v>
       </c>
       <c r="H341" s="51">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="I341" s="51">
         <v>202</v>
@@ -13541,7 +13520,7 @@
         <v>228</v>
       </c>
       <c r="H342" s="51">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I342" s="51">
         <v>202</v>
@@ -13556,7 +13535,7 @@
         <v>229</v>
       </c>
       <c r="H343" s="51">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I343" s="51">
         <v>202</v>
@@ -13571,7 +13550,7 @@
         <v>230</v>
       </c>
       <c r="H344" s="51">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I344" s="51">
         <v>202</v>
@@ -13728,7 +13707,7 @@
       </c>
       <c r="H354" s="51"/>
       <c r="I354" s="51">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="355" spans="5:9" x14ac:dyDescent="0.25">
@@ -13741,7 +13720,7 @@
       </c>
       <c r="H355" s="51"/>
       <c r="I355" s="51">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="356" spans="5:9" x14ac:dyDescent="0.25">
@@ -13754,7 +13733,7 @@
       </c>
       <c r="H356" s="51"/>
       <c r="I356" s="51">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="357" spans="5:9" x14ac:dyDescent="0.25">
@@ -13767,7 +13746,7 @@
       </c>
       <c r="H357" s="51"/>
       <c r="I357" s="51">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="358" spans="5:9" x14ac:dyDescent="0.25">
@@ -13780,7 +13759,7 @@
       </c>
       <c r="H358" s="51"/>
       <c r="I358" s="51">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="359" spans="5:9" x14ac:dyDescent="0.25">
@@ -13793,7 +13772,7 @@
       </c>
       <c r="H359" s="51"/>
       <c r="I359" s="51">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="360" spans="5:9" x14ac:dyDescent="0.25">
@@ -13805,10 +13784,10 @@
         <v>228</v>
       </c>
       <c r="H360" s="51">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I360" s="51">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="361" spans="5:9" x14ac:dyDescent="0.25">
@@ -13821,7 +13800,7 @@
       </c>
       <c r="H361" s="51"/>
       <c r="I361" s="51">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="362" spans="5:9" x14ac:dyDescent="0.25">
@@ -13834,7 +13813,7 @@
       </c>
       <c r="H362" s="51"/>
       <c r="I362" s="51">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="363" spans="5:9" x14ac:dyDescent="0.25">
@@ -13968,11 +13947,8 @@
       <c r="G372" t="s">
         <v>222</v>
       </c>
-      <c r="H372">
-        <v>1</v>
-      </c>
       <c r="I372">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="373" spans="5:9" x14ac:dyDescent="0.25">
@@ -13983,8 +13959,11 @@
       <c r="G373" t="s">
         <v>223</v>
       </c>
+      <c r="H373">
+        <v>1</v>
+      </c>
       <c r="I373">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="374" spans="5:9" x14ac:dyDescent="0.25">
@@ -13996,7 +13975,7 @@
         <v>224</v>
       </c>
       <c r="I374">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="375" spans="5:9" x14ac:dyDescent="0.25">
@@ -14008,7 +13987,7 @@
         <v>225</v>
       </c>
       <c r="I375">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="376" spans="5:9" x14ac:dyDescent="0.25">
@@ -14020,7 +13999,7 @@
         <v>226</v>
       </c>
       <c r="I376">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="377" spans="5:9" x14ac:dyDescent="0.25">
@@ -14032,7 +14011,7 @@
         <v>227</v>
       </c>
       <c r="I377">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="378" spans="5:9" x14ac:dyDescent="0.25">
@@ -14044,7 +14023,7 @@
         <v>228</v>
       </c>
       <c r="I378">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="379" spans="5:9" x14ac:dyDescent="0.25">
@@ -14056,7 +14035,7 @@
         <v>229</v>
       </c>
       <c r="I379">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="380" spans="5:9" x14ac:dyDescent="0.25">
@@ -14068,7 +14047,7 @@
         <v>230</v>
       </c>
       <c r="I380">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="381" spans="5:9" x14ac:dyDescent="0.25">
@@ -14110,7 +14089,7 @@
         <v>224</v>
       </c>
       <c r="H383">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I383">
         <v>113</v>
@@ -14151,9 +14130,6 @@
       <c r="G386" t="s">
         <v>227</v>
       </c>
-      <c r="H386">
-        <v>1</v>
-      </c>
       <c r="I386">
         <v>113</v>
       </c>
@@ -14209,7 +14185,7 @@
         <v>222</v>
       </c>
       <c r="H390">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I390">
         <v>195</v>
@@ -14224,7 +14200,7 @@
         <v>223</v>
       </c>
       <c r="H391">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I391">
         <v>195</v>
@@ -14239,7 +14215,7 @@
         <v>224</v>
       </c>
       <c r="H392">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I392">
         <v>195</v>
@@ -14254,7 +14230,7 @@
         <v>225</v>
       </c>
       <c r="H393">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I393">
         <v>195</v>
@@ -14269,7 +14245,7 @@
         <v>226</v>
       </c>
       <c r="H394">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I394">
         <v>195</v>
@@ -14284,7 +14260,7 @@
         <v>227</v>
       </c>
       <c r="H395">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="I395">
         <v>195</v>
@@ -14299,7 +14275,7 @@
         <v>228</v>
       </c>
       <c r="H396">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I396">
         <v>195</v>
@@ -14314,7 +14290,7 @@
         <v>229</v>
       </c>
       <c r="H397">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I397">
         <v>195</v>
@@ -14329,7 +14305,7 @@
         <v>230</v>
       </c>
       <c r="H398">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I398">
         <v>195</v>
@@ -14347,7 +14323,7 @@
         <v>222</v>
       </c>
       <c r="H399">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I399">
         <v>161</v>
@@ -14362,7 +14338,7 @@
         <v>223</v>
       </c>
       <c r="H400">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I400">
         <v>161</v>
@@ -14377,7 +14353,7 @@
         <v>224</v>
       </c>
       <c r="H401">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I401">
         <v>161</v>
@@ -14392,7 +14368,7 @@
         <v>225</v>
       </c>
       <c r="H402">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I402">
         <v>161</v>
@@ -14407,7 +14383,7 @@
         <v>226</v>
       </c>
       <c r="H403">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I403">
         <v>161</v>
@@ -14422,7 +14398,7 @@
         <v>227</v>
       </c>
       <c r="H404">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="I404">
         <v>161</v>
@@ -14452,7 +14428,7 @@
         <v>229</v>
       </c>
       <c r="H406">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I406">
         <v>161</v>
@@ -14467,7 +14443,7 @@
         <v>230</v>
       </c>
       <c r="H407">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I407">
         <v>161</v>

--- a/data/ventas.xlsx
+++ b/data/ventas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cesar\Desktop\Reportes Ventas Rap\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1ED77F2B-C804-4A4C-B2B1-B2CB88BD6181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BE1BB90A-BFEB-48EE-87C3-D034647CF518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="231">
   <si>
     <t>GOMEZ MARTÍN</t>
   </si>
@@ -761,12 +761,6 @@
   </si>
   <si>
     <t>145 - PILAS</t>
-  </si>
-  <si>
-    <t>42 - ROMERO ARIEL</t>
-  </si>
-  <si>
-    <t>123 - TORRES ROLANDO</t>
   </si>
 </sst>
 </file>
@@ -950,6 +944,7 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="41">
@@ -2487,7 +2482,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34" bestFit="1" customWidth="1"/>
@@ -2534,22 +2529,22 @@
         <v>0</v>
       </c>
       <c r="C2" s="96">
-        <v>20239.264746040899</v>
+        <v>12759.648138517299</v>
       </c>
       <c r="D2" s="96">
-        <v>97497.216435570401</v>
+        <v>61262.625914064098</v>
       </c>
       <c r="E2" s="96">
-        <v>347488527.93282223</v>
+        <v>223094212.44056469</v>
       </c>
       <c r="F2" s="96">
         <v>0</v>
       </c>
       <c r="G2" s="96">
-        <v>208601.67291691661</v>
+        <v>141404.35170655229</v>
       </c>
       <c r="H2" s="96">
-        <v>208601.74</v>
+        <v>141404.38</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -2560,22 +2555,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="96">
-        <v>287.35735488500001</v>
+        <v>168.2765046287</v>
       </c>
       <c r="D3" s="96">
-        <v>636.38716535089998</v>
+        <v>491.7907233853</v>
       </c>
       <c r="E3" s="96">
-        <v>6953389.0972305397</v>
+        <v>4713478.3902184051</v>
       </c>
       <c r="F3" s="96">
         <v>0</v>
       </c>
       <c r="G3" s="96">
-        <v>208601.67291691661</v>
+        <v>141404.35170655229</v>
       </c>
       <c r="H3" s="96">
-        <v>208601.74</v>
+        <v>141404.38</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2586,13 +2581,13 @@
         <v>1</v>
       </c>
       <c r="C4" s="96">
-        <v>155.42341269729999</v>
+        <v>89.716765872799996</v>
       </c>
       <c r="D4" s="96">
-        <v>326.98499999799998</v>
+        <v>228.65250000060001</v>
       </c>
       <c r="E4" s="96">
-        <v>4842984.6712837927</v>
+        <v>3490474.4748070529</v>
       </c>
       <c r="F4" s="96">
         <v>0</v>
@@ -2612,13 +2607,13 @@
         <v>1</v>
       </c>
       <c r="C5" s="96">
-        <v>200.08797618950001</v>
+        <v>113.08222222160001</v>
       </c>
       <c r="D5" s="96">
-        <v>776.02249999560001</v>
+        <v>487.77000000160001</v>
       </c>
       <c r="E5" s="96">
-        <v>4538116.0675083203</v>
+        <v>2539362.2668490014</v>
       </c>
       <c r="F5" s="96">
         <v>0</v>
@@ -2638,13 +2633,13 @@
         <v>1</v>
       </c>
       <c r="C6" s="96">
-        <v>397.30575396749998</v>
+        <v>319.23392857089999</v>
       </c>
       <c r="D6" s="96">
-        <v>1116.1477142923</v>
+        <v>1011.7841785766</v>
       </c>
       <c r="E6" s="96">
-        <v>7971555.33420307</v>
+        <v>5960130.3637676956</v>
       </c>
       <c r="F6" s="96">
         <v>0</v>
@@ -2664,13 +2659,13 @@
         <v>1</v>
       </c>
       <c r="C7" s="96">
-        <v>418.16251984000002</v>
+        <v>219.94720238030001</v>
       </c>
       <c r="D7" s="96">
-        <v>1324.0909999978001</v>
+        <v>984.96450000130005</v>
       </c>
       <c r="E7" s="96">
-        <v>8068882.1386908181</v>
+        <v>4232380.5042614806</v>
       </c>
       <c r="F7" s="96">
         <v>0</v>
@@ -2690,13 +2685,13 @@
         <v>1</v>
       </c>
       <c r="C8" s="96">
-        <v>1635.1115740742</v>
+        <v>1614.9333333334</v>
       </c>
       <c r="D8" s="96">
-        <v>1870.3864768542001</v>
+        <v>1507.4840000014001</v>
       </c>
       <c r="E8" s="96">
-        <v>17061083.040882383</v>
+        <v>16463801.298558187</v>
       </c>
       <c r="F8" s="96">
         <v>0</v>
@@ -2716,13 +2711,13 @@
         <v>1</v>
       </c>
       <c r="C9" s="96">
-        <v>198.23150793619999</v>
+        <v>113.1691071427</v>
       </c>
       <c r="D9" s="96">
-        <v>911.56750000140005</v>
+        <v>643.5574999982</v>
       </c>
       <c r="E9" s="96">
-        <v>3586477.5079781078</v>
+        <v>2229458.8498637299</v>
       </c>
       <c r="F9" s="96">
         <v>0</v>
@@ -2742,13 +2737,13 @@
         <v>1</v>
       </c>
       <c r="C10" s="96">
-        <v>151.87760912690001</v>
+        <v>67.089751984100005</v>
       </c>
       <c r="D10" s="96">
-        <v>538.00411458880001</v>
+        <v>200.80203124760001</v>
       </c>
       <c r="E10" s="96">
-        <v>3996158.8131728824</v>
+        <v>2237337.654012111</v>
       </c>
       <c r="F10" s="96">
         <v>0</v>
@@ -2768,13 +2763,13 @@
         <v>1</v>
       </c>
       <c r="C11" s="96">
-        <v>157.76408730060001</v>
+        <v>69.604761904499995</v>
       </c>
       <c r="D11" s="96">
-        <v>362.56459523730001</v>
+        <v>303.04959523730003</v>
       </c>
       <c r="E11" s="96">
-        <v>2958594.3353685732</v>
+        <v>1556471.8667402903</v>
       </c>
       <c r="F11" s="96">
         <v>0</v>
@@ -2794,13 +2789,13 @@
         <v>1</v>
       </c>
       <c r="C12" s="96">
-        <v>376.22777777610003</v>
+        <v>178.19682539589999</v>
       </c>
       <c r="D12" s="96">
-        <v>2353.8501190427</v>
+        <v>527.69845237909999</v>
       </c>
       <c r="E12" s="96">
-        <v>6404448.8053096188</v>
+        <v>3454829.7358999122</v>
       </c>
       <c r="F12" s="96">
         <v>0</v>
@@ -2820,13 +2815,13 @@
         <v>1</v>
       </c>
       <c r="C13" s="96">
-        <v>340.59277777739999</v>
+        <v>225.7950396821</v>
       </c>
       <c r="D13" s="96">
-        <v>1049.3365119081</v>
+        <v>829.79151190790003</v>
       </c>
       <c r="E13" s="96">
-        <v>6622431.8650625329</v>
+        <v>4650179.1579327742</v>
       </c>
       <c r="F13" s="96">
         <v>0</v>
@@ -2846,13 +2841,13 @@
         <v>1</v>
       </c>
       <c r="C14" s="96">
-        <v>1689.6688492064</v>
+        <v>1444.0819444447</v>
       </c>
       <c r="D14" s="96">
-        <v>14984.7324999998</v>
+        <v>13580.7225000012</v>
       </c>
       <c r="E14" s="96">
-        <v>39689592.681744099</v>
+        <v>35677866.984969728</v>
       </c>
       <c r="F14" s="96">
         <v>0</v>
@@ -2872,13 +2867,13 @@
         <v>1</v>
       </c>
       <c r="C15" s="96">
-        <v>322.91230158680003</v>
+        <v>203.11855158700001</v>
       </c>
       <c r="D15" s="96">
-        <v>1065.8074999979999</v>
+        <v>755.52499999940005</v>
       </c>
       <c r="E15" s="96">
-        <v>6197917.8190731332</v>
+        <v>3799689.1529486589</v>
       </c>
       <c r="F15" s="96">
         <v>0</v>
@@ -2898,13 +2893,13 @@
         <v>1</v>
       </c>
       <c r="C16" s="96">
-        <v>214.65501984030001</v>
+        <v>128.3049206343</v>
       </c>
       <c r="D16" s="96">
-        <v>1133.6685119097999</v>
+        <v>693.45458333670001</v>
       </c>
       <c r="E16" s="96">
-        <v>5255755.4759214995</v>
+        <v>3126324.9965506792</v>
       </c>
       <c r="F16" s="96">
         <v>0</v>
@@ -2924,13 +2919,13 @@
         <v>1</v>
       </c>
       <c r="C17" s="96">
-        <v>480.26246031580001</v>
+        <v>214.7180555544</v>
       </c>
       <c r="D17" s="96">
-        <v>1416.7735238169</v>
+        <v>616.00885714909998</v>
       </c>
       <c r="E17" s="96">
-        <v>9288875.7683896385</v>
+        <v>5092283.3348378455</v>
       </c>
       <c r="F17" s="96">
         <v>0</v>
@@ -2950,13 +2945,13 @@
         <v>1</v>
       </c>
       <c r="C18" s="96">
-        <v>588.94634920609997</v>
+        <v>339.81365079310001</v>
       </c>
       <c r="D18" s="96">
-        <v>2848.4188452368999</v>
+        <v>2209.1249285679</v>
       </c>
       <c r="E18" s="96">
-        <v>12202147.531287048</v>
+        <v>6538018.3834050605</v>
       </c>
       <c r="F18" s="96">
         <v>0</v>
@@ -2976,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="C19" s="96">
-        <v>441.94708994609999</v>
+        <v>242.1867394173</v>
       </c>
       <c r="D19" s="96">
-        <v>1784.6717142952</v>
+        <v>821.9142142938</v>
       </c>
       <c r="E19" s="96">
-        <v>9037854.5756811257</v>
+        <v>5313079.7996425815</v>
       </c>
       <c r="F19" s="96">
         <v>0</v>
@@ -3002,13 +2997,13 @@
         <v>1</v>
       </c>
       <c r="C20" s="96">
-        <v>1691.1757341268999</v>
+        <v>1331.513234127</v>
       </c>
       <c r="D20" s="96">
-        <v>8709.6164999951998</v>
+        <v>7081.0849999985003</v>
       </c>
       <c r="E20" s="96">
-        <v>25307057.946538661</v>
+        <v>18543635.055367131</v>
       </c>
       <c r="F20" s="96">
         <v>0</v>
@@ -3028,13 +3023,13 @@
         <v>1</v>
       </c>
       <c r="C21" s="96">
-        <v>264.46081349069999</v>
+        <v>174.00490079319999</v>
       </c>
       <c r="D21" s="96">
-        <v>939.2292142901</v>
+        <v>605.7746071478</v>
       </c>
       <c r="E21" s="96">
-        <v>5595341.8938343767</v>
+        <v>3621062.6775038806</v>
       </c>
       <c r="F21" s="96">
         <v>0</v>
@@ -3054,13 +3049,13 @@
         <v>1</v>
       </c>
       <c r="C22" s="96">
-        <v>197.9982142849</v>
+        <v>123.90625</v>
       </c>
       <c r="D22" s="96">
-        <v>505.67851190179999</v>
+        <v>291.22892856869998</v>
       </c>
       <c r="E22" s="96">
-        <v>3109025.2196221473</v>
+        <v>1931060.2247250369</v>
       </c>
       <c r="F22" s="96">
         <v>0</v>
@@ -3080,13 +3075,13 @@
         <v>1</v>
       </c>
       <c r="C23" s="96">
-        <v>781.37513888820001</v>
+        <v>128.10228174549999</v>
       </c>
       <c r="D23" s="96">
-        <v>4836.2267976160001</v>
+        <v>339.25166666370001</v>
       </c>
       <c r="E23" s="96">
-        <v>16984006.336814482</v>
+        <v>1999132.6820728134</v>
       </c>
       <c r="F23" s="96">
         <v>0</v>
@@ -3106,13 +3101,13 @@
         <v>1</v>
       </c>
       <c r="C24" s="96">
-        <v>731.66458333349999</v>
+        <v>748.66458333349999</v>
       </c>
       <c r="D24" s="96">
-        <v>4795.7219583328997</v>
+        <v>4813.7219583328997</v>
       </c>
       <c r="E24" s="96">
-        <v>13810777.689331688</v>
+        <v>13993499.751331689</v>
       </c>
       <c r="F24" s="96">
         <v>0</v>
@@ -3132,13 +3127,13 @@
         <v>1</v>
       </c>
       <c r="C25" s="96">
-        <v>298.05575396820001</v>
+        <v>151.11507936480001</v>
       </c>
       <c r="D25" s="96">
-        <v>850.76000000500005</v>
+        <v>563.25500000219995</v>
       </c>
       <c r="E25" s="96">
-        <v>4865926.9418352479</v>
+        <v>3265458.2459612871</v>
       </c>
       <c r="F25" s="96">
         <v>0</v>
@@ -3158,13 +3153,13 @@
         <v>1</v>
       </c>
       <c r="C26" s="96">
-        <v>200.69081349109999</v>
+        <v>78.740436507300004</v>
       </c>
       <c r="D26" s="96">
-        <v>459.23708333330001</v>
+        <v>282.00000000040001</v>
       </c>
       <c r="E26" s="96">
-        <v>3089173.5689832573</v>
+        <v>1905347.2963424551</v>
       </c>
       <c r="F26" s="96">
         <v>0</v>
@@ -3184,13 +3179,13 @@
         <v>1</v>
       </c>
       <c r="C27" s="96">
-        <v>1888.5</v>
+        <v>1334.5</v>
       </c>
       <c r="D27" s="96">
-        <v>9736.84</v>
+        <v>2577.1799999999998</v>
       </c>
       <c r="E27" s="96">
-        <v>23468686.842</v>
+        <v>13136953.343350001</v>
       </c>
       <c r="F27" s="96">
         <v>0</v>
@@ -3210,13 +3205,13 @@
         <v>1</v>
       </c>
       <c r="C28" s="96">
-        <v>424.6578339939</v>
+        <v>224.8947354492</v>
       </c>
       <c r="D28" s="96">
-        <v>1810.8346354224</v>
+        <v>1004.4995833371</v>
       </c>
       <c r="E28" s="96">
-        <v>8516814.03087065</v>
+        <v>4525419.7648018571</v>
       </c>
       <c r="F28" s="96">
         <v>0</v>
@@ -3236,13 +3231,13 @@
         <v>1</v>
       </c>
       <c r="C29" s="96">
-        <v>1351.4300000001001</v>
+        <v>386.73</v>
       </c>
       <c r="D29" s="96">
-        <v>2346.2820833356</v>
+        <v>1523.5400000018999</v>
       </c>
       <c r="E29" s="96">
-        <v>17555809.912466466</v>
+        <v>7197381.3632933144</v>
       </c>
       <c r="F29" s="96">
         <v>0</v>
@@ -3262,13 +3257,13 @@
         <v>1</v>
       </c>
       <c r="C30" s="96">
-        <v>111.48898809560001</v>
+        <v>73.557242063700002</v>
       </c>
       <c r="D30" s="96">
-        <v>371.92416667719999</v>
+        <v>290.52000000279997</v>
       </c>
       <c r="E30" s="96">
-        <v>2098536.1960838647</v>
+        <v>1342266.2312651528</v>
       </c>
       <c r="F30" s="96">
         <v>0</v>
@@ -3288,13 +3283,13 @@
         <v>1</v>
       </c>
       <c r="C31" s="96">
-        <v>172.14345238000001</v>
+        <v>90.458531745100004</v>
       </c>
       <c r="D31" s="96">
-        <v>351.31749999890002</v>
+        <v>283.59499999920001</v>
       </c>
       <c r="E31" s="96">
-        <v>2883607.9842428509</v>
+        <v>1662817.6962441357</v>
       </c>
       <c r="F31" s="96">
         <v>0</v>
@@ -3314,13 +3309,13 @@
         <v>1</v>
       </c>
       <c r="C32" s="96">
-        <v>55.931944444599999</v>
+        <v>28.535912698600001</v>
       </c>
       <c r="D32" s="96">
-        <v>392.40416666760001</v>
+        <v>178.64666666860001</v>
       </c>
       <c r="E32" s="96">
-        <v>1626463.4655310514</v>
+        <v>920475.59202497394</v>
       </c>
       <c r="F32" s="96">
         <v>0</v>
@@ -3340,13 +3335,13 @@
         <v>1</v>
       </c>
       <c r="C33" s="96">
-        <v>308.6682738092</v>
+        <v>215.69446428559999</v>
       </c>
       <c r="D33" s="96">
-        <v>704.99600000179998</v>
+        <v>439.00999999959998</v>
       </c>
       <c r="E33" s="96">
-        <v>4975553.6144345868</v>
+        <v>2806120.8392654946</v>
       </c>
       <c r="F33" s="96">
         <v>0</v>
@@ -3360,19 +3355,19 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="96" t="s">
-        <v>231</v>
+        <v>206</v>
       </c>
       <c r="B34" s="96">
         <v>1</v>
       </c>
       <c r="C34" s="96">
-        <v>25.288194444399998</v>
+        <v>-25</v>
       </c>
       <c r="D34" s="96">
-        <v>354.02</v>
+        <v>0</v>
       </c>
       <c r="E34" s="96">
-        <v>715253.15687714703</v>
+        <v>-233849</v>
       </c>
       <c r="F34" s="96">
         <v>0</v>
@@ -3386,19 +3381,19 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="96" t="s">
-        <v>206</v>
+        <v>162</v>
       </c>
       <c r="B35" s="96">
         <v>1</v>
       </c>
       <c r="C35" s="96">
-        <v>-25</v>
+        <v>186.83611111089999</v>
       </c>
       <c r="D35" s="96">
-        <v>0</v>
+        <v>804.41601190910001</v>
       </c>
       <c r="E35" s="96">
-        <v>-233849</v>
+        <v>3880349.2779353959</v>
       </c>
       <c r="F35" s="96">
         <v>0</v>
@@ -3412,19 +3407,19 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="96" t="s">
-        <v>162</v>
+        <v>107</v>
       </c>
       <c r="B36" s="96">
         <v>1</v>
       </c>
       <c r="C36" s="96">
-        <v>285.49811507840002</v>
+        <v>414.39123015899997</v>
       </c>
       <c r="D36" s="96">
-        <v>1243.7466071438</v>
+        <v>2342.8888214259</v>
       </c>
       <c r="E36" s="96">
-        <v>5822405.6030015703</v>
+        <v>7342359.2744361712</v>
       </c>
       <c r="F36" s="96">
         <v>0</v>
@@ -3438,19 +3433,19 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="96" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B37" s="96">
         <v>1</v>
       </c>
       <c r="C37" s="96">
-        <v>414.39123015899997</v>
+        <v>197.30909090899999</v>
       </c>
       <c r="D37" s="96">
-        <v>2342.8888214259</v>
+        <v>2277.9899999992999</v>
       </c>
       <c r="E37" s="96">
-        <v>7342359.2744361712</v>
+        <v>4699575.8856638623</v>
       </c>
       <c r="F37" s="96">
         <v>0</v>
@@ -3464,19 +3459,19 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="96" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B38" s="96">
         <v>1</v>
       </c>
       <c r="C38" s="96">
-        <v>308.39242424230002</v>
+        <v>283.9166666667</v>
       </c>
       <c r="D38" s="96">
-        <v>3260.7299999989</v>
+        <v>3082.25</v>
       </c>
       <c r="E38" s="96">
-        <v>6663134.8062294191</v>
+        <v>5825319.4707523696</v>
       </c>
       <c r="F38" s="96">
         <v>0</v>
@@ -3490,19 +3485,19 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="96" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B39" s="96">
         <v>1</v>
       </c>
       <c r="C39" s="96">
-        <v>471.4166666667</v>
+        <v>131.14181216910001</v>
       </c>
       <c r="D39" s="96">
-        <v>5734.2</v>
+        <v>471.4394986822</v>
       </c>
       <c r="E39" s="96">
-        <v>10196205.867152149</v>
+        <v>3150944.560423614</v>
       </c>
       <c r="F39" s="96">
         <v>0</v>
@@ -3516,19 +3511,19 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="96" t="s">
-        <v>109</v>
+        <v>140</v>
       </c>
       <c r="B40" s="96">
         <v>1</v>
       </c>
       <c r="C40" s="96">
-        <v>757.61760582019997</v>
+        <v>548.43968253950004</v>
       </c>
       <c r="D40" s="96">
-        <v>4224.4444986853996</v>
+        <v>4046.0241666669999</v>
       </c>
       <c r="E40" s="96">
-        <v>6909391.5039921645</v>
+        <v>7402539.5016198214</v>
       </c>
       <c r="F40" s="96">
         <v>0</v>
@@ -3542,19 +3537,19 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="96" t="s">
-        <v>140</v>
+        <v>217</v>
       </c>
       <c r="B41" s="96">
         <v>1</v>
       </c>
       <c r="C41" s="96">
-        <v>679.35634920610005</v>
+        <v>6</v>
       </c>
       <c r="D41" s="96">
-        <v>4883.0241666669999</v>
+        <v>81</v>
       </c>
       <c r="E41" s="96">
-        <v>8825883.2392010316</v>
+        <v>149294.68419999999</v>
       </c>
       <c r="F41" s="96">
         <v>0</v>
@@ -3568,19 +3563,19 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="96" t="s">
-        <v>217</v>
+        <v>145</v>
       </c>
       <c r="B42" s="96">
         <v>1</v>
       </c>
       <c r="C42" s="96">
-        <v>32</v>
+        <v>-6.2142857142999999</v>
       </c>
       <c r="D42" s="96">
-        <v>424.04</v>
+        <v>-6.2810714286999998</v>
       </c>
       <c r="E42" s="96">
-        <v>746511.00490000006</v>
+        <v>-275260.76904147147</v>
       </c>
       <c r="F42" s="96">
         <v>0</v>
@@ -3594,19 +3589,19 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="96" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B43" s="96">
         <v>1</v>
       </c>
       <c r="C43" s="96">
-        <v>74.818551587300007</v>
+        <v>-3.2847222223000001</v>
       </c>
       <c r="D43" s="96">
-        <v>229.00349106979999</v>
+        <v>-20.505000001599999</v>
       </c>
       <c r="E43" s="96">
-        <v>3760393.1741207056</v>
+        <v>-402349.89063324447</v>
       </c>
       <c r="F43" s="96">
         <v>0</v>
@@ -3620,19 +3615,19 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="96" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="B44" s="96">
         <v>1</v>
       </c>
       <c r="C44" s="96">
-        <v>123.917063492</v>
+        <v>184.42559523840001</v>
       </c>
       <c r="D44" s="96">
-        <v>1239.6349404736</v>
+        <v>2016.0000000025</v>
       </c>
       <c r="E44" s="96">
-        <v>1913900.6624423866</v>
+        <v>3629491.4663937623</v>
       </c>
       <c r="F44" s="96">
         <v>0</v>
@@ -3641,58 +3636,6 @@
         <v>0</v>
       </c>
       <c r="H44" s="96">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="96" t="s">
-        <v>156</v>
-      </c>
-      <c r="B45" s="96">
-        <v>1</v>
-      </c>
-      <c r="C45" s="96">
-        <v>234.9175793654</v>
-      </c>
-      <c r="D45" s="96">
-        <v>2276.0000000041</v>
-      </c>
-      <c r="E45" s="96">
-        <v>4664188.216696891</v>
-      </c>
-      <c r="F45" s="96">
-        <v>0</v>
-      </c>
-      <c r="G45" s="96">
-        <v>0</v>
-      </c>
-      <c r="H45" s="96">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="96" t="s">
-        <v>232</v>
-      </c>
-      <c r="B46" s="96">
-        <v>1</v>
-      </c>
-      <c r="C46" s="96">
-        <v>321.875</v>
-      </c>
-      <c r="D46" s="96">
-        <v>-24.9999999996</v>
-      </c>
-      <c r="E46" s="96">
-        <v>1599703.2523960921</v>
-      </c>
-      <c r="F46" s="96">
-        <v>0</v>
-      </c>
-      <c r="G46" s="96">
-        <v>0</v>
-      </c>
-      <c r="H46" s="96">
         <v>0</v>
       </c>
     </row>
@@ -3773,44 +3716,44 @@
       </c>
       <c r="D2" s="59">
         <f>IFERROR(+VLOOKUP(B2,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>12202147.531287048</v>
+        <v>6538018.3834050605</v>
       </c>
       <c r="E2" s="59">
-        <v>10180781.322442733</v>
+        <v>4682028.2206923608</v>
       </c>
       <c r="F2" s="59">
         <f t="shared" ref="F2:F9" si="0">+D2-E2</f>
-        <v>2021366.2088443153</v>
+        <v>1855990.1627126997</v>
       </c>
       <c r="G2" s="60">
         <f t="shared" ref="G2:G41" si="1">+D2/C2</f>
-        <v>0.3780203401737795</v>
+        <v>0.20254663591143432</v>
       </c>
       <c r="H2" s="59">
         <f>+D2/$N$3*$N$4</f>
-        <v>58570308.150177836</v>
+        <v>52304147.067240477</v>
       </c>
       <c r="I2" s="60">
         <f t="shared" ref="I2:I41" si="2">+H2/C2</f>
-        <v>1.8144976328341418</v>
+        <v>1.6203730872914743</v>
       </c>
       <c r="J2" s="59">
         <f>+D2/$N$3</f>
-        <v>2440429.5062574097</v>
+        <v>2179339.46113502</v>
       </c>
       <c r="K2" s="59">
         <f t="shared" ref="K2:K41" si="3">+(C2-D2)/$N$2</f>
-        <v>1056680.4793138793</v>
+        <v>1225764.6788021759</v>
       </c>
       <c r="L2" s="61" cm="1">
         <f t="array" ref="L2">+_xlfn.IFS(I2&gt;114%,H2*0.02,I2&gt;109%,H2*0.015,I2&gt;104%,H2*0.0125,I2&gt;99%,H2*0.01,I2&lt;99%,H2*0)</f>
-        <v>1171406.1630035567</v>
+        <v>1046082.9413448096</v>
       </c>
       <c r="M2" s="53" t="s">
         <v>36</v>
       </c>
       <c r="N2">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -3823,45 +3766,45 @@
       </c>
       <c r="D3" s="4">
         <f>IFERROR(+VLOOKUP(B3,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>9288875.7683896385</v>
+        <v>5092283.3348378455</v>
       </c>
       <c r="E3" s="4">
-        <v>6362623.1530077159</v>
+        <v>2774896.9225576972</v>
       </c>
       <c r="F3" s="4">
         <f t="shared" si="0"/>
-        <v>2926252.6153819226</v>
+        <v>2317386.4122801484</v>
       </c>
       <c r="G3" s="5">
         <f t="shared" si="1"/>
-        <v>0.29980819360899963</v>
+        <v>0.16435877774987445</v>
       </c>
       <c r="H3" s="4">
         <f t="shared" ref="H3:H41" si="4">+D3/$N$3*$N$4</f>
-        <v>44586603.688270271</v>
+        <v>40738266.678702764</v>
       </c>
       <c r="I3" s="5">
         <f t="shared" si="2"/>
-        <v>1.4390793293231983</v>
+        <v>1.3148702219989956</v>
       </c>
       <c r="J3" s="4">
         <f t="shared" ref="J3:J41" si="5">+D3/$N$3</f>
-        <v>1857775.1536779278</v>
+        <v>1697427.7782792819</v>
       </c>
       <c r="K3" s="4">
         <f t="shared" si="3"/>
-        <v>1141781.7058154535</v>
+        <v>1232878.3259069242</v>
       </c>
       <c r="L3" s="63" cm="1">
         <f t="array" ref="L3">+_xlfn.IFS(I3&gt;114%,H3*0.02,I3&gt;109%,H3*0.015,I3&gt;104%,H3*0.0125,I3&gt;99%,H3*0.01,I3&lt;99%,H3*0)</f>
-        <v>891732.07376540545</v>
+        <v>814765.33357405534</v>
       </c>
       <c r="M3" s="53" t="s">
         <v>40</v>
       </c>
       <c r="N3">
         <f>N4-N2</f>
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -3874,38 +3817,38 @@
       </c>
       <c r="D4" s="4">
         <f>IFERROR(+VLOOKUP(B4,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>6197917.8190731332</v>
+        <v>3799689.1529486589</v>
       </c>
       <c r="E4" s="4">
-        <v>4655359.4802594241</v>
+        <v>2224929.6365325735</v>
       </c>
       <c r="F4" s="4">
         <f t="shared" si="0"/>
-        <v>1542558.3388137091</v>
+        <v>1574759.5164160854</v>
       </c>
       <c r="G4" s="5">
         <f t="shared" si="1"/>
-        <v>0.21831317346146409</v>
+        <v>0.13383885062086462</v>
       </c>
       <c r="H4" s="4">
         <f t="shared" si="4"/>
-        <v>29750005.531551037</v>
+        <v>30397513.223589271</v>
       </c>
       <c r="I4" s="5">
         <f t="shared" si="2"/>
-        <v>1.0479032326150275</v>
+        <v>1.070710804966917</v>
       </c>
       <c r="J4" s="4">
         <f t="shared" si="5"/>
-        <v>1239583.5638146265</v>
+        <v>1266563.0509828862</v>
       </c>
       <c r="K4" s="4">
         <f t="shared" si="3"/>
-        <v>1168005.970582901</v>
+        <v>1170968.6717714092</v>
       </c>
       <c r="L4" s="63" cm="1">
         <f t="array" ref="L4">+_xlfn.IFS(I4&gt;114%,H4*0.02,I4&gt;109%,H4*0.015,I4&gt;104%,H4*0.0125,I4&gt;99%,H4*0.01,I4&lt;99%,H4*0)</f>
-        <v>371875.06914438796</v>
+        <v>379968.9152948659</v>
       </c>
       <c r="M4" s="53" t="s">
         <v>47</v>
@@ -3924,38 +3867,38 @@
       </c>
       <c r="D5" s="4">
         <f>IFERROR(+VLOOKUP(B5,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>6622431.8650625329</v>
+        <v>4650179.1579327742</v>
       </c>
       <c r="E5" s="4">
-        <v>5672001.5032034451</v>
+        <v>3752668.2666791501</v>
       </c>
       <c r="F5" s="4">
         <f t="shared" si="0"/>
-        <v>950430.36185908783</v>
+        <v>897510.89125362411</v>
       </c>
       <c r="G5" s="5">
         <f t="shared" si="1"/>
-        <v>0.23326609979322546</v>
+        <v>0.16379619716940358</v>
       </c>
       <c r="H5" s="4">
         <f t="shared" si="4"/>
-        <v>31787672.952300161</v>
+        <v>37201433.263462193</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" si="2"/>
-        <v>1.1196772790074823</v>
+        <v>1.3103695773552286</v>
       </c>
       <c r="J5" s="4">
         <f t="shared" si="5"/>
-        <v>1324486.3730125066</v>
+        <v>1550059.7193109246</v>
       </c>
       <c r="K5" s="4">
         <f t="shared" si="3"/>
-        <v>1145663.1260571433</v>
+        <v>1130469.1477245467</v>
       </c>
       <c r="L5" s="63" cm="1">
         <f t="array" ref="L5">+_xlfn.IFS(I5&gt;114%,H5*0.02,I5&gt;109%,H5*0.015,I5&gt;104%,H5*0.0125,I5&gt;99%,H5*0.01,I5&lt;99%,H5*0)</f>
-        <v>476815.09428450238</v>
+        <v>744028.66526924388</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
@@ -3968,38 +3911,38 @@
       </c>
       <c r="D6" s="4">
         <f>IFERROR(+VLOOKUP(B6,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>6404448.8053096188</v>
+        <v>3454829.7358999122</v>
       </c>
       <c r="E6" s="4">
-        <v>5810906.7980635744</v>
+        <v>1763034.9919922091</v>
       </c>
       <c r="F6" s="4">
         <f t="shared" si="0"/>
-        <v>593542.00724604446</v>
+        <v>1691794.7439077031</v>
       </c>
       <c r="G6" s="5">
         <f t="shared" si="1"/>
-        <v>0.27219702432644627</v>
+        <v>0.14683455239533538</v>
       </c>
       <c r="H6" s="4">
         <f t="shared" si="4"/>
-        <v>30741354.265486173</v>
+        <v>27638637.887199298</v>
       </c>
       <c r="I6" s="5">
         <f t="shared" si="2"/>
-        <v>1.3065457167669423</v>
+        <v>1.1746764191626831</v>
       </c>
       <c r="J6" s="4">
         <f t="shared" si="5"/>
-        <v>1280889.7610619238</v>
+        <v>1151609.9119666375</v>
       </c>
       <c r="K6" s="4">
         <f t="shared" si="3"/>
-        <v>901277.67011634237</v>
+        <v>955899.75245810545</v>
       </c>
       <c r="L6" s="63" cm="1">
         <f t="array" ref="L6">+_xlfn.IFS(I6&gt;114%,H6*0.02,I6&gt;109%,H6*0.015,I6&gt;104%,H6*0.0125,I6&gt;99%,H6*0.01,I6&lt;99%,H6*0)</f>
-        <v>614827.08530972351</v>
+        <v>552772.75774398597</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
@@ -4012,34 +3955,34 @@
       </c>
       <c r="D7" s="4">
         <f>IFERROR(+VLOOKUP(B7,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>3586477.5079781078</v>
+        <v>2229458.8498637299</v>
       </c>
       <c r="E7" s="4">
-        <v>2938195.7767915935</v>
+        <v>1244100.7657470268</v>
       </c>
       <c r="F7" s="4">
         <f t="shared" ref="F7:F8" si="6">+D7-E7</f>
-        <v>648281.73118651425</v>
+        <v>985358.08411670313</v>
       </c>
       <c r="G7" s="5">
         <f t="shared" si="1"/>
-        <v>0.12928036879577476</v>
+        <v>8.0364441623913901E-2</v>
       </c>
       <c r="H7" s="4">
         <f t="shared" si="4"/>
-        <v>17215092.038294919</v>
+        <v>17835670.798909839</v>
       </c>
       <c r="I7" s="5">
         <f t="shared" si="2"/>
-        <v>0.62054577021971891</v>
+        <v>0.64291553299131121</v>
       </c>
       <c r="J7" s="4">
         <f t="shared" si="5"/>
-        <v>717295.50159562158</v>
+        <v>743152.94995457667</v>
       </c>
       <c r="K7" s="4">
         <f t="shared" si="3"/>
-        <v>1271335.7643413893</v>
+        <v>1214876.103838132</v>
       </c>
       <c r="L7" s="63" cm="1">
         <f t="array" ref="L7">+_xlfn.IFS(I7&gt;114%,H7*0.02,I7&gt;109%,H7*0.015,I7&gt;104%,H7*0.0125,I7&gt;99%,H7*0.01,I7&lt;99%,H7*0)</f>
@@ -4056,38 +3999,38 @@
       </c>
       <c r="D8" s="4">
         <f>IFERROR(+VLOOKUP(B8,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>8068882.1386908181</v>
+        <v>4232380.5042614806</v>
       </c>
       <c r="E8" s="4">
-        <v>6168952.3513542237</v>
+        <v>2332273.4502824824</v>
       </c>
       <c r="F8" s="4">
         <f t="shared" si="6"/>
-        <v>1899929.7873365944</v>
+        <v>1900107.0539789982</v>
       </c>
       <c r="G8" s="5">
         <f t="shared" si="1"/>
-        <v>0.22519232106693524</v>
+        <v>0.11812040044839839</v>
       </c>
       <c r="H8" s="4">
         <f t="shared" si="4"/>
-        <v>38730634.265715927</v>
+        <v>33859044.034091845</v>
       </c>
       <c r="I8" s="5">
         <f t="shared" si="2"/>
-        <v>1.0809231411212892</v>
+        <v>0.94496320358718711</v>
       </c>
       <c r="J8" s="4">
         <f t="shared" si="5"/>
-        <v>1613776.4277381636</v>
+        <v>1410793.5014204935</v>
       </c>
       <c r="K8" s="4">
         <f t="shared" si="3"/>
-        <v>1461167.8567487835</v>
+        <v>1504699.5672693441</v>
       </c>
       <c r="L8" s="63" cm="1">
         <f t="array" ref="L8">+_xlfn.IFS(I8&gt;114%,H8*0.02,I8&gt;109%,H8*0.015,I8&gt;104%,H8*0.0125,I8&gt;99%,H8*0.01,I8&lt;99%,H8*0)</f>
-        <v>484132.92832144909</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
@@ -4100,38 +4043,38 @@
       </c>
       <c r="D9" s="4">
         <f>IFERROR(+VLOOKUP(B9,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>7971555.33420307</v>
+        <v>5960130.3637676956</v>
       </c>
       <c r="E9" s="4">
-        <v>6899879.8473196756</v>
+        <v>4892925.4103550436</v>
       </c>
       <c r="F9" s="4">
         <f t="shared" si="0"/>
-        <v>1071675.4868833944</v>
+        <v>1067204.953412652</v>
       </c>
       <c r="G9" s="5">
         <f t="shared" si="1"/>
-        <v>0.22247605273782814</v>
+        <v>0.16633971935747391</v>
       </c>
       <c r="H9" s="4">
         <f t="shared" si="4"/>
-        <v>38263465.604174733</v>
+        <v>47681042.910141565</v>
       </c>
       <c r="I9" s="5">
         <f t="shared" si="2"/>
-        <v>1.0678850531415751</v>
+        <v>1.3307177548597913</v>
       </c>
       <c r="J9" s="4">
         <f t="shared" si="5"/>
-        <v>1594311.066840614</v>
+        <v>1986710.1212558986</v>
       </c>
       <c r="K9" s="4">
         <f t="shared" si="3"/>
-        <v>1466290.3201428754</v>
+        <v>1422425.7644357148</v>
       </c>
       <c r="L9" s="63" cm="1">
         <f t="array" ref="L9">+_xlfn.IFS(I9&gt;114%,H9*0.02,I9&gt;109%,H9*0.015,I9&gt;104%,H9*0.0125,I9&gt;99%,H9*0.01,I9&lt;99%,H9*0)</f>
-        <v>478293.32005218416</v>
+        <v>953620.85820283135</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4142,34 +4085,34 @@
       </c>
       <c r="D10" s="64">
         <f>+SUM(D2:D9)</f>
-        <v>60342736.769993968</v>
+        <v>35956969.48291716</v>
       </c>
       <c r="E10" s="65">
-        <v>48688700.232442394</v>
+        <v>23666857.664838541</v>
       </c>
       <c r="F10" s="64">
         <f>+SUM(F2:F9)</f>
-        <v>11654036.537551582</v>
+        <v>12290111.818078615</v>
       </c>
       <c r="G10" s="66">
         <f t="shared" si="1"/>
-        <v>0.2483499872890047</v>
+        <v>0.14798654141378115</v>
       </c>
       <c r="H10" s="64">
         <f t="shared" si="4"/>
-        <v>289645136.49597102</v>
+        <v>287655755.86333728</v>
       </c>
       <c r="I10" s="66">
         <f t="shared" si="2"/>
-        <v>1.1920799389872223</v>
+        <v>1.1838923313102492</v>
       </c>
       <c r="J10" s="64">
         <f t="shared" si="5"/>
-        <v>12068547.353998793</v>
+        <v>11985656.494305721</v>
       </c>
       <c r="K10" s="67">
         <f t="shared" si="3"/>
-        <v>9612202.8931187652</v>
+        <v>9857982.0122063495</v>
       </c>
       <c r="L10" s="68"/>
     </row>
@@ -4185,38 +4128,38 @@
       </c>
       <c r="D11" s="59">
         <f>IFERROR(+VLOOKUP(B11,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>25307057.946538661</v>
+        <v>18543635.055367131</v>
       </c>
       <c r="E11" s="59">
-        <v>21714287.032106198</v>
+        <v>7023074.0484903501</v>
       </c>
       <c r="F11" s="59">
         <f t="shared" ref="F11:F16" si="7">+D11-E11</f>
-        <v>3592770.9144324623</v>
+        <v>11520561.006876782</v>
       </c>
       <c r="G11" s="60">
         <f t="shared" si="1"/>
-        <v>0.26097297562008082</v>
+        <v>0.19122679647058316</v>
       </c>
       <c r="H11" s="59">
         <f t="shared" si="4"/>
-        <v>121473878.14338556</v>
+        <v>148349080.44293705</v>
       </c>
       <c r="I11" s="60">
         <f t="shared" si="2"/>
-        <v>1.2526702829763878</v>
+        <v>1.5298143717646653</v>
       </c>
       <c r="J11" s="59">
         <f t="shared" si="5"/>
-        <v>5061411.5893077319</v>
+        <v>6181211.6851223772</v>
       </c>
       <c r="K11" s="59">
         <f t="shared" si="3"/>
-        <v>3771836.3438736238</v>
+        <v>3734681.5916557326</v>
       </c>
       <c r="L11" s="61" cm="1">
         <f t="array" ref="L11">+_xlfn.IFS(I11&gt;114%,H11*0.0125,I11&gt;109%,H11*0.01,I11&gt;104%,H11*0.0075,I11&gt;99%,H11*0.005,I11&lt;99%,H11*0)</f>
-        <v>1518423.4767923197</v>
+        <v>1854363.5055367132</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4232,11 +4175,11 @@
         <v>7342359.2744361712</v>
       </c>
       <c r="E12" s="4">
-        <v>7342359.2744361712</v>
+        <v>7395442.6965926401</v>
       </c>
       <c r="F12" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-53083.422156468965</v>
       </c>
       <c r="G12" s="5">
         <f t="shared" si="1"/>
@@ -4244,23 +4187,23 @@
       </c>
       <c r="H12" s="4">
         <f t="shared" si="4"/>
-        <v>35243324.517293625</v>
+        <v>58738874.195489362</v>
       </c>
       <c r="I12" s="5">
         <f t="shared" si="2"/>
-        <v>1.1142054710316522</v>
+        <v>1.8570091183860868</v>
       </c>
       <c r="J12" s="4">
         <f t="shared" si="5"/>
-        <v>1468471.8548872343</v>
+        <v>2447453.0914787236</v>
       </c>
       <c r="K12" s="4">
         <f t="shared" si="3"/>
-        <v>1278344.3754805701</v>
+        <v>1156597.2921014682</v>
       </c>
       <c r="L12" s="63" cm="1">
         <f t="array" ref="L12">+_xlfn.IFS(I12&gt;114%,H12*0.02,I12&gt;109%,H12*0.015,I12&gt;104%,H12*0.0125,I12&gt;99%,H12*0.01,I12&lt;99%,H12*0)</f>
-        <v>528649.86775940435</v>
+        <v>1174777.4839097874</v>
       </c>
       <c r="M12" s="27"/>
     </row>
@@ -4274,38 +4217,38 @@
       </c>
       <c r="D13" s="4">
         <f>IFERROR(+VLOOKUP(B13,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>39689592.681744099</v>
+        <v>35677866.984969728</v>
       </c>
       <c r="E13" s="4">
-        <v>38609317.055148289</v>
+        <v>27711765.916719597</v>
       </c>
       <c r="F13" s="4">
         <f t="shared" si="7"/>
-        <v>1080275.6265958101</v>
+        <v>7966101.0682501309</v>
       </c>
       <c r="G13" s="5">
         <f t="shared" si="1"/>
-        <v>0.30919586980090541</v>
+        <v>0.27794311731832977</v>
       </c>
       <c r="H13" s="4">
         <f t="shared" si="4"/>
-        <v>190510044.87237167</v>
+        <v>285422935.87975782</v>
       </c>
       <c r="I13" s="5">
         <f t="shared" si="2"/>
-        <v>1.4841401750443461</v>
+        <v>2.2235449385466382</v>
       </c>
       <c r="J13" s="4">
         <f t="shared" si="5"/>
-        <v>7937918.5363488197</v>
+        <v>11892622.328323243</v>
       </c>
       <c r="K13" s="4">
         <f t="shared" si="3"/>
-        <v>4667069.6522568883</v>
+        <v>4413621.3852216788</v>
       </c>
       <c r="L13" s="63" cm="1">
         <f t="array" ref="L13">+_xlfn.IFS(I13&gt;114%,H13*0.0125,I13&gt;109%,H13*0.01,I13&gt;104%,H13*0.0075,I13&gt;99%,H13*0.005,I13&lt;99%,H13*0)</f>
-        <v>2381375.5609046458</v>
+        <v>3567786.6984969731</v>
       </c>
       <c r="M13" s="53" t="s">
         <v>61</v>
@@ -4324,34 +4267,34 @@
       </c>
       <c r="D14" s="4">
         <f>IFERROR(+VLOOKUP(B14,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>6663134.8062294191</v>
+        <v>4699575.8856638623</v>
       </c>
       <c r="E14" s="4">
-        <v>5554944.6639294196</v>
+        <v>968840.97419863928</v>
       </c>
       <c r="F14" s="4">
         <f t="shared" si="7"/>
-        <v>1108190.1422999995</v>
+        <v>3730734.9114652229</v>
       </c>
       <c r="G14" s="5">
         <f t="shared" si="1"/>
-        <v>0.15696779186946522</v>
+        <v>0.11071095977316531</v>
       </c>
       <c r="H14" s="4">
         <f t="shared" si="4"/>
-        <v>31983047.069901209</v>
+        <v>37596607.085310899</v>
       </c>
       <c r="I14" s="5">
         <f t="shared" si="2"/>
-        <v>0.75344540097343304</v>
+        <v>0.88568767818532246</v>
       </c>
       <c r="J14" s="4">
         <f t="shared" si="5"/>
-        <v>1332626.9612458837</v>
+        <v>1566525.2952212875</v>
       </c>
       <c r="K14" s="4">
         <f t="shared" si="3"/>
-        <v>1883469.6099339779</v>
+        <v>1797594.3575862448</v>
       </c>
       <c r="L14" s="63" cm="1">
         <f t="array" ref="L14">+_xlfn.IFS(I14&gt;109%,H14*0.015,I14&gt;104%,H14*0.0125,I14&gt;99%,H14*0.01,I14&lt;99%,H14*0)</f>
@@ -4369,38 +4312,38 @@
       </c>
       <c r="D15" s="4">
         <f>IFERROR(+VLOOKUP(B15,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>10196205.867152149</v>
+        <v>5825319.4707523696</v>
       </c>
       <c r="E15" s="4">
-        <v>8252554.4917521486</v>
+        <v>1445131.6450023698</v>
       </c>
       <c r="F15" s="4">
         <f t="shared" si="7"/>
-        <v>1943651.3754000003</v>
+        <v>4380187.8257499998</v>
       </c>
       <c r="G15" s="5">
         <f t="shared" si="1"/>
-        <v>0.24019864027320303</v>
+        <v>0.13723083216076207</v>
       </c>
       <c r="H15" s="4">
         <f t="shared" si="4"/>
-        <v>48941788.162330315</v>
+        <v>46602555.766018957</v>
       </c>
       <c r="I15" s="5">
         <f t="shared" si="2"/>
-        <v>1.1529534733113747</v>
+        <v>1.0978466572860965</v>
       </c>
       <c r="J15" s="4">
         <f t="shared" si="5"/>
-        <v>2039241.1734304298</v>
+        <v>1941773.1569174565</v>
       </c>
       <c r="K15" s="4">
         <f t="shared" si="3"/>
-        <v>1697518.5014643606</v>
+        <v>1743987.5202010777</v>
       </c>
       <c r="L15" s="63" cm="1">
         <f t="array" ref="L15">+_xlfn.IFS(I15&gt;109%,H15*0.015,I15&gt;104%,H15*0.0125,I15&gt;99%,H15*0.01,I15&lt;99%,H15*0)</f>
-        <v>734126.82243495469</v>
+        <v>699038.3364902843</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4411,34 +4354,34 @@
       </c>
       <c r="D16" s="64">
         <f>+SUM(D11:D15)</f>
-        <v>89198350.576100498</v>
+        <v>72088756.671189263</v>
       </c>
       <c r="E16" s="65">
-        <v>81473462.517372221</v>
+        <v>44544255.281003602</v>
       </c>
       <c r="F16" s="64">
         <f t="shared" si="7"/>
-        <v>7724888.0587282777</v>
+        <v>27544501.390185662</v>
       </c>
       <c r="G16" s="66">
         <f t="shared" si="1"/>
-        <v>0.26091697432810329</v>
+        <v>0.21086914894994976</v>
       </c>
       <c r="H16" s="64">
         <f t="shared" si="4"/>
-        <v>428152082.76528239</v>
+        <v>576710053.36951411</v>
       </c>
       <c r="I16" s="66">
         <f t="shared" si="2"/>
-        <v>1.2524014767748959</v>
+        <v>1.6869531915995981</v>
       </c>
       <c r="J16" s="64">
         <f t="shared" si="5"/>
-        <v>17839670.1152201</v>
+        <v>24029585.557063088</v>
       </c>
       <c r="K16" s="67">
         <f t="shared" si="3"/>
-        <v>13298238.483009422</v>
+        <v>12846482.146766203</v>
       </c>
       <c r="L16" s="68"/>
     </row>
@@ -4454,34 +4397,34 @@
       </c>
       <c r="D17" s="59">
         <f>IFERROR(+VLOOKUP(B17,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>4842984.6712837927</v>
+        <v>3490474.4748070529</v>
       </c>
       <c r="E17" s="59">
-        <v>3831780.4656781647</v>
+        <v>1647814.3144255385</v>
       </c>
       <c r="F17" s="59">
         <f t="shared" ref="F17:F40" si="8">+D17-E17</f>
-        <v>1011204.205605628</v>
+        <v>1842660.1603815143</v>
       </c>
       <c r="G17" s="60">
         <f t="shared" si="1"/>
-        <v>0.1650753861222426</v>
+        <v>0.11897444670744077</v>
       </c>
       <c r="H17" s="59">
         <f t="shared" si="4"/>
-        <v>23246326.422162205</v>
+        <v>27923795.798456423</v>
       </c>
       <c r="I17" s="60">
         <f t="shared" si="2"/>
-        <v>0.79236185338676446</v>
+        <v>0.95179557365952616</v>
       </c>
       <c r="J17" s="59">
         <f t="shared" si="5"/>
-        <v>968596.93425675854</v>
+        <v>1163491.491602351</v>
       </c>
       <c r="K17" s="59">
         <f t="shared" si="3"/>
-        <v>1289212.2874324322</v>
+        <v>1230835.4122710929</v>
       </c>
       <c r="L17" s="61" cm="1">
         <f t="array" ref="L17">+_xlfn.IFS(I17&gt;114%,H17*0.02,I17&gt;109%,H17*0.015,I17&gt;104%,H17*0.0125,I17&gt;99%,H17*0.01,I17&lt;99%,H17*0)</f>
@@ -4498,34 +4441,34 @@
       </c>
       <c r="D18" s="4">
         <f>IFERROR(+VLOOKUP(B18,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>4538116.0675083203</v>
+        <v>2539362.2668490014</v>
       </c>
       <c r="E18" s="4">
-        <v>3383340.6159000443</v>
+        <v>1318807.9914469167</v>
       </c>
       <c r="F18" s="4">
         <f t="shared" si="8"/>
-        <v>1154775.451608276</v>
+        <v>1220554.2754020847</v>
       </c>
       <c r="G18" s="5">
         <f t="shared" si="1"/>
-        <v>0.18181914680884448</v>
+        <v>0.10173928430406153</v>
       </c>
       <c r="H18" s="4">
         <f t="shared" si="4"/>
-        <v>21782957.124039941</v>
+        <v>20314898.134792011</v>
       </c>
       <c r="I18" s="5">
         <f t="shared" si="2"/>
-        <v>0.87273190468245365</v>
+        <v>0.8139142744324922</v>
       </c>
       <c r="J18" s="4">
         <f t="shared" si="5"/>
-        <v>907623.21350166411</v>
+        <v>846454.08894966717</v>
       </c>
       <c r="K18" s="4">
         <f t="shared" si="3"/>
-        <v>1074809.9911837727</v>
+        <v>1067625.8872929048</v>
       </c>
       <c r="L18" s="63" cm="1">
         <f t="array" ref="L18">+_xlfn.IFS(I18&gt;114%,H18*0.02,I18&gt;109%,H18*0.015,I18&gt;104%,H18*0.0125,I18&gt;99%,H18*0.01,I18&lt;99%,H18*0)</f>
@@ -4542,34 +4485,34 @@
       </c>
       <c r="D19" s="4">
         <f>IFERROR(+VLOOKUP(B19,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>5255755.4759214995</v>
+        <v>3126324.9965506792</v>
       </c>
       <c r="E19" s="4">
-        <v>4172472.7522102422</v>
+        <v>1974051.5620993127</v>
       </c>
       <c r="F19" s="4">
         <f t="shared" si="8"/>
-        <v>1083282.7237112573</v>
+        <v>1152273.4344513665</v>
       </c>
       <c r="G19" s="5">
         <f t="shared" si="1"/>
-        <v>0.20326513458940426</v>
+        <v>0.12090990041401692</v>
       </c>
       <c r="H19" s="4">
         <f t="shared" si="4"/>
-        <v>25227626.284423195</v>
+        <v>25010599.972405434</v>
       </c>
       <c r="I19" s="5">
         <f t="shared" si="2"/>
-        <v>0.97567264602914039</v>
+        <v>0.96727920331213535</v>
       </c>
       <c r="J19" s="4">
         <f t="shared" si="5"/>
-        <v>1051151.0951842999</v>
+        <v>1042108.3321835598</v>
       </c>
       <c r="K19" s="4">
         <f t="shared" si="3"/>
-        <v>1084257.6152409737</v>
+        <v>1082396.4366166343</v>
       </c>
       <c r="L19" s="63" cm="1">
         <f t="array" ref="L19">+_xlfn.IFS(I19&gt;114%,H19*0.02,I19&gt;109%,H19*0.015,I19&gt;104%,H19*0.0125,I19&gt;99%,H19*0.01,I19&lt;99%,H19*0)</f>
@@ -4586,38 +4529,38 @@
       </c>
       <c r="D20" s="4">
         <f>IFERROR(+VLOOKUP(B20,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>9037854.5756811257</v>
+        <v>5313079.7996425815</v>
       </c>
       <c r="E20" s="4">
-        <v>8068602.606727235</v>
+        <v>3804498.4929125779</v>
       </c>
       <c r="F20" s="4">
         <f t="shared" si="8"/>
-        <v>969251.96895389073</v>
+        <v>1508581.3067300036</v>
       </c>
       <c r="G20" s="5">
         <f t="shared" si="1"/>
-        <v>0.2693996528474501</v>
+        <v>0.15837186155063132</v>
       </c>
       <c r="H20" s="4">
         <f t="shared" si="4"/>
-        <v>43381701.963269398</v>
+        <v>42504638.397140652</v>
       </c>
       <c r="I20" s="5">
         <f t="shared" si="2"/>
-        <v>1.2931183336677603</v>
+        <v>1.2669748924050506</v>
       </c>
       <c r="J20" s="4">
         <f t="shared" si="5"/>
-        <v>1807570.9151362251</v>
+        <v>1771026.5998808604</v>
       </c>
       <c r="K20" s="4">
         <f t="shared" si="3"/>
-        <v>1290014.4960167827</v>
+        <v>1344526.2000170199</v>
       </c>
       <c r="L20" s="63" cm="1">
         <f t="array" ref="L20">+_xlfn.IFS(I20&gt;114%,H20*0.02,I20&gt;109%,H20*0.015,I20&gt;104%,H20*0.0125,I20&gt;99%,H20*0.01,I20&lt;99%,H20*0)</f>
-        <v>867634.03926538792</v>
+        <v>850092.76794281311</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4630,38 +4573,38 @@
       </c>
       <c r="D21" s="4">
         <f>IFERROR(+VLOOKUP(B21,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>5595341.8938343767</v>
+        <v>3621062.6775038806</v>
       </c>
       <c r="E21" s="4">
-        <v>4521737.6382463202</v>
+        <v>2482567.9113498144</v>
       </c>
       <c r="F21" s="4">
         <f t="shared" ref="F21:F23" si="9">+D21-E21</f>
-        <v>1073604.2555880565</v>
+        <v>1138494.7661540662</v>
       </c>
       <c r="G21" s="5">
         <f t="shared" si="1"/>
-        <v>0.2197827718053561</v>
+        <v>0.14223388083214142</v>
       </c>
       <c r="H21" s="4">
         <f t="shared" si="4"/>
-        <v>26857641.090405006</v>
+        <v>28968501.420031041</v>
       </c>
       <c r="I21" s="5">
         <f t="shared" si="2"/>
-        <v>1.0549573046657093</v>
+        <v>1.1378710466571311</v>
       </c>
       <c r="J21" s="4">
         <f t="shared" si="5"/>
-        <v>1119068.3787668752</v>
+        <v>1207020.8925012934</v>
       </c>
       <c r="K21" s="4">
         <f t="shared" si="3"/>
-        <v>1045429.9003245066</v>
+        <v>1039878.4439283867</v>
       </c>
       <c r="L21" s="63" cm="1">
         <f t="array" ref="L21">+_xlfn.IFS(I21&gt;114%,H21*0.02,I21&gt;109%,H21*0.015,I21&gt;104%,H21*0.0125,I21&gt;99%,H21*0.01,I21&lt;99%,H21*0)</f>
-        <v>335720.51363006257</v>
+        <v>434527.52130046563</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4674,38 +4617,38 @@
       </c>
       <c r="D22" s="4">
         <f>IFERROR(+VLOOKUP(B22,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>8516814.03087065</v>
+        <v>4525419.7648018571</v>
       </c>
       <c r="E22" s="4">
-        <v>6604601.1312453747</v>
+        <v>3717567.9331198842</v>
       </c>
       <c r="F22" s="4">
         <f t="shared" si="9"/>
-        <v>1912212.8996252753</v>
+        <v>807851.83168197284</v>
       </c>
       <c r="G22" s="5">
         <f t="shared" si="1"/>
-        <v>0.26830619320450694</v>
+        <v>0.14256483062156253</v>
       </c>
       <c r="H22" s="4">
         <f t="shared" si="4"/>
-        <v>40880707.348179117</v>
+        <v>36203358.118414856</v>
       </c>
       <c r="I22" s="5">
         <f t="shared" si="2"/>
-        <v>1.2878697273816331</v>
+        <v>1.1405186449725002</v>
       </c>
       <c r="J22" s="4">
         <f t="shared" si="5"/>
-        <v>1703362.8061741299</v>
+        <v>1508473.2549339524</v>
       </c>
       <c r="K22" s="4">
         <f t="shared" si="3"/>
-        <v>1222425.061533124</v>
+        <v>1296070.0207237212</v>
       </c>
       <c r="L22" s="63" cm="1">
         <f t="array" ref="L22">+_xlfn.IFS(I22&gt;114%,H22*0.02,I22&gt;109%,H22*0.015,I22&gt;104%,H22*0.0125,I22&gt;99%,H22*0.01,I22&lt;99%,H22*0)</f>
-        <v>817614.14696358237</v>
+        <v>724067.16236829711</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4718,38 +4661,38 @@
       </c>
       <c r="D23" s="4">
         <f>IFERROR(+VLOOKUP(B23,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>5822405.6030015703</v>
+        <v>3880349.2779353959</v>
       </c>
       <c r="E23" s="4">
-        <v>5027241.122842595</v>
+        <v>2007902.2622231084</v>
       </c>
       <c r="F23" s="4">
         <f t="shared" si="9"/>
-        <v>795164.48015897535</v>
+        <v>1872447.0157122875</v>
       </c>
       <c r="G23" s="5">
         <f t="shared" si="1"/>
-        <v>0.21221814455355015</v>
+        <v>0.1414330399034098</v>
       </c>
       <c r="H23" s="4">
         <f t="shared" si="4"/>
-        <v>27947546.894407541</v>
+        <v>31042794.223483168</v>
       </c>
       <c r="I23" s="5">
         <f t="shared" si="2"/>
-        <v>1.0186470938570409</v>
+        <v>1.1314643192272784</v>
       </c>
       <c r="J23" s="4">
         <f t="shared" si="5"/>
-        <v>1164481.1206003141</v>
+        <v>1293449.7593117987</v>
       </c>
       <c r="K23" s="4">
         <f t="shared" si="3"/>
-        <v>1137554.7698420228</v>
+        <v>1121695.0929554575</v>
       </c>
       <c r="L23" s="63" cm="1">
         <f t="array" ref="L23">+_xlfn.IFS(I23&gt;114%,H23*0.02,I23&gt;109%,H23*0.015,I23&gt;104%,H23*0.0125,I23&gt;99%,H23*0.01,I23&lt;99%,H23*0)</f>
-        <v>279475.4689440754</v>
+        <v>465641.9133522475</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4762,38 +4705,38 @@
       </c>
       <c r="D24" s="4">
         <f>IFERROR(+VLOOKUP(B24,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>6909391.5039921645</v>
+        <v>3150944.560423614</v>
       </c>
       <c r="E24" s="4">
-        <v>4507114.506957056</v>
+        <v>2373341.2642009868</v>
       </c>
       <c r="F24" s="4">
         <f t="shared" si="8"/>
-        <v>2402276.9970351085</v>
+        <v>777603.29622262716</v>
       </c>
       <c r="G24" s="5">
         <f t="shared" si="1"/>
-        <v>0.20628710091961586</v>
+        <v>9.407474133614499E-2</v>
       </c>
       <c r="H24" s="4">
         <f t="shared" si="4"/>
-        <v>33165079.21916239</v>
+        <v>25207556.483388916</v>
       </c>
       <c r="I24" s="5">
         <f t="shared" si="2"/>
-        <v>0.99017808441415622</v>
+        <v>0.75259793068916003</v>
       </c>
       <c r="J24" s="4">
         <f t="shared" si="5"/>
-        <v>1381878.3007984329</v>
+        <v>1050314.8534745381</v>
       </c>
       <c r="K24" s="4">
         <f t="shared" si="3"/>
-        <v>1399192.8155793599</v>
+        <v>1444910.020932209</v>
       </c>
       <c r="L24" s="63" cm="1">
         <f t="array" ref="L24">+_xlfn.IFS(I24&gt;114%,H24*0.02,I24&gt;109%,H24*0.015,I24&gt;104%,H24*0.0125,I24&gt;99%,H24*0.01,I24&lt;99%,H24*0)</f>
-        <v>331650.79219162388</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4806,38 +4749,38 @@
       </c>
       <c r="D25" s="4">
         <f>IFERROR(+VLOOKUP(B25,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>8825883.2392010316</v>
+        <v>7402539.5016198214</v>
       </c>
       <c r="E25" s="4">
-        <v>7398936.6723073218</v>
+        <v>-2433547.0814999999</v>
       </c>
       <c r="F25" s="4">
         <f t="shared" si="8"/>
-        <v>1426946.5668937098</v>
+        <v>9836086.5831198208</v>
       </c>
       <c r="G25" s="5">
         <f t="shared" si="1"/>
-        <v>0.16324592497544999</v>
+        <v>0.13691937400008347</v>
       </c>
       <c r="H25" s="4">
         <f t="shared" si="4"/>
-        <v>42364239.548164949</v>
+        <v>59220316.012958571</v>
       </c>
       <c r="I25" s="5">
         <f t="shared" si="2"/>
-        <v>0.78358043988215986</v>
+        <v>1.0953549920006678</v>
       </c>
       <c r="J25" s="4">
         <f t="shared" si="5"/>
-        <v>1765176.6478402063</v>
+        <v>2467513.1672066073</v>
       </c>
       <c r="K25" s="4">
         <f t="shared" si="3"/>
-        <v>2381003.6645157356</v>
+        <v>2222019.6839704849</v>
       </c>
       <c r="L25" s="63" cm="1">
         <f t="array" ref="L25">+_xlfn.IFS(I25&gt;109%,H25*0.015,I25&gt;104%,H25*0.0125,I25&gt;99%,H25*0.01,I25&lt;99%,H25*0)</f>
-        <v>0</v>
+        <v>888304.74019437854</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4848,34 +4791,34 @@
       </c>
       <c r="D26" s="67">
         <f>+SUM(D17:D25)</f>
-        <v>59344547.061294533</v>
+        <v>37049557.32013388</v>
       </c>
       <c r="E26" s="65">
-        <v>47515827.512114353</v>
+        <v>16893004.650278136</v>
       </c>
       <c r="F26" s="67">
         <f>+D26-E26</f>
-        <v>11828719.54918018</v>
+        <v>20156552.669855744</v>
       </c>
       <c r="G26" s="66">
         <f t="shared" si="1"/>
-        <v>0.20757196754299401</v>
+        <v>0.12958982569357178</v>
       </c>
       <c r="H26" s="64">
         <f t="shared" si="4"/>
-        <v>284853825.89421374</v>
+        <v>296396458.56107104</v>
       </c>
       <c r="I26" s="66">
         <f t="shared" si="2"/>
-        <v>0.99634544420637117</v>
+        <v>1.0367186055485742</v>
       </c>
       <c r="J26" s="64">
         <f t="shared" si="5"/>
-        <v>11868909.412258906</v>
+        <v>12349852.440044627</v>
       </c>
       <c r="K26" s="67">
         <f t="shared" si="3"/>
-        <v>11923900.60166871</v>
+        <v>11849957.198707912</v>
       </c>
       <c r="L26" s="68"/>
     </row>
@@ -4891,38 +4834,38 @@
       </c>
       <c r="D27" s="59">
         <f>IFERROR(+VLOOKUP(B27,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>17555809.912466466</v>
+        <v>7197381.3632933144</v>
       </c>
       <c r="E27" s="59">
-        <v>14993819.966923174</v>
+        <v>5151540.6591492426</v>
       </c>
       <c r="F27" s="59">
         <f t="shared" si="8"/>
-        <v>2561989.9455432929</v>
+        <v>2045840.7041440718</v>
       </c>
       <c r="G27" s="60">
         <f t="shared" si="1"/>
-        <v>0.21415348213558646</v>
+        <v>8.7796819907039525E-2</v>
       </c>
       <c r="H27" s="59">
         <f t="shared" si="4"/>
-        <v>84267887.579839051</v>
+        <v>57579050.906346515</v>
       </c>
       <c r="I27" s="60">
         <f t="shared" si="2"/>
-        <v>1.0279367142508151</v>
+        <v>0.7023745592563162</v>
       </c>
       <c r="J27" s="59">
         <f t="shared" si="5"/>
-        <v>3511161.9824932935</v>
+        <v>2399127.1210977715</v>
       </c>
       <c r="K27" s="59">
         <f t="shared" si="3"/>
-        <v>3390625.7940807124</v>
+        <v>3560967.5541288895</v>
       </c>
       <c r="L27" s="61" cm="1">
         <f t="array" ref="L27">+_xlfn.IFS(I27&gt;114%,H27*0.0125,I27&gt;109%,H27*0.01,I27&gt;104%,H27*0.0075,I27&gt;99%,H27*0.005,I27&lt;99%,H27*0)</f>
-        <v>421339.43789919524</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4935,34 +4878,34 @@
       </c>
       <c r="D28" s="4">
         <f>IFERROR(+VLOOKUP(B28,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>2883607.9842428509</v>
+        <v>1662817.6962441357</v>
       </c>
       <c r="E28" s="4">
-        <v>2246997.9859188953</v>
+        <v>1127867.2813395613</v>
       </c>
       <c r="F28" s="4">
         <f t="shared" si="8"/>
-        <v>636609.99832395557</v>
+        <v>534950.4149045744</v>
       </c>
       <c r="G28" s="5">
         <f t="shared" si="1"/>
-        <v>0.13731466591632624</v>
+        <v>7.9181795059244553E-2</v>
       </c>
       <c r="H28" s="4">
         <f t="shared" si="4"/>
-        <v>13841318.324365683</v>
+        <v>13302541.569953088</v>
       </c>
       <c r="I28" s="5">
         <f t="shared" si="2"/>
-        <v>0.65911039639836588</v>
+        <v>0.63345436047395653</v>
       </c>
       <c r="J28" s="4">
         <f t="shared" si="5"/>
-        <v>576721.59684857016</v>
+        <v>554272.56541471195</v>
       </c>
       <c r="K28" s="4">
         <f t="shared" si="3"/>
-        <v>953494.31661879737</v>
+        <v>920818.2049407555</v>
       </c>
       <c r="L28" s="63" cm="1">
         <f t="array" ref="L28">+_xlfn.IFS(I28&gt;114%,H28*0.02,I28&gt;109%,H28*0.015,I28&gt;104%,H28*0.0125,I28&gt;99%,H28*0.01,I28&lt;99%,H28*0)</f>
@@ -4979,34 +4922,34 @@
       </c>
       <c r="D29" s="4">
         <f>IFERROR(+VLOOKUP(B29,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>3996158.8131728824</v>
+        <v>2237337.654012111</v>
       </c>
       <c r="E29" s="4">
-        <v>2863924.6281832345</v>
+        <v>3336344.5485263281</v>
       </c>
       <c r="F29" s="4">
         <f t="shared" si="8"/>
-        <v>1132234.1849896479</v>
+        <v>-1099006.894514217</v>
       </c>
       <c r="G29" s="5">
         <f t="shared" si="1"/>
-        <v>0.15525273461512304</v>
+        <v>8.6921667852077181E-2</v>
       </c>
       <c r="H29" s="4">
         <f t="shared" si="4"/>
-        <v>19181562.303229839</v>
+        <v>17898701.232096888</v>
       </c>
       <c r="I29" s="5">
         <f t="shared" si="2"/>
-        <v>0.74521312615259072</v>
+        <v>0.69537334281661745</v>
       </c>
       <c r="J29" s="4">
         <f t="shared" si="5"/>
-        <v>799231.76263457653</v>
+        <v>745779.21800403704</v>
       </c>
       <c r="K29" s="4">
         <f t="shared" si="3"/>
-        <v>1144396.9045698482</v>
+        <v>1119160.1117137091</v>
       </c>
       <c r="L29" s="63" cm="1">
         <f t="array" ref="L29">+_xlfn.IFS(I29&gt;114%,H29*0.02,I29&gt;109%,H29*0.015,I29&gt;104%,H29*0.0125,I29&gt;99%,H29*0.01,I29&lt;99%,H29*0)</f>
@@ -5024,34 +4967,34 @@
       </c>
       <c r="D30" s="4">
         <f>IFERROR(+VLOOKUP(B30,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>4975553.6144345868</v>
+        <v>2806120.8392654946</v>
       </c>
       <c r="E30" s="4">
-        <v>4669958.7290065279</v>
+        <v>1465987.5738126547</v>
       </c>
       <c r="F30" s="4">
         <f t="shared" si="8"/>
-        <v>305594.88542805891</v>
+        <v>1340133.2654528399</v>
       </c>
       <c r="G30" s="5">
         <f t="shared" si="1"/>
-        <v>0.13013697386454762</v>
+        <v>7.3394862686401677E-2</v>
       </c>
       <c r="H30" s="4">
         <f t="shared" si="4"/>
-        <v>23882657.34928602</v>
+        <v>22448966.714123957</v>
       </c>
       <c r="I30" s="5">
         <f t="shared" si="2"/>
-        <v>0.62465747454982867</v>
+        <v>0.58715890149121341</v>
       </c>
       <c r="J30" s="4">
         <f t="shared" si="5"/>
-        <v>995110.72288691741</v>
+        <v>935373.61308849824</v>
       </c>
       <c r="K30" s="4">
         <f t="shared" si="3"/>
-        <v>1750402.710404794</v>
+        <v>1687004.0129933418</v>
       </c>
       <c r="L30" s="63" cm="1">
         <f t="array" ref="L30">+_xlfn.IFS(I30&gt;114%,H30*0.02,I30&gt;109%,H30*0.015,I30&gt;104%,H30*0.0125,I30&gt;99%,H30*0.01,I30&lt;99%,H30*0)</f>
@@ -5069,38 +5012,38 @@
       </c>
       <c r="D31" s="4">
         <f>IFERROR(+VLOOKUP(B31,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>4865926.9418352479</v>
+        <v>3265458.2459612871</v>
       </c>
       <c r="E31" s="4">
-        <v>4425690.3579718489</v>
+        <v>2185400.7533588032</v>
       </c>
       <c r="F31" s="4">
         <f t="shared" si="8"/>
-        <v>440236.58386339899</v>
+        <v>1080057.4926024838</v>
       </c>
       <c r="G31" s="5">
         <f t="shared" si="1"/>
-        <v>0.19145697728077624</v>
+        <v>0.12848420715756434</v>
       </c>
       <c r="H31" s="4">
         <f t="shared" si="4"/>
-        <v>23356449.320809193</v>
+        <v>26123665.967690296</v>
       </c>
       <c r="I31" s="5">
         <f t="shared" si="2"/>
-        <v>0.91899349094772598</v>
+        <v>1.0278736572605147</v>
       </c>
       <c r="J31" s="4">
         <f t="shared" si="5"/>
-        <v>973185.38836704963</v>
+        <v>1088486.0819870958</v>
       </c>
       <c r="K31" s="4">
         <f t="shared" si="3"/>
-        <v>1081543.3188507764</v>
+        <v>1054751.9882875578</v>
       </c>
       <c r="L31" s="63" cm="1">
         <f t="array" ref="L31">+_xlfn.IFS(I31&gt;114%,H31*0.02,I31&gt;109%,H31*0.015,I31&gt;104%,H31*0.0125,I31&gt;99%,H31*0.01,I31&lt;99%,H31*0)</f>
-        <v>0</v>
+        <v>261236.65967690296</v>
       </c>
       <c r="M31" s="27"/>
     </row>
@@ -5114,34 +5057,34 @@
       </c>
       <c r="D32" s="4">
         <f>IFERROR(+VLOOKUP(B32,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>2958594.3353685732</v>
+        <v>1556471.8667402903</v>
       </c>
       <c r="E32" s="4">
-        <v>2292259.0263364343</v>
+        <v>772280.47046408884</v>
       </c>
       <c r="F32" s="4">
         <f t="shared" si="8"/>
-        <v>666335.3090321389</v>
+        <v>784191.39627620147</v>
       </c>
       <c r="G32" s="5">
         <f t="shared" si="1"/>
-        <v>0.11740453711780052</v>
+        <v>6.1764756616678185E-2</v>
       </c>
       <c r="H32" s="4">
         <f t="shared" si="4"/>
-        <v>14201252.80976915</v>
+        <v>12451774.933922322</v>
       </c>
       <c r="I32" s="5">
         <f t="shared" si="2"/>
-        <v>0.56354177816544249</v>
+        <v>0.49411805293342548</v>
       </c>
       <c r="J32" s="4">
         <f t="shared" si="5"/>
-        <v>591718.86707371462</v>
+        <v>518823.95558009675</v>
       </c>
       <c r="K32" s="4">
         <f t="shared" si="3"/>
-        <v>1170600.2981384962</v>
+        <v>1125882.2920599862</v>
       </c>
       <c r="L32" s="63" cm="1">
         <f t="array" ref="L32">+_xlfn.IFS(I32&gt;114%,H32*0.02,I32&gt;109%,H32*0.015,I32&gt;104%,H32*0.0125,I32&gt;99%,H32*0.01,I32&lt;99%,H32*0)</f>
@@ -5159,34 +5102,34 @@
       </c>
       <c r="D33" s="4">
         <f>IFERROR(+VLOOKUP(B33,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>3089173.5689832573</v>
+        <v>1905347.2963424551</v>
       </c>
       <c r="E33" s="4">
-        <v>2299134.4748592312</v>
+        <v>1312962.2237802313</v>
       </c>
       <c r="F33" s="4">
         <f t="shared" si="8"/>
-        <v>790039.09412402613</v>
+        <v>592385.07256222377</v>
       </c>
       <c r="G33" s="5">
         <f t="shared" si="1"/>
-        <v>0.1165868859004692</v>
+        <v>7.19087169687775E-2</v>
       </c>
       <c r="H33" s="4">
         <f t="shared" si="4"/>
-        <v>14828033.131119635</v>
+        <v>15242778.370739641</v>
       </c>
       <c r="I33" s="5">
         <f t="shared" si="2"/>
-        <v>0.55961705232225212</v>
+        <v>0.57526973575022</v>
       </c>
       <c r="J33" s="4">
         <f t="shared" si="5"/>
-        <v>617834.71379665146</v>
+        <v>635115.76544748503</v>
       </c>
       <c r="K33" s="4">
         <f t="shared" si="3"/>
-        <v>1231977.706895618</v>
+        <v>1171019.1763646449</v>
       </c>
       <c r="L33" s="63" cm="1">
         <f t="array" ref="L33">+_xlfn.IFS(I33&gt;114%,H33*0.02,I33&gt;109%,H33*0.015,I33&gt;104%,H33*0.0125,I33&gt;99%,H33*0.01,I33&lt;99%,H33*0)</f>
@@ -5203,34 +5146,34 @@
       </c>
       <c r="D34" s="4">
         <f>IFERROR(+VLOOKUP(B34,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>2098536.1960838647</v>
+        <v>1342266.2312651528</v>
       </c>
       <c r="E34" s="4">
-        <v>1808557.8257932956</v>
+        <v>1012363.4850253685</v>
       </c>
       <c r="F34" s="4">
         <f t="shared" si="8"/>
-        <v>289978.37029056903</v>
+        <v>329902.74623978429</v>
       </c>
       <c r="G34" s="5">
         <f t="shared" si="1"/>
-        <v>9.9930295051612605E-2</v>
+        <v>6.3917439584054894E-2</v>
       </c>
       <c r="H34" s="4">
         <f t="shared" si="4"/>
-        <v>10072973.741202552</v>
+        <v>10738129.850121222</v>
       </c>
       <c r="I34" s="5">
         <f t="shared" si="2"/>
-        <v>0.47966541624774056</v>
+        <v>0.51133951667243915</v>
       </c>
       <c r="J34" s="4">
         <f t="shared" si="5"/>
-        <v>419707.23921677296</v>
+        <v>447422.07708838425</v>
       </c>
       <c r="K34" s="4">
         <f t="shared" si="3"/>
-        <v>994813.88441663864</v>
+        <v>936082.56041594502</v>
       </c>
       <c r="L34" s="63" cm="1">
         <f t="array" ref="L34">+_xlfn.IFS(I34&gt;114%,H34*0.02,I34&gt;109%,H34*0.015,I34&gt;104%,H34*0.0125,I34&gt;99%,H34*0.01,I34&lt;99%,H34*0)</f>
@@ -5247,34 +5190,34 @@
       </c>
       <c r="D35" s="4">
         <f>IFERROR(+VLOOKUP(B35,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>1626463.4655310514</v>
+        <v>920475.59202497394</v>
       </c>
       <c r="E35" s="4">
-        <v>1134886.8601273343</v>
+        <v>474208.7541035653</v>
       </c>
       <c r="F35" s="4">
         <f t="shared" si="8"/>
-        <v>491576.60540371714</v>
+        <v>446266.83792140865</v>
       </c>
       <c r="G35" s="5">
         <f t="shared" si="1"/>
-        <v>6.5960348506016314E-2</v>
+        <v>3.7329391116341579E-2</v>
       </c>
       <c r="H35" s="4">
         <f t="shared" si="4"/>
-        <v>7807024.6345490459</v>
+        <v>7363804.7361997925</v>
       </c>
       <c r="I35" s="5">
         <f t="shared" si="2"/>
-        <v>0.31660967282887825</v>
+        <v>0.29863512893073269</v>
       </c>
       <c r="J35" s="4">
         <f t="shared" si="5"/>
-        <v>325292.69310621027</v>
+        <v>306825.197341658</v>
       </c>
       <c r="K35" s="4">
         <f t="shared" si="3"/>
-        <v>1212196.659708892</v>
+        <v>1130367.8289511916</v>
       </c>
       <c r="L35" s="63" cm="1">
         <f t="array" ref="L35">+_xlfn.IFS(I35&gt;114%,H35*0.02,I35&gt;109%,H35*0.015,I35&gt;104%,H35*0.0125,I35&gt;99%,H35*0.01,I35&lt;99%,H35*0)</f>
@@ -5291,34 +5234,34 @@
       </c>
       <c r="D36" s="4">
         <f>IFERROR(+VLOOKUP(B36,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>3109025.2196221473</v>
+        <v>1931060.2247250369</v>
       </c>
       <c r="E36" s="4">
-        <v>2633216.6305364068</v>
+        <v>1231155.9948169386</v>
       </c>
       <c r="F36" s="4">
         <f t="shared" si="8"/>
-        <v>475808.5890857405</v>
+        <v>699904.22990809823</v>
       </c>
       <c r="G36" s="5">
         <f t="shared" si="1"/>
-        <v>0.12320290151068544</v>
+        <v>7.6523091924907347E-2</v>
       </c>
       <c r="H36" s="4">
         <f t="shared" si="4"/>
-        <v>14923321.054186307</v>
+        <v>15448481.797800295</v>
       </c>
       <c r="I36" s="5">
         <f t="shared" si="2"/>
-        <v>0.59137392725129012</v>
+        <v>0.61218473539925877</v>
       </c>
       <c r="J36" s="4">
         <f t="shared" si="5"/>
-        <v>621805.04392442945</v>
+        <v>643686.74157501233</v>
       </c>
       <c r="K36" s="4">
         <f t="shared" si="3"/>
-        <v>1164524.9884409397</v>
+        <v>1109711.4178702363</v>
       </c>
       <c r="L36" s="63" cm="1">
         <f t="array" ref="L36">+_xlfn.IFS(I36&gt;114%,H36*0.02,I36&gt;109%,H36*0.015,I36&gt;104%,H36*0.0125,I36&gt;99%,H36*0.01,I36&lt;99%,H36*0)</f>
@@ -5335,38 +5278,38 @@
       </c>
       <c r="D37" s="4">
         <f>IFERROR(+VLOOKUP(B37,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>17061083.040882383</v>
+        <v>16463801.298558187</v>
       </c>
       <c r="E37" s="4">
-        <v>17081843.43377829</v>
+        <v>-974804.98299181263</v>
       </c>
       <c r="F37" s="4">
         <f t="shared" si="8"/>
-        <v>-20760.392895907164</v>
+        <v>17438606.281549998</v>
       </c>
       <c r="G37" s="5">
         <f t="shared" si="1"/>
-        <v>0.13983147558233025</v>
+        <v>0.13493619506775525</v>
       </c>
       <c r="H37" s="4">
         <f t="shared" si="4"/>
-        <v>81893198.596235424</v>
+        <v>131710410.38846549</v>
       </c>
       <c r="I37" s="5">
         <f t="shared" si="2"/>
-        <v>0.67119108279518513</v>
+        <v>1.079489560542042</v>
       </c>
       <c r="J37" s="4">
         <f t="shared" si="5"/>
-        <v>3412216.6081764763</v>
+        <v>5487933.7661860622</v>
       </c>
       <c r="K37" s="4">
         <f t="shared" si="3"/>
-        <v>5523719.3136377698</v>
+        <v>5026092.7953067524</v>
       </c>
       <c r="L37" s="63" cm="1">
         <f t="array" ref="L37">+_xlfn.IFS(I37&gt;114%,H37*0.0125,I37&gt;109%,H37*0.01,I37&gt;104%,H37*0.0075,I37&gt;99%,H37*0.005,I37&lt;99%,H37*0)</f>
-        <v>0</v>
+        <v>987828.07791349117</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
@@ -5379,34 +5322,34 @@
       </c>
       <c r="D38" s="4">
         <f>IFERROR(+VLOOKUP(B38,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>746511.00490000006</v>
+        <v>149294.68419999999</v>
       </c>
       <c r="E38" s="4">
-        <v>280769.63740000001</v>
+        <v>0</v>
       </c>
       <c r="F38" s="4">
         <f t="shared" ref="F38" si="10">+D38-E38</f>
-        <v>465741.36750000005</v>
+        <v>149294.68419999999</v>
       </c>
       <c r="G38" s="5">
         <f t="shared" si="1"/>
-        <v>2.0910672406162466E-2</v>
+        <v>4.1819239271708684E-3</v>
       </c>
       <c r="H38" s="4">
         <f t="shared" si="4"/>
-        <v>3583252.8235200006</v>
+        <v>1194357.4735999999</v>
       </c>
       <c r="I38" s="5">
         <f t="shared" si="2"/>
-        <v>0.10037122754957985</v>
+        <v>3.3455391417366948E-2</v>
       </c>
       <c r="J38" s="4">
         <f t="shared" si="5"/>
-        <v>149302.20098000002</v>
+        <v>49764.894733333327</v>
       </c>
       <c r="K38" s="4">
         <f t="shared" si="3"/>
-        <v>1839657.3155315788</v>
+        <v>1692890.7293238097</v>
       </c>
       <c r="L38" s="63" cm="1">
         <f t="array" ref="L38">+_xlfn.IFS(I38&gt;109%,H38*0.015,I38&gt;104%,H38*0.0125,I38&gt;99%,H38*0.01,I38&lt;99%,H38*0)</f>
@@ -5423,38 +5366,38 @@
       </c>
       <c r="D39" s="4">
         <f>IFERROR(+VLOOKUP(B39,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>6953389.0972305397</v>
+        <v>4713478.3902184051</v>
       </c>
       <c r="E39" s="4">
-        <v>6167950.3247244535</v>
+        <v>3667023.6813626946</v>
       </c>
       <c r="F39" s="4">
         <f t="shared" si="8"/>
-        <v>785438.77250608616</v>
+        <v>1046454.7088557105</v>
       </c>
       <c r="G39" s="5">
         <f t="shared" si="1"/>
-        <v>0.19122981493305272</v>
+        <v>0.12962852900198119</v>
       </c>
       <c r="H39" s="4">
         <f t="shared" si="4"/>
-        <v>33376267.666706588</v>
+        <v>37707827.12174724</v>
       </c>
       <c r="I39" s="5">
         <f t="shared" si="2"/>
-        <v>0.91790311167865302</v>
+        <v>1.0370282320158495</v>
       </c>
       <c r="J39" s="4">
         <f t="shared" si="5"/>
-        <v>1390677.8194461078</v>
+        <v>1571159.4634061351</v>
       </c>
       <c r="K39" s="4">
         <f t="shared" si="3"/>
-        <v>1547791.5074615506</v>
+        <v>1507045.2070848378</v>
       </c>
       <c r="L39" s="63" cm="1">
         <f t="array" ref="L39">+_xlfn.IFS(I39&gt;114%,H39*0.02,I39&gt;109%,H39*0.015,I39&gt;104%,H39*0.0125,I39&gt;99%,H39*0.01,I39&lt;99%,H39*0)</f>
-        <v>0</v>
+        <v>377078.27121747239</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -5465,34 +5408,34 @@
       </c>
       <c r="D40" s="67">
         <f>+SUM(D27:D39)</f>
-        <v>71919833.194753855</v>
+        <v>46151311.382850848</v>
       </c>
       <c r="E40" s="65">
-        <v>62899009.881559134</v>
+        <v>20762330.442747667</v>
       </c>
       <c r="F40" s="67">
         <f t="shared" si="8"/>
-        <v>9020823.3131947219</v>
+        <v>25388980.940103181</v>
       </c>
       <c r="G40" s="66">
         <f t="shared" si="1"/>
-        <v>0.14128828734254617</v>
+        <v>9.0665390258040754E-2</v>
       </c>
       <c r="H40" s="64">
         <f t="shared" si="4"/>
-        <v>345215199.33481848</v>
+        <v>369210491.06280679</v>
       </c>
       <c r="I40" s="66">
         <f t="shared" si="2"/>
-        <v>0.67818377924422157</v>
+        <v>0.72532312206432603</v>
       </c>
       <c r="J40" s="64">
         <f t="shared" si="5"/>
-        <v>14383966.638950771</v>
+        <v>15383770.460950283</v>
       </c>
       <c r="K40" s="67">
         <f t="shared" si="3"/>
-        <v>23005744.718756411</v>
+        <v>22041793.87944166</v>
       </c>
       <c r="L40" s="68"/>
     </row>
@@ -5506,34 +5449,34 @@
       </c>
       <c r="D41" s="81">
         <f>+D40+D26+D10+D16</f>
-        <v>280805467.60214281</v>
+        <v>191246594.85709113</v>
       </c>
       <c r="E41" s="82">
-        <v>240577000.14348808</v>
+        <v>105866448.03886795</v>
       </c>
       <c r="F41" s="81">
         <f>+D41-E41</f>
-        <v>40228467.458654732</v>
+        <v>85380146.818223178</v>
       </c>
       <c r="G41" s="83">
         <f t="shared" si="1"/>
-        <v>0.20351656306191793</v>
+        <v>0.13860787688705689</v>
       </c>
       <c r="H41" s="81">
         <f t="shared" si="4"/>
-        <v>1347866244.4902854</v>
+        <v>1529972758.856729</v>
       </c>
       <c r="I41" s="83">
         <f t="shared" si="2"/>
-        <v>0.97687950269720591</v>
+        <v>1.1088630150964551</v>
       </c>
       <c r="J41" s="81">
         <f t="shared" si="5"/>
-        <v>56161093.520428561</v>
+        <v>63748864.952363707</v>
       </c>
       <c r="K41" s="81">
         <f t="shared" si="3"/>
-        <v>57840088.394262806</v>
+        <v>56596216.773144998</v>
       </c>
       <c r="L41" s="84"/>
     </row>
@@ -5581,34 +5524,34 @@
       </c>
       <c r="D43" s="4">
         <f>IFERROR(+VLOOKUP(B43,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>3760393.1741207056</v>
+        <v>-275260.76904147147</v>
       </c>
       <c r="E43" s="4">
-        <v>-275260.76904147147</v>
+        <v>0</v>
       </c>
       <c r="F43" s="4">
         <f t="shared" ref="F43" si="11">+D43-E43</f>
-        <v>4035653.9431621772</v>
+        <v>-275260.76904147147</v>
       </c>
       <c r="G43" s="5">
         <f>+D43/C43</f>
-        <v>9.4009829353017646E-2</v>
+        <v>-6.8815192260367865E-3</v>
       </c>
       <c r="H43" s="4">
         <f t="shared" ref="H43" si="12">+D43/$N$3*$N$4</f>
-        <v>18049887.23577939</v>
+        <v>-2202086.1523317718</v>
       </c>
       <c r="I43" s="5">
         <f>+H43/C43</f>
-        <v>0.45124718089448473</v>
+        <v>-5.5052153808294292E-2</v>
       </c>
       <c r="J43" s="4">
         <f t="shared" ref="J43" si="13">+D43/$N$3</f>
-        <v>752078.63482414116</v>
+        <v>-91753.589680490491</v>
       </c>
       <c r="K43" s="4">
         <f>+(C43-D43)/$N$2</f>
-        <v>1907347.7276778575</v>
+        <v>1917869.5604305463</v>
       </c>
       <c r="L43" s="4" cm="1">
         <f t="array" ref="L43">+_xlfn.IFS(I43&gt;114%,H43*0.02,I43&gt;109%,H43*0.015,I43&gt;104%,H43*0.0125,I43&gt;99%,H43*0.01,I43&lt;99%,H43*0)</f>
@@ -5624,34 +5567,34 @@
       </c>
       <c r="D44" s="4">
         <f>IFERROR(+VLOOKUP(B44,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>1913900.6624423866</v>
+        <v>-402349.89063324447</v>
       </c>
       <c r="E44" s="4">
-        <v>-402349.89063324447</v>
+        <v>-388379.73864699452</v>
       </c>
       <c r="F44" s="4">
         <f t="shared" ref="F44" si="14">+D44-E44</f>
-        <v>2316250.5530756311</v>
+        <v>-13970.151986249955</v>
       </c>
       <c r="G44" s="5">
         <f>+D44/C44</f>
-        <v>6.3796688748079561E-2</v>
+        <v>-1.3411663021108149E-2</v>
       </c>
       <c r="H44" s="4">
         <f t="shared" ref="H44" si="15">+D44/$N$3*$N$4</f>
-        <v>9186723.1797234565</v>
+        <v>-3218799.1250659563</v>
       </c>
       <c r="I44" s="5">
         <f>+H44/C44</f>
-        <v>0.30622410599078187</v>
+        <v>-0.10729330416886521</v>
       </c>
       <c r="J44" s="4">
         <f t="shared" ref="J44" si="16">+D44/$N$3</f>
-        <v>382780.13248847733</v>
+        <v>-134116.6302110815</v>
       </c>
       <c r="K44" s="4">
         <f>+(C44-D44)/$N$2</f>
-        <v>1478215.7546082954</v>
+        <v>1447730.9471730117</v>
       </c>
       <c r="L44" s="4" cm="1">
         <f t="array" ref="L44">+_xlfn.IFS(I44&gt;114%,H44*0.02,I44&gt;109%,H44*0.015,I44&gt;104%,H44*0.0125,I44&gt;99%,H44*0.01,I44&lt;99%,H44*0)</f>
@@ -5793,14 +5736,14 @@
       </c>
       <c r="D2" s="22">
         <f>H2/G2</f>
-        <v>0.51388888888888884</v>
+        <v>0.22222222222222221</v>
       </c>
       <c r="E2" s="13">
         <v>33</v>
       </c>
       <c r="F2" s="12">
         <f>+H2-E2</f>
-        <v>4</v>
+        <v>-17</v>
       </c>
       <c r="G2" s="13">
         <f>VLOOKUP(B2,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -5808,11 +5751,11 @@
       </c>
       <c r="H2" s="13">
         <f>VLOOKUP(B2,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="I2" s="17">
         <f>(+G2*$M$2)-H2</f>
-        <v>24.199999999999996</v>
+        <v>45.199999999999996</v>
       </c>
       <c r="J2" t="s">
         <v>55</v>
@@ -5858,14 +5801,14 @@
       </c>
       <c r="D3" s="22">
         <f t="shared" ref="D3:D38" si="0">H3/G3</f>
-        <v>0.22175732217573221</v>
+        <v>0.23012552301255229</v>
       </c>
       <c r="E3" s="13">
         <v>1</v>
       </c>
       <c r="F3" s="12">
         <f t="shared" ref="F3:F38" si="1">+H3-E3</f>
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G3" s="13">
         <f>VLOOKUP(B3,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -5873,11 +5816,11 @@
       </c>
       <c r="H3" s="13">
         <f>VLOOKUP(B3,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I3" s="17">
         <f t="shared" ref="I3:I38" si="2">(+G3*$M$2)-H3</f>
-        <v>150.15</v>
+        <v>148.15</v>
       </c>
       <c r="J3" t="s">
         <v>56</v>
@@ -5896,14 +5839,14 @@
         <v>145 - ALMACEN</v>
       </c>
       <c r="S3" s="12">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="T3" s="12">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="U3" s="41">
         <f>+S3/T3</f>
-        <v>8.4112149532710276E-2</v>
+        <v>7.0422535211267609E-2</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
@@ -5917,14 +5860,14 @@
       </c>
       <c r="D4" s="22">
         <f t="shared" si="0"/>
-        <v>0.52422907488986781</v>
+        <v>0.25550660792951541</v>
       </c>
       <c r="E4" s="13">
         <v>126</v>
       </c>
       <c r="F4" s="12">
         <f t="shared" si="1"/>
-        <v>-7</v>
+        <v>-68</v>
       </c>
       <c r="G4" s="13">
         <f>VLOOKUP(B4,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -5932,11 +5875,11 @@
       </c>
       <c r="H4" s="13">
         <f>VLOOKUP(B4,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>119</v>
+        <v>58</v>
       </c>
       <c r="I4" s="17">
         <f t="shared" si="2"/>
-        <v>73.949999999999989</v>
+        <v>134.94999999999999</v>
       </c>
       <c r="J4" t="s">
         <v>57</v>
@@ -5954,14 +5897,14 @@
         <v>145 - Articulos Sin Asociar Agrupacion</v>
       </c>
       <c r="S4" s="13">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T4" s="13">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="U4" s="5">
         <f t="shared" ref="U4:U11" si="3">+S4/T4</f>
-        <v>7.0093457943925228E-2</v>
+        <v>3.2863849765258218E-2</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
@@ -5975,14 +5918,14 @@
       </c>
       <c r="D5" s="22">
         <f t="shared" si="0"/>
-        <v>0.41538461538461541</v>
+        <v>0.18461538461538463</v>
       </c>
       <c r="E5" s="13">
         <v>21</v>
       </c>
       <c r="F5" s="12">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>-9</v>
       </c>
       <c r="G5" s="13">
         <f>VLOOKUP(B5,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -5990,11 +5933,11 @@
       </c>
       <c r="H5" s="13">
         <f>VLOOKUP(B5,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I5" s="17">
         <f t="shared" si="2"/>
-        <v>28.25</v>
+        <v>43.25</v>
       </c>
       <c r="K5" t="s">
         <v>64</v>
@@ -6009,14 +5952,14 @@
         <v>145 - BEBIDAS</v>
       </c>
       <c r="S5" s="13">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="T5" s="13">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="U5" s="5">
         <f t="shared" si="3"/>
-        <v>0.13084112149532709</v>
+        <v>5.1643192488262914E-2</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
@@ -6030,14 +5973,14 @@
       </c>
       <c r="D6" s="22">
         <f t="shared" si="0"/>
-        <v>0.50724637681159424</v>
+        <v>0.28502415458937197</v>
       </c>
       <c r="E6" s="13">
         <v>100</v>
       </c>
       <c r="F6" s="12">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>-41</v>
       </c>
       <c r="G6" s="13">
         <f>VLOOKUP(B6,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6045,11 +5988,11 @@
       </c>
       <c r="H6" s="13">
         <f>VLOOKUP(B6,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>105</v>
+        <v>59</v>
       </c>
       <c r="I6" s="17">
         <f t="shared" si="2"/>
-        <v>70.949999999999989</v>
+        <v>116.94999999999999</v>
       </c>
       <c r="J6" t="s">
         <v>58</v>
@@ -6067,14 +6010,14 @@
         <v>145 - CHOCOLATE</v>
       </c>
       <c r="S6" s="13">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T6" s="13">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="U6" s="5">
         <f t="shared" si="3"/>
-        <v>6.0747663551401869E-2</v>
+        <v>3.2863849765258218E-2</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
@@ -6088,14 +6031,14 @@
       </c>
       <c r="D7" s="22">
         <f t="shared" si="0"/>
-        <v>0.32323232323232326</v>
+        <v>0.20202020202020202</v>
       </c>
       <c r="E7" s="13">
         <v>81</v>
       </c>
       <c r="F7" s="12">
         <f t="shared" si="1"/>
-        <v>-17</v>
+        <v>-41</v>
       </c>
       <c r="G7" s="13">
         <f>VLOOKUP(B7,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6103,11 +6046,11 @@
       </c>
       <c r="H7" s="13">
         <f>VLOOKUP(B7,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="I7" s="17">
         <f t="shared" si="2"/>
-        <v>104.29999999999998</v>
+        <v>128.29999999999998</v>
       </c>
       <c r="J7" t="s">
         <v>58</v>
@@ -6125,14 +6068,14 @@
         <v>145 - GALLETITAS</v>
       </c>
       <c r="S7" s="13">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="T7" s="13">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="U7" s="5">
         <f t="shared" si="3"/>
-        <v>0.17289719626168223</v>
+        <v>8.9201877934272297E-2</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
@@ -6146,26 +6089,26 @@
       </c>
       <c r="D8" s="22">
         <f t="shared" si="0"/>
-        <v>0.43457943925233644</v>
+        <v>0.22535211267605634</v>
       </c>
       <c r="E8" s="13">
         <v>89</v>
       </c>
       <c r="F8" s="12">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>-41</v>
       </c>
       <c r="G8" s="13">
         <f>VLOOKUP(B8,'Base Cobertura'!$A:$C,3,FALSE)</f>
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H8" s="13">
         <f>VLOOKUP(B8,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>93</v>
+        <v>48</v>
       </c>
       <c r="I8" s="17">
         <f t="shared" si="2"/>
-        <v>88.9</v>
+        <v>133.04999999999998</v>
       </c>
       <c r="J8" t="s">
         <v>55</v>
@@ -6184,14 +6127,14 @@
         <v>145 - GOLOSINAS</v>
       </c>
       <c r="S8" s="13">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="T8" s="13">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="U8" s="5">
         <f t="shared" si="3"/>
-        <v>0.1822429906542056</v>
+        <v>8.4507042253521125E-2</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
@@ -6205,26 +6148,26 @@
       </c>
       <c r="D9" s="22">
         <f>H9/G9</f>
-        <v>0.42603550295857989</v>
+        <v>0.21818181818181817</v>
       </c>
       <c r="E9" s="13">
         <v>92</v>
       </c>
       <c r="F9" s="12">
         <f t="shared" si="1"/>
-        <v>-20</v>
+        <v>-56</v>
       </c>
       <c r="G9" s="13">
         <f>VLOOKUP(B9,'Base Cobertura'!$A:$C,3,FALSE)</f>
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="H9" s="13">
         <f>VLOOKUP(B9,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="I9" s="17">
         <f t="shared" si="2"/>
-        <v>71.650000000000006</v>
+        <v>104.25</v>
       </c>
       <c r="J9" t="s">
         <v>55</v>
@@ -6242,14 +6185,14 @@
         <v>145 - MASCOTAS</v>
       </c>
       <c r="S9" s="13">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T9" s="13">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="U9" s="5">
         <f t="shared" si="3"/>
-        <v>4.2056074766355138E-2</v>
+        <v>3.2863849765258218E-2</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
@@ -6263,26 +6206,26 @@
       </c>
       <c r="D10" s="22">
         <f t="shared" si="0"/>
-        <v>0.3487179487179487</v>
+        <v>0.15979381443298968</v>
       </c>
       <c r="E10" s="13">
         <v>64</v>
       </c>
       <c r="F10" s="12">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>-33</v>
       </c>
       <c r="G10" s="13">
         <f>VLOOKUP(B10,'Base Cobertura'!$A:$C,3,FALSE)</f>
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H10" s="13">
         <f>VLOOKUP(B10,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="I10" s="17">
         <f t="shared" si="2"/>
-        <v>97.75</v>
+        <v>133.9</v>
       </c>
       <c r="J10" t="s">
         <v>58</v>
@@ -6300,14 +6243,14 @@
         <v>145 - NO PERECEDEROS</v>
       </c>
       <c r="S10" s="13">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T10" s="13">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="U10" s="5">
         <f t="shared" si="3"/>
-        <v>2.336448598130841E-2</v>
+        <v>9.3896713615023476E-3</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
@@ -6321,14 +6264,14 @@
       </c>
       <c r="D11" s="32">
         <f t="shared" si="0"/>
-        <v>0.16831683168316833</v>
+        <v>7.9207920792079209E-2</v>
       </c>
       <c r="E11" s="31">
         <v>19</v>
       </c>
       <c r="F11" s="33">
         <f t="shared" si="1"/>
-        <v>-2</v>
+        <v>-11</v>
       </c>
       <c r="G11" s="13">
         <f>VLOOKUP(B11,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6336,11 +6279,11 @@
       </c>
       <c r="H11" s="13">
         <f>VLOOKUP(B11,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="I11" s="34">
         <f t="shared" si="2"/>
-        <v>68.849999999999994</v>
+        <v>77.849999999999994</v>
       </c>
       <c r="J11" t="s">
         <v>59</v>
@@ -6355,14 +6298,14 @@
         <v>145 - PILAS</v>
       </c>
       <c r="S11" s="13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T11" s="13">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="U11" s="5">
         <f t="shared" si="3"/>
-        <v>2.336448598130841E-2</v>
+        <v>1.4084507042253521E-2</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
@@ -6376,14 +6319,14 @@
       </c>
       <c r="D12" s="32">
         <f t="shared" si="0"/>
-        <v>0.19047619047619047</v>
+        <v>7.6190476190476197E-2</v>
       </c>
       <c r="E12" s="31">
         <v>24</v>
       </c>
       <c r="F12" s="33">
         <f t="shared" si="1"/>
-        <v>-4</v>
+        <v>-16</v>
       </c>
       <c r="G12" s="13">
         <f>VLOOKUP(B12,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6391,11 +6334,11 @@
       </c>
       <c r="H12" s="13">
         <f>VLOOKUP(B12,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="I12" s="34">
         <f t="shared" si="2"/>
-        <v>69.25</v>
+        <v>81.25</v>
       </c>
       <c r="J12" t="s">
         <v>59</v>
@@ -6412,14 +6355,14 @@
       </c>
       <c r="D13" s="22">
         <f t="shared" si="0"/>
-        <v>0.41153846153846152</v>
+        <v>0.20384615384615384</v>
       </c>
       <c r="E13" s="13">
         <v>144</v>
       </c>
       <c r="F13" s="12">
         <f t="shared" si="1"/>
-        <v>-37</v>
+        <v>-91</v>
       </c>
       <c r="G13" s="13">
         <f>VLOOKUP(B13,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6427,11 +6370,11 @@
       </c>
       <c r="H13" s="13">
         <f>VLOOKUP(B13,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>107</v>
+        <v>53</v>
       </c>
       <c r="I13" s="17">
         <f t="shared" si="2"/>
-        <v>114</v>
+        <v>168</v>
       </c>
       <c r="J13" t="s">
         <v>57</v>
@@ -6451,14 +6394,14 @@
       </c>
       <c r="D14" s="22">
         <f t="shared" si="0"/>
-        <v>0.38461538461538464</v>
+        <v>0.21978021978021978</v>
       </c>
       <c r="E14" s="13">
         <v>85</v>
       </c>
       <c r="F14" s="12">
         <f t="shared" si="1"/>
-        <v>-15</v>
+        <v>-45</v>
       </c>
       <c r="G14" s="13">
         <f>VLOOKUP(B14,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6466,11 +6409,11 @@
       </c>
       <c r="H14" s="13">
         <f>VLOOKUP(B14,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="I14" s="17">
         <f t="shared" si="2"/>
-        <v>84.699999999999989</v>
+        <v>114.69999999999999</v>
       </c>
       <c r="J14" t="s">
         <v>55</v>
@@ -6486,15 +6429,15 @@
       <c r="E15" s="14"/>
       <c r="F15" s="16">
         <f>+SUM(F2:F14)</f>
-        <v>-27</v>
+        <v>-415</v>
       </c>
       <c r="G15" s="8">
         <f>+SUM(G2:G14)</f>
-        <v>2234</v>
+        <v>2228</v>
       </c>
       <c r="H15" s="8">
         <f>+SUM(H2:H14)</f>
-        <v>852</v>
+        <v>464</v>
       </c>
       <c r="I15" s="8"/>
     </row>
@@ -6511,14 +6454,14 @@
       </c>
       <c r="D16" s="22">
         <f t="shared" si="0"/>
-        <v>0.49689440993788819</v>
+        <v>0.29813664596273293</v>
       </c>
       <c r="E16" s="13">
         <v>90</v>
       </c>
       <c r="F16" s="12">
         <f t="shared" si="1"/>
-        <v>-10</v>
+        <v>-42</v>
       </c>
       <c r="G16" s="13">
         <f>VLOOKUP(B16,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6526,11 +6469,11 @@
       </c>
       <c r="H16" s="13">
         <f>VLOOKUP(B16,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="I16" s="17">
         <f t="shared" si="2"/>
-        <v>56.849999999999994</v>
+        <v>88.85</v>
       </c>
       <c r="J16" t="s">
         <v>55</v>
@@ -6550,14 +6493,14 @@
       </c>
       <c r="D17" s="22">
         <f t="shared" si="0"/>
-        <v>0.33663366336633666</v>
+        <v>0.22277227722772278</v>
       </c>
       <c r="E17" s="13">
         <v>92</v>
       </c>
       <c r="F17" s="12">
         <f t="shared" si="1"/>
-        <v>-24</v>
+        <v>-47</v>
       </c>
       <c r="G17" s="13">
         <f>VLOOKUP(B17,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6565,11 +6508,11 @@
       </c>
       <c r="H17" s="13">
         <f>VLOOKUP(B17,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="I17" s="17">
         <f t="shared" si="2"/>
-        <v>103.69999999999999</v>
+        <v>126.69999999999999</v>
       </c>
       <c r="J17" t="s">
         <v>55</v>
@@ -6589,14 +6532,14 @@
       </c>
       <c r="D18" s="22">
         <f t="shared" si="0"/>
-        <v>0.53529411764705881</v>
+        <v>0.3</v>
       </c>
       <c r="E18" s="13">
         <v>88</v>
       </c>
       <c r="F18" s="12">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>-37</v>
       </c>
       <c r="G18" s="13">
         <f>VLOOKUP(B18,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6604,11 +6547,11 @@
       </c>
       <c r="H18" s="13">
         <f>VLOOKUP(B18,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="I18" s="17">
         <f t="shared" si="2"/>
-        <v>53.5</v>
+        <v>93.5</v>
       </c>
       <c r="J18" t="s">
         <v>58</v>
@@ -6628,14 +6571,14 @@
       </c>
       <c r="D19" s="22">
         <f t="shared" si="0"/>
-        <v>0.55625000000000002</v>
+        <v>0.33750000000000002</v>
       </c>
       <c r="E19" s="13">
         <v>95</v>
       </c>
       <c r="F19" s="12">
         <f t="shared" si="1"/>
-        <v>-6</v>
+        <v>-41</v>
       </c>
       <c r="G19" s="13">
         <f>VLOOKUP(B19,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6643,11 +6586,11 @@
       </c>
       <c r="H19" s="13">
         <f>VLOOKUP(B19,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>89</v>
+        <v>54</v>
       </c>
       <c r="I19" s="17">
         <f t="shared" si="2"/>
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="J19" t="s">
         <v>58</v>
@@ -6667,14 +6610,14 @@
       </c>
       <c r="D20" s="22">
         <f t="shared" si="0"/>
-        <v>0.50847457627118642</v>
+        <v>0.2824858757062147</v>
       </c>
       <c r="E20" s="13">
         <v>83</v>
       </c>
       <c r="F20" s="12">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>-33</v>
       </c>
       <c r="G20" s="13">
         <f>VLOOKUP(B20,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6682,11 +6625,11 @@
       </c>
       <c r="H20" s="13">
         <f>VLOOKUP(B20,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="I20" s="17">
         <f t="shared" si="2"/>
-        <v>60.449999999999989</v>
+        <v>100.44999999999999</v>
       </c>
       <c r="J20" t="s">
         <v>55</v>
@@ -6706,14 +6649,14 @@
       </c>
       <c r="D21" s="22">
         <f t="shared" si="0"/>
-        <v>0.47928994082840237</v>
+        <v>0.30769230769230771</v>
       </c>
       <c r="E21" s="13">
         <v>64</v>
       </c>
       <c r="F21" s="12">
         <f t="shared" si="1"/>
-        <v>17</v>
+        <v>-12</v>
       </c>
       <c r="G21" s="13">
         <f>VLOOKUP(B21,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6721,11 +6664,11 @@
       </c>
       <c r="H21" s="13">
         <f>VLOOKUP(B21,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="I21" s="17">
         <f t="shared" si="2"/>
-        <v>62.650000000000006</v>
+        <v>91.65</v>
       </c>
       <c r="J21" t="s">
         <v>58</v>
@@ -6745,14 +6688,14 @@
       </c>
       <c r="D22" s="22">
         <f t="shared" si="0"/>
-        <v>0.20707070707070707</v>
+        <v>0</v>
       </c>
       <c r="E22" s="13">
         <v>66</v>
       </c>
       <c r="F22" s="12">
         <f t="shared" si="1"/>
-        <v>-25</v>
+        <v>-66</v>
       </c>
       <c r="G22" s="13">
         <f>VLOOKUP(B22,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6760,11 +6703,11 @@
       </c>
       <c r="H22" s="13">
         <f>VLOOKUP(B22,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="I22" s="17">
         <f t="shared" si="2"/>
-        <v>127.29999999999998</v>
+        <v>168.29999999999998</v>
       </c>
       <c r="J22" t="s">
         <v>58</v>
@@ -6784,14 +6727,14 @@
       </c>
       <c r="D23" s="22">
         <f t="shared" si="0"/>
-        <v>0.43478260869565216</v>
+        <v>0.20289855072463769</v>
       </c>
       <c r="E23" s="13">
         <v>70</v>
       </c>
       <c r="F23" s="12">
         <f t="shared" si="1"/>
-        <v>-10</v>
+        <v>-42</v>
       </c>
       <c r="G23" s="13">
         <f>VLOOKUP(B23,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6799,11 +6742,11 @@
       </c>
       <c r="H23" s="13">
         <f>VLOOKUP(B23,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="I23" s="17">
         <f t="shared" si="2"/>
-        <v>57.3</v>
+        <v>89.3</v>
       </c>
       <c r="J23" t="s">
         <v>58</v>
@@ -6823,14 +6766,14 @@
       </c>
       <c r="D24" s="22">
         <f t="shared" si="0"/>
-        <v>0.48823529411764705</v>
+        <v>0.22941176470588234</v>
       </c>
       <c r="E24" s="13">
         <v>79</v>
       </c>
       <c r="F24" s="12">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>-40</v>
       </c>
       <c r="G24" s="13">
         <f>VLOOKUP(B24,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6838,11 +6781,11 @@
       </c>
       <c r="H24" s="13">
         <f>VLOOKUP(B24,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>83</v>
+        <v>39</v>
       </c>
       <c r="I24" s="17">
         <f t="shared" si="2"/>
-        <v>61.5</v>
+        <v>105.5</v>
       </c>
       <c r="J24" t="s">
         <v>60</v>
@@ -6858,7 +6801,7 @@
       <c r="E25" s="14"/>
       <c r="F25" s="16">
         <f>+SUM(F16:F24)</f>
-        <v>-44</v>
+        <v>-360</v>
       </c>
       <c r="G25" s="8">
         <f>+SUM(G16:G24)</f>
@@ -6866,7 +6809,7 @@
       </c>
       <c r="H25" s="8">
         <f>+SUM(H16:H24)</f>
-        <v>683</v>
+        <v>367</v>
       </c>
       <c r="I25" s="8"/>
     </row>
@@ -6883,14 +6826,14 @@
       </c>
       <c r="D26" s="22">
         <f t="shared" si="0"/>
-        <v>0.30357142857142855</v>
+        <v>0.14285714285714285</v>
       </c>
       <c r="E26" s="13">
         <v>20</v>
       </c>
       <c r="F26" s="12">
         <f>+H26-E26</f>
-        <v>-3</v>
+        <v>-12</v>
       </c>
       <c r="G26" s="13">
         <f>VLOOKUP(B26,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6898,11 +6841,11 @@
       </c>
       <c r="H26" s="13">
         <f>VLOOKUP(B26,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="I26" s="17">
         <f t="shared" si="2"/>
-        <v>30.6</v>
+        <v>39.6</v>
       </c>
       <c r="J26" t="s">
         <v>55</v>
@@ -6922,14 +6865,14 @@
       </c>
       <c r="D27" s="22">
         <f t="shared" si="0"/>
-        <v>0.41666666666666669</v>
+        <v>0.21153846153846154</v>
       </c>
       <c r="E27" s="13">
         <v>68</v>
       </c>
       <c r="F27" s="12">
         <f t="shared" si="1"/>
-        <v>-3</v>
+        <v>-35</v>
       </c>
       <c r="G27" s="13">
         <f>VLOOKUP(B27,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6937,11 +6880,11 @@
       </c>
       <c r="H27" s="13">
         <f>VLOOKUP(B27,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="I27" s="17">
         <f t="shared" si="2"/>
-        <v>67.599999999999994</v>
+        <v>99.6</v>
       </c>
       <c r="J27" t="s">
         <v>58</v>
@@ -6961,14 +6904,14 @@
       </c>
       <c r="D28" s="22">
         <f t="shared" si="0"/>
-        <v>0.36645962732919257</v>
+        <v>0.21739130434782608</v>
       </c>
       <c r="E28" s="13">
         <v>80</v>
       </c>
       <c r="F28" s="12">
         <f t="shared" si="1"/>
-        <v>-21</v>
+        <v>-45</v>
       </c>
       <c r="G28" s="13">
         <f>VLOOKUP(B28,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6976,11 +6919,11 @@
       </c>
       <c r="H28" s="13">
         <f>VLOOKUP(B28,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="I28" s="17">
         <f t="shared" si="2"/>
-        <v>77.849999999999994</v>
+        <v>101.85</v>
       </c>
       <c r="J28" t="s">
         <v>58</v>
@@ -7000,14 +6943,14 @@
       </c>
       <c r="D29" s="22">
         <f t="shared" si="0"/>
-        <v>0.20481927710843373</v>
+        <v>0.10441767068273092</v>
       </c>
       <c r="E29" s="13">
         <v>68</v>
       </c>
       <c r="F29" s="12">
         <f t="shared" si="1"/>
-        <v>-17</v>
+        <v>-42</v>
       </c>
       <c r="G29" s="13">
         <f>VLOOKUP(B29,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7015,11 +6958,11 @@
       </c>
       <c r="H29" s="13">
         <f>VLOOKUP(B29,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="I29" s="17">
         <f t="shared" si="2"/>
-        <v>160.65</v>
+        <v>185.65</v>
       </c>
       <c r="J29" t="s">
         <v>58</v>
@@ -7039,14 +6982,14 @@
       </c>
       <c r="D30" s="22">
         <f t="shared" si="0"/>
-        <v>0.51428571428571423</v>
+        <v>0.23571428571428571</v>
       </c>
       <c r="E30" s="13">
         <v>73</v>
       </c>
       <c r="F30" s="12">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-40</v>
       </c>
       <c r="G30" s="13">
         <f>VLOOKUP(B30,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7054,11 +6997,11 @@
       </c>
       <c r="H30" s="13">
         <f>VLOOKUP(B30,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>72</v>
+        <v>33</v>
       </c>
       <c r="I30" s="17">
         <f t="shared" si="2"/>
-        <v>47</v>
+        <v>86</v>
       </c>
       <c r="J30" t="s">
         <v>55</v>
@@ -7078,14 +7021,14 @@
       </c>
       <c r="D31" s="22">
         <f t="shared" si="0"/>
-        <v>0.2983425414364641</v>
+        <v>0.17679558011049723</v>
       </c>
       <c r="E31" s="13">
         <v>40</v>
       </c>
       <c r="F31" s="12">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>-8</v>
       </c>
       <c r="G31" s="13">
         <f>VLOOKUP(B31,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7093,11 +7036,11 @@
       </c>
       <c r="H31" s="13">
         <f>VLOOKUP(B31,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="I31" s="17">
         <f t="shared" si="2"/>
-        <v>99.85</v>
+        <v>121.85</v>
       </c>
       <c r="J31" t="s">
         <v>58</v>
@@ -7117,14 +7060,14 @@
       </c>
       <c r="D32" s="22">
         <f t="shared" si="0"/>
-        <v>0.35119047619047616</v>
+        <v>0.21428571428571427</v>
       </c>
       <c r="E32" s="13">
         <v>67</v>
       </c>
       <c r="F32" s="12">
         <f t="shared" si="1"/>
-        <v>-8</v>
+        <v>-31</v>
       </c>
       <c r="G32" s="13">
         <f>VLOOKUP(B32,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7132,11 +7075,11 @@
       </c>
       <c r="H32" s="13">
         <f>VLOOKUP(B32,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="I32" s="17">
         <f t="shared" si="2"/>
-        <v>83.799999999999983</v>
+        <v>106.79999999999998</v>
       </c>
       <c r="J32" t="s">
         <v>58</v>
@@ -7156,14 +7099,14 @@
       </c>
       <c r="D33" s="22">
         <f t="shared" si="0"/>
-        <v>0.39534883720930231</v>
+        <v>0.23837209302325582</v>
       </c>
       <c r="E33" s="13">
         <v>66</v>
       </c>
       <c r="F33" s="12">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>-25</v>
       </c>
       <c r="G33" s="13">
         <f>VLOOKUP(B33,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7171,11 +7114,11 @@
       </c>
       <c r="H33" s="13">
         <f>VLOOKUP(B33,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="I33" s="17">
         <f t="shared" si="2"/>
-        <v>78.199999999999989</v>
+        <v>105.19999999999999</v>
       </c>
       <c r="J33" t="s">
         <v>58</v>
@@ -7195,26 +7138,26 @@
       </c>
       <c r="D34" s="22">
         <f t="shared" si="0"/>
-        <v>0.19718309859154928</v>
+        <v>9.2198581560283682E-2</v>
       </c>
       <c r="E34" s="13">
         <v>82</v>
       </c>
       <c r="F34" s="12">
         <f t="shared" si="1"/>
-        <v>-54</v>
+        <v>-69</v>
       </c>
       <c r="G34" s="13">
         <f>VLOOKUP(B34,'Base Cobertura'!$A:$C,3,FALSE)</f>
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H34" s="13">
         <f>VLOOKUP(B34,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="I34" s="17">
         <f t="shared" si="2"/>
-        <v>92.7</v>
+        <v>106.85</v>
       </c>
       <c r="J34" t="s">
         <v>55</v>
@@ -7234,14 +7177,14 @@
       </c>
       <c r="D35" s="22">
         <f t="shared" si="0"/>
-        <v>0.398876404494382</v>
+        <v>0.17415730337078653</v>
       </c>
       <c r="E35" s="13">
         <v>81</v>
       </c>
       <c r="F35" s="12">
         <f t="shared" si="1"/>
-        <v>-10</v>
+        <v>-50</v>
       </c>
       <c r="G35" s="13">
         <f>VLOOKUP(B35,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7249,11 +7192,11 @@
       </c>
       <c r="H35" s="13">
         <f>VLOOKUP(B35,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>71</v>
+        <v>31</v>
       </c>
       <c r="I35" s="17">
         <f t="shared" si="2"/>
-        <v>80.299999999999983</v>
+        <v>120.29999999999998</v>
       </c>
       <c r="J35" t="s">
         <v>58</v>
@@ -7273,14 +7216,14 @@
       </c>
       <c r="D36" s="22">
         <f t="shared" si="0"/>
-        <v>2.6548672566371681E-2</v>
+        <v>8.8495575221238937E-3</v>
       </c>
       <c r="E36" s="13">
         <v>0</v>
       </c>
       <c r="F36" s="12">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G36" s="13">
         <f>VLOOKUP(B36,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7288,11 +7231,11 @@
       </c>
       <c r="H36" s="13">
         <f>VLOOKUP(B36,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I36" s="17">
         <f t="shared" si="2"/>
-        <v>93.05</v>
+        <v>95.05</v>
       </c>
       <c r="J36" t="s">
         <v>58</v>
@@ -7309,26 +7252,26 @@
       </c>
       <c r="D37" s="22">
         <f t="shared" si="0"/>
-        <v>3.8461538461538464E-2</v>
+        <v>9.7087378640776691E-3</v>
       </c>
       <c r="E37" s="13">
         <v>17</v>
       </c>
       <c r="F37" s="12">
         <f t="shared" si="1"/>
-        <v>-13</v>
+        <v>-16</v>
       </c>
       <c r="G37" s="13">
         <f>VLOOKUP(B37,'Base Cobertura'!$A:$C,3,FALSE)</f>
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H37" s="13">
         <f>VLOOKUP(B37,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I37" s="17">
         <f t="shared" si="2"/>
-        <v>84.399999999999991</v>
+        <v>86.55</v>
       </c>
       <c r="J37" t="s">
         <v>59</v>
@@ -7345,14 +7288,14 @@
       </c>
       <c r="D38" s="22">
         <f t="shared" si="0"/>
-        <v>0.47244094488188976</v>
+        <v>0.29133858267716534</v>
       </c>
       <c r="E38" s="13">
         <v>60</v>
       </c>
       <c r="F38" s="12">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-23</v>
       </c>
       <c r="G38" s="13">
         <f>VLOOKUP(B38,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7360,11 +7303,11 @@
       </c>
       <c r="H38" s="13">
         <f>VLOOKUP(B38,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="I38" s="17">
         <f t="shared" si="2"/>
-        <v>47.95</v>
+        <v>70.95</v>
       </c>
       <c r="J38" t="s">
         <v>55</v>
@@ -7380,15 +7323,15 @@
       <c r="E39" s="14"/>
       <c r="F39" s="8">
         <f>+SUM(F26:F38)</f>
-        <v>-111</v>
+        <v>-395</v>
       </c>
       <c r="G39" s="8">
         <f>+SUM(G26:G38)</f>
-        <v>1947</v>
+        <v>1945</v>
       </c>
       <c r="H39" s="8">
         <f>+SUM(H26:H38)</f>
-        <v>611</v>
+        <v>327</v>
       </c>
       <c r="I39" s="8"/>
       <c r="L39" t="s">
@@ -7404,20 +7347,20 @@
       <c r="E40" s="6"/>
       <c r="F40" s="8">
         <f>+SUM(F39+F25+F15)</f>
-        <v>-182</v>
+        <v>-1170</v>
       </c>
       <c r="G40" s="8">
         <f>+G15+G25+G39</f>
-        <v>5726</v>
+        <v>5718</v>
       </c>
       <c r="H40" s="8">
         <f>+H15+H25+H39</f>
-        <v>2146</v>
+        <v>1158</v>
       </c>
       <c r="I40" s="8"/>
       <c r="L40" s="1">
         <f>+H40/G40</f>
-        <v>0.37478169752008383</v>
+        <v>0.20251836306400839</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
@@ -7462,26 +7405,26 @@
       </c>
       <c r="D42" s="22">
         <f t="shared" si="4"/>
-        <v>8.3333333333333332E-3</v>
+        <v>0</v>
       </c>
       <c r="E42" s="13">
         <v>60</v>
       </c>
       <c r="F42" s="12">
         <f t="shared" si="5"/>
-        <v>-59</v>
+        <v>-60</v>
       </c>
       <c r="G42" s="13">
         <f>VLOOKUP(B42,'Base Cobertura'!$A:$C,3,FALSE)</f>
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H42" s="13">
         <f>VLOOKUP(B42,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42" s="17">
         <f t="shared" si="6"/>
-        <v>101</v>
+        <v>101.14999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -8055,7 +7998,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B3" s="51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" s="51">
         <v>3408</v>
@@ -8063,9 +8006,7 @@
       <c r="G3" t="s">
         <v>222</v>
       </c>
-      <c r="H3" s="51">
-        <v>1</v>
-      </c>
+      <c r="H3" s="51"/>
       <c r="I3" s="51">
         <v>3408</v>
       </c>
@@ -8075,16 +8016,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="51">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C4" s="51">
         <v>127</v>
       </c>
       <c r="G4" t="s">
         <v>223</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
       </c>
       <c r="I4" s="51">
         <v>3408</v>
@@ -8095,7 +8033,7 @@
         <v>10</v>
       </c>
       <c r="B5" s="51">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="C5" s="51">
         <v>181</v>
@@ -8113,10 +8051,10 @@
         <v>100</v>
       </c>
       <c r="B6" s="51">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C6" s="51">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="G6" t="s">
         <v>225</v>
@@ -8131,17 +8069,15 @@
         <v>11</v>
       </c>
       <c r="B7" s="51">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="C7" s="51">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G7" t="s">
         <v>226</v>
       </c>
-      <c r="H7" s="51">
-        <v>1</v>
-      </c>
+      <c r="H7" s="51"/>
       <c r="I7" s="51">
         <v>3408</v>
       </c>
@@ -8151,10 +8087,10 @@
         <v>12</v>
       </c>
       <c r="B8" s="51">
-        <v>93</v>
+        <v>48</v>
       </c>
       <c r="C8" s="51">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G8" t="s">
         <v>227</v>
@@ -8171,7 +8107,7 @@
         <v>123</v>
       </c>
       <c r="B9" s="51">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C9" s="51">
         <v>489</v>
@@ -8179,9 +8115,7 @@
       <c r="G9" t="s">
         <v>228</v>
       </c>
-      <c r="H9" s="51">
-        <v>1</v>
-      </c>
+      <c r="H9" s="51"/>
       <c r="I9" s="51">
         <v>3408</v>
       </c>
@@ -8191,16 +8125,13 @@
         <v>15</v>
       </c>
       <c r="B10" s="51">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="C10" s="51">
         <v>65</v>
       </c>
       <c r="G10" t="s">
         <v>229</v>
-      </c>
-      <c r="H10">
-        <v>1</v>
       </c>
       <c r="I10" s="51">
         <v>3408</v>
@@ -8211,7 +8142,7 @@
         <v>16</v>
       </c>
       <c r="B11" s="51">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="C11" s="51">
         <v>198</v>
@@ -8229,7 +8160,7 @@
         <v>18</v>
       </c>
       <c r="B12" s="51">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="C12" s="51">
         <v>177</v>
@@ -8245,7 +8176,7 @@
         <v>222</v>
       </c>
       <c r="H12">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="I12" s="51">
         <v>127</v>
@@ -8256,7 +8187,7 @@
         <v>19</v>
       </c>
       <c r="B13" s="51">
-        <v>105</v>
+        <v>59</v>
       </c>
       <c r="C13" s="51">
         <v>207</v>
@@ -8269,7 +8200,7 @@
         <v>223</v>
       </c>
       <c r="H13" s="51">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="I13" s="51">
         <v>127</v>
@@ -8280,7 +8211,7 @@
         <v>2</v>
       </c>
       <c r="B14" s="51">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="C14" s="51">
         <v>138</v>
@@ -8293,7 +8224,7 @@
         <v>224</v>
       </c>
       <c r="H14" s="51">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="I14" s="51">
         <v>127</v>
@@ -8304,7 +8235,7 @@
         <v>20</v>
       </c>
       <c r="B15" s="51">
-        <v>119</v>
+        <v>58</v>
       </c>
       <c r="C15" s="51">
         <v>227</v>
@@ -8317,7 +8248,7 @@
         <v>225</v>
       </c>
       <c r="H15" s="51">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="I15" s="51">
         <v>127</v>
@@ -8328,7 +8259,7 @@
         <v>21</v>
       </c>
       <c r="B16" s="51">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="C16" s="51">
         <v>170</v>
@@ -8341,7 +8272,7 @@
         <v>226</v>
       </c>
       <c r="H16" s="51">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="I16" s="51">
         <v>127</v>
@@ -8352,7 +8283,7 @@
         <v>22</v>
       </c>
       <c r="B17" s="51">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="C17" s="51">
         <v>72</v>
@@ -8365,7 +8296,7 @@
         <v>227</v>
       </c>
       <c r="H17" s="51">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="I17" s="51">
         <v>127</v>
@@ -8376,7 +8307,7 @@
         <v>23</v>
       </c>
       <c r="B18" s="51">
-        <v>89</v>
+        <v>54</v>
       </c>
       <c r="C18" s="51">
         <v>160</v>
@@ -8389,7 +8320,7 @@
         <v>228</v>
       </c>
       <c r="H18" s="51">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I18" s="51">
         <v>127</v>
@@ -8400,7 +8331,7 @@
         <v>24</v>
       </c>
       <c r="B19" s="51">
-        <v>71</v>
+        <v>31</v>
       </c>
       <c r="C19" s="51">
         <v>178</v>
@@ -8413,7 +8344,7 @@
         <v>229</v>
       </c>
       <c r="H19" s="51">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I19" s="51">
         <v>127</v>
@@ -8424,7 +8355,7 @@
         <v>25</v>
       </c>
       <c r="B20" s="51">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="C20" s="51">
         <v>172</v>
@@ -8437,7 +8368,7 @@
         <v>230</v>
       </c>
       <c r="H20">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I20" s="51">
         <v>127</v>
@@ -8448,10 +8379,10 @@
         <v>26</v>
       </c>
       <c r="B21" s="51">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C21" s="51">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E21">
         <f>+$F$21</f>
@@ -8464,7 +8395,7 @@
         <v>222</v>
       </c>
       <c r="H21" s="51">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I21" s="51">
         <v>181</v>
@@ -8475,7 +8406,7 @@
         <v>27</v>
       </c>
       <c r="B22" s="51">
-        <v>72</v>
+        <v>33</v>
       </c>
       <c r="C22" s="51">
         <v>140</v>
@@ -8499,7 +8430,7 @@
         <v>28</v>
       </c>
       <c r="B23" s="51">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="C23" s="51">
         <v>168</v>
@@ -8512,7 +8443,7 @@
         <v>224</v>
       </c>
       <c r="H23" s="51">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I23" s="51">
         <v>181</v>
@@ -8523,7 +8454,7 @@
         <v>3</v>
       </c>
       <c r="B24" s="51">
-        <v>83</v>
+        <v>39</v>
       </c>
       <c r="C24" s="51">
         <v>170</v>
@@ -8536,7 +8467,7 @@
         <v>225</v>
       </c>
       <c r="H24" s="51">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I24" s="51">
         <v>181</v>
@@ -8547,10 +8478,10 @@
         <v>30</v>
       </c>
       <c r="B25" s="51">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C25" s="51">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E25">
         <f t="shared" si="1"/>
@@ -8560,7 +8491,7 @@
         <v>226</v>
       </c>
       <c r="H25" s="51">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="I25" s="51">
         <v>181</v>
@@ -8571,7 +8502,7 @@
         <v>31</v>
       </c>
       <c r="B26" s="51">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="C26" s="51">
         <v>161</v>
@@ -8584,7 +8515,7 @@
         <v>227</v>
       </c>
       <c r="H26" s="51">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I26" s="51">
         <v>181</v>
@@ -8595,7 +8526,7 @@
         <v>32</v>
       </c>
       <c r="B27" s="51">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C27" s="51">
         <v>56</v>
@@ -8608,7 +8539,7 @@
         <v>228</v>
       </c>
       <c r="H27" s="51">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I27" s="51">
         <v>181</v>
@@ -8619,7 +8550,7 @@
         <v>33</v>
       </c>
       <c r="B28" s="51">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="C28" s="51">
         <v>172</v>
@@ -8632,7 +8563,7 @@
         <v>229</v>
       </c>
       <c r="H28" s="51">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I28" s="51">
         <v>181</v>
@@ -8643,7 +8574,7 @@
         <v>36</v>
       </c>
       <c r="B29" s="51">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="C29" s="51">
         <v>156</v>
@@ -8655,9 +8586,7 @@
       <c r="G29" t="s">
         <v>230</v>
       </c>
-      <c r="H29" s="51">
-        <v>3</v>
-      </c>
+      <c r="H29" s="51"/>
       <c r="I29" s="51">
         <v>181</v>
       </c>
@@ -8667,10 +8596,10 @@
         <v>37</v>
       </c>
       <c r="B30" s="51">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="C30" s="51">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E30">
         <f>+$F$30</f>
@@ -8683,10 +8612,10 @@
         <v>222</v>
       </c>
       <c r="H30" s="51">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I30" s="51">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
@@ -8694,7 +8623,7 @@
         <v>4</v>
       </c>
       <c r="B31" s="51">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="C31" s="51">
         <v>182</v>
@@ -8707,10 +8636,10 @@
         <v>223</v>
       </c>
       <c r="H31" s="51">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I31" s="51">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
@@ -8718,7 +8647,7 @@
         <v>40</v>
       </c>
       <c r="B32" s="51">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="C32" s="51">
         <v>249</v>
@@ -8731,19 +8660,17 @@
         <v>224</v>
       </c>
       <c r="H32" s="51">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I32" s="51">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>42</v>
       </c>
-      <c r="B33" s="51">
-        <v>4</v>
-      </c>
+      <c r="B33" s="51"/>
       <c r="C33" s="51">
         <v>52</v>
       </c>
@@ -8755,10 +8682,10 @@
         <v>225</v>
       </c>
       <c r="H33" s="51">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I33" s="51">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
@@ -8777,10 +8704,10 @@
         <v>226</v>
       </c>
       <c r="H34" s="51">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I34" s="51">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
@@ -8788,7 +8715,7 @@
         <v>44</v>
       </c>
       <c r="B35" s="51">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="C35" s="51">
         <v>169</v>
@@ -8801,10 +8728,10 @@
         <v>227</v>
       </c>
       <c r="H35" s="51">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I35" s="51">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
@@ -8812,7 +8739,7 @@
         <v>49</v>
       </c>
       <c r="B36" s="51">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C36" s="51">
         <v>239</v>
@@ -8825,10 +8752,10 @@
         <v>228</v>
       </c>
       <c r="H36" s="51">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I36" s="51">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
@@ -8836,7 +8763,7 @@
         <v>5</v>
       </c>
       <c r="B37" s="51">
-        <v>107</v>
+        <v>53</v>
       </c>
       <c r="C37" s="51">
         <v>260</v>
@@ -8849,10 +8776,10 @@
         <v>229</v>
       </c>
       <c r="H37" s="51">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I37" s="51">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
@@ -8860,7 +8787,7 @@
         <v>52</v>
       </c>
       <c r="B38" s="51">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C38" s="51">
         <v>101</v>
@@ -8874,7 +8801,7 @@
       </c>
       <c r="H38" s="51"/>
       <c r="I38" s="51">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
@@ -8882,7 +8809,7 @@
         <v>53</v>
       </c>
       <c r="B39" s="51">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C39" s="51">
         <v>105</v>
@@ -8898,10 +8825,10 @@
         <v>222</v>
       </c>
       <c r="H39" s="51">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I39" s="51">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
@@ -8909,7 +8836,7 @@
         <v>54</v>
       </c>
       <c r="B40" s="51">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="C40" s="51">
         <v>202</v>
@@ -8921,20 +8848,15 @@
       <c r="G40" t="s">
         <v>223</v>
       </c>
-      <c r="H40" s="51">
-        <v>8</v>
-      </c>
+      <c r="H40" s="51"/>
       <c r="I40" s="51">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>56</v>
       </c>
-      <c r="B41">
-        <v>41</v>
-      </c>
       <c r="C41" s="51">
         <v>198</v>
       </c>
@@ -8946,10 +8868,10 @@
         <v>224</v>
       </c>
       <c r="H41" s="51">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I41" s="51">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
@@ -8957,10 +8879,10 @@
         <v>57</v>
       </c>
       <c r="B42" s="51">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C42" s="51">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E42">
         <f t="shared" si="3"/>
@@ -8970,10 +8892,10 @@
         <v>225</v>
       </c>
       <c r="H42" s="51">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I42" s="51">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
@@ -8992,21 +8914,19 @@
         <v>226</v>
       </c>
       <c r="H43" s="51">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="I43" s="51">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>59</v>
       </c>
-      <c r="B44" s="51">
-        <v>1</v>
-      </c>
+      <c r="B44" s="51"/>
       <c r="C44" s="51">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E44">
         <f t="shared" si="3"/>
@@ -9016,10 +8936,10 @@
         <v>227</v>
       </c>
       <c r="H44" s="51">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="I44" s="51">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
@@ -9027,7 +8947,7 @@
         <v>7</v>
       </c>
       <c r="B45" s="51">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C45" s="51">
         <v>113</v>
@@ -9040,10 +8960,10 @@
         <v>228</v>
       </c>
       <c r="H45" s="51">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I45" s="51">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
@@ -9051,10 +8971,10 @@
         <v>8</v>
       </c>
       <c r="B46" s="51">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="C46" s="51">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E46">
         <f t="shared" si="3"/>
@@ -9064,10 +8984,10 @@
         <v>229</v>
       </c>
       <c r="H46" s="51">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I46" s="51">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
@@ -9075,7 +8995,7 @@
         <v>9</v>
       </c>
       <c r="B47" s="51">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="C47" s="51">
         <v>161</v>
@@ -9088,10 +9008,10 @@
         <v>230</v>
       </c>
       <c r="H47" s="51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I47" s="51">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
@@ -9108,10 +9028,10 @@
         <v>222</v>
       </c>
       <c r="H48" s="51">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I48" s="51">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="49" spans="2:9" x14ac:dyDescent="0.25">
@@ -9125,10 +9045,10 @@
         <v>223</v>
       </c>
       <c r="H49" s="51">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I49" s="51">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="50" spans="2:9" x14ac:dyDescent="0.25">
@@ -9140,10 +9060,10 @@
         <v>224</v>
       </c>
       <c r="H50" s="51">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="I50" s="51">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="51" spans="2:9" x14ac:dyDescent="0.25">
@@ -9155,10 +9075,10 @@
         <v>225</v>
       </c>
       <c r="H51" s="51">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I51" s="51">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.25">
@@ -9170,10 +9090,10 @@
         <v>226</v>
       </c>
       <c r="H52" s="51">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="I52" s="51">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.25">
@@ -9185,10 +9105,10 @@
         <v>227</v>
       </c>
       <c r="H53" s="51">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="I53" s="51">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.25">
@@ -9200,10 +9120,10 @@
         <v>228</v>
       </c>
       <c r="H54" s="51">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I54" s="51">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.25">
@@ -9215,10 +9135,10 @@
         <v>229</v>
       </c>
       <c r="H55" s="51">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I55" s="51">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.25">
@@ -9230,10 +9150,10 @@
         <v>230</v>
       </c>
       <c r="H56" s="51">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I56" s="51">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="57" spans="2:9" x14ac:dyDescent="0.25">
@@ -9248,7 +9168,7 @@
         <v>222</v>
       </c>
       <c r="H57" s="51">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I57" s="51">
         <v>489</v>
@@ -9263,7 +9183,7 @@
         <v>223</v>
       </c>
       <c r="H58" s="51">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I58" s="51">
         <v>489</v>
@@ -9278,7 +9198,7 @@
         <v>224</v>
       </c>
       <c r="H59" s="51">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I59" s="51">
         <v>489</v>
@@ -9292,9 +9212,7 @@
       <c r="G60" t="s">
         <v>225</v>
       </c>
-      <c r="H60" s="51">
-        <v>1</v>
-      </c>
+      <c r="H60" s="51"/>
       <c r="I60" s="51">
         <v>489</v>
       </c>
@@ -9308,7 +9226,7 @@
         <v>226</v>
       </c>
       <c r="H61" s="51">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I61" s="51">
         <v>489</v>
@@ -9336,7 +9254,7 @@
         <v>228</v>
       </c>
       <c r="H63" s="51">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I63" s="51">
         <v>489</v>
@@ -9350,9 +9268,7 @@
       <c r="G64" t="s">
         <v>229</v>
       </c>
-      <c r="H64" s="51">
-        <v>2</v>
-      </c>
+      <c r="H64" s="51"/>
       <c r="I64" s="51">
         <v>489</v>
       </c>
@@ -9382,7 +9298,7 @@
         <v>222</v>
       </c>
       <c r="H66" s="51">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I66" s="51">
         <v>65</v>
@@ -9397,7 +9313,7 @@
         <v>223</v>
       </c>
       <c r="H67" s="51">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I67" s="51">
         <v>65</v>
@@ -9412,7 +9328,7 @@
         <v>224</v>
       </c>
       <c r="H68" s="51">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I68" s="51">
         <v>65</v>
@@ -9427,7 +9343,7 @@
         <v>225</v>
       </c>
       <c r="H69" s="51">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I69" s="51">
         <v>65</v>
@@ -9442,7 +9358,7 @@
         <v>226</v>
       </c>
       <c r="H70" s="51">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I70" s="51">
         <v>65</v>
@@ -9457,7 +9373,7 @@
         <v>227</v>
       </c>
       <c r="H71" s="51">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I71" s="51">
         <v>65</v>
@@ -9472,7 +9388,7 @@
         <v>228</v>
       </c>
       <c r="H72" s="51">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I72" s="51">
         <v>65</v>
@@ -9487,7 +9403,7 @@
         <v>229</v>
       </c>
       <c r="H73" s="51">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I73" s="51">
         <v>65</v>
@@ -9520,7 +9436,7 @@
         <v>222</v>
       </c>
       <c r="H75" s="51">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I75" s="51">
         <v>198</v>
@@ -9535,7 +9451,7 @@
         <v>223</v>
       </c>
       <c r="H76">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I76" s="51">
         <v>198</v>
@@ -9550,7 +9466,7 @@
         <v>224</v>
       </c>
       <c r="H77" s="51">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="I77" s="51">
         <v>198</v>
@@ -9565,7 +9481,7 @@
         <v>225</v>
       </c>
       <c r="H78" s="51">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="I78" s="51">
         <v>198</v>
@@ -9580,7 +9496,7 @@
         <v>226</v>
       </c>
       <c r="H79" s="51">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I79" s="51">
         <v>198</v>
@@ -9595,7 +9511,7 @@
         <v>227</v>
       </c>
       <c r="H80" s="51">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="I80" s="51">
         <v>198</v>
@@ -9610,7 +9526,7 @@
         <v>228</v>
       </c>
       <c r="H81" s="51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I81" s="51">
         <v>198</v>
@@ -9625,7 +9541,7 @@
         <v>229</v>
       </c>
       <c r="H82" s="51">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I82" s="51">
         <v>198</v>
@@ -9640,7 +9556,7 @@
         <v>230</v>
       </c>
       <c r="H83" s="51">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I83" s="51">
         <v>198</v>
@@ -9658,7 +9574,7 @@
         <v>222</v>
       </c>
       <c r="H84" s="51">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="I84" s="51">
         <v>177</v>
@@ -9673,7 +9589,7 @@
         <v>223</v>
       </c>
       <c r="H85" s="51">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I85" s="51">
         <v>177</v>
@@ -9688,7 +9604,7 @@
         <v>224</v>
       </c>
       <c r="H86" s="51">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="I86" s="51">
         <v>177</v>
@@ -9703,7 +9619,7 @@
         <v>225</v>
       </c>
       <c r="H87" s="51">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I87" s="51">
         <v>177</v>
@@ -9718,7 +9634,7 @@
         <v>226</v>
       </c>
       <c r="H88" s="51">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="I88" s="51">
         <v>177</v>
@@ -9733,7 +9649,7 @@
         <v>227</v>
       </c>
       <c r="H89" s="51">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="I89" s="51">
         <v>177</v>
@@ -9748,7 +9664,7 @@
         <v>228</v>
       </c>
       <c r="H90" s="51">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I90" s="51">
         <v>177</v>
@@ -9763,7 +9679,7 @@
         <v>229</v>
       </c>
       <c r="H91" s="51">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I91" s="51">
         <v>177</v>
@@ -9778,7 +9694,7 @@
         <v>230</v>
       </c>
       <c r="H92" s="51">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I92" s="51">
         <v>177</v>
@@ -9796,7 +9712,7 @@
         <v>222</v>
       </c>
       <c r="H93" s="51">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="I93" s="51">
         <v>207</v>
@@ -9811,7 +9727,7 @@
         <v>223</v>
       </c>
       <c r="H94" s="51">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I94" s="51">
         <v>207</v>
@@ -9826,7 +9742,7 @@
         <v>224</v>
       </c>
       <c r="H95" s="51">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="I95" s="51">
         <v>207</v>
@@ -9841,7 +9757,7 @@
         <v>225</v>
       </c>
       <c r="H96" s="51">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="I96" s="51">
         <v>207</v>
@@ -9856,7 +9772,7 @@
         <v>226</v>
       </c>
       <c r="H97" s="51">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="I97" s="51">
         <v>207</v>
@@ -9871,7 +9787,7 @@
         <v>227</v>
       </c>
       <c r="H98" s="51">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="I98" s="51">
         <v>207</v>
@@ -9885,9 +9801,7 @@
       <c r="G99" t="s">
         <v>228</v>
       </c>
-      <c r="H99" s="51">
-        <v>6</v>
-      </c>
+      <c r="H99" s="51"/>
       <c r="I99" s="51">
         <v>207</v>
       </c>
@@ -9901,7 +9815,7 @@
         <v>229</v>
       </c>
       <c r="H100" s="51">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I100" s="51">
         <v>207</v>
@@ -9916,7 +9830,7 @@
         <v>230</v>
       </c>
       <c r="H101" s="51">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="I101" s="51">
         <v>207</v>
@@ -9934,7 +9848,7 @@
         <v>222</v>
       </c>
       <c r="H102" s="51">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I102" s="51">
         <v>138</v>
@@ -9949,7 +9863,7 @@
         <v>223</v>
       </c>
       <c r="H103" s="51">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="I103" s="51">
         <v>138</v>
@@ -9964,7 +9878,7 @@
         <v>224</v>
       </c>
       <c r="H104" s="51">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I104" s="51">
         <v>138</v>
@@ -9979,7 +9893,7 @@
         <v>225</v>
       </c>
       <c r="H105" s="51">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I105" s="51">
         <v>138</v>
@@ -9994,7 +9908,7 @@
         <v>226</v>
       </c>
       <c r="H106" s="51">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="I106" s="51">
         <v>138</v>
@@ -10009,7 +9923,7 @@
         <v>227</v>
       </c>
       <c r="H107" s="51">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="I107" s="51">
         <v>138</v>
@@ -10039,7 +9953,7 @@
         <v>229</v>
       </c>
       <c r="H109" s="51">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I109" s="51">
         <v>138</v>
@@ -10054,7 +9968,7 @@
         <v>230</v>
       </c>
       <c r="H110" s="51">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I110" s="51">
         <v>138</v>
@@ -10072,7 +9986,7 @@
         <v>222</v>
       </c>
       <c r="H111" s="51">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="I111" s="51">
         <v>227</v>
@@ -10087,7 +10001,7 @@
         <v>223</v>
       </c>
       <c r="H112" s="51">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="I112" s="51">
         <v>227</v>
@@ -10102,7 +10016,7 @@
         <v>224</v>
       </c>
       <c r="H113" s="51">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="I113" s="51">
         <v>227</v>
@@ -10117,7 +10031,7 @@
         <v>225</v>
       </c>
       <c r="H114" s="51">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="I114" s="51">
         <v>227</v>
@@ -10132,7 +10046,7 @@
         <v>226</v>
       </c>
       <c r="H115" s="51">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="I115" s="51">
         <v>227</v>
@@ -10147,7 +10061,7 @@
         <v>227</v>
       </c>
       <c r="H116">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="I116" s="51">
         <v>227</v>
@@ -10162,7 +10076,7 @@
         <v>228</v>
       </c>
       <c r="H117" s="51">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I117" s="51">
         <v>227</v>
@@ -10177,7 +10091,7 @@
         <v>229</v>
       </c>
       <c r="H118" s="51">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I118" s="51">
         <v>227</v>
@@ -10192,7 +10106,7 @@
         <v>230</v>
       </c>
       <c r="H119" s="51">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="I119" s="51">
         <v>227</v>
@@ -10210,7 +10124,7 @@
         <v>222</v>
       </c>
       <c r="H120" s="51">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="I120" s="51">
         <v>170</v>
@@ -10225,7 +10139,7 @@
         <v>223</v>
       </c>
       <c r="H121" s="51">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="I121" s="51">
         <v>170</v>
@@ -10240,7 +10154,7 @@
         <v>224</v>
       </c>
       <c r="H122" s="51">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="I122" s="51">
         <v>170</v>
@@ -10255,7 +10169,7 @@
         <v>225</v>
       </c>
       <c r="H123" s="51">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="I123" s="51">
         <v>170</v>
@@ -10270,7 +10184,7 @@
         <v>226</v>
       </c>
       <c r="H124">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="I124" s="51">
         <v>170</v>
@@ -10285,7 +10199,7 @@
         <v>227</v>
       </c>
       <c r="H125" s="51">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="I125" s="51">
         <v>170</v>
@@ -10300,7 +10214,7 @@
         <v>228</v>
       </c>
       <c r="H126" s="51">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I126" s="51">
         <v>170</v>
@@ -10315,7 +10229,7 @@
         <v>229</v>
       </c>
       <c r="H127" s="51">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="I127" s="51">
         <v>170</v>
@@ -10330,7 +10244,7 @@
         <v>230</v>
       </c>
       <c r="H128" s="51">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I128" s="51">
         <v>170</v>
@@ -10348,7 +10262,7 @@
         <v>222</v>
       </c>
       <c r="H129" s="51">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="I129" s="51">
         <v>72</v>
@@ -10363,7 +10277,7 @@
         <v>223</v>
       </c>
       <c r="H130" s="51">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I130" s="51">
         <v>72</v>
@@ -10378,7 +10292,7 @@
         <v>224</v>
       </c>
       <c r="H131" s="51">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="I131" s="51">
         <v>72</v>
@@ -10393,7 +10307,7 @@
         <v>225</v>
       </c>
       <c r="H132" s="51">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I132" s="51">
         <v>72</v>
@@ -10408,7 +10322,7 @@
         <v>226</v>
       </c>
       <c r="H133" s="51">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="I133" s="51">
         <v>72</v>
@@ -10423,7 +10337,7 @@
         <v>227</v>
       </c>
       <c r="H134" s="51">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I134" s="51">
         <v>72</v>
@@ -10438,7 +10352,7 @@
         <v>228</v>
       </c>
       <c r="H135" s="51">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="I135" s="51">
         <v>72</v>
@@ -10453,7 +10367,7 @@
         <v>229</v>
       </c>
       <c r="H136" s="51">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I136" s="51">
         <v>72</v>
@@ -10468,7 +10382,7 @@
         <v>230</v>
       </c>
       <c r="H137" s="51">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I137" s="51">
         <v>72</v>
@@ -10486,7 +10400,7 @@
         <v>222</v>
       </c>
       <c r="H138" s="51">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="I138" s="51">
         <v>160</v>
@@ -10501,7 +10415,7 @@
         <v>223</v>
       </c>
       <c r="H139" s="51">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="I139" s="51">
         <v>160</v>
@@ -10516,7 +10430,7 @@
         <v>224</v>
       </c>
       <c r="H140">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="I140" s="51">
         <v>160</v>
@@ -10531,7 +10445,7 @@
         <v>225</v>
       </c>
       <c r="H141" s="51">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I141" s="51">
         <v>160</v>
@@ -10546,7 +10460,7 @@
         <v>226</v>
       </c>
       <c r="H142" s="51">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="I142" s="51">
         <v>160</v>
@@ -10561,7 +10475,7 @@
         <v>227</v>
       </c>
       <c r="H143" s="51">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="I143" s="51">
         <v>160</v>
@@ -10576,7 +10490,7 @@
         <v>228</v>
       </c>
       <c r="H144" s="51">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I144" s="51">
         <v>160</v>
@@ -10591,7 +10505,7 @@
         <v>229</v>
       </c>
       <c r="H145" s="51">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I145" s="51">
         <v>160</v>
@@ -10606,7 +10520,7 @@
         <v>230</v>
       </c>
       <c r="H146" s="51">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I146" s="51">
         <v>160</v>
@@ -10624,7 +10538,7 @@
         <v>222</v>
       </c>
       <c r="H147" s="51">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I147" s="51">
         <v>178</v>
@@ -10639,7 +10553,7 @@
         <v>223</v>
       </c>
       <c r="H148">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I148" s="51">
         <v>178</v>
@@ -10654,7 +10568,7 @@
         <v>224</v>
       </c>
       <c r="H149" s="51">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="I149" s="51">
         <v>178</v>
@@ -10669,7 +10583,7 @@
         <v>225</v>
       </c>
       <c r="H150" s="51">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="I150" s="51">
         <v>178</v>
@@ -10684,7 +10598,7 @@
         <v>226</v>
       </c>
       <c r="H151" s="51">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="I151" s="51">
         <v>178</v>
@@ -10699,7 +10613,7 @@
         <v>227</v>
       </c>
       <c r="H152" s="51">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="I152" s="51">
         <v>178</v>
@@ -10714,7 +10628,7 @@
         <v>228</v>
       </c>
       <c r="H153" s="51">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I153" s="51">
         <v>178</v>
@@ -10728,9 +10642,7 @@
       <c r="G154" t="s">
         <v>229</v>
       </c>
-      <c r="H154" s="51">
-        <v>5</v>
-      </c>
+      <c r="H154" s="51"/>
       <c r="I154" s="51">
         <v>178</v>
       </c>
@@ -10762,7 +10674,7 @@
         <v>222</v>
       </c>
       <c r="H156" s="51">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="I156" s="51">
         <v>172</v>
@@ -10777,7 +10689,7 @@
         <v>223</v>
       </c>
       <c r="H157" s="51">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="I157" s="51">
         <v>172</v>
@@ -10792,7 +10704,7 @@
         <v>224</v>
       </c>
       <c r="H158" s="51">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="I158" s="51">
         <v>172</v>
@@ -10807,7 +10719,7 @@
         <v>225</v>
       </c>
       <c r="H159" s="51">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="I159" s="51">
         <v>172</v>
@@ -10822,7 +10734,7 @@
         <v>226</v>
       </c>
       <c r="H160" s="51">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="I160" s="51">
         <v>172</v>
@@ -10837,7 +10749,7 @@
         <v>227</v>
       </c>
       <c r="H161" s="51">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="I161" s="51">
         <v>172</v>
@@ -10852,7 +10764,7 @@
         <v>228</v>
       </c>
       <c r="H162" s="51">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="I162" s="51">
         <v>172</v>
@@ -10867,7 +10779,7 @@
         <v>229</v>
       </c>
       <c r="H163" s="51">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I163" s="51">
         <v>172</v>
@@ -10882,7 +10794,7 @@
         <v>230</v>
       </c>
       <c r="H164">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I164" s="51">
         <v>172</v>
@@ -10903,7 +10815,7 @@
         <v>12</v>
       </c>
       <c r="I165" s="51">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="166" spans="5:9" x14ac:dyDescent="0.25">
@@ -10918,7 +10830,7 @@
         <v>6</v>
       </c>
       <c r="I166" s="51">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="167" spans="5:9" x14ac:dyDescent="0.25">
@@ -10930,10 +10842,10 @@
         <v>224</v>
       </c>
       <c r="H167" s="51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I167" s="51">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="168" spans="5:9" x14ac:dyDescent="0.25">
@@ -10948,7 +10860,7 @@
         <v>15</v>
       </c>
       <c r="I168" s="51">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="169" spans="5:9" x14ac:dyDescent="0.25">
@@ -10963,7 +10875,7 @@
         <v>11</v>
       </c>
       <c r="I169" s="51">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="170" spans="5:9" x14ac:dyDescent="0.25">
@@ -10978,7 +10890,7 @@
         <v>12</v>
       </c>
       <c r="I170" s="51">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="171" spans="5:9" x14ac:dyDescent="0.25">
@@ -10990,10 +10902,10 @@
         <v>228</v>
       </c>
       <c r="H171" s="51">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I171" s="51">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="172" spans="5:9" x14ac:dyDescent="0.25">
@@ -11008,7 +10920,7 @@
         <v>6</v>
       </c>
       <c r="I172" s="51">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="173" spans="5:9" x14ac:dyDescent="0.25">
@@ -11023,7 +10935,7 @@
         <v>11</v>
       </c>
       <c r="I173" s="51">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="174" spans="5:9" x14ac:dyDescent="0.25">
@@ -11038,7 +10950,7 @@
         <v>222</v>
       </c>
       <c r="H174" s="51">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I174" s="51">
         <v>140</v>
@@ -11053,7 +10965,7 @@
         <v>223</v>
       </c>
       <c r="H175" s="51">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I175" s="51">
         <v>140</v>
@@ -11068,7 +10980,7 @@
         <v>224</v>
       </c>
       <c r="H176" s="51">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="I176" s="51">
         <v>140</v>
@@ -11083,7 +10995,7 @@
         <v>225</v>
       </c>
       <c r="H177" s="51">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I177" s="51">
         <v>140</v>
@@ -11098,7 +11010,7 @@
         <v>226</v>
       </c>
       <c r="H178" s="51">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="I178" s="51">
         <v>140</v>
@@ -11113,7 +11025,7 @@
         <v>227</v>
       </c>
       <c r="H179" s="51">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="I179" s="51">
         <v>140</v>
@@ -11128,7 +11040,7 @@
         <v>228</v>
       </c>
       <c r="H180">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="I180" s="51">
         <v>140</v>
@@ -11143,7 +11055,7 @@
         <v>229</v>
       </c>
       <c r="H181" s="51">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I181" s="51">
         <v>140</v>
@@ -11158,7 +11070,7 @@
         <v>230</v>
       </c>
       <c r="H182" s="51">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I182" s="51">
         <v>140</v>
@@ -11176,7 +11088,7 @@
         <v>222</v>
       </c>
       <c r="H183" s="51">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I183" s="51">
         <v>168</v>
@@ -11191,7 +11103,7 @@
         <v>223</v>
       </c>
       <c r="H184" s="51">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I184" s="51">
         <v>168</v>
@@ -11206,7 +11118,7 @@
         <v>224</v>
       </c>
       <c r="H185" s="51">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I185" s="51">
         <v>168</v>
@@ -11221,7 +11133,7 @@
         <v>225</v>
       </c>
       <c r="H186">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I186" s="51">
         <v>168</v>
@@ -11236,7 +11148,7 @@
         <v>226</v>
       </c>
       <c r="H187" s="51">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="I187" s="51">
         <v>168</v>
@@ -11251,7 +11163,7 @@
         <v>227</v>
       </c>
       <c r="H188" s="51">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="I188" s="51">
         <v>168</v>
@@ -11281,7 +11193,7 @@
         <v>229</v>
       </c>
       <c r="H190" s="51">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I190" s="51">
         <v>168</v>
@@ -11296,7 +11208,7 @@
         <v>230</v>
       </c>
       <c r="H191" s="51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I191" s="51">
         <v>168</v>
@@ -11314,7 +11226,7 @@
         <v>222</v>
       </c>
       <c r="H192" s="51">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I192" s="51">
         <v>170</v>
@@ -11329,7 +11241,7 @@
         <v>223</v>
       </c>
       <c r="H193" s="51">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I193" s="51">
         <v>170</v>
@@ -11344,7 +11256,7 @@
         <v>224</v>
       </c>
       <c r="H194" s="51">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="I194" s="51">
         <v>170</v>
@@ -11359,7 +11271,7 @@
         <v>225</v>
       </c>
       <c r="H195" s="51">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="I195" s="51">
         <v>170</v>
@@ -11374,7 +11286,7 @@
         <v>226</v>
       </c>
       <c r="H196">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="I196" s="51">
         <v>170</v>
@@ -11389,7 +11301,7 @@
         <v>227</v>
       </c>
       <c r="H197" s="51">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I197" s="51">
         <v>170</v>
@@ -11404,7 +11316,7 @@
         <v>228</v>
       </c>
       <c r="H198" s="51">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I198" s="51">
         <v>170</v>
@@ -11419,7 +11331,7 @@
         <v>229</v>
       </c>
       <c r="H199" s="51">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I199" s="51">
         <v>170</v>
@@ -11434,7 +11346,7 @@
         <v>230</v>
       </c>
       <c r="H200" s="51">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I200" s="51">
         <v>170</v>
@@ -11452,10 +11364,10 @@
         <v>222</v>
       </c>
       <c r="H201" s="51">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I201" s="51">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="202" spans="5:9" x14ac:dyDescent="0.25">
@@ -11466,11 +11378,9 @@
       <c r="G202" t="s">
         <v>223</v>
       </c>
-      <c r="H202" s="51">
-        <v>1</v>
-      </c>
+      <c r="H202" s="51"/>
       <c r="I202" s="51">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="203" spans="5:9" x14ac:dyDescent="0.25">
@@ -11482,10 +11392,10 @@
         <v>224</v>
       </c>
       <c r="H203" s="51">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I203" s="51">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="204" spans="5:9" x14ac:dyDescent="0.25">
@@ -11498,7 +11408,7 @@
       </c>
       <c r="H204" s="51"/>
       <c r="I204" s="51">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="205" spans="5:9" x14ac:dyDescent="0.25">
@@ -11509,11 +11419,9 @@
       <c r="G205" t="s">
         <v>226</v>
       </c>
-      <c r="H205" s="51">
-        <v>3</v>
-      </c>
+      <c r="H205" s="51"/>
       <c r="I205" s="51">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="206" spans="5:9" x14ac:dyDescent="0.25">
@@ -11526,7 +11434,7 @@
       </c>
       <c r="H206" s="51"/>
       <c r="I206" s="51">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="207" spans="5:9" x14ac:dyDescent="0.25">
@@ -11537,11 +11445,9 @@
       <c r="G207" t="s">
         <v>228</v>
       </c>
-      <c r="H207" s="51">
-        <v>8</v>
-      </c>
+      <c r="H207" s="51"/>
       <c r="I207" s="51">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="208" spans="5:9" x14ac:dyDescent="0.25">
@@ -11554,7 +11460,7 @@
       </c>
       <c r="H208" s="51"/>
       <c r="I208" s="51">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="209" spans="5:9" x14ac:dyDescent="0.25">
@@ -11567,7 +11473,7 @@
       </c>
       <c r="H209" s="51"/>
       <c r="I209" s="51">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="210" spans="5:9" x14ac:dyDescent="0.25">
@@ -11582,7 +11488,7 @@
         <v>222</v>
       </c>
       <c r="H210" s="51">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="I210" s="51">
         <v>161</v>
@@ -11597,7 +11503,7 @@
         <v>223</v>
       </c>
       <c r="H211" s="51">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I211" s="51">
         <v>161</v>
@@ -11612,7 +11518,7 @@
         <v>224</v>
       </c>
       <c r="H212">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="I212" s="51">
         <v>161</v>
@@ -11627,7 +11533,7 @@
         <v>225</v>
       </c>
       <c r="H213" s="51">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="I213" s="51">
         <v>161</v>
@@ -11642,7 +11548,7 @@
         <v>226</v>
       </c>
       <c r="H214" s="51">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="I214" s="51">
         <v>161</v>
@@ -11657,7 +11563,7 @@
         <v>227</v>
       </c>
       <c r="H215" s="51">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="I215" s="51">
         <v>161</v>
@@ -11672,7 +11578,7 @@
         <v>228</v>
       </c>
       <c r="H216" s="51">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I216" s="51">
         <v>161</v>
@@ -11687,7 +11593,7 @@
         <v>229</v>
       </c>
       <c r="H217" s="51">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="I217" s="51">
         <v>161</v>
@@ -11702,7 +11608,7 @@
         <v>230</v>
       </c>
       <c r="H218" s="51">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I218" s="51">
         <v>161</v>
@@ -11720,7 +11626,7 @@
         <v>222</v>
       </c>
       <c r="H219" s="51">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I219" s="51">
         <v>56</v>
@@ -11735,7 +11641,7 @@
         <v>223</v>
       </c>
       <c r="H220" s="51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I220" s="51">
         <v>56</v>
@@ -11750,7 +11656,7 @@
         <v>224</v>
       </c>
       <c r="H221" s="51">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I221" s="51">
         <v>56</v>
@@ -11765,7 +11671,7 @@
         <v>225</v>
       </c>
       <c r="H222" s="51">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I222" s="51">
         <v>56</v>
@@ -11780,7 +11686,7 @@
         <v>226</v>
       </c>
       <c r="H223" s="51">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I223" s="51">
         <v>56</v>
@@ -11795,7 +11701,7 @@
         <v>227</v>
       </c>
       <c r="H224" s="51">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I224" s="51">
         <v>56</v>
@@ -11810,7 +11716,7 @@
         <v>228</v>
       </c>
       <c r="H225" s="51">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I225" s="51">
         <v>56</v>
@@ -11825,7 +11731,7 @@
         <v>229</v>
       </c>
       <c r="H226" s="51">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I226" s="51">
         <v>56</v>
@@ -11840,7 +11746,7 @@
         <v>230</v>
       </c>
       <c r="H227" s="51">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I227" s="51">
         <v>56</v>
@@ -11858,7 +11764,7 @@
         <v>222</v>
       </c>
       <c r="H228" s="51">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I228" s="51">
         <v>172</v>
@@ -11873,7 +11779,7 @@
         <v>223</v>
       </c>
       <c r="H229" s="51">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I229" s="51">
         <v>172</v>
@@ -11888,7 +11794,7 @@
         <v>224</v>
       </c>
       <c r="H230" s="51">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="I230" s="51">
         <v>172</v>
@@ -11903,7 +11809,7 @@
         <v>225</v>
       </c>
       <c r="H231" s="51">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I231" s="51">
         <v>172</v>
@@ -11918,7 +11824,7 @@
         <v>226</v>
       </c>
       <c r="H232" s="51">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="I232" s="51">
         <v>172</v>
@@ -11933,7 +11839,7 @@
         <v>227</v>
       </c>
       <c r="H233" s="51">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="I233" s="51">
         <v>172</v>
@@ -11963,7 +11869,7 @@
         <v>229</v>
       </c>
       <c r="H235" s="51">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I235" s="51">
         <v>172</v>
@@ -11978,7 +11884,7 @@
         <v>230</v>
       </c>
       <c r="H236">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I236" s="51">
         <v>172</v>
@@ -11996,7 +11902,7 @@
         <v>222</v>
       </c>
       <c r="H237" s="51">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I237" s="51">
         <v>156</v>
@@ -12011,7 +11917,7 @@
         <v>223</v>
       </c>
       <c r="H238" s="51">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I238" s="51">
         <v>156</v>
@@ -12026,7 +11932,7 @@
         <v>224</v>
       </c>
       <c r="H239" s="51">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="I239" s="51">
         <v>156</v>
@@ -12041,7 +11947,7 @@
         <v>225</v>
       </c>
       <c r="H240" s="51">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I240" s="51">
         <v>156</v>
@@ -12056,7 +11962,7 @@
         <v>226</v>
       </c>
       <c r="H241" s="51">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="I241" s="51">
         <v>156</v>
@@ -12071,7 +11977,7 @@
         <v>227</v>
       </c>
       <c r="H242" s="51">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="I242" s="51">
         <v>156</v>
@@ -12086,7 +11992,7 @@
         <v>228</v>
       </c>
       <c r="H243" s="51">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I243" s="51">
         <v>156</v>
@@ -12101,7 +12007,7 @@
         <v>229</v>
       </c>
       <c r="H244">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I244" s="51">
         <v>156</v>
@@ -12115,9 +12021,7 @@
       <c r="G245" t="s">
         <v>230</v>
       </c>
-      <c r="H245" s="51">
-        <v>5</v>
-      </c>
+      <c r="H245" s="51"/>
       <c r="I245" s="51">
         <v>156</v>
       </c>
@@ -12134,10 +12038,10 @@
         <v>222</v>
       </c>
       <c r="H246" s="51">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I246" s="51">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="247" spans="5:9" x14ac:dyDescent="0.25">
@@ -12148,11 +12052,9 @@
       <c r="G247" t="s">
         <v>223</v>
       </c>
-      <c r="H247" s="51">
-        <v>3</v>
-      </c>
+      <c r="H247" s="51"/>
       <c r="I247" s="51">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="248" spans="5:9" x14ac:dyDescent="0.25">
@@ -12164,10 +12066,10 @@
         <v>224</v>
       </c>
       <c r="H248" s="51">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I248" s="51">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="249" spans="5:9" x14ac:dyDescent="0.25">
@@ -12178,11 +12080,9 @@
       <c r="G249" t="s">
         <v>225</v>
       </c>
-      <c r="H249" s="51">
-        <v>5</v>
-      </c>
+      <c r="H249" s="51"/>
       <c r="I249" s="51">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="250" spans="5:9" x14ac:dyDescent="0.25">
@@ -12194,10 +12094,10 @@
         <v>226</v>
       </c>
       <c r="H250" s="51">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I250" s="51">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="251" spans="5:9" x14ac:dyDescent="0.25">
@@ -12209,10 +12109,10 @@
         <v>227</v>
       </c>
       <c r="H251" s="51">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I251" s="51">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="252" spans="5:9" x14ac:dyDescent="0.25">
@@ -12224,10 +12124,10 @@
         <v>228</v>
       </c>
       <c r="H252">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I252" s="51">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="253" spans="5:9" x14ac:dyDescent="0.25">
@@ -12239,10 +12139,10 @@
         <v>229</v>
       </c>
       <c r="H253" s="51">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I253" s="51">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="254" spans="5:9" x14ac:dyDescent="0.25">
@@ -12253,11 +12153,9 @@
       <c r="G254" t="s">
         <v>230</v>
       </c>
-      <c r="H254" s="51">
-        <v>4</v>
-      </c>
+      <c r="H254" s="51"/>
       <c r="I254" s="51">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="255" spans="5:9" x14ac:dyDescent="0.25">
@@ -12272,7 +12170,7 @@
         <v>222</v>
       </c>
       <c r="H255" s="51">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I255" s="51">
         <v>182</v>
@@ -12287,7 +12185,7 @@
         <v>223</v>
       </c>
       <c r="H256" s="51">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I256" s="51">
         <v>182</v>
@@ -12302,7 +12200,7 @@
         <v>224</v>
       </c>
       <c r="H257" s="51">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="I257" s="51">
         <v>182</v>
@@ -12317,7 +12215,7 @@
         <v>225</v>
       </c>
       <c r="H258">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="I258" s="51">
         <v>182</v>
@@ -12332,7 +12230,7 @@
         <v>226</v>
       </c>
       <c r="H259" s="51">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="I259" s="51">
         <v>182</v>
@@ -12347,7 +12245,7 @@
         <v>227</v>
       </c>
       <c r="H260">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="I260" s="51">
         <v>182</v>
@@ -12362,7 +12260,7 @@
         <v>228</v>
       </c>
       <c r="H261" s="51">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I261" s="51">
         <v>182</v>
@@ -12377,7 +12275,7 @@
         <v>229</v>
       </c>
       <c r="H262" s="51">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I262" s="51">
         <v>182</v>
@@ -12392,7 +12290,7 @@
         <v>230</v>
       </c>
       <c r="H263" s="51">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I263" s="51">
         <v>182</v>
@@ -12410,7 +12308,7 @@
         <v>222</v>
       </c>
       <c r="H264" s="51">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I264" s="51">
         <v>249</v>
@@ -12425,7 +12323,7 @@
         <v>223</v>
       </c>
       <c r="H265">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I265" s="51">
         <v>249</v>
@@ -12440,7 +12338,7 @@
         <v>224</v>
       </c>
       <c r="H266" s="51">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I266" s="51">
         <v>249</v>
@@ -12455,7 +12353,7 @@
         <v>225</v>
       </c>
       <c r="H267" s="51">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I267" s="51">
         <v>249</v>
@@ -12470,7 +12368,7 @@
         <v>226</v>
       </c>
       <c r="H268">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="I268" s="51">
         <v>249</v>
@@ -12485,7 +12383,7 @@
         <v>227</v>
       </c>
       <c r="H269" s="51">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="I269" s="51">
         <v>249</v>
@@ -12500,7 +12398,7 @@
         <v>228</v>
       </c>
       <c r="H270" s="51">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I270" s="51">
         <v>249</v>
@@ -12515,7 +12413,7 @@
         <v>229</v>
       </c>
       <c r="H271" s="51">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I271" s="51">
         <v>249</v>
@@ -12530,7 +12428,7 @@
         <v>230</v>
       </c>
       <c r="H272" s="51">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I272" s="51">
         <v>249</v>
@@ -12598,9 +12496,7 @@
       <c r="G277" t="s">
         <v>226</v>
       </c>
-      <c r="H277" s="51">
-        <v>3</v>
-      </c>
+      <c r="H277" s="51"/>
       <c r="I277" s="51">
         <v>52</v>
       </c>
@@ -12613,9 +12509,7 @@
       <c r="G278" t="s">
         <v>227</v>
       </c>
-      <c r="H278" s="51">
-        <v>2</v>
-      </c>
+      <c r="H278" s="51"/>
       <c r="I278" s="51">
         <v>52</v>
       </c>
@@ -12628,9 +12522,7 @@
       <c r="G279" t="s">
         <v>228</v>
       </c>
-      <c r="H279" s="51">
-        <v>4</v>
-      </c>
+      <c r="H279" s="51"/>
       <c r="I279" s="51">
         <v>52</v>
       </c>
@@ -12643,9 +12535,7 @@
       <c r="G280" t="s">
         <v>229</v>
       </c>
-      <c r="H280" s="51">
-        <v>1</v>
-      </c>
+      <c r="H280" s="51"/>
       <c r="I280" s="51">
         <v>52</v>
       </c>
@@ -12658,9 +12548,7 @@
       <c r="G281" t="s">
         <v>230</v>
       </c>
-      <c r="H281" s="51">
-        <v>2</v>
-      </c>
+      <c r="H281" s="51"/>
       <c r="I281" s="51">
         <v>52</v>
       </c>
@@ -12791,7 +12679,7 @@
         <v>222</v>
       </c>
       <c r="H291">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I291" s="51">
         <v>169</v>
@@ -12806,7 +12694,7 @@
         <v>223</v>
       </c>
       <c r="H292">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I292" s="51">
         <v>169</v>
@@ -12821,7 +12709,7 @@
         <v>224</v>
       </c>
       <c r="H293">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I293" s="51">
         <v>169</v>
@@ -12836,7 +12724,7 @@
         <v>225</v>
       </c>
       <c r="H294">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I294" s="51">
         <v>169</v>
@@ -12851,7 +12739,7 @@
         <v>226</v>
       </c>
       <c r="H295">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="I295" s="51">
         <v>169</v>
@@ -12866,7 +12754,7 @@
         <v>227</v>
       </c>
       <c r="H296">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="I296" s="51">
         <v>169</v>
@@ -12881,7 +12769,7 @@
         <v>228</v>
       </c>
       <c r="H297" s="51">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I297" s="51">
         <v>169</v>
@@ -12896,7 +12784,7 @@
         <v>229</v>
       </c>
       <c r="H298">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I298" s="51">
         <v>169</v>
@@ -12911,7 +12799,7 @@
         <v>230</v>
       </c>
       <c r="H299" s="51">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I299" s="51">
         <v>169</v>
@@ -12959,7 +12847,7 @@
         <v>224</v>
       </c>
       <c r="H302" s="51">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I302" s="51">
         <v>239</v>
@@ -12989,7 +12877,7 @@
         <v>226</v>
       </c>
       <c r="H304" s="51">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I304" s="51">
         <v>239</v>
@@ -13067,7 +12955,7 @@
         <v>222</v>
       </c>
       <c r="H309">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="I309" s="51">
         <v>260</v>
@@ -13082,7 +12970,7 @@
         <v>223</v>
       </c>
       <c r="H310">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="I310" s="51">
         <v>260</v>
@@ -13097,7 +12985,7 @@
         <v>224</v>
       </c>
       <c r="H311">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="I311" s="51">
         <v>260</v>
@@ -13112,7 +13000,7 @@
         <v>225</v>
       </c>
       <c r="H312">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="I312" s="51">
         <v>260</v>
@@ -13127,7 +13015,7 @@
         <v>226</v>
       </c>
       <c r="H313">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="I313" s="51">
         <v>260</v>
@@ -13142,7 +13030,7 @@
         <v>227</v>
       </c>
       <c r="H314">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="I314" s="51">
         <v>260</v>
@@ -13157,7 +13045,7 @@
         <v>228</v>
       </c>
       <c r="H315" s="51">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I315" s="51">
         <v>260</v>
@@ -13172,7 +13060,7 @@
         <v>229</v>
       </c>
       <c r="H316">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I316" s="51">
         <v>260</v>
@@ -13187,7 +13075,7 @@
         <v>230</v>
       </c>
       <c r="H317" s="51">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I317" s="51">
         <v>260</v>
@@ -13219,9 +13107,7 @@
       <c r="G319" t="s">
         <v>223</v>
       </c>
-      <c r="H319" s="51">
-        <v>2</v>
-      </c>
+      <c r="H319" s="51"/>
       <c r="I319" s="51">
         <v>101</v>
       </c>
@@ -13286,7 +13172,7 @@
         <v>228</v>
       </c>
       <c r="H324" s="51">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="I324" s="51">
         <v>101</v>
@@ -13341,9 +13227,6 @@
       <c r="G328" t="s">
         <v>223</v>
       </c>
-      <c r="H328">
-        <v>1</v>
-      </c>
       <c r="I328" s="51">
         <v>105</v>
       </c>
@@ -13407,7 +13290,7 @@
         <v>228</v>
       </c>
       <c r="H333" s="51">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="I333" s="51">
         <v>105</v>
@@ -13451,7 +13334,7 @@
         <v>222</v>
       </c>
       <c r="H336" s="51">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I336" s="51">
         <v>202</v>
@@ -13466,7 +13349,7 @@
         <v>223</v>
       </c>
       <c r="H337" s="51">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I337" s="51">
         <v>202</v>
@@ -13481,7 +13364,7 @@
         <v>224</v>
       </c>
       <c r="H338" s="51">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I338" s="51">
         <v>202</v>
@@ -13496,7 +13379,7 @@
         <v>225</v>
       </c>
       <c r="H339" s="51">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="I339" s="51">
         <v>202</v>
@@ -13511,7 +13394,7 @@
         <v>226</v>
       </c>
       <c r="H340">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="I340" s="51">
         <v>202</v>
@@ -13526,7 +13409,7 @@
         <v>227</v>
       </c>
       <c r="H341" s="51">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="I341" s="51">
         <v>202</v>
@@ -13541,7 +13424,7 @@
         <v>228</v>
       </c>
       <c r="H342" s="51">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I342" s="51">
         <v>202</v>
@@ -13556,7 +13439,7 @@
         <v>229</v>
       </c>
       <c r="H343" s="51">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I343" s="51">
         <v>202</v>
@@ -13571,7 +13454,7 @@
         <v>230</v>
       </c>
       <c r="H344" s="51">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="I344" s="51">
         <v>202</v>
@@ -13588,9 +13471,6 @@
       <c r="G345" t="s">
         <v>222</v>
       </c>
-      <c r="H345">
-        <v>6</v>
-      </c>
       <c r="I345" s="51">
         <v>198</v>
       </c>
@@ -13603,9 +13483,7 @@
       <c r="G346" t="s">
         <v>223</v>
       </c>
-      <c r="H346" s="51">
-        <v>8</v>
-      </c>
+      <c r="H346" s="51"/>
       <c r="I346" s="51">
         <v>198</v>
       </c>
@@ -13618,9 +13496,7 @@
       <c r="G347" t="s">
         <v>224</v>
       </c>
-      <c r="H347" s="51">
-        <v>17</v>
-      </c>
+      <c r="H347" s="51"/>
       <c r="I347" s="51">
         <v>198</v>
       </c>
@@ -13633,9 +13509,6 @@
       <c r="G348" t="s">
         <v>225</v>
       </c>
-      <c r="H348">
-        <v>6</v>
-      </c>
       <c r="I348" s="51">
         <v>198</v>
       </c>
@@ -13648,9 +13521,7 @@
       <c r="G349" t="s">
         <v>226</v>
       </c>
-      <c r="H349" s="51">
-        <v>14</v>
-      </c>
+      <c r="H349" s="51"/>
       <c r="I349" s="51">
         <v>198</v>
       </c>
@@ -13663,9 +13534,7 @@
       <c r="G350" t="s">
         <v>227</v>
       </c>
-      <c r="H350" s="51">
-        <v>6</v>
-      </c>
+      <c r="H350" s="51"/>
       <c r="I350" s="51">
         <v>198</v>
       </c>
@@ -13678,9 +13547,7 @@
       <c r="G351" t="s">
         <v>228</v>
       </c>
-      <c r="H351" s="51">
-        <v>18</v>
-      </c>
+      <c r="H351" s="51"/>
       <c r="I351" s="51">
         <v>198</v>
       </c>
@@ -13693,9 +13560,6 @@
       <c r="G352" t="s">
         <v>229</v>
       </c>
-      <c r="H352">
-        <v>4</v>
-      </c>
       <c r="I352" s="51">
         <v>198</v>
       </c>
@@ -13708,9 +13572,7 @@
       <c r="G353" t="s">
         <v>230</v>
       </c>
-      <c r="H353" s="51">
-        <v>2</v>
-      </c>
+      <c r="H353" s="51"/>
       <c r="I353" s="51">
         <v>198</v>
       </c>
@@ -13728,7 +13590,7 @@
       </c>
       <c r="H354" s="51"/>
       <c r="I354" s="51">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="355" spans="5:9" x14ac:dyDescent="0.25">
@@ -13741,7 +13603,7 @@
       </c>
       <c r="H355" s="51"/>
       <c r="I355" s="51">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="356" spans="5:9" x14ac:dyDescent="0.25">
@@ -13754,7 +13616,7 @@
       </c>
       <c r="H356" s="51"/>
       <c r="I356" s="51">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="357" spans="5:9" x14ac:dyDescent="0.25">
@@ -13767,7 +13629,7 @@
       </c>
       <c r="H357" s="51"/>
       <c r="I357" s="51">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="358" spans="5:9" x14ac:dyDescent="0.25">
@@ -13780,7 +13642,7 @@
       </c>
       <c r="H358" s="51"/>
       <c r="I358" s="51">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="359" spans="5:9" x14ac:dyDescent="0.25">
@@ -13793,7 +13655,7 @@
       </c>
       <c r="H359" s="51"/>
       <c r="I359" s="51">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="360" spans="5:9" x14ac:dyDescent="0.25">
@@ -13805,10 +13667,10 @@
         <v>228</v>
       </c>
       <c r="H360" s="51">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I360" s="51">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="361" spans="5:9" x14ac:dyDescent="0.25">
@@ -13821,7 +13683,7 @@
       </c>
       <c r="H361" s="51"/>
       <c r="I361" s="51">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="362" spans="5:9" x14ac:dyDescent="0.25">
@@ -13834,7 +13696,7 @@
       </c>
       <c r="H362" s="51"/>
       <c r="I362" s="51">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="363" spans="5:9" x14ac:dyDescent="0.25">
@@ -13968,11 +13830,8 @@
       <c r="G372" t="s">
         <v>222</v>
       </c>
-      <c r="H372">
-        <v>1</v>
-      </c>
       <c r="I372">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="373" spans="5:9" x14ac:dyDescent="0.25">
@@ -13984,7 +13843,7 @@
         <v>223</v>
       </c>
       <c r="I373">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="374" spans="5:9" x14ac:dyDescent="0.25">
@@ -13996,7 +13855,7 @@
         <v>224</v>
       </c>
       <c r="I374">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="375" spans="5:9" x14ac:dyDescent="0.25">
@@ -14008,7 +13867,7 @@
         <v>225</v>
       </c>
       <c r="I375">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="376" spans="5:9" x14ac:dyDescent="0.25">
@@ -14020,7 +13879,7 @@
         <v>226</v>
       </c>
       <c r="I376">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="377" spans="5:9" x14ac:dyDescent="0.25">
@@ -14032,7 +13891,7 @@
         <v>227</v>
       </c>
       <c r="I377">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="378" spans="5:9" x14ac:dyDescent="0.25">
@@ -14044,7 +13903,7 @@
         <v>228</v>
       </c>
       <c r="I378">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="379" spans="5:9" x14ac:dyDescent="0.25">
@@ -14056,7 +13915,7 @@
         <v>229</v>
       </c>
       <c r="I379">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="380" spans="5:9" x14ac:dyDescent="0.25">
@@ -14068,7 +13927,7 @@
         <v>230</v>
       </c>
       <c r="I380">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="381" spans="5:9" x14ac:dyDescent="0.25">
@@ -14110,7 +13969,7 @@
         <v>224</v>
       </c>
       <c r="H383">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I383">
         <v>113</v>
@@ -14151,9 +14010,6 @@
       <c r="G386" t="s">
         <v>227</v>
       </c>
-      <c r="H386">
-        <v>1</v>
-      </c>
       <c r="I386">
         <v>113</v>
       </c>
@@ -14209,10 +14065,10 @@
         <v>222</v>
       </c>
       <c r="H390">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="I390">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="391" spans="5:9" x14ac:dyDescent="0.25">
@@ -14223,11 +14079,8 @@
       <c r="G391" t="s">
         <v>223</v>
       </c>
-      <c r="H391">
-        <v>4</v>
-      </c>
       <c r="I391">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="392" spans="5:9" x14ac:dyDescent="0.25">
@@ -14239,10 +14092,10 @@
         <v>224</v>
       </c>
       <c r="H392">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="I392">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="393" spans="5:9" x14ac:dyDescent="0.25">
@@ -14254,10 +14107,10 @@
         <v>225</v>
       </c>
       <c r="H393">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I393">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="394" spans="5:9" x14ac:dyDescent="0.25">
@@ -14269,10 +14122,10 @@
         <v>226</v>
       </c>
       <c r="H394">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="I394">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="395" spans="5:9" x14ac:dyDescent="0.25">
@@ -14284,10 +14137,10 @@
         <v>227</v>
       </c>
       <c r="H395">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="I395">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="396" spans="5:9" x14ac:dyDescent="0.25">
@@ -14299,10 +14152,10 @@
         <v>228</v>
       </c>
       <c r="H396">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I396">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="397" spans="5:9" x14ac:dyDescent="0.25">
@@ -14314,10 +14167,10 @@
         <v>229</v>
       </c>
       <c r="H397">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I397">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="398" spans="5:9" x14ac:dyDescent="0.25">
@@ -14329,10 +14182,10 @@
         <v>230</v>
       </c>
       <c r="H398">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I398">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="399" spans="5:9" x14ac:dyDescent="0.25">
@@ -14347,7 +14200,7 @@
         <v>222</v>
       </c>
       <c r="H399">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="I399">
         <v>161</v>
@@ -14362,7 +14215,7 @@
         <v>223</v>
       </c>
       <c r="H400">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I400">
         <v>161</v>
@@ -14377,7 +14230,7 @@
         <v>224</v>
       </c>
       <c r="H401">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="I401">
         <v>161</v>
@@ -14392,7 +14245,7 @@
         <v>225</v>
       </c>
       <c r="H402">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I402">
         <v>161</v>
@@ -14407,7 +14260,7 @@
         <v>226</v>
       </c>
       <c r="H403">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="I403">
         <v>161</v>
@@ -14422,7 +14275,7 @@
         <v>227</v>
       </c>
       <c r="H404">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="I404">
         <v>161</v>
@@ -14452,7 +14305,7 @@
         <v>229</v>
       </c>
       <c r="H406">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I406">
         <v>161</v>
@@ -14467,7 +14320,7 @@
         <v>230</v>
       </c>
       <c r="H407">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I407">
         <v>161</v>

--- a/data/ventas.xlsx
+++ b/data/ventas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cesar\Desktop\Reportes Ventas Rap\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BE1BB90A-BFEB-48EE-87C3-D034647CF518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1ED77F2B-C804-4A4C-B2B1-B2CB88BD6181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="233">
   <si>
     <t>GOMEZ MARTÍN</t>
   </si>
@@ -761,6 +761,12 @@
   </si>
   <si>
     <t>145 - PILAS</t>
+  </si>
+  <si>
+    <t>42 - ROMERO ARIEL</t>
+  </si>
+  <si>
+    <t>123 - TORRES ROLANDO</t>
   </si>
 </sst>
 </file>
@@ -944,7 +950,6 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="41">
@@ -2482,7 +2487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34" bestFit="1" customWidth="1"/>
@@ -2529,22 +2534,22 @@
         <v>0</v>
       </c>
       <c r="C2" s="96">
-        <v>12759.648138517299</v>
+        <v>20239.264746040899</v>
       </c>
       <c r="D2" s="96">
-        <v>61262.625914064098</v>
+        <v>97497.216435570401</v>
       </c>
       <c r="E2" s="96">
-        <v>223094212.44056469</v>
+        <v>347488527.93282223</v>
       </c>
       <c r="F2" s="96">
         <v>0</v>
       </c>
       <c r="G2" s="96">
-        <v>141404.35170655229</v>
+        <v>208601.67291691661</v>
       </c>
       <c r="H2" s="96">
-        <v>141404.38</v>
+        <v>208601.74</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -2555,22 +2560,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="96">
-        <v>168.2765046287</v>
+        <v>287.35735488500001</v>
       </c>
       <c r="D3" s="96">
-        <v>491.7907233853</v>
+        <v>636.38716535089998</v>
       </c>
       <c r="E3" s="96">
-        <v>4713478.3902184051</v>
+        <v>6953389.0972305397</v>
       </c>
       <c r="F3" s="96">
         <v>0</v>
       </c>
       <c r="G3" s="96">
-        <v>141404.35170655229</v>
+        <v>208601.67291691661</v>
       </c>
       <c r="H3" s="96">
-        <v>141404.38</v>
+        <v>208601.74</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2581,13 +2586,13 @@
         <v>1</v>
       </c>
       <c r="C4" s="96">
-        <v>89.716765872799996</v>
+        <v>155.42341269729999</v>
       </c>
       <c r="D4" s="96">
-        <v>228.65250000060001</v>
+        <v>326.98499999799998</v>
       </c>
       <c r="E4" s="96">
-        <v>3490474.4748070529</v>
+        <v>4842984.6712837927</v>
       </c>
       <c r="F4" s="96">
         <v>0</v>
@@ -2607,13 +2612,13 @@
         <v>1</v>
       </c>
       <c r="C5" s="96">
-        <v>113.08222222160001</v>
+        <v>200.08797618950001</v>
       </c>
       <c r="D5" s="96">
-        <v>487.77000000160001</v>
+        <v>776.02249999560001</v>
       </c>
       <c r="E5" s="96">
-        <v>2539362.2668490014</v>
+        <v>4538116.0675083203</v>
       </c>
       <c r="F5" s="96">
         <v>0</v>
@@ -2633,13 +2638,13 @@
         <v>1</v>
       </c>
       <c r="C6" s="96">
-        <v>319.23392857089999</v>
+        <v>397.30575396749998</v>
       </c>
       <c r="D6" s="96">
-        <v>1011.7841785766</v>
+        <v>1116.1477142923</v>
       </c>
       <c r="E6" s="96">
-        <v>5960130.3637676956</v>
+        <v>7971555.33420307</v>
       </c>
       <c r="F6" s="96">
         <v>0</v>
@@ -2659,13 +2664,13 @@
         <v>1</v>
       </c>
       <c r="C7" s="96">
-        <v>219.94720238030001</v>
+        <v>418.16251984000002</v>
       </c>
       <c r="D7" s="96">
-        <v>984.96450000130005</v>
+        <v>1324.0909999978001</v>
       </c>
       <c r="E7" s="96">
-        <v>4232380.5042614806</v>
+        <v>8068882.1386908181</v>
       </c>
       <c r="F7" s="96">
         <v>0</v>
@@ -2685,13 +2690,13 @@
         <v>1</v>
       </c>
       <c r="C8" s="96">
-        <v>1614.9333333334</v>
+        <v>1635.1115740742</v>
       </c>
       <c r="D8" s="96">
-        <v>1507.4840000014001</v>
+        <v>1870.3864768542001</v>
       </c>
       <c r="E8" s="96">
-        <v>16463801.298558187</v>
+        <v>17061083.040882383</v>
       </c>
       <c r="F8" s="96">
         <v>0</v>
@@ -2711,13 +2716,13 @@
         <v>1</v>
       </c>
       <c r="C9" s="96">
-        <v>113.1691071427</v>
+        <v>198.23150793619999</v>
       </c>
       <c r="D9" s="96">
-        <v>643.5574999982</v>
+        <v>911.56750000140005</v>
       </c>
       <c r="E9" s="96">
-        <v>2229458.8498637299</v>
+        <v>3586477.5079781078</v>
       </c>
       <c r="F9" s="96">
         <v>0</v>
@@ -2737,13 +2742,13 @@
         <v>1</v>
       </c>
       <c r="C10" s="96">
-        <v>67.089751984100005</v>
+        <v>151.87760912690001</v>
       </c>
       <c r="D10" s="96">
-        <v>200.80203124760001</v>
+        <v>538.00411458880001</v>
       </c>
       <c r="E10" s="96">
-        <v>2237337.654012111</v>
+        <v>3996158.8131728824</v>
       </c>
       <c r="F10" s="96">
         <v>0</v>
@@ -2763,13 +2768,13 @@
         <v>1</v>
       </c>
       <c r="C11" s="96">
-        <v>69.604761904499995</v>
+        <v>157.76408730060001</v>
       </c>
       <c r="D11" s="96">
-        <v>303.04959523730003</v>
+        <v>362.56459523730001</v>
       </c>
       <c r="E11" s="96">
-        <v>1556471.8667402903</v>
+        <v>2958594.3353685732</v>
       </c>
       <c r="F11" s="96">
         <v>0</v>
@@ -2789,13 +2794,13 @@
         <v>1</v>
       </c>
       <c r="C12" s="96">
-        <v>178.19682539589999</v>
+        <v>376.22777777610003</v>
       </c>
       <c r="D12" s="96">
-        <v>527.69845237909999</v>
+        <v>2353.8501190427</v>
       </c>
       <c r="E12" s="96">
-        <v>3454829.7358999122</v>
+        <v>6404448.8053096188</v>
       </c>
       <c r="F12" s="96">
         <v>0</v>
@@ -2815,13 +2820,13 @@
         <v>1</v>
       </c>
       <c r="C13" s="96">
-        <v>225.7950396821</v>
+        <v>340.59277777739999</v>
       </c>
       <c r="D13" s="96">
-        <v>829.79151190790003</v>
+        <v>1049.3365119081</v>
       </c>
       <c r="E13" s="96">
-        <v>4650179.1579327742</v>
+        <v>6622431.8650625329</v>
       </c>
       <c r="F13" s="96">
         <v>0</v>
@@ -2841,13 +2846,13 @@
         <v>1</v>
       </c>
       <c r="C14" s="96">
-        <v>1444.0819444447</v>
+        <v>1689.6688492064</v>
       </c>
       <c r="D14" s="96">
-        <v>13580.7225000012</v>
+        <v>14984.7324999998</v>
       </c>
       <c r="E14" s="96">
-        <v>35677866.984969728</v>
+        <v>39689592.681744099</v>
       </c>
       <c r="F14" s="96">
         <v>0</v>
@@ -2867,13 +2872,13 @@
         <v>1</v>
       </c>
       <c r="C15" s="96">
-        <v>203.11855158700001</v>
+        <v>322.91230158680003</v>
       </c>
       <c r="D15" s="96">
-        <v>755.52499999940005</v>
+        <v>1065.8074999979999</v>
       </c>
       <c r="E15" s="96">
-        <v>3799689.1529486589</v>
+        <v>6197917.8190731332</v>
       </c>
       <c r="F15" s="96">
         <v>0</v>
@@ -2893,13 +2898,13 @@
         <v>1</v>
       </c>
       <c r="C16" s="96">
-        <v>128.3049206343</v>
+        <v>214.65501984030001</v>
       </c>
       <c r="D16" s="96">
-        <v>693.45458333670001</v>
+        <v>1133.6685119097999</v>
       </c>
       <c r="E16" s="96">
-        <v>3126324.9965506792</v>
+        <v>5255755.4759214995</v>
       </c>
       <c r="F16" s="96">
         <v>0</v>
@@ -2919,13 +2924,13 @@
         <v>1</v>
       </c>
       <c r="C17" s="96">
-        <v>214.7180555544</v>
+        <v>480.26246031580001</v>
       </c>
       <c r="D17" s="96">
-        <v>616.00885714909998</v>
+        <v>1416.7735238169</v>
       </c>
       <c r="E17" s="96">
-        <v>5092283.3348378455</v>
+        <v>9288875.7683896385</v>
       </c>
       <c r="F17" s="96">
         <v>0</v>
@@ -2945,13 +2950,13 @@
         <v>1</v>
       </c>
       <c r="C18" s="96">
-        <v>339.81365079310001</v>
+        <v>588.94634920609997</v>
       </c>
       <c r="D18" s="96">
-        <v>2209.1249285679</v>
+        <v>2848.4188452368999</v>
       </c>
       <c r="E18" s="96">
-        <v>6538018.3834050605</v>
+        <v>12202147.531287048</v>
       </c>
       <c r="F18" s="96">
         <v>0</v>
@@ -2971,13 +2976,13 @@
         <v>1</v>
       </c>
       <c r="C19" s="96">
-        <v>242.1867394173</v>
+        <v>441.94708994609999</v>
       </c>
       <c r="D19" s="96">
-        <v>821.9142142938</v>
+        <v>1784.6717142952</v>
       </c>
       <c r="E19" s="96">
-        <v>5313079.7996425815</v>
+        <v>9037854.5756811257</v>
       </c>
       <c r="F19" s="96">
         <v>0</v>
@@ -2997,13 +3002,13 @@
         <v>1</v>
       </c>
       <c r="C20" s="96">
-        <v>1331.513234127</v>
+        <v>1691.1757341268999</v>
       </c>
       <c r="D20" s="96">
-        <v>7081.0849999985003</v>
+        <v>8709.6164999951998</v>
       </c>
       <c r="E20" s="96">
-        <v>18543635.055367131</v>
+        <v>25307057.946538661</v>
       </c>
       <c r="F20" s="96">
         <v>0</v>
@@ -3023,13 +3028,13 @@
         <v>1</v>
       </c>
       <c r="C21" s="96">
-        <v>174.00490079319999</v>
+        <v>264.46081349069999</v>
       </c>
       <c r="D21" s="96">
-        <v>605.7746071478</v>
+        <v>939.2292142901</v>
       </c>
       <c r="E21" s="96">
-        <v>3621062.6775038806</v>
+        <v>5595341.8938343767</v>
       </c>
       <c r="F21" s="96">
         <v>0</v>
@@ -3049,13 +3054,13 @@
         <v>1</v>
       </c>
       <c r="C22" s="96">
-        <v>123.90625</v>
+        <v>197.9982142849</v>
       </c>
       <c r="D22" s="96">
-        <v>291.22892856869998</v>
+        <v>505.67851190179999</v>
       </c>
       <c r="E22" s="96">
-        <v>1931060.2247250369</v>
+        <v>3109025.2196221473</v>
       </c>
       <c r="F22" s="96">
         <v>0</v>
@@ -3075,13 +3080,13 @@
         <v>1</v>
       </c>
       <c r="C23" s="96">
-        <v>128.10228174549999</v>
+        <v>781.37513888820001</v>
       </c>
       <c r="D23" s="96">
-        <v>339.25166666370001</v>
+        <v>4836.2267976160001</v>
       </c>
       <c r="E23" s="96">
-        <v>1999132.6820728134</v>
+        <v>16984006.336814482</v>
       </c>
       <c r="F23" s="96">
         <v>0</v>
@@ -3101,13 +3106,13 @@
         <v>1</v>
       </c>
       <c r="C24" s="96">
-        <v>748.66458333349999</v>
+        <v>731.66458333349999</v>
       </c>
       <c r="D24" s="96">
-        <v>4813.7219583328997</v>
+        <v>4795.7219583328997</v>
       </c>
       <c r="E24" s="96">
-        <v>13993499.751331689</v>
+        <v>13810777.689331688</v>
       </c>
       <c r="F24" s="96">
         <v>0</v>
@@ -3127,13 +3132,13 @@
         <v>1</v>
       </c>
       <c r="C25" s="96">
-        <v>151.11507936480001</v>
+        <v>298.05575396820001</v>
       </c>
       <c r="D25" s="96">
-        <v>563.25500000219995</v>
+        <v>850.76000000500005</v>
       </c>
       <c r="E25" s="96">
-        <v>3265458.2459612871</v>
+        <v>4865926.9418352479</v>
       </c>
       <c r="F25" s="96">
         <v>0</v>
@@ -3153,13 +3158,13 @@
         <v>1</v>
       </c>
       <c r="C26" s="96">
-        <v>78.740436507300004</v>
+        <v>200.69081349109999</v>
       </c>
       <c r="D26" s="96">
-        <v>282.00000000040001</v>
+        <v>459.23708333330001</v>
       </c>
       <c r="E26" s="96">
-        <v>1905347.2963424551</v>
+        <v>3089173.5689832573</v>
       </c>
       <c r="F26" s="96">
         <v>0</v>
@@ -3179,13 +3184,13 @@
         <v>1</v>
       </c>
       <c r="C27" s="96">
-        <v>1334.5</v>
+        <v>1888.5</v>
       </c>
       <c r="D27" s="96">
-        <v>2577.1799999999998</v>
+        <v>9736.84</v>
       </c>
       <c r="E27" s="96">
-        <v>13136953.343350001</v>
+        <v>23468686.842</v>
       </c>
       <c r="F27" s="96">
         <v>0</v>
@@ -3205,13 +3210,13 @@
         <v>1</v>
       </c>
       <c r="C28" s="96">
-        <v>224.8947354492</v>
+        <v>424.6578339939</v>
       </c>
       <c r="D28" s="96">
-        <v>1004.4995833371</v>
+        <v>1810.8346354224</v>
       </c>
       <c r="E28" s="96">
-        <v>4525419.7648018571</v>
+        <v>8516814.03087065</v>
       </c>
       <c r="F28" s="96">
         <v>0</v>
@@ -3231,13 +3236,13 @@
         <v>1</v>
       </c>
       <c r="C29" s="96">
-        <v>386.73</v>
+        <v>1351.4300000001001</v>
       </c>
       <c r="D29" s="96">
-        <v>1523.5400000018999</v>
+        <v>2346.2820833356</v>
       </c>
       <c r="E29" s="96">
-        <v>7197381.3632933144</v>
+        <v>17555809.912466466</v>
       </c>
       <c r="F29" s="96">
         <v>0</v>
@@ -3257,13 +3262,13 @@
         <v>1</v>
       </c>
       <c r="C30" s="96">
-        <v>73.557242063700002</v>
+        <v>111.48898809560001</v>
       </c>
       <c r="D30" s="96">
-        <v>290.52000000279997</v>
+        <v>371.92416667719999</v>
       </c>
       <c r="E30" s="96">
-        <v>1342266.2312651528</v>
+        <v>2098536.1960838647</v>
       </c>
       <c r="F30" s="96">
         <v>0</v>
@@ -3283,13 +3288,13 @@
         <v>1</v>
       </c>
       <c r="C31" s="96">
-        <v>90.458531745100004</v>
+        <v>172.14345238000001</v>
       </c>
       <c r="D31" s="96">
-        <v>283.59499999920001</v>
+        <v>351.31749999890002</v>
       </c>
       <c r="E31" s="96">
-        <v>1662817.6962441357</v>
+        <v>2883607.9842428509</v>
       </c>
       <c r="F31" s="96">
         <v>0</v>
@@ -3309,13 +3314,13 @@
         <v>1</v>
       </c>
       <c r="C32" s="96">
-        <v>28.535912698600001</v>
+        <v>55.931944444599999</v>
       </c>
       <c r="D32" s="96">
-        <v>178.64666666860001</v>
+        <v>392.40416666760001</v>
       </c>
       <c r="E32" s="96">
-        <v>920475.59202497394</v>
+        <v>1626463.4655310514</v>
       </c>
       <c r="F32" s="96">
         <v>0</v>
@@ -3335,13 +3340,13 @@
         <v>1</v>
       </c>
       <c r="C33" s="96">
-        <v>215.69446428559999</v>
+        <v>308.6682738092</v>
       </c>
       <c r="D33" s="96">
-        <v>439.00999999959998</v>
+        <v>704.99600000179998</v>
       </c>
       <c r="E33" s="96">
-        <v>2806120.8392654946</v>
+        <v>4975553.6144345868</v>
       </c>
       <c r="F33" s="96">
         <v>0</v>
@@ -3355,19 +3360,19 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="96" t="s">
-        <v>206</v>
+        <v>231</v>
       </c>
       <c r="B34" s="96">
         <v>1</v>
       </c>
       <c r="C34" s="96">
-        <v>-25</v>
+        <v>25.288194444399998</v>
       </c>
       <c r="D34" s="96">
-        <v>0</v>
+        <v>354.02</v>
       </c>
       <c r="E34" s="96">
-        <v>-233849</v>
+        <v>715253.15687714703</v>
       </c>
       <c r="F34" s="96">
         <v>0</v>
@@ -3381,19 +3386,19 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="96" t="s">
-        <v>162</v>
+        <v>206</v>
       </c>
       <c r="B35" s="96">
         <v>1</v>
       </c>
       <c r="C35" s="96">
-        <v>186.83611111089999</v>
+        <v>-25</v>
       </c>
       <c r="D35" s="96">
-        <v>804.41601190910001</v>
+        <v>0</v>
       </c>
       <c r="E35" s="96">
-        <v>3880349.2779353959</v>
+        <v>-233849</v>
       </c>
       <c r="F35" s="96">
         <v>0</v>
@@ -3407,19 +3412,19 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="96" t="s">
-        <v>107</v>
+        <v>162</v>
       </c>
       <c r="B36" s="96">
         <v>1</v>
       </c>
       <c r="C36" s="96">
-        <v>414.39123015899997</v>
+        <v>285.49811507840002</v>
       </c>
       <c r="D36" s="96">
-        <v>2342.8888214259</v>
+        <v>1243.7466071438</v>
       </c>
       <c r="E36" s="96">
-        <v>7342359.2744361712</v>
+        <v>5822405.6030015703</v>
       </c>
       <c r="F36" s="96">
         <v>0</v>
@@ -3433,19 +3438,19 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="96" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B37" s="96">
         <v>1</v>
       </c>
       <c r="C37" s="96">
-        <v>197.30909090899999</v>
+        <v>414.39123015899997</v>
       </c>
       <c r="D37" s="96">
-        <v>2277.9899999992999</v>
+        <v>2342.8888214259</v>
       </c>
       <c r="E37" s="96">
-        <v>4699575.8856638623</v>
+        <v>7342359.2744361712</v>
       </c>
       <c r="F37" s="96">
         <v>0</v>
@@ -3459,19 +3464,19 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="96" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B38" s="96">
         <v>1</v>
       </c>
       <c r="C38" s="96">
-        <v>283.9166666667</v>
+        <v>308.39242424230002</v>
       </c>
       <c r="D38" s="96">
-        <v>3082.25</v>
+        <v>3260.7299999989</v>
       </c>
       <c r="E38" s="96">
-        <v>5825319.4707523696</v>
+        <v>6663134.8062294191</v>
       </c>
       <c r="F38" s="96">
         <v>0</v>
@@ -3485,19 +3490,19 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="96" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B39" s="96">
         <v>1</v>
       </c>
       <c r="C39" s="96">
-        <v>131.14181216910001</v>
+        <v>471.4166666667</v>
       </c>
       <c r="D39" s="96">
-        <v>471.4394986822</v>
+        <v>5734.2</v>
       </c>
       <c r="E39" s="96">
-        <v>3150944.560423614</v>
+        <v>10196205.867152149</v>
       </c>
       <c r="F39" s="96">
         <v>0</v>
@@ -3511,19 +3516,19 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="96" t="s">
-        <v>140</v>
+        <v>109</v>
       </c>
       <c r="B40" s="96">
         <v>1</v>
       </c>
       <c r="C40" s="96">
-        <v>548.43968253950004</v>
+        <v>757.61760582019997</v>
       </c>
       <c r="D40" s="96">
-        <v>4046.0241666669999</v>
+        <v>4224.4444986853996</v>
       </c>
       <c r="E40" s="96">
-        <v>7402539.5016198214</v>
+        <v>6909391.5039921645</v>
       </c>
       <c r="F40" s="96">
         <v>0</v>
@@ -3537,19 +3542,19 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="96" t="s">
-        <v>217</v>
+        <v>140</v>
       </c>
       <c r="B41" s="96">
         <v>1</v>
       </c>
       <c r="C41" s="96">
-        <v>6</v>
+        <v>679.35634920610005</v>
       </c>
       <c r="D41" s="96">
-        <v>81</v>
+        <v>4883.0241666669999</v>
       </c>
       <c r="E41" s="96">
-        <v>149294.68419999999</v>
+        <v>8825883.2392010316</v>
       </c>
       <c r="F41" s="96">
         <v>0</v>
@@ -3563,19 +3568,19 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="96" t="s">
-        <v>145</v>
+        <v>217</v>
       </c>
       <c r="B42" s="96">
         <v>1</v>
       </c>
       <c r="C42" s="96">
-        <v>-6.2142857142999999</v>
+        <v>32</v>
       </c>
       <c r="D42" s="96">
-        <v>-6.2810714286999998</v>
+        <v>424.04</v>
       </c>
       <c r="E42" s="96">
-        <v>-275260.76904147147</v>
+        <v>746511.00490000006</v>
       </c>
       <c r="F42" s="96">
         <v>0</v>
@@ -3589,19 +3594,19 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="96" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B43" s="96">
         <v>1</v>
       </c>
       <c r="C43" s="96">
-        <v>-3.2847222223000001</v>
+        <v>74.818551587300007</v>
       </c>
       <c r="D43" s="96">
-        <v>-20.505000001599999</v>
+        <v>229.00349106979999</v>
       </c>
       <c r="E43" s="96">
-        <v>-402349.89063324447</v>
+        <v>3760393.1741207056</v>
       </c>
       <c r="F43" s="96">
         <v>0</v>
@@ -3615,19 +3620,19 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="96" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="B44" s="96">
         <v>1</v>
       </c>
       <c r="C44" s="96">
-        <v>184.42559523840001</v>
+        <v>123.917063492</v>
       </c>
       <c r="D44" s="96">
-        <v>2016.0000000025</v>
+        <v>1239.6349404736</v>
       </c>
       <c r="E44" s="96">
-        <v>3629491.4663937623</v>
+        <v>1913900.6624423866</v>
       </c>
       <c r="F44" s="96">
         <v>0</v>
@@ -3636,6 +3641,58 @@
         <v>0</v>
       </c>
       <c r="H44" s="96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="96" t="s">
+        <v>156</v>
+      </c>
+      <c r="B45" s="96">
+        <v>1</v>
+      </c>
+      <c r="C45" s="96">
+        <v>234.9175793654</v>
+      </c>
+      <c r="D45" s="96">
+        <v>2276.0000000041</v>
+      </c>
+      <c r="E45" s="96">
+        <v>4664188.216696891</v>
+      </c>
+      <c r="F45" s="96">
+        <v>0</v>
+      </c>
+      <c r="G45" s="96">
+        <v>0</v>
+      </c>
+      <c r="H45" s="96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="96" t="s">
+        <v>232</v>
+      </c>
+      <c r="B46" s="96">
+        <v>1</v>
+      </c>
+      <c r="C46" s="96">
+        <v>321.875</v>
+      </c>
+      <c r="D46" s="96">
+        <v>-24.9999999996</v>
+      </c>
+      <c r="E46" s="96">
+        <v>1599703.2523960921</v>
+      </c>
+      <c r="F46" s="96">
+        <v>0</v>
+      </c>
+      <c r="G46" s="96">
+        <v>0</v>
+      </c>
+      <c r="H46" s="96">
         <v>0</v>
       </c>
     </row>
@@ -3716,44 +3773,44 @@
       </c>
       <c r="D2" s="59">
         <f>IFERROR(+VLOOKUP(B2,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>6538018.3834050605</v>
+        <v>12202147.531287048</v>
       </c>
       <c r="E2" s="59">
-        <v>4682028.2206923608</v>
+        <v>10180781.322442733</v>
       </c>
       <c r="F2" s="59">
         <f t="shared" ref="F2:F9" si="0">+D2-E2</f>
-        <v>1855990.1627126997</v>
+        <v>2021366.2088443153</v>
       </c>
       <c r="G2" s="60">
         <f t="shared" ref="G2:G41" si="1">+D2/C2</f>
-        <v>0.20254663591143432</v>
+        <v>0.3780203401737795</v>
       </c>
       <c r="H2" s="59">
         <f>+D2/$N$3*$N$4</f>
-        <v>52304147.067240477</v>
+        <v>58570308.150177836</v>
       </c>
       <c r="I2" s="60">
         <f t="shared" ref="I2:I41" si="2">+H2/C2</f>
-        <v>1.6203730872914743</v>
+        <v>1.8144976328341418</v>
       </c>
       <c r="J2" s="59">
         <f>+D2/$N$3</f>
-        <v>2179339.46113502</v>
+        <v>2440429.5062574097</v>
       </c>
       <c r="K2" s="59">
         <f t="shared" ref="K2:K41" si="3">+(C2-D2)/$N$2</f>
-        <v>1225764.6788021759</v>
+        <v>1056680.4793138793</v>
       </c>
       <c r="L2" s="61" cm="1">
         <f t="array" ref="L2">+_xlfn.IFS(I2&gt;114%,H2*0.02,I2&gt;109%,H2*0.015,I2&gt;104%,H2*0.0125,I2&gt;99%,H2*0.01,I2&lt;99%,H2*0)</f>
-        <v>1046082.9413448096</v>
+        <v>1171406.1630035567</v>
       </c>
       <c r="M2" s="53" t="s">
         <v>36</v>
       </c>
       <c r="N2">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -3766,45 +3823,45 @@
       </c>
       <c r="D3" s="4">
         <f>IFERROR(+VLOOKUP(B3,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>5092283.3348378455</v>
+        <v>9288875.7683896385</v>
       </c>
       <c r="E3" s="4">
-        <v>2774896.9225576972</v>
+        <v>6362623.1530077159</v>
       </c>
       <c r="F3" s="4">
         <f t="shared" si="0"/>
-        <v>2317386.4122801484</v>
+        <v>2926252.6153819226</v>
       </c>
       <c r="G3" s="5">
         <f t="shared" si="1"/>
-        <v>0.16435877774987445</v>
+        <v>0.29980819360899963</v>
       </c>
       <c r="H3" s="4">
         <f t="shared" ref="H3:H41" si="4">+D3/$N$3*$N$4</f>
-        <v>40738266.678702764</v>
+        <v>44586603.688270271</v>
       </c>
       <c r="I3" s="5">
         <f t="shared" si="2"/>
-        <v>1.3148702219989956</v>
+        <v>1.4390793293231983</v>
       </c>
       <c r="J3" s="4">
         <f t="shared" ref="J3:J41" si="5">+D3/$N$3</f>
-        <v>1697427.7782792819</v>
+        <v>1857775.1536779278</v>
       </c>
       <c r="K3" s="4">
         <f t="shared" si="3"/>
-        <v>1232878.3259069242</v>
+        <v>1141781.7058154535</v>
       </c>
       <c r="L3" s="63" cm="1">
         <f t="array" ref="L3">+_xlfn.IFS(I3&gt;114%,H3*0.02,I3&gt;109%,H3*0.015,I3&gt;104%,H3*0.0125,I3&gt;99%,H3*0.01,I3&lt;99%,H3*0)</f>
-        <v>814765.33357405534</v>
+        <v>891732.07376540545</v>
       </c>
       <c r="M3" s="53" t="s">
         <v>40</v>
       </c>
       <c r="N3">
         <f>N4-N2</f>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -3817,38 +3874,38 @@
       </c>
       <c r="D4" s="4">
         <f>IFERROR(+VLOOKUP(B4,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>3799689.1529486589</v>
+        <v>6197917.8190731332</v>
       </c>
       <c r="E4" s="4">
-        <v>2224929.6365325735</v>
+        <v>4655359.4802594241</v>
       </c>
       <c r="F4" s="4">
         <f t="shared" si="0"/>
-        <v>1574759.5164160854</v>
+        <v>1542558.3388137091</v>
       </c>
       <c r="G4" s="5">
         <f t="shared" si="1"/>
-        <v>0.13383885062086462</v>
+        <v>0.21831317346146409</v>
       </c>
       <c r="H4" s="4">
         <f t="shared" si="4"/>
-        <v>30397513.223589271</v>
+        <v>29750005.531551037</v>
       </c>
       <c r="I4" s="5">
         <f t="shared" si="2"/>
-        <v>1.070710804966917</v>
+        <v>1.0479032326150275</v>
       </c>
       <c r="J4" s="4">
         <f t="shared" si="5"/>
-        <v>1266563.0509828862</v>
+        <v>1239583.5638146265</v>
       </c>
       <c r="K4" s="4">
         <f t="shared" si="3"/>
-        <v>1170968.6717714092</v>
+        <v>1168005.970582901</v>
       </c>
       <c r="L4" s="63" cm="1">
         <f t="array" ref="L4">+_xlfn.IFS(I4&gt;114%,H4*0.02,I4&gt;109%,H4*0.015,I4&gt;104%,H4*0.0125,I4&gt;99%,H4*0.01,I4&lt;99%,H4*0)</f>
-        <v>379968.9152948659</v>
+        <v>371875.06914438796</v>
       </c>
       <c r="M4" s="53" t="s">
         <v>47</v>
@@ -3867,38 +3924,38 @@
       </c>
       <c r="D5" s="4">
         <f>IFERROR(+VLOOKUP(B5,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>4650179.1579327742</v>
+        <v>6622431.8650625329</v>
       </c>
       <c r="E5" s="4">
-        <v>3752668.2666791501</v>
+        <v>5672001.5032034451</v>
       </c>
       <c r="F5" s="4">
         <f t="shared" si="0"/>
-        <v>897510.89125362411</v>
+        <v>950430.36185908783</v>
       </c>
       <c r="G5" s="5">
         <f t="shared" si="1"/>
-        <v>0.16379619716940358</v>
+        <v>0.23326609979322546</v>
       </c>
       <c r="H5" s="4">
         <f t="shared" si="4"/>
-        <v>37201433.263462193</v>
+        <v>31787672.952300161</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" si="2"/>
-        <v>1.3103695773552286</v>
+        <v>1.1196772790074823</v>
       </c>
       <c r="J5" s="4">
         <f t="shared" si="5"/>
-        <v>1550059.7193109246</v>
+        <v>1324486.3730125066</v>
       </c>
       <c r="K5" s="4">
         <f t="shared" si="3"/>
-        <v>1130469.1477245467</v>
+        <v>1145663.1260571433</v>
       </c>
       <c r="L5" s="63" cm="1">
         <f t="array" ref="L5">+_xlfn.IFS(I5&gt;114%,H5*0.02,I5&gt;109%,H5*0.015,I5&gt;104%,H5*0.0125,I5&gt;99%,H5*0.01,I5&lt;99%,H5*0)</f>
-        <v>744028.66526924388</v>
+        <v>476815.09428450238</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
@@ -3911,38 +3968,38 @@
       </c>
       <c r="D6" s="4">
         <f>IFERROR(+VLOOKUP(B6,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>3454829.7358999122</v>
+        <v>6404448.8053096188</v>
       </c>
       <c r="E6" s="4">
-        <v>1763034.9919922091</v>
+        <v>5810906.7980635744</v>
       </c>
       <c r="F6" s="4">
         <f t="shared" si="0"/>
-        <v>1691794.7439077031</v>
+        <v>593542.00724604446</v>
       </c>
       <c r="G6" s="5">
         <f t="shared" si="1"/>
-        <v>0.14683455239533538</v>
+        <v>0.27219702432644627</v>
       </c>
       <c r="H6" s="4">
         <f t="shared" si="4"/>
-        <v>27638637.887199298</v>
+        <v>30741354.265486173</v>
       </c>
       <c r="I6" s="5">
         <f t="shared" si="2"/>
-        <v>1.1746764191626831</v>
+        <v>1.3065457167669423</v>
       </c>
       <c r="J6" s="4">
         <f t="shared" si="5"/>
-        <v>1151609.9119666375</v>
+        <v>1280889.7610619238</v>
       </c>
       <c r="K6" s="4">
         <f t="shared" si="3"/>
-        <v>955899.75245810545</v>
+        <v>901277.67011634237</v>
       </c>
       <c r="L6" s="63" cm="1">
         <f t="array" ref="L6">+_xlfn.IFS(I6&gt;114%,H6*0.02,I6&gt;109%,H6*0.015,I6&gt;104%,H6*0.0125,I6&gt;99%,H6*0.01,I6&lt;99%,H6*0)</f>
-        <v>552772.75774398597</v>
+        <v>614827.08530972351</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
@@ -3955,34 +4012,34 @@
       </c>
       <c r="D7" s="4">
         <f>IFERROR(+VLOOKUP(B7,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>2229458.8498637299</v>
+        <v>3586477.5079781078</v>
       </c>
       <c r="E7" s="4">
-        <v>1244100.7657470268</v>
+        <v>2938195.7767915935</v>
       </c>
       <c r="F7" s="4">
         <f t="shared" ref="F7:F8" si="6">+D7-E7</f>
-        <v>985358.08411670313</v>
+        <v>648281.73118651425</v>
       </c>
       <c r="G7" s="5">
         <f t="shared" si="1"/>
-        <v>8.0364441623913901E-2</v>
+        <v>0.12928036879577476</v>
       </c>
       <c r="H7" s="4">
         <f t="shared" si="4"/>
-        <v>17835670.798909839</v>
+        <v>17215092.038294919</v>
       </c>
       <c r="I7" s="5">
         <f t="shared" si="2"/>
-        <v>0.64291553299131121</v>
+        <v>0.62054577021971891</v>
       </c>
       <c r="J7" s="4">
         <f t="shared" si="5"/>
-        <v>743152.94995457667</v>
+        <v>717295.50159562158</v>
       </c>
       <c r="K7" s="4">
         <f t="shared" si="3"/>
-        <v>1214876.103838132</v>
+        <v>1271335.7643413893</v>
       </c>
       <c r="L7" s="63" cm="1">
         <f t="array" ref="L7">+_xlfn.IFS(I7&gt;114%,H7*0.02,I7&gt;109%,H7*0.015,I7&gt;104%,H7*0.0125,I7&gt;99%,H7*0.01,I7&lt;99%,H7*0)</f>
@@ -3999,38 +4056,38 @@
       </c>
       <c r="D8" s="4">
         <f>IFERROR(+VLOOKUP(B8,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>4232380.5042614806</v>
+        <v>8068882.1386908181</v>
       </c>
       <c r="E8" s="4">
-        <v>2332273.4502824824</v>
+        <v>6168952.3513542237</v>
       </c>
       <c r="F8" s="4">
         <f t="shared" si="6"/>
-        <v>1900107.0539789982</v>
+        <v>1899929.7873365944</v>
       </c>
       <c r="G8" s="5">
         <f t="shared" si="1"/>
-        <v>0.11812040044839839</v>
+        <v>0.22519232106693524</v>
       </c>
       <c r="H8" s="4">
         <f t="shared" si="4"/>
-        <v>33859044.034091845</v>
+        <v>38730634.265715927</v>
       </c>
       <c r="I8" s="5">
         <f t="shared" si="2"/>
-        <v>0.94496320358718711</v>
+        <v>1.0809231411212892</v>
       </c>
       <c r="J8" s="4">
         <f t="shared" si="5"/>
-        <v>1410793.5014204935</v>
+        <v>1613776.4277381636</v>
       </c>
       <c r="K8" s="4">
         <f t="shared" si="3"/>
-        <v>1504699.5672693441</v>
+        <v>1461167.8567487835</v>
       </c>
       <c r="L8" s="63" cm="1">
         <f t="array" ref="L8">+_xlfn.IFS(I8&gt;114%,H8*0.02,I8&gt;109%,H8*0.015,I8&gt;104%,H8*0.0125,I8&gt;99%,H8*0.01,I8&lt;99%,H8*0)</f>
-        <v>0</v>
+        <v>484132.92832144909</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
@@ -4043,38 +4100,38 @@
       </c>
       <c r="D9" s="4">
         <f>IFERROR(+VLOOKUP(B9,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>5960130.3637676956</v>
+        <v>7971555.33420307</v>
       </c>
       <c r="E9" s="4">
-        <v>4892925.4103550436</v>
+        <v>6899879.8473196756</v>
       </c>
       <c r="F9" s="4">
         <f t="shared" si="0"/>
-        <v>1067204.953412652</v>
+        <v>1071675.4868833944</v>
       </c>
       <c r="G9" s="5">
         <f t="shared" si="1"/>
-        <v>0.16633971935747391</v>
+        <v>0.22247605273782814</v>
       </c>
       <c r="H9" s="4">
         <f t="shared" si="4"/>
-        <v>47681042.910141565</v>
+        <v>38263465.604174733</v>
       </c>
       <c r="I9" s="5">
         <f t="shared" si="2"/>
-        <v>1.3307177548597913</v>
+        <v>1.0678850531415751</v>
       </c>
       <c r="J9" s="4">
         <f t="shared" si="5"/>
-        <v>1986710.1212558986</v>
+        <v>1594311.066840614</v>
       </c>
       <c r="K9" s="4">
         <f t="shared" si="3"/>
-        <v>1422425.7644357148</v>
+        <v>1466290.3201428754</v>
       </c>
       <c r="L9" s="63" cm="1">
         <f t="array" ref="L9">+_xlfn.IFS(I9&gt;114%,H9*0.02,I9&gt;109%,H9*0.015,I9&gt;104%,H9*0.0125,I9&gt;99%,H9*0.01,I9&lt;99%,H9*0)</f>
-        <v>953620.85820283135</v>
+        <v>478293.32005218416</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4085,34 +4142,34 @@
       </c>
       <c r="D10" s="64">
         <f>+SUM(D2:D9)</f>
-        <v>35956969.48291716</v>
+        <v>60342736.769993968</v>
       </c>
       <c r="E10" s="65">
-        <v>23666857.664838541</v>
+        <v>48688700.232442394</v>
       </c>
       <c r="F10" s="64">
         <f>+SUM(F2:F9)</f>
-        <v>12290111.818078615</v>
+        <v>11654036.537551582</v>
       </c>
       <c r="G10" s="66">
         <f t="shared" si="1"/>
-        <v>0.14798654141378115</v>
+        <v>0.2483499872890047</v>
       </c>
       <c r="H10" s="64">
         <f t="shared" si="4"/>
-        <v>287655755.86333728</v>
+        <v>289645136.49597102</v>
       </c>
       <c r="I10" s="66">
         <f t="shared" si="2"/>
-        <v>1.1838923313102492</v>
+        <v>1.1920799389872223</v>
       </c>
       <c r="J10" s="64">
         <f t="shared" si="5"/>
-        <v>11985656.494305721</v>
+        <v>12068547.353998793</v>
       </c>
       <c r="K10" s="67">
         <f t="shared" si="3"/>
-        <v>9857982.0122063495</v>
+        <v>9612202.8931187652</v>
       </c>
       <c r="L10" s="68"/>
     </row>
@@ -4128,38 +4185,38 @@
       </c>
       <c r="D11" s="59">
         <f>IFERROR(+VLOOKUP(B11,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>18543635.055367131</v>
+        <v>25307057.946538661</v>
       </c>
       <c r="E11" s="59">
-        <v>7023074.0484903501</v>
+        <v>21714287.032106198</v>
       </c>
       <c r="F11" s="59">
         <f t="shared" ref="F11:F16" si="7">+D11-E11</f>
-        <v>11520561.006876782</v>
+        <v>3592770.9144324623</v>
       </c>
       <c r="G11" s="60">
         <f t="shared" si="1"/>
-        <v>0.19122679647058316</v>
+        <v>0.26097297562008082</v>
       </c>
       <c r="H11" s="59">
         <f t="shared" si="4"/>
-        <v>148349080.44293705</v>
+        <v>121473878.14338556</v>
       </c>
       <c r="I11" s="60">
         <f t="shared" si="2"/>
-        <v>1.5298143717646653</v>
+        <v>1.2526702829763878</v>
       </c>
       <c r="J11" s="59">
         <f t="shared" si="5"/>
-        <v>6181211.6851223772</v>
+        <v>5061411.5893077319</v>
       </c>
       <c r="K11" s="59">
         <f t="shared" si="3"/>
-        <v>3734681.5916557326</v>
+        <v>3771836.3438736238</v>
       </c>
       <c r="L11" s="61" cm="1">
         <f t="array" ref="L11">+_xlfn.IFS(I11&gt;114%,H11*0.0125,I11&gt;109%,H11*0.01,I11&gt;104%,H11*0.0075,I11&gt;99%,H11*0.005,I11&lt;99%,H11*0)</f>
-        <v>1854363.5055367132</v>
+        <v>1518423.4767923197</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4175,11 +4232,11 @@
         <v>7342359.2744361712</v>
       </c>
       <c r="E12" s="4">
-        <v>7395442.6965926401</v>
+        <v>7342359.2744361712</v>
       </c>
       <c r="F12" s="4">
         <f t="shared" si="7"/>
-        <v>-53083.422156468965</v>
+        <v>0</v>
       </c>
       <c r="G12" s="5">
         <f t="shared" si="1"/>
@@ -4187,23 +4244,23 @@
       </c>
       <c r="H12" s="4">
         <f t="shared" si="4"/>
-        <v>58738874.195489362</v>
+        <v>35243324.517293625</v>
       </c>
       <c r="I12" s="5">
         <f t="shared" si="2"/>
-        <v>1.8570091183860868</v>
+        <v>1.1142054710316522</v>
       </c>
       <c r="J12" s="4">
         <f t="shared" si="5"/>
-        <v>2447453.0914787236</v>
+        <v>1468471.8548872343</v>
       </c>
       <c r="K12" s="4">
         <f t="shared" si="3"/>
-        <v>1156597.2921014682</v>
+        <v>1278344.3754805701</v>
       </c>
       <c r="L12" s="63" cm="1">
         <f t="array" ref="L12">+_xlfn.IFS(I12&gt;114%,H12*0.02,I12&gt;109%,H12*0.015,I12&gt;104%,H12*0.0125,I12&gt;99%,H12*0.01,I12&lt;99%,H12*0)</f>
-        <v>1174777.4839097874</v>
+        <v>528649.86775940435</v>
       </c>
       <c r="M12" s="27"/>
     </row>
@@ -4217,38 +4274,38 @@
       </c>
       <c r="D13" s="4">
         <f>IFERROR(+VLOOKUP(B13,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>35677866.984969728</v>
+        <v>39689592.681744099</v>
       </c>
       <c r="E13" s="4">
-        <v>27711765.916719597</v>
+        <v>38609317.055148289</v>
       </c>
       <c r="F13" s="4">
         <f t="shared" si="7"/>
-        <v>7966101.0682501309</v>
+        <v>1080275.6265958101</v>
       </c>
       <c r="G13" s="5">
         <f t="shared" si="1"/>
-        <v>0.27794311731832977</v>
+        <v>0.30919586980090541</v>
       </c>
       <c r="H13" s="4">
         <f t="shared" si="4"/>
-        <v>285422935.87975782</v>
+        <v>190510044.87237167</v>
       </c>
       <c r="I13" s="5">
         <f t="shared" si="2"/>
-        <v>2.2235449385466382</v>
+        <v>1.4841401750443461</v>
       </c>
       <c r="J13" s="4">
         <f t="shared" si="5"/>
-        <v>11892622.328323243</v>
+        <v>7937918.5363488197</v>
       </c>
       <c r="K13" s="4">
         <f t="shared" si="3"/>
-        <v>4413621.3852216788</v>
+        <v>4667069.6522568883</v>
       </c>
       <c r="L13" s="63" cm="1">
         <f t="array" ref="L13">+_xlfn.IFS(I13&gt;114%,H13*0.0125,I13&gt;109%,H13*0.01,I13&gt;104%,H13*0.0075,I13&gt;99%,H13*0.005,I13&lt;99%,H13*0)</f>
-        <v>3567786.6984969731</v>
+        <v>2381375.5609046458</v>
       </c>
       <c r="M13" s="53" t="s">
         <v>61</v>
@@ -4267,34 +4324,34 @@
       </c>
       <c r="D14" s="4">
         <f>IFERROR(+VLOOKUP(B14,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>4699575.8856638623</v>
+        <v>6663134.8062294191</v>
       </c>
       <c r="E14" s="4">
-        <v>968840.97419863928</v>
+        <v>5554944.6639294196</v>
       </c>
       <c r="F14" s="4">
         <f t="shared" si="7"/>
-        <v>3730734.9114652229</v>
+        <v>1108190.1422999995</v>
       </c>
       <c r="G14" s="5">
         <f t="shared" si="1"/>
-        <v>0.11071095977316531</v>
+        <v>0.15696779186946522</v>
       </c>
       <c r="H14" s="4">
         <f t="shared" si="4"/>
-        <v>37596607.085310899</v>
+        <v>31983047.069901209</v>
       </c>
       <c r="I14" s="5">
         <f t="shared" si="2"/>
-        <v>0.88568767818532246</v>
+        <v>0.75344540097343304</v>
       </c>
       <c r="J14" s="4">
         <f t="shared" si="5"/>
-        <v>1566525.2952212875</v>
+        <v>1332626.9612458837</v>
       </c>
       <c r="K14" s="4">
         <f t="shared" si="3"/>
-        <v>1797594.3575862448</v>
+        <v>1883469.6099339779</v>
       </c>
       <c r="L14" s="63" cm="1">
         <f t="array" ref="L14">+_xlfn.IFS(I14&gt;109%,H14*0.015,I14&gt;104%,H14*0.0125,I14&gt;99%,H14*0.01,I14&lt;99%,H14*0)</f>
@@ -4312,38 +4369,38 @@
       </c>
       <c r="D15" s="4">
         <f>IFERROR(+VLOOKUP(B15,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>5825319.4707523696</v>
+        <v>10196205.867152149</v>
       </c>
       <c r="E15" s="4">
-        <v>1445131.6450023698</v>
+        <v>8252554.4917521486</v>
       </c>
       <c r="F15" s="4">
         <f t="shared" si="7"/>
-        <v>4380187.8257499998</v>
+        <v>1943651.3754000003</v>
       </c>
       <c r="G15" s="5">
         <f t="shared" si="1"/>
-        <v>0.13723083216076207</v>
+        <v>0.24019864027320303</v>
       </c>
       <c r="H15" s="4">
         <f t="shared" si="4"/>
-        <v>46602555.766018957</v>
+        <v>48941788.162330315</v>
       </c>
       <c r="I15" s="5">
         <f t="shared" si="2"/>
-        <v>1.0978466572860965</v>
+        <v>1.1529534733113747</v>
       </c>
       <c r="J15" s="4">
         <f t="shared" si="5"/>
-        <v>1941773.1569174565</v>
+        <v>2039241.1734304298</v>
       </c>
       <c r="K15" s="4">
         <f t="shared" si="3"/>
-        <v>1743987.5202010777</v>
+        <v>1697518.5014643606</v>
       </c>
       <c r="L15" s="63" cm="1">
         <f t="array" ref="L15">+_xlfn.IFS(I15&gt;109%,H15*0.015,I15&gt;104%,H15*0.0125,I15&gt;99%,H15*0.01,I15&lt;99%,H15*0)</f>
-        <v>699038.3364902843</v>
+        <v>734126.82243495469</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4354,34 +4411,34 @@
       </c>
       <c r="D16" s="64">
         <f>+SUM(D11:D15)</f>
-        <v>72088756.671189263</v>
+        <v>89198350.576100498</v>
       </c>
       <c r="E16" s="65">
-        <v>44544255.281003602</v>
+        <v>81473462.517372221</v>
       </c>
       <c r="F16" s="64">
         <f t="shared" si="7"/>
-        <v>27544501.390185662</v>
+        <v>7724888.0587282777</v>
       </c>
       <c r="G16" s="66">
         <f t="shared" si="1"/>
-        <v>0.21086914894994976</v>
+        <v>0.26091697432810329</v>
       </c>
       <c r="H16" s="64">
         <f t="shared" si="4"/>
-        <v>576710053.36951411</v>
+        <v>428152082.76528239</v>
       </c>
       <c r="I16" s="66">
         <f t="shared" si="2"/>
-        <v>1.6869531915995981</v>
+        <v>1.2524014767748959</v>
       </c>
       <c r="J16" s="64">
         <f t="shared" si="5"/>
-        <v>24029585.557063088</v>
+        <v>17839670.1152201</v>
       </c>
       <c r="K16" s="67">
         <f t="shared" si="3"/>
-        <v>12846482.146766203</v>
+        <v>13298238.483009422</v>
       </c>
       <c r="L16" s="68"/>
     </row>
@@ -4397,34 +4454,34 @@
       </c>
       <c r="D17" s="59">
         <f>IFERROR(+VLOOKUP(B17,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>3490474.4748070529</v>
+        <v>4842984.6712837927</v>
       </c>
       <c r="E17" s="59">
-        <v>1647814.3144255385</v>
+        <v>3831780.4656781647</v>
       </c>
       <c r="F17" s="59">
         <f t="shared" ref="F17:F40" si="8">+D17-E17</f>
-        <v>1842660.1603815143</v>
+        <v>1011204.205605628</v>
       </c>
       <c r="G17" s="60">
         <f t="shared" si="1"/>
-        <v>0.11897444670744077</v>
+        <v>0.1650753861222426</v>
       </c>
       <c r="H17" s="59">
         <f t="shared" si="4"/>
-        <v>27923795.798456423</v>
+        <v>23246326.422162205</v>
       </c>
       <c r="I17" s="60">
         <f t="shared" si="2"/>
-        <v>0.95179557365952616</v>
+        <v>0.79236185338676446</v>
       </c>
       <c r="J17" s="59">
         <f t="shared" si="5"/>
-        <v>1163491.491602351</v>
+        <v>968596.93425675854</v>
       </c>
       <c r="K17" s="59">
         <f t="shared" si="3"/>
-        <v>1230835.4122710929</v>
+        <v>1289212.2874324322</v>
       </c>
       <c r="L17" s="61" cm="1">
         <f t="array" ref="L17">+_xlfn.IFS(I17&gt;114%,H17*0.02,I17&gt;109%,H17*0.015,I17&gt;104%,H17*0.0125,I17&gt;99%,H17*0.01,I17&lt;99%,H17*0)</f>
@@ -4441,34 +4498,34 @@
       </c>
       <c r="D18" s="4">
         <f>IFERROR(+VLOOKUP(B18,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>2539362.2668490014</v>
+        <v>4538116.0675083203</v>
       </c>
       <c r="E18" s="4">
-        <v>1318807.9914469167</v>
+        <v>3383340.6159000443</v>
       </c>
       <c r="F18" s="4">
         <f t="shared" si="8"/>
-        <v>1220554.2754020847</v>
+        <v>1154775.451608276</v>
       </c>
       <c r="G18" s="5">
         <f t="shared" si="1"/>
-        <v>0.10173928430406153</v>
+        <v>0.18181914680884448</v>
       </c>
       <c r="H18" s="4">
         <f t="shared" si="4"/>
-        <v>20314898.134792011</v>
+        <v>21782957.124039941</v>
       </c>
       <c r="I18" s="5">
         <f t="shared" si="2"/>
-        <v>0.8139142744324922</v>
+        <v>0.87273190468245365</v>
       </c>
       <c r="J18" s="4">
         <f t="shared" si="5"/>
-        <v>846454.08894966717</v>
+        <v>907623.21350166411</v>
       </c>
       <c r="K18" s="4">
         <f t="shared" si="3"/>
-        <v>1067625.8872929048</v>
+        <v>1074809.9911837727</v>
       </c>
       <c r="L18" s="63" cm="1">
         <f t="array" ref="L18">+_xlfn.IFS(I18&gt;114%,H18*0.02,I18&gt;109%,H18*0.015,I18&gt;104%,H18*0.0125,I18&gt;99%,H18*0.01,I18&lt;99%,H18*0)</f>
@@ -4485,34 +4542,34 @@
       </c>
       <c r="D19" s="4">
         <f>IFERROR(+VLOOKUP(B19,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>3126324.9965506792</v>
+        <v>5255755.4759214995</v>
       </c>
       <c r="E19" s="4">
-        <v>1974051.5620993127</v>
+        <v>4172472.7522102422</v>
       </c>
       <c r="F19" s="4">
         <f t="shared" si="8"/>
-        <v>1152273.4344513665</v>
+        <v>1083282.7237112573</v>
       </c>
       <c r="G19" s="5">
         <f t="shared" si="1"/>
-        <v>0.12090990041401692</v>
+        <v>0.20326513458940426</v>
       </c>
       <c r="H19" s="4">
         <f t="shared" si="4"/>
-        <v>25010599.972405434</v>
+        <v>25227626.284423195</v>
       </c>
       <c r="I19" s="5">
         <f t="shared" si="2"/>
-        <v>0.96727920331213535</v>
+        <v>0.97567264602914039</v>
       </c>
       <c r="J19" s="4">
         <f t="shared" si="5"/>
-        <v>1042108.3321835598</v>
+        <v>1051151.0951842999</v>
       </c>
       <c r="K19" s="4">
         <f t="shared" si="3"/>
-        <v>1082396.4366166343</v>
+        <v>1084257.6152409737</v>
       </c>
       <c r="L19" s="63" cm="1">
         <f t="array" ref="L19">+_xlfn.IFS(I19&gt;114%,H19*0.02,I19&gt;109%,H19*0.015,I19&gt;104%,H19*0.0125,I19&gt;99%,H19*0.01,I19&lt;99%,H19*0)</f>
@@ -4529,38 +4586,38 @@
       </c>
       <c r="D20" s="4">
         <f>IFERROR(+VLOOKUP(B20,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>5313079.7996425815</v>
+        <v>9037854.5756811257</v>
       </c>
       <c r="E20" s="4">
-        <v>3804498.4929125779</v>
+        <v>8068602.606727235</v>
       </c>
       <c r="F20" s="4">
         <f t="shared" si="8"/>
-        <v>1508581.3067300036</v>
+        <v>969251.96895389073</v>
       </c>
       <c r="G20" s="5">
         <f t="shared" si="1"/>
-        <v>0.15837186155063132</v>
+        <v>0.2693996528474501</v>
       </c>
       <c r="H20" s="4">
         <f t="shared" si="4"/>
-        <v>42504638.397140652</v>
+        <v>43381701.963269398</v>
       </c>
       <c r="I20" s="5">
         <f t="shared" si="2"/>
-        <v>1.2669748924050506</v>
+        <v>1.2931183336677603</v>
       </c>
       <c r="J20" s="4">
         <f t="shared" si="5"/>
-        <v>1771026.5998808604</v>
+        <v>1807570.9151362251</v>
       </c>
       <c r="K20" s="4">
         <f t="shared" si="3"/>
-        <v>1344526.2000170199</v>
+        <v>1290014.4960167827</v>
       </c>
       <c r="L20" s="63" cm="1">
         <f t="array" ref="L20">+_xlfn.IFS(I20&gt;114%,H20*0.02,I20&gt;109%,H20*0.015,I20&gt;104%,H20*0.0125,I20&gt;99%,H20*0.01,I20&lt;99%,H20*0)</f>
-        <v>850092.76794281311</v>
+        <v>867634.03926538792</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4573,38 +4630,38 @@
       </c>
       <c r="D21" s="4">
         <f>IFERROR(+VLOOKUP(B21,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>3621062.6775038806</v>
+        <v>5595341.8938343767</v>
       </c>
       <c r="E21" s="4">
-        <v>2482567.9113498144</v>
+        <v>4521737.6382463202</v>
       </c>
       <c r="F21" s="4">
         <f t="shared" ref="F21:F23" si="9">+D21-E21</f>
-        <v>1138494.7661540662</v>
+        <v>1073604.2555880565</v>
       </c>
       <c r="G21" s="5">
         <f t="shared" si="1"/>
-        <v>0.14223388083214142</v>
+        <v>0.2197827718053561</v>
       </c>
       <c r="H21" s="4">
         <f t="shared" si="4"/>
-        <v>28968501.420031041</v>
+        <v>26857641.090405006</v>
       </c>
       <c r="I21" s="5">
         <f t="shared" si="2"/>
-        <v>1.1378710466571311</v>
+        <v>1.0549573046657093</v>
       </c>
       <c r="J21" s="4">
         <f t="shared" si="5"/>
-        <v>1207020.8925012934</v>
+        <v>1119068.3787668752</v>
       </c>
       <c r="K21" s="4">
         <f t="shared" si="3"/>
-        <v>1039878.4439283867</v>
+        <v>1045429.9003245066</v>
       </c>
       <c r="L21" s="63" cm="1">
         <f t="array" ref="L21">+_xlfn.IFS(I21&gt;114%,H21*0.02,I21&gt;109%,H21*0.015,I21&gt;104%,H21*0.0125,I21&gt;99%,H21*0.01,I21&lt;99%,H21*0)</f>
-        <v>434527.52130046563</v>
+        <v>335720.51363006257</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4617,38 +4674,38 @@
       </c>
       <c r="D22" s="4">
         <f>IFERROR(+VLOOKUP(B22,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>4525419.7648018571</v>
+        <v>8516814.03087065</v>
       </c>
       <c r="E22" s="4">
-        <v>3717567.9331198842</v>
+        <v>6604601.1312453747</v>
       </c>
       <c r="F22" s="4">
         <f t="shared" si="9"/>
-        <v>807851.83168197284</v>
+        <v>1912212.8996252753</v>
       </c>
       <c r="G22" s="5">
         <f t="shared" si="1"/>
-        <v>0.14256483062156253</v>
+        <v>0.26830619320450694</v>
       </c>
       <c r="H22" s="4">
         <f t="shared" si="4"/>
-        <v>36203358.118414856</v>
+        <v>40880707.348179117</v>
       </c>
       <c r="I22" s="5">
         <f t="shared" si="2"/>
-        <v>1.1405186449725002</v>
+        <v>1.2878697273816331</v>
       </c>
       <c r="J22" s="4">
         <f t="shared" si="5"/>
-        <v>1508473.2549339524</v>
+        <v>1703362.8061741299</v>
       </c>
       <c r="K22" s="4">
         <f t="shared" si="3"/>
-        <v>1296070.0207237212</v>
+        <v>1222425.061533124</v>
       </c>
       <c r="L22" s="63" cm="1">
         <f t="array" ref="L22">+_xlfn.IFS(I22&gt;114%,H22*0.02,I22&gt;109%,H22*0.015,I22&gt;104%,H22*0.0125,I22&gt;99%,H22*0.01,I22&lt;99%,H22*0)</f>
-        <v>724067.16236829711</v>
+        <v>817614.14696358237</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4661,38 +4718,38 @@
       </c>
       <c r="D23" s="4">
         <f>IFERROR(+VLOOKUP(B23,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>3880349.2779353959</v>
+        <v>5822405.6030015703</v>
       </c>
       <c r="E23" s="4">
-        <v>2007902.2622231084</v>
+        <v>5027241.122842595</v>
       </c>
       <c r="F23" s="4">
         <f t="shared" si="9"/>
-        <v>1872447.0157122875</v>
+        <v>795164.48015897535</v>
       </c>
       <c r="G23" s="5">
         <f t="shared" si="1"/>
-        <v>0.1414330399034098</v>
+        <v>0.21221814455355015</v>
       </c>
       <c r="H23" s="4">
         <f t="shared" si="4"/>
-        <v>31042794.223483168</v>
+        <v>27947546.894407541</v>
       </c>
       <c r="I23" s="5">
         <f t="shared" si="2"/>
-        <v>1.1314643192272784</v>
+        <v>1.0186470938570409</v>
       </c>
       <c r="J23" s="4">
         <f t="shared" si="5"/>
-        <v>1293449.7593117987</v>
+        <v>1164481.1206003141</v>
       </c>
       <c r="K23" s="4">
         <f t="shared" si="3"/>
-        <v>1121695.0929554575</v>
+        <v>1137554.7698420228</v>
       </c>
       <c r="L23" s="63" cm="1">
         <f t="array" ref="L23">+_xlfn.IFS(I23&gt;114%,H23*0.02,I23&gt;109%,H23*0.015,I23&gt;104%,H23*0.0125,I23&gt;99%,H23*0.01,I23&lt;99%,H23*0)</f>
-        <v>465641.9133522475</v>
+        <v>279475.4689440754</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4705,38 +4762,38 @@
       </c>
       <c r="D24" s="4">
         <f>IFERROR(+VLOOKUP(B24,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>3150944.560423614</v>
+        <v>6909391.5039921645</v>
       </c>
       <c r="E24" s="4">
-        <v>2373341.2642009868</v>
+        <v>4507114.506957056</v>
       </c>
       <c r="F24" s="4">
         <f t="shared" si="8"/>
-        <v>777603.29622262716</v>
+        <v>2402276.9970351085</v>
       </c>
       <c r="G24" s="5">
         <f t="shared" si="1"/>
-        <v>9.407474133614499E-2</v>
+        <v>0.20628710091961586</v>
       </c>
       <c r="H24" s="4">
         <f t="shared" si="4"/>
-        <v>25207556.483388916</v>
+        <v>33165079.21916239</v>
       </c>
       <c r="I24" s="5">
         <f t="shared" si="2"/>
-        <v>0.75259793068916003</v>
+        <v>0.99017808441415622</v>
       </c>
       <c r="J24" s="4">
         <f t="shared" si="5"/>
-        <v>1050314.8534745381</v>
+        <v>1381878.3007984329</v>
       </c>
       <c r="K24" s="4">
         <f t="shared" si="3"/>
-        <v>1444910.020932209</v>
+        <v>1399192.8155793599</v>
       </c>
       <c r="L24" s="63" cm="1">
         <f t="array" ref="L24">+_xlfn.IFS(I24&gt;114%,H24*0.02,I24&gt;109%,H24*0.015,I24&gt;104%,H24*0.0125,I24&gt;99%,H24*0.01,I24&lt;99%,H24*0)</f>
-        <v>0</v>
+        <v>331650.79219162388</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4749,38 +4806,38 @@
       </c>
       <c r="D25" s="4">
         <f>IFERROR(+VLOOKUP(B25,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>7402539.5016198214</v>
+        <v>8825883.2392010316</v>
       </c>
       <c r="E25" s="4">
-        <v>-2433547.0814999999</v>
+        <v>7398936.6723073218</v>
       </c>
       <c r="F25" s="4">
         <f t="shared" si="8"/>
-        <v>9836086.5831198208</v>
+        <v>1426946.5668937098</v>
       </c>
       <c r="G25" s="5">
         <f t="shared" si="1"/>
-        <v>0.13691937400008347</v>
+        <v>0.16324592497544999</v>
       </c>
       <c r="H25" s="4">
         <f t="shared" si="4"/>
-        <v>59220316.012958571</v>
+        <v>42364239.548164949</v>
       </c>
       <c r="I25" s="5">
         <f t="shared" si="2"/>
-        <v>1.0953549920006678</v>
+        <v>0.78358043988215986</v>
       </c>
       <c r="J25" s="4">
         <f t="shared" si="5"/>
-        <v>2467513.1672066073</v>
+        <v>1765176.6478402063</v>
       </c>
       <c r="K25" s="4">
         <f t="shared" si="3"/>
-        <v>2222019.6839704849</v>
+        <v>2381003.6645157356</v>
       </c>
       <c r="L25" s="63" cm="1">
         <f t="array" ref="L25">+_xlfn.IFS(I25&gt;109%,H25*0.015,I25&gt;104%,H25*0.0125,I25&gt;99%,H25*0.01,I25&lt;99%,H25*0)</f>
-        <v>888304.74019437854</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4791,34 +4848,34 @@
       </c>
       <c r="D26" s="67">
         <f>+SUM(D17:D25)</f>
-        <v>37049557.32013388</v>
+        <v>59344547.061294533</v>
       </c>
       <c r="E26" s="65">
-        <v>16893004.650278136</v>
+        <v>47515827.512114353</v>
       </c>
       <c r="F26" s="67">
         <f>+D26-E26</f>
-        <v>20156552.669855744</v>
+        <v>11828719.54918018</v>
       </c>
       <c r="G26" s="66">
         <f t="shared" si="1"/>
-        <v>0.12958982569357178</v>
+        <v>0.20757196754299401</v>
       </c>
       <c r="H26" s="64">
         <f t="shared" si="4"/>
-        <v>296396458.56107104</v>
+        <v>284853825.89421374</v>
       </c>
       <c r="I26" s="66">
         <f t="shared" si="2"/>
-        <v>1.0367186055485742</v>
+        <v>0.99634544420637117</v>
       </c>
       <c r="J26" s="64">
         <f t="shared" si="5"/>
-        <v>12349852.440044627</v>
+        <v>11868909.412258906</v>
       </c>
       <c r="K26" s="67">
         <f t="shared" si="3"/>
-        <v>11849957.198707912</v>
+        <v>11923900.60166871</v>
       </c>
       <c r="L26" s="68"/>
     </row>
@@ -4834,38 +4891,38 @@
       </c>
       <c r="D27" s="59">
         <f>IFERROR(+VLOOKUP(B27,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>7197381.3632933144</v>
+        <v>17555809.912466466</v>
       </c>
       <c r="E27" s="59">
-        <v>5151540.6591492426</v>
+        <v>14993819.966923174</v>
       </c>
       <c r="F27" s="59">
         <f t="shared" si="8"/>
-        <v>2045840.7041440718</v>
+        <v>2561989.9455432929</v>
       </c>
       <c r="G27" s="60">
         <f t="shared" si="1"/>
-        <v>8.7796819907039525E-2</v>
+        <v>0.21415348213558646</v>
       </c>
       <c r="H27" s="59">
         <f t="shared" si="4"/>
-        <v>57579050.906346515</v>
+        <v>84267887.579839051</v>
       </c>
       <c r="I27" s="60">
         <f t="shared" si="2"/>
-        <v>0.7023745592563162</v>
+        <v>1.0279367142508151</v>
       </c>
       <c r="J27" s="59">
         <f t="shared" si="5"/>
-        <v>2399127.1210977715</v>
+        <v>3511161.9824932935</v>
       </c>
       <c r="K27" s="59">
         <f t="shared" si="3"/>
-        <v>3560967.5541288895</v>
+        <v>3390625.7940807124</v>
       </c>
       <c r="L27" s="61" cm="1">
         <f t="array" ref="L27">+_xlfn.IFS(I27&gt;114%,H27*0.0125,I27&gt;109%,H27*0.01,I27&gt;104%,H27*0.0075,I27&gt;99%,H27*0.005,I27&lt;99%,H27*0)</f>
-        <v>0</v>
+        <v>421339.43789919524</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4878,34 +4935,34 @@
       </c>
       <c r="D28" s="4">
         <f>IFERROR(+VLOOKUP(B28,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>1662817.6962441357</v>
+        <v>2883607.9842428509</v>
       </c>
       <c r="E28" s="4">
-        <v>1127867.2813395613</v>
+        <v>2246997.9859188953</v>
       </c>
       <c r="F28" s="4">
         <f t="shared" si="8"/>
-        <v>534950.4149045744</v>
+        <v>636609.99832395557</v>
       </c>
       <c r="G28" s="5">
         <f t="shared" si="1"/>
-        <v>7.9181795059244553E-2</v>
+        <v>0.13731466591632624</v>
       </c>
       <c r="H28" s="4">
         <f t="shared" si="4"/>
-        <v>13302541.569953088</v>
+        <v>13841318.324365683</v>
       </c>
       <c r="I28" s="5">
         <f t="shared" si="2"/>
-        <v>0.63345436047395653</v>
+        <v>0.65911039639836588</v>
       </c>
       <c r="J28" s="4">
         <f t="shared" si="5"/>
-        <v>554272.56541471195</v>
+        <v>576721.59684857016</v>
       </c>
       <c r="K28" s="4">
         <f t="shared" si="3"/>
-        <v>920818.2049407555</v>
+        <v>953494.31661879737</v>
       </c>
       <c r="L28" s="63" cm="1">
         <f t="array" ref="L28">+_xlfn.IFS(I28&gt;114%,H28*0.02,I28&gt;109%,H28*0.015,I28&gt;104%,H28*0.0125,I28&gt;99%,H28*0.01,I28&lt;99%,H28*0)</f>
@@ -4922,34 +4979,34 @@
       </c>
       <c r="D29" s="4">
         <f>IFERROR(+VLOOKUP(B29,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>2237337.654012111</v>
+        <v>3996158.8131728824</v>
       </c>
       <c r="E29" s="4">
-        <v>3336344.5485263281</v>
+        <v>2863924.6281832345</v>
       </c>
       <c r="F29" s="4">
         <f t="shared" si="8"/>
-        <v>-1099006.894514217</v>
+        <v>1132234.1849896479</v>
       </c>
       <c r="G29" s="5">
         <f t="shared" si="1"/>
-        <v>8.6921667852077181E-2</v>
+        <v>0.15525273461512304</v>
       </c>
       <c r="H29" s="4">
         <f t="shared" si="4"/>
-        <v>17898701.232096888</v>
+        <v>19181562.303229839</v>
       </c>
       <c r="I29" s="5">
         <f t="shared" si="2"/>
-        <v>0.69537334281661745</v>
+        <v>0.74521312615259072</v>
       </c>
       <c r="J29" s="4">
         <f t="shared" si="5"/>
-        <v>745779.21800403704</v>
+        <v>799231.76263457653</v>
       </c>
       <c r="K29" s="4">
         <f t="shared" si="3"/>
-        <v>1119160.1117137091</v>
+        <v>1144396.9045698482</v>
       </c>
       <c r="L29" s="63" cm="1">
         <f t="array" ref="L29">+_xlfn.IFS(I29&gt;114%,H29*0.02,I29&gt;109%,H29*0.015,I29&gt;104%,H29*0.0125,I29&gt;99%,H29*0.01,I29&lt;99%,H29*0)</f>
@@ -4967,34 +5024,34 @@
       </c>
       <c r="D30" s="4">
         <f>IFERROR(+VLOOKUP(B30,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>2806120.8392654946</v>
+        <v>4975553.6144345868</v>
       </c>
       <c r="E30" s="4">
-        <v>1465987.5738126547</v>
+        <v>4669958.7290065279</v>
       </c>
       <c r="F30" s="4">
         <f t="shared" si="8"/>
-        <v>1340133.2654528399</v>
+        <v>305594.88542805891</v>
       </c>
       <c r="G30" s="5">
         <f t="shared" si="1"/>
-        <v>7.3394862686401677E-2</v>
+        <v>0.13013697386454762</v>
       </c>
       <c r="H30" s="4">
         <f t="shared" si="4"/>
-        <v>22448966.714123957</v>
+        <v>23882657.34928602</v>
       </c>
       <c r="I30" s="5">
         <f t="shared" si="2"/>
-        <v>0.58715890149121341</v>
+        <v>0.62465747454982867</v>
       </c>
       <c r="J30" s="4">
         <f t="shared" si="5"/>
-        <v>935373.61308849824</v>
+        <v>995110.72288691741</v>
       </c>
       <c r="K30" s="4">
         <f t="shared" si="3"/>
-        <v>1687004.0129933418</v>
+        <v>1750402.710404794</v>
       </c>
       <c r="L30" s="63" cm="1">
         <f t="array" ref="L30">+_xlfn.IFS(I30&gt;114%,H30*0.02,I30&gt;109%,H30*0.015,I30&gt;104%,H30*0.0125,I30&gt;99%,H30*0.01,I30&lt;99%,H30*0)</f>
@@ -5012,38 +5069,38 @@
       </c>
       <c r="D31" s="4">
         <f>IFERROR(+VLOOKUP(B31,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>3265458.2459612871</v>
+        <v>4865926.9418352479</v>
       </c>
       <c r="E31" s="4">
-        <v>2185400.7533588032</v>
+        <v>4425690.3579718489</v>
       </c>
       <c r="F31" s="4">
         <f t="shared" si="8"/>
-        <v>1080057.4926024838</v>
+        <v>440236.58386339899</v>
       </c>
       <c r="G31" s="5">
         <f t="shared" si="1"/>
-        <v>0.12848420715756434</v>
+        <v>0.19145697728077624</v>
       </c>
       <c r="H31" s="4">
         <f t="shared" si="4"/>
-        <v>26123665.967690296</v>
+        <v>23356449.320809193</v>
       </c>
       <c r="I31" s="5">
         <f t="shared" si="2"/>
-        <v>1.0278736572605147</v>
+        <v>0.91899349094772598</v>
       </c>
       <c r="J31" s="4">
         <f t="shared" si="5"/>
-        <v>1088486.0819870958</v>
+        <v>973185.38836704963</v>
       </c>
       <c r="K31" s="4">
         <f t="shared" si="3"/>
-        <v>1054751.9882875578</v>
+        <v>1081543.3188507764</v>
       </c>
       <c r="L31" s="63" cm="1">
         <f t="array" ref="L31">+_xlfn.IFS(I31&gt;114%,H31*0.02,I31&gt;109%,H31*0.015,I31&gt;104%,H31*0.0125,I31&gt;99%,H31*0.01,I31&lt;99%,H31*0)</f>
-        <v>261236.65967690296</v>
+        <v>0</v>
       </c>
       <c r="M31" s="27"/>
     </row>
@@ -5057,34 +5114,34 @@
       </c>
       <c r="D32" s="4">
         <f>IFERROR(+VLOOKUP(B32,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>1556471.8667402903</v>
+        <v>2958594.3353685732</v>
       </c>
       <c r="E32" s="4">
-        <v>772280.47046408884</v>
+        <v>2292259.0263364343</v>
       </c>
       <c r="F32" s="4">
         <f t="shared" si="8"/>
-        <v>784191.39627620147</v>
+        <v>666335.3090321389</v>
       </c>
       <c r="G32" s="5">
         <f t="shared" si="1"/>
-        <v>6.1764756616678185E-2</v>
+        <v>0.11740453711780052</v>
       </c>
       <c r="H32" s="4">
         <f t="shared" si="4"/>
-        <v>12451774.933922322</v>
+        <v>14201252.80976915</v>
       </c>
       <c r="I32" s="5">
         <f t="shared" si="2"/>
-        <v>0.49411805293342548</v>
+        <v>0.56354177816544249</v>
       </c>
       <c r="J32" s="4">
         <f t="shared" si="5"/>
-        <v>518823.95558009675</v>
+        <v>591718.86707371462</v>
       </c>
       <c r="K32" s="4">
         <f t="shared" si="3"/>
-        <v>1125882.2920599862</v>
+        <v>1170600.2981384962</v>
       </c>
       <c r="L32" s="63" cm="1">
         <f t="array" ref="L32">+_xlfn.IFS(I32&gt;114%,H32*0.02,I32&gt;109%,H32*0.015,I32&gt;104%,H32*0.0125,I32&gt;99%,H32*0.01,I32&lt;99%,H32*0)</f>
@@ -5102,34 +5159,34 @@
       </c>
       <c r="D33" s="4">
         <f>IFERROR(+VLOOKUP(B33,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>1905347.2963424551</v>
+        <v>3089173.5689832573</v>
       </c>
       <c r="E33" s="4">
-        <v>1312962.2237802313</v>
+        <v>2299134.4748592312</v>
       </c>
       <c r="F33" s="4">
         <f t="shared" si="8"/>
-        <v>592385.07256222377</v>
+        <v>790039.09412402613</v>
       </c>
       <c r="G33" s="5">
         <f t="shared" si="1"/>
-        <v>7.19087169687775E-2</v>
+        <v>0.1165868859004692</v>
       </c>
       <c r="H33" s="4">
         <f t="shared" si="4"/>
-        <v>15242778.370739641</v>
+        <v>14828033.131119635</v>
       </c>
       <c r="I33" s="5">
         <f t="shared" si="2"/>
-        <v>0.57526973575022</v>
+        <v>0.55961705232225212</v>
       </c>
       <c r="J33" s="4">
         <f t="shared" si="5"/>
-        <v>635115.76544748503</v>
+        <v>617834.71379665146</v>
       </c>
       <c r="K33" s="4">
         <f t="shared" si="3"/>
-        <v>1171019.1763646449</v>
+        <v>1231977.706895618</v>
       </c>
       <c r="L33" s="63" cm="1">
         <f t="array" ref="L33">+_xlfn.IFS(I33&gt;114%,H33*0.02,I33&gt;109%,H33*0.015,I33&gt;104%,H33*0.0125,I33&gt;99%,H33*0.01,I33&lt;99%,H33*0)</f>
@@ -5146,34 +5203,34 @@
       </c>
       <c r="D34" s="4">
         <f>IFERROR(+VLOOKUP(B34,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>1342266.2312651528</v>
+        <v>2098536.1960838647</v>
       </c>
       <c r="E34" s="4">
-        <v>1012363.4850253685</v>
+        <v>1808557.8257932956</v>
       </c>
       <c r="F34" s="4">
         <f t="shared" si="8"/>
-        <v>329902.74623978429</v>
+        <v>289978.37029056903</v>
       </c>
       <c r="G34" s="5">
         <f t="shared" si="1"/>
-        <v>6.3917439584054894E-2</v>
+        <v>9.9930295051612605E-2</v>
       </c>
       <c r="H34" s="4">
         <f t="shared" si="4"/>
-        <v>10738129.850121222</v>
+        <v>10072973.741202552</v>
       </c>
       <c r="I34" s="5">
         <f t="shared" si="2"/>
-        <v>0.51133951667243915</v>
+        <v>0.47966541624774056</v>
       </c>
       <c r="J34" s="4">
         <f t="shared" si="5"/>
-        <v>447422.07708838425</v>
+        <v>419707.23921677296</v>
       </c>
       <c r="K34" s="4">
         <f t="shared" si="3"/>
-        <v>936082.56041594502</v>
+        <v>994813.88441663864</v>
       </c>
       <c r="L34" s="63" cm="1">
         <f t="array" ref="L34">+_xlfn.IFS(I34&gt;114%,H34*0.02,I34&gt;109%,H34*0.015,I34&gt;104%,H34*0.0125,I34&gt;99%,H34*0.01,I34&lt;99%,H34*0)</f>
@@ -5190,34 +5247,34 @@
       </c>
       <c r="D35" s="4">
         <f>IFERROR(+VLOOKUP(B35,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>920475.59202497394</v>
+        <v>1626463.4655310514</v>
       </c>
       <c r="E35" s="4">
-        <v>474208.7541035653</v>
+        <v>1134886.8601273343</v>
       </c>
       <c r="F35" s="4">
         <f t="shared" si="8"/>
-        <v>446266.83792140865</v>
+        <v>491576.60540371714</v>
       </c>
       <c r="G35" s="5">
         <f t="shared" si="1"/>
-        <v>3.7329391116341579E-2</v>
+        <v>6.5960348506016314E-2</v>
       </c>
       <c r="H35" s="4">
         <f t="shared" si="4"/>
-        <v>7363804.7361997925</v>
+        <v>7807024.6345490459</v>
       </c>
       <c r="I35" s="5">
         <f t="shared" si="2"/>
-        <v>0.29863512893073269</v>
+        <v>0.31660967282887825</v>
       </c>
       <c r="J35" s="4">
         <f t="shared" si="5"/>
-        <v>306825.197341658</v>
+        <v>325292.69310621027</v>
       </c>
       <c r="K35" s="4">
         <f t="shared" si="3"/>
-        <v>1130367.8289511916</v>
+        <v>1212196.659708892</v>
       </c>
       <c r="L35" s="63" cm="1">
         <f t="array" ref="L35">+_xlfn.IFS(I35&gt;114%,H35*0.02,I35&gt;109%,H35*0.015,I35&gt;104%,H35*0.0125,I35&gt;99%,H35*0.01,I35&lt;99%,H35*0)</f>
@@ -5234,34 +5291,34 @@
       </c>
       <c r="D36" s="4">
         <f>IFERROR(+VLOOKUP(B36,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>1931060.2247250369</v>
+        <v>3109025.2196221473</v>
       </c>
       <c r="E36" s="4">
-        <v>1231155.9948169386</v>
+        <v>2633216.6305364068</v>
       </c>
       <c r="F36" s="4">
         <f t="shared" si="8"/>
-        <v>699904.22990809823</v>
+        <v>475808.5890857405</v>
       </c>
       <c r="G36" s="5">
         <f t="shared" si="1"/>
-        <v>7.6523091924907347E-2</v>
+        <v>0.12320290151068544</v>
       </c>
       <c r="H36" s="4">
         <f t="shared" si="4"/>
-        <v>15448481.797800295</v>
+        <v>14923321.054186307</v>
       </c>
       <c r="I36" s="5">
         <f t="shared" si="2"/>
-        <v>0.61218473539925877</v>
+        <v>0.59137392725129012</v>
       </c>
       <c r="J36" s="4">
         <f t="shared" si="5"/>
-        <v>643686.74157501233</v>
+        <v>621805.04392442945</v>
       </c>
       <c r="K36" s="4">
         <f t="shared" si="3"/>
-        <v>1109711.4178702363</v>
+        <v>1164524.9884409397</v>
       </c>
       <c r="L36" s="63" cm="1">
         <f t="array" ref="L36">+_xlfn.IFS(I36&gt;114%,H36*0.02,I36&gt;109%,H36*0.015,I36&gt;104%,H36*0.0125,I36&gt;99%,H36*0.01,I36&lt;99%,H36*0)</f>
@@ -5278,38 +5335,38 @@
       </c>
       <c r="D37" s="4">
         <f>IFERROR(+VLOOKUP(B37,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>16463801.298558187</v>
+        <v>17061083.040882383</v>
       </c>
       <c r="E37" s="4">
-        <v>-974804.98299181263</v>
+        <v>17081843.43377829</v>
       </c>
       <c r="F37" s="4">
         <f t="shared" si="8"/>
-        <v>17438606.281549998</v>
+        <v>-20760.392895907164</v>
       </c>
       <c r="G37" s="5">
         <f t="shared" si="1"/>
-        <v>0.13493619506775525</v>
+        <v>0.13983147558233025</v>
       </c>
       <c r="H37" s="4">
         <f t="shared" si="4"/>
-        <v>131710410.38846549</v>
+        <v>81893198.596235424</v>
       </c>
       <c r="I37" s="5">
         <f t="shared" si="2"/>
-        <v>1.079489560542042</v>
+        <v>0.67119108279518513</v>
       </c>
       <c r="J37" s="4">
         <f t="shared" si="5"/>
-        <v>5487933.7661860622</v>
+        <v>3412216.6081764763</v>
       </c>
       <c r="K37" s="4">
         <f t="shared" si="3"/>
-        <v>5026092.7953067524</v>
+        <v>5523719.3136377698</v>
       </c>
       <c r="L37" s="63" cm="1">
         <f t="array" ref="L37">+_xlfn.IFS(I37&gt;114%,H37*0.0125,I37&gt;109%,H37*0.01,I37&gt;104%,H37*0.0075,I37&gt;99%,H37*0.005,I37&lt;99%,H37*0)</f>
-        <v>987828.07791349117</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
@@ -5322,34 +5379,34 @@
       </c>
       <c r="D38" s="4">
         <f>IFERROR(+VLOOKUP(B38,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>149294.68419999999</v>
+        <v>746511.00490000006</v>
       </c>
       <c r="E38" s="4">
-        <v>0</v>
+        <v>280769.63740000001</v>
       </c>
       <c r="F38" s="4">
         <f t="shared" ref="F38" si="10">+D38-E38</f>
-        <v>149294.68419999999</v>
+        <v>465741.36750000005</v>
       </c>
       <c r="G38" s="5">
         <f t="shared" si="1"/>
-        <v>4.1819239271708684E-3</v>
+        <v>2.0910672406162466E-2</v>
       </c>
       <c r="H38" s="4">
         <f t="shared" si="4"/>
-        <v>1194357.4735999999</v>
+        <v>3583252.8235200006</v>
       </c>
       <c r="I38" s="5">
         <f t="shared" si="2"/>
-        <v>3.3455391417366948E-2</v>
+        <v>0.10037122754957985</v>
       </c>
       <c r="J38" s="4">
         <f t="shared" si="5"/>
-        <v>49764.894733333327</v>
+        <v>149302.20098000002</v>
       </c>
       <c r="K38" s="4">
         <f t="shared" si="3"/>
-        <v>1692890.7293238097</v>
+        <v>1839657.3155315788</v>
       </c>
       <c r="L38" s="63" cm="1">
         <f t="array" ref="L38">+_xlfn.IFS(I38&gt;109%,H38*0.015,I38&gt;104%,H38*0.0125,I38&gt;99%,H38*0.01,I38&lt;99%,H38*0)</f>
@@ -5366,38 +5423,38 @@
       </c>
       <c r="D39" s="4">
         <f>IFERROR(+VLOOKUP(B39,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>4713478.3902184051</v>
+        <v>6953389.0972305397</v>
       </c>
       <c r="E39" s="4">
-        <v>3667023.6813626946</v>
+        <v>6167950.3247244535</v>
       </c>
       <c r="F39" s="4">
         <f t="shared" si="8"/>
-        <v>1046454.7088557105</v>
+        <v>785438.77250608616</v>
       </c>
       <c r="G39" s="5">
         <f t="shared" si="1"/>
-        <v>0.12962852900198119</v>
+        <v>0.19122981493305272</v>
       </c>
       <c r="H39" s="4">
         <f t="shared" si="4"/>
-        <v>37707827.12174724</v>
+        <v>33376267.666706588</v>
       </c>
       <c r="I39" s="5">
         <f t="shared" si="2"/>
-        <v>1.0370282320158495</v>
+        <v>0.91790311167865302</v>
       </c>
       <c r="J39" s="4">
         <f t="shared" si="5"/>
-        <v>1571159.4634061351</v>
+        <v>1390677.8194461078</v>
       </c>
       <c r="K39" s="4">
         <f t="shared" si="3"/>
-        <v>1507045.2070848378</v>
+        <v>1547791.5074615506</v>
       </c>
       <c r="L39" s="63" cm="1">
         <f t="array" ref="L39">+_xlfn.IFS(I39&gt;114%,H39*0.02,I39&gt;109%,H39*0.015,I39&gt;104%,H39*0.0125,I39&gt;99%,H39*0.01,I39&lt;99%,H39*0)</f>
-        <v>377078.27121747239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -5408,34 +5465,34 @@
       </c>
       <c r="D40" s="67">
         <f>+SUM(D27:D39)</f>
-        <v>46151311.382850848</v>
+        <v>71919833.194753855</v>
       </c>
       <c r="E40" s="65">
-        <v>20762330.442747667</v>
+        <v>62899009.881559134</v>
       </c>
       <c r="F40" s="67">
         <f t="shared" si="8"/>
-        <v>25388980.940103181</v>
+        <v>9020823.3131947219</v>
       </c>
       <c r="G40" s="66">
         <f t="shared" si="1"/>
-        <v>9.0665390258040754E-2</v>
+        <v>0.14128828734254617</v>
       </c>
       <c r="H40" s="64">
         <f t="shared" si="4"/>
-        <v>369210491.06280679</v>
+        <v>345215199.33481848</v>
       </c>
       <c r="I40" s="66">
         <f t="shared" si="2"/>
-        <v>0.72532312206432603</v>
+        <v>0.67818377924422157</v>
       </c>
       <c r="J40" s="64">
         <f t="shared" si="5"/>
-        <v>15383770.460950283</v>
+        <v>14383966.638950771</v>
       </c>
       <c r="K40" s="67">
         <f t="shared" si="3"/>
-        <v>22041793.87944166</v>
+        <v>23005744.718756411</v>
       </c>
       <c r="L40" s="68"/>
     </row>
@@ -5449,34 +5506,34 @@
       </c>
       <c r="D41" s="81">
         <f>+D40+D26+D10+D16</f>
-        <v>191246594.85709113</v>
+        <v>280805467.60214281</v>
       </c>
       <c r="E41" s="82">
-        <v>105866448.03886795</v>
+        <v>240577000.14348808</v>
       </c>
       <c r="F41" s="81">
         <f>+D41-E41</f>
-        <v>85380146.818223178</v>
+        <v>40228467.458654732</v>
       </c>
       <c r="G41" s="83">
         <f t="shared" si="1"/>
-        <v>0.13860787688705689</v>
+        <v>0.20351656306191793</v>
       </c>
       <c r="H41" s="81">
         <f t="shared" si="4"/>
-        <v>1529972758.856729</v>
+        <v>1347866244.4902854</v>
       </c>
       <c r="I41" s="83">
         <f t="shared" si="2"/>
-        <v>1.1088630150964551</v>
+        <v>0.97687950269720591</v>
       </c>
       <c r="J41" s="81">
         <f t="shared" si="5"/>
-        <v>63748864.952363707</v>
+        <v>56161093.520428561</v>
       </c>
       <c r="K41" s="81">
         <f t="shared" si="3"/>
-        <v>56596216.773144998</v>
+        <v>57840088.394262806</v>
       </c>
       <c r="L41" s="84"/>
     </row>
@@ -5524,34 +5581,34 @@
       </c>
       <c r="D43" s="4">
         <f>IFERROR(+VLOOKUP(B43,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>3760393.1741207056</v>
+      </c>
+      <c r="E43" s="4">
         <v>-275260.76904147147</v>
-      </c>
-      <c r="E43" s="4">
-        <v>0</v>
       </c>
       <c r="F43" s="4">
         <f t="shared" ref="F43" si="11">+D43-E43</f>
-        <v>-275260.76904147147</v>
+        <v>4035653.9431621772</v>
       </c>
       <c r="G43" s="5">
         <f>+D43/C43</f>
-        <v>-6.8815192260367865E-3</v>
+        <v>9.4009829353017646E-2</v>
       </c>
       <c r="H43" s="4">
         <f t="shared" ref="H43" si="12">+D43/$N$3*$N$4</f>
-        <v>-2202086.1523317718</v>
+        <v>18049887.23577939</v>
       </c>
       <c r="I43" s="5">
         <f>+H43/C43</f>
-        <v>-5.5052153808294292E-2</v>
+        <v>0.45124718089448473</v>
       </c>
       <c r="J43" s="4">
         <f t="shared" ref="J43" si="13">+D43/$N$3</f>
-        <v>-91753.589680490491</v>
+        <v>752078.63482414116</v>
       </c>
       <c r="K43" s="4">
         <f>+(C43-D43)/$N$2</f>
-        <v>1917869.5604305463</v>
+        <v>1907347.7276778575</v>
       </c>
       <c r="L43" s="4" cm="1">
         <f t="array" ref="L43">+_xlfn.IFS(I43&gt;114%,H43*0.02,I43&gt;109%,H43*0.015,I43&gt;104%,H43*0.0125,I43&gt;99%,H43*0.01,I43&lt;99%,H43*0)</f>
@@ -5567,34 +5624,34 @@
       </c>
       <c r="D44" s="4">
         <f>IFERROR(+VLOOKUP(B44,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>1913900.6624423866</v>
+      </c>
+      <c r="E44" s="4">
         <v>-402349.89063324447</v>
-      </c>
-      <c r="E44" s="4">
-        <v>-388379.73864699452</v>
       </c>
       <c r="F44" s="4">
         <f t="shared" ref="F44" si="14">+D44-E44</f>
-        <v>-13970.151986249955</v>
+        <v>2316250.5530756311</v>
       </c>
       <c r="G44" s="5">
         <f>+D44/C44</f>
-        <v>-1.3411663021108149E-2</v>
+        <v>6.3796688748079561E-2</v>
       </c>
       <c r="H44" s="4">
         <f t="shared" ref="H44" si="15">+D44/$N$3*$N$4</f>
-        <v>-3218799.1250659563</v>
+        <v>9186723.1797234565</v>
       </c>
       <c r="I44" s="5">
         <f>+H44/C44</f>
-        <v>-0.10729330416886521</v>
+        <v>0.30622410599078187</v>
       </c>
       <c r="J44" s="4">
         <f t="shared" ref="J44" si="16">+D44/$N$3</f>
-        <v>-134116.6302110815</v>
+        <v>382780.13248847733</v>
       </c>
       <c r="K44" s="4">
         <f>+(C44-D44)/$N$2</f>
-        <v>1447730.9471730117</v>
+        <v>1478215.7546082954</v>
       </c>
       <c r="L44" s="4" cm="1">
         <f t="array" ref="L44">+_xlfn.IFS(I44&gt;114%,H44*0.02,I44&gt;109%,H44*0.015,I44&gt;104%,H44*0.0125,I44&gt;99%,H44*0.01,I44&lt;99%,H44*0)</f>
@@ -5736,14 +5793,14 @@
       </c>
       <c r="D2" s="22">
         <f>H2/G2</f>
-        <v>0.22222222222222221</v>
+        <v>0.51388888888888884</v>
       </c>
       <c r="E2" s="13">
         <v>33</v>
       </c>
       <c r="F2" s="12">
         <f>+H2-E2</f>
-        <v>-17</v>
+        <v>4</v>
       </c>
       <c r="G2" s="13">
         <f>VLOOKUP(B2,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -5751,11 +5808,11 @@
       </c>
       <c r="H2" s="13">
         <f>VLOOKUP(B2,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="I2" s="17">
         <f>(+G2*$M$2)-H2</f>
-        <v>45.199999999999996</v>
+        <v>24.199999999999996</v>
       </c>
       <c r="J2" t="s">
         <v>55</v>
@@ -5801,14 +5858,14 @@
       </c>
       <c r="D3" s="22">
         <f t="shared" ref="D3:D38" si="0">H3/G3</f>
-        <v>0.23012552301255229</v>
+        <v>0.22175732217573221</v>
       </c>
       <c r="E3" s="13">
         <v>1</v>
       </c>
       <c r="F3" s="12">
         <f t="shared" ref="F3:F38" si="1">+H3-E3</f>
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G3" s="13">
         <f>VLOOKUP(B3,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -5816,11 +5873,11 @@
       </c>
       <c r="H3" s="13">
         <f>VLOOKUP(B3,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I3" s="17">
         <f t="shared" ref="I3:I38" si="2">(+G3*$M$2)-H3</f>
-        <v>148.15</v>
+        <v>150.15</v>
       </c>
       <c r="J3" t="s">
         <v>56</v>
@@ -5839,14 +5896,14 @@
         <v>145 - ALMACEN</v>
       </c>
       <c r="S3" s="12">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="T3" s="12">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="U3" s="41">
         <f>+S3/T3</f>
-        <v>7.0422535211267609E-2</v>
+        <v>8.4112149532710276E-2</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
@@ -5860,14 +5917,14 @@
       </c>
       <c r="D4" s="22">
         <f t="shared" si="0"/>
-        <v>0.25550660792951541</v>
+        <v>0.52422907488986781</v>
       </c>
       <c r="E4" s="13">
         <v>126</v>
       </c>
       <c r="F4" s="12">
         <f t="shared" si="1"/>
-        <v>-68</v>
+        <v>-7</v>
       </c>
       <c r="G4" s="13">
         <f>VLOOKUP(B4,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -5875,11 +5932,11 @@
       </c>
       <c r="H4" s="13">
         <f>VLOOKUP(B4,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>58</v>
+        <v>119</v>
       </c>
       <c r="I4" s="17">
         <f t="shared" si="2"/>
-        <v>134.94999999999999</v>
+        <v>73.949999999999989</v>
       </c>
       <c r="J4" t="s">
         <v>57</v>
@@ -5897,14 +5954,14 @@
         <v>145 - Articulos Sin Asociar Agrupacion</v>
       </c>
       <c r="S4" s="13">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T4" s="13">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="U4" s="5">
         <f t="shared" ref="U4:U11" si="3">+S4/T4</f>
-        <v>3.2863849765258218E-2</v>
+        <v>7.0093457943925228E-2</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
@@ -5918,14 +5975,14 @@
       </c>
       <c r="D5" s="22">
         <f t="shared" si="0"/>
-        <v>0.18461538461538463</v>
+        <v>0.41538461538461541</v>
       </c>
       <c r="E5" s="13">
         <v>21</v>
       </c>
       <c r="F5" s="12">
         <f t="shared" si="1"/>
-        <v>-9</v>
+        <v>6</v>
       </c>
       <c r="G5" s="13">
         <f>VLOOKUP(B5,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -5933,11 +5990,11 @@
       </c>
       <c r="H5" s="13">
         <f>VLOOKUP(B5,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="I5" s="17">
         <f t="shared" si="2"/>
-        <v>43.25</v>
+        <v>28.25</v>
       </c>
       <c r="K5" t="s">
         <v>64</v>
@@ -5952,14 +6009,14 @@
         <v>145 - BEBIDAS</v>
       </c>
       <c r="S5" s="13">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="T5" s="13">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="U5" s="5">
         <f t="shared" si="3"/>
-        <v>5.1643192488262914E-2</v>
+        <v>0.13084112149532709</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
@@ -5973,14 +6030,14 @@
       </c>
       <c r="D6" s="22">
         <f t="shared" si="0"/>
-        <v>0.28502415458937197</v>
+        <v>0.50724637681159424</v>
       </c>
       <c r="E6" s="13">
         <v>100</v>
       </c>
       <c r="F6" s="12">
         <f t="shared" si="1"/>
-        <v>-41</v>
+        <v>5</v>
       </c>
       <c r="G6" s="13">
         <f>VLOOKUP(B6,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -5988,11 +6045,11 @@
       </c>
       <c r="H6" s="13">
         <f>VLOOKUP(B6,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>59</v>
+        <v>105</v>
       </c>
       <c r="I6" s="17">
         <f t="shared" si="2"/>
-        <v>116.94999999999999</v>
+        <v>70.949999999999989</v>
       </c>
       <c r="J6" t="s">
         <v>58</v>
@@ -6010,14 +6067,14 @@
         <v>145 - CHOCOLATE</v>
       </c>
       <c r="S6" s="13">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T6" s="13">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="U6" s="5">
         <f t="shared" si="3"/>
-        <v>3.2863849765258218E-2</v>
+        <v>6.0747663551401869E-2</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
@@ -6031,14 +6088,14 @@
       </c>
       <c r="D7" s="22">
         <f t="shared" si="0"/>
-        <v>0.20202020202020202</v>
+        <v>0.32323232323232326</v>
       </c>
       <c r="E7" s="13">
         <v>81</v>
       </c>
       <c r="F7" s="12">
         <f t="shared" si="1"/>
-        <v>-41</v>
+        <v>-17</v>
       </c>
       <c r="G7" s="13">
         <f>VLOOKUP(B7,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6046,11 +6103,11 @@
       </c>
       <c r="H7" s="13">
         <f>VLOOKUP(B7,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="I7" s="17">
         <f t="shared" si="2"/>
-        <v>128.29999999999998</v>
+        <v>104.29999999999998</v>
       </c>
       <c r="J7" t="s">
         <v>58</v>
@@ -6068,14 +6125,14 @@
         <v>145 - GALLETITAS</v>
       </c>
       <c r="S7" s="13">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="T7" s="13">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="U7" s="5">
         <f t="shared" si="3"/>
-        <v>8.9201877934272297E-2</v>
+        <v>0.17289719626168223</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
@@ -6089,26 +6146,26 @@
       </c>
       <c r="D8" s="22">
         <f t="shared" si="0"/>
-        <v>0.22535211267605634</v>
+        <v>0.43457943925233644</v>
       </c>
       <c r="E8" s="13">
         <v>89</v>
       </c>
       <c r="F8" s="12">
         <f t="shared" si="1"/>
-        <v>-41</v>
+        <v>4</v>
       </c>
       <c r="G8" s="13">
         <f>VLOOKUP(B8,'Base Cobertura'!$A:$C,3,FALSE)</f>
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H8" s="13">
         <f>VLOOKUP(B8,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>48</v>
+        <v>93</v>
       </c>
       <c r="I8" s="17">
         <f t="shared" si="2"/>
-        <v>133.04999999999998</v>
+        <v>88.9</v>
       </c>
       <c r="J8" t="s">
         <v>55</v>
@@ -6127,14 +6184,14 @@
         <v>145 - GOLOSINAS</v>
       </c>
       <c r="S8" s="13">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="T8" s="13">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="U8" s="5">
         <f t="shared" si="3"/>
-        <v>8.4507042253521125E-2</v>
+        <v>0.1822429906542056</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
@@ -6148,26 +6205,26 @@
       </c>
       <c r="D9" s="22">
         <f>H9/G9</f>
-        <v>0.21818181818181817</v>
+        <v>0.42603550295857989</v>
       </c>
       <c r="E9" s="13">
         <v>92</v>
       </c>
       <c r="F9" s="12">
         <f t="shared" si="1"/>
-        <v>-56</v>
+        <v>-20</v>
       </c>
       <c r="G9" s="13">
         <f>VLOOKUP(B9,'Base Cobertura'!$A:$C,3,FALSE)</f>
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="H9" s="13">
         <f>VLOOKUP(B9,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="I9" s="17">
         <f t="shared" si="2"/>
-        <v>104.25</v>
+        <v>71.650000000000006</v>
       </c>
       <c r="J9" t="s">
         <v>55</v>
@@ -6185,14 +6242,14 @@
         <v>145 - MASCOTAS</v>
       </c>
       <c r="S9" s="13">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T9" s="13">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="U9" s="5">
         <f t="shared" si="3"/>
-        <v>3.2863849765258218E-2</v>
+        <v>4.2056074766355138E-2</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
@@ -6206,26 +6263,26 @@
       </c>
       <c r="D10" s="22">
         <f t="shared" si="0"/>
-        <v>0.15979381443298968</v>
+        <v>0.3487179487179487</v>
       </c>
       <c r="E10" s="13">
         <v>64</v>
       </c>
       <c r="F10" s="12">
         <f t="shared" si="1"/>
-        <v>-33</v>
+        <v>4</v>
       </c>
       <c r="G10" s="13">
         <f>VLOOKUP(B10,'Base Cobertura'!$A:$C,3,FALSE)</f>
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H10" s="13">
         <f>VLOOKUP(B10,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>31</v>
+        <v>68</v>
       </c>
       <c r="I10" s="17">
         <f t="shared" si="2"/>
-        <v>133.9</v>
+        <v>97.75</v>
       </c>
       <c r="J10" t="s">
         <v>58</v>
@@ -6243,14 +6300,14 @@
         <v>145 - NO PERECEDEROS</v>
       </c>
       <c r="S10" s="13">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T10" s="13">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="U10" s="5">
         <f t="shared" si="3"/>
-        <v>9.3896713615023476E-3</v>
+        <v>2.336448598130841E-2</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
@@ -6264,14 +6321,14 @@
       </c>
       <c r="D11" s="32">
         <f t="shared" si="0"/>
-        <v>7.9207920792079209E-2</v>
+        <v>0.16831683168316833</v>
       </c>
       <c r="E11" s="31">
         <v>19</v>
       </c>
       <c r="F11" s="33">
         <f t="shared" si="1"/>
-        <v>-11</v>
+        <v>-2</v>
       </c>
       <c r="G11" s="13">
         <f>VLOOKUP(B11,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6279,11 +6336,11 @@
       </c>
       <c r="H11" s="13">
         <f>VLOOKUP(B11,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="I11" s="34">
         <f t="shared" si="2"/>
-        <v>77.849999999999994</v>
+        <v>68.849999999999994</v>
       </c>
       <c r="J11" t="s">
         <v>59</v>
@@ -6298,14 +6355,14 @@
         <v>145 - PILAS</v>
       </c>
       <c r="S11" s="13">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T11" s="13">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="U11" s="5">
         <f t="shared" si="3"/>
-        <v>1.4084507042253521E-2</v>
+        <v>2.336448598130841E-2</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
@@ -6319,14 +6376,14 @@
       </c>
       <c r="D12" s="32">
         <f t="shared" si="0"/>
-        <v>7.6190476190476197E-2</v>
+        <v>0.19047619047619047</v>
       </c>
       <c r="E12" s="31">
         <v>24</v>
       </c>
       <c r="F12" s="33">
         <f t="shared" si="1"/>
-        <v>-16</v>
+        <v>-4</v>
       </c>
       <c r="G12" s="13">
         <f>VLOOKUP(B12,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6334,11 +6391,11 @@
       </c>
       <c r="H12" s="13">
         <f>VLOOKUP(B12,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="I12" s="34">
         <f t="shared" si="2"/>
-        <v>81.25</v>
+        <v>69.25</v>
       </c>
       <c r="J12" t="s">
         <v>59</v>
@@ -6355,14 +6412,14 @@
       </c>
       <c r="D13" s="22">
         <f t="shared" si="0"/>
-        <v>0.20384615384615384</v>
+        <v>0.41153846153846152</v>
       </c>
       <c r="E13" s="13">
         <v>144</v>
       </c>
       <c r="F13" s="12">
         <f t="shared" si="1"/>
-        <v>-91</v>
+        <v>-37</v>
       </c>
       <c r="G13" s="13">
         <f>VLOOKUP(B13,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6370,11 +6427,11 @@
       </c>
       <c r="H13" s="13">
         <f>VLOOKUP(B13,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>53</v>
+        <v>107</v>
       </c>
       <c r="I13" s="17">
         <f t="shared" si="2"/>
-        <v>168</v>
+        <v>114</v>
       </c>
       <c r="J13" t="s">
         <v>57</v>
@@ -6394,14 +6451,14 @@
       </c>
       <c r="D14" s="22">
         <f t="shared" si="0"/>
-        <v>0.21978021978021978</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="E14" s="13">
         <v>85</v>
       </c>
       <c r="F14" s="12">
         <f t="shared" si="1"/>
-        <v>-45</v>
+        <v>-15</v>
       </c>
       <c r="G14" s="13">
         <f>VLOOKUP(B14,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6409,11 +6466,11 @@
       </c>
       <c r="H14" s="13">
         <f>VLOOKUP(B14,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="I14" s="17">
         <f t="shared" si="2"/>
-        <v>114.69999999999999</v>
+        <v>84.699999999999989</v>
       </c>
       <c r="J14" t="s">
         <v>55</v>
@@ -6429,15 +6486,15 @@
       <c r="E15" s="14"/>
       <c r="F15" s="16">
         <f>+SUM(F2:F14)</f>
-        <v>-415</v>
+        <v>-27</v>
       </c>
       <c r="G15" s="8">
         <f>+SUM(G2:G14)</f>
-        <v>2228</v>
+        <v>2234</v>
       </c>
       <c r="H15" s="8">
         <f>+SUM(H2:H14)</f>
-        <v>464</v>
+        <v>852</v>
       </c>
       <c r="I15" s="8"/>
     </row>
@@ -6454,14 +6511,14 @@
       </c>
       <c r="D16" s="22">
         <f t="shared" si="0"/>
-        <v>0.29813664596273293</v>
+        <v>0.49689440993788819</v>
       </c>
       <c r="E16" s="13">
         <v>90</v>
       </c>
       <c r="F16" s="12">
         <f t="shared" si="1"/>
-        <v>-42</v>
+        <v>-10</v>
       </c>
       <c r="G16" s="13">
         <f>VLOOKUP(B16,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6469,11 +6526,11 @@
       </c>
       <c r="H16" s="13">
         <f>VLOOKUP(B16,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="I16" s="17">
         <f t="shared" si="2"/>
-        <v>88.85</v>
+        <v>56.849999999999994</v>
       </c>
       <c r="J16" t="s">
         <v>55</v>
@@ -6493,14 +6550,14 @@
       </c>
       <c r="D17" s="22">
         <f t="shared" si="0"/>
-        <v>0.22277227722772278</v>
+        <v>0.33663366336633666</v>
       </c>
       <c r="E17" s="13">
         <v>92</v>
       </c>
       <c r="F17" s="12">
         <f t="shared" si="1"/>
-        <v>-47</v>
+        <v>-24</v>
       </c>
       <c r="G17" s="13">
         <f>VLOOKUP(B17,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6508,11 +6565,11 @@
       </c>
       <c r="H17" s="13">
         <f>VLOOKUP(B17,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="I17" s="17">
         <f t="shared" si="2"/>
-        <v>126.69999999999999</v>
+        <v>103.69999999999999</v>
       </c>
       <c r="J17" t="s">
         <v>55</v>
@@ -6532,14 +6589,14 @@
       </c>
       <c r="D18" s="22">
         <f t="shared" si="0"/>
-        <v>0.3</v>
+        <v>0.53529411764705881</v>
       </c>
       <c r="E18" s="13">
         <v>88</v>
       </c>
       <c r="F18" s="12">
         <f t="shared" si="1"/>
-        <v>-37</v>
+        <v>3</v>
       </c>
       <c r="G18" s="13">
         <f>VLOOKUP(B18,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6547,11 +6604,11 @@
       </c>
       <c r="H18" s="13">
         <f>VLOOKUP(B18,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="I18" s="17">
         <f t="shared" si="2"/>
-        <v>93.5</v>
+        <v>53.5</v>
       </c>
       <c r="J18" t="s">
         <v>58</v>
@@ -6571,14 +6628,14 @@
       </c>
       <c r="D19" s="22">
         <f t="shared" si="0"/>
-        <v>0.33750000000000002</v>
+        <v>0.55625000000000002</v>
       </c>
       <c r="E19" s="13">
         <v>95</v>
       </c>
       <c r="F19" s="12">
         <f t="shared" si="1"/>
-        <v>-41</v>
+        <v>-6</v>
       </c>
       <c r="G19" s="13">
         <f>VLOOKUP(B19,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6586,11 +6643,11 @@
       </c>
       <c r="H19" s="13">
         <f>VLOOKUP(B19,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="I19" s="17">
         <f t="shared" si="2"/>
-        <v>82</v>
+        <v>47</v>
       </c>
       <c r="J19" t="s">
         <v>58</v>
@@ -6610,14 +6667,14 @@
       </c>
       <c r="D20" s="22">
         <f t="shared" si="0"/>
-        <v>0.2824858757062147</v>
+        <v>0.50847457627118642</v>
       </c>
       <c r="E20" s="13">
         <v>83</v>
       </c>
       <c r="F20" s="12">
         <f t="shared" si="1"/>
-        <v>-33</v>
+        <v>7</v>
       </c>
       <c r="G20" s="13">
         <f>VLOOKUP(B20,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6625,11 +6682,11 @@
       </c>
       <c r="H20" s="13">
         <f>VLOOKUP(B20,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="I20" s="17">
         <f t="shared" si="2"/>
-        <v>100.44999999999999</v>
+        <v>60.449999999999989</v>
       </c>
       <c r="J20" t="s">
         <v>55</v>
@@ -6649,14 +6706,14 @@
       </c>
       <c r="D21" s="22">
         <f t="shared" si="0"/>
-        <v>0.30769230769230771</v>
+        <v>0.47928994082840237</v>
       </c>
       <c r="E21" s="13">
         <v>64</v>
       </c>
       <c r="F21" s="12">
         <f t="shared" si="1"/>
-        <v>-12</v>
+        <v>17</v>
       </c>
       <c r="G21" s="13">
         <f>VLOOKUP(B21,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6664,11 +6721,11 @@
       </c>
       <c r="H21" s="13">
         <f>VLOOKUP(B21,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="I21" s="17">
         <f t="shared" si="2"/>
-        <v>91.65</v>
+        <v>62.650000000000006</v>
       </c>
       <c r="J21" t="s">
         <v>58</v>
@@ -6688,14 +6745,14 @@
       </c>
       <c r="D22" s="22">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.20707070707070707</v>
       </c>
       <c r="E22" s="13">
         <v>66</v>
       </c>
       <c r="F22" s="12">
         <f t="shared" si="1"/>
-        <v>-66</v>
+        <v>-25</v>
       </c>
       <c r="G22" s="13">
         <f>VLOOKUP(B22,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6703,11 +6760,11 @@
       </c>
       <c r="H22" s="13">
         <f>VLOOKUP(B22,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="I22" s="17">
         <f t="shared" si="2"/>
-        <v>168.29999999999998</v>
+        <v>127.29999999999998</v>
       </c>
       <c r="J22" t="s">
         <v>58</v>
@@ -6727,14 +6784,14 @@
       </c>
       <c r="D23" s="22">
         <f t="shared" si="0"/>
-        <v>0.20289855072463769</v>
+        <v>0.43478260869565216</v>
       </c>
       <c r="E23" s="13">
         <v>70</v>
       </c>
       <c r="F23" s="12">
         <f t="shared" si="1"/>
-        <v>-42</v>
+        <v>-10</v>
       </c>
       <c r="G23" s="13">
         <f>VLOOKUP(B23,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6742,11 +6799,11 @@
       </c>
       <c r="H23" s="13">
         <f>VLOOKUP(B23,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="I23" s="17">
         <f t="shared" si="2"/>
-        <v>89.3</v>
+        <v>57.3</v>
       </c>
       <c r="J23" t="s">
         <v>58</v>
@@ -6766,14 +6823,14 @@
       </c>
       <c r="D24" s="22">
         <f t="shared" si="0"/>
-        <v>0.22941176470588234</v>
+        <v>0.48823529411764705</v>
       </c>
       <c r="E24" s="13">
         <v>79</v>
       </c>
       <c r="F24" s="12">
         <f t="shared" si="1"/>
-        <v>-40</v>
+        <v>4</v>
       </c>
       <c r="G24" s="13">
         <f>VLOOKUP(B24,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6781,11 +6838,11 @@
       </c>
       <c r="H24" s="13">
         <f>VLOOKUP(B24,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>39</v>
+        <v>83</v>
       </c>
       <c r="I24" s="17">
         <f t="shared" si="2"/>
-        <v>105.5</v>
+        <v>61.5</v>
       </c>
       <c r="J24" t="s">
         <v>60</v>
@@ -6801,7 +6858,7 @@
       <c r="E25" s="14"/>
       <c r="F25" s="16">
         <f>+SUM(F16:F24)</f>
-        <v>-360</v>
+        <v>-44</v>
       </c>
       <c r="G25" s="8">
         <f>+SUM(G16:G24)</f>
@@ -6809,7 +6866,7 @@
       </c>
       <c r="H25" s="8">
         <f>+SUM(H16:H24)</f>
-        <v>367</v>
+        <v>683</v>
       </c>
       <c r="I25" s="8"/>
     </row>
@@ -6826,14 +6883,14 @@
       </c>
       <c r="D26" s="22">
         <f t="shared" si="0"/>
-        <v>0.14285714285714285</v>
+        <v>0.30357142857142855</v>
       </c>
       <c r="E26" s="13">
         <v>20</v>
       </c>
       <c r="F26" s="12">
         <f>+H26-E26</f>
-        <v>-12</v>
+        <v>-3</v>
       </c>
       <c r="G26" s="13">
         <f>VLOOKUP(B26,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6841,11 +6898,11 @@
       </c>
       <c r="H26" s="13">
         <f>VLOOKUP(B26,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="I26" s="17">
         <f t="shared" si="2"/>
-        <v>39.6</v>
+        <v>30.6</v>
       </c>
       <c r="J26" t="s">
         <v>55</v>
@@ -6865,14 +6922,14 @@
       </c>
       <c r="D27" s="22">
         <f t="shared" si="0"/>
-        <v>0.21153846153846154</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="E27" s="13">
         <v>68</v>
       </c>
       <c r="F27" s="12">
         <f t="shared" si="1"/>
-        <v>-35</v>
+        <v>-3</v>
       </c>
       <c r="G27" s="13">
         <f>VLOOKUP(B27,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6880,11 +6937,11 @@
       </c>
       <c r="H27" s="13">
         <f>VLOOKUP(B27,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="I27" s="17">
         <f t="shared" si="2"/>
-        <v>99.6</v>
+        <v>67.599999999999994</v>
       </c>
       <c r="J27" t="s">
         <v>58</v>
@@ -6904,14 +6961,14 @@
       </c>
       <c r="D28" s="22">
         <f t="shared" si="0"/>
-        <v>0.21739130434782608</v>
+        <v>0.36645962732919257</v>
       </c>
       <c r="E28" s="13">
         <v>80</v>
       </c>
       <c r="F28" s="12">
         <f t="shared" si="1"/>
-        <v>-45</v>
+        <v>-21</v>
       </c>
       <c r="G28" s="13">
         <f>VLOOKUP(B28,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6919,11 +6976,11 @@
       </c>
       <c r="H28" s="13">
         <f>VLOOKUP(B28,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="I28" s="17">
         <f t="shared" si="2"/>
-        <v>101.85</v>
+        <v>77.849999999999994</v>
       </c>
       <c r="J28" t="s">
         <v>58</v>
@@ -6943,14 +7000,14 @@
       </c>
       <c r="D29" s="22">
         <f t="shared" si="0"/>
-        <v>0.10441767068273092</v>
+        <v>0.20481927710843373</v>
       </c>
       <c r="E29" s="13">
         <v>68</v>
       </c>
       <c r="F29" s="12">
         <f t="shared" si="1"/>
-        <v>-42</v>
+        <v>-17</v>
       </c>
       <c r="G29" s="13">
         <f>VLOOKUP(B29,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6958,11 +7015,11 @@
       </c>
       <c r="H29" s="13">
         <f>VLOOKUP(B29,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="I29" s="17">
         <f t="shared" si="2"/>
-        <v>185.65</v>
+        <v>160.65</v>
       </c>
       <c r="J29" t="s">
         <v>58</v>
@@ -6982,14 +7039,14 @@
       </c>
       <c r="D30" s="22">
         <f t="shared" si="0"/>
-        <v>0.23571428571428571</v>
+        <v>0.51428571428571423</v>
       </c>
       <c r="E30" s="13">
         <v>73</v>
       </c>
       <c r="F30" s="12">
         <f t="shared" si="1"/>
-        <v>-40</v>
+        <v>-1</v>
       </c>
       <c r="G30" s="13">
         <f>VLOOKUP(B30,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6997,11 +7054,11 @@
       </c>
       <c r="H30" s="13">
         <f>VLOOKUP(B30,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="I30" s="17">
         <f t="shared" si="2"/>
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="J30" t="s">
         <v>55</v>
@@ -7021,14 +7078,14 @@
       </c>
       <c r="D31" s="22">
         <f t="shared" si="0"/>
-        <v>0.17679558011049723</v>
+        <v>0.2983425414364641</v>
       </c>
       <c r="E31" s="13">
         <v>40</v>
       </c>
       <c r="F31" s="12">
         <f t="shared" si="1"/>
-        <v>-8</v>
+        <v>14</v>
       </c>
       <c r="G31" s="13">
         <f>VLOOKUP(B31,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7036,11 +7093,11 @@
       </c>
       <c r="H31" s="13">
         <f>VLOOKUP(B31,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="I31" s="17">
         <f t="shared" si="2"/>
-        <v>121.85</v>
+        <v>99.85</v>
       </c>
       <c r="J31" t="s">
         <v>58</v>
@@ -7060,14 +7117,14 @@
       </c>
       <c r="D32" s="22">
         <f t="shared" si="0"/>
-        <v>0.21428571428571427</v>
+        <v>0.35119047619047616</v>
       </c>
       <c r="E32" s="13">
         <v>67</v>
       </c>
       <c r="F32" s="12">
         <f t="shared" si="1"/>
-        <v>-31</v>
+        <v>-8</v>
       </c>
       <c r="G32" s="13">
         <f>VLOOKUP(B32,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7075,11 +7132,11 @@
       </c>
       <c r="H32" s="13">
         <f>VLOOKUP(B32,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I32" s="17">
         <f t="shared" si="2"/>
-        <v>106.79999999999998</v>
+        <v>83.799999999999983</v>
       </c>
       <c r="J32" t="s">
         <v>58</v>
@@ -7099,14 +7156,14 @@
       </c>
       <c r="D33" s="22">
         <f t="shared" si="0"/>
-        <v>0.23837209302325582</v>
+        <v>0.39534883720930231</v>
       </c>
       <c r="E33" s="13">
         <v>66</v>
       </c>
       <c r="F33" s="12">
         <f t="shared" si="1"/>
-        <v>-25</v>
+        <v>2</v>
       </c>
       <c r="G33" s="13">
         <f>VLOOKUP(B33,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7114,11 +7171,11 @@
       </c>
       <c r="H33" s="13">
         <f>VLOOKUP(B33,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="I33" s="17">
         <f t="shared" si="2"/>
-        <v>105.19999999999999</v>
+        <v>78.199999999999989</v>
       </c>
       <c r="J33" t="s">
         <v>58</v>
@@ -7138,26 +7195,26 @@
       </c>
       <c r="D34" s="22">
         <f t="shared" si="0"/>
-        <v>9.2198581560283682E-2</v>
+        <v>0.19718309859154928</v>
       </c>
       <c r="E34" s="13">
         <v>82</v>
       </c>
       <c r="F34" s="12">
         <f t="shared" si="1"/>
-        <v>-69</v>
+        <v>-54</v>
       </c>
       <c r="G34" s="13">
         <f>VLOOKUP(B34,'Base Cobertura'!$A:$C,3,FALSE)</f>
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H34" s="13">
         <f>VLOOKUP(B34,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="I34" s="17">
         <f t="shared" si="2"/>
-        <v>106.85</v>
+        <v>92.7</v>
       </c>
       <c r="J34" t="s">
         <v>55</v>
@@ -7177,14 +7234,14 @@
       </c>
       <c r="D35" s="22">
         <f t="shared" si="0"/>
-        <v>0.17415730337078653</v>
+        <v>0.398876404494382</v>
       </c>
       <c r="E35" s="13">
         <v>81</v>
       </c>
       <c r="F35" s="12">
         <f t="shared" si="1"/>
-        <v>-50</v>
+        <v>-10</v>
       </c>
       <c r="G35" s="13">
         <f>VLOOKUP(B35,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7192,11 +7249,11 @@
       </c>
       <c r="H35" s="13">
         <f>VLOOKUP(B35,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>31</v>
+        <v>71</v>
       </c>
       <c r="I35" s="17">
         <f t="shared" si="2"/>
-        <v>120.29999999999998</v>
+        <v>80.299999999999983</v>
       </c>
       <c r="J35" t="s">
         <v>58</v>
@@ -7216,14 +7273,14 @@
       </c>
       <c r="D36" s="22">
         <f t="shared" si="0"/>
-        <v>8.8495575221238937E-3</v>
+        <v>2.6548672566371681E-2</v>
       </c>
       <c r="E36" s="13">
         <v>0</v>
       </c>
       <c r="F36" s="12">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G36" s="13">
         <f>VLOOKUP(B36,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7231,11 +7288,11 @@
       </c>
       <c r="H36" s="13">
         <f>VLOOKUP(B36,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I36" s="17">
         <f t="shared" si="2"/>
-        <v>95.05</v>
+        <v>93.05</v>
       </c>
       <c r="J36" t="s">
         <v>58</v>
@@ -7252,26 +7309,26 @@
       </c>
       <c r="D37" s="22">
         <f t="shared" si="0"/>
-        <v>9.7087378640776691E-3</v>
+        <v>3.8461538461538464E-2</v>
       </c>
       <c r="E37" s="13">
         <v>17</v>
       </c>
       <c r="F37" s="12">
         <f t="shared" si="1"/>
-        <v>-16</v>
+        <v>-13</v>
       </c>
       <c r="G37" s="13">
         <f>VLOOKUP(B37,'Base Cobertura'!$A:$C,3,FALSE)</f>
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H37" s="13">
         <f>VLOOKUP(B37,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I37" s="17">
         <f t="shared" si="2"/>
-        <v>86.55</v>
+        <v>84.399999999999991</v>
       </c>
       <c r="J37" t="s">
         <v>59</v>
@@ -7288,14 +7345,14 @@
       </c>
       <c r="D38" s="22">
         <f t="shared" si="0"/>
-        <v>0.29133858267716534</v>
+        <v>0.47244094488188976</v>
       </c>
       <c r="E38" s="13">
         <v>60</v>
       </c>
       <c r="F38" s="12">
         <f t="shared" si="1"/>
-        <v>-23</v>
+        <v>0</v>
       </c>
       <c r="G38" s="13">
         <f>VLOOKUP(B38,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7303,11 +7360,11 @@
       </c>
       <c r="H38" s="13">
         <f>VLOOKUP(B38,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="I38" s="17">
         <f t="shared" si="2"/>
-        <v>70.95</v>
+        <v>47.95</v>
       </c>
       <c r="J38" t="s">
         <v>55</v>
@@ -7323,15 +7380,15 @@
       <c r="E39" s="14"/>
       <c r="F39" s="8">
         <f>+SUM(F26:F38)</f>
-        <v>-395</v>
+        <v>-111</v>
       </c>
       <c r="G39" s="8">
         <f>+SUM(G26:G38)</f>
-        <v>1945</v>
+        <v>1947</v>
       </c>
       <c r="H39" s="8">
         <f>+SUM(H26:H38)</f>
-        <v>327</v>
+        <v>611</v>
       </c>
       <c r="I39" s="8"/>
       <c r="L39" t="s">
@@ -7347,20 +7404,20 @@
       <c r="E40" s="6"/>
       <c r="F40" s="8">
         <f>+SUM(F39+F25+F15)</f>
-        <v>-1170</v>
+        <v>-182</v>
       </c>
       <c r="G40" s="8">
         <f>+G15+G25+G39</f>
-        <v>5718</v>
+        <v>5726</v>
       </c>
       <c r="H40" s="8">
         <f>+H15+H25+H39</f>
-        <v>1158</v>
+        <v>2146</v>
       </c>
       <c r="I40" s="8"/>
       <c r="L40" s="1">
         <f>+H40/G40</f>
-        <v>0.20251836306400839</v>
+        <v>0.37478169752008383</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
@@ -7405,26 +7462,26 @@
       </c>
       <c r="D42" s="22">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8.3333333333333332E-3</v>
       </c>
       <c r="E42" s="13">
         <v>60</v>
       </c>
       <c r="F42" s="12">
         <f t="shared" si="5"/>
-        <v>-60</v>
+        <v>-59</v>
       </c>
       <c r="G42" s="13">
         <f>VLOOKUP(B42,'Base Cobertura'!$A:$C,3,FALSE)</f>
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H42" s="13">
         <f>VLOOKUP(B42,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42" s="17">
         <f t="shared" si="6"/>
-        <v>101.14999999999999</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -7998,7 +8055,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B3" s="51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="51">
         <v>3408</v>
@@ -8006,7 +8063,9 @@
       <c r="G3" t="s">
         <v>222</v>
       </c>
-      <c r="H3" s="51"/>
+      <c r="H3" s="51">
+        <v>1</v>
+      </c>
       <c r="I3" s="51">
         <v>3408</v>
       </c>
@@ -8016,13 +8075,16 @@
         <v>1</v>
       </c>
       <c r="B4" s="51">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="C4" s="51">
         <v>127</v>
       </c>
       <c r="G4" t="s">
         <v>223</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
       </c>
       <c r="I4" s="51">
         <v>3408</v>
@@ -8033,7 +8095,7 @@
         <v>10</v>
       </c>
       <c r="B5" s="51">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="C5" s="51">
         <v>181</v>
@@ -8051,10 +8113,10 @@
         <v>100</v>
       </c>
       <c r="B6" s="51">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C6" s="51">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G6" t="s">
         <v>225</v>
@@ -8069,15 +8131,17 @@
         <v>11</v>
       </c>
       <c r="B7" s="51">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="C7" s="51">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="G7" t="s">
         <v>226</v>
       </c>
-      <c r="H7" s="51"/>
+      <c r="H7" s="51">
+        <v>1</v>
+      </c>
       <c r="I7" s="51">
         <v>3408</v>
       </c>
@@ -8087,10 +8151,10 @@
         <v>12</v>
       </c>
       <c r="B8" s="51">
-        <v>48</v>
+        <v>93</v>
       </c>
       <c r="C8" s="51">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G8" t="s">
         <v>227</v>
@@ -8107,7 +8171,7 @@
         <v>123</v>
       </c>
       <c r="B9" s="51">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C9" s="51">
         <v>489</v>
@@ -8115,7 +8179,9 @@
       <c r="G9" t="s">
         <v>228</v>
       </c>
-      <c r="H9" s="51"/>
+      <c r="H9" s="51">
+        <v>1</v>
+      </c>
       <c r="I9" s="51">
         <v>3408</v>
       </c>
@@ -8125,13 +8191,16 @@
         <v>15</v>
       </c>
       <c r="B10" s="51">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="C10" s="51">
         <v>65</v>
       </c>
       <c r="G10" t="s">
         <v>229</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
       </c>
       <c r="I10" s="51">
         <v>3408</v>
@@ -8142,7 +8211,7 @@
         <v>16</v>
       </c>
       <c r="B11" s="51">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="C11" s="51">
         <v>198</v>
@@ -8160,7 +8229,7 @@
         <v>18</v>
       </c>
       <c r="B12" s="51">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="C12" s="51">
         <v>177</v>
@@ -8176,7 +8245,7 @@
         <v>222</v>
       </c>
       <c r="H12">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="I12" s="51">
         <v>127</v>
@@ -8187,7 +8256,7 @@
         <v>19</v>
       </c>
       <c r="B13" s="51">
-        <v>59</v>
+        <v>105</v>
       </c>
       <c r="C13" s="51">
         <v>207</v>
@@ -8200,7 +8269,7 @@
         <v>223</v>
       </c>
       <c r="H13" s="51">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="I13" s="51">
         <v>127</v>
@@ -8211,7 +8280,7 @@
         <v>2</v>
       </c>
       <c r="B14" s="51">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="C14" s="51">
         <v>138</v>
@@ -8224,7 +8293,7 @@
         <v>224</v>
       </c>
       <c r="H14" s="51">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="I14" s="51">
         <v>127</v>
@@ -8235,7 +8304,7 @@
         <v>20</v>
       </c>
       <c r="B15" s="51">
-        <v>58</v>
+        <v>119</v>
       </c>
       <c r="C15" s="51">
         <v>227</v>
@@ -8248,7 +8317,7 @@
         <v>225</v>
       </c>
       <c r="H15" s="51">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="I15" s="51">
         <v>127</v>
@@ -8259,7 +8328,7 @@
         <v>21</v>
       </c>
       <c r="B16" s="51">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="C16" s="51">
         <v>170</v>
@@ -8272,7 +8341,7 @@
         <v>226</v>
       </c>
       <c r="H16" s="51">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="I16" s="51">
         <v>127</v>
@@ -8283,7 +8352,7 @@
         <v>22</v>
       </c>
       <c r="B17" s="51">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="C17" s="51">
         <v>72</v>
@@ -8296,7 +8365,7 @@
         <v>227</v>
       </c>
       <c r="H17" s="51">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="I17" s="51">
         <v>127</v>
@@ -8307,7 +8376,7 @@
         <v>23</v>
       </c>
       <c r="B18" s="51">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="C18" s="51">
         <v>160</v>
@@ -8320,7 +8389,7 @@
         <v>228</v>
       </c>
       <c r="H18" s="51">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I18" s="51">
         <v>127</v>
@@ -8331,7 +8400,7 @@
         <v>24</v>
       </c>
       <c r="B19" s="51">
-        <v>31</v>
+        <v>71</v>
       </c>
       <c r="C19" s="51">
         <v>178</v>
@@ -8344,7 +8413,7 @@
         <v>229</v>
       </c>
       <c r="H19" s="51">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I19" s="51">
         <v>127</v>
@@ -8355,7 +8424,7 @@
         <v>25</v>
       </c>
       <c r="B20" s="51">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="C20" s="51">
         <v>172</v>
@@ -8368,7 +8437,7 @@
         <v>230</v>
       </c>
       <c r="H20">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I20" s="51">
         <v>127</v>
@@ -8379,10 +8448,10 @@
         <v>26</v>
       </c>
       <c r="B21" s="51">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C21" s="51">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E21">
         <f>+$F$21</f>
@@ -8395,7 +8464,7 @@
         <v>222</v>
       </c>
       <c r="H21" s="51">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I21" s="51">
         <v>181</v>
@@ -8406,7 +8475,7 @@
         <v>27</v>
       </c>
       <c r="B22" s="51">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="C22" s="51">
         <v>140</v>
@@ -8430,7 +8499,7 @@
         <v>28</v>
       </c>
       <c r="B23" s="51">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C23" s="51">
         <v>168</v>
@@ -8443,7 +8512,7 @@
         <v>224</v>
       </c>
       <c r="H23" s="51">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="I23" s="51">
         <v>181</v>
@@ -8454,7 +8523,7 @@
         <v>3</v>
       </c>
       <c r="B24" s="51">
-        <v>39</v>
+        <v>83</v>
       </c>
       <c r="C24" s="51">
         <v>170</v>
@@ -8467,7 +8536,7 @@
         <v>225</v>
       </c>
       <c r="H24" s="51">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I24" s="51">
         <v>181</v>
@@ -8478,10 +8547,10 @@
         <v>30</v>
       </c>
       <c r="B25" s="51">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C25" s="51">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E25">
         <f t="shared" si="1"/>
@@ -8491,7 +8560,7 @@
         <v>226</v>
       </c>
       <c r="H25" s="51">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="I25" s="51">
         <v>181</v>
@@ -8502,7 +8571,7 @@
         <v>31</v>
       </c>
       <c r="B26" s="51">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="C26" s="51">
         <v>161</v>
@@ -8515,7 +8584,7 @@
         <v>227</v>
       </c>
       <c r="H26" s="51">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I26" s="51">
         <v>181</v>
@@ -8526,7 +8595,7 @@
         <v>32</v>
       </c>
       <c r="B27" s="51">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C27" s="51">
         <v>56</v>
@@ -8539,7 +8608,7 @@
         <v>228</v>
       </c>
       <c r="H27" s="51">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I27" s="51">
         <v>181</v>
@@ -8550,7 +8619,7 @@
         <v>33</v>
       </c>
       <c r="B28" s="51">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="C28" s="51">
         <v>172</v>
@@ -8563,7 +8632,7 @@
         <v>229</v>
       </c>
       <c r="H28" s="51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I28" s="51">
         <v>181</v>
@@ -8574,7 +8643,7 @@
         <v>36</v>
       </c>
       <c r="B29" s="51">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="C29" s="51">
         <v>156</v>
@@ -8586,7 +8655,9 @@
       <c r="G29" t="s">
         <v>230</v>
       </c>
-      <c r="H29" s="51"/>
+      <c r="H29" s="51">
+        <v>3</v>
+      </c>
       <c r="I29" s="51">
         <v>181</v>
       </c>
@@ -8596,10 +8667,10 @@
         <v>37</v>
       </c>
       <c r="B30" s="51">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C30" s="51">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E30">
         <f>+$F$30</f>
@@ -8612,10 +8683,10 @@
         <v>222</v>
       </c>
       <c r="H30" s="51">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I30" s="51">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
@@ -8623,7 +8694,7 @@
         <v>4</v>
       </c>
       <c r="B31" s="51">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="C31" s="51">
         <v>182</v>
@@ -8636,10 +8707,10 @@
         <v>223</v>
       </c>
       <c r="H31" s="51">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I31" s="51">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
@@ -8647,7 +8718,7 @@
         <v>40</v>
       </c>
       <c r="B32" s="51">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="C32" s="51">
         <v>249</v>
@@ -8660,17 +8731,19 @@
         <v>224</v>
       </c>
       <c r="H32" s="51">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I32" s="51">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>42</v>
       </c>
-      <c r="B33" s="51"/>
+      <c r="B33" s="51">
+        <v>4</v>
+      </c>
       <c r="C33" s="51">
         <v>52</v>
       </c>
@@ -8682,10 +8755,10 @@
         <v>225</v>
       </c>
       <c r="H33" s="51">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I33" s="51">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
@@ -8704,10 +8777,10 @@
         <v>226</v>
       </c>
       <c r="H34" s="51">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I34" s="51">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
@@ -8715,7 +8788,7 @@
         <v>44</v>
       </c>
       <c r="B35" s="51">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="C35" s="51">
         <v>169</v>
@@ -8728,10 +8801,10 @@
         <v>227</v>
       </c>
       <c r="H35" s="51">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I35" s="51">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
@@ -8739,7 +8812,7 @@
         <v>49</v>
       </c>
       <c r="B36" s="51">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C36" s="51">
         <v>239</v>
@@ -8752,10 +8825,10 @@
         <v>228</v>
       </c>
       <c r="H36" s="51">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I36" s="51">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
@@ -8763,7 +8836,7 @@
         <v>5</v>
       </c>
       <c r="B37" s="51">
-        <v>53</v>
+        <v>107</v>
       </c>
       <c r="C37" s="51">
         <v>260</v>
@@ -8776,10 +8849,10 @@
         <v>229</v>
       </c>
       <c r="H37" s="51">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I37" s="51">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
@@ -8787,7 +8860,7 @@
         <v>52</v>
       </c>
       <c r="B38" s="51">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C38" s="51">
         <v>101</v>
@@ -8801,7 +8874,7 @@
       </c>
       <c r="H38" s="51"/>
       <c r="I38" s="51">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
@@ -8809,7 +8882,7 @@
         <v>53</v>
       </c>
       <c r="B39" s="51">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C39" s="51">
         <v>105</v>
@@ -8825,10 +8898,10 @@
         <v>222</v>
       </c>
       <c r="H39" s="51">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I39" s="51">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
@@ -8836,7 +8909,7 @@
         <v>54</v>
       </c>
       <c r="B40" s="51">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="C40" s="51">
         <v>202</v>
@@ -8848,15 +8921,20 @@
       <c r="G40" t="s">
         <v>223</v>
       </c>
-      <c r="H40" s="51"/>
+      <c r="H40" s="51">
+        <v>8</v>
+      </c>
       <c r="I40" s="51">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>56</v>
       </c>
+      <c r="B41">
+        <v>41</v>
+      </c>
       <c r="C41" s="51">
         <v>198</v>
       </c>
@@ -8868,10 +8946,10 @@
         <v>224</v>
       </c>
       <c r="H41" s="51">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="I41" s="51">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
@@ -8879,10 +8957,10 @@
         <v>57</v>
       </c>
       <c r="B42" s="51">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C42" s="51">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E42">
         <f t="shared" si="3"/>
@@ -8892,10 +8970,10 @@
         <v>225</v>
       </c>
       <c r="H42" s="51">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="I42" s="51">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
@@ -8914,19 +8992,21 @@
         <v>226</v>
       </c>
       <c r="H43" s="51">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="I43" s="51">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>59</v>
       </c>
-      <c r="B44" s="51"/>
+      <c r="B44" s="51">
+        <v>1</v>
+      </c>
       <c r="C44" s="51">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E44">
         <f t="shared" si="3"/>
@@ -8936,10 +9016,10 @@
         <v>227</v>
       </c>
       <c r="H44" s="51">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="I44" s="51">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
@@ -8947,7 +9027,7 @@
         <v>7</v>
       </c>
       <c r="B45" s="51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C45" s="51">
         <v>113</v>
@@ -8960,10 +9040,10 @@
         <v>228</v>
       </c>
       <c r="H45" s="51">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I45" s="51">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
@@ -8971,10 +9051,10 @@
         <v>8</v>
       </c>
       <c r="B46" s="51">
-        <v>31</v>
+        <v>68</v>
       </c>
       <c r="C46" s="51">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E46">
         <f t="shared" si="3"/>
@@ -8984,10 +9064,10 @@
         <v>229</v>
       </c>
       <c r="H46" s="51">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I46" s="51">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
@@ -8995,7 +9075,7 @@
         <v>9</v>
       </c>
       <c r="B47" s="51">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="C47" s="51">
         <v>161</v>
@@ -9008,10 +9088,10 @@
         <v>230</v>
       </c>
       <c r="H47" s="51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I47" s="51">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
@@ -9028,10 +9108,10 @@
         <v>222</v>
       </c>
       <c r="H48" s="51">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I48" s="51">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="49" spans="2:9" x14ac:dyDescent="0.25">
@@ -9045,10 +9125,10 @@
         <v>223</v>
       </c>
       <c r="H49" s="51">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="I49" s="51">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="50" spans="2:9" x14ac:dyDescent="0.25">
@@ -9060,10 +9140,10 @@
         <v>224</v>
       </c>
       <c r="H50" s="51">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="I50" s="51">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="51" spans="2:9" x14ac:dyDescent="0.25">
@@ -9075,10 +9155,10 @@
         <v>225</v>
       </c>
       <c r="H51" s="51">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I51" s="51">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.25">
@@ -9090,10 +9170,10 @@
         <v>226</v>
       </c>
       <c r="H52" s="51">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="I52" s="51">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.25">
@@ -9105,10 +9185,10 @@
         <v>227</v>
       </c>
       <c r="H53" s="51">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="I53" s="51">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.25">
@@ -9120,10 +9200,10 @@
         <v>228</v>
       </c>
       <c r="H54" s="51">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I54" s="51">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.25">
@@ -9135,10 +9215,10 @@
         <v>229</v>
       </c>
       <c r="H55" s="51">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I55" s="51">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.25">
@@ -9150,10 +9230,10 @@
         <v>230</v>
       </c>
       <c r="H56" s="51">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I56" s="51">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="57" spans="2:9" x14ac:dyDescent="0.25">
@@ -9168,7 +9248,7 @@
         <v>222</v>
       </c>
       <c r="H57" s="51">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I57" s="51">
         <v>489</v>
@@ -9183,7 +9263,7 @@
         <v>223</v>
       </c>
       <c r="H58" s="51">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I58" s="51">
         <v>489</v>
@@ -9198,7 +9278,7 @@
         <v>224</v>
       </c>
       <c r="H59" s="51">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I59" s="51">
         <v>489</v>
@@ -9212,7 +9292,9 @@
       <c r="G60" t="s">
         <v>225</v>
       </c>
-      <c r="H60" s="51"/>
+      <c r="H60" s="51">
+        <v>1</v>
+      </c>
       <c r="I60" s="51">
         <v>489</v>
       </c>
@@ -9226,7 +9308,7 @@
         <v>226</v>
       </c>
       <c r="H61" s="51">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I61" s="51">
         <v>489</v>
@@ -9254,7 +9336,7 @@
         <v>228</v>
       </c>
       <c r="H63" s="51">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I63" s="51">
         <v>489</v>
@@ -9268,7 +9350,9 @@
       <c r="G64" t="s">
         <v>229</v>
       </c>
-      <c r="H64" s="51"/>
+      <c r="H64" s="51">
+        <v>2</v>
+      </c>
       <c r="I64" s="51">
         <v>489</v>
       </c>
@@ -9298,7 +9382,7 @@
         <v>222</v>
       </c>
       <c r="H66" s="51">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I66" s="51">
         <v>65</v>
@@ -9313,7 +9397,7 @@
         <v>223</v>
       </c>
       <c r="H67" s="51">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I67" s="51">
         <v>65</v>
@@ -9328,7 +9412,7 @@
         <v>224</v>
       </c>
       <c r="H68" s="51">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I68" s="51">
         <v>65</v>
@@ -9343,7 +9427,7 @@
         <v>225</v>
       </c>
       <c r="H69" s="51">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I69" s="51">
         <v>65</v>
@@ -9358,7 +9442,7 @@
         <v>226</v>
       </c>
       <c r="H70" s="51">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I70" s="51">
         <v>65</v>
@@ -9373,7 +9457,7 @@
         <v>227</v>
       </c>
       <c r="H71" s="51">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I71" s="51">
         <v>65</v>
@@ -9388,7 +9472,7 @@
         <v>228</v>
       </c>
       <c r="H72" s="51">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I72" s="51">
         <v>65</v>
@@ -9403,7 +9487,7 @@
         <v>229</v>
       </c>
       <c r="H73" s="51">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I73" s="51">
         <v>65</v>
@@ -9436,7 +9520,7 @@
         <v>222</v>
       </c>
       <c r="H75" s="51">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I75" s="51">
         <v>198</v>
@@ -9451,7 +9535,7 @@
         <v>223</v>
       </c>
       <c r="H76">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I76" s="51">
         <v>198</v>
@@ -9466,7 +9550,7 @@
         <v>224</v>
       </c>
       <c r="H77" s="51">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="I77" s="51">
         <v>198</v>
@@ -9481,7 +9565,7 @@
         <v>225</v>
       </c>
       <c r="H78" s="51">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="I78" s="51">
         <v>198</v>
@@ -9496,7 +9580,7 @@
         <v>226</v>
       </c>
       <c r="H79" s="51">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="I79" s="51">
         <v>198</v>
@@ -9511,7 +9595,7 @@
         <v>227</v>
       </c>
       <c r="H80" s="51">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="I80" s="51">
         <v>198</v>
@@ -9526,7 +9610,7 @@
         <v>228</v>
       </c>
       <c r="H81" s="51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I81" s="51">
         <v>198</v>
@@ -9541,7 +9625,7 @@
         <v>229</v>
       </c>
       <c r="H82" s="51">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I82" s="51">
         <v>198</v>
@@ -9556,7 +9640,7 @@
         <v>230</v>
       </c>
       <c r="H83" s="51">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I83" s="51">
         <v>198</v>
@@ -9574,7 +9658,7 @@
         <v>222</v>
       </c>
       <c r="H84" s="51">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="I84" s="51">
         <v>177</v>
@@ -9589,7 +9673,7 @@
         <v>223</v>
       </c>
       <c r="H85" s="51">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="I85" s="51">
         <v>177</v>
@@ -9604,7 +9688,7 @@
         <v>224</v>
       </c>
       <c r="H86" s="51">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="I86" s="51">
         <v>177</v>
@@ -9619,7 +9703,7 @@
         <v>225</v>
       </c>
       <c r="H87" s="51">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I87" s="51">
         <v>177</v>
@@ -9634,7 +9718,7 @@
         <v>226</v>
       </c>
       <c r="H88" s="51">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I88" s="51">
         <v>177</v>
@@ -9649,7 +9733,7 @@
         <v>227</v>
       </c>
       <c r="H89" s="51">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="I89" s="51">
         <v>177</v>
@@ -9664,7 +9748,7 @@
         <v>228</v>
       </c>
       <c r="H90" s="51">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I90" s="51">
         <v>177</v>
@@ -9679,7 +9763,7 @@
         <v>229</v>
       </c>
       <c r="H91" s="51">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I91" s="51">
         <v>177</v>
@@ -9694,7 +9778,7 @@
         <v>230</v>
       </c>
       <c r="H92" s="51">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="I92" s="51">
         <v>177</v>
@@ -9712,7 +9796,7 @@
         <v>222</v>
       </c>
       <c r="H93" s="51">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="I93" s="51">
         <v>207</v>
@@ -9727,7 +9811,7 @@
         <v>223</v>
       </c>
       <c r="H94" s="51">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I94" s="51">
         <v>207</v>
@@ -9742,7 +9826,7 @@
         <v>224</v>
       </c>
       <c r="H95" s="51">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="I95" s="51">
         <v>207</v>
@@ -9757,7 +9841,7 @@
         <v>225</v>
       </c>
       <c r="H96" s="51">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="I96" s="51">
         <v>207</v>
@@ -9772,7 +9856,7 @@
         <v>226</v>
       </c>
       <c r="H97" s="51">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="I97" s="51">
         <v>207</v>
@@ -9787,7 +9871,7 @@
         <v>227</v>
       </c>
       <c r="H98" s="51">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="I98" s="51">
         <v>207</v>
@@ -9801,7 +9885,9 @@
       <c r="G99" t="s">
         <v>228</v>
       </c>
-      <c r="H99" s="51"/>
+      <c r="H99" s="51">
+        <v>6</v>
+      </c>
       <c r="I99" s="51">
         <v>207</v>
       </c>
@@ -9815,7 +9901,7 @@
         <v>229</v>
       </c>
       <c r="H100" s="51">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I100" s="51">
         <v>207</v>
@@ -9830,7 +9916,7 @@
         <v>230</v>
       </c>
       <c r="H101" s="51">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I101" s="51">
         <v>207</v>
@@ -9848,7 +9934,7 @@
         <v>222</v>
       </c>
       <c r="H102" s="51">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I102" s="51">
         <v>138</v>
@@ -9863,7 +9949,7 @@
         <v>223</v>
       </c>
       <c r="H103" s="51">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="I103" s="51">
         <v>138</v>
@@ -9878,7 +9964,7 @@
         <v>224</v>
       </c>
       <c r="H104" s="51">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I104" s="51">
         <v>138</v>
@@ -9893,7 +9979,7 @@
         <v>225</v>
       </c>
       <c r="H105" s="51">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I105" s="51">
         <v>138</v>
@@ -9908,7 +9994,7 @@
         <v>226</v>
       </c>
       <c r="H106" s="51">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="I106" s="51">
         <v>138</v>
@@ -9923,7 +10009,7 @@
         <v>227</v>
       </c>
       <c r="H107" s="51">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="I107" s="51">
         <v>138</v>
@@ -9953,7 +10039,7 @@
         <v>229</v>
       </c>
       <c r="H109" s="51">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I109" s="51">
         <v>138</v>
@@ -9968,7 +10054,7 @@
         <v>230</v>
       </c>
       <c r="H110" s="51">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I110" s="51">
         <v>138</v>
@@ -9986,7 +10072,7 @@
         <v>222</v>
       </c>
       <c r="H111" s="51">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="I111" s="51">
         <v>227</v>
@@ -10001,7 +10087,7 @@
         <v>223</v>
       </c>
       <c r="H112" s="51">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="I112" s="51">
         <v>227</v>
@@ -10016,7 +10102,7 @@
         <v>224</v>
       </c>
       <c r="H113" s="51">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="I113" s="51">
         <v>227</v>
@@ -10031,7 +10117,7 @@
         <v>225</v>
       </c>
       <c r="H114" s="51">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="I114" s="51">
         <v>227</v>
@@ -10046,7 +10132,7 @@
         <v>226</v>
       </c>
       <c r="H115" s="51">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="I115" s="51">
         <v>227</v>
@@ -10061,7 +10147,7 @@
         <v>227</v>
       </c>
       <c r="H116">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="I116" s="51">
         <v>227</v>
@@ -10076,7 +10162,7 @@
         <v>228</v>
       </c>
       <c r="H117" s="51">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I117" s="51">
         <v>227</v>
@@ -10091,7 +10177,7 @@
         <v>229</v>
       </c>
       <c r="H118" s="51">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="I118" s="51">
         <v>227</v>
@@ -10106,7 +10192,7 @@
         <v>230</v>
       </c>
       <c r="H119" s="51">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="I119" s="51">
         <v>227</v>
@@ -10124,7 +10210,7 @@
         <v>222</v>
       </c>
       <c r="H120" s="51">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="I120" s="51">
         <v>170</v>
@@ -10139,7 +10225,7 @@
         <v>223</v>
       </c>
       <c r="H121" s="51">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I121" s="51">
         <v>170</v>
@@ -10154,7 +10240,7 @@
         <v>224</v>
       </c>
       <c r="H122" s="51">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="I122" s="51">
         <v>170</v>
@@ -10169,7 +10255,7 @@
         <v>225</v>
       </c>
       <c r="H123" s="51">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="I123" s="51">
         <v>170</v>
@@ -10184,7 +10270,7 @@
         <v>226</v>
       </c>
       <c r="H124">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="I124" s="51">
         <v>170</v>
@@ -10199,7 +10285,7 @@
         <v>227</v>
       </c>
       <c r="H125" s="51">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="I125" s="51">
         <v>170</v>
@@ -10214,7 +10300,7 @@
         <v>228</v>
       </c>
       <c r="H126" s="51">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I126" s="51">
         <v>170</v>
@@ -10229,7 +10315,7 @@
         <v>229</v>
       </c>
       <c r="H127" s="51">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="I127" s="51">
         <v>170</v>
@@ -10244,7 +10330,7 @@
         <v>230</v>
       </c>
       <c r="H128" s="51">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I128" s="51">
         <v>170</v>
@@ -10262,7 +10348,7 @@
         <v>222</v>
       </c>
       <c r="H129" s="51">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="I129" s="51">
         <v>72</v>
@@ -10277,7 +10363,7 @@
         <v>223</v>
       </c>
       <c r="H130" s="51">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I130" s="51">
         <v>72</v>
@@ -10292,7 +10378,7 @@
         <v>224</v>
       </c>
       <c r="H131" s="51">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="I131" s="51">
         <v>72</v>
@@ -10307,7 +10393,7 @@
         <v>225</v>
       </c>
       <c r="H132" s="51">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I132" s="51">
         <v>72</v>
@@ -10322,7 +10408,7 @@
         <v>226</v>
       </c>
       <c r="H133" s="51">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="I133" s="51">
         <v>72</v>
@@ -10337,7 +10423,7 @@
         <v>227</v>
       </c>
       <c r="H134" s="51">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I134" s="51">
         <v>72</v>
@@ -10352,7 +10438,7 @@
         <v>228</v>
       </c>
       <c r="H135" s="51">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="I135" s="51">
         <v>72</v>
@@ -10367,7 +10453,7 @@
         <v>229</v>
       </c>
       <c r="H136" s="51">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I136" s="51">
         <v>72</v>
@@ -10382,7 +10468,7 @@
         <v>230</v>
       </c>
       <c r="H137" s="51">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I137" s="51">
         <v>72</v>
@@ -10400,7 +10486,7 @@
         <v>222</v>
       </c>
       <c r="H138" s="51">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="I138" s="51">
         <v>160</v>
@@ -10415,7 +10501,7 @@
         <v>223</v>
       </c>
       <c r="H139" s="51">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="I139" s="51">
         <v>160</v>
@@ -10430,7 +10516,7 @@
         <v>224</v>
       </c>
       <c r="H140">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="I140" s="51">
         <v>160</v>
@@ -10445,7 +10531,7 @@
         <v>225</v>
       </c>
       <c r="H141" s="51">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I141" s="51">
         <v>160</v>
@@ -10460,7 +10546,7 @@
         <v>226</v>
       </c>
       <c r="H142" s="51">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="I142" s="51">
         <v>160</v>
@@ -10475,7 +10561,7 @@
         <v>227</v>
       </c>
       <c r="H143" s="51">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="I143" s="51">
         <v>160</v>
@@ -10490,7 +10576,7 @@
         <v>228</v>
       </c>
       <c r="H144" s="51">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I144" s="51">
         <v>160</v>
@@ -10505,7 +10591,7 @@
         <v>229</v>
       </c>
       <c r="H145" s="51">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I145" s="51">
         <v>160</v>
@@ -10520,7 +10606,7 @@
         <v>230</v>
       </c>
       <c r="H146" s="51">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I146" s="51">
         <v>160</v>
@@ -10538,7 +10624,7 @@
         <v>222</v>
       </c>
       <c r="H147" s="51">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I147" s="51">
         <v>178</v>
@@ -10553,7 +10639,7 @@
         <v>223</v>
       </c>
       <c r="H148">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I148" s="51">
         <v>178</v>
@@ -10568,7 +10654,7 @@
         <v>224</v>
       </c>
       <c r="H149" s="51">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="I149" s="51">
         <v>178</v>
@@ -10583,7 +10669,7 @@
         <v>225</v>
       </c>
       <c r="H150" s="51">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="I150" s="51">
         <v>178</v>
@@ -10598,7 +10684,7 @@
         <v>226</v>
       </c>
       <c r="H151" s="51">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="I151" s="51">
         <v>178</v>
@@ -10613,7 +10699,7 @@
         <v>227</v>
       </c>
       <c r="H152" s="51">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="I152" s="51">
         <v>178</v>
@@ -10628,7 +10714,7 @@
         <v>228</v>
       </c>
       <c r="H153" s="51">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I153" s="51">
         <v>178</v>
@@ -10642,7 +10728,9 @@
       <c r="G154" t="s">
         <v>229</v>
       </c>
-      <c r="H154" s="51"/>
+      <c r="H154" s="51">
+        <v>5</v>
+      </c>
       <c r="I154" s="51">
         <v>178</v>
       </c>
@@ -10674,7 +10762,7 @@
         <v>222</v>
       </c>
       <c r="H156" s="51">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="I156" s="51">
         <v>172</v>
@@ -10689,7 +10777,7 @@
         <v>223</v>
       </c>
       <c r="H157" s="51">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="I157" s="51">
         <v>172</v>
@@ -10704,7 +10792,7 @@
         <v>224</v>
       </c>
       <c r="H158" s="51">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="I158" s="51">
         <v>172</v>
@@ -10719,7 +10807,7 @@
         <v>225</v>
       </c>
       <c r="H159" s="51">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="I159" s="51">
         <v>172</v>
@@ -10734,7 +10822,7 @@
         <v>226</v>
       </c>
       <c r="H160" s="51">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="I160" s="51">
         <v>172</v>
@@ -10749,7 +10837,7 @@
         <v>227</v>
       </c>
       <c r="H161" s="51">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="I161" s="51">
         <v>172</v>
@@ -10764,7 +10852,7 @@
         <v>228</v>
       </c>
       <c r="H162" s="51">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="I162" s="51">
         <v>172</v>
@@ -10779,7 +10867,7 @@
         <v>229</v>
       </c>
       <c r="H163" s="51">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I163" s="51">
         <v>172</v>
@@ -10794,7 +10882,7 @@
         <v>230</v>
       </c>
       <c r="H164">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I164" s="51">
         <v>172</v>
@@ -10815,7 +10903,7 @@
         <v>12</v>
       </c>
       <c r="I165" s="51">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="166" spans="5:9" x14ac:dyDescent="0.25">
@@ -10830,7 +10918,7 @@
         <v>6</v>
       </c>
       <c r="I166" s="51">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="167" spans="5:9" x14ac:dyDescent="0.25">
@@ -10842,10 +10930,10 @@
         <v>224</v>
       </c>
       <c r="H167" s="51">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I167" s="51">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="168" spans="5:9" x14ac:dyDescent="0.25">
@@ -10860,7 +10948,7 @@
         <v>15</v>
       </c>
       <c r="I168" s="51">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="169" spans="5:9" x14ac:dyDescent="0.25">
@@ -10875,7 +10963,7 @@
         <v>11</v>
       </c>
       <c r="I169" s="51">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="170" spans="5:9" x14ac:dyDescent="0.25">
@@ -10890,7 +10978,7 @@
         <v>12</v>
       </c>
       <c r="I170" s="51">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="171" spans="5:9" x14ac:dyDescent="0.25">
@@ -10902,10 +10990,10 @@
         <v>228</v>
       </c>
       <c r="H171" s="51">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I171" s="51">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="172" spans="5:9" x14ac:dyDescent="0.25">
@@ -10920,7 +11008,7 @@
         <v>6</v>
       </c>
       <c r="I172" s="51">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="173" spans="5:9" x14ac:dyDescent="0.25">
@@ -10935,7 +11023,7 @@
         <v>11</v>
       </c>
       <c r="I173" s="51">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="174" spans="5:9" x14ac:dyDescent="0.25">
@@ -10950,7 +11038,7 @@
         <v>222</v>
       </c>
       <c r="H174" s="51">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="I174" s="51">
         <v>140</v>
@@ -10965,7 +11053,7 @@
         <v>223</v>
       </c>
       <c r="H175" s="51">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I175" s="51">
         <v>140</v>
@@ -10980,7 +11068,7 @@
         <v>224</v>
       </c>
       <c r="H176" s="51">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="I176" s="51">
         <v>140</v>
@@ -10995,7 +11083,7 @@
         <v>225</v>
       </c>
       <c r="H177" s="51">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I177" s="51">
         <v>140</v>
@@ -11010,7 +11098,7 @@
         <v>226</v>
       </c>
       <c r="H178" s="51">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="I178" s="51">
         <v>140</v>
@@ -11025,7 +11113,7 @@
         <v>227</v>
       </c>
       <c r="H179" s="51">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="I179" s="51">
         <v>140</v>
@@ -11040,7 +11128,7 @@
         <v>228</v>
       </c>
       <c r="H180">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="I180" s="51">
         <v>140</v>
@@ -11055,7 +11143,7 @@
         <v>229</v>
       </c>
       <c r="H181" s="51">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I181" s="51">
         <v>140</v>
@@ -11070,7 +11158,7 @@
         <v>230</v>
       </c>
       <c r="H182" s="51">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I182" s="51">
         <v>140</v>
@@ -11088,7 +11176,7 @@
         <v>222</v>
       </c>
       <c r="H183" s="51">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="I183" s="51">
         <v>168</v>
@@ -11103,7 +11191,7 @@
         <v>223</v>
       </c>
       <c r="H184" s="51">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I184" s="51">
         <v>168</v>
@@ -11118,7 +11206,7 @@
         <v>224</v>
       </c>
       <c r="H185" s="51">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I185" s="51">
         <v>168</v>
@@ -11133,7 +11221,7 @@
         <v>225</v>
       </c>
       <c r="H186">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I186" s="51">
         <v>168</v>
@@ -11148,7 +11236,7 @@
         <v>226</v>
       </c>
       <c r="H187" s="51">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="I187" s="51">
         <v>168</v>
@@ -11163,7 +11251,7 @@
         <v>227</v>
       </c>
       <c r="H188" s="51">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="I188" s="51">
         <v>168</v>
@@ -11193,7 +11281,7 @@
         <v>229</v>
       </c>
       <c r="H190" s="51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I190" s="51">
         <v>168</v>
@@ -11208,7 +11296,7 @@
         <v>230</v>
       </c>
       <c r="H191" s="51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I191" s="51">
         <v>168</v>
@@ -11226,7 +11314,7 @@
         <v>222</v>
       </c>
       <c r="H192" s="51">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I192" s="51">
         <v>170</v>
@@ -11241,7 +11329,7 @@
         <v>223</v>
       </c>
       <c r="H193" s="51">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I193" s="51">
         <v>170</v>
@@ -11256,7 +11344,7 @@
         <v>224</v>
       </c>
       <c r="H194" s="51">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="I194" s="51">
         <v>170</v>
@@ -11271,7 +11359,7 @@
         <v>225</v>
       </c>
       <c r="H195" s="51">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="I195" s="51">
         <v>170</v>
@@ -11286,7 +11374,7 @@
         <v>226</v>
       </c>
       <c r="H196">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="I196" s="51">
         <v>170</v>
@@ -11301,7 +11389,7 @@
         <v>227</v>
       </c>
       <c r="H197" s="51">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I197" s="51">
         <v>170</v>
@@ -11316,7 +11404,7 @@
         <v>228</v>
       </c>
       <c r="H198" s="51">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I198" s="51">
         <v>170</v>
@@ -11331,7 +11419,7 @@
         <v>229</v>
       </c>
       <c r="H199" s="51">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I199" s="51">
         <v>170</v>
@@ -11346,7 +11434,7 @@
         <v>230</v>
       </c>
       <c r="H200" s="51">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I200" s="51">
         <v>170</v>
@@ -11364,10 +11452,10 @@
         <v>222</v>
       </c>
       <c r="H201" s="51">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I201" s="51">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="202" spans="5:9" x14ac:dyDescent="0.25">
@@ -11378,9 +11466,11 @@
       <c r="G202" t="s">
         <v>223</v>
       </c>
-      <c r="H202" s="51"/>
+      <c r="H202" s="51">
+        <v>1</v>
+      </c>
       <c r="I202" s="51">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="203" spans="5:9" x14ac:dyDescent="0.25">
@@ -11392,10 +11482,10 @@
         <v>224</v>
       </c>
       <c r="H203" s="51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I203" s="51">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="204" spans="5:9" x14ac:dyDescent="0.25">
@@ -11408,7 +11498,7 @@
       </c>
       <c r="H204" s="51"/>
       <c r="I204" s="51">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="205" spans="5:9" x14ac:dyDescent="0.25">
@@ -11419,9 +11509,11 @@
       <c r="G205" t="s">
         <v>226</v>
       </c>
-      <c r="H205" s="51"/>
+      <c r="H205" s="51">
+        <v>3</v>
+      </c>
       <c r="I205" s="51">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="206" spans="5:9" x14ac:dyDescent="0.25">
@@ -11434,7 +11526,7 @@
       </c>
       <c r="H206" s="51"/>
       <c r="I206" s="51">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="207" spans="5:9" x14ac:dyDescent="0.25">
@@ -11445,9 +11537,11 @@
       <c r="G207" t="s">
         <v>228</v>
       </c>
-      <c r="H207" s="51"/>
+      <c r="H207" s="51">
+        <v>8</v>
+      </c>
       <c r="I207" s="51">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="208" spans="5:9" x14ac:dyDescent="0.25">
@@ -11460,7 +11554,7 @@
       </c>
       <c r="H208" s="51"/>
       <c r="I208" s="51">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="209" spans="5:9" x14ac:dyDescent="0.25">
@@ -11473,7 +11567,7 @@
       </c>
       <c r="H209" s="51"/>
       <c r="I209" s="51">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="210" spans="5:9" x14ac:dyDescent="0.25">
@@ -11488,7 +11582,7 @@
         <v>222</v>
       </c>
       <c r="H210" s="51">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="I210" s="51">
         <v>161</v>
@@ -11503,7 +11597,7 @@
         <v>223</v>
       </c>
       <c r="H211" s="51">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I211" s="51">
         <v>161</v>
@@ -11518,7 +11612,7 @@
         <v>224</v>
       </c>
       <c r="H212">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="I212" s="51">
         <v>161</v>
@@ -11533,7 +11627,7 @@
         <v>225</v>
       </c>
       <c r="H213" s="51">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="I213" s="51">
         <v>161</v>
@@ -11548,7 +11642,7 @@
         <v>226</v>
       </c>
       <c r="H214" s="51">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="I214" s="51">
         <v>161</v>
@@ -11563,7 +11657,7 @@
         <v>227</v>
       </c>
       <c r="H215" s="51">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="I215" s="51">
         <v>161</v>
@@ -11578,7 +11672,7 @@
         <v>228</v>
       </c>
       <c r="H216" s="51">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I216" s="51">
         <v>161</v>
@@ -11593,7 +11687,7 @@
         <v>229</v>
       </c>
       <c r="H217" s="51">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="I217" s="51">
         <v>161</v>
@@ -11608,7 +11702,7 @@
         <v>230</v>
       </c>
       <c r="H218" s="51">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I218" s="51">
         <v>161</v>
@@ -11626,7 +11720,7 @@
         <v>222</v>
       </c>
       <c r="H219" s="51">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I219" s="51">
         <v>56</v>
@@ -11641,7 +11735,7 @@
         <v>223</v>
       </c>
       <c r="H220" s="51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I220" s="51">
         <v>56</v>
@@ -11656,7 +11750,7 @@
         <v>224</v>
       </c>
       <c r="H221" s="51">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I221" s="51">
         <v>56</v>
@@ -11671,7 +11765,7 @@
         <v>225</v>
       </c>
       <c r="H222" s="51">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I222" s="51">
         <v>56</v>
@@ -11686,7 +11780,7 @@
         <v>226</v>
       </c>
       <c r="H223" s="51">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="I223" s="51">
         <v>56</v>
@@ -11701,7 +11795,7 @@
         <v>227</v>
       </c>
       <c r="H224" s="51">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I224" s="51">
         <v>56</v>
@@ -11716,7 +11810,7 @@
         <v>228</v>
       </c>
       <c r="H225" s="51">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I225" s="51">
         <v>56</v>
@@ -11731,7 +11825,7 @@
         <v>229</v>
       </c>
       <c r="H226" s="51">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I226" s="51">
         <v>56</v>
@@ -11746,7 +11840,7 @@
         <v>230</v>
       </c>
       <c r="H227" s="51">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I227" s="51">
         <v>56</v>
@@ -11764,7 +11858,7 @@
         <v>222</v>
       </c>
       <c r="H228" s="51">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I228" s="51">
         <v>172</v>
@@ -11779,7 +11873,7 @@
         <v>223</v>
       </c>
       <c r="H229" s="51">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I229" s="51">
         <v>172</v>
@@ -11794,7 +11888,7 @@
         <v>224</v>
       </c>
       <c r="H230" s="51">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="I230" s="51">
         <v>172</v>
@@ -11809,7 +11903,7 @@
         <v>225</v>
       </c>
       <c r="H231" s="51">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I231" s="51">
         <v>172</v>
@@ -11824,7 +11918,7 @@
         <v>226</v>
       </c>
       <c r="H232" s="51">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="I232" s="51">
         <v>172</v>
@@ -11839,7 +11933,7 @@
         <v>227</v>
       </c>
       <c r="H233" s="51">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I233" s="51">
         <v>172</v>
@@ -11869,7 +11963,7 @@
         <v>229</v>
       </c>
       <c r="H235" s="51">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I235" s="51">
         <v>172</v>
@@ -11884,7 +11978,7 @@
         <v>230</v>
       </c>
       <c r="H236">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I236" s="51">
         <v>172</v>
@@ -11902,7 +11996,7 @@
         <v>222</v>
       </c>
       <c r="H237" s="51">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I237" s="51">
         <v>156</v>
@@ -11917,7 +12011,7 @@
         <v>223</v>
       </c>
       <c r="H238" s="51">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I238" s="51">
         <v>156</v>
@@ -11932,7 +12026,7 @@
         <v>224</v>
       </c>
       <c r="H239" s="51">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="I239" s="51">
         <v>156</v>
@@ -11947,7 +12041,7 @@
         <v>225</v>
       </c>
       <c r="H240" s="51">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I240" s="51">
         <v>156</v>
@@ -11962,7 +12056,7 @@
         <v>226</v>
       </c>
       <c r="H241" s="51">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="I241" s="51">
         <v>156</v>
@@ -11977,7 +12071,7 @@
         <v>227</v>
       </c>
       <c r="H242" s="51">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="I242" s="51">
         <v>156</v>
@@ -11992,7 +12086,7 @@
         <v>228</v>
       </c>
       <c r="H243" s="51">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I243" s="51">
         <v>156</v>
@@ -12007,7 +12101,7 @@
         <v>229</v>
       </c>
       <c r="H244">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I244" s="51">
         <v>156</v>
@@ -12021,7 +12115,9 @@
       <c r="G245" t="s">
         <v>230</v>
       </c>
-      <c r="H245" s="51"/>
+      <c r="H245" s="51">
+        <v>5</v>
+      </c>
       <c r="I245" s="51">
         <v>156</v>
       </c>
@@ -12038,10 +12134,10 @@
         <v>222</v>
       </c>
       <c r="H246" s="51">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I246" s="51">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="247" spans="5:9" x14ac:dyDescent="0.25">
@@ -12052,9 +12148,11 @@
       <c r="G247" t="s">
         <v>223</v>
       </c>
-      <c r="H247" s="51"/>
+      <c r="H247" s="51">
+        <v>3</v>
+      </c>
       <c r="I247" s="51">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="248" spans="5:9" x14ac:dyDescent="0.25">
@@ -12066,10 +12164,10 @@
         <v>224</v>
       </c>
       <c r="H248" s="51">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I248" s="51">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="249" spans="5:9" x14ac:dyDescent="0.25">
@@ -12080,9 +12178,11 @@
       <c r="G249" t="s">
         <v>225</v>
       </c>
-      <c r="H249" s="51"/>
+      <c r="H249" s="51">
+        <v>5</v>
+      </c>
       <c r="I249" s="51">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="250" spans="5:9" x14ac:dyDescent="0.25">
@@ -12094,10 +12194,10 @@
         <v>226</v>
       </c>
       <c r="H250" s="51">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="I250" s="51">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="251" spans="5:9" x14ac:dyDescent="0.25">
@@ -12109,10 +12209,10 @@
         <v>227</v>
       </c>
       <c r="H251" s="51">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I251" s="51">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="252" spans="5:9" x14ac:dyDescent="0.25">
@@ -12124,10 +12224,10 @@
         <v>228</v>
       </c>
       <c r="H252">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I252" s="51">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="253" spans="5:9" x14ac:dyDescent="0.25">
@@ -12139,10 +12239,10 @@
         <v>229</v>
       </c>
       <c r="H253" s="51">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I253" s="51">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="254" spans="5:9" x14ac:dyDescent="0.25">
@@ -12153,9 +12253,11 @@
       <c r="G254" t="s">
         <v>230</v>
       </c>
-      <c r="H254" s="51"/>
+      <c r="H254" s="51">
+        <v>4</v>
+      </c>
       <c r="I254" s="51">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="255" spans="5:9" x14ac:dyDescent="0.25">
@@ -12170,7 +12272,7 @@
         <v>222</v>
       </c>
       <c r="H255" s="51">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I255" s="51">
         <v>182</v>
@@ -12185,7 +12287,7 @@
         <v>223</v>
       </c>
       <c r="H256" s="51">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I256" s="51">
         <v>182</v>
@@ -12200,7 +12302,7 @@
         <v>224</v>
       </c>
       <c r="H257" s="51">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="I257" s="51">
         <v>182</v>
@@ -12215,7 +12317,7 @@
         <v>225</v>
       </c>
       <c r="H258">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="I258" s="51">
         <v>182</v>
@@ -12230,7 +12332,7 @@
         <v>226</v>
       </c>
       <c r="H259" s="51">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="I259" s="51">
         <v>182</v>
@@ -12245,7 +12347,7 @@
         <v>227</v>
       </c>
       <c r="H260">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="I260" s="51">
         <v>182</v>
@@ -12260,7 +12362,7 @@
         <v>228</v>
       </c>
       <c r="H261" s="51">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I261" s="51">
         <v>182</v>
@@ -12275,7 +12377,7 @@
         <v>229</v>
       </c>
       <c r="H262" s="51">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I262" s="51">
         <v>182</v>
@@ -12290,7 +12392,7 @@
         <v>230</v>
       </c>
       <c r="H263" s="51">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I263" s="51">
         <v>182</v>
@@ -12308,7 +12410,7 @@
         <v>222</v>
       </c>
       <c r="H264" s="51">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I264" s="51">
         <v>249</v>
@@ -12323,7 +12425,7 @@
         <v>223</v>
       </c>
       <c r="H265">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I265" s="51">
         <v>249</v>
@@ -12338,7 +12440,7 @@
         <v>224</v>
       </c>
       <c r="H266" s="51">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I266" s="51">
         <v>249</v>
@@ -12353,7 +12455,7 @@
         <v>225</v>
       </c>
       <c r="H267" s="51">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="I267" s="51">
         <v>249</v>
@@ -12368,7 +12470,7 @@
         <v>226</v>
       </c>
       <c r="H268">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="I268" s="51">
         <v>249</v>
@@ -12383,7 +12485,7 @@
         <v>227</v>
       </c>
       <c r="H269" s="51">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="I269" s="51">
         <v>249</v>
@@ -12398,7 +12500,7 @@
         <v>228</v>
       </c>
       <c r="H270" s="51">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I270" s="51">
         <v>249</v>
@@ -12413,7 +12515,7 @@
         <v>229</v>
       </c>
       <c r="H271" s="51">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I271" s="51">
         <v>249</v>
@@ -12428,7 +12530,7 @@
         <v>230</v>
       </c>
       <c r="H272" s="51">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I272" s="51">
         <v>249</v>
@@ -12496,7 +12598,9 @@
       <c r="G277" t="s">
         <v>226</v>
       </c>
-      <c r="H277" s="51"/>
+      <c r="H277" s="51">
+        <v>3</v>
+      </c>
       <c r="I277" s="51">
         <v>52</v>
       </c>
@@ -12509,7 +12613,9 @@
       <c r="G278" t="s">
         <v>227</v>
       </c>
-      <c r="H278" s="51"/>
+      <c r="H278" s="51">
+        <v>2</v>
+      </c>
       <c r="I278" s="51">
         <v>52</v>
       </c>
@@ -12522,7 +12628,9 @@
       <c r="G279" t="s">
         <v>228</v>
       </c>
-      <c r="H279" s="51"/>
+      <c r="H279" s="51">
+        <v>4</v>
+      </c>
       <c r="I279" s="51">
         <v>52</v>
       </c>
@@ -12535,7 +12643,9 @@
       <c r="G280" t="s">
         <v>229</v>
       </c>
-      <c r="H280" s="51"/>
+      <c r="H280" s="51">
+        <v>1</v>
+      </c>
       <c r="I280" s="51">
         <v>52</v>
       </c>
@@ -12548,7 +12658,9 @@
       <c r="G281" t="s">
         <v>230</v>
       </c>
-      <c r="H281" s="51"/>
+      <c r="H281" s="51">
+        <v>2</v>
+      </c>
       <c r="I281" s="51">
         <v>52</v>
       </c>
@@ -12679,7 +12791,7 @@
         <v>222</v>
       </c>
       <c r="H291">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I291" s="51">
         <v>169</v>
@@ -12694,7 +12806,7 @@
         <v>223</v>
       </c>
       <c r="H292">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I292" s="51">
         <v>169</v>
@@ -12709,7 +12821,7 @@
         <v>224</v>
       </c>
       <c r="H293">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I293" s="51">
         <v>169</v>
@@ -12724,7 +12836,7 @@
         <v>225</v>
       </c>
       <c r="H294">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="I294" s="51">
         <v>169</v>
@@ -12739,7 +12851,7 @@
         <v>226</v>
       </c>
       <c r="H295">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="I295" s="51">
         <v>169</v>
@@ -12754,7 +12866,7 @@
         <v>227</v>
       </c>
       <c r="H296">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="I296" s="51">
         <v>169</v>
@@ -12769,7 +12881,7 @@
         <v>228</v>
       </c>
       <c r="H297" s="51">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I297" s="51">
         <v>169</v>
@@ -12784,7 +12896,7 @@
         <v>229</v>
       </c>
       <c r="H298">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I298" s="51">
         <v>169</v>
@@ -12799,7 +12911,7 @@
         <v>230</v>
       </c>
       <c r="H299" s="51">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I299" s="51">
         <v>169</v>
@@ -12847,7 +12959,7 @@
         <v>224</v>
       </c>
       <c r="H302" s="51">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I302" s="51">
         <v>239</v>
@@ -12877,7 +12989,7 @@
         <v>226</v>
       </c>
       <c r="H304" s="51">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I304" s="51">
         <v>239</v>
@@ -12955,7 +13067,7 @@
         <v>222</v>
       </c>
       <c r="H309">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="I309" s="51">
         <v>260</v>
@@ -12970,7 +13082,7 @@
         <v>223</v>
       </c>
       <c r="H310">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I310" s="51">
         <v>260</v>
@@ -12985,7 +13097,7 @@
         <v>224</v>
       </c>
       <c r="H311">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="I311" s="51">
         <v>260</v>
@@ -13000,7 +13112,7 @@
         <v>225</v>
       </c>
       <c r="H312">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="I312" s="51">
         <v>260</v>
@@ -13015,7 +13127,7 @@
         <v>226</v>
       </c>
       <c r="H313">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="I313" s="51">
         <v>260</v>
@@ -13030,7 +13142,7 @@
         <v>227</v>
       </c>
       <c r="H314">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="I314" s="51">
         <v>260</v>
@@ -13045,7 +13157,7 @@
         <v>228</v>
       </c>
       <c r="H315" s="51">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I315" s="51">
         <v>260</v>
@@ -13060,7 +13172,7 @@
         <v>229</v>
       </c>
       <c r="H316">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I316" s="51">
         <v>260</v>
@@ -13075,7 +13187,7 @@
         <v>230</v>
       </c>
       <c r="H317" s="51">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I317" s="51">
         <v>260</v>
@@ -13107,7 +13219,9 @@
       <c r="G319" t="s">
         <v>223</v>
       </c>
-      <c r="H319" s="51"/>
+      <c r="H319" s="51">
+        <v>2</v>
+      </c>
       <c r="I319" s="51">
         <v>101</v>
       </c>
@@ -13172,7 +13286,7 @@
         <v>228</v>
       </c>
       <c r="H324" s="51">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="I324" s="51">
         <v>101</v>
@@ -13227,6 +13341,9 @@
       <c r="G328" t="s">
         <v>223</v>
       </c>
+      <c r="H328">
+        <v>1</v>
+      </c>
       <c r="I328" s="51">
         <v>105</v>
       </c>
@@ -13290,7 +13407,7 @@
         <v>228</v>
       </c>
       <c r="H333" s="51">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="I333" s="51">
         <v>105</v>
@@ -13334,7 +13451,7 @@
         <v>222</v>
       </c>
       <c r="H336" s="51">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I336" s="51">
         <v>202</v>
@@ -13349,7 +13466,7 @@
         <v>223</v>
       </c>
       <c r="H337" s="51">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I337" s="51">
         <v>202</v>
@@ -13364,7 +13481,7 @@
         <v>224</v>
       </c>
       <c r="H338" s="51">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I338" s="51">
         <v>202</v>
@@ -13379,7 +13496,7 @@
         <v>225</v>
       </c>
       <c r="H339" s="51">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I339" s="51">
         <v>202</v>
@@ -13394,7 +13511,7 @@
         <v>226</v>
       </c>
       <c r="H340">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I340" s="51">
         <v>202</v>
@@ -13409,7 +13526,7 @@
         <v>227</v>
       </c>
       <c r="H341" s="51">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="I341" s="51">
         <v>202</v>
@@ -13424,7 +13541,7 @@
         <v>228</v>
       </c>
       <c r="H342" s="51">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I342" s="51">
         <v>202</v>
@@ -13439,7 +13556,7 @@
         <v>229</v>
       </c>
       <c r="H343" s="51">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I343" s="51">
         <v>202</v>
@@ -13454,7 +13571,7 @@
         <v>230</v>
       </c>
       <c r="H344" s="51">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="I344" s="51">
         <v>202</v>
@@ -13471,6 +13588,9 @@
       <c r="G345" t="s">
         <v>222</v>
       </c>
+      <c r="H345">
+        <v>6</v>
+      </c>
       <c r="I345" s="51">
         <v>198</v>
       </c>
@@ -13483,7 +13603,9 @@
       <c r="G346" t="s">
         <v>223</v>
       </c>
-      <c r="H346" s="51"/>
+      <c r="H346" s="51">
+        <v>8</v>
+      </c>
       <c r="I346" s="51">
         <v>198</v>
       </c>
@@ -13496,7 +13618,9 @@
       <c r="G347" t="s">
         <v>224</v>
       </c>
-      <c r="H347" s="51"/>
+      <c r="H347" s="51">
+        <v>17</v>
+      </c>
       <c r="I347" s="51">
         <v>198</v>
       </c>
@@ -13509,6 +13633,9 @@
       <c r="G348" t="s">
         <v>225</v>
       </c>
+      <c r="H348">
+        <v>6</v>
+      </c>
       <c r="I348" s="51">
         <v>198</v>
       </c>
@@ -13521,7 +13648,9 @@
       <c r="G349" t="s">
         <v>226</v>
       </c>
-      <c r="H349" s="51"/>
+      <c r="H349" s="51">
+        <v>14</v>
+      </c>
       <c r="I349" s="51">
         <v>198</v>
       </c>
@@ -13534,7 +13663,9 @@
       <c r="G350" t="s">
         <v>227</v>
       </c>
-      <c r="H350" s="51"/>
+      <c r="H350" s="51">
+        <v>6</v>
+      </c>
       <c r="I350" s="51">
         <v>198</v>
       </c>
@@ -13547,7 +13678,9 @@
       <c r="G351" t="s">
         <v>228</v>
       </c>
-      <c r="H351" s="51"/>
+      <c r="H351" s="51">
+        <v>18</v>
+      </c>
       <c r="I351" s="51">
         <v>198</v>
       </c>
@@ -13560,6 +13693,9 @@
       <c r="G352" t="s">
         <v>229</v>
       </c>
+      <c r="H352">
+        <v>4</v>
+      </c>
       <c r="I352" s="51">
         <v>198</v>
       </c>
@@ -13572,7 +13708,9 @@
       <c r="G353" t="s">
         <v>230</v>
       </c>
-      <c r="H353" s="51"/>
+      <c r="H353" s="51">
+        <v>2</v>
+      </c>
       <c r="I353" s="51">
         <v>198</v>
       </c>
@@ -13590,7 +13728,7 @@
       </c>
       <c r="H354" s="51"/>
       <c r="I354" s="51">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="355" spans="5:9" x14ac:dyDescent="0.25">
@@ -13603,7 +13741,7 @@
       </c>
       <c r="H355" s="51"/>
       <c r="I355" s="51">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="356" spans="5:9" x14ac:dyDescent="0.25">
@@ -13616,7 +13754,7 @@
       </c>
       <c r="H356" s="51"/>
       <c r="I356" s="51">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="357" spans="5:9" x14ac:dyDescent="0.25">
@@ -13629,7 +13767,7 @@
       </c>
       <c r="H357" s="51"/>
       <c r="I357" s="51">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="358" spans="5:9" x14ac:dyDescent="0.25">
@@ -13642,7 +13780,7 @@
       </c>
       <c r="H358" s="51"/>
       <c r="I358" s="51">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="359" spans="5:9" x14ac:dyDescent="0.25">
@@ -13655,7 +13793,7 @@
       </c>
       <c r="H359" s="51"/>
       <c r="I359" s="51">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="360" spans="5:9" x14ac:dyDescent="0.25">
@@ -13667,10 +13805,10 @@
         <v>228</v>
       </c>
       <c r="H360" s="51">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I360" s="51">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="361" spans="5:9" x14ac:dyDescent="0.25">
@@ -13683,7 +13821,7 @@
       </c>
       <c r="H361" s="51"/>
       <c r="I361" s="51">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="362" spans="5:9" x14ac:dyDescent="0.25">
@@ -13696,7 +13834,7 @@
       </c>
       <c r="H362" s="51"/>
       <c r="I362" s="51">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="363" spans="5:9" x14ac:dyDescent="0.25">
@@ -13830,8 +13968,11 @@
       <c r="G372" t="s">
         <v>222</v>
       </c>
+      <c r="H372">
+        <v>1</v>
+      </c>
       <c r="I372">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="373" spans="5:9" x14ac:dyDescent="0.25">
@@ -13843,7 +13984,7 @@
         <v>223</v>
       </c>
       <c r="I373">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="374" spans="5:9" x14ac:dyDescent="0.25">
@@ -13855,7 +13996,7 @@
         <v>224</v>
       </c>
       <c r="I374">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="375" spans="5:9" x14ac:dyDescent="0.25">
@@ -13867,7 +14008,7 @@
         <v>225</v>
       </c>
       <c r="I375">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="376" spans="5:9" x14ac:dyDescent="0.25">
@@ -13879,7 +14020,7 @@
         <v>226</v>
       </c>
       <c r="I376">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="377" spans="5:9" x14ac:dyDescent="0.25">
@@ -13891,7 +14032,7 @@
         <v>227</v>
       </c>
       <c r="I377">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="378" spans="5:9" x14ac:dyDescent="0.25">
@@ -13903,7 +14044,7 @@
         <v>228</v>
       </c>
       <c r="I378">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="379" spans="5:9" x14ac:dyDescent="0.25">
@@ -13915,7 +14056,7 @@
         <v>229</v>
       </c>
       <c r="I379">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="380" spans="5:9" x14ac:dyDescent="0.25">
@@ -13927,7 +14068,7 @@
         <v>230</v>
       </c>
       <c r="I380">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="381" spans="5:9" x14ac:dyDescent="0.25">
@@ -13969,7 +14110,7 @@
         <v>224</v>
       </c>
       <c r="H383">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I383">
         <v>113</v>
@@ -14010,6 +14151,9 @@
       <c r="G386" t="s">
         <v>227</v>
       </c>
+      <c r="H386">
+        <v>1</v>
+      </c>
       <c r="I386">
         <v>113</v>
       </c>
@@ -14065,10 +14209,10 @@
         <v>222</v>
       </c>
       <c r="H390">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="I390">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="391" spans="5:9" x14ac:dyDescent="0.25">
@@ -14079,8 +14223,11 @@
       <c r="G391" t="s">
         <v>223</v>
       </c>
+      <c r="H391">
+        <v>4</v>
+      </c>
       <c r="I391">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="392" spans="5:9" x14ac:dyDescent="0.25">
@@ -14092,10 +14239,10 @@
         <v>224</v>
       </c>
       <c r="H392">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="I392">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="393" spans="5:9" x14ac:dyDescent="0.25">
@@ -14107,10 +14254,10 @@
         <v>225</v>
       </c>
       <c r="H393">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I393">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="394" spans="5:9" x14ac:dyDescent="0.25">
@@ -14122,10 +14269,10 @@
         <v>226</v>
       </c>
       <c r="H394">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="I394">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="395" spans="5:9" x14ac:dyDescent="0.25">
@@ -14137,10 +14284,10 @@
         <v>227</v>
       </c>
       <c r="H395">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="I395">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="396" spans="5:9" x14ac:dyDescent="0.25">
@@ -14152,10 +14299,10 @@
         <v>228</v>
       </c>
       <c r="H396">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I396">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="397" spans="5:9" x14ac:dyDescent="0.25">
@@ -14167,10 +14314,10 @@
         <v>229</v>
       </c>
       <c r="H397">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I397">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="398" spans="5:9" x14ac:dyDescent="0.25">
@@ -14182,10 +14329,10 @@
         <v>230</v>
       </c>
       <c r="H398">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I398">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="399" spans="5:9" x14ac:dyDescent="0.25">
@@ -14200,7 +14347,7 @@
         <v>222</v>
       </c>
       <c r="H399">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I399">
         <v>161</v>
@@ -14215,7 +14362,7 @@
         <v>223</v>
       </c>
       <c r="H400">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I400">
         <v>161</v>
@@ -14230,7 +14377,7 @@
         <v>224</v>
       </c>
       <c r="H401">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="I401">
         <v>161</v>
@@ -14245,7 +14392,7 @@
         <v>225</v>
       </c>
       <c r="H402">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I402">
         <v>161</v>
@@ -14260,7 +14407,7 @@
         <v>226</v>
       </c>
       <c r="H403">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="I403">
         <v>161</v>
@@ -14275,7 +14422,7 @@
         <v>227</v>
       </c>
       <c r="H404">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="I404">
         <v>161</v>
@@ -14305,7 +14452,7 @@
         <v>229</v>
       </c>
       <c r="H406">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I406">
         <v>161</v>
@@ -14320,7 +14467,7 @@
         <v>230</v>
       </c>
       <c r="H407">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I407">
         <v>161</v>

--- a/data/ventas.xlsx
+++ b/data/ventas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cesar\Desktop\Reportes Ventas Rap\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BE1BB90A-BFEB-48EE-87C3-D034647CF518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{349C1206-A2E4-4AA5-898B-16F0DAD2F070}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="233">
   <si>
     <t>GOMEZ MARTÍN</t>
   </si>
@@ -761,6 +761,12 @@
   </si>
   <si>
     <t>145 - PILAS</t>
+  </si>
+  <si>
+    <t>42 - ROMERO ARIEL</t>
+  </si>
+  <si>
+    <t>123 - TORRES ROLANDO</t>
   </si>
 </sst>
 </file>
@@ -944,7 +950,6 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="41">
@@ -2482,7 +2487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34" bestFit="1" customWidth="1"/>
@@ -2529,22 +2534,22 @@
         <v>0</v>
       </c>
       <c r="C2" s="96">
-        <v>12759.648138517299</v>
+        <v>17146.3661547753</v>
       </c>
       <c r="D2" s="96">
-        <v>61262.625914064098</v>
+        <v>85454.712087362597</v>
       </c>
       <c r="E2" s="96">
-        <v>223094212.44056469</v>
+        <v>298472871.26286787</v>
       </c>
       <c r="F2" s="96">
         <v>0</v>
       </c>
       <c r="G2" s="96">
-        <v>141404.35170655229</v>
+        <v>185038.5097417341</v>
       </c>
       <c r="H2" s="96">
-        <v>141404.38</v>
+        <v>185038.5</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -2555,22 +2560,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="96">
-        <v>168.2765046287</v>
+        <v>250.12620409120001</v>
       </c>
       <c r="D3" s="96">
-        <v>491.7907233853</v>
+        <v>592.11105820729995</v>
       </c>
       <c r="E3" s="96">
-        <v>4713478.3902184051</v>
+        <v>6167950.3247244535</v>
       </c>
       <c r="F3" s="96">
         <v>0</v>
       </c>
       <c r="G3" s="96">
-        <v>141404.35170655229</v>
+        <v>185038.5097417341</v>
       </c>
       <c r="H3" s="96">
-        <v>141404.38</v>
+        <v>185038.5</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2581,13 +2586,13 @@
         <v>1</v>
       </c>
       <c r="C4" s="96">
-        <v>89.716765872799996</v>
+        <v>104.8786706344</v>
       </c>
       <c r="D4" s="96">
-        <v>228.65250000060001</v>
+        <v>236.1575000002</v>
       </c>
       <c r="E4" s="96">
-        <v>3490474.4748070529</v>
+        <v>3831780.4656781647</v>
       </c>
       <c r="F4" s="96">
         <v>0</v>
@@ -2607,13 +2612,13 @@
         <v>1</v>
       </c>
       <c r="C5" s="96">
-        <v>113.08222222160001</v>
+        <v>160.9195238085</v>
       </c>
       <c r="D5" s="96">
-        <v>487.77000000160001</v>
+        <v>612.02249999640003</v>
       </c>
       <c r="E5" s="96">
-        <v>2539362.2668490014</v>
+        <v>3383340.6159000443</v>
       </c>
       <c r="F5" s="96">
         <v>0</v>
@@ -2633,13 +2638,13 @@
         <v>1</v>
       </c>
       <c r="C6" s="96">
-        <v>319.23392857089999</v>
+        <v>361.47559523759998</v>
       </c>
       <c r="D6" s="96">
-        <v>1011.7841785766</v>
+        <v>1048.2891785794</v>
       </c>
       <c r="E6" s="96">
-        <v>5960130.3637676956</v>
+        <v>6899879.8473196756</v>
       </c>
       <c r="F6" s="96">
         <v>0</v>
@@ -2659,13 +2664,13 @@
         <v>1</v>
       </c>
       <c r="C7" s="96">
-        <v>219.94720238030001</v>
+        <v>327.00688491969998</v>
       </c>
       <c r="D7" s="96">
-        <v>984.96450000130005</v>
+        <v>1128.9845000005</v>
       </c>
       <c r="E7" s="96">
-        <v>4232380.5042614806</v>
+        <v>6168952.3513542237</v>
       </c>
       <c r="F7" s="96">
         <v>0</v>
@@ -2685,13 +2690,13 @@
         <v>1</v>
       </c>
       <c r="C8" s="96">
-        <v>1614.9333333334</v>
+        <v>1635.1449074075001</v>
       </c>
       <c r="D8" s="96">
-        <v>1507.4840000014001</v>
+        <v>1871.1244768535</v>
       </c>
       <c r="E8" s="96">
-        <v>16463801.298558187</v>
+        <v>17081843.43377829</v>
       </c>
       <c r="F8" s="96">
         <v>0</v>
@@ -2711,13 +2716,13 @@
         <v>1</v>
       </c>
       <c r="C9" s="96">
-        <v>113.1691071427</v>
+        <v>151.30611111069999</v>
       </c>
       <c r="D9" s="96">
-        <v>643.5574999982</v>
+        <v>844.06249999780005</v>
       </c>
       <c r="E9" s="96">
-        <v>2229458.8498637299</v>
+        <v>2938195.7767915935</v>
       </c>
       <c r="F9" s="96">
         <v>0</v>
@@ -2737,13 +2742,13 @@
         <v>1</v>
       </c>
       <c r="C10" s="96">
-        <v>67.089751984100005</v>
+        <v>97.588759920800001</v>
       </c>
       <c r="D10" s="96">
-        <v>200.80203124760001</v>
+        <v>283.49911458560001</v>
       </c>
       <c r="E10" s="96">
-        <v>2237337.654012111</v>
+        <v>2863924.6281832345</v>
       </c>
       <c r="F10" s="96">
         <v>0</v>
@@ -2763,13 +2768,13 @@
         <v>1</v>
       </c>
       <c r="C11" s="96">
-        <v>69.604761904499995</v>
+        <v>115.3075396819</v>
       </c>
       <c r="D11" s="96">
-        <v>303.04959523730003</v>
+        <v>293.55459523730002</v>
       </c>
       <c r="E11" s="96">
-        <v>1556471.8667402903</v>
+        <v>2292259.0263364343</v>
       </c>
       <c r="F11" s="96">
         <v>0</v>
@@ -2789,13 +2794,13 @@
         <v>1</v>
       </c>
       <c r="C12" s="96">
-        <v>178.19682539589999</v>
+        <v>345.86944444289998</v>
       </c>
       <c r="D12" s="96">
-        <v>527.69845237909999</v>
+        <v>2278.2034523770999</v>
       </c>
       <c r="E12" s="96">
-        <v>3454829.7358999122</v>
+        <v>5810906.7980635744</v>
       </c>
       <c r="F12" s="96">
         <v>0</v>
@@ -2815,13 +2820,13 @@
         <v>1</v>
       </c>
       <c r="C13" s="96">
-        <v>225.7950396821</v>
+        <v>276.10170634870002</v>
       </c>
       <c r="D13" s="96">
-        <v>829.79151190790003</v>
+        <v>940.33651190850003</v>
       </c>
       <c r="E13" s="96">
-        <v>4650179.1579327742</v>
+        <v>5672001.5032034451</v>
       </c>
       <c r="F13" s="96">
         <v>0</v>
@@ -2841,13 +2846,13 @@
         <v>1</v>
       </c>
       <c r="C14" s="96">
-        <v>1444.0819444447</v>
+        <v>1609.1910714287001</v>
       </c>
       <c r="D14" s="96">
-        <v>13580.7225000012</v>
+        <v>14799.4800000014</v>
       </c>
       <c r="E14" s="96">
-        <v>35677866.984969728</v>
+        <v>38609317.055148289</v>
       </c>
       <c r="F14" s="96">
         <v>0</v>
@@ -2867,13 +2872,13 @@
         <v>1</v>
       </c>
       <c r="C15" s="96">
-        <v>203.11855158700001</v>
+        <v>247.15327380900001</v>
       </c>
       <c r="D15" s="96">
-        <v>755.52499999940005</v>
+        <v>974.77749999800005</v>
       </c>
       <c r="E15" s="96">
-        <v>3799689.1529486589</v>
+        <v>4655359.4802594241</v>
       </c>
       <c r="F15" s="96">
         <v>0</v>
@@ -2893,13 +2898,13 @@
         <v>1</v>
       </c>
       <c r="C16" s="96">
-        <v>128.3049206343</v>
+        <v>178.4678174595</v>
       </c>
       <c r="D16" s="96">
-        <v>693.45458333670001</v>
+        <v>966.66851190839998</v>
       </c>
       <c r="E16" s="96">
-        <v>3126324.9965506792</v>
+        <v>4172472.7522102422</v>
       </c>
       <c r="F16" s="96">
         <v>0</v>
@@ -2919,13 +2924,13 @@
         <v>1</v>
       </c>
       <c r="C17" s="96">
-        <v>214.7180555544</v>
+        <v>300.13720237960001</v>
       </c>
       <c r="D17" s="96">
-        <v>616.00885714909998</v>
+        <v>957.02602381810004</v>
       </c>
       <c r="E17" s="96">
-        <v>5092283.3348378455</v>
+        <v>6362623.1530077159</v>
       </c>
       <c r="F17" s="96">
         <v>0</v>
@@ -2945,13 +2950,13 @@
         <v>1</v>
       </c>
       <c r="C18" s="96">
-        <v>339.81365079310001</v>
+        <v>484.40908730130002</v>
       </c>
       <c r="D18" s="96">
-        <v>2209.1249285679</v>
+        <v>2532.7421785693</v>
       </c>
       <c r="E18" s="96">
-        <v>6538018.3834050605</v>
+        <v>10180781.322442733</v>
       </c>
       <c r="F18" s="96">
         <v>0</v>
@@ -2971,13 +2976,13 @@
         <v>1</v>
       </c>
       <c r="C19" s="96">
-        <v>242.1867394173</v>
+        <v>381.46455026360002</v>
       </c>
       <c r="D19" s="96">
-        <v>821.9142142938</v>
+        <v>1583.1667142941999</v>
       </c>
       <c r="E19" s="96">
-        <v>5313079.7996425815</v>
+        <v>8068602.606727235</v>
       </c>
       <c r="F19" s="96">
         <v>0</v>
@@ -2997,13 +3002,13 @@
         <v>1</v>
       </c>
       <c r="C20" s="96">
-        <v>1331.513234127</v>
+        <v>1502.1562896826999</v>
       </c>
       <c r="D20" s="96">
-        <v>7081.0849999985003</v>
+        <v>8207.8199999985009</v>
       </c>
       <c r="E20" s="96">
-        <v>18543635.055367131</v>
+        <v>21714287.032106198</v>
       </c>
       <c r="F20" s="96">
         <v>0</v>
@@ -3023,13 +3028,13 @@
         <v>1</v>
       </c>
       <c r="C21" s="96">
-        <v>174.00490079319999</v>
+        <v>211.5864484121</v>
       </c>
       <c r="D21" s="96">
-        <v>605.7746071478</v>
+        <v>833.7746071478</v>
       </c>
       <c r="E21" s="96">
-        <v>3621062.6775038806</v>
+        <v>4521737.6382463202</v>
       </c>
       <c r="F21" s="96">
         <v>0</v>
@@ -3049,13 +3054,13 @@
         <v>1</v>
       </c>
       <c r="C22" s="96">
-        <v>123.90625</v>
+        <v>165.08382936460001</v>
       </c>
       <c r="D22" s="96">
-        <v>291.22892856869998</v>
+        <v>427.67851190099998</v>
       </c>
       <c r="E22" s="96">
-        <v>1931060.2247250369</v>
+        <v>2633216.6305364068</v>
       </c>
       <c r="F22" s="96">
         <v>0</v>
@@ -3075,13 +3080,13 @@
         <v>1</v>
       </c>
       <c r="C23" s="96">
-        <v>128.10228174549999</v>
+        <v>790.79180555489995</v>
       </c>
       <c r="D23" s="96">
-        <v>339.25166666370001</v>
+        <v>4836.2267976160001</v>
       </c>
       <c r="E23" s="96">
-        <v>1999132.6820728134</v>
+        <v>17286368.69822238</v>
       </c>
       <c r="F23" s="96">
         <v>0</v>
@@ -3101,13 +3106,13 @@
         <v>1</v>
       </c>
       <c r="C24" s="96">
-        <v>748.66458333349999</v>
+        <v>731.66458333349999</v>
       </c>
       <c r="D24" s="96">
-        <v>4813.7219583328997</v>
+        <v>4795.7219583328997</v>
       </c>
       <c r="E24" s="96">
-        <v>13993499.751331689</v>
+        <v>13810777.689331688</v>
       </c>
       <c r="F24" s="96">
         <v>0</v>
@@ -3127,13 +3132,13 @@
         <v>1</v>
       </c>
       <c r="C25" s="96">
-        <v>151.11507936480001</v>
+        <v>266.02386904759999</v>
       </c>
       <c r="D25" s="96">
-        <v>563.25500000219995</v>
+        <v>745.76000000479996</v>
       </c>
       <c r="E25" s="96">
-        <v>3265458.2459612871</v>
+        <v>4425690.3579718489</v>
       </c>
       <c r="F25" s="96">
         <v>0</v>
@@ -3153,13 +3158,13 @@
         <v>1</v>
       </c>
       <c r="C26" s="96">
-        <v>78.740436507300004</v>
+        <v>116.358075396</v>
       </c>
       <c r="D26" s="96">
-        <v>282.00000000040001</v>
+        <v>329.2370833343</v>
       </c>
       <c r="E26" s="96">
-        <v>1905347.2963424551</v>
+        <v>2299134.4748592312</v>
       </c>
       <c r="F26" s="96">
         <v>0</v>
@@ -3179,13 +3184,13 @@
         <v>1</v>
       </c>
       <c r="C27" s="96">
-        <v>1334.5</v>
+        <v>1858.5</v>
       </c>
       <c r="D27" s="96">
-        <v>2577.1799999999998</v>
+        <v>9370.84</v>
       </c>
       <c r="E27" s="96">
-        <v>13136953.343350001</v>
+        <v>22612109.009</v>
       </c>
       <c r="F27" s="96">
         <v>0</v>
@@ -3205,13 +3210,13 @@
         <v>1</v>
       </c>
       <c r="C28" s="96">
-        <v>224.8947354492</v>
+        <v>335.03509589909999</v>
       </c>
       <c r="D28" s="96">
-        <v>1004.4995833371</v>
+        <v>1431.6175520900999</v>
       </c>
       <c r="E28" s="96">
-        <v>4525419.7648018571</v>
+        <v>6604601.1312453747</v>
       </c>
       <c r="F28" s="96">
         <v>0</v>
@@ -3231,13 +3236,13 @@
         <v>1</v>
       </c>
       <c r="C29" s="96">
-        <v>386.73</v>
+        <v>1070.0341666667</v>
       </c>
       <c r="D29" s="96">
-        <v>1523.5400000018999</v>
+        <v>2070.5600000021</v>
       </c>
       <c r="E29" s="96">
-        <v>7197381.3632933144</v>
+        <v>14993819.966923174</v>
       </c>
       <c r="F29" s="96">
         <v>0</v>
@@ -3257,13 +3262,13 @@
         <v>1</v>
       </c>
       <c r="C30" s="96">
-        <v>73.557242063700002</v>
+        <v>94.954265873200001</v>
       </c>
       <c r="D30" s="96">
-        <v>290.52000000279997</v>
+        <v>328.6716666758</v>
       </c>
       <c r="E30" s="96">
-        <v>1342266.2312651528</v>
+        <v>1808557.8257932956</v>
       </c>
       <c r="F30" s="96">
         <v>0</v>
@@ -3283,13 +3288,13 @@
         <v>1</v>
       </c>
       <c r="C31" s="96">
-        <v>90.458531745100004</v>
+        <v>129.67519841169999</v>
       </c>
       <c r="D31" s="96">
-        <v>283.59499999920001</v>
+        <v>329.79500000109999</v>
       </c>
       <c r="E31" s="96">
-        <v>1662817.6962441357</v>
+        <v>2246997.9859188953</v>
       </c>
       <c r="F31" s="96">
         <v>0</v>
@@ -3309,13 +3314,13 @@
         <v>1</v>
       </c>
       <c r="C32" s="96">
-        <v>28.535912698600001</v>
+        <v>35.690277778000002</v>
       </c>
       <c r="D32" s="96">
-        <v>178.64666666860001</v>
+        <v>226.89916666760001</v>
       </c>
       <c r="E32" s="96">
-        <v>920475.59202497394</v>
+        <v>1134886.8601273343</v>
       </c>
       <c r="F32" s="96">
         <v>0</v>
@@ -3335,13 +3340,13 @@
         <v>1</v>
       </c>
       <c r="C33" s="96">
-        <v>215.69446428559999</v>
+        <v>295.61113095220003</v>
       </c>
       <c r="D33" s="96">
-        <v>439.00999999959998</v>
+        <v>667.99600000179998</v>
       </c>
       <c r="E33" s="96">
-        <v>2806120.8392654946</v>
+        <v>4669958.7290065279</v>
       </c>
       <c r="F33" s="96">
         <v>0</v>
@@ -3355,19 +3360,19 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="96" t="s">
-        <v>206</v>
+        <v>231</v>
       </c>
       <c r="B34" s="96">
         <v>1</v>
       </c>
       <c r="C34" s="96">
-        <v>-25</v>
+        <v>25.288194444399998</v>
       </c>
       <c r="D34" s="96">
-        <v>0</v>
+        <v>354.02</v>
       </c>
       <c r="E34" s="96">
-        <v>-233849</v>
+        <v>715253.15687714703</v>
       </c>
       <c r="F34" s="96">
         <v>0</v>
@@ -3381,19 +3386,19 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="96" t="s">
-        <v>162</v>
+        <v>206</v>
       </c>
       <c r="B35" s="96">
         <v>1</v>
       </c>
       <c r="C35" s="96">
-        <v>186.83611111089999</v>
+        <v>-25</v>
       </c>
       <c r="D35" s="96">
-        <v>804.41601190910001</v>
+        <v>0</v>
       </c>
       <c r="E35" s="96">
-        <v>3880349.2779353959</v>
+        <v>-233849</v>
       </c>
       <c r="F35" s="96">
         <v>0</v>
@@ -3407,19 +3412,19 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="96" t="s">
-        <v>107</v>
+        <v>162</v>
       </c>
       <c r="B36" s="96">
         <v>1</v>
       </c>
       <c r="C36" s="96">
-        <v>414.39123015899997</v>
+        <v>249.8000992058</v>
       </c>
       <c r="D36" s="96">
-        <v>2342.8888214259</v>
+        <v>1087.4160119085</v>
       </c>
       <c r="E36" s="96">
-        <v>7342359.2744361712</v>
+        <v>5027241.122842595</v>
       </c>
       <c r="F36" s="96">
         <v>0</v>
@@ -3433,19 +3438,19 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="96" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B37" s="96">
         <v>1</v>
       </c>
       <c r="C37" s="96">
-        <v>197.30909090899999</v>
+        <v>414.39123015899997</v>
       </c>
       <c r="D37" s="96">
-        <v>2277.9899999992999</v>
+        <v>2342.8888214259</v>
       </c>
       <c r="E37" s="96">
-        <v>4699575.8856638623</v>
+        <v>7342359.2744361712</v>
       </c>
       <c r="F37" s="96">
         <v>0</v>
@@ -3459,19 +3464,19 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="96" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B38" s="96">
         <v>1</v>
       </c>
       <c r="C38" s="96">
-        <v>283.9166666667</v>
+        <v>259.89242424230002</v>
       </c>
       <c r="D38" s="96">
-        <v>3082.25</v>
+        <v>2636.4299999988998</v>
       </c>
       <c r="E38" s="96">
-        <v>5825319.4707523696</v>
+        <v>5554944.6639294196</v>
       </c>
       <c r="F38" s="96">
         <v>0</v>
@@ -3485,19 +3490,19 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="96" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B39" s="96">
         <v>1</v>
       </c>
       <c r="C39" s="96">
-        <v>131.14181216910001</v>
+        <v>403.9166666667</v>
       </c>
       <c r="D39" s="96">
-        <v>471.4394986822</v>
+        <v>4611.43</v>
       </c>
       <c r="E39" s="96">
-        <v>3150944.560423614</v>
+        <v>8252554.4917521486</v>
       </c>
       <c r="F39" s="96">
         <v>0</v>
@@ -3511,19 +3516,19 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="96" t="s">
-        <v>140</v>
+        <v>109</v>
       </c>
       <c r="B40" s="96">
         <v>1</v>
       </c>
       <c r="C40" s="96">
-        <v>548.43968253950004</v>
+        <v>319.48347883600002</v>
       </c>
       <c r="D40" s="96">
-        <v>4046.0241666669999</v>
+        <v>1582.4444986829001</v>
       </c>
       <c r="E40" s="96">
-        <v>7402539.5016198214</v>
+        <v>4507114.506957056</v>
       </c>
       <c r="F40" s="96">
         <v>0</v>
@@ -3537,19 +3542,19 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="96" t="s">
-        <v>217</v>
+        <v>140</v>
       </c>
       <c r="B41" s="96">
         <v>1</v>
       </c>
       <c r="C41" s="96">
-        <v>6</v>
+        <v>548.18968253950004</v>
       </c>
       <c r="D41" s="96">
-        <v>81</v>
+        <v>4043.0241666669999</v>
       </c>
       <c r="E41" s="96">
-        <v>149294.68419999999</v>
+        <v>7398936.6723073218</v>
       </c>
       <c r="F41" s="96">
         <v>0</v>
@@ -3563,19 +3568,19 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="96" t="s">
-        <v>145</v>
+        <v>217</v>
       </c>
       <c r="B42" s="96">
         <v>1</v>
       </c>
       <c r="C42" s="96">
-        <v>-6.2142857142999999</v>
+        <v>11</v>
       </c>
       <c r="D42" s="96">
-        <v>-6.2810714286999998</v>
+        <v>126.04</v>
       </c>
       <c r="E42" s="96">
-        <v>-275260.76904147147</v>
+        <v>280769.63740000001</v>
       </c>
       <c r="F42" s="96">
         <v>0</v>
@@ -3589,19 +3594,19 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="96" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B43" s="96">
         <v>1</v>
       </c>
       <c r="C43" s="96">
-        <v>-3.2847222223000001</v>
+        <v>-6.2142857142999999</v>
       </c>
       <c r="D43" s="96">
-        <v>-20.505000001599999</v>
+        <v>-6.2810714286999998</v>
       </c>
       <c r="E43" s="96">
-        <v>-402349.89063324447</v>
+        <v>-275260.76904147147</v>
       </c>
       <c r="F43" s="96">
         <v>0</v>
@@ -3615,19 +3620,19 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="96" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="B44" s="96">
         <v>1</v>
       </c>
       <c r="C44" s="96">
-        <v>184.42559523840001</v>
+        <v>-3.2847222223000001</v>
       </c>
       <c r="D44" s="96">
-        <v>2016.0000000025</v>
+        <v>-20.505000001599999</v>
       </c>
       <c r="E44" s="96">
-        <v>3629491.4663937623</v>
+        <v>-402349.89063324447</v>
       </c>
       <c r="F44" s="96">
         <v>0</v>
@@ -3636,6 +3641,58 @@
         <v>0</v>
       </c>
       <c r="H44" s="96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="96" t="s">
+        <v>156</v>
+      </c>
+      <c r="B45" s="96">
+        <v>1</v>
+      </c>
+      <c r="C45" s="96">
+        <v>217.31500000029999</v>
+      </c>
+      <c r="D45" s="96">
+        <v>2178.0000000025002</v>
+      </c>
+      <c r="E45" s="96">
+        <v>4246358.1772271991</v>
+      </c>
+      <c r="F45" s="96">
+        <v>0</v>
+      </c>
+      <c r="G45" s="96">
+        <v>0</v>
+      </c>
+      <c r="H45" s="96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="96" t="s">
+        <v>232</v>
+      </c>
+      <c r="B46" s="96">
+        <v>1</v>
+      </c>
+      <c r="C46" s="96">
+        <v>101.875</v>
+      </c>
+      <c r="D46" s="96">
+        <v>-24.9999999996</v>
+      </c>
+      <c r="E46" s="96">
+        <v>136464.048396092</v>
+      </c>
+      <c r="F46" s="96">
+        <v>0</v>
+      </c>
+      <c r="G46" s="96">
+        <v>0</v>
+      </c>
+      <c r="H46" s="96">
         <v>0</v>
       </c>
     </row>
@@ -3716,44 +3773,44 @@
       </c>
       <c r="D2" s="59">
         <f>IFERROR(+VLOOKUP(B2,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>10180781.322442733</v>
+      </c>
+      <c r="E2" s="59">
         <v>6538018.3834050605</v>
-      </c>
-      <c r="E2" s="59">
-        <v>4682028.2206923608</v>
       </c>
       <c r="F2" s="59">
         <f t="shared" ref="F2:F9" si="0">+D2-E2</f>
-        <v>1855990.1627126997</v>
+        <v>3642762.9390376722</v>
       </c>
       <c r="G2" s="60">
         <f t="shared" ref="G2:G41" si="1">+D2/C2</f>
-        <v>0.20254663591143432</v>
+        <v>0.31539877786895837</v>
       </c>
       <c r="H2" s="59">
         <f>+D2/$N$3*$N$4</f>
-        <v>52304147.067240477</v>
+        <v>61084687.934656397</v>
       </c>
       <c r="I2" s="60">
         <f t="shared" ref="I2:I41" si="2">+H2/C2</f>
-        <v>1.6203730872914743</v>
+        <v>1.8923926672137501</v>
       </c>
       <c r="J2" s="59">
         <f>+D2/$N$3</f>
-        <v>2179339.46113502</v>
+        <v>2545195.3306106832</v>
       </c>
       <c r="K2" s="59">
         <f t="shared" ref="K2:K41" si="3">+(C2-D2)/$N$2</f>
-        <v>1225764.6788021759</v>
+        <v>1104914.765790401</v>
       </c>
       <c r="L2" s="61" cm="1">
         <f t="array" ref="L2">+_xlfn.IFS(I2&gt;114%,H2*0.02,I2&gt;109%,H2*0.015,I2&gt;104%,H2*0.0125,I2&gt;99%,H2*0.01,I2&lt;99%,H2*0)</f>
-        <v>1046082.9413448096</v>
+        <v>1221693.7586931279</v>
       </c>
       <c r="M2" s="53" t="s">
         <v>36</v>
       </c>
       <c r="N2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -3766,45 +3823,45 @@
       </c>
       <c r="D3" s="4">
         <f>IFERROR(+VLOOKUP(B3,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>6362623.1530077159</v>
+      </c>
+      <c r="E3" s="4">
         <v>5092283.3348378455</v>
-      </c>
-      <c r="E3" s="4">
-        <v>2774896.9225576972</v>
       </c>
       <c r="F3" s="4">
         <f t="shared" si="0"/>
-        <v>2317386.4122801484</v>
+        <v>1270339.8181698704</v>
       </c>
       <c r="G3" s="5">
         <f t="shared" si="1"/>
-        <v>0.16435877774987445</v>
+        <v>0.20536032580062649</v>
       </c>
       <c r="H3" s="4">
         <f t="shared" ref="H3:H41" si="4">+D3/$N$3*$N$4</f>
-        <v>40738266.678702764</v>
+        <v>38175738.918046296</v>
       </c>
       <c r="I3" s="5">
         <f t="shared" si="2"/>
-        <v>1.3148702219989956</v>
+        <v>1.2321619548037588</v>
       </c>
       <c r="J3" s="4">
         <f t="shared" ref="J3:J41" si="5">+D3/$N$3</f>
-        <v>1697427.7782792819</v>
+        <v>1590655.788251929</v>
       </c>
       <c r="K3" s="4">
         <f t="shared" si="3"/>
-        <v>1232878.3259069242</v>
+        <v>1231005.251293777</v>
       </c>
       <c r="L3" s="63" cm="1">
         <f t="array" ref="L3">+_xlfn.IFS(I3&gt;114%,H3*0.02,I3&gt;109%,H3*0.015,I3&gt;104%,H3*0.0125,I3&gt;99%,H3*0.01,I3&lt;99%,H3*0)</f>
-        <v>814765.33357405534</v>
+        <v>763514.77836092596</v>
       </c>
       <c r="M3" s="53" t="s">
         <v>40</v>
       </c>
       <c r="N3">
         <f>N4-N2</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -3817,38 +3874,38 @@
       </c>
       <c r="D4" s="4">
         <f>IFERROR(+VLOOKUP(B4,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>4655359.4802594241</v>
+      </c>
+      <c r="E4" s="4">
         <v>3799689.1529486589</v>
-      </c>
-      <c r="E4" s="4">
-        <v>2224929.6365325735</v>
       </c>
       <c r="F4" s="4">
         <f t="shared" si="0"/>
-        <v>1574759.5164160854</v>
+        <v>855670.32731076516</v>
       </c>
       <c r="G4" s="5">
         <f t="shared" si="1"/>
-        <v>0.13383885062086462</v>
+        <v>0.16397866693420166</v>
       </c>
       <c r="H4" s="4">
         <f t="shared" si="4"/>
-        <v>30397513.223589271</v>
+        <v>27932156.881556544</v>
       </c>
       <c r="I4" s="5">
         <f t="shared" si="2"/>
-        <v>1.070710804966917</v>
+        <v>0.98387200160521004</v>
       </c>
       <c r="J4" s="4">
         <f t="shared" si="5"/>
-        <v>1266563.0509828862</v>
+        <v>1163839.870064856</v>
       </c>
       <c r="K4" s="4">
         <f t="shared" si="3"/>
-        <v>1170968.6717714092</v>
+        <v>1186733.5889944416</v>
       </c>
       <c r="L4" s="63" cm="1">
         <f t="array" ref="L4">+_xlfn.IFS(I4&gt;114%,H4*0.02,I4&gt;109%,H4*0.015,I4&gt;104%,H4*0.0125,I4&gt;99%,H4*0.01,I4&lt;99%,H4*0)</f>
-        <v>379968.9152948659</v>
+        <v>0</v>
       </c>
       <c r="M4" s="53" t="s">
         <v>47</v>
@@ -3867,38 +3924,38 @@
       </c>
       <c r="D5" s="4">
         <f>IFERROR(+VLOOKUP(B5,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>5672001.5032034451</v>
+      </c>
+      <c r="E5" s="4">
         <v>4650179.1579327742</v>
-      </c>
-      <c r="E5" s="4">
-        <v>3752668.2666791501</v>
       </c>
       <c r="F5" s="4">
         <f t="shared" si="0"/>
-        <v>897510.89125362411</v>
+        <v>1021822.345270671</v>
       </c>
       <c r="G5" s="5">
         <f t="shared" si="1"/>
-        <v>0.16379619716940358</v>
+        <v>0.19978849093996473</v>
       </c>
       <c r="H5" s="4">
         <f t="shared" si="4"/>
-        <v>37201433.263462193</v>
+        <v>34032009.019220673</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" si="2"/>
-        <v>1.3103695773552286</v>
+        <v>1.1987309456397885</v>
       </c>
       <c r="J5" s="4">
         <f t="shared" si="5"/>
-        <v>1550059.7193109246</v>
+        <v>1418000.3758008613</v>
       </c>
       <c r="K5" s="4">
         <f t="shared" si="3"/>
-        <v>1130469.1477245467</v>
+        <v>1135901.4878472404</v>
       </c>
       <c r="L5" s="63" cm="1">
         <f t="array" ref="L5">+_xlfn.IFS(I5&gt;114%,H5*0.02,I5&gt;109%,H5*0.015,I5&gt;104%,H5*0.0125,I5&gt;99%,H5*0.01,I5&lt;99%,H5*0)</f>
-        <v>744028.66526924388</v>
+        <v>680640.18038441346</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
@@ -3911,38 +3968,38 @@
       </c>
       <c r="D6" s="4">
         <f>IFERROR(+VLOOKUP(B6,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>5810906.7980635744</v>
+      </c>
+      <c r="E6" s="4">
         <v>3454829.7358999122</v>
-      </c>
-      <c r="E6" s="4">
-        <v>1763034.9919922091</v>
       </c>
       <c r="F6" s="4">
         <f t="shared" si="0"/>
-        <v>1691794.7439077031</v>
+        <v>2356077.0621636622</v>
       </c>
       <c r="G6" s="5">
         <f t="shared" si="1"/>
-        <v>0.14683455239533538</v>
+        <v>0.24697075223084025</v>
       </c>
       <c r="H6" s="4">
         <f t="shared" si="4"/>
-        <v>27638637.887199298</v>
+        <v>34865440.788381442</v>
       </c>
       <c r="I6" s="5">
         <f t="shared" si="2"/>
-        <v>1.1746764191626831</v>
+        <v>1.4818245133850414</v>
       </c>
       <c r="J6" s="4">
         <f t="shared" si="5"/>
-        <v>1151609.9119666375</v>
+        <v>1452726.6995158936</v>
       </c>
       <c r="K6" s="4">
         <f t="shared" si="3"/>
-        <v>955899.75245810545</v>
+        <v>885890.88697282749</v>
       </c>
       <c r="L6" s="63" cm="1">
         <f t="array" ref="L6">+_xlfn.IFS(I6&gt;114%,H6*0.02,I6&gt;109%,H6*0.015,I6&gt;104%,H6*0.0125,I6&gt;99%,H6*0.01,I6&lt;99%,H6*0)</f>
-        <v>552772.75774398597</v>
+        <v>697308.81576762884</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
@@ -3955,34 +4012,34 @@
       </c>
       <c r="D7" s="4">
         <f>IFERROR(+VLOOKUP(B7,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>2938195.7767915935</v>
+      </c>
+      <c r="E7" s="4">
         <v>2229458.8498637299</v>
-      </c>
-      <c r="E7" s="4">
-        <v>1244100.7657470268</v>
       </c>
       <c r="F7" s="4">
         <f t="shared" ref="F7:F8" si="6">+D7-E7</f>
-        <v>985358.08411670313</v>
+        <v>708736.92692786362</v>
       </c>
       <c r="G7" s="5">
         <f t="shared" si="1"/>
-        <v>8.0364441623913901E-2</v>
+        <v>0.10591200774933836</v>
       </c>
       <c r="H7" s="4">
         <f t="shared" si="4"/>
-        <v>17835670.798909839</v>
+        <v>17629174.660749562</v>
       </c>
       <c r="I7" s="5">
         <f t="shared" si="2"/>
-        <v>0.64291553299131121</v>
+        <v>0.63547204649603017</v>
       </c>
       <c r="J7" s="4">
         <f t="shared" si="5"/>
-        <v>743152.94995457667</v>
+        <v>734548.94419789838</v>
       </c>
       <c r="K7" s="4">
         <f t="shared" si="3"/>
-        <v>1214876.103838132</v>
+        <v>1240183.0626836454</v>
       </c>
       <c r="L7" s="63" cm="1">
         <f t="array" ref="L7">+_xlfn.IFS(I7&gt;114%,H7*0.02,I7&gt;109%,H7*0.015,I7&gt;104%,H7*0.0125,I7&gt;99%,H7*0.01,I7&lt;99%,H7*0)</f>
@@ -3999,38 +4056,38 @@
       </c>
       <c r="D8" s="4">
         <f>IFERROR(+VLOOKUP(B8,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>6168952.3513542237</v>
+      </c>
+      <c r="E8" s="4">
         <v>4232380.5042614806</v>
-      </c>
-      <c r="E8" s="4">
-        <v>2332273.4502824824</v>
       </c>
       <c r="F8" s="4">
         <f t="shared" si="6"/>
-        <v>1900107.0539789982</v>
+        <v>1936571.847092743</v>
       </c>
       <c r="G8" s="5">
         <f t="shared" si="1"/>
-        <v>0.11812040044839839</v>
+        <v>0.17216767758838331</v>
       </c>
       <c r="H8" s="4">
         <f t="shared" si="4"/>
-        <v>33859044.034091845</v>
+        <v>37013714.108125344</v>
       </c>
       <c r="I8" s="5">
         <f t="shared" si="2"/>
-        <v>0.94496320358718711</v>
+        <v>1.0330060655302999</v>
       </c>
       <c r="J8" s="4">
         <f t="shared" si="5"/>
-        <v>1410793.5014204935</v>
+        <v>1542238.0878385559</v>
       </c>
       <c r="K8" s="4">
         <f t="shared" si="3"/>
-        <v>1504699.5672693441</v>
+        <v>1483105.9532781742</v>
       </c>
       <c r="L8" s="63" cm="1">
         <f t="array" ref="L8">+_xlfn.IFS(I8&gt;114%,H8*0.02,I8&gt;109%,H8*0.015,I8&gt;104%,H8*0.0125,I8&gt;99%,H8*0.01,I8&lt;99%,H8*0)</f>
-        <v>0</v>
+        <v>370137.14108125347</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
@@ -4043,38 +4100,38 @@
       </c>
       <c r="D9" s="4">
         <f>IFERROR(+VLOOKUP(B9,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>6899879.8473196756</v>
+      </c>
+      <c r="E9" s="4">
         <v>5960130.3637676956</v>
-      </c>
-      <c r="E9" s="4">
-        <v>4892925.4103550436</v>
       </c>
       <c r="F9" s="4">
         <f t="shared" si="0"/>
-        <v>1067204.953412652</v>
+        <v>939749.48355198</v>
       </c>
       <c r="G9" s="5">
         <f t="shared" si="1"/>
-        <v>0.16633971935747391</v>
+        <v>0.19256694188781318</v>
       </c>
       <c r="H9" s="4">
         <f t="shared" si="4"/>
-        <v>47681042.910141565</v>
+        <v>41399279.08391805</v>
       </c>
       <c r="I9" s="5">
         <f t="shared" si="2"/>
-        <v>1.3307177548597913</v>
+        <v>1.155401651326879</v>
       </c>
       <c r="J9" s="4">
         <f t="shared" si="5"/>
-        <v>1986710.1212558986</v>
+        <v>1724969.9618299189</v>
       </c>
       <c r="K9" s="4">
         <f t="shared" si="3"/>
-        <v>1422425.7644357148</v>
+        <v>1446559.5784799014</v>
       </c>
       <c r="L9" s="63" cm="1">
         <f t="array" ref="L9">+_xlfn.IFS(I9&gt;114%,H9*0.02,I9&gt;109%,H9*0.015,I9&gt;104%,H9*0.0125,I9&gt;99%,H9*0.01,I9&lt;99%,H9*0)</f>
-        <v>953620.85820283135</v>
+        <v>827985.58167836105</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4085,34 +4142,34 @@
       </c>
       <c r="D10" s="64">
         <f>+SUM(D2:D9)</f>
+        <v>48688700.232442394</v>
+      </c>
+      <c r="E10" s="65">
         <v>35956969.48291716</v>
-      </c>
-      <c r="E10" s="65">
-        <v>23666857.664838541</v>
       </c>
       <c r="F10" s="64">
         <f>+SUM(F2:F9)</f>
-        <v>12290111.818078615</v>
+        <v>12731730.749525227</v>
       </c>
       <c r="G10" s="66">
         <f t="shared" si="1"/>
-        <v>0.14798654141378115</v>
+        <v>0.2003859740391824</v>
       </c>
       <c r="H10" s="64">
         <f t="shared" si="4"/>
-        <v>287655755.86333728</v>
+        <v>292132201.39465439</v>
       </c>
       <c r="I10" s="66">
         <f t="shared" si="2"/>
-        <v>1.1838923313102492</v>
+        <v>1.2023158442350945</v>
       </c>
       <c r="J10" s="64">
         <f t="shared" si="5"/>
-        <v>11985656.494305721</v>
+        <v>12172175.058110598</v>
       </c>
       <c r="K10" s="67">
         <f t="shared" si="3"/>
-        <v>9857982.0122063495</v>
+        <v>9714294.5753404051</v>
       </c>
       <c r="L10" s="68"/>
     </row>
@@ -4128,38 +4185,38 @@
       </c>
       <c r="D11" s="59">
         <f>IFERROR(+VLOOKUP(B11,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>21714287.032106198</v>
+      </c>
+      <c r="E11" s="59">
         <v>18543635.055367131</v>
-      </c>
-      <c r="E11" s="59">
-        <v>7023074.0484903501</v>
       </c>
       <c r="F11" s="59">
         <f t="shared" ref="F11:F16" si="7">+D11-E11</f>
-        <v>11520561.006876782</v>
+        <v>3170651.9767390676</v>
       </c>
       <c r="G11" s="60">
         <f t="shared" si="1"/>
-        <v>0.19122679647058316</v>
+        <v>0.22392338580835955</v>
       </c>
       <c r="H11" s="59">
         <f t="shared" si="4"/>
-        <v>148349080.44293705</v>
+        <v>130285722.19263719</v>
       </c>
       <c r="I11" s="60">
         <f t="shared" si="2"/>
-        <v>1.5298143717646653</v>
+        <v>1.3435403148501575</v>
       </c>
       <c r="J11" s="59">
         <f t="shared" si="5"/>
-        <v>6181211.6851223772</v>
+        <v>5428571.7580265496</v>
       </c>
       <c r="K11" s="59">
         <f t="shared" si="3"/>
-        <v>3734681.5916557326</v>
+        <v>3762883.0724015655</v>
       </c>
       <c r="L11" s="61" cm="1">
         <f t="array" ref="L11">+_xlfn.IFS(I11&gt;114%,H11*0.0125,I11&gt;109%,H11*0.01,I11&gt;104%,H11*0.0075,I11&gt;99%,H11*0.005,I11&lt;99%,H11*0)</f>
-        <v>1854363.5055367132</v>
+        <v>1628571.5274079649</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4175,11 +4232,11 @@
         <v>7342359.2744361712</v>
       </c>
       <c r="E12" s="4">
-        <v>7395442.6965926401</v>
+        <v>7342359.2744361712</v>
       </c>
       <c r="F12" s="4">
         <f t="shared" si="7"/>
-        <v>-53083.422156468965</v>
+        <v>0</v>
       </c>
       <c r="G12" s="5">
         <f t="shared" si="1"/>
@@ -4187,23 +4244,23 @@
       </c>
       <c r="H12" s="4">
         <f t="shared" si="4"/>
-        <v>58738874.195489362</v>
+        <v>44054155.646617025</v>
       </c>
       <c r="I12" s="5">
         <f t="shared" si="2"/>
-        <v>1.8570091183860868</v>
+        <v>1.3927568387895652</v>
       </c>
       <c r="J12" s="4">
         <f t="shared" si="5"/>
-        <v>2447453.0914787236</v>
+        <v>1835589.8186090428</v>
       </c>
       <c r="K12" s="4">
         <f t="shared" si="3"/>
-        <v>1156597.2921014682</v>
+        <v>1214427.1567065415</v>
       </c>
       <c r="L12" s="63" cm="1">
         <f t="array" ref="L12">+_xlfn.IFS(I12&gt;114%,H12*0.02,I12&gt;109%,H12*0.015,I12&gt;104%,H12*0.0125,I12&gt;99%,H12*0.01,I12&lt;99%,H12*0)</f>
-        <v>1174777.4839097874</v>
+        <v>881083.11293234047</v>
       </c>
       <c r="M12" s="27"/>
     </row>
@@ -4217,38 +4274,38 @@
       </c>
       <c r="D13" s="4">
         <f>IFERROR(+VLOOKUP(B13,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>38609317.055148289</v>
+      </c>
+      <c r="E13" s="4">
         <v>35677866.984969728</v>
-      </c>
-      <c r="E13" s="4">
-        <v>27711765.916719597</v>
       </c>
       <c r="F13" s="4">
         <f t="shared" si="7"/>
-        <v>7966101.0682501309</v>
+        <v>2931450.0701785609</v>
       </c>
       <c r="G13" s="5">
         <f t="shared" si="1"/>
-        <v>0.27794311731832977</v>
+        <v>0.30078014317281015</v>
       </c>
       <c r="H13" s="4">
         <f t="shared" si="4"/>
-        <v>285422935.87975782</v>
+        <v>231655902.33088973</v>
       </c>
       <c r="I13" s="5">
         <f t="shared" si="2"/>
-        <v>2.2235449385466382</v>
+        <v>1.8046808590368608</v>
       </c>
       <c r="J13" s="4">
         <f t="shared" si="5"/>
-        <v>11892622.328323243</v>
+        <v>9652329.2637870722</v>
       </c>
       <c r="K13" s="4">
         <f t="shared" si="3"/>
-        <v>4413621.3852216788</v>
+        <v>4487729.9509738348</v>
       </c>
       <c r="L13" s="63" cm="1">
         <f t="array" ref="L13">+_xlfn.IFS(I13&gt;114%,H13*0.0125,I13&gt;109%,H13*0.01,I13&gt;104%,H13*0.0075,I13&gt;99%,H13*0.005,I13&lt;99%,H13*0)</f>
-        <v>3567786.6984969731</v>
+        <v>2895698.7791361217</v>
       </c>
       <c r="M13" s="53" t="s">
         <v>61</v>
@@ -4267,34 +4324,34 @@
       </c>
       <c r="D14" s="4">
         <f>IFERROR(+VLOOKUP(B14,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>5554944.6639294196</v>
+      </c>
+      <c r="E14" s="4">
         <v>4699575.8856638623</v>
-      </c>
-      <c r="E14" s="4">
-        <v>968840.97419863928</v>
       </c>
       <c r="F14" s="4">
         <f t="shared" si="7"/>
-        <v>3730734.9114652229</v>
+        <v>855368.77826555725</v>
       </c>
       <c r="G14" s="5">
         <f t="shared" si="1"/>
-        <v>0.11071095977316531</v>
+        <v>0.13086143732809949</v>
       </c>
       <c r="H14" s="4">
         <f t="shared" si="4"/>
-        <v>37596607.085310899</v>
+        <v>33329667.983576518</v>
       </c>
       <c r="I14" s="5">
         <f t="shared" si="2"/>
-        <v>0.88568767818532246</v>
+        <v>0.78516862396859699</v>
       </c>
       <c r="J14" s="4">
         <f t="shared" si="5"/>
-        <v>1566525.2952212875</v>
+        <v>1388736.1659823549</v>
       </c>
       <c r="K14" s="4">
         <f t="shared" si="3"/>
-        <v>1797594.3575862448</v>
+        <v>1844705.6365522791</v>
       </c>
       <c r="L14" s="63" cm="1">
         <f t="array" ref="L14">+_xlfn.IFS(I14&gt;109%,H14*0.015,I14&gt;104%,H14*0.0125,I14&gt;99%,H14*0.01,I14&lt;99%,H14*0)</f>
@@ -4312,38 +4369,38 @@
       </c>
       <c r="D15" s="4">
         <f>IFERROR(+VLOOKUP(B15,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>8252554.4917521486</v>
+      </c>
+      <c r="E15" s="4">
         <v>5825319.4707523696</v>
-      </c>
-      <c r="E15" s="4">
-        <v>1445131.6450023698</v>
       </c>
       <c r="F15" s="4">
         <f t="shared" si="7"/>
-        <v>4380187.8257499998</v>
+        <v>2427235.020999779</v>
       </c>
       <c r="G15" s="5">
         <f t="shared" si="1"/>
-        <v>0.13723083216076207</v>
+        <v>0.1944107831409482</v>
       </c>
       <c r="H15" s="4">
         <f t="shared" si="4"/>
-        <v>46602555.766018957</v>
+        <v>49515326.950512893</v>
       </c>
       <c r="I15" s="5">
         <f t="shared" si="2"/>
-        <v>1.0978466572860965</v>
+        <v>1.1664646988456893</v>
       </c>
       <c r="J15" s="4">
         <f t="shared" si="5"/>
-        <v>1941773.1569174565</v>
+        <v>2063138.6229380372</v>
       </c>
       <c r="K15" s="4">
         <f t="shared" si="3"/>
-        <v>1743987.5202010777</v>
+        <v>1709825.1451611426</v>
       </c>
       <c r="L15" s="63" cm="1">
         <f t="array" ref="L15">+_xlfn.IFS(I15&gt;109%,H15*0.015,I15&gt;104%,H15*0.0125,I15&gt;99%,H15*0.01,I15&lt;99%,H15*0)</f>
-        <v>699038.3364902843</v>
+        <v>742729.90425769333</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4354,34 +4411,34 @@
       </c>
       <c r="D16" s="64">
         <f>+SUM(D11:D15)</f>
+        <v>81473462.517372221</v>
+      </c>
+      <c r="E16" s="65">
         <v>72088756.671189263</v>
-      </c>
-      <c r="E16" s="65">
-        <v>44544255.281003602</v>
       </c>
       <c r="F16" s="64">
         <f t="shared" si="7"/>
-        <v>27544501.390185662</v>
+        <v>9384705.8461829573</v>
       </c>
       <c r="G16" s="66">
         <f t="shared" si="1"/>
-        <v>0.21086914894994976</v>
+        <v>0.23832065493106369</v>
       </c>
       <c r="H16" s="64">
         <f t="shared" si="4"/>
-        <v>576710053.36951411</v>
+        <v>488840775.10423332</v>
       </c>
       <c r="I16" s="66">
         <f t="shared" si="2"/>
-        <v>1.6869531915995981</v>
+        <v>1.4299239295863821</v>
       </c>
       <c r="J16" s="64">
         <f t="shared" si="5"/>
-        <v>24029585.557063088</v>
+        <v>20368365.629343055</v>
       </c>
       <c r="K16" s="67">
         <f t="shared" si="3"/>
-        <v>12846482.146766203</v>
+        <v>13019570.961795364</v>
       </c>
       <c r="L16" s="68"/>
     </row>
@@ -4397,34 +4454,34 @@
       </c>
       <c r="D17" s="59">
         <f>IFERROR(+VLOOKUP(B17,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>3831780.4656781647</v>
+      </c>
+      <c r="E17" s="59">
         <v>3490474.4748070529</v>
-      </c>
-      <c r="E17" s="59">
-        <v>1647814.3144255385</v>
       </c>
       <c r="F17" s="59">
         <f t="shared" ref="F17:F40" si="8">+D17-E17</f>
-        <v>1842660.1603815143</v>
+        <v>341305.99087111186</v>
       </c>
       <c r="G17" s="60">
         <f t="shared" si="1"/>
-        <v>0.11897444670744077</v>
+        <v>0.13060802022729012</v>
       </c>
       <c r="H17" s="59">
         <f t="shared" si="4"/>
-        <v>27923795.798456423</v>
+        <v>22990682.794068988</v>
       </c>
       <c r="I17" s="60">
         <f t="shared" si="2"/>
-        <v>0.95179557365952616</v>
+        <v>0.78364812136374074</v>
       </c>
       <c r="J17" s="59">
         <f t="shared" si="5"/>
-        <v>1163491.491602351</v>
+        <v>957945.11641954118</v>
       </c>
       <c r="K17" s="59">
         <f t="shared" si="3"/>
-        <v>1230835.4122710929</v>
+        <v>1275311.8833410919</v>
       </c>
       <c r="L17" s="61" cm="1">
         <f t="array" ref="L17">+_xlfn.IFS(I17&gt;114%,H17*0.02,I17&gt;109%,H17*0.015,I17&gt;104%,H17*0.0125,I17&gt;99%,H17*0.01,I17&lt;99%,H17*0)</f>
@@ -4441,34 +4498,34 @@
       </c>
       <c r="D18" s="4">
         <f>IFERROR(+VLOOKUP(B18,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>3383340.6159000443</v>
+      </c>
+      <c r="E18" s="4">
         <v>2539362.2668490014</v>
-      </c>
-      <c r="E18" s="4">
-        <v>1318807.9914469167</v>
       </c>
       <c r="F18" s="4">
         <f t="shared" si="8"/>
-        <v>1220554.2754020847</v>
+        <v>843978.34905104293</v>
       </c>
       <c r="G18" s="5">
         <f t="shared" si="1"/>
-        <v>0.10173928430406153</v>
+        <v>0.13555318881132356</v>
       </c>
       <c r="H18" s="4">
         <f t="shared" si="4"/>
-        <v>20314898.134792011</v>
+        <v>20300043.695400268</v>
       </c>
       <c r="I18" s="5">
         <f t="shared" si="2"/>
-        <v>0.8139142744324922</v>
+        <v>0.81331913286794133</v>
       </c>
       <c r="J18" s="4">
         <f t="shared" si="5"/>
-        <v>846454.08894966717</v>
+        <v>845835.15397501108</v>
       </c>
       <c r="K18" s="4">
         <f t="shared" si="3"/>
-        <v>1067625.8872929048</v>
+        <v>1078808.264204998</v>
       </c>
       <c r="L18" s="63" cm="1">
         <f t="array" ref="L18">+_xlfn.IFS(I18&gt;114%,H18*0.02,I18&gt;109%,H18*0.015,I18&gt;104%,H18*0.0125,I18&gt;99%,H18*0.01,I18&lt;99%,H18*0)</f>
@@ -4485,34 +4542,34 @@
       </c>
       <c r="D19" s="4">
         <f>IFERROR(+VLOOKUP(B19,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>4172472.7522102422</v>
+      </c>
+      <c r="E19" s="4">
         <v>3126324.9965506792</v>
-      </c>
-      <c r="E19" s="4">
-        <v>1974051.5620993127</v>
       </c>
       <c r="F19" s="4">
         <f t="shared" si="8"/>
-        <v>1152273.4344513665</v>
+        <v>1046147.755659563</v>
       </c>
       <c r="G19" s="5">
         <f t="shared" si="1"/>
-        <v>0.12090990041401692</v>
+        <v>0.16136942432618312</v>
       </c>
       <c r="H19" s="4">
         <f t="shared" si="4"/>
-        <v>25010599.972405434</v>
+        <v>25034836.513261452</v>
       </c>
       <c r="I19" s="5">
         <f t="shared" si="2"/>
-        <v>0.96727920331213535</v>
+        <v>0.96821654595709861</v>
       </c>
       <c r="J19" s="4">
         <f t="shared" si="5"/>
-        <v>1042108.3321835598</v>
+        <v>1043118.1880525606</v>
       </c>
       <c r="K19" s="4">
         <f t="shared" si="3"/>
-        <v>1082396.4366166343</v>
+        <v>1084208.8706644881</v>
       </c>
       <c r="L19" s="63" cm="1">
         <f t="array" ref="L19">+_xlfn.IFS(I19&gt;114%,H19*0.02,I19&gt;109%,H19*0.015,I19&gt;104%,H19*0.0125,I19&gt;99%,H19*0.01,I19&lt;99%,H19*0)</f>
@@ -4529,38 +4586,38 @@
       </c>
       <c r="D20" s="4">
         <f>IFERROR(+VLOOKUP(B20,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>8068602.606727235</v>
+      </c>
+      <c r="E20" s="4">
         <v>5313079.7996425815</v>
-      </c>
-      <c r="E20" s="4">
-        <v>3804498.4929125779</v>
       </c>
       <c r="F20" s="4">
         <f t="shared" si="8"/>
-        <v>1508581.3067300036</v>
+        <v>2755522.8070846535</v>
       </c>
       <c r="G20" s="5">
         <f t="shared" si="1"/>
-        <v>0.15837186155063132</v>
+        <v>0.24050826698022318</v>
       </c>
       <c r="H20" s="4">
         <f t="shared" si="4"/>
-        <v>42504638.397140652</v>
+        <v>48411615.64036341</v>
       </c>
       <c r="I20" s="5">
         <f t="shared" si="2"/>
-        <v>1.2669748924050506</v>
+        <v>1.4430496018813392</v>
       </c>
       <c r="J20" s="4">
         <f t="shared" si="5"/>
-        <v>1771026.5998808604</v>
+        <v>2017150.6516818088</v>
       </c>
       <c r="K20" s="4">
         <f t="shared" si="3"/>
-        <v>1344526.2000170199</v>
+        <v>1273976.3696636383</v>
       </c>
       <c r="L20" s="63" cm="1">
         <f t="array" ref="L20">+_xlfn.IFS(I20&gt;114%,H20*0.02,I20&gt;109%,H20*0.015,I20&gt;104%,H20*0.0125,I20&gt;99%,H20*0.01,I20&lt;99%,H20*0)</f>
-        <v>850092.76794281311</v>
+        <v>968232.31280726823</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4573,38 +4630,38 @@
       </c>
       <c r="D21" s="4">
         <f>IFERROR(+VLOOKUP(B21,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>4521737.6382463202</v>
+      </c>
+      <c r="E21" s="4">
         <v>3621062.6775038806</v>
-      </c>
-      <c r="E21" s="4">
-        <v>2482567.9113498144</v>
       </c>
       <c r="F21" s="4">
         <f t="shared" ref="F21:F23" si="9">+D21-E21</f>
-        <v>1138494.7661540662</v>
+        <v>900674.96074243961</v>
       </c>
       <c r="G21" s="5">
         <f t="shared" si="1"/>
-        <v>0.14223388083214142</v>
+        <v>0.17761202985745514</v>
       </c>
       <c r="H21" s="4">
         <f t="shared" si="4"/>
-        <v>28968501.420031041</v>
+        <v>27130425.829477921</v>
       </c>
       <c r="I21" s="5">
         <f t="shared" si="2"/>
-        <v>1.1378710466571311</v>
+        <v>1.0656721791447308</v>
       </c>
       <c r="J21" s="4">
         <f t="shared" si="5"/>
-        <v>1207020.8925012934</v>
+        <v>1130434.40956158</v>
       </c>
       <c r="K21" s="4">
         <f t="shared" si="3"/>
-        <v>1039878.4439283867</v>
+        <v>1046838.618087684</v>
       </c>
       <c r="L21" s="63" cm="1">
         <f t="array" ref="L21">+_xlfn.IFS(I21&gt;114%,H21*0.02,I21&gt;109%,H21*0.015,I21&gt;104%,H21*0.0125,I21&gt;99%,H21*0.01,I21&lt;99%,H21*0)</f>
-        <v>434527.52130046563</v>
+        <v>339130.32286847406</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4617,38 +4674,38 @@
       </c>
       <c r="D22" s="4">
         <f>IFERROR(+VLOOKUP(B22,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>6604601.1312453747</v>
+      </c>
+      <c r="E22" s="4">
         <v>4525419.7648018571</v>
-      </c>
-      <c r="E22" s="4">
-        <v>3717567.9331198842</v>
       </c>
       <c r="F22" s="4">
         <f t="shared" si="9"/>
-        <v>807851.83168197284</v>
+        <v>2079181.3664435176</v>
       </c>
       <c r="G22" s="5">
         <f t="shared" si="1"/>
-        <v>0.14256483062156253</v>
+        <v>0.20806552552815036</v>
       </c>
       <c r="H22" s="4">
         <f t="shared" si="4"/>
-        <v>36203358.118414856</v>
+        <v>39627606.787472248</v>
       </c>
       <c r="I22" s="5">
         <f t="shared" si="2"/>
-        <v>1.1405186449725002</v>
+        <v>1.2483931531689021</v>
       </c>
       <c r="J22" s="4">
         <f t="shared" si="5"/>
-        <v>1508473.2549339524</v>
+        <v>1651150.2828113437</v>
       </c>
       <c r="K22" s="4">
         <f t="shared" si="3"/>
-        <v>1296070.0207237212</v>
+        <v>1256914.4534377314</v>
       </c>
       <c r="L22" s="63" cm="1">
         <f t="array" ref="L22">+_xlfn.IFS(I22&gt;114%,H22*0.02,I22&gt;109%,H22*0.015,I22&gt;104%,H22*0.0125,I22&gt;99%,H22*0.01,I22&lt;99%,H22*0)</f>
-        <v>724067.16236829711</v>
+        <v>792552.13574944495</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4661,38 +4718,38 @@
       </c>
       <c r="D23" s="4">
         <f>IFERROR(+VLOOKUP(B23,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>5027241.122842595</v>
+      </c>
+      <c r="E23" s="4">
         <v>3880349.2779353959</v>
-      </c>
-      <c r="E23" s="4">
-        <v>2007902.2622231084</v>
       </c>
       <c r="F23" s="4">
         <f t="shared" si="9"/>
-        <v>1872447.0157122875</v>
+        <v>1146891.844907199</v>
       </c>
       <c r="G23" s="5">
         <f t="shared" si="1"/>
-        <v>0.1414330399034098</v>
+        <v>0.18323556551315615</v>
       </c>
       <c r="H23" s="4">
         <f t="shared" si="4"/>
-        <v>31042794.223483168</v>
+        <v>30163446.73705557</v>
       </c>
       <c r="I23" s="5">
         <f t="shared" si="2"/>
-        <v>1.1314643192272784</v>
+        <v>1.0994133930789369</v>
       </c>
       <c r="J23" s="4">
         <f t="shared" si="5"/>
-        <v>1293449.7593117987</v>
+        <v>1256810.2807106487</v>
       </c>
       <c r="K23" s="4">
         <f t="shared" si="3"/>
-        <v>1121695.0929554575</v>
+        <v>1120435.2553578704</v>
       </c>
       <c r="L23" s="63" cm="1">
         <f t="array" ref="L23">+_xlfn.IFS(I23&gt;114%,H23*0.02,I23&gt;109%,H23*0.015,I23&gt;104%,H23*0.0125,I23&gt;99%,H23*0.01,I23&lt;99%,H23*0)</f>
-        <v>465641.9133522475</v>
+        <v>452451.70105583355</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4705,34 +4762,34 @@
       </c>
       <c r="D24" s="4">
         <f>IFERROR(+VLOOKUP(B24,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>4507114.506957056</v>
+      </c>
+      <c r="E24" s="4">
         <v>3150944.560423614</v>
-      </c>
-      <c r="E24" s="4">
-        <v>2373341.2642009868</v>
       </c>
       <c r="F24" s="4">
         <f t="shared" si="8"/>
-        <v>777603.29622262716</v>
+        <v>1356169.946533442</v>
       </c>
       <c r="G24" s="5">
         <f t="shared" si="1"/>
-        <v>9.407474133614499E-2</v>
+        <v>0.13456461174847464</v>
       </c>
       <c r="H24" s="4">
         <f t="shared" si="4"/>
-        <v>25207556.483388916</v>
+        <v>27042687.041742336</v>
       </c>
       <c r="I24" s="5">
         <f t="shared" si="2"/>
-        <v>0.75259793068916003</v>
+        <v>0.80738767049084792</v>
       </c>
       <c r="J24" s="4">
         <f t="shared" si="5"/>
-        <v>1050314.8534745381</v>
+        <v>1126778.626739264</v>
       </c>
       <c r="K24" s="4">
         <f t="shared" si="3"/>
-        <v>1444910.020932209</v>
+        <v>1449347.0246521472</v>
       </c>
       <c r="L24" s="63" cm="1">
         <f t="array" ref="L24">+_xlfn.IFS(I24&gt;114%,H24*0.02,I24&gt;109%,H24*0.015,I24&gt;104%,H24*0.0125,I24&gt;99%,H24*0.01,I24&lt;99%,H24*0)</f>
@@ -4749,38 +4806,38 @@
       </c>
       <c r="D25" s="4">
         <f>IFERROR(+VLOOKUP(B25,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>7398936.6723073218</v>
+      </c>
+      <c r="E25" s="4">
         <v>7402539.5016198214</v>
-      </c>
-      <c r="E25" s="4">
-        <v>-2433547.0814999999</v>
       </c>
       <c r="F25" s="4">
         <f t="shared" si="8"/>
-        <v>9836086.5831198208</v>
+        <v>-3602.8293124996126</v>
       </c>
       <c r="G25" s="5">
         <f t="shared" si="1"/>
-        <v>0.13691937400008347</v>
+        <v>0.13685273509407175</v>
       </c>
       <c r="H25" s="4">
         <f t="shared" si="4"/>
-        <v>59220316.012958571</v>
+        <v>44393620.033843935</v>
       </c>
       <c r="I25" s="5">
         <f t="shared" si="2"/>
-        <v>1.0953549920006678</v>
+        <v>0.82111641056443052</v>
       </c>
       <c r="J25" s="4">
         <f t="shared" si="5"/>
-        <v>2467513.1672066073</v>
+        <v>1849734.1680768305</v>
       </c>
       <c r="K25" s="4">
         <f t="shared" si="3"/>
-        <v>2222019.6839704849</v>
+        <v>2333300.8096346343</v>
       </c>
       <c r="L25" s="63" cm="1">
         <f t="array" ref="L25">+_xlfn.IFS(I25&gt;109%,H25*0.015,I25&gt;104%,H25*0.0125,I25&gt;99%,H25*0.01,I25&lt;99%,H25*0)</f>
-        <v>888304.74019437854</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4791,34 +4848,34 @@
       </c>
       <c r="D26" s="67">
         <f>+SUM(D17:D25)</f>
+        <v>47515827.512114353</v>
+      </c>
+      <c r="E26" s="65">
         <v>37049557.32013388</v>
-      </c>
-      <c r="E26" s="65">
-        <v>16893004.650278136</v>
       </c>
       <c r="F26" s="67">
         <f>+D26-E26</f>
-        <v>20156552.669855744</v>
+        <v>10466270.191980474</v>
       </c>
       <c r="G26" s="66">
         <f t="shared" si="1"/>
-        <v>0.12958982569357178</v>
+        <v>0.16619814784222828</v>
       </c>
       <c r="H26" s="64">
         <f t="shared" si="4"/>
-        <v>296396458.56107104</v>
+        <v>285094965.07268614</v>
       </c>
       <c r="I26" s="66">
         <f t="shared" si="2"/>
-        <v>1.0367186055485742</v>
+        <v>0.99718888705336972</v>
       </c>
       <c r="J26" s="64">
         <f t="shared" si="5"/>
-        <v>12349852.440044627</v>
+        <v>11878956.878028588</v>
       </c>
       <c r="K26" s="67">
         <f t="shared" si="3"/>
-        <v>11849957.198707912</v>
+        <v>11919141.549044285</v>
       </c>
       <c r="L26" s="68"/>
     </row>
@@ -4834,38 +4891,38 @@
       </c>
       <c r="D27" s="59">
         <f>IFERROR(+VLOOKUP(B27,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>14993819.966923174</v>
+      </c>
+      <c r="E27" s="59">
         <v>7197381.3632933144</v>
-      </c>
-      <c r="E27" s="59">
-        <v>5151540.6591492426</v>
       </c>
       <c r="F27" s="59">
         <f t="shared" si="8"/>
-        <v>2045840.7041440718</v>
+        <v>7796438.6036298592</v>
       </c>
       <c r="G27" s="60">
         <f t="shared" si="1"/>
-        <v>8.7796819907039525E-2</v>
+        <v>0.1829012032165232</v>
       </c>
       <c r="H27" s="59">
         <f t="shared" si="4"/>
-        <v>57579050.906346515</v>
+        <v>89962919.801539034</v>
       </c>
       <c r="I27" s="60">
         <f t="shared" si="2"/>
-        <v>0.7023745592563162</v>
+        <v>1.0974072192991391</v>
       </c>
       <c r="J27" s="59">
         <f t="shared" si="5"/>
-        <v>2399127.1210977715</v>
+        <v>3748454.9917307934</v>
       </c>
       <c r="K27" s="59">
         <f t="shared" si="3"/>
-        <v>3560967.5541288895</v>
+        <v>3349194.0016538412</v>
       </c>
       <c r="L27" s="61" cm="1">
         <f t="array" ref="L27">+_xlfn.IFS(I27&gt;114%,H27*0.0125,I27&gt;109%,H27*0.01,I27&gt;104%,H27*0.0075,I27&gt;99%,H27*0.005,I27&lt;99%,H27*0)</f>
-        <v>0</v>
+        <v>899629.19801539031</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4878,34 +4935,34 @@
       </c>
       <c r="D28" s="4">
         <f>IFERROR(+VLOOKUP(B28,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>2246997.9859188953</v>
+      </c>
+      <c r="E28" s="4">
         <v>1662817.6962441357</v>
-      </c>
-      <c r="E28" s="4">
-        <v>1127867.2813395613</v>
       </c>
       <c r="F28" s="4">
         <f t="shared" si="8"/>
-        <v>534950.4149045744</v>
+        <v>584180.28967475961</v>
       </c>
       <c r="G28" s="5">
         <f t="shared" si="1"/>
-        <v>7.9181795059244553E-2</v>
+        <v>0.10699990409137597</v>
       </c>
       <c r="H28" s="4">
         <f t="shared" si="4"/>
-        <v>13302541.569953088</v>
+        <v>13481987.915513372</v>
       </c>
       <c r="I28" s="5">
         <f t="shared" si="2"/>
-        <v>0.63345436047395653</v>
+        <v>0.64199942454825576</v>
       </c>
       <c r="J28" s="4">
         <f t="shared" si="5"/>
-        <v>554272.56541471195</v>
+        <v>561749.49647972384</v>
       </c>
       <c r="K28" s="4">
         <f t="shared" si="3"/>
-        <v>920818.2049407555</v>
+        <v>937650.10070405528</v>
       </c>
       <c r="L28" s="63" cm="1">
         <f t="array" ref="L28">+_xlfn.IFS(I28&gt;114%,H28*0.02,I28&gt;109%,H28*0.015,I28&gt;104%,H28*0.0125,I28&gt;99%,H28*0.01,I28&lt;99%,H28*0)</f>
@@ -4922,34 +4979,34 @@
       </c>
       <c r="D29" s="4">
         <f>IFERROR(+VLOOKUP(B29,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>2863924.6281832345</v>
+      </c>
+      <c r="E29" s="4">
         <v>2237337.654012111</v>
-      </c>
-      <c r="E29" s="4">
-        <v>3336344.5485263281</v>
       </c>
       <c r="F29" s="4">
         <f t="shared" si="8"/>
-        <v>-1099006.894514217</v>
+        <v>626586.97417112347</v>
       </c>
       <c r="G29" s="5">
         <f t="shared" si="1"/>
-        <v>8.6921667852077181E-2</v>
+        <v>0.11126487986197331</v>
       </c>
       <c r="H29" s="4">
         <f t="shared" si="4"/>
-        <v>17898701.232096888</v>
+        <v>17183547.769099407</v>
       </c>
       <c r="I29" s="5">
         <f t="shared" si="2"/>
-        <v>0.69537334281661745</v>
+        <v>0.66758927917183986</v>
       </c>
       <c r="J29" s="4">
         <f t="shared" si="5"/>
-        <v>745779.21800403704</v>
+        <v>715981.15704580862</v>
       </c>
       <c r="K29" s="4">
         <f t="shared" si="3"/>
-        <v>1119160.1117137091</v>
+        <v>1143788.7685908382</v>
       </c>
       <c r="L29" s="63" cm="1">
         <f t="array" ref="L29">+_xlfn.IFS(I29&gt;114%,H29*0.02,I29&gt;109%,H29*0.015,I29&gt;104%,H29*0.0125,I29&gt;99%,H29*0.01,I29&lt;99%,H29*0)</f>
@@ -4967,34 +5024,34 @@
       </c>
       <c r="D30" s="4">
         <f>IFERROR(+VLOOKUP(B30,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>4669958.7290065279</v>
+      </c>
+      <c r="E30" s="4">
         <v>2806120.8392654946</v>
-      </c>
-      <c r="E30" s="4">
-        <v>1465987.5738126547</v>
       </c>
       <c r="F30" s="4">
         <f t="shared" si="8"/>
-        <v>1340133.2654528399</v>
+        <v>1863837.8897410333</v>
       </c>
       <c r="G30" s="5">
         <f t="shared" si="1"/>
-        <v>7.3394862686401677E-2</v>
+        <v>0.12214405554833929</v>
       </c>
       <c r="H30" s="4">
         <f t="shared" si="4"/>
-        <v>22448966.714123957</v>
+        <v>28019752.374039166</v>
       </c>
       <c r="I30" s="5">
         <f t="shared" si="2"/>
-        <v>0.58715890149121341</v>
+        <v>0.73286433329003575</v>
       </c>
       <c r="J30" s="4">
         <f t="shared" si="5"/>
-        <v>935373.61308849824</v>
+        <v>1167489.682251632</v>
       </c>
       <c r="K30" s="4">
         <f t="shared" si="3"/>
-        <v>1687004.0129933418</v>
+        <v>1678162.3191559571</v>
       </c>
       <c r="L30" s="63" cm="1">
         <f t="array" ref="L30">+_xlfn.IFS(I30&gt;114%,H30*0.02,I30&gt;109%,H30*0.015,I30&gt;104%,H30*0.0125,I30&gt;99%,H30*0.01,I30&lt;99%,H30*0)</f>
@@ -5012,38 +5069,38 @@
       </c>
       <c r="D31" s="4">
         <f>IFERROR(+VLOOKUP(B31,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>4425690.3579718489</v>
+      </c>
+      <c r="E31" s="4">
         <v>3265458.2459612871</v>
-      </c>
-      <c r="E31" s="4">
-        <v>2185400.7533588032</v>
       </c>
       <c r="F31" s="4">
         <f t="shared" si="8"/>
-        <v>1080057.4926024838</v>
+        <v>1160232.1120105619</v>
       </c>
       <c r="G31" s="5">
         <f t="shared" si="1"/>
-        <v>0.12848420715756434</v>
+        <v>0.17413522817882371</v>
       </c>
       <c r="H31" s="4">
         <f t="shared" si="4"/>
-        <v>26123665.967690296</v>
+        <v>26554142.147831094</v>
       </c>
       <c r="I31" s="5">
         <f t="shared" si="2"/>
-        <v>1.0278736572605147</v>
+        <v>1.0448113690729421</v>
       </c>
       <c r="J31" s="4">
         <f t="shared" si="5"/>
-        <v>1088486.0819870958</v>
+        <v>1106422.5894929622</v>
       </c>
       <c r="K31" s="4">
         <f t="shared" si="3"/>
-        <v>1054751.9882875578</v>
+        <v>1049477.9821014076</v>
       </c>
       <c r="L31" s="63" cm="1">
         <f t="array" ref="L31">+_xlfn.IFS(I31&gt;114%,H31*0.02,I31&gt;109%,H31*0.015,I31&gt;104%,H31*0.0125,I31&gt;99%,H31*0.01,I31&lt;99%,H31*0)</f>
-        <v>261236.65967690296</v>
+        <v>331926.77684788872</v>
       </c>
       <c r="M31" s="27"/>
     </row>
@@ -5057,34 +5114,34 @@
       </c>
       <c r="D32" s="4">
         <f>IFERROR(+VLOOKUP(B32,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>2292259.0263364343</v>
+      </c>
+      <c r="E32" s="4">
         <v>1556471.8667402903</v>
-      </c>
-      <c r="E32" s="4">
-        <v>772280.47046408884</v>
       </c>
       <c r="F32" s="4">
         <f t="shared" si="8"/>
-        <v>784191.39627620147</v>
+        <v>735787.15959614399</v>
       </c>
       <c r="G32" s="5">
         <f t="shared" si="1"/>
-        <v>6.1764756616678185E-2</v>
+        <v>9.0962659775255333E-2</v>
       </c>
       <c r="H32" s="4">
         <f t="shared" si="4"/>
-        <v>12451774.933922322</v>
+        <v>13753554.158018606</v>
       </c>
       <c r="I32" s="5">
         <f t="shared" si="2"/>
-        <v>0.49411805293342548</v>
+        <v>0.54577595865153194</v>
       </c>
       <c r="J32" s="4">
         <f t="shared" si="5"/>
-        <v>518823.95558009675</v>
+        <v>573064.75658410857</v>
       </c>
       <c r="K32" s="4">
         <f t="shared" si="3"/>
-        <v>1125882.2920599862</v>
+        <v>1145387.0486831781</v>
       </c>
       <c r="L32" s="63" cm="1">
         <f t="array" ref="L32">+_xlfn.IFS(I32&gt;114%,H32*0.02,I32&gt;109%,H32*0.015,I32&gt;104%,H32*0.0125,I32&gt;99%,H32*0.01,I32&lt;99%,H32*0)</f>
@@ -5102,34 +5159,34 @@
       </c>
       <c r="D33" s="4">
         <f>IFERROR(+VLOOKUP(B33,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>2299134.4748592312</v>
+      </c>
+      <c r="E33" s="4">
         <v>1905347.2963424551</v>
-      </c>
-      <c r="E33" s="4">
-        <v>1312962.2237802313</v>
       </c>
       <c r="F33" s="4">
         <f t="shared" si="8"/>
-        <v>592385.07256222377</v>
+        <v>393787.17851677607</v>
       </c>
       <c r="G33" s="5">
         <f t="shared" si="1"/>
-        <v>7.19087169687775E-2</v>
+        <v>8.6770433161019039E-2</v>
       </c>
       <c r="H33" s="4">
         <f t="shared" si="4"/>
-        <v>15242778.370739641</v>
+        <v>13794806.849155387</v>
       </c>
       <c r="I33" s="5">
         <f t="shared" si="2"/>
-        <v>0.57526973575022</v>
+        <v>0.52062259896611418</v>
       </c>
       <c r="J33" s="4">
         <f t="shared" si="5"/>
-        <v>635115.76544748503</v>
+        <v>574783.61871480779</v>
       </c>
       <c r="K33" s="4">
         <f t="shared" si="3"/>
-        <v>1171019.1763646449</v>
+        <v>1209880.7762570386</v>
       </c>
       <c r="L33" s="63" cm="1">
         <f t="array" ref="L33">+_xlfn.IFS(I33&gt;114%,H33*0.02,I33&gt;109%,H33*0.015,I33&gt;104%,H33*0.0125,I33&gt;99%,H33*0.01,I33&lt;99%,H33*0)</f>
@@ -5146,34 +5203,34 @@
       </c>
       <c r="D34" s="4">
         <f>IFERROR(+VLOOKUP(B34,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>1808557.8257932956</v>
+      </c>
+      <c r="E34" s="4">
         <v>1342266.2312651528</v>
-      </c>
-      <c r="E34" s="4">
-        <v>1012363.4850253685</v>
       </c>
       <c r="F34" s="4">
         <f t="shared" si="8"/>
-        <v>329902.74623978429</v>
+        <v>466291.59452814283</v>
       </c>
       <c r="G34" s="5">
         <f t="shared" si="1"/>
-        <v>6.3917439584054894E-2</v>
+        <v>8.6121801228252179E-2</v>
       </c>
       <c r="H34" s="4">
         <f t="shared" si="4"/>
-        <v>10738129.850121222</v>
+        <v>10851346.954759773</v>
       </c>
       <c r="I34" s="5">
         <f t="shared" si="2"/>
-        <v>0.51133951667243915</v>
+        <v>0.51673080736951305</v>
       </c>
       <c r="J34" s="4">
         <f t="shared" si="5"/>
-        <v>447422.07708838425</v>
+        <v>452139.45644832391</v>
       </c>
       <c r="K34" s="4">
         <f t="shared" si="3"/>
-        <v>936082.56041594502</v>
+        <v>959572.10871033522</v>
       </c>
       <c r="L34" s="63" cm="1">
         <f t="array" ref="L34">+_xlfn.IFS(I34&gt;114%,H34*0.02,I34&gt;109%,H34*0.015,I34&gt;104%,H34*0.0125,I34&gt;99%,H34*0.01,I34&lt;99%,H34*0)</f>
@@ -5190,34 +5247,34 @@
       </c>
       <c r="D35" s="4">
         <f>IFERROR(+VLOOKUP(B35,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>1134886.8601273343</v>
+      </c>
+      <c r="E35" s="4">
         <v>920475.59202497394</v>
-      </c>
-      <c r="E35" s="4">
-        <v>474208.7541035653</v>
       </c>
       <c r="F35" s="4">
         <f t="shared" si="8"/>
-        <v>446266.83792140865</v>
+        <v>214411.26810236031</v>
       </c>
       <c r="G35" s="5">
         <f t="shared" si="1"/>
-        <v>3.7329391116341579E-2</v>
+        <v>4.6024724437604296E-2</v>
       </c>
       <c r="H35" s="4">
         <f t="shared" si="4"/>
-        <v>7363804.7361997925</v>
+        <v>6809321.160764005</v>
       </c>
       <c r="I35" s="5">
         <f t="shared" si="2"/>
-        <v>0.29863512893073269</v>
+        <v>0.27614834662562576</v>
       </c>
       <c r="J35" s="4">
         <f t="shared" si="5"/>
-        <v>306825.197341658</v>
+        <v>283721.71503183356</v>
       </c>
       <c r="K35" s="4">
         <f t="shared" si="3"/>
-        <v>1130367.8289511916</v>
+        <v>1176165.6569936334</v>
       </c>
       <c r="L35" s="63" cm="1">
         <f t="array" ref="L35">+_xlfn.IFS(I35&gt;114%,H35*0.02,I35&gt;109%,H35*0.015,I35&gt;104%,H35*0.0125,I35&gt;99%,H35*0.01,I35&lt;99%,H35*0)</f>
@@ -5234,34 +5291,34 @@
       </c>
       <c r="D36" s="4">
         <f>IFERROR(+VLOOKUP(B36,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>2633216.6305364068</v>
+      </c>
+      <c r="E36" s="4">
         <v>1931060.2247250369</v>
-      </c>
-      <c r="E36" s="4">
-        <v>1231155.9948169386</v>
       </c>
       <c r="F36" s="4">
         <f t="shared" si="8"/>
-        <v>699904.22990809823</v>
+        <v>702156.40581136988</v>
       </c>
       <c r="G36" s="5">
         <f t="shared" si="1"/>
-        <v>7.6523091924907347E-2</v>
+        <v>0.1043477959396238</v>
       </c>
       <c r="H36" s="4">
         <f t="shared" si="4"/>
-        <v>15448481.797800295</v>
+        <v>15799299.78321844</v>
       </c>
       <c r="I36" s="5">
         <f t="shared" si="2"/>
-        <v>0.61218473539925877</v>
+        <v>0.62608677563774284</v>
       </c>
       <c r="J36" s="4">
         <f t="shared" si="5"/>
-        <v>643686.74157501233</v>
+        <v>658304.15763410169</v>
       </c>
       <c r="K36" s="4">
         <f t="shared" si="3"/>
-        <v>1109711.4178702363</v>
+        <v>1130089.1684731797</v>
       </c>
       <c r="L36" s="63" cm="1">
         <f t="array" ref="L36">+_xlfn.IFS(I36&gt;114%,H36*0.02,I36&gt;109%,H36*0.015,I36&gt;104%,H36*0.0125,I36&gt;99%,H36*0.01,I36&lt;99%,H36*0)</f>
@@ -5278,38 +5335,38 @@
       </c>
       <c r="D37" s="4">
         <f>IFERROR(+VLOOKUP(B37,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>17081843.43377829</v>
+      </c>
+      <c r="E37" s="4">
         <v>16463801.298558187</v>
-      </c>
-      <c r="E37" s="4">
-        <v>-974804.98299181263</v>
       </c>
       <c r="F37" s="4">
         <f t="shared" si="8"/>
-        <v>17438606.281549998</v>
+        <v>618042.13522010297</v>
       </c>
       <c r="G37" s="5">
         <f t="shared" si="1"/>
-        <v>0.13493619506775525</v>
+        <v>0.14000162634974328</v>
       </c>
       <c r="H37" s="4">
         <f t="shared" si="4"/>
-        <v>131710410.38846549</v>
+        <v>102491060.60266975</v>
       </c>
       <c r="I37" s="5">
         <f t="shared" si="2"/>
-        <v>1.079489560542042</v>
+        <v>0.84000975809845979</v>
       </c>
       <c r="J37" s="4">
         <f t="shared" si="5"/>
-        <v>5487933.7661860622</v>
+        <v>4270460.8584445724</v>
       </c>
       <c r="K37" s="4">
         <f t="shared" si="3"/>
-        <v>5026092.7953067524</v>
+        <v>5246495.3283110857</v>
       </c>
       <c r="L37" s="63" cm="1">
         <f t="array" ref="L37">+_xlfn.IFS(I37&gt;114%,H37*0.0125,I37&gt;109%,H37*0.01,I37&gt;104%,H37*0.0075,I37&gt;99%,H37*0.005,I37&lt;99%,H37*0)</f>
-        <v>987828.07791349117</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
@@ -5322,34 +5379,34 @@
       </c>
       <c r="D38" s="4">
         <f>IFERROR(+VLOOKUP(B38,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>280769.63740000001</v>
+      </c>
+      <c r="E38" s="4">
         <v>149294.68419999999</v>
-      </c>
-      <c r="E38" s="4">
-        <v>0</v>
       </c>
       <c r="F38" s="4">
         <f t="shared" ref="F38" si="10">+D38-E38</f>
-        <v>149294.68419999999</v>
+        <v>131474.95320000002</v>
       </c>
       <c r="G38" s="5">
         <f t="shared" si="1"/>
-        <v>4.1819239271708684E-3</v>
+        <v>7.8646957254901971E-3</v>
       </c>
       <c r="H38" s="4">
         <f t="shared" si="4"/>
-        <v>1194357.4735999999</v>
+        <v>1684617.8244</v>
       </c>
       <c r="I38" s="5">
         <f t="shared" si="2"/>
-        <v>3.3455391417366948E-2</v>
+        <v>4.7188174352941176E-2</v>
       </c>
       <c r="J38" s="4">
         <f t="shared" si="5"/>
-        <v>49764.894733333327</v>
+        <v>70192.409350000002</v>
       </c>
       <c r="K38" s="4">
         <f t="shared" si="3"/>
-        <v>1692890.7293238097</v>
+        <v>1770961.51813</v>
       </c>
       <c r="L38" s="63" cm="1">
         <f t="array" ref="L38">+_xlfn.IFS(I38&gt;109%,H38*0.015,I38&gt;104%,H38*0.0125,I38&gt;99%,H38*0.01,I38&lt;99%,H38*0)</f>
@@ -5366,38 +5423,38 @@
       </c>
       <c r="D39" s="4">
         <f>IFERROR(+VLOOKUP(B39,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>6167950.3247244535</v>
+      </c>
+      <c r="E39" s="4">
         <v>4713478.3902184051</v>
-      </c>
-      <c r="E39" s="4">
-        <v>3667023.6813626946</v>
       </c>
       <c r="F39" s="4">
         <f t="shared" si="8"/>
-        <v>1046454.7088557105</v>
+        <v>1454471.9345060484</v>
       </c>
       <c r="G39" s="5">
         <f t="shared" si="1"/>
-        <v>0.12962852900198119</v>
+        <v>0.16962893671276072</v>
       </c>
       <c r="H39" s="4">
         <f t="shared" si="4"/>
-        <v>37707827.12174724</v>
+        <v>37007701.948346719</v>
       </c>
       <c r="I39" s="5">
         <f t="shared" si="2"/>
-        <v>1.0370282320158495</v>
+        <v>1.0177736202765644</v>
       </c>
       <c r="J39" s="4">
         <f t="shared" si="5"/>
-        <v>1571159.4634061351</v>
+        <v>1541987.5811811134</v>
       </c>
       <c r="K39" s="4">
         <f t="shared" si="3"/>
-        <v>1507045.2070848378</v>
+        <v>1509673.8707137774</v>
       </c>
       <c r="L39" s="63" cm="1">
         <f t="array" ref="L39">+_xlfn.IFS(I39&gt;114%,H39*0.02,I39&gt;109%,H39*0.015,I39&gt;104%,H39*0.0125,I39&gt;99%,H39*0.01,I39&lt;99%,H39*0)</f>
-        <v>377078.27121747239</v>
+        <v>370077.01948346721</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -5408,34 +5465,34 @@
       </c>
       <c r="D40" s="67">
         <f>+SUM(D27:D39)</f>
+        <v>62899009.881559134</v>
+      </c>
+      <c r="E40" s="65">
         <v>46151311.382850848</v>
-      </c>
-      <c r="E40" s="65">
-        <v>20762330.442747667</v>
       </c>
       <c r="F40" s="67">
         <f t="shared" si="8"/>
-        <v>25388980.940103181</v>
+        <v>16747698.498708285</v>
       </c>
       <c r="G40" s="66">
         <f t="shared" si="1"/>
-        <v>9.0665390258040754E-2</v>
+        <v>0.12356665730358822</v>
       </c>
       <c r="H40" s="64">
         <f t="shared" si="4"/>
-        <v>369210491.06280679</v>
+        <v>377394059.2893548</v>
       </c>
       <c r="I40" s="66">
         <f t="shared" si="2"/>
-        <v>0.72532312206432603</v>
+        <v>0.74139994382152929</v>
       </c>
       <c r="J40" s="64">
         <f t="shared" si="5"/>
-        <v>15383770.460950283</v>
+        <v>15724752.470389783</v>
       </c>
       <c r="K40" s="67">
         <f t="shared" si="3"/>
-        <v>22041793.87944166</v>
+        <v>22306498.648478329</v>
       </c>
       <c r="L40" s="68"/>
     </row>
@@ -5449,34 +5506,34 @@
       </c>
       <c r="D41" s="81">
         <f>+D40+D26+D10+D16</f>
+        <v>240577000.14348808</v>
+      </c>
+      <c r="E41" s="82">
         <v>191246594.85709113</v>
-      </c>
-      <c r="E41" s="82">
-        <v>105866448.03886795</v>
       </c>
       <c r="F41" s="81">
         <f>+D41-E41</f>
-        <v>85380146.818223178</v>
+        <v>49330405.28639695</v>
       </c>
       <c r="G41" s="83">
         <f t="shared" si="1"/>
-        <v>0.13860787688705689</v>
+        <v>0.17436058008072636</v>
       </c>
       <c r="H41" s="81">
         <f t="shared" si="4"/>
-        <v>1529972758.856729</v>
+        <v>1443462000.8609285</v>
       </c>
       <c r="I41" s="83">
         <f t="shared" si="2"/>
-        <v>1.1088630150964551</v>
+        <v>1.046163480484358</v>
       </c>
       <c r="J41" s="81">
         <f t="shared" si="5"/>
-        <v>63748864.952363707</v>
+        <v>60144250.03587202</v>
       </c>
       <c r="K41" s="81">
         <f t="shared" si="3"/>
-        <v>56596216.773144998</v>
+        <v>56959507.347482398</v>
       </c>
       <c r="L41" s="84"/>
     </row>
@@ -5527,11 +5584,11 @@
         <v>-275260.76904147147</v>
       </c>
       <c r="E43" s="4">
-        <v>0</v>
+        <v>-275260.76904147147</v>
       </c>
       <c r="F43" s="4">
         <f t="shared" ref="F43" si="11">+D43-E43</f>
-        <v>-275260.76904147147</v>
+        <v>0</v>
       </c>
       <c r="G43" s="5">
         <f>+D43/C43</f>
@@ -5539,19 +5596,19 @@
       </c>
       <c r="H43" s="4">
         <f t="shared" ref="H43" si="12">+D43/$N$3*$N$4</f>
-        <v>-2202086.1523317718</v>
+        <v>-1651564.614248829</v>
       </c>
       <c r="I43" s="5">
         <f>+H43/C43</f>
-        <v>-5.5052153808294292E-2</v>
+        <v>-4.1289115356220721E-2</v>
       </c>
       <c r="J43" s="4">
         <f t="shared" ref="J43" si="13">+D43/$N$3</f>
-        <v>-91753.589680490491</v>
+        <v>-68815.192260367869</v>
       </c>
       <c r="K43" s="4">
         <f>+(C43-D43)/$N$2</f>
-        <v>1917869.5604305463</v>
+        <v>2013763.0384520735</v>
       </c>
       <c r="L43" s="4" cm="1">
         <f t="array" ref="L43">+_xlfn.IFS(I43&gt;114%,H43*0.02,I43&gt;109%,H43*0.015,I43&gt;104%,H43*0.0125,I43&gt;99%,H43*0.01,I43&lt;99%,H43*0)</f>
@@ -5570,11 +5627,11 @@
         <v>-402349.89063324447</v>
       </c>
       <c r="E44" s="4">
-        <v>-388379.73864699452</v>
+        <v>-402349.89063324447</v>
       </c>
       <c r="F44" s="4">
         <f t="shared" ref="F44" si="14">+D44-E44</f>
-        <v>-13970.151986249955</v>
+        <v>0</v>
       </c>
       <c r="G44" s="5">
         <f>+D44/C44</f>
@@ -5582,19 +5639,19 @@
       </c>
       <c r="H44" s="4">
         <f t="shared" ref="H44" si="15">+D44/$N$3*$N$4</f>
-        <v>-3218799.1250659563</v>
+        <v>-2414099.3437994667</v>
       </c>
       <c r="I44" s="5">
         <f>+H44/C44</f>
-        <v>-0.10729330416886521</v>
+        <v>-8.0469978126648897E-2</v>
       </c>
       <c r="J44" s="4">
         <f t="shared" ref="J44" si="16">+D44/$N$3</f>
-        <v>-134116.6302110815</v>
+        <v>-100587.47265831112</v>
       </c>
       <c r="K44" s="4">
         <f>+(C44-D44)/$N$2</f>
-        <v>1447730.9471730117</v>
+        <v>1520117.4945316622</v>
       </c>
       <c r="L44" s="4" cm="1">
         <f t="array" ref="L44">+_xlfn.IFS(I44&gt;114%,H44*0.02,I44&gt;109%,H44*0.015,I44&gt;104%,H44*0.0125,I44&gt;99%,H44*0.01,I44&lt;99%,H44*0)</f>
@@ -5736,14 +5793,14 @@
       </c>
       <c r="D2" s="22">
         <f>H2/G2</f>
-        <v>0.22222222222222221</v>
+        <v>0.40277777777777779</v>
       </c>
       <c r="E2" s="13">
         <v>33</v>
       </c>
       <c r="F2" s="12">
         <f>+H2-E2</f>
-        <v>-17</v>
+        <v>-4</v>
       </c>
       <c r="G2" s="13">
         <f>VLOOKUP(B2,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -5751,11 +5808,11 @@
       </c>
       <c r="H2" s="13">
         <f>VLOOKUP(B2,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="I2" s="17">
         <f>(+G2*$M$2)-H2</f>
-        <v>45.199999999999996</v>
+        <v>32.199999999999996</v>
       </c>
       <c r="J2" t="s">
         <v>55</v>
@@ -5801,14 +5858,14 @@
       </c>
       <c r="D3" s="22">
         <f t="shared" ref="D3:D38" si="0">H3/G3</f>
-        <v>0.23012552301255229</v>
+        <v>0.22175732217573221</v>
       </c>
       <c r="E3" s="13">
         <v>1</v>
       </c>
       <c r="F3" s="12">
         <f t="shared" ref="F3:F38" si="1">+H3-E3</f>
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G3" s="13">
         <f>VLOOKUP(B3,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -5816,11 +5873,11 @@
       </c>
       <c r="H3" s="13">
         <f>VLOOKUP(B3,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I3" s="17">
         <f t="shared" ref="I3:I38" si="2">(+G3*$M$2)-H3</f>
-        <v>148.15</v>
+        <v>150.15</v>
       </c>
       <c r="J3" t="s">
         <v>56</v>
@@ -5839,14 +5896,14 @@
         <v>145 - ALMACEN</v>
       </c>
       <c r="S3" s="12">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T3" s="12">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="U3" s="41">
         <f>+S3/T3</f>
-        <v>7.0422535211267609E-2</v>
+        <v>7.476635514018691E-2</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
@@ -5860,14 +5917,14 @@
       </c>
       <c r="D4" s="22">
         <f t="shared" si="0"/>
-        <v>0.25550660792951541</v>
+        <v>0.42290748898678415</v>
       </c>
       <c r="E4" s="13">
         <v>126</v>
       </c>
       <c r="F4" s="12">
         <f t="shared" si="1"/>
-        <v>-68</v>
+        <v>-30</v>
       </c>
       <c r="G4" s="13">
         <f>VLOOKUP(B4,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -5875,11 +5932,11 @@
       </c>
       <c r="H4" s="13">
         <f>VLOOKUP(B4,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="I4" s="17">
         <f t="shared" si="2"/>
-        <v>134.94999999999999</v>
+        <v>96.949999999999989</v>
       </c>
       <c r="J4" t="s">
         <v>57</v>
@@ -5897,14 +5954,14 @@
         <v>145 - Articulos Sin Asociar Agrupacion</v>
       </c>
       <c r="S4" s="13">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T4" s="13">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="U4" s="5">
         <f t="shared" ref="U4:U11" si="3">+S4/T4</f>
-        <v>3.2863849765258218E-2</v>
+        <v>5.6074766355140186E-2</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
@@ -5918,14 +5975,14 @@
       </c>
       <c r="D5" s="22">
         <f t="shared" si="0"/>
-        <v>0.18461538461538463</v>
+        <v>0.29230769230769232</v>
       </c>
       <c r="E5" s="13">
         <v>21</v>
       </c>
       <c r="F5" s="12">
         <f t="shared" si="1"/>
-        <v>-9</v>
+        <v>-2</v>
       </c>
       <c r="G5" s="13">
         <f>VLOOKUP(B5,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -5933,11 +5990,11 @@
       </c>
       <c r="H5" s="13">
         <f>VLOOKUP(B5,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I5" s="17">
         <f t="shared" si="2"/>
-        <v>43.25</v>
+        <v>36.25</v>
       </c>
       <c r="K5" t="s">
         <v>64</v>
@@ -5952,14 +6009,14 @@
         <v>145 - BEBIDAS</v>
       </c>
       <c r="S5" s="13">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="T5" s="13">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="U5" s="5">
         <f t="shared" si="3"/>
-        <v>5.1643192488262914E-2</v>
+        <v>7.9439252336448593E-2</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
@@ -5973,14 +6030,14 @@
       </c>
       <c r="D6" s="22">
         <f t="shared" si="0"/>
-        <v>0.28502415458937197</v>
+        <v>0.42995169082125606</v>
       </c>
       <c r="E6" s="13">
         <v>100</v>
       </c>
       <c r="F6" s="12">
         <f t="shared" si="1"/>
-        <v>-41</v>
+        <v>-11</v>
       </c>
       <c r="G6" s="13">
         <f>VLOOKUP(B6,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -5988,11 +6045,11 @@
       </c>
       <c r="H6" s="13">
         <f>VLOOKUP(B6,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="I6" s="17">
         <f t="shared" si="2"/>
-        <v>116.94999999999999</v>
+        <v>86.949999999999989</v>
       </c>
       <c r="J6" t="s">
         <v>58</v>
@@ -6010,14 +6067,14 @@
         <v>145 - CHOCOLATE</v>
       </c>
       <c r="S6" s="13">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T6" s="13">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="U6" s="5">
         <f t="shared" si="3"/>
-        <v>3.2863849765258218E-2</v>
+        <v>5.1401869158878503E-2</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
@@ -6031,14 +6088,14 @@
       </c>
       <c r="D7" s="22">
         <f t="shared" si="0"/>
-        <v>0.20202020202020202</v>
+        <v>0.27777777777777779</v>
       </c>
       <c r="E7" s="13">
         <v>81</v>
       </c>
       <c r="F7" s="12">
         <f t="shared" si="1"/>
-        <v>-41</v>
+        <v>-26</v>
       </c>
       <c r="G7" s="13">
         <f>VLOOKUP(B7,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6046,11 +6103,11 @@
       </c>
       <c r="H7" s="13">
         <f>VLOOKUP(B7,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="I7" s="17">
         <f t="shared" si="2"/>
-        <v>128.29999999999998</v>
+        <v>113.29999999999998</v>
       </c>
       <c r="J7" t="s">
         <v>58</v>
@@ -6068,14 +6125,14 @@
         <v>145 - GALLETITAS</v>
       </c>
       <c r="S7" s="13">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="T7" s="13">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="U7" s="5">
         <f t="shared" si="3"/>
-        <v>8.9201877934272297E-2</v>
+        <v>0.13551401869158877</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
@@ -6089,26 +6146,26 @@
       </c>
       <c r="D8" s="22">
         <f t="shared" si="0"/>
-        <v>0.22535211267605634</v>
+        <v>0.32242990654205606</v>
       </c>
       <c r="E8" s="13">
         <v>89</v>
       </c>
       <c r="F8" s="12">
         <f t="shared" si="1"/>
-        <v>-41</v>
+        <v>-20</v>
       </c>
       <c r="G8" s="13">
         <f>VLOOKUP(B8,'Base Cobertura'!$A:$C,3,FALSE)</f>
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H8" s="13">
         <f>VLOOKUP(B8,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="I8" s="17">
         <f t="shared" si="2"/>
-        <v>133.04999999999998</v>
+        <v>112.9</v>
       </c>
       <c r="J8" t="s">
         <v>55</v>
@@ -6127,14 +6184,14 @@
         <v>145 - GOLOSINAS</v>
       </c>
       <c r="S8" s="13">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="T8" s="13">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="U8" s="5">
         <f t="shared" si="3"/>
-        <v>8.4507042253521125E-2</v>
+        <v>0.12149532710280374</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
@@ -6148,26 +6205,26 @@
       </c>
       <c r="D9" s="22">
         <f>H9/G9</f>
-        <v>0.21818181818181817</v>
+        <v>0.3592814371257485</v>
       </c>
       <c r="E9" s="13">
         <v>92</v>
       </c>
       <c r="F9" s="12">
         <f t="shared" si="1"/>
-        <v>-56</v>
+        <v>-32</v>
       </c>
       <c r="G9" s="13">
         <f>VLOOKUP(B9,'Base Cobertura'!$A:$C,3,FALSE)</f>
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H9" s="13">
         <f>VLOOKUP(B9,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="I9" s="17">
         <f t="shared" si="2"/>
-        <v>104.25</v>
+        <v>81.949999999999989</v>
       </c>
       <c r="J9" t="s">
         <v>55</v>
@@ -6188,11 +6245,11 @@
         <v>7</v>
       </c>
       <c r="T9" s="13">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="U9" s="5">
         <f t="shared" si="3"/>
-        <v>3.2863849765258218E-2</v>
+        <v>3.2710280373831772E-2</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
@@ -6206,26 +6263,26 @@
       </c>
       <c r="D10" s="22">
         <f t="shared" si="0"/>
-        <v>0.15979381443298968</v>
+        <v>0.28205128205128205</v>
       </c>
       <c r="E10" s="13">
         <v>64</v>
       </c>
       <c r="F10" s="12">
         <f t="shared" si="1"/>
-        <v>-33</v>
+        <v>-9</v>
       </c>
       <c r="G10" s="13">
         <f>VLOOKUP(B10,'Base Cobertura'!$A:$C,3,FALSE)</f>
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H10" s="13">
         <f>VLOOKUP(B10,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="I10" s="17">
         <f t="shared" si="2"/>
-        <v>133.9</v>
+        <v>110.75</v>
       </c>
       <c r="J10" t="s">
         <v>58</v>
@@ -6243,14 +6300,14 @@
         <v>145 - NO PERECEDEROS</v>
       </c>
       <c r="S10" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T10" s="13">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="U10" s="5">
         <f t="shared" si="3"/>
-        <v>9.3896713615023476E-3</v>
+        <v>1.4018691588785047E-2</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
@@ -6264,14 +6321,14 @@
       </c>
       <c r="D11" s="32">
         <f t="shared" si="0"/>
-        <v>7.9207920792079209E-2</v>
+        <v>0.13861386138613863</v>
       </c>
       <c r="E11" s="31">
         <v>19</v>
       </c>
       <c r="F11" s="33">
         <f t="shared" si="1"/>
-        <v>-11</v>
+        <v>-5</v>
       </c>
       <c r="G11" s="13">
         <f>VLOOKUP(B11,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6279,11 +6336,11 @@
       </c>
       <c r="H11" s="13">
         <f>VLOOKUP(B11,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I11" s="34">
         <f t="shared" si="2"/>
-        <v>77.849999999999994</v>
+        <v>71.849999999999994</v>
       </c>
       <c r="J11" t="s">
         <v>59</v>
@@ -6298,14 +6355,14 @@
         <v>145 - PILAS</v>
       </c>
       <c r="S11" s="13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T11" s="13">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="U11" s="5">
         <f t="shared" si="3"/>
-        <v>1.4084507042253521E-2</v>
+        <v>1.8691588785046728E-2</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
@@ -6319,14 +6376,14 @@
       </c>
       <c r="D12" s="32">
         <f t="shared" si="0"/>
-        <v>7.6190476190476197E-2</v>
+        <v>0.13333333333333333</v>
       </c>
       <c r="E12" s="31">
         <v>24</v>
       </c>
       <c r="F12" s="33">
         <f t="shared" si="1"/>
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="G12" s="13">
         <f>VLOOKUP(B12,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6334,11 +6391,11 @@
       </c>
       <c r="H12" s="13">
         <f>VLOOKUP(B12,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I12" s="34">
         <f t="shared" si="2"/>
-        <v>81.25</v>
+        <v>75.25</v>
       </c>
       <c r="J12" t="s">
         <v>59</v>
@@ -6355,14 +6412,14 @@
       </c>
       <c r="D13" s="22">
         <f t="shared" si="0"/>
-        <v>0.20384615384615384</v>
+        <v>0.35</v>
       </c>
       <c r="E13" s="13">
         <v>144</v>
       </c>
       <c r="F13" s="12">
         <f t="shared" si="1"/>
-        <v>-91</v>
+        <v>-53</v>
       </c>
       <c r="G13" s="13">
         <f>VLOOKUP(B13,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6370,11 +6427,11 @@
       </c>
       <c r="H13" s="13">
         <f>VLOOKUP(B13,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="I13" s="17">
         <f t="shared" si="2"/>
-        <v>168</v>
+        <v>130</v>
       </c>
       <c r="J13" t="s">
         <v>57</v>
@@ -6394,14 +6451,14 @@
       </c>
       <c r="D14" s="22">
         <f t="shared" si="0"/>
-        <v>0.21978021978021978</v>
+        <v>0.31868131868131866</v>
       </c>
       <c r="E14" s="13">
         <v>85</v>
       </c>
       <c r="F14" s="12">
         <f t="shared" si="1"/>
-        <v>-45</v>
+        <v>-27</v>
       </c>
       <c r="G14" s="13">
         <f>VLOOKUP(B14,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6409,11 +6466,11 @@
       </c>
       <c r="H14" s="13">
         <f>VLOOKUP(B14,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="I14" s="17">
         <f t="shared" si="2"/>
-        <v>114.69999999999999</v>
+        <v>96.699999999999989</v>
       </c>
       <c r="J14" t="s">
         <v>55</v>
@@ -6429,15 +6486,15 @@
       <c r="E15" s="14"/>
       <c r="F15" s="16">
         <f>+SUM(F2:F14)</f>
-        <v>-415</v>
+        <v>-177</v>
       </c>
       <c r="G15" s="8">
         <f>+SUM(G2:G14)</f>
-        <v>2228</v>
+        <v>2232</v>
       </c>
       <c r="H15" s="8">
         <f>+SUM(H2:H14)</f>
-        <v>464</v>
+        <v>702</v>
       </c>
       <c r="I15" s="8"/>
     </row>
@@ -6454,14 +6511,14 @@
       </c>
       <c r="D16" s="22">
         <f t="shared" si="0"/>
-        <v>0.29813664596273293</v>
+        <v>0.40993788819875776</v>
       </c>
       <c r="E16" s="13">
         <v>90</v>
       </c>
       <c r="F16" s="12">
         <f t="shared" si="1"/>
-        <v>-42</v>
+        <v>-24</v>
       </c>
       <c r="G16" s="13">
         <f>VLOOKUP(B16,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6469,11 +6526,11 @@
       </c>
       <c r="H16" s="13">
         <f>VLOOKUP(B16,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="I16" s="17">
         <f t="shared" si="2"/>
-        <v>88.85</v>
+        <v>70.849999999999994</v>
       </c>
       <c r="J16" t="s">
         <v>55</v>
@@ -6493,14 +6550,14 @@
       </c>
       <c r="D17" s="22">
         <f t="shared" si="0"/>
-        <v>0.22277227722772278</v>
+        <v>0.28712871287128711</v>
       </c>
       <c r="E17" s="13">
         <v>92</v>
       </c>
       <c r="F17" s="12">
         <f t="shared" si="1"/>
-        <v>-47</v>
+        <v>-34</v>
       </c>
       <c r="G17" s="13">
         <f>VLOOKUP(B17,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6508,11 +6565,11 @@
       </c>
       <c r="H17" s="13">
         <f>VLOOKUP(B17,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="I17" s="17">
         <f t="shared" si="2"/>
-        <v>126.69999999999999</v>
+        <v>113.69999999999999</v>
       </c>
       <c r="J17" t="s">
         <v>55</v>
@@ -6532,14 +6589,14 @@
       </c>
       <c r="D18" s="22">
         <f t="shared" si="0"/>
-        <v>0.3</v>
+        <v>0.44117647058823528</v>
       </c>
       <c r="E18" s="13">
         <v>88</v>
       </c>
       <c r="F18" s="12">
         <f t="shared" si="1"/>
-        <v>-37</v>
+        <v>-13</v>
       </c>
       <c r="G18" s="13">
         <f>VLOOKUP(B18,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6547,11 +6604,11 @@
       </c>
       <c r="H18" s="13">
         <f>VLOOKUP(B18,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="I18" s="17">
         <f t="shared" si="2"/>
-        <v>93.5</v>
+        <v>69.5</v>
       </c>
       <c r="J18" t="s">
         <v>58</v>
@@ -6571,14 +6628,14 @@
       </c>
       <c r="D19" s="22">
         <f t="shared" si="0"/>
-        <v>0.33750000000000002</v>
+        <v>0.51249999999999996</v>
       </c>
       <c r="E19" s="13">
         <v>95</v>
       </c>
       <c r="F19" s="12">
         <f t="shared" si="1"/>
-        <v>-41</v>
+        <v>-13</v>
       </c>
       <c r="G19" s="13">
         <f>VLOOKUP(B19,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6586,11 +6643,11 @@
       </c>
       <c r="H19" s="13">
         <f>VLOOKUP(B19,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="I19" s="17">
         <f t="shared" si="2"/>
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="J19" t="s">
         <v>58</v>
@@ -6610,14 +6667,14 @@
       </c>
       <c r="D20" s="22">
         <f t="shared" si="0"/>
-        <v>0.2824858757062147</v>
+        <v>0.43502824858757061</v>
       </c>
       <c r="E20" s="13">
         <v>83</v>
       </c>
       <c r="F20" s="12">
         <f t="shared" si="1"/>
-        <v>-33</v>
+        <v>-6</v>
       </c>
       <c r="G20" s="13">
         <f>VLOOKUP(B20,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6625,11 +6682,11 @@
       </c>
       <c r="H20" s="13">
         <f>VLOOKUP(B20,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="I20" s="17">
         <f t="shared" si="2"/>
-        <v>100.44999999999999</v>
+        <v>73.449999999999989</v>
       </c>
       <c r="J20" t="s">
         <v>55</v>
@@ -6649,14 +6706,14 @@
       </c>
       <c r="D21" s="22">
         <f t="shared" si="0"/>
-        <v>0.30769230769230771</v>
+        <v>0.42011834319526625</v>
       </c>
       <c r="E21" s="13">
         <v>64</v>
       </c>
       <c r="F21" s="12">
         <f t="shared" si="1"/>
-        <v>-12</v>
+        <v>7</v>
       </c>
       <c r="G21" s="13">
         <f>VLOOKUP(B21,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6664,11 +6721,11 @@
       </c>
       <c r="H21" s="13">
         <f>VLOOKUP(B21,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="I21" s="17">
         <f t="shared" si="2"/>
-        <v>91.65</v>
+        <v>72.650000000000006</v>
       </c>
       <c r="J21" t="s">
         <v>58</v>
@@ -6688,14 +6745,14 @@
       </c>
       <c r="D22" s="22">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.20707070707070707</v>
       </c>
       <c r="E22" s="13">
         <v>66</v>
       </c>
       <c r="F22" s="12">
         <f t="shared" si="1"/>
-        <v>-66</v>
+        <v>-25</v>
       </c>
       <c r="G22" s="13">
         <f>VLOOKUP(B22,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6703,11 +6760,11 @@
       </c>
       <c r="H22" s="13">
         <f>VLOOKUP(B22,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="I22" s="17">
         <f t="shared" si="2"/>
-        <v>168.29999999999998</v>
+        <v>127.29999999999998</v>
       </c>
       <c r="J22" t="s">
         <v>58</v>
@@ -6727,14 +6784,14 @@
       </c>
       <c r="D23" s="22">
         <f t="shared" si="0"/>
-        <v>0.20289855072463769</v>
+        <v>0.39130434782608697</v>
       </c>
       <c r="E23" s="13">
         <v>70</v>
       </c>
       <c r="F23" s="12">
         <f t="shared" si="1"/>
-        <v>-42</v>
+        <v>-16</v>
       </c>
       <c r="G23" s="13">
         <f>VLOOKUP(B23,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6742,11 +6799,11 @@
       </c>
       <c r="H23" s="13">
         <f>VLOOKUP(B23,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="I23" s="17">
         <f t="shared" si="2"/>
-        <v>89.3</v>
+        <v>63.3</v>
       </c>
       <c r="J23" t="s">
         <v>58</v>
@@ -6766,14 +6823,14 @@
       </c>
       <c r="D24" s="22">
         <f t="shared" si="0"/>
-        <v>0.22941176470588234</v>
+        <v>0.41764705882352943</v>
       </c>
       <c r="E24" s="13">
         <v>79</v>
       </c>
       <c r="F24" s="12">
         <f t="shared" si="1"/>
-        <v>-40</v>
+        <v>-8</v>
       </c>
       <c r="G24" s="13">
         <f>VLOOKUP(B24,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6781,11 +6838,11 @@
       </c>
       <c r="H24" s="13">
         <f>VLOOKUP(B24,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="I24" s="17">
         <f t="shared" si="2"/>
-        <v>105.5</v>
+        <v>73.5</v>
       </c>
       <c r="J24" t="s">
         <v>60</v>
@@ -6801,7 +6858,7 @@
       <c r="E25" s="14"/>
       <c r="F25" s="16">
         <f>+SUM(F16:F24)</f>
-        <v>-360</v>
+        <v>-132</v>
       </c>
       <c r="G25" s="8">
         <f>+SUM(G16:G24)</f>
@@ -6809,7 +6866,7 @@
       </c>
       <c r="H25" s="8">
         <f>+SUM(H16:H24)</f>
-        <v>367</v>
+        <v>595</v>
       </c>
       <c r="I25" s="8"/>
     </row>
@@ -6826,14 +6883,14 @@
       </c>
       <c r="D26" s="22">
         <f t="shared" si="0"/>
-        <v>0.14285714285714285</v>
+        <v>0.23214285714285715</v>
       </c>
       <c r="E26" s="13">
         <v>20</v>
       </c>
       <c r="F26" s="12">
         <f>+H26-E26</f>
-        <v>-12</v>
+        <v>-7</v>
       </c>
       <c r="G26" s="13">
         <f>VLOOKUP(B26,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6841,11 +6898,11 @@
       </c>
       <c r="H26" s="13">
         <f>VLOOKUP(B26,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I26" s="17">
         <f t="shared" si="2"/>
-        <v>39.6</v>
+        <v>34.6</v>
       </c>
       <c r="J26" t="s">
         <v>55</v>
@@ -6865,14 +6922,14 @@
       </c>
       <c r="D27" s="22">
         <f t="shared" si="0"/>
-        <v>0.21153846153846154</v>
+        <v>0.35256410256410259</v>
       </c>
       <c r="E27" s="13">
         <v>68</v>
       </c>
       <c r="F27" s="12">
         <f t="shared" si="1"/>
-        <v>-35</v>
+        <v>-13</v>
       </c>
       <c r="G27" s="13">
         <f>VLOOKUP(B27,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6880,11 +6937,11 @@
       </c>
       <c r="H27" s="13">
         <f>VLOOKUP(B27,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="I27" s="17">
         <f t="shared" si="2"/>
-        <v>99.6</v>
+        <v>77.599999999999994</v>
       </c>
       <c r="J27" t="s">
         <v>58</v>
@@ -6904,14 +6961,14 @@
       </c>
       <c r="D28" s="22">
         <f t="shared" si="0"/>
-        <v>0.21739130434782608</v>
+        <v>0.29813664596273293</v>
       </c>
       <c r="E28" s="13">
         <v>80</v>
       </c>
       <c r="F28" s="12">
         <f t="shared" si="1"/>
-        <v>-45</v>
+        <v>-32</v>
       </c>
       <c r="G28" s="13">
         <f>VLOOKUP(B28,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6919,11 +6976,11 @@
       </c>
       <c r="H28" s="13">
         <f>VLOOKUP(B28,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I28" s="17">
         <f t="shared" si="2"/>
-        <v>101.85</v>
+        <v>88.85</v>
       </c>
       <c r="J28" t="s">
         <v>58</v>
@@ -6943,14 +7000,14 @@
       </c>
       <c r="D29" s="22">
         <f t="shared" si="0"/>
-        <v>0.10441767068273092</v>
+        <v>0.1606425702811245</v>
       </c>
       <c r="E29" s="13">
         <v>68</v>
       </c>
       <c r="F29" s="12">
         <f t="shared" si="1"/>
-        <v>-42</v>
+        <v>-28</v>
       </c>
       <c r="G29" s="13">
         <f>VLOOKUP(B29,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6958,11 +7015,11 @@
       </c>
       <c r="H29" s="13">
         <f>VLOOKUP(B29,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="I29" s="17">
         <f t="shared" si="2"/>
-        <v>185.65</v>
+        <v>171.65</v>
       </c>
       <c r="J29" t="s">
         <v>58</v>
@@ -6982,14 +7039,14 @@
       </c>
       <c r="D30" s="22">
         <f t="shared" si="0"/>
-        <v>0.23571428571428571</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="E30" s="13">
         <v>73</v>
       </c>
       <c r="F30" s="12">
         <f t="shared" si="1"/>
-        <v>-40</v>
+        <v>-13</v>
       </c>
       <c r="G30" s="13">
         <f>VLOOKUP(B30,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6997,11 +7054,11 @@
       </c>
       <c r="H30" s="13">
         <f>VLOOKUP(B30,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="I30" s="17">
         <f t="shared" si="2"/>
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="J30" t="s">
         <v>55</v>
@@ -7021,14 +7078,14 @@
       </c>
       <c r="D31" s="22">
         <f t="shared" si="0"/>
-        <v>0.17679558011049723</v>
+        <v>0.25966850828729282</v>
       </c>
       <c r="E31" s="13">
         <v>40</v>
       </c>
       <c r="F31" s="12">
         <f t="shared" si="1"/>
-        <v>-8</v>
+        <v>7</v>
       </c>
       <c r="G31" s="13">
         <f>VLOOKUP(B31,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7036,11 +7093,11 @@
       </c>
       <c r="H31" s="13">
         <f>VLOOKUP(B31,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="I31" s="17">
         <f t="shared" si="2"/>
-        <v>121.85</v>
+        <v>106.85</v>
       </c>
       <c r="J31" t="s">
         <v>58</v>
@@ -7060,14 +7117,14 @@
       </c>
       <c r="D32" s="22">
         <f t="shared" si="0"/>
-        <v>0.21428571428571427</v>
+        <v>0.30357142857142855</v>
       </c>
       <c r="E32" s="13">
         <v>67</v>
       </c>
       <c r="F32" s="12">
         <f t="shared" si="1"/>
-        <v>-31</v>
+        <v>-16</v>
       </c>
       <c r="G32" s="13">
         <f>VLOOKUP(B32,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7075,11 +7132,11 @@
       </c>
       <c r="H32" s="13">
         <f>VLOOKUP(B32,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="I32" s="17">
         <f t="shared" si="2"/>
-        <v>106.79999999999998</v>
+        <v>91.799999999999983</v>
       </c>
       <c r="J32" t="s">
         <v>58</v>
@@ -7099,14 +7156,14 @@
       </c>
       <c r="D33" s="22">
         <f t="shared" si="0"/>
-        <v>0.23837209302325582</v>
+        <v>0.34883720930232559</v>
       </c>
       <c r="E33" s="13">
         <v>66</v>
       </c>
       <c r="F33" s="12">
         <f t="shared" si="1"/>
-        <v>-25</v>
+        <v>-6</v>
       </c>
       <c r="G33" s="13">
         <f>VLOOKUP(B33,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7114,11 +7171,11 @@
       </c>
       <c r="H33" s="13">
         <f>VLOOKUP(B33,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="I33" s="17">
         <f t="shared" si="2"/>
-        <v>105.19999999999999</v>
+        <v>86.199999999999989</v>
       </c>
       <c r="J33" t="s">
         <v>58</v>
@@ -7138,26 +7195,26 @@
       </c>
       <c r="D34" s="22">
         <f t="shared" si="0"/>
-        <v>9.2198581560283682E-2</v>
+        <v>0.14788732394366197</v>
       </c>
       <c r="E34" s="13">
         <v>82</v>
       </c>
       <c r="F34" s="12">
         <f t="shared" si="1"/>
-        <v>-69</v>
+        <v>-61</v>
       </c>
       <c r="G34" s="13">
         <f>VLOOKUP(B34,'Base Cobertura'!$A:$C,3,FALSE)</f>
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H34" s="13">
         <f>VLOOKUP(B34,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="I34" s="17">
         <f t="shared" si="2"/>
-        <v>106.85</v>
+        <v>99.7</v>
       </c>
       <c r="J34" t="s">
         <v>55</v>
@@ -7177,14 +7234,14 @@
       </c>
       <c r="D35" s="22">
         <f t="shared" si="0"/>
-        <v>0.17415730337078653</v>
+        <v>0.2808988764044944</v>
       </c>
       <c r="E35" s="13">
         <v>81</v>
       </c>
       <c r="F35" s="12">
         <f t="shared" si="1"/>
-        <v>-50</v>
+        <v>-31</v>
       </c>
       <c r="G35" s="13">
         <f>VLOOKUP(B35,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7192,11 +7249,11 @@
       </c>
       <c r="H35" s="13">
         <f>VLOOKUP(B35,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="I35" s="17">
         <f t="shared" si="2"/>
-        <v>120.29999999999998</v>
+        <v>101.29999999999998</v>
       </c>
       <c r="J35" t="s">
         <v>58</v>
@@ -7252,14 +7309,14 @@
       </c>
       <c r="D37" s="22">
         <f t="shared" si="0"/>
-        <v>9.7087378640776691E-3</v>
+        <v>1.9417475728155338E-2</v>
       </c>
       <c r="E37" s="13">
         <v>17</v>
       </c>
       <c r="F37" s="12">
         <f t="shared" si="1"/>
-        <v>-16</v>
+        <v>-15</v>
       </c>
       <c r="G37" s="13">
         <f>VLOOKUP(B37,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7267,11 +7324,11 @@
       </c>
       <c r="H37" s="13">
         <f>VLOOKUP(B37,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I37" s="17">
         <f t="shared" si="2"/>
-        <v>86.55</v>
+        <v>85.55</v>
       </c>
       <c r="J37" t="s">
         <v>59</v>
@@ -7288,14 +7345,14 @@
       </c>
       <c r="D38" s="22">
         <f t="shared" si="0"/>
-        <v>0.29133858267716534</v>
+        <v>0.40157480314960631</v>
       </c>
       <c r="E38" s="13">
         <v>60</v>
       </c>
       <c r="F38" s="12">
         <f t="shared" si="1"/>
-        <v>-23</v>
+        <v>-9</v>
       </c>
       <c r="G38" s="13">
         <f>VLOOKUP(B38,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7303,11 +7360,11 @@
       </c>
       <c r="H38" s="13">
         <f>VLOOKUP(B38,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="I38" s="17">
         <f t="shared" si="2"/>
-        <v>70.95</v>
+        <v>56.95</v>
       </c>
       <c r="J38" t="s">
         <v>55</v>
@@ -7323,15 +7380,15 @@
       <c r="E39" s="14"/>
       <c r="F39" s="8">
         <f>+SUM(F26:F38)</f>
-        <v>-395</v>
+        <v>-223</v>
       </c>
       <c r="G39" s="8">
         <f>+SUM(G26:G38)</f>
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="H39" s="8">
         <f>+SUM(H26:H38)</f>
-        <v>327</v>
+        <v>499</v>
       </c>
       <c r="I39" s="8"/>
       <c r="L39" t="s">
@@ -7347,20 +7404,20 @@
       <c r="E40" s="6"/>
       <c r="F40" s="8">
         <f>+SUM(F39+F25+F15)</f>
-        <v>-1170</v>
+        <v>-532</v>
       </c>
       <c r="G40" s="8">
         <f>+G15+G25+G39</f>
-        <v>5718</v>
+        <v>5723</v>
       </c>
       <c r="H40" s="8">
         <f>+H15+H25+H39</f>
-        <v>1158</v>
+        <v>1796</v>
       </c>
       <c r="I40" s="8"/>
       <c r="L40" s="1">
         <f>+H40/G40</f>
-        <v>0.20251836306400839</v>
+        <v>0.31382142233094529</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
@@ -7405,14 +7462,14 @@
       </c>
       <c r="D42" s="22">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8.4033613445378148E-3</v>
       </c>
       <c r="E42" s="13">
         <v>60</v>
       </c>
       <c r="F42" s="12">
         <f t="shared" si="5"/>
-        <v>-60</v>
+        <v>-59</v>
       </c>
       <c r="G42" s="13">
         <f>VLOOKUP(B42,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7420,11 +7477,11 @@
       </c>
       <c r="H42" s="13">
         <f>VLOOKUP(B42,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42" s="17">
         <f t="shared" si="6"/>
-        <v>101.14999999999999</v>
+        <v>100.14999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -7998,7 +8055,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B3" s="51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="51">
         <v>3408</v>
@@ -8006,7 +8063,9 @@
       <c r="G3" t="s">
         <v>222</v>
       </c>
-      <c r="H3" s="51"/>
+      <c r="H3" s="51">
+        <v>1</v>
+      </c>
       <c r="I3" s="51">
         <v>3408</v>
       </c>
@@ -8016,13 +8075,16 @@
         <v>1</v>
       </c>
       <c r="B4" s="51">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="C4" s="51">
         <v>127</v>
       </c>
       <c r="G4" t="s">
         <v>223</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
       </c>
       <c r="I4" s="51">
         <v>3408</v>
@@ -8033,7 +8095,7 @@
         <v>10</v>
       </c>
       <c r="B5" s="51">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="C5" s="51">
         <v>181</v>
@@ -8051,7 +8113,7 @@
         <v>100</v>
       </c>
       <c r="B6" s="51">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C6" s="51">
         <v>2024</v>
@@ -8069,15 +8131,17 @@
         <v>11</v>
       </c>
       <c r="B7" s="51">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="C7" s="51">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="G7" t="s">
         <v>226</v>
       </c>
-      <c r="H7" s="51"/>
+      <c r="H7" s="51">
+        <v>1</v>
+      </c>
       <c r="I7" s="51">
         <v>3408</v>
       </c>
@@ -8087,10 +8151,10 @@
         <v>12</v>
       </c>
       <c r="B8" s="51">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="C8" s="51">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G8" t="s">
         <v>227</v>
@@ -8107,7 +8171,7 @@
         <v>123</v>
       </c>
       <c r="B9" s="51">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C9" s="51">
         <v>489</v>
@@ -8115,7 +8179,9 @@
       <c r="G9" t="s">
         <v>228</v>
       </c>
-      <c r="H9" s="51"/>
+      <c r="H9" s="51">
+        <v>1</v>
+      </c>
       <c r="I9" s="51">
         <v>3408</v>
       </c>
@@ -8125,13 +8191,16 @@
         <v>15</v>
       </c>
       <c r="B10" s="51">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C10" s="51">
         <v>65</v>
       </c>
       <c r="G10" t="s">
         <v>229</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
       </c>
       <c r="I10" s="51">
         <v>3408</v>
@@ -8142,7 +8211,7 @@
         <v>16</v>
       </c>
       <c r="B11" s="51">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="C11" s="51">
         <v>198</v>
@@ -8160,7 +8229,7 @@
         <v>18</v>
       </c>
       <c r="B12" s="51">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="C12" s="51">
         <v>177</v>
@@ -8176,7 +8245,7 @@
         <v>222</v>
       </c>
       <c r="H12">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="I12" s="51">
         <v>127</v>
@@ -8187,7 +8256,7 @@
         <v>19</v>
       </c>
       <c r="B13" s="51">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="C13" s="51">
         <v>207</v>
@@ -8200,7 +8269,7 @@
         <v>223</v>
       </c>
       <c r="H13" s="51">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I13" s="51">
         <v>127</v>
@@ -8211,7 +8280,7 @@
         <v>2</v>
       </c>
       <c r="B14" s="51">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="C14" s="51">
         <v>138</v>
@@ -8224,7 +8293,7 @@
         <v>224</v>
       </c>
       <c r="H14" s="51">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I14" s="51">
         <v>127</v>
@@ -8235,7 +8304,7 @@
         <v>20</v>
       </c>
       <c r="B15" s="51">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="C15" s="51">
         <v>227</v>
@@ -8248,7 +8317,7 @@
         <v>225</v>
       </c>
       <c r="H15" s="51">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I15" s="51">
         <v>127</v>
@@ -8259,7 +8328,7 @@
         <v>21</v>
       </c>
       <c r="B16" s="51">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="C16" s="51">
         <v>170</v>
@@ -8272,7 +8341,7 @@
         <v>226</v>
       </c>
       <c r="H16" s="51">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="I16" s="51">
         <v>127</v>
@@ -8283,7 +8352,7 @@
         <v>22</v>
       </c>
       <c r="B17" s="51">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="C17" s="51">
         <v>72</v>
@@ -8296,7 +8365,7 @@
         <v>227</v>
       </c>
       <c r="H17" s="51">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="I17" s="51">
         <v>127</v>
@@ -8307,7 +8376,7 @@
         <v>23</v>
       </c>
       <c r="B18" s="51">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="C18" s="51">
         <v>160</v>
@@ -8320,7 +8389,7 @@
         <v>228</v>
       </c>
       <c r="H18" s="51">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I18" s="51">
         <v>127</v>
@@ -8331,7 +8400,7 @@
         <v>24</v>
       </c>
       <c r="B19" s="51">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="C19" s="51">
         <v>178</v>
@@ -8344,7 +8413,7 @@
         <v>229</v>
       </c>
       <c r="H19" s="51">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I19" s="51">
         <v>127</v>
@@ -8368,7 +8437,7 @@
         <v>230</v>
       </c>
       <c r="H20">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I20" s="51">
         <v>127</v>
@@ -8379,7 +8448,7 @@
         <v>26</v>
       </c>
       <c r="B21" s="51">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C21" s="51">
         <v>162</v>
@@ -8395,7 +8464,7 @@
         <v>222</v>
       </c>
       <c r="H21" s="51">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I21" s="51">
         <v>181</v>
@@ -8406,7 +8475,7 @@
         <v>27</v>
       </c>
       <c r="B22" s="51">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="C22" s="51">
         <v>140</v>
@@ -8418,9 +8487,7 @@
       <c r="G22" t="s">
         <v>223</v>
       </c>
-      <c r="H22" s="51">
-        <v>1</v>
-      </c>
+      <c r="H22" s="51"/>
       <c r="I22" s="51">
         <v>181</v>
       </c>
@@ -8430,7 +8497,7 @@
         <v>28</v>
       </c>
       <c r="B23" s="51">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="C23" s="51">
         <v>168</v>
@@ -8443,7 +8510,7 @@
         <v>224</v>
       </c>
       <c r="H23" s="51">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I23" s="51">
         <v>181</v>
@@ -8454,7 +8521,7 @@
         <v>3</v>
       </c>
       <c r="B24" s="51">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="C24" s="51">
         <v>170</v>
@@ -8467,7 +8534,7 @@
         <v>225</v>
       </c>
       <c r="H24" s="51">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I24" s="51">
         <v>181</v>
@@ -8478,7 +8545,7 @@
         <v>30</v>
       </c>
       <c r="B25" s="51">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C25" s="51">
         <v>138</v>
@@ -8491,7 +8558,7 @@
         <v>226</v>
       </c>
       <c r="H25" s="51">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I25" s="51">
         <v>181</v>
@@ -8502,7 +8569,7 @@
         <v>31</v>
       </c>
       <c r="B26" s="51">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="C26" s="51">
         <v>161</v>
@@ -8515,7 +8582,7 @@
         <v>227</v>
       </c>
       <c r="H26" s="51">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I26" s="51">
         <v>181</v>
@@ -8526,7 +8593,7 @@
         <v>32</v>
       </c>
       <c r="B27" s="51">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C27" s="51">
         <v>56</v>
@@ -8539,7 +8606,7 @@
         <v>228</v>
       </c>
       <c r="H27" s="51">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I27" s="51">
         <v>181</v>
@@ -8550,7 +8617,7 @@
         <v>33</v>
       </c>
       <c r="B28" s="51">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="C28" s="51">
         <v>172</v>
@@ -8563,7 +8630,7 @@
         <v>229</v>
       </c>
       <c r="H28" s="51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I28" s="51">
         <v>181</v>
@@ -8574,7 +8641,7 @@
         <v>36</v>
       </c>
       <c r="B29" s="51">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C29" s="51">
         <v>156</v>
@@ -8586,7 +8653,9 @@
       <c r="G29" t="s">
         <v>230</v>
       </c>
-      <c r="H29" s="51"/>
+      <c r="H29" s="51">
+        <v>3</v>
+      </c>
       <c r="I29" s="51">
         <v>181</v>
       </c>
@@ -8596,10 +8665,10 @@
         <v>37</v>
       </c>
       <c r="B30" s="51">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C30" s="51">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E30">
         <f>+$F$30</f>
@@ -8612,7 +8681,7 @@
         <v>222</v>
       </c>
       <c r="H30" s="51">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I30" s="51">
         <v>2024</v>
@@ -8623,7 +8692,7 @@
         <v>4</v>
       </c>
       <c r="B31" s="51">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="C31" s="51">
         <v>182</v>
@@ -8636,7 +8705,7 @@
         <v>223</v>
       </c>
       <c r="H31" s="51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I31" s="51">
         <v>2024</v>
@@ -8647,7 +8716,7 @@
         <v>40</v>
       </c>
       <c r="B32" s="51">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="C32" s="51">
         <v>249</v>
@@ -8682,7 +8751,7 @@
         <v>225</v>
       </c>
       <c r="H33" s="51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I33" s="51">
         <v>2024</v>
@@ -8704,7 +8773,7 @@
         <v>226</v>
       </c>
       <c r="H34" s="51">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I34" s="51">
         <v>2024</v>
@@ -8715,7 +8784,7 @@
         <v>44</v>
       </c>
       <c r="B35" s="51">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="C35" s="51">
         <v>169</v>
@@ -8728,7 +8797,7 @@
         <v>227</v>
       </c>
       <c r="H35" s="51">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I35" s="51">
         <v>2024</v>
@@ -8739,7 +8808,7 @@
         <v>49</v>
       </c>
       <c r="B36" s="51">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C36" s="51">
         <v>239</v>
@@ -8752,7 +8821,7 @@
         <v>228</v>
       </c>
       <c r="H36" s="51">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I36" s="51">
         <v>2024</v>
@@ -8763,7 +8832,7 @@
         <v>5</v>
       </c>
       <c r="B37" s="51">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="C37" s="51">
         <v>260</v>
@@ -8776,7 +8845,7 @@
         <v>229</v>
       </c>
       <c r="H37" s="51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I37" s="51">
         <v>2024</v>
@@ -8787,7 +8856,7 @@
         <v>52</v>
       </c>
       <c r="B38" s="51">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C38" s="51">
         <v>101</v>
@@ -8809,7 +8878,7 @@
         <v>53</v>
       </c>
       <c r="B39" s="51">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C39" s="51">
         <v>105</v>
@@ -8825,10 +8894,10 @@
         <v>222</v>
       </c>
       <c r="H39" s="51">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I39" s="51">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
@@ -8836,7 +8905,7 @@
         <v>54</v>
       </c>
       <c r="B40" s="51">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="C40" s="51">
         <v>202</v>
@@ -8848,15 +8917,20 @@
       <c r="G40" t="s">
         <v>223</v>
       </c>
-      <c r="H40" s="51"/>
+      <c r="H40" s="51">
+        <v>3</v>
+      </c>
       <c r="I40" s="51">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>56</v>
       </c>
+      <c r="B41">
+        <v>41</v>
+      </c>
       <c r="C41" s="51">
         <v>198</v>
       </c>
@@ -8868,10 +8942,10 @@
         <v>224</v>
       </c>
       <c r="H41" s="51">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="I41" s="51">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
@@ -8879,7 +8953,7 @@
         <v>57</v>
       </c>
       <c r="B42" s="51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C42" s="51">
         <v>103</v>
@@ -8892,10 +8966,10 @@
         <v>225</v>
       </c>
       <c r="H42" s="51">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I42" s="51">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
@@ -8914,17 +8988,19 @@
         <v>226</v>
       </c>
       <c r="H43" s="51">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="I43" s="51">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>59</v>
       </c>
-      <c r="B44" s="51"/>
+      <c r="B44" s="51">
+        <v>1</v>
+      </c>
       <c r="C44" s="51">
         <v>119</v>
       </c>
@@ -8936,10 +9012,10 @@
         <v>227</v>
       </c>
       <c r="H44" s="51">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="I44" s="51">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
@@ -8960,10 +9036,10 @@
         <v>228</v>
       </c>
       <c r="H45" s="51">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I45" s="51">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
@@ -8971,10 +9047,10 @@
         <v>8</v>
       </c>
       <c r="B46" s="51">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="C46" s="51">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E46">
         <f t="shared" si="3"/>
@@ -8987,7 +9063,7 @@
         <v>6</v>
       </c>
       <c r="I46" s="51">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
@@ -8995,7 +9071,7 @@
         <v>9</v>
       </c>
       <c r="B47" s="51">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="C47" s="51">
         <v>161</v>
@@ -9008,10 +9084,10 @@
         <v>230</v>
       </c>
       <c r="H47" s="51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I47" s="51">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
@@ -9028,10 +9104,10 @@
         <v>222</v>
       </c>
       <c r="H48" s="51">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I48" s="51">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="49" spans="2:9" x14ac:dyDescent="0.25">
@@ -9045,10 +9121,10 @@
         <v>223</v>
       </c>
       <c r="H49" s="51">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I49" s="51">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="50" spans="2:9" x14ac:dyDescent="0.25">
@@ -9060,10 +9136,10 @@
         <v>224</v>
       </c>
       <c r="H50" s="51">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="I50" s="51">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="51" spans="2:9" x14ac:dyDescent="0.25">
@@ -9075,10 +9151,10 @@
         <v>225</v>
       </c>
       <c r="H51" s="51">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I51" s="51">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.25">
@@ -9090,10 +9166,10 @@
         <v>226</v>
       </c>
       <c r="H52" s="51">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="I52" s="51">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.25">
@@ -9105,10 +9181,10 @@
         <v>227</v>
       </c>
       <c r="H53" s="51">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="I53" s="51">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.25">
@@ -9123,7 +9199,7 @@
         <v>7</v>
       </c>
       <c r="I54" s="51">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.25">
@@ -9135,10 +9211,10 @@
         <v>229</v>
       </c>
       <c r="H55" s="51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I55" s="51">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.25">
@@ -9150,10 +9226,10 @@
         <v>230</v>
       </c>
       <c r="H56" s="51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I56" s="51">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="57" spans="2:9" x14ac:dyDescent="0.25">
@@ -9168,7 +9244,7 @@
         <v>222</v>
       </c>
       <c r="H57" s="51">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I57" s="51">
         <v>489</v>
@@ -9183,7 +9259,7 @@
         <v>223</v>
       </c>
       <c r="H58" s="51">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I58" s="51">
         <v>489</v>
@@ -9198,7 +9274,7 @@
         <v>224</v>
       </c>
       <c r="H59" s="51">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I59" s="51">
         <v>489</v>
@@ -9226,7 +9302,7 @@
         <v>226</v>
       </c>
       <c r="H61" s="51">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I61" s="51">
         <v>489</v>
@@ -9254,7 +9330,7 @@
         <v>228</v>
       </c>
       <c r="H63" s="51">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I63" s="51">
         <v>489</v>
@@ -9268,7 +9344,9 @@
       <c r="G64" t="s">
         <v>229</v>
       </c>
-      <c r="H64" s="51"/>
+      <c r="H64" s="51">
+        <v>1</v>
+      </c>
       <c r="I64" s="51">
         <v>489</v>
       </c>
@@ -9298,7 +9376,7 @@
         <v>222</v>
       </c>
       <c r="H66" s="51">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I66" s="51">
         <v>65</v>
@@ -9313,7 +9391,7 @@
         <v>223</v>
       </c>
       <c r="H67" s="51">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I67" s="51">
         <v>65</v>
@@ -9328,7 +9406,7 @@
         <v>224</v>
       </c>
       <c r="H68" s="51">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I68" s="51">
         <v>65</v>
@@ -9343,7 +9421,7 @@
         <v>225</v>
       </c>
       <c r="H69" s="51">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I69" s="51">
         <v>65</v>
@@ -9358,7 +9436,7 @@
         <v>226</v>
       </c>
       <c r="H70" s="51">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I70" s="51">
         <v>65</v>
@@ -9373,7 +9451,7 @@
         <v>227</v>
       </c>
       <c r="H71" s="51">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I71" s="51">
         <v>65</v>
@@ -9388,7 +9466,7 @@
         <v>228</v>
       </c>
       <c r="H72" s="51">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I72" s="51">
         <v>65</v>
@@ -9403,7 +9481,7 @@
         <v>229</v>
       </c>
       <c r="H73" s="51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I73" s="51">
         <v>65</v>
@@ -9436,7 +9514,7 @@
         <v>222</v>
       </c>
       <c r="H75" s="51">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I75" s="51">
         <v>198</v>
@@ -9451,7 +9529,7 @@
         <v>223</v>
       </c>
       <c r="H76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I76" s="51">
         <v>198</v>
@@ -9466,7 +9544,7 @@
         <v>224</v>
       </c>
       <c r="H77" s="51">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="I77" s="51">
         <v>198</v>
@@ -9481,7 +9559,7 @@
         <v>225</v>
       </c>
       <c r="H78" s="51">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I78" s="51">
         <v>198</v>
@@ -9496,7 +9574,7 @@
         <v>226</v>
       </c>
       <c r="H79" s="51">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I79" s="51">
         <v>198</v>
@@ -9511,7 +9589,7 @@
         <v>227</v>
       </c>
       <c r="H80" s="51">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I80" s="51">
         <v>198</v>
@@ -9541,7 +9619,7 @@
         <v>229</v>
       </c>
       <c r="H82" s="51">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I82" s="51">
         <v>198</v>
@@ -9556,7 +9634,7 @@
         <v>230</v>
       </c>
       <c r="H83" s="51">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I83" s="51">
         <v>198</v>
@@ -9574,7 +9652,7 @@
         <v>222</v>
       </c>
       <c r="H84" s="51">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="I84" s="51">
         <v>177</v>
@@ -9589,7 +9667,7 @@
         <v>223</v>
       </c>
       <c r="H85" s="51">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I85" s="51">
         <v>177</v>
@@ -9604,7 +9682,7 @@
         <v>224</v>
       </c>
       <c r="H86" s="51">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I86" s="51">
         <v>177</v>
@@ -9619,7 +9697,7 @@
         <v>225</v>
       </c>
       <c r="H87" s="51">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I87" s="51">
         <v>177</v>
@@ -9634,7 +9712,7 @@
         <v>226</v>
       </c>
       <c r="H88" s="51">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="I88" s="51">
         <v>177</v>
@@ -9649,7 +9727,7 @@
         <v>227</v>
       </c>
       <c r="H89" s="51">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="I89" s="51">
         <v>177</v>
@@ -9664,7 +9742,7 @@
         <v>228</v>
       </c>
       <c r="H90" s="51">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I90" s="51">
         <v>177</v>
@@ -9679,7 +9757,7 @@
         <v>229</v>
       </c>
       <c r="H91" s="51">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I91" s="51">
         <v>177</v>
@@ -9694,7 +9772,7 @@
         <v>230</v>
       </c>
       <c r="H92" s="51">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I92" s="51">
         <v>177</v>
@@ -9712,7 +9790,7 @@
         <v>222</v>
       </c>
       <c r="H93" s="51">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I93" s="51">
         <v>207</v>
@@ -9727,7 +9805,7 @@
         <v>223</v>
       </c>
       <c r="H94" s="51">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I94" s="51">
         <v>207</v>
@@ -9742,7 +9820,7 @@
         <v>224</v>
       </c>
       <c r="H95" s="51">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="I95" s="51">
         <v>207</v>
@@ -9757,7 +9835,7 @@
         <v>225</v>
       </c>
       <c r="H96" s="51">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="I96" s="51">
         <v>207</v>
@@ -9772,7 +9850,7 @@
         <v>226</v>
       </c>
       <c r="H97" s="51">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="I97" s="51">
         <v>207</v>
@@ -9787,7 +9865,7 @@
         <v>227</v>
       </c>
       <c r="H98" s="51">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="I98" s="51">
         <v>207</v>
@@ -9801,7 +9879,9 @@
       <c r="G99" t="s">
         <v>228</v>
       </c>
-      <c r="H99" s="51"/>
+      <c r="H99" s="51">
+        <v>6</v>
+      </c>
       <c r="I99" s="51">
         <v>207</v>
       </c>
@@ -9815,7 +9895,7 @@
         <v>229</v>
       </c>
       <c r="H100" s="51">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I100" s="51">
         <v>207</v>
@@ -9830,7 +9910,7 @@
         <v>230</v>
       </c>
       <c r="H101" s="51">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I101" s="51">
         <v>207</v>
@@ -9848,7 +9928,7 @@
         <v>222</v>
       </c>
       <c r="H102" s="51">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I102" s="51">
         <v>138</v>
@@ -9863,7 +9943,7 @@
         <v>223</v>
       </c>
       <c r="H103" s="51">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="I103" s="51">
         <v>138</v>
@@ -9878,7 +9958,7 @@
         <v>224</v>
       </c>
       <c r="H104" s="51">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I104" s="51">
         <v>138</v>
@@ -9893,7 +9973,7 @@
         <v>225</v>
       </c>
       <c r="H105" s="51">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I105" s="51">
         <v>138</v>
@@ -9908,7 +9988,7 @@
         <v>226</v>
       </c>
       <c r="H106" s="51">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="I106" s="51">
         <v>138</v>
@@ -9923,7 +10003,7 @@
         <v>227</v>
       </c>
       <c r="H107" s="51">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="I107" s="51">
         <v>138</v>
@@ -9953,7 +10033,7 @@
         <v>229</v>
       </c>
       <c r="H109" s="51">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I109" s="51">
         <v>138</v>
@@ -9968,7 +10048,7 @@
         <v>230</v>
       </c>
       <c r="H110" s="51">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I110" s="51">
         <v>138</v>
@@ -9986,7 +10066,7 @@
         <v>222</v>
       </c>
       <c r="H111" s="51">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="I111" s="51">
         <v>227</v>
@@ -10001,7 +10081,7 @@
         <v>223</v>
       </c>
       <c r="H112" s="51">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="I112" s="51">
         <v>227</v>
@@ -10016,7 +10096,7 @@
         <v>224</v>
       </c>
       <c r="H113" s="51">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="I113" s="51">
         <v>227</v>
@@ -10031,7 +10111,7 @@
         <v>225</v>
       </c>
       <c r="H114" s="51">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="I114" s="51">
         <v>227</v>
@@ -10046,7 +10126,7 @@
         <v>226</v>
       </c>
       <c r="H115" s="51">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="I115" s="51">
         <v>227</v>
@@ -10061,7 +10141,7 @@
         <v>227</v>
       </c>
       <c r="H116">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="I116" s="51">
         <v>227</v>
@@ -10076,7 +10156,7 @@
         <v>228</v>
       </c>
       <c r="H117" s="51">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I117" s="51">
         <v>227</v>
@@ -10091,7 +10171,7 @@
         <v>229</v>
       </c>
       <c r="H118" s="51">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I118" s="51">
         <v>227</v>
@@ -10106,7 +10186,7 @@
         <v>230</v>
       </c>
       <c r="H119" s="51">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I119" s="51">
         <v>227</v>
@@ -10124,7 +10204,7 @@
         <v>222</v>
       </c>
       <c r="H120" s="51">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="I120" s="51">
         <v>170</v>
@@ -10139,7 +10219,7 @@
         <v>223</v>
       </c>
       <c r="H121" s="51">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I121" s="51">
         <v>170</v>
@@ -10154,7 +10234,7 @@
         <v>224</v>
       </c>
       <c r="H122" s="51">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="I122" s="51">
         <v>170</v>
@@ -10169,7 +10249,7 @@
         <v>225</v>
       </c>
       <c r="H123" s="51">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="I123" s="51">
         <v>170</v>
@@ -10184,7 +10264,7 @@
         <v>226</v>
       </c>
       <c r="H124">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="I124" s="51">
         <v>170</v>
@@ -10199,7 +10279,7 @@
         <v>227</v>
       </c>
       <c r="H125" s="51">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="I125" s="51">
         <v>170</v>
@@ -10214,7 +10294,7 @@
         <v>228</v>
       </c>
       <c r="H126" s="51">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I126" s="51">
         <v>170</v>
@@ -10229,7 +10309,7 @@
         <v>229</v>
       </c>
       <c r="H127" s="51">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I127" s="51">
         <v>170</v>
@@ -10244,7 +10324,7 @@
         <v>230</v>
       </c>
       <c r="H128" s="51">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I128" s="51">
         <v>170</v>
@@ -10262,7 +10342,7 @@
         <v>222</v>
       </c>
       <c r="H129" s="51">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="I129" s="51">
         <v>72</v>
@@ -10277,7 +10357,7 @@
         <v>223</v>
       </c>
       <c r="H130" s="51">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I130" s="51">
         <v>72</v>
@@ -10292,7 +10372,7 @@
         <v>224</v>
       </c>
       <c r="H131" s="51">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I131" s="51">
         <v>72</v>
@@ -10307,7 +10387,7 @@
         <v>225</v>
       </c>
       <c r="H132" s="51">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I132" s="51">
         <v>72</v>
@@ -10322,7 +10402,7 @@
         <v>226</v>
       </c>
       <c r="H133" s="51">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="I133" s="51">
         <v>72</v>
@@ -10352,7 +10432,7 @@
         <v>228</v>
       </c>
       <c r="H135" s="51">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I135" s="51">
         <v>72</v>
@@ -10367,7 +10447,7 @@
         <v>229</v>
       </c>
       <c r="H136" s="51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I136" s="51">
         <v>72</v>
@@ -10382,7 +10462,7 @@
         <v>230</v>
       </c>
       <c r="H137" s="51">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I137" s="51">
         <v>72</v>
@@ -10400,7 +10480,7 @@
         <v>222</v>
       </c>
       <c r="H138" s="51">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="I138" s="51">
         <v>160</v>
@@ -10415,7 +10495,7 @@
         <v>223</v>
       </c>
       <c r="H139" s="51">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I139" s="51">
         <v>160</v>
@@ -10430,7 +10510,7 @@
         <v>224</v>
       </c>
       <c r="H140">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="I140" s="51">
         <v>160</v>
@@ -10445,7 +10525,7 @@
         <v>225</v>
       </c>
       <c r="H141" s="51">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I141" s="51">
         <v>160</v>
@@ -10460,7 +10540,7 @@
         <v>226</v>
       </c>
       <c r="H142" s="51">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="I142" s="51">
         <v>160</v>
@@ -10475,7 +10555,7 @@
         <v>227</v>
       </c>
       <c r="H143" s="51">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="I143" s="51">
         <v>160</v>
@@ -10490,7 +10570,7 @@
         <v>228</v>
       </c>
       <c r="H144" s="51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I144" s="51">
         <v>160</v>
@@ -10505,7 +10585,7 @@
         <v>229</v>
       </c>
       <c r="H145" s="51">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I145" s="51">
         <v>160</v>
@@ -10520,7 +10600,7 @@
         <v>230</v>
       </c>
       <c r="H146" s="51">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I146" s="51">
         <v>160</v>
@@ -10538,7 +10618,7 @@
         <v>222</v>
       </c>
       <c r="H147" s="51">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I147" s="51">
         <v>178</v>
@@ -10553,7 +10633,7 @@
         <v>223</v>
       </c>
       <c r="H148">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I148" s="51">
         <v>178</v>
@@ -10568,7 +10648,7 @@
         <v>224</v>
       </c>
       <c r="H149" s="51">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="I149" s="51">
         <v>178</v>
@@ -10583,7 +10663,7 @@
         <v>225</v>
       </c>
       <c r="H150" s="51">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I150" s="51">
         <v>178</v>
@@ -10598,7 +10678,7 @@
         <v>226</v>
       </c>
       <c r="H151" s="51">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="I151" s="51">
         <v>178</v>
@@ -10613,7 +10693,7 @@
         <v>227</v>
       </c>
       <c r="H152" s="51">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I152" s="51">
         <v>178</v>
@@ -10628,7 +10708,7 @@
         <v>228</v>
       </c>
       <c r="H153" s="51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I153" s="51">
         <v>178</v>
@@ -10642,7 +10722,9 @@
       <c r="G154" t="s">
         <v>229</v>
       </c>
-      <c r="H154" s="51"/>
+      <c r="H154" s="51">
+        <v>5</v>
+      </c>
       <c r="I154" s="51">
         <v>178</v>
       </c>
@@ -10842,7 +10924,7 @@
         <v>224</v>
       </c>
       <c r="H167" s="51">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I167" s="51">
         <v>162</v>
@@ -10902,7 +10984,7 @@
         <v>228</v>
       </c>
       <c r="H171" s="51">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I171" s="51">
         <v>162</v>
@@ -10950,7 +11032,7 @@
         <v>222</v>
       </c>
       <c r="H174" s="51">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I174" s="51">
         <v>140</v>
@@ -10965,7 +11047,7 @@
         <v>223</v>
       </c>
       <c r="H175" s="51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I175" s="51">
         <v>140</v>
@@ -10980,7 +11062,7 @@
         <v>224</v>
       </c>
       <c r="H176" s="51">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="I176" s="51">
         <v>140</v>
@@ -10995,7 +11077,7 @@
         <v>225</v>
       </c>
       <c r="H177" s="51">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I177" s="51">
         <v>140</v>
@@ -11010,7 +11092,7 @@
         <v>226</v>
       </c>
       <c r="H178" s="51">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="I178" s="51">
         <v>140</v>
@@ -11025,7 +11107,7 @@
         <v>227</v>
       </c>
       <c r="H179" s="51">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="I179" s="51">
         <v>140</v>
@@ -11040,7 +11122,7 @@
         <v>228</v>
       </c>
       <c r="H180">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I180" s="51">
         <v>140</v>
@@ -11055,7 +11137,7 @@
         <v>229</v>
       </c>
       <c r="H181" s="51">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I181" s="51">
         <v>140</v>
@@ -11070,7 +11152,7 @@
         <v>230</v>
       </c>
       <c r="H182" s="51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I182" s="51">
         <v>140</v>
@@ -11088,7 +11170,7 @@
         <v>222</v>
       </c>
       <c r="H183" s="51">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I183" s="51">
         <v>168</v>
@@ -11103,7 +11185,7 @@
         <v>223</v>
       </c>
       <c r="H184" s="51">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I184" s="51">
         <v>168</v>
@@ -11118,7 +11200,7 @@
         <v>224</v>
       </c>
       <c r="H185" s="51">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I185" s="51">
         <v>168</v>
@@ -11133,7 +11215,7 @@
         <v>225</v>
       </c>
       <c r="H186">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I186" s="51">
         <v>168</v>
@@ -11148,7 +11230,7 @@
         <v>226</v>
       </c>
       <c r="H187" s="51">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="I187" s="51">
         <v>168</v>
@@ -11163,7 +11245,7 @@
         <v>227</v>
       </c>
       <c r="H188" s="51">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="I188" s="51">
         <v>168</v>
@@ -11193,7 +11275,7 @@
         <v>229</v>
       </c>
       <c r="H190" s="51">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I190" s="51">
         <v>168</v>
@@ -11226,7 +11308,7 @@
         <v>222</v>
       </c>
       <c r="H192" s="51">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I192" s="51">
         <v>170</v>
@@ -11241,7 +11323,7 @@
         <v>223</v>
       </c>
       <c r="H193" s="51">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I193" s="51">
         <v>170</v>
@@ -11256,7 +11338,7 @@
         <v>224</v>
       </c>
       <c r="H194" s="51">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="I194" s="51">
         <v>170</v>
@@ -11271,7 +11353,7 @@
         <v>225</v>
       </c>
       <c r="H195" s="51">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I195" s="51">
         <v>170</v>
@@ -11286,7 +11368,7 @@
         <v>226</v>
       </c>
       <c r="H196">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="I196" s="51">
         <v>170</v>
@@ -11301,7 +11383,7 @@
         <v>227</v>
       </c>
       <c r="H197" s="51">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="I197" s="51">
         <v>170</v>
@@ -11316,7 +11398,7 @@
         <v>228</v>
       </c>
       <c r="H198" s="51">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I198" s="51">
         <v>170</v>
@@ -11346,7 +11428,7 @@
         <v>230</v>
       </c>
       <c r="H200" s="51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I200" s="51">
         <v>170</v>
@@ -11364,7 +11446,7 @@
         <v>222</v>
       </c>
       <c r="H201" s="51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I201" s="51">
         <v>138</v>
@@ -11392,7 +11474,7 @@
         <v>224</v>
       </c>
       <c r="H203" s="51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I203" s="51">
         <v>138</v>
@@ -11419,7 +11501,9 @@
       <c r="G205" t="s">
         <v>226</v>
       </c>
-      <c r="H205" s="51"/>
+      <c r="H205" s="51">
+        <v>3</v>
+      </c>
       <c r="I205" s="51">
         <v>138</v>
       </c>
@@ -11445,7 +11529,9 @@
       <c r="G207" t="s">
         <v>228</v>
       </c>
-      <c r="H207" s="51"/>
+      <c r="H207" s="51">
+        <v>2</v>
+      </c>
       <c r="I207" s="51">
         <v>138</v>
       </c>
@@ -11488,7 +11574,7 @@
         <v>222</v>
       </c>
       <c r="H210" s="51">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="I210" s="51">
         <v>161</v>
@@ -11503,7 +11589,7 @@
         <v>223</v>
       </c>
       <c r="H211" s="51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I211" s="51">
         <v>161</v>
@@ -11518,7 +11604,7 @@
         <v>224</v>
       </c>
       <c r="H212">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I212" s="51">
         <v>161</v>
@@ -11533,7 +11619,7 @@
         <v>225</v>
       </c>
       <c r="H213" s="51">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I213" s="51">
         <v>161</v>
@@ -11548,7 +11634,7 @@
         <v>226</v>
       </c>
       <c r="H214" s="51">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="I214" s="51">
         <v>161</v>
@@ -11563,7 +11649,7 @@
         <v>227</v>
       </c>
       <c r="H215" s="51">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I215" s="51">
         <v>161</v>
@@ -11593,7 +11679,7 @@
         <v>229</v>
       </c>
       <c r="H217" s="51">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I217" s="51">
         <v>161</v>
@@ -11608,7 +11694,7 @@
         <v>230</v>
       </c>
       <c r="H218" s="51">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I218" s="51">
         <v>161</v>
@@ -11626,7 +11712,7 @@
         <v>222</v>
       </c>
       <c r="H219" s="51">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I219" s="51">
         <v>56</v>
@@ -11656,7 +11742,7 @@
         <v>224</v>
       </c>
       <c r="H221" s="51">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I221" s="51">
         <v>56</v>
@@ -11671,7 +11757,7 @@
         <v>225</v>
       </c>
       <c r="H222" s="51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I222" s="51">
         <v>56</v>
@@ -11686,7 +11772,7 @@
         <v>226</v>
       </c>
       <c r="H223" s="51">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I223" s="51">
         <v>56</v>
@@ -11701,7 +11787,7 @@
         <v>227</v>
       </c>
       <c r="H224" s="51">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I224" s="51">
         <v>56</v>
@@ -11716,7 +11802,7 @@
         <v>228</v>
       </c>
       <c r="H225" s="51">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I225" s="51">
         <v>56</v>
@@ -11731,7 +11817,7 @@
         <v>229</v>
       </c>
       <c r="H226" s="51">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I226" s="51">
         <v>56</v>
@@ -11746,7 +11832,7 @@
         <v>230</v>
       </c>
       <c r="H227" s="51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I227" s="51">
         <v>56</v>
@@ -11764,7 +11850,7 @@
         <v>222</v>
       </c>
       <c r="H228" s="51">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I228" s="51">
         <v>172</v>
@@ -11779,7 +11865,7 @@
         <v>223</v>
       </c>
       <c r="H229" s="51">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I229" s="51">
         <v>172</v>
@@ -11794,7 +11880,7 @@
         <v>224</v>
       </c>
       <c r="H230" s="51">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I230" s="51">
         <v>172</v>
@@ -11809,7 +11895,7 @@
         <v>225</v>
       </c>
       <c r="H231" s="51">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I231" s="51">
         <v>172</v>
@@ -11824,7 +11910,7 @@
         <v>226</v>
       </c>
       <c r="H232" s="51">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I232" s="51">
         <v>172</v>
@@ -11839,7 +11925,7 @@
         <v>227</v>
       </c>
       <c r="H233" s="51">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I233" s="51">
         <v>172</v>
@@ -11869,7 +11955,7 @@
         <v>229</v>
       </c>
       <c r="H235" s="51">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I235" s="51">
         <v>172</v>
@@ -11884,7 +11970,7 @@
         <v>230</v>
       </c>
       <c r="H236">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I236" s="51">
         <v>172</v>
@@ -11902,7 +11988,7 @@
         <v>222</v>
       </c>
       <c r="H237" s="51">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I237" s="51">
         <v>156</v>
@@ -11932,7 +12018,7 @@
         <v>224</v>
       </c>
       <c r="H239" s="51">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I239" s="51">
         <v>156</v>
@@ -11947,7 +12033,7 @@
         <v>225</v>
       </c>
       <c r="H240" s="51">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I240" s="51">
         <v>156</v>
@@ -11962,7 +12048,7 @@
         <v>226</v>
       </c>
       <c r="H241" s="51">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="I241" s="51">
         <v>156</v>
@@ -11977,7 +12063,7 @@
         <v>227</v>
       </c>
       <c r="H242" s="51">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I242" s="51">
         <v>156</v>
@@ -11992,7 +12078,7 @@
         <v>228</v>
       </c>
       <c r="H243" s="51">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I243" s="51">
         <v>156</v>
@@ -12007,7 +12093,7 @@
         <v>229</v>
       </c>
       <c r="H244">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I244" s="51">
         <v>156</v>
@@ -12021,7 +12107,9 @@
       <c r="G245" t="s">
         <v>230</v>
       </c>
-      <c r="H245" s="51"/>
+      <c r="H245" s="51">
+        <v>2</v>
+      </c>
       <c r="I245" s="51">
         <v>156</v>
       </c>
@@ -12038,10 +12126,10 @@
         <v>222</v>
       </c>
       <c r="H246" s="51">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I246" s="51">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="247" spans="5:9" x14ac:dyDescent="0.25">
@@ -12052,9 +12140,11 @@
       <c r="G247" t="s">
         <v>223</v>
       </c>
-      <c r="H247" s="51"/>
+      <c r="H247" s="51">
+        <v>2</v>
+      </c>
       <c r="I247" s="51">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="248" spans="5:9" x14ac:dyDescent="0.25">
@@ -12066,10 +12156,10 @@
         <v>224</v>
       </c>
       <c r="H248" s="51">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I248" s="51">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="249" spans="5:9" x14ac:dyDescent="0.25">
@@ -12080,9 +12170,11 @@
       <c r="G249" t="s">
         <v>225</v>
       </c>
-      <c r="H249" s="51"/>
+      <c r="H249" s="51">
+        <v>4</v>
+      </c>
       <c r="I249" s="51">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="250" spans="5:9" x14ac:dyDescent="0.25">
@@ -12094,10 +12186,10 @@
         <v>226</v>
       </c>
       <c r="H250" s="51">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I250" s="51">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="251" spans="5:9" x14ac:dyDescent="0.25">
@@ -12109,10 +12201,10 @@
         <v>227</v>
       </c>
       <c r="H251" s="51">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I251" s="51">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="252" spans="5:9" x14ac:dyDescent="0.25">
@@ -12124,10 +12216,10 @@
         <v>228</v>
       </c>
       <c r="H252">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I252" s="51">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="253" spans="5:9" x14ac:dyDescent="0.25">
@@ -12139,10 +12231,10 @@
         <v>229</v>
       </c>
       <c r="H253" s="51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I253" s="51">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="254" spans="5:9" x14ac:dyDescent="0.25">
@@ -12153,9 +12245,11 @@
       <c r="G254" t="s">
         <v>230</v>
       </c>
-      <c r="H254" s="51"/>
+      <c r="H254" s="51">
+        <v>3</v>
+      </c>
       <c r="I254" s="51">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="255" spans="5:9" x14ac:dyDescent="0.25">
@@ -12170,7 +12264,7 @@
         <v>222</v>
       </c>
       <c r="H255" s="51">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I255" s="51">
         <v>182</v>
@@ -12185,7 +12279,7 @@
         <v>223</v>
       </c>
       <c r="H256" s="51">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I256" s="51">
         <v>182</v>
@@ -12200,7 +12294,7 @@
         <v>224</v>
       </c>
       <c r="H257" s="51">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="I257" s="51">
         <v>182</v>
@@ -12215,7 +12309,7 @@
         <v>225</v>
       </c>
       <c r="H258">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I258" s="51">
         <v>182</v>
@@ -12230,7 +12324,7 @@
         <v>226</v>
       </c>
       <c r="H259" s="51">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="I259" s="51">
         <v>182</v>
@@ -12245,7 +12339,7 @@
         <v>227</v>
       </c>
       <c r="H260">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I260" s="51">
         <v>182</v>
@@ -12260,7 +12354,7 @@
         <v>228</v>
       </c>
       <c r="H261" s="51">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I261" s="51">
         <v>182</v>
@@ -12275,7 +12369,7 @@
         <v>229</v>
       </c>
       <c r="H262" s="51">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I262" s="51">
         <v>182</v>
@@ -12290,7 +12384,7 @@
         <v>230</v>
       </c>
       <c r="H263" s="51">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I263" s="51">
         <v>182</v>
@@ -12308,7 +12402,7 @@
         <v>222</v>
       </c>
       <c r="H264" s="51">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I264" s="51">
         <v>249</v>
@@ -12338,7 +12432,7 @@
         <v>224</v>
       </c>
       <c r="H266" s="51">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I266" s="51">
         <v>249</v>
@@ -12353,7 +12447,7 @@
         <v>225</v>
       </c>
       <c r="H267" s="51">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I267" s="51">
         <v>249</v>
@@ -12368,7 +12462,7 @@
         <v>226</v>
       </c>
       <c r="H268">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="I268" s="51">
         <v>249</v>
@@ -12383,7 +12477,7 @@
         <v>227</v>
       </c>
       <c r="H269" s="51">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I269" s="51">
         <v>249</v>
@@ -12413,7 +12507,7 @@
         <v>229</v>
       </c>
       <c r="H271" s="51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I271" s="51">
         <v>249</v>
@@ -12428,7 +12522,7 @@
         <v>230</v>
       </c>
       <c r="H272" s="51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I272" s="51">
         <v>249</v>
@@ -12679,7 +12773,7 @@
         <v>222</v>
       </c>
       <c r="H291">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I291" s="51">
         <v>169</v>
@@ -12694,7 +12788,7 @@
         <v>223</v>
       </c>
       <c r="H292">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I292" s="51">
         <v>169</v>
@@ -12709,7 +12803,7 @@
         <v>224</v>
       </c>
       <c r="H293">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="I293" s="51">
         <v>169</v>
@@ -12724,7 +12818,7 @@
         <v>225</v>
       </c>
       <c r="H294">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I294" s="51">
         <v>169</v>
@@ -12739,7 +12833,7 @@
         <v>226</v>
       </c>
       <c r="H295">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="I295" s="51">
         <v>169</v>
@@ -12754,7 +12848,7 @@
         <v>227</v>
       </c>
       <c r="H296">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="I296" s="51">
         <v>169</v>
@@ -12769,7 +12863,7 @@
         <v>228</v>
       </c>
       <c r="H297" s="51">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I297" s="51">
         <v>169</v>
@@ -12799,7 +12893,7 @@
         <v>230</v>
       </c>
       <c r="H299" s="51">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I299" s="51">
         <v>169</v>
@@ -12847,7 +12941,7 @@
         <v>224</v>
       </c>
       <c r="H302" s="51">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I302" s="51">
         <v>239</v>
@@ -12877,7 +12971,7 @@
         <v>226</v>
       </c>
       <c r="H304" s="51">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I304" s="51">
         <v>239</v>
@@ -12955,7 +13049,7 @@
         <v>222</v>
       </c>
       <c r="H309">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="I309" s="51">
         <v>260</v>
@@ -12970,7 +13064,7 @@
         <v>223</v>
       </c>
       <c r="H310">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I310" s="51">
         <v>260</v>
@@ -12985,7 +13079,7 @@
         <v>224</v>
       </c>
       <c r="H311">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="I311" s="51">
         <v>260</v>
@@ -13000,7 +13094,7 @@
         <v>225</v>
       </c>
       <c r="H312">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I312" s="51">
         <v>260</v>
@@ -13015,7 +13109,7 @@
         <v>226</v>
       </c>
       <c r="H313">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="I313" s="51">
         <v>260</v>
@@ -13030,7 +13124,7 @@
         <v>227</v>
       </c>
       <c r="H314">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="I314" s="51">
         <v>260</v>
@@ -13045,7 +13139,7 @@
         <v>228</v>
       </c>
       <c r="H315" s="51">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I315" s="51">
         <v>260</v>
@@ -13060,7 +13154,7 @@
         <v>229</v>
       </c>
       <c r="H316">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I316" s="51">
         <v>260</v>
@@ -13075,7 +13169,7 @@
         <v>230</v>
       </c>
       <c r="H317" s="51">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I317" s="51">
         <v>260</v>
@@ -13107,7 +13201,9 @@
       <c r="G319" t="s">
         <v>223</v>
       </c>
-      <c r="H319" s="51"/>
+      <c r="H319" s="51">
+        <v>1</v>
+      </c>
       <c r="I319" s="51">
         <v>101</v>
       </c>
@@ -13172,7 +13268,7 @@
         <v>228</v>
       </c>
       <c r="H324" s="51">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I324" s="51">
         <v>101</v>
@@ -13290,7 +13386,7 @@
         <v>228</v>
       </c>
       <c r="H333" s="51">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I333" s="51">
         <v>105</v>
@@ -13334,7 +13430,7 @@
         <v>222</v>
       </c>
       <c r="H336" s="51">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I336" s="51">
         <v>202</v>
@@ -13349,7 +13445,7 @@
         <v>223</v>
       </c>
       <c r="H337" s="51">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I337" s="51">
         <v>202</v>
@@ -13364,7 +13460,7 @@
         <v>224</v>
       </c>
       <c r="H338" s="51">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I338" s="51">
         <v>202</v>
@@ -13379,7 +13475,7 @@
         <v>225</v>
       </c>
       <c r="H339" s="51">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I339" s="51">
         <v>202</v>
@@ -13394,7 +13490,7 @@
         <v>226</v>
       </c>
       <c r="H340">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I340" s="51">
         <v>202</v>
@@ -13409,7 +13505,7 @@
         <v>227</v>
       </c>
       <c r="H341" s="51">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I341" s="51">
         <v>202</v>
@@ -13424,7 +13520,7 @@
         <v>228</v>
       </c>
       <c r="H342" s="51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I342" s="51">
         <v>202</v>
@@ -13439,7 +13535,7 @@
         <v>229</v>
       </c>
       <c r="H343" s="51">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I343" s="51">
         <v>202</v>
@@ -13454,7 +13550,7 @@
         <v>230</v>
       </c>
       <c r="H344" s="51">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I344" s="51">
         <v>202</v>
@@ -13471,6 +13567,9 @@
       <c r="G345" t="s">
         <v>222</v>
       </c>
+      <c r="H345">
+        <v>6</v>
+      </c>
       <c r="I345" s="51">
         <v>198</v>
       </c>
@@ -13483,7 +13582,9 @@
       <c r="G346" t="s">
         <v>223</v>
       </c>
-      <c r="H346" s="51"/>
+      <c r="H346" s="51">
+        <v>8</v>
+      </c>
       <c r="I346" s="51">
         <v>198</v>
       </c>
@@ -13496,7 +13597,9 @@
       <c r="G347" t="s">
         <v>224</v>
       </c>
-      <c r="H347" s="51"/>
+      <c r="H347" s="51">
+        <v>17</v>
+      </c>
       <c r="I347" s="51">
         <v>198</v>
       </c>
@@ -13509,6 +13612,9 @@
       <c r="G348" t="s">
         <v>225</v>
       </c>
+      <c r="H348">
+        <v>6</v>
+      </c>
       <c r="I348" s="51">
         <v>198</v>
       </c>
@@ -13521,7 +13627,9 @@
       <c r="G349" t="s">
         <v>226</v>
       </c>
-      <c r="H349" s="51"/>
+      <c r="H349" s="51">
+        <v>14</v>
+      </c>
       <c r="I349" s="51">
         <v>198</v>
       </c>
@@ -13534,7 +13642,9 @@
       <c r="G350" t="s">
         <v>227</v>
       </c>
-      <c r="H350" s="51"/>
+      <c r="H350" s="51">
+        <v>6</v>
+      </c>
       <c r="I350" s="51">
         <v>198</v>
       </c>
@@ -13547,7 +13657,9 @@
       <c r="G351" t="s">
         <v>228</v>
       </c>
-      <c r="H351" s="51"/>
+      <c r="H351" s="51">
+        <v>18</v>
+      </c>
       <c r="I351" s="51">
         <v>198</v>
       </c>
@@ -13560,6 +13672,9 @@
       <c r="G352" t="s">
         <v>229</v>
       </c>
+      <c r="H352">
+        <v>4</v>
+      </c>
       <c r="I352" s="51">
         <v>198</v>
       </c>
@@ -13572,7 +13687,9 @@
       <c r="G353" t="s">
         <v>230</v>
       </c>
-      <c r="H353" s="51"/>
+      <c r="H353" s="51">
+        <v>2</v>
+      </c>
       <c r="I353" s="51">
         <v>198</v>
       </c>
@@ -13667,7 +13784,7 @@
         <v>228</v>
       </c>
       <c r="H360" s="51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I360" s="51">
         <v>103</v>
@@ -13842,6 +13959,9 @@
       <c r="G373" t="s">
         <v>223</v>
       </c>
+      <c r="H373">
+        <v>1</v>
+      </c>
       <c r="I373">
         <v>119</v>
       </c>
@@ -14065,10 +14185,10 @@
         <v>222</v>
       </c>
       <c r="H390">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I390">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="391" spans="5:9" x14ac:dyDescent="0.25">
@@ -14079,8 +14199,11 @@
       <c r="G391" t="s">
         <v>223</v>
       </c>
+      <c r="H391">
+        <v>3</v>
+      </c>
       <c r="I391">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="392" spans="5:9" x14ac:dyDescent="0.25">
@@ -14092,10 +14215,10 @@
         <v>224</v>
       </c>
       <c r="H392">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I392">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="393" spans="5:9" x14ac:dyDescent="0.25">
@@ -14107,10 +14230,10 @@
         <v>225</v>
       </c>
       <c r="H393">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I393">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="394" spans="5:9" x14ac:dyDescent="0.25">
@@ -14122,10 +14245,10 @@
         <v>226</v>
       </c>
       <c r="H394">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="I394">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="395" spans="5:9" x14ac:dyDescent="0.25">
@@ -14137,10 +14260,10 @@
         <v>227</v>
       </c>
       <c r="H395">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="I395">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="396" spans="5:9" x14ac:dyDescent="0.25">
@@ -14152,10 +14275,10 @@
         <v>228</v>
       </c>
       <c r="H396">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I396">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="397" spans="5:9" x14ac:dyDescent="0.25">
@@ -14167,10 +14290,10 @@
         <v>229</v>
       </c>
       <c r="H397">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I397">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="398" spans="5:9" x14ac:dyDescent="0.25">
@@ -14182,10 +14305,10 @@
         <v>230</v>
       </c>
       <c r="H398">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I398">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="399" spans="5:9" x14ac:dyDescent="0.25">
@@ -14200,7 +14323,7 @@
         <v>222</v>
       </c>
       <c r="H399">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I399">
         <v>161</v>
@@ -14215,7 +14338,7 @@
         <v>223</v>
       </c>
       <c r="H400">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I400">
         <v>161</v>
@@ -14230,7 +14353,7 @@
         <v>224</v>
       </c>
       <c r="H401">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I401">
         <v>161</v>
@@ -14245,7 +14368,7 @@
         <v>225</v>
       </c>
       <c r="H402">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I402">
         <v>161</v>
@@ -14260,7 +14383,7 @@
         <v>226</v>
       </c>
       <c r="H403">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I403">
         <v>161</v>
@@ -14275,7 +14398,7 @@
         <v>227</v>
       </c>
       <c r="H404">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I404">
         <v>161</v>
@@ -14305,7 +14428,7 @@
         <v>229</v>
       </c>
       <c r="H406">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I406">
         <v>161</v>
@@ -14320,7 +14443,7 @@
         <v>230</v>
       </c>
       <c r="H407">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I407">
         <v>161</v>

--- a/data/ventas.xlsx
+++ b/data/ventas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cesar\Desktop\Reportes Ventas Rap\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1ED77F2B-C804-4A4C-B2B1-B2CB88BD6181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7CA9088C-DB13-4089-81E8-81DF93022920}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2534,22 +2534,22 @@
         <v>0</v>
       </c>
       <c r="C2" s="96">
-        <v>20239.264746040899</v>
+        <v>23536.120041674199</v>
       </c>
       <c r="D2" s="96">
-        <v>97497.216435570401</v>
+        <v>118844.0518090774</v>
       </c>
       <c r="E2" s="96">
-        <v>347488527.93282223</v>
+        <v>404778139.42970479</v>
       </c>
       <c r="F2" s="96">
         <v>0</v>
       </c>
       <c r="G2" s="96">
-        <v>208601.67291691661</v>
+        <v>219962.89139595471</v>
       </c>
       <c r="H2" s="96">
-        <v>208601.74</v>
+        <v>219963</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -2560,22 +2560,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="96">
-        <v>287.35735488500001</v>
+        <v>304.92164059919997</v>
       </c>
       <c r="D3" s="96">
-        <v>636.38716535089998</v>
+        <v>609.84716534890003</v>
       </c>
       <c r="E3" s="96">
-        <v>6953389.0972305397</v>
+        <v>7332096.3798651379</v>
       </c>
       <c r="F3" s="96">
         <v>0</v>
       </c>
       <c r="G3" s="96">
-        <v>208601.67291691661</v>
+        <v>219962.89139595471</v>
       </c>
       <c r="H3" s="96">
-        <v>208601.74</v>
+        <v>219963</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2586,13 +2586,13 @@
         <v>1</v>
       </c>
       <c r="C4" s="96">
-        <v>155.42341269729999</v>
+        <v>176.8288769829</v>
       </c>
       <c r="D4" s="96">
-        <v>326.98499999799998</v>
+        <v>368.48999999900002</v>
       </c>
       <c r="E4" s="96">
-        <v>4842984.6712837927</v>
+        <v>5569721.4797102707</v>
       </c>
       <c r="F4" s="96">
         <v>0</v>
@@ -2612,13 +2612,13 @@
         <v>1</v>
       </c>
       <c r="C5" s="96">
-        <v>200.08797618950001</v>
+        <v>242.08867063389999</v>
       </c>
       <c r="D5" s="96">
-        <v>776.02249999560001</v>
+        <v>958.47710713790002</v>
       </c>
       <c r="E5" s="96">
-        <v>4538116.0675083203</v>
+        <v>5463522.8209966822</v>
       </c>
       <c r="F5" s="96">
         <v>0</v>
@@ -2638,13 +2638,13 @@
         <v>1</v>
       </c>
       <c r="C6" s="96">
-        <v>397.30575396749998</v>
+        <v>422.23492063399999</v>
       </c>
       <c r="D6" s="96">
-        <v>1116.1477142923</v>
+        <v>1210.8927142914999</v>
       </c>
       <c r="E6" s="96">
-        <v>7971555.33420307</v>
+        <v>8696250.9292322323</v>
       </c>
       <c r="F6" s="96">
         <v>0</v>
@@ -2664,13 +2664,13 @@
         <v>1</v>
       </c>
       <c r="C7" s="96">
-        <v>418.16251984000002</v>
+        <v>470.69109126870001</v>
       </c>
       <c r="D7" s="96">
-        <v>1324.0909999978001</v>
+        <v>1524.0909999988</v>
       </c>
       <c r="E7" s="96">
-        <v>8068882.1386908181</v>
+        <v>9117515.4833692927</v>
       </c>
       <c r="F7" s="96">
         <v>0</v>
@@ -2690,13 +2690,13 @@
         <v>1</v>
       </c>
       <c r="C8" s="96">
-        <v>1635.1115740742</v>
+        <v>2244.1115740741998</v>
       </c>
       <c r="D8" s="96">
-        <v>1870.3864768542001</v>
+        <v>2660.9464768541998</v>
       </c>
       <c r="E8" s="96">
-        <v>17061083.040882383</v>
+        <v>26940309.263082385</v>
       </c>
       <c r="F8" s="96">
         <v>0</v>
@@ -2716,13 +2716,13 @@
         <v>1</v>
       </c>
       <c r="C9" s="96">
-        <v>198.23150793619999</v>
+        <v>232.0398412696</v>
       </c>
       <c r="D9" s="96">
-        <v>911.56750000140005</v>
+        <v>1086.5675000014</v>
       </c>
       <c r="E9" s="96">
-        <v>3586477.5079781078</v>
+        <v>4065628.6784671973</v>
       </c>
       <c r="F9" s="96">
         <v>0</v>
@@ -2742,13 +2742,13 @@
         <v>1</v>
       </c>
       <c r="C10" s="96">
-        <v>151.87760912690001</v>
+        <v>185.462529762</v>
       </c>
       <c r="D10" s="96">
-        <v>538.00411458880001</v>
+        <v>863.00411458940005</v>
       </c>
       <c r="E10" s="96">
-        <v>3996158.8131728824</v>
+        <v>6335712.8592704926</v>
       </c>
       <c r="F10" s="96">
         <v>0</v>
@@ -2768,13 +2768,13 @@
         <v>1</v>
       </c>
       <c r="C11" s="96">
-        <v>157.76408730060001</v>
+        <v>188.60525793549999</v>
       </c>
       <c r="D11" s="96">
-        <v>362.56459523730001</v>
+        <v>684.56459523729995</v>
       </c>
       <c r="E11" s="96">
-        <v>2958594.3353685732</v>
+        <v>3800655.2343727285</v>
       </c>
       <c r="F11" s="96">
         <v>0</v>
@@ -2794,13 +2794,13 @@
         <v>1</v>
       </c>
       <c r="C12" s="96">
-        <v>376.22777777610003</v>
+        <v>392.8326984112</v>
       </c>
       <c r="D12" s="96">
-        <v>2353.8501190427</v>
+        <v>2464.8501190417001</v>
       </c>
       <c r="E12" s="96">
-        <v>6404448.8053096188</v>
+        <v>6728186.3048162535</v>
       </c>
       <c r="F12" s="96">
         <v>0</v>
@@ -2820,13 +2820,13 @@
         <v>1</v>
       </c>
       <c r="C13" s="96">
-        <v>340.59277777739999</v>
+        <v>382.97797618999999</v>
       </c>
       <c r="D13" s="96">
-        <v>1049.3365119081</v>
+        <v>1212.3465119081</v>
       </c>
       <c r="E13" s="96">
-        <v>6622431.8650625329</v>
+        <v>7646569.2805425785</v>
       </c>
       <c r="F13" s="96">
         <v>0</v>
@@ -2846,13 +2846,13 @@
         <v>1</v>
       </c>
       <c r="C14" s="96">
-        <v>1689.6688492064</v>
+        <v>1784.0438492065</v>
       </c>
       <c r="D14" s="96">
-        <v>14984.7324999998</v>
+        <v>15478.012499999801</v>
       </c>
       <c r="E14" s="96">
-        <v>39689592.681744099</v>
+        <v>41231894.308746725</v>
       </c>
       <c r="F14" s="96">
         <v>0</v>
@@ -2872,13 +2872,13 @@
         <v>1</v>
       </c>
       <c r="C15" s="96">
-        <v>322.91230158680003</v>
+        <v>359.23888888840003</v>
       </c>
       <c r="D15" s="96">
-        <v>1065.8074999979999</v>
+        <v>1179.3074999966</v>
       </c>
       <c r="E15" s="96">
-        <v>6197917.8190731332</v>
+        <v>6977673.3087740811</v>
       </c>
       <c r="F15" s="96">
         <v>0</v>
@@ -2898,13 +2898,13 @@
         <v>1</v>
       </c>
       <c r="C16" s="96">
-        <v>214.65501984030001</v>
+        <v>241.7752579353</v>
       </c>
       <c r="D16" s="96">
-        <v>1133.6685119097999</v>
+        <v>1283.1735119088</v>
       </c>
       <c r="E16" s="96">
-        <v>5255755.4759214995</v>
+        <v>5986642.3849513531</v>
       </c>
       <c r="F16" s="96">
         <v>0</v>
@@ -2924,13 +2924,13 @@
         <v>1</v>
       </c>
       <c r="C17" s="96">
-        <v>480.26246031580001</v>
+        <v>514.63587301380005</v>
       </c>
       <c r="D17" s="96">
-        <v>1416.7735238169</v>
+        <v>1512.2785238153001</v>
       </c>
       <c r="E17" s="96">
-        <v>9288875.7683896385</v>
+        <v>10212334.874835599</v>
       </c>
       <c r="F17" s="96">
         <v>0</v>
@@ -2950,13 +2950,13 @@
         <v>1</v>
       </c>
       <c r="C18" s="96">
-        <v>588.94634920609997</v>
+        <v>653.25121031690003</v>
       </c>
       <c r="D18" s="96">
-        <v>2848.4188452368999</v>
+        <v>3068.6327738059999</v>
       </c>
       <c r="E18" s="96">
-        <v>12202147.531287048</v>
+        <v>12888810.036315698</v>
       </c>
       <c r="F18" s="96">
         <v>0</v>
@@ -2976,13 +2976,13 @@
         <v>1</v>
       </c>
       <c r="C19" s="96">
-        <v>441.94708994609999</v>
+        <v>519.40931216779995</v>
       </c>
       <c r="D19" s="96">
-        <v>1784.6717142952</v>
+        <v>1972.9242142894</v>
       </c>
       <c r="E19" s="96">
-        <v>9037854.5756811257</v>
+        <v>10086924.880174421</v>
       </c>
       <c r="F19" s="96">
         <v>0</v>
@@ -3002,13 +3002,13 @@
         <v>1</v>
       </c>
       <c r="C20" s="96">
-        <v>1691.1757341268999</v>
+        <v>1834.8007341268999</v>
       </c>
       <c r="D20" s="96">
-        <v>8709.6164999951998</v>
+        <v>9290.8964999950003</v>
       </c>
       <c r="E20" s="96">
-        <v>25307057.946538661</v>
+        <v>27236244.29200922</v>
       </c>
       <c r="F20" s="96">
         <v>0</v>
@@ -3028,13 +3028,13 @@
         <v>1</v>
       </c>
       <c r="C21" s="96">
-        <v>264.46081349069999</v>
+        <v>290.11200396679999</v>
       </c>
       <c r="D21" s="96">
-        <v>939.2292142901</v>
+        <v>1023.2292142913</v>
       </c>
       <c r="E21" s="96">
-        <v>5595341.8938343767</v>
+        <v>6172988.7852142667</v>
       </c>
       <c r="F21" s="96">
         <v>0</v>
@@ -3054,13 +3054,13 @@
         <v>1</v>
       </c>
       <c r="C22" s="96">
-        <v>197.9982142849</v>
+        <v>214.7938492056</v>
       </c>
       <c r="D22" s="96">
-        <v>505.67851190179999</v>
+        <v>568.13101190359998</v>
       </c>
       <c r="E22" s="96">
-        <v>3109025.2196221473</v>
+        <v>3355300.6510111671</v>
       </c>
       <c r="F22" s="96">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         <v>1</v>
       </c>
       <c r="C23" s="96">
-        <v>781.37513888820001</v>
+        <v>786.37513888820001</v>
       </c>
       <c r="D23" s="96">
         <v>4836.2267976160001</v>
       </c>
       <c r="E23" s="96">
-        <v>16984006.336814482</v>
+        <v>17058609.68881448</v>
       </c>
       <c r="F23" s="96">
         <v>0</v>
@@ -3132,13 +3132,13 @@
         <v>1</v>
       </c>
       <c r="C25" s="96">
-        <v>298.05575396820001</v>
+        <v>315.21142857130002</v>
       </c>
       <c r="D25" s="96">
-        <v>850.76000000500005</v>
+        <v>945.48208333850005</v>
       </c>
       <c r="E25" s="96">
-        <v>4865926.9418352479</v>
+        <v>5326745.1355416654</v>
       </c>
       <c r="F25" s="96">
         <v>0</v>
@@ -3158,13 +3158,13 @@
         <v>1</v>
       </c>
       <c r="C26" s="96">
-        <v>200.69081349109999</v>
+        <v>212.21638888800001</v>
       </c>
       <c r="D26" s="96">
-        <v>459.23708333330001</v>
+        <v>513.23708333510001</v>
       </c>
       <c r="E26" s="96">
-        <v>3089173.5689832573</v>
+        <v>3355234.3973482912</v>
       </c>
       <c r="F26" s="96">
         <v>0</v>
@@ -3184,13 +3184,13 @@
         <v>1</v>
       </c>
       <c r="C27" s="96">
-        <v>1888.5</v>
+        <v>1886.5</v>
       </c>
       <c r="D27" s="96">
-        <v>9736.84</v>
+        <v>9716.84</v>
       </c>
       <c r="E27" s="96">
-        <v>23468686.842</v>
+        <v>23429640.094719999</v>
       </c>
       <c r="F27" s="96">
         <v>0</v>
@@ -3210,13 +3210,13 @@
         <v>1</v>
       </c>
       <c r="C28" s="96">
-        <v>424.6578339939</v>
+        <v>493.60180224750002</v>
       </c>
       <c r="D28" s="96">
-        <v>1810.8346354224</v>
+        <v>2090.0317187555002</v>
       </c>
       <c r="E28" s="96">
-        <v>8516814.03087065</v>
+        <v>9510778.0994110405</v>
       </c>
       <c r="F28" s="96">
         <v>0</v>
@@ -3236,13 +3236,13 @@
         <v>1</v>
       </c>
       <c r="C29" s="96">
-        <v>1351.4300000001001</v>
+        <v>1460.9161111113001</v>
       </c>
       <c r="D29" s="96">
-        <v>2346.2820833356</v>
+        <v>2536.7420833368001</v>
       </c>
       <c r="E29" s="96">
-        <v>17555809.912466466</v>
+        <v>18937147.75616448</v>
       </c>
       <c r="F29" s="96">
         <v>0</v>
@@ -3262,13 +3262,13 @@
         <v>1</v>
       </c>
       <c r="C30" s="96">
-        <v>111.48898809560001</v>
+        <v>133.1834325399</v>
       </c>
       <c r="D30" s="96">
-        <v>371.92416667719999</v>
+        <v>450.17666667719999</v>
       </c>
       <c r="E30" s="96">
-        <v>2098536.1960838647</v>
+        <v>2447356.6153951334</v>
       </c>
       <c r="F30" s="96">
         <v>0</v>
@@ -3288,13 +3288,13 @@
         <v>1</v>
       </c>
       <c r="C31" s="96">
-        <v>172.14345238000001</v>
+        <v>210.9894841258</v>
       </c>
       <c r="D31" s="96">
-        <v>351.31749999890002</v>
+        <v>446.56999999829998</v>
       </c>
       <c r="E31" s="96">
-        <v>2883607.9842428509</v>
+        <v>3339149.8528803443</v>
       </c>
       <c r="F31" s="96">
         <v>0</v>
@@ -3314,13 +3314,13 @@
         <v>1</v>
       </c>
       <c r="C32" s="96">
-        <v>55.931944444599999</v>
+        <v>67.658134920600006</v>
       </c>
       <c r="D32" s="96">
-        <v>392.40416666760001</v>
+        <v>439.60125000070002</v>
       </c>
       <c r="E32" s="96">
-        <v>1626463.4655310514</v>
+        <v>1956633.4710906136</v>
       </c>
       <c r="F32" s="96">
         <v>0</v>
@@ -3340,13 +3340,13 @@
         <v>1</v>
       </c>
       <c r="C33" s="96">
-        <v>308.6682738092</v>
+        <v>315.11827380919999</v>
       </c>
       <c r="D33" s="96">
-        <v>704.99600000179998</v>
+        <v>755.99600000379996</v>
       </c>
       <c r="E33" s="96">
-        <v>4975553.6144345868</v>
+        <v>5102416.1731653139</v>
       </c>
       <c r="F33" s="96">
         <v>0</v>
@@ -3392,13 +3392,13 @@
         <v>1</v>
       </c>
       <c r="C35" s="96">
-        <v>-25</v>
+        <v>233</v>
       </c>
       <c r="D35" s="96">
-        <v>0</v>
+        <v>292.8</v>
       </c>
       <c r="E35" s="96">
-        <v>-233849</v>
+        <v>3102340.9134</v>
       </c>
       <c r="F35" s="96">
         <v>0</v>
@@ -3418,13 +3418,13 @@
         <v>1</v>
       </c>
       <c r="C36" s="96">
-        <v>285.49811507840002</v>
+        <v>299.38214285610002</v>
       </c>
       <c r="D36" s="96">
-        <v>1243.7466071438</v>
+        <v>1317.7466071432</v>
       </c>
       <c r="E36" s="96">
-        <v>5822405.6030015703</v>
+        <v>6142976.0828060079</v>
       </c>
       <c r="F36" s="96">
         <v>0</v>
@@ -3470,13 +3470,13 @@
         <v>1</v>
       </c>
       <c r="C38" s="96">
-        <v>308.39242424230002</v>
+        <v>313.39242424230002</v>
       </c>
       <c r="D38" s="96">
-        <v>3260.7299999989</v>
+        <v>3329.8899999988998</v>
       </c>
       <c r="E38" s="96">
-        <v>6663134.8062294191</v>
+        <v>6878414.3543294193</v>
       </c>
       <c r="F38" s="96">
         <v>0</v>
@@ -3496,13 +3496,13 @@
         <v>1</v>
       </c>
       <c r="C39" s="96">
-        <v>471.4166666667</v>
+        <v>582.91666666670005</v>
       </c>
       <c r="D39" s="96">
-        <v>5734.2</v>
+        <v>7056.58</v>
       </c>
       <c r="E39" s="96">
-        <v>10196205.867152149</v>
+        <v>12288523.154902149</v>
       </c>
       <c r="F39" s="96">
         <v>0</v>
@@ -3522,13 +3522,13 @@
         <v>1</v>
       </c>
       <c r="C40" s="96">
-        <v>757.61760582019997</v>
+        <v>783.70252645510004</v>
       </c>
       <c r="D40" s="96">
-        <v>4224.4444986853996</v>
+        <v>4461.5912844021996</v>
       </c>
       <c r="E40" s="96">
-        <v>6909391.5039921645</v>
+        <v>7360714.5095196133</v>
       </c>
       <c r="F40" s="96">
         <v>0</v>
@@ -3548,13 +3548,13 @@
         <v>1</v>
       </c>
       <c r="C41" s="96">
-        <v>679.35634920610005</v>
+        <v>911.18134920600005</v>
       </c>
       <c r="D41" s="96">
-        <v>4883.0241666669999</v>
+        <v>6551.529166667</v>
       </c>
       <c r="E41" s="96">
-        <v>8825883.2392010316</v>
+        <v>12160822.067982538</v>
       </c>
       <c r="F41" s="96">
         <v>0</v>
@@ -3574,13 +3574,13 @@
         <v>1</v>
       </c>
       <c r="C42" s="96">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="D42" s="96">
-        <v>424.04</v>
+        <v>648.04</v>
       </c>
       <c r="E42" s="96">
-        <v>746511.00490000006</v>
+        <v>1084549.0049000001</v>
       </c>
       <c r="F42" s="96">
         <v>0</v>
@@ -3600,13 +3600,13 @@
         <v>1</v>
       </c>
       <c r="C43" s="96">
-        <v>74.818551587300007</v>
+        <v>249.55500992079999</v>
       </c>
       <c r="D43" s="96">
-        <v>229.00349106979999</v>
+        <v>1124.5225014852999</v>
       </c>
       <c r="E43" s="96">
-        <v>3760393.1741207056</v>
+        <v>8104352.0621971888</v>
       </c>
       <c r="F43" s="96">
         <v>0</v>
@@ -3626,13 +3626,13 @@
         <v>1</v>
       </c>
       <c r="C44" s="96">
-        <v>123.917063492</v>
+        <v>1041.2170634924</v>
       </c>
       <c r="D44" s="96">
-        <v>1239.6349404736</v>
+        <v>12428.4199404746</v>
       </c>
       <c r="E44" s="96">
-        <v>1913900.6624423866</v>
+        <v>14041795.823822808</v>
       </c>
       <c r="F44" s="96">
         <v>0</v>
@@ -3652,13 +3652,13 @@
         <v>1</v>
       </c>
       <c r="C45" s="96">
-        <v>234.9175793654</v>
+        <v>265.92759920690003</v>
       </c>
       <c r="D45" s="96">
-        <v>2276.0000000041</v>
+        <v>2413.7347916711001</v>
       </c>
       <c r="E45" s="96">
-        <v>4664188.216696891</v>
+        <v>5323073.1675148038</v>
       </c>
       <c r="F45" s="96">
         <v>0</v>
@@ -3678,13 +3678,13 @@
         <v>1</v>
       </c>
       <c r="C46" s="96">
-        <v>321.875</v>
+        <v>101.875</v>
       </c>
       <c r="D46" s="96">
         <v>-24.9999999996</v>
       </c>
       <c r="E46" s="96">
-        <v>1599703.2523960921</v>
+        <v>113494.647396092</v>
       </c>
       <c r="F46" s="96">
         <v>0</v>
@@ -3773,44 +3773,44 @@
       </c>
       <c r="D2" s="59">
         <f>IFERROR(+VLOOKUP(B2,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>12888810.036315698</v>
+      </c>
+      <c r="E2" s="59">
         <v>12202147.531287048</v>
-      </c>
-      <c r="E2" s="59">
-        <v>10180781.322442733</v>
       </c>
       <c r="F2" s="59">
         <f t="shared" ref="F2:F9" si="0">+D2-E2</f>
-        <v>2021366.2088443153</v>
+        <v>686662.50502865016</v>
       </c>
       <c r="G2" s="60">
         <f t="shared" ref="G2:G41" si="1">+D2/C2</f>
-        <v>0.3780203401737795</v>
+        <v>0.39929302132027034</v>
       </c>
       <c r="H2" s="59">
         <f>+D2/$N$3*$N$4</f>
-        <v>58570308.150177836</v>
+        <v>51555240.145262793</v>
       </c>
       <c r="I2" s="60">
         <f t="shared" ref="I2:I41" si="2">+H2/C2</f>
-        <v>1.8144976328341418</v>
+        <v>1.5971720852810813</v>
       </c>
       <c r="J2" s="59">
         <f>+D2/$N$3</f>
-        <v>2440429.5062574097</v>
+        <v>2148135.0060526165</v>
       </c>
       <c r="K2" s="59">
         <f t="shared" ref="K2:K41" si="3">+(C2-D2)/$N$2</f>
-        <v>1056680.4793138793</v>
+        <v>1077237.0334408365</v>
       </c>
       <c r="L2" s="61" cm="1">
         <f t="array" ref="L2">+_xlfn.IFS(I2&gt;114%,H2*0.02,I2&gt;109%,H2*0.015,I2&gt;104%,H2*0.0125,I2&gt;99%,H2*0.01,I2&lt;99%,H2*0)</f>
-        <v>1171406.1630035567</v>
+        <v>1031104.8029052559</v>
       </c>
       <c r="M2" s="53" t="s">
         <v>36</v>
       </c>
       <c r="N2">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -3823,45 +3823,45 @@
       </c>
       <c r="D3" s="4">
         <f>IFERROR(+VLOOKUP(B3,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>10212334.874835599</v>
+      </c>
+      <c r="E3" s="4">
         <v>9288875.7683896385</v>
-      </c>
-      <c r="E3" s="4">
-        <v>6362623.1530077159</v>
       </c>
       <c r="F3" s="4">
         <f t="shared" si="0"/>
-        <v>2926252.6153819226</v>
+        <v>923459.1064459607</v>
       </c>
       <c r="G3" s="5">
         <f t="shared" si="1"/>
-        <v>0.29980819360899963</v>
+        <v>0.3296138034027607</v>
       </c>
       <c r="H3" s="4">
         <f t="shared" ref="H3:H41" si="4">+D3/$N$3*$N$4</f>
-        <v>44586603.688270271</v>
+        <v>40849339.499342397</v>
       </c>
       <c r="I3" s="5">
         <f t="shared" si="2"/>
-        <v>1.4390793293231983</v>
+        <v>1.3184552136110428</v>
       </c>
       <c r="J3" s="4">
         <f t="shared" ref="J3:J41" si="5">+D3/$N$3</f>
-        <v>1857775.1536779278</v>
+        <v>1702055.8124725998</v>
       </c>
       <c r="K3" s="4">
         <f t="shared" si="3"/>
-        <v>1141781.7058154535</v>
+        <v>1153910.7391137586</v>
       </c>
       <c r="L3" s="63" cm="1">
         <f t="array" ref="L3">+_xlfn.IFS(I3&gt;114%,H3*0.02,I3&gt;109%,H3*0.015,I3&gt;104%,H3*0.0125,I3&gt;99%,H3*0.01,I3&lt;99%,H3*0)</f>
-        <v>891732.07376540545</v>
+        <v>816986.7899868479</v>
       </c>
       <c r="M3" s="53" t="s">
         <v>40</v>
       </c>
       <c r="N3">
         <f>N4-N2</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -3874,38 +3874,38 @@
       </c>
       <c r="D4" s="4">
         <f>IFERROR(+VLOOKUP(B4,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>6977673.3087740811</v>
+      </c>
+      <c r="E4" s="4">
         <v>6197917.8190731332</v>
-      </c>
-      <c r="E4" s="4">
-        <v>4655359.4802594241</v>
       </c>
       <c r="F4" s="4">
         <f t="shared" si="0"/>
-        <v>1542558.3388137091</v>
+        <v>779755.48970094789</v>
       </c>
       <c r="G4" s="5">
         <f t="shared" si="1"/>
-        <v>0.21831317346146409</v>
+        <v>0.24577899350779522</v>
       </c>
       <c r="H4" s="4">
         <f t="shared" si="4"/>
-        <v>29750005.531551037</v>
+        <v>27910693.235096328</v>
       </c>
       <c r="I4" s="5">
         <f t="shared" si="2"/>
-        <v>1.0479032326150275</v>
+        <v>0.98311597403118101</v>
       </c>
       <c r="J4" s="4">
         <f t="shared" si="5"/>
-        <v>1239583.5638146265</v>
+        <v>1162945.5514623469</v>
       </c>
       <c r="K4" s="4">
         <f t="shared" si="3"/>
-        <v>1168005.970582901</v>
+        <v>1189575.4417430097</v>
       </c>
       <c r="L4" s="63" cm="1">
         <f t="array" ref="L4">+_xlfn.IFS(I4&gt;114%,H4*0.02,I4&gt;109%,H4*0.015,I4&gt;104%,H4*0.0125,I4&gt;99%,H4*0.01,I4&lt;99%,H4*0)</f>
-        <v>371875.06914438796</v>
+        <v>0</v>
       </c>
       <c r="M4" s="53" t="s">
         <v>47</v>
@@ -3924,38 +3924,38 @@
       </c>
       <c r="D5" s="4">
         <f>IFERROR(+VLOOKUP(B5,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>7646569.2805425785</v>
+      </c>
+      <c r="E5" s="4">
         <v>6622431.8650625329</v>
-      </c>
-      <c r="E5" s="4">
-        <v>5672001.5032034451</v>
       </c>
       <c r="F5" s="4">
         <f t="shared" si="0"/>
-        <v>950430.36185908783</v>
+        <v>1024137.4154800456</v>
       </c>
       <c r="G5" s="5">
         <f t="shared" si="1"/>
-        <v>0.23326609979322546</v>
+        <v>0.26933993874378875</v>
       </c>
       <c r="H5" s="4">
         <f t="shared" si="4"/>
-        <v>31787672.952300161</v>
+        <v>30586277.122170314</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" si="2"/>
-        <v>1.1196772790074823</v>
+        <v>1.077359754975155</v>
       </c>
       <c r="J5" s="4">
         <f t="shared" si="5"/>
-        <v>1324486.3730125066</v>
+        <v>1274428.2134237632</v>
       </c>
       <c r="K5" s="4">
         <f t="shared" si="3"/>
-        <v>1145663.1260571433</v>
+        <v>1152414.5544225376</v>
       </c>
       <c r="L5" s="63" cm="1">
         <f t="array" ref="L5">+_xlfn.IFS(I5&gt;114%,H5*0.02,I5&gt;109%,H5*0.015,I5&gt;104%,H5*0.0125,I5&gt;99%,H5*0.01,I5&lt;99%,H5*0)</f>
-        <v>476815.09428450238</v>
+        <v>382328.46402712894</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
@@ -3968,38 +3968,38 @@
       </c>
       <c r="D6" s="4">
         <f>IFERROR(+VLOOKUP(B6,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>6728186.3048162535</v>
+      </c>
+      <c r="E6" s="4">
         <v>6404448.8053096188</v>
-      </c>
-      <c r="E6" s="4">
-        <v>5810906.7980635744</v>
       </c>
       <c r="F6" s="4">
         <f t="shared" si="0"/>
-        <v>593542.00724604446</v>
+        <v>323737.49950663466</v>
       </c>
       <c r="G6" s="5">
         <f t="shared" si="1"/>
-        <v>0.27219702432644627</v>
+        <v>0.2859562699239025</v>
       </c>
       <c r="H6" s="4">
         <f t="shared" si="4"/>
-        <v>30741354.265486173</v>
+        <v>26912745.219265014</v>
       </c>
       <c r="I6" s="5">
         <f t="shared" si="2"/>
-        <v>1.3065457167669423</v>
+        <v>1.14382507969561</v>
       </c>
       <c r="J6" s="4">
         <f t="shared" si="5"/>
-        <v>1280889.7610619238</v>
+        <v>1121364.3841360423</v>
       </c>
       <c r="K6" s="4">
         <f t="shared" si="3"/>
-        <v>901277.67011634237</v>
+        <v>933363.2351502151</v>
       </c>
       <c r="L6" s="63" cm="1">
         <f t="array" ref="L6">+_xlfn.IFS(I6&gt;114%,H6*0.02,I6&gt;109%,H6*0.015,I6&gt;104%,H6*0.0125,I6&gt;99%,H6*0.01,I6&lt;99%,H6*0)</f>
-        <v>614827.08530972351</v>
+        <v>538254.90438530024</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
@@ -4012,34 +4012,34 @@
       </c>
       <c r="D7" s="4">
         <f>IFERROR(+VLOOKUP(B7,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>4065628.6784671973</v>
+      </c>
+      <c r="E7" s="4">
         <v>3586477.5079781078</v>
-      </c>
-      <c r="E7" s="4">
-        <v>2938195.7767915935</v>
       </c>
       <c r="F7" s="4">
         <f t="shared" ref="F7:F8" si="6">+D7-E7</f>
-        <v>648281.73118651425</v>
+        <v>479151.17048908956</v>
       </c>
       <c r="G7" s="5">
         <f t="shared" si="1"/>
-        <v>0.12928036879577476</v>
+        <v>0.14655214587843052</v>
       </c>
       <c r="H7" s="4">
         <f t="shared" si="4"/>
-        <v>17215092.038294919</v>
+        <v>16262514.713868789</v>
       </c>
       <c r="I7" s="5">
         <f t="shared" si="2"/>
-        <v>0.62054577021971891</v>
+        <v>0.58620858351372207</v>
       </c>
       <c r="J7" s="4">
         <f t="shared" si="5"/>
-        <v>717295.50159562158</v>
+        <v>677604.77974453289</v>
       </c>
       <c r="K7" s="4">
         <f t="shared" si="3"/>
-        <v>1271335.7643413893</v>
+        <v>1315346.0195554059</v>
       </c>
       <c r="L7" s="63" cm="1">
         <f t="array" ref="L7">+_xlfn.IFS(I7&gt;114%,H7*0.02,I7&gt;109%,H7*0.015,I7&gt;104%,H7*0.0125,I7&gt;99%,H7*0.01,I7&lt;99%,H7*0)</f>
@@ -4056,38 +4056,38 @@
       </c>
       <c r="D8" s="4">
         <f>IFERROR(+VLOOKUP(B8,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>9117515.4833692927</v>
+      </c>
+      <c r="E8" s="4">
         <v>8068882.1386908181</v>
-      </c>
-      <c r="E8" s="4">
-        <v>6168952.3513542237</v>
       </c>
       <c r="F8" s="4">
         <f t="shared" si="6"/>
-        <v>1899929.7873365944</v>
+        <v>1048633.3446784746</v>
       </c>
       <c r="G8" s="5">
         <f t="shared" si="1"/>
-        <v>0.22519232106693524</v>
+        <v>0.25445835479718426</v>
       </c>
       <c r="H8" s="4">
         <f t="shared" si="4"/>
-        <v>38730634.265715927</v>
+        <v>36470061.933477171</v>
       </c>
       <c r="I8" s="5">
         <f t="shared" si="2"/>
-        <v>1.0809231411212892</v>
+        <v>1.017833419188737</v>
       </c>
       <c r="J8" s="4">
         <f t="shared" si="5"/>
-        <v>1613776.4277381636</v>
+        <v>1519585.9138948822</v>
       </c>
       <c r="K8" s="4">
         <f t="shared" si="3"/>
-        <v>1461167.8567487835</v>
+        <v>1484086.4407526897</v>
       </c>
       <c r="L8" s="63" cm="1">
         <f t="array" ref="L8">+_xlfn.IFS(I8&gt;114%,H8*0.02,I8&gt;109%,H8*0.015,I8&gt;104%,H8*0.0125,I8&gt;99%,H8*0.01,I8&lt;99%,H8*0)</f>
-        <v>484132.92832144909</v>
+        <v>364700.61933477171</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
@@ -4100,38 +4100,38 @@
       </c>
       <c r="D9" s="4">
         <f>IFERROR(+VLOOKUP(B9,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>8696250.9292322323</v>
+      </c>
+      <c r="E9" s="4">
         <v>7971555.33420307</v>
-      </c>
-      <c r="E9" s="4">
-        <v>6899879.8473196756</v>
       </c>
       <c r="F9" s="4">
         <f t="shared" si="0"/>
-        <v>1071675.4868833944</v>
+        <v>724695.59502916224</v>
       </c>
       <c r="G9" s="5">
         <f t="shared" si="1"/>
-        <v>0.22247605273782814</v>
+        <v>0.24270139254407788</v>
       </c>
       <c r="H9" s="4">
         <f t="shared" si="4"/>
-        <v>38263465.604174733</v>
+        <v>34785003.716928929</v>
       </c>
       <c r="I9" s="5">
         <f t="shared" si="2"/>
-        <v>1.0678850531415751</v>
+        <v>0.97080557017631153</v>
       </c>
       <c r="J9" s="4">
         <f t="shared" si="5"/>
-        <v>1594311.066840614</v>
+        <v>1449375.1548720386</v>
       </c>
       <c r="K9" s="4">
         <f t="shared" si="3"/>
-        <v>1466290.3201428754</v>
+        <v>1507490.0270936373</v>
       </c>
       <c r="L9" s="63" cm="1">
         <f t="array" ref="L9">+_xlfn.IFS(I9&gt;114%,H9*0.02,I9&gt;109%,H9*0.015,I9&gt;104%,H9*0.0125,I9&gt;99%,H9*0.01,I9&lt;99%,H9*0)</f>
-        <v>478293.32005218416</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4142,34 +4142,34 @@
       </c>
       <c r="D10" s="64">
         <f>+SUM(D2:D9)</f>
+        <v>66332968.896352932</v>
+      </c>
+      <c r="E10" s="65">
         <v>60342736.769993968</v>
-      </c>
-      <c r="E10" s="65">
-        <v>48688700.232442394</v>
       </c>
       <c r="F10" s="64">
         <f>+SUM(F2:F9)</f>
-        <v>11654036.537551582</v>
+        <v>5990232.1263589654</v>
       </c>
       <c r="G10" s="66">
         <f t="shared" si="1"/>
-        <v>0.2483499872890047</v>
+        <v>0.27300372611609741</v>
       </c>
       <c r="H10" s="64">
         <f t="shared" si="4"/>
-        <v>289645136.49597102</v>
+        <v>265331875.58541173</v>
       </c>
       <c r="I10" s="66">
         <f t="shared" si="2"/>
-        <v>1.1920799389872223</v>
+        <v>1.0920149044643896</v>
       </c>
       <c r="J10" s="64">
         <f t="shared" si="5"/>
-        <v>12068547.353998793</v>
+        <v>11055494.816058822</v>
       </c>
       <c r="K10" s="67">
         <f t="shared" si="3"/>
-        <v>9612202.8931187652</v>
+        <v>9813423.4912720881</v>
       </c>
       <c r="L10" s="68"/>
     </row>
@@ -4185,38 +4185,38 @@
       </c>
       <c r="D11" s="59">
         <f>IFERROR(+VLOOKUP(B11,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>27236244.29200922</v>
+      </c>
+      <c r="E11" s="59">
         <v>25307057.946538661</v>
-      </c>
-      <c r="E11" s="59">
-        <v>21714287.032106198</v>
       </c>
       <c r="F11" s="59">
         <f t="shared" ref="F11:F16" si="7">+D11-E11</f>
-        <v>3592770.9144324623</v>
+        <v>1929186.3454705589</v>
       </c>
       <c r="G11" s="60">
         <f t="shared" si="1"/>
-        <v>0.26097297562008082</v>
+        <v>0.28086724788857825</v>
       </c>
       <c r="H11" s="59">
         <f t="shared" si="4"/>
-        <v>121473878.14338556</v>
+        <v>108944977.16803688</v>
       </c>
       <c r="I11" s="60">
         <f t="shared" si="2"/>
-        <v>1.2526702829763878</v>
+        <v>1.123468991554313</v>
       </c>
       <c r="J11" s="59">
         <f t="shared" si="5"/>
-        <v>5061411.5893077319</v>
+        <v>4539374.0486682029</v>
       </c>
       <c r="K11" s="59">
         <f t="shared" si="3"/>
-        <v>3771836.3438736238</v>
+        <v>3874205.7882293495</v>
       </c>
       <c r="L11" s="61" cm="1">
         <f t="array" ref="L11">+_xlfn.IFS(I11&gt;114%,H11*0.0125,I11&gt;109%,H11*0.01,I11&gt;104%,H11*0.0075,I11&gt;99%,H11*0.005,I11&lt;99%,H11*0)</f>
-        <v>1518423.4767923197</v>
+        <v>1089449.7716803688</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4244,23 +4244,23 @@
       </c>
       <c r="H12" s="4">
         <f t="shared" si="4"/>
-        <v>35243324.517293625</v>
+        <v>29369437.097744681</v>
       </c>
       <c r="I12" s="5">
         <f t="shared" si="2"/>
-        <v>1.1142054710316522</v>
+        <v>0.92850455919304342</v>
       </c>
       <c r="J12" s="4">
         <f t="shared" si="5"/>
-        <v>1468471.8548872343</v>
+        <v>1223726.5457393618</v>
       </c>
       <c r="K12" s="4">
         <f t="shared" si="3"/>
-        <v>1278344.3754805701</v>
+        <v>1349363.5074517129</v>
       </c>
       <c r="L12" s="63" cm="1">
         <f t="array" ref="L12">+_xlfn.IFS(I12&gt;114%,H12*0.02,I12&gt;109%,H12*0.015,I12&gt;104%,H12*0.0125,I12&gt;99%,H12*0.01,I12&lt;99%,H12*0)</f>
-        <v>528649.86775940435</v>
+        <v>0</v>
       </c>
       <c r="M12" s="27"/>
     </row>
@@ -4274,38 +4274,38 @@
       </c>
       <c r="D13" s="4">
         <f>IFERROR(+VLOOKUP(B13,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>41231894.308746725</v>
+      </c>
+      <c r="E13" s="4">
         <v>39689592.681744099</v>
-      </c>
-      <c r="E13" s="4">
-        <v>38609317.055148289</v>
       </c>
       <c r="F13" s="4">
         <f t="shared" si="7"/>
-        <v>1080275.6265958101</v>
+        <v>1542301.6270026267</v>
       </c>
       <c r="G13" s="5">
         <f t="shared" si="1"/>
-        <v>0.30919586980090541</v>
+        <v>0.32121094128022992</v>
       </c>
       <c r="H13" s="4">
         <f t="shared" si="4"/>
-        <v>190510044.87237167</v>
+        <v>164927577.2349869</v>
       </c>
       <c r="I13" s="5">
         <f t="shared" si="2"/>
-        <v>1.4841401750443461</v>
+        <v>1.2848437651209197</v>
       </c>
       <c r="J13" s="4">
         <f t="shared" si="5"/>
-        <v>7937918.5363488197</v>
+        <v>6871982.3847911209</v>
       </c>
       <c r="K13" s="4">
         <f t="shared" si="3"/>
-        <v>4667069.6522568883</v>
+        <v>4840667.8758821255</v>
       </c>
       <c r="L13" s="63" cm="1">
         <f t="array" ref="L13">+_xlfn.IFS(I13&gt;114%,H13*0.0125,I13&gt;109%,H13*0.01,I13&gt;104%,H13*0.0075,I13&gt;99%,H13*0.005,I13&lt;99%,H13*0)</f>
-        <v>2381375.5609046458</v>
+        <v>2061594.7154373364</v>
       </c>
       <c r="M13" s="53" t="s">
         <v>61</v>
@@ -4324,34 +4324,34 @@
       </c>
       <c r="D14" s="4">
         <f>IFERROR(+VLOOKUP(B14,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>6878414.3543294193</v>
+      </c>
+      <c r="E14" s="4">
         <v>6663134.8062294191</v>
-      </c>
-      <c r="E14" s="4">
-        <v>5554944.6639294196</v>
       </c>
       <c r="F14" s="4">
         <f t="shared" si="7"/>
-        <v>1108190.1422999995</v>
+        <v>215279.54810000025</v>
       </c>
       <c r="G14" s="5">
         <f t="shared" si="1"/>
-        <v>0.15696779186946522</v>
+        <v>0.16203927192841899</v>
       </c>
       <c r="H14" s="4">
         <f t="shared" si="4"/>
-        <v>31983047.069901209</v>
+        <v>27513657.417317674</v>
       </c>
       <c r="I14" s="5">
         <f t="shared" si="2"/>
-        <v>0.75344540097343304</v>
+        <v>0.64815708771367586</v>
       </c>
       <c r="J14" s="4">
         <f t="shared" si="5"/>
-        <v>1332626.9612458837</v>
+        <v>1146402.3923882365</v>
       </c>
       <c r="K14" s="4">
         <f t="shared" si="3"/>
-        <v>1883469.6099339779</v>
+        <v>1976146.835591421</v>
       </c>
       <c r="L14" s="63" cm="1">
         <f t="array" ref="L14">+_xlfn.IFS(I14&gt;109%,H14*0.015,I14&gt;104%,H14*0.0125,I14&gt;99%,H14*0.01,I14&lt;99%,H14*0)</f>
@@ -4369,38 +4369,38 @@
       </c>
       <c r="D15" s="4">
         <f>IFERROR(+VLOOKUP(B15,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>12288523.154902149</v>
+      </c>
+      <c r="E15" s="4">
         <v>10196205.867152149</v>
-      </c>
-      <c r="E15" s="4">
-        <v>8252554.4917521486</v>
       </c>
       <c r="F15" s="4">
         <f t="shared" si="7"/>
-        <v>1943651.3754000003</v>
+        <v>2092317.2877500001</v>
       </c>
       <c r="G15" s="5">
         <f t="shared" si="1"/>
-        <v>0.24019864027320303</v>
+        <v>0.28948871680615529</v>
       </c>
       <c r="H15" s="4">
         <f t="shared" si="4"/>
-        <v>48941788.162330315</v>
+        <v>49154092.619608596</v>
       </c>
       <c r="I15" s="5">
         <f t="shared" si="2"/>
-        <v>1.1529534733113747</v>
+        <v>1.1579548672246212</v>
       </c>
       <c r="J15" s="4">
         <f t="shared" si="5"/>
-        <v>2039241.1734304298</v>
+        <v>2048087.1924836915</v>
       </c>
       <c r="K15" s="4">
         <f t="shared" si="3"/>
-        <v>1697518.5014643606</v>
+        <v>1675585.2355596027</v>
       </c>
       <c r="L15" s="63" cm="1">
         <f t="array" ref="L15">+_xlfn.IFS(I15&gt;109%,H15*0.015,I15&gt;104%,H15*0.0125,I15&gt;99%,H15*0.01,I15&lt;99%,H15*0)</f>
-        <v>734126.82243495469</v>
+        <v>737311.38929412887</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4411,34 +4411,34 @@
       </c>
       <c r="D16" s="64">
         <f>+SUM(D11:D15)</f>
+        <v>94977435.384423673</v>
+      </c>
+      <c r="E16" s="65">
         <v>89198350.576100498</v>
-      </c>
-      <c r="E16" s="65">
-        <v>81473462.517372221</v>
       </c>
       <c r="F16" s="64">
         <f t="shared" si="7"/>
-        <v>7724888.0587282777</v>
+        <v>5779084.8083231747</v>
       </c>
       <c r="G16" s="66">
         <f t="shared" si="1"/>
-        <v>0.26091697432810329</v>
+        <v>0.27782156183263057</v>
       </c>
       <c r="H16" s="64">
         <f t="shared" si="4"/>
-        <v>428152082.76528239</v>
+        <v>379909741.53769469</v>
       </c>
       <c r="I16" s="66">
         <f t="shared" si="2"/>
-        <v>1.2524014767748959</v>
+        <v>1.1112862473305223</v>
       </c>
       <c r="J16" s="64">
         <f t="shared" si="5"/>
-        <v>17839670.1152201</v>
+        <v>15829572.564070612</v>
       </c>
       <c r="K16" s="67">
         <f t="shared" si="3"/>
-        <v>13298238.483009422</v>
+        <v>13715969.242714213</v>
       </c>
       <c r="L16" s="68"/>
     </row>
@@ -4454,34 +4454,34 @@
       </c>
       <c r="D17" s="59">
         <f>IFERROR(+VLOOKUP(B17,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>5569721.4797102707</v>
+      </c>
+      <c r="E17" s="59">
         <v>4842984.6712837927</v>
-      </c>
-      <c r="E17" s="59">
-        <v>3831780.4656781647</v>
       </c>
       <c r="F17" s="59">
         <f t="shared" ref="F17:F40" si="8">+D17-E17</f>
-        <v>1011204.205605628</v>
+        <v>726736.80842647795</v>
       </c>
       <c r="G17" s="60">
         <f t="shared" si="1"/>
-        <v>0.1650753861222426</v>
+        <v>0.18984654841222071</v>
       </c>
       <c r="H17" s="59">
         <f t="shared" si="4"/>
-        <v>23246326.422162205</v>
+        <v>22278885.918841083</v>
       </c>
       <c r="I17" s="60">
         <f t="shared" si="2"/>
-        <v>0.79236185338676446</v>
+        <v>0.75938619364888282</v>
       </c>
       <c r="J17" s="59">
         <f t="shared" si="5"/>
-        <v>968596.93425675854</v>
+        <v>928286.91328504507</v>
       </c>
       <c r="K17" s="59">
         <f t="shared" si="3"/>
-        <v>1289212.2874324322</v>
+        <v>1320460.9251549852</v>
       </c>
       <c r="L17" s="61" cm="1">
         <f t="array" ref="L17">+_xlfn.IFS(I17&gt;114%,H17*0.02,I17&gt;109%,H17*0.015,I17&gt;104%,H17*0.0125,I17&gt;99%,H17*0.01,I17&lt;99%,H17*0)</f>
@@ -4498,34 +4498,34 @@
       </c>
       <c r="D18" s="4">
         <f>IFERROR(+VLOOKUP(B18,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>5463522.8209966822</v>
+      </c>
+      <c r="E18" s="4">
         <v>4538116.0675083203</v>
-      </c>
-      <c r="E18" s="4">
-        <v>3383340.6159000443</v>
       </c>
       <c r="F18" s="4">
         <f t="shared" si="8"/>
-        <v>1154775.451608276</v>
+        <v>925406.75348836184</v>
       </c>
       <c r="G18" s="5">
         <f t="shared" si="1"/>
-        <v>0.18181914680884448</v>
+        <v>0.21889547184492469</v>
       </c>
       <c r="H18" s="4">
         <f t="shared" si="4"/>
-        <v>21782957.124039941</v>
+        <v>21854091.283986729</v>
       </c>
       <c r="I18" s="5">
         <f t="shared" si="2"/>
-        <v>0.87273190468245365</v>
+        <v>0.87558188737969878</v>
       </c>
       <c r="J18" s="4">
         <f t="shared" si="5"/>
-        <v>907623.21350166411</v>
+        <v>910587.13683278032</v>
       </c>
       <c r="K18" s="4">
         <f t="shared" si="3"/>
-        <v>1074809.9911837727</v>
+        <v>1083110.17105574</v>
       </c>
       <c r="L18" s="63" cm="1">
         <f t="array" ref="L18">+_xlfn.IFS(I18&gt;114%,H18*0.02,I18&gt;109%,H18*0.015,I18&gt;104%,H18*0.0125,I18&gt;99%,H18*0.01,I18&lt;99%,H18*0)</f>
@@ -4542,34 +4542,34 @@
       </c>
       <c r="D19" s="4">
         <f>IFERROR(+VLOOKUP(B19,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>5986642.3849513531</v>
+      </c>
+      <c r="E19" s="4">
         <v>5255755.4759214995</v>
-      </c>
-      <c r="E19" s="4">
-        <v>4172472.7522102422</v>
       </c>
       <c r="F19" s="4">
         <f t="shared" si="8"/>
-        <v>1083282.7237112573</v>
+        <v>730886.90902985353</v>
       </c>
       <c r="G19" s="5">
         <f t="shared" si="1"/>
-        <v>0.20326513458940426</v>
+        <v>0.23153201774525331</v>
       </c>
       <c r="H19" s="4">
         <f t="shared" si="4"/>
-        <v>25227626.284423195</v>
+        <v>23946569.539805412</v>
       </c>
       <c r="I19" s="5">
         <f t="shared" si="2"/>
-        <v>0.97567264602914039</v>
+        <v>0.92612807098101324</v>
       </c>
       <c r="J19" s="4">
         <f t="shared" si="5"/>
-        <v>1051151.0951842999</v>
+        <v>997773.73082522547</v>
       </c>
       <c r="K19" s="4">
         <f t="shared" si="3"/>
-        <v>1084257.6152409737</v>
+        <v>1103889.3211415915</v>
       </c>
       <c r="L19" s="63" cm="1">
         <f t="array" ref="L19">+_xlfn.IFS(I19&gt;114%,H19*0.02,I19&gt;109%,H19*0.015,I19&gt;104%,H19*0.0125,I19&gt;99%,H19*0.01,I19&lt;99%,H19*0)</f>
@@ -4586,38 +4586,38 @@
       </c>
       <c r="D20" s="4">
         <f>IFERROR(+VLOOKUP(B20,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>10086924.880174421</v>
+      </c>
+      <c r="E20" s="4">
         <v>9037854.5756811257</v>
-      </c>
-      <c r="E20" s="4">
-        <v>8068602.606727235</v>
       </c>
       <c r="F20" s="4">
         <f t="shared" si="8"/>
-        <v>969251.96895389073</v>
+        <v>1049070.304493295</v>
       </c>
       <c r="G20" s="5">
         <f t="shared" si="1"/>
-        <v>0.2693996528474501</v>
+        <v>0.30067025733399805</v>
       </c>
       <c r="H20" s="4">
         <f t="shared" si="4"/>
-        <v>43381701.963269398</v>
+        <v>40347699.520697683</v>
       </c>
       <c r="I20" s="5">
         <f t="shared" si="2"/>
-        <v>1.2931183336677603</v>
+        <v>1.2026810293359922</v>
       </c>
       <c r="J20" s="4">
         <f t="shared" si="5"/>
-        <v>1807570.9151362251</v>
+        <v>1681154.1466957368</v>
       </c>
       <c r="K20" s="4">
         <f t="shared" si="3"/>
-        <v>1290014.4960167827</v>
+        <v>1303400.2844347544</v>
       </c>
       <c r="L20" s="63" cm="1">
         <f t="array" ref="L20">+_xlfn.IFS(I20&gt;114%,H20*0.02,I20&gt;109%,H20*0.015,I20&gt;104%,H20*0.0125,I20&gt;99%,H20*0.01,I20&lt;99%,H20*0)</f>
-        <v>867634.03926538792</v>
+        <v>806953.99041395367</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4630,38 +4630,38 @@
       </c>
       <c r="D21" s="4">
         <f>IFERROR(+VLOOKUP(B21,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>6172988.7852142667</v>
+      </c>
+      <c r="E21" s="4">
         <v>5595341.8938343767</v>
-      </c>
-      <c r="E21" s="4">
-        <v>4521737.6382463202</v>
       </c>
       <c r="F21" s="4">
         <f t="shared" ref="F21:F23" si="9">+D21-E21</f>
-        <v>1073604.2555880565</v>
+        <v>577646.89137989003</v>
       </c>
       <c r="G21" s="5">
         <f t="shared" si="1"/>
-        <v>0.2197827718053561</v>
+        <v>0.24247250861162994</v>
       </c>
       <c r="H21" s="4">
         <f t="shared" si="4"/>
-        <v>26857641.090405006</v>
+        <v>24691955.140857067</v>
       </c>
       <c r="I21" s="5">
         <f t="shared" si="2"/>
-        <v>1.0549573046657093</v>
+        <v>0.96989003444651978</v>
       </c>
       <c r="J21" s="4">
         <f t="shared" si="5"/>
-        <v>1119068.3787668752</v>
+        <v>1028831.4642023778</v>
       </c>
       <c r="K21" s="4">
         <f t="shared" si="3"/>
-        <v>1045429.9003245066</v>
+        <v>1071417.8452658739</v>
       </c>
       <c r="L21" s="63" cm="1">
         <f t="array" ref="L21">+_xlfn.IFS(I21&gt;114%,H21*0.02,I21&gt;109%,H21*0.015,I21&gt;104%,H21*0.0125,I21&gt;99%,H21*0.01,I21&lt;99%,H21*0)</f>
-        <v>335720.51363006257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4674,38 +4674,38 @@
       </c>
       <c r="D22" s="4">
         <f>IFERROR(+VLOOKUP(B22,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>9510778.0994110405</v>
+      </c>
+      <c r="E22" s="4">
         <v>8516814.03087065</v>
-      </c>
-      <c r="E22" s="4">
-        <v>6604601.1312453747</v>
       </c>
       <c r="F22" s="4">
         <f t="shared" si="9"/>
-        <v>1912212.8996252753</v>
+        <v>993964.06854039058</v>
       </c>
       <c r="G22" s="5">
         <f t="shared" si="1"/>
-        <v>0.26830619320450694</v>
+        <v>0.29961916005402178</v>
       </c>
       <c r="H22" s="4">
         <f t="shared" si="4"/>
-        <v>40880707.348179117</v>
+        <v>38043112.397644162</v>
       </c>
       <c r="I22" s="5">
         <f t="shared" si="2"/>
-        <v>1.2878697273816331</v>
+        <v>1.1984766402160871</v>
       </c>
       <c r="J22" s="4">
         <f t="shared" si="5"/>
-        <v>1703362.8061741299</v>
+        <v>1585129.6832351733</v>
       </c>
       <c r="K22" s="4">
         <f t="shared" si="3"/>
-        <v>1222425.061533124</v>
+        <v>1235117.3389216091</v>
       </c>
       <c r="L22" s="63" cm="1">
         <f t="array" ref="L22">+_xlfn.IFS(I22&gt;114%,H22*0.02,I22&gt;109%,H22*0.015,I22&gt;104%,H22*0.0125,I22&gt;99%,H22*0.01,I22&lt;99%,H22*0)</f>
-        <v>817614.14696358237</v>
+        <v>760862.24795288325</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4718,38 +4718,38 @@
       </c>
       <c r="D23" s="4">
         <f>IFERROR(+VLOOKUP(B23,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>6142976.0828060079</v>
+      </c>
+      <c r="E23" s="4">
         <v>5822405.6030015703</v>
-      </c>
-      <c r="E23" s="4">
-        <v>5027241.122842595</v>
       </c>
       <c r="F23" s="4">
         <f t="shared" si="9"/>
-        <v>795164.48015897535</v>
+        <v>320570.47980443761</v>
       </c>
       <c r="G23" s="5">
         <f t="shared" si="1"/>
-        <v>0.21221814455355015</v>
+        <v>0.22390246836425612</v>
       </c>
       <c r="H23" s="4">
         <f t="shared" si="4"/>
-        <v>27947546.894407541</v>
+        <v>24571904.331224032</v>
       </c>
       <c r="I23" s="5">
         <f t="shared" si="2"/>
-        <v>1.0186470938570409</v>
+        <v>0.89560987345702447</v>
       </c>
       <c r="J23" s="4">
         <f t="shared" si="5"/>
-        <v>1164481.1206003141</v>
+        <v>1023829.3471343346</v>
       </c>
       <c r="K23" s="4">
         <f t="shared" si="3"/>
-        <v>1137554.7698420228</v>
+        <v>1182942.7859552221</v>
       </c>
       <c r="L23" s="63" cm="1">
         <f t="array" ref="L23">+_xlfn.IFS(I23&gt;114%,H23*0.02,I23&gt;109%,H23*0.015,I23&gt;104%,H23*0.0125,I23&gt;99%,H23*0.01,I23&lt;99%,H23*0)</f>
-        <v>279475.4689440754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4762,38 +4762,38 @@
       </c>
       <c r="D24" s="4">
         <f>IFERROR(+VLOOKUP(B24,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>7360714.5095196133</v>
+      </c>
+      <c r="E24" s="4">
         <v>6909391.5039921645</v>
-      </c>
-      <c r="E24" s="4">
-        <v>4507114.506957056</v>
       </c>
       <c r="F24" s="4">
         <f t="shared" si="8"/>
-        <v>2402276.9970351085</v>
+        <v>451323.00552744884</v>
       </c>
       <c r="G24" s="5">
         <f t="shared" si="1"/>
-        <v>0.20628710091961586</v>
+        <v>0.21976182070279676</v>
       </c>
       <c r="H24" s="4">
         <f t="shared" si="4"/>
-        <v>33165079.21916239</v>
+        <v>29442858.038078457</v>
       </c>
       <c r="I24" s="5">
         <f t="shared" si="2"/>
-        <v>0.99017808441415622</v>
+        <v>0.87904728281118716</v>
       </c>
       <c r="J24" s="4">
         <f t="shared" si="5"/>
-        <v>1381878.3007984329</v>
+        <v>1226785.7515866023</v>
       </c>
       <c r="K24" s="4">
         <f t="shared" si="3"/>
-        <v>1399192.8155793599</v>
+        <v>1451852.2494711326</v>
       </c>
       <c r="L24" s="63" cm="1">
         <f t="array" ref="L24">+_xlfn.IFS(I24&gt;114%,H24*0.02,I24&gt;109%,H24*0.015,I24&gt;104%,H24*0.0125,I24&gt;99%,H24*0.01,I24&lt;99%,H24*0)</f>
-        <v>331650.79219162388</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4806,34 +4806,34 @@
       </c>
       <c r="D25" s="4">
         <f>IFERROR(+VLOOKUP(B25,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>12160822.067982538</v>
+      </c>
+      <c r="E25" s="4">
         <v>8825883.2392010316</v>
-      </c>
-      <c r="E25" s="4">
-        <v>7398936.6723073218</v>
       </c>
       <c r="F25" s="4">
         <f t="shared" si="8"/>
-        <v>1426946.5668937098</v>
+        <v>3334938.828781506</v>
       </c>
       <c r="G25" s="5">
         <f t="shared" si="1"/>
-        <v>0.16324592497544999</v>
+        <v>0.22492985610008884</v>
       </c>
       <c r="H25" s="4">
         <f t="shared" si="4"/>
-        <v>42364239.548164949</v>
+        <v>48643288.271930151</v>
       </c>
       <c r="I25" s="5">
         <f t="shared" si="2"/>
-        <v>0.78358043988215986</v>
+        <v>0.89971942440035535</v>
       </c>
       <c r="J25" s="4">
         <f t="shared" si="5"/>
-        <v>1765176.6478402063</v>
+        <v>2026803.6779970897</v>
       </c>
       <c r="K25" s="4">
         <f t="shared" si="3"/>
-        <v>2381003.6645157356</v>
+        <v>2328007.2665009703</v>
       </c>
       <c r="L25" s="63" cm="1">
         <f t="array" ref="L25">+_xlfn.IFS(I25&gt;109%,H25*0.015,I25&gt;104%,H25*0.0125,I25&gt;99%,H25*0.01,I25&lt;99%,H25*0)</f>
@@ -4848,34 +4848,34 @@
       </c>
       <c r="D26" s="67">
         <f>+SUM(D17:D25)</f>
+        <v>68455091.110766187</v>
+      </c>
+      <c r="E26" s="65">
         <v>59344547.061294533</v>
-      </c>
-      <c r="E26" s="65">
-        <v>47515827.512114353</v>
       </c>
       <c r="F26" s="67">
         <f>+D26-E26</f>
-        <v>11828719.54918018</v>
+        <v>9110544.049471654</v>
       </c>
       <c r="G26" s="66">
         <f t="shared" si="1"/>
-        <v>0.20757196754299401</v>
+        <v>0.23943830821592416</v>
       </c>
       <c r="H26" s="64">
         <f t="shared" si="4"/>
-        <v>284853825.89421374</v>
+        <v>273820364.44306475</v>
       </c>
       <c r="I26" s="66">
         <f t="shared" si="2"/>
-        <v>0.99634544420637117</v>
+        <v>0.95775323286369662</v>
       </c>
       <c r="J26" s="64">
         <f t="shared" si="5"/>
-        <v>11868909.412258906</v>
+        <v>11409181.851794364</v>
       </c>
       <c r="K26" s="67">
         <f t="shared" si="3"/>
-        <v>11923900.60166871</v>
+        <v>12080198.187901881</v>
       </c>
       <c r="L26" s="68"/>
     </row>
@@ -4891,38 +4891,38 @@
       </c>
       <c r="D27" s="59">
         <f>IFERROR(+VLOOKUP(B27,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>18937147.75616448</v>
+      </c>
+      <c r="E27" s="59">
         <v>17555809.912466466</v>
-      </c>
-      <c r="E27" s="59">
-        <v>14993819.966923174</v>
       </c>
       <c r="F27" s="59">
         <f t="shared" si="8"/>
-        <v>2561989.9455432929</v>
+        <v>1381337.8436980136</v>
       </c>
       <c r="G27" s="60">
         <f t="shared" si="1"/>
-        <v>0.21415348213558646</v>
+        <v>0.23100364801847917</v>
       </c>
       <c r="H27" s="59">
         <f t="shared" si="4"/>
-        <v>84267887.579839051</v>
+        <v>75748591.02465792</v>
       </c>
       <c r="I27" s="60">
         <f t="shared" si="2"/>
-        <v>1.0279367142508151</v>
+        <v>0.92401459207391667</v>
       </c>
       <c r="J27" s="59">
         <f t="shared" si="5"/>
-        <v>3511161.9824932935</v>
+        <v>3156191.2926940802</v>
       </c>
       <c r="K27" s="59">
         <f t="shared" si="3"/>
-        <v>3390625.7940807124</v>
+        <v>3502252.9024353069</v>
       </c>
       <c r="L27" s="61" cm="1">
         <f t="array" ref="L27">+_xlfn.IFS(I27&gt;114%,H27*0.0125,I27&gt;109%,H27*0.01,I27&gt;104%,H27*0.0075,I27&gt;99%,H27*0.005,I27&lt;99%,H27*0)</f>
-        <v>421339.43789919524</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4935,34 +4935,34 @@
       </c>
       <c r="D28" s="4">
         <f>IFERROR(+VLOOKUP(B28,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>3339149.8528803443</v>
+      </c>
+      <c r="E28" s="4">
         <v>2883607.9842428509</v>
-      </c>
-      <c r="E28" s="4">
-        <v>2246997.9859188953</v>
       </c>
       <c r="F28" s="4">
         <f t="shared" si="8"/>
-        <v>636609.99832395557</v>
+        <v>455541.86863749335</v>
       </c>
       <c r="G28" s="5">
         <f t="shared" si="1"/>
-        <v>0.13731466591632624</v>
+        <v>0.15900713585144496</v>
       </c>
       <c r="H28" s="4">
         <f t="shared" si="4"/>
-        <v>13841318.324365683</v>
+        <v>13356599.411521379</v>
       </c>
       <c r="I28" s="5">
         <f t="shared" si="2"/>
-        <v>0.65911039639836588</v>
+        <v>0.63602854340577997</v>
       </c>
       <c r="J28" s="4">
         <f t="shared" si="5"/>
-        <v>576721.59684857016</v>
+        <v>556524.97548005742</v>
       </c>
       <c r="K28" s="4">
         <f t="shared" si="3"/>
-        <v>953494.31661879737</v>
+        <v>981158.34150664753</v>
       </c>
       <c r="L28" s="63" cm="1">
         <f t="array" ref="L28">+_xlfn.IFS(I28&gt;114%,H28*0.02,I28&gt;109%,H28*0.015,I28&gt;104%,H28*0.0125,I28&gt;99%,H28*0.01,I28&lt;99%,H28*0)</f>
@@ -4979,34 +4979,34 @@
       </c>
       <c r="D29" s="4">
         <f>IFERROR(+VLOOKUP(B29,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>6335712.8592704926</v>
+      </c>
+      <c r="E29" s="4">
         <v>3996158.8131728824</v>
-      </c>
-      <c r="E29" s="4">
-        <v>2863924.6281832345</v>
       </c>
       <c r="F29" s="4">
         <f t="shared" si="8"/>
-        <v>1132234.1849896479</v>
+        <v>2339554.0460976101</v>
       </c>
       <c r="G29" s="5">
         <f t="shared" si="1"/>
-        <v>0.15525273461512304</v>
+        <v>0.24614555955471479</v>
       </c>
       <c r="H29" s="4">
         <f t="shared" si="4"/>
-        <v>19181562.303229839</v>
+        <v>25342851.43708197</v>
       </c>
       <c r="I29" s="5">
         <f t="shared" si="2"/>
-        <v>0.74521312615259072</v>
+        <v>0.98458223821885915</v>
       </c>
       <c r="J29" s="4">
         <f t="shared" si="5"/>
-        <v>799231.76263457653</v>
+        <v>1055952.1432117487</v>
       </c>
       <c r="K29" s="4">
         <f t="shared" si="3"/>
-        <v>1144396.9045698482</v>
+        <v>1077999.2855960838</v>
       </c>
       <c r="L29" s="63" cm="1">
         <f t="array" ref="L29">+_xlfn.IFS(I29&gt;114%,H29*0.02,I29&gt;109%,H29*0.015,I29&gt;104%,H29*0.0125,I29&gt;99%,H29*0.01,I29&lt;99%,H29*0)</f>
@@ -5024,34 +5024,34 @@
       </c>
       <c r="D30" s="4">
         <f>IFERROR(+VLOOKUP(B30,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>5102416.1731653139</v>
+      </c>
+      <c r="E30" s="4">
         <v>4975553.6144345868</v>
-      </c>
-      <c r="E30" s="4">
-        <v>4669958.7290065279</v>
       </c>
       <c r="F30" s="4">
         <f t="shared" si="8"/>
-        <v>305594.88542805891</v>
+        <v>126862.55873072706</v>
       </c>
       <c r="G30" s="5">
         <f t="shared" si="1"/>
-        <v>0.13013697386454762</v>
+        <v>0.13345509899579622</v>
       </c>
       <c r="H30" s="4">
         <f t="shared" si="4"/>
-        <v>23882657.34928602</v>
+        <v>20409664.692661256</v>
       </c>
       <c r="I30" s="5">
         <f t="shared" si="2"/>
-        <v>0.62465747454982867</v>
+        <v>0.53382039598318487</v>
       </c>
       <c r="J30" s="4">
         <f t="shared" si="5"/>
-        <v>995110.72288691741</v>
+        <v>850402.69552755228</v>
       </c>
       <c r="K30" s="4">
         <f t="shared" si="3"/>
-        <v>1750402.710404794</v>
+        <v>1840599.3854977977</v>
       </c>
       <c r="L30" s="63" cm="1">
         <f t="array" ref="L30">+_xlfn.IFS(I30&gt;114%,H30*0.02,I30&gt;109%,H30*0.015,I30&gt;104%,H30*0.0125,I30&gt;99%,H30*0.01,I30&lt;99%,H30*0)</f>
@@ -5069,34 +5069,34 @@
       </c>
       <c r="D31" s="4">
         <f>IFERROR(+VLOOKUP(B31,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>5326745.1355416654</v>
+      </c>
+      <c r="E31" s="4">
         <v>4865926.9418352479</v>
-      </c>
-      <c r="E31" s="4">
-        <v>4425690.3579718489</v>
       </c>
       <c r="F31" s="4">
         <f t="shared" si="8"/>
-        <v>440236.58386339899</v>
+        <v>460818.19370641746</v>
       </c>
       <c r="G31" s="5">
         <f t="shared" si="1"/>
-        <v>0.19145697728077624</v>
+        <v>0.20958853977598746</v>
       </c>
       <c r="H31" s="4">
         <f t="shared" si="4"/>
-        <v>23356449.320809193</v>
+        <v>21306980.542166661</v>
       </c>
       <c r="I31" s="5">
         <f t="shared" si="2"/>
-        <v>0.91899349094772598</v>
+        <v>0.83835415910394984</v>
       </c>
       <c r="J31" s="4">
         <f t="shared" si="5"/>
-        <v>973185.38836704963</v>
+        <v>887790.85592361086</v>
       </c>
       <c r="K31" s="4">
         <f t="shared" si="3"/>
-        <v>1081543.3188507764</v>
+        <v>1116028.048025463</v>
       </c>
       <c r="L31" s="63" cm="1">
         <f t="array" ref="L31">+_xlfn.IFS(I31&gt;114%,H31*0.02,I31&gt;109%,H31*0.015,I31&gt;104%,H31*0.0125,I31&gt;99%,H31*0.01,I31&lt;99%,H31*0)</f>
@@ -5114,34 +5114,34 @@
       </c>
       <c r="D32" s="4">
         <f>IFERROR(+VLOOKUP(B32,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>3800655.2343727285</v>
+      </c>
+      <c r="E32" s="4">
         <v>2958594.3353685732</v>
-      </c>
-      <c r="E32" s="4">
-        <v>2292259.0263364343</v>
       </c>
       <c r="F32" s="4">
         <f t="shared" si="8"/>
-        <v>666335.3090321389</v>
+        <v>842060.8990041553</v>
       </c>
       <c r="G32" s="5">
         <f t="shared" si="1"/>
-        <v>0.11740453711780052</v>
+        <v>0.15081965215764795</v>
       </c>
       <c r="H32" s="4">
         <f t="shared" si="4"/>
-        <v>14201252.80976915</v>
+        <v>15202620.937490914</v>
       </c>
       <c r="I32" s="5">
         <f t="shared" si="2"/>
-        <v>0.56354177816544249</v>
+        <v>0.60327860863059179</v>
       </c>
       <c r="J32" s="4">
         <f t="shared" si="5"/>
-        <v>591718.86707371462</v>
+        <v>633442.53906212142</v>
       </c>
       <c r="K32" s="4">
         <f t="shared" si="3"/>
-        <v>1170600.2981384962</v>
+        <v>1188852.4869792929</v>
       </c>
       <c r="L32" s="63" cm="1">
         <f t="array" ref="L32">+_xlfn.IFS(I32&gt;114%,H32*0.02,I32&gt;109%,H32*0.015,I32&gt;104%,H32*0.0125,I32&gt;99%,H32*0.01,I32&lt;99%,H32*0)</f>
@@ -5159,34 +5159,34 @@
       </c>
       <c r="D33" s="4">
         <f>IFERROR(+VLOOKUP(B33,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>3355234.3973482912</v>
+      </c>
+      <c r="E33" s="4">
         <v>3089173.5689832573</v>
-      </c>
-      <c r="E33" s="4">
-        <v>2299134.4748592312</v>
       </c>
       <c r="F33" s="4">
         <f t="shared" si="8"/>
-        <v>790039.09412402613</v>
+        <v>266060.82836503396</v>
       </c>
       <c r="G33" s="5">
         <f t="shared" si="1"/>
-        <v>0.1165868859004692</v>
+        <v>0.12662814863514549</v>
       </c>
       <c r="H33" s="4">
         <f t="shared" si="4"/>
-        <v>14828033.131119635</v>
+        <v>13420937.589393165</v>
       </c>
       <c r="I33" s="5">
         <f t="shared" si="2"/>
-        <v>0.55961705232225212</v>
+        <v>0.50651259454058195</v>
       </c>
       <c r="J33" s="4">
         <f t="shared" si="5"/>
-        <v>617834.71379665146</v>
+        <v>559205.73289138183</v>
       </c>
       <c r="K33" s="4">
         <f t="shared" si="3"/>
-        <v>1231977.706895618</v>
+        <v>1285639.7557028728</v>
       </c>
       <c r="L33" s="63" cm="1">
         <f t="array" ref="L33">+_xlfn.IFS(I33&gt;114%,H33*0.02,I33&gt;109%,H33*0.015,I33&gt;104%,H33*0.0125,I33&gt;99%,H33*0.01,I33&lt;99%,H33*0)</f>
@@ -5203,34 +5203,34 @@
       </c>
       <c r="D34" s="4">
         <f>IFERROR(+VLOOKUP(B34,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>2447356.6153951334</v>
+      </c>
+      <c r="E34" s="4">
         <v>2098536.1960838647</v>
-      </c>
-      <c r="E34" s="4">
-        <v>1808557.8257932956</v>
       </c>
       <c r="F34" s="4">
         <f t="shared" si="8"/>
-        <v>289978.37029056903</v>
+        <v>348820.41931126872</v>
       </c>
       <c r="G34" s="5">
         <f t="shared" si="1"/>
-        <v>9.9930295051612605E-2</v>
+        <v>0.11654079120929206</v>
       </c>
       <c r="H34" s="4">
         <f t="shared" si="4"/>
-        <v>10072973.741202552</v>
+        <v>9789426.4615805335</v>
       </c>
       <c r="I34" s="5">
         <f t="shared" si="2"/>
-        <v>0.47966541624774056</v>
+        <v>0.46616316483716824</v>
       </c>
       <c r="J34" s="4">
         <f t="shared" si="5"/>
-        <v>419707.23921677296</v>
+        <v>407892.76923252223</v>
       </c>
       <c r="K34" s="4">
         <f t="shared" si="3"/>
-        <v>994813.88441663864</v>
+        <v>1030702.410255826</v>
       </c>
       <c r="L34" s="63" cm="1">
         <f t="array" ref="L34">+_xlfn.IFS(I34&gt;114%,H34*0.02,I34&gt;109%,H34*0.015,I34&gt;104%,H34*0.0125,I34&gt;99%,H34*0.01,I34&lt;99%,H34*0)</f>
@@ -5247,34 +5247,34 @@
       </c>
       <c r="D35" s="4">
         <f>IFERROR(+VLOOKUP(B35,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>1956633.4710906136</v>
+      </c>
+      <c r="E35" s="4">
         <v>1626463.4655310514</v>
-      </c>
-      <c r="E35" s="4">
-        <v>1134886.8601273343</v>
       </c>
       <c r="F35" s="4">
         <f t="shared" si="8"/>
-        <v>491576.60540371714</v>
+        <v>330170.00555956224</v>
       </c>
       <c r="G35" s="5">
         <f t="shared" si="1"/>
-        <v>6.5960348506016314E-2</v>
+        <v>7.9350214982870343E-2</v>
       </c>
       <c r="H35" s="4">
         <f t="shared" si="4"/>
-        <v>7807024.6345490459</v>
+        <v>7826533.8843624545</v>
       </c>
       <c r="I35" s="5">
         <f t="shared" si="2"/>
-        <v>0.31660967282887825</v>
+        <v>0.31740085993148137</v>
       </c>
       <c r="J35" s="4">
         <f t="shared" si="5"/>
-        <v>325292.69310621027</v>
+        <v>326105.57851510227</v>
       </c>
       <c r="K35" s="4">
         <f t="shared" si="3"/>
-        <v>1212196.659708892</v>
+        <v>1261198.1404949659</v>
       </c>
       <c r="L35" s="63" cm="1">
         <f t="array" ref="L35">+_xlfn.IFS(I35&gt;114%,H35*0.02,I35&gt;109%,H35*0.015,I35&gt;104%,H35*0.0125,I35&gt;99%,H35*0.01,I35&lt;99%,H35*0)</f>
@@ -5291,34 +5291,34 @@
       </c>
       <c r="D36" s="4">
         <f>IFERROR(+VLOOKUP(B36,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>3355300.6510111671</v>
+      </c>
+      <c r="E36" s="4">
         <v>3109025.2196221473</v>
-      </c>
-      <c r="E36" s="4">
-        <v>2633216.6305364068</v>
       </c>
       <c r="F36" s="4">
         <f t="shared" si="8"/>
-        <v>475808.5890857405</v>
+        <v>246275.43138901982</v>
       </c>
       <c r="G36" s="5">
         <f t="shared" si="1"/>
-        <v>0.12320290151068544</v>
+        <v>0.13296218153402684</v>
       </c>
       <c r="H36" s="4">
         <f t="shared" si="4"/>
-        <v>14923321.054186307</v>
+        <v>13421202.604044668</v>
       </c>
       <c r="I36" s="5">
         <f t="shared" si="2"/>
-        <v>0.59137392725129012</v>
+        <v>0.53184872613610734</v>
       </c>
       <c r="J36" s="4">
         <f t="shared" si="5"/>
-        <v>621805.04392442945</v>
+        <v>559216.77516852785</v>
       </c>
       <c r="K36" s="4">
         <f t="shared" si="3"/>
-        <v>1164524.9884409397</v>
+        <v>1215538.8527216017</v>
       </c>
       <c r="L36" s="63" cm="1">
         <f t="array" ref="L36">+_xlfn.IFS(I36&gt;114%,H36*0.02,I36&gt;109%,H36*0.015,I36&gt;104%,H36*0.0125,I36&gt;99%,H36*0.01,I36&lt;99%,H36*0)</f>
@@ -5335,34 +5335,34 @@
       </c>
       <c r="D37" s="4">
         <f>IFERROR(+VLOOKUP(B37,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>26940309.263082385</v>
+      </c>
+      <c r="E37" s="4">
         <v>17061083.040882383</v>
-      </c>
-      <c r="E37" s="4">
-        <v>17081843.43377829</v>
       </c>
       <c r="F37" s="4">
         <f t="shared" si="8"/>
-        <v>-20760.392895907164</v>
+        <v>9879226.2222000025</v>
       </c>
       <c r="G37" s="5">
         <f t="shared" si="1"/>
-        <v>0.13983147558233025</v>
+        <v>0.2208009414100067</v>
       </c>
       <c r="H37" s="4">
         <f t="shared" si="4"/>
-        <v>81893198.596235424</v>
+        <v>107761237.05232954</v>
       </c>
       <c r="I37" s="5">
         <f t="shared" si="2"/>
-        <v>0.67119108279518513</v>
+        <v>0.88320376564002678</v>
       </c>
       <c r="J37" s="4">
         <f t="shared" si="5"/>
-        <v>3412216.6081764763</v>
+        <v>4490051.5438470645</v>
       </c>
       <c r="K37" s="4">
         <f t="shared" si="3"/>
-        <v>5523719.3136377698</v>
+        <v>5281746.7076065345</v>
       </c>
       <c r="L37" s="63" cm="1">
         <f t="array" ref="L37">+_xlfn.IFS(I37&gt;114%,H37*0.0125,I37&gt;109%,H37*0.01,I37&gt;104%,H37*0.0075,I37&gt;99%,H37*0.005,I37&lt;99%,H37*0)</f>
@@ -5379,34 +5379,34 @@
       </c>
       <c r="D38" s="4">
         <f>IFERROR(+VLOOKUP(B38,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>1084549.0049000001</v>
+      </c>
+      <c r="E38" s="4">
         <v>746511.00490000006</v>
-      </c>
-      <c r="E38" s="4">
-        <v>280769.63740000001</v>
       </c>
       <c r="F38" s="4">
         <f t="shared" ref="F38" si="10">+D38-E38</f>
-        <v>465741.36750000005</v>
+        <v>338038</v>
       </c>
       <c r="G38" s="5">
         <f t="shared" si="1"/>
-        <v>2.0910672406162466E-2</v>
+        <v>3.0379523946778713E-2</v>
       </c>
       <c r="H38" s="4">
         <f t="shared" si="4"/>
-        <v>3583252.8235200006</v>
+        <v>4338196.0196000002</v>
       </c>
       <c r="I38" s="5">
         <f t="shared" si="2"/>
-        <v>0.10037122754957985</v>
+        <v>0.12151809578711485</v>
       </c>
       <c r="J38" s="4">
         <f t="shared" si="5"/>
-        <v>149302.20098000002</v>
+        <v>180758.16748333335</v>
       </c>
       <c r="K38" s="4">
         <f t="shared" si="3"/>
-        <v>1839657.3155315788</v>
+        <v>1923080.6108388889</v>
       </c>
       <c r="L38" s="63" cm="1">
         <f t="array" ref="L38">+_xlfn.IFS(I38&gt;109%,H38*0.015,I38&gt;104%,H38*0.0125,I38&gt;99%,H38*0.01,I38&lt;99%,H38*0)</f>
@@ -5423,34 +5423,34 @@
       </c>
       <c r="D39" s="4">
         <f>IFERROR(+VLOOKUP(B39,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>7332096.3798651379</v>
+      </c>
+      <c r="E39" s="4">
         <v>6953389.0972305397</v>
-      </c>
-      <c r="E39" s="4">
-        <v>6167950.3247244535</v>
       </c>
       <c r="F39" s="4">
         <f t="shared" si="8"/>
-        <v>785438.77250608616</v>
+        <v>378707.2826345982</v>
       </c>
       <c r="G39" s="5">
         <f t="shared" si="1"/>
-        <v>0.19122981493305272</v>
+        <v>0.20164489778824021</v>
       </c>
       <c r="H39" s="4">
         <f t="shared" si="4"/>
-        <v>33376267.666706588</v>
+        <v>29328385.519460551</v>
       </c>
       <c r="I39" s="5">
         <f t="shared" si="2"/>
-        <v>0.91790311167865302</v>
+        <v>0.80657959115296085</v>
       </c>
       <c r="J39" s="4">
         <f t="shared" si="5"/>
-        <v>1390677.8194461078</v>
+        <v>1222016.0633108562</v>
       </c>
       <c r="K39" s="4">
         <f t="shared" si="3"/>
-        <v>1547791.5074615506</v>
+        <v>1612740.6310630478</v>
       </c>
       <c r="L39" s="63" cm="1">
         <f t="array" ref="L39">+_xlfn.IFS(I39&gt;114%,H39*0.02,I39&gt;109%,H39*0.015,I39&gt;104%,H39*0.0125,I39&gt;99%,H39*0.01,I39&lt;99%,H39*0)</f>
@@ -5465,34 +5465,34 @@
       </c>
       <c r="D40" s="67">
         <f>+SUM(D27:D39)</f>
+        <v>89313306.794087753</v>
+      </c>
+      <c r="E40" s="65">
         <v>71919833.194753855</v>
-      </c>
-      <c r="E40" s="65">
-        <v>62899009.881559134</v>
       </c>
       <c r="F40" s="67">
         <f t="shared" si="8"/>
-        <v>9020823.3131947219</v>
+        <v>17393473.599333897</v>
       </c>
       <c r="G40" s="66">
         <f t="shared" si="1"/>
-        <v>0.14128828734254617</v>
+        <v>0.17545819551145081</v>
       </c>
       <c r="H40" s="64">
         <f t="shared" si="4"/>
-        <v>345215199.33481848</v>
+        <v>357253227.17635101</v>
       </c>
       <c r="I40" s="66">
         <f t="shared" si="2"/>
-        <v>0.67818377924422157</v>
+        <v>0.70183278204580324</v>
       </c>
       <c r="J40" s="64">
         <f t="shared" si="5"/>
-        <v>14383966.638950771</v>
+        <v>14885551.132347958</v>
       </c>
       <c r="K40" s="67">
         <f t="shared" si="3"/>
-        <v>23005744.718756411</v>
+        <v>23317537.558724329</v>
       </c>
       <c r="L40" s="68"/>
     </row>
@@ -5506,34 +5506,34 @@
       </c>
       <c r="D41" s="81">
         <f>+D40+D26+D10+D16</f>
+        <v>319078802.18563056</v>
+      </c>
+      <c r="E41" s="82">
         <v>280805467.60214281</v>
-      </c>
-      <c r="E41" s="82">
-        <v>240577000.14348808</v>
       </c>
       <c r="F41" s="81">
         <f>+D41-E41</f>
-        <v>40228467.458654732</v>
+        <v>38273334.583487749</v>
       </c>
       <c r="G41" s="83">
         <f t="shared" si="1"/>
-        <v>0.20351656306191793</v>
+        <v>0.23125554399367962</v>
       </c>
       <c r="H41" s="81">
         <f t="shared" si="4"/>
-        <v>1347866244.4902854</v>
+        <v>1276315208.7425222</v>
       </c>
       <c r="I41" s="83">
         <f t="shared" si="2"/>
-        <v>0.97687950269720591</v>
+        <v>0.92502217597471847</v>
       </c>
       <c r="J41" s="81">
         <f t="shared" si="5"/>
-        <v>56161093.520428561</v>
+        <v>53179800.36427176</v>
       </c>
       <c r="K41" s="81">
         <f t="shared" si="3"/>
-        <v>57840088.394262806</v>
+        <v>58927130.272639193</v>
       </c>
       <c r="L41" s="84"/>
     </row>
@@ -5581,34 +5581,34 @@
       </c>
       <c r="D43" s="4">
         <f>IFERROR(+VLOOKUP(B43,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>8104352.0621971888</v>
+      </c>
+      <c r="E43" s="4">
         <v>3760393.1741207056</v>
-      </c>
-      <c r="E43" s="4">
-        <v>-275260.76904147147</v>
       </c>
       <c r="F43" s="4">
         <f t="shared" ref="F43" si="11">+D43-E43</f>
-        <v>4035653.9431621772</v>
+        <v>4343958.8880764833</v>
       </c>
       <c r="G43" s="5">
         <f>+D43/C43</f>
-        <v>9.4009829353017646E-2</v>
+        <v>0.20260880155492972</v>
       </c>
       <c r="H43" s="4">
         <f t="shared" ref="H43" si="12">+D43/$N$3*$N$4</f>
-        <v>18049887.23577939</v>
+        <v>32417408.248788752</v>
       </c>
       <c r="I43" s="5">
         <f>+H43/C43</f>
-        <v>0.45124718089448473</v>
+        <v>0.81043520621971876</v>
       </c>
       <c r="J43" s="4">
         <f t="shared" ref="J43" si="13">+D43/$N$3</f>
-        <v>752078.63482414116</v>
+        <v>1350725.3436995314</v>
       </c>
       <c r="K43" s="4">
         <f>+(C43-D43)/$N$2</f>
-        <v>1907347.7276778575</v>
+        <v>1771980.440989045</v>
       </c>
       <c r="L43" s="4" cm="1">
         <f t="array" ref="L43">+_xlfn.IFS(I43&gt;114%,H43*0.02,I43&gt;109%,H43*0.015,I43&gt;104%,H43*0.0125,I43&gt;99%,H43*0.01,I43&lt;99%,H43*0)</f>
@@ -5624,38 +5624,38 @@
       </c>
       <c r="D44" s="4">
         <f>IFERROR(+VLOOKUP(B44,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>14041795.823822808</v>
+      </c>
+      <c r="E44" s="4">
         <v>1913900.6624423866</v>
-      </c>
-      <c r="E44" s="4">
-        <v>-402349.89063324447</v>
       </c>
       <c r="F44" s="4">
         <f t="shared" ref="F44" si="14">+D44-E44</f>
-        <v>2316250.5530756311</v>
+        <v>12127895.161380421</v>
       </c>
       <c r="G44" s="5">
         <f>+D44/C44</f>
-        <v>6.3796688748079561E-2</v>
+        <v>0.46805986079409356</v>
       </c>
       <c r="H44" s="4">
         <f t="shared" ref="H44" si="15">+D44/$N$3*$N$4</f>
-        <v>9186723.1797234565</v>
+        <v>56167183.29529123</v>
       </c>
       <c r="I44" s="5">
         <f>+H44/C44</f>
-        <v>0.30622410599078187</v>
+        <v>1.8722394431763743</v>
       </c>
       <c r="J44" s="4">
         <f t="shared" ref="J44" si="16">+D44/$N$3</f>
-        <v>382780.13248847733</v>
+        <v>2340299.3039704678</v>
       </c>
       <c r="K44" s="4">
         <f>+(C44-D44)/$N$2</f>
-        <v>1478215.7546082954</v>
+        <v>886566.89867651067</v>
       </c>
       <c r="L44" s="4" cm="1">
         <f t="array" ref="L44">+_xlfn.IFS(I44&gt;114%,H44*0.02,I44&gt;109%,H44*0.015,I44&gt;104%,H44*0.0125,I44&gt;99%,H44*0.01,I44&lt;99%,H44*0)</f>
-        <v>0</v>
+        <v>1123343.6659058246</v>
       </c>
     </row>
   </sheetData>
@@ -5793,14 +5793,14 @@
       </c>
       <c r="D2" s="22">
         <f>H2/G2</f>
-        <v>0.51388888888888884</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="E2" s="13">
         <v>33</v>
       </c>
       <c r="F2" s="12">
         <f>+H2-E2</f>
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G2" s="13">
         <f>VLOOKUP(B2,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -5808,11 +5808,11 @@
       </c>
       <c r="H2" s="13">
         <f>VLOOKUP(B2,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I2" s="17">
         <f>(+G2*$M$2)-H2</f>
-        <v>24.199999999999996</v>
+        <v>19.199999999999996</v>
       </c>
       <c r="J2" t="s">
         <v>55</v>
@@ -5896,14 +5896,14 @@
         <v>145 - ALMACEN</v>
       </c>
       <c r="S3" s="12">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="T3" s="12">
         <v>214</v>
       </c>
       <c r="U3" s="41">
         <f>+S3/T3</f>
-        <v>8.4112149532710276E-2</v>
+        <v>0.12616822429906541</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
@@ -5917,14 +5917,14 @@
       </c>
       <c r="D4" s="22">
         <f t="shared" si="0"/>
-        <v>0.52422907488986781</v>
+        <v>0.58590308370044053</v>
       </c>
       <c r="E4" s="13">
         <v>126</v>
       </c>
       <c r="F4" s="12">
         <f t="shared" si="1"/>
-        <v>-7</v>
+        <v>7</v>
       </c>
       <c r="G4" s="13">
         <f>VLOOKUP(B4,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -5932,11 +5932,11 @@
       </c>
       <c r="H4" s="13">
         <f>VLOOKUP(B4,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="I4" s="17">
         <f t="shared" si="2"/>
-        <v>73.949999999999989</v>
+        <v>59.949999999999989</v>
       </c>
       <c r="J4" t="s">
         <v>57</v>
@@ -5954,14 +5954,14 @@
         <v>145 - Articulos Sin Asociar Agrupacion</v>
       </c>
       <c r="S4" s="13">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T4" s="13">
         <v>214</v>
       </c>
       <c r="U4" s="5">
         <f t="shared" ref="U4:U11" si="3">+S4/T4</f>
-        <v>7.0093457943925228E-2</v>
+        <v>7.476635514018691E-2</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
@@ -5975,14 +5975,14 @@
       </c>
       <c r="D5" s="22">
         <f t="shared" si="0"/>
-        <v>0.41538461538461541</v>
+        <v>0.49230769230769234</v>
       </c>
       <c r="E5" s="13">
         <v>21</v>
       </c>
       <c r="F5" s="12">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G5" s="13">
         <f>VLOOKUP(B5,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -5990,11 +5990,11 @@
       </c>
       <c r="H5" s="13">
         <f>VLOOKUP(B5,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="I5" s="17">
         <f t="shared" si="2"/>
-        <v>28.25</v>
+        <v>23.25</v>
       </c>
       <c r="K5" t="s">
         <v>64</v>
@@ -6009,14 +6009,14 @@
         <v>145 - BEBIDAS</v>
       </c>
       <c r="S5" s="13">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="T5" s="13">
         <v>214</v>
       </c>
       <c r="U5" s="5">
         <f t="shared" si="3"/>
-        <v>0.13084112149532709</v>
+        <v>0.1822429906542056</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
@@ -6030,14 +6030,14 @@
       </c>
       <c r="D6" s="22">
         <f t="shared" si="0"/>
-        <v>0.50724637681159424</v>
+        <v>0.59420289855072461</v>
       </c>
       <c r="E6" s="13">
         <v>100</v>
       </c>
       <c r="F6" s="12">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="G6" s="13">
         <f>VLOOKUP(B6,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6045,11 +6045,11 @@
       </c>
       <c r="H6" s="13">
         <f>VLOOKUP(B6,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="I6" s="17">
         <f t="shared" si="2"/>
-        <v>70.949999999999989</v>
+        <v>52.949999999999989</v>
       </c>
       <c r="J6" t="s">
         <v>58</v>
@@ -6067,14 +6067,14 @@
         <v>145 - CHOCOLATE</v>
       </c>
       <c r="S6" s="13">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T6" s="13">
         <v>214</v>
       </c>
       <c r="U6" s="5">
         <f t="shared" si="3"/>
-        <v>6.0747663551401869E-2</v>
+        <v>7.0093457943925228E-2</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
@@ -6088,14 +6088,14 @@
       </c>
       <c r="D7" s="22">
         <f t="shared" si="0"/>
-        <v>0.32323232323232326</v>
+        <v>0.39898989898989901</v>
       </c>
       <c r="E7" s="13">
         <v>81</v>
       </c>
       <c r="F7" s="12">
         <f t="shared" si="1"/>
-        <v>-17</v>
+        <v>-2</v>
       </c>
       <c r="G7" s="13">
         <f>VLOOKUP(B7,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6103,11 +6103,11 @@
       </c>
       <c r="H7" s="13">
         <f>VLOOKUP(B7,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="I7" s="17">
         <f t="shared" si="2"/>
-        <v>104.29999999999998</v>
+        <v>89.299999999999983</v>
       </c>
       <c r="J7" t="s">
         <v>58</v>
@@ -6125,14 +6125,14 @@
         <v>145 - GALLETITAS</v>
       </c>
       <c r="S7" s="13">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="T7" s="13">
         <v>214</v>
       </c>
       <c r="U7" s="5">
         <f t="shared" si="3"/>
-        <v>0.17289719626168223</v>
+        <v>0.22429906542056074</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
@@ -6146,14 +6146,14 @@
       </c>
       <c r="D8" s="22">
         <f t="shared" si="0"/>
-        <v>0.43457943925233644</v>
+        <v>0.54672897196261683</v>
       </c>
       <c r="E8" s="13">
         <v>89</v>
       </c>
       <c r="F8" s="12">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="G8" s="13">
         <f>VLOOKUP(B8,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6161,11 +6161,11 @@
       </c>
       <c r="H8" s="13">
         <f>VLOOKUP(B8,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="I8" s="17">
         <f t="shared" si="2"/>
-        <v>88.9</v>
+        <v>64.900000000000006</v>
       </c>
       <c r="J8" t="s">
         <v>55</v>
@@ -6184,14 +6184,14 @@
         <v>145 - GOLOSINAS</v>
       </c>
       <c r="S8" s="13">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="T8" s="13">
         <v>214</v>
       </c>
       <c r="U8" s="5">
         <f t="shared" si="3"/>
-        <v>0.1822429906542056</v>
+        <v>0.21962616822429906</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
@@ -6205,26 +6205,26 @@
       </c>
       <c r="D9" s="22">
         <f>H9/G9</f>
-        <v>0.42603550295857989</v>
+        <v>0.50292397660818711</v>
       </c>
       <c r="E9" s="13">
         <v>92</v>
       </c>
       <c r="F9" s="12">
         <f t="shared" si="1"/>
-        <v>-20</v>
+        <v>-6</v>
       </c>
       <c r="G9" s="13">
         <f>VLOOKUP(B9,'Base Cobertura'!$A:$C,3,FALSE)</f>
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H9" s="13">
         <f>VLOOKUP(B9,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="I9" s="17">
         <f t="shared" si="2"/>
-        <v>71.650000000000006</v>
+        <v>59.349999999999994</v>
       </c>
       <c r="J9" t="s">
         <v>55</v>
@@ -6242,14 +6242,14 @@
         <v>145 - MASCOTAS</v>
       </c>
       <c r="S9" s="13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T9" s="13">
         <v>214</v>
       </c>
       <c r="U9" s="5">
         <f t="shared" si="3"/>
-        <v>4.2056074766355138E-2</v>
+        <v>4.6728971962616821E-2</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
@@ -6263,14 +6263,14 @@
       </c>
       <c r="D10" s="22">
         <f t="shared" si="0"/>
-        <v>0.3487179487179487</v>
+        <v>0.39487179487179486</v>
       </c>
       <c r="E10" s="13">
         <v>64</v>
       </c>
       <c r="F10" s="12">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="G10" s="13">
         <f>VLOOKUP(B10,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6278,11 +6278,11 @@
       </c>
       <c r="H10" s="13">
         <f>VLOOKUP(B10,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="I10" s="17">
         <f t="shared" si="2"/>
-        <v>97.75</v>
+        <v>88.75</v>
       </c>
       <c r="J10" t="s">
         <v>58</v>
@@ -6300,14 +6300,14 @@
         <v>145 - NO PERECEDEROS</v>
       </c>
       <c r="S10" s="13">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T10" s="13">
         <v>214</v>
       </c>
       <c r="U10" s="5">
         <f t="shared" si="3"/>
-        <v>2.336448598130841E-2</v>
+        <v>3.7383177570093455E-2</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
@@ -6321,14 +6321,14 @@
       </c>
       <c r="D11" s="32">
         <f t="shared" si="0"/>
-        <v>0.16831683168316833</v>
+        <v>0.21782178217821782</v>
       </c>
       <c r="E11" s="31">
         <v>19</v>
       </c>
       <c r="F11" s="33">
         <f t="shared" si="1"/>
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="G11" s="13">
         <f>VLOOKUP(B11,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6336,11 +6336,11 @@
       </c>
       <c r="H11" s="13">
         <f>VLOOKUP(B11,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I11" s="34">
         <f t="shared" si="2"/>
-        <v>68.849999999999994</v>
+        <v>63.849999999999994</v>
       </c>
       <c r="J11" t="s">
         <v>59</v>
@@ -6355,14 +6355,14 @@
         <v>145 - PILAS</v>
       </c>
       <c r="S11" s="13">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T11" s="13">
         <v>214</v>
       </c>
       <c r="U11" s="5">
         <f t="shared" si="3"/>
-        <v>2.336448598130841E-2</v>
+        <v>5.6074766355140186E-2</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
@@ -6376,14 +6376,14 @@
       </c>
       <c r="D12" s="32">
         <f t="shared" si="0"/>
-        <v>0.19047619047619047</v>
+        <v>0.21904761904761905</v>
       </c>
       <c r="E12" s="31">
         <v>24</v>
       </c>
       <c r="F12" s="33">
         <f t="shared" si="1"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="G12" s="13">
         <f>VLOOKUP(B12,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6391,11 +6391,11 @@
       </c>
       <c r="H12" s="13">
         <f>VLOOKUP(B12,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I12" s="34">
         <f t="shared" si="2"/>
-        <v>69.25</v>
+        <v>66.25</v>
       </c>
       <c r="J12" t="s">
         <v>59</v>
@@ -6412,14 +6412,14 @@
       </c>
       <c r="D13" s="22">
         <f t="shared" si="0"/>
-        <v>0.41153846153846152</v>
+        <v>0.51923076923076927</v>
       </c>
       <c r="E13" s="13">
         <v>144</v>
       </c>
       <c r="F13" s="12">
         <f t="shared" si="1"/>
-        <v>-37</v>
+        <v>-9</v>
       </c>
       <c r="G13" s="13">
         <f>VLOOKUP(B13,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6427,11 +6427,11 @@
       </c>
       <c r="H13" s="13">
         <f>VLOOKUP(B13,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="I13" s="17">
         <f t="shared" si="2"/>
-        <v>114</v>
+        <v>86</v>
       </c>
       <c r="J13" t="s">
         <v>57</v>
@@ -6451,14 +6451,14 @@
       </c>
       <c r="D14" s="22">
         <f t="shared" si="0"/>
-        <v>0.38461538461538464</v>
+        <v>0.42307692307692307</v>
       </c>
       <c r="E14" s="13">
         <v>85</v>
       </c>
       <c r="F14" s="12">
         <f t="shared" si="1"/>
-        <v>-15</v>
+        <v>-8</v>
       </c>
       <c r="G14" s="13">
         <f>VLOOKUP(B14,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6466,11 +6466,11 @@
       </c>
       <c r="H14" s="13">
         <f>VLOOKUP(B14,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="I14" s="17">
         <f t="shared" si="2"/>
-        <v>84.699999999999989</v>
+        <v>77.699999999999989</v>
       </c>
       <c r="J14" t="s">
         <v>55</v>
@@ -6486,15 +6486,15 @@
       <c r="E15" s="14"/>
       <c r="F15" s="16">
         <f>+SUM(F2:F14)</f>
-        <v>-27</v>
+        <v>120</v>
       </c>
       <c r="G15" s="8">
         <f>+SUM(G2:G14)</f>
-        <v>2234</v>
+        <v>2236</v>
       </c>
       <c r="H15" s="8">
         <f>+SUM(H2:H14)</f>
-        <v>852</v>
+        <v>999</v>
       </c>
       <c r="I15" s="8"/>
     </row>
@@ -6511,14 +6511,14 @@
       </c>
       <c r="D16" s="22">
         <f t="shared" si="0"/>
-        <v>0.49689440993788819</v>
+        <v>0.60869565217391308</v>
       </c>
       <c r="E16" s="13">
         <v>90</v>
       </c>
       <c r="F16" s="12">
         <f t="shared" si="1"/>
-        <v>-10</v>
+        <v>8</v>
       </c>
       <c r="G16" s="13">
         <f>VLOOKUP(B16,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6526,11 +6526,11 @@
       </c>
       <c r="H16" s="13">
         <f>VLOOKUP(B16,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="I16" s="17">
         <f t="shared" si="2"/>
-        <v>56.849999999999994</v>
+        <v>38.849999999999994</v>
       </c>
       <c r="J16" t="s">
         <v>55</v>
@@ -6550,14 +6550,14 @@
       </c>
       <c r="D17" s="22">
         <f t="shared" si="0"/>
-        <v>0.33663366336633666</v>
+        <v>0.37128712871287128</v>
       </c>
       <c r="E17" s="13">
         <v>92</v>
       </c>
       <c r="F17" s="12">
         <f t="shared" si="1"/>
-        <v>-24</v>
+        <v>-17</v>
       </c>
       <c r="G17" s="13">
         <f>VLOOKUP(B17,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6565,11 +6565,11 @@
       </c>
       <c r="H17" s="13">
         <f>VLOOKUP(B17,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="I17" s="17">
         <f t="shared" si="2"/>
-        <v>103.69999999999999</v>
+        <v>96.699999999999989</v>
       </c>
       <c r="J17" t="s">
         <v>55</v>
@@ -6589,14 +6589,14 @@
       </c>
       <c r="D18" s="22">
         <f t="shared" si="0"/>
-        <v>0.53529411764705881</v>
+        <v>0.62941176470588234</v>
       </c>
       <c r="E18" s="13">
         <v>88</v>
       </c>
       <c r="F18" s="12">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="G18" s="13">
         <f>VLOOKUP(B18,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6604,11 +6604,11 @@
       </c>
       <c r="H18" s="13">
         <f>VLOOKUP(B18,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="I18" s="17">
         <f t="shared" si="2"/>
-        <v>53.5</v>
+        <v>37.5</v>
       </c>
       <c r="J18" t="s">
         <v>58</v>
@@ -6628,14 +6628,14 @@
       </c>
       <c r="D19" s="22">
         <f t="shared" si="0"/>
-        <v>0.55625000000000002</v>
+        <v>0.625</v>
       </c>
       <c r="E19" s="13">
         <v>95</v>
       </c>
       <c r="F19" s="12">
         <f t="shared" si="1"/>
-        <v>-6</v>
+        <v>5</v>
       </c>
       <c r="G19" s="13">
         <f>VLOOKUP(B19,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6643,11 +6643,11 @@
       </c>
       <c r="H19" s="13">
         <f>VLOOKUP(B19,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="I19" s="17">
         <f t="shared" si="2"/>
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="J19" t="s">
         <v>58</v>
@@ -6667,14 +6667,14 @@
       </c>
       <c r="D20" s="22">
         <f t="shared" si="0"/>
-        <v>0.50847457627118642</v>
+        <v>0.60451977401129942</v>
       </c>
       <c r="E20" s="13">
         <v>83</v>
       </c>
       <c r="F20" s="12">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="G20" s="13">
         <f>VLOOKUP(B20,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6682,11 +6682,11 @@
       </c>
       <c r="H20" s="13">
         <f>VLOOKUP(B20,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="I20" s="17">
         <f t="shared" si="2"/>
-        <v>60.449999999999989</v>
+        <v>43.449999999999989</v>
       </c>
       <c r="J20" t="s">
         <v>55</v>
@@ -6706,14 +6706,14 @@
       </c>
       <c r="D21" s="22">
         <f t="shared" si="0"/>
-        <v>0.47928994082840237</v>
+        <v>0.57396449704142016</v>
       </c>
       <c r="E21" s="13">
         <v>64</v>
       </c>
       <c r="F21" s="12">
         <f t="shared" si="1"/>
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G21" s="13">
         <f>VLOOKUP(B21,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6721,11 +6721,11 @@
       </c>
       <c r="H21" s="13">
         <f>VLOOKUP(B21,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="I21" s="17">
         <f t="shared" si="2"/>
-        <v>62.650000000000006</v>
+        <v>46.650000000000006</v>
       </c>
       <c r="J21" t="s">
         <v>58</v>
@@ -6745,14 +6745,14 @@
       </c>
       <c r="D22" s="22">
         <f t="shared" si="0"/>
-        <v>0.20707070707070707</v>
+        <v>0.27777777777777779</v>
       </c>
       <c r="E22" s="13">
         <v>66</v>
       </c>
       <c r="F22" s="12">
         <f t="shared" si="1"/>
-        <v>-25</v>
+        <v>-11</v>
       </c>
       <c r="G22" s="13">
         <f>VLOOKUP(B22,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6760,11 +6760,11 @@
       </c>
       <c r="H22" s="13">
         <f>VLOOKUP(B22,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="I22" s="17">
         <f t="shared" si="2"/>
-        <v>127.29999999999998</v>
+        <v>113.29999999999998</v>
       </c>
       <c r="J22" t="s">
         <v>58</v>
@@ -6784,14 +6784,14 @@
       </c>
       <c r="D23" s="22">
         <f t="shared" si="0"/>
-        <v>0.43478260869565216</v>
+        <v>0.52898550724637683</v>
       </c>
       <c r="E23" s="13">
         <v>70</v>
       </c>
       <c r="F23" s="12">
         <f t="shared" si="1"/>
-        <v>-10</v>
+        <v>3</v>
       </c>
       <c r="G23" s="13">
         <f>VLOOKUP(B23,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6799,11 +6799,11 @@
       </c>
       <c r="H23" s="13">
         <f>VLOOKUP(B23,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="I23" s="17">
         <f t="shared" si="2"/>
-        <v>57.3</v>
+        <v>44.3</v>
       </c>
       <c r="J23" t="s">
         <v>58</v>
@@ -6823,14 +6823,14 @@
       </c>
       <c r="D24" s="22">
         <f t="shared" si="0"/>
-        <v>0.48823529411764705</v>
+        <v>0.54705882352941182</v>
       </c>
       <c r="E24" s="13">
         <v>79</v>
       </c>
       <c r="F24" s="12">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G24" s="13">
         <f>VLOOKUP(B24,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6838,11 +6838,11 @@
       </c>
       <c r="H24" s="13">
         <f>VLOOKUP(B24,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="I24" s="17">
         <f t="shared" si="2"/>
-        <v>61.5</v>
+        <v>51.5</v>
       </c>
       <c r="J24" t="s">
         <v>60</v>
@@ -6858,7 +6858,7 @@
       <c r="E25" s="14"/>
       <c r="F25" s="16">
         <f>+SUM(F16:F24)</f>
-        <v>-44</v>
+        <v>78</v>
       </c>
       <c r="G25" s="8">
         <f>+SUM(G16:G24)</f>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="H25" s="8">
         <f>+SUM(H16:H24)</f>
-        <v>683</v>
+        <v>805</v>
       </c>
       <c r="I25" s="8"/>
     </row>
@@ -6883,26 +6883,26 @@
       </c>
       <c r="D26" s="22">
         <f t="shared" si="0"/>
-        <v>0.30357142857142855</v>
+        <v>0.38596491228070173</v>
       </c>
       <c r="E26" s="13">
         <v>20</v>
       </c>
       <c r="F26" s="12">
         <f>+H26-E26</f>
-        <v>-3</v>
+        <v>2</v>
       </c>
       <c r="G26" s="13">
         <f>VLOOKUP(B26,'Base Cobertura'!$A:$C,3,FALSE)</f>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H26" s="13">
         <f>VLOOKUP(B26,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I26" s="17">
         <f t="shared" si="2"/>
-        <v>30.6</v>
+        <v>26.449999999999996</v>
       </c>
       <c r="J26" t="s">
         <v>55</v>
@@ -6922,26 +6922,26 @@
       </c>
       <c r="D27" s="22">
         <f t="shared" si="0"/>
-        <v>0.41666666666666669</v>
+        <v>0.50318471337579618</v>
       </c>
       <c r="E27" s="13">
         <v>68</v>
       </c>
       <c r="F27" s="12">
         <f t="shared" si="1"/>
-        <v>-3</v>
+        <v>11</v>
       </c>
       <c r="G27" s="13">
         <f>VLOOKUP(B27,'Base Cobertura'!$A:$C,3,FALSE)</f>
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H27" s="13">
         <f>VLOOKUP(B27,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="I27" s="17">
         <f t="shared" si="2"/>
-        <v>67.599999999999994</v>
+        <v>54.449999999999989</v>
       </c>
       <c r="J27" t="s">
         <v>58</v>
@@ -6961,14 +6961,14 @@
       </c>
       <c r="D28" s="22">
         <f t="shared" si="0"/>
-        <v>0.36645962732919257</v>
+        <v>0.52173913043478259</v>
       </c>
       <c r="E28" s="13">
         <v>80</v>
       </c>
       <c r="F28" s="12">
         <f t="shared" si="1"/>
-        <v>-21</v>
+        <v>4</v>
       </c>
       <c r="G28" s="13">
         <f>VLOOKUP(B28,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6976,11 +6976,11 @@
       </c>
       <c r="H28" s="13">
         <f>VLOOKUP(B28,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="I28" s="17">
         <f t="shared" si="2"/>
-        <v>77.849999999999994</v>
+        <v>52.849999999999994</v>
       </c>
       <c r="J28" t="s">
         <v>58</v>
@@ -7000,14 +7000,14 @@
       </c>
       <c r="D29" s="22">
         <f t="shared" si="0"/>
-        <v>0.20481927710843373</v>
+        <v>0.26506024096385544</v>
       </c>
       <c r="E29" s="13">
         <v>68</v>
       </c>
       <c r="F29" s="12">
         <f t="shared" si="1"/>
-        <v>-17</v>
+        <v>-2</v>
       </c>
       <c r="G29" s="13">
         <f>VLOOKUP(B29,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7015,11 +7015,11 @@
       </c>
       <c r="H29" s="13">
         <f>VLOOKUP(B29,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="I29" s="17">
         <f t="shared" si="2"/>
-        <v>160.65</v>
+        <v>145.65</v>
       </c>
       <c r="J29" t="s">
         <v>58</v>
@@ -7039,14 +7039,14 @@
       </c>
       <c r="D30" s="22">
         <f t="shared" si="0"/>
-        <v>0.51428571428571423</v>
+        <v>0.6071428571428571</v>
       </c>
       <c r="E30" s="13">
         <v>73</v>
       </c>
       <c r="F30" s="12">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="G30" s="13">
         <f>VLOOKUP(B30,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7054,11 +7054,11 @@
       </c>
       <c r="H30" s="13">
         <f>VLOOKUP(B30,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="I30" s="17">
         <f t="shared" si="2"/>
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="J30" t="s">
         <v>55</v>
@@ -7078,14 +7078,14 @@
       </c>
       <c r="D31" s="22">
         <f t="shared" si="0"/>
-        <v>0.2983425414364641</v>
+        <v>0.40883977900552487</v>
       </c>
       <c r="E31" s="13">
         <v>40</v>
       </c>
       <c r="F31" s="12">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="G31" s="13">
         <f>VLOOKUP(B31,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7093,11 +7093,11 @@
       </c>
       <c r="H31" s="13">
         <f>VLOOKUP(B31,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="I31" s="17">
         <f t="shared" si="2"/>
-        <v>99.85</v>
+        <v>79.849999999999994</v>
       </c>
       <c r="J31" t="s">
         <v>58</v>
@@ -7117,14 +7117,14 @@
       </c>
       <c r="D32" s="22">
         <f t="shared" si="0"/>
-        <v>0.35119047619047616</v>
+        <v>0.45238095238095238</v>
       </c>
       <c r="E32" s="13">
         <v>67</v>
       </c>
       <c r="F32" s="12">
         <f t="shared" si="1"/>
-        <v>-8</v>
+        <v>9</v>
       </c>
       <c r="G32" s="13">
         <f>VLOOKUP(B32,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7132,11 +7132,11 @@
       </c>
       <c r="H32" s="13">
         <f>VLOOKUP(B32,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="I32" s="17">
         <f t="shared" si="2"/>
-        <v>83.799999999999983</v>
+        <v>66.799999999999983</v>
       </c>
       <c r="J32" t="s">
         <v>58</v>
@@ -7156,14 +7156,14 @@
       </c>
       <c r="D33" s="22">
         <f t="shared" si="0"/>
-        <v>0.39534883720930231</v>
+        <v>0.48255813953488375</v>
       </c>
       <c r="E33" s="13">
         <v>66</v>
       </c>
       <c r="F33" s="12">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="G33" s="13">
         <f>VLOOKUP(B33,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7171,11 +7171,11 @@
       </c>
       <c r="H33" s="13">
         <f>VLOOKUP(B33,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="I33" s="17">
         <f t="shared" si="2"/>
-        <v>78.199999999999989</v>
+        <v>63.199999999999989</v>
       </c>
       <c r="J33" t="s">
         <v>58</v>
@@ -7195,14 +7195,14 @@
       </c>
       <c r="D34" s="22">
         <f t="shared" si="0"/>
-        <v>0.19718309859154928</v>
+        <v>0.26760563380281688</v>
       </c>
       <c r="E34" s="13">
         <v>82</v>
       </c>
       <c r="F34" s="12">
         <f t="shared" si="1"/>
-        <v>-54</v>
+        <v>-44</v>
       </c>
       <c r="G34" s="13">
         <f>VLOOKUP(B34,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7210,11 +7210,11 @@
       </c>
       <c r="H34" s="13">
         <f>VLOOKUP(B34,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="I34" s="17">
         <f t="shared" si="2"/>
-        <v>92.7</v>
+        <v>82.7</v>
       </c>
       <c r="J34" t="s">
         <v>55</v>
@@ -7234,14 +7234,14 @@
       </c>
       <c r="D35" s="22">
         <f t="shared" si="0"/>
-        <v>0.398876404494382</v>
+        <v>0.449438202247191</v>
       </c>
       <c r="E35" s="13">
         <v>81</v>
       </c>
       <c r="F35" s="12">
         <f t="shared" si="1"/>
-        <v>-10</v>
+        <v>-1</v>
       </c>
       <c r="G35" s="13">
         <f>VLOOKUP(B35,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7249,11 +7249,11 @@
       </c>
       <c r="H35" s="13">
         <f>VLOOKUP(B35,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="I35" s="17">
         <f t="shared" si="2"/>
-        <v>80.299999999999983</v>
+        <v>71.299999999999983</v>
       </c>
       <c r="J35" t="s">
         <v>58</v>
@@ -7273,14 +7273,14 @@
       </c>
       <c r="D36" s="22">
         <f t="shared" si="0"/>
-        <v>2.6548672566371681E-2</v>
+        <v>3.5398230088495575E-2</v>
       </c>
       <c r="E36" s="13">
         <v>0</v>
       </c>
       <c r="F36" s="12">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G36" s="13">
         <f>VLOOKUP(B36,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7288,11 +7288,11 @@
       </c>
       <c r="H36" s="13">
         <f>VLOOKUP(B36,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I36" s="17">
         <f t="shared" si="2"/>
-        <v>93.05</v>
+        <v>92.05</v>
       </c>
       <c r="J36" t="s">
         <v>58</v>
@@ -7309,14 +7309,14 @@
       </c>
       <c r="D37" s="22">
         <f t="shared" si="0"/>
-        <v>3.8461538461538464E-2</v>
+        <v>5.7692307692307696E-2</v>
       </c>
       <c r="E37" s="13">
         <v>17</v>
       </c>
       <c r="F37" s="12">
         <f t="shared" si="1"/>
-        <v>-13</v>
+        <v>-11</v>
       </c>
       <c r="G37" s="13">
         <f>VLOOKUP(B37,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7324,11 +7324,11 @@
       </c>
       <c r="H37" s="13">
         <f>VLOOKUP(B37,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I37" s="17">
         <f t="shared" si="2"/>
-        <v>84.399999999999991</v>
+        <v>82.399999999999991</v>
       </c>
       <c r="J37" t="s">
         <v>59</v>
@@ -7345,14 +7345,14 @@
       </c>
       <c r="D38" s="22">
         <f t="shared" si="0"/>
-        <v>0.47244094488188976</v>
+        <v>0.53543307086614178</v>
       </c>
       <c r="E38" s="13">
         <v>60</v>
       </c>
       <c r="F38" s="12">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G38" s="13">
         <f>VLOOKUP(B38,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7360,11 +7360,11 @@
       </c>
       <c r="H38" s="13">
         <f>VLOOKUP(B38,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="I38" s="17">
         <f t="shared" si="2"/>
-        <v>47.95</v>
+        <v>39.950000000000003</v>
       </c>
       <c r="J38" t="s">
         <v>55</v>
@@ -7380,15 +7380,15 @@
       <c r="E39" s="14"/>
       <c r="F39" s="8">
         <f>+SUM(F26:F38)</f>
-        <v>-111</v>
+        <v>43</v>
       </c>
       <c r="G39" s="8">
         <f>+SUM(G26:G38)</f>
-        <v>1947</v>
+        <v>1949</v>
       </c>
       <c r="H39" s="8">
         <f>+SUM(H26:H38)</f>
-        <v>611</v>
+        <v>765</v>
       </c>
       <c r="I39" s="8"/>
       <c r="L39" t="s">
@@ -7404,20 +7404,20 @@
       <c r="E40" s="6"/>
       <c r="F40" s="8">
         <f>+SUM(F39+F25+F15)</f>
-        <v>-182</v>
+        <v>241</v>
       </c>
       <c r="G40" s="8">
         <f>+G15+G25+G39</f>
-        <v>5726</v>
+        <v>5730</v>
       </c>
       <c r="H40" s="8">
         <f>+H15+H25+H39</f>
-        <v>2146</v>
+        <v>2569</v>
       </c>
       <c r="I40" s="8"/>
       <c r="L40" s="1">
         <f>+H40/G40</f>
-        <v>0.37478169752008383</v>
+        <v>0.44834205933682375</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
@@ -7430,14 +7430,14 @@
       </c>
       <c r="D41" s="22">
         <f t="shared" ref="D41:D42" si="4">H41/G41</f>
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="E41" s="13">
         <v>60</v>
       </c>
       <c r="F41" s="12">
         <f t="shared" ref="F41:F42" si="5">+H41-E41</f>
-        <v>-60</v>
+        <v>-42</v>
       </c>
       <c r="G41" s="13">
         <f>VLOOKUP(B41,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7445,11 +7445,11 @@
       </c>
       <c r="H41" s="13">
         <f>VLOOKUP(B41,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I41" s="17">
         <f t="shared" ref="I41:I42" si="6">(+G41*$M$2)-H41</f>
-        <v>102</v>
+        <v>84</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
@@ -7462,26 +7462,26 @@
       </c>
       <c r="D42" s="22">
         <f t="shared" si="4"/>
-        <v>8.3333333333333332E-3</v>
+        <v>0.18032786885245902</v>
       </c>
       <c r="E42" s="13">
         <v>60</v>
       </c>
       <c r="F42" s="12">
         <f t="shared" si="5"/>
-        <v>-59</v>
+        <v>-38</v>
       </c>
       <c r="G42" s="13">
         <f>VLOOKUP(B42,'Base Cobertura'!$A:$C,3,FALSE)</f>
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H42" s="13">
         <f>VLOOKUP(B42,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="I42" s="17">
         <f t="shared" si="6"/>
-        <v>101</v>
+        <v>81.7</v>
       </c>
     </row>
   </sheetData>
@@ -8075,7 +8075,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="51">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="C4" s="51">
         <v>127</v>
@@ -8095,7 +8095,7 @@
         <v>10</v>
       </c>
       <c r="B5" s="51">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="C5" s="51">
         <v>181</v>
@@ -8113,7 +8113,7 @@
         <v>100</v>
       </c>
       <c r="B6" s="51">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C6" s="51">
         <v>2025</v>
@@ -8131,10 +8131,10 @@
         <v>11</v>
       </c>
       <c r="B7" s="51">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="C7" s="51">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G7" t="s">
         <v>226</v>
@@ -8151,7 +8151,7 @@
         <v>12</v>
       </c>
       <c r="B8" s="51">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="C8" s="51">
         <v>214</v>
@@ -8171,7 +8171,7 @@
         <v>123</v>
       </c>
       <c r="B9" s="51">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C9" s="51">
         <v>489</v>
@@ -8191,7 +8191,7 @@
         <v>15</v>
       </c>
       <c r="B10" s="51">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C10" s="51">
         <v>65</v>
@@ -8211,7 +8211,7 @@
         <v>16</v>
       </c>
       <c r="B11" s="51">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="C11" s="51">
         <v>198</v>
@@ -8229,7 +8229,7 @@
         <v>18</v>
       </c>
       <c r="B12" s="51">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="C12" s="51">
         <v>177</v>
@@ -8245,7 +8245,7 @@
         <v>222</v>
       </c>
       <c r="H12">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I12" s="51">
         <v>127</v>
@@ -8256,7 +8256,7 @@
         <v>19</v>
       </c>
       <c r="B13" s="51">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="C13" s="51">
         <v>207</v>
@@ -8269,7 +8269,7 @@
         <v>223</v>
       </c>
       <c r="H13" s="51">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I13" s="51">
         <v>127</v>
@@ -8280,7 +8280,7 @@
         <v>2</v>
       </c>
       <c r="B14" s="51">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="C14" s="51">
         <v>138</v>
@@ -8293,7 +8293,7 @@
         <v>224</v>
       </c>
       <c r="H14" s="51">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I14" s="51">
         <v>127</v>
@@ -8304,7 +8304,7 @@
         <v>20</v>
       </c>
       <c r="B15" s="51">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="C15" s="51">
         <v>227</v>
@@ -8328,7 +8328,7 @@
         <v>21</v>
       </c>
       <c r="B16" s="51">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="C16" s="51">
         <v>170</v>
@@ -8341,7 +8341,7 @@
         <v>226</v>
       </c>
       <c r="H16" s="51">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I16" s="51">
         <v>127</v>
@@ -8352,7 +8352,7 @@
         <v>22</v>
       </c>
       <c r="B17" s="51">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C17" s="51">
         <v>72</v>
@@ -8365,7 +8365,7 @@
         <v>227</v>
       </c>
       <c r="H17" s="51">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I17" s="51">
         <v>127</v>
@@ -8376,7 +8376,7 @@
         <v>23</v>
       </c>
       <c r="B18" s="51">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="C18" s="51">
         <v>160</v>
@@ -8389,7 +8389,7 @@
         <v>228</v>
       </c>
       <c r="H18" s="51">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I18" s="51">
         <v>127</v>
@@ -8400,7 +8400,7 @@
         <v>24</v>
       </c>
       <c r="B19" s="51">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="C19" s="51">
         <v>178</v>
@@ -8413,7 +8413,7 @@
         <v>229</v>
       </c>
       <c r="H19" s="51">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I19" s="51">
         <v>127</v>
@@ -8437,7 +8437,7 @@
         <v>230</v>
       </c>
       <c r="H20">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I20" s="51">
         <v>127</v>
@@ -8464,7 +8464,7 @@
         <v>222</v>
       </c>
       <c r="H21" s="51">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I21" s="51">
         <v>181</v>
@@ -8475,7 +8475,7 @@
         <v>27</v>
       </c>
       <c r="B22" s="51">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="C22" s="51">
         <v>140</v>
@@ -8488,7 +8488,7 @@
         <v>223</v>
       </c>
       <c r="H22" s="51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I22" s="51">
         <v>181</v>
@@ -8499,7 +8499,7 @@
         <v>28</v>
       </c>
       <c r="B23" s="51">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="C23" s="51">
         <v>168</v>
@@ -8512,7 +8512,7 @@
         <v>224</v>
       </c>
       <c r="H23" s="51">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="I23" s="51">
         <v>181</v>
@@ -8523,7 +8523,7 @@
         <v>3</v>
       </c>
       <c r="B24" s="51">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="C24" s="51">
         <v>170</v>
@@ -8536,7 +8536,7 @@
         <v>225</v>
       </c>
       <c r="H24" s="51">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I24" s="51">
         <v>181</v>
@@ -8547,7 +8547,7 @@
         <v>30</v>
       </c>
       <c r="B25" s="51">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C25" s="51">
         <v>139</v>
@@ -8560,7 +8560,7 @@
         <v>226</v>
       </c>
       <c r="H25" s="51">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="I25" s="51">
         <v>181</v>
@@ -8571,7 +8571,7 @@
         <v>31</v>
       </c>
       <c r="B26" s="51">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="C26" s="51">
         <v>161</v>
@@ -8584,7 +8584,7 @@
         <v>227</v>
       </c>
       <c r="H26" s="51">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I26" s="51">
         <v>181</v>
@@ -8595,10 +8595,10 @@
         <v>32</v>
       </c>
       <c r="B27" s="51">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C27" s="51">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E27">
         <f t="shared" si="1"/>
@@ -8608,7 +8608,7 @@
         <v>228</v>
       </c>
       <c r="H27" s="51">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I27" s="51">
         <v>181</v>
@@ -8619,7 +8619,7 @@
         <v>33</v>
       </c>
       <c r="B28" s="51">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="C28" s="51">
         <v>172</v>
@@ -8632,7 +8632,7 @@
         <v>229</v>
       </c>
       <c r="H28" s="51">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I28" s="51">
         <v>181</v>
@@ -8643,10 +8643,10 @@
         <v>36</v>
       </c>
       <c r="B29" s="51">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="C29" s="51">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E29">
         <f t="shared" si="1"/>
@@ -8656,7 +8656,7 @@
         <v>230</v>
       </c>
       <c r="H29" s="51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I29" s="51">
         <v>181</v>
@@ -8667,7 +8667,7 @@
         <v>37</v>
       </c>
       <c r="B30" s="51">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="C30" s="51">
         <v>142</v>
@@ -8683,7 +8683,7 @@
         <v>222</v>
       </c>
       <c r="H30" s="51">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I30" s="51">
         <v>2025</v>
@@ -8694,7 +8694,7 @@
         <v>4</v>
       </c>
       <c r="B31" s="51">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="C31" s="51">
         <v>182</v>
@@ -8707,7 +8707,7 @@
         <v>223</v>
       </c>
       <c r="H31" s="51">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I31" s="51">
         <v>2025</v>
@@ -8718,7 +8718,7 @@
         <v>40</v>
       </c>
       <c r="B32" s="51">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="C32" s="51">
         <v>249</v>
@@ -8731,7 +8731,7 @@
         <v>224</v>
       </c>
       <c r="H32" s="51">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I32" s="51">
         <v>2025</v>
@@ -8755,7 +8755,7 @@
         <v>225</v>
       </c>
       <c r="H33" s="51">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I33" s="51">
         <v>2025</v>
@@ -8777,7 +8777,7 @@
         <v>226</v>
       </c>
       <c r="H34" s="51">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I34" s="51">
         <v>2025</v>
@@ -8788,7 +8788,7 @@
         <v>44</v>
       </c>
       <c r="B35" s="51">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="C35" s="51">
         <v>169</v>
@@ -8801,7 +8801,7 @@
         <v>227</v>
       </c>
       <c r="H35" s="51">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I35" s="51">
         <v>2025</v>
@@ -8825,7 +8825,7 @@
         <v>228</v>
       </c>
       <c r="H36" s="51">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I36" s="51">
         <v>2025</v>
@@ -8836,7 +8836,7 @@
         <v>5</v>
       </c>
       <c r="B37" s="51">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="C37" s="51">
         <v>260</v>
@@ -8860,7 +8860,7 @@
         <v>52</v>
       </c>
       <c r="B38" s="51">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C38" s="51">
         <v>101</v>
@@ -8872,7 +8872,9 @@
       <c r="G38" t="s">
         <v>230</v>
       </c>
-      <c r="H38" s="51"/>
+      <c r="H38" s="51">
+        <v>1</v>
+      </c>
       <c r="I38" s="51">
         <v>2025</v>
       </c>
@@ -8882,7 +8884,7 @@
         <v>53</v>
       </c>
       <c r="B39" s="51">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C39" s="51">
         <v>105</v>
@@ -8898,10 +8900,10 @@
         <v>222</v>
       </c>
       <c r="H39" s="51">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I39" s="51">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
@@ -8909,7 +8911,7 @@
         <v>54</v>
       </c>
       <c r="B40" s="51">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C40" s="51">
         <v>202</v>
@@ -8922,10 +8924,10 @@
         <v>223</v>
       </c>
       <c r="H40" s="51">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I40" s="51">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
@@ -8933,7 +8935,7 @@
         <v>56</v>
       </c>
       <c r="B41">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="C41" s="51">
         <v>198</v>
@@ -8946,10 +8948,10 @@
         <v>224</v>
       </c>
       <c r="H41" s="51">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="I41" s="51">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
@@ -8957,7 +8959,7 @@
         <v>57</v>
       </c>
       <c r="B42" s="51">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C42" s="51">
         <v>104</v>
@@ -8970,17 +8972,19 @@
         <v>225</v>
       </c>
       <c r="H42" s="51">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I42" s="51">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>58</v>
       </c>
-      <c r="B43" s="51"/>
+      <c r="B43" s="51">
+        <v>18</v>
+      </c>
       <c r="C43" s="51">
         <v>120</v>
       </c>
@@ -8992,10 +8996,10 @@
         <v>226</v>
       </c>
       <c r="H43" s="51">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I43" s="51">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
@@ -9003,10 +9007,10 @@
         <v>59</v>
       </c>
       <c r="B44" s="51">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="C44" s="51">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E44">
         <f t="shared" si="3"/>
@@ -9016,10 +9020,10 @@
         <v>227</v>
       </c>
       <c r="H44" s="51">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I44" s="51">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
@@ -9027,7 +9031,7 @@
         <v>7</v>
       </c>
       <c r="B45" s="51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C45" s="51">
         <v>113</v>
@@ -9040,10 +9044,10 @@
         <v>228</v>
       </c>
       <c r="H45" s="51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I45" s="51">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
@@ -9051,7 +9055,7 @@
         <v>8</v>
       </c>
       <c r="B46" s="51">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="C46" s="51">
         <v>195</v>
@@ -9064,10 +9068,10 @@
         <v>229</v>
       </c>
       <c r="H46" s="51">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I46" s="51">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
@@ -9075,7 +9079,7 @@
         <v>9</v>
       </c>
       <c r="B47" s="51">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="C47" s="51">
         <v>161</v>
@@ -9088,10 +9092,10 @@
         <v>230</v>
       </c>
       <c r="H47" s="51">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I47" s="51">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
@@ -9108,7 +9112,7 @@
         <v>222</v>
       </c>
       <c r="H48" s="51">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="I48" s="51">
         <v>214</v>
@@ -9125,7 +9129,7 @@
         <v>223</v>
       </c>
       <c r="H49" s="51">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I49" s="51">
         <v>214</v>
@@ -9140,7 +9144,7 @@
         <v>224</v>
       </c>
       <c r="H50" s="51">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="I50" s="51">
         <v>214</v>
@@ -9155,7 +9159,7 @@
         <v>225</v>
       </c>
       <c r="H51" s="51">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I51" s="51">
         <v>214</v>
@@ -9170,7 +9174,7 @@
         <v>226</v>
       </c>
       <c r="H52" s="51">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="I52" s="51">
         <v>214</v>
@@ -9185,7 +9189,7 @@
         <v>227</v>
       </c>
       <c r="H53" s="51">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="I53" s="51">
         <v>214</v>
@@ -9200,7 +9204,7 @@
         <v>228</v>
       </c>
       <c r="H54" s="51">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I54" s="51">
         <v>214</v>
@@ -9215,7 +9219,7 @@
         <v>229</v>
       </c>
       <c r="H55" s="51">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I55" s="51">
         <v>214</v>
@@ -9230,7 +9234,7 @@
         <v>230</v>
       </c>
       <c r="H56" s="51">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I56" s="51">
         <v>214</v>
@@ -9278,7 +9282,7 @@
         <v>224</v>
       </c>
       <c r="H59" s="51">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I59" s="51">
         <v>489</v>
@@ -9322,7 +9326,9 @@
       <c r="G62" t="s">
         <v>227</v>
       </c>
-      <c r="H62" s="51"/>
+      <c r="H62" s="51">
+        <v>1</v>
+      </c>
       <c r="I62" s="51">
         <v>489</v>
       </c>
@@ -9382,7 +9388,7 @@
         <v>222</v>
       </c>
       <c r="H66" s="51">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I66" s="51">
         <v>65</v>
@@ -9397,7 +9403,7 @@
         <v>223</v>
       </c>
       <c r="H67" s="51">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I67" s="51">
         <v>65</v>
@@ -9412,7 +9418,7 @@
         <v>224</v>
       </c>
       <c r="H68" s="51">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I68" s="51">
         <v>65</v>
@@ -9427,7 +9433,7 @@
         <v>225</v>
       </c>
       <c r="H69" s="51">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I69" s="51">
         <v>65</v>
@@ -9442,7 +9448,7 @@
         <v>226</v>
       </c>
       <c r="H70" s="51">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I70" s="51">
         <v>65</v>
@@ -9457,7 +9463,7 @@
         <v>227</v>
       </c>
       <c r="H71" s="51">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I71" s="51">
         <v>65</v>
@@ -9472,7 +9478,7 @@
         <v>228</v>
       </c>
       <c r="H72" s="51">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I72" s="51">
         <v>65</v>
@@ -9487,7 +9493,7 @@
         <v>229</v>
       </c>
       <c r="H73" s="51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I73" s="51">
         <v>65</v>
@@ -9502,7 +9508,7 @@
         <v>230</v>
       </c>
       <c r="H74" s="51">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I74" s="51">
         <v>65</v>
@@ -9520,7 +9526,7 @@
         <v>222</v>
       </c>
       <c r="H75" s="51">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I75" s="51">
         <v>198</v>
@@ -9535,7 +9541,7 @@
         <v>223</v>
       </c>
       <c r="H76">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I76" s="51">
         <v>198</v>
@@ -9550,7 +9556,7 @@
         <v>224</v>
       </c>
       <c r="H77" s="51">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="I77" s="51">
         <v>198</v>
@@ -9565,7 +9571,7 @@
         <v>225</v>
       </c>
       <c r="H78" s="51">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I78" s="51">
         <v>198</v>
@@ -9580,7 +9586,7 @@
         <v>226</v>
       </c>
       <c r="H79" s="51">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="I79" s="51">
         <v>198</v>
@@ -9595,7 +9601,7 @@
         <v>227</v>
       </c>
       <c r="H80" s="51">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="I80" s="51">
         <v>198</v>
@@ -9625,7 +9631,7 @@
         <v>229</v>
       </c>
       <c r="H82" s="51">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I82" s="51">
         <v>198</v>
@@ -9640,7 +9646,7 @@
         <v>230</v>
       </c>
       <c r="H83" s="51">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I83" s="51">
         <v>198</v>
@@ -9658,7 +9664,7 @@
         <v>222</v>
       </c>
       <c r="H84" s="51">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I84" s="51">
         <v>177</v>
@@ -9673,7 +9679,7 @@
         <v>223</v>
       </c>
       <c r="H85" s="51">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I85" s="51">
         <v>177</v>
@@ -9688,7 +9694,7 @@
         <v>224</v>
       </c>
       <c r="H86" s="51">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="I86" s="51">
         <v>177</v>
@@ -9703,7 +9709,7 @@
         <v>225</v>
       </c>
       <c r="H87" s="51">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I87" s="51">
         <v>177</v>
@@ -9718,7 +9724,7 @@
         <v>226</v>
       </c>
       <c r="H88" s="51">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="I88" s="51">
         <v>177</v>
@@ -9733,7 +9739,7 @@
         <v>227</v>
       </c>
       <c r="H89" s="51">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="I89" s="51">
         <v>177</v>
@@ -9748,7 +9754,7 @@
         <v>228</v>
       </c>
       <c r="H90" s="51">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I90" s="51">
         <v>177</v>
@@ -9763,7 +9769,7 @@
         <v>229</v>
       </c>
       <c r="H91" s="51">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I91" s="51">
         <v>177</v>
@@ -9778,7 +9784,7 @@
         <v>230</v>
       </c>
       <c r="H92" s="51">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I92" s="51">
         <v>177</v>
@@ -9796,7 +9802,7 @@
         <v>222</v>
       </c>
       <c r="H93" s="51">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I93" s="51">
         <v>207</v>
@@ -9811,7 +9817,7 @@
         <v>223</v>
       </c>
       <c r="H94" s="51">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I94" s="51">
         <v>207</v>
@@ -9826,7 +9832,7 @@
         <v>224</v>
       </c>
       <c r="H95" s="51">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I95" s="51">
         <v>207</v>
@@ -9841,7 +9847,7 @@
         <v>225</v>
       </c>
       <c r="H96" s="51">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I96" s="51">
         <v>207</v>
@@ -9856,7 +9862,7 @@
         <v>226</v>
       </c>
       <c r="H97" s="51">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="I97" s="51">
         <v>207</v>
@@ -9871,7 +9877,7 @@
         <v>227</v>
       </c>
       <c r="H98" s="51">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="I98" s="51">
         <v>207</v>
@@ -9901,7 +9907,7 @@
         <v>229</v>
       </c>
       <c r="H100" s="51">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I100" s="51">
         <v>207</v>
@@ -9916,7 +9922,7 @@
         <v>230</v>
       </c>
       <c r="H101" s="51">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I101" s="51">
         <v>207</v>
@@ -9934,7 +9940,7 @@
         <v>222</v>
       </c>
       <c r="H102" s="51">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I102" s="51">
         <v>138</v>
@@ -9949,7 +9955,7 @@
         <v>223</v>
       </c>
       <c r="H103" s="51">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="I103" s="51">
         <v>138</v>
@@ -9964,7 +9970,7 @@
         <v>224</v>
       </c>
       <c r="H104" s="51">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="I104" s="51">
         <v>138</v>
@@ -9979,7 +9985,7 @@
         <v>225</v>
       </c>
       <c r="H105" s="51">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I105" s="51">
         <v>138</v>
@@ -9994,7 +10000,7 @@
         <v>226</v>
       </c>
       <c r="H106" s="51">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="I106" s="51">
         <v>138</v>
@@ -10009,7 +10015,7 @@
         <v>227</v>
       </c>
       <c r="H107" s="51">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I107" s="51">
         <v>138</v>
@@ -10024,7 +10030,7 @@
         <v>228</v>
       </c>
       <c r="H108" s="51">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I108" s="51">
         <v>138</v>
@@ -10039,7 +10045,7 @@
         <v>229</v>
       </c>
       <c r="H109" s="51">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I109" s="51">
         <v>138</v>
@@ -10054,7 +10060,7 @@
         <v>230</v>
       </c>
       <c r="H110" s="51">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I110" s="51">
         <v>138</v>
@@ -10072,7 +10078,7 @@
         <v>222</v>
       </c>
       <c r="H111" s="51">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="I111" s="51">
         <v>227</v>
@@ -10087,7 +10093,7 @@
         <v>223</v>
       </c>
       <c r="H112" s="51">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="I112" s="51">
         <v>227</v>
@@ -10102,7 +10108,7 @@
         <v>224</v>
       </c>
       <c r="H113" s="51">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="I113" s="51">
         <v>227</v>
@@ -10117,7 +10123,7 @@
         <v>225</v>
       </c>
       <c r="H114" s="51">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="I114" s="51">
         <v>227</v>
@@ -10132,7 +10138,7 @@
         <v>226</v>
       </c>
       <c r="H115" s="51">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="I115" s="51">
         <v>227</v>
@@ -10147,7 +10153,7 @@
         <v>227</v>
       </c>
       <c r="H116">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="I116" s="51">
         <v>227</v>
@@ -10162,7 +10168,7 @@
         <v>228</v>
       </c>
       <c r="H117" s="51">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I117" s="51">
         <v>227</v>
@@ -10177,7 +10183,7 @@
         <v>229</v>
       </c>
       <c r="H118" s="51">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I118" s="51">
         <v>227</v>
@@ -10210,7 +10216,7 @@
         <v>222</v>
       </c>
       <c r="H120" s="51">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="I120" s="51">
         <v>170</v>
@@ -10225,7 +10231,7 @@
         <v>223</v>
       </c>
       <c r="H121" s="51">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I121" s="51">
         <v>170</v>
@@ -10240,7 +10246,7 @@
         <v>224</v>
       </c>
       <c r="H122" s="51">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="I122" s="51">
         <v>170</v>
@@ -10255,7 +10261,7 @@
         <v>225</v>
       </c>
       <c r="H123" s="51">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I123" s="51">
         <v>170</v>
@@ -10270,7 +10276,7 @@
         <v>226</v>
       </c>
       <c r="H124">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="I124" s="51">
         <v>170</v>
@@ -10285,7 +10291,7 @@
         <v>227</v>
       </c>
       <c r="H125" s="51">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="I125" s="51">
         <v>170</v>
@@ -10300,7 +10306,7 @@
         <v>228</v>
       </c>
       <c r="H126" s="51">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I126" s="51">
         <v>170</v>
@@ -10315,7 +10321,7 @@
         <v>229</v>
       </c>
       <c r="H127" s="51">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I127" s="51">
         <v>170</v>
@@ -10330,7 +10336,7 @@
         <v>230</v>
       </c>
       <c r="H128" s="51">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I128" s="51">
         <v>170</v>
@@ -10348,7 +10354,7 @@
         <v>222</v>
       </c>
       <c r="H129" s="51">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I129" s="51">
         <v>72</v>
@@ -10363,7 +10369,7 @@
         <v>223</v>
       </c>
       <c r="H130" s="51">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I130" s="51">
         <v>72</v>
@@ -10378,7 +10384,7 @@
         <v>224</v>
       </c>
       <c r="H131" s="51">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I131" s="51">
         <v>72</v>
@@ -10393,7 +10399,7 @@
         <v>225</v>
       </c>
       <c r="H132" s="51">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I132" s="51">
         <v>72</v>
@@ -10408,7 +10414,7 @@
         <v>226</v>
       </c>
       <c r="H133" s="51">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="I133" s="51">
         <v>72</v>
@@ -10423,7 +10429,7 @@
         <v>227</v>
       </c>
       <c r="H134" s="51">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I134" s="51">
         <v>72</v>
@@ -10438,7 +10444,7 @@
         <v>228</v>
       </c>
       <c r="H135" s="51">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I135" s="51">
         <v>72</v>
@@ -10453,7 +10459,7 @@
         <v>229</v>
       </c>
       <c r="H136" s="51">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I136" s="51">
         <v>72</v>
@@ -10468,7 +10474,7 @@
         <v>230</v>
       </c>
       <c r="H137" s="51">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I137" s="51">
         <v>72</v>
@@ -10486,7 +10492,7 @@
         <v>222</v>
       </c>
       <c r="H138" s="51">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="I138" s="51">
         <v>160</v>
@@ -10501,7 +10507,7 @@
         <v>223</v>
       </c>
       <c r="H139" s="51">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I139" s="51">
         <v>160</v>
@@ -10516,7 +10522,7 @@
         <v>224</v>
       </c>
       <c r="H140">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="I140" s="51">
         <v>160</v>
@@ -10531,7 +10537,7 @@
         <v>225</v>
       </c>
       <c r="H141" s="51">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="I141" s="51">
         <v>160</v>
@@ -10546,7 +10552,7 @@
         <v>226</v>
       </c>
       <c r="H142" s="51">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="I142" s="51">
         <v>160</v>
@@ -10561,7 +10567,7 @@
         <v>227</v>
       </c>
       <c r="H143" s="51">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I143" s="51">
         <v>160</v>
@@ -10576,7 +10582,7 @@
         <v>228</v>
       </c>
       <c r="H144" s="51">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I144" s="51">
         <v>160</v>
@@ -10591,7 +10597,7 @@
         <v>229</v>
       </c>
       <c r="H145" s="51">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I145" s="51">
         <v>160</v>
@@ -10606,7 +10612,7 @@
         <v>230</v>
       </c>
       <c r="H146" s="51">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I146" s="51">
         <v>160</v>
@@ -10624,7 +10630,7 @@
         <v>222</v>
       </c>
       <c r="H147" s="51">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I147" s="51">
         <v>178</v>
@@ -10639,7 +10645,7 @@
         <v>223</v>
       </c>
       <c r="H148">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I148" s="51">
         <v>178</v>
@@ -10654,7 +10660,7 @@
         <v>224</v>
       </c>
       <c r="H149" s="51">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="I149" s="51">
         <v>178</v>
@@ -10669,7 +10675,7 @@
         <v>225</v>
       </c>
       <c r="H150" s="51">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I150" s="51">
         <v>178</v>
@@ -10684,7 +10690,7 @@
         <v>226</v>
       </c>
       <c r="H151" s="51">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="I151" s="51">
         <v>178</v>
@@ -10699,7 +10705,7 @@
         <v>227</v>
       </c>
       <c r="H152" s="51">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="I152" s="51">
         <v>178</v>
@@ -10744,7 +10750,7 @@
         <v>230</v>
       </c>
       <c r="H155" s="51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I155" s="51">
         <v>178</v>
@@ -10792,7 +10798,7 @@
         <v>224</v>
       </c>
       <c r="H158" s="51">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I158" s="51">
         <v>172</v>
@@ -11038,7 +11044,7 @@
         <v>222</v>
       </c>
       <c r="H174" s="51">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I174" s="51">
         <v>140</v>
@@ -11053,7 +11059,7 @@
         <v>223</v>
       </c>
       <c r="H175" s="51">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I175" s="51">
         <v>140</v>
@@ -11068,7 +11074,7 @@
         <v>224</v>
       </c>
       <c r="H176" s="51">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I176" s="51">
         <v>140</v>
@@ -11098,7 +11104,7 @@
         <v>226</v>
       </c>
       <c r="H178" s="51">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="I178" s="51">
         <v>140</v>
@@ -11113,7 +11119,7 @@
         <v>227</v>
       </c>
       <c r="H179" s="51">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="I179" s="51">
         <v>140</v>
@@ -11128,7 +11134,7 @@
         <v>228</v>
       </c>
       <c r="H180">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I180" s="51">
         <v>140</v>
@@ -11176,7 +11182,7 @@
         <v>222</v>
       </c>
       <c r="H183" s="51">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I183" s="51">
         <v>168</v>
@@ -11191,7 +11197,7 @@
         <v>223</v>
       </c>
       <c r="H184" s="51">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I184" s="51">
         <v>168</v>
@@ -11206,7 +11212,7 @@
         <v>224</v>
       </c>
       <c r="H185" s="51">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I185" s="51">
         <v>168</v>
@@ -11221,7 +11227,7 @@
         <v>225</v>
       </c>
       <c r="H186">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I186" s="51">
         <v>168</v>
@@ -11236,7 +11242,7 @@
         <v>226</v>
       </c>
       <c r="H187" s="51">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="I187" s="51">
         <v>168</v>
@@ -11251,7 +11257,7 @@
         <v>227</v>
       </c>
       <c r="H188" s="51">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="I188" s="51">
         <v>168</v>
@@ -11266,7 +11272,7 @@
         <v>228</v>
       </c>
       <c r="H189" s="51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I189" s="51">
         <v>168</v>
@@ -11281,7 +11287,7 @@
         <v>229</v>
       </c>
       <c r="H190" s="51">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I190" s="51">
         <v>168</v>
@@ -11296,7 +11302,7 @@
         <v>230</v>
       </c>
       <c r="H191" s="51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I191" s="51">
         <v>168</v>
@@ -11314,7 +11320,7 @@
         <v>222</v>
       </c>
       <c r="H192" s="51">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I192" s="51">
         <v>170</v>
@@ -11329,7 +11335,7 @@
         <v>223</v>
       </c>
       <c r="H193" s="51">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I193" s="51">
         <v>170</v>
@@ -11344,7 +11350,7 @@
         <v>224</v>
       </c>
       <c r="H194" s="51">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="I194" s="51">
         <v>170</v>
@@ -11359,7 +11365,7 @@
         <v>225</v>
       </c>
       <c r="H195" s="51">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I195" s="51">
         <v>170</v>
@@ -11374,7 +11380,7 @@
         <v>226</v>
       </c>
       <c r="H196">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="I196" s="51">
         <v>170</v>
@@ -11389,7 +11395,7 @@
         <v>227</v>
       </c>
       <c r="H197" s="51">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="I197" s="51">
         <v>170</v>
@@ -11419,7 +11425,7 @@
         <v>229</v>
       </c>
       <c r="H199" s="51">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I199" s="51">
         <v>170</v>
@@ -11434,7 +11440,7 @@
         <v>230</v>
       </c>
       <c r="H200" s="51">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I200" s="51">
         <v>170</v>
@@ -11538,7 +11544,7 @@
         <v>228</v>
       </c>
       <c r="H207" s="51">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I207" s="51">
         <v>139</v>
@@ -11582,7 +11588,7 @@
         <v>222</v>
       </c>
       <c r="H210" s="51">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I210" s="51">
         <v>161</v>
@@ -11597,7 +11603,7 @@
         <v>223</v>
       </c>
       <c r="H211" s="51">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I211" s="51">
         <v>161</v>
@@ -11612,7 +11618,7 @@
         <v>224</v>
       </c>
       <c r="H212">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="I212" s="51">
         <v>161</v>
@@ -11627,7 +11633,7 @@
         <v>225</v>
       </c>
       <c r="H213" s="51">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="I213" s="51">
         <v>161</v>
@@ -11642,7 +11648,7 @@
         <v>226</v>
       </c>
       <c r="H214" s="51">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="I214" s="51">
         <v>161</v>
@@ -11657,7 +11663,7 @@
         <v>227</v>
       </c>
       <c r="H215" s="51">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="I215" s="51">
         <v>161</v>
@@ -11672,7 +11678,7 @@
         <v>228</v>
       </c>
       <c r="H216" s="51">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I216" s="51">
         <v>161</v>
@@ -11687,7 +11693,7 @@
         <v>229</v>
       </c>
       <c r="H217" s="51">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I217" s="51">
         <v>161</v>
@@ -11702,7 +11708,7 @@
         <v>230</v>
       </c>
       <c r="H218" s="51">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I218" s="51">
         <v>161</v>
@@ -11720,10 +11726,10 @@
         <v>222</v>
       </c>
       <c r="H219" s="51">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I219" s="51">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="220" spans="5:9" x14ac:dyDescent="0.25">
@@ -11735,10 +11741,10 @@
         <v>223</v>
       </c>
       <c r="H220" s="51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I220" s="51">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="221" spans="5:9" x14ac:dyDescent="0.25">
@@ -11750,10 +11756,10 @@
         <v>224</v>
       </c>
       <c r="H221" s="51">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I221" s="51">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="222" spans="5:9" x14ac:dyDescent="0.25">
@@ -11765,10 +11771,10 @@
         <v>225</v>
       </c>
       <c r="H222" s="51">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I222" s="51">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="223" spans="5:9" x14ac:dyDescent="0.25">
@@ -11780,10 +11786,10 @@
         <v>226</v>
       </c>
       <c r="H223" s="51">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I223" s="51">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="224" spans="5:9" x14ac:dyDescent="0.25">
@@ -11795,10 +11801,10 @@
         <v>227</v>
       </c>
       <c r="H224" s="51">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I224" s="51">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="225" spans="5:9" x14ac:dyDescent="0.25">
@@ -11810,10 +11816,10 @@
         <v>228</v>
       </c>
       <c r="H225" s="51">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I225" s="51">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="226" spans="5:9" x14ac:dyDescent="0.25">
@@ -11828,7 +11834,7 @@
         <v>8</v>
       </c>
       <c r="I226" s="51">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="227" spans="5:9" x14ac:dyDescent="0.25">
@@ -11840,10 +11846,10 @@
         <v>230</v>
       </c>
       <c r="H227" s="51">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I227" s="51">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="228" spans="5:9" x14ac:dyDescent="0.25">
@@ -11858,7 +11864,7 @@
         <v>222</v>
       </c>
       <c r="H228" s="51">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I228" s="51">
         <v>172</v>
@@ -11873,7 +11879,7 @@
         <v>223</v>
       </c>
       <c r="H229" s="51">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I229" s="51">
         <v>172</v>
@@ -11888,7 +11894,7 @@
         <v>224</v>
       </c>
       <c r="H230" s="51">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="I230" s="51">
         <v>172</v>
@@ -11903,7 +11909,7 @@
         <v>225</v>
       </c>
       <c r="H231" s="51">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I231" s="51">
         <v>172</v>
@@ -11918,7 +11924,7 @@
         <v>226</v>
       </c>
       <c r="H232" s="51">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I232" s="51">
         <v>172</v>
@@ -11933,7 +11939,7 @@
         <v>227</v>
       </c>
       <c r="H233" s="51">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I233" s="51">
         <v>172</v>
@@ -11948,7 +11954,7 @@
         <v>228</v>
       </c>
       <c r="H234" s="51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I234" s="51">
         <v>172</v>
@@ -11963,7 +11969,7 @@
         <v>229</v>
       </c>
       <c r="H235" s="51">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I235" s="51">
         <v>172</v>
@@ -11978,7 +11984,7 @@
         <v>230</v>
       </c>
       <c r="H236">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I236" s="51">
         <v>172</v>
@@ -11996,10 +12002,10 @@
         <v>222</v>
       </c>
       <c r="H237" s="51">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I237" s="51">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="238" spans="5:9" x14ac:dyDescent="0.25">
@@ -12014,7 +12020,7 @@
         <v>6</v>
       </c>
       <c r="I238" s="51">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="239" spans="5:9" x14ac:dyDescent="0.25">
@@ -12026,10 +12032,10 @@
         <v>224</v>
       </c>
       <c r="H239" s="51">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="I239" s="51">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="240" spans="5:9" x14ac:dyDescent="0.25">
@@ -12041,10 +12047,10 @@
         <v>225</v>
       </c>
       <c r="H240" s="51">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I240" s="51">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="241" spans="5:9" x14ac:dyDescent="0.25">
@@ -12056,10 +12062,10 @@
         <v>226</v>
       </c>
       <c r="H241" s="51">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="I241" s="51">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="242" spans="5:9" x14ac:dyDescent="0.25">
@@ -12071,10 +12077,10 @@
         <v>227</v>
       </c>
       <c r="H242" s="51">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I242" s="51">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="243" spans="5:9" x14ac:dyDescent="0.25">
@@ -12086,10 +12092,10 @@
         <v>228</v>
       </c>
       <c r="H243" s="51">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I243" s="51">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="244" spans="5:9" x14ac:dyDescent="0.25">
@@ -12101,10 +12107,10 @@
         <v>229</v>
       </c>
       <c r="H244">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I244" s="51">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="245" spans="5:9" x14ac:dyDescent="0.25">
@@ -12116,10 +12122,10 @@
         <v>230</v>
       </c>
       <c r="H245" s="51">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I245" s="51">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="246" spans="5:9" x14ac:dyDescent="0.25">
@@ -12134,7 +12140,7 @@
         <v>222</v>
       </c>
       <c r="H246" s="51">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I246" s="51">
         <v>142</v>
@@ -12164,7 +12170,7 @@
         <v>224</v>
       </c>
       <c r="H248" s="51">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I248" s="51">
         <v>142</v>
@@ -12179,7 +12185,7 @@
         <v>225</v>
       </c>
       <c r="H249" s="51">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I249" s="51">
         <v>142</v>
@@ -12194,7 +12200,7 @@
         <v>226</v>
       </c>
       <c r="H250" s="51">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="I250" s="51">
         <v>142</v>
@@ -12209,7 +12215,7 @@
         <v>227</v>
       </c>
       <c r="H251" s="51">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I251" s="51">
         <v>142</v>
@@ -12224,7 +12230,7 @@
         <v>228</v>
       </c>
       <c r="H252">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I252" s="51">
         <v>142</v>
@@ -12239,7 +12245,7 @@
         <v>229</v>
       </c>
       <c r="H253" s="51">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I253" s="51">
         <v>142</v>
@@ -12254,7 +12260,7 @@
         <v>230</v>
       </c>
       <c r="H254" s="51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I254" s="51">
         <v>142</v>
@@ -12272,7 +12278,7 @@
         <v>222</v>
       </c>
       <c r="H255" s="51">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I255" s="51">
         <v>182</v>
@@ -12287,7 +12293,7 @@
         <v>223</v>
       </c>
       <c r="H256" s="51">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I256" s="51">
         <v>182</v>
@@ -12302,7 +12308,7 @@
         <v>224</v>
       </c>
       <c r="H257" s="51">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I257" s="51">
         <v>182</v>
@@ -12317,7 +12323,7 @@
         <v>225</v>
       </c>
       <c r="H258">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I258" s="51">
         <v>182</v>
@@ -12332,7 +12338,7 @@
         <v>226</v>
       </c>
       <c r="H259" s="51">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I259" s="51">
         <v>182</v>
@@ -12347,7 +12353,7 @@
         <v>227</v>
       </c>
       <c r="H260">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I260" s="51">
         <v>182</v>
@@ -12362,7 +12368,7 @@
         <v>228</v>
       </c>
       <c r="H261" s="51">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I261" s="51">
         <v>182</v>
@@ -12377,7 +12383,7 @@
         <v>229</v>
       </c>
       <c r="H262" s="51">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I262" s="51">
         <v>182</v>
@@ -12392,7 +12398,7 @@
         <v>230</v>
       </c>
       <c r="H263" s="51">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I263" s="51">
         <v>182</v>
@@ -12410,7 +12416,7 @@
         <v>222</v>
       </c>
       <c r="H264" s="51">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I264" s="51">
         <v>249</v>
@@ -12425,7 +12431,7 @@
         <v>223</v>
       </c>
       <c r="H265">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I265" s="51">
         <v>249</v>
@@ -12440,7 +12446,7 @@
         <v>224</v>
       </c>
       <c r="H266" s="51">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I266" s="51">
         <v>249</v>
@@ -12455,7 +12461,7 @@
         <v>225</v>
       </c>
       <c r="H267" s="51">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I267" s="51">
         <v>249</v>
@@ -12470,7 +12476,7 @@
         <v>226</v>
       </c>
       <c r="H268">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="I268" s="51">
         <v>249</v>
@@ -12485,7 +12491,7 @@
         <v>227</v>
       </c>
       <c r="H269" s="51">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I269" s="51">
         <v>249</v>
@@ -12500,7 +12506,7 @@
         <v>228</v>
       </c>
       <c r="H270" s="51">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I270" s="51">
         <v>249</v>
@@ -12515,7 +12521,7 @@
         <v>229</v>
       </c>
       <c r="H271" s="51">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I271" s="51">
         <v>249</v>
@@ -12791,7 +12797,7 @@
         <v>222</v>
       </c>
       <c r="H291">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I291" s="51">
         <v>169</v>
@@ -12806,7 +12812,7 @@
         <v>223</v>
       </c>
       <c r="H292">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I292" s="51">
         <v>169</v>
@@ -12821,7 +12827,7 @@
         <v>224</v>
       </c>
       <c r="H293">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="I293" s="51">
         <v>169</v>
@@ -12836,7 +12842,7 @@
         <v>225</v>
       </c>
       <c r="H294">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I294" s="51">
         <v>169</v>
@@ -12851,7 +12857,7 @@
         <v>226</v>
       </c>
       <c r="H295">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="I295" s="51">
         <v>169</v>
@@ -12866,7 +12872,7 @@
         <v>227</v>
       </c>
       <c r="H296">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="I296" s="51">
         <v>169</v>
@@ -12881,7 +12887,7 @@
         <v>228</v>
       </c>
       <c r="H297" s="51">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I297" s="51">
         <v>169</v>
@@ -12896,7 +12902,7 @@
         <v>229</v>
       </c>
       <c r="H298">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I298" s="51">
         <v>169</v>
@@ -12911,7 +12917,7 @@
         <v>230</v>
       </c>
       <c r="H299" s="51">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I299" s="51">
         <v>169</v>
@@ -13067,7 +13073,7 @@
         <v>222</v>
       </c>
       <c r="H309">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="I309" s="51">
         <v>260</v>
@@ -13082,7 +13088,7 @@
         <v>223</v>
       </c>
       <c r="H310">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I310" s="51">
         <v>260</v>
@@ -13097,7 +13103,7 @@
         <v>224</v>
       </c>
       <c r="H311">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="I311" s="51">
         <v>260</v>
@@ -13112,7 +13118,7 @@
         <v>225</v>
       </c>
       <c r="H312">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I312" s="51">
         <v>260</v>
@@ -13127,7 +13133,7 @@
         <v>226</v>
       </c>
       <c r="H313">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="I313" s="51">
         <v>260</v>
@@ -13142,7 +13148,7 @@
         <v>227</v>
       </c>
       <c r="H314">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="I314" s="51">
         <v>260</v>
@@ -13157,7 +13163,7 @@
         <v>228</v>
       </c>
       <c r="H315" s="51">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="I315" s="51">
         <v>260</v>
@@ -13172,7 +13178,7 @@
         <v>229</v>
       </c>
       <c r="H316">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I316" s="51">
         <v>260</v>
@@ -13187,7 +13193,7 @@
         <v>230</v>
       </c>
       <c r="H317" s="51">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I317" s="51">
         <v>260</v>
@@ -13220,7 +13226,7 @@
         <v>223</v>
       </c>
       <c r="H319" s="51">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I319" s="51">
         <v>101</v>
@@ -13286,7 +13292,7 @@
         <v>228</v>
       </c>
       <c r="H324" s="51">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I324" s="51">
         <v>101</v>
@@ -13342,7 +13348,7 @@
         <v>223</v>
       </c>
       <c r="H328">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I328" s="51">
         <v>105</v>
@@ -13407,7 +13413,7 @@
         <v>228</v>
       </c>
       <c r="H333" s="51">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I333" s="51">
         <v>105</v>
@@ -13451,7 +13457,7 @@
         <v>222</v>
       </c>
       <c r="H336" s="51">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I336" s="51">
         <v>202</v>
@@ -13466,7 +13472,7 @@
         <v>223</v>
       </c>
       <c r="H337" s="51">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I337" s="51">
         <v>202</v>
@@ -13481,7 +13487,7 @@
         <v>224</v>
       </c>
       <c r="H338" s="51">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I338" s="51">
         <v>202</v>
@@ -13496,7 +13502,7 @@
         <v>225</v>
       </c>
       <c r="H339" s="51">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I339" s="51">
         <v>202</v>
@@ -13511,7 +13517,7 @@
         <v>226</v>
       </c>
       <c r="H340">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="I340" s="51">
         <v>202</v>
@@ -13526,7 +13532,7 @@
         <v>227</v>
       </c>
       <c r="H341" s="51">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I341" s="51">
         <v>202</v>
@@ -13541,7 +13547,7 @@
         <v>228</v>
       </c>
       <c r="H342" s="51">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I342" s="51">
         <v>202</v>
@@ -13589,7 +13595,7 @@
         <v>222</v>
       </c>
       <c r="H345">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I345" s="51">
         <v>198</v>
@@ -13619,7 +13625,7 @@
         <v>224</v>
       </c>
       <c r="H347" s="51">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="I347" s="51">
         <v>198</v>
@@ -13634,7 +13640,7 @@
         <v>225</v>
       </c>
       <c r="H348">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I348" s="51">
         <v>198</v>
@@ -13649,7 +13655,7 @@
         <v>226</v>
       </c>
       <c r="H349" s="51">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="I349" s="51">
         <v>198</v>
@@ -13664,7 +13670,7 @@
         <v>227</v>
       </c>
       <c r="H350" s="51">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I350" s="51">
         <v>198</v>
@@ -13679,7 +13685,7 @@
         <v>228</v>
       </c>
       <c r="H351" s="51">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I351" s="51">
         <v>198</v>
@@ -13694,7 +13700,7 @@
         <v>229</v>
       </c>
       <c r="H352">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I352" s="51">
         <v>198</v>
@@ -13709,7 +13715,7 @@
         <v>230</v>
       </c>
       <c r="H353" s="51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I353" s="51">
         <v>198</v>
@@ -13739,7 +13745,9 @@
       <c r="G355" t="s">
         <v>223</v>
       </c>
-      <c r="H355" s="51"/>
+      <c r="H355" s="51">
+        <v>1</v>
+      </c>
       <c r="I355" s="51">
         <v>104</v>
       </c>
@@ -13805,7 +13813,7 @@
         <v>228</v>
       </c>
       <c r="H360" s="51">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I360" s="51">
         <v>104</v>
@@ -13848,7 +13856,9 @@
       <c r="G363" t="s">
         <v>222</v>
       </c>
-      <c r="H363" s="51"/>
+      <c r="H363" s="51">
+        <v>1</v>
+      </c>
       <c r="I363" s="51">
         <v>120</v>
       </c>
@@ -13861,7 +13871,9 @@
       <c r="G364" t="s">
         <v>223</v>
       </c>
-      <c r="H364" s="51"/>
+      <c r="H364" s="51">
+        <v>8</v>
+      </c>
       <c r="I364" s="51">
         <v>120</v>
       </c>
@@ -13874,7 +13886,9 @@
       <c r="G365" t="s">
         <v>224</v>
       </c>
-      <c r="H365" s="51"/>
+      <c r="H365" s="51">
+        <v>5</v>
+      </c>
       <c r="I365" s="51">
         <v>120</v>
       </c>
@@ -13887,7 +13901,9 @@
       <c r="G366" t="s">
         <v>225</v>
       </c>
-      <c r="H366" s="51"/>
+      <c r="H366" s="51">
+        <v>11</v>
+      </c>
       <c r="I366" s="51">
         <v>120</v>
       </c>
@@ -13900,7 +13916,9 @@
       <c r="G367" t="s">
         <v>226</v>
       </c>
-      <c r="H367" s="51"/>
+      <c r="H367" s="51">
+        <v>12</v>
+      </c>
       <c r="I367" s="51">
         <v>120</v>
       </c>
@@ -13913,7 +13931,9 @@
       <c r="G368" t="s">
         <v>227</v>
       </c>
-      <c r="H368" s="51"/>
+      <c r="H368" s="51">
+        <v>13</v>
+      </c>
       <c r="I368" s="51">
         <v>120</v>
       </c>
@@ -13926,7 +13946,9 @@
       <c r="G369" t="s">
         <v>228</v>
       </c>
-      <c r="H369" s="51"/>
+      <c r="H369" s="51">
+        <v>1</v>
+      </c>
       <c r="I369" s="51">
         <v>120</v>
       </c>
@@ -13939,7 +13961,9 @@
       <c r="G370" t="s">
         <v>229</v>
       </c>
-      <c r="H370" s="51"/>
+      <c r="H370" s="51">
+        <v>1</v>
+      </c>
       <c r="I370" s="51">
         <v>120</v>
       </c>
@@ -13952,7 +13976,9 @@
       <c r="G371" t="s">
         <v>230</v>
       </c>
-      <c r="H371" s="35"/>
+      <c r="H371" s="35">
+        <v>1</v>
+      </c>
       <c r="I371" s="35">
         <v>120</v>
       </c>
@@ -13969,10 +13995,10 @@
         <v>222</v>
       </c>
       <c r="H372">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I372">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="373" spans="5:9" x14ac:dyDescent="0.25">
@@ -13983,8 +14009,11 @@
       <c r="G373" t="s">
         <v>223</v>
       </c>
+      <c r="H373">
+        <v>7</v>
+      </c>
       <c r="I373">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="374" spans="5:9" x14ac:dyDescent="0.25">
@@ -13995,8 +14024,11 @@
       <c r="G374" t="s">
         <v>224</v>
       </c>
+      <c r="H374">
+        <v>6</v>
+      </c>
       <c r="I374">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="375" spans="5:9" x14ac:dyDescent="0.25">
@@ -14007,8 +14039,11 @@
       <c r="G375" t="s">
         <v>225</v>
       </c>
+      <c r="H375">
+        <v>8</v>
+      </c>
       <c r="I375">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="376" spans="5:9" x14ac:dyDescent="0.25">
@@ -14019,8 +14054,11 @@
       <c r="G376" t="s">
         <v>226</v>
       </c>
+      <c r="H376">
+        <v>8</v>
+      </c>
       <c r="I376">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="377" spans="5:9" x14ac:dyDescent="0.25">
@@ -14031,8 +14069,11 @@
       <c r="G377" t="s">
         <v>227</v>
       </c>
+      <c r="H377">
+        <v>8</v>
+      </c>
       <c r="I377">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="378" spans="5:9" x14ac:dyDescent="0.25">
@@ -14043,8 +14084,11 @@
       <c r="G378" t="s">
         <v>228</v>
       </c>
+      <c r="H378">
+        <v>5</v>
+      </c>
       <c r="I378">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="379" spans="5:9" x14ac:dyDescent="0.25">
@@ -14055,8 +14099,11 @@
       <c r="G379" t="s">
         <v>229</v>
       </c>
+      <c r="H379">
+        <v>1</v>
+      </c>
       <c r="I379">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="380" spans="5:9" x14ac:dyDescent="0.25">
@@ -14067,8 +14114,11 @@
       <c r="G380" t="s">
         <v>230</v>
       </c>
+      <c r="H380">
+        <v>2</v>
+      </c>
       <c r="I380">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="381" spans="5:9" x14ac:dyDescent="0.25">
@@ -14083,7 +14133,7 @@
         <v>222</v>
       </c>
       <c r="H381">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I381">
         <v>113</v>
@@ -14110,7 +14160,7 @@
         <v>224</v>
       </c>
       <c r="H383">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I383">
         <v>113</v>
@@ -14124,6 +14174,9 @@
       <c r="G384" t="s">
         <v>225</v>
       </c>
+      <c r="H384">
+        <v>1</v>
+      </c>
       <c r="I384">
         <v>113</v>
       </c>
@@ -14137,7 +14190,7 @@
         <v>226</v>
       </c>
       <c r="H385">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I385">
         <v>113</v>
@@ -14152,7 +14205,7 @@
         <v>227</v>
       </c>
       <c r="H386">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I386">
         <v>113</v>
@@ -14167,7 +14220,7 @@
         <v>228</v>
       </c>
       <c r="H387">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I387">
         <v>113</v>
@@ -14193,6 +14246,9 @@
       <c r="G389" t="s">
         <v>230</v>
       </c>
+      <c r="H389">
+        <v>1</v>
+      </c>
       <c r="I389">
         <v>113</v>
       </c>
@@ -14209,7 +14265,7 @@
         <v>222</v>
       </c>
       <c r="H390">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I390">
         <v>195</v>
@@ -14239,7 +14295,7 @@
         <v>224</v>
       </c>
       <c r="H392">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="I392">
         <v>195</v>
@@ -14254,7 +14310,7 @@
         <v>225</v>
       </c>
       <c r="H393">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I393">
         <v>195</v>
@@ -14269,7 +14325,7 @@
         <v>226</v>
       </c>
       <c r="H394">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="I394">
         <v>195</v>
@@ -14284,7 +14340,7 @@
         <v>227</v>
       </c>
       <c r="H395">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I395">
         <v>195</v>
@@ -14329,7 +14385,7 @@
         <v>230</v>
       </c>
       <c r="H398">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I398">
         <v>195</v>
@@ -14347,7 +14403,7 @@
         <v>222</v>
       </c>
       <c r="H399">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I399">
         <v>161</v>
@@ -14362,7 +14418,7 @@
         <v>223</v>
       </c>
       <c r="H400">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="I400">
         <v>161</v>
@@ -14377,7 +14433,7 @@
         <v>224</v>
       </c>
       <c r="H401">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="I401">
         <v>161</v>
@@ -14392,7 +14448,7 @@
         <v>225</v>
       </c>
       <c r="H402">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I402">
         <v>161</v>
@@ -14407,7 +14463,7 @@
         <v>226</v>
       </c>
       <c r="H403">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="I403">
         <v>161</v>
@@ -14422,7 +14478,7 @@
         <v>227</v>
       </c>
       <c r="H404">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="I404">
         <v>161</v>
@@ -14437,7 +14493,7 @@
         <v>228</v>
       </c>
       <c r="H405">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I405">
         <v>161</v>
@@ -14452,7 +14508,7 @@
         <v>229</v>
       </c>
       <c r="H406">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I406">
         <v>161</v>
@@ -14467,7 +14523,7 @@
         <v>230</v>
       </c>
       <c r="H407">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I407">
         <v>161</v>

--- a/data/ventas.xlsx
+++ b/data/ventas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cesar\Desktop\Reportes Ventas Rap\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6B7F95CC-75A4-4989-8061-4EFEBCB32D3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4280214F-A38A-482A-AB9D-CA7830ADA495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2534,22 +2534,22 @@
         <v>0</v>
       </c>
       <c r="C2" s="96">
-        <v>25611.065696433299</v>
+        <v>30050.344867064101</v>
       </c>
       <c r="D2" s="96">
-        <v>126133.20713944281</v>
+        <v>151749.4632585053</v>
       </c>
       <c r="E2" s="96">
-        <v>434907848.11576813</v>
+        <v>507558440.84656405</v>
       </c>
       <c r="F2" s="96">
         <v>0</v>
       </c>
       <c r="G2" s="96">
-        <v>250001.682277908</v>
+        <v>264552.02407153812</v>
       </c>
       <c r="H2" s="96">
-        <v>250001.75</v>
+        <v>264552.11</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -2560,22 +2560,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="96">
-        <v>363.88285091659998</v>
+        <v>393.20745409130001</v>
       </c>
       <c r="D3" s="96">
-        <v>718.55759094129996</v>
+        <v>738.55759094179996</v>
       </c>
       <c r="E3" s="96">
-        <v>8333389.4092635857</v>
+        <v>8818400.8023845814</v>
       </c>
       <c r="F3" s="96">
         <v>0</v>
       </c>
       <c r="G3" s="96">
-        <v>250001.682277908</v>
+        <v>264552.02407153812</v>
       </c>
       <c r="H3" s="96">
-        <v>250001.75</v>
+        <v>264552.11</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2586,13 +2586,13 @@
         <v>1</v>
       </c>
       <c r="C4" s="96">
-        <v>195.03998809379999</v>
+        <v>215.3798690461</v>
       </c>
       <c r="D4" s="96">
-        <v>402.48999999900002</v>
+        <v>429.50910714399998</v>
       </c>
       <c r="E4" s="96">
-        <v>5940437.3079375168</v>
+        <v>6449843.5922434218</v>
       </c>
       <c r="F4" s="96">
         <v>0</v>
@@ -2612,13 +2612,13 @@
         <v>1</v>
       </c>
       <c r="C5" s="96">
-        <v>264.28033730039999</v>
+        <v>287.8868849191</v>
       </c>
       <c r="D5" s="96">
-        <v>1028.4771071376999</v>
+        <v>1084.9771071369</v>
       </c>
       <c r="E5" s="96">
-        <v>5899873.0951455031</v>
+        <v>6596329.3614597432</v>
       </c>
       <c r="F5" s="96">
         <v>0</v>
@@ -2638,13 +2638,13 @@
         <v>1</v>
       </c>
       <c r="C6" s="96">
-        <v>504.5438492056</v>
+        <v>623.45456349139999</v>
       </c>
       <c r="D6" s="96">
-        <v>1468.7514881038001</v>
+        <v>1736.7514881101999</v>
       </c>
       <c r="E6" s="96">
-        <v>10378829.479285927</v>
+        <v>13014610.776669662</v>
       </c>
       <c r="F6" s="96">
         <v>0</v>
@@ -2664,13 +2664,13 @@
         <v>1</v>
       </c>
       <c r="C7" s="96">
-        <v>527.00327380809995</v>
+        <v>596.52415476040005</v>
       </c>
       <c r="D7" s="96">
-        <v>1735.0909999968001</v>
+        <v>1890.2880833329</v>
       </c>
       <c r="E7" s="96">
-        <v>10363253.207426563</v>
+        <v>11328941.073388485</v>
       </c>
       <c r="F7" s="96">
         <v>0</v>
@@ -2690,13 +2690,13 @@
         <v>1</v>
       </c>
       <c r="C8" s="96">
-        <v>2207.1115740741998</v>
+        <v>2267.1115740741998</v>
       </c>
       <c r="D8" s="96">
         <v>2600.9464768541998</v>
       </c>
       <c r="E8" s="96">
-        <v>26700664.115582384</v>
+        <v>28341762.515582383</v>
       </c>
       <c r="F8" s="96">
         <v>0</v>
@@ -2716,13 +2716,13 @@
         <v>1</v>
       </c>
       <c r="C9" s="96">
-        <v>269.37525793629999</v>
+        <v>318.65723412649999</v>
       </c>
       <c r="D9" s="96">
-        <v>1238.1587500005</v>
+        <v>1452.5929166666999</v>
       </c>
       <c r="E9" s="96">
-        <v>4840096.3237659615</v>
+        <v>5878949.2572204797</v>
       </c>
       <c r="F9" s="96">
         <v>0</v>
@@ -2742,13 +2742,13 @@
         <v>1</v>
       </c>
       <c r="C10" s="96">
-        <v>210.0905059525</v>
+        <v>240.56374007950001</v>
       </c>
       <c r="D10" s="96">
-        <v>897.42411459009998</v>
+        <v>989.48656459439997</v>
       </c>
       <c r="E10" s="96">
-        <v>6757662.8877063803</v>
+        <v>7520013.6941604447</v>
       </c>
       <c r="F10" s="96">
         <v>0</v>
@@ -2768,13 +2768,13 @@
         <v>1</v>
       </c>
       <c r="C11" s="96">
-        <v>202.59692460209999</v>
+        <v>246.6115674589</v>
       </c>
       <c r="D11" s="96">
-        <v>711.06959523729995</v>
+        <v>799.06959523789999</v>
       </c>
       <c r="E11" s="96">
-        <v>4132620.3846785584</v>
+        <v>4813267.3862359719</v>
       </c>
       <c r="F11" s="96">
         <v>0</v>
@@ -2794,13 +2794,13 @@
         <v>1</v>
       </c>
       <c r="C12" s="96">
-        <v>482.02853174410001</v>
+        <v>535.28547618829998</v>
       </c>
       <c r="D12" s="96">
-        <v>2873.0472023734001</v>
+        <v>2973.4162023743002</v>
       </c>
       <c r="E12" s="96">
-        <v>7873914.9061112888</v>
+        <v>8765227.9594276343</v>
       </c>
       <c r="F12" s="96">
         <v>0</v>
@@ -2820,13 +2820,13 @@
         <v>1</v>
       </c>
       <c r="C13" s="96">
-        <v>421.31408730099997</v>
+        <v>451.5398253962</v>
       </c>
       <c r="D13" s="96">
-        <v>1365.8715119108999</v>
+        <v>1525.3093690521</v>
       </c>
       <c r="E13" s="96">
-        <v>8636687.304375954</v>
+        <v>10185885.70934353</v>
       </c>
       <c r="F13" s="96">
         <v>0</v>
@@ -2846,13 +2846,13 @@
         <v>1</v>
       </c>
       <c r="C14" s="96">
-        <v>1339.7132936508001</v>
+        <v>1878.736904762</v>
       </c>
       <c r="D14" s="96">
-        <v>8570.2649999973</v>
+        <v>11394.0133333304</v>
       </c>
       <c r="E14" s="96">
-        <v>25842742.680006113</v>
+        <v>32020542.941609319</v>
       </c>
       <c r="F14" s="96">
         <v>0</v>
@@ -2872,13 +2872,13 @@
         <v>1</v>
       </c>
       <c r="C15" s="96">
-        <v>426.04166666570001</v>
+        <v>529.64027777650006</v>
       </c>
       <c r="D15" s="96">
-        <v>1430.822499996</v>
+        <v>1935.5799999952001</v>
       </c>
       <c r="E15" s="96">
-        <v>8367738.4832338309</v>
+        <v>9837944.9718231615</v>
       </c>
       <c r="F15" s="96">
         <v>0</v>
@@ -2898,13 +2898,13 @@
         <v>1</v>
       </c>
       <c r="C16" s="96">
-        <v>279.93787698279999</v>
+        <v>311.38753968129998</v>
       </c>
       <c r="D16" s="96">
-        <v>1427.9260119119999</v>
+        <v>1621.2710119139001</v>
       </c>
       <c r="E16" s="96">
-        <v>6987566.4676926713</v>
+        <v>7830460.6488101464</v>
       </c>
       <c r="F16" s="96">
         <v>0</v>
@@ -2924,13 +2924,13 @@
         <v>1</v>
       </c>
       <c r="C17" s="96">
-        <v>537.59083333149999</v>
+        <v>626.74599206139999</v>
       </c>
       <c r="D17" s="96">
-        <v>1554.7785238158999</v>
+        <v>1744.6222738143999</v>
       </c>
       <c r="E17" s="96">
-        <v>10570739.693693133</v>
+        <v>12180676.72377059</v>
       </c>
       <c r="F17" s="96">
         <v>0</v>
@@ -2950,13 +2950,13 @@
         <v>1</v>
       </c>
       <c r="C18" s="96">
-        <v>744.11172619009994</v>
+        <v>823.53900793590003</v>
       </c>
       <c r="D18" s="96">
-        <v>3288.1152738087999</v>
+        <v>3499.9758690460999</v>
       </c>
       <c r="E18" s="96">
-        <v>14544874.419634702</v>
+        <v>16024694.976201845</v>
       </c>
       <c r="F18" s="96">
         <v>0</v>
@@ -2976,13 +2976,13 @@
         <v>1</v>
       </c>
       <c r="C19" s="96">
-        <v>571.65216931090004</v>
+        <v>721.2968121678</v>
       </c>
       <c r="D19" s="96">
-        <v>2198.1381428650998</v>
+        <v>2697.1481428653001</v>
       </c>
       <c r="E19" s="96">
-        <v>11219784.289331133</v>
+        <v>13898645.433865212</v>
       </c>
       <c r="F19" s="96">
         <v>0</v>
@@ -3002,13 +3002,13 @@
         <v>1</v>
       </c>
       <c r="C20" s="96">
-        <v>2555.1168055557</v>
+        <v>2807.6356944447998</v>
       </c>
       <c r="D20" s="96">
-        <v>11598.8506666628</v>
+        <v>12452.8206666639</v>
       </c>
       <c r="E20" s="96">
-        <v>33209684.287959997</v>
+        <v>37584435.958896145</v>
       </c>
       <c r="F20" s="96">
         <v>0</v>
@@ -3028,13 +3028,13 @@
         <v>1</v>
       </c>
       <c r="C21" s="96">
-        <v>304.63680555370001</v>
+        <v>327.87930555359998</v>
       </c>
       <c r="D21" s="96">
-        <v>1112.2292142900999</v>
+        <v>1206.7342142885</v>
       </c>
       <c r="E21" s="96">
-        <v>6572144.8133745482</v>
+        <v>7188705.5862517217</v>
       </c>
       <c r="F21" s="96">
         <v>0</v>
@@ -3054,13 +3054,13 @@
         <v>1</v>
       </c>
       <c r="C22" s="96">
-        <v>259.68611111000001</v>
+        <v>283.72748015740001</v>
       </c>
       <c r="D22" s="96">
-        <v>792.65601190309997</v>
+        <v>876.65601190109999</v>
       </c>
       <c r="E22" s="96">
-        <v>4306128.2350271344</v>
+        <v>4684076.524209898</v>
       </c>
       <c r="F22" s="96">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         <v>1</v>
       </c>
       <c r="C23" s="96">
-        <v>950.75670634820005</v>
+        <v>963.42337301489999</v>
       </c>
       <c r="D23" s="96">
-        <v>6242.1771547587996</v>
+        <v>6410.1771547587996</v>
       </c>
       <c r="E23" s="96">
-        <v>20172876.390481945</v>
+        <v>20358292.590482842</v>
       </c>
       <c r="F23" s="96">
         <v>0</v>
@@ -3106,13 +3106,13 @@
         <v>1</v>
       </c>
       <c r="C24" s="96">
-        <v>731.66458333349999</v>
+        <v>1862.3525793652</v>
       </c>
       <c r="D24" s="96">
-        <v>4795.7219583328997</v>
+        <v>15300.7601488083</v>
       </c>
       <c r="E24" s="96">
-        <v>13810777.689331688</v>
+        <v>32533139.2798471</v>
       </c>
       <c r="F24" s="96">
         <v>0</v>
@@ -3132,13 +3132,13 @@
         <v>1</v>
       </c>
       <c r="C25" s="96">
-        <v>340.14777777720002</v>
+        <v>405.38249999919998</v>
       </c>
       <c r="D25" s="96">
-        <v>1173.7395833383</v>
+        <v>1404.0220833387</v>
       </c>
       <c r="E25" s="96">
-        <v>6235749.7584266458</v>
+        <v>7212918.424210974</v>
       </c>
       <c r="F25" s="96">
         <v>0</v>
@@ -3158,13 +3158,13 @@
         <v>1</v>
       </c>
       <c r="C26" s="96">
-        <v>246.43285714199999</v>
+        <v>284.10333333210002</v>
       </c>
       <c r="D26" s="96">
-        <v>613.9945833347</v>
+        <v>761.78791666910001</v>
       </c>
       <c r="E26" s="96">
-        <v>3832290.7361907284</v>
+        <v>5035112.3818729157</v>
       </c>
       <c r="F26" s="96">
         <v>0</v>
@@ -3210,13 +3210,13 @@
         <v>1</v>
       </c>
       <c r="C28" s="96">
-        <v>579.47321097760005</v>
+        <v>634.36102843740002</v>
       </c>
       <c r="D28" s="96">
-        <v>2639.4981473278999</v>
+        <v>2820.3755878042998</v>
       </c>
       <c r="E28" s="96">
-        <v>11431823.194593111</v>
+        <v>12482971.675436357</v>
       </c>
       <c r="F28" s="96">
         <v>0</v>
@@ -3236,13 +3236,13 @@
         <v>1</v>
       </c>
       <c r="C29" s="96">
-        <v>1564.5369444447001</v>
+        <v>2151.9008333335</v>
       </c>
       <c r="D29" s="96">
-        <v>3010.7420833383999</v>
+        <v>5841.2620833384999</v>
       </c>
       <c r="E29" s="96">
-        <v>21388145.925452832</v>
+        <v>28353385.45531898</v>
       </c>
       <c r="F29" s="96">
         <v>0</v>
@@ -3262,13 +3262,13 @@
         <v>1</v>
       </c>
       <c r="C30" s="96">
-        <v>178.7501984129</v>
+        <v>197.61617063489999</v>
       </c>
       <c r="D30" s="96">
-        <v>688.43916667320002</v>
+        <v>797.35166667420003</v>
       </c>
       <c r="E30" s="96">
-        <v>3372720.3592291768</v>
+        <v>3805787.6012926684</v>
       </c>
       <c r="F30" s="96">
         <v>0</v>
@@ -3288,13 +3288,13 @@
         <v>1</v>
       </c>
       <c r="C31" s="96">
-        <v>224.93710317329999</v>
+        <v>257.15317460160003</v>
       </c>
       <c r="D31" s="96">
-        <v>479.58999999909997</v>
+        <v>558.59000000030005</v>
       </c>
       <c r="E31" s="96">
-        <v>3875759.7054576175</v>
+        <v>4367804.0145924808</v>
       </c>
       <c r="F31" s="96">
         <v>0</v>
@@ -3314,13 +3314,13 @@
         <v>1</v>
       </c>
       <c r="C32" s="96">
-        <v>88.429761904800003</v>
+        <v>160.09107142849999</v>
       </c>
       <c r="D32" s="96">
-        <v>549.61125000029995</v>
+        <v>629.16624999830003</v>
       </c>
       <c r="E32" s="96">
-        <v>2627029.9340391951</v>
+        <v>3442297.9978710278</v>
       </c>
       <c r="F32" s="96">
         <v>0</v>
@@ -3340,13 +3340,13 @@
         <v>1</v>
       </c>
       <c r="C33" s="96">
-        <v>344.67829365</v>
+        <v>360.20210317369998</v>
       </c>
       <c r="D33" s="96">
-        <v>1064.2985000041999</v>
+        <v>1178.3085000034</v>
       </c>
       <c r="E33" s="96">
-        <v>5871001.8178605409</v>
+        <v>6348650.0493735028</v>
       </c>
       <c r="F33" s="96">
         <v>0</v>
@@ -3418,13 +3418,13 @@
         <v>1</v>
       </c>
       <c r="C36" s="96">
-        <v>347.46670634819998</v>
+        <v>383.11065476070002</v>
       </c>
       <c r="D36" s="96">
-        <v>1480.9436904767001</v>
+        <v>1692.1407738109999</v>
       </c>
       <c r="E36" s="96">
-        <v>7002297.6074060109</v>
+        <v>7824662.7877200451</v>
       </c>
       <c r="F36" s="96">
         <v>0</v>
@@ -3470,13 +3470,13 @@
         <v>1</v>
       </c>
       <c r="C38" s="96">
-        <v>316.89242424230002</v>
+        <v>462.89242424230002</v>
       </c>
       <c r="D38" s="96">
-        <v>3410.1299999989001</v>
+        <v>5401.7499999989004</v>
       </c>
       <c r="E38" s="96">
-        <v>6979221.568329419</v>
+        <v>10040043.519329419</v>
       </c>
       <c r="F38" s="96">
         <v>0</v>
@@ -3496,13 +3496,13 @@
         <v>1</v>
       </c>
       <c r="C39" s="96">
-        <v>903.58333333329995</v>
+        <v>961.75</v>
       </c>
       <c r="D39" s="96">
-        <v>10709.479999998801</v>
+        <v>11522.639999998801</v>
       </c>
       <c r="E39" s="96">
-        <v>19182792.083198067</v>
+        <v>20528174.766575135</v>
       </c>
       <c r="F39" s="96">
         <v>0</v>
@@ -3522,13 +3522,13 @@
         <v>1</v>
       </c>
       <c r="C40" s="96">
-        <v>783.70252645510004</v>
+        <v>788.22911375679996</v>
       </c>
       <c r="D40" s="96">
-        <v>4461.5912844021996</v>
+        <v>4495.562712977</v>
       </c>
       <c r="E40" s="96">
-        <v>7360714.5095196133</v>
+        <v>7599049.4142421484</v>
       </c>
       <c r="F40" s="96">
         <v>0</v>
@@ -3574,13 +3574,13 @@
         <v>1</v>
       </c>
       <c r="C42" s="96">
-        <v>56</v>
+        <v>100.0611111111</v>
       </c>
       <c r="D42" s="96">
-        <v>798.04</v>
+        <v>1475.5799999999001</v>
       </c>
       <c r="E42" s="96">
-        <v>1256116.5299</v>
+        <v>2478634.4092995184</v>
       </c>
       <c r="F42" s="96">
         <v>0</v>
@@ -3603,7 +3603,7 @@
         <v>249.55500992079999</v>
       </c>
       <c r="D43" s="96">
-        <v>1124.5225014852999</v>
+        <v>1125.0769014857001</v>
       </c>
       <c r="E43" s="96">
         <v>8104352.0621971888</v>
@@ -3652,13 +3652,13 @@
         <v>1</v>
       </c>
       <c r="C45" s="96">
-        <v>272.1541865085</v>
+        <v>355.19942460380003</v>
       </c>
       <c r="D45" s="96">
-        <v>2481.7347916711001</v>
+        <v>3289.8991916700002</v>
       </c>
       <c r="E45" s="96">
-        <v>5468726.5718661454</v>
+        <v>7159889.4382920526</v>
       </c>
       <c r="F45" s="96">
         <v>0</v>
@@ -3678,13 +3678,13 @@
         <v>1</v>
       </c>
       <c r="C46" s="96">
-        <v>101.875</v>
+        <v>321.875</v>
       </c>
       <c r="D46" s="96">
         <v>-24.9999999996</v>
       </c>
       <c r="E46" s="96">
-        <v>113494.647396092</v>
+        <v>1576733.851396092</v>
       </c>
       <c r="F46" s="96">
         <v>0</v>
@@ -3773,44 +3773,44 @@
       </c>
       <c r="D2" s="59">
         <f>IFERROR(+VLOOKUP(B2,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>16024694.976201845</v>
+      </c>
+      <c r="E2" s="59">
         <v>14544874.419634702</v>
-      </c>
-      <c r="E2" s="59">
-        <v>12888810.036315698</v>
       </c>
       <c r="F2" s="59">
         <f t="shared" ref="F2:F9" si="0">+D2-E2</f>
-        <v>1656064.3833190035</v>
+        <v>1479820.5565671436</v>
       </c>
       <c r="G2" s="60">
         <f t="shared" ref="G2:G41" si="1">+D2/C2</f>
-        <v>0.45059759864379156</v>
+        <v>0.49644217385117384</v>
       </c>
       <c r="H2" s="59">
         <f>+D2/$N$3*$N$4</f>
-        <v>49868140.867318973</v>
+        <v>48074084.928605534</v>
       </c>
       <c r="I2" s="60">
         <f t="shared" ref="I2:I41" si="2">+H2/C2</f>
-        <v>1.5449060524929996</v>
+        <v>1.4893265215535216</v>
       </c>
       <c r="J2" s="59">
         <f>+D2/$N$3</f>
-        <v>2077839.2028049573</v>
+        <v>2003086.8720252307</v>
       </c>
       <c r="K2" s="59">
         <f t="shared" ref="K2:K41" si="3">+(C2-D2)/$N$2</f>
-        <v>1043188.3658009443</v>
+        <v>1015898.8538780567</v>
       </c>
       <c r="L2" s="61" cm="1">
         <f t="array" ref="L2">+_xlfn.IFS(I2&gt;114%,H2*0.02,I2&gt;109%,H2*0.015,I2&gt;104%,H2*0.0125,I2&gt;99%,H2*0.01,I2&lt;99%,H2*0)</f>
-        <v>997362.81734637951</v>
+        <v>961481.69857211073</v>
       </c>
       <c r="M2" s="53" t="s">
         <v>36</v>
       </c>
       <c r="N2">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -3823,45 +3823,45 @@
       </c>
       <c r="D3" s="4">
         <f>IFERROR(+VLOOKUP(B3,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>12180676.72377059</v>
+      </c>
+      <c r="E3" s="4">
         <v>10570739.693693133</v>
-      </c>
-      <c r="E3" s="4">
-        <v>10212334.874835599</v>
       </c>
       <c r="F3" s="4">
         <f t="shared" si="0"/>
-        <v>358404.81885753386</v>
+        <v>1609937.0300774574</v>
       </c>
       <c r="G3" s="5">
         <f t="shared" si="1"/>
-        <v>0.34118169428661804</v>
+        <v>0.39314409800982325</v>
       </c>
       <c r="H3" s="4">
         <f t="shared" ref="H3:H41" si="4">+D3/$N$3*$N$4</f>
-        <v>36242536.092662171</v>
+        <v>36542030.171311773</v>
       </c>
       <c r="I3" s="5">
         <f t="shared" si="2"/>
-        <v>1.1697658089826906</v>
+        <v>1.1794322940294697</v>
       </c>
       <c r="J3" s="4">
         <f t="shared" ref="J3:J41" si="5">+D3/$N$3</f>
-        <v>1510105.6705275904</v>
+        <v>1522584.5904713238</v>
       </c>
       <c r="K3" s="4">
         <f t="shared" si="3"/>
-        <v>1200705.2050111836</v>
+        <v>1175128.2159445416</v>
       </c>
       <c r="L3" s="63" cm="1">
         <f t="array" ref="L3">+_xlfn.IFS(I3&gt;114%,H3*0.02,I3&gt;109%,H3*0.015,I3&gt;104%,H3*0.0125,I3&gt;99%,H3*0.01,I3&lt;99%,H3*0)</f>
-        <v>724850.72185324342</v>
+        <v>730840.6034262355</v>
       </c>
       <c r="M3" s="53" t="s">
         <v>40</v>
       </c>
       <c r="N3">
         <f>N4-N2</f>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -3874,38 +3874,38 @@
       </c>
       <c r="D4" s="4">
         <f>IFERROR(+VLOOKUP(B4,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>9837944.9718231615</v>
+      </c>
+      <c r="E4" s="4">
         <v>8367738.4832338309</v>
-      </c>
-      <c r="E4" s="4">
-        <v>6977673.3087740811</v>
       </c>
       <c r="F4" s="4">
         <f t="shared" si="0"/>
-        <v>1390065.1744597498</v>
+        <v>1470206.4885893306</v>
       </c>
       <c r="G4" s="5">
         <f t="shared" si="1"/>
-        <v>0.29474213700425966</v>
+        <v>0.3465281486192977</v>
       </c>
       <c r="H4" s="4">
         <f t="shared" si="4"/>
-        <v>28689389.085373133</v>
+        <v>29513834.915469483</v>
       </c>
       <c r="I4" s="5">
         <f t="shared" si="2"/>
-        <v>1.0105444697288901</v>
+        <v>1.0395844458578931</v>
       </c>
       <c r="J4" s="4">
         <f t="shared" si="5"/>
-        <v>1195391.2118905473</v>
+        <v>1229743.1214778952</v>
       </c>
       <c r="K4" s="4">
         <f t="shared" si="3"/>
-        <v>1177781.9280537895</v>
+        <v>1159505.3930203184</v>
       </c>
       <c r="L4" s="63" cm="1">
         <f t="array" ref="L4">+_xlfn.IFS(I4&gt;114%,H4*0.02,I4&gt;109%,H4*0.015,I4&gt;104%,H4*0.0125,I4&gt;99%,H4*0.01,I4&lt;99%,H4*0)</f>
-        <v>286893.89085373137</v>
+        <v>295138.34915469482</v>
       </c>
       <c r="M4" s="53" t="s">
         <v>47</v>
@@ -3924,38 +3924,38 @@
       </c>
       <c r="D5" s="4">
         <f>IFERROR(+VLOOKUP(B5,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>10185885.70934353</v>
+      </c>
+      <c r="E5" s="4">
         <v>8636687.304375954</v>
-      </c>
-      <c r="E5" s="4">
-        <v>7646569.2805425785</v>
       </c>
       <c r="F5" s="4">
         <f t="shared" si="0"/>
-        <v>990118.02383337542</v>
+        <v>1549198.4049675763</v>
       </c>
       <c r="G5" s="5">
         <f t="shared" si="1"/>
-        <v>0.30421549117839375</v>
+        <v>0.35878388494914037</v>
       </c>
       <c r="H5" s="4">
         <f t="shared" si="4"/>
-        <v>29611499.329288989</v>
+        <v>30557657.128030591</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" si="2"/>
-        <v>1.0430245411830645</v>
+        <v>1.0763516548474212</v>
       </c>
       <c r="J5" s="4">
         <f t="shared" si="5"/>
-        <v>1233812.4720537078</v>
+        <v>1273235.7136679413</v>
       </c>
       <c r="K5" s="4">
         <f t="shared" si="3"/>
-        <v>1161961.4091630764</v>
+        <v>1137759.0969252952</v>
       </c>
       <c r="L5" s="63" cm="1">
         <f t="array" ref="L5">+_xlfn.IFS(I5&gt;114%,H5*0.02,I5&gt;109%,H5*0.015,I5&gt;104%,H5*0.0125,I5&gt;99%,H5*0.01,I5&lt;99%,H5*0)</f>
-        <v>370143.74161611241</v>
+        <v>381970.71410038241</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
@@ -3968,38 +3968,38 @@
       </c>
       <c r="D6" s="4">
         <f>IFERROR(+VLOOKUP(B6,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>8765227.9594276343</v>
+      </c>
+      <c r="E6" s="4">
         <v>7873914.9061112888</v>
-      </c>
-      <c r="E6" s="4">
-        <v>6728186.3048162535</v>
       </c>
       <c r="F6" s="4">
         <f t="shared" si="0"/>
-        <v>1145728.6012950353</v>
+        <v>891313.05331634544</v>
       </c>
       <c r="G6" s="5">
         <f t="shared" si="1"/>
-        <v>0.33465115771809623</v>
+        <v>0.37253306890690768</v>
       </c>
       <c r="H6" s="4">
         <f t="shared" si="4"/>
-        <v>26996279.678095847</v>
+        <v>26295683.878282905</v>
       </c>
       <c r="I6" s="5">
         <f t="shared" si="2"/>
-        <v>1.1473753978906158</v>
+        <v>1.117599206720723</v>
       </c>
       <c r="J6" s="4">
         <f t="shared" si="5"/>
-        <v>1124844.986587327</v>
+        <v>1095653.4949284543</v>
       </c>
       <c r="K6" s="4">
         <f t="shared" si="3"/>
-        <v>920871.15478875511</v>
+        <v>922718.5361307807</v>
       </c>
       <c r="L6" s="63" cm="1">
         <f t="array" ref="L6">+_xlfn.IFS(I6&gt;114%,H6*0.02,I6&gt;109%,H6*0.015,I6&gt;104%,H6*0.0125,I6&gt;99%,H6*0.01,I6&lt;99%,H6*0)</f>
-        <v>539925.59356191696</v>
+        <v>394435.25817424356</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
@@ -4012,34 +4012,34 @@
       </c>
       <c r="D7" s="4">
         <f>IFERROR(+VLOOKUP(B7,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>5878949.2572204797</v>
+      </c>
+      <c r="E7" s="4">
         <v>4840096.3237659615</v>
-      </c>
-      <c r="E7" s="4">
-        <v>4065628.6784671973</v>
       </c>
       <c r="F7" s="4">
         <f t="shared" ref="F7:F8" si="6">+D7-E7</f>
-        <v>774467.64529876411</v>
+        <v>1038852.9334545182</v>
       </c>
       <c r="G7" s="5">
         <f t="shared" si="1"/>
-        <v>0.17446908180843293</v>
+        <v>0.21191621205330838</v>
       </c>
       <c r="H7" s="4">
         <f t="shared" si="4"/>
-        <v>16594615.967197582</v>
+        <v>17636847.771661438</v>
       </c>
       <c r="I7" s="5">
         <f t="shared" si="2"/>
-        <v>0.5981797090574843</v>
+        <v>0.63574863615992505</v>
       </c>
       <c r="J7" s="4">
         <f t="shared" si="5"/>
-        <v>691442.33196656592</v>
+        <v>734868.65715255996</v>
       </c>
       <c r="K7" s="4">
         <f t="shared" si="3"/>
-        <v>1347162.3945116792</v>
+        <v>1366431.7358277515</v>
       </c>
       <c r="L7" s="63" cm="1">
         <f t="array" ref="L7">+_xlfn.IFS(I7&gt;114%,H7*0.02,I7&gt;109%,H7*0.015,I7&gt;104%,H7*0.0125,I7&gt;99%,H7*0.01,I7&lt;99%,H7*0)</f>
@@ -4056,38 +4056,38 @@
       </c>
       <c r="D8" s="4">
         <f>IFERROR(+VLOOKUP(B8,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>11328941.073388485</v>
+      </c>
+      <c r="E8" s="4">
         <v>10363253.207426563</v>
-      </c>
-      <c r="E8" s="4">
-        <v>9117515.4833692927</v>
       </c>
       <c r="F8" s="4">
         <f t="shared" si="6"/>
-        <v>1245737.7240572702</v>
+        <v>965687.86596192233</v>
       </c>
       <c r="G8" s="5">
         <f t="shared" si="1"/>
-        <v>0.28922532309579596</v>
+        <v>0.31617645315622644</v>
       </c>
       <c r="H8" s="4">
         <f t="shared" si="4"/>
-        <v>35531153.854033932</v>
+        <v>33986823.220165454</v>
       </c>
       <c r="I8" s="5">
         <f t="shared" si="2"/>
-        <v>0.9916296791855862</v>
+        <v>0.94852935946867933</v>
       </c>
       <c r="J8" s="4">
         <f t="shared" si="5"/>
-        <v>1480464.7439180803</v>
+        <v>1416117.6341735607</v>
       </c>
       <c r="K8" s="4">
         <f t="shared" si="3"/>
-        <v>1498106.953499479</v>
+        <v>1531383.1464705761</v>
       </c>
       <c r="L8" s="63" cm="1">
         <f t="array" ref="L8">+_xlfn.IFS(I8&gt;114%,H8*0.02,I8&gt;109%,H8*0.015,I8&gt;104%,H8*0.0125,I8&gt;99%,H8*0.01,I8&lt;99%,H8*0)</f>
-        <v>355311.53854033933</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
@@ -4100,38 +4100,38 @@
       </c>
       <c r="D9" s="4">
         <f>IFERROR(+VLOOKUP(B9,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>13014610.776669662</v>
+      </c>
+      <c r="E9" s="4">
         <v>10378829.479285927</v>
-      </c>
-      <c r="E9" s="4">
-        <v>8696250.9292322323</v>
       </c>
       <c r="F9" s="4">
         <f t="shared" si="0"/>
-        <v>1682578.5500536952</v>
+        <v>2635781.297383735</v>
       </c>
       <c r="G9" s="5">
         <f t="shared" si="1"/>
-        <v>0.28966003719290251</v>
+        <v>0.3632213679919376</v>
       </c>
       <c r="H9" s="4">
         <f t="shared" si="4"/>
-        <v>35584558.214694604</v>
+        <v>39043832.330008984</v>
       </c>
       <c r="I9" s="5">
         <f t="shared" si="2"/>
-        <v>0.99312012751852274</v>
+        <v>1.0896641039758126</v>
       </c>
       <c r="J9" s="4">
         <f t="shared" si="5"/>
-        <v>1482689.9256122753</v>
+        <v>1626826.3470837078</v>
       </c>
       <c r="K9" s="4">
         <f t="shared" si="3"/>
-        <v>1497190.702213634</v>
+        <v>1426028.7900155026</v>
       </c>
       <c r="L9" s="63" cm="1">
         <f t="array" ref="L9">+_xlfn.IFS(I9&gt;114%,H9*0.02,I9&gt;109%,H9*0.015,I9&gt;104%,H9*0.0125,I9&gt;99%,H9*0.01,I9&lt;99%,H9*0)</f>
-        <v>355845.58214694605</v>
+        <v>488047.90412511234</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4142,34 +4142,34 @@
       </c>
       <c r="D10" s="64">
         <f>+SUM(D2:D9)</f>
+        <v>87216931.447845384</v>
+      </c>
+      <c r="E10" s="65">
         <v>75576133.817527354</v>
-      </c>
-      <c r="E10" s="65">
-        <v>66332968.896352932</v>
       </c>
       <c r="F10" s="64">
         <f>+SUM(F2:F9)</f>
-        <v>9243164.9211744275</v>
+        <v>11640797.630318029</v>
       </c>
       <c r="G10" s="66">
         <f t="shared" si="1"/>
-        <v>0.31104541950885256</v>
+        <v>0.3589549459617683</v>
       </c>
       <c r="H10" s="64">
         <f t="shared" si="4"/>
-        <v>259118173.08866525</v>
+        <v>261650794.34353614</v>
       </c>
       <c r="I10" s="66">
         <f t="shared" si="2"/>
-        <v>1.0664414383160661</v>
+        <v>1.076864837885305</v>
       </c>
       <c r="J10" s="64">
         <f t="shared" si="5"/>
-        <v>10796590.545361051</v>
+        <v>10902116.430980673</v>
       </c>
       <c r="K10" s="67">
         <f t="shared" si="3"/>
-        <v>9846968.113042539</v>
+        <v>9734853.7682128213</v>
       </c>
       <c r="L10" s="68"/>
     </row>
@@ -4185,38 +4185,38 @@
       </c>
       <c r="D11" s="59">
         <f>IFERROR(+VLOOKUP(B11,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>37584435.958896145</v>
+      </c>
+      <c r="E11" s="59">
         <v>33209684.287959997</v>
-      </c>
-      <c r="E11" s="59">
-        <v>27236244.29200922</v>
       </c>
       <c r="F11" s="59">
         <f t="shared" ref="F11:F16" si="7">+D11-E11</f>
-        <v>5973439.9959507771</v>
+        <v>4374751.6709361486</v>
       </c>
       <c r="G11" s="60">
         <f t="shared" si="1"/>
-        <v>0.34246691758248254</v>
+        <v>0.38758049671028788</v>
       </c>
       <c r="H11" s="59">
         <f t="shared" si="4"/>
-        <v>113861774.70157713</v>
+        <v>112753307.87668844</v>
       </c>
       <c r="I11" s="60">
         <f t="shared" si="2"/>
-        <v>1.1741722888542259</v>
+        <v>1.1627414901308637</v>
       </c>
       <c r="J11" s="59">
         <f t="shared" si="5"/>
-        <v>4744240.6125657139</v>
+        <v>4698054.4948620182</v>
       </c>
       <c r="K11" s="59">
         <f t="shared" si="3"/>
-        <v>3750721.4230692657</v>
+        <v>3711719.5325775854</v>
       </c>
       <c r="L11" s="61" cm="1">
         <f t="array" ref="L11">+_xlfn.IFS(I11&gt;114%,H11*0.0125,I11&gt;109%,H11*0.01,I11&gt;104%,H11*0.0075,I11&gt;99%,H11*0.005,I11&lt;99%,H11*0)</f>
-        <v>1423272.1837697141</v>
+        <v>1409416.3484586056</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4232,11 +4232,11 @@
         <v>12982127.936856734</v>
       </c>
       <c r="E12" s="4">
-        <v>7342359.2744361712</v>
+        <v>12982127.936856734</v>
       </c>
       <c r="F12" s="4">
         <f t="shared" si="7"/>
-        <v>5639768.6624205625</v>
+        <v>0</v>
       </c>
       <c r="G12" s="5">
         <f t="shared" si="1"/>
@@ -4244,23 +4244,23 @@
       </c>
       <c r="H12" s="4">
         <f t="shared" si="4"/>
-        <v>44510152.926365942</v>
+        <v>38946383.810570203</v>
       </c>
       <c r="I12" s="5">
         <f t="shared" si="2"/>
-        <v>1.4071730345040894</v>
+        <v>1.2312764051910783</v>
       </c>
       <c r="J12" s="4">
         <f t="shared" si="5"/>
-        <v>1854589.7052652477</v>
+        <v>1622765.9921070917</v>
       </c>
       <c r="K12" s="4">
         <f t="shared" si="3"/>
-        <v>1096986.733630016</v>
+        <v>1165548.404481892</v>
       </c>
       <c r="L12" s="63" cm="1">
         <f t="array" ref="L12">+_xlfn.IFS(I12&gt;114%,H12*0.02,I12&gt;109%,H12*0.015,I12&gt;104%,H12*0.0125,I12&gt;99%,H12*0.01,I12&lt;99%,H12*0)</f>
-        <v>890203.05852731888</v>
+        <v>778927.67621140403</v>
       </c>
       <c r="M12" s="27"/>
     </row>
@@ -4274,34 +4274,34 @@
       </c>
       <c r="D13" s="4">
         <f>IFERROR(+VLOOKUP(B13,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>32020542.941609319</v>
+      </c>
+      <c r="E13" s="4">
         <v>25842742.680006113</v>
-      </c>
-      <c r="E13" s="4">
-        <v>41231894.308746725</v>
       </c>
       <c r="F13" s="4">
         <f t="shared" si="7"/>
-        <v>-15389151.628740612</v>
+        <v>6177800.2616032064</v>
       </c>
       <c r="G13" s="5">
         <f t="shared" si="1"/>
-        <v>0.20132404393912623</v>
+        <v>0.24945127821586574</v>
       </c>
       <c r="H13" s="4">
         <f t="shared" si="4"/>
-        <v>88603689.188592389</v>
+        <v>96061628.824827954</v>
       </c>
       <c r="I13" s="5">
         <f t="shared" si="2"/>
-        <v>0.69025386493414709</v>
+        <v>0.74835383464759719</v>
       </c>
       <c r="J13" s="4">
         <f t="shared" si="5"/>
-        <v>3691820.3828580161</v>
+        <v>4002567.8677011649</v>
       </c>
       <c r="K13" s="4">
         <f t="shared" si="3"/>
-        <v>6030657.2585069919</v>
+        <v>6021460.8208134789</v>
       </c>
       <c r="L13" s="63" cm="1">
         <f t="array" ref="L13">+_xlfn.IFS(I13&gt;114%,H13*0.0125,I13&gt;109%,H13*0.01,I13&gt;104%,H13*0.0075,I13&gt;99%,H13*0.005,I13&lt;99%,H13*0)</f>
@@ -4324,34 +4324,34 @@
       </c>
       <c r="D14" s="4">
         <f>IFERROR(+VLOOKUP(B14,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>10040043.519329419</v>
+      </c>
+      <c r="E14" s="4">
         <v>6979221.568329419</v>
-      </c>
-      <c r="E14" s="4">
-        <v>6878414.3543294193</v>
       </c>
       <c r="F14" s="4">
         <f t="shared" si="7"/>
-        <v>100807.21399999969</v>
+        <v>3060821.9510000004</v>
       </c>
       <c r="G14" s="5">
         <f t="shared" si="1"/>
-        <v>0.16441405290557995</v>
+        <v>0.23651982247591513</v>
       </c>
       <c r="H14" s="4">
         <f t="shared" si="4"/>
-        <v>23928759.662843723</v>
+        <v>30120130.557988256</v>
       </c>
       <c r="I14" s="5">
         <f t="shared" si="2"/>
-        <v>0.5637053242477027</v>
+        <v>0.70955946742774534</v>
       </c>
       <c r="J14" s="4">
         <f t="shared" si="5"/>
-        <v>997031.65261848841</v>
+        <v>1255005.4399161774</v>
       </c>
       <c r="K14" s="4">
         <f t="shared" si="3"/>
-        <v>2086460.930979152</v>
+        <v>2025563.3672278486</v>
       </c>
       <c r="L14" s="63" cm="1">
         <f t="array" ref="L14">+_xlfn.IFS(I14&gt;109%,H14*0.015,I14&gt;104%,H14*0.0125,I14&gt;99%,H14*0.01,I14&lt;99%,H14*0)</f>
@@ -4369,38 +4369,38 @@
       </c>
       <c r="D15" s="4">
         <f>IFERROR(+VLOOKUP(B15,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>20528174.766575135</v>
+      </c>
+      <c r="E15" s="4">
         <v>19182792.083198067</v>
-      </c>
-      <c r="E15" s="4">
-        <v>12288523.154902149</v>
       </c>
       <c r="F15" s="4">
         <f t="shared" si="7"/>
-        <v>6894268.9282959178</v>
+        <v>1345382.6833770685</v>
       </c>
       <c r="G15" s="5">
         <f t="shared" si="1"/>
-        <v>0.45190148522517892</v>
+        <v>0.48359553842543518</v>
       </c>
       <c r="H15" s="4">
         <f t="shared" si="4"/>
-        <v>65769572.856679089</v>
+        <v>61584524.299725406</v>
       </c>
       <c r="I15" s="5">
         <f t="shared" si="2"/>
-        <v>1.549376520772042</v>
+        <v>1.4507866152763056</v>
       </c>
       <c r="J15" s="4">
         <f t="shared" si="5"/>
-        <v>2740398.8690282954</v>
+        <v>2566021.8458218919</v>
       </c>
       <c r="K15" s="4">
         <f t="shared" si="3"/>
-        <v>1368603.8418692313</v>
+        <v>1370055.1642749915</v>
       </c>
       <c r="L15" s="63" cm="1">
         <f t="array" ref="L15">+_xlfn.IFS(I15&gt;109%,H15*0.015,I15&gt;104%,H15*0.0125,I15&gt;99%,H15*0.01,I15&lt;99%,H15*0)</f>
-        <v>986543.59285018628</v>
+        <v>923767.86449588102</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4411,34 +4411,34 @@
       </c>
       <c r="D16" s="64">
         <f>+SUM(D11:D15)</f>
+        <v>113155325.12326676</v>
+      </c>
+      <c r="E16" s="65">
         <v>98196568.556350335</v>
-      </c>
-      <c r="E16" s="65">
-        <v>94977435.384423673</v>
       </c>
       <c r="F16" s="64">
         <f t="shared" si="7"/>
-        <v>3219133.1719266623</v>
+        <v>14958756.566916421</v>
       </c>
       <c r="G16" s="66">
         <f t="shared" si="1"/>
-        <v>0.28723795217789533</v>
+        <v>0.33099429383603618</v>
       </c>
       <c r="H16" s="64">
         <f t="shared" si="4"/>
-        <v>336673949.33605826</v>
+        <v>339465975.36980027</v>
       </c>
       <c r="I16" s="66">
         <f t="shared" si="2"/>
-        <v>0.98481583603849809</v>
+        <v>0.99298288150810854</v>
       </c>
       <c r="J16" s="64">
         <f t="shared" si="5"/>
-        <v>14028081.222335761</v>
+        <v>14144415.640408345</v>
       </c>
       <c r="K16" s="67">
         <f t="shared" si="3"/>
-        <v>14333430.188054657</v>
+        <v>14294347.289375797</v>
       </c>
       <c r="L16" s="68"/>
     </row>
@@ -4454,34 +4454,34 @@
       </c>
       <c r="D17" s="59">
         <f>IFERROR(+VLOOKUP(B17,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>6449843.5922434218</v>
+      </c>
+      <c r="E17" s="59">
         <v>5940437.3079375168</v>
-      </c>
-      <c r="E17" s="59">
-        <v>5569721.4797102707</v>
       </c>
       <c r="F17" s="59">
         <f t="shared" ref="F17:F40" si="8">+D17-E17</f>
-        <v>370715.82822724618</v>
+        <v>509406.28430590499</v>
       </c>
       <c r="G17" s="60">
         <f t="shared" si="1"/>
-        <v>0.20248256992372748</v>
+        <v>0.21984592016794852</v>
       </c>
       <c r="H17" s="59">
         <f t="shared" si="4"/>
-        <v>20367213.627214342</v>
+        <v>19349530.776730265</v>
       </c>
       <c r="I17" s="60">
         <f t="shared" si="2"/>
-        <v>0.6942259540242085</v>
+        <v>0.65953776050384549</v>
       </c>
       <c r="J17" s="59">
         <f t="shared" si="5"/>
-        <v>848633.90113393101</v>
+        <v>806230.44903042773</v>
       </c>
       <c r="K17" s="59">
         <f t="shared" si="3"/>
-        <v>1376328.2837977933</v>
+        <v>1430510.9087660364</v>
       </c>
       <c r="L17" s="61" cm="1">
         <f t="array" ref="L17">+_xlfn.IFS(I17&gt;114%,H17*0.02,I17&gt;109%,H17*0.015,I17&gt;104%,H17*0.0125,I17&gt;99%,H17*0.01,I17&lt;99%,H17*0)</f>
@@ -4498,34 +4498,34 @@
       </c>
       <c r="D18" s="4">
         <f>IFERROR(+VLOOKUP(B18,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>6596329.3614597432</v>
+      </c>
+      <c r="E18" s="4">
         <v>5899873.0951455031</v>
-      </c>
-      <c r="E18" s="4">
-        <v>5463522.8209966822</v>
       </c>
       <c r="F18" s="4">
         <f t="shared" si="8"/>
-        <v>436350.2741488209</v>
+        <v>696456.26631424017</v>
       </c>
       <c r="G18" s="5">
         <f t="shared" si="1"/>
-        <v>0.23637780005675121</v>
+        <v>0.26428124770930433</v>
       </c>
       <c r="H18" s="4">
         <f t="shared" si="4"/>
-        <v>20228136.326213151</v>
+        <v>19788988.08437923</v>
       </c>
       <c r="I18" s="5">
         <f t="shared" si="2"/>
-        <v>0.81043817162314702</v>
+        <v>0.79284374312791295</v>
       </c>
       <c r="J18" s="4">
         <f t="shared" si="5"/>
-        <v>842839.01359221467</v>
+        <v>824541.1701824679</v>
       </c>
       <c r="K18" s="4">
         <f t="shared" si="3"/>
-        <v>1121154.870873794</v>
+        <v>1147698.5336587662</v>
       </c>
       <c r="L18" s="63" cm="1">
         <f t="array" ref="L18">+_xlfn.IFS(I18&gt;114%,H18*0.02,I18&gt;109%,H18*0.015,I18&gt;104%,H18*0.0125,I18&gt;99%,H18*0.01,I18&lt;99%,H18*0)</f>
@@ -4542,34 +4542,34 @@
       </c>
       <c r="D19" s="4">
         <f>IFERROR(+VLOOKUP(B19,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>7830460.6488101464</v>
+      </c>
+      <c r="E19" s="4">
         <v>6987566.4676926713</v>
-      </c>
-      <c r="E19" s="4">
-        <v>5986642.3849513531</v>
       </c>
       <c r="F19" s="4">
         <f t="shared" si="8"/>
-        <v>1000924.0827413183</v>
+        <v>842894.18111747503</v>
       </c>
       <c r="G19" s="5">
         <f t="shared" si="1"/>
-        <v>0.27024252650546504</v>
+        <v>0.30284126515576909</v>
       </c>
       <c r="H19" s="4">
         <f t="shared" si="4"/>
-        <v>23957370.746374875</v>
+        <v>23491381.946430437</v>
       </c>
       <c r="I19" s="5">
         <f t="shared" si="2"/>
-        <v>0.92654580516159457</v>
+        <v>0.90852379546730722</v>
       </c>
       <c r="J19" s="4">
         <f t="shared" si="5"/>
-        <v>998223.7810989531</v>
+        <v>978807.5811012683</v>
       </c>
       <c r="K19" s="4">
         <f t="shared" si="3"/>
-        <v>1109946.0998710191</v>
+        <v>1126636.8447931157</v>
       </c>
       <c r="L19" s="63" cm="1">
         <f t="array" ref="L19">+_xlfn.IFS(I19&gt;114%,H19*0.02,I19&gt;109%,H19*0.015,I19&gt;104%,H19*0.0125,I19&gt;99%,H19*0.01,I19&lt;99%,H19*0)</f>
@@ -4586,38 +4586,38 @@
       </c>
       <c r="D20" s="4">
         <f>IFERROR(+VLOOKUP(B20,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>13898645.433865212</v>
+      </c>
+      <c r="E20" s="4">
         <v>11219784.289331133</v>
-      </c>
-      <c r="E20" s="4">
-        <v>10086924.880174421</v>
       </c>
       <c r="F20" s="4">
         <f t="shared" si="8"/>
-        <v>1132859.4091567118</v>
+        <v>2678861.1445340794</v>
       </c>
       <c r="G20" s="5">
         <f t="shared" si="1"/>
-        <v>0.33443844081119073</v>
+        <v>0.41428972147971321</v>
       </c>
       <c r="H20" s="4">
         <f t="shared" si="4"/>
-        <v>38467831.849135309</v>
+        <v>41695936.301595636</v>
       </c>
       <c r="I20" s="5">
         <f t="shared" si="2"/>
-        <v>1.1466460827812253</v>
+        <v>1.2428691644391396</v>
       </c>
       <c r="J20" s="4">
         <f t="shared" si="5"/>
-        <v>1602826.3270473047</v>
+        <v>1737330.6792331515</v>
       </c>
       <c r="K20" s="4">
         <f t="shared" si="3"/>
-        <v>1313432.1006275807</v>
+        <v>1228092.7853834243</v>
       </c>
       <c r="L20" s="63" cm="1">
         <f t="array" ref="L20">+_xlfn.IFS(I20&gt;114%,H20*0.02,I20&gt;109%,H20*0.015,I20&gt;104%,H20*0.0125,I20&gt;99%,H20*0.01,I20&lt;99%,H20*0)</f>
-        <v>769356.63698270626</v>
+        <v>833918.72603191272</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4630,34 +4630,34 @@
       </c>
       <c r="D21" s="4">
         <f>IFERROR(+VLOOKUP(B21,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>7188705.5862517217</v>
+      </c>
+      <c r="E21" s="4">
         <v>6572144.8133745482</v>
-      </c>
-      <c r="E21" s="4">
-        <v>6172988.7852142667</v>
       </c>
       <c r="F21" s="4">
         <f t="shared" ref="F21:F23" si="9">+D21-E21</f>
-        <v>399156.02816028148</v>
+        <v>616560.7728771735</v>
       </c>
       <c r="G21" s="5">
         <f t="shared" si="1"/>
-        <v>0.25815119633374256</v>
+        <v>0.28236945470303337</v>
       </c>
       <c r="H21" s="4">
         <f t="shared" si="4"/>
-        <v>22533067.931569882</v>
+        <v>21566116.758755166</v>
       </c>
       <c r="I21" s="5">
         <f t="shared" si="2"/>
-        <v>0.88508981600140313</v>
+        <v>0.84710836410910006</v>
       </c>
       <c r="J21" s="4">
         <f t="shared" si="5"/>
-        <v>938877.83048207837</v>
+        <v>898588.19828146521</v>
       </c>
       <c r="K21" s="4">
         <f t="shared" si="3"/>
-        <v>1110962.6580367913</v>
+        <v>1141862.7758592675</v>
       </c>
       <c r="L21" s="63" cm="1">
         <f t="array" ref="L21">+_xlfn.IFS(I21&gt;114%,H21*0.02,I21&gt;109%,H21*0.015,I21&gt;104%,H21*0.0125,I21&gt;99%,H21*0.01,I21&lt;99%,H21*0)</f>
@@ -4674,38 +4674,38 @@
       </c>
       <c r="D22" s="4">
         <f>IFERROR(+VLOOKUP(B22,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>12482971.675436357</v>
+      </c>
+      <c r="E22" s="4">
         <v>11431823.194593111</v>
-      </c>
-      <c r="E22" s="4">
-        <v>9510778.0994110405</v>
       </c>
       <c r="F22" s="4">
         <f t="shared" si="9"/>
-        <v>1921045.0951820705</v>
+        <v>1051148.480843246</v>
       </c>
       <c r="G22" s="5">
         <f t="shared" si="1"/>
-        <v>0.36013806942485377</v>
+        <v>0.39325252353474593</v>
       </c>
       <c r="H22" s="4">
         <f t="shared" si="4"/>
-        <v>39194822.381462097</v>
+        <v>37448915.026309073</v>
       </c>
       <c r="I22" s="5">
         <f t="shared" si="2"/>
-        <v>1.2347590951709273</v>
+        <v>1.1797575706042378</v>
       </c>
       <c r="J22" s="4">
         <f t="shared" si="5"/>
-        <v>1633117.5992275872</v>
+        <v>1560371.4594295446</v>
       </c>
       <c r="K22" s="4">
         <f t="shared" si="3"/>
-        <v>1194768.6473768761</v>
+        <v>1203744.907785228</v>
       </c>
       <c r="L22" s="63" cm="1">
         <f t="array" ref="L22">+_xlfn.IFS(I22&gt;114%,H22*0.02,I22&gt;109%,H22*0.015,I22&gt;104%,H22*0.0125,I22&gt;99%,H22*0.01,I22&lt;99%,H22*0)</f>
-        <v>783896.44762924197</v>
+        <v>748978.30052618147</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4718,34 +4718,34 @@
       </c>
       <c r="D23" s="4">
         <f>IFERROR(+VLOOKUP(B23,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>7824662.7877200451</v>
+      </c>
+      <c r="E23" s="4">
         <v>7002297.6074060109</v>
-      </c>
-      <c r="E23" s="4">
-        <v>6142976.0828060079</v>
       </c>
       <c r="F23" s="4">
         <f t="shared" si="9"/>
-        <v>859321.52460000291</v>
+        <v>822365.18031403422</v>
       </c>
       <c r="G23" s="5">
         <f t="shared" si="1"/>
-        <v>0.25522347757590025</v>
+        <v>0.28519748224189617</v>
       </c>
       <c r="H23" s="4">
         <f t="shared" si="4"/>
-        <v>24007877.511106323</v>
+        <v>23473988.363160133</v>
       </c>
       <c r="I23" s="5">
         <f t="shared" si="2"/>
-        <v>0.87505192311737223</v>
+        <v>0.85559244672568857</v>
       </c>
       <c r="J23" s="4">
         <f t="shared" si="5"/>
-        <v>1000328.2296294301</v>
+        <v>978082.84846500563</v>
       </c>
       <c r="K23" s="4">
         <f t="shared" si="3"/>
-        <v>1201979.3307408229</v>
+        <v>1225705.2151424973</v>
       </c>
       <c r="L23" s="63" cm="1">
         <f t="array" ref="L23">+_xlfn.IFS(I23&gt;114%,H23*0.02,I23&gt;109%,H23*0.015,I23&gt;104%,H23*0.0125,I23&gt;99%,H23*0.01,I23&lt;99%,H23*0)</f>
@@ -4762,34 +4762,34 @@
       </c>
       <c r="D24" s="4">
         <f>IFERROR(+VLOOKUP(B24,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>7360714.5095196133</v>
+        <v>7599049.4142421484</v>
       </c>
       <c r="E24" s="4">
         <v>7360714.5095196133</v>
       </c>
       <c r="F24" s="4">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>238334.90472253505</v>
       </c>
       <c r="G24" s="5">
         <f t="shared" si="1"/>
-        <v>0.21976182070279676</v>
+        <v>0.22687755824853539</v>
       </c>
       <c r="H24" s="4">
         <f t="shared" si="4"/>
-        <v>25236735.461210102</v>
+        <v>22797148.242726445</v>
       </c>
       <c r="I24" s="5">
         <f t="shared" si="2"/>
-        <v>0.75346909955244601</v>
+        <v>0.68063267474560618</v>
       </c>
       <c r="J24" s="4">
         <f t="shared" si="5"/>
-        <v>1051530.6442170877</v>
+        <v>949881.17678026855</v>
       </c>
       <c r="K24" s="4">
         <f t="shared" si="3"/>
-        <v>1537255.3229694346</v>
+        <v>1618437.8491098657</v>
       </c>
       <c r="L24" s="63" cm="1">
         <f t="array" ref="L24">+_xlfn.IFS(I24&gt;114%,H24*0.02,I24&gt;109%,H24*0.015,I24&gt;104%,H24*0.0125,I24&gt;99%,H24*0.01,I24&lt;99%,H24*0)</f>
@@ -4821,19 +4821,19 @@
       </c>
       <c r="H25" s="4">
         <f t="shared" si="4"/>
-        <v>41694247.090225846</v>
+        <v>36482466.203947611</v>
       </c>
       <c r="I25" s="5">
         <f t="shared" si="2"/>
-        <v>0.77118807805744749</v>
+        <v>0.67478956830026648</v>
       </c>
       <c r="J25" s="4">
         <f t="shared" si="5"/>
-        <v>1737260.2954260767</v>
+        <v>1520102.7584978172</v>
       </c>
       <c r="K25" s="4">
         <f t="shared" si="3"/>
-        <v>2464948.8704127925</v>
+        <v>2619008.1748135919</v>
       </c>
       <c r="L25" s="63" cm="1">
         <f t="array" ref="L25">+_xlfn.IFS(I25&gt;109%,H25*0.015,I25&gt;104%,H25*0.0125,I25&gt;99%,H25*0.01,I25&lt;99%,H25*0)</f>
@@ -4848,34 +4848,34 @@
       </c>
       <c r="D26" s="67">
         <f>+SUM(D17:D25)</f>
+        <v>82031490.568011329</v>
+      </c>
+      <c r="E26" s="65">
         <v>74575463.35298264</v>
-      </c>
-      <c r="E26" s="65">
-        <v>68455091.110766187</v>
       </c>
       <c r="F26" s="67">
         <f>+D26-E26</f>
-        <v>6120372.242216453</v>
+        <v>7456027.2150286883</v>
       </c>
       <c r="G26" s="66">
         <f t="shared" si="1"/>
-        <v>0.26084579671019531</v>
+        <v>0.28692506288909292</v>
       </c>
       <c r="H26" s="64">
         <f t="shared" si="4"/>
-        <v>255687302.92451191</v>
+        <v>246094471.70403397</v>
       </c>
       <c r="I26" s="66">
         <f t="shared" si="2"/>
-        <v>0.89432844586352678</v>
+        <v>0.86077518866727865</v>
       </c>
       <c r="J26" s="64">
         <f t="shared" si="5"/>
-        <v>10653637.621854663</v>
+        <v>10253936.321001416</v>
       </c>
       <c r="K26" s="67">
         <f t="shared" si="3"/>
-        <v>12430776.184706906</v>
+        <v>12741697.995311793</v>
       </c>
       <c r="L26" s="68"/>
     </row>
@@ -4891,38 +4891,38 @@
       </c>
       <c r="D27" s="59">
         <f>IFERROR(+VLOOKUP(B27,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>28353385.45531898</v>
+      </c>
+      <c r="E27" s="59">
         <v>21388145.925452832</v>
-      </c>
-      <c r="E27" s="59">
-        <v>18937147.75616448</v>
       </c>
       <c r="F27" s="59">
         <f t="shared" si="8"/>
-        <v>2450998.1692883521</v>
+        <v>6965239.5298661478</v>
       </c>
       <c r="G27" s="60">
         <f t="shared" si="1"/>
-        <v>0.26090200048858203</v>
+        <v>0.34586705232421722</v>
       </c>
       <c r="H27" s="59">
         <f t="shared" si="4"/>
-        <v>73330786.030123994</v>
+        <v>85060156.365956932</v>
       </c>
       <c r="I27" s="60">
         <f t="shared" si="2"/>
-        <v>0.89452114453228126</v>
+        <v>1.0376011569726515</v>
       </c>
       <c r="J27" s="59">
         <f t="shared" si="5"/>
-        <v>3055449.4179218332</v>
+        <v>3544173.1819148725</v>
       </c>
       <c r="K27" s="59">
         <f t="shared" si="3"/>
-        <v>3564091.4161498337</v>
+        <v>3351519.6590425638</v>
       </c>
       <c r="L27" s="61" cm="1">
         <f t="array" ref="L27">+_xlfn.IFS(I27&gt;114%,H27*0.0125,I27&gt;109%,H27*0.01,I27&gt;104%,H27*0.0075,I27&gt;99%,H27*0.005,I27&lt;99%,H27*0)</f>
-        <v>0</v>
+        <v>425300.78182978468</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4935,34 +4935,34 @@
       </c>
       <c r="D28" s="4">
         <f>IFERROR(+VLOOKUP(B28,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>4367804.0145924808</v>
+      </c>
+      <c r="E28" s="4">
         <v>3875759.7054576175</v>
-      </c>
-      <c r="E28" s="4">
-        <v>3339149.8528803443</v>
       </c>
       <c r="F28" s="4">
         <f t="shared" si="8"/>
-        <v>536609.85257727327</v>
+        <v>492044.30913486332</v>
       </c>
       <c r="G28" s="5">
         <f t="shared" si="1"/>
-        <v>0.18455998597417225</v>
+        <v>0.2079906673615467</v>
       </c>
       <c r="H28" s="4">
         <f t="shared" si="4"/>
-        <v>13288318.990140401</v>
+        <v>13103412.043777443</v>
       </c>
       <c r="I28" s="5">
         <f t="shared" si="2"/>
-        <v>0.63277709476859056</v>
+        <v>0.62397200208464021</v>
       </c>
       <c r="J28" s="4">
         <f t="shared" si="5"/>
-        <v>553679.95792251674</v>
+        <v>545975.50182406011</v>
       </c>
       <c r="K28" s="4">
         <f t="shared" si="3"/>
-        <v>1007308.2526201402</v>
+        <v>1039512.24908797</v>
       </c>
       <c r="L28" s="63" cm="1">
         <f t="array" ref="L28">+_xlfn.IFS(I28&gt;114%,H28*0.02,I28&gt;109%,H28*0.015,I28&gt;104%,H28*0.0125,I28&gt;99%,H28*0.01,I28&lt;99%,H28*0)</f>
@@ -4979,34 +4979,34 @@
       </c>
       <c r="D29" s="4">
         <f>IFERROR(+VLOOKUP(B29,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>7520013.6941604447</v>
+      </c>
+      <c r="E29" s="4">
         <v>6757662.8877063803</v>
-      </c>
-      <c r="E29" s="4">
-        <v>6335712.8592704926</v>
       </c>
       <c r="F29" s="4">
         <f t="shared" si="8"/>
-        <v>421950.02843588777</v>
+        <v>762350.80645406432</v>
       </c>
       <c r="G29" s="5">
         <f t="shared" si="1"/>
-        <v>0.26253852561243451</v>
+        <v>0.29215622925521451</v>
       </c>
       <c r="H29" s="4">
         <f t="shared" si="4"/>
-        <v>23169129.900707588</v>
+        <v>22560041.082481332</v>
       </c>
       <c r="I29" s="5">
         <f t="shared" si="2"/>
-        <v>0.90013208781406107</v>
+        <v>0.87646868776564346</v>
       </c>
       <c r="J29" s="4">
         <f t="shared" si="5"/>
-        <v>965380.41252948286</v>
+        <v>940001.71177005558</v>
       </c>
       <c r="K29" s="4">
         <f t="shared" si="3"/>
-        <v>1116590.4183702129</v>
+        <v>1138730.3941149721</v>
       </c>
       <c r="L29" s="63" cm="1">
         <f t="array" ref="L29">+_xlfn.IFS(I29&gt;114%,H29*0.02,I29&gt;109%,H29*0.015,I29&gt;104%,H29*0.0125,I29&gt;99%,H29*0.01,I29&lt;99%,H29*0)</f>
@@ -5024,34 +5024,34 @@
       </c>
       <c r="D30" s="4">
         <f>IFERROR(+VLOOKUP(B30,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>6348650.0493735028</v>
+      </c>
+      <c r="E30" s="4">
         <v>5871001.8178605409</v>
-      </c>
-      <c r="E30" s="4">
-        <v>5102416.1731653139</v>
       </c>
       <c r="F30" s="4">
         <f t="shared" si="8"/>
-        <v>768585.64469522703</v>
+        <v>477648.23151296191</v>
       </c>
       <c r="G30" s="5">
         <f t="shared" si="1"/>
-        <v>0.15355766801770304</v>
+        <v>0.16605068894315708</v>
       </c>
       <c r="H30" s="4">
         <f t="shared" si="4"/>
-        <v>20129149.08980757</v>
+        <v>19045950.148120508</v>
       </c>
       <c r="I30" s="5">
         <f t="shared" si="2"/>
-        <v>0.52648343320355329</v>
+        <v>0.49815206682947122</v>
       </c>
       <c r="J30" s="4">
         <f t="shared" si="5"/>
-        <v>838714.54540864867</v>
+        <v>793581.25617168786</v>
       </c>
       <c r="K30" s="4">
         <f t="shared" si="3"/>
-        <v>1903659.0173097136</v>
+        <v>1992784.6914220105</v>
       </c>
       <c r="L30" s="63" cm="1">
         <f t="array" ref="L30">+_xlfn.IFS(I30&gt;114%,H30*0.02,I30&gt;109%,H30*0.015,I30&gt;104%,H30*0.0125,I30&gt;99%,H30*0.01,I30&lt;99%,H30*0)</f>
@@ -5069,34 +5069,34 @@
       </c>
       <c r="D31" s="4">
         <f>IFERROR(+VLOOKUP(B31,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>7212918.424210974</v>
+      </c>
+      <c r="E31" s="4">
         <v>6235749.7584266458</v>
-      </c>
-      <c r="E31" s="4">
-        <v>5326745.1355416654</v>
       </c>
       <c r="F31" s="4">
         <f t="shared" si="8"/>
-        <v>909004.6228849804</v>
+        <v>977168.66578432824</v>
       </c>
       <c r="G31" s="5">
         <f t="shared" si="1"/>
-        <v>0.24535464960709202</v>
+        <v>0.28380277291039724</v>
       </c>
       <c r="H31" s="4">
         <f t="shared" si="4"/>
-        <v>21379713.457462788</v>
+        <v>21638755.272632923</v>
       </c>
       <c r="I31" s="5">
         <f t="shared" si="2"/>
-        <v>0.84121594151002987</v>
+        <v>0.85140831873119183</v>
       </c>
       <c r="J31" s="4">
         <f t="shared" si="5"/>
-        <v>890821.39406094945</v>
+        <v>901614.80302637175</v>
       </c>
       <c r="K31" s="4">
         <f t="shared" si="3"/>
-        <v>1128205.8965631386</v>
+        <v>1137645.7234868142</v>
       </c>
       <c r="L31" s="63" cm="1">
         <f t="array" ref="L31">+_xlfn.IFS(I31&gt;114%,H31*0.02,I31&gt;109%,H31*0.015,I31&gt;104%,H31*0.0125,I31&gt;99%,H31*0.01,I31&lt;99%,H31*0)</f>
@@ -5114,34 +5114,34 @@
       </c>
       <c r="D32" s="4">
         <f>IFERROR(+VLOOKUP(B32,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>4813267.3862359719</v>
+      </c>
+      <c r="E32" s="4">
         <v>4132620.3846785584</v>
-      </c>
-      <c r="E32" s="4">
-        <v>3800655.2343727285</v>
       </c>
       <c r="F32" s="4">
         <f t="shared" si="8"/>
-        <v>331965.15030582994</v>
+        <v>680647.00155741349</v>
       </c>
       <c r="G32" s="5">
         <f t="shared" si="1"/>
-        <v>0.1639928724078793</v>
+        <v>0.19100267405698301</v>
       </c>
       <c r="H32" s="4">
         <f t="shared" si="4"/>
-        <v>14168984.176040772</v>
+        <v>14439802.158707917</v>
       </c>
       <c r="I32" s="5">
         <f t="shared" si="2"/>
-        <v>0.56226127682701477</v>
+        <v>0.57300802217094904</v>
       </c>
       <c r="J32" s="4">
         <f t="shared" si="5"/>
-        <v>590374.34066836548</v>
+        <v>601658.42327949649</v>
       </c>
       <c r="K32" s="4">
         <f t="shared" si="3"/>
-        <v>1239257.6244306732</v>
+        <v>1274170.7883602518</v>
       </c>
       <c r="L32" s="63" cm="1">
         <f t="array" ref="L32">+_xlfn.IFS(I32&gt;114%,H32*0.02,I32&gt;109%,H32*0.015,I32&gt;104%,H32*0.0125,I32&gt;99%,H32*0.01,I32&lt;99%,H32*0)</f>
@@ -5159,34 +5159,34 @@
       </c>
       <c r="D33" s="4">
         <f>IFERROR(+VLOOKUP(B33,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>5035112.3818729157</v>
+      </c>
+      <c r="E33" s="4">
         <v>3832290.7361907284</v>
-      </c>
-      <c r="E33" s="4">
-        <v>3355234.3973482912</v>
       </c>
       <c r="F33" s="4">
         <f t="shared" si="8"/>
-        <v>477056.33884243714</v>
+        <v>1202821.6456821873</v>
       </c>
       <c r="G33" s="5">
         <f t="shared" si="1"/>
-        <v>0.14463248270790677</v>
+        <v>0.19002754609047962</v>
       </c>
       <c r="H33" s="4">
         <f t="shared" si="4"/>
-        <v>13139282.524082497</v>
+        <v>15105337.145618748</v>
       </c>
       <c r="I33" s="5">
         <f t="shared" si="2"/>
-        <v>0.49588279785568029</v>
+        <v>0.5700826382714389</v>
       </c>
       <c r="J33" s="4">
         <f t="shared" si="5"/>
-        <v>547470.10517010407</v>
+        <v>629389.04773411446</v>
       </c>
       <c r="K33" s="4">
         <f t="shared" si="3"/>
-        <v>1333203.4861064276</v>
+        <v>1341352.3511329428</v>
       </c>
       <c r="L33" s="63" cm="1">
         <f t="array" ref="L33">+_xlfn.IFS(I33&gt;114%,H33*0.02,I33&gt;109%,H33*0.015,I33&gt;104%,H33*0.0125,I33&gt;99%,H33*0.01,I33&lt;99%,H33*0)</f>
@@ -5203,34 +5203,34 @@
       </c>
       <c r="D34" s="4">
         <f>IFERROR(+VLOOKUP(B34,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>3805787.6012926684</v>
+      </c>
+      <c r="E34" s="4">
         <v>3372720.3592291768</v>
-      </c>
-      <c r="E34" s="4">
-        <v>2447356.6153951334</v>
       </c>
       <c r="F34" s="4">
         <f t="shared" si="8"/>
-        <v>925363.74383404339</v>
+        <v>433067.24206349161</v>
       </c>
       <c r="G34" s="5">
         <f t="shared" si="1"/>
-        <v>0.16060573139186557</v>
+        <v>0.18122798101393658</v>
       </c>
       <c r="H34" s="4">
         <f t="shared" si="4"/>
-        <v>11563612.66021432</v>
+        <v>11417362.803878006</v>
       </c>
       <c r="I34" s="5">
         <f t="shared" si="2"/>
-        <v>0.55064822191496765</v>
+        <v>0.54368394304180978</v>
       </c>
       <c r="J34" s="4">
         <f t="shared" si="5"/>
-        <v>481817.1941755967</v>
+        <v>475723.45016158355</v>
       </c>
       <c r="K34" s="4">
         <f t="shared" si="3"/>
-        <v>1036898.8023982837</v>
+        <v>1074638.2749192081</v>
       </c>
       <c r="L34" s="63" cm="1">
         <f t="array" ref="L34">+_xlfn.IFS(I34&gt;114%,H34*0.02,I34&gt;109%,H34*0.015,I34&gt;104%,H34*0.0125,I34&gt;99%,H34*0.01,I34&lt;99%,H34*0)</f>
@@ -5247,34 +5247,34 @@
       </c>
       <c r="D35" s="4">
         <f>IFERROR(+VLOOKUP(B35,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>3442297.9978710278</v>
+      </c>
+      <c r="E35" s="4">
         <v>2627029.9340391951</v>
-      </c>
-      <c r="E35" s="4">
-        <v>1956633.4710906136</v>
       </c>
       <c r="F35" s="4">
         <f t="shared" si="8"/>
-        <v>670396.46294858144</v>
+        <v>815268.06383183273</v>
       </c>
       <c r="G35" s="5">
         <f t="shared" si="1"/>
-        <v>0.10653778191592229</v>
+        <v>0.13960053847689724</v>
       </c>
       <c r="H35" s="4">
         <f t="shared" si="4"/>
-        <v>9006959.7738486677</v>
+        <v>10326893.993613083</v>
       </c>
       <c r="I35" s="5">
         <f t="shared" si="2"/>
-        <v>0.36527239514030496</v>
+        <v>0.41880161543069172</v>
       </c>
       <c r="J35" s="4">
         <f t="shared" si="5"/>
-        <v>375289.99057702784</v>
+        <v>430287.24973387847</v>
       </c>
       <c r="K35" s="4">
         <f t="shared" si="3"/>
-        <v>1295951.1803506357</v>
+        <v>1325993.8751330609</v>
       </c>
       <c r="L35" s="63" cm="1">
         <f t="array" ref="L35">+_xlfn.IFS(I35&gt;114%,H35*0.02,I35&gt;109%,H35*0.015,I35&gt;104%,H35*0.0125,I35&gt;99%,H35*0.01,I35&lt;99%,H35*0)</f>
@@ -5291,34 +5291,34 @@
       </c>
       <c r="D36" s="4">
         <f>IFERROR(+VLOOKUP(B36,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>4684076.524209898</v>
+      </c>
+      <c r="E36" s="4">
         <v>4306128.2350271344</v>
-      </c>
-      <c r="E36" s="4">
-        <v>3355300.6510111671</v>
       </c>
       <c r="F36" s="4">
         <f t="shared" si="8"/>
-        <v>950827.58401596732</v>
+        <v>377948.28918276355</v>
       </c>
       <c r="G36" s="5">
         <f t="shared" si="1"/>
-        <v>0.17064110303257912</v>
+        <v>0.18561824942381208</v>
       </c>
       <c r="H36" s="4">
         <f t="shared" si="4"/>
-        <v>14763868.234378746</v>
+        <v>14052229.572629694</v>
       </c>
       <c r="I36" s="5">
         <f t="shared" si="2"/>
-        <v>0.58505521039741415</v>
+        <v>0.55685474827143622</v>
       </c>
       <c r="J36" s="4">
         <f t="shared" si="5"/>
-        <v>615161.17643244774</v>
+        <v>585509.56552623725</v>
       </c>
       <c r="K36" s="4">
         <f t="shared" si="3"/>
-        <v>1231110.1038219333</v>
+        <v>1284432.7172368814</v>
       </c>
       <c r="L36" s="63" cm="1">
         <f t="array" ref="L36">+_xlfn.IFS(I36&gt;114%,H36*0.02,I36&gt;109%,H36*0.015,I36&gt;104%,H36*0.0125,I36&gt;99%,H36*0.01,I36&lt;99%,H36*0)</f>
@@ -5335,34 +5335,34 @@
       </c>
       <c r="D37" s="4">
         <f>IFERROR(+VLOOKUP(B37,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>28341762.515582383</v>
+      </c>
+      <c r="E37" s="4">
         <v>26700664.115582384</v>
-      </c>
-      <c r="E37" s="4">
-        <v>26940309.263082385</v>
       </c>
       <c r="F37" s="4">
         <f t="shared" si="8"/>
-        <v>-239645.14750000089</v>
+        <v>1641098.3999999985</v>
       </c>
       <c r="G37" s="5">
         <f t="shared" si="1"/>
-        <v>0.2188368260891462</v>
+        <v>0.2322871568974495</v>
       </c>
       <c r="H37" s="4">
         <f t="shared" si="4"/>
-        <v>91545134.110568166</v>
+        <v>85025287.546747148</v>
       </c>
       <c r="I37" s="5">
         <f t="shared" si="2"/>
-        <v>0.75029768944850117</v>
+        <v>0.69686147069234849</v>
       </c>
       <c r="J37" s="4">
         <f t="shared" si="5"/>
-        <v>3814380.5879403404</v>
+        <v>3542720.3144477978</v>
       </c>
       <c r="K37" s="4">
         <f t="shared" si="3"/>
-        <v>5606534.4637892721</v>
+        <v>5854374.2177761011</v>
       </c>
       <c r="L37" s="63" cm="1">
         <f t="array" ref="L37">+_xlfn.IFS(I37&gt;114%,H37*0.0125,I37&gt;109%,H37*0.01,I37&gt;104%,H37*0.0075,I37&gt;99%,H37*0.005,I37&lt;99%,H37*0)</f>
@@ -5379,34 +5379,34 @@
       </c>
       <c r="D38" s="4">
         <f>IFERROR(+VLOOKUP(B38,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>2478634.4092995184</v>
+      </c>
+      <c r="E38" s="4">
         <v>1256116.5299</v>
-      </c>
-      <c r="E38" s="4">
-        <v>1084549.0049000001</v>
       </c>
       <c r="F38" s="4">
         <f t="shared" ref="F38" si="10">+D38-E38</f>
-        <v>171567.52499999991</v>
+        <v>1222517.8793995185</v>
       </c>
       <c r="G38" s="5">
         <f t="shared" si="1"/>
-        <v>3.5185336971988793E-2</v>
+        <v>6.9429535274496315E-2</v>
       </c>
       <c r="H38" s="4">
         <f t="shared" si="4"/>
-        <v>4306685.2453714283</v>
+        <v>7435903.2278985549</v>
       </c>
       <c r="I38" s="5">
         <f t="shared" si="2"/>
-        <v>0.12063544104681873</v>
+        <v>0.20828860582348893</v>
       </c>
       <c r="J38" s="4">
         <f t="shared" si="5"/>
-        <v>179445.21855714286</v>
+        <v>309829.30116243981</v>
       </c>
       <c r="K38" s="4">
         <f t="shared" si="3"/>
-        <v>2026110.7923588236</v>
+        <v>2076335.3494187801</v>
       </c>
       <c r="L38" s="63" cm="1">
         <f t="array" ref="L38">+_xlfn.IFS(I38&gt;109%,H38*0.015,I38&gt;104%,H38*0.0125,I38&gt;99%,H38*0.01,I38&lt;99%,H38*0)</f>
@@ -5423,34 +5423,34 @@
       </c>
       <c r="D39" s="4">
         <f>IFERROR(+VLOOKUP(B39,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>8818400.8023845814</v>
+      </c>
+      <c r="E39" s="4">
         <v>8333389.4092635857</v>
-      </c>
-      <c r="E39" s="4">
-        <v>7332096.3798651379</v>
       </c>
       <c r="F39" s="4">
         <f t="shared" si="8"/>
-        <v>1001293.0293984478</v>
+        <v>485011.39312099572</v>
       </c>
       <c r="G39" s="5">
         <f t="shared" si="1"/>
-        <v>0.22918212863037507</v>
+        <v>0.2425207520915432</v>
       </c>
       <c r="H39" s="4">
         <f t="shared" si="4"/>
-        <v>28571620.831760861</v>
+        <v>26455202.407153744</v>
       </c>
       <c r="I39" s="5">
         <f t="shared" si="2"/>
-        <v>0.78576729816128577</v>
+        <v>0.72756225627462967</v>
       </c>
       <c r="J39" s="4">
         <f t="shared" si="5"/>
-        <v>1190484.2013233693</v>
+        <v>1102300.1002980727</v>
       </c>
       <c r="K39" s="4">
         <f t="shared" si="3"/>
-        <v>1648708.1370433185</v>
+        <v>1721439.1835384637</v>
       </c>
       <c r="L39" s="63" cm="1">
         <f t="array" ref="L39">+_xlfn.IFS(I39&gt;114%,H39*0.02,I39&gt;109%,H39*0.015,I39&gt;104%,H39*0.0125,I39&gt;99%,H39*0.01,I39&lt;99%,H39*0)</f>
@@ -5465,34 +5465,34 @@
       </c>
       <c r="D40" s="67">
         <f>+SUM(D27:D39)</f>
+        <v>115222111.25640535</v>
+      </c>
+      <c r="E40" s="65">
         <v>98689279.798814774</v>
-      </c>
-      <c r="E40" s="65">
-        <v>89313306.794087753</v>
       </c>
       <c r="F40" s="67">
         <f t="shared" si="8"/>
-        <v>9375973.0047270209</v>
+        <v>16532831.45759058</v>
       </c>
       <c r="G40" s="66">
         <f t="shared" si="1"/>
-        <v>0.19387752588476509</v>
+        <v>0.22635668132496897</v>
       </c>
       <c r="H40" s="64">
         <f t="shared" si="4"/>
-        <v>338363245.02450776</v>
+        <v>345666333.76921606</v>
       </c>
       <c r="I40" s="66">
         <f t="shared" si="2"/>
-        <v>0.66472294589062308</v>
+        <v>0.67907004397490689</v>
       </c>
       <c r="J40" s="64">
         <f t="shared" si="5"/>
-        <v>14098468.542687824</v>
+        <v>14402763.907050669</v>
       </c>
       <c r="K40" s="67">
         <f t="shared" si="3"/>
-        <v>24137629.591312408</v>
+        <v>24612929.474670023</v>
       </c>
       <c r="L40" s="68"/>
     </row>
@@ -5506,34 +5506,34 @@
       </c>
       <c r="D41" s="81">
         <f>+D40+D26+D10+D16</f>
+        <v>397625858.39552885</v>
+      </c>
+      <c r="E41" s="82">
         <v>347037445.52567512</v>
-      </c>
-      <c r="E41" s="82">
-        <v>319078802.18563056</v>
       </c>
       <c r="F41" s="81">
         <f>+D41-E41</f>
-        <v>27958643.340044558</v>
+        <v>50588412.869853735</v>
       </c>
       <c r="G41" s="83">
         <f t="shared" si="1"/>
-        <v>0.25151884958038478</v>
+        <v>0.28818330631602479</v>
       </c>
       <c r="H41" s="81">
         <f t="shared" si="4"/>
-        <v>1189842670.3737433</v>
+        <v>1192877575.1865866</v>
       </c>
       <c r="I41" s="83">
         <f t="shared" si="2"/>
-        <v>0.86235034141846212</v>
+        <v>0.86454991894807443</v>
       </c>
       <c r="J41" s="81">
         <f t="shared" si="5"/>
-        <v>49576777.932239302</v>
+        <v>49703232.299441107</v>
       </c>
       <c r="K41" s="81">
         <f t="shared" si="3"/>
-        <v>60748805.974556528</v>
+        <v>61383830.543600455</v>
       </c>
       <c r="L41" s="84"/>
     </row>
@@ -5596,19 +5596,19 @@
       </c>
       <c r="H43" s="4">
         <f t="shared" ref="H43" si="12">+D43/$N$3*$N$4</f>
-        <v>27786349.92753322</v>
+        <v>24313056.186591566</v>
       </c>
       <c r="I43" s="5">
         <f>+H43/C43</f>
-        <v>0.69465874818833051</v>
+        <v>0.6078264046647891</v>
       </c>
       <c r="J43" s="4">
         <f t="shared" ref="J43" si="13">+D43/$N$3</f>
-        <v>1157764.5803138842</v>
+        <v>1013044.0077746486</v>
       </c>
       <c r="K43" s="4">
         <f>+(C43-D43)/$N$2</f>
-        <v>1876214.5845766359</v>
+        <v>1993477.9961126756</v>
       </c>
       <c r="L43" s="4" cm="1">
         <f t="array" ref="L43">+_xlfn.IFS(I43&gt;114%,H43*0.02,I43&gt;109%,H43*0.015,I43&gt;104%,H43*0.0125,I43&gt;99%,H43*0.01,I43&lt;99%,H43*0)</f>
@@ -5639,23 +5639,23 @@
       </c>
       <c r="H44" s="4">
         <f t="shared" ref="H44" si="15">+D44/$N$3*$N$4</f>
-        <v>48143299.967392482</v>
+        <v>42125387.471468419</v>
       </c>
       <c r="I44" s="5">
         <f>+H44/C44</f>
-        <v>1.6047766655797493</v>
+        <v>1.4041795823822807</v>
       </c>
       <c r="J44" s="4">
         <f t="shared" ref="J44" si="16">+D44/$N$3</f>
-        <v>2005970.8319746868</v>
+        <v>1755224.4779778509</v>
       </c>
       <c r="K44" s="4">
         <f>+(C44-D44)/$N$2</f>
-        <v>938717.89271630545</v>
+        <v>997387.76101107453</v>
       </c>
       <c r="L44" s="4" cm="1">
         <f t="array" ref="L44">+_xlfn.IFS(I44&gt;114%,H44*0.02,I44&gt;109%,H44*0.015,I44&gt;104%,H44*0.0125,I44&gt;99%,H44*0.01,I44&lt;99%,H44*0)</f>
-        <v>962865.99934784963</v>
+        <v>842507.74942936841</v>
       </c>
     </row>
   </sheetData>
@@ -5793,14 +5793,14 @@
       </c>
       <c r="D2" s="22">
         <f>H2/G2</f>
-        <v>0.58333333333333337</v>
+        <v>0.59722222222222221</v>
       </c>
       <c r="E2" s="13">
         <v>33</v>
       </c>
       <c r="F2" s="12">
         <f>+H2-E2</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2" s="13">
         <f>VLOOKUP(B2,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -5808,11 +5808,11 @@
       </c>
       <c r="H2" s="13">
         <f>VLOOKUP(B2,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I2" s="17">
         <f>(+G2*$M$2)-H2</f>
-        <v>19.199999999999996</v>
+        <v>18.199999999999996</v>
       </c>
       <c r="J2" t="s">
         <v>55</v>
@@ -5858,14 +5858,14 @@
       </c>
       <c r="D3" s="22">
         <f t="shared" ref="D3:D38" si="0">H3/G3</f>
-        <v>0.22175732217573221</v>
+        <v>0.35146443514644349</v>
       </c>
       <c r="E3" s="13">
         <v>1</v>
       </c>
       <c r="F3" s="12">
         <f t="shared" ref="F3:F38" si="1">+H3-E3</f>
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="G3" s="13">
         <f>VLOOKUP(B3,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -5873,11 +5873,11 @@
       </c>
       <c r="H3" s="13">
         <f>VLOOKUP(B3,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="I3" s="17">
         <f t="shared" ref="I3:I38" si="2">(+G3*$M$2)-H3</f>
-        <v>150.15</v>
+        <v>119.15</v>
       </c>
       <c r="J3" t="s">
         <v>56</v>
@@ -5896,14 +5896,14 @@
         <v>145 - ALMACEN</v>
       </c>
       <c r="S3" s="12">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="T3" s="12">
         <v>214</v>
       </c>
       <c r="U3" s="41">
         <f>+S3/T3</f>
-        <v>0.14485981308411214</v>
+        <v>0.16822429906542055</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
@@ -5917,14 +5917,14 @@
       </c>
       <c r="D4" s="22">
         <f t="shared" si="0"/>
-        <v>0.62114537444933926</v>
+        <v>0.65198237885462551</v>
       </c>
       <c r="E4" s="13">
         <v>126</v>
       </c>
       <c r="F4" s="12">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G4" s="13">
         <f>VLOOKUP(B4,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -5932,11 +5932,11 @@
       </c>
       <c r="H4" s="13">
         <f>VLOOKUP(B4,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="I4" s="17">
         <f t="shared" si="2"/>
-        <v>51.949999999999989</v>
+        <v>44.949999999999989</v>
       </c>
       <c r="J4" t="s">
         <v>57</v>
@@ -5954,14 +5954,14 @@
         <v>145 - Articulos Sin Asociar Agrupacion</v>
       </c>
       <c r="S4" s="13">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T4" s="13">
         <v>214</v>
       </c>
       <c r="U4" s="5">
         <f t="shared" ref="U4:U11" si="3">+S4/T4</f>
-        <v>7.476635514018691E-2</v>
+        <v>7.9439252336448593E-2</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
@@ -6009,14 +6009,14 @@
         <v>145 - BEBIDAS</v>
       </c>
       <c r="S5" s="13">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="T5" s="13">
         <v>214</v>
       </c>
       <c r="U5" s="5">
         <f t="shared" si="3"/>
-        <v>0.19626168224299065</v>
+        <v>0.21962616822429906</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
@@ -6030,14 +6030,14 @@
       </c>
       <c r="D6" s="22">
         <f t="shared" si="0"/>
-        <v>0.63285024154589375</v>
+        <v>0.64251207729468596</v>
       </c>
       <c r="E6" s="13">
         <v>100</v>
       </c>
       <c r="F6" s="12">
         <f t="shared" si="1"/>
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G6" s="13">
         <f>VLOOKUP(B6,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6045,11 +6045,11 @@
       </c>
       <c r="H6" s="13">
         <f>VLOOKUP(B6,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="I6" s="17">
         <f t="shared" si="2"/>
-        <v>44.949999999999989</v>
+        <v>42.949999999999989</v>
       </c>
       <c r="J6" t="s">
         <v>58</v>
@@ -6067,14 +6067,14 @@
         <v>145 - CHOCOLATE</v>
       </c>
       <c r="S6" s="13">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="T6" s="13">
         <v>214</v>
       </c>
       <c r="U6" s="5">
         <f t="shared" si="3"/>
-        <v>6.5420560747663545E-2</v>
+        <v>8.4112149532710276E-2</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
@@ -6088,14 +6088,14 @@
       </c>
       <c r="D7" s="22">
         <f t="shared" si="0"/>
-        <v>0.43939393939393939</v>
+        <v>0.46969696969696972</v>
       </c>
       <c r="E7" s="13">
         <v>81</v>
       </c>
       <c r="F7" s="12">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G7" s="13">
         <f>VLOOKUP(B7,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6103,11 +6103,11 @@
       </c>
       <c r="H7" s="13">
         <f>VLOOKUP(B7,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="I7" s="17">
         <f t="shared" si="2"/>
-        <v>81.299999999999983</v>
+        <v>75.299999999999983</v>
       </c>
       <c r="J7" t="s">
         <v>58</v>
@@ -6125,14 +6125,14 @@
         <v>145 - GALLETITAS</v>
       </c>
       <c r="S7" s="13">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="T7" s="13">
         <v>214</v>
       </c>
       <c r="U7" s="5">
         <f t="shared" si="3"/>
-        <v>0.23364485981308411</v>
+        <v>0.24299065420560748</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
@@ -6146,14 +6146,14 @@
       </c>
       <c r="D8" s="22">
         <f t="shared" si="0"/>
-        <v>0.56542056074766356</v>
+        <v>0.58411214953271029</v>
       </c>
       <c r="E8" s="13">
         <v>89</v>
       </c>
       <c r="F8" s="12">
         <f t="shared" si="1"/>
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G8" s="13">
         <f>VLOOKUP(B8,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6161,11 +6161,11 @@
       </c>
       <c r="H8" s="13">
         <f>VLOOKUP(B8,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="I8" s="17">
         <f t="shared" si="2"/>
-        <v>60.900000000000006</v>
+        <v>56.900000000000006</v>
       </c>
       <c r="J8" t="s">
         <v>55</v>
@@ -6205,14 +6205,14 @@
       </c>
       <c r="D9" s="22">
         <f>H9/G9</f>
-        <v>0.5625</v>
+        <v>0.60624999999999996</v>
       </c>
       <c r="E9" s="13">
         <v>92</v>
       </c>
       <c r="F9" s="12">
         <f t="shared" si="1"/>
-        <v>-2</v>
+        <v>5</v>
       </c>
       <c r="G9" s="13">
         <f>VLOOKUP(B9,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6220,11 +6220,11 @@
       </c>
       <c r="H9" s="13">
         <f>VLOOKUP(B9,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="I9" s="17">
         <f t="shared" si="2"/>
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="J9" t="s">
         <v>55</v>
@@ -6263,14 +6263,14 @@
       </c>
       <c r="D10" s="22">
         <f t="shared" si="0"/>
-        <v>0.4358974358974359</v>
+        <v>0.46153846153846156</v>
       </c>
       <c r="E10" s="13">
         <v>64</v>
       </c>
       <c r="F10" s="12">
         <f t="shared" si="1"/>
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G10" s="13">
         <f>VLOOKUP(B10,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6278,11 +6278,11 @@
       </c>
       <c r="H10" s="13">
         <f>VLOOKUP(B10,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="I10" s="17">
         <f t="shared" si="2"/>
-        <v>80.75</v>
+        <v>75.75</v>
       </c>
       <c r="J10" t="s">
         <v>58</v>
@@ -6300,14 +6300,14 @@
         <v>145 - NO PERECEDEROS</v>
       </c>
       <c r="S10" s="13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T10" s="13">
         <v>214</v>
       </c>
       <c r="U10" s="5">
         <f t="shared" si="3"/>
-        <v>3.7383177570093455E-2</v>
+        <v>4.2056074766355138E-2</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
@@ -6321,14 +6321,14 @@
       </c>
       <c r="D11" s="32">
         <f t="shared" si="0"/>
-        <v>0.22772277227722773</v>
+        <v>0.23762376237623761</v>
       </c>
       <c r="E11" s="31">
         <v>19</v>
       </c>
       <c r="F11" s="33">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G11" s="13">
         <f>VLOOKUP(B11,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6336,11 +6336,11 @@
       </c>
       <c r="H11" s="13">
         <f>VLOOKUP(B11,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I11" s="34">
         <f t="shared" si="2"/>
-        <v>62.849999999999994</v>
+        <v>61.849999999999994</v>
       </c>
       <c r="J11" t="s">
         <v>59</v>
@@ -6355,14 +6355,14 @@
         <v>145 - PILAS</v>
       </c>
       <c r="S11" s="13">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="T11" s="13">
         <v>214</v>
       </c>
       <c r="U11" s="5">
         <f t="shared" si="3"/>
-        <v>5.6074766355140186E-2</v>
+        <v>6.5420560747663545E-2</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
@@ -6376,14 +6376,14 @@
       </c>
       <c r="D12" s="32">
         <f t="shared" si="0"/>
-        <v>0.22857142857142856</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="E12" s="31">
         <v>24</v>
       </c>
       <c r="F12" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G12" s="13">
         <f>VLOOKUP(B12,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6391,11 +6391,11 @@
       </c>
       <c r="H12" s="13">
         <f>VLOOKUP(B12,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I12" s="34">
         <f t="shared" si="2"/>
-        <v>65.25</v>
+        <v>59.25</v>
       </c>
       <c r="J12" t="s">
         <v>59</v>
@@ -6412,14 +6412,14 @@
       </c>
       <c r="D13" s="22">
         <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
+        <v>0.58461538461538465</v>
       </c>
       <c r="E13" s="13">
         <v>144</v>
       </c>
       <c r="F13" s="12">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G13" s="13">
         <f>VLOOKUP(B13,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6427,11 +6427,11 @@
       </c>
       <c r="H13" s="13">
         <f>VLOOKUP(B13,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="I13" s="17">
         <f t="shared" si="2"/>
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="J13" t="s">
         <v>57</v>
@@ -6451,14 +6451,14 @@
       </c>
       <c r="D14" s="22">
         <f t="shared" si="0"/>
-        <v>0.46703296703296704</v>
+        <v>0.51098901098901095</v>
       </c>
       <c r="E14" s="13">
         <v>85</v>
       </c>
       <c r="F14" s="12">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G14" s="13">
         <f>VLOOKUP(B14,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6466,11 +6466,11 @@
       </c>
       <c r="H14" s="13">
         <f>VLOOKUP(B14,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="I14" s="17">
         <f t="shared" si="2"/>
-        <v>69.699999999999989</v>
+        <v>61.699999999999989</v>
       </c>
       <c r="J14" t="s">
         <v>55</v>
@@ -6486,7 +6486,7 @@
       <c r="E15" s="14"/>
       <c r="F15" s="16">
         <f>+SUM(F2:F14)</f>
-        <v>181</v>
+        <v>268</v>
       </c>
       <c r="G15" s="8">
         <f>+SUM(G2:G14)</f>
@@ -6494,7 +6494,7 @@
       </c>
       <c r="H15" s="8">
         <f>+SUM(H2:H14)</f>
-        <v>1060</v>
+        <v>1147</v>
       </c>
       <c r="I15" s="8"/>
     </row>
@@ -6511,14 +6511,14 @@
       </c>
       <c r="D16" s="22">
         <f t="shared" si="0"/>
-        <v>0.64375000000000004</v>
+        <v>0.68125000000000002</v>
       </c>
       <c r="E16" s="13">
         <v>90</v>
       </c>
       <c r="F16" s="12">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G16" s="13">
         <f>VLOOKUP(B16,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6526,11 +6526,11 @@
       </c>
       <c r="H16" s="13">
         <f>VLOOKUP(B16,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="I16" s="17">
         <f t="shared" si="2"/>
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="J16" t="s">
         <v>55</v>
@@ -6550,14 +6550,14 @@
       </c>
       <c r="D17" s="22">
         <f t="shared" si="0"/>
-        <v>0.37128712871287128</v>
+        <v>0.36138613861386137</v>
       </c>
       <c r="E17" s="13">
         <v>92</v>
       </c>
       <c r="F17" s="12">
         <f t="shared" si="1"/>
-        <v>-17</v>
+        <v>-19</v>
       </c>
       <c r="G17" s="13">
         <f>VLOOKUP(B17,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6565,11 +6565,11 @@
       </c>
       <c r="H17" s="13">
         <f>VLOOKUP(B17,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I17" s="17">
         <f t="shared" si="2"/>
-        <v>96.699999999999989</v>
+        <v>98.699999999999989</v>
       </c>
       <c r="J17" t="s">
         <v>55</v>
@@ -6589,14 +6589,14 @@
       </c>
       <c r="D18" s="22">
         <f t="shared" si="0"/>
-        <v>0.67647058823529416</v>
+        <v>0.68823529411764706</v>
       </c>
       <c r="E18" s="13">
         <v>88</v>
       </c>
       <c r="F18" s="12">
         <f t="shared" si="1"/>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G18" s="13">
         <f>VLOOKUP(B18,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6604,11 +6604,11 @@
       </c>
       <c r="H18" s="13">
         <f>VLOOKUP(B18,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I18" s="17">
         <f t="shared" si="2"/>
-        <v>29.5</v>
+        <v>27.5</v>
       </c>
       <c r="J18" t="s">
         <v>58</v>
@@ -6628,14 +6628,14 @@
       </c>
       <c r="D19" s="22">
         <f t="shared" si="0"/>
-        <v>0.66233766233766234</v>
+        <v>0.68181818181818177</v>
       </c>
       <c r="E19" s="13">
         <v>95</v>
       </c>
       <c r="F19" s="12">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G19" s="13">
         <f>VLOOKUP(B19,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6643,11 +6643,11 @@
       </c>
       <c r="H19" s="13">
         <f>VLOOKUP(B19,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="I19" s="17">
         <f t="shared" si="2"/>
-        <v>28.900000000000006</v>
+        <v>25.900000000000006</v>
       </c>
       <c r="J19" t="s">
         <v>58</v>
@@ -6667,14 +6667,14 @@
       </c>
       <c r="D20" s="22">
         <f t="shared" si="0"/>
-        <v>0.63276836158192096</v>
+        <v>0.64971751412429379</v>
       </c>
       <c r="E20" s="13">
         <v>83</v>
       </c>
       <c r="F20" s="12">
         <f t="shared" si="1"/>
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G20" s="13">
         <f>VLOOKUP(B20,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6682,11 +6682,11 @@
       </c>
       <c r="H20" s="13">
         <f>VLOOKUP(B20,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="I20" s="17">
         <f t="shared" si="2"/>
-        <v>38.449999999999989</v>
+        <v>35.449999999999989</v>
       </c>
       <c r="J20" t="s">
         <v>55</v>
@@ -6706,14 +6706,14 @@
       </c>
       <c r="D21" s="22">
         <f t="shared" si="0"/>
-        <v>0.59171597633136097</v>
+        <v>0.62130177514792895</v>
       </c>
       <c r="E21" s="13">
         <v>64</v>
       </c>
       <c r="F21" s="12">
         <f t="shared" si="1"/>
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G21" s="13">
         <f>VLOOKUP(B21,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6721,11 +6721,11 @@
       </c>
       <c r="H21" s="13">
         <f>VLOOKUP(B21,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="I21" s="17">
         <f t="shared" si="2"/>
-        <v>43.650000000000006</v>
+        <v>38.650000000000006</v>
       </c>
       <c r="J21" t="s">
         <v>58</v>
@@ -6784,14 +6784,14 @@
       </c>
       <c r="D23" s="22">
         <f t="shared" si="0"/>
-        <v>0.54347826086956519</v>
+        <v>0.55797101449275366</v>
       </c>
       <c r="E23" s="13">
         <v>70</v>
       </c>
       <c r="F23" s="12">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G23" s="13">
         <f>VLOOKUP(B23,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6799,11 +6799,11 @@
       </c>
       <c r="H23" s="13">
         <f>VLOOKUP(B23,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I23" s="17">
         <f t="shared" si="2"/>
-        <v>42.3</v>
+        <v>40.299999999999997</v>
       </c>
       <c r="J23" t="s">
         <v>58</v>
@@ -6823,14 +6823,14 @@
       </c>
       <c r="D24" s="22">
         <f t="shared" si="0"/>
-        <v>0.57058823529411762</v>
+        <v>0.58823529411764708</v>
       </c>
       <c r="E24" s="13">
         <v>79</v>
       </c>
       <c r="F24" s="12">
         <f t="shared" si="1"/>
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G24" s="13">
         <f>VLOOKUP(B24,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6838,11 +6838,11 @@
       </c>
       <c r="H24" s="13">
         <f>VLOOKUP(B24,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I24" s="17">
         <f t="shared" si="2"/>
-        <v>47.5</v>
+        <v>44.5</v>
       </c>
       <c r="J24" t="s">
         <v>60</v>
@@ -6858,7 +6858,7 @@
       <c r="E25" s="14"/>
       <c r="F25" s="16">
         <f>+SUM(F16:F24)</f>
-        <v>112</v>
+        <v>134</v>
       </c>
       <c r="G25" s="8">
         <f>+SUM(G16:G24)</f>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="H25" s="8">
         <f>+SUM(H16:H24)</f>
-        <v>839</v>
+        <v>861</v>
       </c>
       <c r="I25" s="8"/>
     </row>
@@ -6883,14 +6883,14 @@
       </c>
       <c r="D26" s="22">
         <f t="shared" si="0"/>
-        <v>0.40350877192982454</v>
+        <v>0.45614035087719296</v>
       </c>
       <c r="E26" s="13">
         <v>20</v>
       </c>
       <c r="F26" s="12">
         <f>+H26-E26</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G26" s="13">
         <f>VLOOKUP(B26,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6898,11 +6898,11 @@
       </c>
       <c r="H26" s="13">
         <f>VLOOKUP(B26,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I26" s="17">
         <f t="shared" si="2"/>
-        <v>25.449999999999996</v>
+        <v>22.449999999999996</v>
       </c>
       <c r="J26" t="s">
         <v>55</v>
@@ -6922,14 +6922,14 @@
       </c>
       <c r="D27" s="22">
         <f t="shared" si="0"/>
-        <v>0.50318471337579618</v>
+        <v>0.51592356687898089</v>
       </c>
       <c r="E27" s="13">
         <v>68</v>
       </c>
       <c r="F27" s="12">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G27" s="13">
         <f>VLOOKUP(B27,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6937,11 +6937,11 @@
       </c>
       <c r="H27" s="13">
         <f>VLOOKUP(B27,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I27" s="17">
         <f t="shared" si="2"/>
-        <v>54.449999999999989</v>
+        <v>52.449999999999989</v>
       </c>
       <c r="J27" t="s">
         <v>58</v>
@@ -6961,14 +6961,14 @@
       </c>
       <c r="D28" s="22">
         <f t="shared" si="0"/>
-        <v>0.55900621118012417</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="E28" s="13">
         <v>80</v>
       </c>
       <c r="F28" s="12">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G28" s="13">
         <f>VLOOKUP(B28,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6976,11 +6976,11 @@
       </c>
       <c r="H28" s="13">
         <f>VLOOKUP(B28,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I28" s="17">
         <f t="shared" si="2"/>
-        <v>46.849999999999994</v>
+        <v>44.849999999999994</v>
       </c>
       <c r="J28" t="s">
         <v>58</v>
@@ -7000,14 +7000,14 @@
       </c>
       <c r="D29" s="22">
         <f t="shared" si="0"/>
-        <v>0.27710843373493976</v>
+        <v>0.30522088353413657</v>
       </c>
       <c r="E29" s="13">
         <v>68</v>
       </c>
       <c r="F29" s="12">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G29" s="13">
         <f>VLOOKUP(B29,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7015,11 +7015,11 @@
       </c>
       <c r="H29" s="13">
         <f>VLOOKUP(B29,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="I29" s="17">
         <f t="shared" si="2"/>
-        <v>142.65</v>
+        <v>135.65</v>
       </c>
       <c r="J29" t="s">
         <v>58</v>
@@ -7039,14 +7039,14 @@
       </c>
       <c r="D30" s="22">
         <f t="shared" si="0"/>
-        <v>0.66187050359712229</v>
+        <v>0.69784172661870503</v>
       </c>
       <c r="E30" s="13">
         <v>73</v>
       </c>
       <c r="F30" s="12">
         <f t="shared" si="1"/>
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G30" s="13">
         <f>VLOOKUP(B30,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7054,11 +7054,11 @@
       </c>
       <c r="H30" s="13">
         <f>VLOOKUP(B30,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="I30" s="17">
         <f t="shared" si="2"/>
-        <v>26.149999999999991</v>
+        <v>21.149999999999991</v>
       </c>
       <c r="J30" t="s">
         <v>55</v>
@@ -7078,14 +7078,14 @@
       </c>
       <c r="D31" s="22">
         <f t="shared" si="0"/>
-        <v>0.4143646408839779</v>
+        <v>0.43093922651933703</v>
       </c>
       <c r="E31" s="13">
         <v>40</v>
       </c>
       <c r="F31" s="12">
         <f t="shared" si="1"/>
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G31" s="13">
         <f>VLOOKUP(B31,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7093,11 +7093,11 @@
       </c>
       <c r="H31" s="13">
         <f>VLOOKUP(B31,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I31" s="17">
         <f t="shared" si="2"/>
-        <v>78.849999999999994</v>
+        <v>75.849999999999994</v>
       </c>
       <c r="J31" t="s">
         <v>58</v>
@@ -7117,14 +7117,14 @@
       </c>
       <c r="D32" s="22">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0.52976190476190477</v>
       </c>
       <c r="E32" s="13">
         <v>67</v>
       </c>
       <c r="F32" s="12">
         <f t="shared" si="1"/>
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G32" s="13">
         <f>VLOOKUP(B32,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7132,11 +7132,11 @@
       </c>
       <c r="H32" s="13">
         <f>VLOOKUP(B32,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="I32" s="17">
         <f t="shared" si="2"/>
-        <v>58.799999999999983</v>
+        <v>53.799999999999983</v>
       </c>
       <c r="J32" t="s">
         <v>58</v>
@@ -7156,14 +7156,14 @@
       </c>
       <c r="D33" s="22">
         <f t="shared" si="0"/>
-        <v>0.5178571428571429</v>
+        <v>0.5357142857142857</v>
       </c>
       <c r="E33" s="13">
         <v>66</v>
       </c>
       <c r="F33" s="12">
         <f t="shared" si="1"/>
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G33" s="13">
         <f>VLOOKUP(B33,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7171,11 +7171,11 @@
       </c>
       <c r="H33" s="13">
         <f>VLOOKUP(B33,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I33" s="17">
         <f t="shared" si="2"/>
-        <v>55.799999999999983</v>
+        <v>52.799999999999983</v>
       </c>
       <c r="J33" t="s">
         <v>58</v>
@@ -7195,14 +7195,14 @@
       </c>
       <c r="D34" s="22">
         <f t="shared" si="0"/>
-        <v>0.3380281690140845</v>
+        <v>0.40845070422535212</v>
       </c>
       <c r="E34" s="13">
         <v>82</v>
       </c>
       <c r="F34" s="12">
         <f t="shared" si="1"/>
-        <v>-34</v>
+        <v>-24</v>
       </c>
       <c r="G34" s="13">
         <f>VLOOKUP(B34,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7210,11 +7210,11 @@
       </c>
       <c r="H34" s="13">
         <f>VLOOKUP(B34,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="I34" s="17">
         <f t="shared" si="2"/>
-        <v>72.7</v>
+        <v>62.7</v>
       </c>
       <c r="J34" t="s">
         <v>55</v>
@@ -7234,14 +7234,14 @@
       </c>
       <c r="D35" s="22">
         <f t="shared" si="0"/>
-        <v>0.48314606741573035</v>
+        <v>0.5056179775280899</v>
       </c>
       <c r="E35" s="13">
         <v>81</v>
       </c>
       <c r="F35" s="12">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G35" s="13">
         <f>VLOOKUP(B35,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7249,11 +7249,11 @@
       </c>
       <c r="H35" s="13">
         <f>VLOOKUP(B35,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="I35" s="17">
         <f t="shared" si="2"/>
-        <v>65.299999999999983</v>
+        <v>61.299999999999983</v>
       </c>
       <c r="J35" t="s">
         <v>58</v>
@@ -7273,7 +7273,7 @@
       </c>
       <c r="D36" s="22">
         <f t="shared" si="0"/>
-        <v>3.5398230088495575E-2</v>
+        <v>3.5087719298245612E-2</v>
       </c>
       <c r="E36" s="13">
         <v>0</v>
@@ -7284,7 +7284,7 @@
       </c>
       <c r="G36" s="13">
         <f>VLOOKUP(B36,'Base Cobertura'!$A:$C,3,FALSE)</f>
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H36" s="13">
         <f>VLOOKUP(B36,'Base Cobertura'!$A:$C,2,FALSE)</f>
@@ -7292,7 +7292,7 @@
       </c>
       <c r="I36" s="17">
         <f t="shared" si="2"/>
-        <v>92.05</v>
+        <v>92.899999999999991</v>
       </c>
       <c r="J36" t="s">
         <v>58</v>
@@ -7309,14 +7309,14 @@
       </c>
       <c r="D37" s="22">
         <f t="shared" si="0"/>
-        <v>6.7307692307692304E-2</v>
+        <v>7.6923076923076927E-2</v>
       </c>
       <c r="E37" s="13">
         <v>17</v>
       </c>
       <c r="F37" s="12">
         <f t="shared" si="1"/>
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="G37" s="13">
         <f>VLOOKUP(B37,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7324,11 +7324,11 @@
       </c>
       <c r="H37" s="13">
         <f>VLOOKUP(B37,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I37" s="17">
         <f t="shared" si="2"/>
-        <v>81.399999999999991</v>
+        <v>80.399999999999991</v>
       </c>
       <c r="J37" t="s">
         <v>59</v>
@@ -7345,14 +7345,14 @@
       </c>
       <c r="D38" s="22">
         <f t="shared" si="0"/>
-        <v>0.55905511811023623</v>
+        <v>0.59055118110236215</v>
       </c>
       <c r="E38" s="13">
         <v>60</v>
       </c>
       <c r="F38" s="12">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G38" s="13">
         <f>VLOOKUP(B38,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7360,11 +7360,11 @@
       </c>
       <c r="H38" s="13">
         <f>VLOOKUP(B38,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="I38" s="17">
         <f t="shared" si="2"/>
-        <v>36.950000000000003</v>
+        <v>32.950000000000003</v>
       </c>
       <c r="J38" t="s">
         <v>55</v>
@@ -7380,15 +7380,15 @@
       <c r="E39" s="14"/>
       <c r="F39" s="8">
         <f>+SUM(F26:F38)</f>
-        <v>93</v>
+        <v>142</v>
       </c>
       <c r="G39" s="8">
         <f>+SUM(G26:G38)</f>
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="H39" s="8">
         <f>+SUM(H26:H38)</f>
-        <v>815</v>
+        <v>864</v>
       </c>
       <c r="I39" s="8"/>
       <c r="L39" t="s">
@@ -7404,20 +7404,20 @@
       <c r="E40" s="6"/>
       <c r="F40" s="8">
         <f>+SUM(F39+F25+F15)</f>
-        <v>386</v>
+        <v>544</v>
       </c>
       <c r="G40" s="8">
         <f>+G15+G25+G39</f>
-        <v>5707</v>
+        <v>5708</v>
       </c>
       <c r="H40" s="8">
         <f>+H15+H25+H39</f>
-        <v>2714</v>
+        <v>2872</v>
       </c>
       <c r="I40" s="8"/>
       <c r="L40" s="1">
         <f>+H40/G40</f>
-        <v>0.47555633432626598</v>
+        <v>0.50315346881569722</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
@@ -8075,7 +8075,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="51">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C4" s="51">
         <v>127</v>
@@ -8095,7 +8095,7 @@
         <v>10</v>
       </c>
       <c r="B5" s="51">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C5" s="51">
         <v>181</v>
@@ -8113,7 +8113,7 @@
         <v>100</v>
       </c>
       <c r="B6" s="51">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C6" s="51">
         <v>2027</v>
@@ -8131,7 +8131,7 @@
         <v>11</v>
       </c>
       <c r="B7" s="51">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="C7" s="51">
         <v>160</v>
@@ -8151,7 +8151,7 @@
         <v>12</v>
       </c>
       <c r="B8" s="51">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C8" s="51">
         <v>214</v>
@@ -8171,7 +8171,7 @@
         <v>123</v>
       </c>
       <c r="B9" s="51">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" s="51">
         <v>489</v>
@@ -8211,7 +8211,7 @@
         <v>16</v>
       </c>
       <c r="B11" s="51">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C11" s="51">
         <v>198</v>
@@ -8229,7 +8229,7 @@
         <v>18</v>
       </c>
       <c r="B12" s="51">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C12" s="51">
         <v>177</v>
@@ -8245,7 +8245,7 @@
         <v>222</v>
       </c>
       <c r="H12">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I12" s="51">
         <v>127</v>
@@ -8256,7 +8256,7 @@
         <v>19</v>
       </c>
       <c r="B13" s="51">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C13" s="51">
         <v>207</v>
@@ -8269,7 +8269,7 @@
         <v>223</v>
       </c>
       <c r="H13" s="51">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I13" s="51">
         <v>127</v>
@@ -8280,7 +8280,7 @@
         <v>2</v>
       </c>
       <c r="B14" s="51">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C14" s="51">
         <v>138</v>
@@ -8293,7 +8293,7 @@
         <v>224</v>
       </c>
       <c r="H14" s="51">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I14" s="51">
         <v>127</v>
@@ -8304,7 +8304,7 @@
         <v>20</v>
       </c>
       <c r="B15" s="51">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="C15" s="51">
         <v>227</v>
@@ -8317,7 +8317,7 @@
         <v>225</v>
       </c>
       <c r="H15" s="51">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I15" s="51">
         <v>127</v>
@@ -8328,7 +8328,7 @@
         <v>21</v>
       </c>
       <c r="B16" s="51">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C16" s="51">
         <v>170</v>
@@ -8341,7 +8341,7 @@
         <v>226</v>
       </c>
       <c r="H16" s="51">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I16" s="51">
         <v>127</v>
@@ -8352,7 +8352,7 @@
         <v>22</v>
       </c>
       <c r="B17" s="51">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C17" s="51">
         <v>72</v>
@@ -8365,7 +8365,7 @@
         <v>227</v>
       </c>
       <c r="H17" s="51">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="I17" s="51">
         <v>127</v>
@@ -8376,7 +8376,7 @@
         <v>23</v>
       </c>
       <c r="B18" s="51">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C18" s="51">
         <v>154</v>
@@ -8389,7 +8389,7 @@
         <v>228</v>
       </c>
       <c r="H18" s="51">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I18" s="51">
         <v>127</v>
@@ -8400,7 +8400,7 @@
         <v>24</v>
       </c>
       <c r="B19" s="51">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C19" s="51">
         <v>178</v>
@@ -8413,7 +8413,7 @@
         <v>229</v>
       </c>
       <c r="H19" s="51">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I19" s="51">
         <v>127</v>
@@ -8424,7 +8424,7 @@
         <v>25</v>
       </c>
       <c r="B20" s="51">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C20" s="51">
         <v>172</v>
@@ -8437,7 +8437,7 @@
         <v>230</v>
       </c>
       <c r="H20">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I20" s="51">
         <v>127</v>
@@ -8451,7 +8451,7 @@
         <v>31</v>
       </c>
       <c r="C21" s="51">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E21">
         <f>+$F$21</f>
@@ -8464,7 +8464,7 @@
         <v>222</v>
       </c>
       <c r="H21" s="51">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I21" s="51">
         <v>181</v>
@@ -8475,7 +8475,7 @@
         <v>27</v>
       </c>
       <c r="B22" s="51">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C22" s="51">
         <v>139</v>
@@ -8499,7 +8499,7 @@
         <v>28</v>
       </c>
       <c r="B23" s="51">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C23" s="51">
         <v>168</v>
@@ -8512,7 +8512,7 @@
         <v>224</v>
       </c>
       <c r="H23" s="51">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I23" s="51">
         <v>181</v>
@@ -8523,7 +8523,7 @@
         <v>3</v>
       </c>
       <c r="B24" s="51">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C24" s="51">
         <v>170</v>
@@ -8536,7 +8536,7 @@
         <v>225</v>
       </c>
       <c r="H24" s="51">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I24" s="51">
         <v>181</v>
@@ -8547,7 +8547,7 @@
         <v>30</v>
       </c>
       <c r="B25" s="51">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C25" s="51">
         <v>139</v>
@@ -8560,7 +8560,7 @@
         <v>226</v>
       </c>
       <c r="H25" s="51">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I25" s="51">
         <v>181</v>
@@ -8571,7 +8571,7 @@
         <v>31</v>
       </c>
       <c r="B26" s="51">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C26" s="51">
         <v>160</v>
@@ -8584,7 +8584,7 @@
         <v>227</v>
       </c>
       <c r="H26" s="51">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I26" s="51">
         <v>181</v>
@@ -8595,7 +8595,7 @@
         <v>32</v>
       </c>
       <c r="B27" s="51">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C27" s="51">
         <v>57</v>
@@ -8619,7 +8619,7 @@
         <v>33</v>
       </c>
       <c r="B28" s="51">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C28" s="51">
         <v>168</v>
@@ -8632,7 +8632,7 @@
         <v>229</v>
       </c>
       <c r="H28" s="51">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I28" s="51">
         <v>181</v>
@@ -8643,7 +8643,7 @@
         <v>36</v>
       </c>
       <c r="B29" s="51">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C29" s="51">
         <v>157</v>
@@ -8667,7 +8667,7 @@
         <v>37</v>
       </c>
       <c r="B30" s="51">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C30" s="51">
         <v>142</v>
@@ -8683,7 +8683,7 @@
         <v>222</v>
       </c>
       <c r="H30" s="51">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I30" s="51">
         <v>2027</v>
@@ -8694,7 +8694,7 @@
         <v>4</v>
       </c>
       <c r="B31" s="51">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="C31" s="51">
         <v>182</v>
@@ -8718,7 +8718,7 @@
         <v>40</v>
       </c>
       <c r="B32" s="51">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="C32" s="51">
         <v>249</v>
@@ -8731,7 +8731,7 @@
         <v>224</v>
       </c>
       <c r="H32" s="51">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I32" s="51">
         <v>2027</v>
@@ -8766,7 +8766,7 @@
         <v>43</v>
       </c>
       <c r="B34" s="51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C34" s="51">
         <v>93</v>
@@ -8790,7 +8790,7 @@
         <v>44</v>
       </c>
       <c r="B35" s="51">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C35" s="51">
         <v>169</v>
@@ -8814,7 +8814,7 @@
         <v>49</v>
       </c>
       <c r="B36" s="51">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="C36" s="51">
         <v>239</v>
@@ -8827,7 +8827,7 @@
         <v>228</v>
       </c>
       <c r="H36" s="51">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I36" s="51">
         <v>2027</v>
@@ -8838,7 +8838,7 @@
         <v>5</v>
       </c>
       <c r="B37" s="51">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="C37" s="51">
         <v>260</v>
@@ -8862,7 +8862,7 @@
         <v>52</v>
       </c>
       <c r="B38" s="51">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C38" s="51">
         <v>101</v>
@@ -8886,7 +8886,7 @@
         <v>53</v>
       </c>
       <c r="B39" s="51">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C39" s="51">
         <v>105</v>
@@ -8902,7 +8902,7 @@
         <v>222</v>
       </c>
       <c r="H39" s="51">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="I39" s="51">
         <v>160</v>
@@ -8913,7 +8913,7 @@
         <v>54</v>
       </c>
       <c r="B40" s="51">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C40" s="51">
         <v>202</v>
@@ -8926,7 +8926,7 @@
         <v>223</v>
       </c>
       <c r="H40" s="51">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I40" s="51">
         <v>160</v>
@@ -8950,7 +8950,7 @@
         <v>224</v>
       </c>
       <c r="H41" s="51">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="I41" s="51">
         <v>160</v>
@@ -8961,7 +8961,7 @@
         <v>57</v>
       </c>
       <c r="B42" s="51">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C42" s="51">
         <v>104</v>
@@ -8974,7 +8974,7 @@
         <v>225</v>
       </c>
       <c r="H42" s="51">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I42" s="51">
         <v>160</v>
@@ -8998,7 +8998,7 @@
         <v>226</v>
       </c>
       <c r="H43" s="51">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="I43" s="51">
         <v>160</v>
@@ -9022,7 +9022,7 @@
         <v>227</v>
       </c>
       <c r="H44" s="51">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I44" s="51">
         <v>160</v>
@@ -9036,7 +9036,7 @@
         <v>4</v>
       </c>
       <c r="C45" s="51">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E45">
         <f t="shared" si="3"/>
@@ -9046,7 +9046,7 @@
         <v>228</v>
       </c>
       <c r="H45" s="51">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I45" s="51">
         <v>160</v>
@@ -9057,7 +9057,7 @@
         <v>8</v>
       </c>
       <c r="B46" s="51">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C46" s="51">
         <v>195</v>
@@ -9070,7 +9070,7 @@
         <v>229</v>
       </c>
       <c r="H46" s="51">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I46" s="51">
         <v>160</v>
@@ -9081,7 +9081,7 @@
         <v>9</v>
       </c>
       <c r="B47" s="51">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C47" s="51">
         <v>161</v>
@@ -9114,7 +9114,7 @@
         <v>222</v>
       </c>
       <c r="H48" s="51">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="I48" s="51">
         <v>214</v>
@@ -9131,7 +9131,7 @@
         <v>223</v>
       </c>
       <c r="H49" s="51">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I49" s="51">
         <v>214</v>
@@ -9146,7 +9146,7 @@
         <v>224</v>
       </c>
       <c r="H50" s="51">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I50" s="51">
         <v>214</v>
@@ -9161,7 +9161,7 @@
         <v>225</v>
       </c>
       <c r="H51" s="51">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I51" s="51">
         <v>214</v>
@@ -9176,7 +9176,7 @@
         <v>226</v>
       </c>
       <c r="H52" s="51">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I52" s="51">
         <v>214</v>
@@ -9221,7 +9221,7 @@
         <v>229</v>
       </c>
       <c r="H55" s="51">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I55" s="51">
         <v>214</v>
@@ -9236,7 +9236,7 @@
         <v>230</v>
       </c>
       <c r="H56" s="51">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I56" s="51">
         <v>214</v>
@@ -9254,7 +9254,7 @@
         <v>222</v>
       </c>
       <c r="H57" s="51">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I57" s="51">
         <v>489</v>
@@ -9269,7 +9269,7 @@
         <v>223</v>
       </c>
       <c r="H58" s="51">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I58" s="51">
         <v>489</v>
@@ -9284,7 +9284,7 @@
         <v>224</v>
       </c>
       <c r="H59" s="51">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I59" s="51">
         <v>489</v>
@@ -9314,7 +9314,7 @@
         <v>226</v>
       </c>
       <c r="H61" s="51">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I61" s="51">
         <v>489</v>
@@ -9420,7 +9420,7 @@
         <v>224</v>
       </c>
       <c r="H68" s="51">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I68" s="51">
         <v>65</v>
@@ -9435,7 +9435,7 @@
         <v>225</v>
       </c>
       <c r="H69" s="51">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I69" s="51">
         <v>65</v>
@@ -9450,7 +9450,7 @@
         <v>226</v>
       </c>
       <c r="H70" s="51">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I70" s="51">
         <v>65</v>
@@ -9495,7 +9495,7 @@
         <v>229</v>
       </c>
       <c r="H73" s="51">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I73" s="51">
         <v>65</v>
@@ -9510,7 +9510,7 @@
         <v>230</v>
       </c>
       <c r="H74" s="51">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I74" s="51">
         <v>65</v>
@@ -9528,7 +9528,7 @@
         <v>222</v>
       </c>
       <c r="H75" s="51">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I75" s="51">
         <v>198</v>
@@ -9543,7 +9543,7 @@
         <v>223</v>
       </c>
       <c r="H76">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I76" s="51">
         <v>198</v>
@@ -9558,7 +9558,7 @@
         <v>224</v>
       </c>
       <c r="H77" s="51">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="I77" s="51">
         <v>198</v>
@@ -9573,7 +9573,7 @@
         <v>225</v>
       </c>
       <c r="H78" s="51">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I78" s="51">
         <v>198</v>
@@ -9588,7 +9588,7 @@
         <v>226</v>
       </c>
       <c r="H79" s="51">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="I79" s="51">
         <v>198</v>
@@ -9603,7 +9603,7 @@
         <v>227</v>
       </c>
       <c r="H80" s="51">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I80" s="51">
         <v>198</v>
@@ -9618,7 +9618,7 @@
         <v>228</v>
       </c>
       <c r="H81" s="51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I81" s="51">
         <v>198</v>
@@ -9633,7 +9633,7 @@
         <v>229</v>
       </c>
       <c r="H82" s="51">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I82" s="51">
         <v>198</v>
@@ -9648,7 +9648,7 @@
         <v>230</v>
       </c>
       <c r="H83" s="51">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I83" s="51">
         <v>198</v>
@@ -9666,7 +9666,7 @@
         <v>222</v>
       </c>
       <c r="H84" s="51">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I84" s="51">
         <v>177</v>
@@ -9681,7 +9681,7 @@
         <v>223</v>
       </c>
       <c r="H85" s="51">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I85" s="51">
         <v>177</v>
@@ -9696,7 +9696,7 @@
         <v>224</v>
       </c>
       <c r="H86" s="51">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I86" s="51">
         <v>177</v>
@@ -9711,7 +9711,7 @@
         <v>225</v>
       </c>
       <c r="H87" s="51">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I87" s="51">
         <v>177</v>
@@ -9726,7 +9726,7 @@
         <v>226</v>
       </c>
       <c r="H88" s="51">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I88" s="51">
         <v>177</v>
@@ -9741,7 +9741,7 @@
         <v>227</v>
       </c>
       <c r="H89" s="51">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I89" s="51">
         <v>177</v>
@@ -9771,7 +9771,7 @@
         <v>229</v>
       </c>
       <c r="H91" s="51">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="I91" s="51">
         <v>177</v>
@@ -9786,7 +9786,7 @@
         <v>230</v>
       </c>
       <c r="H92" s="51">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I92" s="51">
         <v>177</v>
@@ -9804,7 +9804,7 @@
         <v>222</v>
       </c>
       <c r="H93" s="51">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I93" s="51">
         <v>207</v>
@@ -9819,7 +9819,7 @@
         <v>223</v>
       </c>
       <c r="H94" s="51">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I94" s="51">
         <v>207</v>
@@ -9834,7 +9834,7 @@
         <v>224</v>
       </c>
       <c r="H95" s="51">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I95" s="51">
         <v>207</v>
@@ -9864,7 +9864,7 @@
         <v>226</v>
       </c>
       <c r="H97" s="51">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I97" s="51">
         <v>207</v>
@@ -9879,7 +9879,7 @@
         <v>227</v>
       </c>
       <c r="H98" s="51">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I98" s="51">
         <v>207</v>
@@ -9957,7 +9957,7 @@
         <v>223</v>
       </c>
       <c r="H103" s="51">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I103" s="51">
         <v>138</v>
@@ -9972,7 +9972,7 @@
         <v>224</v>
       </c>
       <c r="H104" s="51">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I104" s="51">
         <v>138</v>
@@ -9987,7 +9987,7 @@
         <v>225</v>
       </c>
       <c r="H105" s="51">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I105" s="51">
         <v>138</v>
@@ -10002,7 +10002,7 @@
         <v>226</v>
       </c>
       <c r="H106" s="51">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I106" s="51">
         <v>138</v>
@@ -10017,7 +10017,7 @@
         <v>227</v>
       </c>
       <c r="H107" s="51">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I107" s="51">
         <v>138</v>
@@ -10047,7 +10047,7 @@
         <v>229</v>
       </c>
       <c r="H109" s="51">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I109" s="51">
         <v>138</v>
@@ -10062,7 +10062,7 @@
         <v>230</v>
       </c>
       <c r="H110" s="51">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I110" s="51">
         <v>138</v>
@@ -10080,7 +10080,7 @@
         <v>222</v>
       </c>
       <c r="H111" s="51">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I111" s="51">
         <v>227</v>
@@ -10095,7 +10095,7 @@
         <v>223</v>
       </c>
       <c r="H112" s="51">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I112" s="51">
         <v>227</v>
@@ -10110,7 +10110,7 @@
         <v>224</v>
       </c>
       <c r="H113" s="51">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I113" s="51">
         <v>227</v>
@@ -10125,7 +10125,7 @@
         <v>225</v>
       </c>
       <c r="H114" s="51">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="I114" s="51">
         <v>227</v>
@@ -10140,7 +10140,7 @@
         <v>226</v>
       </c>
       <c r="H115" s="51">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="I115" s="51">
         <v>227</v>
@@ -10155,7 +10155,7 @@
         <v>227</v>
       </c>
       <c r="H116">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I116" s="51">
         <v>227</v>
@@ -10170,7 +10170,7 @@
         <v>228</v>
       </c>
       <c r="H117" s="51">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I117" s="51">
         <v>227</v>
@@ -10185,7 +10185,7 @@
         <v>229</v>
       </c>
       <c r="H118" s="51">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I118" s="51">
         <v>227</v>
@@ -10200,7 +10200,7 @@
         <v>230</v>
       </c>
       <c r="H119" s="51">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I119" s="51">
         <v>227</v>
@@ -10218,7 +10218,7 @@
         <v>222</v>
       </c>
       <c r="H120" s="51">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I120" s="51">
         <v>170</v>
@@ -10233,7 +10233,7 @@
         <v>223</v>
       </c>
       <c r="H121" s="51">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I121" s="51">
         <v>170</v>
@@ -10248,7 +10248,7 @@
         <v>224</v>
       </c>
       <c r="H122" s="51">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="I122" s="51">
         <v>170</v>
@@ -10263,7 +10263,7 @@
         <v>225</v>
       </c>
       <c r="H123" s="51">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I123" s="51">
         <v>170</v>
@@ -10278,7 +10278,7 @@
         <v>226</v>
       </c>
       <c r="H124">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="I124" s="51">
         <v>170</v>
@@ -10293,7 +10293,7 @@
         <v>227</v>
       </c>
       <c r="H125" s="51">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="I125" s="51">
         <v>170</v>
@@ -10308,7 +10308,7 @@
         <v>228</v>
       </c>
       <c r="H126" s="51">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I126" s="51">
         <v>170</v>
@@ -10338,7 +10338,7 @@
         <v>230</v>
       </c>
       <c r="H128" s="51">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I128" s="51">
         <v>170</v>
@@ -10356,7 +10356,7 @@
         <v>222</v>
       </c>
       <c r="H129" s="51">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I129" s="51">
         <v>72</v>
@@ -10386,7 +10386,7 @@
         <v>224</v>
       </c>
       <c r="H131" s="51">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I131" s="51">
         <v>72</v>
@@ -10416,7 +10416,7 @@
         <v>226</v>
       </c>
       <c r="H133" s="51">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I133" s="51">
         <v>72</v>
@@ -10431,7 +10431,7 @@
         <v>227</v>
       </c>
       <c r="H134" s="51">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I134" s="51">
         <v>72</v>
@@ -10461,7 +10461,7 @@
         <v>229</v>
       </c>
       <c r="H136" s="51">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I136" s="51">
         <v>72</v>
@@ -10494,7 +10494,7 @@
         <v>222</v>
       </c>
       <c r="H138" s="51">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I138" s="51">
         <v>154</v>
@@ -10524,7 +10524,7 @@
         <v>224</v>
       </c>
       <c r="H140">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I140" s="51">
         <v>154</v>
@@ -10554,7 +10554,7 @@
         <v>226</v>
       </c>
       <c r="H142" s="51">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="I142" s="51">
         <v>154</v>
@@ -10569,7 +10569,7 @@
         <v>227</v>
       </c>
       <c r="H143" s="51">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="I143" s="51">
         <v>154</v>
@@ -10599,7 +10599,7 @@
         <v>229</v>
       </c>
       <c r="H145" s="51">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I145" s="51">
         <v>154</v>
@@ -10614,7 +10614,7 @@
         <v>230</v>
       </c>
       <c r="H146" s="51">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I146" s="51">
         <v>154</v>
@@ -10632,7 +10632,7 @@
         <v>222</v>
       </c>
       <c r="H147" s="51">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I147" s="51">
         <v>178</v>
@@ -10662,7 +10662,7 @@
         <v>224</v>
       </c>
       <c r="H149" s="51">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I149" s="51">
         <v>178</v>
@@ -10677,7 +10677,7 @@
         <v>225</v>
       </c>
       <c r="H150" s="51">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I150" s="51">
         <v>178</v>
@@ -10692,7 +10692,7 @@
         <v>226</v>
       </c>
       <c r="H151" s="51">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I151" s="51">
         <v>178</v>
@@ -10707,7 +10707,7 @@
         <v>227</v>
       </c>
       <c r="H152" s="51">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I152" s="51">
         <v>178</v>
@@ -10722,7 +10722,7 @@
         <v>228</v>
       </c>
       <c r="H153" s="51">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I153" s="51">
         <v>178</v>
@@ -10737,7 +10737,7 @@
         <v>229</v>
       </c>
       <c r="H154" s="51">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I154" s="51">
         <v>178</v>
@@ -10770,7 +10770,7 @@
         <v>222</v>
       </c>
       <c r="H156" s="51">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I156" s="51">
         <v>172</v>
@@ -10785,7 +10785,7 @@
         <v>223</v>
       </c>
       <c r="H157" s="51">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I157" s="51">
         <v>172</v>
@@ -10800,7 +10800,7 @@
         <v>224</v>
       </c>
       <c r="H158" s="51">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I158" s="51">
         <v>172</v>
@@ -10815,7 +10815,7 @@
         <v>225</v>
       </c>
       <c r="H159" s="51">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I159" s="51">
         <v>172</v>
@@ -10830,7 +10830,7 @@
         <v>226</v>
       </c>
       <c r="H160" s="51">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I160" s="51">
         <v>172</v>
@@ -10845,7 +10845,7 @@
         <v>227</v>
       </c>
       <c r="H161" s="51">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I161" s="51">
         <v>172</v>
@@ -10860,7 +10860,7 @@
         <v>228</v>
       </c>
       <c r="H162" s="51">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I162" s="51">
         <v>172</v>
@@ -10875,7 +10875,7 @@
         <v>229</v>
       </c>
       <c r="H163" s="51">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I163" s="51">
         <v>172</v>
@@ -10890,7 +10890,7 @@
         <v>230</v>
       </c>
       <c r="H164">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I164" s="51">
         <v>172</v>
@@ -10911,7 +10911,7 @@
         <v>12</v>
       </c>
       <c r="I165" s="51">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="166" spans="5:9" x14ac:dyDescent="0.25">
@@ -10926,7 +10926,7 @@
         <v>6</v>
       </c>
       <c r="I166" s="51">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="167" spans="5:9" x14ac:dyDescent="0.25">
@@ -10941,7 +10941,7 @@
         <v>3</v>
       </c>
       <c r="I167" s="51">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="168" spans="5:9" x14ac:dyDescent="0.25">
@@ -10956,7 +10956,7 @@
         <v>15</v>
       </c>
       <c r="I168" s="51">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="169" spans="5:9" x14ac:dyDescent="0.25">
@@ -10971,7 +10971,7 @@
         <v>11</v>
       </c>
       <c r="I169" s="51">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="170" spans="5:9" x14ac:dyDescent="0.25">
@@ -10986,7 +10986,7 @@
         <v>12</v>
       </c>
       <c r="I170" s="51">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="171" spans="5:9" x14ac:dyDescent="0.25">
@@ -11001,7 +11001,7 @@
         <v>16</v>
       </c>
       <c r="I171" s="51">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="172" spans="5:9" x14ac:dyDescent="0.25">
@@ -11016,7 +11016,7 @@
         <v>6</v>
       </c>
       <c r="I172" s="51">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="173" spans="5:9" x14ac:dyDescent="0.25">
@@ -11031,7 +11031,7 @@
         <v>11</v>
       </c>
       <c r="I173" s="51">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="174" spans="5:9" x14ac:dyDescent="0.25">
@@ -11046,7 +11046,7 @@
         <v>222</v>
       </c>
       <c r="H174" s="51">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I174" s="51">
         <v>139</v>
@@ -11061,7 +11061,7 @@
         <v>223</v>
       </c>
       <c r="H175" s="51">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I175" s="51">
         <v>139</v>
@@ -11076,7 +11076,7 @@
         <v>224</v>
       </c>
       <c r="H176" s="51">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I176" s="51">
         <v>139</v>
@@ -11091,7 +11091,7 @@
         <v>225</v>
       </c>
       <c r="H177" s="51">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I177" s="51">
         <v>139</v>
@@ -11106,7 +11106,7 @@
         <v>226</v>
       </c>
       <c r="H178" s="51">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="I178" s="51">
         <v>139</v>
@@ -11121,7 +11121,7 @@
         <v>227</v>
       </c>
       <c r="H179" s="51">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I179" s="51">
         <v>139</v>
@@ -11136,7 +11136,7 @@
         <v>228</v>
       </c>
       <c r="H180">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I180" s="51">
         <v>139</v>
@@ -11151,7 +11151,7 @@
         <v>229</v>
       </c>
       <c r="H181" s="51">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I181" s="51">
         <v>139</v>
@@ -11184,7 +11184,7 @@
         <v>222</v>
       </c>
       <c r="H183" s="51">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I183" s="51">
         <v>168</v>
@@ -11199,7 +11199,7 @@
         <v>223</v>
       </c>
       <c r="H184" s="51">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I184" s="51">
         <v>168</v>
@@ -11214,7 +11214,7 @@
         <v>224</v>
       </c>
       <c r="H185" s="51">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I185" s="51">
         <v>168</v>
@@ -11229,7 +11229,7 @@
         <v>225</v>
       </c>
       <c r="H186">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I186" s="51">
         <v>168</v>
@@ -11244,7 +11244,7 @@
         <v>226</v>
       </c>
       <c r="H187" s="51">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="I187" s="51">
         <v>168</v>
@@ -11259,7 +11259,7 @@
         <v>227</v>
       </c>
       <c r="H188" s="51">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I188" s="51">
         <v>168</v>
@@ -11274,7 +11274,7 @@
         <v>228</v>
       </c>
       <c r="H189" s="51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I189" s="51">
         <v>168</v>
@@ -11289,7 +11289,7 @@
         <v>229</v>
       </c>
       <c r="H190" s="51">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I190" s="51">
         <v>168</v>
@@ -11304,7 +11304,7 @@
         <v>230</v>
       </c>
       <c r="H191" s="51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I191" s="51">
         <v>168</v>
@@ -11322,7 +11322,7 @@
         <v>222</v>
       </c>
       <c r="H192" s="51">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I192" s="51">
         <v>170</v>
@@ -11337,7 +11337,7 @@
         <v>223</v>
       </c>
       <c r="H193" s="51">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I193" s="51">
         <v>170</v>
@@ -11367,7 +11367,7 @@
         <v>225</v>
       </c>
       <c r="H195" s="51">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I195" s="51">
         <v>170</v>
@@ -11382,7 +11382,7 @@
         <v>226</v>
       </c>
       <c r="H196">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="I196" s="51">
         <v>170</v>
@@ -11397,7 +11397,7 @@
         <v>227</v>
       </c>
       <c r="H197" s="51">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="I197" s="51">
         <v>170</v>
@@ -11412,7 +11412,7 @@
         <v>228</v>
       </c>
       <c r="H198" s="51">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I198" s="51">
         <v>170</v>
@@ -11427,7 +11427,7 @@
         <v>229</v>
       </c>
       <c r="H199" s="51">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I199" s="51">
         <v>170</v>
@@ -11442,7 +11442,7 @@
         <v>230</v>
       </c>
       <c r="H200" s="51">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I200" s="51">
         <v>170</v>
@@ -11546,7 +11546,7 @@
         <v>228</v>
       </c>
       <c r="H207" s="51">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I207" s="51">
         <v>139</v>
@@ -11590,7 +11590,7 @@
         <v>222</v>
       </c>
       <c r="H210" s="51">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I210" s="51">
         <v>160</v>
@@ -11605,7 +11605,7 @@
         <v>223</v>
       </c>
       <c r="H211" s="51">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="I211" s="51">
         <v>160</v>
@@ -11620,7 +11620,7 @@
         <v>224</v>
       </c>
       <c r="H212">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I212" s="51">
         <v>160</v>
@@ -11635,7 +11635,7 @@
         <v>225</v>
       </c>
       <c r="H213" s="51">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I213" s="51">
         <v>160</v>
@@ -11650,7 +11650,7 @@
         <v>226</v>
       </c>
       <c r="H214" s="51">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="I214" s="51">
         <v>160</v>
@@ -11665,7 +11665,7 @@
         <v>227</v>
       </c>
       <c r="H215" s="51">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="I215" s="51">
         <v>160</v>
@@ -11680,7 +11680,7 @@
         <v>228</v>
       </c>
       <c r="H216" s="51">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I216" s="51">
         <v>160</v>
@@ -11695,7 +11695,7 @@
         <v>229</v>
       </c>
       <c r="H217" s="51">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I217" s="51">
         <v>160</v>
@@ -11710,7 +11710,7 @@
         <v>230</v>
       </c>
       <c r="H218" s="51">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I218" s="51">
         <v>160</v>
@@ -11728,7 +11728,7 @@
         <v>222</v>
       </c>
       <c r="H219" s="51">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I219" s="51">
         <v>57</v>
@@ -11743,7 +11743,7 @@
         <v>223</v>
       </c>
       <c r="H220" s="51">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I220" s="51">
         <v>57</v>
@@ -11788,7 +11788,7 @@
         <v>226</v>
       </c>
       <c r="H223" s="51">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I223" s="51">
         <v>57</v>
@@ -11818,7 +11818,7 @@
         <v>228</v>
       </c>
       <c r="H225" s="51">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I225" s="51">
         <v>57</v>
@@ -11833,7 +11833,7 @@
         <v>229</v>
       </c>
       <c r="H226" s="51">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I226" s="51">
         <v>57</v>
@@ -11848,7 +11848,7 @@
         <v>230</v>
       </c>
       <c r="H227" s="51">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I227" s="51">
         <v>57</v>
@@ -11866,7 +11866,7 @@
         <v>222</v>
       </c>
       <c r="H228" s="51">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I228" s="51">
         <v>168</v>
@@ -11896,7 +11896,7 @@
         <v>224</v>
       </c>
       <c r="H230" s="51">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I230" s="51">
         <v>168</v>
@@ -11911,7 +11911,7 @@
         <v>225</v>
       </c>
       <c r="H231" s="51">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I231" s="51">
         <v>168</v>
@@ -11926,7 +11926,7 @@
         <v>226</v>
       </c>
       <c r="H232" s="51">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="I232" s="51">
         <v>168</v>
@@ -11941,7 +11941,7 @@
         <v>227</v>
       </c>
       <c r="H233" s="51">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I233" s="51">
         <v>168</v>
@@ -11956,7 +11956,7 @@
         <v>228</v>
       </c>
       <c r="H234" s="51">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I234" s="51">
         <v>168</v>
@@ -11971,7 +11971,7 @@
         <v>229</v>
       </c>
       <c r="H235" s="51">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I235" s="51">
         <v>168</v>
@@ -11986,7 +11986,7 @@
         <v>230</v>
       </c>
       <c r="H236">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I236" s="51">
         <v>168</v>
@@ -12004,7 +12004,7 @@
         <v>222</v>
       </c>
       <c r="H237" s="51">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I237" s="51">
         <v>157</v>
@@ -12019,7 +12019,7 @@
         <v>223</v>
       </c>
       <c r="H238" s="51">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I238" s="51">
         <v>157</v>
@@ -12049,7 +12049,7 @@
         <v>225</v>
       </c>
       <c r="H240" s="51">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I240" s="51">
         <v>157</v>
@@ -12064,7 +12064,7 @@
         <v>226</v>
       </c>
       <c r="H241" s="51">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I241" s="51">
         <v>157</v>
@@ -12079,7 +12079,7 @@
         <v>227</v>
       </c>
       <c r="H242" s="51">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I242" s="51">
         <v>157</v>
@@ -12142,7 +12142,7 @@
         <v>222</v>
       </c>
       <c r="H246" s="51">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I246" s="51">
         <v>142</v>
@@ -12172,7 +12172,7 @@
         <v>224</v>
       </c>
       <c r="H248" s="51">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I248" s="51">
         <v>142</v>
@@ -12187,7 +12187,7 @@
         <v>225</v>
       </c>
       <c r="H249" s="51">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I249" s="51">
         <v>142</v>
@@ -12202,7 +12202,7 @@
         <v>226</v>
       </c>
       <c r="H250" s="51">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I250" s="51">
         <v>142</v>
@@ -12232,7 +12232,7 @@
         <v>228</v>
       </c>
       <c r="H252">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I252" s="51">
         <v>142</v>
@@ -12247,7 +12247,7 @@
         <v>229</v>
       </c>
       <c r="H253" s="51">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I253" s="51">
         <v>142</v>
@@ -12262,7 +12262,7 @@
         <v>230</v>
       </c>
       <c r="H254" s="51">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I254" s="51">
         <v>142</v>
@@ -12280,7 +12280,7 @@
         <v>222</v>
       </c>
       <c r="H255" s="51">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I255" s="51">
         <v>182</v>
@@ -12295,7 +12295,7 @@
         <v>223</v>
       </c>
       <c r="H256" s="51">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I256" s="51">
         <v>182</v>
@@ -12310,7 +12310,7 @@
         <v>224</v>
       </c>
       <c r="H257" s="51">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I257" s="51">
         <v>182</v>
@@ -12325,7 +12325,7 @@
         <v>225</v>
       </c>
       <c r="H258">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I258" s="51">
         <v>182</v>
@@ -12340,7 +12340,7 @@
         <v>226</v>
       </c>
       <c r="H259" s="51">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="I259" s="51">
         <v>182</v>
@@ -12355,7 +12355,7 @@
         <v>227</v>
       </c>
       <c r="H260">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I260" s="51">
         <v>182</v>
@@ -12385,7 +12385,7 @@
         <v>229</v>
       </c>
       <c r="H262" s="51">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I262" s="51">
         <v>182</v>
@@ -12400,7 +12400,7 @@
         <v>230</v>
       </c>
       <c r="H263" s="51">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I263" s="51">
         <v>182</v>
@@ -12418,7 +12418,7 @@
         <v>222</v>
       </c>
       <c r="H264" s="51">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I264" s="51">
         <v>249</v>
@@ -12463,7 +12463,7 @@
         <v>225</v>
       </c>
       <c r="H267" s="51">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I267" s="51">
         <v>249</v>
@@ -12478,7 +12478,7 @@
         <v>226</v>
       </c>
       <c r="H268">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="I268" s="51">
         <v>249</v>
@@ -12493,7 +12493,7 @@
         <v>227</v>
       </c>
       <c r="H269" s="51">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I269" s="51">
         <v>249</v>
@@ -12508,7 +12508,7 @@
         <v>228</v>
       </c>
       <c r="H270" s="51">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I270" s="51">
         <v>249</v>
@@ -12538,7 +12538,7 @@
         <v>230</v>
       </c>
       <c r="H272" s="51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I272" s="51">
         <v>249</v>
@@ -12711,7 +12711,7 @@
         <v>224</v>
       </c>
       <c r="H284">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I284" s="51">
         <v>93</v>
@@ -12808,7 +12808,7 @@
         <v>222</v>
       </c>
       <c r="H291">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I291" s="51">
         <v>169</v>
@@ -12823,7 +12823,7 @@
         <v>223</v>
       </c>
       <c r="H292">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I292" s="51">
         <v>169</v>
@@ -12838,7 +12838,7 @@
         <v>224</v>
       </c>
       <c r="H293">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="I293" s="51">
         <v>169</v>
@@ -12853,7 +12853,7 @@
         <v>225</v>
       </c>
       <c r="H294">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I294" s="51">
         <v>169</v>
@@ -12868,7 +12868,7 @@
         <v>226</v>
       </c>
       <c r="H295">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="I295" s="51">
         <v>169</v>
@@ -12883,7 +12883,7 @@
         <v>227</v>
       </c>
       <c r="H296">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I296" s="51">
         <v>169</v>
@@ -12913,7 +12913,7 @@
         <v>229</v>
       </c>
       <c r="H298">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I298" s="51">
         <v>169</v>
@@ -12928,7 +12928,7 @@
         <v>230</v>
       </c>
       <c r="H299" s="51">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I299" s="51">
         <v>169</v>
@@ -12946,7 +12946,7 @@
         <v>222</v>
       </c>
       <c r="H300" s="51">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="I300" s="51">
         <v>239</v>
@@ -12961,7 +12961,7 @@
         <v>223</v>
       </c>
       <c r="H301" s="51">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I301" s="51">
         <v>239</v>
@@ -12976,7 +12976,7 @@
         <v>224</v>
       </c>
       <c r="H302" s="51">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="I302" s="51">
         <v>239</v>
@@ -12991,7 +12991,7 @@
         <v>225</v>
       </c>
       <c r="H303" s="51">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I303" s="51">
         <v>239</v>
@@ -13006,7 +13006,7 @@
         <v>226</v>
       </c>
       <c r="H304" s="51">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="I304" s="51">
         <v>239</v>
@@ -13021,7 +13021,7 @@
         <v>227</v>
       </c>
       <c r="H305" s="51">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="I305" s="51">
         <v>239</v>
@@ -13036,7 +13036,7 @@
         <v>228</v>
       </c>
       <c r="H306" s="51">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="I306" s="51">
         <v>239</v>
@@ -13051,7 +13051,7 @@
         <v>229</v>
       </c>
       <c r="H307">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I307" s="51">
         <v>239</v>
@@ -13066,7 +13066,7 @@
         <v>230</v>
       </c>
       <c r="H308">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="I308" s="51">
         <v>239</v>
@@ -13084,7 +13084,7 @@
         <v>222</v>
       </c>
       <c r="H309">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="I309" s="51">
         <v>260</v>
@@ -13099,7 +13099,7 @@
         <v>223</v>
       </c>
       <c r="H310">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I310" s="51">
         <v>260</v>
@@ -13114,7 +13114,7 @@
         <v>224</v>
       </c>
       <c r="H311">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="I311" s="51">
         <v>260</v>
@@ -13129,7 +13129,7 @@
         <v>225</v>
       </c>
       <c r="H312">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I312" s="51">
         <v>260</v>
@@ -13144,7 +13144,7 @@
         <v>226</v>
       </c>
       <c r="H313">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="I313" s="51">
         <v>260</v>
@@ -13159,7 +13159,7 @@
         <v>227</v>
       </c>
       <c r="H314">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I314" s="51">
         <v>260</v>
@@ -13174,7 +13174,7 @@
         <v>228</v>
       </c>
       <c r="H315" s="51">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I315" s="51">
         <v>260</v>
@@ -13189,7 +13189,7 @@
         <v>229</v>
       </c>
       <c r="H316">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I316" s="51">
         <v>260</v>
@@ -13204,7 +13204,7 @@
         <v>230</v>
       </c>
       <c r="H317" s="51">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I317" s="51">
         <v>260</v>
@@ -13237,7 +13237,7 @@
         <v>223</v>
       </c>
       <c r="H319" s="51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I319" s="51">
         <v>101</v>
@@ -13303,7 +13303,7 @@
         <v>228</v>
       </c>
       <c r="H324" s="51">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I324" s="51">
         <v>101</v>
@@ -13424,7 +13424,7 @@
         <v>228</v>
       </c>
       <c r="H333" s="51">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I333" s="51">
         <v>105</v>
@@ -13468,7 +13468,7 @@
         <v>222</v>
       </c>
       <c r="H336" s="51">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I336" s="51">
         <v>202</v>
@@ -13483,7 +13483,7 @@
         <v>223</v>
       </c>
       <c r="H337" s="51">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I337" s="51">
         <v>202</v>
@@ -13528,7 +13528,7 @@
         <v>226</v>
       </c>
       <c r="H340">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I340" s="51">
         <v>202</v>
@@ -13558,7 +13558,7 @@
         <v>228</v>
       </c>
       <c r="H342" s="51">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I342" s="51">
         <v>202</v>
@@ -13824,7 +13824,7 @@
         <v>228</v>
       </c>
       <c r="H360" s="51">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I360" s="51">
         <v>104</v>
@@ -14147,7 +14147,7 @@
         <v>2</v>
       </c>
       <c r="I381">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="382" spans="5:9" x14ac:dyDescent="0.25">
@@ -14159,7 +14159,7 @@
         <v>223</v>
       </c>
       <c r="I382">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="383" spans="5:9" x14ac:dyDescent="0.25">
@@ -14174,7 +14174,7 @@
         <v>3</v>
       </c>
       <c r="I383">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="384" spans="5:9" x14ac:dyDescent="0.25">
@@ -14189,7 +14189,7 @@
         <v>1</v>
       </c>
       <c r="I384">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="385" spans="5:9" x14ac:dyDescent="0.25">
@@ -14204,7 +14204,7 @@
         <v>2</v>
       </c>
       <c r="I385">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="386" spans="5:9" x14ac:dyDescent="0.25">
@@ -14219,7 +14219,7 @@
         <v>2</v>
       </c>
       <c r="I386">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="387" spans="5:9" x14ac:dyDescent="0.25">
@@ -14234,7 +14234,7 @@
         <v>2</v>
       </c>
       <c r="I387">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="388" spans="5:9" x14ac:dyDescent="0.25">
@@ -14246,7 +14246,7 @@
         <v>229</v>
       </c>
       <c r="I388">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="389" spans="5:9" x14ac:dyDescent="0.25">
@@ -14261,7 +14261,7 @@
         <v>1</v>
       </c>
       <c r="I389">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="390" spans="5:9" x14ac:dyDescent="0.25">
@@ -14276,7 +14276,7 @@
         <v>222</v>
       </c>
       <c r="H390">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I390">
         <v>195</v>
@@ -14291,7 +14291,7 @@
         <v>223</v>
       </c>
       <c r="H391">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I391">
         <v>195</v>
@@ -14306,7 +14306,7 @@
         <v>224</v>
       </c>
       <c r="H392">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I392">
         <v>195</v>
@@ -14336,7 +14336,7 @@
         <v>226</v>
       </c>
       <c r="H394">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I394">
         <v>195</v>
@@ -14351,7 +14351,7 @@
         <v>227</v>
       </c>
       <c r="H395">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="I395">
         <v>195</v>
@@ -14366,7 +14366,7 @@
         <v>228</v>
       </c>
       <c r="H396">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I396">
         <v>195</v>
@@ -14396,7 +14396,7 @@
         <v>230</v>
       </c>
       <c r="H398">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I398">
         <v>195</v>
@@ -14414,7 +14414,7 @@
         <v>222</v>
       </c>
       <c r="H399">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I399">
         <v>161</v>
@@ -14429,7 +14429,7 @@
         <v>223</v>
       </c>
       <c r="H400">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I400">
         <v>161</v>
@@ -14444,7 +14444,7 @@
         <v>224</v>
       </c>
       <c r="H401">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I401">
         <v>161</v>
@@ -14459,7 +14459,7 @@
         <v>225</v>
       </c>
       <c r="H402">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I402">
         <v>161</v>
@@ -14474,7 +14474,7 @@
         <v>226</v>
       </c>
       <c r="H403">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I403">
         <v>161</v>
@@ -14489,7 +14489,7 @@
         <v>227</v>
       </c>
       <c r="H404">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I404">
         <v>161</v>
@@ -14504,7 +14504,7 @@
         <v>228</v>
       </c>
       <c r="H405">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I405">
         <v>161</v>
@@ -14519,7 +14519,7 @@
         <v>229</v>
       </c>
       <c r="H406">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I406">
         <v>161</v>
@@ -14534,7 +14534,7 @@
         <v>230</v>
       </c>
       <c r="H407">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I407">
         <v>161</v>

--- a/data/ventas.xlsx
+++ b/data/ventas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cesar\Desktop\Reportes Ventas Rap\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4280214F-A38A-482A-AB9D-CA7830ADA495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE81802B-425A-45B1-9121-0E0DB3801FFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="235">
   <si>
     <t>GOMEZ MARTÍN</t>
   </si>
@@ -767,6 +767,12 @@
   </si>
   <si>
     <t>123 - TORRES ROLANDO</t>
+  </si>
+  <si>
+    <t>31 - RENZO RAMOS</t>
+  </si>
+  <si>
+    <t>54 - BARTSCHAT EMILIANO NAHUEL</t>
   </si>
 </sst>
 </file>
@@ -2534,22 +2540,22 @@
         <v>0</v>
       </c>
       <c r="C2" s="96">
-        <v>30050.344867064101</v>
+        <v>36360.698065472701</v>
       </c>
       <c r="D2" s="96">
-        <v>151749.4632585053</v>
+        <v>189518.4324835093</v>
       </c>
       <c r="E2" s="96">
-        <v>507558440.84656405</v>
+        <v>594107844.49346352</v>
       </c>
       <c r="F2" s="96">
         <v>0</v>
       </c>
       <c r="G2" s="96">
-        <v>264552.02407153812</v>
+        <v>297915.18096689001</v>
       </c>
       <c r="H2" s="96">
-        <v>264552.11</v>
+        <v>297915.34000000003</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -2560,22 +2566,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="96">
-        <v>393.20745409130001</v>
+        <v>442.75209694799997</v>
       </c>
       <c r="D3" s="96">
-        <v>738.55759094179996</v>
+        <v>813.20675760330005</v>
       </c>
       <c r="E3" s="96">
-        <v>8818400.8023845814</v>
+        <v>9930506.0322296303</v>
       </c>
       <c r="F3" s="96">
         <v>0</v>
       </c>
       <c r="G3" s="96">
-        <v>264552.02407153812</v>
+        <v>297915.18096689001</v>
       </c>
       <c r="H3" s="96">
-        <v>264552.11</v>
+        <v>297915.34000000003</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2586,13 +2592,13 @@
         <v>1</v>
       </c>
       <c r="C4" s="96">
-        <v>215.3798690461</v>
+        <v>268.42818253809997</v>
       </c>
       <c r="D4" s="96">
-        <v>429.50910714399998</v>
+        <v>484.74910714139997</v>
       </c>
       <c r="E4" s="96">
-        <v>6449843.5922434218</v>
+        <v>7416441.7657084363</v>
       </c>
       <c r="F4" s="96">
         <v>0</v>
@@ -2612,13 +2618,13 @@
         <v>1</v>
       </c>
       <c r="C5" s="96">
-        <v>287.8868849191</v>
+        <v>357.47226190290002</v>
       </c>
       <c r="D5" s="96">
-        <v>1084.9771071369</v>
+        <v>1231.5221071393</v>
       </c>
       <c r="E5" s="96">
-        <v>6596329.3614597432</v>
+        <v>8097618.1083014421</v>
       </c>
       <c r="F5" s="96">
         <v>0</v>
@@ -2638,13 +2644,13 @@
         <v>1</v>
       </c>
       <c r="C6" s="96">
-        <v>623.45456349139999</v>
+        <v>806.83978174499998</v>
       </c>
       <c r="D6" s="96">
-        <v>1736.7514881101999</v>
+        <v>2090.7614881134</v>
       </c>
       <c r="E6" s="96">
-        <v>13014610.776669662</v>
+        <v>15645728.431611888</v>
       </c>
       <c r="F6" s="96">
         <v>0</v>
@@ -2664,13 +2670,13 @@
         <v>1</v>
       </c>
       <c r="C7" s="96">
-        <v>596.52415476040005</v>
+        <v>699.55609920439997</v>
       </c>
       <c r="D7" s="96">
-        <v>1890.2880833329</v>
+        <v>2280.2210119055999</v>
       </c>
       <c r="E7" s="96">
-        <v>11328941.073388485</v>
+        <v>13226460.381280242</v>
       </c>
       <c r="F7" s="96">
         <v>0</v>
@@ -2690,13 +2696,13 @@
         <v>1</v>
       </c>
       <c r="C8" s="96">
-        <v>2267.1115740741998</v>
+        <v>2271.2782407408999</v>
       </c>
       <c r="D8" s="96">
-        <v>2600.9464768541998</v>
+        <v>2665.9464768541998</v>
       </c>
       <c r="E8" s="96">
-        <v>28341762.515582383</v>
+        <v>28457978.498885799</v>
       </c>
       <c r="F8" s="96">
         <v>0</v>
@@ -2716,13 +2722,13 @@
         <v>1</v>
       </c>
       <c r="C9" s="96">
-        <v>318.65723412649999</v>
+        <v>407.30359126960002</v>
       </c>
       <c r="D9" s="96">
-        <v>1452.5929166666999</v>
+        <v>1735.8554166650999</v>
       </c>
       <c r="E9" s="96">
-        <v>5878949.2572204797</v>
+        <v>7404424.1934615131</v>
       </c>
       <c r="F9" s="96">
         <v>0</v>
@@ -2742,13 +2748,13 @@
         <v>1</v>
       </c>
       <c r="C10" s="96">
-        <v>240.56374007950001</v>
+        <v>258.18834325389997</v>
       </c>
       <c r="D10" s="96">
-        <v>989.48656459439997</v>
+        <v>1001.6023979274</v>
       </c>
       <c r="E10" s="96">
-        <v>7520013.6941604447</v>
+        <v>8509221.7116328403</v>
       </c>
       <c r="F10" s="96">
         <v>0</v>
@@ -2768,13 +2774,13 @@
         <v>1</v>
       </c>
       <c r="C11" s="96">
-        <v>246.6115674589</v>
+        <v>290.60501190309998</v>
       </c>
       <c r="D11" s="96">
-        <v>799.06959523789999</v>
+        <v>922.06959523789999</v>
       </c>
       <c r="E11" s="96">
-        <v>4813267.3862359719</v>
+        <v>5611548.663038048</v>
       </c>
       <c r="F11" s="96">
         <v>0</v>
@@ -2794,13 +2800,13 @@
         <v>1</v>
       </c>
       <c r="C12" s="96">
-        <v>535.28547618829998</v>
+        <v>642.36189682300005</v>
       </c>
       <c r="D12" s="96">
-        <v>2973.4162023743002</v>
+        <v>3208.0478690399</v>
       </c>
       <c r="E12" s="96">
-        <v>8765227.9594276343</v>
+        <v>10222287.133025508</v>
       </c>
       <c r="F12" s="96">
         <v>0</v>
@@ -2820,13 +2826,13 @@
         <v>1</v>
       </c>
       <c r="C13" s="96">
-        <v>451.5398253962</v>
+        <v>524.17395237999995</v>
       </c>
       <c r="D13" s="96">
-        <v>1525.3093690521</v>
+        <v>1740.8193690511</v>
       </c>
       <c r="E13" s="96">
-        <v>10185885.70934353</v>
+        <v>11920566.462441558</v>
       </c>
       <c r="F13" s="96">
         <v>0</v>
@@ -2846,13 +2852,13 @@
         <v>1</v>
       </c>
       <c r="C14" s="96">
-        <v>1878.736904762</v>
+        <v>3301.3271825398001</v>
       </c>
       <c r="D14" s="96">
-        <v>11394.0133333304</v>
+        <v>32008.832499996799</v>
       </c>
       <c r="E14" s="96">
-        <v>32020542.941609319</v>
+        <v>54947546.702784903</v>
       </c>
       <c r="F14" s="96">
         <v>0</v>
@@ -2872,13 +2878,13 @@
         <v>1</v>
       </c>
       <c r="C15" s="96">
-        <v>529.64027777650006</v>
+        <v>653.42529761749995</v>
       </c>
       <c r="D15" s="96">
-        <v>1935.5799999952001</v>
+        <v>2323.3916666609998</v>
       </c>
       <c r="E15" s="96">
-        <v>9837944.9718231615</v>
+        <v>11854719.440338746</v>
       </c>
       <c r="F15" s="96">
         <v>0</v>
@@ -2898,13 +2904,13 @@
         <v>1</v>
       </c>
       <c r="C16" s="96">
-        <v>311.38753968129998</v>
+        <v>351.44507936330001</v>
       </c>
       <c r="D16" s="96">
-        <v>1621.2710119139001</v>
+        <v>1753.0385119133</v>
       </c>
       <c r="E16" s="96">
-        <v>7830460.6488101464</v>
+        <v>9015875.5390208997</v>
       </c>
       <c r="F16" s="96">
         <v>0</v>
@@ -2924,13 +2930,13 @@
         <v>1</v>
       </c>
       <c r="C17" s="96">
-        <v>626.74599206139999</v>
+        <v>723.14480158490005</v>
       </c>
       <c r="D17" s="96">
-        <v>1744.6222738143999</v>
+        <v>1961.8446190520999</v>
       </c>
       <c r="E17" s="96">
-        <v>12180676.72377059</v>
+        <v>14059558.299505398</v>
       </c>
       <c r="F17" s="96">
         <v>0</v>
@@ -2950,13 +2956,13 @@
         <v>1</v>
       </c>
       <c r="C18" s="96">
-        <v>823.53900793590003</v>
+        <v>902.89089285620003</v>
       </c>
       <c r="D18" s="96">
-        <v>3499.9758690460999</v>
+        <v>3941.1758690411002</v>
       </c>
       <c r="E18" s="96">
-        <v>16024694.976201845</v>
+        <v>17439906.551381622</v>
       </c>
       <c r="F18" s="96">
         <v>0</v>
@@ -2976,13 +2982,13 @@
         <v>1</v>
       </c>
       <c r="C19" s="96">
-        <v>721.2968121678</v>
+        <v>813.47657407259999</v>
       </c>
       <c r="D19" s="96">
-        <v>2697.1481428653001</v>
+        <v>2893.2247261999</v>
       </c>
       <c r="E19" s="96">
-        <v>13898645.433865212</v>
+        <v>15820251.940252023</v>
       </c>
       <c r="F19" s="96">
         <v>0</v>
@@ -3002,13 +3008,13 @@
         <v>1</v>
       </c>
       <c r="C20" s="96">
-        <v>2807.6356944447998</v>
+        <v>2976.6077182544</v>
       </c>
       <c r="D20" s="96">
-        <v>12452.8206666639</v>
+        <v>13411.3243333307</v>
       </c>
       <c r="E20" s="96">
-        <v>37584435.958896145</v>
+        <v>41338677.54260511</v>
       </c>
       <c r="F20" s="96">
         <v>0</v>
@@ -3028,13 +3034,13 @@
         <v>1</v>
       </c>
       <c r="C21" s="96">
-        <v>327.87930555359998</v>
+        <v>377.26049602939997</v>
       </c>
       <c r="D21" s="96">
-        <v>1206.7342142885</v>
+        <v>1435.7342142929001</v>
       </c>
       <c r="E21" s="96">
-        <v>7188705.5862517217</v>
+        <v>8244716.2501042979</v>
       </c>
       <c r="F21" s="96">
         <v>0</v>
@@ -3054,13 +3060,13 @@
         <v>1</v>
       </c>
       <c r="C22" s="96">
-        <v>283.72748015740001</v>
+        <v>318.46501190359999</v>
       </c>
       <c r="D22" s="96">
-        <v>876.65601190109999</v>
+        <v>1015.5265238078</v>
       </c>
       <c r="E22" s="96">
-        <v>4684076.524209898</v>
+        <v>5567175.7313747797</v>
       </c>
       <c r="F22" s="96">
         <v>0</v>
@@ -3132,13 +3138,13 @@
         <v>1</v>
       </c>
       <c r="C25" s="96">
-        <v>405.38249999919998</v>
+        <v>457.83190476089999</v>
       </c>
       <c r="D25" s="96">
-        <v>1404.0220833387</v>
+        <v>1735.0420833439</v>
       </c>
       <c r="E25" s="96">
-        <v>7212918.424210974</v>
+        <v>8331163.463863492</v>
       </c>
       <c r="F25" s="96">
         <v>0</v>
@@ -3158,13 +3164,13 @@
         <v>1</v>
       </c>
       <c r="C26" s="96">
-        <v>284.10333333210002</v>
+        <v>312.9566071415</v>
       </c>
       <c r="D26" s="96">
-        <v>761.78791666910001</v>
+        <v>884.78791666810002</v>
       </c>
       <c r="E26" s="96">
-        <v>5035112.3818729157</v>
+        <v>5482149.478754703</v>
       </c>
       <c r="F26" s="96">
         <v>0</v>
@@ -3184,13 +3190,13 @@
         <v>1</v>
       </c>
       <c r="C27" s="96">
-        <v>1886.5</v>
+        <v>3686.5</v>
       </c>
       <c r="D27" s="96">
-        <v>9716.84</v>
+        <v>15335.54</v>
       </c>
       <c r="E27" s="96">
-        <v>23429640.094719999</v>
+        <v>38194190.065520003</v>
       </c>
       <c r="F27" s="96">
         <v>0</v>
@@ -3204,19 +3210,19 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="96" t="s">
-        <v>101</v>
+        <v>233</v>
       </c>
       <c r="B28" s="96">
         <v>1</v>
       </c>
       <c r="C28" s="96">
-        <v>634.36102843740002</v>
+        <v>666.16360780230002</v>
       </c>
       <c r="D28" s="96">
-        <v>2820.3755878042998</v>
+        <v>2898.6280878054999</v>
       </c>
       <c r="E28" s="96">
-        <v>12482971.675436357</v>
+        <v>13022386.541284554</v>
       </c>
       <c r="F28" s="96">
         <v>0</v>
@@ -3236,13 +3242,13 @@
         <v>1</v>
       </c>
       <c r="C29" s="96">
-        <v>2151.9008333335</v>
+        <v>2331.5627380954002</v>
       </c>
       <c r="D29" s="96">
-        <v>5841.2620833384999</v>
+        <v>6328.3620833379</v>
       </c>
       <c r="E29" s="96">
-        <v>28353385.45531898</v>
+        <v>30033987.082212482</v>
       </c>
       <c r="F29" s="96">
         <v>0</v>
@@ -3262,13 +3268,13 @@
         <v>1</v>
       </c>
       <c r="C30" s="96">
-        <v>197.61617063489999</v>
+        <v>228.48978174600001</v>
       </c>
       <c r="D30" s="96">
-        <v>797.35166667420003</v>
+        <v>951.225833341</v>
       </c>
       <c r="E30" s="96">
-        <v>3805787.6012926684</v>
+        <v>4657516.3901073569</v>
       </c>
       <c r="F30" s="96">
         <v>0</v>
@@ -3288,13 +3294,13 @@
         <v>1</v>
       </c>
       <c r="C31" s="96">
-        <v>257.15317460160003</v>
+        <v>308.55198412530001</v>
       </c>
       <c r="D31" s="96">
-        <v>558.59000000030005</v>
+        <v>696.84250000010002</v>
       </c>
       <c r="E31" s="96">
-        <v>4367804.0145924808</v>
+        <v>5212708.9840588067</v>
       </c>
       <c r="F31" s="96">
         <v>0</v>
@@ -3314,13 +3320,13 @@
         <v>1</v>
       </c>
       <c r="C32" s="96">
-        <v>160.09107142849999</v>
+        <v>167.07162698400001</v>
       </c>
       <c r="D32" s="96">
-        <v>629.16624999830003</v>
+        <v>587.41874999870004</v>
       </c>
       <c r="E32" s="96">
-        <v>3442297.9978710278</v>
+        <v>3564392.4785372978</v>
       </c>
       <c r="F32" s="96">
         <v>0</v>
@@ -3340,13 +3346,13 @@
         <v>1</v>
       </c>
       <c r="C33" s="96">
-        <v>360.20210317369998</v>
+        <v>399.29178571360001</v>
       </c>
       <c r="D33" s="96">
-        <v>1178.3085000034</v>
+        <v>1439.6110000041999</v>
       </c>
       <c r="E33" s="96">
-        <v>6348650.0493735028</v>
+        <v>7023786.2862272449</v>
       </c>
       <c r="F33" s="96">
         <v>0</v>
@@ -3418,13 +3424,13 @@
         <v>1</v>
       </c>
       <c r="C36" s="96">
-        <v>383.11065476070002</v>
+        <v>660.91938491940004</v>
       </c>
       <c r="D36" s="96">
-        <v>1692.1407738109999</v>
+        <v>1829.4147023833</v>
       </c>
       <c r="E36" s="96">
-        <v>7824662.7877200451</v>
+        <v>11034688.327347409</v>
       </c>
       <c r="F36" s="96">
         <v>0</v>
@@ -3444,13 +3450,13 @@
         <v>1</v>
       </c>
       <c r="C37" s="96">
-        <v>652.08799603219995</v>
+        <v>644.06299603219998</v>
       </c>
       <c r="D37" s="96">
-        <v>4076.6771547639</v>
+        <v>3989.6771547639</v>
       </c>
       <c r="E37" s="96">
-        <v>12982127.936856734</v>
+        <v>12726652.901956733</v>
       </c>
       <c r="F37" s="96">
         <v>0</v>
@@ -3470,13 +3476,13 @@
         <v>1</v>
       </c>
       <c r="C38" s="96">
-        <v>462.89242424230002</v>
+        <v>465.39242424230002</v>
       </c>
       <c r="D38" s="96">
-        <v>5401.7499999989004</v>
+        <v>5421.5099999988997</v>
       </c>
       <c r="E38" s="96">
-        <v>10040043.519329419</v>
+        <v>10126859.110729419</v>
       </c>
       <c r="F38" s="96">
         <v>0</v>
@@ -3496,13 +3502,13 @@
         <v>1</v>
       </c>
       <c r="C39" s="96">
-        <v>961.75</v>
+        <v>1099.0833333333001</v>
       </c>
       <c r="D39" s="96">
-        <v>11522.639999998801</v>
+        <v>13338.5399999982</v>
       </c>
       <c r="E39" s="96">
-        <v>20528174.766575135</v>
+        <v>23985001.331072558</v>
       </c>
       <c r="F39" s="96">
         <v>0</v>
@@ -3516,19 +3522,19 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="96" t="s">
-        <v>109</v>
+        <v>234</v>
       </c>
       <c r="B40" s="96">
         <v>1</v>
       </c>
       <c r="C40" s="96">
-        <v>788.22911375679996</v>
+        <v>806.41085978859996</v>
       </c>
       <c r="D40" s="96">
-        <v>4495.562712977</v>
+        <v>4559.2816415463003</v>
       </c>
       <c r="E40" s="96">
-        <v>7599049.4142421484</v>
+        <v>8128233.8339369334</v>
       </c>
       <c r="F40" s="96">
         <v>0</v>
@@ -3548,13 +3554,13 @@
         <v>1</v>
       </c>
       <c r="C41" s="96">
-        <v>911.18134920600005</v>
+        <v>1673.2005158728</v>
       </c>
       <c r="D41" s="96">
-        <v>6551.529166667</v>
+        <v>9762.1595238119007</v>
       </c>
       <c r="E41" s="96">
-        <v>12160822.067982538</v>
+        <v>19638670.354043003</v>
       </c>
       <c r="F41" s="96">
         <v>0</v>
@@ -3574,13 +3580,13 @@
         <v>1</v>
       </c>
       <c r="C42" s="96">
-        <v>100.0611111111</v>
+        <v>112.0611111111</v>
       </c>
       <c r="D42" s="96">
-        <v>1475.5799999999001</v>
+        <v>1639.5799999999001</v>
       </c>
       <c r="E42" s="96">
-        <v>2478634.4092995184</v>
+        <v>2767832.4172995184</v>
       </c>
       <c r="F42" s="96">
         <v>0</v>
@@ -3600,13 +3606,13 @@
         <v>1</v>
       </c>
       <c r="C43" s="96">
-        <v>249.55500992079999</v>
+        <v>227.30500992079999</v>
       </c>
       <c r="D43" s="96">
-        <v>1125.0769014857001</v>
+        <v>1095.8402098199001</v>
       </c>
       <c r="E43" s="96">
-        <v>8104352.0621971888</v>
+        <v>6840893.5633781236</v>
       </c>
       <c r="F43" s="96">
         <v>0</v>
@@ -3626,13 +3632,13 @@
         <v>1</v>
       </c>
       <c r="C44" s="96">
-        <v>1041.2170634924</v>
+        <v>1046.7694444448</v>
       </c>
       <c r="D44" s="96">
-        <v>12428.4199404746</v>
+        <v>12465.4199404748</v>
       </c>
       <c r="E44" s="96">
-        <v>14041795.823822808</v>
+        <v>14127537.863605659</v>
       </c>
       <c r="F44" s="96">
         <v>0</v>
@@ -3652,13 +3658,13 @@
         <v>1</v>
       </c>
       <c r="C45" s="96">
-        <v>355.19942460380003</v>
+        <v>359.1312896833</v>
       </c>
       <c r="D45" s="96">
-        <v>3289.8991916700002</v>
+        <v>3307.8991916711002</v>
       </c>
       <c r="E45" s="96">
-        <v>7159889.4382920526</v>
+        <v>7281079.6085403729</v>
       </c>
       <c r="F45" s="96">
         <v>0</v>
@@ -3773,44 +3779,44 @@
       </c>
       <c r="D2" s="59">
         <f>IFERROR(+VLOOKUP(B2,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>17439906.551381622</v>
+      </c>
+      <c r="E2" s="59">
         <v>16024694.976201845</v>
-      </c>
-      <c r="E2" s="59">
-        <v>14544874.419634702</v>
       </c>
       <c r="F2" s="59">
         <f t="shared" ref="F2:F9" si="0">+D2-E2</f>
-        <v>1479820.5565671436</v>
+        <v>1415211.5751797762</v>
       </c>
       <c r="G2" s="60">
         <f t="shared" ref="G2:G41" si="1">+D2/C2</f>
-        <v>0.49644217385117384</v>
+        <v>0.54028517441280544</v>
       </c>
       <c r="H2" s="59">
         <f>+D2/$N$3*$N$4</f>
-        <v>48074084.928605534</v>
+        <v>46506417.470350988</v>
       </c>
       <c r="I2" s="60">
         <f t="shared" ref="I2:I41" si="2">+H2/C2</f>
-        <v>1.4893265215535216</v>
+        <v>1.4407604651008143</v>
       </c>
       <c r="J2" s="59">
         <f>+D2/$N$3</f>
-        <v>2003086.8720252307</v>
+        <v>1937767.3945979578</v>
       </c>
       <c r="K2" s="59">
         <f t="shared" ref="K2:K41" si="3">+(C2-D2)/$N$2</f>
-        <v>1015898.8538780567</v>
+        <v>989278.00579127541</v>
       </c>
       <c r="L2" s="61" cm="1">
         <f t="array" ref="L2">+_xlfn.IFS(I2&gt;114%,H2*0.02,I2&gt;109%,H2*0.015,I2&gt;104%,H2*0.0125,I2&gt;99%,H2*0.01,I2&lt;99%,H2*0)</f>
-        <v>961481.69857211073</v>
+        <v>930128.34940701979</v>
       </c>
       <c r="M2" s="53" t="s">
         <v>36</v>
       </c>
       <c r="N2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -3823,45 +3829,45 @@
       </c>
       <c r="D3" s="4">
         <f>IFERROR(+VLOOKUP(B3,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>14059558.299505398</v>
+      </c>
+      <c r="E3" s="4">
         <v>12180676.72377059</v>
-      </c>
-      <c r="E3" s="4">
-        <v>10570739.693693133</v>
       </c>
       <c r="F3" s="4">
         <f t="shared" si="0"/>
-        <v>1609937.0300774574</v>
+        <v>1878881.5757348072</v>
       </c>
       <c r="G3" s="5">
         <f t="shared" si="1"/>
-        <v>0.39314409800982325</v>
+        <v>0.45378696860813894</v>
       </c>
       <c r="H3" s="4">
         <f t="shared" ref="H3:H41" si="4">+D3/$N$3*$N$4</f>
-        <v>36542030.171311773</v>
+        <v>37492155.46534773</v>
       </c>
       <c r="I3" s="5">
         <f t="shared" si="2"/>
-        <v>1.1794322940294697</v>
+        <v>1.2100985829550372</v>
       </c>
       <c r="J3" s="4">
         <f t="shared" ref="J3:J41" si="5">+D3/$N$3</f>
-        <v>1522584.5904713238</v>
+        <v>1562173.1443894887</v>
       </c>
       <c r="K3" s="4">
         <f t="shared" si="3"/>
-        <v>1175128.2159445416</v>
+        <v>1128211.3252918571</v>
       </c>
       <c r="L3" s="63" cm="1">
         <f t="array" ref="L3">+_xlfn.IFS(I3&gt;114%,H3*0.02,I3&gt;109%,H3*0.015,I3&gt;104%,H3*0.0125,I3&gt;99%,H3*0.01,I3&lt;99%,H3*0)</f>
-        <v>730840.6034262355</v>
+        <v>749843.10930695466</v>
       </c>
       <c r="M3" s="53" t="s">
         <v>40</v>
       </c>
       <c r="N3">
         <f>N4-N2</f>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -3874,38 +3880,38 @@
       </c>
       <c r="D4" s="4">
         <f>IFERROR(+VLOOKUP(B4,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>11854719.440338746</v>
+      </c>
+      <c r="E4" s="4">
         <v>9837944.9718231615</v>
-      </c>
-      <c r="E4" s="4">
-        <v>8367738.4832338309</v>
       </c>
       <c r="F4" s="4">
         <f t="shared" si="0"/>
-        <v>1470206.4885893306</v>
+        <v>2016774.4685155842</v>
       </c>
       <c r="G4" s="5">
         <f t="shared" si="1"/>
-        <v>0.3465281486192977</v>
+        <v>0.41756626936087565</v>
       </c>
       <c r="H4" s="4">
         <f t="shared" si="4"/>
-        <v>29513834.915469483</v>
+        <v>31612585.174236655</v>
       </c>
       <c r="I4" s="5">
         <f t="shared" si="2"/>
-        <v>1.0395844458578931</v>
+        <v>1.1135100516290017</v>
       </c>
       <c r="J4" s="4">
         <f t="shared" si="5"/>
-        <v>1229743.1214778952</v>
+        <v>1317191.0489265274</v>
       </c>
       <c r="K4" s="4">
         <f t="shared" si="3"/>
-        <v>1159505.3930203184</v>
+        <v>1102354.1213206339</v>
       </c>
       <c r="L4" s="63" cm="1">
         <f t="array" ref="L4">+_xlfn.IFS(I4&gt;114%,H4*0.02,I4&gt;109%,H4*0.015,I4&gt;104%,H4*0.0125,I4&gt;99%,H4*0.01,I4&lt;99%,H4*0)</f>
-        <v>295138.34915469482</v>
+        <v>474188.77761354978</v>
       </c>
       <c r="M4" s="53" t="s">
         <v>47</v>
@@ -3924,38 +3930,38 @@
       </c>
       <c r="D5" s="4">
         <f>IFERROR(+VLOOKUP(B5,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>11920566.462441558</v>
+      </c>
+      <c r="E5" s="4">
         <v>10185885.70934353</v>
-      </c>
-      <c r="E5" s="4">
-        <v>8636687.304375954</v>
       </c>
       <c r="F5" s="4">
         <f t="shared" si="0"/>
-        <v>1549198.4049675763</v>
+        <v>1734680.7530980278</v>
       </c>
       <c r="G5" s="5">
         <f t="shared" si="1"/>
-        <v>0.35878388494914037</v>
+        <v>0.41988564060423328</v>
       </c>
       <c r="H5" s="4">
         <f t="shared" si="4"/>
-        <v>30557657.128030591</v>
+        <v>31788177.233177491</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" si="2"/>
-        <v>1.0763516548474212</v>
+        <v>1.119695041611289</v>
       </c>
       <c r="J5" s="4">
         <f t="shared" si="5"/>
-        <v>1273235.7136679413</v>
+        <v>1324507.3847157287</v>
       </c>
       <c r="K5" s="4">
         <f t="shared" si="3"/>
-        <v>1137759.0969252952</v>
+        <v>1097964.319847113</v>
       </c>
       <c r="L5" s="63" cm="1">
         <f t="array" ref="L5">+_xlfn.IFS(I5&gt;114%,H5*0.02,I5&gt;109%,H5*0.015,I5&gt;104%,H5*0.0125,I5&gt;99%,H5*0.01,I5&lt;99%,H5*0)</f>
-        <v>381970.71410038241</v>
+        <v>476822.65849766234</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
@@ -3968,38 +3974,38 @@
       </c>
       <c r="D6" s="4">
         <f>IFERROR(+VLOOKUP(B6,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>10222287.133025508</v>
+      </c>
+      <c r="E6" s="4">
         <v>8765227.9594276343</v>
-      </c>
-      <c r="E6" s="4">
-        <v>7873914.9061112888</v>
       </c>
       <c r="F6" s="4">
         <f t="shared" si="0"/>
-        <v>891313.05331634544</v>
+        <v>1457059.1735978741</v>
       </c>
       <c r="G6" s="5">
         <f t="shared" si="1"/>
-        <v>0.37253306890690768</v>
+        <v>0.43445989249117684</v>
       </c>
       <c r="H6" s="4">
         <f t="shared" si="4"/>
-        <v>26295683.878282905</v>
+        <v>27259432.354734689</v>
       </c>
       <c r="I6" s="5">
         <f t="shared" si="2"/>
-        <v>1.117599206720723</v>
+        <v>1.1585597133098049</v>
       </c>
       <c r="J6" s="4">
         <f t="shared" si="5"/>
-        <v>1095653.4949284543</v>
+        <v>1135809.6814472787</v>
       </c>
       <c r="K6" s="4">
         <f t="shared" si="3"/>
-        <v>922718.5361307807</v>
+        <v>887095.82696630782</v>
       </c>
       <c r="L6" s="63" cm="1">
         <f t="array" ref="L6">+_xlfn.IFS(I6&gt;114%,H6*0.02,I6&gt;109%,H6*0.015,I6&gt;104%,H6*0.0125,I6&gt;99%,H6*0.01,I6&lt;99%,H6*0)</f>
-        <v>394435.25817424356</v>
+        <v>545188.64709469373</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
@@ -4012,34 +4018,34 @@
       </c>
       <c r="D7" s="4">
         <f>IFERROR(+VLOOKUP(B7,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>7404424.1934615131</v>
+      </c>
+      <c r="E7" s="4">
         <v>5878949.2572204797</v>
-      </c>
-      <c r="E7" s="4">
-        <v>4840096.3237659615</v>
       </c>
       <c r="F7" s="4">
         <f t="shared" ref="F7:F8" si="6">+D7-E7</f>
-        <v>1038852.9334545182</v>
+        <v>1525474.9362410335</v>
       </c>
       <c r="G7" s="5">
         <f t="shared" si="1"/>
-        <v>0.21191621205330838</v>
+        <v>0.26690441758568656</v>
       </c>
       <c r="H7" s="4">
         <f t="shared" si="4"/>
-        <v>17636847.771661438</v>
+        <v>19745131.182564035</v>
       </c>
       <c r="I7" s="5">
         <f t="shared" si="2"/>
-        <v>0.63574863615992505</v>
+        <v>0.7117451135618309</v>
       </c>
       <c r="J7" s="4">
         <f t="shared" si="5"/>
-        <v>734868.65715255996</v>
+        <v>822713.7992735015</v>
       </c>
       <c r="K7" s="4">
         <f t="shared" si="3"/>
-        <v>1366431.7358277515</v>
+        <v>1355828.8558001996</v>
       </c>
       <c r="L7" s="63" cm="1">
         <f t="array" ref="L7">+_xlfn.IFS(I7&gt;114%,H7*0.02,I7&gt;109%,H7*0.015,I7&gt;104%,H7*0.0125,I7&gt;99%,H7*0.01,I7&lt;99%,H7*0)</f>
@@ -4056,34 +4062,34 @@
       </c>
       <c r="D8" s="4">
         <f>IFERROR(+VLOOKUP(B8,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>13226460.381280242</v>
+      </c>
+      <c r="E8" s="4">
         <v>11328941.073388485</v>
-      </c>
-      <c r="E8" s="4">
-        <v>10363253.207426563</v>
       </c>
       <c r="F8" s="4">
         <f t="shared" si="6"/>
-        <v>965687.86596192233</v>
+        <v>1897519.3078917563</v>
       </c>
       <c r="G8" s="5">
         <f t="shared" si="1"/>
-        <v>0.31617645315622644</v>
+        <v>0.36913382319445087</v>
       </c>
       <c r="H8" s="4">
         <f t="shared" si="4"/>
-        <v>33986823.220165454</v>
+        <v>35270561.016747311</v>
       </c>
       <c r="I8" s="5">
         <f t="shared" si="2"/>
-        <v>0.94852935946867933</v>
+        <v>0.98435686185186899</v>
       </c>
       <c r="J8" s="4">
         <f t="shared" si="5"/>
-        <v>1416117.6341735607</v>
+        <v>1469606.7090311379</v>
       </c>
       <c r="K8" s="4">
         <f t="shared" si="3"/>
-        <v>1531383.1464705761</v>
+        <v>1506974.0690424973</v>
       </c>
       <c r="L8" s="63" cm="1">
         <f t="array" ref="L8">+_xlfn.IFS(I8&gt;114%,H8*0.02,I8&gt;109%,H8*0.015,I8&gt;104%,H8*0.0125,I8&gt;99%,H8*0.01,I8&lt;99%,H8*0)</f>
@@ -4100,38 +4106,38 @@
       </c>
       <c r="D9" s="4">
         <f>IFERROR(+VLOOKUP(B9,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>15645728.431611888</v>
+      </c>
+      <c r="E9" s="4">
         <v>13014610.776669662</v>
-      </c>
-      <c r="E9" s="4">
-        <v>10378829.479285927</v>
       </c>
       <c r="F9" s="4">
         <f t="shared" si="0"/>
-        <v>2635781.297383735</v>
+        <v>2631117.6549422257</v>
       </c>
       <c r="G9" s="5">
         <f t="shared" si="1"/>
-        <v>0.3632213679919376</v>
+        <v>0.43665254241392093</v>
       </c>
       <c r="H9" s="4">
         <f t="shared" si="4"/>
-        <v>39043832.330008984</v>
+        <v>41721942.484298371</v>
       </c>
       <c r="I9" s="5">
         <f t="shared" si="2"/>
-        <v>1.0896641039758126</v>
+        <v>1.1644067797704558</v>
       </c>
       <c r="J9" s="4">
         <f t="shared" si="5"/>
-        <v>1626826.3470837078</v>
+        <v>1738414.2701790987</v>
       </c>
       <c r="K9" s="4">
         <f t="shared" si="3"/>
-        <v>1426028.7900155026</v>
+        <v>1345689.5323537211</v>
       </c>
       <c r="L9" s="63" cm="1">
         <f t="array" ref="L9">+_xlfn.IFS(I9&gt;114%,H9*0.02,I9&gt;109%,H9*0.015,I9&gt;104%,H9*0.0125,I9&gt;99%,H9*0.01,I9&lt;99%,H9*0)</f>
-        <v>488047.90412511234</v>
+        <v>834438.84968596743</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4142,34 +4148,34 @@
       </c>
       <c r="D10" s="64">
         <f>+SUM(D2:D9)</f>
+        <v>101773650.89304647</v>
+      </c>
+      <c r="E10" s="65">
         <v>87216931.447845384</v>
-      </c>
-      <c r="E10" s="65">
-        <v>75576133.817527354</v>
       </c>
       <c r="F10" s="64">
         <f>+SUM(F2:F9)</f>
-        <v>11640797.630318029</v>
+        <v>14556719.445201084</v>
       </c>
       <c r="G10" s="66">
         <f t="shared" si="1"/>
-        <v>0.3589549459617683</v>
+        <v>0.41886540549172074</v>
       </c>
       <c r="H10" s="64">
         <f t="shared" si="4"/>
-        <v>261650794.34353614</v>
+        <v>271396402.38145727</v>
       </c>
       <c r="I10" s="66">
         <f t="shared" si="2"/>
-        <v>1.076864837885305</v>
+        <v>1.1169744146445888</v>
       </c>
       <c r="J10" s="64">
         <f t="shared" si="5"/>
-        <v>10902116.430980673</v>
+        <v>11308183.43256072</v>
       </c>
       <c r="K10" s="67">
         <f t="shared" si="3"/>
-        <v>9734853.7682128213</v>
+        <v>9413396.0564136021</v>
       </c>
       <c r="L10" s="68"/>
     </row>
@@ -4185,38 +4191,38 @@
       </c>
       <c r="D11" s="59">
         <f>IFERROR(+VLOOKUP(B11,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>41338677.54260511</v>
+      </c>
+      <c r="E11" s="59">
         <v>37584435.958896145</v>
-      </c>
-      <c r="E11" s="59">
-        <v>33209684.287959997</v>
       </c>
       <c r="F11" s="59">
         <f t="shared" ref="F11:F16" si="7">+D11-E11</f>
-        <v>4374751.6709361486</v>
+        <v>3754241.5837089643</v>
       </c>
       <c r="G11" s="60">
         <f t="shared" si="1"/>
-        <v>0.38758049671028788</v>
+        <v>0.4262952141368222</v>
       </c>
       <c r="H11" s="59">
         <f t="shared" si="4"/>
-        <v>112753307.87668844</v>
+        <v>110236473.44694695</v>
       </c>
       <c r="I11" s="60">
         <f t="shared" si="2"/>
-        <v>1.1627414901308637</v>
+        <v>1.1367872376981925</v>
       </c>
       <c r="J11" s="59">
         <f t="shared" si="5"/>
-        <v>4698054.4948620182</v>
+        <v>4593186.3936227895</v>
       </c>
       <c r="K11" s="59">
         <f t="shared" si="3"/>
-        <v>3711719.5325775854</v>
+        <v>3708884.7291688267</v>
       </c>
       <c r="L11" s="61" cm="1">
         <f t="array" ref="L11">+_xlfn.IFS(I11&gt;114%,H11*0.0125,I11&gt;109%,H11*0.01,I11&gt;104%,H11*0.0075,I11&gt;99%,H11*0.005,I11&lt;99%,H11*0)</f>
-        <v>1409416.3484586056</v>
+        <v>1102364.7344694694</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4229,38 +4235,38 @@
       </c>
       <c r="D12" s="4">
         <f>IFERROR(+VLOOKUP(B12,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>12982127.936856734</v>
+        <v>12726652.901956733</v>
       </c>
       <c r="E12" s="4">
         <v>12982127.936856734</v>
       </c>
       <c r="F12" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-255475.03490000032</v>
       </c>
       <c r="G12" s="5">
         <f t="shared" si="1"/>
-        <v>0.41042546839702609</v>
+        <v>0.40234871384857518</v>
       </c>
       <c r="H12" s="4">
         <f t="shared" si="4"/>
-        <v>38946383.810570203</v>
+        <v>33937741.071884625</v>
       </c>
       <c r="I12" s="5">
         <f t="shared" si="2"/>
-        <v>1.2312764051910783</v>
+        <v>1.0729299035962006</v>
       </c>
       <c r="J12" s="4">
         <f t="shared" si="5"/>
-        <v>1622765.9921070917</v>
+        <v>1414072.5446618593</v>
       </c>
       <c r="K12" s="4">
         <f t="shared" si="3"/>
-        <v>1165548.404481892</v>
+        <v>1260283.3004406847</v>
       </c>
       <c r="L12" s="63" cm="1">
         <f t="array" ref="L12">+_xlfn.IFS(I12&gt;114%,H12*0.02,I12&gt;109%,H12*0.015,I12&gt;104%,H12*0.0125,I12&gt;99%,H12*0.01,I12&lt;99%,H12*0)</f>
-        <v>778927.67621140403</v>
+        <v>424221.76339855784</v>
       </c>
       <c r="M12" s="27"/>
     </row>
@@ -4274,38 +4280,38 @@
       </c>
       <c r="D13" s="4">
         <f>IFERROR(+VLOOKUP(B13,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>54947546.702784903</v>
+      </c>
+      <c r="E13" s="4">
         <v>32020542.941609319</v>
-      </c>
-      <c r="E13" s="4">
-        <v>25842742.680006113</v>
       </c>
       <c r="F13" s="4">
         <f t="shared" si="7"/>
-        <v>6177800.2616032064</v>
+        <v>22927003.761175584</v>
       </c>
       <c r="G13" s="5">
         <f t="shared" si="1"/>
-        <v>0.24945127821586574</v>
+        <v>0.4280606916887833</v>
       </c>
       <c r="H13" s="4">
         <f t="shared" si="4"/>
-        <v>96061628.824827954</v>
+        <v>146526791.20742643</v>
       </c>
       <c r="I13" s="5">
         <f t="shared" si="2"/>
-        <v>0.74835383464759719</v>
+        <v>1.1414951778367557</v>
       </c>
       <c r="J13" s="4">
         <f t="shared" si="5"/>
-        <v>4002567.8677011649</v>
+        <v>6105282.9669761006</v>
       </c>
       <c r="K13" s="4">
         <f t="shared" si="3"/>
-        <v>6021460.8208134789</v>
+        <v>4894424.6247893395</v>
       </c>
       <c r="L13" s="63" cm="1">
         <f t="array" ref="L13">+_xlfn.IFS(I13&gt;114%,H13*0.0125,I13&gt;109%,H13*0.01,I13&gt;104%,H13*0.0075,I13&gt;99%,H13*0.005,I13&lt;99%,H13*0)</f>
-        <v>0</v>
+        <v>1831584.8900928304</v>
       </c>
       <c r="M13" s="53" t="s">
         <v>61</v>
@@ -4324,34 +4330,34 @@
       </c>
       <c r="D14" s="4">
         <f>IFERROR(+VLOOKUP(B14,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>10126859.110729419</v>
+      </c>
+      <c r="E14" s="4">
         <v>10040043.519329419</v>
-      </c>
-      <c r="E14" s="4">
-        <v>6979221.568329419</v>
       </c>
       <c r="F14" s="4">
         <f t="shared" si="7"/>
-        <v>3060821.9510000004</v>
+        <v>86815.591399999335</v>
       </c>
       <c r="G14" s="5">
         <f t="shared" si="1"/>
-        <v>0.23651982247591513</v>
+        <v>0.23856499371710921</v>
       </c>
       <c r="H14" s="4">
         <f t="shared" si="4"/>
-        <v>30120130.557988256</v>
+        <v>27004957.628611781</v>
       </c>
       <c r="I14" s="5">
         <f t="shared" si="2"/>
-        <v>0.70955946742774534</v>
+        <v>0.63617331657895781</v>
       </c>
       <c r="J14" s="4">
         <f t="shared" si="5"/>
-        <v>1255005.4399161774</v>
+        <v>1125206.5678588243</v>
       </c>
       <c r="K14" s="4">
         <f t="shared" si="3"/>
-        <v>2025563.3672278486</v>
+        <v>2154813.2189497054</v>
       </c>
       <c r="L14" s="63" cm="1">
         <f t="array" ref="L14">+_xlfn.IFS(I14&gt;109%,H14*0.015,I14&gt;104%,H14*0.0125,I14&gt;99%,H14*0.01,I14&lt;99%,H14*0)</f>
@@ -4369,38 +4375,38 @@
       </c>
       <c r="D15" s="4">
         <f>IFERROR(+VLOOKUP(B15,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>23985001.331072558</v>
+      </c>
+      <c r="E15" s="4">
         <v>20528174.766575135</v>
-      </c>
-      <c r="E15" s="4">
-        <v>19182792.083198067</v>
       </c>
       <c r="F15" s="4">
         <f t="shared" si="7"/>
-        <v>1345382.6833770685</v>
+        <v>3456826.5644974224</v>
       </c>
       <c r="G15" s="5">
         <f t="shared" si="1"/>
-        <v>0.48359553842543518</v>
+        <v>0.56503024573431015</v>
       </c>
       <c r="H15" s="4">
         <f t="shared" si="4"/>
-        <v>61584524.299725406</v>
+        <v>63960003.549526826</v>
       </c>
       <c r="I15" s="5">
         <f t="shared" si="2"/>
-        <v>1.4507866152763056</v>
+        <v>1.5067473219581604</v>
       </c>
       <c r="J15" s="4">
         <f t="shared" si="5"/>
-        <v>2566021.8458218919</v>
+        <v>2665000.1478969511</v>
       </c>
       <c r="K15" s="4">
         <f t="shared" si="3"/>
-        <v>1370055.1642749915</v>
+        <v>1230937.0709268295</v>
       </c>
       <c r="L15" s="63" cm="1">
         <f t="array" ref="L15">+_xlfn.IFS(I15&gt;109%,H15*0.015,I15&gt;104%,H15*0.0125,I15&gt;99%,H15*0.01,I15&lt;99%,H15*0)</f>
-        <v>923767.86449588102</v>
+        <v>959400.05324290239</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4411,34 +4417,34 @@
       </c>
       <c r="D16" s="64">
         <f>+SUM(D11:D15)</f>
+        <v>143124737.58914873</v>
+      </c>
+      <c r="E16" s="65">
         <v>113155325.12326676</v>
-      </c>
-      <c r="E16" s="65">
-        <v>98196568.556350335</v>
       </c>
       <c r="F16" s="64">
         <f t="shared" si="7"/>
-        <v>14958756.566916421</v>
+        <v>29969412.465881974</v>
       </c>
       <c r="G16" s="66">
         <f t="shared" si="1"/>
-        <v>0.33099429383603618</v>
+        <v>0.41865878956365116</v>
       </c>
       <c r="H16" s="64">
         <f t="shared" si="4"/>
-        <v>339465975.36980027</v>
+        <v>381665966.90439659</v>
       </c>
       <c r="I16" s="66">
         <f t="shared" si="2"/>
-        <v>0.99298288150810854</v>
+        <v>1.1164234388364029</v>
       </c>
       <c r="J16" s="64">
         <f t="shared" si="5"/>
-        <v>14144415.640408345</v>
+        <v>15902748.621016525</v>
       </c>
       <c r="K16" s="67">
         <f t="shared" si="3"/>
-        <v>14294347.289375797</v>
+        <v>13249342.944275385</v>
       </c>
       <c r="L16" s="68"/>
     </row>
@@ -4454,34 +4460,34 @@
       </c>
       <c r="D17" s="59">
         <f>IFERROR(+VLOOKUP(B17,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>7416441.7657084363</v>
+      </c>
+      <c r="E17" s="59">
         <v>6449843.5922434218</v>
-      </c>
-      <c r="E17" s="59">
-        <v>5940437.3079375168</v>
       </c>
       <c r="F17" s="59">
         <f t="shared" ref="F17:F40" si="8">+D17-E17</f>
-        <v>509406.28430590499</v>
+        <v>966598.17346501444</v>
       </c>
       <c r="G17" s="60">
         <f t="shared" si="1"/>
-        <v>0.21984592016794852</v>
+        <v>0.25279286870072071</v>
       </c>
       <c r="H17" s="59">
         <f t="shared" si="4"/>
-        <v>19349530.776730265</v>
+        <v>19777178.041889161</v>
       </c>
       <c r="I17" s="60">
         <f t="shared" si="2"/>
-        <v>0.65953776050384549</v>
+        <v>0.67411431653525511</v>
       </c>
       <c r="J17" s="59">
         <f t="shared" si="5"/>
-        <v>806230.44903042773</v>
+        <v>824049.08507871511</v>
       </c>
       <c r="K17" s="59">
         <f t="shared" si="3"/>
-        <v>1430510.9087660364</v>
+        <v>1461438.4244527712</v>
       </c>
       <c r="L17" s="61" cm="1">
         <f t="array" ref="L17">+_xlfn.IFS(I17&gt;114%,H17*0.02,I17&gt;109%,H17*0.015,I17&gt;104%,H17*0.0125,I17&gt;99%,H17*0.01,I17&lt;99%,H17*0)</f>
@@ -4498,34 +4504,34 @@
       </c>
       <c r="D18" s="4">
         <f>IFERROR(+VLOOKUP(B18,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>8097618.1083014421</v>
+      </c>
+      <c r="E18" s="4">
         <v>6596329.3614597432</v>
-      </c>
-      <c r="E18" s="4">
-        <v>5899873.0951455031</v>
       </c>
       <c r="F18" s="4">
         <f t="shared" si="8"/>
-        <v>696456.26631424017</v>
+        <v>1501288.7468416989</v>
       </c>
       <c r="G18" s="5">
         <f t="shared" si="1"/>
-        <v>0.26428124770930433</v>
+        <v>0.32443022473058819</v>
       </c>
       <c r="H18" s="4">
         <f t="shared" si="4"/>
-        <v>19788988.08437923</v>
+        <v>21593648.288803846</v>
       </c>
       <c r="I18" s="5">
         <f t="shared" si="2"/>
-        <v>0.79284374312791295</v>
+        <v>0.8651472659482351</v>
       </c>
       <c r="J18" s="4">
         <f t="shared" si="5"/>
-        <v>824541.1701824679</v>
+        <v>899735.34536682686</v>
       </c>
       <c r="K18" s="4">
         <f t="shared" si="3"/>
-        <v>1147698.5336587662</v>
+        <v>1124125.8527799039</v>
       </c>
       <c r="L18" s="63" cm="1">
         <f t="array" ref="L18">+_xlfn.IFS(I18&gt;114%,H18*0.02,I18&gt;109%,H18*0.015,I18&gt;104%,H18*0.0125,I18&gt;99%,H18*0.01,I18&lt;99%,H18*0)</f>
@@ -4542,34 +4548,34 @@
       </c>
       <c r="D19" s="4">
         <f>IFERROR(+VLOOKUP(B19,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>9015875.5390208997</v>
+      </c>
+      <c r="E19" s="4">
         <v>7830460.6488101464</v>
-      </c>
-      <c r="E19" s="4">
-        <v>6987566.4676926713</v>
       </c>
       <c r="F19" s="4">
         <f t="shared" si="8"/>
-        <v>842894.18111747503</v>
+        <v>1185414.8902107533</v>
       </c>
       <c r="G19" s="5">
         <f t="shared" si="1"/>
-        <v>0.30284126515576909</v>
+        <v>0.34868691347538122</v>
       </c>
       <c r="H19" s="4">
         <f t="shared" si="4"/>
-        <v>23491381.946430437</v>
+        <v>24042334.7707224</v>
       </c>
       <c r="I19" s="5">
         <f t="shared" si="2"/>
-        <v>0.90852379546730722</v>
+        <v>0.92983176926768329</v>
       </c>
       <c r="J19" s="4">
         <f t="shared" si="5"/>
-        <v>978807.5811012683</v>
+        <v>1001763.9487801</v>
       </c>
       <c r="K19" s="4">
         <f t="shared" si="3"/>
-        <v>1126636.8447931157</v>
+        <v>1122718.3084319399</v>
       </c>
       <c r="L19" s="63" cm="1">
         <f t="array" ref="L19">+_xlfn.IFS(I19&gt;114%,H19*0.02,I19&gt;109%,H19*0.015,I19&gt;104%,H19*0.0125,I19&gt;99%,H19*0.01,I19&lt;99%,H19*0)</f>
@@ -4586,38 +4592,38 @@
       </c>
       <c r="D20" s="4">
         <f>IFERROR(+VLOOKUP(B20,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>15820251.940252023</v>
+      </c>
+      <c r="E20" s="4">
         <v>13898645.433865212</v>
-      </c>
-      <c r="E20" s="4">
-        <v>11219784.289331133</v>
       </c>
       <c r="F20" s="4">
         <f t="shared" si="8"/>
-        <v>2678861.1445340794</v>
+        <v>1921606.5063868109</v>
       </c>
       <c r="G20" s="5">
         <f t="shared" si="1"/>
-        <v>0.41428972147971321</v>
+        <v>0.47156881591468802</v>
       </c>
       <c r="H20" s="4">
         <f t="shared" si="4"/>
-        <v>41695936.301595636</v>
+        <v>42187338.507338732</v>
       </c>
       <c r="I20" s="5">
         <f t="shared" si="2"/>
-        <v>1.2428691644391396</v>
+        <v>1.2575168424391683</v>
       </c>
       <c r="J20" s="4">
         <f t="shared" si="5"/>
-        <v>1737330.6792331515</v>
+        <v>1757805.7711391137</v>
       </c>
       <c r="K20" s="4">
         <f t="shared" si="3"/>
-        <v>1228092.7853834243</v>
+        <v>1181858.5373165319</v>
       </c>
       <c r="L20" s="63" cm="1">
         <f t="array" ref="L20">+_xlfn.IFS(I20&gt;114%,H20*0.02,I20&gt;109%,H20*0.015,I20&gt;104%,H20*0.0125,I20&gt;99%,H20*0.01,I20&lt;99%,H20*0)</f>
-        <v>833918.72603191272</v>
+        <v>843746.77014677471</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4630,34 +4636,34 @@
       </c>
       <c r="D21" s="4">
         <f>IFERROR(+VLOOKUP(B21,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>8244716.2501042979</v>
+      </c>
+      <c r="E21" s="4">
         <v>7188705.5862517217</v>
-      </c>
-      <c r="E21" s="4">
-        <v>6572144.8133745482</v>
       </c>
       <c r="F21" s="4">
         <f t="shared" ref="F21:F23" si="9">+D21-E21</f>
-        <v>616560.7728771735</v>
+        <v>1056010.6638525762</v>
       </c>
       <c r="G21" s="5">
         <f t="shared" si="1"/>
-        <v>0.28236945470303337</v>
+        <v>0.32384912746678018</v>
       </c>
       <c r="H21" s="4">
         <f t="shared" si="4"/>
-        <v>21566116.758755166</v>
+        <v>21985910.000278126</v>
       </c>
       <c r="I21" s="5">
         <f t="shared" si="2"/>
-        <v>0.84710836410910006</v>
+        <v>0.86359767324474712</v>
       </c>
       <c r="J21" s="4">
         <f t="shared" si="5"/>
-        <v>898588.19828146521</v>
+        <v>916079.58334492194</v>
       </c>
       <c r="K21" s="4">
         <f t="shared" si="3"/>
-        <v>1141862.7758592675</v>
+        <v>1147586.249993047</v>
       </c>
       <c r="L21" s="63" cm="1">
         <f t="array" ref="L21">+_xlfn.IFS(I21&gt;114%,H21*0.02,I21&gt;109%,H21*0.015,I21&gt;104%,H21*0.0125,I21&gt;99%,H21*0.01,I21&lt;99%,H21*0)</f>
@@ -4674,38 +4680,38 @@
       </c>
       <c r="D22" s="4">
         <f>IFERROR(+VLOOKUP(B22,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>0</v>
+      </c>
+      <c r="E22" s="4">
         <v>12482971.675436357</v>
-      </c>
-      <c r="E22" s="4">
-        <v>11431823.194593111</v>
       </c>
       <c r="F22" s="4">
         <f t="shared" si="9"/>
-        <v>1051148.480843246</v>
+        <v>-12482971.675436357</v>
       </c>
       <c r="G22" s="5">
         <f t="shared" si="1"/>
-        <v>0.39325252353474593</v>
+        <v>0</v>
       </c>
       <c r="H22" s="4">
         <f t="shared" si="4"/>
-        <v>37448915.026309073</v>
+        <v>0</v>
       </c>
       <c r="I22" s="5">
         <f t="shared" si="2"/>
-        <v>1.1797575706042378</v>
+        <v>0</v>
       </c>
       <c r="J22" s="4">
         <f t="shared" si="5"/>
-        <v>1560371.4594295446</v>
+        <v>0</v>
       </c>
       <c r="K22" s="4">
         <f t="shared" si="3"/>
-        <v>1203744.907785228</v>
+        <v>2116192.6800000002</v>
       </c>
       <c r="L22" s="63" cm="1">
         <f t="array" ref="L22">+_xlfn.IFS(I22&gt;114%,H22*0.02,I22&gt;109%,H22*0.015,I22&gt;104%,H22*0.0125,I22&gt;99%,H22*0.01,I22&lt;99%,H22*0)</f>
-        <v>748978.30052618147</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4718,38 +4724,38 @@
       </c>
       <c r="D23" s="4">
         <f>IFERROR(+VLOOKUP(B23,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>11034688.327347409</v>
+      </c>
+      <c r="E23" s="4">
         <v>7824662.7877200451</v>
-      </c>
-      <c r="E23" s="4">
-        <v>7002297.6074060109</v>
       </c>
       <c r="F23" s="4">
         <f t="shared" si="9"/>
-        <v>822365.18031403422</v>
+        <v>3210025.5396273639</v>
       </c>
       <c r="G23" s="5">
         <f t="shared" si="1"/>
-        <v>0.28519748224189617</v>
+        <v>0.40219820504245851</v>
       </c>
       <c r="H23" s="4">
         <f t="shared" si="4"/>
-        <v>23473988.363160133</v>
+        <v>29425835.539593089</v>
       </c>
       <c r="I23" s="5">
         <f t="shared" si="2"/>
-        <v>0.85559244672568857</v>
+        <v>1.0725285467798893</v>
       </c>
       <c r="J23" s="4">
         <f t="shared" si="5"/>
-        <v>978082.84846500563</v>
+        <v>1226076.4808163787</v>
       </c>
       <c r="K23" s="4">
         <f t="shared" si="3"/>
-        <v>1225705.2151424973</v>
+        <v>1093417.1935101731</v>
       </c>
       <c r="L23" s="63" cm="1">
         <f t="array" ref="L23">+_xlfn.IFS(I23&gt;114%,H23*0.02,I23&gt;109%,H23*0.015,I23&gt;104%,H23*0.0125,I23&gt;99%,H23*0.01,I23&lt;99%,H23*0)</f>
-        <v>0</v>
+        <v>367822.94424491364</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4762,34 +4768,34 @@
       </c>
       <c r="D24" s="4">
         <f>IFERROR(+VLOOKUP(B24,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>0</v>
+      </c>
+      <c r="E24" s="4">
         <v>7599049.4142421484</v>
-      </c>
-      <c r="E24" s="4">
-        <v>7360714.5095196133</v>
       </c>
       <c r="F24" s="4">
         <f t="shared" si="8"/>
-        <v>238334.90472253505</v>
+        <v>-7599049.4142421484</v>
       </c>
       <c r="G24" s="5">
         <f t="shared" si="1"/>
-        <v>0.22687755824853539</v>
+        <v>0</v>
       </c>
       <c r="H24" s="4">
         <f t="shared" si="4"/>
-        <v>22797148.242726445</v>
+        <v>0</v>
       </c>
       <c r="I24" s="5">
         <f t="shared" si="2"/>
-        <v>0.68063267474560618</v>
+        <v>0</v>
       </c>
       <c r="J24" s="4">
         <f t="shared" si="5"/>
-        <v>949881.17678026855</v>
+        <v>0</v>
       </c>
       <c r="K24" s="4">
         <f t="shared" si="3"/>
-        <v>1618437.8491098657</v>
+        <v>2232937</v>
       </c>
       <c r="L24" s="63" cm="1">
         <f t="array" ref="L24">+_xlfn.IFS(I24&gt;114%,H24*0.02,I24&gt;109%,H24*0.015,I24&gt;104%,H24*0.0125,I24&gt;99%,H24*0.01,I24&lt;99%,H24*0)</f>
@@ -4806,34 +4812,34 @@
       </c>
       <c r="D25" s="4">
         <f>IFERROR(+VLOOKUP(B25,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>12160822.067982538</v>
+        <v>19638670.354043003</v>
       </c>
       <c r="E25" s="4">
         <v>12160822.067982538</v>
       </c>
       <c r="F25" s="4">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>7477848.2860604655</v>
       </c>
       <c r="G25" s="5">
         <f t="shared" si="1"/>
-        <v>0.22492985610008884</v>
+        <v>0.36324216175829638</v>
       </c>
       <c r="H25" s="4">
         <f t="shared" si="4"/>
-        <v>36482466.203947611</v>
+        <v>52369787.610781342</v>
       </c>
       <c r="I25" s="5">
         <f t="shared" si="2"/>
-        <v>0.67478956830026648</v>
+        <v>0.96864576468879038</v>
       </c>
       <c r="J25" s="4">
         <f t="shared" si="5"/>
-        <v>1520102.7584978172</v>
+        <v>2182074.4837825559</v>
       </c>
       <c r="K25" s="4">
         <f t="shared" si="3"/>
-        <v>2619008.1748135919</v>
+        <v>2295085.500730467</v>
       </c>
       <c r="L25" s="63" cm="1">
         <f t="array" ref="L25">+_xlfn.IFS(I25&gt;109%,H25*0.015,I25&gt;104%,H25*0.0125,I25&gt;99%,H25*0.01,I25&lt;99%,H25*0)</f>
@@ -4848,34 +4854,34 @@
       </c>
       <c r="D26" s="67">
         <f>+SUM(D17:D25)</f>
+        <v>79268262.284777522</v>
+      </c>
+      <c r="E26" s="65">
         <v>82031490.568011329</v>
-      </c>
-      <c r="E26" s="65">
-        <v>74575463.35298264</v>
       </c>
       <c r="F26" s="67">
         <f>+D26-E26</f>
-        <v>7456027.2150286883</v>
+        <v>-2763228.2832338065</v>
       </c>
       <c r="G26" s="66">
         <f t="shared" si="1"/>
-        <v>0.28692506288909292</v>
+        <v>0.27726000080800778</v>
       </c>
       <c r="H26" s="64">
         <f t="shared" si="4"/>
-        <v>246094471.70403397</v>
+        <v>211382032.75940672</v>
       </c>
       <c r="I26" s="66">
         <f t="shared" si="2"/>
-        <v>0.86077518866727865</v>
+        <v>0.73936000215468733</v>
       </c>
       <c r="J26" s="64">
         <f t="shared" si="5"/>
-        <v>10253936.321001416</v>
+        <v>8807584.6983086132</v>
       </c>
       <c r="K26" s="67">
         <f t="shared" si="3"/>
-        <v>12741697.995311793</v>
+        <v>13775359.747214833</v>
       </c>
       <c r="L26" s="68"/>
     </row>
@@ -4891,38 +4897,38 @@
       </c>
       <c r="D27" s="59">
         <f>IFERROR(+VLOOKUP(B27,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>30033987.082212482</v>
+      </c>
+      <c r="E27" s="59">
         <v>28353385.45531898</v>
-      </c>
-      <c r="E27" s="59">
-        <v>21388145.925452832</v>
       </c>
       <c r="F27" s="59">
         <f t="shared" si="8"/>
-        <v>6965239.5298661478</v>
+        <v>1680601.6268935017</v>
       </c>
       <c r="G27" s="60">
         <f t="shared" si="1"/>
-        <v>0.34586705232421722</v>
+        <v>0.36636776931058668</v>
       </c>
       <c r="H27" s="59">
         <f t="shared" si="4"/>
-        <v>85060156.365956932</v>
+        <v>80090632.219233289</v>
       </c>
       <c r="I27" s="60">
         <f t="shared" si="2"/>
-        <v>1.0376011569726515</v>
+        <v>0.97698071816156451</v>
       </c>
       <c r="J27" s="59">
         <f t="shared" si="5"/>
-        <v>3544173.1819148725</v>
+        <v>3337109.6758013871</v>
       </c>
       <c r="K27" s="59">
         <f t="shared" si="3"/>
-        <v>3351519.6590425638</v>
+        <v>3462914.1945191682</v>
       </c>
       <c r="L27" s="61" cm="1">
         <f t="array" ref="L27">+_xlfn.IFS(I27&gt;114%,H27*0.0125,I27&gt;109%,H27*0.01,I27&gt;104%,H27*0.0075,I27&gt;99%,H27*0.005,I27&lt;99%,H27*0)</f>
-        <v>425300.78182978468</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4935,34 +4941,34 @@
       </c>
       <c r="D28" s="4">
         <f>IFERROR(+VLOOKUP(B28,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>5212708.9840588067</v>
+      </c>
+      <c r="E28" s="4">
         <v>4367804.0145924808</v>
-      </c>
-      <c r="E28" s="4">
-        <v>3875759.7054576175</v>
       </c>
       <c r="F28" s="4">
         <f t="shared" si="8"/>
-        <v>492044.30913486332</v>
+        <v>844904.96946632583</v>
       </c>
       <c r="G28" s="5">
         <f t="shared" si="1"/>
-        <v>0.2079906673615467</v>
+        <v>0.24822423733613366</v>
       </c>
       <c r="H28" s="4">
         <f t="shared" si="4"/>
-        <v>13103412.043777443</v>
+        <v>13900557.290823486</v>
       </c>
       <c r="I28" s="5">
         <f t="shared" si="2"/>
-        <v>0.62397200208464021</v>
+        <v>0.6619312995630231</v>
       </c>
       <c r="J28" s="4">
         <f t="shared" si="5"/>
-        <v>545975.50182406011</v>
+        <v>579189.88711764524</v>
       </c>
       <c r="K28" s="4">
         <f t="shared" si="3"/>
-        <v>1039512.24908797</v>
+        <v>1052486.0677294128</v>
       </c>
       <c r="L28" s="63" cm="1">
         <f t="array" ref="L28">+_xlfn.IFS(I28&gt;114%,H28*0.02,I28&gt;109%,H28*0.015,I28&gt;104%,H28*0.0125,I28&gt;99%,H28*0.01,I28&lt;99%,H28*0)</f>
@@ -4979,34 +4985,34 @@
       </c>
       <c r="D29" s="4">
         <f>IFERROR(+VLOOKUP(B29,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>8509221.7116328403</v>
+      </c>
+      <c r="E29" s="4">
         <v>7520013.6941604447</v>
-      </c>
-      <c r="E29" s="4">
-        <v>6757662.8877063803</v>
       </c>
       <c r="F29" s="4">
         <f t="shared" si="8"/>
-        <v>762350.80645406432</v>
+        <v>989208.01747239567</v>
       </c>
       <c r="G29" s="5">
         <f t="shared" si="1"/>
-        <v>0.29215622925521451</v>
+        <v>0.33058744708107868</v>
       </c>
       <c r="H29" s="4">
         <f t="shared" si="4"/>
-        <v>22560041.082481332</v>
+        <v>22691257.897687573</v>
       </c>
       <c r="I29" s="5">
         <f t="shared" si="2"/>
-        <v>0.87646868776564346</v>
+        <v>0.88156652554954307</v>
       </c>
       <c r="J29" s="4">
         <f t="shared" si="5"/>
-        <v>940001.71177005558</v>
+        <v>945469.07907031558</v>
       </c>
       <c r="K29" s="4">
         <f t="shared" si="3"/>
-        <v>1138730.3941149721</v>
+        <v>1148698.5525578107</v>
       </c>
       <c r="L29" s="63" cm="1">
         <f t="array" ref="L29">+_xlfn.IFS(I29&gt;114%,H29*0.02,I29&gt;109%,H29*0.015,I29&gt;104%,H29*0.0125,I29&gt;99%,H29*0.01,I29&lt;99%,H29*0)</f>
@@ -5024,34 +5030,34 @@
       </c>
       <c r="D30" s="4">
         <f>IFERROR(+VLOOKUP(B30,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>7023786.2862272449</v>
+      </c>
+      <c r="E30" s="4">
         <v>6348650.0493735028</v>
-      </c>
-      <c r="E30" s="4">
-        <v>5871001.8178605409</v>
       </c>
       <c r="F30" s="4">
         <f t="shared" si="8"/>
-        <v>477648.23151296191</v>
+        <v>675136.23685374204</v>
       </c>
       <c r="G30" s="5">
         <f t="shared" si="1"/>
-        <v>0.16605068894315708</v>
+        <v>0.18370906298932413</v>
       </c>
       <c r="H30" s="4">
         <f t="shared" si="4"/>
-        <v>19045950.148120508</v>
+        <v>18730096.763272654</v>
       </c>
       <c r="I30" s="5">
         <f t="shared" si="2"/>
-        <v>0.49815206682947122</v>
+        <v>0.48989083463819771</v>
       </c>
       <c r="J30" s="4">
         <f t="shared" si="5"/>
-        <v>793581.25617168786</v>
+        <v>780420.69846969389</v>
       </c>
       <c r="K30" s="4">
         <f t="shared" si="3"/>
-        <v>1992784.6914220105</v>
+        <v>2080627.9217265618</v>
       </c>
       <c r="L30" s="63" cm="1">
         <f t="array" ref="L30">+_xlfn.IFS(I30&gt;114%,H30*0.02,I30&gt;109%,H30*0.015,I30&gt;104%,H30*0.0125,I30&gt;99%,H30*0.01,I30&lt;99%,H30*0)</f>
@@ -5069,34 +5075,34 @@
       </c>
       <c r="D31" s="4">
         <f>IFERROR(+VLOOKUP(B31,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>8331163.463863492</v>
+      </c>
+      <c r="E31" s="4">
         <v>7212918.424210974</v>
-      </c>
-      <c r="E31" s="4">
-        <v>6235749.7584266458</v>
       </c>
       <c r="F31" s="4">
         <f t="shared" si="8"/>
-        <v>977168.66578432824</v>
+        <v>1118245.039652518</v>
       </c>
       <c r="G31" s="5">
         <f t="shared" si="1"/>
-        <v>0.28380277291039724</v>
+        <v>0.32780175146274348</v>
       </c>
       <c r="H31" s="4">
         <f t="shared" si="4"/>
-        <v>21638755.272632923</v>
+        <v>22216435.903635979</v>
       </c>
       <c r="I31" s="5">
         <f t="shared" si="2"/>
-        <v>0.85140831873119183</v>
+        <v>0.87413800390064933</v>
       </c>
       <c r="J31" s="4">
         <f t="shared" si="5"/>
-        <v>901614.80302637175</v>
+        <v>925684.82931816578</v>
       </c>
       <c r="K31" s="4">
         <f t="shared" si="3"/>
-        <v>1137645.7234868142</v>
+        <v>1138939.1024091006</v>
       </c>
       <c r="L31" s="63" cm="1">
         <f t="array" ref="L31">+_xlfn.IFS(I31&gt;114%,H31*0.02,I31&gt;109%,H31*0.015,I31&gt;104%,H31*0.0125,I31&gt;99%,H31*0.01,I31&lt;99%,H31*0)</f>
@@ -5114,34 +5120,34 @@
       </c>
       <c r="D32" s="4">
         <f>IFERROR(+VLOOKUP(B32,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>5611548.663038048</v>
+      </c>
+      <c r="E32" s="4">
         <v>4813267.3862359719</v>
-      </c>
-      <c r="E32" s="4">
-        <v>4132620.3846785584</v>
       </c>
       <c r="F32" s="4">
         <f t="shared" si="8"/>
-        <v>680647.00155741349</v>
+        <v>798281.27680207603</v>
       </c>
       <c r="G32" s="5">
         <f t="shared" si="1"/>
-        <v>0.19100267405698301</v>
+        <v>0.22268050250150984</v>
       </c>
       <c r="H32" s="4">
         <f t="shared" si="4"/>
-        <v>14439802.158707917</v>
+        <v>14964129.768101461</v>
       </c>
       <c r="I32" s="5">
         <f t="shared" si="2"/>
-        <v>0.57300802217094904</v>
+        <v>0.5938146733373596</v>
       </c>
       <c r="J32" s="4">
         <f t="shared" si="5"/>
-        <v>601658.42327949649</v>
+        <v>623505.40700422751</v>
       </c>
       <c r="K32" s="4">
         <f t="shared" si="3"/>
-        <v>1274170.7883602518</v>
+        <v>1305896.7557974635</v>
       </c>
       <c r="L32" s="63" cm="1">
         <f t="array" ref="L32">+_xlfn.IFS(I32&gt;114%,H32*0.02,I32&gt;109%,H32*0.015,I32&gt;104%,H32*0.0125,I32&gt;99%,H32*0.01,I32&lt;99%,H32*0)</f>
@@ -5159,34 +5165,34 @@
       </c>
       <c r="D33" s="4">
         <f>IFERROR(+VLOOKUP(B33,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>5482149.478754703</v>
+      </c>
+      <c r="E33" s="4">
         <v>5035112.3818729157</v>
-      </c>
-      <c r="E33" s="4">
-        <v>3832290.7361907284</v>
       </c>
       <c r="F33" s="4">
         <f t="shared" si="8"/>
-        <v>1202821.6456821873</v>
+        <v>447037.09688178729</v>
       </c>
       <c r="G33" s="5">
         <f t="shared" si="1"/>
-        <v>0.19002754609047962</v>
+        <v>0.20689893963428357</v>
       </c>
       <c r="H33" s="4">
         <f t="shared" si="4"/>
-        <v>15105337.145618748</v>
+        <v>14619065.276679207</v>
       </c>
       <c r="I33" s="5">
         <f t="shared" si="2"/>
-        <v>0.5700826382714389</v>
+        <v>0.55173050569142279</v>
       </c>
       <c r="J33" s="4">
         <f t="shared" si="5"/>
-        <v>629389.04773411446</v>
+        <v>609127.71986163361</v>
       </c>
       <c r="K33" s="4">
         <f t="shared" si="3"/>
-        <v>1341352.3511329428</v>
+        <v>1400973.3680830197</v>
       </c>
       <c r="L33" s="63" cm="1">
         <f t="array" ref="L33">+_xlfn.IFS(I33&gt;114%,H33*0.02,I33&gt;109%,H33*0.015,I33&gt;104%,H33*0.0125,I33&gt;99%,H33*0.01,I33&lt;99%,H33*0)</f>
@@ -5203,34 +5209,34 @@
       </c>
       <c r="D34" s="4">
         <f>IFERROR(+VLOOKUP(B34,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>4657516.3901073569</v>
+      </c>
+      <c r="E34" s="4">
         <v>3805787.6012926684</v>
-      </c>
-      <c r="E34" s="4">
-        <v>3372720.3592291768</v>
       </c>
       <c r="F34" s="4">
         <f t="shared" si="8"/>
-        <v>433067.24206349161</v>
+        <v>851728.78881468857</v>
       </c>
       <c r="G34" s="5">
         <f t="shared" si="1"/>
-        <v>0.18122798101393658</v>
+        <v>0.22178649476701701</v>
       </c>
       <c r="H34" s="4">
         <f t="shared" si="4"/>
-        <v>11417362.803878006</v>
+        <v>12420043.706952952</v>
       </c>
       <c r="I34" s="5">
         <f t="shared" si="2"/>
-        <v>0.54368394304180978</v>
+        <v>0.59143065271204531</v>
       </c>
       <c r="J34" s="4">
         <f t="shared" si="5"/>
-        <v>475723.45016158355</v>
+        <v>517501.82112303964</v>
       </c>
       <c r="K34" s="4">
         <f t="shared" si="3"/>
-        <v>1074638.2749192081</v>
+        <v>1089498.9073261763</v>
       </c>
       <c r="L34" s="63" cm="1">
         <f t="array" ref="L34">+_xlfn.IFS(I34&gt;114%,H34*0.02,I34&gt;109%,H34*0.015,I34&gt;104%,H34*0.0125,I34&gt;99%,H34*0.01,I34&lt;99%,H34*0)</f>
@@ -5247,34 +5253,34 @@
       </c>
       <c r="D35" s="4">
         <f>IFERROR(+VLOOKUP(B35,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>3564392.4785372978</v>
+      </c>
+      <c r="E35" s="4">
         <v>3442297.9978710278</v>
-      </c>
-      <c r="E35" s="4">
-        <v>2627029.9340391951</v>
       </c>
       <c r="F35" s="4">
         <f t="shared" si="8"/>
-        <v>815268.06383183273</v>
+        <v>122094.48066627001</v>
       </c>
       <c r="G35" s="5">
         <f t="shared" si="1"/>
-        <v>0.13960053847689724</v>
+        <v>0.14455201428073816</v>
       </c>
       <c r="H35" s="4">
         <f t="shared" si="4"/>
-        <v>10326893.993613083</v>
+        <v>9505046.6094327942</v>
       </c>
       <c r="I35" s="5">
         <f t="shared" si="2"/>
-        <v>0.41880161543069172</v>
+        <v>0.38547203808196845</v>
       </c>
       <c r="J35" s="4">
         <f t="shared" si="5"/>
-        <v>430287.24973387847</v>
+        <v>396043.60872636642</v>
       </c>
       <c r="K35" s="4">
         <f t="shared" si="3"/>
-        <v>1325993.8751330609</v>
+        <v>1406253.83476418</v>
       </c>
       <c r="L35" s="63" cm="1">
         <f t="array" ref="L35">+_xlfn.IFS(I35&gt;114%,H35*0.02,I35&gt;109%,H35*0.015,I35&gt;104%,H35*0.0125,I35&gt;99%,H35*0.01,I35&lt;99%,H35*0)</f>
@@ -5291,34 +5297,34 @@
       </c>
       <c r="D36" s="4">
         <f>IFERROR(+VLOOKUP(B36,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>5567175.7313747797</v>
+      </c>
+      <c r="E36" s="4">
         <v>4684076.524209898</v>
-      </c>
-      <c r="E36" s="4">
-        <v>4306128.2350271344</v>
       </c>
       <c r="F36" s="4">
         <f t="shared" si="8"/>
-        <v>377948.28918276355</v>
+        <v>883099.20716488175</v>
       </c>
       <c r="G36" s="5">
         <f t="shared" si="1"/>
-        <v>0.18561824942381208</v>
+        <v>0.2206132645680515</v>
       </c>
       <c r="H36" s="4">
         <f t="shared" si="4"/>
-        <v>14052229.572629694</v>
+        <v>14845801.950332746</v>
       </c>
       <c r="I36" s="5">
         <f t="shared" si="2"/>
-        <v>0.55685474827143622</v>
+        <v>0.58830203884813737</v>
       </c>
       <c r="J36" s="4">
         <f t="shared" si="5"/>
-        <v>585509.56552623725</v>
+        <v>618575.08126386441</v>
       </c>
       <c r="K36" s="4">
         <f t="shared" si="3"/>
-        <v>1284432.7172368814</v>
+        <v>1311188.2845750148</v>
       </c>
       <c r="L36" s="63" cm="1">
         <f t="array" ref="L36">+_xlfn.IFS(I36&gt;114%,H36*0.02,I36&gt;109%,H36*0.015,I36&gt;104%,H36*0.0125,I36&gt;99%,H36*0.01,I36&lt;99%,H36*0)</f>
@@ -5335,34 +5341,34 @@
       </c>
       <c r="D37" s="4">
         <f>IFERROR(+VLOOKUP(B37,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>28457978.498885799</v>
+      </c>
+      <c r="E37" s="4">
         <v>28341762.515582383</v>
-      </c>
-      <c r="E37" s="4">
-        <v>26700664.115582384</v>
       </c>
       <c r="F37" s="4">
         <f t="shared" si="8"/>
-        <v>1641098.3999999985</v>
+        <v>116215.98330341652</v>
       </c>
       <c r="G37" s="5">
         <f t="shared" si="1"/>
-        <v>0.2322871568974495</v>
+        <v>0.23323965518801099</v>
       </c>
       <c r="H37" s="4">
         <f t="shared" si="4"/>
-        <v>85025287.546747148</v>
+        <v>75887942.663695469</v>
       </c>
       <c r="I37" s="5">
         <f t="shared" si="2"/>
-        <v>0.69686147069234849</v>
+        <v>0.62197241383469604</v>
       </c>
       <c r="J37" s="4">
         <f t="shared" si="5"/>
-        <v>3542720.3144477978</v>
+        <v>3161997.6109873112</v>
       </c>
       <c r="K37" s="4">
         <f t="shared" si="3"/>
-        <v>5854374.2177761011</v>
+        <v>6236918.1000742801</v>
       </c>
       <c r="L37" s="63" cm="1">
         <f t="array" ref="L37">+_xlfn.IFS(I37&gt;114%,H37*0.0125,I37&gt;109%,H37*0.01,I37&gt;104%,H37*0.0075,I37&gt;99%,H37*0.005,I37&lt;99%,H37*0)</f>
@@ -5379,34 +5385,34 @@
       </c>
       <c r="D38" s="4">
         <f>IFERROR(+VLOOKUP(B38,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>2767832.4172995184</v>
+      </c>
+      <c r="E38" s="4">
         <v>2478634.4092995184</v>
-      </c>
-      <c r="E38" s="4">
-        <v>1256116.5299</v>
       </c>
       <c r="F38" s="4">
         <f t="shared" ref="F38" si="10">+D38-E38</f>
-        <v>1222517.8793995185</v>
+        <v>289198.00799999991</v>
       </c>
       <c r="G38" s="5">
         <f t="shared" si="1"/>
-        <v>6.9429535274496315E-2</v>
+        <v>7.7530319812311441E-2</v>
       </c>
       <c r="H38" s="4">
         <f t="shared" si="4"/>
-        <v>7435903.2278985549</v>
+        <v>7380886.446132049</v>
       </c>
       <c r="I38" s="5">
         <f t="shared" si="2"/>
-        <v>0.20828860582348893</v>
+        <v>0.20674751949949716</v>
       </c>
       <c r="J38" s="4">
         <f t="shared" si="5"/>
-        <v>309829.30116243981</v>
+        <v>307536.93525550206</v>
       </c>
       <c r="K38" s="4">
         <f t="shared" si="3"/>
-        <v>2076335.3494187801</v>
+        <v>2195477.8388466989</v>
       </c>
       <c r="L38" s="63" cm="1">
         <f t="array" ref="L38">+_xlfn.IFS(I38&gt;109%,H38*0.015,I38&gt;104%,H38*0.0125,I38&gt;99%,H38*0.01,I38&lt;99%,H38*0)</f>
@@ -5423,34 +5429,34 @@
       </c>
       <c r="D39" s="4">
         <f>IFERROR(+VLOOKUP(B39,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>9930506.0322296303</v>
+      </c>
+      <c r="E39" s="4">
         <v>8818400.8023845814</v>
-      </c>
-      <c r="E39" s="4">
-        <v>8333389.4092635857</v>
       </c>
       <c r="F39" s="4">
         <f t="shared" si="8"/>
-        <v>485011.39312099572</v>
+        <v>1112105.2298450489</v>
       </c>
       <c r="G39" s="5">
         <f t="shared" si="1"/>
-        <v>0.2425207520915432</v>
+        <v>0.27310550354375979</v>
       </c>
       <c r="H39" s="4">
         <f t="shared" si="4"/>
-        <v>26455202.407153744</v>
+        <v>26481349.419279017</v>
       </c>
       <c r="I39" s="5">
         <f t="shared" si="2"/>
-        <v>0.72756225627462967</v>
+        <v>0.72828134278335954</v>
       </c>
       <c r="J39" s="4">
         <f t="shared" si="5"/>
-        <v>1102300.1002980727</v>
+        <v>1103389.5591366256</v>
       </c>
       <c r="K39" s="4">
         <f t="shared" si="3"/>
-        <v>1721439.1835384637</v>
+        <v>1762061.4471180246</v>
       </c>
       <c r="L39" s="63" cm="1">
         <f t="array" ref="L39">+_xlfn.IFS(I39&gt;114%,H39*0.02,I39&gt;109%,H39*0.015,I39&gt;104%,H39*0.0125,I39&gt;99%,H39*0.01,I39&lt;99%,H39*0)</f>
@@ -5465,34 +5471,34 @@
       </c>
       <c r="D40" s="67">
         <f>+SUM(D27:D39)</f>
+        <v>125149967.21822201</v>
+      </c>
+      <c r="E40" s="65">
         <v>115222111.25640535</v>
-      </c>
-      <c r="E40" s="65">
-        <v>98689279.798814774</v>
       </c>
       <c r="F40" s="67">
         <f t="shared" si="8"/>
-        <v>16532831.45759058</v>
+        <v>9927855.9618166536</v>
       </c>
       <c r="G40" s="66">
         <f t="shared" si="1"/>
-        <v>0.22635668132496897</v>
+        <v>0.24586019938834067</v>
       </c>
       <c r="H40" s="64">
         <f t="shared" si="4"/>
-        <v>345666333.76921606</v>
+        <v>333733245.91525865</v>
       </c>
       <c r="I40" s="66">
         <f t="shared" si="2"/>
-        <v>0.67907004397490689</v>
+        <v>0.65562719836890837</v>
       </c>
       <c r="J40" s="64">
         <f t="shared" si="5"/>
-        <v>14402763.907050669</v>
+        <v>13905551.913135778</v>
       </c>
       <c r="K40" s="67">
         <f t="shared" si="3"/>
-        <v>24612929.474670023</v>
+        <v>25591934.375526913</v>
       </c>
       <c r="L40" s="68"/>
     </row>
@@ -5506,34 +5512,34 @@
       </c>
       <c r="D41" s="81">
         <f>+D40+D26+D10+D16</f>
+        <v>449316617.9851948</v>
+      </c>
+      <c r="E41" s="82">
         <v>397625858.39552885</v>
-      </c>
-      <c r="E41" s="82">
-        <v>347037445.52567512</v>
       </c>
       <c r="F41" s="81">
         <f>+D41-E41</f>
-        <v>50588412.869853735</v>
+        <v>51690759.589665949</v>
       </c>
       <c r="G41" s="83">
         <f t="shared" si="1"/>
-        <v>0.28818330631602479</v>
+        <v>0.32564669983033401</v>
       </c>
       <c r="H41" s="81">
         <f t="shared" si="4"/>
-        <v>1192877575.1865866</v>
+        <v>1198177647.9605193</v>
       </c>
       <c r="I41" s="83">
         <f t="shared" si="2"/>
-        <v>0.86454991894807443</v>
+        <v>0.86839119954755728</v>
       </c>
       <c r="J41" s="81">
         <f t="shared" si="5"/>
-        <v>49703232.299441107</v>
+        <v>49924068.665021643</v>
       </c>
       <c r="K41" s="81">
         <f t="shared" si="3"/>
-        <v>61383830.543600455</v>
+        <v>62030035.273862749</v>
       </c>
       <c r="L41" s="84"/>
     </row>
@@ -5581,34 +5587,34 @@
       </c>
       <c r="D43" s="4">
         <f>IFERROR(+VLOOKUP(B43,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>8104352.0621971888</v>
+        <v>6840893.5633781236</v>
       </c>
       <c r="E43" s="4">
         <v>8104352.0621971888</v>
       </c>
       <c r="F43" s="4">
         <f t="shared" ref="F43" si="11">+D43-E43</f>
-        <v>0</v>
+        <v>-1263458.4988190653</v>
       </c>
       <c r="G43" s="5">
         <f>+D43/C43</f>
-        <v>0.20260880155492972</v>
+        <v>0.17102233908445308</v>
       </c>
       <c r="H43" s="4">
         <f t="shared" ref="H43" si="12">+D43/$N$3*$N$4</f>
-        <v>24313056.186591566</v>
+        <v>18242382.835674997</v>
       </c>
       <c r="I43" s="5">
         <f>+H43/C43</f>
-        <v>0.6078264046647891</v>
+        <v>0.45605957089187493</v>
       </c>
       <c r="J43" s="4">
         <f t="shared" ref="J43" si="13">+D43/$N$3</f>
-        <v>1013044.0077746486</v>
+        <v>760099.28481979156</v>
       </c>
       <c r="K43" s="4">
         <f>+(C43-D43)/$N$2</f>
-        <v>1993477.9961126756</v>
+        <v>2210607.0957747917</v>
       </c>
       <c r="L43" s="4" cm="1">
         <f t="array" ref="L43">+_xlfn.IFS(I43&gt;114%,H43*0.02,I43&gt;109%,H43*0.015,I43&gt;104%,H43*0.0125,I43&gt;99%,H43*0.01,I43&lt;99%,H43*0)</f>
@@ -5624,38 +5630,38 @@
       </c>
       <c r="D44" s="4">
         <f>IFERROR(+VLOOKUP(B44,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>14041795.823822808</v>
+        <v>14127537.863605659</v>
       </c>
       <c r="E44" s="4">
         <v>14041795.823822808</v>
       </c>
       <c r="F44" s="4">
         <f t="shared" ref="F44" si="14">+D44-E44</f>
-        <v>0</v>
+        <v>85742.039782851934</v>
       </c>
       <c r="G44" s="5">
         <f>+D44/C44</f>
-        <v>0.46805986079409356</v>
+        <v>0.47091792878685529</v>
       </c>
       <c r="H44" s="4">
         <f t="shared" ref="H44" si="15">+D44/$N$3*$N$4</f>
-        <v>42125387.471468419</v>
+        <v>37673434.302948423</v>
       </c>
       <c r="I44" s="5">
         <f>+H44/C44</f>
-        <v>1.4041795823822807</v>
+        <v>1.2557811434316142</v>
       </c>
       <c r="J44" s="4">
         <f t="shared" ref="J44" si="16">+D44/$N$3</f>
-        <v>1755224.4779778509</v>
+        <v>1569726.4292895177</v>
       </c>
       <c r="K44" s="4">
         <f>+(C44-D44)/$N$2</f>
-        <v>997387.76101107453</v>
+        <v>1058164.1424262894</v>
       </c>
       <c r="L44" s="4" cm="1">
         <f t="array" ref="L44">+_xlfn.IFS(I44&gt;114%,H44*0.02,I44&gt;109%,H44*0.015,I44&gt;104%,H44*0.0125,I44&gt;99%,H44*0.01,I44&lt;99%,H44*0)</f>
-        <v>842507.74942936841</v>
+        <v>753468.68605896842</v>
       </c>
     </row>
   </sheetData>
@@ -5793,26 +5799,26 @@
       </c>
       <c r="D2" s="22">
         <f>H2/G2</f>
-        <v>0.59722222222222221</v>
+        <v>0.61643835616438358</v>
       </c>
       <c r="E2" s="13">
         <v>33</v>
       </c>
       <c r="F2" s="12">
         <f>+H2-E2</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G2" s="13">
         <f>VLOOKUP(B2,'Base Cobertura'!$A:$C,3,FALSE)</f>
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H2" s="13">
         <f>VLOOKUP(B2,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I2" s="17">
         <f>(+G2*$M$2)-H2</f>
-        <v>18.199999999999996</v>
+        <v>17.049999999999997</v>
       </c>
       <c r="J2" t="s">
         <v>55</v>
@@ -5896,14 +5902,14 @@
         <v>145 - ALMACEN</v>
       </c>
       <c r="S3" s="12">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="T3" s="12">
         <v>214</v>
       </c>
       <c r="U3" s="41">
         <f>+S3/T3</f>
-        <v>0.16822429906542055</v>
+        <v>0.1822429906542056</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
@@ -5917,14 +5923,14 @@
       </c>
       <c r="D4" s="22">
         <f t="shared" si="0"/>
-        <v>0.65198237885462551</v>
+        <v>0.69162995594713661</v>
       </c>
       <c r="E4" s="13">
         <v>126</v>
       </c>
       <c r="F4" s="12">
         <f t="shared" si="1"/>
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="G4" s="13">
         <f>VLOOKUP(B4,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -5932,11 +5938,11 @@
       </c>
       <c r="H4" s="13">
         <f>VLOOKUP(B4,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="I4" s="17">
         <f t="shared" si="2"/>
-        <v>44.949999999999989</v>
+        <v>35.949999999999989</v>
       </c>
       <c r="J4" t="s">
         <v>57</v>
@@ -5954,14 +5960,14 @@
         <v>145 - Articulos Sin Asociar Agrupacion</v>
       </c>
       <c r="S4" s="13">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="T4" s="13">
         <v>214</v>
       </c>
       <c r="U4" s="5">
         <f t="shared" ref="U4:U11" si="3">+S4/T4</f>
-        <v>7.9439252336448593E-2</v>
+        <v>0.10280373831775701</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
@@ -5975,14 +5981,14 @@
       </c>
       <c r="D5" s="22">
         <f t="shared" si="0"/>
-        <v>0.53846153846153844</v>
+        <v>0.58461538461538465</v>
       </c>
       <c r="E5" s="13">
         <v>21</v>
       </c>
       <c r="F5" s="12">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G5" s="13">
         <f>VLOOKUP(B5,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -5990,11 +5996,11 @@
       </c>
       <c r="H5" s="13">
         <f>VLOOKUP(B5,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I5" s="17">
         <f t="shared" si="2"/>
-        <v>20.25</v>
+        <v>17.25</v>
       </c>
       <c r="K5" t="s">
         <v>64</v>
@@ -6009,14 +6015,14 @@
         <v>145 - BEBIDAS</v>
       </c>
       <c r="S5" s="13">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="T5" s="13">
         <v>214</v>
       </c>
       <c r="U5" s="5">
         <f t="shared" si="3"/>
-        <v>0.21962616822429906</v>
+        <v>0.23364485981308411</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
@@ -6030,14 +6036,14 @@
       </c>
       <c r="D6" s="22">
         <f t="shared" si="0"/>
-        <v>0.64251207729468596</v>
+        <v>0.68599033816425126</v>
       </c>
       <c r="E6" s="13">
         <v>100</v>
       </c>
       <c r="F6" s="12">
         <f t="shared" si="1"/>
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="G6" s="13">
         <f>VLOOKUP(B6,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6045,11 +6051,11 @@
       </c>
       <c r="H6" s="13">
         <f>VLOOKUP(B6,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="I6" s="17">
         <f t="shared" si="2"/>
-        <v>42.949999999999989</v>
+        <v>33.949999999999989</v>
       </c>
       <c r="J6" t="s">
         <v>58</v>
@@ -6067,14 +6073,14 @@
         <v>145 - CHOCOLATE</v>
       </c>
       <c r="S6" s="13">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="T6" s="13">
         <v>214</v>
       </c>
       <c r="U6" s="5">
         <f t="shared" si="3"/>
-        <v>8.4112149532710276E-2</v>
+        <v>0.11214953271028037</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
@@ -6088,14 +6094,14 @@
       </c>
       <c r="D7" s="22">
         <f t="shared" si="0"/>
-        <v>0.46969696969696972</v>
+        <v>0.48989898989898989</v>
       </c>
       <c r="E7" s="13">
         <v>81</v>
       </c>
       <c r="F7" s="12">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G7" s="13">
         <f>VLOOKUP(B7,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6103,11 +6109,11 @@
       </c>
       <c r="H7" s="13">
         <f>VLOOKUP(B7,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="I7" s="17">
         <f t="shared" si="2"/>
-        <v>75.299999999999983</v>
+        <v>71.299999999999983</v>
       </c>
       <c r="J7" t="s">
         <v>58</v>
@@ -6125,14 +6131,14 @@
         <v>145 - GALLETITAS</v>
       </c>
       <c r="S7" s="13">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="T7" s="13">
         <v>214</v>
       </c>
       <c r="U7" s="5">
         <f t="shared" si="3"/>
-        <v>0.24299065420560748</v>
+        <v>0.27570093457943923</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
@@ -6146,14 +6152,14 @@
       </c>
       <c r="D8" s="22">
         <f t="shared" si="0"/>
-        <v>0.58411214953271029</v>
+        <v>0.64485981308411211</v>
       </c>
       <c r="E8" s="13">
         <v>89</v>
       </c>
       <c r="F8" s="12">
         <f t="shared" si="1"/>
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="G8" s="13">
         <f>VLOOKUP(B8,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6161,11 +6167,11 @@
       </c>
       <c r="H8" s="13">
         <f>VLOOKUP(B8,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="I8" s="17">
         <f t="shared" si="2"/>
-        <v>56.900000000000006</v>
+        <v>43.900000000000006</v>
       </c>
       <c r="J8" t="s">
         <v>55</v>
@@ -6184,14 +6190,14 @@
         <v>145 - GOLOSINAS</v>
       </c>
       <c r="S8" s="13">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="T8" s="13">
         <v>214</v>
       </c>
       <c r="U8" s="5">
         <f t="shared" si="3"/>
-        <v>0.22429906542056074</v>
+        <v>0.23831775700934579</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
@@ -6205,26 +6211,26 @@
       </c>
       <c r="D9" s="22">
         <f>H9/G9</f>
-        <v>0.60624999999999996</v>
+        <v>0.61728395061728392</v>
       </c>
       <c r="E9" s="13">
         <v>92</v>
       </c>
       <c r="F9" s="12">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G9" s="13">
         <f>VLOOKUP(B9,'Base Cobertura'!$A:$C,3,FALSE)</f>
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H9" s="13">
         <f>VLOOKUP(B9,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I9" s="17">
         <f t="shared" si="2"/>
-        <v>39</v>
+        <v>37.699999999999989</v>
       </c>
       <c r="J9" t="s">
         <v>55</v>
@@ -6242,14 +6248,14 @@
         <v>145 - MASCOTAS</v>
       </c>
       <c r="S9" s="13">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T9" s="13">
         <v>214</v>
       </c>
       <c r="U9" s="5">
         <f t="shared" si="3"/>
-        <v>4.6728971962616821E-2</v>
+        <v>5.6074766355140186E-2</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
@@ -6263,14 +6269,14 @@
       </c>
       <c r="D10" s="22">
         <f t="shared" si="0"/>
-        <v>0.46153846153846156</v>
+        <v>0.49230769230769234</v>
       </c>
       <c r="E10" s="13">
         <v>64</v>
       </c>
       <c r="F10" s="12">
         <f t="shared" si="1"/>
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G10" s="13">
         <f>VLOOKUP(B10,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6278,11 +6284,11 @@
       </c>
       <c r="H10" s="13">
         <f>VLOOKUP(B10,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="I10" s="17">
         <f t="shared" si="2"/>
-        <v>75.75</v>
+        <v>69.75</v>
       </c>
       <c r="J10" t="s">
         <v>58</v>
@@ -6300,14 +6306,14 @@
         <v>145 - NO PERECEDEROS</v>
       </c>
       <c r="S10" s="13">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="T10" s="13">
         <v>214</v>
       </c>
       <c r="U10" s="5">
         <f t="shared" si="3"/>
-        <v>4.2056074766355138E-2</v>
+        <v>6.5420560747663545E-2</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
@@ -6321,14 +6327,14 @@
       </c>
       <c r="D11" s="32">
         <f t="shared" si="0"/>
-        <v>0.23762376237623761</v>
+        <v>0.27722772277227725</v>
       </c>
       <c r="E11" s="31">
         <v>19</v>
       </c>
       <c r="F11" s="33">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G11" s="13">
         <f>VLOOKUP(B11,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6336,11 +6342,11 @@
       </c>
       <c r="H11" s="13">
         <f>VLOOKUP(B11,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I11" s="34">
         <f t="shared" si="2"/>
-        <v>61.849999999999994</v>
+        <v>57.849999999999994</v>
       </c>
       <c r="J11" t="s">
         <v>59</v>
@@ -6355,14 +6361,14 @@
         <v>145 - PILAS</v>
       </c>
       <c r="S11" s="13">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="T11" s="13">
         <v>214</v>
       </c>
       <c r="U11" s="5">
         <f t="shared" si="3"/>
-        <v>6.5420560747663545E-2</v>
+        <v>0.10747663551401869</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
@@ -6376,14 +6382,14 @@
       </c>
       <c r="D12" s="32">
         <f t="shared" si="0"/>
-        <v>0.2857142857142857</v>
+        <v>0.32380952380952382</v>
       </c>
       <c r="E12" s="31">
         <v>24</v>
       </c>
       <c r="F12" s="33">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G12" s="13">
         <f>VLOOKUP(B12,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6391,11 +6397,11 @@
       </c>
       <c r="H12" s="13">
         <f>VLOOKUP(B12,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I12" s="34">
         <f t="shared" si="2"/>
-        <v>59.25</v>
+        <v>55.25</v>
       </c>
       <c r="J12" t="s">
         <v>59</v>
@@ -6412,14 +6418,14 @@
       </c>
       <c r="D13" s="22">
         <f t="shared" si="0"/>
-        <v>0.58461538461538465</v>
+        <v>0.62692307692307692</v>
       </c>
       <c r="E13" s="13">
         <v>144</v>
       </c>
       <c r="F13" s="12">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="G13" s="13">
         <f>VLOOKUP(B13,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6427,11 +6433,11 @@
       </c>
       <c r="H13" s="13">
         <f>VLOOKUP(B13,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="I13" s="17">
         <f t="shared" si="2"/>
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="J13" t="s">
         <v>57</v>
@@ -6451,14 +6457,14 @@
       </c>
       <c r="D14" s="22">
         <f t="shared" si="0"/>
-        <v>0.51098901098901095</v>
+        <v>0.52197802197802201</v>
       </c>
       <c r="E14" s="13">
         <v>85</v>
       </c>
       <c r="F14" s="12">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G14" s="13">
         <f>VLOOKUP(B14,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6466,11 +6472,11 @@
       </c>
       <c r="H14" s="13">
         <f>VLOOKUP(B14,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I14" s="17">
         <f t="shared" si="2"/>
-        <v>61.699999999999989</v>
+        <v>59.699999999999989</v>
       </c>
       <c r="J14" t="s">
         <v>55</v>
@@ -6486,15 +6492,15 @@
       <c r="E15" s="14"/>
       <c r="F15" s="16">
         <f>+SUM(F2:F14)</f>
-        <v>268</v>
+        <v>338</v>
       </c>
       <c r="G15" s="8">
         <f>+SUM(G2:G14)</f>
-        <v>2225</v>
+        <v>2228</v>
       </c>
       <c r="H15" s="8">
         <f>+SUM(H2:H14)</f>
-        <v>1147</v>
+        <v>1217</v>
       </c>
       <c r="I15" s="8"/>
     </row>
@@ -6511,14 +6517,14 @@
       </c>
       <c r="D16" s="22">
         <f t="shared" si="0"/>
-        <v>0.68125000000000002</v>
+        <v>0.70625000000000004</v>
       </c>
       <c r="E16" s="13">
         <v>90</v>
       </c>
       <c r="F16" s="12">
         <f t="shared" si="1"/>
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G16" s="13">
         <f>VLOOKUP(B16,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6526,11 +6532,11 @@
       </c>
       <c r="H16" s="13">
         <f>VLOOKUP(B16,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="I16" s="17">
         <f t="shared" si="2"/>
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J16" t="s">
         <v>55</v>
@@ -6550,14 +6556,14 @@
       </c>
       <c r="D17" s="22">
         <f t="shared" si="0"/>
-        <v>0.36138613861386137</v>
+        <v>0.37128712871287128</v>
       </c>
       <c r="E17" s="13">
         <v>92</v>
       </c>
       <c r="F17" s="12">
         <f t="shared" si="1"/>
-        <v>-19</v>
+        <v>-17</v>
       </c>
       <c r="G17" s="13">
         <f>VLOOKUP(B17,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6565,11 +6571,11 @@
       </c>
       <c r="H17" s="13">
         <f>VLOOKUP(B17,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I17" s="17">
         <f t="shared" si="2"/>
-        <v>98.699999999999989</v>
+        <v>96.699999999999989</v>
       </c>
       <c r="J17" t="s">
         <v>55</v>
@@ -6589,14 +6595,14 @@
       </c>
       <c r="D18" s="22">
         <f t="shared" si="0"/>
-        <v>0.68823529411764706</v>
+        <v>0.71764705882352942</v>
       </c>
       <c r="E18" s="13">
         <v>88</v>
       </c>
       <c r="F18" s="12">
         <f t="shared" si="1"/>
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G18" s="13">
         <f>VLOOKUP(B18,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6604,11 +6610,11 @@
       </c>
       <c r="H18" s="13">
         <f>VLOOKUP(B18,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I18" s="17">
         <f t="shared" si="2"/>
-        <v>27.5</v>
+        <v>22.5</v>
       </c>
       <c r="J18" t="s">
         <v>58</v>
@@ -6628,14 +6634,14 @@
       </c>
       <c r="D19" s="22">
         <f t="shared" si="0"/>
-        <v>0.68181818181818177</v>
+        <v>0.69480519480519476</v>
       </c>
       <c r="E19" s="13">
         <v>95</v>
       </c>
       <c r="F19" s="12">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G19" s="13">
         <f>VLOOKUP(B19,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6643,11 +6649,11 @@
       </c>
       <c r="H19" s="13">
         <f>VLOOKUP(B19,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="I19" s="17">
         <f t="shared" si="2"/>
-        <v>25.900000000000006</v>
+        <v>23.900000000000006</v>
       </c>
       <c r="J19" t="s">
         <v>58</v>
@@ -6667,14 +6673,14 @@
       </c>
       <c r="D20" s="22">
         <f t="shared" si="0"/>
-        <v>0.64971751412429379</v>
+        <v>0.68926553672316382</v>
       </c>
       <c r="E20" s="13">
         <v>83</v>
       </c>
       <c r="F20" s="12">
         <f t="shared" si="1"/>
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="G20" s="13">
         <f>VLOOKUP(B20,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6682,11 +6688,11 @@
       </c>
       <c r="H20" s="13">
         <f>VLOOKUP(B20,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="I20" s="17">
         <f t="shared" si="2"/>
-        <v>35.449999999999989</v>
+        <v>28.449999999999989</v>
       </c>
       <c r="J20" t="s">
         <v>55</v>
@@ -6706,14 +6712,14 @@
       </c>
       <c r="D21" s="22">
         <f t="shared" si="0"/>
-        <v>0.62130177514792895</v>
+        <v>0.65088757396449703</v>
       </c>
       <c r="E21" s="13">
         <v>64</v>
       </c>
       <c r="F21" s="12">
         <f t="shared" si="1"/>
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G21" s="13">
         <f>VLOOKUP(B21,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6721,11 +6727,11 @@
       </c>
       <c r="H21" s="13">
         <f>VLOOKUP(B21,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="I21" s="17">
         <f t="shared" si="2"/>
-        <v>38.650000000000006</v>
+        <v>33.650000000000006</v>
       </c>
       <c r="J21" t="s">
         <v>58</v>
@@ -6784,14 +6790,14 @@
       </c>
       <c r="D23" s="22">
         <f t="shared" si="0"/>
-        <v>0.55797101449275366</v>
+        <v>0.57971014492753625</v>
       </c>
       <c r="E23" s="13">
         <v>70</v>
       </c>
       <c r="F23" s="12">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G23" s="13">
         <f>VLOOKUP(B23,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6799,11 +6805,11 @@
       </c>
       <c r="H23" s="13">
         <f>VLOOKUP(B23,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="I23" s="17">
         <f t="shared" si="2"/>
-        <v>40.299999999999997</v>
+        <v>37.299999999999997</v>
       </c>
       <c r="J23" t="s">
         <v>58</v>
@@ -6823,14 +6829,14 @@
       </c>
       <c r="D24" s="22">
         <f t="shared" si="0"/>
-        <v>0.58823529411764708</v>
+        <v>0.62352941176470589</v>
       </c>
       <c r="E24" s="13">
         <v>79</v>
       </c>
       <c r="F24" s="12">
         <f t="shared" si="1"/>
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G24" s="13">
         <f>VLOOKUP(B24,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6838,11 +6844,11 @@
       </c>
       <c r="H24" s="13">
         <f>VLOOKUP(B24,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="I24" s="17">
         <f t="shared" si="2"/>
-        <v>44.5</v>
+        <v>38.5</v>
       </c>
       <c r="J24" t="s">
         <v>60</v>
@@ -6858,7 +6864,7 @@
       <c r="E25" s="14"/>
       <c r="F25" s="16">
         <f>+SUM(F16:F24)</f>
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="G25" s="8">
         <f>+SUM(G16:G24)</f>
@@ -6866,7 +6872,7 @@
       </c>
       <c r="H25" s="8">
         <f>+SUM(H16:H24)</f>
-        <v>861</v>
+        <v>895</v>
       </c>
       <c r="I25" s="8"/>
     </row>
@@ -6883,14 +6889,14 @@
       </c>
       <c r="D26" s="22">
         <f t="shared" si="0"/>
-        <v>0.45614035087719296</v>
+        <v>0.56140350877192979</v>
       </c>
       <c r="E26" s="13">
         <v>20</v>
       </c>
       <c r="F26" s="12">
         <f>+H26-E26</f>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G26" s="13">
         <f>VLOOKUP(B26,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6898,11 +6904,11 @@
       </c>
       <c r="H26" s="13">
         <f>VLOOKUP(B26,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I26" s="17">
         <f t="shared" si="2"/>
-        <v>22.449999999999996</v>
+        <v>16.449999999999996</v>
       </c>
       <c r="J26" t="s">
         <v>55</v>
@@ -6922,14 +6928,14 @@
       </c>
       <c r="D27" s="22">
         <f t="shared" si="0"/>
-        <v>0.51592356687898089</v>
+        <v>0.57324840764331209</v>
       </c>
       <c r="E27" s="13">
         <v>68</v>
       </c>
       <c r="F27" s="12">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G27" s="13">
         <f>VLOOKUP(B27,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6937,11 +6943,11 @@
       </c>
       <c r="H27" s="13">
         <f>VLOOKUP(B27,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I27" s="17">
         <f t="shared" si="2"/>
-        <v>52.449999999999989</v>
+        <v>43.449999999999989</v>
       </c>
       <c r="J27" t="s">
         <v>58</v>
@@ -6961,14 +6967,14 @@
       </c>
       <c r="D28" s="22">
         <f t="shared" si="0"/>
-        <v>0.5714285714285714</v>
+        <v>0.63354037267080743</v>
       </c>
       <c r="E28" s="13">
         <v>80</v>
       </c>
       <c r="F28" s="12">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G28" s="13">
         <f>VLOOKUP(B28,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6976,11 +6982,11 @@
       </c>
       <c r="H28" s="13">
         <f>VLOOKUP(B28,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="I28" s="17">
         <f t="shared" si="2"/>
-        <v>44.849999999999994</v>
+        <v>34.849999999999994</v>
       </c>
       <c r="J28" t="s">
         <v>58</v>
@@ -7000,14 +7006,14 @@
       </c>
       <c r="D29" s="22">
         <f t="shared" si="0"/>
-        <v>0.30522088353413657</v>
+        <v>0.3253012048192771</v>
       </c>
       <c r="E29" s="13">
         <v>68</v>
       </c>
       <c r="F29" s="12">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G29" s="13">
         <f>VLOOKUP(B29,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7015,11 +7021,11 @@
       </c>
       <c r="H29" s="13">
         <f>VLOOKUP(B29,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="I29" s="17">
         <f t="shared" si="2"/>
-        <v>135.65</v>
+        <v>130.65</v>
       </c>
       <c r="J29" t="s">
         <v>58</v>
@@ -7039,14 +7045,14 @@
       </c>
       <c r="D30" s="22">
         <f t="shared" si="0"/>
-        <v>0.69784172661870503</v>
+        <v>0.74820143884892087</v>
       </c>
       <c r="E30" s="13">
         <v>73</v>
       </c>
       <c r="F30" s="12">
         <f t="shared" si="1"/>
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G30" s="13">
         <f>VLOOKUP(B30,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7054,11 +7060,11 @@
       </c>
       <c r="H30" s="13">
         <f>VLOOKUP(B30,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="I30" s="17">
         <f t="shared" si="2"/>
-        <v>21.149999999999991</v>
+        <v>14.149999999999991</v>
       </c>
       <c r="J30" t="s">
         <v>55</v>
@@ -7078,14 +7084,14 @@
       </c>
       <c r="D31" s="22">
         <f t="shared" si="0"/>
-        <v>0.43093922651933703</v>
+        <v>0.49171270718232046</v>
       </c>
       <c r="E31" s="13">
         <v>40</v>
       </c>
       <c r="F31" s="12">
         <f t="shared" si="1"/>
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="G31" s="13">
         <f>VLOOKUP(B31,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7093,11 +7099,11 @@
       </c>
       <c r="H31" s="13">
         <f>VLOOKUP(B31,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I31" s="17">
         <f t="shared" si="2"/>
-        <v>75.849999999999994</v>
+        <v>64.849999999999994</v>
       </c>
       <c r="J31" t="s">
         <v>58</v>
@@ -7117,14 +7123,14 @@
       </c>
       <c r="D32" s="22">
         <f t="shared" si="0"/>
-        <v>0.52976190476190477</v>
+        <v>0.60119047619047616</v>
       </c>
       <c r="E32" s="13">
         <v>67</v>
       </c>
       <c r="F32" s="12">
         <f t="shared" si="1"/>
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G32" s="13">
         <f>VLOOKUP(B32,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7132,11 +7138,11 @@
       </c>
       <c r="H32" s="13">
         <f>VLOOKUP(B32,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="I32" s="17">
         <f t="shared" si="2"/>
-        <v>53.799999999999983</v>
+        <v>41.799999999999983</v>
       </c>
       <c r="J32" t="s">
         <v>58</v>
@@ -7156,14 +7162,14 @@
       </c>
       <c r="D33" s="22">
         <f t="shared" si="0"/>
-        <v>0.5357142857142857</v>
+        <v>0.55952380952380953</v>
       </c>
       <c r="E33" s="13">
         <v>66</v>
       </c>
       <c r="F33" s="12">
         <f t="shared" si="1"/>
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G33" s="13">
         <f>VLOOKUP(B33,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7171,11 +7177,11 @@
       </c>
       <c r="H33" s="13">
         <f>VLOOKUP(B33,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="I33" s="17">
         <f t="shared" si="2"/>
-        <v>52.799999999999983</v>
+        <v>48.799999999999983</v>
       </c>
       <c r="J33" t="s">
         <v>58</v>
@@ -7195,14 +7201,14 @@
       </c>
       <c r="D34" s="22">
         <f t="shared" si="0"/>
-        <v>0.40845070422535212</v>
+        <v>0.46478873239436619</v>
       </c>
       <c r="E34" s="13">
         <v>82</v>
       </c>
       <c r="F34" s="12">
         <f t="shared" si="1"/>
-        <v>-24</v>
+        <v>-16</v>
       </c>
       <c r="G34" s="13">
         <f>VLOOKUP(B34,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7210,11 +7216,11 @@
       </c>
       <c r="H34" s="13">
         <f>VLOOKUP(B34,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="I34" s="17">
         <f t="shared" si="2"/>
-        <v>62.7</v>
+        <v>54.7</v>
       </c>
       <c r="J34" t="s">
         <v>55</v>
@@ -7234,14 +7240,14 @@
       </c>
       <c r="D35" s="22">
         <f t="shared" si="0"/>
-        <v>0.5056179775280899</v>
+        <v>0.5449438202247191</v>
       </c>
       <c r="E35" s="13">
         <v>81</v>
       </c>
       <c r="F35" s="12">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="G35" s="13">
         <f>VLOOKUP(B35,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7249,11 +7255,11 @@
       </c>
       <c r="H35" s="13">
         <f>VLOOKUP(B35,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="I35" s="17">
         <f t="shared" si="2"/>
-        <v>61.299999999999983</v>
+        <v>54.299999999999983</v>
       </c>
       <c r="J35" t="s">
         <v>58</v>
@@ -7273,14 +7279,14 @@
       </c>
       <c r="D36" s="22">
         <f t="shared" si="0"/>
-        <v>3.5087719298245612E-2</v>
+        <v>4.3859649122807015E-2</v>
       </c>
       <c r="E36" s="13">
         <v>0</v>
       </c>
       <c r="F36" s="12">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G36" s="13">
         <f>VLOOKUP(B36,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7288,11 +7294,11 @@
       </c>
       <c r="H36" s="13">
         <f>VLOOKUP(B36,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I36" s="17">
         <f t="shared" si="2"/>
-        <v>92.899999999999991</v>
+        <v>91.899999999999991</v>
       </c>
       <c r="J36" t="s">
         <v>58</v>
@@ -7309,14 +7315,14 @@
       </c>
       <c r="D37" s="22">
         <f t="shared" si="0"/>
-        <v>7.6923076923076927E-2</v>
+        <v>0.14423076923076922</v>
       </c>
       <c r="E37" s="13">
         <v>17</v>
       </c>
       <c r="F37" s="12">
         <f t="shared" si="1"/>
-        <v>-9</v>
+        <v>-2</v>
       </c>
       <c r="G37" s="13">
         <f>VLOOKUP(B37,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7324,11 +7330,11 @@
       </c>
       <c r="H37" s="13">
         <f>VLOOKUP(B37,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I37" s="17">
         <f t="shared" si="2"/>
-        <v>80.399999999999991</v>
+        <v>73.399999999999991</v>
       </c>
       <c r="J37" t="s">
         <v>59</v>
@@ -7345,14 +7351,14 @@
       </c>
       <c r="D38" s="22">
         <f t="shared" si="0"/>
-        <v>0.59055118110236215</v>
+        <v>0.61417322834645671</v>
       </c>
       <c r="E38" s="13">
         <v>60</v>
       </c>
       <c r="F38" s="12">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G38" s="13">
         <f>VLOOKUP(B38,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7360,11 +7366,11 @@
       </c>
       <c r="H38" s="13">
         <f>VLOOKUP(B38,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I38" s="17">
         <f t="shared" si="2"/>
-        <v>32.950000000000003</v>
+        <v>29.950000000000003</v>
       </c>
       <c r="J38" t="s">
         <v>55</v>
@@ -7380,7 +7386,7 @@
       <c r="E39" s="14"/>
       <c r="F39" s="8">
         <f>+SUM(F26:F38)</f>
-        <v>142</v>
+        <v>232</v>
       </c>
       <c r="G39" s="8">
         <f>+SUM(G26:G38)</f>
@@ -7388,7 +7394,7 @@
       </c>
       <c r="H39" s="8">
         <f>+SUM(H26:H38)</f>
-        <v>864</v>
+        <v>954</v>
       </c>
       <c r="I39" s="8"/>
       <c r="L39" t="s">
@@ -7404,20 +7410,20 @@
       <c r="E40" s="6"/>
       <c r="F40" s="8">
         <f>+SUM(F39+F25+F15)</f>
-        <v>544</v>
+        <v>738</v>
       </c>
       <c r="G40" s="8">
         <f>+G15+G25+G39</f>
-        <v>5708</v>
+        <v>5711</v>
       </c>
       <c r="H40" s="8">
         <f>+H15+H25+H39</f>
-        <v>2872</v>
+        <v>3066</v>
       </c>
       <c r="I40" s="8"/>
       <c r="L40" s="1">
         <f>+H40/G40</f>
-        <v>0.50315346881569722</v>
+        <v>0.5368586937489056</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
@@ -7430,7 +7436,7 @@
       </c>
       <c r="D41" s="22">
         <f t="shared" ref="D41:D42" si="4">H41/G41</f>
-        <v>0.20833333333333334</v>
+        <v>0.20661157024793389</v>
       </c>
       <c r="E41" s="13">
         <v>60</v>
@@ -7441,7 +7447,7 @@
       </c>
       <c r="G41" s="13">
         <f>VLOOKUP(B41,'Base Cobertura'!$A:$C,3,FALSE)</f>
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H41" s="13">
         <f>VLOOKUP(B41,'Base Cobertura'!$A:$C,2,FALSE)</f>
@@ -7449,7 +7455,7 @@
       </c>
       <c r="I41" s="17">
         <f t="shared" ref="I41:I42" si="6">(+G41*$M$2)-H41</f>
-        <v>77</v>
+        <v>77.849999999999994</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
@@ -8075,7 +8081,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="51">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C4" s="51">
         <v>127</v>
@@ -8095,7 +8101,7 @@
         <v>10</v>
       </c>
       <c r="B5" s="51">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="C5" s="51">
         <v>181</v>
@@ -8131,10 +8137,10 @@
         <v>11</v>
       </c>
       <c r="B7" s="51">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C7" s="51">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="G7" t="s">
         <v>226</v>
@@ -8151,7 +8157,7 @@
         <v>12</v>
       </c>
       <c r="B8" s="51">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="C8" s="51">
         <v>214</v>
@@ -8171,7 +8177,7 @@
         <v>123</v>
       </c>
       <c r="B9" s="51">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C9" s="51">
         <v>489</v>
@@ -8191,7 +8197,7 @@
         <v>15</v>
       </c>
       <c r="B10" s="51">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C10" s="51">
         <v>65</v>
@@ -8211,7 +8217,7 @@
         <v>16</v>
       </c>
       <c r="B11" s="51">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C11" s="51">
         <v>198</v>
@@ -8229,7 +8235,7 @@
         <v>18</v>
       </c>
       <c r="B12" s="51">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="C12" s="51">
         <v>177</v>
@@ -8245,7 +8251,7 @@
         <v>222</v>
       </c>
       <c r="H12">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I12" s="51">
         <v>127</v>
@@ -8256,7 +8262,7 @@
         <v>19</v>
       </c>
       <c r="B13" s="51">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="C13" s="51">
         <v>207</v>
@@ -8280,7 +8286,7 @@
         <v>2</v>
       </c>
       <c r="B14" s="51">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C14" s="51">
         <v>138</v>
@@ -8293,7 +8299,7 @@
         <v>224</v>
       </c>
       <c r="H14" s="51">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I14" s="51">
         <v>127</v>
@@ -8304,7 +8310,7 @@
         <v>20</v>
       </c>
       <c r="B15" s="51">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="C15" s="51">
         <v>227</v>
@@ -8328,7 +8334,7 @@
         <v>21</v>
       </c>
       <c r="B16" s="51">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C16" s="51">
         <v>170</v>
@@ -8341,7 +8347,7 @@
         <v>226</v>
       </c>
       <c r="H16" s="51">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="I16" s="51">
         <v>127</v>
@@ -8352,10 +8358,10 @@
         <v>22</v>
       </c>
       <c r="B17" s="51">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C17" s="51">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E17">
         <f t="shared" si="0"/>
@@ -8365,7 +8371,7 @@
         <v>227</v>
       </c>
       <c r="H17" s="51">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I17" s="51">
         <v>127</v>
@@ -8376,7 +8382,7 @@
         <v>23</v>
       </c>
       <c r="B18" s="51">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C18" s="51">
         <v>154</v>
@@ -8389,7 +8395,7 @@
         <v>228</v>
       </c>
       <c r="H18" s="51">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I18" s="51">
         <v>127</v>
@@ -8400,7 +8406,7 @@
         <v>24</v>
       </c>
       <c r="B19" s="51">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="C19" s="51">
         <v>178</v>
@@ -8437,7 +8443,7 @@
         <v>230</v>
       </c>
       <c r="H20">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I20" s="51">
         <v>127</v>
@@ -8448,7 +8454,7 @@
         <v>26</v>
       </c>
       <c r="B21" s="51">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="C21" s="51">
         <v>165</v>
@@ -8464,7 +8470,7 @@
         <v>222</v>
       </c>
       <c r="H21" s="51">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I21" s="51">
         <v>181</v>
@@ -8475,7 +8481,7 @@
         <v>27</v>
       </c>
       <c r="B22" s="51">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="C22" s="51">
         <v>139</v>
@@ -8488,7 +8494,7 @@
         <v>223</v>
       </c>
       <c r="H22" s="51">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I22" s="51">
         <v>181</v>
@@ -8499,7 +8505,7 @@
         <v>28</v>
       </c>
       <c r="B23" s="51">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="C23" s="51">
         <v>168</v>
@@ -8512,7 +8518,7 @@
         <v>224</v>
       </c>
       <c r="H23" s="51">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I23" s="51">
         <v>181</v>
@@ -8523,7 +8529,7 @@
         <v>3</v>
       </c>
       <c r="B24" s="51">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="C24" s="51">
         <v>170</v>
@@ -8536,7 +8542,7 @@
         <v>225</v>
       </c>
       <c r="H24" s="51">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="I24" s="51">
         <v>181</v>
@@ -8547,7 +8553,7 @@
         <v>30</v>
       </c>
       <c r="B25" s="51">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C25" s="51">
         <v>139</v>
@@ -8560,7 +8566,7 @@
         <v>226</v>
       </c>
       <c r="H25" s="51">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I25" s="51">
         <v>181</v>
@@ -8571,7 +8577,7 @@
         <v>31</v>
       </c>
       <c r="B26" s="51">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C26" s="51">
         <v>160</v>
@@ -8584,7 +8590,7 @@
         <v>227</v>
       </c>
       <c r="H26" s="51">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I26" s="51">
         <v>181</v>
@@ -8595,7 +8601,7 @@
         <v>32</v>
       </c>
       <c r="B27" s="51">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C27" s="51">
         <v>57</v>
@@ -8608,7 +8614,7 @@
         <v>228</v>
       </c>
       <c r="H27" s="51">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I27" s="51">
         <v>181</v>
@@ -8619,7 +8625,7 @@
         <v>33</v>
       </c>
       <c r="B28" s="51">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C28" s="51">
         <v>168</v>
@@ -8632,7 +8638,7 @@
         <v>229</v>
       </c>
       <c r="H28" s="51">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I28" s="51">
         <v>181</v>
@@ -8643,7 +8649,7 @@
         <v>36</v>
       </c>
       <c r="B29" s="51">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="C29" s="51">
         <v>157</v>
@@ -8656,7 +8662,7 @@
         <v>230</v>
       </c>
       <c r="H29" s="51">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I29" s="51">
         <v>181</v>
@@ -8667,7 +8673,7 @@
         <v>37</v>
       </c>
       <c r="B30" s="51">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C30" s="51">
         <v>142</v>
@@ -8694,7 +8700,7 @@
         <v>4</v>
       </c>
       <c r="B31" s="51">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C31" s="51">
         <v>182</v>
@@ -8718,7 +8724,7 @@
         <v>40</v>
       </c>
       <c r="B32" s="51">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C32" s="51">
         <v>249</v>
@@ -8790,7 +8796,7 @@
         <v>44</v>
       </c>
       <c r="B35" s="51">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C35" s="51">
         <v>169</v>
@@ -8803,7 +8809,7 @@
         <v>227</v>
       </c>
       <c r="H35" s="51">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I35" s="51">
         <v>2027</v>
@@ -8838,7 +8844,7 @@
         <v>5</v>
       </c>
       <c r="B37" s="51">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="C37" s="51">
         <v>260</v>
@@ -8851,7 +8857,7 @@
         <v>229</v>
       </c>
       <c r="H37" s="51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I37" s="51">
         <v>2027</v>
@@ -8862,7 +8868,7 @@
         <v>52</v>
       </c>
       <c r="B38" s="51">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C38" s="51">
         <v>101</v>
@@ -8886,7 +8892,7 @@
         <v>53</v>
       </c>
       <c r="B39" s="51">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C39" s="51">
         <v>105</v>
@@ -8902,10 +8908,10 @@
         <v>222</v>
       </c>
       <c r="H39" s="51">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I39" s="51">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
@@ -8913,7 +8919,7 @@
         <v>54</v>
       </c>
       <c r="B40" s="51">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C40" s="51">
         <v>202</v>
@@ -8926,10 +8932,10 @@
         <v>223</v>
       </c>
       <c r="H40" s="51">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I40" s="51">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
@@ -8953,7 +8959,7 @@
         <v>43</v>
       </c>
       <c r="I41" s="51">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
@@ -8961,7 +8967,7 @@
         <v>57</v>
       </c>
       <c r="B42" s="51">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C42" s="51">
         <v>104</v>
@@ -8977,7 +8983,7 @@
         <v>29</v>
       </c>
       <c r="I42" s="51">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
@@ -8988,7 +8994,7 @@
         <v>25</v>
       </c>
       <c r="C43" s="51">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E43">
         <f t="shared" si="3"/>
@@ -8998,10 +9004,10 @@
         <v>226</v>
       </c>
       <c r="H43" s="51">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="I43" s="51">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
@@ -9022,10 +9028,10 @@
         <v>227</v>
       </c>
       <c r="H44" s="51">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I44" s="51">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
@@ -9033,7 +9039,7 @@
         <v>7</v>
       </c>
       <c r="B45" s="51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C45" s="51">
         <v>114</v>
@@ -9046,10 +9052,10 @@
         <v>228</v>
       </c>
       <c r="H45" s="51">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I45" s="51">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
@@ -9057,7 +9063,7 @@
         <v>8</v>
       </c>
       <c r="B46" s="51">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C46" s="51">
         <v>195</v>
@@ -9070,10 +9076,10 @@
         <v>229</v>
       </c>
       <c r="H46" s="51">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I46" s="51">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
@@ -9081,7 +9087,7 @@
         <v>9</v>
       </c>
       <c r="B47" s="51">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C47" s="51">
         <v>161</v>
@@ -9097,7 +9103,7 @@
         <v>9</v>
       </c>
       <c r="I47" s="51">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
@@ -9114,7 +9120,7 @@
         <v>222</v>
       </c>
       <c r="H48" s="51">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="I48" s="51">
         <v>214</v>
@@ -9131,7 +9137,7 @@
         <v>223</v>
       </c>
       <c r="H49" s="51">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I49" s="51">
         <v>214</v>
@@ -9146,7 +9152,7 @@
         <v>224</v>
       </c>
       <c r="H50" s="51">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I50" s="51">
         <v>214</v>
@@ -9161,7 +9167,7 @@
         <v>225</v>
       </c>
       <c r="H51" s="51">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I51" s="51">
         <v>214</v>
@@ -9176,7 +9182,7 @@
         <v>226</v>
       </c>
       <c r="H52" s="51">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="I52" s="51">
         <v>214</v>
@@ -9191,7 +9197,7 @@
         <v>227</v>
       </c>
       <c r="H53" s="51">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="I53" s="51">
         <v>214</v>
@@ -9206,7 +9212,7 @@
         <v>228</v>
       </c>
       <c r="H54" s="51">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I54" s="51">
         <v>214</v>
@@ -9221,7 +9227,7 @@
         <v>229</v>
       </c>
       <c r="H55" s="51">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I55" s="51">
         <v>214</v>
@@ -9236,7 +9242,7 @@
         <v>230</v>
       </c>
       <c r="H56" s="51">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="I56" s="51">
         <v>214</v>
@@ -9254,7 +9260,7 @@
         <v>222</v>
       </c>
       <c r="H57" s="51">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I57" s="51">
         <v>489</v>
@@ -9269,7 +9275,7 @@
         <v>223</v>
       </c>
       <c r="H58" s="51">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I58" s="51">
         <v>489</v>
@@ -9284,7 +9290,7 @@
         <v>224</v>
       </c>
       <c r="H59" s="51">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I59" s="51">
         <v>489</v>
@@ -9329,7 +9335,7 @@
         <v>227</v>
       </c>
       <c r="H62" s="51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I62" s="51">
         <v>489</v>
@@ -9344,7 +9350,7 @@
         <v>228</v>
       </c>
       <c r="H63" s="51">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I63" s="51">
         <v>489</v>
@@ -9390,7 +9396,7 @@
         <v>222</v>
       </c>
       <c r="H66" s="51">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I66" s="51">
         <v>65</v>
@@ -9420,7 +9426,7 @@
         <v>224</v>
       </c>
       <c r="H68" s="51">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I68" s="51">
         <v>65</v>
@@ -9435,7 +9441,7 @@
         <v>225</v>
       </c>
       <c r="H69" s="51">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I69" s="51">
         <v>65</v>
@@ -9450,7 +9456,7 @@
         <v>226</v>
       </c>
       <c r="H70" s="51">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I70" s="51">
         <v>65</v>
@@ -9465,7 +9471,7 @@
         <v>227</v>
       </c>
       <c r="H71" s="51">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I71" s="51">
         <v>65</v>
@@ -9480,7 +9486,7 @@
         <v>228</v>
       </c>
       <c r="H72" s="51">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I72" s="51">
         <v>65</v>
@@ -9528,7 +9534,7 @@
         <v>222</v>
       </c>
       <c r="H75" s="51">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I75" s="51">
         <v>198</v>
@@ -9543,7 +9549,7 @@
         <v>223</v>
       </c>
       <c r="H76">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I76" s="51">
         <v>198</v>
@@ -9558,7 +9564,7 @@
         <v>224</v>
       </c>
       <c r="H77" s="51">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="I77" s="51">
         <v>198</v>
@@ -9573,7 +9579,7 @@
         <v>225</v>
       </c>
       <c r="H78" s="51">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I78" s="51">
         <v>198</v>
@@ -9588,7 +9594,7 @@
         <v>226</v>
       </c>
       <c r="H79" s="51">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="I79" s="51">
         <v>198</v>
@@ -9603,7 +9609,7 @@
         <v>227</v>
       </c>
       <c r="H80" s="51">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I80" s="51">
         <v>198</v>
@@ -9618,7 +9624,7 @@
         <v>228</v>
       </c>
       <c r="H81" s="51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I81" s="51">
         <v>198</v>
@@ -9633,7 +9639,7 @@
         <v>229</v>
       </c>
       <c r="H82" s="51">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I82" s="51">
         <v>198</v>
@@ -9648,7 +9654,7 @@
         <v>230</v>
       </c>
       <c r="H83" s="51">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I83" s="51">
         <v>198</v>
@@ -9681,7 +9687,7 @@
         <v>223</v>
       </c>
       <c r="H85" s="51">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I85" s="51">
         <v>177</v>
@@ -9696,7 +9702,7 @@
         <v>224</v>
       </c>
       <c r="H86" s="51">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I86" s="51">
         <v>177</v>
@@ -9711,7 +9717,7 @@
         <v>225</v>
       </c>
       <c r="H87" s="51">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I87" s="51">
         <v>177</v>
@@ -9726,7 +9732,7 @@
         <v>226</v>
       </c>
       <c r="H88" s="51">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="I88" s="51">
         <v>177</v>
@@ -9741,7 +9747,7 @@
         <v>227</v>
       </c>
       <c r="H89" s="51">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I89" s="51">
         <v>177</v>
@@ -9756,7 +9762,7 @@
         <v>228</v>
       </c>
       <c r="H90" s="51">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I90" s="51">
         <v>177</v>
@@ -9771,7 +9777,7 @@
         <v>229</v>
       </c>
       <c r="H91" s="51">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I91" s="51">
         <v>177</v>
@@ -9786,7 +9792,7 @@
         <v>230</v>
       </c>
       <c r="H92" s="51">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I92" s="51">
         <v>177</v>
@@ -9804,7 +9810,7 @@
         <v>222</v>
       </c>
       <c r="H93" s="51">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I93" s="51">
         <v>207</v>
@@ -9834,7 +9840,7 @@
         <v>224</v>
       </c>
       <c r="H95" s="51">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="I95" s="51">
         <v>207</v>
@@ -9849,7 +9855,7 @@
         <v>225</v>
       </c>
       <c r="H96" s="51">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I96" s="51">
         <v>207</v>
@@ -9864,7 +9870,7 @@
         <v>226</v>
       </c>
       <c r="H97" s="51">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="I97" s="51">
         <v>207</v>
@@ -9879,7 +9885,7 @@
         <v>227</v>
       </c>
       <c r="H98" s="51">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I98" s="51">
         <v>207</v>
@@ -9909,7 +9915,7 @@
         <v>229</v>
       </c>
       <c r="H100" s="51">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I100" s="51">
         <v>207</v>
@@ -9924,7 +9930,7 @@
         <v>230</v>
       </c>
       <c r="H101" s="51">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I101" s="51">
         <v>207</v>
@@ -9942,7 +9948,7 @@
         <v>222</v>
       </c>
       <c r="H102" s="51">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I102" s="51">
         <v>138</v>
@@ -9957,7 +9963,7 @@
         <v>223</v>
       </c>
       <c r="H103" s="51">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I103" s="51">
         <v>138</v>
@@ -9972,7 +9978,7 @@
         <v>224</v>
       </c>
       <c r="H104" s="51">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I104" s="51">
         <v>138</v>
@@ -9987,7 +9993,7 @@
         <v>225</v>
       </c>
       <c r="H105" s="51">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I105" s="51">
         <v>138</v>
@@ -10002,7 +10008,7 @@
         <v>226</v>
       </c>
       <c r="H106" s="51">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I106" s="51">
         <v>138</v>
@@ -10017,7 +10023,7 @@
         <v>227</v>
       </c>
       <c r="H107" s="51">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I107" s="51">
         <v>138</v>
@@ -10062,7 +10068,7 @@
         <v>230</v>
       </c>
       <c r="H110" s="51">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I110" s="51">
         <v>138</v>
@@ -10080,7 +10086,7 @@
         <v>222</v>
       </c>
       <c r="H111" s="51">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="I111" s="51">
         <v>227</v>
@@ -10095,7 +10101,7 @@
         <v>223</v>
       </c>
       <c r="H112" s="51">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I112" s="51">
         <v>227</v>
@@ -10110,7 +10116,7 @@
         <v>224</v>
       </c>
       <c r="H113" s="51">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="I113" s="51">
         <v>227</v>
@@ -10125,7 +10131,7 @@
         <v>225</v>
       </c>
       <c r="H114" s="51">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="I114" s="51">
         <v>227</v>
@@ -10140,7 +10146,7 @@
         <v>226</v>
       </c>
       <c r="H115" s="51">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="I115" s="51">
         <v>227</v>
@@ -10155,7 +10161,7 @@
         <v>227</v>
       </c>
       <c r="H116">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="I116" s="51">
         <v>227</v>
@@ -10185,7 +10191,7 @@
         <v>229</v>
       </c>
       <c r="H118" s="51">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I118" s="51">
         <v>227</v>
@@ -10200,7 +10206,7 @@
         <v>230</v>
       </c>
       <c r="H119" s="51">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I119" s="51">
         <v>227</v>
@@ -10218,7 +10224,7 @@
         <v>222</v>
       </c>
       <c r="H120" s="51">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="I120" s="51">
         <v>170</v>
@@ -10233,7 +10239,7 @@
         <v>223</v>
       </c>
       <c r="H121" s="51">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I121" s="51">
         <v>170</v>
@@ -10248,7 +10254,7 @@
         <v>224</v>
       </c>
       <c r="H122" s="51">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="I122" s="51">
         <v>170</v>
@@ -10263,7 +10269,7 @@
         <v>225</v>
       </c>
       <c r="H123" s="51">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I123" s="51">
         <v>170</v>
@@ -10278,7 +10284,7 @@
         <v>226</v>
       </c>
       <c r="H124">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="I124" s="51">
         <v>170</v>
@@ -10293,7 +10299,7 @@
         <v>227</v>
       </c>
       <c r="H125" s="51">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="I125" s="51">
         <v>170</v>
@@ -10308,7 +10314,7 @@
         <v>228</v>
       </c>
       <c r="H126" s="51">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I126" s="51">
         <v>170</v>
@@ -10323,7 +10329,7 @@
         <v>229</v>
       </c>
       <c r="H127" s="51">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I127" s="51">
         <v>170</v>
@@ -10338,7 +10344,7 @@
         <v>230</v>
       </c>
       <c r="H128" s="51">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I128" s="51">
         <v>170</v>
@@ -10356,10 +10362,10 @@
         <v>222</v>
       </c>
       <c r="H129" s="51">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I129" s="51">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="130" spans="5:9" x14ac:dyDescent="0.25">
@@ -10371,10 +10377,10 @@
         <v>223</v>
       </c>
       <c r="H130" s="51">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I130" s="51">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="131" spans="5:9" x14ac:dyDescent="0.25">
@@ -10386,10 +10392,10 @@
         <v>224</v>
       </c>
       <c r="H131" s="51">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I131" s="51">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="132" spans="5:9" x14ac:dyDescent="0.25">
@@ -10401,10 +10407,10 @@
         <v>225</v>
       </c>
       <c r="H132" s="51">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I132" s="51">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="133" spans="5:9" x14ac:dyDescent="0.25">
@@ -10416,10 +10422,10 @@
         <v>226</v>
       </c>
       <c r="H133" s="51">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I133" s="51">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="134" spans="5:9" x14ac:dyDescent="0.25">
@@ -10434,7 +10440,7 @@
         <v>20</v>
       </c>
       <c r="I134" s="51">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="135" spans="5:9" x14ac:dyDescent="0.25">
@@ -10446,10 +10452,10 @@
         <v>228</v>
       </c>
       <c r="H135" s="51">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I135" s="51">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="136" spans="5:9" x14ac:dyDescent="0.25">
@@ -10461,10 +10467,10 @@
         <v>229</v>
       </c>
       <c r="H136" s="51">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I136" s="51">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="137" spans="5:9" x14ac:dyDescent="0.25">
@@ -10476,10 +10482,10 @@
         <v>230</v>
       </c>
       <c r="H137" s="51">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I137" s="51">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="138" spans="5:9" x14ac:dyDescent="0.25">
@@ -10494,7 +10500,7 @@
         <v>222</v>
       </c>
       <c r="H138" s="51">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I138" s="51">
         <v>154</v>
@@ -10509,7 +10515,7 @@
         <v>223</v>
       </c>
       <c r="H139" s="51">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I139" s="51">
         <v>154</v>
@@ -10524,7 +10530,7 @@
         <v>224</v>
       </c>
       <c r="H140">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I140" s="51">
         <v>154</v>
@@ -10539,7 +10545,7 @@
         <v>225</v>
       </c>
       <c r="H141" s="51">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I141" s="51">
         <v>154</v>
@@ -10554,7 +10560,7 @@
         <v>226</v>
       </c>
       <c r="H142" s="51">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="I142" s="51">
         <v>154</v>
@@ -10569,7 +10575,7 @@
         <v>227</v>
       </c>
       <c r="H143" s="51">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I143" s="51">
         <v>154</v>
@@ -10584,7 +10590,7 @@
         <v>228</v>
       </c>
       <c r="H144" s="51">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I144" s="51">
         <v>154</v>
@@ -10599,7 +10605,7 @@
         <v>229</v>
       </c>
       <c r="H145" s="51">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I145" s="51">
         <v>154</v>
@@ -10614,7 +10620,7 @@
         <v>230</v>
       </c>
       <c r="H146" s="51">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I146" s="51">
         <v>154</v>
@@ -10632,7 +10638,7 @@
         <v>222</v>
       </c>
       <c r="H147" s="51">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="I147" s="51">
         <v>178</v>
@@ -10647,7 +10653,7 @@
         <v>223</v>
       </c>
       <c r="H148">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I148" s="51">
         <v>178</v>
@@ -10662,7 +10668,7 @@
         <v>224</v>
       </c>
       <c r="H149" s="51">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="I149" s="51">
         <v>178</v>
@@ -10692,7 +10698,7 @@
         <v>226</v>
       </c>
       <c r="H151" s="51">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="I151" s="51">
         <v>178</v>
@@ -10707,7 +10713,7 @@
         <v>227</v>
       </c>
       <c r="H152" s="51">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I152" s="51">
         <v>178</v>
@@ -10737,7 +10743,7 @@
         <v>229</v>
       </c>
       <c r="H154" s="51">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I154" s="51">
         <v>178</v>
@@ -10752,7 +10758,7 @@
         <v>230</v>
       </c>
       <c r="H155" s="51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I155" s="51">
         <v>178</v>
@@ -10845,7 +10851,7 @@
         <v>227</v>
       </c>
       <c r="H161" s="51">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I161" s="51">
         <v>172</v>
@@ -10908,7 +10914,7 @@
         <v>222</v>
       </c>
       <c r="H165" s="51">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="I165" s="51">
         <v>165</v>
@@ -10923,7 +10929,7 @@
         <v>223</v>
       </c>
       <c r="H166" s="51">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I166" s="51">
         <v>165</v>
@@ -10938,7 +10944,7 @@
         <v>224</v>
       </c>
       <c r="H167" s="51">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I167" s="51">
         <v>165</v>
@@ -10953,7 +10959,7 @@
         <v>225</v>
       </c>
       <c r="H168" s="51">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="I168" s="51">
         <v>165</v>
@@ -10968,7 +10974,7 @@
         <v>226</v>
       </c>
       <c r="H169" s="51">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="I169" s="51">
         <v>165</v>
@@ -10983,7 +10989,7 @@
         <v>227</v>
       </c>
       <c r="H170" s="51">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="I170" s="51">
         <v>165</v>
@@ -10998,7 +11004,7 @@
         <v>228</v>
       </c>
       <c r="H171" s="51">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="I171" s="51">
         <v>165</v>
@@ -11013,7 +11019,7 @@
         <v>229</v>
       </c>
       <c r="H172" s="51">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I172" s="51">
         <v>165</v>
@@ -11028,7 +11034,7 @@
         <v>230</v>
       </c>
       <c r="H173" s="51">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="I173" s="51">
         <v>165</v>
@@ -11046,7 +11052,7 @@
         <v>222</v>
       </c>
       <c r="H174" s="51">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I174" s="51">
         <v>139</v>
@@ -11076,7 +11082,7 @@
         <v>224</v>
       </c>
       <c r="H176" s="51">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I176" s="51">
         <v>139</v>
@@ -11091,7 +11097,7 @@
         <v>225</v>
       </c>
       <c r="H177" s="51">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I177" s="51">
         <v>139</v>
@@ -11106,7 +11112,7 @@
         <v>226</v>
       </c>
       <c r="H178" s="51">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="I178" s="51">
         <v>139</v>
@@ -11121,7 +11127,7 @@
         <v>227</v>
       </c>
       <c r="H179" s="51">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="I179" s="51">
         <v>139</v>
@@ -11136,7 +11142,7 @@
         <v>228</v>
       </c>
       <c r="H180">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I180" s="51">
         <v>139</v>
@@ -11151,7 +11157,7 @@
         <v>229</v>
       </c>
       <c r="H181" s="51">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I181" s="51">
         <v>139</v>
@@ -11184,7 +11190,7 @@
         <v>222</v>
       </c>
       <c r="H183" s="51">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I183" s="51">
         <v>168</v>
@@ -11199,7 +11205,7 @@
         <v>223</v>
       </c>
       <c r="H184" s="51">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I184" s="51">
         <v>168</v>
@@ -11214,7 +11220,7 @@
         <v>224</v>
       </c>
       <c r="H185" s="51">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I185" s="51">
         <v>168</v>
@@ -11229,7 +11235,7 @@
         <v>225</v>
       </c>
       <c r="H186">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I186" s="51">
         <v>168</v>
@@ -11244,7 +11250,7 @@
         <v>226</v>
       </c>
       <c r="H187" s="51">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="I187" s="51">
         <v>168</v>
@@ -11259,7 +11265,7 @@
         <v>227</v>
       </c>
       <c r="H188" s="51">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="I188" s="51">
         <v>168</v>
@@ -11274,7 +11280,7 @@
         <v>228</v>
       </c>
       <c r="H189" s="51">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I189" s="51">
         <v>168</v>
@@ -11289,7 +11295,7 @@
         <v>229</v>
       </c>
       <c r="H190" s="51">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I190" s="51">
         <v>168</v>
@@ -11304,7 +11310,7 @@
         <v>230</v>
       </c>
       <c r="H191" s="51">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I191" s="51">
         <v>168</v>
@@ -11322,7 +11328,7 @@
         <v>222</v>
       </c>
       <c r="H192" s="51">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I192" s="51">
         <v>170</v>
@@ -11337,7 +11343,7 @@
         <v>223</v>
       </c>
       <c r="H193" s="51">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I193" s="51">
         <v>170</v>
@@ -11352,7 +11358,7 @@
         <v>224</v>
       </c>
       <c r="H194" s="51">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I194" s="51">
         <v>170</v>
@@ -11367,7 +11373,7 @@
         <v>225</v>
       </c>
       <c r="H195" s="51">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I195" s="51">
         <v>170</v>
@@ -11382,7 +11388,7 @@
         <v>226</v>
       </c>
       <c r="H196">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="I196" s="51">
         <v>170</v>
@@ -11397,7 +11403,7 @@
         <v>227</v>
       </c>
       <c r="H197" s="51">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I197" s="51">
         <v>170</v>
@@ -11412,7 +11418,7 @@
         <v>228</v>
       </c>
       <c r="H198" s="51">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I198" s="51">
         <v>170</v>
@@ -11427,7 +11433,7 @@
         <v>229</v>
       </c>
       <c r="H199" s="51">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I199" s="51">
         <v>170</v>
@@ -11442,7 +11448,7 @@
         <v>230</v>
       </c>
       <c r="H200" s="51">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I200" s="51">
         <v>170</v>
@@ -11546,7 +11552,7 @@
         <v>228</v>
       </c>
       <c r="H207" s="51">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I207" s="51">
         <v>139</v>
@@ -11590,7 +11596,7 @@
         <v>222</v>
       </c>
       <c r="H210" s="51">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I210" s="51">
         <v>160</v>
@@ -11605,7 +11611,7 @@
         <v>223</v>
       </c>
       <c r="H211" s="51">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I211" s="51">
         <v>160</v>
@@ -11620,7 +11626,7 @@
         <v>224</v>
       </c>
       <c r="H212">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="I212" s="51">
         <v>160</v>
@@ -11635,7 +11641,7 @@
         <v>225</v>
       </c>
       <c r="H213" s="51">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I213" s="51">
         <v>160</v>
@@ -11650,7 +11656,7 @@
         <v>226</v>
       </c>
       <c r="H214" s="51">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I214" s="51">
         <v>160</v>
@@ -11665,7 +11671,7 @@
         <v>227</v>
       </c>
       <c r="H215" s="51">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="I215" s="51">
         <v>160</v>
@@ -11695,7 +11701,7 @@
         <v>229</v>
       </c>
       <c r="H217" s="51">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I217" s="51">
         <v>160</v>
@@ -11710,7 +11716,7 @@
         <v>230</v>
       </c>
       <c r="H218" s="51">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I218" s="51">
         <v>160</v>
@@ -11728,7 +11734,7 @@
         <v>222</v>
       </c>
       <c r="H219" s="51">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I219" s="51">
         <v>57</v>
@@ -11743,7 +11749,7 @@
         <v>223</v>
       </c>
       <c r="H220" s="51">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I220" s="51">
         <v>57</v>
@@ -11758,7 +11764,7 @@
         <v>224</v>
       </c>
       <c r="H221" s="51">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I221" s="51">
         <v>57</v>
@@ -11773,7 +11779,7 @@
         <v>225</v>
       </c>
       <c r="H222" s="51">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I222" s="51">
         <v>57</v>
@@ -11788,7 +11794,7 @@
         <v>226</v>
       </c>
       <c r="H223" s="51">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I223" s="51">
         <v>57</v>
@@ -11803,7 +11809,7 @@
         <v>227</v>
       </c>
       <c r="H224" s="51">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I224" s="51">
         <v>57</v>
@@ -11818,7 +11824,7 @@
         <v>228</v>
       </c>
       <c r="H225" s="51">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I225" s="51">
         <v>57</v>
@@ -11866,7 +11872,7 @@
         <v>222</v>
       </c>
       <c r="H228" s="51">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I228" s="51">
         <v>168</v>
@@ -11881,7 +11887,7 @@
         <v>223</v>
       </c>
       <c r="H229" s="51">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I229" s="51">
         <v>168</v>
@@ -11896,7 +11902,7 @@
         <v>224</v>
       </c>
       <c r="H230" s="51">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I230" s="51">
         <v>168</v>
@@ -11911,7 +11917,7 @@
         <v>225</v>
       </c>
       <c r="H231" s="51">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I231" s="51">
         <v>168</v>
@@ -11926,7 +11932,7 @@
         <v>226</v>
       </c>
       <c r="H232" s="51">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I232" s="51">
         <v>168</v>
@@ -11941,7 +11947,7 @@
         <v>227</v>
       </c>
       <c r="H233" s="51">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I233" s="51">
         <v>168</v>
@@ -11956,7 +11962,7 @@
         <v>228</v>
       </c>
       <c r="H234" s="51">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I234" s="51">
         <v>168</v>
@@ -11971,7 +11977,7 @@
         <v>229</v>
       </c>
       <c r="H235" s="51">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I235" s="51">
         <v>168</v>
@@ -12004,7 +12010,7 @@
         <v>222</v>
       </c>
       <c r="H237" s="51">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I237" s="51">
         <v>157</v>
@@ -12034,7 +12040,7 @@
         <v>224</v>
       </c>
       <c r="H239" s="51">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I239" s="51">
         <v>157</v>
@@ -12049,7 +12055,7 @@
         <v>225</v>
       </c>
       <c r="H240" s="51">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I240" s="51">
         <v>157</v>
@@ -12064,7 +12070,7 @@
         <v>226</v>
       </c>
       <c r="H241" s="51">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="I241" s="51">
         <v>157</v>
@@ -12079,7 +12085,7 @@
         <v>227</v>
       </c>
       <c r="H242" s="51">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="I242" s="51">
         <v>157</v>
@@ -12094,7 +12100,7 @@
         <v>228</v>
       </c>
       <c r="H243" s="51">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I243" s="51">
         <v>157</v>
@@ -12124,7 +12130,7 @@
         <v>230</v>
       </c>
       <c r="H245" s="51">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I245" s="51">
         <v>157</v>
@@ -12142,7 +12148,7 @@
         <v>222</v>
       </c>
       <c r="H246" s="51">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I246" s="51">
         <v>142</v>
@@ -12157,7 +12163,7 @@
         <v>223</v>
       </c>
       <c r="H247" s="51">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I247" s="51">
         <v>142</v>
@@ -12172,7 +12178,7 @@
         <v>224</v>
       </c>
       <c r="H248" s="51">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I248" s="51">
         <v>142</v>
@@ -12187,7 +12193,7 @@
         <v>225</v>
       </c>
       <c r="H249" s="51">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I249" s="51">
         <v>142</v>
@@ -12202,7 +12208,7 @@
         <v>226</v>
       </c>
       <c r="H250" s="51">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I250" s="51">
         <v>142</v>
@@ -12217,7 +12223,7 @@
         <v>227</v>
       </c>
       <c r="H251" s="51">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I251" s="51">
         <v>142</v>
@@ -12232,7 +12238,7 @@
         <v>228</v>
       </c>
       <c r="H252">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I252" s="51">
         <v>142</v>
@@ -12247,7 +12253,7 @@
         <v>229</v>
       </c>
       <c r="H253" s="51">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I253" s="51">
         <v>142</v>
@@ -12280,7 +12286,7 @@
         <v>222</v>
       </c>
       <c r="H255" s="51">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I255" s="51">
         <v>182</v>
@@ -12295,7 +12301,7 @@
         <v>223</v>
       </c>
       <c r="H256" s="51">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I256" s="51">
         <v>182</v>
@@ -12310,7 +12316,7 @@
         <v>224</v>
       </c>
       <c r="H257" s="51">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I257" s="51">
         <v>182</v>
@@ -12325,7 +12331,7 @@
         <v>225</v>
       </c>
       <c r="H258">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I258" s="51">
         <v>182</v>
@@ -12340,7 +12346,7 @@
         <v>226</v>
       </c>
       <c r="H259" s="51">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="I259" s="51">
         <v>182</v>
@@ -12355,7 +12361,7 @@
         <v>227</v>
       </c>
       <c r="H260">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I260" s="51">
         <v>182</v>
@@ -12385,7 +12391,7 @@
         <v>229</v>
       </c>
       <c r="H262" s="51">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I262" s="51">
         <v>182</v>
@@ -12400,7 +12406,7 @@
         <v>230</v>
       </c>
       <c r="H263" s="51">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I263" s="51">
         <v>182</v>
@@ -12448,7 +12454,7 @@
         <v>224</v>
       </c>
       <c r="H266" s="51">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I266" s="51">
         <v>249</v>
@@ -12463,7 +12469,7 @@
         <v>225</v>
       </c>
       <c r="H267" s="51">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I267" s="51">
         <v>249</v>
@@ -12478,7 +12484,7 @@
         <v>226</v>
       </c>
       <c r="H268">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="I268" s="51">
         <v>249</v>
@@ -12493,7 +12499,7 @@
         <v>227</v>
       </c>
       <c r="H269" s="51">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I269" s="51">
         <v>249</v>
@@ -12508,7 +12514,7 @@
         <v>228</v>
       </c>
       <c r="H270" s="51">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I270" s="51">
         <v>249</v>
@@ -12538,7 +12544,7 @@
         <v>230</v>
       </c>
       <c r="H272" s="51">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I272" s="51">
         <v>249</v>
@@ -12823,7 +12829,7 @@
         <v>223</v>
       </c>
       <c r="H292">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I292" s="51">
         <v>169</v>
@@ -12838,7 +12844,7 @@
         <v>224</v>
       </c>
       <c r="H293">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="I293" s="51">
         <v>169</v>
@@ -12853,7 +12859,7 @@
         <v>225</v>
       </c>
       <c r="H294">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I294" s="51">
         <v>169</v>
@@ -12868,7 +12874,7 @@
         <v>226</v>
       </c>
       <c r="H295">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="I295" s="51">
         <v>169</v>
@@ -12883,7 +12889,7 @@
         <v>227</v>
       </c>
       <c r="H296">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="I296" s="51">
         <v>169</v>
@@ -12898,7 +12904,7 @@
         <v>228</v>
       </c>
       <c r="H297" s="51">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I297" s="51">
         <v>169</v>
@@ -12928,7 +12934,7 @@
         <v>230</v>
       </c>
       <c r="H299" s="51">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I299" s="51">
         <v>169</v>
@@ -13084,7 +13090,7 @@
         <v>222</v>
       </c>
       <c r="H309">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="I309" s="51">
         <v>260</v>
@@ -13099,7 +13105,7 @@
         <v>223</v>
       </c>
       <c r="H310">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I310" s="51">
         <v>260</v>
@@ -13114,7 +13120,7 @@
         <v>224</v>
       </c>
       <c r="H311">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="I311" s="51">
         <v>260</v>
@@ -13129,7 +13135,7 @@
         <v>225</v>
       </c>
       <c r="H312">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I312" s="51">
         <v>260</v>
@@ -13144,7 +13150,7 @@
         <v>226</v>
       </c>
       <c r="H313">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="I313" s="51">
         <v>260</v>
@@ -13159,7 +13165,7 @@
         <v>227</v>
       </c>
       <c r="H314">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="I314" s="51">
         <v>260</v>
@@ -13204,7 +13210,7 @@
         <v>230</v>
       </c>
       <c r="H317" s="51">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I317" s="51">
         <v>260</v>
@@ -13303,7 +13309,7 @@
         <v>228</v>
       </c>
       <c r="H324" s="51">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I324" s="51">
         <v>101</v>
@@ -13359,7 +13365,7 @@
         <v>223</v>
       </c>
       <c r="H328">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I328" s="51">
         <v>105</v>
@@ -13424,7 +13430,7 @@
         <v>228</v>
       </c>
       <c r="H333" s="51">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I333" s="51">
         <v>105</v>
@@ -13468,7 +13474,7 @@
         <v>222</v>
       </c>
       <c r="H336" s="51">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I336" s="51">
         <v>202</v>
@@ -13498,7 +13504,7 @@
         <v>224</v>
       </c>
       <c r="H338" s="51">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I338" s="51">
         <v>202</v>
@@ -13513,7 +13519,7 @@
         <v>225</v>
       </c>
       <c r="H339" s="51">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I339" s="51">
         <v>202</v>
@@ -13528,7 +13534,7 @@
         <v>226</v>
       </c>
       <c r="H340">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="I340" s="51">
         <v>202</v>
@@ -13543,7 +13549,7 @@
         <v>227</v>
       </c>
       <c r="H341" s="51">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I341" s="51">
         <v>202</v>
@@ -13558,7 +13564,7 @@
         <v>228</v>
       </c>
       <c r="H342" s="51">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I342" s="51">
         <v>202</v>
@@ -13573,7 +13579,7 @@
         <v>229</v>
       </c>
       <c r="H343" s="51">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I343" s="51">
         <v>202</v>
@@ -13824,7 +13830,7 @@
         <v>228</v>
       </c>
       <c r="H360" s="51">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I360" s="51">
         <v>104</v>
@@ -13871,7 +13877,7 @@
         <v>1</v>
       </c>
       <c r="I363" s="51">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="364" spans="5:9" x14ac:dyDescent="0.25">
@@ -13886,7 +13892,7 @@
         <v>9</v>
       </c>
       <c r="I364" s="51">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="365" spans="5:9" x14ac:dyDescent="0.25">
@@ -13901,7 +13907,7 @@
         <v>7</v>
       </c>
       <c r="I365" s="51">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="366" spans="5:9" x14ac:dyDescent="0.25">
@@ -13916,7 +13922,7 @@
         <v>14</v>
       </c>
       <c r="I366" s="51">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="367" spans="5:9" x14ac:dyDescent="0.25">
@@ -13931,7 +13937,7 @@
         <v>17</v>
       </c>
       <c r="I367" s="51">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="368" spans="5:9" x14ac:dyDescent="0.25">
@@ -13946,7 +13952,7 @@
         <v>16</v>
       </c>
       <c r="I368" s="51">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="369" spans="5:9" x14ac:dyDescent="0.25">
@@ -13961,7 +13967,7 @@
         <v>3</v>
       </c>
       <c r="I369" s="51">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="370" spans="5:9" x14ac:dyDescent="0.25">
@@ -13976,7 +13982,7 @@
         <v>2</v>
       </c>
       <c r="I370" s="51">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="371" spans="5:9" x14ac:dyDescent="0.25">
@@ -13991,7 +13997,7 @@
         <v>1</v>
       </c>
       <c r="I371" s="35">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="372" spans="5:9" x14ac:dyDescent="0.25">
@@ -14021,7 +14027,7 @@
         <v>223</v>
       </c>
       <c r="H373">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I373">
         <v>122</v>
@@ -14216,7 +14222,7 @@
         <v>227</v>
       </c>
       <c r="H386">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I386">
         <v>114</v>
@@ -14245,6 +14251,9 @@
       <c r="G388" t="s">
         <v>229</v>
       </c>
+      <c r="H388">
+        <v>1</v>
+      </c>
       <c r="I388">
         <v>114</v>
       </c>
@@ -14276,7 +14285,7 @@
         <v>222</v>
       </c>
       <c r="H390">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I390">
         <v>195</v>
@@ -14291,7 +14300,7 @@
         <v>223</v>
       </c>
       <c r="H391">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I391">
         <v>195</v>
@@ -14306,7 +14315,7 @@
         <v>224</v>
       </c>
       <c r="H392">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I392">
         <v>195</v>
@@ -14321,7 +14330,7 @@
         <v>225</v>
       </c>
       <c r="H393">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I393">
         <v>195</v>
@@ -14336,7 +14345,7 @@
         <v>226</v>
       </c>
       <c r="H394">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="I394">
         <v>195</v>
@@ -14351,7 +14360,7 @@
         <v>227</v>
       </c>
       <c r="H395">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I395">
         <v>195</v>
@@ -14396,7 +14405,7 @@
         <v>230</v>
       </c>
       <c r="H398">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I398">
         <v>195</v>
@@ -14414,7 +14423,7 @@
         <v>222</v>
       </c>
       <c r="H399">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I399">
         <v>161</v>
@@ -14429,7 +14438,7 @@
         <v>223</v>
       </c>
       <c r="H400">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I400">
         <v>161</v>
@@ -14444,7 +14453,7 @@
         <v>224</v>
       </c>
       <c r="H401">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I401">
         <v>161</v>
@@ -14459,7 +14468,7 @@
         <v>225</v>
       </c>
       <c r="H402">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I402">
         <v>161</v>
@@ -14474,7 +14483,7 @@
         <v>226</v>
       </c>
       <c r="H403">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="I403">
         <v>161</v>
@@ -14489,7 +14498,7 @@
         <v>227</v>
       </c>
       <c r="H404">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I404">
         <v>161</v>
@@ -14519,7 +14528,7 @@
         <v>229</v>
       </c>
       <c r="H406">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I406">
         <v>161</v>
@@ -14534,7 +14543,7 @@
         <v>230</v>
       </c>
       <c r="H407">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I407">
         <v>161</v>

--- a/data/ventas.xlsx
+++ b/data/ventas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cesar\Desktop\Reportes Ventas Rap\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE81802B-425A-45B1-9121-0E0DB3801FFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E5DB899-2851-4ED1-8092-A74C6D5B7C1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4673,45 +4673,45 @@
     <row r="22" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="91"/>
       <c r="B22" s="19" t="s">
-        <v>101</v>
+        <v>233</v>
       </c>
       <c r="C22" s="71">
         <v>31742890.200000003</v>
       </c>
       <c r="D22" s="4">
         <f>IFERROR(+VLOOKUP(B22,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>0</v>
+        <v>13022386.541284554</v>
       </c>
       <c r="E22" s="4">
         <v>12482971.675436357</v>
       </c>
       <c r="F22" s="4">
         <f t="shared" si="9"/>
-        <v>-12482971.675436357</v>
+        <v>539414.86584819667</v>
       </c>
       <c r="G22" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.41024577343888341</v>
       </c>
       <c r="H22" s="4">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>34726364.110092148</v>
       </c>
       <c r="I22" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.0939887291703558</v>
       </c>
       <c r="J22" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1446931.837920506</v>
       </c>
       <c r="K22" s="4">
         <f t="shared" si="3"/>
-        <v>2116192.6800000002</v>
+        <v>1248033.5772476967</v>
       </c>
       <c r="L22" s="63" cm="1">
         <f t="array" ref="L22">+_xlfn.IFS(I22&gt;114%,H22*0.02,I22&gt;109%,H22*0.015,I22&gt;104%,H22*0.0125,I22&gt;99%,H22*0.01,I22&lt;99%,H22*0)</f>
-        <v>0</v>
+        <v>520895.46165138221</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4761,41 +4761,41 @@
     <row r="24" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="91"/>
       <c r="B24" s="19" t="s">
-        <v>109</v>
+        <v>234</v>
       </c>
       <c r="C24" s="71">
         <v>33494055</v>
       </c>
       <c r="D24" s="4">
         <f>IFERROR(+VLOOKUP(B24,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>0</v>
+        <v>8128233.8339369334</v>
       </c>
       <c r="E24" s="4">
         <v>7599049.4142421484</v>
       </c>
       <c r="F24" s="4">
         <f t="shared" si="8"/>
-        <v>-7599049.4142421484</v>
+        <v>529184.41969478503</v>
       </c>
       <c r="G24" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.24267691188591328</v>
       </c>
       <c r="H24" s="4">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>21675290.223831821</v>
       </c>
       <c r="I24" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.64713843169576868</v>
       </c>
       <c r="J24" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>903137.09265965922</v>
       </c>
       <c r="K24" s="4">
         <f t="shared" si="3"/>
-        <v>2232937</v>
+        <v>1691054.7444042044</v>
       </c>
       <c r="L24" s="63" cm="1">
         <f t="array" ref="L24">+_xlfn.IFS(I24&gt;114%,H24*0.02,I24&gt;109%,H24*0.015,I24&gt;104%,H24*0.0125,I24&gt;99%,H24*0.01,I24&lt;99%,H24*0)</f>
@@ -4854,34 +4854,34 @@
       </c>
       <c r="D26" s="67">
         <f>+SUM(D17:D25)</f>
-        <v>79268262.284777522</v>
+        <v>100418882.659999</v>
       </c>
       <c r="E26" s="65">
         <v>82031490.568011329</v>
       </c>
       <c r="F26" s="67">
         <f>+D26-E26</f>
-        <v>-2763228.2832338065</v>
+        <v>18387392.091987669</v>
       </c>
       <c r="G26" s="66">
         <f t="shared" si="1"/>
-        <v>0.27726000080800778</v>
+        <v>0.35123943284420017</v>
       </c>
       <c r="H26" s="64">
         <f t="shared" si="4"/>
-        <v>211382032.75940672</v>
+        <v>267783687.09333068</v>
       </c>
       <c r="I26" s="66">
         <f t="shared" si="2"/>
-        <v>0.73936000215468733</v>
+        <v>0.93663848758453383</v>
       </c>
       <c r="J26" s="64">
         <f t="shared" si="5"/>
-        <v>8807584.6983086132</v>
+        <v>11157653.628888778</v>
       </c>
       <c r="K26" s="67">
         <f t="shared" si="3"/>
-        <v>13775359.747214833</v>
+        <v>12365318.388866734</v>
       </c>
       <c r="L26" s="68"/>
     </row>
@@ -5512,34 +5512,34 @@
       </c>
       <c r="D41" s="81">
         <f>+D40+D26+D10+D16</f>
-        <v>449316617.9851948</v>
+        <v>470467238.36041617</v>
       </c>
       <c r="E41" s="82">
         <v>397625858.39552885</v>
       </c>
       <c r="F41" s="81">
         <f>+D41-E41</f>
-        <v>51690759.589665949</v>
+        <v>72841379.964887321</v>
       </c>
       <c r="G41" s="83">
         <f t="shared" si="1"/>
-        <v>0.32564669983033401</v>
+        <v>0.34097582287822004</v>
       </c>
       <c r="H41" s="81">
         <f t="shared" si="4"/>
-        <v>1198177647.9605193</v>
+        <v>1254579302.2944431</v>
       </c>
       <c r="I41" s="83">
         <f t="shared" si="2"/>
-        <v>0.86839119954755728</v>
+        <v>0.90926886100858684</v>
       </c>
       <c r="J41" s="81">
         <f t="shared" si="5"/>
-        <v>49924068.665021643</v>
+        <v>52274137.595601797</v>
       </c>
       <c r="K41" s="81">
         <f t="shared" si="3"/>
-        <v>62030035.273862749</v>
+        <v>60619993.915514663</v>
       </c>
       <c r="L41" s="84"/>
     </row>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="C16" s="12" t="str">
         <f>+AVANCE!B22</f>
-        <v>31 - BARTSCHAT EMILIANO NAHUEL</v>
+        <v>31 - RENZO RAMOS</v>
       </c>
       <c r="D16" s="22">
         <f t="shared" si="0"/>
@@ -6552,7 +6552,7 @@
       </c>
       <c r="C17" s="13" t="str">
         <f>+AVANCE!B24</f>
-        <v>54 - CAÑETE DIEGO</v>
+        <v>54 - BARTSCHAT EMILIANO NAHUEL</v>
       </c>
       <c r="D17" s="22">
         <f t="shared" si="0"/>

--- a/data/ventas.xlsx
+++ b/data/ventas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cesar\Desktop\Reportes Ventas Rap\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E5DB899-2851-4ED1-8092-A74C6D5B7C1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A26E35A1-85C9-4B96-A606-D43697F9660D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -956,6 +956,7 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="41">
@@ -2540,22 +2541,22 @@
         <v>0</v>
       </c>
       <c r="C2" s="96">
-        <v>36360.698065472701</v>
+        <v>41928.631166658197</v>
       </c>
       <c r="D2" s="96">
-        <v>189518.4324835093</v>
+        <v>207302.19131536529</v>
       </c>
       <c r="E2" s="96">
-        <v>594107844.49346352</v>
+        <v>677561890.16147554</v>
       </c>
       <c r="F2" s="96">
         <v>0</v>
       </c>
       <c r="G2" s="96">
-        <v>297915.18096689001</v>
+        <v>332451.74828047713</v>
       </c>
       <c r="H2" s="96">
-        <v>297915.34000000003</v>
+        <v>332451.90999999997</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -2566,22 +2567,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="96">
-        <v>442.75209694799997</v>
+        <v>500.14311877310001</v>
       </c>
       <c r="D3" s="96">
-        <v>813.20675760330005</v>
+        <v>880.13180968409995</v>
       </c>
       <c r="E3" s="96">
-        <v>9930506.0322296303</v>
+        <v>11081724.942682527</v>
       </c>
       <c r="F3" s="96">
         <v>0</v>
       </c>
       <c r="G3" s="96">
-        <v>297915.18096689001</v>
+        <v>332451.74828047713</v>
       </c>
       <c r="H3" s="96">
-        <v>297915.34000000003</v>
+        <v>332451.90999999997</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2592,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="C4" s="96">
-        <v>268.42818253809997</v>
+        <v>287.18810317290001</v>
       </c>
       <c r="D4" s="96">
-        <v>484.74910714139997</v>
+        <v>527.75910714140002</v>
       </c>
       <c r="E4" s="96">
-        <v>7416441.7657084363</v>
+        <v>7935947.3890327429</v>
       </c>
       <c r="F4" s="96">
         <v>0</v>
@@ -2618,13 +2619,13 @@
         <v>1</v>
       </c>
       <c r="C5" s="96">
-        <v>357.47226190290002</v>
+        <v>396.25083333129999</v>
       </c>
       <c r="D5" s="96">
-        <v>1231.5221071393</v>
+        <v>1278.5221071381</v>
       </c>
       <c r="E5" s="96">
-        <v>8097618.1083014421</v>
+        <v>8747383.1666885894</v>
       </c>
       <c r="F5" s="96">
         <v>0</v>
@@ -2644,13 +2645,13 @@
         <v>1</v>
       </c>
       <c r="C6" s="96">
-        <v>806.83978174499998</v>
+        <v>852.71874999889997</v>
       </c>
       <c r="D6" s="96">
-        <v>2090.7614881134</v>
+        <v>2348.9985714469999</v>
       </c>
       <c r="E6" s="96">
-        <v>15645728.431611888</v>
+        <v>16797290.894173365</v>
       </c>
       <c r="F6" s="96">
         <v>0</v>
@@ -2670,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="C7" s="96">
-        <v>699.55609920439997</v>
+        <v>771.12899602920004</v>
       </c>
       <c r="D7" s="96">
-        <v>2280.2210119055999</v>
+        <v>2640.9885119064002</v>
       </c>
       <c r="E7" s="96">
-        <v>13226460.381280242</v>
+        <v>14914934.086527392</v>
       </c>
       <c r="F7" s="96">
         <v>0</v>
@@ -2696,13 +2697,13 @@
         <v>1</v>
       </c>
       <c r="C8" s="96">
-        <v>2271.2782407408999</v>
+        <v>2434.2782407408999</v>
       </c>
       <c r="D8" s="96">
-        <v>2665.9464768541998</v>
+        <v>3889.9464768542002</v>
       </c>
       <c r="E8" s="96">
-        <v>28457978.498885799</v>
+        <v>33451176.522885799</v>
       </c>
       <c r="F8" s="96">
         <v>0</v>
@@ -2722,13 +2723,13 @@
         <v>1</v>
       </c>
       <c r="C9" s="96">
-        <v>407.30359126960002</v>
+        <v>492.95461507919998</v>
       </c>
       <c r="D9" s="96">
-        <v>1735.8554166650999</v>
+        <v>2075.5115416671001</v>
       </c>
       <c r="E9" s="96">
-        <v>7404424.1934615131</v>
+        <v>8806933.4567012265</v>
       </c>
       <c r="F9" s="96">
         <v>0</v>
@@ -2748,13 +2749,13 @@
         <v>1</v>
       </c>
       <c r="C10" s="96">
-        <v>258.18834325389997</v>
+        <v>421.65004960290003</v>
       </c>
       <c r="D10" s="96">
-        <v>1001.6023979274</v>
+        <v>1037.2136479307001</v>
       </c>
       <c r="E10" s="96">
-        <v>8509221.7116328403</v>
+        <v>9823471.9917300809</v>
       </c>
       <c r="F10" s="96">
         <v>0</v>
@@ -2774,13 +2775,13 @@
         <v>1</v>
       </c>
       <c r="C11" s="96">
-        <v>290.60501190309998</v>
+        <v>387.68936904610001</v>
       </c>
       <c r="D11" s="96">
-        <v>922.06959523789999</v>
+        <v>962.63459523810002</v>
       </c>
       <c r="E11" s="96">
-        <v>5611548.663038048</v>
+        <v>6665534.1859788187</v>
       </c>
       <c r="F11" s="96">
         <v>0</v>
@@ -2800,13 +2801,13 @@
         <v>1</v>
       </c>
       <c r="C12" s="96">
-        <v>642.36189682300005</v>
+        <v>679.03967460050001</v>
       </c>
       <c r="D12" s="96">
-        <v>3208.0478690399</v>
+        <v>3407.0478690399</v>
       </c>
       <c r="E12" s="96">
-        <v>10222287.133025508</v>
+        <v>10931376.163111016</v>
       </c>
       <c r="F12" s="96">
         <v>0</v>
@@ -2826,13 +2827,13 @@
         <v>1</v>
       </c>
       <c r="C13" s="96">
-        <v>524.17395237999995</v>
+        <v>871.83837301480003</v>
       </c>
       <c r="D13" s="96">
-        <v>1740.8193690511</v>
+        <v>1883.8193690534999</v>
       </c>
       <c r="E13" s="96">
-        <v>11920566.462441558</v>
+        <v>14492216.412792483</v>
       </c>
       <c r="F13" s="96">
         <v>0</v>
@@ -2852,13 +2853,13 @@
         <v>1</v>
       </c>
       <c r="C14" s="96">
-        <v>3301.3271825398001</v>
+        <v>3687.1787698415001</v>
       </c>
       <c r="D14" s="96">
-        <v>32008.832499996799</v>
+        <v>34116.466666663298</v>
       </c>
       <c r="E14" s="96">
-        <v>54947546.702784903</v>
+        <v>59180827.134406224</v>
       </c>
       <c r="F14" s="96">
         <v>0</v>
@@ -2878,13 +2879,13 @@
         <v>1</v>
       </c>
       <c r="C15" s="96">
-        <v>653.42529761749995</v>
+        <v>695.49613095029997</v>
       </c>
       <c r="D15" s="96">
-        <v>2323.3916666609998</v>
+        <v>2584.5916666585999</v>
       </c>
       <c r="E15" s="96">
-        <v>11854719.440338746</v>
+        <v>12686900.332479352</v>
       </c>
       <c r="F15" s="96">
         <v>0</v>
@@ -2904,13 +2905,13 @@
         <v>1</v>
       </c>
       <c r="C16" s="96">
-        <v>351.44507936330001</v>
+        <v>372.736309522</v>
       </c>
       <c r="D16" s="96">
-        <v>1753.0385119133</v>
+        <v>1829.9713690543999</v>
       </c>
       <c r="E16" s="96">
-        <v>9015875.5390208997</v>
+        <v>9582764.4529769439</v>
       </c>
       <c r="F16" s="96">
         <v>0</v>
@@ -2930,13 +2931,13 @@
         <v>1</v>
       </c>
       <c r="C17" s="96">
-        <v>723.14480158490005</v>
+        <v>840.47349206139995</v>
       </c>
       <c r="D17" s="96">
-        <v>1961.8446190520999</v>
+        <v>2245.6983690565999</v>
       </c>
       <c r="E17" s="96">
-        <v>14059558.299505398</v>
+        <v>16167381.13479867</v>
       </c>
       <c r="F17" s="96">
         <v>0</v>
@@ -2956,13 +2957,13 @@
         <v>1</v>
       </c>
       <c r="C18" s="96">
-        <v>902.89089285620003</v>
+        <v>971.22653571319995</v>
       </c>
       <c r="D18" s="96">
-        <v>3941.1758690411002</v>
+        <v>4114.9628690424997</v>
       </c>
       <c r="E18" s="96">
-        <v>17439906.551381622</v>
+        <v>19062578.988594737</v>
       </c>
       <c r="F18" s="96">
         <v>0</v>
@@ -2982,13 +2983,13 @@
         <v>1</v>
       </c>
       <c r="C19" s="96">
-        <v>813.47657407259999</v>
+        <v>939.20582407220002</v>
       </c>
       <c r="D19" s="96">
-        <v>2893.2247261999</v>
+        <v>3457.2247262034998</v>
       </c>
       <c r="E19" s="96">
-        <v>15820251.940252023</v>
+        <v>18556073.997634564</v>
       </c>
       <c r="F19" s="96">
         <v>0</v>
@@ -3008,13 +3009,13 @@
         <v>1</v>
       </c>
       <c r="C20" s="96">
-        <v>2976.6077182544</v>
+        <v>3071.8499801587</v>
       </c>
       <c r="D20" s="96">
-        <v>13411.3243333307</v>
+        <v>13712.0793333276</v>
       </c>
       <c r="E20" s="96">
-        <v>41338677.54260511</v>
+        <v>45072979.61650601</v>
       </c>
       <c r="F20" s="96">
         <v>0</v>
@@ -3034,13 +3035,13 @@
         <v>1</v>
       </c>
       <c r="C21" s="96">
-        <v>377.26049602939997</v>
+        <v>420.4204166641</v>
       </c>
       <c r="D21" s="96">
-        <v>1435.7342142929001</v>
+        <v>1629.9108809618001</v>
       </c>
       <c r="E21" s="96">
-        <v>8244716.2501042979</v>
+        <v>9684737.8484921921</v>
       </c>
       <c r="F21" s="96">
         <v>0</v>
@@ -3060,13 +3061,13 @@
         <v>1</v>
       </c>
       <c r="C22" s="96">
-        <v>318.46501190359999</v>
+        <v>348.21431745899997</v>
       </c>
       <c r="D22" s="96">
-        <v>1015.5265238078</v>
+        <v>1238.0315238086</v>
       </c>
       <c r="E22" s="96">
-        <v>5567175.7313747797</v>
+        <v>6222492.2724699304</v>
       </c>
       <c r="F22" s="96">
         <v>0</v>
@@ -3086,13 +3087,13 @@
         <v>1</v>
       </c>
       <c r="C23" s="96">
-        <v>963.42337301489999</v>
+        <v>1923.2949206333999</v>
       </c>
       <c r="D23" s="96">
-        <v>6410.1771547587996</v>
+        <v>10953.3035833293</v>
       </c>
       <c r="E23" s="96">
-        <v>20358292.590482842</v>
+        <v>36341982.308257863</v>
       </c>
       <c r="F23" s="96">
         <v>0</v>
@@ -3112,13 +3113,13 @@
         <v>1</v>
       </c>
       <c r="C24" s="96">
-        <v>1862.3525793652</v>
+        <v>1862.3213293652</v>
       </c>
       <c r="D24" s="96">
         <v>15300.7601488083</v>
       </c>
       <c r="E24" s="96">
-        <v>32533139.2798471</v>
+        <v>32504670.724847101</v>
       </c>
       <c r="F24" s="96">
         <v>0</v>
@@ -3138,13 +3139,13 @@
         <v>1</v>
       </c>
       <c r="C25" s="96">
-        <v>457.83190476089999</v>
+        <v>515.25296825299995</v>
       </c>
       <c r="D25" s="96">
-        <v>1735.0420833439</v>
+        <v>1997.2391666768001</v>
       </c>
       <c r="E25" s="96">
-        <v>8331163.463863492</v>
+        <v>9407600.5395302419</v>
       </c>
       <c r="F25" s="96">
         <v>0</v>
@@ -3164,13 +3165,13 @@
         <v>1</v>
       </c>
       <c r="C26" s="96">
-        <v>312.9566071415</v>
+        <v>454.00863095120002</v>
       </c>
       <c r="D26" s="96">
-        <v>884.78791666810002</v>
+        <v>959.78791666929999</v>
       </c>
       <c r="E26" s="96">
-        <v>5482149.478754703</v>
+        <v>6448364.3120282274</v>
       </c>
       <c r="F26" s="96">
         <v>0</v>
@@ -3190,13 +3191,13 @@
         <v>1</v>
       </c>
       <c r="C27" s="96">
-        <v>3686.5</v>
+        <v>5166.5</v>
       </c>
       <c r="D27" s="96">
         <v>15335.54</v>
       </c>
       <c r="E27" s="96">
-        <v>38194190.065520003</v>
+        <v>50661514.217519999</v>
       </c>
       <c r="F27" s="96">
         <v>0</v>
@@ -3216,13 +3217,13 @@
         <v>1</v>
       </c>
       <c r="C28" s="96">
-        <v>666.16360780230002</v>
+        <v>705.33491732590005</v>
       </c>
       <c r="D28" s="96">
-        <v>2898.6280878054999</v>
+        <v>3127.0876711410001</v>
       </c>
       <c r="E28" s="96">
-        <v>13022386.541284554</v>
+        <v>13932220.499480665</v>
       </c>
       <c r="F28" s="96">
         <v>0</v>
@@ -3242,13 +3243,13 @@
         <v>1</v>
       </c>
       <c r="C29" s="96">
-        <v>2331.5627380954002</v>
+        <v>2601.9821825396998</v>
       </c>
       <c r="D29" s="96">
-        <v>6328.3620833379</v>
+        <v>7049.6216666716</v>
       </c>
       <c r="E29" s="96">
-        <v>30033987.082212482</v>
+        <v>33450220.947755333</v>
       </c>
       <c r="F29" s="96">
         <v>0</v>
@@ -3268,13 +3269,13 @@
         <v>1</v>
       </c>
       <c r="C30" s="96">
-        <v>228.48978174600001</v>
+        <v>259.70168650789998</v>
       </c>
       <c r="D30" s="96">
-        <v>951.225833341</v>
+        <v>1219.7308333378</v>
       </c>
       <c r="E30" s="96">
-        <v>4657516.3901073569</v>
+        <v>5618690.4157067938</v>
       </c>
       <c r="F30" s="96">
         <v>0</v>
@@ -3294,13 +3295,13 @@
         <v>1</v>
       </c>
       <c r="C31" s="96">
-        <v>308.55198412530001</v>
+        <v>328.83323412499999</v>
       </c>
       <c r="D31" s="96">
-        <v>696.84250000010002</v>
+        <v>741.89249999850006</v>
       </c>
       <c r="E31" s="96">
-        <v>5212708.9840588067</v>
+        <v>5777964.8325451156</v>
       </c>
       <c r="F31" s="96">
         <v>0</v>
@@ -3320,13 +3321,13 @@
         <v>1</v>
       </c>
       <c r="C32" s="96">
-        <v>167.07162698400001</v>
+        <v>174.87857142839999</v>
       </c>
       <c r="D32" s="96">
-        <v>587.41874999870004</v>
+        <v>674.03041666670003</v>
       </c>
       <c r="E32" s="96">
-        <v>3564392.4785372978</v>
+        <v>3802949.3075159392</v>
       </c>
       <c r="F32" s="96">
         <v>0</v>
@@ -3346,13 +3347,13 @@
         <v>1</v>
       </c>
       <c r="C33" s="96">
-        <v>399.29178571360001</v>
+        <v>471.37511904659999</v>
       </c>
       <c r="D33" s="96">
-        <v>1439.6110000041999</v>
+        <v>1852.1960000014001</v>
       </c>
       <c r="E33" s="96">
-        <v>7023786.2862272449</v>
+        <v>8588184.3117468338</v>
       </c>
       <c r="F33" s="96">
         <v>0</v>
@@ -3372,13 +3373,13 @@
         <v>1</v>
       </c>
       <c r="C34" s="96">
-        <v>25.288194444399998</v>
+        <v>67.860218253900001</v>
       </c>
       <c r="D34" s="96">
-        <v>354.02</v>
+        <v>852.25708333290004</v>
       </c>
       <c r="E34" s="96">
-        <v>715253.15687714703</v>
+        <v>1880938.5392911113</v>
       </c>
       <c r="F34" s="96">
         <v>0</v>
@@ -3424,13 +3425,13 @@
         <v>1</v>
       </c>
       <c r="C36" s="96">
-        <v>660.91938491940004</v>
+        <v>738.56251190319995</v>
       </c>
       <c r="D36" s="96">
-        <v>1829.4147023833</v>
+        <v>2450.4147023866999</v>
       </c>
       <c r="E36" s="96">
-        <v>11034688.327347409</v>
+        <v>12619217.089428457</v>
       </c>
       <c r="F36" s="96">
         <v>0</v>
@@ -3476,13 +3477,13 @@
         <v>1</v>
       </c>
       <c r="C38" s="96">
-        <v>465.39242424230002</v>
+        <v>543.83686868660004</v>
       </c>
       <c r="D38" s="96">
-        <v>5421.5099999988997</v>
+        <v>6586.7099999968004</v>
       </c>
       <c r="E38" s="96">
-        <v>10126859.110729419</v>
+        <v>12063016.447646325</v>
       </c>
       <c r="F38" s="96">
         <v>0</v>
@@ -3502,13 +3503,13 @@
         <v>1</v>
       </c>
       <c r="C39" s="96">
-        <v>1099.0833333333001</v>
+        <v>1148.5833333333001</v>
       </c>
       <c r="D39" s="96">
-        <v>13338.5399999982</v>
+        <v>14031.3499999982</v>
       </c>
       <c r="E39" s="96">
-        <v>23985001.331072558</v>
+        <v>25192644.671372555</v>
       </c>
       <c r="F39" s="96">
         <v>0</v>
@@ -3528,13 +3529,13 @@
         <v>1</v>
       </c>
       <c r="C40" s="96">
-        <v>806.41085978859996</v>
+        <v>919.90530423300004</v>
       </c>
       <c r="D40" s="96">
-        <v>4559.2816415463003</v>
+        <v>5011.6447367884002</v>
       </c>
       <c r="E40" s="96">
-        <v>8128233.8339369334</v>
+        <v>10463850.92498962</v>
       </c>
       <c r="F40" s="96">
         <v>0</v>
@@ -3554,13 +3555,13 @@
         <v>1</v>
       </c>
       <c r="C41" s="96">
-        <v>1673.2005158728</v>
+        <v>1673.1505158728</v>
       </c>
       <c r="D41" s="96">
-        <v>9762.1595238119007</v>
+        <v>9756.1595238119007</v>
       </c>
       <c r="E41" s="96">
-        <v>19638670.354043003</v>
+        <v>19594052.122893002</v>
       </c>
       <c r="F41" s="96">
         <v>0</v>
@@ -3580,13 +3581,13 @@
         <v>1</v>
       </c>
       <c r="C42" s="96">
-        <v>112.0611111111</v>
+        <v>162.06111111109999</v>
       </c>
       <c r="D42" s="96">
-        <v>1639.5799999999001</v>
+        <v>2287.8899999998998</v>
       </c>
       <c r="E42" s="96">
-        <v>2767832.4172995184</v>
+        <v>4305943.4722995181</v>
       </c>
       <c r="F42" s="96">
         <v>0</v>
@@ -3658,13 +3659,13 @@
         <v>1</v>
       </c>
       <c r="C45" s="96">
-        <v>359.1312896833</v>
+        <v>381.49339285799999</v>
       </c>
       <c r="D45" s="96">
-        <v>3307.8991916711002</v>
+        <v>3434.3270488133999</v>
       </c>
       <c r="E45" s="96">
-        <v>7281079.6085403729</v>
+        <v>7757835.1522215344</v>
       </c>
       <c r="F45" s="96">
         <v>0</v>
@@ -3719,7 +3720,7 @@
     <col min="2" max="2" width="48" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.42578125" style="2" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="18.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="18.85546875" style="2" bestFit="1" customWidth="1"/>
@@ -3779,44 +3780,44 @@
       </c>
       <c r="D2" s="59">
         <f>IFERROR(+VLOOKUP(B2,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>19062578.988594737</v>
+      </c>
+      <c r="E2" s="59">
         <v>17439906.551381622</v>
-      </c>
-      <c r="E2" s="59">
-        <v>16024694.976201845</v>
       </c>
       <c r="F2" s="59">
         <f t="shared" ref="F2:F9" si="0">+D2-E2</f>
-        <v>1415211.5751797762</v>
+        <v>1622672.4372131154</v>
       </c>
       <c r="G2" s="60">
         <f t="shared" ref="G2:G41" si="1">+D2/C2</f>
-        <v>0.54028517441280544</v>
+        <v>0.59055527523998486</v>
       </c>
       <c r="H2" s="59">
         <f>+D2/$N$3*$N$4</f>
-        <v>46506417.470350988</v>
+        <v>45750189.572627366</v>
       </c>
       <c r="I2" s="60">
         <f t="shared" ref="I2:I41" si="2">+H2/C2</f>
-        <v>1.4407604651008143</v>
+        <v>1.4173326605759635</v>
       </c>
       <c r="J2" s="59">
         <f>+D2/$N$3</f>
-        <v>1937767.3945979578</v>
+        <v>1906257.8988594736</v>
       </c>
       <c r="K2" s="59">
         <f t="shared" ref="K2:K41" si="3">+(C2-D2)/$N$2</f>
-        <v>989278.00579127541</v>
+        <v>944035.54640400119</v>
       </c>
       <c r="L2" s="61" cm="1">
         <f t="array" ref="L2">+_xlfn.IFS(I2&gt;114%,H2*0.02,I2&gt;109%,H2*0.015,I2&gt;104%,H2*0.0125,I2&gt;99%,H2*0.01,I2&lt;99%,H2*0)</f>
-        <v>930128.34940701979</v>
+        <v>915003.7914525473</v>
       </c>
       <c r="M2" s="53" t="s">
         <v>36</v>
       </c>
       <c r="N2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -3829,45 +3830,45 @@
       </c>
       <c r="D3" s="4">
         <f>IFERROR(+VLOOKUP(B3,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>16167381.13479867</v>
+      </c>
+      <c r="E3" s="4">
         <v>14059558.299505398</v>
-      </c>
-      <c r="E3" s="4">
-        <v>12180676.72377059</v>
       </c>
       <c r="F3" s="4">
         <f t="shared" si="0"/>
-        <v>1878881.5757348072</v>
+        <v>2107822.8352932725</v>
       </c>
       <c r="G3" s="5">
         <f t="shared" si="1"/>
-        <v>0.45378696860813894</v>
+        <v>0.52181915812752067</v>
       </c>
       <c r="H3" s="4">
         <f t="shared" ref="H3:H41" si="4">+D3/$N$3*$N$4</f>
-        <v>37492155.46534773</v>
+        <v>38801714.723516807</v>
       </c>
       <c r="I3" s="5">
         <f t="shared" si="2"/>
-        <v>1.2100985829550372</v>
+        <v>1.2523659795060496</v>
       </c>
       <c r="J3" s="4">
         <f t="shared" ref="J3:J41" si="5">+D3/$N$3</f>
-        <v>1562173.1443894887</v>
+        <v>1616738.1134798671</v>
       </c>
       <c r="K3" s="4">
         <f t="shared" si="3"/>
-        <v>1128211.3252918571</v>
+        <v>1058239.0745774703</v>
       </c>
       <c r="L3" s="63" cm="1">
         <f t="array" ref="L3">+_xlfn.IFS(I3&gt;114%,H3*0.02,I3&gt;109%,H3*0.015,I3&gt;104%,H3*0.0125,I3&gt;99%,H3*0.01,I3&lt;99%,H3*0)</f>
-        <v>749843.10930695466</v>
+        <v>776034.29447033617</v>
       </c>
       <c r="M3" s="53" t="s">
         <v>40</v>
       </c>
       <c r="N3">
         <f>N4-N2</f>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -3880,38 +3881,38 @@
       </c>
       <c r="D4" s="4">
         <f>IFERROR(+VLOOKUP(B4,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>12686900.332479352</v>
+      </c>
+      <c r="E4" s="4">
         <v>11854719.440338746</v>
-      </c>
-      <c r="E4" s="4">
-        <v>9837944.9718231615</v>
       </c>
       <c r="F4" s="4">
         <f t="shared" si="0"/>
-        <v>2016774.4685155842</v>
+        <v>832180.89214060642</v>
       </c>
       <c r="G4" s="5">
         <f t="shared" si="1"/>
-        <v>0.41756626936087565</v>
+        <v>0.44687870246512368</v>
       </c>
       <c r="H4" s="4">
         <f t="shared" si="4"/>
-        <v>31612585.174236655</v>
+        <v>30448560.797950443</v>
       </c>
       <c r="I4" s="5">
         <f t="shared" si="2"/>
-        <v>1.1135100516290017</v>
+        <v>1.0725088859162968</v>
       </c>
       <c r="J4" s="4">
         <f t="shared" si="5"/>
-        <v>1317191.0489265274</v>
+        <v>1268690.0332479351</v>
       </c>
       <c r="K4" s="4">
         <f t="shared" si="3"/>
-        <v>1102354.1213206339</v>
+        <v>1121652.2091192072</v>
       </c>
       <c r="L4" s="63" cm="1">
         <f t="array" ref="L4">+_xlfn.IFS(I4&gt;114%,H4*0.02,I4&gt;109%,H4*0.015,I4&gt;104%,H4*0.0125,I4&gt;99%,H4*0.01,I4&lt;99%,H4*0)</f>
-        <v>474188.77761354978</v>
+        <v>380607.00997438055</v>
       </c>
       <c r="M4" s="53" t="s">
         <v>47</v>
@@ -3930,38 +3931,38 @@
       </c>
       <c r="D5" s="4">
         <f>IFERROR(+VLOOKUP(B5,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>14492216.412792483</v>
+      </c>
+      <c r="E5" s="4">
         <v>11920566.462441558</v>
-      </c>
-      <c r="E5" s="4">
-        <v>10185885.70934353</v>
       </c>
       <c r="F5" s="4">
         <f t="shared" si="0"/>
-        <v>1734680.7530980278</v>
+        <v>2571649.9503509253</v>
       </c>
       <c r="G5" s="5">
         <f t="shared" si="1"/>
-        <v>0.41988564060423328</v>
+        <v>0.51046849085846357</v>
       </c>
       <c r="H5" s="4">
         <f t="shared" si="4"/>
-        <v>31788177.233177491</v>
+        <v>34781319.390701957</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" si="2"/>
-        <v>1.119695041611289</v>
+        <v>1.2251243780603125</v>
       </c>
       <c r="J5" s="4">
         <f t="shared" si="5"/>
-        <v>1324507.3847157287</v>
+        <v>1449221.6412792483</v>
       </c>
       <c r="K5" s="4">
         <f t="shared" si="3"/>
-        <v>1097964.319847113</v>
+        <v>992701.06052541209</v>
       </c>
       <c r="L5" s="63" cm="1">
         <f t="array" ref="L5">+_xlfn.IFS(I5&gt;114%,H5*0.02,I5&gt;109%,H5*0.015,I5&gt;104%,H5*0.0125,I5&gt;99%,H5*0.01,I5&lt;99%,H5*0)</f>
-        <v>476822.65849766234</v>
+        <v>695626.38781403913</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
@@ -3974,38 +3975,38 @@
       </c>
       <c r="D6" s="4">
         <f>IFERROR(+VLOOKUP(B6,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>10931376.163111016</v>
+      </c>
+      <c r="E6" s="4">
         <v>10222287.133025508</v>
-      </c>
-      <c r="E6" s="4">
-        <v>8765227.9594276343</v>
       </c>
       <c r="F6" s="4">
         <f t="shared" si="0"/>
-        <v>1457059.1735978741</v>
+        <v>709089.03008550778</v>
       </c>
       <c r="G6" s="5">
         <f t="shared" si="1"/>
-        <v>0.43445989249117684</v>
+        <v>0.46459705649064303</v>
       </c>
       <c r="H6" s="4">
         <f t="shared" si="4"/>
-        <v>27259432.354734689</v>
+        <v>26235302.791466441</v>
       </c>
       <c r="I6" s="5">
         <f t="shared" si="2"/>
-        <v>1.1585597133098049</v>
+        <v>1.1150329355775432</v>
       </c>
       <c r="J6" s="4">
         <f t="shared" si="5"/>
-        <v>1135809.6814472787</v>
+        <v>1093137.6163111017</v>
       </c>
       <c r="K6" s="4">
         <f t="shared" si="3"/>
-        <v>887095.82696630782</v>
+        <v>899810.59817207919</v>
       </c>
       <c r="L6" s="63" cm="1">
         <f t="array" ref="L6">+_xlfn.IFS(I6&gt;114%,H6*0.02,I6&gt;109%,H6*0.015,I6&gt;104%,H6*0.0125,I6&gt;99%,H6*0.01,I6&lt;99%,H6*0)</f>
-        <v>545188.64709469373</v>
+        <v>393529.5418719966</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
@@ -4018,34 +4019,34 @@
       </c>
       <c r="D7" s="4">
         <f>IFERROR(+VLOOKUP(B7,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>8806933.4567012265</v>
+      </c>
+      <c r="E7" s="4">
         <v>7404424.1934615131</v>
-      </c>
-      <c r="E7" s="4">
-        <v>5878949.2572204797</v>
       </c>
       <c r="F7" s="4">
         <f t="shared" ref="F7:F8" si="6">+D7-E7</f>
-        <v>1525474.9362410335</v>
+        <v>1402509.2632397134</v>
       </c>
       <c r="G7" s="5">
         <f t="shared" si="1"/>
-        <v>0.26690441758568656</v>
+        <v>0.31746012702141607</v>
       </c>
       <c r="H7" s="4">
         <f t="shared" si="4"/>
-        <v>19745131.182564035</v>
+        <v>21136640.296082944</v>
       </c>
       <c r="I7" s="5">
         <f t="shared" si="2"/>
-        <v>0.7117451135618309</v>
+        <v>0.76190430485139859</v>
       </c>
       <c r="J7" s="4">
         <f t="shared" si="5"/>
-        <v>822713.7992735015</v>
+        <v>880693.34567012265</v>
       </c>
       <c r="K7" s="4">
         <f t="shared" si="3"/>
-        <v>1355828.8558001996</v>
+        <v>1352494.5409830913</v>
       </c>
       <c r="L7" s="63" cm="1">
         <f t="array" ref="L7">+_xlfn.IFS(I7&gt;114%,H7*0.02,I7&gt;109%,H7*0.015,I7&gt;104%,H7*0.0125,I7&gt;99%,H7*0.01,I7&lt;99%,H7*0)</f>
@@ -4062,38 +4063,38 @@
       </c>
       <c r="D8" s="4">
         <f>IFERROR(+VLOOKUP(B8,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>14914934.086527392</v>
+      </c>
+      <c r="E8" s="4">
         <v>13226460.381280242</v>
-      </c>
-      <c r="E8" s="4">
-        <v>11328941.073388485</v>
       </c>
       <c r="F8" s="4">
         <f t="shared" si="6"/>
-        <v>1897519.3078917563</v>
+        <v>1688473.7052471507</v>
       </c>
       <c r="G8" s="5">
         <f t="shared" si="1"/>
-        <v>0.36913382319445087</v>
+        <v>0.41625699418759998</v>
       </c>
       <c r="H8" s="4">
         <f t="shared" si="4"/>
-        <v>35270561.016747311</v>
+        <v>35795841.807665735</v>
       </c>
       <c r="I8" s="5">
         <f t="shared" si="2"/>
-        <v>0.98435686185186899</v>
+        <v>0.9990167860502398</v>
       </c>
       <c r="J8" s="4">
         <f t="shared" si="5"/>
-        <v>1469606.7090311379</v>
+        <v>1491493.4086527391</v>
       </c>
       <c r="K8" s="4">
         <f t="shared" si="3"/>
-        <v>1506974.0690424973</v>
+        <v>1494009.8093135937</v>
       </c>
       <c r="L8" s="63" cm="1">
         <f t="array" ref="L8">+_xlfn.IFS(I8&gt;114%,H8*0.02,I8&gt;109%,H8*0.015,I8&gt;104%,H8*0.0125,I8&gt;99%,H8*0.01,I8&lt;99%,H8*0)</f>
-        <v>0</v>
+        <v>357958.41807665734</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
@@ -4106,38 +4107,38 @@
       </c>
       <c r="D9" s="4">
         <f>IFERROR(+VLOOKUP(B9,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>16797290.894173365</v>
+      </c>
+      <c r="E9" s="4">
         <v>15645728.431611888</v>
-      </c>
-      <c r="E9" s="4">
-        <v>13014610.776669662</v>
       </c>
       <c r="F9" s="4">
         <f t="shared" si="0"/>
-        <v>2631117.6549422257</v>
+        <v>1151562.462561477</v>
       </c>
       <c r="G9" s="5">
         <f t="shared" si="1"/>
-        <v>0.43665254241392093</v>
+        <v>0.46879119797245289</v>
       </c>
       <c r="H9" s="4">
         <f t="shared" si="4"/>
-        <v>41721942.484298371</v>
+        <v>40313498.146016076</v>
       </c>
       <c r="I9" s="5">
         <f t="shared" si="2"/>
-        <v>1.1644067797704558</v>
+        <v>1.1250988751338868</v>
       </c>
       <c r="J9" s="4">
         <f t="shared" si="5"/>
-        <v>1738414.2701790987</v>
+        <v>1679729.0894173365</v>
       </c>
       <c r="K9" s="4">
         <f t="shared" si="3"/>
-        <v>1345689.5323537211</v>
+        <v>1359555.7516245956</v>
       </c>
       <c r="L9" s="63" cm="1">
         <f t="array" ref="L9">+_xlfn.IFS(I9&gt;114%,H9*0.02,I9&gt;109%,H9*0.015,I9&gt;104%,H9*0.0125,I9&gt;99%,H9*0.01,I9&lt;99%,H9*0)</f>
-        <v>834438.84968596743</v>
+        <v>604702.4721902411</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4148,34 +4149,34 @@
       </c>
       <c r="D10" s="64">
         <f>+SUM(D2:D9)</f>
+        <v>113859611.46917823</v>
+      </c>
+      <c r="E10" s="65">
         <v>101773650.89304647</v>
-      </c>
-      <c r="E10" s="65">
-        <v>87216931.447845384</v>
       </c>
       <c r="F10" s="64">
         <f>+SUM(F2:F9)</f>
-        <v>14556719.445201084</v>
+        <v>12085960.576131769</v>
       </c>
       <c r="G10" s="66">
         <f t="shared" si="1"/>
-        <v>0.41886540549172074</v>
+        <v>0.46860706979340161</v>
       </c>
       <c r="H10" s="64">
         <f t="shared" si="4"/>
-        <v>271396402.38145727</v>
+        <v>273263067.5260278</v>
       </c>
       <c r="I10" s="66">
         <f t="shared" si="2"/>
-        <v>1.1169744146445888</v>
+        <v>1.124656967504164</v>
       </c>
       <c r="J10" s="64">
         <f t="shared" si="5"/>
-        <v>11308183.43256072</v>
+        <v>11385961.146917824</v>
       </c>
       <c r="K10" s="67">
         <f t="shared" si="3"/>
-        <v>9413396.0564136021</v>
+        <v>9222498.5907194484</v>
       </c>
       <c r="L10" s="68"/>
     </row>
@@ -4191,38 +4192,38 @@
       </c>
       <c r="D11" s="59">
         <f>IFERROR(+VLOOKUP(B11,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>45072979.61650601</v>
+      </c>
+      <c r="E11" s="59">
         <v>41338677.54260511</v>
-      </c>
-      <c r="E11" s="59">
-        <v>37584435.958896145</v>
       </c>
       <c r="F11" s="59">
         <f t="shared" ref="F11:F16" si="7">+D11-E11</f>
-        <v>3754241.5837089643</v>
+        <v>3734302.0739009008</v>
       </c>
       <c r="G11" s="60">
         <f t="shared" si="1"/>
-        <v>0.4262952141368222</v>
+        <v>0.46480431014272316</v>
       </c>
       <c r="H11" s="59">
         <f t="shared" si="4"/>
-        <v>110236473.44694695</v>
+        <v>108175151.07961442</v>
       </c>
       <c r="I11" s="60">
         <f t="shared" si="2"/>
-        <v>1.1367872376981925</v>
+        <v>1.1155303443425355</v>
       </c>
       <c r="J11" s="59">
         <f t="shared" si="5"/>
-        <v>4593186.3936227895</v>
+        <v>4507297.9616506007</v>
       </c>
       <c r="K11" s="59">
         <f t="shared" si="3"/>
-        <v>3708884.7291688267</v>
+        <v>3707069.2045451072</v>
       </c>
       <c r="L11" s="61" cm="1">
         <f t="array" ref="L11">+_xlfn.IFS(I11&gt;114%,H11*0.0125,I11&gt;109%,H11*0.01,I11&gt;104%,H11*0.0075,I11&gt;99%,H11*0.005,I11&lt;99%,H11*0)</f>
-        <v>1102364.7344694694</v>
+        <v>1081751.5107961441</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4238,11 +4239,11 @@
         <v>12726652.901956733</v>
       </c>
       <c r="E12" s="4">
-        <v>12982127.936856734</v>
+        <v>12726652.901956733</v>
       </c>
       <c r="F12" s="4">
         <f t="shared" si="7"/>
-        <v>-255475.03490000032</v>
+        <v>0</v>
       </c>
       <c r="G12" s="5">
         <f t="shared" si="1"/>
@@ -4250,23 +4251,23 @@
       </c>
       <c r="H12" s="4">
         <f t="shared" si="4"/>
-        <v>33937741.071884625</v>
+        <v>30543966.964696158</v>
       </c>
       <c r="I12" s="5">
         <f t="shared" si="2"/>
-        <v>1.0729299035962006</v>
+        <v>0.96563691323658041</v>
       </c>
       <c r="J12" s="4">
         <f t="shared" si="5"/>
-        <v>1414072.5446618593</v>
+        <v>1272665.2901956732</v>
       </c>
       <c r="K12" s="4">
         <f t="shared" si="3"/>
-        <v>1260283.3004406847</v>
+        <v>1350303.5361864478</v>
       </c>
       <c r="L12" s="63" cm="1">
         <f t="array" ref="L12">+_xlfn.IFS(I12&gt;114%,H12*0.02,I12&gt;109%,H12*0.015,I12&gt;104%,H12*0.0125,I12&gt;99%,H12*0.01,I12&lt;99%,H12*0)</f>
-        <v>424221.76339855784</v>
+        <v>0</v>
       </c>
       <c r="M12" s="27"/>
     </row>
@@ -4280,38 +4281,38 @@
       </c>
       <c r="D13" s="4">
         <f>IFERROR(+VLOOKUP(B13,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>59180827.134406224</v>
+      </c>
+      <c r="E13" s="4">
         <v>54947546.702784903</v>
-      </c>
-      <c r="E13" s="4">
-        <v>32020542.941609319</v>
       </c>
       <c r="F13" s="4">
         <f t="shared" si="7"/>
-        <v>22927003.761175584</v>
+        <v>4233280.4316213205</v>
       </c>
       <c r="G13" s="5">
         <f t="shared" si="1"/>
-        <v>0.4280606916887833</v>
+        <v>0.46103943338719244</v>
       </c>
       <c r="H13" s="4">
         <f t="shared" si="4"/>
-        <v>146526791.20742643</v>
+        <v>142033985.12257493</v>
       </c>
       <c r="I13" s="5">
         <f t="shared" si="2"/>
-        <v>1.1414951778367557</v>
+        <v>1.1064946401292617</v>
       </c>
       <c r="J13" s="4">
         <f t="shared" si="5"/>
-        <v>6105282.9669761006</v>
+        <v>5918082.7134406222</v>
       </c>
       <c r="K13" s="4">
         <f t="shared" si="3"/>
-        <v>4894424.6247893395</v>
+        <v>4941649.2100156257</v>
       </c>
       <c r="L13" s="63" cm="1">
         <f t="array" ref="L13">+_xlfn.IFS(I13&gt;114%,H13*0.0125,I13&gt;109%,H13*0.01,I13&gt;104%,H13*0.0075,I13&gt;99%,H13*0.005,I13&lt;99%,H13*0)</f>
-        <v>1831584.8900928304</v>
+        <v>1420339.8512257494</v>
       </c>
       <c r="M13" s="53" t="s">
         <v>61</v>
@@ -4330,34 +4331,34 @@
       </c>
       <c r="D14" s="4">
         <f>IFERROR(+VLOOKUP(B14,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>12063016.447646325</v>
+      </c>
+      <c r="E14" s="4">
         <v>10126859.110729419</v>
-      </c>
-      <c r="E14" s="4">
-        <v>10040043.519329419</v>
       </c>
       <c r="F14" s="4">
         <f t="shared" si="7"/>
-        <v>86815.591399999335</v>
+        <v>1936157.3369169068</v>
       </c>
       <c r="G14" s="5">
         <f t="shared" si="1"/>
-        <v>0.23856499371710921</v>
+        <v>0.28417630892021439</v>
       </c>
       <c r="H14" s="4">
         <f t="shared" si="4"/>
-        <v>27004957.628611781</v>
+        <v>28951239.474351179</v>
       </c>
       <c r="I14" s="5">
         <f t="shared" si="2"/>
-        <v>0.63617331657895781</v>
+        <v>0.68202314140851439</v>
       </c>
       <c r="J14" s="4">
         <f t="shared" si="5"/>
-        <v>1125206.5678588243</v>
+        <v>1206301.6447646325</v>
       </c>
       <c r="K14" s="4">
         <f t="shared" si="3"/>
-        <v>2154813.2189497054</v>
+        <v>2170431.4962377623</v>
       </c>
       <c r="L14" s="63" cm="1">
         <f t="array" ref="L14">+_xlfn.IFS(I14&gt;109%,H14*0.015,I14&gt;104%,H14*0.0125,I14&gt;99%,H14*0.01,I14&lt;99%,H14*0)</f>
@@ -4375,38 +4376,38 @@
       </c>
       <c r="D15" s="4">
         <f>IFERROR(+VLOOKUP(B15,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>25192644.671372555</v>
+      </c>
+      <c r="E15" s="4">
         <v>23985001.331072558</v>
-      </c>
-      <c r="E15" s="4">
-        <v>20528174.766575135</v>
       </c>
       <c r="F15" s="4">
         <f t="shared" si="7"/>
-        <v>3456826.5644974224</v>
+        <v>1207643.3402999975</v>
       </c>
       <c r="G15" s="5">
         <f t="shared" si="1"/>
-        <v>0.56503024573431015</v>
+        <v>0.59347948381899263</v>
       </c>
       <c r="H15" s="4">
         <f t="shared" si="4"/>
-        <v>63960003.549526826</v>
+        <v>60462347.211294137</v>
       </c>
       <c r="I15" s="5">
         <f t="shared" si="2"/>
-        <v>1.5067473219581604</v>
+        <v>1.4243507611655826</v>
       </c>
       <c r="J15" s="4">
         <f t="shared" si="5"/>
-        <v>2665000.1478969511</v>
+        <v>2519264.4671372557</v>
       </c>
       <c r="K15" s="4">
         <f t="shared" si="3"/>
-        <v>1230937.0709268295</v>
+        <v>1232600.9088287461</v>
       </c>
       <c r="L15" s="63" cm="1">
         <f t="array" ref="L15">+_xlfn.IFS(I15&gt;109%,H15*0.015,I15&gt;104%,H15*0.0125,I15&gt;99%,H15*0.01,I15&lt;99%,H15*0)</f>
-        <v>959400.05324290239</v>
+        <v>906935.20816941198</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4417,34 +4418,34 @@
       </c>
       <c r="D16" s="64">
         <f>+SUM(D11:D15)</f>
+        <v>154236120.77188784</v>
+      </c>
+      <c r="E16" s="65">
         <v>143124737.58914873</v>
-      </c>
-      <c r="E16" s="65">
-        <v>113155325.12326676</v>
       </c>
       <c r="F16" s="64">
         <f t="shared" si="7"/>
-        <v>29969412.465881974</v>
+        <v>11111383.182739109</v>
       </c>
       <c r="G16" s="66">
         <f t="shared" si="1"/>
-        <v>0.41865878956365116</v>
+        <v>0.45116105515394389</v>
       </c>
       <c r="H16" s="64">
         <f t="shared" si="4"/>
-        <v>381665966.90439659</v>
+        <v>370166689.85253084</v>
       </c>
       <c r="I16" s="66">
         <f t="shared" si="2"/>
-        <v>1.1164234388364029</v>
+        <v>1.0827865323694654</v>
       </c>
       <c r="J16" s="64">
         <f t="shared" si="5"/>
-        <v>15902748.621016525</v>
+        <v>15423612.077188784</v>
       </c>
       <c r="K16" s="67">
         <f t="shared" si="3"/>
-        <v>13249342.944275385</v>
+        <v>13402054.355813691</v>
       </c>
       <c r="L16" s="68"/>
     </row>
@@ -4460,34 +4461,34 @@
       </c>
       <c r="D17" s="59">
         <f>IFERROR(+VLOOKUP(B17,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>7935947.3890327429</v>
+      </c>
+      <c r="E17" s="59">
         <v>7416441.7657084363</v>
-      </c>
-      <c r="E17" s="59">
-        <v>6449843.5922434218</v>
       </c>
       <c r="F17" s="59">
         <f t="shared" ref="F17:F40" si="8">+D17-E17</f>
-        <v>966598.17346501444</v>
+        <v>519505.62332430668</v>
       </c>
       <c r="G17" s="60">
         <f t="shared" si="1"/>
-        <v>0.25279286870072071</v>
+        <v>0.27050045961494162</v>
       </c>
       <c r="H17" s="59">
         <f t="shared" si="4"/>
-        <v>19777178.041889161</v>
+        <v>19046273.733678583</v>
       </c>
       <c r="I17" s="60">
         <f t="shared" si="2"/>
-        <v>0.67411431653525511</v>
+        <v>0.64920110307585999</v>
       </c>
       <c r="J17" s="59">
         <f t="shared" si="5"/>
-        <v>824049.08507871511</v>
+        <v>793594.73890327429</v>
       </c>
       <c r="K17" s="59">
         <f t="shared" si="3"/>
-        <v>1461438.4244527712</v>
+        <v>1528719.33881909</v>
       </c>
       <c r="L17" s="61" cm="1">
         <f t="array" ref="L17">+_xlfn.IFS(I17&gt;114%,H17*0.02,I17&gt;109%,H17*0.015,I17&gt;104%,H17*0.0125,I17&gt;99%,H17*0.01,I17&lt;99%,H17*0)</f>
@@ -4504,34 +4505,34 @@
       </c>
       <c r="D18" s="4">
         <f>IFERROR(+VLOOKUP(B18,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>8747383.1666885894</v>
+      </c>
+      <c r="E18" s="4">
         <v>8097618.1083014421</v>
-      </c>
-      <c r="E18" s="4">
-        <v>6596329.3614597432</v>
       </c>
       <c r="F18" s="4">
         <f t="shared" si="8"/>
-        <v>1501288.7468416989</v>
+        <v>649765.05838714726</v>
       </c>
       <c r="G18" s="5">
         <f t="shared" si="1"/>
-        <v>0.32443022473058819</v>
+        <v>0.35046299400857084</v>
       </c>
       <c r="H18" s="4">
         <f t="shared" si="4"/>
-        <v>21593648.288803846</v>
+        <v>20993719.600052617</v>
       </c>
       <c r="I18" s="5">
         <f t="shared" si="2"/>
-        <v>0.8651472659482351</v>
+        <v>0.84111118562057019</v>
       </c>
       <c r="J18" s="4">
         <f t="shared" si="5"/>
-        <v>899735.34536682686</v>
+        <v>874738.31666885898</v>
       </c>
       <c r="K18" s="4">
         <f t="shared" si="3"/>
-        <v>1124125.8527799039</v>
+        <v>1158008.7666651008</v>
       </c>
       <c r="L18" s="63" cm="1">
         <f t="array" ref="L18">+_xlfn.IFS(I18&gt;114%,H18*0.02,I18&gt;109%,H18*0.015,I18&gt;104%,H18*0.0125,I18&gt;99%,H18*0.01,I18&lt;99%,H18*0)</f>
@@ -4548,34 +4549,34 @@
       </c>
       <c r="D19" s="4">
         <f>IFERROR(+VLOOKUP(B19,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>9582764.4529769439</v>
+      </c>
+      <c r="E19" s="4">
         <v>9015875.5390208997</v>
-      </c>
-      <c r="E19" s="4">
-        <v>7830460.6488101464</v>
       </c>
       <c r="F19" s="4">
         <f t="shared" si="8"/>
-        <v>1185414.8902107533</v>
+        <v>566888.91395604424</v>
       </c>
       <c r="G19" s="5">
         <f t="shared" si="1"/>
-        <v>0.34868691347538122</v>
+        <v>0.37061121187937296</v>
       </c>
       <c r="H19" s="4">
         <f t="shared" si="4"/>
-        <v>24042334.7707224</v>
+        <v>22998634.687144667</v>
       </c>
       <c r="I19" s="5">
         <f t="shared" si="2"/>
-        <v>0.92983176926768329</v>
+        <v>0.88946690851049515</v>
       </c>
       <c r="J19" s="4">
         <f t="shared" si="5"/>
-        <v>1001763.9487801</v>
+        <v>958276.44529769442</v>
       </c>
       <c r="K19" s="4">
         <f t="shared" si="3"/>
-        <v>1122718.3084319399</v>
+        <v>1162420.4080373612</v>
       </c>
       <c r="L19" s="63" cm="1">
         <f t="array" ref="L19">+_xlfn.IFS(I19&gt;114%,H19*0.02,I19&gt;109%,H19*0.015,I19&gt;104%,H19*0.0125,I19&gt;99%,H19*0.01,I19&lt;99%,H19*0)</f>
@@ -4592,38 +4593,38 @@
       </c>
       <c r="D20" s="4">
         <f>IFERROR(+VLOOKUP(B20,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>18556073.997634564</v>
+      </c>
+      <c r="E20" s="4">
         <v>15820251.940252023</v>
-      </c>
-      <c r="E20" s="4">
-        <v>13898645.433865212</v>
       </c>
       <c r="F20" s="4">
         <f t="shared" si="8"/>
-        <v>1921606.5063868109</v>
+        <v>2735822.0573825408</v>
       </c>
       <c r="G20" s="5">
         <f t="shared" si="1"/>
-        <v>0.47156881591468802</v>
+        <v>0.55311798295864967</v>
       </c>
       <c r="H20" s="4">
         <f t="shared" si="4"/>
-        <v>42187338.507338732</v>
+        <v>44534577.59432295</v>
       </c>
       <c r="I20" s="5">
         <f t="shared" si="2"/>
-        <v>1.2575168424391683</v>
+        <v>1.3274831591007592</v>
       </c>
       <c r="J20" s="4">
         <f t="shared" si="5"/>
-        <v>1757805.7711391137</v>
+        <v>1855607.3997634563</v>
       </c>
       <c r="K20" s="4">
         <f t="shared" si="3"/>
-        <v>1181858.5373165319</v>
+        <v>1070861.1430261026</v>
       </c>
       <c r="L20" s="63" cm="1">
         <f t="array" ref="L20">+_xlfn.IFS(I20&gt;114%,H20*0.02,I20&gt;109%,H20*0.015,I20&gt;104%,H20*0.0125,I20&gt;99%,H20*0.01,I20&lt;99%,H20*0)</f>
-        <v>843746.77014677471</v>
+        <v>890691.551886459</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4636,34 +4637,34 @@
       </c>
       <c r="D21" s="4">
         <f>IFERROR(+VLOOKUP(B21,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>9684737.8484921921</v>
+      </c>
+      <c r="E21" s="4">
         <v>8244716.2501042979</v>
-      </c>
-      <c r="E21" s="4">
-        <v>7188705.5862517217</v>
       </c>
       <c r="F21" s="4">
         <f t="shared" ref="F21:F23" si="9">+D21-E21</f>
-        <v>1056010.6638525762</v>
+        <v>1440021.5983878942</v>
       </c>
       <c r="G21" s="5">
         <f t="shared" si="1"/>
-        <v>0.32384912746678018</v>
+        <v>0.3804125947862696</v>
       </c>
       <c r="H21" s="4">
         <f t="shared" si="4"/>
-        <v>21985910.000278126</v>
+        <v>23243370.836381264</v>
       </c>
       <c r="I21" s="5">
         <f t="shared" si="2"/>
-        <v>0.86359767324474712</v>
+        <v>0.91299022748704717</v>
       </c>
       <c r="J21" s="4">
         <f t="shared" si="5"/>
-        <v>916079.58334492194</v>
+        <v>968473.78484921926</v>
       </c>
       <c r="K21" s="4">
         <f t="shared" si="3"/>
-        <v>1147586.249993047</v>
+        <v>1126698.0108219862</v>
       </c>
       <c r="L21" s="63" cm="1">
         <f t="array" ref="L21">+_xlfn.IFS(I21&gt;114%,H21*0.02,I21&gt;109%,H21*0.015,I21&gt;104%,H21*0.0125,I21&gt;99%,H21*0.01,I21&lt;99%,H21*0)</f>
@@ -4680,38 +4681,38 @@
       </c>
       <c r="D22" s="4">
         <f>IFERROR(+VLOOKUP(B22,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>13932220.499480665</v>
+      </c>
+      <c r="E22" s="4">
         <v>13022386.541284554</v>
-      </c>
-      <c r="E22" s="4">
-        <v>12482971.675436357</v>
       </c>
       <c r="F22" s="4">
         <f t="shared" si="9"/>
-        <v>539414.86584819667</v>
+        <v>909833.95819611102</v>
       </c>
       <c r="G22" s="5">
         <f t="shared" si="1"/>
-        <v>0.41024577343888341</v>
+        <v>0.43890837953629891</v>
       </c>
       <c r="H22" s="4">
         <f t="shared" si="4"/>
-        <v>34726364.110092148</v>
+        <v>33437329.198753595</v>
       </c>
       <c r="I22" s="5">
         <f t="shared" si="2"/>
-        <v>1.0939887291703558</v>
+        <v>1.0533801108871175</v>
       </c>
       <c r="J22" s="4">
         <f t="shared" si="5"/>
-        <v>1446931.837920506</v>
+        <v>1393222.0499480665</v>
       </c>
       <c r="K22" s="4">
         <f t="shared" si="3"/>
-        <v>1248033.5772476967</v>
+        <v>1272190.6928942385</v>
       </c>
       <c r="L22" s="63" cm="1">
         <f t="array" ref="L22">+_xlfn.IFS(I22&gt;114%,H22*0.02,I22&gt;109%,H22*0.015,I22&gt;104%,H22*0.0125,I22&gt;99%,H22*0.01,I22&lt;99%,H22*0)</f>
-        <v>520895.46165138221</v>
+        <v>417966.61498441995</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4724,38 +4725,38 @@
       </c>
       <c r="D23" s="4">
         <f>IFERROR(+VLOOKUP(B23,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>12619217.089428457</v>
+      </c>
+      <c r="E23" s="4">
         <v>11034688.327347409</v>
-      </c>
-      <c r="E23" s="4">
-        <v>7824662.7877200451</v>
       </c>
       <c r="F23" s="4">
         <f t="shared" si="9"/>
-        <v>3210025.5396273639</v>
+        <v>1584528.7620810475</v>
       </c>
       <c r="G23" s="5">
         <f t="shared" si="1"/>
-        <v>0.40219820504245851</v>
+        <v>0.45995195440461595</v>
       </c>
       <c r="H23" s="4">
         <f t="shared" si="4"/>
-        <v>29425835.539593089</v>
+        <v>30286121.014628299</v>
       </c>
       <c r="I23" s="5">
         <f t="shared" si="2"/>
-        <v>1.0725285467798893</v>
+        <v>1.1038846905710784</v>
       </c>
       <c r="J23" s="4">
         <f t="shared" si="5"/>
-        <v>1226076.4808163787</v>
+        <v>1261921.7089428457</v>
       </c>
       <c r="K23" s="4">
         <f t="shared" si="3"/>
-        <v>1093417.1935101731</v>
+        <v>1058337.7957551104</v>
       </c>
       <c r="L23" s="63" cm="1">
         <f t="array" ref="L23">+_xlfn.IFS(I23&gt;114%,H23*0.02,I23&gt;109%,H23*0.015,I23&gt;104%,H23*0.0125,I23&gt;99%,H23*0.01,I23&lt;99%,H23*0)</f>
-        <v>367822.94424491364</v>
+        <v>454291.81521942449</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4768,34 +4769,34 @@
       </c>
       <c r="D24" s="4">
         <f>IFERROR(+VLOOKUP(B24,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>10463850.92498962</v>
+      </c>
+      <c r="E24" s="4">
         <v>8128233.8339369334</v>
-      </c>
-      <c r="E24" s="4">
-        <v>7599049.4142421484</v>
       </c>
       <c r="F24" s="4">
         <f t="shared" si="8"/>
-        <v>529184.41969478503</v>
+        <v>2335617.0910526868</v>
       </c>
       <c r="G24" s="5">
         <f t="shared" si="1"/>
-        <v>0.24267691188591328</v>
+        <v>0.31240919993084204</v>
       </c>
       <c r="H24" s="4">
         <f t="shared" si="4"/>
-        <v>21675290.223831821</v>
+        <v>25113242.219975092</v>
       </c>
       <c r="I24" s="5">
         <f t="shared" si="2"/>
-        <v>0.64713843169576868</v>
+        <v>0.74978207983402101</v>
       </c>
       <c r="J24" s="4">
         <f t="shared" si="5"/>
-        <v>903137.09265965922</v>
+        <v>1046385.0924989621</v>
       </c>
       <c r="K24" s="4">
         <f t="shared" si="3"/>
-        <v>1691054.7444042044</v>
+        <v>1645014.5767864559</v>
       </c>
       <c r="L24" s="63" cm="1">
         <f t="array" ref="L24">+_xlfn.IFS(I24&gt;114%,H24*0.02,I24&gt;109%,H24*0.015,I24&gt;104%,H24*0.0125,I24&gt;99%,H24*0.01,I24&lt;99%,H24*0)</f>
@@ -4812,34 +4813,34 @@
       </c>
       <c r="D25" s="4">
         <f>IFERROR(+VLOOKUP(B25,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>19594052.122893002</v>
+      </c>
+      <c r="E25" s="4">
         <v>19638670.354043003</v>
-      </c>
-      <c r="E25" s="4">
-        <v>12160822.067982538</v>
       </c>
       <c r="F25" s="4">
         <f t="shared" si="8"/>
-        <v>7477848.2860604655</v>
+        <v>-44618.231150001287</v>
       </c>
       <c r="G25" s="5">
         <f t="shared" si="1"/>
-        <v>0.36324216175829638</v>
+        <v>0.36241689087974011</v>
       </c>
       <c r="H25" s="4">
         <f t="shared" si="4"/>
-        <v>52369787.610781342</v>
+        <v>47025725.09494321</v>
       </c>
       <c r="I25" s="5">
         <f t="shared" si="2"/>
-        <v>0.96864576468879038</v>
+        <v>0.86980053811137636</v>
       </c>
       <c r="J25" s="4">
         <f t="shared" si="5"/>
-        <v>2182074.4837825559</v>
+        <v>1959405.2122893003</v>
       </c>
       <c r="K25" s="4">
         <f t="shared" si="3"/>
-        <v>2295085.500730467</v>
+        <v>2462207.1958647859</v>
       </c>
       <c r="L25" s="63" cm="1">
         <f t="array" ref="L25">+_xlfn.IFS(I25&gt;109%,H25*0.015,I25&gt;104%,H25*0.0125,I25&gt;99%,H25*0.01,I25&lt;99%,H25*0)</f>
@@ -4854,34 +4855,34 @@
       </c>
       <c r="D26" s="67">
         <f>+SUM(D17:D25)</f>
+        <v>111116247.49161679</v>
+      </c>
+      <c r="E26" s="65">
         <v>100418882.659999</v>
-      </c>
-      <c r="E26" s="65">
-        <v>82031490.568011329</v>
       </c>
       <c r="F26" s="67">
         <f>+D26-E26</f>
-        <v>18387392.091987669</v>
+        <v>10697364.831617787</v>
       </c>
       <c r="G26" s="66">
         <f t="shared" si="1"/>
-        <v>0.35123943284420017</v>
+        <v>0.38865606462556163</v>
       </c>
       <c r="H26" s="64">
         <f t="shared" si="4"/>
-        <v>267783687.09333068</v>
+        <v>266678993.9798803</v>
       </c>
       <c r="I26" s="66">
         <f t="shared" si="2"/>
-        <v>0.93663848758453383</v>
+        <v>0.93277455510134788</v>
       </c>
       <c r="J26" s="64">
         <f t="shared" si="5"/>
-        <v>11157653.628888778</v>
+        <v>11111624.749161679</v>
       </c>
       <c r="K26" s="67">
         <f t="shared" si="3"/>
-        <v>12365318.388866734</v>
+        <v>12484457.928670231</v>
       </c>
       <c r="L26" s="68"/>
     </row>
@@ -4897,34 +4898,34 @@
       </c>
       <c r="D27" s="59">
         <f>IFERROR(+VLOOKUP(B27,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>33450220.947755333</v>
+      </c>
+      <c r="E27" s="59">
         <v>30033987.082212482</v>
-      </c>
-      <c r="E27" s="59">
-        <v>28353385.45531898</v>
       </c>
       <c r="F27" s="59">
         <f t="shared" si="8"/>
-        <v>1680601.6268935017</v>
+        <v>3416233.8655428514</v>
       </c>
       <c r="G27" s="60">
         <f t="shared" si="1"/>
-        <v>0.36636776931058668</v>
+        <v>0.40804049086221417</v>
       </c>
       <c r="H27" s="59">
         <f t="shared" si="4"/>
-        <v>80090632.219233289</v>
+        <v>80280530.274612799</v>
       </c>
       <c r="I27" s="60">
         <f t="shared" si="2"/>
-        <v>0.97698071816156451</v>
+        <v>0.97929717806931393</v>
       </c>
       <c r="J27" s="59">
         <f t="shared" si="5"/>
-        <v>3337109.6758013871</v>
+        <v>3345022.0947755333</v>
       </c>
       <c r="K27" s="59">
         <f t="shared" si="3"/>
-        <v>3462914.1945191682</v>
+        <v>3466248.5037317616</v>
       </c>
       <c r="L27" s="61" cm="1">
         <f t="array" ref="L27">+_xlfn.IFS(I27&gt;114%,H27*0.0125,I27&gt;109%,H27*0.01,I27&gt;104%,H27*0.0075,I27&gt;99%,H27*0.005,I27&lt;99%,H27*0)</f>
@@ -4941,34 +4942,34 @@
       </c>
       <c r="D28" s="4">
         <f>IFERROR(+VLOOKUP(B28,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>5777964.8325451156</v>
+      </c>
+      <c r="E28" s="4">
         <v>5212708.9840588067</v>
-      </c>
-      <c r="E28" s="4">
-        <v>4367804.0145924808</v>
       </c>
       <c r="F28" s="4">
         <f t="shared" si="8"/>
-        <v>844904.96946632583</v>
+        <v>565255.84848630894</v>
       </c>
       <c r="G28" s="5">
         <f t="shared" si="1"/>
-        <v>0.24822423733613366</v>
+        <v>0.27514118250214836</v>
       </c>
       <c r="H28" s="4">
         <f t="shared" si="4"/>
-        <v>13900557.290823486</v>
+        <v>13867115.598108279</v>
       </c>
       <c r="I28" s="5">
         <f t="shared" si="2"/>
-        <v>0.6619312995630231</v>
+        <v>0.66033883800515614</v>
       </c>
       <c r="J28" s="4">
         <f t="shared" si="5"/>
-        <v>579189.88711764524</v>
+        <v>577796.48325451161</v>
       </c>
       <c r="K28" s="4">
         <f t="shared" si="3"/>
-        <v>1052486.0677294128</v>
+        <v>1087288.2262467775</v>
       </c>
       <c r="L28" s="63" cm="1">
         <f t="array" ref="L28">+_xlfn.IFS(I28&gt;114%,H28*0.02,I28&gt;109%,H28*0.015,I28&gt;104%,H28*0.0125,I28&gt;99%,H28*0.01,I28&lt;99%,H28*0)</f>
@@ -4985,34 +4986,34 @@
       </c>
       <c r="D29" s="4">
         <f>IFERROR(+VLOOKUP(B29,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>9823471.9917300809</v>
+      </c>
+      <c r="E29" s="4">
         <v>8509221.7116328403</v>
-      </c>
-      <c r="E29" s="4">
-        <v>7520013.6941604447</v>
       </c>
       <c r="F29" s="4">
         <f t="shared" si="8"/>
-        <v>989208.01747239567</v>
+        <v>1314250.2800972406</v>
       </c>
       <c r="G29" s="5">
         <f t="shared" si="1"/>
-        <v>0.33058744708107868</v>
+        <v>0.38164671661791244</v>
       </c>
       <c r="H29" s="4">
         <f t="shared" si="4"/>
-        <v>22691257.897687573</v>
+        <v>23576332.780152194</v>
       </c>
       <c r="I29" s="5">
         <f t="shared" si="2"/>
-        <v>0.88156652554954307</v>
+        <v>0.91595211988298986</v>
       </c>
       <c r="J29" s="4">
         <f t="shared" si="5"/>
-        <v>945469.07907031558</v>
+        <v>982347.19917300809</v>
       </c>
       <c r="K29" s="4">
         <f t="shared" si="3"/>
-        <v>1148698.5525578107</v>
+        <v>1136873.429162137</v>
       </c>
       <c r="L29" s="63" cm="1">
         <f t="array" ref="L29">+_xlfn.IFS(I29&gt;114%,H29*0.02,I29&gt;109%,H29*0.015,I29&gt;104%,H29*0.0125,I29&gt;99%,H29*0.01,I29&lt;99%,H29*0)</f>
@@ -5030,34 +5031,34 @@
       </c>
       <c r="D30" s="4">
         <f>IFERROR(+VLOOKUP(B30,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>8588184.3117468338</v>
+      </c>
+      <c r="E30" s="4">
         <v>7023786.2862272449</v>
-      </c>
-      <c r="E30" s="4">
-        <v>6348650.0493735028</v>
       </c>
       <c r="F30" s="4">
         <f t="shared" si="8"/>
-        <v>675136.23685374204</v>
+        <v>1564398.025519589</v>
       </c>
       <c r="G30" s="5">
         <f t="shared" si="1"/>
-        <v>0.18370906298932413</v>
+        <v>0.22462632380833508</v>
       </c>
       <c r="H30" s="4">
         <f t="shared" si="4"/>
-        <v>18730096.763272654</v>
+        <v>20611642.348192401</v>
       </c>
       <c r="I30" s="5">
         <f t="shared" si="2"/>
-        <v>0.48989083463819771</v>
+        <v>0.53910317714000422</v>
       </c>
       <c r="J30" s="4">
         <f t="shared" si="5"/>
-        <v>780420.69846969389</v>
+        <v>858818.43117468338</v>
       </c>
       <c r="K30" s="4">
         <f t="shared" si="3"/>
-        <v>2080627.9217265618</v>
+        <v>2117501.4857413457</v>
       </c>
       <c r="L30" s="63" cm="1">
         <f t="array" ref="L30">+_xlfn.IFS(I30&gt;114%,H30*0.02,I30&gt;109%,H30*0.015,I30&gt;104%,H30*0.0125,I30&gt;99%,H30*0.01,I30&lt;99%,H30*0)</f>
@@ -5075,34 +5076,34 @@
       </c>
       <c r="D31" s="4">
         <f>IFERROR(+VLOOKUP(B31,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>9407600.5395302419</v>
+      </c>
+      <c r="E31" s="4">
         <v>8331163.463863492</v>
-      </c>
-      <c r="E31" s="4">
-        <v>7212918.424210974</v>
       </c>
       <c r="F31" s="4">
         <f t="shared" si="8"/>
-        <v>1118245.039652518</v>
+        <v>1076437.0756667498</v>
       </c>
       <c r="G31" s="5">
         <f t="shared" si="1"/>
-        <v>0.32780175146274348</v>
+        <v>0.37015573482575392</v>
       </c>
       <c r="H31" s="4">
         <f t="shared" si="4"/>
-        <v>22216435.903635979</v>
+        <v>22578241.294872582</v>
       </c>
       <c r="I31" s="5">
         <f t="shared" si="2"/>
-        <v>0.87413800390064933</v>
+        <v>0.88837376358180942</v>
       </c>
       <c r="J31" s="4">
         <f t="shared" si="5"/>
-        <v>925684.82931816578</v>
+        <v>940760.05395302421</v>
       </c>
       <c r="K31" s="4">
         <f t="shared" si="3"/>
-        <v>1138939.1024091006</v>
+        <v>1143403.532890697</v>
       </c>
       <c r="L31" s="63" cm="1">
         <f t="array" ref="L31">+_xlfn.IFS(I31&gt;114%,H31*0.02,I31&gt;109%,H31*0.015,I31&gt;104%,H31*0.0125,I31&gt;99%,H31*0.01,I31&lt;99%,H31*0)</f>
@@ -5120,34 +5121,34 @@
       </c>
       <c r="D32" s="4">
         <f>IFERROR(+VLOOKUP(B32,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>6665534.1859788187</v>
+      </c>
+      <c r="E32" s="4">
         <v>5611548.663038048</v>
-      </c>
-      <c r="E32" s="4">
-        <v>4813267.3862359719</v>
       </c>
       <c r="F32" s="4">
         <f t="shared" si="8"/>
-        <v>798281.27680207603</v>
+        <v>1053985.5229407707</v>
       </c>
       <c r="G32" s="5">
         <f t="shared" si="1"/>
-        <v>0.22268050250150984</v>
+        <v>0.26450532484042932</v>
       </c>
       <c r="H32" s="4">
         <f t="shared" si="4"/>
-        <v>14964129.768101461</v>
+        <v>15997282.046349166</v>
       </c>
       <c r="I32" s="5">
         <f t="shared" si="2"/>
-        <v>0.5938146733373596</v>
+        <v>0.63481277961703042</v>
       </c>
       <c r="J32" s="4">
         <f t="shared" si="5"/>
-        <v>623505.40700422751</v>
+        <v>666553.41859788192</v>
       </c>
       <c r="K32" s="4">
         <f t="shared" si="3"/>
-        <v>1305896.7557974635</v>
+        <v>1323890.4152872271</v>
       </c>
       <c r="L32" s="63" cm="1">
         <f t="array" ref="L32">+_xlfn.IFS(I32&gt;114%,H32*0.02,I32&gt;109%,H32*0.015,I32&gt;104%,H32*0.0125,I32&gt;99%,H32*0.01,I32&lt;99%,H32*0)</f>
@@ -5165,34 +5166,34 @@
       </c>
       <c r="D33" s="4">
         <f>IFERROR(+VLOOKUP(B33,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>6448364.3120282274</v>
+      </c>
+      <c r="E33" s="4">
         <v>5482149.478754703</v>
-      </c>
-      <c r="E33" s="4">
-        <v>5035112.3818729157</v>
       </c>
       <c r="F33" s="4">
         <f t="shared" si="8"/>
-        <v>447037.09688178729</v>
+        <v>966214.83327352442</v>
       </c>
       <c r="G33" s="5">
         <f t="shared" si="1"/>
-        <v>0.20689893963428357</v>
+        <v>0.24336434891178077</v>
       </c>
       <c r="H33" s="4">
         <f t="shared" si="4"/>
-        <v>14619065.276679207</v>
+        <v>15476074.348867744</v>
       </c>
       <c r="I33" s="5">
         <f t="shared" si="2"/>
-        <v>0.55173050569142279</v>
+        <v>0.5840744373882738</v>
       </c>
       <c r="J33" s="4">
         <f t="shared" si="5"/>
-        <v>609127.71986163361</v>
+        <v>644836.43120282271</v>
       </c>
       <c r="K33" s="4">
         <f t="shared" si="3"/>
-        <v>1400973.3680830197</v>
+        <v>1432027.5491408408</v>
       </c>
       <c r="L33" s="63" cm="1">
         <f t="array" ref="L33">+_xlfn.IFS(I33&gt;114%,H33*0.02,I33&gt;109%,H33*0.015,I33&gt;104%,H33*0.0125,I33&gt;99%,H33*0.01,I33&lt;99%,H33*0)</f>
@@ -5209,34 +5210,34 @@
       </c>
       <c r="D34" s="4">
         <f>IFERROR(+VLOOKUP(B34,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>5618690.4157067938</v>
+      </c>
+      <c r="E34" s="4">
         <v>4657516.3901073569</v>
-      </c>
-      <c r="E34" s="4">
-        <v>3805787.6012926684</v>
       </c>
       <c r="F34" s="4">
         <f t="shared" si="8"/>
-        <v>851728.78881468857</v>
+        <v>961174.02559943683</v>
       </c>
       <c r="G34" s="5">
         <f t="shared" si="1"/>
-        <v>0.22178649476701701</v>
+        <v>0.2675566864622283</v>
       </c>
       <c r="H34" s="4">
         <f t="shared" si="4"/>
-        <v>12420043.706952952</v>
+        <v>13484856.997696307</v>
       </c>
       <c r="I34" s="5">
         <f t="shared" si="2"/>
-        <v>0.59143065271204531</v>
+        <v>0.64213604750934794</v>
       </c>
       <c r="J34" s="4">
         <f t="shared" si="5"/>
-        <v>517501.82112303964</v>
+        <v>561869.0415706794</v>
       </c>
       <c r="K34" s="4">
         <f t="shared" si="3"/>
-        <v>1089498.9073261763</v>
+        <v>1098664.9703066575</v>
       </c>
       <c r="L34" s="63" cm="1">
         <f t="array" ref="L34">+_xlfn.IFS(I34&gt;114%,H34*0.02,I34&gt;109%,H34*0.015,I34&gt;104%,H34*0.0125,I34&gt;99%,H34*0.01,I34&lt;99%,H34*0)</f>
@@ -5253,34 +5254,34 @@
       </c>
       <c r="D35" s="4">
         <f>IFERROR(+VLOOKUP(B35,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>3802949.3075159392</v>
+      </c>
+      <c r="E35" s="4">
         <v>3564392.4785372978</v>
-      </c>
-      <c r="E35" s="4">
-        <v>3442297.9978710278</v>
       </c>
       <c r="F35" s="4">
         <f t="shared" si="8"/>
-        <v>122094.48066627001</v>
+        <v>238556.82897864142</v>
       </c>
       <c r="G35" s="5">
         <f t="shared" si="1"/>
-        <v>0.14455201428073816</v>
+        <v>0.15422655779886363</v>
       </c>
       <c r="H35" s="4">
         <f t="shared" si="4"/>
-        <v>9505046.6094327942</v>
+        <v>9127078.3380382545</v>
       </c>
       <c r="I35" s="5">
         <f t="shared" si="2"/>
-        <v>0.38547203808196845</v>
+        <v>0.37014373871727274</v>
       </c>
       <c r="J35" s="4">
         <f t="shared" si="5"/>
-        <v>396043.60872636642</v>
+        <v>380294.9307515939</v>
       </c>
       <c r="K35" s="4">
         <f t="shared" si="3"/>
-        <v>1406253.83476418</v>
+        <v>1489660.7637488616</v>
       </c>
       <c r="L35" s="63" cm="1">
         <f t="array" ref="L35">+_xlfn.IFS(I35&gt;114%,H35*0.02,I35&gt;109%,H35*0.015,I35&gt;104%,H35*0.0125,I35&gt;99%,H35*0.01,I35&lt;99%,H35*0)</f>
@@ -5297,34 +5298,34 @@
       </c>
       <c r="D36" s="4">
         <f>IFERROR(+VLOOKUP(B36,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>6222492.2724699304</v>
+      </c>
+      <c r="E36" s="4">
         <v>5567175.7313747797</v>
-      </c>
-      <c r="E36" s="4">
-        <v>4684076.524209898</v>
       </c>
       <c r="F36" s="4">
         <f t="shared" si="8"/>
-        <v>883099.20716488175</v>
+        <v>655316.54109515063</v>
       </c>
       <c r="G36" s="5">
         <f t="shared" si="1"/>
-        <v>0.2206132645680515</v>
+        <v>0.24658182177412047</v>
       </c>
       <c r="H36" s="4">
         <f t="shared" si="4"/>
-        <v>14845801.950332746</v>
+        <v>14933981.453927832</v>
       </c>
       <c r="I36" s="5">
         <f t="shared" si="2"/>
-        <v>0.58830203884813737</v>
+        <v>0.59179637225788906</v>
       </c>
       <c r="J36" s="4">
         <f t="shared" si="5"/>
-        <v>618575.08126386441</v>
+        <v>622249.22724699299</v>
       </c>
       <c r="K36" s="4">
         <f t="shared" si="3"/>
-        <v>1311188.2845750148</v>
+        <v>1358036.2662521477</v>
       </c>
       <c r="L36" s="63" cm="1">
         <f t="array" ref="L36">+_xlfn.IFS(I36&gt;114%,H36*0.02,I36&gt;109%,H36*0.015,I36&gt;104%,H36*0.0125,I36&gt;99%,H36*0.01,I36&lt;99%,H36*0)</f>
@@ -5341,34 +5342,34 @@
       </c>
       <c r="D37" s="4">
         <f>IFERROR(+VLOOKUP(B37,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>33451176.522885799</v>
+      </c>
+      <c r="E37" s="4">
         <v>28457978.498885799</v>
-      </c>
-      <c r="E37" s="4">
-        <v>28341762.515582383</v>
       </c>
       <c r="F37" s="4">
         <f t="shared" si="8"/>
-        <v>116215.98330341652</v>
+        <v>4993198.0240000002</v>
       </c>
       <c r="G37" s="5">
         <f t="shared" si="1"/>
-        <v>0.23323965518801099</v>
+        <v>0.27416356640148021</v>
       </c>
       <c r="H37" s="4">
         <f t="shared" si="4"/>
-        <v>75887942.663695469</v>
+        <v>80282823.654925913</v>
       </c>
       <c r="I37" s="5">
         <f t="shared" si="2"/>
-        <v>0.62197241383469604</v>
+        <v>0.65799255936355239</v>
       </c>
       <c r="J37" s="4">
         <f t="shared" si="5"/>
-        <v>3161997.6109873112</v>
+        <v>3345117.6522885798</v>
       </c>
       <c r="K37" s="4">
         <f t="shared" si="3"/>
-        <v>6236918.1000742801</v>
+        <v>6325755.2483652998</v>
       </c>
       <c r="L37" s="63" cm="1">
         <f t="array" ref="L37">+_xlfn.IFS(I37&gt;114%,H37*0.0125,I37&gt;109%,H37*0.01,I37&gt;104%,H37*0.0075,I37&gt;99%,H37*0.005,I37&lt;99%,H37*0)</f>
@@ -5385,34 +5386,34 @@
       </c>
       <c r="D38" s="4">
         <f>IFERROR(+VLOOKUP(B38,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>4305943.4722995181</v>
+      </c>
+      <c r="E38" s="4">
         <v>2767832.4172995184</v>
-      </c>
-      <c r="E38" s="4">
-        <v>2478634.4092995184</v>
       </c>
       <c r="F38" s="4">
         <f t="shared" ref="F38" si="10">+D38-E38</f>
-        <v>289198.00799999991</v>
+        <v>1538111.0549999997</v>
       </c>
       <c r="G38" s="5">
         <f t="shared" si="1"/>
-        <v>7.7530319812311441E-2</v>
+        <v>0.12061466308962235</v>
       </c>
       <c r="H38" s="4">
         <f t="shared" si="4"/>
-        <v>7380886.446132049</v>
+        <v>10334264.333518844</v>
       </c>
       <c r="I38" s="5">
         <f t="shared" si="2"/>
-        <v>0.20674751949949716</v>
+        <v>0.28947519141509365</v>
       </c>
       <c r="J38" s="4">
         <f t="shared" si="5"/>
-        <v>307536.93525550206</v>
+        <v>430594.34722995182</v>
       </c>
       <c r="K38" s="4">
         <f t="shared" si="3"/>
-        <v>2195477.8388466989</v>
+        <v>2242432.6091214633</v>
       </c>
       <c r="L38" s="63" cm="1">
         <f t="array" ref="L38">+_xlfn.IFS(I38&gt;109%,H38*0.015,I38&gt;104%,H38*0.0125,I38&gt;99%,H38*0.01,I38&lt;99%,H38*0)</f>
@@ -5429,34 +5430,34 @@
       </c>
       <c r="D39" s="4">
         <f>IFERROR(+VLOOKUP(B39,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>11081724.942682527</v>
+      </c>
+      <c r="E39" s="4">
         <v>9930506.0322296303</v>
-      </c>
-      <c r="E39" s="4">
-        <v>8818400.8023845814</v>
       </c>
       <c r="F39" s="4">
         <f t="shared" si="8"/>
-        <v>1112105.2298450489</v>
+        <v>1151218.9104528967</v>
       </c>
       <c r="G39" s="5">
         <f t="shared" si="1"/>
-        <v>0.27310550354375979</v>
+        <v>0.30476594654716088</v>
       </c>
       <c r="H39" s="4">
         <f t="shared" si="4"/>
-        <v>26481349.419279017</v>
+        <v>26596139.862438068</v>
       </c>
       <c r="I39" s="5">
         <f t="shared" si="2"/>
-        <v>0.72828134278335954</v>
+        <v>0.73143827171318621</v>
       </c>
       <c r="J39" s="4">
         <f t="shared" si="5"/>
-        <v>1103389.5591366256</v>
+        <v>1108172.4942682527</v>
       </c>
       <c r="K39" s="4">
         <f t="shared" si="3"/>
-        <v>1762061.4471180246</v>
+        <v>1805693.0568798196</v>
       </c>
       <c r="L39" s="63" cm="1">
         <f t="array" ref="L39">+_xlfn.IFS(I39&gt;114%,H39*0.02,I39&gt;109%,H39*0.015,I39&gt;104%,H39*0.0125,I39&gt;99%,H39*0.01,I39&lt;99%,H39*0)</f>
@@ -5471,34 +5472,34 @@
       </c>
       <c r="D40" s="67">
         <f>+SUM(D27:D39)</f>
+        <v>144644318.05487517</v>
+      </c>
+      <c r="E40" s="65">
         <v>125149967.21822201</v>
-      </c>
-      <c r="E40" s="65">
-        <v>115222111.25640535</v>
       </c>
       <c r="F40" s="67">
         <f t="shared" si="8"/>
-        <v>9927855.9618166536</v>
+        <v>19494350.836653158</v>
       </c>
       <c r="G40" s="66">
         <f t="shared" si="1"/>
-        <v>0.24586019938834067</v>
+        <v>0.28415733274106886</v>
       </c>
       <c r="H40" s="64">
         <f t="shared" si="4"/>
-        <v>333733245.91525865</v>
+        <v>347146363.33170044</v>
       </c>
       <c r="I40" s="66">
         <f t="shared" si="2"/>
-        <v>0.65562719836890837</v>
+        <v>0.68197759857856532</v>
       </c>
       <c r="J40" s="64">
         <f t="shared" si="5"/>
-        <v>13905551.913135778</v>
+        <v>14464431.805487517</v>
       </c>
       <c r="K40" s="67">
         <f t="shared" si="3"/>
-        <v>25591934.375526913</v>
+        <v>26027476.056875043</v>
       </c>
       <c r="L40" s="68"/>
     </row>
@@ -5512,34 +5513,34 @@
       </c>
       <c r="D41" s="81">
         <f>+D40+D26+D10+D16</f>
+        <v>523856297.78755802</v>
+      </c>
+      <c r="E41" s="82">
         <v>470467238.36041617</v>
-      </c>
-      <c r="E41" s="82">
-        <v>397625858.39552885</v>
       </c>
       <c r="F41" s="81">
         <f>+D41-E41</f>
-        <v>72841379.964887321</v>
+        <v>53389059.427141845</v>
       </c>
       <c r="G41" s="83">
         <f t="shared" si="1"/>
-        <v>0.34097582287822004</v>
+        <v>0.37967007613654757</v>
       </c>
       <c r="H41" s="81">
         <f t="shared" si="4"/>
-        <v>1254579302.2944431</v>
+        <v>1257255114.6901393</v>
       </c>
       <c r="I41" s="83">
         <f t="shared" si="2"/>
-        <v>0.90926886100858684</v>
+        <v>0.9112081827277142</v>
       </c>
       <c r="J41" s="81">
         <f t="shared" si="5"/>
-        <v>52274137.595601797</v>
+        <v>52385629.778755799</v>
       </c>
       <c r="K41" s="81">
         <f t="shared" si="3"/>
-        <v>60619993.915514663</v>
+        <v>61136489.236112714</v>
       </c>
       <c r="L41" s="84"/>
     </row>
@@ -5590,11 +5591,11 @@
         <v>6840893.5633781236</v>
       </c>
       <c r="E43" s="4">
-        <v>8104352.0621971888</v>
+        <v>6840893.5633781236</v>
       </c>
       <c r="F43" s="4">
         <f t="shared" ref="F43" si="11">+D43-E43</f>
-        <v>-1263458.4988190653</v>
+        <v>0</v>
       </c>
       <c r="G43" s="5">
         <f>+D43/C43</f>
@@ -5602,19 +5603,19 @@
       </c>
       <c r="H43" s="4">
         <f t="shared" ref="H43" si="12">+D43/$N$3*$N$4</f>
-        <v>18242382.835674997</v>
+        <v>16418144.552107498</v>
       </c>
       <c r="I43" s="5">
         <f>+H43/C43</f>
-        <v>0.45605957089187493</v>
+        <v>0.41045361380268747</v>
       </c>
       <c r="J43" s="4">
         <f t="shared" ref="J43" si="13">+D43/$N$3</f>
-        <v>760099.28481979156</v>
+        <v>684089.35633781238</v>
       </c>
       <c r="K43" s="4">
         <f>+(C43-D43)/$N$2</f>
-        <v>2210607.0957747917</v>
+        <v>2368507.6026158482</v>
       </c>
       <c r="L43" s="4" cm="1">
         <f t="array" ref="L43">+_xlfn.IFS(I43&gt;114%,H43*0.02,I43&gt;109%,H43*0.015,I43&gt;104%,H43*0.0125,I43&gt;99%,H43*0.01,I43&lt;99%,H43*0)</f>
@@ -5633,11 +5634,11 @@
         <v>14127537.863605659</v>
       </c>
       <c r="E44" s="4">
-        <v>14041795.823822808</v>
+        <v>14127537.863605659</v>
       </c>
       <c r="F44" s="4">
         <f t="shared" ref="F44" si="14">+D44-E44</f>
-        <v>85742.039782851934</v>
+        <v>0</v>
       </c>
       <c r="G44" s="5">
         <f>+D44/C44</f>
@@ -5645,23 +5646,23 @@
       </c>
       <c r="H44" s="4">
         <f t="shared" ref="H44" si="15">+D44/$N$3*$N$4</f>
-        <v>37673434.302948423</v>
+        <v>33906090.872653589</v>
       </c>
       <c r="I44" s="5">
         <f>+H44/C44</f>
-        <v>1.2557811434316142</v>
+        <v>1.130203029088453</v>
       </c>
       <c r="J44" s="4">
         <f t="shared" ref="J44" si="16">+D44/$N$3</f>
-        <v>1569726.4292895177</v>
+        <v>1412753.786360566</v>
       </c>
       <c r="K44" s="4">
         <f>+(C44-D44)/$N$2</f>
-        <v>1058164.1424262894</v>
+        <v>1133747.2954567387</v>
       </c>
       <c r="L44" s="4" cm="1">
         <f t="array" ref="L44">+_xlfn.IFS(I44&gt;114%,H44*0.02,I44&gt;109%,H44*0.015,I44&gt;104%,H44*0.0125,I44&gt;99%,H44*0.01,I44&lt;99%,H44*0)</f>
-        <v>753468.68605896842</v>
+        <v>508591.36308980384</v>
       </c>
     </row>
   </sheetData>
@@ -5799,14 +5800,14 @@
       </c>
       <c r="D2" s="22">
         <f>H2/G2</f>
-        <v>0.61643835616438358</v>
+        <v>0.64383561643835618</v>
       </c>
       <c r="E2" s="13">
         <v>33</v>
       </c>
       <c r="F2" s="12">
         <f>+H2-E2</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G2" s="13">
         <f>VLOOKUP(B2,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -5814,11 +5815,11 @@
       </c>
       <c r="H2" s="13">
         <f>VLOOKUP(B2,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I2" s="17">
         <f>(+G2*$M$2)-H2</f>
-        <v>17.049999999999997</v>
+        <v>15.049999999999997</v>
       </c>
       <c r="J2" t="s">
         <v>55</v>
@@ -5864,14 +5865,14 @@
       </c>
       <c r="D3" s="22">
         <f t="shared" ref="D3:D38" si="0">H3/G3</f>
-        <v>0.35146443514644349</v>
+        <v>0.34309623430962344</v>
       </c>
       <c r="E3" s="13">
         <v>1</v>
       </c>
       <c r="F3" s="12">
         <f t="shared" ref="F3:F38" si="1">+H3-E3</f>
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G3" s="13">
         <f>VLOOKUP(B3,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -5879,11 +5880,11 @@
       </c>
       <c r="H3" s="13">
         <f>VLOOKUP(B3,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I3" s="17">
         <f t="shared" ref="I3:I38" si="2">(+G3*$M$2)-H3</f>
-        <v>119.15</v>
+        <v>121.15</v>
       </c>
       <c r="J3" t="s">
         <v>56</v>
@@ -5902,14 +5903,14 @@
         <v>145 - ALMACEN</v>
       </c>
       <c r="S3" s="12">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="T3" s="12">
         <v>214</v>
       </c>
       <c r="U3" s="41">
         <f>+S3/T3</f>
-        <v>0.1822429906542056</v>
+        <v>0.19626168224299065</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
@@ -5923,14 +5924,14 @@
       </c>
       <c r="D4" s="22">
         <f t="shared" si="0"/>
-        <v>0.69162995594713661</v>
+        <v>0.74008810572687223</v>
       </c>
       <c r="E4" s="13">
         <v>126</v>
       </c>
       <c r="F4" s="12">
         <f t="shared" si="1"/>
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G4" s="13">
         <f>VLOOKUP(B4,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -5938,11 +5939,11 @@
       </c>
       <c r="H4" s="13">
         <f>VLOOKUP(B4,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="I4" s="17">
         <f t="shared" si="2"/>
-        <v>35.949999999999989</v>
+        <v>24.949999999999989</v>
       </c>
       <c r="J4" t="s">
         <v>57</v>
@@ -5960,14 +5961,14 @@
         <v>145 - Articulos Sin Asociar Agrupacion</v>
       </c>
       <c r="S4" s="13">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="T4" s="13">
         <v>214</v>
       </c>
       <c r="U4" s="5">
         <f t="shared" ref="U4:U11" si="3">+S4/T4</f>
-        <v>0.10280373831775701</v>
+        <v>0.11214953271028037</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
@@ -5981,14 +5982,14 @@
       </c>
       <c r="D5" s="22">
         <f t="shared" si="0"/>
-        <v>0.58461538461538465</v>
+        <v>0.63076923076923075</v>
       </c>
       <c r="E5" s="13">
         <v>21</v>
       </c>
       <c r="F5" s="12">
         <f t="shared" si="1"/>
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G5" s="13">
         <f>VLOOKUP(B5,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -5996,11 +5997,11 @@
       </c>
       <c r="H5" s="13">
         <f>VLOOKUP(B5,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I5" s="17">
         <f t="shared" si="2"/>
-        <v>17.25</v>
+        <v>14.25</v>
       </c>
       <c r="K5" t="s">
         <v>64</v>
@@ -6015,14 +6016,14 @@
         <v>145 - BEBIDAS</v>
       </c>
       <c r="S5" s="13">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="T5" s="13">
         <v>214</v>
       </c>
       <c r="U5" s="5">
         <f t="shared" si="3"/>
-        <v>0.23364485981308411</v>
+        <v>0.27570093457943923</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
@@ -6036,14 +6037,14 @@
       </c>
       <c r="D6" s="22">
         <f t="shared" si="0"/>
-        <v>0.68599033816425126</v>
+        <v>0.70531400966183577</v>
       </c>
       <c r="E6" s="13">
         <v>100</v>
       </c>
       <c r="F6" s="12">
         <f t="shared" si="1"/>
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G6" s="13">
         <f>VLOOKUP(B6,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6051,11 +6052,11 @@
       </c>
       <c r="H6" s="13">
         <f>VLOOKUP(B6,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="I6" s="17">
         <f t="shared" si="2"/>
-        <v>33.949999999999989</v>
+        <v>29.949999999999989</v>
       </c>
       <c r="J6" t="s">
         <v>58</v>
@@ -6073,14 +6074,14 @@
         <v>145 - CHOCOLATE</v>
       </c>
       <c r="S6" s="13">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="T6" s="13">
         <v>214</v>
       </c>
       <c r="U6" s="5">
         <f t="shared" si="3"/>
-        <v>0.11214953271028037</v>
+        <v>0.13551401869158877</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
@@ -6094,14 +6095,14 @@
       </c>
       <c r="D7" s="22">
         <f t="shared" si="0"/>
-        <v>0.48989898989898989</v>
+        <v>0.57070707070707072</v>
       </c>
       <c r="E7" s="13">
         <v>81</v>
       </c>
       <c r="F7" s="12">
         <f t="shared" si="1"/>
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="G7" s="13">
         <f>VLOOKUP(B7,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6109,11 +6110,11 @@
       </c>
       <c r="H7" s="13">
         <f>VLOOKUP(B7,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="I7" s="17">
         <f t="shared" si="2"/>
-        <v>71.299999999999983</v>
+        <v>55.299999999999983</v>
       </c>
       <c r="J7" t="s">
         <v>58</v>
@@ -6131,14 +6132,14 @@
         <v>145 - GALLETITAS</v>
       </c>
       <c r="S7" s="13">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="T7" s="13">
         <v>214</v>
       </c>
       <c r="U7" s="5">
         <f t="shared" si="3"/>
-        <v>0.27570093457943923</v>
+        <v>0.30841121495327101</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
@@ -6152,14 +6153,14 @@
       </c>
       <c r="D8" s="22">
         <f t="shared" si="0"/>
-        <v>0.64485981308411211</v>
+        <v>0.68691588785046731</v>
       </c>
       <c r="E8" s="13">
         <v>89</v>
       </c>
       <c r="F8" s="12">
         <f t="shared" si="1"/>
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="G8" s="13">
         <f>VLOOKUP(B8,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6167,11 +6168,11 @@
       </c>
       <c r="H8" s="13">
         <f>VLOOKUP(B8,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="I8" s="17">
         <f t="shared" si="2"/>
-        <v>43.900000000000006</v>
+        <v>34.900000000000006</v>
       </c>
       <c r="J8" t="s">
         <v>55</v>
@@ -6190,14 +6191,14 @@
         <v>145 - GOLOSINAS</v>
       </c>
       <c r="S8" s="13">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="T8" s="13">
         <v>214</v>
       </c>
       <c r="U8" s="5">
         <f t="shared" si="3"/>
-        <v>0.23831775700934579</v>
+        <v>0.26168224299065418</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
@@ -6211,26 +6212,26 @@
       </c>
       <c r="D9" s="22">
         <f>H9/G9</f>
-        <v>0.61728395061728392</v>
+        <v>0.65644171779141103</v>
       </c>
       <c r="E9" s="13">
         <v>92</v>
       </c>
       <c r="F9" s="12">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G9" s="13">
         <f>VLOOKUP(B9,'Base Cobertura'!$A:$C,3,FALSE)</f>
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H9" s="13">
         <f>VLOOKUP(B9,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="I9" s="17">
         <f t="shared" si="2"/>
-        <v>37.699999999999989</v>
+        <v>31.549999999999983</v>
       </c>
       <c r="J9" t="s">
         <v>55</v>
@@ -6248,14 +6249,14 @@
         <v>145 - MASCOTAS</v>
       </c>
       <c r="S9" s="13">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T9" s="13">
         <v>214</v>
       </c>
       <c r="U9" s="5">
         <f t="shared" si="3"/>
-        <v>5.6074766355140186E-2</v>
+        <v>7.0093457943925228E-2</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
@@ -6269,14 +6270,14 @@
       </c>
       <c r="D10" s="22">
         <f t="shared" si="0"/>
-        <v>0.49230769230769234</v>
+        <v>0.54871794871794877</v>
       </c>
       <c r="E10" s="13">
         <v>64</v>
       </c>
       <c r="F10" s="12">
         <f t="shared" si="1"/>
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="G10" s="13">
         <f>VLOOKUP(B10,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6284,11 +6285,11 @@
       </c>
       <c r="H10" s="13">
         <f>VLOOKUP(B10,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="I10" s="17">
         <f t="shared" si="2"/>
-        <v>69.75</v>
+        <v>58.75</v>
       </c>
       <c r="J10" t="s">
         <v>58</v>
@@ -6306,14 +6307,14 @@
         <v>145 - NO PERECEDEROS</v>
       </c>
       <c r="S10" s="13">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T10" s="13">
         <v>214</v>
       </c>
       <c r="U10" s="5">
         <f t="shared" si="3"/>
-        <v>6.5420560747663545E-2</v>
+        <v>7.0093457943925228E-2</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
@@ -6361,14 +6362,14 @@
         <v>145 - PILAS</v>
       </c>
       <c r="S11" s="13">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="T11" s="13">
         <v>214</v>
       </c>
       <c r="U11" s="5">
         <f t="shared" si="3"/>
-        <v>0.10747663551401869</v>
+        <v>0.11682242990654206</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
@@ -6382,14 +6383,14 @@
       </c>
       <c r="D12" s="32">
         <f t="shared" si="0"/>
-        <v>0.32380952380952382</v>
+        <v>0.34285714285714286</v>
       </c>
       <c r="E12" s="31">
         <v>24</v>
       </c>
       <c r="F12" s="33">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G12" s="13">
         <f>VLOOKUP(B12,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6397,11 +6398,11 @@
       </c>
       <c r="H12" s="13">
         <f>VLOOKUP(B12,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I12" s="34">
         <f t="shared" si="2"/>
-        <v>55.25</v>
+        <v>53.25</v>
       </c>
       <c r="J12" t="s">
         <v>59</v>
@@ -6418,26 +6419,26 @@
       </c>
       <c r="D13" s="22">
         <f t="shared" si="0"/>
-        <v>0.62692307692307692</v>
+        <v>0.68582375478927204</v>
       </c>
       <c r="E13" s="13">
         <v>144</v>
       </c>
       <c r="F13" s="12">
         <f t="shared" si="1"/>
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="G13" s="13">
         <f>VLOOKUP(B13,'Base Cobertura'!$A:$C,3,FALSE)</f>
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H13" s="13">
         <f>VLOOKUP(B13,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="I13" s="17">
         <f t="shared" si="2"/>
-        <v>58</v>
+        <v>42.849999999999994</v>
       </c>
       <c r="J13" t="s">
         <v>57</v>
@@ -6457,14 +6458,14 @@
       </c>
       <c r="D14" s="22">
         <f t="shared" si="0"/>
-        <v>0.52197802197802201</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="E14" s="13">
         <v>85</v>
       </c>
       <c r="F14" s="12">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G14" s="13">
         <f>VLOOKUP(B14,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6472,11 +6473,11 @@
       </c>
       <c r="H14" s="13">
         <f>VLOOKUP(B14,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="I14" s="17">
         <f t="shared" si="2"/>
-        <v>59.699999999999989</v>
+        <v>50.699999999999989</v>
       </c>
       <c r="J14" t="s">
         <v>55</v>
@@ -6492,15 +6493,15 @@
       <c r="E15" s="14"/>
       <c r="F15" s="16">
         <f>+SUM(F2:F14)</f>
-        <v>338</v>
+        <v>426</v>
       </c>
       <c r="G15" s="8">
         <f>+SUM(G2:G14)</f>
-        <v>2228</v>
+        <v>2230</v>
       </c>
       <c r="H15" s="8">
         <f>+SUM(H2:H14)</f>
-        <v>1217</v>
+        <v>1305</v>
       </c>
       <c r="I15" s="8"/>
     </row>
@@ -6517,14 +6518,14 @@
       </c>
       <c r="D16" s="22">
         <f t="shared" si="0"/>
-        <v>0.70625000000000004</v>
+        <v>0.72499999999999998</v>
       </c>
       <c r="E16" s="13">
         <v>90</v>
       </c>
       <c r="F16" s="12">
         <f t="shared" si="1"/>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G16" s="13">
         <f>VLOOKUP(B16,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6532,11 +6533,11 @@
       </c>
       <c r="H16" s="13">
         <f>VLOOKUP(B16,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="I16" s="17">
         <f t="shared" si="2"/>
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J16" t="s">
         <v>55</v>
@@ -6556,14 +6557,14 @@
       </c>
       <c r="D17" s="22">
         <f t="shared" si="0"/>
-        <v>0.37128712871287128</v>
+        <v>0.38118811881188119</v>
       </c>
       <c r="E17" s="13">
         <v>92</v>
       </c>
       <c r="F17" s="12">
         <f t="shared" si="1"/>
-        <v>-17</v>
+        <v>-15</v>
       </c>
       <c r="G17" s="13">
         <f>VLOOKUP(B17,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6571,11 +6572,11 @@
       </c>
       <c r="H17" s="13">
         <f>VLOOKUP(B17,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I17" s="17">
         <f t="shared" si="2"/>
-        <v>96.699999999999989</v>
+        <v>94.699999999999989</v>
       </c>
       <c r="J17" t="s">
         <v>55</v>
@@ -6595,14 +6596,14 @@
       </c>
       <c r="D18" s="22">
         <f t="shared" si="0"/>
-        <v>0.71764705882352942</v>
+        <v>0.77058823529411768</v>
       </c>
       <c r="E18" s="13">
         <v>88</v>
       </c>
       <c r="F18" s="12">
         <f t="shared" si="1"/>
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="G18" s="13">
         <f>VLOOKUP(B18,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6610,11 +6611,11 @@
       </c>
       <c r="H18" s="13">
         <f>VLOOKUP(B18,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="I18" s="17">
         <f t="shared" si="2"/>
-        <v>22.5</v>
+        <v>13.5</v>
       </c>
       <c r="J18" t="s">
         <v>58</v>
@@ -6634,14 +6635,14 @@
       </c>
       <c r="D19" s="22">
         <f t="shared" si="0"/>
-        <v>0.69480519480519476</v>
+        <v>0.72727272727272729</v>
       </c>
       <c r="E19" s="13">
         <v>95</v>
       </c>
       <c r="F19" s="12">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G19" s="13">
         <f>VLOOKUP(B19,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6649,11 +6650,11 @@
       </c>
       <c r="H19" s="13">
         <f>VLOOKUP(B19,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="I19" s="17">
         <f t="shared" si="2"/>
-        <v>23.900000000000006</v>
+        <v>18.900000000000006</v>
       </c>
       <c r="J19" t="s">
         <v>58</v>
@@ -6673,14 +6674,14 @@
       </c>
       <c r="D20" s="22">
         <f t="shared" si="0"/>
-        <v>0.68926553672316382</v>
+        <v>0.7344632768361582</v>
       </c>
       <c r="E20" s="13">
         <v>83</v>
       </c>
       <c r="F20" s="12">
         <f t="shared" si="1"/>
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="G20" s="13">
         <f>VLOOKUP(B20,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6688,11 +6689,11 @@
       </c>
       <c r="H20" s="13">
         <f>VLOOKUP(B20,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="I20" s="17">
         <f t="shared" si="2"/>
-        <v>28.449999999999989</v>
+        <v>20.449999999999989</v>
       </c>
       <c r="J20" t="s">
         <v>55</v>
@@ -6712,14 +6713,14 @@
       </c>
       <c r="D21" s="22">
         <f t="shared" si="0"/>
-        <v>0.65088757396449703</v>
+        <v>0.68047337278106512</v>
       </c>
       <c r="E21" s="13">
         <v>64</v>
       </c>
       <c r="F21" s="12">
         <f t="shared" si="1"/>
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="G21" s="13">
         <f>VLOOKUP(B21,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6727,11 +6728,11 @@
       </c>
       <c r="H21" s="13">
         <f>VLOOKUP(B21,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="I21" s="17">
         <f t="shared" si="2"/>
-        <v>33.650000000000006</v>
+        <v>28.650000000000006</v>
       </c>
       <c r="J21" t="s">
         <v>58</v>
@@ -6751,14 +6752,14 @@
       </c>
       <c r="D22" s="22">
         <f t="shared" si="0"/>
-        <v>0.30303030303030304</v>
+        <v>0.34848484848484851</v>
       </c>
       <c r="E22" s="13">
         <v>66</v>
       </c>
       <c r="F22" s="12">
         <f t="shared" si="1"/>
-        <v>-6</v>
+        <v>3</v>
       </c>
       <c r="G22" s="13">
         <f>VLOOKUP(B22,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6766,11 +6767,11 @@
       </c>
       <c r="H22" s="13">
         <f>VLOOKUP(B22,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="I22" s="17">
         <f t="shared" si="2"/>
-        <v>108.29999999999998</v>
+        <v>99.299999999999983</v>
       </c>
       <c r="J22" t="s">
         <v>58</v>
@@ -6790,14 +6791,14 @@
       </c>
       <c r="D23" s="22">
         <f t="shared" si="0"/>
-        <v>0.57971014492753625</v>
+        <v>0.63043478260869568</v>
       </c>
       <c r="E23" s="13">
         <v>70</v>
       </c>
       <c r="F23" s="12">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G23" s="13">
         <f>VLOOKUP(B23,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6805,11 +6806,11 @@
       </c>
       <c r="H23" s="13">
         <f>VLOOKUP(B23,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="I23" s="17">
         <f t="shared" si="2"/>
-        <v>37.299999999999997</v>
+        <v>30.299999999999997</v>
       </c>
       <c r="J23" t="s">
         <v>58</v>
@@ -6829,14 +6830,14 @@
       </c>
       <c r="D24" s="22">
         <f t="shared" si="0"/>
-        <v>0.62352941176470589</v>
+        <v>0.68823529411764706</v>
       </c>
       <c r="E24" s="13">
         <v>79</v>
       </c>
       <c r="F24" s="12">
         <f t="shared" si="1"/>
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="G24" s="13">
         <f>VLOOKUP(B24,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6844,11 +6845,11 @@
       </c>
       <c r="H24" s="13">
         <f>VLOOKUP(B24,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="I24" s="17">
         <f t="shared" si="2"/>
-        <v>38.5</v>
+        <v>27.5</v>
       </c>
       <c r="J24" t="s">
         <v>60</v>
@@ -6864,7 +6865,7 @@
       <c r="E25" s="14"/>
       <c r="F25" s="16">
         <f>+SUM(F16:F24)</f>
-        <v>168</v>
+        <v>227</v>
       </c>
       <c r="G25" s="8">
         <f>+SUM(G16:G24)</f>
@@ -6872,7 +6873,7 @@
       </c>
       <c r="H25" s="8">
         <f>+SUM(H16:H24)</f>
-        <v>895</v>
+        <v>954</v>
       </c>
       <c r="I25" s="8"/>
     </row>
@@ -6928,26 +6929,26 @@
       </c>
       <c r="D27" s="22">
         <f t="shared" si="0"/>
-        <v>0.57324840764331209</v>
+        <v>0.61006289308176098</v>
       </c>
       <c r="E27" s="13">
         <v>68</v>
       </c>
       <c r="F27" s="12">
         <f t="shared" si="1"/>
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G27" s="13">
         <f>VLOOKUP(B27,'Base Cobertura'!$A:$C,3,FALSE)</f>
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H27" s="13">
         <f>VLOOKUP(B27,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="I27" s="17">
         <f t="shared" si="2"/>
-        <v>43.449999999999989</v>
+        <v>38.150000000000006</v>
       </c>
       <c r="J27" t="s">
         <v>58</v>
@@ -6967,14 +6968,14 @@
       </c>
       <c r="D28" s="22">
         <f t="shared" si="0"/>
-        <v>0.63354037267080743</v>
+        <v>0.64596273291925466</v>
       </c>
       <c r="E28" s="13">
         <v>80</v>
       </c>
       <c r="F28" s="12">
         <f t="shared" si="1"/>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G28" s="13">
         <f>VLOOKUP(B28,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6982,11 +6983,11 @@
       </c>
       <c r="H28" s="13">
         <f>VLOOKUP(B28,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I28" s="17">
         <f t="shared" si="2"/>
-        <v>34.849999999999994</v>
+        <v>32.849999999999994</v>
       </c>
       <c r="J28" t="s">
         <v>58</v>
@@ -7006,14 +7007,14 @@
       </c>
       <c r="D29" s="22">
         <f t="shared" si="0"/>
-        <v>0.3253012048192771</v>
+        <v>0.34136546184738958</v>
       </c>
       <c r="E29" s="13">
         <v>68</v>
       </c>
       <c r="F29" s="12">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G29" s="13">
         <f>VLOOKUP(B29,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7021,11 +7022,11 @@
       </c>
       <c r="H29" s="13">
         <f>VLOOKUP(B29,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="I29" s="17">
         <f t="shared" si="2"/>
-        <v>130.65</v>
+        <v>126.65</v>
       </c>
       <c r="J29" t="s">
         <v>58</v>
@@ -7045,14 +7046,14 @@
       </c>
       <c r="D30" s="22">
         <f t="shared" si="0"/>
-        <v>0.74820143884892087</v>
+        <v>0.82014388489208634</v>
       </c>
       <c r="E30" s="13">
         <v>73</v>
       </c>
       <c r="F30" s="12">
         <f t="shared" si="1"/>
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="G30" s="13">
         <f>VLOOKUP(B30,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7060,11 +7061,11 @@
       </c>
       <c r="H30" s="13">
         <f>VLOOKUP(B30,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I30" s="17">
         <f t="shared" si="2"/>
-        <v>14.149999999999991</v>
+        <v>4.1499999999999915</v>
       </c>
       <c r="J30" t="s">
         <v>55</v>
@@ -7084,14 +7085,14 @@
       </c>
       <c r="D31" s="22">
         <f t="shared" si="0"/>
-        <v>0.49171270718232046</v>
+        <v>0.51381215469613262</v>
       </c>
       <c r="E31" s="13">
         <v>40</v>
       </c>
       <c r="F31" s="12">
         <f t="shared" si="1"/>
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G31" s="13">
         <f>VLOOKUP(B31,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7099,11 +7100,11 @@
       </c>
       <c r="H31" s="13">
         <f>VLOOKUP(B31,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="I31" s="17">
         <f t="shared" si="2"/>
-        <v>64.849999999999994</v>
+        <v>60.849999999999994</v>
       </c>
       <c r="J31" t="s">
         <v>58</v>
@@ -7123,14 +7124,14 @@
       </c>
       <c r="D32" s="22">
         <f t="shared" si="0"/>
-        <v>0.60119047619047616</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="E32" s="13">
         <v>67</v>
       </c>
       <c r="F32" s="12">
         <f t="shared" si="1"/>
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="G32" s="13">
         <f>VLOOKUP(B32,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7138,11 +7139,11 @@
       </c>
       <c r="H32" s="13">
         <f>VLOOKUP(B32,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="I32" s="17">
         <f t="shared" si="2"/>
-        <v>41.799999999999983</v>
+        <v>34.799999999999983</v>
       </c>
       <c r="J32" t="s">
         <v>58</v>
@@ -7162,14 +7163,14 @@
       </c>
       <c r="D33" s="22">
         <f t="shared" si="0"/>
-        <v>0.55952380952380953</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="E33" s="13">
         <v>66</v>
       </c>
       <c r="F33" s="12">
         <f t="shared" si="1"/>
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="G33" s="13">
         <f>VLOOKUP(B33,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7177,11 +7178,11 @@
       </c>
       <c r="H33" s="13">
         <f>VLOOKUP(B33,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="I33" s="17">
         <f t="shared" si="2"/>
-        <v>48.799999999999983</v>
+        <v>34.799999999999983</v>
       </c>
       <c r="J33" t="s">
         <v>58</v>
@@ -7240,14 +7241,14 @@
       </c>
       <c r="D35" s="22">
         <f t="shared" si="0"/>
-        <v>0.5449438202247191</v>
+        <v>0.5730337078651685</v>
       </c>
       <c r="E35" s="13">
         <v>81</v>
       </c>
       <c r="F35" s="12">
         <f t="shared" si="1"/>
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G35" s="13">
         <f>VLOOKUP(B35,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7255,11 +7256,11 @@
       </c>
       <c r="H35" s="13">
         <f>VLOOKUP(B35,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="I35" s="17">
         <f t="shared" si="2"/>
-        <v>54.299999999999983</v>
+        <v>49.299999999999983</v>
       </c>
       <c r="J35" t="s">
         <v>58</v>
@@ -7279,14 +7280,14 @@
       </c>
       <c r="D36" s="22">
         <f t="shared" si="0"/>
-        <v>4.3859649122807015E-2</v>
+        <v>5.2631578947368418E-2</v>
       </c>
       <c r="E36" s="13">
         <v>0</v>
       </c>
       <c r="F36" s="12">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G36" s="13">
         <f>VLOOKUP(B36,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7294,11 +7295,11 @@
       </c>
       <c r="H36" s="13">
         <f>VLOOKUP(B36,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I36" s="17">
         <f t="shared" si="2"/>
-        <v>91.899999999999991</v>
+        <v>90.899999999999991</v>
       </c>
       <c r="J36" t="s">
         <v>58</v>
@@ -7315,14 +7316,14 @@
       </c>
       <c r="D37" s="22">
         <f t="shared" si="0"/>
-        <v>0.14423076923076922</v>
+        <v>0.16346153846153846</v>
       </c>
       <c r="E37" s="13">
         <v>17</v>
       </c>
       <c r="F37" s="12">
         <f t="shared" si="1"/>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="G37" s="13">
         <f>VLOOKUP(B37,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7330,11 +7331,11 @@
       </c>
       <c r="H37" s="13">
         <f>VLOOKUP(B37,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I37" s="17">
         <f t="shared" si="2"/>
-        <v>73.399999999999991</v>
+        <v>71.399999999999991</v>
       </c>
       <c r="J37" t="s">
         <v>59</v>
@@ -7351,14 +7352,14 @@
       </c>
       <c r="D38" s="22">
         <f t="shared" si="0"/>
-        <v>0.61417322834645671</v>
+        <v>0.62204724409448819</v>
       </c>
       <c r="E38" s="13">
         <v>60</v>
       </c>
       <c r="F38" s="12">
         <f t="shared" si="1"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G38" s="13">
         <f>VLOOKUP(B38,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7366,11 +7367,11 @@
       </c>
       <c r="H38" s="13">
         <f>VLOOKUP(B38,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I38" s="17">
         <f t="shared" si="2"/>
-        <v>29.950000000000003</v>
+        <v>28.950000000000003</v>
       </c>
       <c r="J38" t="s">
         <v>55</v>
@@ -7386,15 +7387,15 @@
       <c r="E39" s="14"/>
       <c r="F39" s="8">
         <f>+SUM(F26:F38)</f>
-        <v>232</v>
+        <v>289</v>
       </c>
       <c r="G39" s="8">
         <f>+SUM(G26:G38)</f>
-        <v>1945</v>
+        <v>1947</v>
       </c>
       <c r="H39" s="8">
         <f>+SUM(H26:H38)</f>
-        <v>954</v>
+        <v>1011</v>
       </c>
       <c r="I39" s="8"/>
       <c r="L39" t="s">
@@ -7410,20 +7411,20 @@
       <c r="E40" s="6"/>
       <c r="F40" s="8">
         <f>+SUM(F39+F25+F15)</f>
-        <v>738</v>
+        <v>942</v>
       </c>
       <c r="G40" s="8">
         <f>+G15+G25+G39</f>
-        <v>5711</v>
+        <v>5715</v>
       </c>
       <c r="H40" s="8">
         <f>+H15+H25+H39</f>
-        <v>3066</v>
+        <v>3270</v>
       </c>
       <c r="I40" s="8"/>
       <c r="L40" s="1">
         <f>+H40/G40</f>
-        <v>0.5368586937489056</v>
+        <v>0.57217847769028873</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
@@ -7436,14 +7437,14 @@
       </c>
       <c r="D41" s="22">
         <f t="shared" ref="D41:D42" si="4">H41/G41</f>
-        <v>0.20661157024793389</v>
+        <v>0.19834710743801653</v>
       </c>
       <c r="E41" s="13">
         <v>60</v>
       </c>
       <c r="F41" s="12">
         <f t="shared" ref="F41:F42" si="5">+H41-E41</f>
-        <v>-35</v>
+        <v>-36</v>
       </c>
       <c r="G41" s="13">
         <f>VLOOKUP(B41,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7451,11 +7452,11 @@
       </c>
       <c r="H41" s="13">
         <f>VLOOKUP(B41,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I41" s="17">
         <f t="shared" ref="I41:I42" si="6">(+G41*$M$2)-H41</f>
-        <v>77.849999999999994</v>
+        <v>78.849999999999994</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
@@ -7468,14 +7469,14 @@
       </c>
       <c r="D42" s="22">
         <f t="shared" si="4"/>
-        <v>0.20491803278688525</v>
+        <v>0.21311475409836064</v>
       </c>
       <c r="E42" s="13">
         <v>60</v>
       </c>
       <c r="F42" s="12">
         <f t="shared" si="5"/>
-        <v>-35</v>
+        <v>-34</v>
       </c>
       <c r="G42" s="13">
         <f>VLOOKUP(B42,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7483,11 +7484,11 @@
       </c>
       <c r="H42" s="13">
         <f>VLOOKUP(B42,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I42" s="17">
         <f t="shared" si="6"/>
-        <v>78.7</v>
+        <v>77.7</v>
       </c>
     </row>
   </sheetData>
@@ -8064,7 +8065,7 @@
         <v>3</v>
       </c>
       <c r="C3" s="51">
-        <v>3430</v>
+        <v>3431</v>
       </c>
       <c r="G3" t="s">
         <v>222</v>
@@ -8073,7 +8074,7 @@
         <v>1</v>
       </c>
       <c r="I3" s="51">
-        <v>3430</v>
+        <v>3431</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -8081,7 +8082,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="51">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C4" s="51">
         <v>127</v>
@@ -8093,7 +8094,7 @@
         <v>2</v>
       </c>
       <c r="I4" s="51">
-        <v>3430</v>
+        <v>3431</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -8101,7 +8102,7 @@
         <v>10</v>
       </c>
       <c r="B5" s="51">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C5" s="51">
         <v>181</v>
@@ -8111,7 +8112,7 @@
       </c>
       <c r="H5" s="51"/>
       <c r="I5" s="51">
-        <v>3430</v>
+        <v>3431</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -8119,7 +8120,7 @@
         <v>100</v>
       </c>
       <c r="B6" s="51">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C6" s="51">
         <v>2027</v>
@@ -8129,7 +8130,7 @@
       </c>
       <c r="H6" s="51"/>
       <c r="I6" s="51">
-        <v>3430</v>
+        <v>3431</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -8137,10 +8138,10 @@
         <v>11</v>
       </c>
       <c r="B7" s="51">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="C7" s="51">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G7" t="s">
         <v>226</v>
@@ -8149,7 +8150,7 @@
         <v>2</v>
       </c>
       <c r="I7" s="51">
-        <v>3430</v>
+        <v>3431</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -8157,7 +8158,7 @@
         <v>12</v>
       </c>
       <c r="B8" s="51">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C8" s="51">
         <v>214</v>
@@ -8169,7 +8170,7 @@
         <v>2</v>
       </c>
       <c r="I8" s="51">
-        <v>3430</v>
+        <v>3431</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -8189,7 +8190,7 @@
         <v>1</v>
       </c>
       <c r="I9" s="51">
-        <v>3430</v>
+        <v>3431</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -8197,7 +8198,7 @@
         <v>15</v>
       </c>
       <c r="B10" s="51">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C10" s="51">
         <v>65</v>
@@ -8209,7 +8210,7 @@
         <v>1</v>
       </c>
       <c r="I10" s="51">
-        <v>3430</v>
+        <v>3431</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -8217,7 +8218,7 @@
         <v>16</v>
       </c>
       <c r="B11" s="51">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="C11" s="51">
         <v>198</v>
@@ -8227,7 +8228,7 @@
       </c>
       <c r="H11" s="51"/>
       <c r="I11" s="51">
-        <v>3430</v>
+        <v>3431</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -8235,7 +8236,7 @@
         <v>18</v>
       </c>
       <c r="B12" s="51">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="C12" s="51">
         <v>177</v>
@@ -8251,7 +8252,7 @@
         <v>222</v>
       </c>
       <c r="H12">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I12" s="51">
         <v>127</v>
@@ -8262,7 +8263,7 @@
         <v>19</v>
       </c>
       <c r="B13" s="51">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C13" s="51">
         <v>207</v>
@@ -8275,7 +8276,7 @@
         <v>223</v>
       </c>
       <c r="H13" s="51">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I13" s="51">
         <v>127</v>
@@ -8286,7 +8287,7 @@
         <v>2</v>
       </c>
       <c r="B14" s="51">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="C14" s="51">
         <v>138</v>
@@ -8310,7 +8311,7 @@
         <v>20</v>
       </c>
       <c r="B15" s="51">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="C15" s="51">
         <v>227</v>
@@ -8323,7 +8324,7 @@
         <v>225</v>
       </c>
       <c r="H15" s="51">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I15" s="51">
         <v>127</v>
@@ -8334,7 +8335,7 @@
         <v>21</v>
       </c>
       <c r="B16" s="51">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="C16" s="51">
         <v>170</v>
@@ -8347,7 +8348,7 @@
         <v>226</v>
       </c>
       <c r="H16" s="51">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I16" s="51">
         <v>127</v>
@@ -8358,7 +8359,7 @@
         <v>22</v>
       </c>
       <c r="B17" s="51">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C17" s="51">
         <v>73</v>
@@ -8371,7 +8372,7 @@
         <v>227</v>
       </c>
       <c r="H17" s="51">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I17" s="51">
         <v>127</v>
@@ -8382,7 +8383,7 @@
         <v>23</v>
       </c>
       <c r="B18" s="51">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C18" s="51">
         <v>154</v>
@@ -8395,7 +8396,7 @@
         <v>228</v>
       </c>
       <c r="H18" s="51">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I18" s="51">
         <v>127</v>
@@ -8406,7 +8407,7 @@
         <v>24</v>
       </c>
       <c r="B19" s="51">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C19" s="51">
         <v>178</v>
@@ -8419,7 +8420,7 @@
         <v>229</v>
       </c>
       <c r="H19" s="51">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I19" s="51">
         <v>127</v>
@@ -8443,7 +8444,7 @@
         <v>230</v>
       </c>
       <c r="H20">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I20" s="51">
         <v>127</v>
@@ -8470,7 +8471,7 @@
         <v>222</v>
       </c>
       <c r="H21" s="51">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I21" s="51">
         <v>181</v>
@@ -8481,7 +8482,7 @@
         <v>27</v>
       </c>
       <c r="B22" s="51">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="C22" s="51">
         <v>139</v>
@@ -8494,7 +8495,7 @@
         <v>223</v>
       </c>
       <c r="H22" s="51">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I22" s="51">
         <v>181</v>
@@ -8505,7 +8506,7 @@
         <v>28</v>
       </c>
       <c r="B23" s="51">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="C23" s="51">
         <v>168</v>
@@ -8518,7 +8519,7 @@
         <v>224</v>
       </c>
       <c r="H23" s="51">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I23" s="51">
         <v>181</v>
@@ -8529,7 +8530,7 @@
         <v>3</v>
       </c>
       <c r="B24" s="51">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="C24" s="51">
         <v>170</v>
@@ -8542,7 +8543,7 @@
         <v>225</v>
       </c>
       <c r="H24" s="51">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I24" s="51">
         <v>181</v>
@@ -8553,7 +8554,7 @@
         <v>30</v>
       </c>
       <c r="B25" s="51">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C25" s="51">
         <v>139</v>
@@ -8566,7 +8567,7 @@
         <v>226</v>
       </c>
       <c r="H25" s="51">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="I25" s="51">
         <v>181</v>
@@ -8577,7 +8578,7 @@
         <v>31</v>
       </c>
       <c r="B26" s="51">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C26" s="51">
         <v>160</v>
@@ -8590,7 +8591,7 @@
         <v>227</v>
       </c>
       <c r="H26" s="51">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I26" s="51">
         <v>181</v>
@@ -8614,7 +8615,7 @@
         <v>228</v>
       </c>
       <c r="H27" s="51">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I27" s="51">
         <v>181</v>
@@ -8625,7 +8626,7 @@
         <v>33</v>
       </c>
       <c r="B28" s="51">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="C28" s="51">
         <v>168</v>
@@ -8649,10 +8650,10 @@
         <v>36</v>
       </c>
       <c r="B29" s="51">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="C29" s="51">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E29">
         <f t="shared" si="1"/>
@@ -8662,7 +8663,7 @@
         <v>230</v>
       </c>
       <c r="H29" s="51">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I29" s="51">
         <v>181</v>
@@ -8689,7 +8690,7 @@
         <v>222</v>
       </c>
       <c r="H30" s="51">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I30" s="51">
         <v>2027</v>
@@ -8700,7 +8701,7 @@
         <v>4</v>
       </c>
       <c r="B31" s="51">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="C31" s="51">
         <v>182</v>
@@ -8713,7 +8714,7 @@
         <v>223</v>
       </c>
       <c r="H31" s="51">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I31" s="51">
         <v>2027</v>
@@ -8724,7 +8725,7 @@
         <v>40</v>
       </c>
       <c r="B32" s="51">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C32" s="51">
         <v>249</v>
@@ -8761,7 +8762,7 @@
         <v>225</v>
       </c>
       <c r="H33" s="51">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I33" s="51">
         <v>2027</v>
@@ -8796,7 +8797,7 @@
         <v>44</v>
       </c>
       <c r="B35" s="51">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C35" s="51">
         <v>169</v>
@@ -8809,7 +8810,7 @@
         <v>227</v>
       </c>
       <c r="H35" s="51">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I35" s="51">
         <v>2027</v>
@@ -8820,7 +8821,7 @@
         <v>49</v>
       </c>
       <c r="B36" s="51">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C36" s="51">
         <v>239</v>
@@ -8844,10 +8845,10 @@
         <v>5</v>
       </c>
       <c r="B37" s="51">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="C37" s="51">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E37">
         <f t="shared" si="2"/>
@@ -8881,7 +8882,7 @@
         <v>230</v>
       </c>
       <c r="H38" s="51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I38" s="51">
         <v>2027</v>
@@ -8892,7 +8893,7 @@
         <v>53</v>
       </c>
       <c r="B39" s="51">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C39" s="51">
         <v>105</v>
@@ -8908,10 +8909,10 @@
         <v>222</v>
       </c>
       <c r="H39" s="51">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="I39" s="51">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
@@ -8919,7 +8920,7 @@
         <v>54</v>
       </c>
       <c r="B40" s="51">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C40" s="51">
         <v>202</v>
@@ -8932,10 +8933,10 @@
         <v>223</v>
       </c>
       <c r="H40" s="51">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I40" s="51">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
@@ -8943,7 +8944,7 @@
         <v>56</v>
       </c>
       <c r="B41">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="C41" s="51">
         <v>198</v>
@@ -8956,10 +8957,10 @@
         <v>224</v>
       </c>
       <c r="H41" s="51">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="I41" s="51">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
@@ -8967,7 +8968,7 @@
         <v>57</v>
       </c>
       <c r="B42" s="51">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C42" s="51">
         <v>104</v>
@@ -8980,10 +8981,10 @@
         <v>225</v>
       </c>
       <c r="H42" s="51">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I42" s="51">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
@@ -8991,7 +8992,7 @@
         <v>58</v>
       </c>
       <c r="B43" s="51">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C43" s="51">
         <v>121</v>
@@ -9004,10 +9005,10 @@
         <v>226</v>
       </c>
       <c r="H43" s="51">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="I43" s="51">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
@@ -9015,7 +9016,7 @@
         <v>59</v>
       </c>
       <c r="B44" s="51">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C44" s="51">
         <v>122</v>
@@ -9028,10 +9029,10 @@
         <v>227</v>
       </c>
       <c r="H44" s="51">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I44" s="51">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
@@ -9039,7 +9040,7 @@
         <v>7</v>
       </c>
       <c r="B45" s="51">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C45" s="51">
         <v>114</v>
@@ -9052,10 +9053,10 @@
         <v>228</v>
       </c>
       <c r="H45" s="51">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I45" s="51">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
@@ -9063,7 +9064,7 @@
         <v>8</v>
       </c>
       <c r="B46" s="51">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="C46" s="51">
         <v>195</v>
@@ -9076,10 +9077,10 @@
         <v>229</v>
       </c>
       <c r="H46" s="51">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I46" s="51">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
@@ -9087,7 +9088,7 @@
         <v>9</v>
       </c>
       <c r="B47" s="51">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C47" s="51">
         <v>161</v>
@@ -9100,10 +9101,10 @@
         <v>230</v>
       </c>
       <c r="H47" s="51">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I47" s="51">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
@@ -9120,7 +9121,7 @@
         <v>222</v>
       </c>
       <c r="H48" s="51">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I48" s="51">
         <v>214</v>
@@ -9137,7 +9138,7 @@
         <v>223</v>
       </c>
       <c r="H49" s="51">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I49" s="51">
         <v>214</v>
@@ -9152,7 +9153,7 @@
         <v>224</v>
       </c>
       <c r="H50" s="51">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I50" s="51">
         <v>214</v>
@@ -9167,7 +9168,7 @@
         <v>225</v>
       </c>
       <c r="H51" s="51">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I51" s="51">
         <v>214</v>
@@ -9182,7 +9183,7 @@
         <v>226</v>
       </c>
       <c r="H52" s="51">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="I52" s="51">
         <v>214</v>
@@ -9197,7 +9198,7 @@
         <v>227</v>
       </c>
       <c r="H53" s="51">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="I53" s="51">
         <v>214</v>
@@ -9212,7 +9213,7 @@
         <v>228</v>
       </c>
       <c r="H54" s="51">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I54" s="51">
         <v>214</v>
@@ -9227,7 +9228,7 @@
         <v>229</v>
       </c>
       <c r="H55" s="51">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I55" s="51">
         <v>214</v>
@@ -9242,7 +9243,7 @@
         <v>230</v>
       </c>
       <c r="H56" s="51">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I56" s="51">
         <v>214</v>
@@ -9335,7 +9336,7 @@
         <v>227</v>
       </c>
       <c r="H62" s="51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I62" s="51">
         <v>489</v>
@@ -9396,7 +9397,7 @@
         <v>222</v>
       </c>
       <c r="H66" s="51">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I66" s="51">
         <v>65</v>
@@ -9411,7 +9412,7 @@
         <v>223</v>
       </c>
       <c r="H67" s="51">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I67" s="51">
         <v>65</v>
@@ -9426,7 +9427,7 @@
         <v>224</v>
       </c>
       <c r="H68" s="51">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I68" s="51">
         <v>65</v>
@@ -9441,7 +9442,7 @@
         <v>225</v>
       </c>
       <c r="H69" s="51">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I69" s="51">
         <v>65</v>
@@ -9456,7 +9457,7 @@
         <v>226</v>
       </c>
       <c r="H70" s="51">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I70" s="51">
         <v>65</v>
@@ -9471,7 +9472,7 @@
         <v>227</v>
       </c>
       <c r="H71" s="51">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I71" s="51">
         <v>65</v>
@@ -9486,7 +9487,7 @@
         <v>228</v>
       </c>
       <c r="H72" s="51">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I72" s="51">
         <v>65</v>
@@ -9501,7 +9502,7 @@
         <v>229</v>
       </c>
       <c r="H73" s="51">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I73" s="51">
         <v>65</v>
@@ -9516,7 +9517,7 @@
         <v>230</v>
       </c>
       <c r="H74" s="51">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I74" s="51">
         <v>65</v>
@@ -9534,7 +9535,7 @@
         <v>222</v>
       </c>
       <c r="H75" s="51">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I75" s="51">
         <v>198</v>
@@ -9549,7 +9550,7 @@
         <v>223</v>
       </c>
       <c r="H76">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I76" s="51">
         <v>198</v>
@@ -9564,7 +9565,7 @@
         <v>224</v>
       </c>
       <c r="H77" s="51">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="I77" s="51">
         <v>198</v>
@@ -9579,7 +9580,7 @@
         <v>225</v>
       </c>
       <c r="H78" s="51">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I78" s="51">
         <v>198</v>
@@ -9594,7 +9595,7 @@
         <v>226</v>
       </c>
       <c r="H79" s="51">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="I79" s="51">
         <v>198</v>
@@ -9609,7 +9610,7 @@
         <v>227</v>
       </c>
       <c r="H80" s="51">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="I80" s="51">
         <v>198</v>
@@ -9624,7 +9625,7 @@
         <v>228</v>
       </c>
       <c r="H81" s="51">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I81" s="51">
         <v>198</v>
@@ -9639,7 +9640,7 @@
         <v>229</v>
       </c>
       <c r="H82" s="51">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I82" s="51">
         <v>198</v>
@@ -9654,7 +9655,7 @@
         <v>230</v>
       </c>
       <c r="H83" s="51">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I83" s="51">
         <v>198</v>
@@ -9672,7 +9673,7 @@
         <v>222</v>
       </c>
       <c r="H84" s="51">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I84" s="51">
         <v>177</v>
@@ -9687,7 +9688,7 @@
         <v>223</v>
       </c>
       <c r="H85" s="51">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I85" s="51">
         <v>177</v>
@@ -9702,7 +9703,7 @@
         <v>224</v>
       </c>
       <c r="H86" s="51">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I86" s="51">
         <v>177</v>
@@ -9717,7 +9718,7 @@
         <v>225</v>
       </c>
       <c r="H87" s="51">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="I87" s="51">
         <v>177</v>
@@ -9732,7 +9733,7 @@
         <v>226</v>
       </c>
       <c r="H88" s="51">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="I88" s="51">
         <v>177</v>
@@ -9747,7 +9748,7 @@
         <v>227</v>
       </c>
       <c r="H89" s="51">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="I89" s="51">
         <v>177</v>
@@ -9762,7 +9763,7 @@
         <v>228</v>
       </c>
       <c r="H90" s="51">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I90" s="51">
         <v>177</v>
@@ -9777,7 +9778,7 @@
         <v>229</v>
       </c>
       <c r="H91" s="51">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I91" s="51">
         <v>177</v>
@@ -9792,7 +9793,7 @@
         <v>230</v>
       </c>
       <c r="H92" s="51">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="I92" s="51">
         <v>177</v>
@@ -9810,7 +9811,7 @@
         <v>222</v>
       </c>
       <c r="H93" s="51">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I93" s="51">
         <v>207</v>
@@ -9825,7 +9826,7 @@
         <v>223</v>
       </c>
       <c r="H94" s="51">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I94" s="51">
         <v>207</v>
@@ -9840,7 +9841,7 @@
         <v>224</v>
       </c>
       <c r="H95" s="51">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I95" s="51">
         <v>207</v>
@@ -9855,7 +9856,7 @@
         <v>225</v>
       </c>
       <c r="H96" s="51">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I96" s="51">
         <v>207</v>
@@ -9870,7 +9871,7 @@
         <v>226</v>
       </c>
       <c r="H97" s="51">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="I97" s="51">
         <v>207</v>
@@ -9900,7 +9901,7 @@
         <v>228</v>
       </c>
       <c r="H99" s="51">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I99" s="51">
         <v>207</v>
@@ -9930,7 +9931,7 @@
         <v>230</v>
       </c>
       <c r="H101" s="51">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I101" s="51">
         <v>207</v>
@@ -9963,7 +9964,7 @@
         <v>223</v>
       </c>
       <c r="H103" s="51">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I103" s="51">
         <v>138</v>
@@ -9978,7 +9979,7 @@
         <v>224</v>
       </c>
       <c r="H104" s="51">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I104" s="51">
         <v>138</v>
@@ -9993,7 +9994,7 @@
         <v>225</v>
       </c>
       <c r="H105" s="51">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I105" s="51">
         <v>138</v>
@@ -10008,7 +10009,7 @@
         <v>226</v>
       </c>
       <c r="H106" s="51">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="I106" s="51">
         <v>138</v>
@@ -10023,7 +10024,7 @@
         <v>227</v>
       </c>
       <c r="H107" s="51">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I107" s="51">
         <v>138</v>
@@ -10038,7 +10039,7 @@
         <v>228</v>
       </c>
       <c r="H108" s="51">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I108" s="51">
         <v>138</v>
@@ -10053,7 +10054,7 @@
         <v>229</v>
       </c>
       <c r="H109" s="51">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I109" s="51">
         <v>138</v>
@@ -10068,7 +10069,7 @@
         <v>230</v>
       </c>
       <c r="H110" s="51">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I110" s="51">
         <v>138</v>
@@ -10086,7 +10087,7 @@
         <v>222</v>
       </c>
       <c r="H111" s="51">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="I111" s="51">
         <v>227</v>
@@ -10101,7 +10102,7 @@
         <v>223</v>
       </c>
       <c r="H112" s="51">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="I112" s="51">
         <v>227</v>
@@ -10116,7 +10117,7 @@
         <v>224</v>
       </c>
       <c r="H113" s="51">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="I113" s="51">
         <v>227</v>
@@ -10131,7 +10132,7 @@
         <v>225</v>
       </c>
       <c r="H114" s="51">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="I114" s="51">
         <v>227</v>
@@ -10146,7 +10147,7 @@
         <v>226</v>
       </c>
       <c r="H115" s="51">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="I115" s="51">
         <v>227</v>
@@ -10161,7 +10162,7 @@
         <v>227</v>
       </c>
       <c r="H116">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I116" s="51">
         <v>227</v>
@@ -10176,7 +10177,7 @@
         <v>228</v>
       </c>
       <c r="H117" s="51">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I117" s="51">
         <v>227</v>
@@ -10191,7 +10192,7 @@
         <v>229</v>
       </c>
       <c r="H118" s="51">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I118" s="51">
         <v>227</v>
@@ -10206,7 +10207,7 @@
         <v>230</v>
       </c>
       <c r="H119" s="51">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I119" s="51">
         <v>227</v>
@@ -10224,7 +10225,7 @@
         <v>222</v>
       </c>
       <c r="H120" s="51">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I120" s="51">
         <v>170</v>
@@ -10239,7 +10240,7 @@
         <v>223</v>
       </c>
       <c r="H121" s="51">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="I121" s="51">
         <v>170</v>
@@ -10254,7 +10255,7 @@
         <v>224</v>
       </c>
       <c r="H122" s="51">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="I122" s="51">
         <v>170</v>
@@ -10269,7 +10270,7 @@
         <v>225</v>
       </c>
       <c r="H123" s="51">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I123" s="51">
         <v>170</v>
@@ -10284,7 +10285,7 @@
         <v>226</v>
       </c>
       <c r="H124">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="I124" s="51">
         <v>170</v>
@@ -10299,7 +10300,7 @@
         <v>227</v>
       </c>
       <c r="H125" s="51">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I125" s="51">
         <v>170</v>
@@ -10314,7 +10315,7 @@
         <v>228</v>
       </c>
       <c r="H126" s="51">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I126" s="51">
         <v>170</v>
@@ -10329,7 +10330,7 @@
         <v>229</v>
       </c>
       <c r="H127" s="51">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I127" s="51">
         <v>170</v>
@@ -10344,7 +10345,7 @@
         <v>230</v>
       </c>
       <c r="H128" s="51">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I128" s="51">
         <v>170</v>
@@ -10362,7 +10363,7 @@
         <v>222</v>
       </c>
       <c r="H129" s="51">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I129" s="51">
         <v>73</v>
@@ -10377,7 +10378,7 @@
         <v>223</v>
       </c>
       <c r="H130" s="51">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I130" s="51">
         <v>73</v>
@@ -10407,7 +10408,7 @@
         <v>225</v>
       </c>
       <c r="H132" s="51">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I132" s="51">
         <v>73</v>
@@ -10422,7 +10423,7 @@
         <v>226</v>
       </c>
       <c r="H133" s="51">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I133" s="51">
         <v>73</v>
@@ -10437,7 +10438,7 @@
         <v>227</v>
       </c>
       <c r="H134" s="51">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I134" s="51">
         <v>73</v>
@@ -10452,7 +10453,7 @@
         <v>228</v>
       </c>
       <c r="H135" s="51">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I135" s="51">
         <v>73</v>
@@ -10467,7 +10468,7 @@
         <v>229</v>
       </c>
       <c r="H136" s="51">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I136" s="51">
         <v>73</v>
@@ -10482,7 +10483,7 @@
         <v>230</v>
       </c>
       <c r="H137" s="51">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I137" s="51">
         <v>73</v>
@@ -10500,7 +10501,7 @@
         <v>222</v>
       </c>
       <c r="H138" s="51">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I138" s="51">
         <v>154</v>
@@ -10515,7 +10516,7 @@
         <v>223</v>
       </c>
       <c r="H139" s="51">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I139" s="51">
         <v>154</v>
@@ -10530,7 +10531,7 @@
         <v>224</v>
       </c>
       <c r="H140">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I140" s="51">
         <v>154</v>
@@ -10545,7 +10546,7 @@
         <v>225</v>
       </c>
       <c r="H141" s="51">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I141" s="51">
         <v>154</v>
@@ -10560,7 +10561,7 @@
         <v>226</v>
       </c>
       <c r="H142" s="51">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="I142" s="51">
         <v>154</v>
@@ -10575,7 +10576,7 @@
         <v>227</v>
       </c>
       <c r="H143" s="51">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I143" s="51">
         <v>154</v>
@@ -10605,7 +10606,7 @@
         <v>229</v>
       </c>
       <c r="H145" s="51">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I145" s="51">
         <v>154</v>
@@ -10620,7 +10621,7 @@
         <v>230</v>
       </c>
       <c r="H146" s="51">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I146" s="51">
         <v>154</v>
@@ -10638,7 +10639,7 @@
         <v>222</v>
       </c>
       <c r="H147" s="51">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I147" s="51">
         <v>178</v>
@@ -10683,7 +10684,7 @@
         <v>225</v>
       </c>
       <c r="H150" s="51">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I150" s="51">
         <v>178</v>
@@ -10698,7 +10699,7 @@
         <v>226</v>
       </c>
       <c r="H151" s="51">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="I151" s="51">
         <v>178</v>
@@ -10713,7 +10714,7 @@
         <v>227</v>
       </c>
       <c r="H152" s="51">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I152" s="51">
         <v>178</v>
@@ -10728,7 +10729,7 @@
         <v>228</v>
       </c>
       <c r="H153" s="51">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I153" s="51">
         <v>178</v>
@@ -10743,7 +10744,7 @@
         <v>229</v>
       </c>
       <c r="H154" s="51">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I154" s="51">
         <v>178</v>
@@ -10758,7 +10759,7 @@
         <v>230</v>
       </c>
       <c r="H155" s="51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I155" s="51">
         <v>178</v>
@@ -11052,7 +11053,7 @@
         <v>222</v>
       </c>
       <c r="H174" s="51">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I174" s="51">
         <v>139</v>
@@ -11067,7 +11068,7 @@
         <v>223</v>
       </c>
       <c r="H175" s="51">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I175" s="51">
         <v>139</v>
@@ -11082,7 +11083,7 @@
         <v>224</v>
       </c>
       <c r="H176" s="51">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="I176" s="51">
         <v>139</v>
@@ -11097,7 +11098,7 @@
         <v>225</v>
       </c>
       <c r="H177" s="51">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I177" s="51">
         <v>139</v>
@@ -11112,7 +11113,7 @@
         <v>226</v>
       </c>
       <c r="H178" s="51">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="I178" s="51">
         <v>139</v>
@@ -11127,7 +11128,7 @@
         <v>227</v>
       </c>
       <c r="H179" s="51">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="I179" s="51">
         <v>139</v>
@@ -11142,7 +11143,7 @@
         <v>228</v>
       </c>
       <c r="H180">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I180" s="51">
         <v>139</v>
@@ -11157,7 +11158,7 @@
         <v>229</v>
       </c>
       <c r="H181" s="51">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I181" s="51">
         <v>139</v>
@@ -11172,7 +11173,7 @@
         <v>230</v>
       </c>
       <c r="H182" s="51">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I182" s="51">
         <v>139</v>
@@ -11190,7 +11191,7 @@
         <v>222</v>
       </c>
       <c r="H183" s="51">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I183" s="51">
         <v>168</v>
@@ -11205,7 +11206,7 @@
         <v>223</v>
       </c>
       <c r="H184" s="51">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I184" s="51">
         <v>168</v>
@@ -11220,7 +11221,7 @@
         <v>224</v>
       </c>
       <c r="H185" s="51">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I185" s="51">
         <v>168</v>
@@ -11235,7 +11236,7 @@
         <v>225</v>
       </c>
       <c r="H186">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I186" s="51">
         <v>168</v>
@@ -11250,7 +11251,7 @@
         <v>226</v>
       </c>
       <c r="H187" s="51">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="I187" s="51">
         <v>168</v>
@@ -11265,7 +11266,7 @@
         <v>227</v>
       </c>
       <c r="H188" s="51">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I188" s="51">
         <v>168</v>
@@ -11280,7 +11281,7 @@
         <v>228</v>
       </c>
       <c r="H189" s="51">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I189" s="51">
         <v>168</v>
@@ -11295,7 +11296,7 @@
         <v>229</v>
       </c>
       <c r="H190" s="51">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I190" s="51">
         <v>168</v>
@@ -11310,7 +11311,7 @@
         <v>230</v>
       </c>
       <c r="H191" s="51">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I191" s="51">
         <v>168</v>
@@ -11328,7 +11329,7 @@
         <v>222</v>
       </c>
       <c r="H192" s="51">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I192" s="51">
         <v>170</v>
@@ -11343,7 +11344,7 @@
         <v>223</v>
       </c>
       <c r="H193" s="51">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I193" s="51">
         <v>170</v>
@@ -11358,7 +11359,7 @@
         <v>224</v>
       </c>
       <c r="H194" s="51">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="I194" s="51">
         <v>170</v>
@@ -11373,7 +11374,7 @@
         <v>225</v>
       </c>
       <c r="H195" s="51">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I195" s="51">
         <v>170</v>
@@ -11388,7 +11389,7 @@
         <v>226</v>
       </c>
       <c r="H196">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="I196" s="51">
         <v>170</v>
@@ -11403,7 +11404,7 @@
         <v>227</v>
       </c>
       <c r="H197" s="51">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="I197" s="51">
         <v>170</v>
@@ -11433,7 +11434,7 @@
         <v>229</v>
       </c>
       <c r="H199" s="51">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I199" s="51">
         <v>170</v>
@@ -11448,7 +11449,7 @@
         <v>230</v>
       </c>
       <c r="H200" s="51">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I200" s="51">
         <v>170</v>
@@ -11466,7 +11467,7 @@
         <v>222</v>
       </c>
       <c r="H201" s="51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I201" s="51">
         <v>139</v>
@@ -11496,7 +11497,7 @@
         <v>224</v>
       </c>
       <c r="H203" s="51">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I203" s="51">
         <v>139</v>
@@ -11524,7 +11525,7 @@
         <v>226</v>
       </c>
       <c r="H205" s="51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I205" s="51">
         <v>139</v>
@@ -11552,7 +11553,7 @@
         <v>228</v>
       </c>
       <c r="H207" s="51">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I207" s="51">
         <v>139</v>
@@ -11596,7 +11597,7 @@
         <v>222</v>
       </c>
       <c r="H210" s="51">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I210" s="51">
         <v>160</v>
@@ -11611,7 +11612,7 @@
         <v>223</v>
       </c>
       <c r="H211" s="51">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I211" s="51">
         <v>160</v>
@@ -11626,7 +11627,7 @@
         <v>224</v>
       </c>
       <c r="H212">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I212" s="51">
         <v>160</v>
@@ -11641,7 +11642,7 @@
         <v>225</v>
       </c>
       <c r="H213" s="51">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I213" s="51">
         <v>160</v>
@@ -11656,7 +11657,7 @@
         <v>226</v>
       </c>
       <c r="H214" s="51">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I214" s="51">
         <v>160</v>
@@ -11671,7 +11672,7 @@
         <v>227</v>
       </c>
       <c r="H215" s="51">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I215" s="51">
         <v>160</v>
@@ -11686,7 +11687,7 @@
         <v>228</v>
       </c>
       <c r="H216" s="51">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I216" s="51">
         <v>160</v>
@@ -11716,7 +11717,7 @@
         <v>230</v>
       </c>
       <c r="H218" s="51">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I218" s="51">
         <v>160</v>
@@ -11734,7 +11735,7 @@
         <v>222</v>
       </c>
       <c r="H219" s="51">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I219" s="51">
         <v>57</v>
@@ -11749,7 +11750,7 @@
         <v>223</v>
       </c>
       <c r="H220" s="51">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I220" s="51">
         <v>57</v>
@@ -11764,7 +11765,7 @@
         <v>224</v>
       </c>
       <c r="H221" s="51">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I221" s="51">
         <v>57</v>
@@ -11794,7 +11795,7 @@
         <v>226</v>
       </c>
       <c r="H223" s="51">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I223" s="51">
         <v>57</v>
@@ -11824,7 +11825,7 @@
         <v>228</v>
       </c>
       <c r="H225" s="51">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I225" s="51">
         <v>57</v>
@@ -11872,7 +11873,7 @@
         <v>222</v>
       </c>
       <c r="H228" s="51">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="I228" s="51">
         <v>168</v>
@@ -11887,7 +11888,7 @@
         <v>223</v>
       </c>
       <c r="H229" s="51">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I229" s="51">
         <v>168</v>
@@ -11902,7 +11903,7 @@
         <v>224</v>
       </c>
       <c r="H230" s="51">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I230" s="51">
         <v>168</v>
@@ -11917,7 +11918,7 @@
         <v>225</v>
       </c>
       <c r="H231" s="51">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="I231" s="51">
         <v>168</v>
@@ -11932,7 +11933,7 @@
         <v>226</v>
       </c>
       <c r="H232" s="51">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="I232" s="51">
         <v>168</v>
@@ -11947,7 +11948,7 @@
         <v>227</v>
       </c>
       <c r="H233" s="51">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="I233" s="51">
         <v>168</v>
@@ -11962,7 +11963,7 @@
         <v>228</v>
       </c>
       <c r="H234" s="51">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I234" s="51">
         <v>168</v>
@@ -11977,7 +11978,7 @@
         <v>229</v>
       </c>
       <c r="H235" s="51">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I235" s="51">
         <v>168</v>
@@ -12010,10 +12011,10 @@
         <v>222</v>
       </c>
       <c r="H237" s="51">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I237" s="51">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="238" spans="5:9" x14ac:dyDescent="0.25">
@@ -12025,10 +12026,10 @@
         <v>223</v>
       </c>
       <c r="H238" s="51">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I238" s="51">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="239" spans="5:9" x14ac:dyDescent="0.25">
@@ -12040,10 +12041,10 @@
         <v>224</v>
       </c>
       <c r="H239" s="51">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="I239" s="51">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="240" spans="5:9" x14ac:dyDescent="0.25">
@@ -12055,10 +12056,10 @@
         <v>225</v>
       </c>
       <c r="H240" s="51">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I240" s="51">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="241" spans="5:9" x14ac:dyDescent="0.25">
@@ -12070,10 +12071,10 @@
         <v>226</v>
       </c>
       <c r="H241" s="51">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I241" s="51">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="242" spans="5:9" x14ac:dyDescent="0.25">
@@ -12088,7 +12089,7 @@
         <v>33</v>
       </c>
       <c r="I242" s="51">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="243" spans="5:9" x14ac:dyDescent="0.25">
@@ -12100,10 +12101,10 @@
         <v>228</v>
       </c>
       <c r="H243" s="51">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I243" s="51">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="244" spans="5:9" x14ac:dyDescent="0.25">
@@ -12118,7 +12119,7 @@
         <v>8</v>
       </c>
       <c r="I244" s="51">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="245" spans="5:9" x14ac:dyDescent="0.25">
@@ -12130,10 +12131,10 @@
         <v>230</v>
       </c>
       <c r="H245" s="51">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I245" s="51">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="246" spans="5:9" x14ac:dyDescent="0.25">
@@ -12148,7 +12149,7 @@
         <v>222</v>
       </c>
       <c r="H246" s="51">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I246" s="51">
         <v>142</v>
@@ -12163,7 +12164,7 @@
         <v>223</v>
       </c>
       <c r="H247" s="51">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I247" s="51">
         <v>142</v>
@@ -12178,7 +12179,7 @@
         <v>224</v>
       </c>
       <c r="H248" s="51">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I248" s="51">
         <v>142</v>
@@ -12253,7 +12254,7 @@
         <v>229</v>
       </c>
       <c r="H253" s="51">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I253" s="51">
         <v>142</v>
@@ -12286,7 +12287,7 @@
         <v>222</v>
       </c>
       <c r="H255" s="51">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I255" s="51">
         <v>182</v>
@@ -12301,7 +12302,7 @@
         <v>223</v>
       </c>
       <c r="H256" s="51">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I256" s="51">
         <v>182</v>
@@ -12316,7 +12317,7 @@
         <v>224</v>
       </c>
       <c r="H257" s="51">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="I257" s="51">
         <v>182</v>
@@ -12331,7 +12332,7 @@
         <v>225</v>
       </c>
       <c r="H258">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I258" s="51">
         <v>182</v>
@@ -12346,7 +12347,7 @@
         <v>226</v>
       </c>
       <c r="H259" s="51">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="I259" s="51">
         <v>182</v>
@@ -12361,7 +12362,7 @@
         <v>227</v>
       </c>
       <c r="H260">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I260" s="51">
         <v>182</v>
@@ -12391,7 +12392,7 @@
         <v>229</v>
       </c>
       <c r="H262" s="51">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I262" s="51">
         <v>182</v>
@@ -12406,7 +12407,7 @@
         <v>230</v>
       </c>
       <c r="H263" s="51">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I263" s="51">
         <v>182</v>
@@ -12454,7 +12455,7 @@
         <v>224</v>
       </c>
       <c r="H266" s="51">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I266" s="51">
         <v>249</v>
@@ -12469,7 +12470,7 @@
         <v>225</v>
       </c>
       <c r="H267" s="51">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I267" s="51">
         <v>249</v>
@@ -12484,7 +12485,7 @@
         <v>226</v>
       </c>
       <c r="H268">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I268" s="51">
         <v>249</v>
@@ -12499,7 +12500,7 @@
         <v>227</v>
       </c>
       <c r="H269" s="51">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I269" s="51">
         <v>249</v>
@@ -12514,7 +12515,7 @@
         <v>228</v>
       </c>
       <c r="H270" s="51">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I270" s="51">
         <v>249</v>
@@ -12529,7 +12530,7 @@
         <v>229</v>
       </c>
       <c r="H271" s="51">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I271" s="51">
         <v>249</v>
@@ -12544,7 +12545,7 @@
         <v>230</v>
       </c>
       <c r="H272" s="51">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I272" s="51">
         <v>249</v>
@@ -12814,7 +12815,7 @@
         <v>222</v>
       </c>
       <c r="H291">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I291" s="51">
         <v>169</v>
@@ -12829,7 +12830,7 @@
         <v>223</v>
       </c>
       <c r="H292">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I292" s="51">
         <v>169</v>
@@ -12844,7 +12845,7 @@
         <v>224</v>
       </c>
       <c r="H293">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I293" s="51">
         <v>169</v>
@@ -12859,7 +12860,7 @@
         <v>225</v>
       </c>
       <c r="H294">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I294" s="51">
         <v>169</v>
@@ -12874,7 +12875,7 @@
         <v>226</v>
       </c>
       <c r="H295">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="I295" s="51">
         <v>169</v>
@@ -12889,7 +12890,7 @@
         <v>227</v>
       </c>
       <c r="H296">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="I296" s="51">
         <v>169</v>
@@ -12919,7 +12920,7 @@
         <v>229</v>
       </c>
       <c r="H298">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I298" s="51">
         <v>169</v>
@@ -12934,7 +12935,7 @@
         <v>230</v>
       </c>
       <c r="H299" s="51">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I299" s="51">
         <v>169</v>
@@ -12982,7 +12983,7 @@
         <v>224</v>
       </c>
       <c r="H302" s="51">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I302" s="51">
         <v>239</v>
@@ -13012,7 +13013,7 @@
         <v>226</v>
       </c>
       <c r="H304" s="51">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I304" s="51">
         <v>239</v>
@@ -13042,7 +13043,7 @@
         <v>228</v>
       </c>
       <c r="H306" s="51">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I306" s="51">
         <v>239</v>
@@ -13057,7 +13058,7 @@
         <v>229</v>
       </c>
       <c r="H307">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I307" s="51">
         <v>239</v>
@@ -13072,7 +13073,7 @@
         <v>230</v>
       </c>
       <c r="H308">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I308" s="51">
         <v>239</v>
@@ -13090,10 +13091,10 @@
         <v>222</v>
       </c>
       <c r="H309">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="I309" s="51">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="310" spans="5:9" x14ac:dyDescent="0.25">
@@ -13105,10 +13106,10 @@
         <v>223</v>
       </c>
       <c r="H310">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="I310" s="51">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="311" spans="5:9" x14ac:dyDescent="0.25">
@@ -13120,10 +13121,10 @@
         <v>224</v>
       </c>
       <c r="H311">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="I311" s="51">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="312" spans="5:9" x14ac:dyDescent="0.25">
@@ -13135,10 +13136,10 @@
         <v>225</v>
       </c>
       <c r="H312">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="I312" s="51">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="313" spans="5:9" x14ac:dyDescent="0.25">
@@ -13150,10 +13151,10 @@
         <v>226</v>
       </c>
       <c r="H313">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="I313" s="51">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="314" spans="5:9" x14ac:dyDescent="0.25">
@@ -13165,10 +13166,10 @@
         <v>227</v>
       </c>
       <c r="H314">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="I314" s="51">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="315" spans="5:9" x14ac:dyDescent="0.25">
@@ -13180,10 +13181,10 @@
         <v>228</v>
       </c>
       <c r="H315" s="51">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I315" s="51">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="316" spans="5:9" x14ac:dyDescent="0.25">
@@ -13195,10 +13196,10 @@
         <v>229</v>
       </c>
       <c r="H316">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I316" s="51">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="317" spans="5:9" x14ac:dyDescent="0.25">
@@ -13210,10 +13211,10 @@
         <v>230</v>
       </c>
       <c r="H317" s="51">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I317" s="51">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="318" spans="5:9" x14ac:dyDescent="0.25">
@@ -13243,7 +13244,7 @@
         <v>223</v>
       </c>
       <c r="H319" s="51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I319" s="51">
         <v>101</v>
@@ -13430,7 +13431,7 @@
         <v>228</v>
       </c>
       <c r="H333" s="51">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I333" s="51">
         <v>105</v>
@@ -13489,7 +13490,7 @@
         <v>223</v>
       </c>
       <c r="H337" s="51">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I337" s="51">
         <v>202</v>
@@ -13504,7 +13505,7 @@
         <v>224</v>
       </c>
       <c r="H338" s="51">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I338" s="51">
         <v>202</v>
@@ -13519,7 +13520,7 @@
         <v>225</v>
       </c>
       <c r="H339" s="51">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I339" s="51">
         <v>202</v>
@@ -13534,7 +13535,7 @@
         <v>226</v>
       </c>
       <c r="H340">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I340" s="51">
         <v>202</v>
@@ -13549,7 +13550,7 @@
         <v>227</v>
       </c>
       <c r="H341" s="51">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I341" s="51">
         <v>202</v>
@@ -13579,7 +13580,7 @@
         <v>229</v>
       </c>
       <c r="H343" s="51">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I343" s="51">
         <v>202</v>
@@ -13594,7 +13595,7 @@
         <v>230</v>
       </c>
       <c r="H344" s="51">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I344" s="51">
         <v>202</v>
@@ -13612,7 +13613,7 @@
         <v>222</v>
       </c>
       <c r="H345">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I345" s="51">
         <v>198</v>
@@ -13627,7 +13628,7 @@
         <v>223</v>
       </c>
       <c r="H346" s="51">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I346" s="51">
         <v>198</v>
@@ -13642,7 +13643,7 @@
         <v>224</v>
       </c>
       <c r="H347" s="51">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="I347" s="51">
         <v>198</v>
@@ -13657,7 +13658,7 @@
         <v>225</v>
       </c>
       <c r="H348">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="I348" s="51">
         <v>198</v>
@@ -13672,7 +13673,7 @@
         <v>226</v>
       </c>
       <c r="H349" s="51">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I349" s="51">
         <v>198</v>
@@ -13687,7 +13688,7 @@
         <v>227</v>
       </c>
       <c r="H350" s="51">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="I350" s="51">
         <v>198</v>
@@ -13702,7 +13703,7 @@
         <v>228</v>
       </c>
       <c r="H351" s="51">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="I351" s="51">
         <v>198</v>
@@ -13717,7 +13718,7 @@
         <v>229</v>
       </c>
       <c r="H352">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I352" s="51">
         <v>198</v>
@@ -13830,7 +13831,7 @@
         <v>228</v>
       </c>
       <c r="H360" s="51">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I360" s="51">
         <v>104</v>
@@ -13919,7 +13920,7 @@
         <v>225</v>
       </c>
       <c r="H366" s="51">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I366" s="51">
         <v>121</v>
@@ -13949,7 +13950,7 @@
         <v>227</v>
       </c>
       <c r="H368" s="51">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I368" s="51">
         <v>121</v>
@@ -14012,7 +14013,7 @@
         <v>222</v>
       </c>
       <c r="H372">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I372">
         <v>122</v>
@@ -14042,7 +14043,7 @@
         <v>224</v>
       </c>
       <c r="H374">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I374">
         <v>122</v>
@@ -14072,7 +14073,7 @@
         <v>226</v>
       </c>
       <c r="H376">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I376">
         <v>122</v>
@@ -14164,6 +14165,9 @@
       <c r="G382" t="s">
         <v>223</v>
       </c>
+      <c r="H382">
+        <v>1</v>
+      </c>
       <c r="I382">
         <v>114</v>
       </c>
@@ -14177,7 +14181,7 @@
         <v>224</v>
       </c>
       <c r="H383">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I383">
         <v>114</v>
@@ -14237,7 +14241,7 @@
         <v>228</v>
       </c>
       <c r="H387">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I387">
         <v>114</v>
@@ -14285,7 +14289,7 @@
         <v>222</v>
       </c>
       <c r="H390">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="I390">
         <v>195</v>
@@ -14300,7 +14304,7 @@
         <v>223</v>
       </c>
       <c r="H391">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="I391">
         <v>195</v>
@@ -14315,7 +14319,7 @@
         <v>224</v>
       </c>
       <c r="H392">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="I392">
         <v>195</v>
@@ -14330,7 +14334,7 @@
         <v>225</v>
       </c>
       <c r="H393">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I393">
         <v>195</v>
@@ -14345,7 +14349,7 @@
         <v>226</v>
       </c>
       <c r="H394">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="I394">
         <v>195</v>
@@ -14360,7 +14364,7 @@
         <v>227</v>
       </c>
       <c r="H395">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="I395">
         <v>195</v>
@@ -14375,7 +14379,7 @@
         <v>228</v>
       </c>
       <c r="H396">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I396">
         <v>195</v>
@@ -14390,7 +14394,7 @@
         <v>229</v>
       </c>
       <c r="H397">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I397">
         <v>195</v>
@@ -14405,7 +14409,7 @@
         <v>230</v>
       </c>
       <c r="H398">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I398">
         <v>195</v>
@@ -14423,7 +14427,7 @@
         <v>222</v>
       </c>
       <c r="H399">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I399">
         <v>161</v>
@@ -14438,7 +14442,7 @@
         <v>223</v>
       </c>
       <c r="H400">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I400">
         <v>161</v>
@@ -14453,7 +14457,7 @@
         <v>224</v>
       </c>
       <c r="H401">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I401">
         <v>161</v>
@@ -14468,7 +14472,7 @@
         <v>225</v>
       </c>
       <c r="H402">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I402">
         <v>161</v>
@@ -14483,7 +14487,7 @@
         <v>226</v>
       </c>
       <c r="H403">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="I403">
         <v>161</v>
@@ -14498,7 +14502,7 @@
         <v>227</v>
       </c>
       <c r="H404">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I404">
         <v>161</v>
@@ -14513,7 +14517,7 @@
         <v>228</v>
       </c>
       <c r="H405">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I405">
         <v>161</v>

--- a/data/ventas.xlsx
+++ b/data/ventas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cesar\Desktop\Reportes Ventas Rap\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A26E35A1-85C9-4B96-A606-D43697F9660D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9A17FD8D-447C-4CD2-AFC1-AB3369DEF39B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -956,7 +956,6 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="41">
@@ -2541,22 +2540,22 @@
         <v>0</v>
       </c>
       <c r="C2" s="96">
-        <v>41928.631166658197</v>
+        <v>44613.344784379296</v>
       </c>
       <c r="D2" s="96">
-        <v>207302.19131536529</v>
+        <v>221833.72900107491</v>
       </c>
       <c r="E2" s="96">
-        <v>677561890.16147554</v>
+        <v>730628312.80947816</v>
       </c>
       <c r="F2" s="96">
         <v>0</v>
       </c>
       <c r="G2" s="96">
-        <v>332451.74828047713</v>
+        <v>337771.994643885</v>
       </c>
       <c r="H2" s="96">
-        <v>332451.90999999997</v>
+        <v>337772.15</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -2567,22 +2566,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="96">
-        <v>500.14311877310001</v>
+        <v>511.61216639219998</v>
       </c>
       <c r="D3" s="96">
-        <v>880.13180968409995</v>
+        <v>884.13180968389997</v>
       </c>
       <c r="E3" s="96">
-        <v>11081724.942682527</v>
+        <v>11259066.488129456</v>
       </c>
       <c r="F3" s="96">
         <v>0</v>
       </c>
       <c r="G3" s="96">
-        <v>332451.74828047713</v>
+        <v>337771.994643885</v>
       </c>
       <c r="H3" s="96">
-        <v>332451.90999999997</v>
+        <v>337772.15</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2593,13 +2592,13 @@
         <v>1</v>
       </c>
       <c r="C4" s="96">
-        <v>287.18810317290001</v>
+        <v>312.1424603154</v>
       </c>
       <c r="D4" s="96">
-        <v>527.75910714140002</v>
+        <v>599.76410714370002</v>
       </c>
       <c r="E4" s="96">
-        <v>7935947.3890327429</v>
+        <v>8693363.8308905065</v>
       </c>
       <c r="F4" s="96">
         <v>0</v>
@@ -2619,13 +2618,13 @@
         <v>1</v>
       </c>
       <c r="C5" s="96">
-        <v>396.25083333129999</v>
+        <v>420.01353174389999</v>
       </c>
       <c r="D5" s="96">
-        <v>1278.5221071381</v>
+        <v>1394.5421071373</v>
       </c>
       <c r="E5" s="96">
-        <v>8747383.1666885894</v>
+        <v>9146279.4433018658</v>
       </c>
       <c r="F5" s="96">
         <v>0</v>
@@ -2645,13 +2644,13 @@
         <v>1</v>
       </c>
       <c r="C6" s="96">
-        <v>852.71874999889997</v>
+        <v>908.03986111020004</v>
       </c>
       <c r="D6" s="96">
-        <v>2348.9985714469999</v>
+        <v>2552.4027381166002</v>
       </c>
       <c r="E6" s="96">
-        <v>16797290.894173365</v>
+        <v>18863848.650468376</v>
       </c>
       <c r="F6" s="96">
         <v>0</v>
@@ -2671,13 +2670,13 @@
         <v>1</v>
       </c>
       <c r="C7" s="96">
-        <v>771.12899602920004</v>
+        <v>864.77744841050003</v>
       </c>
       <c r="D7" s="96">
-        <v>2640.9885119064002</v>
+        <v>3050.5546785742999</v>
       </c>
       <c r="E7" s="96">
-        <v>14914934.086527392</v>
+        <v>16806749.78055869</v>
       </c>
       <c r="F7" s="96">
         <v>0</v>
@@ -2723,13 +2722,13 @@
         <v>1</v>
       </c>
       <c r="C9" s="96">
-        <v>492.95461507919998</v>
+        <v>530.92689285680001</v>
       </c>
       <c r="D9" s="96">
-        <v>2075.5115416671001</v>
+        <v>2237.5115416683002</v>
       </c>
       <c r="E9" s="96">
-        <v>8806933.4567012265</v>
+        <v>9615921.6737193447</v>
       </c>
       <c r="F9" s="96">
         <v>0</v>
@@ -2749,13 +2748,13 @@
         <v>1</v>
       </c>
       <c r="C10" s="96">
-        <v>421.65004960290003</v>
+        <v>478.68131944409998</v>
       </c>
       <c r="D10" s="96">
-        <v>1037.2136479307001</v>
+        <v>1294.4146598373</v>
       </c>
       <c r="E10" s="96">
-        <v>9823471.9917300809</v>
+        <v>11264156.639444824</v>
       </c>
       <c r="F10" s="96">
         <v>0</v>
@@ -2775,13 +2774,13 @@
         <v>1</v>
       </c>
       <c r="C11" s="96">
-        <v>387.68936904610001</v>
+        <v>420.02474999819998</v>
       </c>
       <c r="D11" s="96">
-        <v>962.63459523810002</v>
+        <v>1011.8970952383</v>
       </c>
       <c r="E11" s="96">
-        <v>6665534.1859788187</v>
+        <v>7333522.0196865257</v>
       </c>
       <c r="F11" s="96">
         <v>0</v>
@@ -2801,13 +2800,13 @@
         <v>1</v>
       </c>
       <c r="C12" s="96">
-        <v>679.03967460050001</v>
+        <v>716.12519047340004</v>
       </c>
       <c r="D12" s="96">
-        <v>3407.0478690399</v>
+        <v>3462.2189107057002</v>
       </c>
       <c r="E12" s="96">
-        <v>10931376.163111016</v>
+        <v>11563280.456663784</v>
       </c>
       <c r="F12" s="96">
         <v>0</v>
@@ -2827,13 +2826,13 @@
         <v>1</v>
       </c>
       <c r="C13" s="96">
-        <v>871.83837301480003</v>
+        <v>911.90615079240001</v>
       </c>
       <c r="D13" s="96">
-        <v>1883.8193690534999</v>
+        <v>1941.9193690540999</v>
       </c>
       <c r="E13" s="96">
-        <v>14492216.412792483</v>
+        <v>15247177.219484905</v>
       </c>
       <c r="F13" s="96">
         <v>0</v>
@@ -2853,13 +2852,13 @@
         <v>1</v>
       </c>
       <c r="C14" s="96">
-        <v>3687.1787698415001</v>
+        <v>3746.1787698415001</v>
       </c>
       <c r="D14" s="96">
-        <v>34116.466666663298</v>
+        <v>34210.876666663302</v>
       </c>
       <c r="E14" s="96">
-        <v>59180827.134406224</v>
+        <v>60038357.598558225</v>
       </c>
       <c r="F14" s="96">
         <v>0</v>
@@ -2879,13 +2878,13 @@
         <v>1</v>
       </c>
       <c r="C15" s="96">
-        <v>695.49613095029997</v>
+        <v>752.42956348990003</v>
       </c>
       <c r="D15" s="96">
-        <v>2584.5916666585999</v>
+        <v>3038.0966666590002</v>
       </c>
       <c r="E15" s="96">
-        <v>12686900.332479352</v>
+        <v>13843506.900515262</v>
       </c>
       <c r="F15" s="96">
         <v>0</v>
@@ -2905,13 +2904,13 @@
         <v>1</v>
       </c>
       <c r="C16" s="96">
-        <v>372.736309522</v>
+        <v>401.00738095060001</v>
       </c>
       <c r="D16" s="96">
-        <v>1829.9713690543999</v>
+        <v>2028.6180357170001</v>
       </c>
       <c r="E16" s="96">
-        <v>9582764.4529769439</v>
+        <v>10467417.738483323</v>
       </c>
       <c r="F16" s="96">
         <v>0</v>
@@ -2931,13 +2930,13 @@
         <v>1</v>
       </c>
       <c r="C17" s="96">
-        <v>840.47349206139995</v>
+        <v>935.11462301339998</v>
       </c>
       <c r="D17" s="96">
-        <v>2245.6983690565999</v>
+        <v>2550.3554523910998</v>
       </c>
       <c r="E17" s="96">
-        <v>16167381.13479867</v>
+        <v>17944639.742629033</v>
       </c>
       <c r="F17" s="96">
         <v>0</v>
@@ -2957,13 +2956,13 @@
         <v>1</v>
       </c>
       <c r="C18" s="96">
-        <v>971.22653571319995</v>
+        <v>1215.4854642843</v>
       </c>
       <c r="D18" s="96">
-        <v>4114.9628690424997</v>
+        <v>5747.0228690426002</v>
       </c>
       <c r="E18" s="96">
-        <v>19062578.988594737</v>
+        <v>22534059.612904426</v>
       </c>
       <c r="F18" s="96">
         <v>0</v>
@@ -2983,13 +2982,13 @@
         <v>1</v>
       </c>
       <c r="C19" s="96">
-        <v>939.20582407220002</v>
+        <v>1058.6512367703999</v>
       </c>
       <c r="D19" s="96">
-        <v>3457.2247262034998</v>
+        <v>3774.0022262019002</v>
       </c>
       <c r="E19" s="96">
-        <v>18556073.997634564</v>
+        <v>20445334.936737273</v>
       </c>
       <c r="F19" s="96">
         <v>0</v>
@@ -3009,13 +3008,13 @@
         <v>1</v>
       </c>
       <c r="C20" s="96">
-        <v>3071.8499801587</v>
+        <v>3280.6037500001999</v>
       </c>
       <c r="D20" s="96">
-        <v>13712.0793333276</v>
+        <v>14250.8118333277</v>
       </c>
       <c r="E20" s="96">
-        <v>45072979.61650601</v>
+        <v>49340595.584204771</v>
       </c>
       <c r="F20" s="96">
         <v>0</v>
@@ -3035,13 +3034,13 @@
         <v>1</v>
       </c>
       <c r="C21" s="96">
-        <v>420.4204166641</v>
+        <v>484.4090674569</v>
       </c>
       <c r="D21" s="96">
-        <v>1629.9108809618001</v>
+        <v>1836.930880961</v>
       </c>
       <c r="E21" s="96">
-        <v>9684737.8484921921</v>
+        <v>10980183.446752926</v>
       </c>
       <c r="F21" s="96">
         <v>0</v>
@@ -3061,13 +3060,13 @@
         <v>1</v>
       </c>
       <c r="C22" s="96">
-        <v>348.21431745899997</v>
+        <v>365.69368253829998</v>
       </c>
       <c r="D22" s="96">
-        <v>1238.0315238086</v>
+        <v>1308.5165238082</v>
       </c>
       <c r="E22" s="96">
-        <v>6222492.2724699304</v>
+        <v>6557112.931111577</v>
       </c>
       <c r="F22" s="96">
         <v>0</v>
@@ -3087,13 +3086,13 @@
         <v>1</v>
       </c>
       <c r="C23" s="96">
-        <v>1923.2949206333999</v>
+        <v>1921.2949206333999</v>
       </c>
       <c r="D23" s="96">
         <v>10953.3035833293</v>
       </c>
       <c r="E23" s="96">
-        <v>36341982.308257863</v>
+        <v>36322023.908257864</v>
       </c>
       <c r="F23" s="96">
         <v>0</v>
@@ -3113,13 +3112,13 @@
         <v>1</v>
       </c>
       <c r="C24" s="96">
-        <v>1862.3213293652</v>
+        <v>1861.3213293652</v>
       </c>
       <c r="D24" s="96">
         <v>15300.7601488083</v>
       </c>
       <c r="E24" s="96">
-        <v>32504670.724847101</v>
+        <v>32490170.4422471</v>
       </c>
       <c r="F24" s="96">
         <v>0</v>
@@ -3139,13 +3138,13 @@
         <v>1</v>
       </c>
       <c r="C25" s="96">
-        <v>515.25296825299995</v>
+        <v>545.86546825280004</v>
       </c>
       <c r="D25" s="96">
-        <v>1997.2391666768001</v>
+        <v>2142.2391666767999</v>
       </c>
       <c r="E25" s="96">
-        <v>9407600.5395302419</v>
+        <v>9777757.9714250863</v>
       </c>
       <c r="F25" s="96">
         <v>0</v>
@@ -3165,13 +3164,13 @@
         <v>1</v>
       </c>
       <c r="C26" s="96">
-        <v>454.00863095120002</v>
+        <v>472.79404761749998</v>
       </c>
       <c r="D26" s="96">
-        <v>959.78791666929999</v>
+        <v>1087.7879166629</v>
       </c>
       <c r="E26" s="96">
-        <v>6448364.3120282274</v>
+        <v>6945315.7802029736</v>
       </c>
       <c r="F26" s="96">
         <v>0</v>
@@ -3191,13 +3190,13 @@
         <v>1</v>
       </c>
       <c r="C27" s="96">
-        <v>5166.5</v>
+        <v>5474.0857142857003</v>
       </c>
       <c r="D27" s="96">
-        <v>15335.54</v>
+        <v>16376.539999999801</v>
       </c>
       <c r="E27" s="96">
-        <v>50661514.217519999</v>
+        <v>54039192.425718747</v>
       </c>
       <c r="F27" s="96">
         <v>0</v>
@@ -3217,13 +3216,13 @@
         <v>1</v>
       </c>
       <c r="C28" s="96">
-        <v>705.33491732590005</v>
+        <v>748.99325065890002</v>
       </c>
       <c r="D28" s="96">
-        <v>3127.0876711410001</v>
+        <v>3262.8351711400001</v>
       </c>
       <c r="E28" s="96">
-        <v>13932220.499480665</v>
+        <v>14579075.923666339</v>
       </c>
       <c r="F28" s="96">
         <v>0</v>
@@ -3243,13 +3242,13 @@
         <v>1</v>
       </c>
       <c r="C29" s="96">
-        <v>2601.9821825396998</v>
+        <v>2655.2766269840999</v>
       </c>
       <c r="D29" s="96">
-        <v>7049.6216666716</v>
+        <v>7266.9416666717998</v>
       </c>
       <c r="E29" s="96">
-        <v>33450220.947755333</v>
+        <v>34411101.004763618</v>
       </c>
       <c r="F29" s="96">
         <v>0</v>
@@ -3269,13 +3268,13 @@
         <v>1</v>
       </c>
       <c r="C30" s="96">
-        <v>259.70168650789998</v>
+        <v>275.06251984120001</v>
       </c>
       <c r="D30" s="96">
-        <v>1219.7308333378</v>
+        <v>1260.8666666715999</v>
       </c>
       <c r="E30" s="96">
-        <v>5618690.4157067938</v>
+        <v>6164880.2550763758</v>
       </c>
       <c r="F30" s="96">
         <v>0</v>
@@ -3295,13 +3294,13 @@
         <v>1</v>
       </c>
       <c r="C31" s="96">
-        <v>328.83323412499999</v>
+        <v>338.64394841080002</v>
       </c>
       <c r="D31" s="96">
-        <v>741.89249999850006</v>
+        <v>888.1449999985</v>
       </c>
       <c r="E31" s="96">
-        <v>5777964.8325451156</v>
+        <v>6108215.4389794497</v>
       </c>
       <c r="F31" s="96">
         <v>0</v>
@@ -3321,13 +3320,13 @@
         <v>1</v>
       </c>
       <c r="C32" s="96">
-        <v>174.87857142839999</v>
+        <v>177.62023809510001</v>
       </c>
       <c r="D32" s="96">
         <v>674.03041666670003</v>
       </c>
       <c r="E32" s="96">
-        <v>3802949.3075159392</v>
+        <v>3882737.6125165834</v>
       </c>
       <c r="F32" s="96">
         <v>0</v>
@@ -3347,13 +3346,13 @@
         <v>1</v>
       </c>
       <c r="C33" s="96">
-        <v>471.37511904659999</v>
+        <v>482.99939153370002</v>
       </c>
       <c r="D33" s="96">
-        <v>1852.1960000014001</v>
+        <v>1947.6025000052</v>
       </c>
       <c r="E33" s="96">
-        <v>8588184.3117468338</v>
+        <v>9010188.8518341817</v>
       </c>
       <c r="F33" s="96">
         <v>0</v>
@@ -3425,13 +3424,13 @@
         <v>1</v>
       </c>
       <c r="C36" s="96">
-        <v>738.56251190319995</v>
+        <v>782.38255158560003</v>
       </c>
       <c r="D36" s="96">
-        <v>2450.4147023866999</v>
+        <v>2593.4347023876999</v>
       </c>
       <c r="E36" s="96">
-        <v>12619217.089428457</v>
+        <v>13476544.027213015</v>
       </c>
       <c r="F36" s="96">
         <v>0</v>
@@ -3477,13 +3476,13 @@
         <v>1</v>
       </c>
       <c r="C38" s="96">
-        <v>543.83686868660004</v>
+        <v>865.17020201989999</v>
       </c>
       <c r="D38" s="96">
-        <v>6586.7099999968004</v>
+        <v>9496.9299999962004</v>
       </c>
       <c r="E38" s="96">
-        <v>12063016.447646325</v>
+        <v>18735817.540831447</v>
       </c>
       <c r="F38" s="96">
         <v>0</v>
@@ -3503,13 +3502,13 @@
         <v>1</v>
       </c>
       <c r="C39" s="96">
-        <v>1148.5833333333001</v>
+        <v>1209.7499999997999</v>
       </c>
       <c r="D39" s="96">
-        <v>14031.3499999982</v>
+        <v>14790.2499999968</v>
       </c>
       <c r="E39" s="96">
-        <v>25192644.671372555</v>
+        <v>27101787.621247634</v>
       </c>
       <c r="F39" s="96">
         <v>0</v>
@@ -3529,13 +3528,13 @@
         <v>1</v>
       </c>
       <c r="C40" s="96">
-        <v>919.90530423300004</v>
+        <v>1090.8088756614</v>
       </c>
       <c r="D40" s="96">
-        <v>5011.6447367884002</v>
+        <v>6808.9522367935997</v>
       </c>
       <c r="E40" s="96">
-        <v>10463850.92498962</v>
+        <v>12878412.530010875</v>
       </c>
       <c r="F40" s="96">
         <v>0</v>
@@ -3555,13 +3554,13 @@
         <v>1</v>
       </c>
       <c r="C41" s="96">
-        <v>1673.1505158728</v>
+        <v>1750.3894047614999</v>
       </c>
       <c r="D41" s="96">
-        <v>9756.1595238119007</v>
+        <v>10233.6645238131</v>
       </c>
       <c r="E41" s="96">
-        <v>19594052.122893002</v>
+        <v>20675373.952008072</v>
       </c>
       <c r="F41" s="96">
         <v>0</v>
@@ -3581,13 +3580,13 @@
         <v>1</v>
       </c>
       <c r="C42" s="96">
-        <v>162.06111111109999</v>
+        <v>199.06111111109999</v>
       </c>
       <c r="D42" s="96">
-        <v>2287.8899999998998</v>
+        <v>2699.7299999999</v>
       </c>
       <c r="E42" s="96">
-        <v>4305943.4722995181</v>
+        <v>4955958.0088995183</v>
       </c>
       <c r="F42" s="96">
         <v>0</v>
@@ -3607,13 +3606,13 @@
         <v>1</v>
       </c>
       <c r="C43" s="96">
-        <v>227.30500992079999</v>
+        <v>290.50262896779998</v>
       </c>
       <c r="D43" s="96">
-        <v>1095.8402098199001</v>
+        <v>1377.1415919577</v>
       </c>
       <c r="E43" s="96">
-        <v>6840893.5633781236</v>
+        <v>10831277.641265372</v>
       </c>
       <c r="F43" s="96">
         <v>0</v>
@@ -3633,13 +3632,13 @@
         <v>1</v>
       </c>
       <c r="C44" s="96">
-        <v>1046.7694444448</v>
+        <v>1143.0010912705</v>
       </c>
       <c r="D44" s="96">
-        <v>12465.4199404748</v>
+        <v>12923.737773806901</v>
       </c>
       <c r="E44" s="96">
-        <v>14127537.863605659</v>
+        <v>16443269.938349089</v>
       </c>
       <c r="F44" s="96">
         <v>0</v>
@@ -3659,13 +3658,13 @@
         <v>1</v>
       </c>
       <c r="C45" s="96">
-        <v>381.49339285799999</v>
+        <v>398.41769841370001</v>
       </c>
       <c r="D45" s="96">
-        <v>3434.3270488133999</v>
+        <v>3574.5670488094001</v>
       </c>
       <c r="E45" s="96">
-        <v>7757835.1522215344</v>
+        <v>8189989.2717900118</v>
       </c>
       <c r="F45" s="96">
         <v>0</v>
@@ -3685,13 +3684,13 @@
         <v>1</v>
       </c>
       <c r="C46" s="96">
-        <v>321.875</v>
+        <v>321.87900000000002</v>
       </c>
       <c r="D46" s="96">
         <v>-24.9999999996</v>
       </c>
       <c r="E46" s="96">
-        <v>1576733.851396092</v>
+        <v>1592393.851396092</v>
       </c>
       <c r="F46" s="96">
         <v>0</v>
@@ -3720,7 +3719,7 @@
     <col min="2" max="2" width="48" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.42578125" style="2" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="17.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="18.85546875" style="2" bestFit="1" customWidth="1"/>
@@ -3780,44 +3779,44 @@
       </c>
       <c r="D2" s="59">
         <f>IFERROR(+VLOOKUP(B2,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>22534059.612904426</v>
+      </c>
+      <c r="E2" s="59">
         <v>19062578.988594737</v>
-      </c>
-      <c r="E2" s="59">
-        <v>17439906.551381622</v>
       </c>
       <c r="F2" s="59">
         <f t="shared" ref="F2:F9" si="0">+D2-E2</f>
-        <v>1622672.4372131154</v>
+        <v>3471480.6243096888</v>
       </c>
       <c r="G2" s="60">
         <f t="shared" ref="G2:G41" si="1">+D2/C2</f>
-        <v>0.59055527523998486</v>
+        <v>0.69810112183325379</v>
       </c>
       <c r="H2" s="59">
         <f>+D2/$N$3*$N$4</f>
-        <v>45750189.572627366</v>
+        <v>49165220.973609656</v>
       </c>
       <c r="I2" s="60">
         <f t="shared" ref="I2:I41" si="2">+H2/C2</f>
-        <v>1.4173326605759635</v>
+        <v>1.5231297203634628</v>
       </c>
       <c r="J2" s="59">
         <f>+D2/$N$3</f>
-        <v>1906257.8988594736</v>
+        <v>2048550.8739004023</v>
       </c>
       <c r="K2" s="59">
         <f t="shared" ref="K2:K41" si="3">+(C2-D2)/$N$2</f>
-        <v>944035.54640400119</v>
+        <v>749616.69425740978</v>
       </c>
       <c r="L2" s="61" cm="1">
         <f t="array" ref="L2">+_xlfn.IFS(I2&gt;114%,H2*0.02,I2&gt;109%,H2*0.015,I2&gt;104%,H2*0.0125,I2&gt;99%,H2*0.01,I2&lt;99%,H2*0)</f>
-        <v>915003.7914525473</v>
+        <v>983304.41947219311</v>
       </c>
       <c r="M2" s="53" t="s">
         <v>36</v>
       </c>
       <c r="N2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -3830,45 +3829,45 @@
       </c>
       <c r="D3" s="4">
         <f>IFERROR(+VLOOKUP(B3,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>17944639.742629033</v>
+      </c>
+      <c r="E3" s="4">
         <v>16167381.13479867</v>
-      </c>
-      <c r="E3" s="4">
-        <v>14059558.299505398</v>
       </c>
       <c r="F3" s="4">
         <f t="shared" si="0"/>
-        <v>2107822.8352932725</v>
+        <v>1777258.6078303624</v>
       </c>
       <c r="G3" s="5">
         <f t="shared" si="1"/>
-        <v>0.52181915812752067</v>
+        <v>0.57918204100759185</v>
       </c>
       <c r="H3" s="4">
         <f t="shared" ref="H3:H41" si="4">+D3/$N$3*$N$4</f>
-        <v>38801714.723516807</v>
+        <v>39151941.256645165</v>
       </c>
       <c r="I3" s="5">
         <f t="shared" si="2"/>
-        <v>1.2523659795060496</v>
+        <v>1.2636699076529279</v>
       </c>
       <c r="J3" s="4">
         <f t="shared" ref="J3:J41" si="5">+D3/$N$3</f>
-        <v>1616738.1134798671</v>
+        <v>1631330.8856935485</v>
       </c>
       <c r="K3" s="4">
         <f t="shared" si="3"/>
-        <v>1058239.0745774703</v>
+        <v>1002929.8797118632</v>
       </c>
       <c r="L3" s="63" cm="1">
         <f t="array" ref="L3">+_xlfn.IFS(I3&gt;114%,H3*0.02,I3&gt;109%,H3*0.015,I3&gt;104%,H3*0.0125,I3&gt;99%,H3*0.01,I3&lt;99%,H3*0)</f>
-        <v>776034.29447033617</v>
+        <v>783038.82513290329</v>
       </c>
       <c r="M3" s="53" t="s">
         <v>40</v>
       </c>
       <c r="N3">
         <f>N4-N2</f>
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -3881,38 +3880,38 @@
       </c>
       <c r="D4" s="4">
         <f>IFERROR(+VLOOKUP(B4,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>13843506.900515262</v>
+      </c>
+      <c r="E4" s="4">
         <v>12686900.332479352</v>
-      </c>
-      <c r="E4" s="4">
-        <v>11854719.440338746</v>
       </c>
       <c r="F4" s="4">
         <f t="shared" si="0"/>
-        <v>832180.89214060642</v>
+        <v>1156606.5680359099</v>
       </c>
       <c r="G4" s="5">
         <f t="shared" si="1"/>
-        <v>0.44687870246512368</v>
+        <v>0.48761858603332059</v>
       </c>
       <c r="H4" s="4">
         <f t="shared" si="4"/>
-        <v>30448560.797950443</v>
+        <v>30204015.055669662</v>
       </c>
       <c r="I4" s="5">
         <f t="shared" si="2"/>
-        <v>1.0725088859162968</v>
+        <v>1.0638950967999721</v>
       </c>
       <c r="J4" s="4">
         <f t="shared" si="5"/>
-        <v>1268690.0332479351</v>
+        <v>1258500.6273195692</v>
       </c>
       <c r="K4" s="4">
         <f t="shared" si="3"/>
-        <v>1121652.2091192072</v>
+        <v>1118963.4122794608</v>
       </c>
       <c r="L4" s="63" cm="1">
         <f t="array" ref="L4">+_xlfn.IFS(I4&gt;114%,H4*0.02,I4&gt;109%,H4*0.015,I4&gt;104%,H4*0.0125,I4&gt;99%,H4*0.01,I4&lt;99%,H4*0)</f>
-        <v>380607.00997438055</v>
+        <v>377550.18819587078</v>
       </c>
       <c r="M4" s="53" t="s">
         <v>47</v>
@@ -3931,38 +3930,38 @@
       </c>
       <c r="D5" s="4">
         <f>IFERROR(+VLOOKUP(B5,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>15247177.219484905</v>
+      </c>
+      <c r="E5" s="4">
         <v>14492216.412792483</v>
-      </c>
-      <c r="E5" s="4">
-        <v>11920566.462441558</v>
       </c>
       <c r="F5" s="4">
         <f t="shared" si="0"/>
-        <v>2571649.9503509253</v>
+        <v>754960.80669242144</v>
       </c>
       <c r="G5" s="5">
         <f t="shared" si="1"/>
-        <v>0.51046849085846357</v>
+        <v>0.53706095212680238</v>
       </c>
       <c r="H5" s="4">
         <f t="shared" si="4"/>
-        <v>34781319.390701957</v>
+        <v>33266568.478876155</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" si="2"/>
-        <v>1.2251243780603125</v>
+        <v>1.1717693500948416</v>
       </c>
       <c r="J5" s="4">
         <f t="shared" si="5"/>
-        <v>1449221.6412792483</v>
+        <v>1386107.0199531731</v>
       </c>
       <c r="K5" s="4">
         <f t="shared" si="3"/>
-        <v>992701.06052541209</v>
+        <v>1010988.7723587191</v>
       </c>
       <c r="L5" s="63" cm="1">
         <f t="array" ref="L5">+_xlfn.IFS(I5&gt;114%,H5*0.02,I5&gt;109%,H5*0.015,I5&gt;104%,H5*0.0125,I5&gt;99%,H5*0.01,I5&lt;99%,H5*0)</f>
-        <v>695626.38781403913</v>
+        <v>665331.36957752309</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
@@ -3975,38 +3974,38 @@
       </c>
       <c r="D6" s="4">
         <f>IFERROR(+VLOOKUP(B6,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>11563280.456663784</v>
+      </c>
+      <c r="E6" s="4">
         <v>10931376.163111016</v>
-      </c>
-      <c r="E6" s="4">
-        <v>10222287.133025508</v>
       </c>
       <c r="F6" s="4">
         <f t="shared" si="0"/>
-        <v>709089.03008550778</v>
+        <v>631904.29355276749</v>
       </c>
       <c r="G6" s="5">
         <f t="shared" si="1"/>
-        <v>0.46459705649064303</v>
+        <v>0.49145377337493906</v>
       </c>
       <c r="H6" s="4">
         <f t="shared" si="4"/>
-        <v>26235302.791466441</v>
+        <v>25228975.541811891</v>
       </c>
       <c r="I6" s="5">
         <f t="shared" si="2"/>
-        <v>1.1150329355775432</v>
+        <v>1.0722627782725942</v>
       </c>
       <c r="J6" s="4">
         <f t="shared" si="5"/>
-        <v>1093137.6163111017</v>
+        <v>1051207.314242162</v>
       </c>
       <c r="K6" s="4">
         <f t="shared" si="3"/>
-        <v>899810.59817207919</v>
+        <v>920418.77545048785</v>
       </c>
       <c r="L6" s="63" cm="1">
         <f t="array" ref="L6">+_xlfn.IFS(I6&gt;114%,H6*0.02,I6&gt;109%,H6*0.015,I6&gt;104%,H6*0.0125,I6&gt;99%,H6*0.01,I6&lt;99%,H6*0)</f>
-        <v>393529.5418719966</v>
+        <v>315362.19427264866</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
@@ -4019,34 +4018,34 @@
       </c>
       <c r="D7" s="4">
         <f>IFERROR(+VLOOKUP(B7,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>9615921.6737193447</v>
+      </c>
+      <c r="E7" s="4">
         <v>8806933.4567012265</v>
-      </c>
-      <c r="E7" s="4">
-        <v>7404424.1934615131</v>
       </c>
       <c r="F7" s="4">
         <f t="shared" ref="F7:F8" si="6">+D7-E7</f>
-        <v>1402509.2632397134</v>
+        <v>808988.21701811813</v>
       </c>
       <c r="G7" s="5">
         <f t="shared" si="1"/>
-        <v>0.31746012702141607</v>
+        <v>0.34662141266028784</v>
       </c>
       <c r="H7" s="4">
         <f t="shared" si="4"/>
-        <v>21136640.296082944</v>
+        <v>20980192.742660388</v>
       </c>
       <c r="I7" s="5">
         <f t="shared" si="2"/>
-        <v>0.76190430485139859</v>
+        <v>0.75626490034971894</v>
       </c>
       <c r="J7" s="4">
         <f t="shared" si="5"/>
-        <v>880693.34567012265</v>
+        <v>874174.69761084951</v>
       </c>
       <c r="K7" s="4">
         <f t="shared" si="3"/>
-        <v>1352494.5409830913</v>
+        <v>1394302.7197496279</v>
       </c>
       <c r="L7" s="63" cm="1">
         <f t="array" ref="L7">+_xlfn.IFS(I7&gt;114%,H7*0.02,I7&gt;109%,H7*0.015,I7&gt;104%,H7*0.0125,I7&gt;99%,H7*0.01,I7&lt;99%,H7*0)</f>
@@ -4063,38 +4062,38 @@
       </c>
       <c r="D8" s="4">
         <f>IFERROR(+VLOOKUP(B8,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>16806749.78055869</v>
+      </c>
+      <c r="E8" s="4">
         <v>14914934.086527392</v>
-      </c>
-      <c r="E8" s="4">
-        <v>13226460.381280242</v>
       </c>
       <c r="F8" s="4">
         <f t="shared" si="6"/>
-        <v>1688473.7052471507</v>
+        <v>1891815.6940312982</v>
       </c>
       <c r="G8" s="5">
         <f t="shared" si="1"/>
-        <v>0.41625699418759998</v>
+        <v>0.46905518355846187</v>
       </c>
       <c r="H8" s="4">
         <f t="shared" si="4"/>
-        <v>35795841.807665735</v>
+        <v>36669272.24849169</v>
       </c>
       <c r="I8" s="5">
         <f t="shared" si="2"/>
-        <v>0.9990167860502398</v>
+        <v>1.0233931277639168</v>
       </c>
       <c r="J8" s="4">
         <f t="shared" si="5"/>
-        <v>1491493.4086527391</v>
+        <v>1527886.3436871537</v>
       </c>
       <c r="K8" s="4">
         <f t="shared" si="3"/>
-        <v>1494009.8093135937</v>
+        <v>1463409.3566430011</v>
       </c>
       <c r="L8" s="63" cm="1">
         <f t="array" ref="L8">+_xlfn.IFS(I8&gt;114%,H8*0.02,I8&gt;109%,H8*0.015,I8&gt;104%,H8*0.0125,I8&gt;99%,H8*0.01,I8&lt;99%,H8*0)</f>
-        <v>357958.41807665734</v>
+        <v>366692.72248491691</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
@@ -4107,38 +4106,38 @@
       </c>
       <c r="D9" s="4">
         <f>IFERROR(+VLOOKUP(B9,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>18863848.650468376</v>
+      </c>
+      <c r="E9" s="4">
         <v>16797290.894173365</v>
-      </c>
-      <c r="E9" s="4">
-        <v>15645728.431611888</v>
       </c>
       <c r="F9" s="4">
         <f t="shared" si="0"/>
-        <v>1151562.462561477</v>
+        <v>2066557.7562950104</v>
       </c>
       <c r="G9" s="5">
         <f t="shared" si="1"/>
-        <v>0.46879119797245289</v>
+        <v>0.5264662178525249</v>
       </c>
       <c r="H9" s="4">
         <f t="shared" si="4"/>
-        <v>40313498.146016076</v>
+        <v>41157487.964658275</v>
       </c>
       <c r="I9" s="5">
         <f t="shared" si="2"/>
-        <v>1.1250988751338868</v>
+        <v>1.1486535662236907</v>
       </c>
       <c r="J9" s="4">
         <f t="shared" si="5"/>
-        <v>1679729.0894173365</v>
+        <v>1714895.3318607614</v>
       </c>
       <c r="K9" s="4">
         <f t="shared" si="3"/>
-        <v>1359555.7516245956</v>
+        <v>1305170.9820345638</v>
       </c>
       <c r="L9" s="63" cm="1">
         <f t="array" ref="L9">+_xlfn.IFS(I9&gt;114%,H9*0.02,I9&gt;109%,H9*0.015,I9&gt;104%,H9*0.0125,I9&gt;99%,H9*0.01,I9&lt;99%,H9*0)</f>
-        <v>604702.4721902411</v>
+        <v>823149.75929316552</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4149,34 +4148,34 @@
       </c>
       <c r="D10" s="64">
         <f>+SUM(D2:D9)</f>
+        <v>126419184.03694384</v>
+      </c>
+      <c r="E10" s="65">
         <v>113859611.46917823</v>
-      </c>
-      <c r="E10" s="65">
-        <v>101773650.89304647</v>
       </c>
       <c r="F10" s="64">
         <f>+SUM(F2:F9)</f>
-        <v>12085960.576131769</v>
+        <v>12559572.567765577</v>
       </c>
       <c r="G10" s="66">
         <f t="shared" si="1"/>
-        <v>0.46860706979340161</v>
+        <v>0.52029795844913396</v>
       </c>
       <c r="H10" s="64">
         <f t="shared" si="4"/>
-        <v>273263067.5260278</v>
+        <v>275823674.26242292</v>
       </c>
       <c r="I10" s="66">
         <f t="shared" si="2"/>
-        <v>1.124656967504164</v>
+        <v>1.1351955457072012</v>
       </c>
       <c r="J10" s="64">
         <f t="shared" si="5"/>
-        <v>11385961.146917824</v>
+        <v>11492653.094267622</v>
       </c>
       <c r="K10" s="67">
         <f t="shared" si="3"/>
-        <v>9222498.5907194484</v>
+        <v>8965800.592485128</v>
       </c>
       <c r="L10" s="68"/>
     </row>
@@ -4192,38 +4191,38 @@
       </c>
       <c r="D11" s="59">
         <f>IFERROR(+VLOOKUP(B11,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>49340595.584204771</v>
+      </c>
+      <c r="E11" s="59">
         <v>45072979.61650601</v>
-      </c>
-      <c r="E11" s="59">
-        <v>41338677.54260511</v>
       </c>
       <c r="F11" s="59">
         <f t="shared" ref="F11:F16" si="7">+D11-E11</f>
-        <v>3734302.0739009008</v>
+        <v>4267615.9676987603</v>
       </c>
       <c r="G11" s="60">
         <f t="shared" si="1"/>
-        <v>0.46480431014272316</v>
+        <v>0.50881307798317643</v>
       </c>
       <c r="H11" s="59">
         <f t="shared" si="4"/>
-        <v>108175151.07961442</v>
+        <v>107652208.54735586</v>
       </c>
       <c r="I11" s="60">
         <f t="shared" si="2"/>
-        <v>1.1155303443425355</v>
+        <v>1.1101376246905665</v>
       </c>
       <c r="J11" s="59">
         <f t="shared" si="5"/>
-        <v>4507297.9616506007</v>
+        <v>4485508.6894731605</v>
       </c>
       <c r="K11" s="59">
         <f t="shared" si="3"/>
-        <v>3707069.2045451072</v>
+        <v>3663950.2227640571</v>
       </c>
       <c r="L11" s="61" cm="1">
         <f t="array" ref="L11">+_xlfn.IFS(I11&gt;114%,H11*0.0125,I11&gt;109%,H11*0.01,I11&gt;104%,H11*0.0075,I11&gt;99%,H11*0.005,I11&lt;99%,H11*0)</f>
-        <v>1081751.5107961441</v>
+        <v>1076522.0854735586</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4251,19 +4250,19 @@
       </c>
       <c r="H12" s="4">
         <f t="shared" si="4"/>
-        <v>30543966.964696158</v>
+        <v>27767242.695178326</v>
       </c>
       <c r="I12" s="5">
         <f t="shared" si="2"/>
-        <v>0.96563691323658041</v>
+        <v>0.87785173930598226</v>
       </c>
       <c r="J12" s="4">
         <f t="shared" si="5"/>
-        <v>1272665.2901956732</v>
+        <v>1156968.4456324303</v>
       </c>
       <c r="K12" s="4">
         <f t="shared" si="3"/>
-        <v>1350303.5361864478</v>
+        <v>1454173.0389700208</v>
       </c>
       <c r="L12" s="63" cm="1">
         <f t="array" ref="L12">+_xlfn.IFS(I12&gt;114%,H12*0.02,I12&gt;109%,H12*0.015,I12&gt;104%,H12*0.0125,I12&gt;99%,H12*0.01,I12&lt;99%,H12*0)</f>
@@ -4281,38 +4280,38 @@
       </c>
       <c r="D13" s="4">
         <f>IFERROR(+VLOOKUP(B13,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>60038357.598558225</v>
+      </c>
+      <c r="E13" s="4">
         <v>59180827.134406224</v>
-      </c>
-      <c r="E13" s="4">
-        <v>54947546.702784903</v>
       </c>
       <c r="F13" s="4">
         <f t="shared" si="7"/>
-        <v>4233280.4316213205</v>
+        <v>857530.46415200084</v>
       </c>
       <c r="G13" s="5">
         <f t="shared" si="1"/>
-        <v>0.46103943338719244</v>
+        <v>0.46771989695028182</v>
       </c>
       <c r="H13" s="4">
         <f t="shared" si="4"/>
-        <v>142033985.12257493</v>
+        <v>130992780.21503612</v>
       </c>
       <c r="I13" s="5">
         <f t="shared" si="2"/>
-        <v>1.1064946401292617</v>
+        <v>1.0204797751642514</v>
       </c>
       <c r="J13" s="4">
         <f t="shared" si="5"/>
-        <v>5918082.7134406222</v>
+        <v>5458032.5089598382</v>
       </c>
       <c r="K13" s="4">
         <f t="shared" si="3"/>
-        <v>4941649.2100156257</v>
+        <v>5255812.190466674</v>
       </c>
       <c r="L13" s="63" cm="1">
         <f t="array" ref="L13">+_xlfn.IFS(I13&gt;114%,H13*0.0125,I13&gt;109%,H13*0.01,I13&gt;104%,H13*0.0075,I13&gt;99%,H13*0.005,I13&lt;99%,H13*0)</f>
-        <v>1420339.8512257494</v>
+        <v>654963.90107518062</v>
       </c>
       <c r="M13" s="53" t="s">
         <v>61</v>
@@ -4331,34 +4330,34 @@
       </c>
       <c r="D14" s="4">
         <f>IFERROR(+VLOOKUP(B14,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>18735817.540831447</v>
+      </c>
+      <c r="E14" s="4">
         <v>12063016.447646325</v>
-      </c>
-      <c r="E14" s="4">
-        <v>10126859.110729419</v>
       </c>
       <c r="F14" s="4">
         <f t="shared" si="7"/>
-        <v>1936157.3369169068</v>
+        <v>6672801.0931851212</v>
       </c>
       <c r="G14" s="5">
         <f t="shared" si="1"/>
-        <v>0.28417630892021439</v>
+        <v>0.44137181578616963</v>
       </c>
       <c r="H14" s="4">
         <f t="shared" si="4"/>
-        <v>28951239.474351179</v>
+        <v>40878147.361814067</v>
       </c>
       <c r="I14" s="5">
         <f t="shared" si="2"/>
-        <v>0.68202314140851439</v>
+        <v>0.96299305262437007</v>
       </c>
       <c r="J14" s="4">
         <f t="shared" si="5"/>
-        <v>1206301.6447646325</v>
+        <v>1703256.140075586</v>
       </c>
       <c r="K14" s="4">
         <f t="shared" si="3"/>
-        <v>2170431.4962377623</v>
+        <v>1824095.3733956579</v>
       </c>
       <c r="L14" s="63" cm="1">
         <f t="array" ref="L14">+_xlfn.IFS(I14&gt;109%,H14*0.015,I14&gt;104%,H14*0.0125,I14&gt;99%,H14*0.01,I14&lt;99%,H14*0)</f>
@@ -4376,38 +4375,38 @@
       </c>
       <c r="D15" s="4">
         <f>IFERROR(+VLOOKUP(B15,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>27101787.621247634</v>
+      </c>
+      <c r="E15" s="4">
         <v>25192644.671372555</v>
-      </c>
-      <c r="E15" s="4">
-        <v>23985001.331072558</v>
       </c>
       <c r="F15" s="4">
         <f t="shared" si="7"/>
-        <v>1207643.3402999975</v>
+        <v>1909142.9498750791</v>
       </c>
       <c r="G15" s="5">
         <f t="shared" si="1"/>
-        <v>0.59347948381899263</v>
+        <v>0.63845440357071082</v>
       </c>
       <c r="H15" s="4">
         <f t="shared" si="4"/>
-        <v>60462347.211294137</v>
+        <v>59131172.991813019</v>
       </c>
       <c r="I15" s="5">
         <f t="shared" si="2"/>
-        <v>1.4243507611655826</v>
+        <v>1.3929914259724598</v>
       </c>
       <c r="J15" s="4">
         <f t="shared" si="5"/>
-        <v>2519264.4671372557</v>
+        <v>2463798.8746588756</v>
       </c>
       <c r="K15" s="4">
         <f t="shared" si="3"/>
-        <v>1232600.9088287461</v>
+        <v>1180559.2133636435</v>
       </c>
       <c r="L15" s="63" cm="1">
         <f t="array" ref="L15">+_xlfn.IFS(I15&gt;109%,H15*0.015,I15&gt;104%,H15*0.0125,I15&gt;99%,H15*0.01,I15&lt;99%,H15*0)</f>
-        <v>906935.20816941198</v>
+        <v>886967.5948771952</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4418,34 +4417,34 @@
       </c>
       <c r="D16" s="64">
         <f>+SUM(D11:D15)</f>
+        <v>167943211.24679881</v>
+      </c>
+      <c r="E16" s="65">
         <v>154236120.77188784</v>
-      </c>
-      <c r="E16" s="65">
-        <v>143124737.58914873</v>
       </c>
       <c r="F16" s="64">
         <f t="shared" si="7"/>
-        <v>11111383.182739109</v>
+        <v>13707090.474910975</v>
       </c>
       <c r="G16" s="66">
         <f t="shared" si="1"/>
-        <v>0.45116105515394389</v>
+        <v>0.49125610792629398</v>
       </c>
       <c r="H16" s="64">
         <f t="shared" si="4"/>
-        <v>370166689.85253084</v>
+        <v>366421551.8111974</v>
       </c>
       <c r="I16" s="66">
         <f t="shared" si="2"/>
-        <v>1.0827865323694654</v>
+        <v>1.0718315082028231</v>
       </c>
       <c r="J16" s="64">
         <f t="shared" si="5"/>
-        <v>15423612.077188784</v>
+        <v>15267564.658799892</v>
       </c>
       <c r="K16" s="67">
         <f t="shared" si="3"/>
-        <v>13402054.355813691</v>
+        <v>13378590.038960053</v>
       </c>
       <c r="L16" s="68"/>
     </row>
@@ -4461,34 +4460,34 @@
       </c>
       <c r="D17" s="59">
         <f>IFERROR(+VLOOKUP(B17,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>8693363.8308905065</v>
+      </c>
+      <c r="E17" s="59">
         <v>7935947.3890327429</v>
-      </c>
-      <c r="E17" s="59">
-        <v>7416441.7657084363</v>
       </c>
       <c r="F17" s="59">
         <f t="shared" ref="F17:F40" si="8">+D17-E17</f>
-        <v>519505.62332430668</v>
+        <v>757416.44185776357</v>
       </c>
       <c r="G17" s="60">
         <f t="shared" si="1"/>
-        <v>0.27050045961494162</v>
+        <v>0.29631735148667698</v>
       </c>
       <c r="H17" s="59">
         <f t="shared" si="4"/>
-        <v>19046273.733678583</v>
+        <v>18967339.267397467</v>
       </c>
       <c r="I17" s="60">
         <f t="shared" si="2"/>
-        <v>0.64920110307585999</v>
+        <v>0.64651058506184067</v>
       </c>
       <c r="J17" s="59">
         <f t="shared" si="5"/>
-        <v>793594.73890327429</v>
+        <v>790305.80280822783</v>
       </c>
       <c r="K17" s="59">
         <f t="shared" si="3"/>
-        <v>1528719.33881909</v>
+        <v>1588050.3308930383</v>
       </c>
       <c r="L17" s="61" cm="1">
         <f t="array" ref="L17">+_xlfn.IFS(I17&gt;114%,H17*0.02,I17&gt;109%,H17*0.015,I17&gt;104%,H17*0.0125,I17&gt;99%,H17*0.01,I17&lt;99%,H17*0)</f>
@@ -4505,34 +4504,34 @@
       </c>
       <c r="D18" s="4">
         <f>IFERROR(+VLOOKUP(B18,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>9146279.4433018658</v>
+      </c>
+      <c r="E18" s="4">
         <v>8747383.1666885894</v>
-      </c>
-      <c r="E18" s="4">
-        <v>8097618.1083014421</v>
       </c>
       <c r="F18" s="4">
         <f t="shared" si="8"/>
-        <v>649765.05838714726</v>
+        <v>398896.27661327645</v>
       </c>
       <c r="G18" s="5">
         <f t="shared" si="1"/>
-        <v>0.35046299400857084</v>
+        <v>0.36644473171649866</v>
       </c>
       <c r="H18" s="4">
         <f t="shared" si="4"/>
-        <v>20993719.600052617</v>
+        <v>19955518.785385888</v>
       </c>
       <c r="I18" s="5">
         <f t="shared" si="2"/>
-        <v>0.84111118562057019</v>
+        <v>0.79951577829054243</v>
       </c>
       <c r="J18" s="4">
         <f t="shared" si="5"/>
-        <v>874738.31666885898</v>
+        <v>831479.94939107867</v>
       </c>
       <c r="K18" s="4">
         <f t="shared" si="3"/>
-        <v>1158008.7666651008</v>
+        <v>1216402.0351306258</v>
       </c>
       <c r="L18" s="63" cm="1">
         <f t="array" ref="L18">+_xlfn.IFS(I18&gt;114%,H18*0.02,I18&gt;109%,H18*0.015,I18&gt;104%,H18*0.0125,I18&gt;99%,H18*0.01,I18&lt;99%,H18*0)</f>
@@ -4549,34 +4548,34 @@
       </c>
       <c r="D19" s="4">
         <f>IFERROR(+VLOOKUP(B19,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>10467417.738483323</v>
+      </c>
+      <c r="E19" s="4">
         <v>9582764.4529769439</v>
-      </c>
-      <c r="E19" s="4">
-        <v>9015875.5390208997</v>
       </c>
       <c r="F19" s="4">
         <f t="shared" si="8"/>
-        <v>566888.91395604424</v>
+        <v>884653.28550637886</v>
       </c>
       <c r="G19" s="5">
         <f t="shared" si="1"/>
-        <v>0.37061121187937296</v>
+        <v>0.40482497429035819</v>
       </c>
       <c r="H19" s="4">
         <f t="shared" si="4"/>
-        <v>22998634.687144667</v>
+        <v>22838002.338509068</v>
       </c>
       <c r="I19" s="5">
         <f t="shared" si="2"/>
-        <v>0.88946690851049515</v>
+        <v>0.88325448936078144</v>
       </c>
       <c r="J19" s="4">
         <f t="shared" si="5"/>
-        <v>958276.44529769442</v>
+        <v>951583.43077121116</v>
       </c>
       <c r="K19" s="4">
         <f t="shared" si="3"/>
-        <v>1162420.4080373612</v>
+        <v>1183787.1097705136</v>
       </c>
       <c r="L19" s="63" cm="1">
         <f t="array" ref="L19">+_xlfn.IFS(I19&gt;114%,H19*0.02,I19&gt;109%,H19*0.015,I19&gt;104%,H19*0.0125,I19&gt;99%,H19*0.01,I19&lt;99%,H19*0)</f>
@@ -4593,38 +4592,38 @@
       </c>
       <c r="D20" s="4">
         <f>IFERROR(+VLOOKUP(B20,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>20445334.936737273</v>
+      </c>
+      <c r="E20" s="4">
         <v>18556073.997634564</v>
-      </c>
-      <c r="E20" s="4">
-        <v>15820251.940252023</v>
       </c>
       <c r="F20" s="4">
         <f t="shared" si="8"/>
-        <v>2735822.0573825408</v>
+        <v>1889260.9391027093</v>
       </c>
       <c r="G20" s="5">
         <f t="shared" si="1"/>
-        <v>0.55311798295864967</v>
+        <v>0.60943292328774434</v>
       </c>
       <c r="H20" s="4">
         <f t="shared" si="4"/>
-        <v>44534577.59432295</v>
+        <v>44608003.498335868</v>
       </c>
       <c r="I20" s="5">
         <f t="shared" si="2"/>
-        <v>1.3274831591007592</v>
+        <v>1.3296718326278056</v>
       </c>
       <c r="J20" s="4">
         <f t="shared" si="5"/>
-        <v>1855607.3997634563</v>
+        <v>1858666.8124306612</v>
       </c>
       <c r="K20" s="4">
         <f t="shared" si="3"/>
-        <v>1070861.1430261026</v>
+        <v>1007907.3125586713</v>
       </c>
       <c r="L20" s="63" cm="1">
         <f t="array" ref="L20">+_xlfn.IFS(I20&gt;114%,H20*0.02,I20&gt;109%,H20*0.015,I20&gt;104%,H20*0.0125,I20&gt;99%,H20*0.01,I20&lt;99%,H20*0)</f>
-        <v>890691.551886459</v>
+        <v>892160.06996671739</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4637,34 +4636,34 @@
       </c>
       <c r="D21" s="4">
         <f>IFERROR(+VLOOKUP(B21,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>10980183.446752926</v>
+      </c>
+      <c r="E21" s="4">
         <v>9684737.8484921921</v>
-      </c>
-      <c r="E21" s="4">
-        <v>8244716.2501042979</v>
       </c>
       <c r="F21" s="4">
         <f t="shared" ref="F21:F23" si="9">+D21-E21</f>
-        <v>1440021.5983878942</v>
+        <v>1295445.5982607342</v>
       </c>
       <c r="G21" s="5">
         <f t="shared" si="1"/>
-        <v>0.3804125947862696</v>
+        <v>0.43129717515883398</v>
       </c>
       <c r="H21" s="4">
         <f t="shared" si="4"/>
-        <v>23243370.836381264</v>
+        <v>23956763.883824568</v>
       </c>
       <c r="I21" s="5">
         <f t="shared" si="2"/>
-        <v>0.91299022748704717</v>
+        <v>0.94101201852836514</v>
       </c>
       <c r="J21" s="4">
         <f t="shared" si="5"/>
-        <v>968473.78484921926</v>
+        <v>998198.49515935697</v>
       </c>
       <c r="K21" s="4">
         <f t="shared" si="3"/>
-        <v>1126698.0108219862</v>
+        <v>1113717.4271728517</v>
       </c>
       <c r="L21" s="63" cm="1">
         <f t="array" ref="L21">+_xlfn.IFS(I21&gt;114%,H21*0.02,I21&gt;109%,H21*0.015,I21&gt;104%,H21*0.0125,I21&gt;99%,H21*0.01,I21&lt;99%,H21*0)</f>
@@ -4681,38 +4680,38 @@
       </c>
       <c r="D22" s="4">
         <f>IFERROR(+VLOOKUP(B22,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>14579075.923666339</v>
+      </c>
+      <c r="E22" s="4">
         <v>13932220.499480665</v>
-      </c>
-      <c r="E22" s="4">
-        <v>13022386.541284554</v>
       </c>
       <c r="F22" s="4">
         <f t="shared" si="9"/>
-        <v>909833.95819611102</v>
+        <v>646855.42418567464</v>
       </c>
       <c r="G22" s="5">
         <f t="shared" si="1"/>
-        <v>0.43890837953629891</v>
+        <v>0.45928634197481921</v>
       </c>
       <c r="H22" s="4">
         <f t="shared" si="4"/>
-        <v>33437329.198753595</v>
+        <v>31808892.92436292</v>
       </c>
       <c r="I22" s="5">
         <f t="shared" si="2"/>
-        <v>1.0533801108871175</v>
+        <v>1.0020792915814236</v>
       </c>
       <c r="J22" s="4">
         <f t="shared" si="5"/>
-        <v>1393222.0499480665</v>
+        <v>1325370.5385151217</v>
       </c>
       <c r="K22" s="4">
         <f t="shared" si="3"/>
-        <v>1272190.6928942385</v>
+        <v>1320293.4058718202</v>
       </c>
       <c r="L22" s="63" cm="1">
         <f t="array" ref="L22">+_xlfn.IFS(I22&gt;114%,H22*0.02,I22&gt;109%,H22*0.015,I22&gt;104%,H22*0.0125,I22&gt;99%,H22*0.01,I22&lt;99%,H22*0)</f>
-        <v>417966.61498441995</v>
+        <v>318088.92924362922</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4725,38 +4724,38 @@
       </c>
       <c r="D23" s="4">
         <f>IFERROR(+VLOOKUP(B23,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>13476544.027213015</v>
+      </c>
+      <c r="E23" s="4">
         <v>12619217.089428457</v>
-      </c>
-      <c r="E23" s="4">
-        <v>11034688.327347409</v>
       </c>
       <c r="F23" s="4">
         <f t="shared" si="9"/>
-        <v>1584528.7620810475</v>
+        <v>857326.93778455816</v>
       </c>
       <c r="G23" s="5">
         <f t="shared" si="1"/>
-        <v>0.45995195440461595</v>
+        <v>0.49120026385228166</v>
       </c>
       <c r="H23" s="4">
         <f t="shared" si="4"/>
-        <v>30286121.014628299</v>
+        <v>29403368.786646578</v>
       </c>
       <c r="I23" s="5">
         <f t="shared" si="2"/>
-        <v>1.1038846905710784</v>
+        <v>1.0717096665867965</v>
       </c>
       <c r="J23" s="4">
         <f t="shared" si="5"/>
-        <v>1261921.7089428457</v>
+        <v>1225140.3661102741</v>
       </c>
       <c r="K23" s="4">
         <f t="shared" si="3"/>
-        <v>1058337.7957551104</v>
+        <v>1073800.1694451531</v>
       </c>
       <c r="L23" s="63" cm="1">
         <f t="array" ref="L23">+_xlfn.IFS(I23&gt;114%,H23*0.02,I23&gt;109%,H23*0.015,I23&gt;104%,H23*0.0125,I23&gt;99%,H23*0.01,I23&lt;99%,H23*0)</f>
-        <v>454291.81521942449</v>
+        <v>367542.10983308224</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4769,34 +4768,34 @@
       </c>
       <c r="D24" s="4">
         <f>IFERROR(+VLOOKUP(B24,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>12878412.530010875</v>
+      </c>
+      <c r="E24" s="4">
         <v>10463850.92498962</v>
-      </c>
-      <c r="E24" s="4">
-        <v>8128233.8339369334</v>
       </c>
       <c r="F24" s="4">
         <f t="shared" si="8"/>
-        <v>2335617.0910526868</v>
+        <v>2414561.6050212551</v>
       </c>
       <c r="G24" s="5">
         <f t="shared" si="1"/>
-        <v>0.31240919993084204</v>
+        <v>0.38449845890594242</v>
       </c>
       <c r="H24" s="4">
         <f t="shared" si="4"/>
-        <v>25113242.219975092</v>
+        <v>28098354.61093282</v>
       </c>
       <c r="I24" s="5">
         <f t="shared" si="2"/>
-        <v>0.74978207983402101</v>
+        <v>0.83890572852205625</v>
       </c>
       <c r="J24" s="4">
         <f t="shared" si="5"/>
-        <v>1046385.0924989621</v>
+        <v>1170764.7754555342</v>
       </c>
       <c r="K24" s="4">
         <f t="shared" si="3"/>
-        <v>1645014.5767864559</v>
+        <v>1585818.6515376249</v>
       </c>
       <c r="L24" s="63" cm="1">
         <f t="array" ref="L24">+_xlfn.IFS(I24&gt;114%,H24*0.02,I24&gt;109%,H24*0.015,I24&gt;104%,H24*0.0125,I24&gt;99%,H24*0.01,I24&lt;99%,H24*0)</f>
@@ -4813,34 +4812,34 @@
       </c>
       <c r="D25" s="4">
         <f>IFERROR(+VLOOKUP(B25,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>20675373.952008072</v>
+      </c>
+      <c r="E25" s="4">
         <v>19594052.122893002</v>
-      </c>
-      <c r="E25" s="4">
-        <v>19638670.354043003</v>
       </c>
       <c r="F25" s="4">
         <f t="shared" si="8"/>
-        <v>-44618.231150001287</v>
+        <v>1081321.8291150704</v>
       </c>
       <c r="G25" s="5">
         <f t="shared" si="1"/>
-        <v>0.36241689087974011</v>
+        <v>0.38241731207339447</v>
       </c>
       <c r="H25" s="4">
         <f t="shared" si="4"/>
-        <v>47025725.09494321</v>
+        <v>45109906.804381251</v>
       </c>
       <c r="I25" s="5">
         <f t="shared" si="2"/>
-        <v>0.86980053811137636</v>
+        <v>0.83436504452376981</v>
       </c>
       <c r="J25" s="4">
         <f t="shared" si="5"/>
-        <v>1959405.2122893003</v>
+        <v>1879579.450182552</v>
       </c>
       <c r="K25" s="4">
         <f t="shared" si="3"/>
-        <v>2462207.1958647859</v>
+        <v>2568429.1471532257</v>
       </c>
       <c r="L25" s="63" cm="1">
         <f t="array" ref="L25">+_xlfn.IFS(I25&gt;109%,H25*0.015,I25&gt;104%,H25*0.0125,I25&gt;99%,H25*0.01,I25&lt;99%,H25*0)</f>
@@ -4855,34 +4854,34 @@
       </c>
       <c r="D26" s="67">
         <f>+SUM(D17:D25)</f>
+        <v>121341985.82906419</v>
+      </c>
+      <c r="E26" s="65">
         <v>111116247.49161679</v>
-      </c>
-      <c r="E26" s="65">
-        <v>100418882.659999</v>
       </c>
       <c r="F26" s="67">
         <f>+D26-E26</f>
-        <v>10697364.831617787</v>
+        <v>10225738.337447405</v>
       </c>
       <c r="G26" s="66">
         <f t="shared" si="1"/>
-        <v>0.38865606462556163</v>
+        <v>0.42442306819021025</v>
       </c>
       <c r="H26" s="64">
         <f t="shared" si="4"/>
-        <v>266678993.9798803</v>
+        <v>264746150.8997764</v>
       </c>
       <c r="I26" s="66">
         <f t="shared" si="2"/>
-        <v>0.93277455510134788</v>
+        <v>0.92601396696045868</v>
       </c>
       <c r="J26" s="64">
         <f t="shared" si="5"/>
-        <v>11111624.749161679</v>
+        <v>11031089.620824017</v>
       </c>
       <c r="K26" s="67">
         <f t="shared" si="3"/>
-        <v>12484457.928670231</v>
+        <v>12658205.589533526</v>
       </c>
       <c r="L26" s="68"/>
     </row>
@@ -4898,34 +4897,34 @@
       </c>
       <c r="D27" s="59">
         <f>IFERROR(+VLOOKUP(B27,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>34411101.004763618</v>
+      </c>
+      <c r="E27" s="59">
         <v>33450220.947755333</v>
-      </c>
-      <c r="E27" s="59">
-        <v>30033987.082212482</v>
       </c>
       <c r="F27" s="59">
         <f t="shared" si="8"/>
-        <v>3416233.8655428514</v>
+        <v>960880.05700828508</v>
       </c>
       <c r="G27" s="60">
         <f t="shared" si="1"/>
-        <v>0.40804049086221417</v>
+        <v>0.41976172794264316</v>
       </c>
       <c r="H27" s="59">
         <f t="shared" si="4"/>
-        <v>80280530.274612799</v>
+        <v>75078765.828575164</v>
       </c>
       <c r="I27" s="60">
         <f t="shared" si="2"/>
-        <v>0.97929717806931393</v>
+        <v>0.91584377005667594</v>
       </c>
       <c r="J27" s="59">
         <f t="shared" si="5"/>
-        <v>3345022.0947755333</v>
+        <v>3128281.9095239653</v>
       </c>
       <c r="K27" s="59">
         <f t="shared" si="3"/>
-        <v>3466248.5037317616</v>
+        <v>3658969.1534797219</v>
       </c>
       <c r="L27" s="61" cm="1">
         <f t="array" ref="L27">+_xlfn.IFS(I27&gt;114%,H27*0.0125,I27&gt;109%,H27*0.01,I27&gt;104%,H27*0.0075,I27&gt;99%,H27*0.005,I27&lt;99%,H27*0)</f>
@@ -4942,34 +4941,34 @@
       </c>
       <c r="D28" s="4">
         <f>IFERROR(+VLOOKUP(B28,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>6108215.4389794497</v>
+      </c>
+      <c r="E28" s="4">
         <v>5777964.8325451156</v>
-      </c>
-      <c r="E28" s="4">
-        <v>5212708.9840588067</v>
       </c>
       <c r="F28" s="4">
         <f t="shared" si="8"/>
-        <v>565255.84848630894</v>
+        <v>330250.60643433407</v>
       </c>
       <c r="G28" s="5">
         <f t="shared" si="1"/>
-        <v>0.27514118250214836</v>
+        <v>0.29086740185616428</v>
       </c>
       <c r="H28" s="4">
         <f t="shared" si="4"/>
-        <v>13867115.598108279</v>
+        <v>13327015.50322789</v>
       </c>
       <c r="I28" s="5">
         <f t="shared" si="2"/>
-        <v>0.66033883800515614</v>
+        <v>0.63461978586799472</v>
       </c>
       <c r="J28" s="4">
         <f t="shared" si="5"/>
-        <v>577796.48325451161</v>
+        <v>555292.31263449544</v>
       </c>
       <c r="K28" s="4">
         <f t="shared" si="3"/>
-        <v>1087288.2262467775</v>
+        <v>1145521.8893092731</v>
       </c>
       <c r="L28" s="63" cm="1">
         <f t="array" ref="L28">+_xlfn.IFS(I28&gt;114%,H28*0.02,I28&gt;109%,H28*0.015,I28&gt;104%,H28*0.0125,I28&gt;99%,H28*0.01,I28&lt;99%,H28*0)</f>
@@ -4986,34 +4985,34 @@
       </c>
       <c r="D29" s="4">
         <f>IFERROR(+VLOOKUP(B29,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>11264156.639444824</v>
+      </c>
+      <c r="E29" s="4">
         <v>9823471.9917300809</v>
-      </c>
-      <c r="E29" s="4">
-        <v>8509221.7116328403</v>
       </c>
       <c r="F29" s="4">
         <f t="shared" si="8"/>
-        <v>1314250.2800972406</v>
+        <v>1440684.6477147434</v>
       </c>
       <c r="G29" s="5">
         <f t="shared" si="1"/>
-        <v>0.38164671661791244</v>
+        <v>0.4376180234985188</v>
       </c>
       <c r="H29" s="4">
         <f t="shared" si="4"/>
-        <v>23576332.780152194</v>
+        <v>24576341.758788709</v>
       </c>
       <c r="I29" s="5">
         <f t="shared" si="2"/>
-        <v>0.91595211988298986</v>
+        <v>0.95480296036040468</v>
       </c>
       <c r="J29" s="4">
         <f t="shared" si="5"/>
-        <v>982347.19917300809</v>
+        <v>1024014.2399495295</v>
       </c>
       <c r="K29" s="4">
         <f t="shared" si="3"/>
-        <v>1136873.429162137</v>
+        <v>1113503.3354273213</v>
       </c>
       <c r="L29" s="63" cm="1">
         <f t="array" ref="L29">+_xlfn.IFS(I29&gt;114%,H29*0.02,I29&gt;109%,H29*0.015,I29&gt;104%,H29*0.0125,I29&gt;99%,H29*0.01,I29&lt;99%,H29*0)</f>
@@ -5031,34 +5030,34 @@
       </c>
       <c r="D30" s="4">
         <f>IFERROR(+VLOOKUP(B30,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>9010188.8518341817</v>
+      </c>
+      <c r="E30" s="4">
         <v>8588184.3117468338</v>
-      </c>
-      <c r="E30" s="4">
-        <v>7023786.2862272449</v>
       </c>
       <c r="F30" s="4">
         <f t="shared" si="8"/>
-        <v>1564398.025519589</v>
+        <v>422004.54008734785</v>
       </c>
       <c r="G30" s="5">
         <f t="shared" si="1"/>
-        <v>0.22462632380833508</v>
+        <v>0.23566396867357053</v>
       </c>
       <c r="H30" s="4">
         <f t="shared" si="4"/>
-        <v>20611642.348192401</v>
+        <v>19658593.858547304</v>
       </c>
       <c r="I30" s="5">
         <f t="shared" si="2"/>
-        <v>0.53910317714000422</v>
+        <v>0.51417593165142661</v>
       </c>
       <c r="J30" s="4">
         <f t="shared" si="5"/>
-        <v>858818.43117468338</v>
+        <v>819108.07743947103</v>
       </c>
       <c r="K30" s="4">
         <f t="shared" si="3"/>
-        <v>2117501.4857413457</v>
+        <v>2247924.3277147301</v>
       </c>
       <c r="L30" s="63" cm="1">
         <f t="array" ref="L30">+_xlfn.IFS(I30&gt;114%,H30*0.02,I30&gt;109%,H30*0.015,I30&gt;104%,H30*0.0125,I30&gt;99%,H30*0.01,I30&lt;99%,H30*0)</f>
@@ -5076,34 +5075,34 @@
       </c>
       <c r="D31" s="4">
         <f>IFERROR(+VLOOKUP(B31,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>9777757.9714250863</v>
+      </c>
+      <c r="E31" s="4">
         <v>9407600.5395302419</v>
-      </c>
-      <c r="E31" s="4">
-        <v>8331163.463863492</v>
       </c>
       <c r="F31" s="4">
         <f t="shared" si="8"/>
-        <v>1076437.0756667498</v>
+        <v>370157.4318948444</v>
       </c>
       <c r="G31" s="5">
         <f t="shared" si="1"/>
-        <v>0.37015573482575392</v>
+        <v>0.38472011770197367</v>
       </c>
       <c r="H31" s="4">
         <f t="shared" si="4"/>
-        <v>22578241.294872582</v>
+        <v>21333290.119472917</v>
       </c>
       <c r="I31" s="5">
         <f t="shared" si="2"/>
-        <v>0.88837376358180942</v>
+        <v>0.83938934771339713</v>
       </c>
       <c r="J31" s="4">
         <f t="shared" si="5"/>
-        <v>940760.05395302421</v>
+        <v>888887.08831137151</v>
       </c>
       <c r="K31" s="4">
         <f t="shared" si="3"/>
-        <v>1143403.532890697</v>
+        <v>1202884.0021980703</v>
       </c>
       <c r="L31" s="63" cm="1">
         <f t="array" ref="L31">+_xlfn.IFS(I31&gt;114%,H31*0.02,I31&gt;109%,H31*0.015,I31&gt;104%,H31*0.0125,I31&gt;99%,H31*0.01,I31&lt;99%,H31*0)</f>
@@ -5121,34 +5120,34 @@
       </c>
       <c r="D32" s="4">
         <f>IFERROR(+VLOOKUP(B32,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>7333522.0196865257</v>
+      </c>
+      <c r="E32" s="4">
         <v>6665534.1859788187</v>
-      </c>
-      <c r="E32" s="4">
-        <v>5611548.663038048</v>
       </c>
       <c r="F32" s="4">
         <f t="shared" si="8"/>
-        <v>1053985.5229407707</v>
+        <v>667987.833707707</v>
       </c>
       <c r="G32" s="5">
         <f t="shared" si="1"/>
-        <v>0.26450532484042932</v>
+        <v>0.2910127785589891</v>
       </c>
       <c r="H32" s="4">
         <f t="shared" si="4"/>
-        <v>15997282.046349166</v>
+        <v>16000411.679316055</v>
       </c>
       <c r="I32" s="5">
         <f t="shared" si="2"/>
-        <v>0.63481277961703042</v>
+        <v>0.63493697140143079</v>
       </c>
       <c r="J32" s="4">
         <f t="shared" si="5"/>
-        <v>666553.41859788192</v>
+        <v>666683.81997150229</v>
       </c>
       <c r="K32" s="4">
         <f t="shared" si="3"/>
-        <v>1323890.4152872271</v>
+        <v>1374344.4600241133</v>
       </c>
       <c r="L32" s="63" cm="1">
         <f t="array" ref="L32">+_xlfn.IFS(I32&gt;114%,H32*0.02,I32&gt;109%,H32*0.015,I32&gt;104%,H32*0.0125,I32&gt;99%,H32*0.01,I32&lt;99%,H32*0)</f>
@@ -5166,34 +5165,34 @@
       </c>
       <c r="D33" s="4">
         <f>IFERROR(+VLOOKUP(B33,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>6945315.7802029736</v>
+      </c>
+      <c r="E33" s="4">
         <v>6448364.3120282274</v>
-      </c>
-      <c r="E33" s="4">
-        <v>5482149.478754703</v>
       </c>
       <c r="F33" s="4">
         <f t="shared" si="8"/>
-        <v>966214.83327352442</v>
+        <v>496951.46817474626</v>
       </c>
       <c r="G33" s="5">
         <f t="shared" si="1"/>
-        <v>0.24336434891178077</v>
+        <v>0.26211953466757143</v>
       </c>
       <c r="H33" s="4">
         <f t="shared" si="4"/>
-        <v>15476074.348867744</v>
+        <v>15153416.247715579</v>
       </c>
       <c r="I33" s="5">
         <f t="shared" si="2"/>
-        <v>0.5840744373882738</v>
+        <v>0.57189716654742861</v>
       </c>
       <c r="J33" s="4">
         <f t="shared" si="5"/>
-        <v>644836.43120282271</v>
+        <v>631392.34365481581</v>
       </c>
       <c r="K33" s="4">
         <f t="shared" si="3"/>
-        <v>1432027.5491408408</v>
+        <v>1503956.4784459251</v>
       </c>
       <c r="L33" s="63" cm="1">
         <f t="array" ref="L33">+_xlfn.IFS(I33&gt;114%,H33*0.02,I33&gt;109%,H33*0.015,I33&gt;104%,H33*0.0125,I33&gt;99%,H33*0.01,I33&lt;99%,H33*0)</f>
@@ -5210,34 +5209,34 @@
       </c>
       <c r="D34" s="4">
         <f>IFERROR(+VLOOKUP(B34,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>6164880.2550763758</v>
+      </c>
+      <c r="E34" s="4">
         <v>5618690.4157067938</v>
-      </c>
-      <c r="E34" s="4">
-        <v>4657516.3901073569</v>
       </c>
       <c r="F34" s="4">
         <f t="shared" si="8"/>
-        <v>961174.02559943683</v>
+        <v>546189.83936958201</v>
       </c>
       <c r="G34" s="5">
         <f t="shared" si="1"/>
-        <v>0.2675566864622283</v>
+        <v>0.29356572643220835</v>
       </c>
       <c r="H34" s="4">
         <f t="shared" si="4"/>
-        <v>13484856.997696307</v>
+        <v>13450647.829257548</v>
       </c>
       <c r="I34" s="5">
         <f t="shared" si="2"/>
-        <v>0.64213604750934794</v>
+        <v>0.64050703948845467</v>
       </c>
       <c r="J34" s="4">
         <f t="shared" si="5"/>
-        <v>561869.0415706794</v>
+        <v>560443.65955239779</v>
       </c>
       <c r="K34" s="4">
         <f t="shared" si="3"/>
-        <v>1098664.9703066575</v>
+        <v>1141163.0573018172</v>
       </c>
       <c r="L34" s="63" cm="1">
         <f t="array" ref="L34">+_xlfn.IFS(I34&gt;114%,H34*0.02,I34&gt;109%,H34*0.015,I34&gt;104%,H34*0.0125,I34&gt;99%,H34*0.01,I34&lt;99%,H34*0)</f>
@@ -5254,34 +5253,34 @@
       </c>
       <c r="D35" s="4">
         <f>IFERROR(+VLOOKUP(B35,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>3882737.6125165834</v>
+      </c>
+      <c r="E35" s="4">
         <v>3802949.3075159392</v>
-      </c>
-      <c r="E35" s="4">
-        <v>3564392.4785372978</v>
       </c>
       <c r="F35" s="4">
         <f t="shared" si="8"/>
-        <v>238556.82897864142</v>
+        <v>79788.305000644177</v>
       </c>
       <c r="G35" s="5">
         <f t="shared" si="1"/>
-        <v>0.15422655779886363</v>
+        <v>0.15746232946916577</v>
       </c>
       <c r="H35" s="4">
         <f t="shared" si="4"/>
-        <v>9127078.3380382545</v>
+        <v>8471427.5182179995</v>
       </c>
       <c r="I35" s="5">
         <f t="shared" si="2"/>
-        <v>0.37014373871727274</v>
+        <v>0.34355417338727073</v>
       </c>
       <c r="J35" s="4">
         <f t="shared" si="5"/>
-        <v>380294.9307515939</v>
+        <v>352976.14659241668</v>
       </c>
       <c r="K35" s="4">
         <f t="shared" si="3"/>
-        <v>1489660.7637488616</v>
+        <v>1598112.4913448782</v>
       </c>
       <c r="L35" s="63" cm="1">
         <f t="array" ref="L35">+_xlfn.IFS(I35&gt;114%,H35*0.02,I35&gt;109%,H35*0.015,I35&gt;104%,H35*0.0125,I35&gt;99%,H35*0.01,I35&lt;99%,H35*0)</f>
@@ -5298,34 +5297,34 @@
       </c>
       <c r="D36" s="4">
         <f>IFERROR(+VLOOKUP(B36,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>6557112.931111577</v>
+      </c>
+      <c r="E36" s="4">
         <v>6222492.2724699304</v>
-      </c>
-      <c r="E36" s="4">
-        <v>5567175.7313747797</v>
       </c>
       <c r="F36" s="4">
         <f t="shared" si="8"/>
-        <v>655316.54109515063</v>
+        <v>334620.65864164662</v>
       </c>
       <c r="G36" s="5">
         <f t="shared" si="1"/>
-        <v>0.24658182177412047</v>
+        <v>0.25984200242169908</v>
       </c>
       <c r="H36" s="4">
         <f t="shared" si="4"/>
-        <v>14933981.453927832</v>
+        <v>14306428.213334348</v>
       </c>
       <c r="I36" s="5">
         <f t="shared" si="2"/>
-        <v>0.59179637225788906</v>
+        <v>0.56692800528370713</v>
       </c>
       <c r="J36" s="4">
         <f t="shared" si="5"/>
-        <v>622249.22724699299</v>
+        <v>596101.17555559787</v>
       </c>
       <c r="K36" s="4">
         <f t="shared" si="3"/>
-        <v>1358036.2662521477</v>
+        <v>1436760.5437606478</v>
       </c>
       <c r="L36" s="63" cm="1">
         <f t="array" ref="L36">+_xlfn.IFS(I36&gt;114%,H36*0.02,I36&gt;109%,H36*0.015,I36&gt;104%,H36*0.0125,I36&gt;99%,H36*0.01,I36&lt;99%,H36*0)</f>
@@ -5345,11 +5344,11 @@
         <v>33451176.522885799</v>
       </c>
       <c r="E37" s="4">
-        <v>28457978.498885799</v>
+        <v>33451176.522885799</v>
       </c>
       <c r="F37" s="4">
         <f t="shared" si="8"/>
-        <v>4993198.0240000002</v>
+        <v>0</v>
       </c>
       <c r="G37" s="5">
         <f t="shared" si="1"/>
@@ -5357,19 +5356,19 @@
       </c>
       <c r="H37" s="4">
         <f t="shared" si="4"/>
-        <v>80282823.654925913</v>
+        <v>72984385.140841737</v>
       </c>
       <c r="I37" s="5">
         <f t="shared" si="2"/>
-        <v>0.65799255936355239</v>
+        <v>0.59817505396686577</v>
       </c>
       <c r="J37" s="4">
         <f t="shared" si="5"/>
-        <v>3345117.6522885798</v>
+        <v>3041016.0475350725</v>
       </c>
       <c r="K37" s="4">
         <f t="shared" si="3"/>
-        <v>6325755.2483652998</v>
+        <v>6812351.8059318615</v>
       </c>
       <c r="L37" s="63" cm="1">
         <f t="array" ref="L37">+_xlfn.IFS(I37&gt;114%,H37*0.0125,I37&gt;109%,H37*0.01,I37&gt;104%,H37*0.0075,I37&gt;99%,H37*0.005,I37&lt;99%,H37*0)</f>
@@ -5386,34 +5385,34 @@
       </c>
       <c r="D38" s="4">
         <f>IFERROR(+VLOOKUP(B38,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>4955958.0088995183</v>
+      </c>
+      <c r="E38" s="4">
         <v>4305943.4722995181</v>
-      </c>
-      <c r="E38" s="4">
-        <v>2767832.4172995184</v>
       </c>
       <c r="F38" s="4">
         <f t="shared" ref="F38" si="10">+D38-E38</f>
-        <v>1538111.0549999997</v>
+        <v>650014.53660000023</v>
       </c>
       <c r="G38" s="5">
         <f t="shared" si="1"/>
-        <v>0.12061466308962235</v>
+        <v>0.13882235319046271</v>
       </c>
       <c r="H38" s="4">
         <f t="shared" si="4"/>
-        <v>10334264.333518844</v>
+        <v>10812999.292144403</v>
       </c>
       <c r="I38" s="5">
         <f t="shared" si="2"/>
-        <v>0.28947519141509365</v>
+        <v>0.30288513423373675</v>
       </c>
       <c r="J38" s="4">
         <f t="shared" si="5"/>
-        <v>430594.34722995182</v>
+        <v>450541.63717268349</v>
       </c>
       <c r="K38" s="4">
         <f t="shared" si="3"/>
-        <v>2242432.6091214633</v>
+        <v>2364926.3070077295</v>
       </c>
       <c r="L38" s="63" cm="1">
         <f t="array" ref="L38">+_xlfn.IFS(I38&gt;109%,H38*0.015,I38&gt;104%,H38*0.0125,I38&gt;99%,H38*0.01,I38&lt;99%,H38*0)</f>
@@ -5430,34 +5429,34 @@
       </c>
       <c r="D39" s="4">
         <f>IFERROR(+VLOOKUP(B39,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>11259066.488129456</v>
+      </c>
+      <c r="E39" s="4">
         <v>11081724.942682527</v>
-      </c>
-      <c r="E39" s="4">
-        <v>9930506.0322296303</v>
       </c>
       <c r="F39" s="4">
         <f t="shared" si="8"/>
-        <v>1151218.9104528967</v>
+        <v>177341.54544692859</v>
       </c>
       <c r="G39" s="5">
         <f t="shared" si="1"/>
-        <v>0.30476594654716088</v>
+        <v>0.3096431352736288</v>
       </c>
       <c r="H39" s="4">
         <f t="shared" si="4"/>
-        <v>26596139.862438068</v>
+        <v>24565235.974100631</v>
       </c>
       <c r="I39" s="5">
         <f t="shared" si="2"/>
-        <v>0.73143827171318621</v>
+        <v>0.67558502241519014</v>
       </c>
       <c r="J39" s="4">
         <f t="shared" si="5"/>
-        <v>1108172.4942682527</v>
+        <v>1023551.4989208597</v>
       </c>
       <c r="K39" s="4">
         <f t="shared" si="3"/>
-        <v>1805693.0568798196</v>
+        <v>1930950.8654515804</v>
       </c>
       <c r="L39" s="63" cm="1">
         <f t="array" ref="L39">+_xlfn.IFS(I39&gt;114%,H39*0.02,I39&gt;109%,H39*0.015,I39&gt;104%,H39*0.0125,I39&gt;99%,H39*0.01,I39&lt;99%,H39*0)</f>
@@ -5472,34 +5471,34 @@
       </c>
       <c r="D40" s="67">
         <f>+SUM(D27:D39)</f>
+        <v>151121189.52495596</v>
+      </c>
+      <c r="E40" s="65">
         <v>144644318.05487517</v>
-      </c>
-      <c r="E40" s="65">
-        <v>125149967.21822201</v>
       </c>
       <c r="F40" s="67">
         <f t="shared" si="8"/>
-        <v>19494350.836653158</v>
+        <v>6476871.4700807929</v>
       </c>
       <c r="G40" s="66">
         <f t="shared" si="1"/>
-        <v>0.28415733274106886</v>
+        <v>0.29688130659773049</v>
       </c>
       <c r="H40" s="64">
         <f t="shared" si="4"/>
-        <v>347146363.33170044</v>
+        <v>329718958.96354026</v>
       </c>
       <c r="I40" s="66">
         <f t="shared" si="2"/>
-        <v>0.68197759857856532</v>
+        <v>0.64774103257686655</v>
       </c>
       <c r="J40" s="64">
         <f t="shared" si="5"/>
-        <v>14464431.805487517</v>
+        <v>13738289.956814177</v>
       </c>
       <c r="K40" s="67">
         <f t="shared" si="3"/>
-        <v>26027476.056875043</v>
+        <v>27531368.717397671</v>
       </c>
       <c r="L40" s="68"/>
     </row>
@@ -5513,34 +5512,34 @@
       </c>
       <c r="D41" s="81">
         <f>+D40+D26+D10+D16</f>
+        <v>566825570.63776278</v>
+      </c>
+      <c r="E41" s="82">
         <v>523856297.78755802</v>
-      </c>
-      <c r="E41" s="82">
-        <v>470467238.36041617</v>
       </c>
       <c r="F41" s="81">
         <f>+D41-E41</f>
-        <v>53389059.427141845</v>
+        <v>42969272.850204766</v>
       </c>
       <c r="G41" s="83">
         <f t="shared" si="1"/>
-        <v>0.37967007613654757</v>
+        <v>0.41081248515877389</v>
       </c>
       <c r="H41" s="81">
         <f t="shared" si="4"/>
-        <v>1257255114.6901393</v>
+        <v>1236710335.9369371</v>
       </c>
       <c r="I41" s="83">
         <f t="shared" si="2"/>
-        <v>0.9112081827277142</v>
+        <v>0.89631814943732502</v>
       </c>
       <c r="J41" s="81">
         <f t="shared" si="5"/>
-        <v>52385629.778755799</v>
+        <v>51529597.33070571</v>
       </c>
       <c r="K41" s="81">
         <f t="shared" si="3"/>
-        <v>61136489.236112714</v>
+        <v>62533967.419644102</v>
       </c>
       <c r="L41" s="84"/>
     </row>
@@ -5588,34 +5587,34 @@
       </c>
       <c r="D43" s="4">
         <f>IFERROR(+VLOOKUP(B43,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>6840893.5633781236</v>
+        <v>10831277.641265372</v>
       </c>
       <c r="E43" s="4">
         <v>6840893.5633781236</v>
       </c>
       <c r="F43" s="4">
         <f t="shared" ref="F43" si="11">+D43-E43</f>
-        <v>0</v>
+        <v>3990384.0778872482</v>
       </c>
       <c r="G43" s="5">
         <f>+D43/C43</f>
-        <v>0.17102233908445308</v>
+        <v>0.27078194103163428</v>
       </c>
       <c r="H43" s="4">
         <f t="shared" ref="H43" si="12">+D43/$N$3*$N$4</f>
-        <v>16418144.552107498</v>
+        <v>23631878.490033537</v>
       </c>
       <c r="I43" s="5">
         <f>+H43/C43</f>
-        <v>0.41045361380268747</v>
+        <v>0.59079696225083844</v>
       </c>
       <c r="J43" s="4">
         <f t="shared" ref="J43" si="13">+D43/$N$3</f>
-        <v>684089.35633781238</v>
+        <v>984661.60375139746</v>
       </c>
       <c r="K43" s="4">
         <f>+(C43-D43)/$N$2</f>
-        <v>2368507.6026158482</v>
+        <v>2243747.8737488175</v>
       </c>
       <c r="L43" s="4" cm="1">
         <f t="array" ref="L43">+_xlfn.IFS(I43&gt;114%,H43*0.02,I43&gt;109%,H43*0.015,I43&gt;104%,H43*0.0125,I43&gt;99%,H43*0.01,I43&lt;99%,H43*0)</f>
@@ -5631,38 +5630,38 @@
       </c>
       <c r="D44" s="4">
         <f>IFERROR(+VLOOKUP(B44,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>14127537.863605659</v>
+        <v>16443269.938349089</v>
       </c>
       <c r="E44" s="4">
         <v>14127537.863605659</v>
       </c>
       <c r="F44" s="4">
         <f t="shared" ref="F44" si="14">+D44-E44</f>
-        <v>0</v>
+        <v>2315732.0747434292</v>
       </c>
       <c r="G44" s="5">
         <f>+D44/C44</f>
-        <v>0.47091792878685529</v>
+        <v>0.54810899794496959</v>
       </c>
       <c r="H44" s="4">
         <f t="shared" ref="H44" si="15">+D44/$N$3*$N$4</f>
-        <v>33906090.872653589</v>
+        <v>35876225.320034377</v>
       </c>
       <c r="I44" s="5">
         <f>+H44/C44</f>
-        <v>1.130203029088453</v>
+        <v>1.1958741773344792</v>
       </c>
       <c r="J44" s="4">
         <f t="shared" ref="J44" si="16">+D44/$N$3</f>
-        <v>1412753.786360566</v>
+        <v>1494842.7216680991</v>
       </c>
       <c r="K44" s="4">
         <f>+(C44-D44)/$N$2</f>
-        <v>1133747.2954567387</v>
+        <v>1042825.3893577624</v>
       </c>
       <c r="L44" s="4" cm="1">
         <f t="array" ref="L44">+_xlfn.IFS(I44&gt;114%,H44*0.02,I44&gt;109%,H44*0.015,I44&gt;104%,H44*0.0125,I44&gt;99%,H44*0.01,I44&lt;99%,H44*0)</f>
-        <v>508591.36308980384</v>
+        <v>717524.5064006875</v>
       </c>
     </row>
   </sheetData>
@@ -5800,14 +5799,14 @@
       </c>
       <c r="D2" s="22">
         <f>H2/G2</f>
-        <v>0.64383561643835618</v>
+        <v>0.68493150684931503</v>
       </c>
       <c r="E2" s="13">
         <v>33</v>
       </c>
       <c r="F2" s="12">
         <f>+H2-E2</f>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G2" s="13">
         <f>VLOOKUP(B2,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -5815,11 +5814,11 @@
       </c>
       <c r="H2" s="13">
         <f>VLOOKUP(B2,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I2" s="17">
         <f>(+G2*$M$2)-H2</f>
-        <v>15.049999999999997</v>
+        <v>12.049999999999997</v>
       </c>
       <c r="J2" t="s">
         <v>55</v>
@@ -5865,7 +5864,7 @@
       </c>
       <c r="D3" s="22">
         <f t="shared" ref="D3:D38" si="0">H3/G3</f>
-        <v>0.34309623430962344</v>
+        <v>0.34024896265560167</v>
       </c>
       <c r="E3" s="13">
         <v>1</v>
@@ -5876,7 +5875,7 @@
       </c>
       <c r="G3" s="13">
         <f>VLOOKUP(B3,'Base Cobertura'!$A:$C,3,FALSE)</f>
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H3" s="13">
         <f>VLOOKUP(B3,'Base Cobertura'!$A:$C,2,FALSE)</f>
@@ -5884,7 +5883,7 @@
       </c>
       <c r="I3" s="17">
         <f t="shared" ref="I3:I38" si="2">(+G3*$M$2)-H3</f>
-        <v>121.15</v>
+        <v>122.85</v>
       </c>
       <c r="J3" t="s">
         <v>56</v>
@@ -5903,14 +5902,14 @@
         <v>145 - ALMACEN</v>
       </c>
       <c r="S3" s="12">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="T3" s="12">
         <v>214</v>
       </c>
       <c r="U3" s="41">
         <f>+S3/T3</f>
-        <v>0.19626168224299065</v>
+        <v>0.2102803738317757</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
@@ -5924,14 +5923,14 @@
       </c>
       <c r="D4" s="22">
         <f t="shared" si="0"/>
-        <v>0.74008810572687223</v>
+        <v>0.78854625550660795</v>
       </c>
       <c r="E4" s="13">
         <v>126</v>
       </c>
       <c r="F4" s="12">
         <f t="shared" si="1"/>
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="G4" s="13">
         <f>VLOOKUP(B4,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -5939,11 +5938,11 @@
       </c>
       <c r="H4" s="13">
         <f>VLOOKUP(B4,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="I4" s="17">
         <f t="shared" si="2"/>
-        <v>24.949999999999989</v>
+        <v>13.949999999999989</v>
       </c>
       <c r="J4" t="s">
         <v>57</v>
@@ -5961,14 +5960,14 @@
         <v>145 - Articulos Sin Asociar Agrupacion</v>
       </c>
       <c r="S4" s="13">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="T4" s="13">
         <v>214</v>
       </c>
       <c r="U4" s="5">
         <f t="shared" ref="U4:U11" si="3">+S4/T4</f>
-        <v>0.11214953271028037</v>
+        <v>0.11682242990654206</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
@@ -5982,14 +5981,14 @@
       </c>
       <c r="D5" s="22">
         <f t="shared" si="0"/>
-        <v>0.63076923076923075</v>
+        <v>0.67692307692307696</v>
       </c>
       <c r="E5" s="13">
         <v>21</v>
       </c>
       <c r="F5" s="12">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G5" s="13">
         <f>VLOOKUP(B5,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -5997,11 +5996,11 @@
       </c>
       <c r="H5" s="13">
         <f>VLOOKUP(B5,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="I5" s="17">
         <f t="shared" si="2"/>
-        <v>14.25</v>
+        <v>11.25</v>
       </c>
       <c r="K5" t="s">
         <v>64</v>
@@ -6016,14 +6015,14 @@
         <v>145 - BEBIDAS</v>
       </c>
       <c r="S5" s="13">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="T5" s="13">
         <v>214</v>
       </c>
       <c r="U5" s="5">
         <f t="shared" si="3"/>
-        <v>0.27570093457943923</v>
+        <v>0.30841121495327101</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
@@ -6037,14 +6036,14 @@
       </c>
       <c r="D6" s="22">
         <f t="shared" si="0"/>
-        <v>0.70531400966183577</v>
+        <v>0.72946859903381644</v>
       </c>
       <c r="E6" s="13">
         <v>100</v>
       </c>
       <c r="F6" s="12">
         <f t="shared" si="1"/>
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="G6" s="13">
         <f>VLOOKUP(B6,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6052,11 +6051,11 @@
       </c>
       <c r="H6" s="13">
         <f>VLOOKUP(B6,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="I6" s="17">
         <f t="shared" si="2"/>
-        <v>29.949999999999989</v>
+        <v>24.949999999999989</v>
       </c>
       <c r="J6" t="s">
         <v>58</v>
@@ -6074,14 +6073,14 @@
         <v>145 - CHOCOLATE</v>
       </c>
       <c r="S6" s="13">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="T6" s="13">
         <v>214</v>
       </c>
       <c r="U6" s="5">
         <f t="shared" si="3"/>
-        <v>0.13551401869158877</v>
+        <v>0.14953271028037382</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
@@ -6095,14 +6094,14 @@
       </c>
       <c r="D7" s="22">
         <f t="shared" si="0"/>
-        <v>0.57070707070707072</v>
+        <v>0.59595959595959591</v>
       </c>
       <c r="E7" s="13">
         <v>81</v>
       </c>
       <c r="F7" s="12">
         <f t="shared" si="1"/>
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G7" s="13">
         <f>VLOOKUP(B7,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6110,11 +6109,11 @@
       </c>
       <c r="H7" s="13">
         <f>VLOOKUP(B7,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="I7" s="17">
         <f t="shared" si="2"/>
-        <v>55.299999999999983</v>
+        <v>50.299999999999983</v>
       </c>
       <c r="J7" t="s">
         <v>58</v>
@@ -6132,14 +6131,14 @@
         <v>145 - GALLETITAS</v>
       </c>
       <c r="S7" s="13">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="T7" s="13">
         <v>214</v>
       </c>
       <c r="U7" s="5">
         <f t="shared" si="3"/>
-        <v>0.30841121495327101</v>
+        <v>0.31775700934579437</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
@@ -6153,14 +6152,14 @@
       </c>
       <c r="D8" s="22">
         <f t="shared" si="0"/>
-        <v>0.68691588785046731</v>
+        <v>0.7429906542056075</v>
       </c>
       <c r="E8" s="13">
         <v>89</v>
       </c>
       <c r="F8" s="12">
         <f t="shared" si="1"/>
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="G8" s="13">
         <f>VLOOKUP(B8,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6168,11 +6167,11 @@
       </c>
       <c r="H8" s="13">
         <f>VLOOKUP(B8,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="I8" s="17">
         <f t="shared" si="2"/>
-        <v>34.900000000000006</v>
+        <v>22.900000000000006</v>
       </c>
       <c r="J8" t="s">
         <v>55</v>
@@ -6191,14 +6190,14 @@
         <v>145 - GOLOSINAS</v>
       </c>
       <c r="S8" s="13">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="T8" s="13">
         <v>214</v>
       </c>
       <c r="U8" s="5">
         <f t="shared" si="3"/>
-        <v>0.26168224299065418</v>
+        <v>0.28037383177570091</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
@@ -6212,26 +6211,26 @@
       </c>
       <c r="D9" s="22">
         <f>H9/G9</f>
-        <v>0.65644171779141103</v>
+        <v>0.66867469879518071</v>
       </c>
       <c r="E9" s="13">
         <v>92</v>
       </c>
       <c r="F9" s="12">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G9" s="13">
         <f>VLOOKUP(B9,'Base Cobertura'!$A:$C,3,FALSE)</f>
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="H9" s="13">
         <f>VLOOKUP(B9,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="I9" s="17">
         <f t="shared" si="2"/>
-        <v>31.549999999999983</v>
+        <v>30.099999999999994</v>
       </c>
       <c r="J9" t="s">
         <v>55</v>
@@ -6270,14 +6269,14 @@
       </c>
       <c r="D10" s="22">
         <f t="shared" si="0"/>
-        <v>0.54871794871794877</v>
+        <v>0.57435897435897432</v>
       </c>
       <c r="E10" s="13">
         <v>64</v>
       </c>
       <c r="F10" s="12">
         <f t="shared" si="1"/>
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="G10" s="13">
         <f>VLOOKUP(B10,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6285,11 +6284,11 @@
       </c>
       <c r="H10" s="13">
         <f>VLOOKUP(B10,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="I10" s="17">
         <f t="shared" si="2"/>
-        <v>58.75</v>
+        <v>53.75</v>
       </c>
       <c r="J10" t="s">
         <v>58</v>
@@ -6307,14 +6306,14 @@
         <v>145 - NO PERECEDEROS</v>
       </c>
       <c r="S10" s="13">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="T10" s="13">
         <v>214</v>
       </c>
       <c r="U10" s="5">
         <f t="shared" si="3"/>
-        <v>7.0093457943925228E-2</v>
+        <v>7.9439252336448593E-2</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
@@ -6328,14 +6327,14 @@
       </c>
       <c r="D11" s="32">
         <f t="shared" si="0"/>
-        <v>0.27722772277227725</v>
+        <v>0.31683168316831684</v>
       </c>
       <c r="E11" s="31">
         <v>19</v>
       </c>
       <c r="F11" s="33">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G11" s="13">
         <f>VLOOKUP(B11,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6343,11 +6342,11 @@
       </c>
       <c r="H11" s="13">
         <f>VLOOKUP(B11,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I11" s="34">
         <f t="shared" si="2"/>
-        <v>57.849999999999994</v>
+        <v>53.849999999999994</v>
       </c>
       <c r="J11" t="s">
         <v>59</v>
@@ -6362,14 +6361,14 @@
         <v>145 - PILAS</v>
       </c>
       <c r="S11" s="13">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="T11" s="13">
         <v>214</v>
       </c>
       <c r="U11" s="5">
         <f t="shared" si="3"/>
-        <v>0.11682242990654206</v>
+        <v>0.13084112149532709</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
@@ -6383,14 +6382,14 @@
       </c>
       <c r="D12" s="32">
         <f t="shared" si="0"/>
-        <v>0.34285714285714286</v>
+        <v>0.40952380952380951</v>
       </c>
       <c r="E12" s="31">
         <v>24</v>
       </c>
       <c r="F12" s="33">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="G12" s="13">
         <f>VLOOKUP(B12,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6398,11 +6397,11 @@
       </c>
       <c r="H12" s="13">
         <f>VLOOKUP(B12,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="I12" s="34">
         <f t="shared" si="2"/>
-        <v>53.25</v>
+        <v>46.25</v>
       </c>
       <c r="J12" t="s">
         <v>59</v>
@@ -6419,14 +6418,14 @@
       </c>
       <c r="D13" s="22">
         <f t="shared" si="0"/>
-        <v>0.68582375478927204</v>
+        <v>0.72796934865900387</v>
       </c>
       <c r="E13" s="13">
         <v>144</v>
       </c>
       <c r="F13" s="12">
         <f t="shared" si="1"/>
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="G13" s="13">
         <f>VLOOKUP(B13,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6434,11 +6433,11 @@
       </c>
       <c r="H13" s="13">
         <f>VLOOKUP(B13,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="I13" s="17">
         <f t="shared" si="2"/>
-        <v>42.849999999999994</v>
+        <v>31.849999999999994</v>
       </c>
       <c r="J13" t="s">
         <v>57</v>
@@ -6458,14 +6457,14 @@
       </c>
       <c r="D14" s="22">
         <f t="shared" si="0"/>
-        <v>0.5714285714285714</v>
+        <v>0.59340659340659341</v>
       </c>
       <c r="E14" s="13">
         <v>85</v>
       </c>
       <c r="F14" s="12">
         <f t="shared" si="1"/>
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G14" s="13">
         <f>VLOOKUP(B14,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6473,11 +6472,11 @@
       </c>
       <c r="H14" s="13">
         <f>VLOOKUP(B14,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="I14" s="17">
         <f t="shared" si="2"/>
-        <v>50.699999999999989</v>
+        <v>46.699999999999989</v>
       </c>
       <c r="J14" t="s">
         <v>55</v>
@@ -6493,15 +6492,15 @@
       <c r="E15" s="14"/>
       <c r="F15" s="16">
         <f>+SUM(F2:F14)</f>
-        <v>426</v>
+        <v>500</v>
       </c>
       <c r="G15" s="8">
         <f>+SUM(G2:G14)</f>
-        <v>2230</v>
+        <v>2235</v>
       </c>
       <c r="H15" s="8">
         <f>+SUM(H2:H14)</f>
-        <v>1305</v>
+        <v>1379</v>
       </c>
       <c r="I15" s="8"/>
     </row>
@@ -6518,14 +6517,14 @@
       </c>
       <c r="D16" s="22">
         <f t="shared" si="0"/>
-        <v>0.72499999999999998</v>
+        <v>0.75</v>
       </c>
       <c r="E16" s="13">
         <v>90</v>
       </c>
       <c r="F16" s="12">
         <f t="shared" si="1"/>
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G16" s="13">
         <f>VLOOKUP(B16,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6533,11 +6532,11 @@
       </c>
       <c r="H16" s="13">
         <f>VLOOKUP(B16,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="I16" s="17">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J16" t="s">
         <v>55</v>
@@ -6557,14 +6556,14 @@
       </c>
       <c r="D17" s="22">
         <f t="shared" si="0"/>
-        <v>0.38118811881188119</v>
+        <v>0.43069306930693069</v>
       </c>
       <c r="E17" s="13">
         <v>92</v>
       </c>
       <c r="F17" s="12">
         <f t="shared" si="1"/>
-        <v>-15</v>
+        <v>-5</v>
       </c>
       <c r="G17" s="13">
         <f>VLOOKUP(B17,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6572,11 +6571,11 @@
       </c>
       <c r="H17" s="13">
         <f>VLOOKUP(B17,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="I17" s="17">
         <f t="shared" si="2"/>
-        <v>94.699999999999989</v>
+        <v>84.699999999999989</v>
       </c>
       <c r="J17" t="s">
         <v>55</v>
@@ -6596,26 +6595,26 @@
       </c>
       <c r="D18" s="22">
         <f t="shared" si="0"/>
-        <v>0.77058823529411768</v>
+        <v>0.78947368421052633</v>
       </c>
       <c r="E18" s="13">
         <v>88</v>
       </c>
       <c r="F18" s="12">
         <f t="shared" si="1"/>
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G18" s="13">
         <f>VLOOKUP(B18,'Base Cobertura'!$A:$C,3,FALSE)</f>
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H18" s="13">
         <f>VLOOKUP(B18,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="I18" s="17">
         <f t="shared" si="2"/>
-        <v>13.5</v>
+        <v>10.349999999999994</v>
       </c>
       <c r="J18" t="s">
         <v>58</v>
@@ -6635,14 +6634,14 @@
       </c>
       <c r="D19" s="22">
         <f t="shared" si="0"/>
-        <v>0.72727272727272729</v>
+        <v>0.74025974025974028</v>
       </c>
       <c r="E19" s="13">
         <v>95</v>
       </c>
       <c r="F19" s="12">
         <f t="shared" si="1"/>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G19" s="13">
         <f>VLOOKUP(B19,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6650,11 +6649,11 @@
       </c>
       <c r="H19" s="13">
         <f>VLOOKUP(B19,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="I19" s="17">
         <f t="shared" si="2"/>
-        <v>18.900000000000006</v>
+        <v>16.900000000000006</v>
       </c>
       <c r="J19" t="s">
         <v>58</v>
@@ -6674,14 +6673,14 @@
       </c>
       <c r="D20" s="22">
         <f t="shared" si="0"/>
-        <v>0.7344632768361582</v>
+        <v>0.76836158192090398</v>
       </c>
       <c r="E20" s="13">
         <v>83</v>
       </c>
       <c r="F20" s="12">
         <f t="shared" si="1"/>
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G20" s="13">
         <f>VLOOKUP(B20,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6689,11 +6688,11 @@
       </c>
       <c r="H20" s="13">
         <f>VLOOKUP(B20,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="I20" s="17">
         <f t="shared" si="2"/>
-        <v>20.449999999999989</v>
+        <v>14.449999999999989</v>
       </c>
       <c r="J20" t="s">
         <v>55</v>
@@ -6713,14 +6712,14 @@
       </c>
       <c r="D21" s="22">
         <f t="shared" si="0"/>
-        <v>0.68047337278106512</v>
+        <v>0.70414201183431957</v>
       </c>
       <c r="E21" s="13">
         <v>64</v>
       </c>
       <c r="F21" s="12">
         <f t="shared" si="1"/>
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G21" s="13">
         <f>VLOOKUP(B21,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6728,11 +6727,11 @@
       </c>
       <c r="H21" s="13">
         <f>VLOOKUP(B21,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I21" s="17">
         <f t="shared" si="2"/>
-        <v>28.650000000000006</v>
+        <v>24.650000000000006</v>
       </c>
       <c r="J21" t="s">
         <v>58</v>
@@ -6830,14 +6829,14 @@
       </c>
       <c r="D24" s="22">
         <f t="shared" si="0"/>
-        <v>0.68823529411764706</v>
+        <v>0.69411764705882351</v>
       </c>
       <c r="E24" s="13">
         <v>79</v>
       </c>
       <c r="F24" s="12">
         <f t="shared" si="1"/>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G24" s="13">
         <f>VLOOKUP(B24,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6845,11 +6844,11 @@
       </c>
       <c r="H24" s="13">
         <f>VLOOKUP(B24,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I24" s="17">
         <f t="shared" si="2"/>
-        <v>27.5</v>
+        <v>26.5</v>
       </c>
       <c r="J24" t="s">
         <v>60</v>
@@ -6865,15 +6864,15 @@
       <c r="E25" s="14"/>
       <c r="F25" s="16">
         <f>+SUM(F16:F24)</f>
-        <v>227</v>
+        <v>258</v>
       </c>
       <c r="G25" s="8">
         <f>+SUM(G16:G24)</f>
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="H25" s="8">
         <f>+SUM(H16:H24)</f>
-        <v>954</v>
+        <v>985</v>
       </c>
       <c r="I25" s="8"/>
     </row>
@@ -6890,14 +6889,14 @@
       </c>
       <c r="D26" s="22">
         <f t="shared" si="0"/>
-        <v>0.56140350877192979</v>
+        <v>0.57894736842105265</v>
       </c>
       <c r="E26" s="13">
         <v>20</v>
       </c>
       <c r="F26" s="12">
         <f>+H26-E26</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G26" s="13">
         <f>VLOOKUP(B26,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6905,11 +6904,11 @@
       </c>
       <c r="H26" s="13">
         <f>VLOOKUP(B26,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I26" s="17">
         <f t="shared" si="2"/>
-        <v>16.449999999999996</v>
+        <v>15.449999999999996</v>
       </c>
       <c r="J26" t="s">
         <v>55</v>
@@ -6929,26 +6928,26 @@
       </c>
       <c r="D27" s="22">
         <f t="shared" si="0"/>
-        <v>0.61006289308176098</v>
+        <v>0.63124999999999998</v>
       </c>
       <c r="E27" s="13">
         <v>68</v>
       </c>
       <c r="F27" s="12">
         <f t="shared" si="1"/>
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G27" s="13">
         <f>VLOOKUP(B27,'Base Cobertura'!$A:$C,3,FALSE)</f>
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H27" s="13">
         <f>VLOOKUP(B27,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I27" s="17">
         <f t="shared" si="2"/>
-        <v>38.150000000000006</v>
+        <v>35</v>
       </c>
       <c r="J27" t="s">
         <v>58</v>
@@ -6968,14 +6967,14 @@
       </c>
       <c r="D28" s="22">
         <f t="shared" si="0"/>
-        <v>0.64596273291925466</v>
+        <v>0.68944099378881984</v>
       </c>
       <c r="E28" s="13">
         <v>80</v>
       </c>
       <c r="F28" s="12">
         <f t="shared" si="1"/>
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G28" s="13">
         <f>VLOOKUP(B28,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6983,11 +6982,11 @@
       </c>
       <c r="H28" s="13">
         <f>VLOOKUP(B28,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="I28" s="17">
         <f t="shared" si="2"/>
-        <v>32.849999999999994</v>
+        <v>25.849999999999994</v>
       </c>
       <c r="J28" t="s">
         <v>58</v>
@@ -7007,26 +7006,26 @@
       </c>
       <c r="D29" s="22">
         <f t="shared" si="0"/>
-        <v>0.34136546184738958</v>
+        <v>0.34799999999999998</v>
       </c>
       <c r="E29" s="13">
         <v>68</v>
       </c>
       <c r="F29" s="12">
         <f t="shared" si="1"/>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G29" s="13">
         <f>VLOOKUP(B29,'Base Cobertura'!$A:$C,3,FALSE)</f>
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H29" s="13">
         <f>VLOOKUP(B29,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I29" s="17">
         <f t="shared" si="2"/>
-        <v>126.65</v>
+        <v>125.5</v>
       </c>
       <c r="J29" t="s">
         <v>58</v>
@@ -7046,14 +7045,14 @@
       </c>
       <c r="D30" s="22">
         <f t="shared" si="0"/>
-        <v>0.82014388489208634</v>
+        <v>0.83453237410071945</v>
       </c>
       <c r="E30" s="13">
         <v>73</v>
       </c>
       <c r="F30" s="12">
         <f t="shared" si="1"/>
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G30" s="13">
         <f>VLOOKUP(B30,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7061,11 +7060,11 @@
       </c>
       <c r="H30" s="13">
         <f>VLOOKUP(B30,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I30" s="17">
         <f t="shared" si="2"/>
-        <v>4.1499999999999915</v>
+        <v>2.1499999999999915</v>
       </c>
       <c r="J30" t="s">
         <v>55</v>
@@ -7085,14 +7084,14 @@
       </c>
       <c r="D31" s="22">
         <f t="shared" si="0"/>
-        <v>0.51381215469613262</v>
+        <v>0.53591160220994472</v>
       </c>
       <c r="E31" s="13">
         <v>40</v>
       </c>
       <c r="F31" s="12">
         <f t="shared" si="1"/>
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G31" s="13">
         <f>VLOOKUP(B31,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7100,11 +7099,11 @@
       </c>
       <c r="H31" s="13">
         <f>VLOOKUP(B31,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="I31" s="17">
         <f t="shared" si="2"/>
-        <v>60.849999999999994</v>
+        <v>56.849999999999994</v>
       </c>
       <c r="J31" t="s">
         <v>58</v>
@@ -7124,14 +7123,14 @@
       </c>
       <c r="D32" s="22">
         <f t="shared" si="0"/>
-        <v>0.6428571428571429</v>
+        <v>0.6607142857142857</v>
       </c>
       <c r="E32" s="13">
         <v>67</v>
       </c>
       <c r="F32" s="12">
         <f t="shared" si="1"/>
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G32" s="13">
         <f>VLOOKUP(B32,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7139,11 +7138,11 @@
       </c>
       <c r="H32" s="13">
         <f>VLOOKUP(B32,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="I32" s="17">
         <f t="shared" si="2"/>
-        <v>34.799999999999983</v>
+        <v>31.799999999999983</v>
       </c>
       <c r="J32" t="s">
         <v>58</v>
@@ -7163,14 +7162,14 @@
       </c>
       <c r="D33" s="22">
         <f t="shared" si="0"/>
-        <v>0.6428571428571429</v>
+        <v>0.67261904761904767</v>
       </c>
       <c r="E33" s="13">
         <v>66</v>
       </c>
       <c r="F33" s="12">
         <f t="shared" si="1"/>
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="G33" s="13">
         <f>VLOOKUP(B33,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7178,11 +7177,11 @@
       </c>
       <c r="H33" s="13">
         <f>VLOOKUP(B33,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I33" s="17">
         <f t="shared" si="2"/>
-        <v>34.799999999999983</v>
+        <v>29.799999999999983</v>
       </c>
       <c r="J33" t="s">
         <v>58</v>
@@ -7202,14 +7201,14 @@
       </c>
       <c r="D34" s="22">
         <f t="shared" si="0"/>
-        <v>0.46478873239436619</v>
+        <v>0.4859154929577465</v>
       </c>
       <c r="E34" s="13">
         <v>82</v>
       </c>
       <c r="F34" s="12">
         <f t="shared" si="1"/>
-        <v>-16</v>
+        <v>-13</v>
       </c>
       <c r="G34" s="13">
         <f>VLOOKUP(B34,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7217,11 +7216,11 @@
       </c>
       <c r="H34" s="13">
         <f>VLOOKUP(B34,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I34" s="17">
         <f t="shared" si="2"/>
-        <v>54.7</v>
+        <v>51.7</v>
       </c>
       <c r="J34" t="s">
         <v>55</v>
@@ -7241,14 +7240,14 @@
       </c>
       <c r="D35" s="22">
         <f t="shared" si="0"/>
-        <v>0.5730337078651685</v>
+        <v>0.61235955056179781</v>
       </c>
       <c r="E35" s="13">
         <v>81</v>
       </c>
       <c r="F35" s="12">
         <f t="shared" si="1"/>
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G35" s="13">
         <f>VLOOKUP(B35,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7256,11 +7255,11 @@
       </c>
       <c r="H35" s="13">
         <f>VLOOKUP(B35,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="I35" s="17">
         <f t="shared" si="2"/>
-        <v>49.299999999999983</v>
+        <v>42.299999999999983</v>
       </c>
       <c r="J35" t="s">
         <v>58</v>
@@ -7280,14 +7279,14 @@
       </c>
       <c r="D36" s="22">
         <f t="shared" si="0"/>
-        <v>5.2631578947368418E-2</v>
+        <v>6.1403508771929821E-2</v>
       </c>
       <c r="E36" s="13">
         <v>0</v>
       </c>
       <c r="F36" s="12">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G36" s="13">
         <f>VLOOKUP(B36,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7295,11 +7294,11 @@
       </c>
       <c r="H36" s="13">
         <f>VLOOKUP(B36,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I36" s="17">
         <f t="shared" si="2"/>
-        <v>90.899999999999991</v>
+        <v>89.899999999999991</v>
       </c>
       <c r="J36" t="s">
         <v>58</v>
@@ -7316,14 +7315,14 @@
       </c>
       <c r="D37" s="22">
         <f t="shared" si="0"/>
-        <v>0.16346153846153846</v>
+        <v>0.20192307692307693</v>
       </c>
       <c r="E37" s="13">
         <v>17</v>
       </c>
       <c r="F37" s="12">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G37" s="13">
         <f>VLOOKUP(B37,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7331,11 +7330,11 @@
       </c>
       <c r="H37" s="13">
         <f>VLOOKUP(B37,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I37" s="17">
         <f t="shared" si="2"/>
-        <v>71.399999999999991</v>
+        <v>67.399999999999991</v>
       </c>
       <c r="J37" t="s">
         <v>59</v>
@@ -7352,14 +7351,14 @@
       </c>
       <c r="D38" s="22">
         <f t="shared" si="0"/>
-        <v>0.62204724409448819</v>
+        <v>0.65354330708661412</v>
       </c>
       <c r="E38" s="13">
         <v>60</v>
       </c>
       <c r="F38" s="12">
         <f t="shared" si="1"/>
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G38" s="13">
         <f>VLOOKUP(B38,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7367,11 +7366,11 @@
       </c>
       <c r="H38" s="13">
         <f>VLOOKUP(B38,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="I38" s="17">
         <f t="shared" si="2"/>
-        <v>28.950000000000003</v>
+        <v>24.950000000000003</v>
       </c>
       <c r="J38" t="s">
         <v>55</v>
@@ -7387,15 +7386,15 @@
       <c r="E39" s="14"/>
       <c r="F39" s="8">
         <f>+SUM(F26:F38)</f>
-        <v>289</v>
+        <v>336</v>
       </c>
       <c r="G39" s="8">
         <f>+SUM(G26:G38)</f>
-        <v>1947</v>
+        <v>1949</v>
       </c>
       <c r="H39" s="8">
         <f>+SUM(H26:H38)</f>
-        <v>1011</v>
+        <v>1058</v>
       </c>
       <c r="I39" s="8"/>
       <c r="L39" t="s">
@@ -7411,20 +7410,20 @@
       <c r="E40" s="6"/>
       <c r="F40" s="8">
         <f>+SUM(F39+F25+F15)</f>
-        <v>942</v>
+        <v>1094</v>
       </c>
       <c r="G40" s="8">
         <f>+G15+G25+G39</f>
-        <v>5715</v>
+        <v>5723</v>
       </c>
       <c r="H40" s="8">
         <f>+H15+H25+H39</f>
-        <v>3270</v>
+        <v>3422</v>
       </c>
       <c r="I40" s="8"/>
       <c r="L40" s="1">
         <f>+H40/G40</f>
-        <v>0.57217847769028873</v>
+        <v>0.59793814432989689</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
@@ -8062,7 +8061,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B3" s="51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" s="51">
         <v>3431</v>
@@ -8082,7 +8081,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="51">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C4" s="51">
         <v>127</v>
@@ -8102,7 +8101,7 @@
         <v>10</v>
       </c>
       <c r="B5" s="51">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C5" s="51">
         <v>181</v>
@@ -8120,7 +8119,7 @@
         <v>100</v>
       </c>
       <c r="B6" s="51">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C6" s="51">
         <v>2027</v>
@@ -8138,10 +8137,10 @@
         <v>11</v>
       </c>
       <c r="B7" s="51">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C7" s="51">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="G7" t="s">
         <v>226</v>
@@ -8158,7 +8157,7 @@
         <v>12</v>
       </c>
       <c r="B8" s="51">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="C8" s="51">
         <v>214</v>
@@ -8178,7 +8177,7 @@
         <v>123</v>
       </c>
       <c r="B9" s="51">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C9" s="51">
         <v>489</v>
@@ -8187,7 +8186,7 @@
         <v>228</v>
       </c>
       <c r="H9" s="51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9" s="51">
         <v>3431</v>
@@ -8198,7 +8197,7 @@
         <v>15</v>
       </c>
       <c r="B10" s="51">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C10" s="51">
         <v>65</v>
@@ -8218,7 +8217,7 @@
         <v>16</v>
       </c>
       <c r="B11" s="51">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C11" s="51">
         <v>198</v>
@@ -8226,7 +8225,9 @@
       <c r="G11" t="s">
         <v>230</v>
       </c>
-      <c r="H11" s="51"/>
+      <c r="H11" s="51">
+        <v>1</v>
+      </c>
       <c r="I11" s="51">
         <v>3431</v>
       </c>
@@ -8236,7 +8237,7 @@
         <v>18</v>
       </c>
       <c r="B12" s="51">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="C12" s="51">
         <v>177</v>
@@ -8252,7 +8253,7 @@
         <v>222</v>
       </c>
       <c r="H12">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I12" s="51">
         <v>127</v>
@@ -8263,7 +8264,7 @@
         <v>19</v>
       </c>
       <c r="B13" s="51">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C13" s="51">
         <v>207</v>
@@ -8276,7 +8277,7 @@
         <v>223</v>
       </c>
       <c r="H13" s="51">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I13" s="51">
         <v>127</v>
@@ -8300,7 +8301,7 @@
         <v>224</v>
       </c>
       <c r="H14" s="51">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I14" s="51">
         <v>127</v>
@@ -8311,7 +8312,7 @@
         <v>20</v>
       </c>
       <c r="B15" s="51">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="C15" s="51">
         <v>227</v>
@@ -8324,7 +8325,7 @@
         <v>225</v>
       </c>
       <c r="H15" s="51">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I15" s="51">
         <v>127</v>
@@ -8335,10 +8336,10 @@
         <v>21</v>
       </c>
       <c r="B16" s="51">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C16" s="51">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E16">
         <f t="shared" si="0"/>
@@ -8348,7 +8349,7 @@
         <v>226</v>
       </c>
       <c r="H16" s="51">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="I16" s="51">
         <v>127</v>
@@ -8359,7 +8360,7 @@
         <v>22</v>
       </c>
       <c r="B17" s="51">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C17" s="51">
         <v>73</v>
@@ -8383,7 +8384,7 @@
         <v>23</v>
       </c>
       <c r="B18" s="51">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C18" s="51">
         <v>154</v>
@@ -8396,7 +8397,7 @@
         <v>228</v>
       </c>
       <c r="H18" s="51">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I18" s="51">
         <v>127</v>
@@ -8407,7 +8408,7 @@
         <v>24</v>
       </c>
       <c r="B19" s="51">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C19" s="51">
         <v>178</v>
@@ -8420,7 +8421,7 @@
         <v>229</v>
       </c>
       <c r="H19" s="51">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I19" s="51">
         <v>127</v>
@@ -8431,7 +8432,7 @@
         <v>25</v>
       </c>
       <c r="B20" s="51">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="C20" s="51">
         <v>172</v>
@@ -8444,7 +8445,7 @@
         <v>230</v>
       </c>
       <c r="H20">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I20" s="51">
         <v>127</v>
@@ -8455,7 +8456,7 @@
         <v>26</v>
       </c>
       <c r="B21" s="51">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C21" s="51">
         <v>165</v>
@@ -8471,7 +8472,7 @@
         <v>222</v>
       </c>
       <c r="H21" s="51">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I21" s="51">
         <v>181</v>
@@ -8482,7 +8483,7 @@
         <v>27</v>
       </c>
       <c r="B22" s="51">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C22" s="51">
         <v>139</v>
@@ -8495,7 +8496,7 @@
         <v>223</v>
       </c>
       <c r="H22" s="51">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I22" s="51">
         <v>181</v>
@@ -8506,7 +8507,7 @@
         <v>28</v>
       </c>
       <c r="B23" s="51">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C23" s="51">
         <v>168</v>
@@ -8519,7 +8520,7 @@
         <v>224</v>
       </c>
       <c r="H23" s="51">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I23" s="51">
         <v>181</v>
@@ -8530,7 +8531,7 @@
         <v>3</v>
       </c>
       <c r="B24" s="51">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C24" s="51">
         <v>170</v>
@@ -8543,7 +8544,7 @@
         <v>225</v>
       </c>
       <c r="H24" s="51">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I24" s="51">
         <v>181</v>
@@ -8567,7 +8568,7 @@
         <v>226</v>
       </c>
       <c r="H25" s="51">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I25" s="51">
         <v>181</v>
@@ -8578,7 +8579,7 @@
         <v>31</v>
       </c>
       <c r="B26" s="51">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C26" s="51">
         <v>160</v>
@@ -8591,7 +8592,7 @@
         <v>227</v>
       </c>
       <c r="H26" s="51">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I26" s="51">
         <v>181</v>
@@ -8602,7 +8603,7 @@
         <v>32</v>
       </c>
       <c r="B27" s="51">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C27" s="51">
         <v>57</v>
@@ -8615,7 +8616,7 @@
         <v>228</v>
       </c>
       <c r="H27" s="51">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I27" s="51">
         <v>181</v>
@@ -8626,7 +8627,7 @@
         <v>33</v>
       </c>
       <c r="B28" s="51">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C28" s="51">
         <v>168</v>
@@ -8650,10 +8651,10 @@
         <v>36</v>
       </c>
       <c r="B29" s="51">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C29" s="51">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E29">
         <f t="shared" si="1"/>
@@ -8663,7 +8664,7 @@
         <v>230</v>
       </c>
       <c r="H29" s="51">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I29" s="51">
         <v>181</v>
@@ -8674,7 +8675,7 @@
         <v>37</v>
       </c>
       <c r="B30" s="51">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C30" s="51">
         <v>142</v>
@@ -8690,7 +8691,7 @@
         <v>222</v>
       </c>
       <c r="H30" s="51">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I30" s="51">
         <v>2027</v>
@@ -8701,7 +8702,7 @@
         <v>4</v>
       </c>
       <c r="B31" s="51">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C31" s="51">
         <v>182</v>
@@ -8714,7 +8715,7 @@
         <v>223</v>
       </c>
       <c r="H31" s="51">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I31" s="51">
         <v>2027</v>
@@ -8725,10 +8726,10 @@
         <v>40</v>
       </c>
       <c r="B32" s="51">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C32" s="51">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E32">
         <f t="shared" si="2"/>
@@ -8738,7 +8739,7 @@
         <v>224</v>
       </c>
       <c r="H32" s="51">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I32" s="51">
         <v>2027</v>
@@ -8749,7 +8750,7 @@
         <v>42</v>
       </c>
       <c r="B33" s="51">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C33" s="51">
         <v>52</v>
@@ -8786,7 +8787,7 @@
         <v>226</v>
       </c>
       <c r="H34" s="51">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I34" s="51">
         <v>2027</v>
@@ -8797,7 +8798,7 @@
         <v>44</v>
       </c>
       <c r="B35" s="51">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C35" s="51">
         <v>169</v>
@@ -8810,7 +8811,7 @@
         <v>227</v>
       </c>
       <c r="H35" s="51">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I35" s="51">
         <v>2027</v>
@@ -8824,7 +8825,7 @@
         <v>82</v>
       </c>
       <c r="C36" s="51">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E36">
         <f t="shared" si="2"/>
@@ -8834,7 +8835,7 @@
         <v>228</v>
       </c>
       <c r="H36" s="51">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I36" s="51">
         <v>2027</v>
@@ -8845,7 +8846,7 @@
         <v>5</v>
       </c>
       <c r="B37" s="51">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="C37" s="51">
         <v>261</v>
@@ -8869,7 +8870,7 @@
         <v>52</v>
       </c>
       <c r="B38" s="51">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C38" s="51">
         <v>101</v>
@@ -8893,7 +8894,7 @@
         <v>53</v>
       </c>
       <c r="B39" s="51">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C39" s="51">
         <v>105</v>
@@ -8912,7 +8913,7 @@
         <v>32</v>
       </c>
       <c r="I39" s="51">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
@@ -8920,7 +8921,7 @@
         <v>54</v>
       </c>
       <c r="B40" s="51">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="C40" s="51">
         <v>202</v>
@@ -8933,10 +8934,10 @@
         <v>223</v>
       </c>
       <c r="H40" s="51">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I40" s="51">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
@@ -8957,10 +8958,10 @@
         <v>224</v>
       </c>
       <c r="H41" s="51">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="I41" s="51">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
@@ -8968,7 +8969,7 @@
         <v>57</v>
       </c>
       <c r="B42" s="51">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C42" s="51">
         <v>104</v>
@@ -8981,10 +8982,10 @@
         <v>225</v>
       </c>
       <c r="H42" s="51">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I42" s="51">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
@@ -9005,10 +9006,10 @@
         <v>226</v>
       </c>
       <c r="H43" s="51">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="I43" s="51">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
@@ -9029,10 +9030,10 @@
         <v>227</v>
       </c>
       <c r="H44" s="51">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I44" s="51">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
@@ -9040,7 +9041,7 @@
         <v>7</v>
       </c>
       <c r="B45" s="51">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C45" s="51">
         <v>114</v>
@@ -9056,7 +9057,7 @@
         <v>10</v>
       </c>
       <c r="I45" s="51">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
@@ -9064,7 +9065,7 @@
         <v>8</v>
       </c>
       <c r="B46" s="51">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C46" s="51">
         <v>195</v>
@@ -9080,7 +9081,7 @@
         <v>18</v>
       </c>
       <c r="I46" s="51">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
@@ -9088,7 +9089,7 @@
         <v>9</v>
       </c>
       <c r="B47" s="51">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="C47" s="51">
         <v>161</v>
@@ -9101,10 +9102,10 @@
         <v>230</v>
       </c>
       <c r="H47" s="51">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I47" s="51">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
@@ -9121,7 +9122,7 @@
         <v>222</v>
       </c>
       <c r="H48" s="51">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="I48" s="51">
         <v>214</v>
@@ -9138,7 +9139,7 @@
         <v>223</v>
       </c>
       <c r="H49" s="51">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I49" s="51">
         <v>214</v>
@@ -9153,7 +9154,7 @@
         <v>224</v>
       </c>
       <c r="H50" s="51">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="I50" s="51">
         <v>214</v>
@@ -9168,7 +9169,7 @@
         <v>225</v>
       </c>
       <c r="H51" s="51">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I51" s="51">
         <v>214</v>
@@ -9183,7 +9184,7 @@
         <v>226</v>
       </c>
       <c r="H52" s="51">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I52" s="51">
         <v>214</v>
@@ -9198,7 +9199,7 @@
         <v>227</v>
       </c>
       <c r="H53" s="51">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="I53" s="51">
         <v>214</v>
@@ -9228,7 +9229,7 @@
         <v>229</v>
       </c>
       <c r="H55" s="51">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I55" s="51">
         <v>214</v>
@@ -9243,7 +9244,7 @@
         <v>230</v>
       </c>
       <c r="H56" s="51">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I56" s="51">
         <v>214</v>
@@ -9261,7 +9262,7 @@
         <v>222</v>
       </c>
       <c r="H57" s="51">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I57" s="51">
         <v>489</v>
@@ -9276,7 +9277,7 @@
         <v>223</v>
       </c>
       <c r="H58" s="51">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I58" s="51">
         <v>489</v>
@@ -9291,7 +9292,7 @@
         <v>224</v>
       </c>
       <c r="H59" s="51">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I59" s="51">
         <v>489</v>
@@ -9321,7 +9322,7 @@
         <v>226</v>
       </c>
       <c r="H61" s="51">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I61" s="51">
         <v>489</v>
@@ -9351,7 +9352,7 @@
         <v>228</v>
       </c>
       <c r="H63" s="51">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I63" s="51">
         <v>489</v>
@@ -9380,7 +9381,9 @@
       <c r="G65" t="s">
         <v>230</v>
       </c>
-      <c r="H65" s="51"/>
+      <c r="H65" s="51">
+        <v>1</v>
+      </c>
       <c r="I65" s="51">
         <v>489</v>
       </c>
@@ -9397,7 +9400,7 @@
         <v>222</v>
       </c>
       <c r="H66" s="51">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I66" s="51">
         <v>65</v>
@@ -9427,7 +9430,7 @@
         <v>224</v>
       </c>
       <c r="H68" s="51">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I68" s="51">
         <v>65</v>
@@ -9457,7 +9460,7 @@
         <v>226</v>
       </c>
       <c r="H70" s="51">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I70" s="51">
         <v>65</v>
@@ -9472,7 +9475,7 @@
         <v>227</v>
       </c>
       <c r="H71" s="51">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I71" s="51">
         <v>65</v>
@@ -9487,7 +9490,7 @@
         <v>228</v>
       </c>
       <c r="H72" s="51">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I72" s="51">
         <v>65</v>
@@ -9502,7 +9505,7 @@
         <v>229</v>
       </c>
       <c r="H73" s="51">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I73" s="51">
         <v>65</v>
@@ -9517,7 +9520,7 @@
         <v>230</v>
       </c>
       <c r="H74" s="51">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I74" s="51">
         <v>65</v>
@@ -9535,7 +9538,7 @@
         <v>222</v>
       </c>
       <c r="H75" s="51">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I75" s="51">
         <v>198</v>
@@ -9565,7 +9568,7 @@
         <v>224</v>
       </c>
       <c r="H77" s="51">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="I77" s="51">
         <v>198</v>
@@ -9580,7 +9583,7 @@
         <v>225</v>
       </c>
       <c r="H78" s="51">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I78" s="51">
         <v>198</v>
@@ -9595,7 +9598,7 @@
         <v>226</v>
       </c>
       <c r="H79" s="51">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="I79" s="51">
         <v>198</v>
@@ -9625,7 +9628,7 @@
         <v>228</v>
       </c>
       <c r="H81" s="51">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I81" s="51">
         <v>198</v>
@@ -9640,7 +9643,7 @@
         <v>229</v>
       </c>
       <c r="H82" s="51">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I82" s="51">
         <v>198</v>
@@ -9673,7 +9676,7 @@
         <v>222</v>
       </c>
       <c r="H84" s="51">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="I84" s="51">
         <v>177</v>
@@ -9688,7 +9691,7 @@
         <v>223</v>
       </c>
       <c r="H85" s="51">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I85" s="51">
         <v>177</v>
@@ -9703,7 +9706,7 @@
         <v>224</v>
       </c>
       <c r="H86" s="51">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="I86" s="51">
         <v>177</v>
@@ -9718,7 +9721,7 @@
         <v>225</v>
       </c>
       <c r="H87" s="51">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I87" s="51">
         <v>177</v>
@@ -9733,7 +9736,7 @@
         <v>226</v>
       </c>
       <c r="H88" s="51">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="I88" s="51">
         <v>177</v>
@@ -9748,7 +9751,7 @@
         <v>227</v>
       </c>
       <c r="H89" s="51">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I89" s="51">
         <v>177</v>
@@ -9778,7 +9781,7 @@
         <v>229</v>
       </c>
       <c r="H91" s="51">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I91" s="51">
         <v>177</v>
@@ -9811,7 +9814,7 @@
         <v>222</v>
       </c>
       <c r="H93" s="51">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I93" s="51">
         <v>207</v>
@@ -9826,7 +9829,7 @@
         <v>223</v>
       </c>
       <c r="H94" s="51">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I94" s="51">
         <v>207</v>
@@ -9841,7 +9844,7 @@
         <v>224</v>
       </c>
       <c r="H95" s="51">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="I95" s="51">
         <v>207</v>
@@ -9856,7 +9859,7 @@
         <v>225</v>
       </c>
       <c r="H96" s="51">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="I96" s="51">
         <v>207</v>
@@ -9871,7 +9874,7 @@
         <v>226</v>
       </c>
       <c r="H97" s="51">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="I97" s="51">
         <v>207</v>
@@ -9886,7 +9889,7 @@
         <v>227</v>
       </c>
       <c r="H98" s="51">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="I98" s="51">
         <v>207</v>
@@ -9916,7 +9919,7 @@
         <v>229</v>
       </c>
       <c r="H100" s="51">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I100" s="51">
         <v>207</v>
@@ -9931,7 +9934,7 @@
         <v>230</v>
       </c>
       <c r="H101" s="51">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I101" s="51">
         <v>207</v>
@@ -9949,7 +9952,7 @@
         <v>222</v>
       </c>
       <c r="H102" s="51">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I102" s="51">
         <v>138</v>
@@ -9979,7 +9982,7 @@
         <v>224</v>
       </c>
       <c r="H104" s="51">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I104" s="51">
         <v>138</v>
@@ -9994,7 +9997,7 @@
         <v>225</v>
       </c>
       <c r="H105" s="51">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I105" s="51">
         <v>138</v>
@@ -10009,7 +10012,7 @@
         <v>226</v>
       </c>
       <c r="H106" s="51">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I106" s="51">
         <v>138</v>
@@ -10024,7 +10027,7 @@
         <v>227</v>
       </c>
       <c r="H107" s="51">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I107" s="51">
         <v>138</v>
@@ -10054,7 +10057,7 @@
         <v>229</v>
       </c>
       <c r="H109" s="51">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I109" s="51">
         <v>138</v>
@@ -10069,7 +10072,7 @@
         <v>230</v>
       </c>
       <c r="H110" s="51">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I110" s="51">
         <v>138</v>
@@ -10102,7 +10105,7 @@
         <v>223</v>
       </c>
       <c r="H112" s="51">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="I112" s="51">
         <v>227</v>
@@ -10117,7 +10120,7 @@
         <v>224</v>
       </c>
       <c r="H113" s="51">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="I113" s="51">
         <v>227</v>
@@ -10147,7 +10150,7 @@
         <v>226</v>
       </c>
       <c r="H115" s="51">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="I115" s="51">
         <v>227</v>
@@ -10162,7 +10165,7 @@
         <v>227</v>
       </c>
       <c r="H116">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I116" s="51">
         <v>227</v>
@@ -10192,7 +10195,7 @@
         <v>229</v>
       </c>
       <c r="H118" s="51">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I118" s="51">
         <v>227</v>
@@ -10207,7 +10210,7 @@
         <v>230</v>
       </c>
       <c r="H119" s="51">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I119" s="51">
         <v>227</v>
@@ -10225,10 +10228,10 @@
         <v>222</v>
       </c>
       <c r="H120" s="51">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I120" s="51">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="121" spans="5:9" x14ac:dyDescent="0.25">
@@ -10240,10 +10243,10 @@
         <v>223</v>
       </c>
       <c r="H121" s="51">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="I121" s="51">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="122" spans="5:9" x14ac:dyDescent="0.25">
@@ -10255,10 +10258,10 @@
         <v>224</v>
       </c>
       <c r="H122" s="51">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="I122" s="51">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="123" spans="5:9" x14ac:dyDescent="0.25">
@@ -10270,10 +10273,10 @@
         <v>225</v>
       </c>
       <c r="H123" s="51">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I123" s="51">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="124" spans="5:9" x14ac:dyDescent="0.25">
@@ -10285,10 +10288,10 @@
         <v>226</v>
       </c>
       <c r="H124">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I124" s="51">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="125" spans="5:9" x14ac:dyDescent="0.25">
@@ -10300,10 +10303,10 @@
         <v>227</v>
       </c>
       <c r="H125" s="51">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I125" s="51">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="126" spans="5:9" x14ac:dyDescent="0.25">
@@ -10318,7 +10321,7 @@
         <v>20</v>
       </c>
       <c r="I126" s="51">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="127" spans="5:9" x14ac:dyDescent="0.25">
@@ -10330,10 +10333,10 @@
         <v>229</v>
       </c>
       <c r="H127" s="51">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I127" s="51">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="128" spans="5:9" x14ac:dyDescent="0.25">
@@ -10345,10 +10348,10 @@
         <v>230</v>
       </c>
       <c r="H128" s="51">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I128" s="51">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="129" spans="5:9" x14ac:dyDescent="0.25">
@@ -10363,7 +10366,7 @@
         <v>222</v>
       </c>
       <c r="H129" s="51">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I129" s="51">
         <v>73</v>
@@ -10378,7 +10381,7 @@
         <v>223</v>
       </c>
       <c r="H130" s="51">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I130" s="51">
         <v>73</v>
@@ -10393,7 +10396,7 @@
         <v>224</v>
       </c>
       <c r="H131" s="51">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I131" s="51">
         <v>73</v>
@@ -10408,7 +10411,7 @@
         <v>225</v>
       </c>
       <c r="H132" s="51">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I132" s="51">
         <v>73</v>
@@ -10423,7 +10426,7 @@
         <v>226</v>
       </c>
       <c r="H133" s="51">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I133" s="51">
         <v>73</v>
@@ -10438,7 +10441,7 @@
         <v>227</v>
       </c>
       <c r="H134" s="51">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I134" s="51">
         <v>73</v>
@@ -10453,7 +10456,7 @@
         <v>228</v>
       </c>
       <c r="H135" s="51">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I135" s="51">
         <v>73</v>
@@ -10468,7 +10471,7 @@
         <v>229</v>
       </c>
       <c r="H136" s="51">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I136" s="51">
         <v>73</v>
@@ -10483,7 +10486,7 @@
         <v>230</v>
       </c>
       <c r="H137" s="51">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I137" s="51">
         <v>73</v>
@@ -10501,7 +10504,7 @@
         <v>222</v>
       </c>
       <c r="H138" s="51">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I138" s="51">
         <v>154</v>
@@ -10516,7 +10519,7 @@
         <v>223</v>
       </c>
       <c r="H139" s="51">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I139" s="51">
         <v>154</v>
@@ -10531,7 +10534,7 @@
         <v>224</v>
       </c>
       <c r="H140">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I140" s="51">
         <v>154</v>
@@ -10546,7 +10549,7 @@
         <v>225</v>
       </c>
       <c r="H141" s="51">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I141" s="51">
         <v>154</v>
@@ -10561,7 +10564,7 @@
         <v>226</v>
       </c>
       <c r="H142" s="51">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I142" s="51">
         <v>154</v>
@@ -10576,7 +10579,7 @@
         <v>227</v>
       </c>
       <c r="H143" s="51">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I143" s="51">
         <v>154</v>
@@ -10621,7 +10624,7 @@
         <v>230</v>
       </c>
       <c r="H146" s="51">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I146" s="51">
         <v>154</v>
@@ -10639,7 +10642,7 @@
         <v>222</v>
       </c>
       <c r="H147" s="51">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I147" s="51">
         <v>178</v>
@@ -10654,7 +10657,7 @@
         <v>223</v>
       </c>
       <c r="H148">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I148" s="51">
         <v>178</v>
@@ -10669,7 +10672,7 @@
         <v>224</v>
       </c>
       <c r="H149" s="51">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I149" s="51">
         <v>178</v>
@@ -10699,7 +10702,7 @@
         <v>226</v>
       </c>
       <c r="H151" s="51">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="I151" s="51">
         <v>178</v>
@@ -10714,7 +10717,7 @@
         <v>227</v>
       </c>
       <c r="H152" s="51">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I152" s="51">
         <v>178</v>
@@ -10729,7 +10732,7 @@
         <v>228</v>
       </c>
       <c r="H153" s="51">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I153" s="51">
         <v>178</v>
@@ -10744,7 +10747,7 @@
         <v>229</v>
       </c>
       <c r="H154" s="51">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I154" s="51">
         <v>178</v>
@@ -10759,7 +10762,7 @@
         <v>230</v>
       </c>
       <c r="H155" s="51">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I155" s="51">
         <v>178</v>
@@ -10777,7 +10780,7 @@
         <v>222</v>
       </c>
       <c r="H156" s="51">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="I156" s="51">
         <v>172</v>
@@ -10792,7 +10795,7 @@
         <v>223</v>
       </c>
       <c r="H157" s="51">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="I157" s="51">
         <v>172</v>
@@ -10807,7 +10810,7 @@
         <v>224</v>
       </c>
       <c r="H158" s="51">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I158" s="51">
         <v>172</v>
@@ -10822,7 +10825,7 @@
         <v>225</v>
       </c>
       <c r="H159" s="51">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I159" s="51">
         <v>172</v>
@@ -10837,7 +10840,7 @@
         <v>226</v>
       </c>
       <c r="H160" s="51">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="I160" s="51">
         <v>172</v>
@@ -10852,7 +10855,7 @@
         <v>227</v>
       </c>
       <c r="H161" s="51">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I161" s="51">
         <v>172</v>
@@ -10867,7 +10870,7 @@
         <v>228</v>
       </c>
       <c r="H162" s="51">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="I162" s="51">
         <v>172</v>
@@ -10882,7 +10885,7 @@
         <v>229</v>
       </c>
       <c r="H163" s="51">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="I163" s="51">
         <v>172</v>
@@ -10897,7 +10900,7 @@
         <v>230</v>
       </c>
       <c r="H164">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I164" s="51">
         <v>172</v>
@@ -11020,7 +11023,7 @@
         <v>229</v>
       </c>
       <c r="H172" s="51">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I172" s="51">
         <v>165</v>
@@ -11053,7 +11056,7 @@
         <v>222</v>
       </c>
       <c r="H174" s="51">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I174" s="51">
         <v>139</v>
@@ -11068,7 +11071,7 @@
         <v>223</v>
       </c>
       <c r="H175" s="51">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I175" s="51">
         <v>139</v>
@@ -11083,7 +11086,7 @@
         <v>224</v>
       </c>
       <c r="H176" s="51">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I176" s="51">
         <v>139</v>
@@ -11098,7 +11101,7 @@
         <v>225</v>
       </c>
       <c r="H177" s="51">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I177" s="51">
         <v>139</v>
@@ -11113,7 +11116,7 @@
         <v>226</v>
       </c>
       <c r="H178" s="51">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="I178" s="51">
         <v>139</v>
@@ -11128,7 +11131,7 @@
         <v>227</v>
       </c>
       <c r="H179" s="51">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I179" s="51">
         <v>139</v>
@@ -11143,7 +11146,7 @@
         <v>228</v>
       </c>
       <c r="H180">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I180" s="51">
         <v>139</v>
@@ -11158,7 +11161,7 @@
         <v>229</v>
       </c>
       <c r="H181" s="51">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I181" s="51">
         <v>139</v>
@@ -11173,7 +11176,7 @@
         <v>230</v>
       </c>
       <c r="H182" s="51">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I182" s="51">
         <v>139</v>
@@ -11191,7 +11194,7 @@
         <v>222</v>
       </c>
       <c r="H183" s="51">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I183" s="51">
         <v>168</v>
@@ -11206,7 +11209,7 @@
         <v>223</v>
       </c>
       <c r="H184" s="51">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I184" s="51">
         <v>168</v>
@@ -11221,7 +11224,7 @@
         <v>224</v>
       </c>
       <c r="H185" s="51">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I185" s="51">
         <v>168</v>
@@ -11251,7 +11254,7 @@
         <v>226</v>
       </c>
       <c r="H187" s="51">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="I187" s="51">
         <v>168</v>
@@ -11266,7 +11269,7 @@
         <v>227</v>
       </c>
       <c r="H188" s="51">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I188" s="51">
         <v>168</v>
@@ -11281,7 +11284,7 @@
         <v>228</v>
       </c>
       <c r="H189" s="51">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I189" s="51">
         <v>168</v>
@@ -11311,7 +11314,7 @@
         <v>230</v>
       </c>
       <c r="H191" s="51">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I191" s="51">
         <v>168</v>
@@ -11329,7 +11332,7 @@
         <v>222</v>
       </c>
       <c r="H192" s="51">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I192" s="51">
         <v>170</v>
@@ -11344,7 +11347,7 @@
         <v>223</v>
       </c>
       <c r="H193" s="51">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I193" s="51">
         <v>170</v>
@@ -11359,7 +11362,7 @@
         <v>224</v>
       </c>
       <c r="H194" s="51">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="I194" s="51">
         <v>170</v>
@@ -11389,7 +11392,7 @@
         <v>226</v>
       </c>
       <c r="H196">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I196" s="51">
         <v>170</v>
@@ -11404,7 +11407,7 @@
         <v>227</v>
       </c>
       <c r="H197" s="51">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="I197" s="51">
         <v>170</v>
@@ -11434,7 +11437,7 @@
         <v>229</v>
       </c>
       <c r="H199" s="51">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I199" s="51">
         <v>170</v>
@@ -11449,7 +11452,7 @@
         <v>230</v>
       </c>
       <c r="H200" s="51">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I200" s="51">
         <v>170</v>
@@ -11597,7 +11600,7 @@
         <v>222</v>
       </c>
       <c r="H210" s="51">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I210" s="51">
         <v>160</v>
@@ -11612,7 +11615,7 @@
         <v>223</v>
       </c>
       <c r="H211" s="51">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I211" s="51">
         <v>160</v>
@@ -11627,7 +11630,7 @@
         <v>224</v>
       </c>
       <c r="H212">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I212" s="51">
         <v>160</v>
@@ -11642,7 +11645,7 @@
         <v>225</v>
       </c>
       <c r="H213" s="51">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I213" s="51">
         <v>160</v>
@@ -11657,7 +11660,7 @@
         <v>226</v>
       </c>
       <c r="H214" s="51">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I214" s="51">
         <v>160</v>
@@ -11672,7 +11675,7 @@
         <v>227</v>
       </c>
       <c r="H215" s="51">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I215" s="51">
         <v>160</v>
@@ -11687,7 +11690,7 @@
         <v>228</v>
       </c>
       <c r="H216" s="51">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I216" s="51">
         <v>160</v>
@@ -11702,7 +11705,7 @@
         <v>229</v>
       </c>
       <c r="H217" s="51">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I217" s="51">
         <v>160</v>
@@ -11717,7 +11720,7 @@
         <v>230</v>
       </c>
       <c r="H218" s="51">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I218" s="51">
         <v>160</v>
@@ -11735,7 +11738,7 @@
         <v>222</v>
       </c>
       <c r="H219" s="51">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I219" s="51">
         <v>57</v>
@@ -11750,7 +11753,7 @@
         <v>223</v>
       </c>
       <c r="H220" s="51">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I220" s="51">
         <v>57</v>
@@ -11765,7 +11768,7 @@
         <v>224</v>
       </c>
       <c r="H221" s="51">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I221" s="51">
         <v>57</v>
@@ -11780,7 +11783,7 @@
         <v>225</v>
       </c>
       <c r="H222" s="51">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I222" s="51">
         <v>57</v>
@@ -11795,7 +11798,7 @@
         <v>226</v>
       </c>
       <c r="H223" s="51">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I223" s="51">
         <v>57</v>
@@ -11810,7 +11813,7 @@
         <v>227</v>
       </c>
       <c r="H224" s="51">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I224" s="51">
         <v>57</v>
@@ -11825,7 +11828,7 @@
         <v>228</v>
       </c>
       <c r="H225" s="51">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I225" s="51">
         <v>57</v>
@@ -11855,7 +11858,7 @@
         <v>230</v>
       </c>
       <c r="H227" s="51">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I227" s="51">
         <v>57</v>
@@ -11873,7 +11876,7 @@
         <v>222</v>
       </c>
       <c r="H228" s="51">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I228" s="51">
         <v>168</v>
@@ -11888,7 +11891,7 @@
         <v>223</v>
       </c>
       <c r="H229" s="51">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I229" s="51">
         <v>168</v>
@@ -11903,7 +11906,7 @@
         <v>224</v>
       </c>
       <c r="H230" s="51">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I230" s="51">
         <v>168</v>
@@ -11918,7 +11921,7 @@
         <v>225</v>
       </c>
       <c r="H231" s="51">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I231" s="51">
         <v>168</v>
@@ -11933,7 +11936,7 @@
         <v>226</v>
       </c>
       <c r="H232" s="51">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="I232" s="51">
         <v>168</v>
@@ -11948,7 +11951,7 @@
         <v>227</v>
       </c>
       <c r="H233" s="51">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I233" s="51">
         <v>168</v>
@@ -11963,7 +11966,7 @@
         <v>228</v>
       </c>
       <c r="H234" s="51">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I234" s="51">
         <v>168</v>
@@ -11978,7 +11981,7 @@
         <v>229</v>
       </c>
       <c r="H235" s="51">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I235" s="51">
         <v>168</v>
@@ -11993,7 +11996,7 @@
         <v>230</v>
       </c>
       <c r="H236">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I236" s="51">
         <v>168</v>
@@ -12011,10 +12014,10 @@
         <v>222</v>
       </c>
       <c r="H237" s="51">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I237" s="51">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="238" spans="5:9" x14ac:dyDescent="0.25">
@@ -12029,7 +12032,7 @@
         <v>10</v>
       </c>
       <c r="I238" s="51">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="239" spans="5:9" x14ac:dyDescent="0.25">
@@ -12041,10 +12044,10 @@
         <v>224</v>
       </c>
       <c r="H239" s="51">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I239" s="51">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="240" spans="5:9" x14ac:dyDescent="0.25">
@@ -12056,10 +12059,10 @@
         <v>225</v>
       </c>
       <c r="H240" s="51">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I240" s="51">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="241" spans="5:9" x14ac:dyDescent="0.25">
@@ -12071,10 +12074,10 @@
         <v>226</v>
       </c>
       <c r="H241" s="51">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="I241" s="51">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="242" spans="5:9" x14ac:dyDescent="0.25">
@@ -12086,10 +12089,10 @@
         <v>227</v>
       </c>
       <c r="H242" s="51">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I242" s="51">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="243" spans="5:9" x14ac:dyDescent="0.25">
@@ -12104,7 +12107,7 @@
         <v>14</v>
       </c>
       <c r="I243" s="51">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="244" spans="5:9" x14ac:dyDescent="0.25">
@@ -12116,10 +12119,10 @@
         <v>229</v>
       </c>
       <c r="H244">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I244" s="51">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="245" spans="5:9" x14ac:dyDescent="0.25">
@@ -12131,10 +12134,10 @@
         <v>230</v>
       </c>
       <c r="H245" s="51">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I245" s="51">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="246" spans="5:9" x14ac:dyDescent="0.25">
@@ -12149,7 +12152,7 @@
         <v>222</v>
       </c>
       <c r="H246" s="51">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I246" s="51">
         <v>142</v>
@@ -12179,7 +12182,7 @@
         <v>224</v>
       </c>
       <c r="H248" s="51">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I248" s="51">
         <v>142</v>
@@ -12194,7 +12197,7 @@
         <v>225</v>
       </c>
       <c r="H249" s="51">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I249" s="51">
         <v>142</v>
@@ -12209,7 +12212,7 @@
         <v>226</v>
       </c>
       <c r="H250" s="51">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="I250" s="51">
         <v>142</v>
@@ -12254,7 +12257,7 @@
         <v>229</v>
       </c>
       <c r="H253" s="51">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I253" s="51">
         <v>142</v>
@@ -12269,7 +12272,7 @@
         <v>230</v>
       </c>
       <c r="H254" s="51">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I254" s="51">
         <v>142</v>
@@ -12287,7 +12290,7 @@
         <v>222</v>
       </c>
       <c r="H255" s="51">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I255" s="51">
         <v>182</v>
@@ -12302,7 +12305,7 @@
         <v>223</v>
       </c>
       <c r="H256" s="51">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I256" s="51">
         <v>182</v>
@@ -12317,7 +12320,7 @@
         <v>224</v>
       </c>
       <c r="H257" s="51">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I257" s="51">
         <v>182</v>
@@ -12332,7 +12335,7 @@
         <v>225</v>
       </c>
       <c r="H258">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I258" s="51">
         <v>182</v>
@@ -12347,7 +12350,7 @@
         <v>226</v>
       </c>
       <c r="H259" s="51">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I259" s="51">
         <v>182</v>
@@ -12362,7 +12365,7 @@
         <v>227</v>
       </c>
       <c r="H260">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="I260" s="51">
         <v>182</v>
@@ -12377,7 +12380,7 @@
         <v>228</v>
       </c>
       <c r="H261" s="51">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I261" s="51">
         <v>182</v>
@@ -12392,7 +12395,7 @@
         <v>229</v>
       </c>
       <c r="H262" s="51">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="I262" s="51">
         <v>182</v>
@@ -12407,7 +12410,7 @@
         <v>230</v>
       </c>
       <c r="H263" s="51">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I263" s="51">
         <v>182</v>
@@ -12425,10 +12428,10 @@
         <v>222</v>
       </c>
       <c r="H264" s="51">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I264" s="51">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="265" spans="5:9" x14ac:dyDescent="0.25">
@@ -12443,7 +12446,7 @@
         <v>3</v>
       </c>
       <c r="I265" s="51">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="266" spans="5:9" x14ac:dyDescent="0.25">
@@ -12458,7 +12461,7 @@
         <v>23</v>
       </c>
       <c r="I266" s="51">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="267" spans="5:9" x14ac:dyDescent="0.25">
@@ -12470,10 +12473,10 @@
         <v>225</v>
       </c>
       <c r="H267" s="51">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I267" s="51">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="268" spans="5:9" x14ac:dyDescent="0.25">
@@ -12485,10 +12488,10 @@
         <v>226</v>
       </c>
       <c r="H268">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I268" s="51">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="269" spans="5:9" x14ac:dyDescent="0.25">
@@ -12503,7 +12506,7 @@
         <v>41</v>
       </c>
       <c r="I269" s="51">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="270" spans="5:9" x14ac:dyDescent="0.25">
@@ -12515,10 +12518,10 @@
         <v>228</v>
       </c>
       <c r="H270" s="51">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I270" s="51">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="271" spans="5:9" x14ac:dyDescent="0.25">
@@ -12530,10 +12533,10 @@
         <v>229</v>
       </c>
       <c r="H271" s="51">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I271" s="51">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="272" spans="5:9" x14ac:dyDescent="0.25">
@@ -12548,7 +12551,7 @@
         <v>9</v>
       </c>
       <c r="I272" s="51">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="273" spans="5:9" x14ac:dyDescent="0.25">
@@ -12562,7 +12565,9 @@
       <c r="G273" t="s">
         <v>222</v>
       </c>
-      <c r="H273" s="51"/>
+      <c r="H273" s="51">
+        <v>2</v>
+      </c>
       <c r="I273" s="51">
         <v>52</v>
       </c>
@@ -12575,7 +12580,9 @@
       <c r="G274" t="s">
         <v>223</v>
       </c>
-      <c r="H274" s="51"/>
+      <c r="H274" s="51">
+        <v>1</v>
+      </c>
       <c r="I274" s="51">
         <v>52</v>
       </c>
@@ -12588,7 +12595,9 @@
       <c r="G275" t="s">
         <v>224</v>
       </c>
-      <c r="H275" s="51"/>
+      <c r="H275" s="51">
+        <v>2</v>
+      </c>
       <c r="I275" s="51">
         <v>52</v>
       </c>
@@ -12601,6 +12610,9 @@
       <c r="G276" t="s">
         <v>225</v>
       </c>
+      <c r="H276">
+        <v>1</v>
+      </c>
       <c r="I276" s="51">
         <v>52</v>
       </c>
@@ -12614,7 +12626,7 @@
         <v>226</v>
       </c>
       <c r="H277" s="51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I277" s="51">
         <v>52</v>
@@ -12644,7 +12656,7 @@
         <v>228</v>
       </c>
       <c r="H279" s="51">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I279" s="51">
         <v>52</v>
@@ -12659,7 +12671,7 @@
         <v>229</v>
       </c>
       <c r="H280" s="51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I280" s="51">
         <v>52</v>
@@ -12674,7 +12686,7 @@
         <v>230</v>
       </c>
       <c r="H281" s="51">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I281" s="51">
         <v>52</v>
@@ -12815,7 +12827,7 @@
         <v>222</v>
       </c>
       <c r="H291">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I291" s="51">
         <v>169</v>
@@ -12830,7 +12842,7 @@
         <v>223</v>
       </c>
       <c r="H292">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I292" s="51">
         <v>169</v>
@@ -12845,7 +12857,7 @@
         <v>224</v>
       </c>
       <c r="H293">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I293" s="51">
         <v>169</v>
@@ -12860,7 +12872,7 @@
         <v>225</v>
       </c>
       <c r="H294">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I294" s="51">
         <v>169</v>
@@ -12875,7 +12887,7 @@
         <v>226</v>
       </c>
       <c r="H295">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="I295" s="51">
         <v>169</v>
@@ -12890,7 +12902,7 @@
         <v>227</v>
       </c>
       <c r="H296">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="I296" s="51">
         <v>169</v>
@@ -12905,7 +12917,7 @@
         <v>228</v>
       </c>
       <c r="H297" s="51">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I297" s="51">
         <v>169</v>
@@ -12935,7 +12947,7 @@
         <v>230</v>
       </c>
       <c r="H299" s="51">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I299" s="51">
         <v>169</v>
@@ -12956,7 +12968,7 @@
         <v>25</v>
       </c>
       <c r="I300" s="51">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="301" spans="5:9" x14ac:dyDescent="0.25">
@@ -12971,7 +12983,7 @@
         <v>12</v>
       </c>
       <c r="I301" s="51">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="302" spans="5:9" x14ac:dyDescent="0.25">
@@ -12986,7 +12998,7 @@
         <v>39</v>
       </c>
       <c r="I302" s="51">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="303" spans="5:9" x14ac:dyDescent="0.25">
@@ -13001,7 +13013,7 @@
         <v>9</v>
       </c>
       <c r="I303" s="51">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="304" spans="5:9" x14ac:dyDescent="0.25">
@@ -13016,7 +13028,7 @@
         <v>28</v>
       </c>
       <c r="I304" s="51">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="305" spans="5:9" x14ac:dyDescent="0.25">
@@ -13031,7 +13043,7 @@
         <v>21</v>
       </c>
       <c r="I305" s="51">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="306" spans="5:9" x14ac:dyDescent="0.25">
@@ -13046,7 +13058,7 @@
         <v>31</v>
       </c>
       <c r="I306" s="51">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="307" spans="5:9" x14ac:dyDescent="0.25">
@@ -13061,7 +13073,7 @@
         <v>12</v>
       </c>
       <c r="I307" s="51">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="308" spans="5:9" x14ac:dyDescent="0.25">
@@ -13076,7 +13088,7 @@
         <v>18</v>
       </c>
       <c r="I308" s="51">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="309" spans="5:9" x14ac:dyDescent="0.25">
@@ -13091,7 +13103,7 @@
         <v>222</v>
       </c>
       <c r="H309">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I309" s="51">
         <v>261</v>
@@ -13106,7 +13118,7 @@
         <v>223</v>
       </c>
       <c r="H310">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="I310" s="51">
         <v>261</v>
@@ -13121,7 +13133,7 @@
         <v>224</v>
       </c>
       <c r="H311">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I311" s="51">
         <v>261</v>
@@ -13136,7 +13148,7 @@
         <v>225</v>
       </c>
       <c r="H312">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I312" s="51">
         <v>261</v>
@@ -13151,7 +13163,7 @@
         <v>226</v>
       </c>
       <c r="H313">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="I313" s="51">
         <v>261</v>
@@ -13166,7 +13178,7 @@
         <v>227</v>
       </c>
       <c r="H314">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="I314" s="51">
         <v>261</v>
@@ -13181,7 +13193,7 @@
         <v>228</v>
       </c>
       <c r="H315" s="51">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I315" s="51">
         <v>261</v>
@@ -13196,7 +13208,7 @@
         <v>229</v>
       </c>
       <c r="H316">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="I316" s="51">
         <v>261</v>
@@ -13211,7 +13223,7 @@
         <v>230</v>
       </c>
       <c r="H317" s="51">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I317" s="51">
         <v>261</v>
@@ -13244,7 +13256,7 @@
         <v>223</v>
       </c>
       <c r="H319" s="51">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I319" s="51">
         <v>101</v>
@@ -13310,7 +13322,7 @@
         <v>228</v>
       </c>
       <c r="H324" s="51">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I324" s="51">
         <v>101</v>
@@ -13366,7 +13378,7 @@
         <v>223</v>
       </c>
       <c r="H328">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I328" s="51">
         <v>105</v>
@@ -13431,7 +13443,7 @@
         <v>228</v>
       </c>
       <c r="H333" s="51">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I333" s="51">
         <v>105</v>
@@ -13475,7 +13487,7 @@
         <v>222</v>
       </c>
       <c r="H336" s="51">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="I336" s="51">
         <v>202</v>
@@ -13490,7 +13502,7 @@
         <v>223</v>
       </c>
       <c r="H337" s="51">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I337" s="51">
         <v>202</v>
@@ -13505,7 +13517,7 @@
         <v>224</v>
       </c>
       <c r="H338" s="51">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="I338" s="51">
         <v>202</v>
@@ -13520,7 +13532,7 @@
         <v>225</v>
       </c>
       <c r="H339" s="51">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="I339" s="51">
         <v>202</v>
@@ -13535,7 +13547,7 @@
         <v>226</v>
       </c>
       <c r="H340">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="I340" s="51">
         <v>202</v>
@@ -13550,7 +13562,7 @@
         <v>227</v>
       </c>
       <c r="H341" s="51">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="I341" s="51">
         <v>202</v>
@@ -13565,7 +13577,7 @@
         <v>228</v>
       </c>
       <c r="H342" s="51">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I342" s="51">
         <v>202</v>
@@ -13595,7 +13607,7 @@
         <v>230</v>
       </c>
       <c r="H344" s="51">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I344" s="51">
         <v>202</v>
@@ -13831,7 +13843,7 @@
         <v>228</v>
       </c>
       <c r="H360" s="51">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I360" s="51">
         <v>104</v>
@@ -14211,7 +14223,7 @@
         <v>226</v>
       </c>
       <c r="H385">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I385">
         <v>114</v>
@@ -14241,7 +14253,7 @@
         <v>228</v>
       </c>
       <c r="H387">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I387">
         <v>114</v>
@@ -14289,7 +14301,7 @@
         <v>222</v>
       </c>
       <c r="H390">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I390">
         <v>195</v>
@@ -14304,7 +14316,7 @@
         <v>223</v>
       </c>
       <c r="H391">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I391">
         <v>195</v>
@@ -14319,7 +14331,7 @@
         <v>224</v>
       </c>
       <c r="H392">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="I392">
         <v>195</v>
@@ -14334,7 +14346,7 @@
         <v>225</v>
       </c>
       <c r="H393">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I393">
         <v>195</v>
@@ -14349,7 +14361,7 @@
         <v>226</v>
       </c>
       <c r="H394">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="I394">
         <v>195</v>
@@ -14364,7 +14376,7 @@
         <v>227</v>
       </c>
       <c r="H395">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="I395">
         <v>195</v>
@@ -14379,7 +14391,7 @@
         <v>228</v>
       </c>
       <c r="H396">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I396">
         <v>195</v>
@@ -14394,7 +14406,7 @@
         <v>229</v>
       </c>
       <c r="H397">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I397">
         <v>195</v>
@@ -14409,7 +14421,7 @@
         <v>230</v>
       </c>
       <c r="H398">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I398">
         <v>195</v>
@@ -14442,7 +14454,7 @@
         <v>223</v>
       </c>
       <c r="H400">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I400">
         <v>161</v>
@@ -14457,7 +14469,7 @@
         <v>224</v>
       </c>
       <c r="H401">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I401">
         <v>161</v>
@@ -14472,7 +14484,7 @@
         <v>225</v>
       </c>
       <c r="H402">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I402">
         <v>161</v>
@@ -14487,7 +14499,7 @@
         <v>226</v>
       </c>
       <c r="H403">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I403">
         <v>161</v>
@@ -14502,7 +14514,7 @@
         <v>227</v>
       </c>
       <c r="H404">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I404">
         <v>161</v>
@@ -14532,7 +14544,7 @@
         <v>229</v>
       </c>
       <c r="H406">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I406">
         <v>161</v>
@@ -14547,7 +14559,7 @@
         <v>230</v>
       </c>
       <c r="H407">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I407">
         <v>161</v>

--- a/data/ventas.xlsx
+++ b/data/ventas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cesar\Desktop\Reportes Ventas Rap\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9A17FD8D-447C-4CD2-AFC1-AB3369DEF39B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5649A19F-6AD5-41CC-B471-DC50A7DC1823}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2540,22 +2540,22 @@
         <v>0</v>
       </c>
       <c r="C2" s="96">
-        <v>44613.344784379296</v>
+        <v>47691.037967698801</v>
       </c>
       <c r="D2" s="96">
-        <v>221833.72900107491</v>
+        <v>238663.40472729539</v>
       </c>
       <c r="E2" s="96">
-        <v>730628312.80947816</v>
+        <v>783242769.06992614</v>
       </c>
       <c r="F2" s="96">
         <v>0</v>
       </c>
       <c r="G2" s="96">
-        <v>337771.994643885</v>
+        <v>337753.91741668503</v>
       </c>
       <c r="H2" s="96">
-        <v>337772.15</v>
+        <v>337754.07</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -2566,22 +2566,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="96">
-        <v>511.61216639219998</v>
+        <v>511.51216639220002</v>
       </c>
       <c r="D3" s="96">
         <v>884.13180968389997</v>
       </c>
       <c r="E3" s="96">
-        <v>11259066.488129456</v>
+        <v>11258463.913889455</v>
       </c>
       <c r="F3" s="96">
         <v>0</v>
       </c>
       <c r="G3" s="96">
-        <v>337771.994643885</v>
+        <v>337753.91741668503</v>
       </c>
       <c r="H3" s="96">
-        <v>337772.15</v>
+        <v>337754.07</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2592,13 +2592,13 @@
         <v>1</v>
       </c>
       <c r="C4" s="96">
-        <v>312.1424603154</v>
+        <v>339.72018849009999</v>
       </c>
       <c r="D4" s="96">
-        <v>599.76410714370002</v>
+        <v>660.09907738820004</v>
       </c>
       <c r="E4" s="96">
-        <v>8693363.8308905065</v>
+        <v>9577653.6863288712</v>
       </c>
       <c r="F4" s="96">
         <v>0</v>
@@ -2618,13 +2618,13 @@
         <v>1</v>
       </c>
       <c r="C5" s="96">
-        <v>420.01353174389999</v>
+        <v>470.33585317239999</v>
       </c>
       <c r="D5" s="96">
-        <v>1394.5421071373</v>
+        <v>1616.7391904716001</v>
       </c>
       <c r="E5" s="96">
-        <v>9146279.4433018658</v>
+        <v>10073320.978867745</v>
       </c>
       <c r="F5" s="96">
         <v>0</v>
@@ -2644,13 +2644,13 @@
         <v>1</v>
       </c>
       <c r="C6" s="96">
-        <v>908.03986111020004</v>
+        <v>961.45374999959995</v>
       </c>
       <c r="D6" s="96">
-        <v>2552.4027381166002</v>
+        <v>2780.9077381187999</v>
       </c>
       <c r="E6" s="96">
-        <v>18863848.650468376</v>
+        <v>20167339.013423331</v>
       </c>
       <c r="F6" s="96">
         <v>0</v>
@@ -2670,13 +2670,13 @@
         <v>1</v>
       </c>
       <c r="C7" s="96">
-        <v>864.77744841050003</v>
+        <v>971.7177738071</v>
       </c>
       <c r="D7" s="96">
-        <v>3050.5546785742999</v>
+        <v>3829.0796785753</v>
       </c>
       <c r="E7" s="96">
-        <v>16806749.78055869</v>
+        <v>19406220.336191598</v>
       </c>
       <c r="F7" s="96">
         <v>0</v>
@@ -2696,13 +2696,13 @@
         <v>1</v>
       </c>
       <c r="C8" s="96">
-        <v>2434.2782407408999</v>
+        <v>2473.1364074076</v>
       </c>
       <c r="D8" s="96">
-        <v>3889.9464768542002</v>
+        <v>3998.4464768564999</v>
       </c>
       <c r="E8" s="96">
-        <v>33451176.522885799</v>
+        <v>34463405.027844027</v>
       </c>
       <c r="F8" s="96">
         <v>0</v>
@@ -2722,13 +2722,13 @@
         <v>1</v>
       </c>
       <c r="C9" s="96">
-        <v>530.92689285680001</v>
+        <v>576.65056746009998</v>
       </c>
       <c r="D9" s="96">
-        <v>2237.5115416683002</v>
+        <v>2650.0165416687</v>
       </c>
       <c r="E9" s="96">
-        <v>9615921.6737193447</v>
+        <v>10717659.288687283</v>
       </c>
       <c r="F9" s="96">
         <v>0</v>
@@ -2748,13 +2748,13 @@
         <v>1</v>
       </c>
       <c r="C10" s="96">
-        <v>478.68131944409998</v>
+        <v>495.37635912669998</v>
       </c>
       <c r="D10" s="96">
-        <v>1294.4146598373</v>
+        <v>1340.3138265031</v>
       </c>
       <c r="E10" s="96">
-        <v>11264156.639444824</v>
+        <v>11631494.832822802</v>
       </c>
       <c r="F10" s="96">
         <v>0</v>
@@ -2774,13 +2774,13 @@
         <v>1</v>
       </c>
       <c r="C11" s="96">
-        <v>420.02474999819998</v>
+        <v>459.1063611093</v>
       </c>
       <c r="D11" s="96">
-        <v>1011.8970952383</v>
+        <v>1150.3370952383</v>
       </c>
       <c r="E11" s="96">
-        <v>7333522.0196865257</v>
+        <v>7991786.3456236413</v>
       </c>
       <c r="F11" s="96">
         <v>0</v>
@@ -2800,13 +2800,13 @@
         <v>1</v>
       </c>
       <c r="C12" s="96">
-        <v>716.12519047340004</v>
+        <v>798.34394047329999</v>
       </c>
       <c r="D12" s="96">
-        <v>3462.2189107057002</v>
+        <v>3718.8703690389002</v>
       </c>
       <c r="E12" s="96">
-        <v>11563280.456663784</v>
+        <v>12574415.55208604</v>
       </c>
       <c r="F12" s="96">
         <v>0</v>
@@ -2826,13 +2826,13 @@
         <v>1</v>
       </c>
       <c r="C13" s="96">
-        <v>911.90615079240001</v>
+        <v>968.04365079210004</v>
       </c>
       <c r="D13" s="96">
-        <v>1941.9193690540999</v>
+        <v>2262.1718690541002</v>
       </c>
       <c r="E13" s="96">
-        <v>15247177.219484905</v>
+        <v>16359393.288683873</v>
       </c>
       <c r="F13" s="96">
         <v>0</v>
@@ -2852,13 +2852,13 @@
         <v>1</v>
       </c>
       <c r="C14" s="96">
-        <v>3746.1787698415001</v>
+        <v>3892.4892857146001</v>
       </c>
       <c r="D14" s="96">
-        <v>34210.876666663302</v>
+        <v>35411.129166664898</v>
       </c>
       <c r="E14" s="96">
-        <v>60038357.598558225</v>
+        <v>62611489.816173963</v>
       </c>
       <c r="F14" s="96">
         <v>0</v>
@@ -2878,13 +2878,13 @@
         <v>1</v>
       </c>
       <c r="C15" s="96">
-        <v>752.42956348990003</v>
+        <v>797.04543650590006</v>
       </c>
       <c r="D15" s="96">
-        <v>3038.0966666590002</v>
+        <v>3142.0966666586</v>
       </c>
       <c r="E15" s="96">
-        <v>13843506.900515262</v>
+        <v>14638836.948941169</v>
       </c>
       <c r="F15" s="96">
         <v>0</v>
@@ -2904,13 +2904,13 @@
         <v>1</v>
       </c>
       <c r="C16" s="96">
-        <v>401.00738095060001</v>
+        <v>425.41124999800002</v>
       </c>
       <c r="D16" s="96">
-        <v>2028.6180357170001</v>
+        <v>2175.1130357194002</v>
       </c>
       <c r="E16" s="96">
-        <v>10467417.738483323</v>
+        <v>11260002.931573136</v>
       </c>
       <c r="F16" s="96">
         <v>0</v>
@@ -2930,13 +2930,13 @@
         <v>1</v>
       </c>
       <c r="C17" s="96">
-        <v>935.11462301339998</v>
+        <v>976.82622221960003</v>
       </c>
       <c r="D17" s="96">
-        <v>2550.3554523910998</v>
+        <v>2719.8554523931002</v>
       </c>
       <c r="E17" s="96">
-        <v>17944639.742629033</v>
+        <v>18892134.412943024</v>
       </c>
       <c r="F17" s="96">
         <v>0</v>
@@ -2956,13 +2956,13 @@
         <v>1</v>
       </c>
       <c r="C18" s="96">
-        <v>1215.4854642843</v>
+        <v>1280.1470714266</v>
       </c>
       <c r="D18" s="96">
-        <v>5747.0228690426002</v>
+        <v>6001.0228690393997</v>
       </c>
       <c r="E18" s="96">
-        <v>22534059.612904426</v>
+        <v>23833343.066456228</v>
       </c>
       <c r="F18" s="96">
         <v>0</v>
@@ -2982,13 +2982,13 @@
         <v>1</v>
       </c>
       <c r="C19" s="96">
-        <v>1058.6512367703999</v>
+        <v>1123.4378756589001</v>
       </c>
       <c r="D19" s="96">
-        <v>3774.0022262019002</v>
+        <v>3967.9302262039</v>
       </c>
       <c r="E19" s="96">
-        <v>20445334.936737273</v>
+        <v>22295266.235117078</v>
       </c>
       <c r="F19" s="96">
         <v>0</v>
@@ -3008,13 +3008,13 @@
         <v>1</v>
       </c>
       <c r="C20" s="96">
-        <v>3280.6037500001999</v>
+        <v>3363.5946388891002</v>
       </c>
       <c r="D20" s="96">
-        <v>14250.8118333277</v>
+        <v>14739.0918333273</v>
       </c>
       <c r="E20" s="96">
-        <v>49340595.584204771</v>
+        <v>51657737.149835296</v>
       </c>
       <c r="F20" s="96">
         <v>0</v>
@@ -3034,13 +3034,13 @@
         <v>1</v>
       </c>
       <c r="C21" s="96">
-        <v>484.4090674569</v>
+        <v>523.02232142529999</v>
       </c>
       <c r="D21" s="96">
-        <v>1836.930880961</v>
+        <v>1996.3987381019001</v>
       </c>
       <c r="E21" s="96">
-        <v>10980183.446752926</v>
+        <v>11678597.247224085</v>
       </c>
       <c r="F21" s="96">
         <v>0</v>
@@ -3060,13 +3060,13 @@
         <v>1</v>
       </c>
       <c r="C22" s="96">
-        <v>365.69368253829998</v>
+        <v>389.55977380809998</v>
       </c>
       <c r="D22" s="96">
-        <v>1308.5165238082</v>
+        <v>1391.7165238095999</v>
       </c>
       <c r="E22" s="96">
-        <v>6557112.931111577</v>
+        <v>7127555.5584793668</v>
       </c>
       <c r="F22" s="96">
         <v>0</v>
@@ -3086,13 +3086,13 @@
         <v>1</v>
       </c>
       <c r="C23" s="96">
-        <v>1921.2949206333999</v>
+        <v>1903.2949206333999</v>
       </c>
       <c r="D23" s="96">
-        <v>10953.3035833293</v>
+        <v>10893.3035833293</v>
       </c>
       <c r="E23" s="96">
-        <v>36322023.908257864</v>
+        <v>36077557.848657869</v>
       </c>
       <c r="F23" s="96">
         <v>0</v>
@@ -3138,13 +3138,13 @@
         <v>1</v>
       </c>
       <c r="C25" s="96">
-        <v>545.86546825280004</v>
+        <v>589.45227380790004</v>
       </c>
       <c r="D25" s="96">
-        <v>2142.2391666767999</v>
+        <v>2385.2491666783999</v>
       </c>
       <c r="E25" s="96">
-        <v>9777757.9714250863</v>
+        <v>10794067.346588679</v>
       </c>
       <c r="F25" s="96">
         <v>0</v>
@@ -3164,13 +3164,13 @@
         <v>1</v>
       </c>
       <c r="C26" s="96">
-        <v>472.79404761749998</v>
+        <v>498.76428571280002</v>
       </c>
       <c r="D26" s="96">
-        <v>1087.7879166629</v>
+        <v>1206.0319166669001</v>
       </c>
       <c r="E26" s="96">
-        <v>6945315.7802029736</v>
+        <v>7538759.4369671568</v>
       </c>
       <c r="F26" s="96">
         <v>0</v>
@@ -3216,13 +3216,13 @@
         <v>1</v>
       </c>
       <c r="C28" s="96">
-        <v>748.99325065890002</v>
+        <v>778.3840244685</v>
       </c>
       <c r="D28" s="96">
-        <v>3262.8351711400001</v>
+        <v>3355.8351711417999</v>
       </c>
       <c r="E28" s="96">
-        <v>14579075.923666339</v>
+        <v>15114947.7812881</v>
       </c>
       <c r="F28" s="96">
         <v>0</v>
@@ -3242,13 +3242,13 @@
         <v>1</v>
       </c>
       <c r="C29" s="96">
-        <v>2655.2766269840999</v>
+        <v>2965.9849603173002</v>
       </c>
       <c r="D29" s="96">
-        <v>7266.9416666717998</v>
+        <v>7595.5816666709998</v>
       </c>
       <c r="E29" s="96">
-        <v>34411101.004763618</v>
+        <v>37484101.183935247</v>
       </c>
       <c r="F29" s="96">
         <v>0</v>
@@ -3268,13 +3268,13 @@
         <v>1</v>
       </c>
       <c r="C30" s="96">
-        <v>275.06251984120001</v>
+        <v>304.95458333319999</v>
       </c>
       <c r="D30" s="96">
-        <v>1260.8666666715999</v>
+        <v>1376.8666666718</v>
       </c>
       <c r="E30" s="96">
-        <v>6164880.2550763758</v>
+        <v>6541870.7729290416</v>
       </c>
       <c r="F30" s="96">
         <v>0</v>
@@ -3294,13 +3294,13 @@
         <v>1</v>
       </c>
       <c r="C31" s="96">
-        <v>338.64394841080002</v>
+        <v>428.45109126770001</v>
       </c>
       <c r="D31" s="96">
-        <v>888.1449999985</v>
+        <v>1137.6699999990999</v>
       </c>
       <c r="E31" s="96">
-        <v>6108215.4389794497</v>
+        <v>7043117.2210489651</v>
       </c>
       <c r="F31" s="96">
         <v>0</v>
@@ -3320,13 +3320,13 @@
         <v>1</v>
       </c>
       <c r="C32" s="96">
-        <v>177.62023809510001</v>
+        <v>183.9674603174</v>
       </c>
       <c r="D32" s="96">
-        <v>674.03041666670003</v>
+        <v>707.0404166651</v>
       </c>
       <c r="E32" s="96">
-        <v>3882737.6125165834</v>
+        <v>4108217.6743740062</v>
       </c>
       <c r="F32" s="96">
         <v>0</v>
@@ -3346,13 +3346,13 @@
         <v>1</v>
       </c>
       <c r="C33" s="96">
-        <v>482.99939153370002</v>
+        <v>492.08900793570001</v>
       </c>
       <c r="D33" s="96">
-        <v>1947.6025000052</v>
+        <v>1996.6025000049999</v>
       </c>
       <c r="E33" s="96">
-        <v>9010188.8518341817</v>
+        <v>9187869.5284201782</v>
       </c>
       <c r="F33" s="96">
         <v>0</v>
@@ -3398,13 +3398,13 @@
         <v>1</v>
       </c>
       <c r="C35" s="96">
-        <v>148</v>
+        <v>921.18333333329997</v>
       </c>
       <c r="D35" s="96">
-        <v>292.8</v>
+        <v>6152.3953333332001</v>
       </c>
       <c r="E35" s="96">
-        <v>2013486.1534</v>
+        <v>11858403.056258887</v>
       </c>
       <c r="F35" s="96">
         <v>0</v>
@@ -3424,13 +3424,13 @@
         <v>1</v>
       </c>
       <c r="C36" s="96">
-        <v>782.38255158560003</v>
+        <v>840.67315872849997</v>
       </c>
       <c r="D36" s="96">
-        <v>2593.4347023876999</v>
+        <v>2927.6872023914998</v>
       </c>
       <c r="E36" s="96">
-        <v>13476544.027213015</v>
+        <v>14549220.102775784</v>
       </c>
       <c r="F36" s="96">
         <v>0</v>
@@ -3476,13 +3476,13 @@
         <v>1</v>
       </c>
       <c r="C38" s="96">
-        <v>865.17020201989999</v>
+        <v>906.70050505009999</v>
       </c>
       <c r="D38" s="96">
-        <v>9496.9299999962004</v>
+        <v>10318.049999995001</v>
       </c>
       <c r="E38" s="96">
-        <v>18735817.540831447</v>
+        <v>20234990.306558445</v>
       </c>
       <c r="F38" s="96">
         <v>0</v>
@@ -3502,13 +3502,13 @@
         <v>1</v>
       </c>
       <c r="C39" s="96">
-        <v>1209.7499999997999</v>
+        <v>1252.5833333331</v>
       </c>
       <c r="D39" s="96">
-        <v>14790.2499999968</v>
+        <v>15232.0899999962</v>
       </c>
       <c r="E39" s="96">
-        <v>27101787.621247634</v>
+        <v>28060601.939276338</v>
       </c>
       <c r="F39" s="96">
         <v>0</v>
@@ -3528,13 +3528,13 @@
         <v>1</v>
       </c>
       <c r="C40" s="96">
-        <v>1090.8088756614</v>
+        <v>1336.1126653440001</v>
       </c>
       <c r="D40" s="96">
-        <v>6808.9522367935997</v>
+        <v>7969.6475939415996</v>
       </c>
       <c r="E40" s="96">
-        <v>12878412.530010875</v>
+        <v>17261217.954442594</v>
       </c>
       <c r="F40" s="96">
         <v>0</v>
@@ -3554,13 +3554,13 @@
         <v>1</v>
       </c>
       <c r="C41" s="96">
-        <v>1750.3894047614999</v>
+        <v>1856.6394047616</v>
       </c>
       <c r="D41" s="96">
-        <v>10233.6645238131</v>
+        <v>11388.664523814299</v>
       </c>
       <c r="E41" s="96">
-        <v>20675373.952008072</v>
+        <v>22089067.174868885</v>
       </c>
       <c r="F41" s="96">
         <v>0</v>
@@ -3580,13 +3580,13 @@
         <v>1</v>
       </c>
       <c r="C42" s="96">
-        <v>199.06111111109999</v>
+        <v>216.06111111109999</v>
       </c>
       <c r="D42" s="96">
-        <v>2699.7299999999</v>
+        <v>2515.5499999999001</v>
       </c>
       <c r="E42" s="96">
-        <v>4955958.0088995183</v>
+        <v>4941053.6803995185</v>
       </c>
       <c r="F42" s="96">
         <v>0</v>
@@ -3606,13 +3606,13 @@
         <v>1</v>
       </c>
       <c r="C43" s="96">
-        <v>290.50262896779998</v>
+        <v>328.44568452319999</v>
       </c>
       <c r="D43" s="96">
-        <v>1377.1415919577</v>
+        <v>1627.1215919568999</v>
       </c>
       <c r="E43" s="96">
-        <v>10831277.641265372</v>
+        <v>11698187.310080834</v>
       </c>
       <c r="F43" s="96">
         <v>0</v>
@@ -3632,13 +3632,13 @@
         <v>1</v>
       </c>
       <c r="C44" s="96">
-        <v>1143.0010912705</v>
+        <v>1299.0927579371</v>
       </c>
       <c r="D44" s="96">
-        <v>12923.737773806901</v>
+        <v>13197.747773807199</v>
       </c>
       <c r="E44" s="96">
-        <v>16443269.938349089</v>
+        <v>18973242.700626545</v>
       </c>
       <c r="F44" s="96">
         <v>0</v>
@@ -3658,13 +3658,13 @@
         <v>1</v>
       </c>
       <c r="C45" s="96">
-        <v>398.41769841370001</v>
+        <v>422.06325396929998</v>
       </c>
       <c r="D45" s="96">
-        <v>3574.5670488094001</v>
+        <v>3750.5670488104001</v>
       </c>
       <c r="E45" s="96">
-        <v>8189989.2717900118</v>
+        <v>8740812.2586272676</v>
       </c>
       <c r="F45" s="96">
         <v>0</v>
@@ -3779,44 +3779,44 @@
       </c>
       <c r="D2" s="59">
         <f>IFERROR(+VLOOKUP(B2,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>23833343.066456228</v>
+      </c>
+      <c r="E2" s="59">
         <v>22534059.612904426</v>
-      </c>
-      <c r="E2" s="59">
-        <v>19062578.988594737</v>
       </c>
       <c r="F2" s="59">
         <f t="shared" ref="F2:F9" si="0">+D2-E2</f>
-        <v>3471480.6243096888</v>
+        <v>1299283.4535518028</v>
       </c>
       <c r="G2" s="60">
         <f t="shared" ref="G2:G41" si="1">+D2/C2</f>
-        <v>0.69810112183325379</v>
+        <v>0.73835268999651871</v>
       </c>
       <c r="H2" s="59">
         <f>+D2/$N$3*$N$4</f>
-        <v>49165220.973609656</v>
+        <v>47666686.132912457</v>
       </c>
       <c r="I2" s="60">
         <f t="shared" ref="I2:I41" si="2">+H2/C2</f>
-        <v>1.5231297203634628</v>
+        <v>1.4767053799930374</v>
       </c>
       <c r="J2" s="59">
         <f>+D2/$N$3</f>
-        <v>2048550.8739004023</v>
+        <v>1986111.9222046856</v>
       </c>
       <c r="K2" s="59">
         <f t="shared" ref="K2:K41" si="3">+(C2-D2)/$N$2</f>
-        <v>749616.69425740978</v>
+        <v>703811.1309828771</v>
       </c>
       <c r="L2" s="61" cm="1">
         <f t="array" ref="L2">+_xlfn.IFS(I2&gt;114%,H2*0.02,I2&gt;109%,H2*0.015,I2&gt;104%,H2*0.0125,I2&gt;99%,H2*0.01,I2&lt;99%,H2*0)</f>
-        <v>983304.41947219311</v>
+        <v>953333.7226582492</v>
       </c>
       <c r="M2" s="53" t="s">
         <v>36</v>
       </c>
       <c r="N2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -3829,45 +3829,45 @@
       </c>
       <c r="D3" s="4">
         <f>IFERROR(+VLOOKUP(B3,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>18892134.412943024</v>
+      </c>
+      <c r="E3" s="4">
         <v>17944639.742629033</v>
-      </c>
-      <c r="E3" s="4">
-        <v>16167381.13479867</v>
       </c>
       <c r="F3" s="4">
         <f t="shared" si="0"/>
-        <v>1777258.6078303624</v>
+        <v>947494.67031399161</v>
       </c>
       <c r="G3" s="5">
         <f t="shared" si="1"/>
-        <v>0.57918204100759185</v>
+        <v>0.60976342379749637</v>
       </c>
       <c r="H3" s="4">
         <f t="shared" ref="H3:H41" si="4">+D3/$N$3*$N$4</f>
-        <v>39151941.256645165</v>
+        <v>37784268.825886048</v>
       </c>
       <c r="I3" s="5">
         <f t="shared" si="2"/>
-        <v>1.2636699076529279</v>
+        <v>1.2195268475949927</v>
       </c>
       <c r="J3" s="4">
         <f t="shared" ref="J3:J41" si="5">+D3/$N$3</f>
-        <v>1631330.8856935485</v>
+        <v>1574344.5344119186</v>
       </c>
       <c r="K3" s="4">
         <f t="shared" si="3"/>
-        <v>1002929.8797118632</v>
+        <v>1007549.4804950192</v>
       </c>
       <c r="L3" s="63" cm="1">
         <f t="array" ref="L3">+_xlfn.IFS(I3&gt;114%,H3*0.02,I3&gt;109%,H3*0.015,I3&gt;104%,H3*0.0125,I3&gt;99%,H3*0.01,I3&lt;99%,H3*0)</f>
-        <v>783038.82513290329</v>
+        <v>755685.37651772099</v>
       </c>
       <c r="M3" s="53" t="s">
         <v>40</v>
       </c>
       <c r="N3">
         <f>N4-N2</f>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -3880,38 +3880,38 @@
       </c>
       <c r="D4" s="4">
         <f>IFERROR(+VLOOKUP(B4,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>14638836.948941169</v>
+      </c>
+      <c r="E4" s="4">
         <v>13843506.900515262</v>
-      </c>
-      <c r="E4" s="4">
-        <v>12686900.332479352</v>
       </c>
       <c r="F4" s="4">
         <f t="shared" si="0"/>
-        <v>1156606.5680359099</v>
+        <v>795330.04842590727</v>
       </c>
       <c r="G4" s="5">
         <f t="shared" si="1"/>
-        <v>0.48761858603332059</v>
+        <v>0.51563299859729439</v>
       </c>
       <c r="H4" s="4">
         <f t="shared" si="4"/>
-        <v>30204015.055669662</v>
+        <v>29277673.897882339</v>
       </c>
       <c r="I4" s="5">
         <f t="shared" si="2"/>
-        <v>1.0638950967999721</v>
+        <v>1.0312659971945888</v>
       </c>
       <c r="J4" s="4">
         <f t="shared" si="5"/>
-        <v>1258500.6273195692</v>
+        <v>1219903.0790784308</v>
       </c>
       <c r="K4" s="4">
         <f t="shared" si="3"/>
-        <v>1118963.4122794608</v>
+        <v>1145932.8592672569</v>
       </c>
       <c r="L4" s="63" cm="1">
         <f t="array" ref="L4">+_xlfn.IFS(I4&gt;114%,H4*0.02,I4&gt;109%,H4*0.015,I4&gt;104%,H4*0.0125,I4&gt;99%,H4*0.01,I4&lt;99%,H4*0)</f>
-        <v>377550.18819587078</v>
+        <v>292776.73897882341</v>
       </c>
       <c r="M4" s="53" t="s">
         <v>47</v>
@@ -3930,38 +3930,38 @@
       </c>
       <c r="D5" s="4">
         <f>IFERROR(+VLOOKUP(B5,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>16359393.288683873</v>
+      </c>
+      <c r="E5" s="4">
         <v>15247177.219484905</v>
-      </c>
-      <c r="E5" s="4">
-        <v>14492216.412792483</v>
       </c>
       <c r="F5" s="4">
         <f t="shared" si="0"/>
-        <v>754960.80669242144</v>
+        <v>1112216.0691989679</v>
       </c>
       <c r="G5" s="5">
         <f t="shared" si="1"/>
-        <v>0.53706095212680238</v>
+        <v>0.57623724112089769</v>
       </c>
       <c r="H5" s="4">
         <f t="shared" si="4"/>
-        <v>33266568.478876155</v>
+        <v>32718786.577367745</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" si="2"/>
-        <v>1.1717693500948416</v>
+        <v>1.1524744822417954</v>
       </c>
       <c r="J5" s="4">
         <f t="shared" si="5"/>
-        <v>1386107.0199531731</v>
+        <v>1363282.7740569895</v>
       </c>
       <c r="K5" s="4">
         <f t="shared" si="3"/>
-        <v>1010988.7723587191</v>
+        <v>1002553.1642886983</v>
       </c>
       <c r="L5" s="63" cm="1">
         <f t="array" ref="L5">+_xlfn.IFS(I5&gt;114%,H5*0.02,I5&gt;109%,H5*0.015,I5&gt;104%,H5*0.0125,I5&gt;99%,H5*0.01,I5&lt;99%,H5*0)</f>
-        <v>665331.36957752309</v>
+        <v>654375.73154735495</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
@@ -3974,38 +3974,38 @@
       </c>
       <c r="D6" s="4">
         <f>IFERROR(+VLOOKUP(B6,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>12574415.55208604</v>
+      </c>
+      <c r="E6" s="4">
         <v>11563280.456663784</v>
-      </c>
-      <c r="E6" s="4">
-        <v>10931376.163111016</v>
       </c>
       <c r="F6" s="4">
         <f t="shared" si="0"/>
-        <v>631904.29355276749</v>
+        <v>1011135.0954222567</v>
       </c>
       <c r="G6" s="5">
         <f t="shared" si="1"/>
-        <v>0.49145377337493906</v>
+        <v>0.53442827009318861</v>
       </c>
       <c r="H6" s="4">
         <f t="shared" si="4"/>
-        <v>25228975.541811891</v>
+        <v>25148831.104172081</v>
       </c>
       <c r="I6" s="5">
         <f t="shared" si="2"/>
-        <v>1.0722627782725942</v>
+        <v>1.0688565401863772</v>
       </c>
       <c r="J6" s="4">
         <f t="shared" si="5"/>
-        <v>1051207.314242162</v>
+        <v>1047867.9626738367</v>
       </c>
       <c r="K6" s="4">
         <f t="shared" si="3"/>
-        <v>920418.77545048785</v>
+        <v>912859.08211950713</v>
       </c>
       <c r="L6" s="63" cm="1">
         <f t="array" ref="L6">+_xlfn.IFS(I6&gt;114%,H6*0.02,I6&gt;109%,H6*0.015,I6&gt;104%,H6*0.0125,I6&gt;99%,H6*0.01,I6&lt;99%,H6*0)</f>
-        <v>315362.19427264866</v>
+        <v>314360.38880215102</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
@@ -4018,34 +4018,34 @@
       </c>
       <c r="D7" s="4">
         <f>IFERROR(+VLOOKUP(B7,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>10717659.288687283</v>
+      </c>
+      <c r="E7" s="4">
         <v>9615921.6737193447</v>
-      </c>
-      <c r="E7" s="4">
-        <v>8806933.4567012265</v>
       </c>
       <c r="F7" s="4">
         <f t="shared" ref="F7:F8" si="6">+D7-E7</f>
-        <v>808988.21701811813</v>
+        <v>1101737.6149679385</v>
       </c>
       <c r="G7" s="5">
         <f t="shared" si="1"/>
-        <v>0.34662141266028784</v>
+        <v>0.38633532271894305</v>
       </c>
       <c r="H7" s="4">
         <f t="shared" si="4"/>
-        <v>20980192.742660388</v>
+        <v>21435318.577374566</v>
       </c>
       <c r="I7" s="5">
         <f t="shared" si="2"/>
-        <v>0.75626490034971894</v>
+        <v>0.77267064543788611</v>
       </c>
       <c r="J7" s="4">
         <f t="shared" si="5"/>
-        <v>874174.69761084951</v>
+        <v>893138.27405727364</v>
       </c>
       <c r="K7" s="4">
         <f t="shared" si="3"/>
-        <v>1394302.7197496279</v>
+        <v>1418683.1451481015</v>
       </c>
       <c r="L7" s="63" cm="1">
         <f t="array" ref="L7">+_xlfn.IFS(I7&gt;114%,H7*0.02,I7&gt;109%,H7*0.015,I7&gt;104%,H7*0.0125,I7&gt;99%,H7*0.01,I7&lt;99%,H7*0)</f>
@@ -4062,38 +4062,38 @@
       </c>
       <c r="D8" s="4">
         <f>IFERROR(+VLOOKUP(B8,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>19406220.336191598</v>
+      </c>
+      <c r="E8" s="4">
         <v>16806749.78055869</v>
-      </c>
-      <c r="E8" s="4">
-        <v>14914934.086527392</v>
       </c>
       <c r="F8" s="4">
         <f t="shared" si="6"/>
-        <v>1891815.6940312982</v>
+        <v>2599470.5556329079</v>
       </c>
       <c r="G8" s="5">
         <f t="shared" si="1"/>
-        <v>0.46905518355846187</v>
+        <v>0.54160312736361316</v>
       </c>
       <c r="H8" s="4">
         <f t="shared" si="4"/>
-        <v>36669272.24849169</v>
+        <v>38812440.672383197</v>
       </c>
       <c r="I8" s="5">
         <f t="shared" si="2"/>
-        <v>1.0233931277639168</v>
+        <v>1.0832062547272263</v>
       </c>
       <c r="J8" s="4">
         <f t="shared" si="5"/>
-        <v>1527886.3436871537</v>
+        <v>1617185.0280159665</v>
       </c>
       <c r="K8" s="4">
         <f t="shared" si="3"/>
-        <v>1463409.3566430011</v>
+        <v>1368737.5900605088</v>
       </c>
       <c r="L8" s="63" cm="1">
         <f t="array" ref="L8">+_xlfn.IFS(I8&gt;114%,H8*0.02,I8&gt;109%,H8*0.015,I8&gt;104%,H8*0.0125,I8&gt;99%,H8*0.01,I8&lt;99%,H8*0)</f>
-        <v>366692.72248491691</v>
+        <v>485155.50840478996</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
@@ -4106,38 +4106,38 @@
       </c>
       <c r="D9" s="4">
         <f>IFERROR(+VLOOKUP(B9,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>20167339.013423331</v>
+      </c>
+      <c r="E9" s="4">
         <v>18863848.650468376</v>
-      </c>
-      <c r="E9" s="4">
-        <v>16797290.894173365</v>
       </c>
       <c r="F9" s="4">
         <f t="shared" si="0"/>
-        <v>2066557.7562950104</v>
+        <v>1303490.3629549555</v>
       </c>
       <c r="G9" s="5">
         <f t="shared" si="1"/>
-        <v>0.5264662178525249</v>
+        <v>0.56284498944403005</v>
       </c>
       <c r="H9" s="4">
         <f t="shared" si="4"/>
-        <v>41157487.964658275</v>
+        <v>40334678.026846662</v>
       </c>
       <c r="I9" s="5">
         <f t="shared" si="2"/>
-        <v>1.1486535662236907</v>
+        <v>1.1256899788880601</v>
       </c>
       <c r="J9" s="4">
         <f t="shared" si="5"/>
-        <v>1714895.3318607614</v>
+        <v>1680611.5844519443</v>
       </c>
       <c r="K9" s="4">
         <f t="shared" si="3"/>
-        <v>1305170.9820345638</v>
+        <v>1305311.033624531</v>
       </c>
       <c r="L9" s="63" cm="1">
         <f t="array" ref="L9">+_xlfn.IFS(I9&gt;114%,H9*0.02,I9&gt;109%,H9*0.015,I9&gt;104%,H9*0.0125,I9&gt;99%,H9*0.01,I9&lt;99%,H9*0)</f>
-        <v>823149.75929316552</v>
+        <v>605020.17040269997</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4148,34 +4148,34 @@
       </c>
       <c r="D10" s="64">
         <f>+SUM(D2:D9)</f>
+        <v>136589341.90741256</v>
+      </c>
+      <c r="E10" s="65">
         <v>126419184.03694384</v>
-      </c>
-      <c r="E10" s="65">
-        <v>113859611.46917823</v>
       </c>
       <c r="F10" s="64">
         <f>+SUM(F2:F9)</f>
-        <v>12559572.567765577</v>
+        <v>10170157.870468728</v>
       </c>
       <c r="G10" s="66">
         <f t="shared" si="1"/>
-        <v>0.52029795844913396</v>
+        <v>0.56215483656000598</v>
       </c>
       <c r="H10" s="64">
         <f t="shared" si="4"/>
-        <v>275823674.26242292</v>
+        <v>273178683.81482512</v>
       </c>
       <c r="I10" s="66">
         <f t="shared" si="2"/>
-        <v>1.1351955457072012</v>
+        <v>1.124309673120012</v>
       </c>
       <c r="J10" s="64">
         <f t="shared" si="5"/>
-        <v>11492653.094267622</v>
+        <v>11382445.158951046</v>
       </c>
       <c r="K10" s="67">
         <f t="shared" si="3"/>
-        <v>8965800.592485128</v>
+        <v>8865437.4859864954</v>
       </c>
       <c r="L10" s="68"/>
     </row>
@@ -4191,38 +4191,38 @@
       </c>
       <c r="D11" s="59">
         <f>IFERROR(+VLOOKUP(B11,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>51657737.149835296</v>
+      </c>
+      <c r="E11" s="59">
         <v>49340595.584204771</v>
-      </c>
-      <c r="E11" s="59">
-        <v>45072979.61650601</v>
       </c>
       <c r="F11" s="59">
         <f t="shared" ref="F11:F16" si="7">+D11-E11</f>
-        <v>4267615.9676987603</v>
+        <v>2317141.5656305254</v>
       </c>
       <c r="G11" s="60">
         <f t="shared" si="1"/>
-        <v>0.50881307798317643</v>
+        <v>0.53270804556862339</v>
       </c>
       <c r="H11" s="59">
         <f t="shared" si="4"/>
-        <v>107652208.54735586</v>
+        <v>103315474.29967059</v>
       </c>
       <c r="I11" s="60">
         <f t="shared" si="2"/>
-        <v>1.1101376246905665</v>
+        <v>1.0654160911372468</v>
       </c>
       <c r="J11" s="59">
         <f t="shared" si="5"/>
-        <v>4485508.6894731605</v>
+        <v>4304811.4291529413</v>
       </c>
       <c r="K11" s="59">
         <f t="shared" si="3"/>
-        <v>3663950.2227640571</v>
+        <v>3776184.2775251847</v>
       </c>
       <c r="L11" s="61" cm="1">
         <f t="array" ref="L11">+_xlfn.IFS(I11&gt;114%,H11*0.0125,I11&gt;109%,H11*0.01,I11&gt;104%,H11*0.0075,I11&gt;99%,H11*0.005,I11&lt;99%,H11*0)</f>
-        <v>1076522.0854735586</v>
+        <v>774866.05724752939</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4250,19 +4250,19 @@
       </c>
       <c r="H12" s="4">
         <f t="shared" si="4"/>
-        <v>27767242.695178326</v>
+        <v>25453305.803913467</v>
       </c>
       <c r="I12" s="5">
         <f t="shared" si="2"/>
-        <v>0.87785173930598226</v>
+        <v>0.80469742769715036</v>
       </c>
       <c r="J12" s="4">
         <f t="shared" si="5"/>
-        <v>1156968.4456324303</v>
+        <v>1060554.4084963945</v>
       </c>
       <c r="K12" s="4">
         <f t="shared" si="3"/>
-        <v>1454173.0389700208</v>
+        <v>1575354.1255508559</v>
       </c>
       <c r="L12" s="63" cm="1">
         <f t="array" ref="L12">+_xlfn.IFS(I12&gt;114%,H12*0.02,I12&gt;109%,H12*0.015,I12&gt;104%,H12*0.0125,I12&gt;99%,H12*0.01,I12&lt;99%,H12*0)</f>
@@ -4280,38 +4280,38 @@
       </c>
       <c r="D13" s="4">
         <f>IFERROR(+VLOOKUP(B13,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>62611489.816173963</v>
+      </c>
+      <c r="E13" s="4">
         <v>60038357.598558225</v>
-      </c>
-      <c r="E13" s="4">
-        <v>59180827.134406224</v>
       </c>
       <c r="F13" s="4">
         <f t="shared" si="7"/>
-        <v>857530.46415200084</v>
+        <v>2573132.2176157385</v>
       </c>
       <c r="G13" s="5">
         <f t="shared" si="1"/>
-        <v>0.46771989695028182</v>
+        <v>0.4877655008575344</v>
       </c>
       <c r="H13" s="4">
         <f t="shared" si="4"/>
-        <v>130992780.21503612</v>
+        <v>125222979.63234791</v>
       </c>
       <c r="I13" s="5">
         <f t="shared" si="2"/>
-        <v>1.0204797751642514</v>
+        <v>0.97553100171506857</v>
       </c>
       <c r="J13" s="4">
         <f t="shared" si="5"/>
-        <v>5458032.5089598382</v>
+        <v>5217624.15134783</v>
       </c>
       <c r="K13" s="4">
         <f t="shared" si="3"/>
-        <v>5255812.190466674</v>
+        <v>5479368.8548709182</v>
       </c>
       <c r="L13" s="63" cm="1">
         <f t="array" ref="L13">+_xlfn.IFS(I13&gt;114%,H13*0.0125,I13&gt;109%,H13*0.01,I13&gt;104%,H13*0.0075,I13&gt;99%,H13*0.005,I13&lt;99%,H13*0)</f>
-        <v>654963.90107518062</v>
+        <v>0</v>
       </c>
       <c r="M13" s="53" t="s">
         <v>61</v>
@@ -4330,34 +4330,34 @@
       </c>
       <c r="D14" s="4">
         <f>IFERROR(+VLOOKUP(B14,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>20234990.306558445</v>
+      </c>
+      <c r="E14" s="4">
         <v>18735817.540831447</v>
-      </c>
-      <c r="E14" s="4">
-        <v>12063016.447646325</v>
       </c>
       <c r="F14" s="4">
         <f t="shared" si="7"/>
-        <v>6672801.0931851212</v>
+        <v>1499172.7657269984</v>
       </c>
       <c r="G14" s="5">
         <f t="shared" si="1"/>
-        <v>0.44137181578616963</v>
+        <v>0.47668880178606288</v>
       </c>
       <c r="H14" s="4">
         <f t="shared" si="4"/>
-        <v>40878147.361814067</v>
+        <v>40469980.61311689</v>
       </c>
       <c r="I14" s="5">
         <f t="shared" si="2"/>
-        <v>0.96299305262437007</v>
+        <v>0.95337760357212575</v>
       </c>
       <c r="J14" s="4">
         <f t="shared" si="5"/>
-        <v>1703256.140075586</v>
+        <v>1686249.1922132038</v>
       </c>
       <c r="K14" s="4">
         <f t="shared" si="3"/>
-        <v>1824095.3733956579</v>
+        <v>1851172.2573680461</v>
       </c>
       <c r="L14" s="63" cm="1">
         <f t="array" ref="L14">+_xlfn.IFS(I14&gt;109%,H14*0.015,I14&gt;104%,H14*0.0125,I14&gt;99%,H14*0.01,I14&lt;99%,H14*0)</f>
@@ -4375,38 +4375,38 @@
       </c>
       <c r="D15" s="4">
         <f>IFERROR(+VLOOKUP(B15,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>28060601.939276338</v>
+      </c>
+      <c r="E15" s="4">
         <v>27101787.621247634</v>
-      </c>
-      <c r="E15" s="4">
-        <v>25192644.671372555</v>
       </c>
       <c r="F15" s="4">
         <f t="shared" si="7"/>
-        <v>1909142.9498750791</v>
+        <v>958814.31802870333</v>
       </c>
       <c r="G15" s="5">
         <f t="shared" si="1"/>
-        <v>0.63845440357071082</v>
+        <v>0.66104181485542413</v>
       </c>
       <c r="H15" s="4">
         <f t="shared" si="4"/>
-        <v>59131172.991813019</v>
+        <v>56121203.878552675</v>
       </c>
       <c r="I15" s="5">
         <f t="shared" si="2"/>
-        <v>1.3929914259724598</v>
+        <v>1.3220836297108483</v>
       </c>
       <c r="J15" s="4">
         <f t="shared" si="5"/>
-        <v>2463798.8746588756</v>
+        <v>2338383.4949396946</v>
       </c>
       <c r="K15" s="4">
         <f t="shared" si="3"/>
-        <v>1180559.2133636435</v>
+        <v>1199037.9546415552</v>
       </c>
       <c r="L15" s="63" cm="1">
         <f t="array" ref="L15">+_xlfn.IFS(I15&gt;109%,H15*0.015,I15&gt;104%,H15*0.0125,I15&gt;99%,H15*0.01,I15&lt;99%,H15*0)</f>
-        <v>886967.5948771952</v>
+        <v>841818.05817829014</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4417,34 +4417,34 @@
       </c>
       <c r="D16" s="64">
         <f>+SUM(D11:D15)</f>
+        <v>175291472.11380076</v>
+      </c>
+      <c r="E16" s="65">
         <v>167943211.24679881</v>
-      </c>
-      <c r="E16" s="65">
-        <v>154236120.77188784</v>
       </c>
       <c r="F16" s="64">
         <f t="shared" si="7"/>
-        <v>13707090.474910975</v>
+        <v>7348260.8670019507</v>
       </c>
       <c r="G16" s="66">
         <f t="shared" si="1"/>
-        <v>0.49125610792629398</v>
+        <v>0.51275074296840728</v>
       </c>
       <c r="H16" s="64">
         <f t="shared" si="4"/>
-        <v>366421551.8111974</v>
+        <v>350582944.22760153</v>
       </c>
       <c r="I16" s="66">
         <f t="shared" si="2"/>
-        <v>1.0718315082028231</v>
+        <v>1.0255014859368146</v>
       </c>
       <c r="J16" s="64">
         <f t="shared" si="5"/>
-        <v>15267564.658799892</v>
+        <v>14607622.676150063</v>
       </c>
       <c r="K16" s="67">
         <f t="shared" si="3"/>
-        <v>13378590.038960053</v>
+        <v>13881117.469956562</v>
       </c>
       <c r="L16" s="68"/>
     </row>
@@ -4460,34 +4460,34 @@
       </c>
       <c r="D17" s="59">
         <f>IFERROR(+VLOOKUP(B17,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>9577653.6863288712</v>
+      </c>
+      <c r="E17" s="59">
         <v>8693363.8308905065</v>
-      </c>
-      <c r="E17" s="59">
-        <v>7935947.3890327429</v>
       </c>
       <c r="F17" s="59">
         <f t="shared" ref="F17:F40" si="8">+D17-E17</f>
-        <v>757416.44185776357</v>
+        <v>884289.85543836467</v>
       </c>
       <c r="G17" s="60">
         <f t="shared" si="1"/>
-        <v>0.29631735148667698</v>
+        <v>0.32645878269871814</v>
       </c>
       <c r="H17" s="59">
         <f t="shared" si="4"/>
-        <v>18967339.267397467</v>
+        <v>19155307.372657742</v>
       </c>
       <c r="I17" s="60">
         <f t="shared" si="2"/>
-        <v>0.64651058506184067</v>
+        <v>0.65291756539743628</v>
       </c>
       <c r="J17" s="59">
         <f t="shared" si="5"/>
-        <v>790305.80280822783</v>
+        <v>798137.80719407264</v>
       </c>
       <c r="K17" s="59">
         <f t="shared" si="3"/>
-        <v>1588050.3308930383</v>
+        <v>1646697.0371809278</v>
       </c>
       <c r="L17" s="61" cm="1">
         <f t="array" ref="L17">+_xlfn.IFS(I17&gt;114%,H17*0.02,I17&gt;109%,H17*0.015,I17&gt;104%,H17*0.0125,I17&gt;99%,H17*0.01,I17&lt;99%,H17*0)</f>
@@ -4504,34 +4504,34 @@
       </c>
       <c r="D18" s="4">
         <f>IFERROR(+VLOOKUP(B18,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>10073320.978867745</v>
+      </c>
+      <c r="E18" s="4">
         <v>9146279.4433018658</v>
-      </c>
-      <c r="E18" s="4">
-        <v>8747383.1666885894</v>
       </c>
       <c r="F18" s="4">
         <f t="shared" si="8"/>
-        <v>398896.27661327645</v>
+        <v>927041.5355658792</v>
       </c>
       <c r="G18" s="5">
         <f t="shared" si="1"/>
-        <v>0.36644473171649866</v>
+        <v>0.40358655412596706</v>
       </c>
       <c r="H18" s="4">
         <f t="shared" si="4"/>
-        <v>19955518.785385888</v>
+        <v>20146641.95773549</v>
       </c>
       <c r="I18" s="5">
         <f t="shared" si="2"/>
-        <v>0.79951577829054243</v>
+        <v>0.80717310825193411</v>
       </c>
       <c r="J18" s="4">
         <f t="shared" si="5"/>
-        <v>831479.94939107867</v>
+        <v>839443.41490564542</v>
       </c>
       <c r="K18" s="4">
         <f t="shared" si="3"/>
-        <v>1216402.0351306258</v>
+        <v>1240515.4100943548</v>
       </c>
       <c r="L18" s="63" cm="1">
         <f t="array" ref="L18">+_xlfn.IFS(I18&gt;114%,H18*0.02,I18&gt;109%,H18*0.015,I18&gt;104%,H18*0.0125,I18&gt;99%,H18*0.01,I18&lt;99%,H18*0)</f>
@@ -4548,34 +4548,34 @@
       </c>
       <c r="D19" s="4">
         <f>IFERROR(+VLOOKUP(B19,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>11260002.931573136</v>
+      </c>
+      <c r="E19" s="4">
         <v>10467417.738483323</v>
-      </c>
-      <c r="E19" s="4">
-        <v>9582764.4529769439</v>
       </c>
       <c r="F19" s="4">
         <f t="shared" si="8"/>
-        <v>884653.28550637886</v>
+        <v>792585.19308981299</v>
       </c>
       <c r="G19" s="5">
         <f t="shared" si="1"/>
-        <v>0.40482497429035819</v>
+        <v>0.435478024396104</v>
       </c>
       <c r="H19" s="4">
         <f t="shared" si="4"/>
-        <v>22838002.338509068</v>
+        <v>22520005.863146272</v>
       </c>
       <c r="I19" s="5">
         <f t="shared" si="2"/>
-        <v>0.88325448936078144</v>
+        <v>0.870956048792208</v>
       </c>
       <c r="J19" s="4">
         <f t="shared" si="5"/>
-        <v>951583.43077121116</v>
+        <v>938333.57763109461</v>
       </c>
       <c r="K19" s="4">
         <f t="shared" si="3"/>
-        <v>1183787.1097705136</v>
+        <v>1216387.2694939054</v>
       </c>
       <c r="L19" s="63" cm="1">
         <f t="array" ref="L19">+_xlfn.IFS(I19&gt;114%,H19*0.02,I19&gt;109%,H19*0.015,I19&gt;104%,H19*0.0125,I19&gt;99%,H19*0.01,I19&lt;99%,H19*0)</f>
@@ -4592,38 +4592,38 @@
       </c>
       <c r="D20" s="4">
         <f>IFERROR(+VLOOKUP(B20,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>22295266.235117078</v>
+      </c>
+      <c r="E20" s="4">
         <v>20445334.936737273</v>
-      </c>
-      <c r="E20" s="4">
-        <v>18556073.997634564</v>
       </c>
       <c r="F20" s="4">
         <f t="shared" si="8"/>
-        <v>1889260.9391027093</v>
+        <v>1849931.2983798049</v>
       </c>
       <c r="G20" s="5">
         <f t="shared" si="1"/>
-        <v>0.60943292328774434</v>
+        <v>0.66457552880345572</v>
       </c>
       <c r="H20" s="4">
         <f t="shared" si="4"/>
-        <v>44608003.498335868</v>
+        <v>44590532.470234156</v>
       </c>
       <c r="I20" s="5">
         <f t="shared" si="2"/>
-        <v>1.3296718326278056</v>
+        <v>1.3291510576069114</v>
       </c>
       <c r="J20" s="4">
         <f t="shared" si="5"/>
-        <v>1858666.8124306612</v>
+        <v>1857938.8529264231</v>
       </c>
       <c r="K20" s="4">
         <f t="shared" si="3"/>
-        <v>1007907.3125586713</v>
+        <v>937738.64707357681</v>
       </c>
       <c r="L20" s="63" cm="1">
         <f t="array" ref="L20">+_xlfn.IFS(I20&gt;114%,H20*0.02,I20&gt;109%,H20*0.015,I20&gt;104%,H20*0.0125,I20&gt;99%,H20*0.01,I20&lt;99%,H20*0)</f>
-        <v>892160.06996671739</v>
+        <v>891810.64940468315</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4636,34 +4636,34 @@
       </c>
       <c r="D21" s="4">
         <f>IFERROR(+VLOOKUP(B21,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>11678597.247224085</v>
+      </c>
+      <c r="E21" s="4">
         <v>10980183.446752926</v>
-      </c>
-      <c r="E21" s="4">
-        <v>9684737.8484921921</v>
       </c>
       <c r="F21" s="4">
         <f t="shared" ref="F21:F23" si="9">+D21-E21</f>
-        <v>1295445.5982607342</v>
+        <v>698413.8004711587</v>
       </c>
       <c r="G21" s="5">
         <f t="shared" si="1"/>
-        <v>0.43129717515883398</v>
+        <v>0.45873058742338357</v>
       </c>
       <c r="H21" s="4">
         <f t="shared" si="4"/>
-        <v>23956763.883824568</v>
+        <v>23357194.49444817</v>
       </c>
       <c r="I21" s="5">
         <f t="shared" si="2"/>
-        <v>0.94101201852836514</v>
+        <v>0.91746117484676715</v>
       </c>
       <c r="J21" s="4">
         <f t="shared" si="5"/>
-        <v>998198.49515935697</v>
+        <v>973216.43726867379</v>
       </c>
       <c r="K21" s="4">
         <f t="shared" si="3"/>
-        <v>1113717.4271728517</v>
+        <v>1148326.0627313263</v>
       </c>
       <c r="L21" s="63" cm="1">
         <f t="array" ref="L21">+_xlfn.IFS(I21&gt;114%,H21*0.02,I21&gt;109%,H21*0.015,I21&gt;104%,H21*0.0125,I21&gt;99%,H21*0.01,I21&lt;99%,H21*0)</f>
@@ -4680,38 +4680,38 @@
       </c>
       <c r="D22" s="4">
         <f>IFERROR(+VLOOKUP(B22,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>15114947.7812881</v>
+      </c>
+      <c r="E22" s="4">
         <v>14579075.923666339</v>
-      </c>
-      <c r="E22" s="4">
-        <v>13932220.499480665</v>
       </c>
       <c r="F22" s="4">
         <f t="shared" si="9"/>
-        <v>646855.42418567464</v>
+        <v>535871.85762176104</v>
       </c>
       <c r="G22" s="5">
         <f t="shared" si="1"/>
-        <v>0.45928634197481921</v>
+        <v>0.47616797607446909</v>
       </c>
       <c r="H22" s="4">
         <f t="shared" si="4"/>
-        <v>31808892.92436292</v>
+        <v>30229895.562576201</v>
       </c>
       <c r="I22" s="5">
         <f t="shared" si="2"/>
-        <v>1.0020792915814236</v>
+        <v>0.95233595214893818</v>
       </c>
       <c r="J22" s="4">
         <f t="shared" si="5"/>
-        <v>1325370.5385151217</v>
+        <v>1259578.9817740084</v>
       </c>
       <c r="K22" s="4">
         <f t="shared" si="3"/>
-        <v>1320293.4058718202</v>
+        <v>1385661.868225992</v>
       </c>
       <c r="L22" s="63" cm="1">
         <f t="array" ref="L22">+_xlfn.IFS(I22&gt;114%,H22*0.02,I22&gt;109%,H22*0.015,I22&gt;104%,H22*0.0125,I22&gt;99%,H22*0.01,I22&lt;99%,H22*0)</f>
-        <v>318088.92924362922</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4724,38 +4724,38 @@
       </c>
       <c r="D23" s="4">
         <f>IFERROR(+VLOOKUP(B23,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>14549220.102775784</v>
+      </c>
+      <c r="E23" s="4">
         <v>13476544.027213015</v>
-      </c>
-      <c r="E23" s="4">
-        <v>12619217.089428457</v>
       </c>
       <c r="F23" s="4">
         <f t="shared" si="9"/>
-        <v>857326.93778455816</v>
+        <v>1072676.0755627695</v>
       </c>
       <c r="G23" s="5">
         <f t="shared" si="1"/>
-        <v>0.49120026385228166</v>
+        <v>0.53029773352110054</v>
       </c>
       <c r="H23" s="4">
         <f t="shared" si="4"/>
-        <v>29403368.786646578</v>
+        <v>29098440.205551568</v>
       </c>
       <c r="I23" s="5">
         <f t="shared" si="2"/>
-        <v>1.0717096665867965</v>
+        <v>1.0605954670422011</v>
       </c>
       <c r="J23" s="4">
         <f t="shared" si="5"/>
-        <v>1225140.3661102741</v>
+        <v>1212435.0085646487</v>
       </c>
       <c r="K23" s="4">
         <f t="shared" si="3"/>
-        <v>1073800.1694451531</v>
+        <v>1073893.8439353516</v>
       </c>
       <c r="L23" s="63" cm="1">
         <f t="array" ref="L23">+_xlfn.IFS(I23&gt;114%,H23*0.02,I23&gt;109%,H23*0.015,I23&gt;104%,H23*0.0125,I23&gt;99%,H23*0.01,I23&lt;99%,H23*0)</f>
-        <v>367542.10983308224</v>
+        <v>363730.50256939465</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4768,38 +4768,38 @@
       </c>
       <c r="D24" s="4">
         <f>IFERROR(+VLOOKUP(B24,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>17261217.954442594</v>
+      </c>
+      <c r="E24" s="4">
         <v>12878412.530010875</v>
-      </c>
-      <c r="E24" s="4">
-        <v>10463850.92498962</v>
       </c>
       <c r="F24" s="4">
         <f t="shared" si="8"/>
-        <v>2414561.6050212551</v>
+        <v>4382805.4244317189</v>
       </c>
       <c r="G24" s="5">
         <f t="shared" si="1"/>
-        <v>0.38449845890594242</v>
+        <v>0.51535169314203955</v>
       </c>
       <c r="H24" s="4">
         <f t="shared" si="4"/>
-        <v>28098354.61093282</v>
+        <v>34522435.908885188</v>
       </c>
       <c r="I24" s="5">
         <f t="shared" si="2"/>
-        <v>0.83890572852205625</v>
+        <v>1.0307033862840791</v>
       </c>
       <c r="J24" s="4">
         <f t="shared" si="5"/>
-        <v>1170764.7754555342</v>
+        <v>1438434.8295368829</v>
       </c>
       <c r="K24" s="4">
         <f t="shared" si="3"/>
-        <v>1585818.6515376249</v>
+        <v>1352736.4204631171</v>
       </c>
       <c r="L24" s="63" cm="1">
         <f t="array" ref="L24">+_xlfn.IFS(I24&gt;114%,H24*0.02,I24&gt;109%,H24*0.015,I24&gt;104%,H24*0.0125,I24&gt;99%,H24*0.01,I24&lt;99%,H24*0)</f>
-        <v>0</v>
+        <v>345224.3590888519</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4812,34 +4812,34 @@
       </c>
       <c r="D25" s="4">
         <f>IFERROR(+VLOOKUP(B25,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>22089067.174868885</v>
+      </c>
+      <c r="E25" s="4">
         <v>20675373.952008072</v>
-      </c>
-      <c r="E25" s="4">
-        <v>19594052.122893002</v>
       </c>
       <c r="F25" s="4">
         <f t="shared" si="8"/>
-        <v>1081321.8291150704</v>
+        <v>1413693.2228608131</v>
       </c>
       <c r="G25" s="5">
         <f t="shared" si="1"/>
-        <v>0.38241731207339447</v>
+        <v>0.40856536451673614</v>
       </c>
       <c r="H25" s="4">
         <f t="shared" si="4"/>
-        <v>45109906.804381251</v>
+        <v>44178134.349737771</v>
       </c>
       <c r="I25" s="5">
         <f t="shared" si="2"/>
-        <v>0.83436504452376981</v>
+        <v>0.81713072903347228</v>
       </c>
       <c r="J25" s="4">
         <f t="shared" si="5"/>
-        <v>1879579.450182552</v>
+        <v>1840755.5979057404</v>
       </c>
       <c r="K25" s="4">
         <f t="shared" si="3"/>
-        <v>2568429.1471532257</v>
+        <v>2664657.1408442603</v>
       </c>
       <c r="L25" s="63" cm="1">
         <f t="array" ref="L25">+_xlfn.IFS(I25&gt;109%,H25*0.015,I25&gt;104%,H25*0.0125,I25&gt;99%,H25*0.01,I25&lt;99%,H25*0)</f>
@@ -4854,34 +4854,34 @@
       </c>
       <c r="D26" s="67">
         <f>+SUM(D17:D25)</f>
+        <v>133899294.09248626</v>
+      </c>
+      <c r="E26" s="65">
         <v>121341985.82906419</v>
-      </c>
-      <c r="E26" s="65">
-        <v>111116247.49161679</v>
       </c>
       <c r="F26" s="67">
         <f>+D26-E26</f>
-        <v>10225738.337447405</v>
+        <v>12557308.263422072</v>
       </c>
       <c r="G26" s="66">
         <f t="shared" si="1"/>
-        <v>0.42442306819021025</v>
+        <v>0.46834530388593854</v>
       </c>
       <c r="H26" s="64">
         <f t="shared" si="4"/>
-        <v>264746150.8997764</v>
+        <v>267798588.18497252</v>
       </c>
       <c r="I26" s="66">
         <f t="shared" si="2"/>
-        <v>0.92601396696045868</v>
+        <v>0.93669060777187707</v>
       </c>
       <c r="J26" s="64">
         <f t="shared" si="5"/>
-        <v>11031089.620824017</v>
+        <v>11158274.507707188</v>
       </c>
       <c r="K26" s="67">
         <f t="shared" si="3"/>
-        <v>12658205.589533526</v>
+        <v>12666613.700042814</v>
       </c>
       <c r="L26" s="68"/>
     </row>
@@ -4897,34 +4897,34 @@
       </c>
       <c r="D27" s="59">
         <f>IFERROR(+VLOOKUP(B27,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>37484101.183935247</v>
+      </c>
+      <c r="E27" s="59">
         <v>34411101.004763618</v>
-      </c>
-      <c r="E27" s="59">
-        <v>33450220.947755333</v>
       </c>
       <c r="F27" s="59">
         <f t="shared" si="8"/>
-        <v>960880.05700828508</v>
+        <v>3073000.1791716293</v>
       </c>
       <c r="G27" s="60">
         <f t="shared" si="1"/>
-        <v>0.41976172794264316</v>
+        <v>0.45724753419448516</v>
       </c>
       <c r="H27" s="59">
         <f t="shared" si="4"/>
-        <v>75078765.828575164</v>
+        <v>74968202.367870495</v>
       </c>
       <c r="I27" s="60">
         <f t="shared" si="2"/>
-        <v>0.91584377005667594</v>
+        <v>0.91449506838897032</v>
       </c>
       <c r="J27" s="59">
         <f t="shared" si="5"/>
-        <v>3128281.9095239653</v>
+        <v>3123675.0986612705</v>
       </c>
       <c r="K27" s="59">
         <f t="shared" si="3"/>
-        <v>3658969.1534797219</v>
+        <v>3707799.9013387295</v>
       </c>
       <c r="L27" s="61" cm="1">
         <f t="array" ref="L27">+_xlfn.IFS(I27&gt;114%,H27*0.0125,I27&gt;109%,H27*0.01,I27&gt;104%,H27*0.0075,I27&gt;99%,H27*0.005,I27&lt;99%,H27*0)</f>
@@ -4941,34 +4941,34 @@
       </c>
       <c r="D28" s="4">
         <f>IFERROR(+VLOOKUP(B28,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>7043117.2210489651</v>
+      </c>
+      <c r="E28" s="4">
         <v>6108215.4389794497</v>
-      </c>
-      <c r="E28" s="4">
-        <v>5777964.8325451156</v>
       </c>
       <c r="F28" s="4">
         <f t="shared" si="8"/>
-        <v>330250.60643433407</v>
+        <v>934901.78206951544</v>
       </c>
       <c r="G28" s="5">
         <f t="shared" si="1"/>
-        <v>0.29086740185616428</v>
+        <v>0.33538653433566501</v>
       </c>
       <c r="H28" s="4">
         <f t="shared" si="4"/>
-        <v>13327015.50322789</v>
+        <v>14086234.44209793</v>
       </c>
       <c r="I28" s="5">
         <f t="shared" si="2"/>
-        <v>0.63461978586799472</v>
+        <v>0.67077306867133002</v>
       </c>
       <c r="J28" s="4">
         <f t="shared" si="5"/>
-        <v>555292.31263449544</v>
+        <v>586926.43508741376</v>
       </c>
       <c r="K28" s="4">
         <f t="shared" si="3"/>
-        <v>1145521.8893092731</v>
+        <v>1163073.5649125862</v>
       </c>
       <c r="L28" s="63" cm="1">
         <f t="array" ref="L28">+_xlfn.IFS(I28&gt;114%,H28*0.02,I28&gt;109%,H28*0.015,I28&gt;104%,H28*0.0125,I28&gt;99%,H28*0.01,I28&lt;99%,H28*0)</f>
@@ -4985,34 +4985,34 @@
       </c>
       <c r="D29" s="4">
         <f>IFERROR(+VLOOKUP(B29,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>11631494.832822802</v>
+      </c>
+      <c r="E29" s="4">
         <v>11264156.639444824</v>
-      </c>
-      <c r="E29" s="4">
-        <v>9823471.9917300809</v>
       </c>
       <c r="F29" s="4">
         <f t="shared" si="8"/>
-        <v>1440684.6477147434</v>
+        <v>367338.19337797724</v>
       </c>
       <c r="G29" s="5">
         <f t="shared" si="1"/>
-        <v>0.4376180234985188</v>
+        <v>0.45188929291416768</v>
       </c>
       <c r="H29" s="4">
         <f t="shared" si="4"/>
-        <v>24576341.758788709</v>
+        <v>23262989.665645603</v>
       </c>
       <c r="I29" s="5">
         <f t="shared" si="2"/>
-        <v>0.95480296036040468</v>
+        <v>0.90377858582833537</v>
       </c>
       <c r="J29" s="4">
         <f t="shared" si="5"/>
-        <v>1024014.2399495295</v>
+        <v>969291.2360685668</v>
       </c>
       <c r="K29" s="4">
         <f t="shared" si="3"/>
-        <v>1113503.3354273213</v>
+        <v>1175683.7639314332</v>
       </c>
       <c r="L29" s="63" cm="1">
         <f t="array" ref="L29">+_xlfn.IFS(I29&gt;114%,H29*0.02,I29&gt;109%,H29*0.015,I29&gt;104%,H29*0.0125,I29&gt;99%,H29*0.01,I29&lt;99%,H29*0)</f>
@@ -5030,34 +5030,34 @@
       </c>
       <c r="D30" s="4">
         <f>IFERROR(+VLOOKUP(B30,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>9187869.5284201782</v>
+      </c>
+      <c r="E30" s="4">
         <v>9010188.8518341817</v>
-      </c>
-      <c r="E30" s="4">
-        <v>8588184.3117468338</v>
       </c>
       <c r="F30" s="4">
         <f t="shared" si="8"/>
-        <v>422004.54008734785</v>
+        <v>177680.67658599652</v>
       </c>
       <c r="G30" s="5">
         <f t="shared" si="1"/>
-        <v>0.23566396867357053</v>
+        <v>0.24031125566049505</v>
       </c>
       <c r="H30" s="4">
         <f t="shared" si="4"/>
-        <v>19658593.858547304</v>
+        <v>18375739.056840356</v>
       </c>
       <c r="I30" s="5">
         <f t="shared" si="2"/>
-        <v>0.51417593165142661</v>
+        <v>0.4806225113209901</v>
       </c>
       <c r="J30" s="4">
         <f t="shared" si="5"/>
-        <v>819108.07743947103</v>
+        <v>765655.79403501481</v>
       </c>
       <c r="K30" s="4">
         <f t="shared" si="3"/>
-        <v>2247924.3277147301</v>
+        <v>2420444.6319754575</v>
       </c>
       <c r="L30" s="63" cm="1">
         <f t="array" ref="L30">+_xlfn.IFS(I30&gt;114%,H30*0.02,I30&gt;109%,H30*0.015,I30&gt;104%,H30*0.0125,I30&gt;99%,H30*0.01,I30&lt;99%,H30*0)</f>
@@ -5075,34 +5075,34 @@
       </c>
       <c r="D31" s="4">
         <f>IFERROR(+VLOOKUP(B31,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>10794067.346588679</v>
+      </c>
+      <c r="E31" s="4">
         <v>9777757.9714250863</v>
-      </c>
-      <c r="E31" s="4">
-        <v>9407600.5395302419</v>
       </c>
       <c r="F31" s="4">
         <f t="shared" si="8"/>
-        <v>370157.4318948444</v>
+        <v>1016309.3751635924</v>
       </c>
       <c r="G31" s="5">
         <f t="shared" si="1"/>
-        <v>0.38472011770197367</v>
+        <v>0.42470828918026299</v>
       </c>
       <c r="H31" s="4">
         <f t="shared" si="4"/>
-        <v>21333290.119472917</v>
+        <v>21588134.693177357</v>
       </c>
       <c r="I31" s="5">
         <f t="shared" si="2"/>
-        <v>0.83938934771339713</v>
+        <v>0.84941657836052598</v>
       </c>
       <c r="J31" s="4">
         <f t="shared" si="5"/>
-        <v>888887.08831137151</v>
+        <v>899505.61221572326</v>
       </c>
       <c r="K31" s="4">
         <f t="shared" si="3"/>
-        <v>1202884.0021980703</v>
+        <v>1218431.8877842769</v>
       </c>
       <c r="L31" s="63" cm="1">
         <f t="array" ref="L31">+_xlfn.IFS(I31&gt;114%,H31*0.02,I31&gt;109%,H31*0.015,I31&gt;104%,H31*0.0125,I31&gt;99%,H31*0.01,I31&lt;99%,H31*0)</f>
@@ -5120,34 +5120,34 @@
       </c>
       <c r="D32" s="4">
         <f>IFERROR(+VLOOKUP(B32,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>7991786.3456236413</v>
+      </c>
+      <c r="E32" s="4">
         <v>7333522.0196865257</v>
-      </c>
-      <c r="E32" s="4">
-        <v>6665534.1859788187</v>
       </c>
       <c r="F32" s="4">
         <f t="shared" si="8"/>
-        <v>667987.833707707</v>
+        <v>658264.32593711559</v>
       </c>
       <c r="G32" s="5">
         <f t="shared" si="1"/>
-        <v>0.2910127785589891</v>
+        <v>0.31713437879458894</v>
       </c>
       <c r="H32" s="4">
         <f t="shared" si="4"/>
-        <v>16000411.679316055</v>
+        <v>15983572.691247284</v>
       </c>
       <c r="I32" s="5">
         <f t="shared" si="2"/>
-        <v>0.63493697140143079</v>
+        <v>0.634268757589178</v>
       </c>
       <c r="J32" s="4">
         <f t="shared" si="5"/>
-        <v>666683.81997150229</v>
+        <v>665982.19546863681</v>
       </c>
       <c r="K32" s="4">
         <f t="shared" si="3"/>
-        <v>1374344.4600241133</v>
+        <v>1434017.8045313631</v>
       </c>
       <c r="L32" s="63" cm="1">
         <f t="array" ref="L32">+_xlfn.IFS(I32&gt;114%,H32*0.02,I32&gt;109%,H32*0.015,I32&gt;104%,H32*0.0125,I32&gt;99%,H32*0.01,I32&lt;99%,H32*0)</f>
@@ -5165,34 +5165,34 @@
       </c>
       <c r="D33" s="4">
         <f>IFERROR(+VLOOKUP(B33,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>7538759.4369671568</v>
+      </c>
+      <c r="E33" s="4">
         <v>6945315.7802029736</v>
-      </c>
-      <c r="E33" s="4">
-        <v>6448364.3120282274</v>
       </c>
       <c r="F33" s="4">
         <f t="shared" si="8"/>
-        <v>496951.46817474626</v>
+        <v>593443.65676418319</v>
       </c>
       <c r="G33" s="5">
         <f t="shared" si="1"/>
-        <v>0.26211953466757143</v>
+        <v>0.284516381705951</v>
       </c>
       <c r="H33" s="4">
         <f t="shared" si="4"/>
-        <v>15153416.247715579</v>
+        <v>15077518.873934314</v>
       </c>
       <c r="I33" s="5">
         <f t="shared" si="2"/>
-        <v>0.57189716654742861</v>
+        <v>0.56903276341190201</v>
       </c>
       <c r="J33" s="4">
         <f t="shared" si="5"/>
-        <v>631392.34365481581</v>
+        <v>628229.9530805964</v>
       </c>
       <c r="K33" s="4">
         <f t="shared" si="3"/>
-        <v>1503956.4784459251</v>
+        <v>1579832.5469194036</v>
       </c>
       <c r="L33" s="63" cm="1">
         <f t="array" ref="L33">+_xlfn.IFS(I33&gt;114%,H33*0.02,I33&gt;109%,H33*0.015,I33&gt;104%,H33*0.0125,I33&gt;99%,H33*0.01,I33&lt;99%,H33*0)</f>
@@ -5209,34 +5209,34 @@
       </c>
       <c r="D34" s="4">
         <f>IFERROR(+VLOOKUP(B34,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>6541870.7729290416</v>
+      </c>
+      <c r="E34" s="4">
         <v>6164880.2550763758</v>
-      </c>
-      <c r="E34" s="4">
-        <v>5618690.4157067938</v>
       </c>
       <c r="F34" s="4">
         <f t="shared" si="8"/>
-        <v>546189.83936958201</v>
+        <v>376990.51785266586</v>
       </c>
       <c r="G34" s="5">
         <f t="shared" si="1"/>
-        <v>0.29356572643220835</v>
+        <v>0.3115176558537639</v>
       </c>
       <c r="H34" s="4">
         <f t="shared" si="4"/>
-        <v>13450647.829257548</v>
+        <v>13083741.545858083</v>
       </c>
       <c r="I34" s="5">
         <f t="shared" si="2"/>
-        <v>0.64050703948845467</v>
+        <v>0.62303531170752779</v>
       </c>
       <c r="J34" s="4">
         <f t="shared" si="5"/>
-        <v>560443.65955239779</v>
+        <v>545155.8977440868</v>
       </c>
       <c r="K34" s="4">
         <f t="shared" si="3"/>
-        <v>1141163.0573018172</v>
+        <v>1204844.1022559132</v>
       </c>
       <c r="L34" s="63" cm="1">
         <f t="array" ref="L34">+_xlfn.IFS(I34&gt;114%,H34*0.02,I34&gt;109%,H34*0.015,I34&gt;104%,H34*0.0125,I34&gt;99%,H34*0.01,I34&lt;99%,H34*0)</f>
@@ -5253,34 +5253,34 @@
       </c>
       <c r="D35" s="4">
         <f>IFERROR(+VLOOKUP(B35,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>4108217.6743740062</v>
+      </c>
+      <c r="E35" s="4">
         <v>3882737.6125165834</v>
-      </c>
-      <c r="E35" s="4">
-        <v>3802949.3075159392</v>
       </c>
       <c r="F35" s="4">
         <f t="shared" si="8"/>
-        <v>79788.305000644177</v>
+        <v>225480.06185742281</v>
       </c>
       <c r="G35" s="5">
         <f t="shared" si="1"/>
-        <v>0.15746232946916577</v>
+        <v>0.16660655175049299</v>
       </c>
       <c r="H35" s="4">
         <f t="shared" si="4"/>
-        <v>8471427.5182179995</v>
+        <v>8216435.3487480134</v>
       </c>
       <c r="I35" s="5">
         <f t="shared" si="2"/>
-        <v>0.34355417338727073</v>
+        <v>0.33321310350098604</v>
       </c>
       <c r="J35" s="4">
         <f t="shared" si="5"/>
-        <v>352976.14659241668</v>
+        <v>342351.47286450054</v>
       </c>
       <c r="K35" s="4">
         <f t="shared" si="3"/>
-        <v>1598112.4913448782</v>
+        <v>1712498.5271354995</v>
       </c>
       <c r="L35" s="63" cm="1">
         <f t="array" ref="L35">+_xlfn.IFS(I35&gt;114%,H35*0.02,I35&gt;109%,H35*0.015,I35&gt;104%,H35*0.0125,I35&gt;99%,H35*0.01,I35&lt;99%,H35*0)</f>
@@ -5297,34 +5297,34 @@
       </c>
       <c r="D36" s="4">
         <f>IFERROR(+VLOOKUP(B36,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>7127555.5584793668</v>
+      </c>
+      <c r="E36" s="4">
         <v>6557112.931111577</v>
-      </c>
-      <c r="E36" s="4">
-        <v>6222492.2724699304</v>
       </c>
       <c r="F36" s="4">
         <f t="shared" si="8"/>
-        <v>334620.65864164662</v>
+        <v>570442.62736778986</v>
       </c>
       <c r="G36" s="5">
         <f t="shared" si="1"/>
-        <v>0.25984200242169908</v>
+        <v>0.28244721848541182</v>
       </c>
       <c r="H36" s="4">
         <f t="shared" si="4"/>
-        <v>14306428.213334348</v>
+        <v>14255111.116958734</v>
       </c>
       <c r="I36" s="5">
         <f t="shared" si="2"/>
-        <v>0.56692800528370713</v>
+        <v>0.56489443697082364</v>
       </c>
       <c r="J36" s="4">
         <f t="shared" si="5"/>
-        <v>596101.17555559787</v>
+        <v>593962.9632066139</v>
       </c>
       <c r="K36" s="4">
         <f t="shared" si="3"/>
-        <v>1436760.5437606478</v>
+        <v>1508953.7034600526</v>
       </c>
       <c r="L36" s="63" cm="1">
         <f t="array" ref="L36">+_xlfn.IFS(I36&gt;114%,H36*0.02,I36&gt;109%,H36*0.015,I36&gt;104%,H36*0.0125,I36&gt;99%,H36*0.01,I36&lt;99%,H36*0)</f>
@@ -5341,34 +5341,34 @@
       </c>
       <c r="D37" s="4">
         <f>IFERROR(+VLOOKUP(B37,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>33451176.522885799</v>
+        <v>34463405.027844027</v>
       </c>
       <c r="E37" s="4">
         <v>33451176.522885799</v>
       </c>
       <c r="F37" s="4">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1012228.5049582273</v>
       </c>
       <c r="G37" s="5">
         <f t="shared" si="1"/>
-        <v>0.27416356640148021</v>
+        <v>0.282459722345135</v>
       </c>
       <c r="H37" s="4">
         <f t="shared" si="4"/>
-        <v>72984385.140841737</v>
+        <v>68926810.055688053</v>
       </c>
       <c r="I37" s="5">
         <f t="shared" si="2"/>
-        <v>0.59817505396686577</v>
+        <v>0.56491944469027</v>
       </c>
       <c r="J37" s="4">
         <f t="shared" si="5"/>
-        <v>3041016.0475350725</v>
+        <v>2871950.4189870022</v>
       </c>
       <c r="K37" s="4">
         <f t="shared" si="3"/>
-        <v>6812351.8059318615</v>
+        <v>7295695.4143463308</v>
       </c>
       <c r="L37" s="63" cm="1">
         <f t="array" ref="L37">+_xlfn.IFS(I37&gt;114%,H37*0.0125,I37&gt;109%,H37*0.01,I37&gt;104%,H37*0.0075,I37&gt;99%,H37*0.005,I37&lt;99%,H37*0)</f>
@@ -5385,34 +5385,34 @@
       </c>
       <c r="D38" s="4">
         <f>IFERROR(+VLOOKUP(B38,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>4941053.6803995185</v>
+      </c>
+      <c r="E38" s="4">
         <v>4955958.0088995183</v>
-      </c>
-      <c r="E38" s="4">
-        <v>4305943.4722995181</v>
       </c>
       <c r="F38" s="4">
         <f t="shared" ref="F38" si="10">+D38-E38</f>
-        <v>650014.53660000023</v>
+        <v>-14904.328499999829</v>
       </c>
       <c r="G38" s="5">
         <f t="shared" si="1"/>
-        <v>0.13882235319046271</v>
+        <v>0.13840486499718538</v>
       </c>
       <c r="H38" s="4">
         <f t="shared" si="4"/>
-        <v>10812999.292144403</v>
+        <v>9882107.3607990369</v>
       </c>
       <c r="I38" s="5">
         <f t="shared" si="2"/>
-        <v>0.30288513423373675</v>
+        <v>0.27680972999437076</v>
       </c>
       <c r="J38" s="4">
         <f t="shared" si="5"/>
-        <v>450541.63717268349</v>
+        <v>411754.47336662654</v>
       </c>
       <c r="K38" s="4">
         <f t="shared" si="3"/>
-        <v>2364926.3070077295</v>
+        <v>2563245.5266333735</v>
       </c>
       <c r="L38" s="63" cm="1">
         <f t="array" ref="L38">+_xlfn.IFS(I38&gt;109%,H38*0.015,I38&gt;104%,H38*0.0125,I38&gt;99%,H38*0.01,I38&lt;99%,H38*0)</f>
@@ -5429,34 +5429,34 @@
       </c>
       <c r="D39" s="4">
         <f>IFERROR(+VLOOKUP(B39,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>11258463.913889455</v>
+      </c>
+      <c r="E39" s="4">
         <v>11259066.488129456</v>
-      </c>
-      <c r="E39" s="4">
-        <v>11081724.942682527</v>
       </c>
       <c r="F39" s="4">
         <f t="shared" si="8"/>
-        <v>177341.54544692859</v>
+        <v>-602.57424000091851</v>
       </c>
       <c r="G39" s="5">
         <f t="shared" si="1"/>
-        <v>0.3096431352736288</v>
+        <v>0.30962656347550455</v>
       </c>
       <c r="H39" s="4">
         <f t="shared" si="4"/>
-        <v>24565235.974100631</v>
+        <v>22516927.827778909</v>
       </c>
       <c r="I39" s="5">
         <f t="shared" si="2"/>
-        <v>0.67558502241519014</v>
+        <v>0.61925312695100909</v>
       </c>
       <c r="J39" s="4">
         <f t="shared" si="5"/>
-        <v>1023551.4989208597</v>
+        <v>938205.32615745452</v>
       </c>
       <c r="K39" s="4">
         <f t="shared" si="3"/>
-        <v>1930950.8654515804</v>
+        <v>2091913.6520925455</v>
       </c>
       <c r="L39" s="63" cm="1">
         <f t="array" ref="L39">+_xlfn.IFS(I39&gt;114%,H39*0.02,I39&gt;109%,H39*0.015,I39&gt;104%,H39*0.0125,I39&gt;99%,H39*0.01,I39&lt;99%,H39*0)</f>
@@ -5471,34 +5471,34 @@
       </c>
       <c r="D40" s="67">
         <f>+SUM(D27:D39)</f>
+        <v>160111762.52332208</v>
+      </c>
+      <c r="E40" s="65">
         <v>151121189.52495596</v>
-      </c>
-      <c r="E40" s="65">
-        <v>144644318.05487517</v>
       </c>
       <c r="F40" s="67">
         <f t="shared" si="8"/>
-        <v>6476871.4700807929</v>
+        <v>8990572.9983661175</v>
       </c>
       <c r="G40" s="66">
         <f t="shared" si="1"/>
-        <v>0.29688130659773049</v>
+        <v>0.31454350914660889</v>
       </c>
       <c r="H40" s="64">
         <f t="shared" si="4"/>
-        <v>329718958.96354026</v>
+        <v>320223525.04664415</v>
       </c>
       <c r="I40" s="66">
         <f t="shared" si="2"/>
-        <v>0.64774103257686655</v>
+        <v>0.62908701829321778</v>
       </c>
       <c r="J40" s="64">
         <f t="shared" si="5"/>
-        <v>13738289.956814177</v>
+        <v>13342646.876943506</v>
       </c>
       <c r="K40" s="67">
         <f t="shared" si="3"/>
-        <v>27531368.717397671</v>
+        <v>29076435.027316969</v>
       </c>
       <c r="L40" s="68"/>
     </row>
@@ -5512,34 +5512,34 @@
       </c>
       <c r="D41" s="81">
         <f>+D40+D26+D10+D16</f>
+        <v>605891870.63702166</v>
+      </c>
+      <c r="E41" s="82">
         <v>566825570.63776278</v>
-      </c>
-      <c r="E41" s="82">
-        <v>523856297.78755802</v>
       </c>
       <c r="F41" s="81">
         <f>+D41-E41</f>
-        <v>42969272.850204766</v>
+        <v>39066299.999258876</v>
       </c>
       <c r="G41" s="83">
         <f t="shared" si="1"/>
-        <v>0.41081248515877389</v>
+        <v>0.43912617568370266</v>
       </c>
       <c r="H41" s="81">
         <f t="shared" si="4"/>
-        <v>1236710335.9369371</v>
+        <v>1211783741.2740433</v>
       </c>
       <c r="I41" s="83">
         <f t="shared" si="2"/>
-        <v>0.89631814943732502</v>
+        <v>0.87825235136740532</v>
       </c>
       <c r="J41" s="81">
         <f t="shared" si="5"/>
-        <v>51529597.33070571</v>
+        <v>50490989.219751805</v>
       </c>
       <c r="K41" s="81">
         <f t="shared" si="3"/>
-        <v>62533967.419644102</v>
+        <v>64489606.371342868</v>
       </c>
       <c r="L41" s="84"/>
     </row>
@@ -5587,34 +5587,34 @@
       </c>
       <c r="D43" s="4">
         <f>IFERROR(+VLOOKUP(B43,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>11698187.310080834</v>
+      </c>
+      <c r="E43" s="4">
         <v>10831277.641265372</v>
-      </c>
-      <c r="E43" s="4">
-        <v>6840893.5633781236</v>
       </c>
       <c r="F43" s="4">
         <f t="shared" ref="F43" si="11">+D43-E43</f>
-        <v>3990384.0778872482</v>
+        <v>866909.66881546192</v>
       </c>
       <c r="G43" s="5">
         <f>+D43/C43</f>
-        <v>0.27078194103163428</v>
+        <v>0.29245468275202086</v>
       </c>
       <c r="H43" s="4">
         <f t="shared" ref="H43" si="12">+D43/$N$3*$N$4</f>
-        <v>23631878.490033537</v>
+        <v>23396374.620161667</v>
       </c>
       <c r="I43" s="5">
         <f>+H43/C43</f>
-        <v>0.59079696225083844</v>
+        <v>0.58490936550404171</v>
       </c>
       <c r="J43" s="4">
         <f t="shared" ref="J43" si="13">+D43/$N$3</f>
-        <v>984661.60375139746</v>
+        <v>974848.94250673614</v>
       </c>
       <c r="K43" s="4">
         <f>+(C43-D43)/$N$2</f>
-        <v>2243747.8737488175</v>
+        <v>2358484.3908265973</v>
       </c>
       <c r="L43" s="4" cm="1">
         <f t="array" ref="L43">+_xlfn.IFS(I43&gt;114%,H43*0.02,I43&gt;109%,H43*0.015,I43&gt;104%,H43*0.0125,I43&gt;99%,H43*0.01,I43&lt;99%,H43*0)</f>
@@ -5630,38 +5630,38 @@
       </c>
       <c r="D44" s="4">
         <f>IFERROR(+VLOOKUP(B44,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>18973242.700626545</v>
+      </c>
+      <c r="E44" s="4">
         <v>16443269.938349089</v>
-      </c>
-      <c r="E44" s="4">
-        <v>14127537.863605659</v>
       </c>
       <c r="F44" s="4">
         <f t="shared" ref="F44" si="14">+D44-E44</f>
-        <v>2315732.0747434292</v>
+        <v>2529972.762277456</v>
       </c>
       <c r="G44" s="5">
         <f>+D44/C44</f>
-        <v>0.54810899794496959</v>
+        <v>0.63244142335421816</v>
       </c>
       <c r="H44" s="4">
         <f t="shared" ref="H44" si="15">+D44/$N$3*$N$4</f>
-        <v>35876225.320034377</v>
+        <v>37946485.401253089</v>
       </c>
       <c r="I44" s="5">
         <f>+H44/C44</f>
-        <v>1.1958741773344792</v>
+        <v>1.2648828467084363</v>
       </c>
       <c r="J44" s="4">
         <f t="shared" ref="J44" si="16">+D44/$N$3</f>
-        <v>1494842.7216680991</v>
+        <v>1581103.5583855454</v>
       </c>
       <c r="K44" s="4">
         <f>+(C44-D44)/$N$2</f>
-        <v>1042825.3893577624</v>
+        <v>918896.44161445461</v>
       </c>
       <c r="L44" s="4" cm="1">
         <f t="array" ref="L44">+_xlfn.IFS(I44&gt;114%,H44*0.02,I44&gt;109%,H44*0.015,I44&gt;104%,H44*0.0125,I44&gt;99%,H44*0.01,I44&lt;99%,H44*0)</f>
-        <v>717524.5064006875</v>
+        <v>758929.70802506176</v>
       </c>
     </row>
   </sheetData>

--- a/data/ventas.xlsx
+++ b/data/ventas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cesar\Desktop\Reportes Ventas Rap\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5649A19F-6AD5-41CC-B471-DC50A7DC1823}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B38A1ECE-0E51-4269-8094-37DB251324AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2540,22 +2540,22 @@
         <v>0</v>
       </c>
       <c r="C2" s="96">
-        <v>47691.037967698801</v>
+        <v>54563.0283089636</v>
       </c>
       <c r="D2" s="96">
-        <v>238663.40472729539</v>
+        <v>260206.8107035108</v>
       </c>
       <c r="E2" s="96">
-        <v>783242769.06992614</v>
+        <v>885063636.71088195</v>
       </c>
       <c r="F2" s="96">
         <v>0</v>
       </c>
       <c r="G2" s="96">
-        <v>337753.91741668503</v>
+        <v>383781.55311044212</v>
       </c>
       <c r="H2" s="96">
-        <v>337754.07</v>
+        <v>383781.74</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -2566,22 +2566,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="96">
-        <v>511.51216639220002</v>
+        <v>572.62823782090004</v>
       </c>
       <c r="D3" s="96">
-        <v>884.13180968389997</v>
+        <v>935.33198825989996</v>
       </c>
       <c r="E3" s="96">
-        <v>11258463.913889455</v>
+        <v>12792718.437014684</v>
       </c>
       <c r="F3" s="96">
         <v>0</v>
       </c>
       <c r="G3" s="96">
-        <v>337753.91741668503</v>
+        <v>383781.55311044212</v>
       </c>
       <c r="H3" s="96">
-        <v>337754.07</v>
+        <v>383781.74</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2592,13 +2592,13 @@
         <v>1</v>
       </c>
       <c r="C4" s="96">
-        <v>339.72018849009999</v>
+        <v>380.24508928329999</v>
       </c>
       <c r="D4" s="96">
-        <v>660.09907738820004</v>
+        <v>750.88741071799996</v>
       </c>
       <c r="E4" s="96">
-        <v>9577653.6863288712</v>
+        <v>10621962.126144474</v>
       </c>
       <c r="F4" s="96">
         <v>0</v>
@@ -2618,13 +2618,13 @@
         <v>1</v>
       </c>
       <c r="C5" s="96">
-        <v>470.33585317239999</v>
+        <v>507.97551587089998</v>
       </c>
       <c r="D5" s="96">
-        <v>1616.7391904716001</v>
+        <v>1706.3107738065</v>
       </c>
       <c r="E5" s="96">
-        <v>10073320.978867745</v>
+        <v>10967412.891714148</v>
       </c>
       <c r="F5" s="96">
         <v>0</v>
@@ -2644,13 +2644,13 @@
         <v>1</v>
       </c>
       <c r="C6" s="96">
-        <v>961.45374999959995</v>
+        <v>1010.0983928567</v>
       </c>
       <c r="D6" s="96">
-        <v>2780.9077381187999</v>
+        <v>2838.9477381194001</v>
       </c>
       <c r="E6" s="96">
-        <v>20167339.013423331</v>
+        <v>21241812.405432917</v>
       </c>
       <c r="F6" s="96">
         <v>0</v>
@@ -2670,13 +2670,13 @@
         <v>1</v>
       </c>
       <c r="C7" s="96">
-        <v>971.7177738071</v>
+        <v>1020.4847182516</v>
       </c>
       <c r="D7" s="96">
-        <v>3829.0796785753</v>
+        <v>3984.8321785777998</v>
       </c>
       <c r="E7" s="96">
-        <v>19406220.336191598</v>
+        <v>20343953.298605677</v>
       </c>
       <c r="F7" s="96">
         <v>0</v>
@@ -2696,13 +2696,13 @@
         <v>1</v>
       </c>
       <c r="C8" s="96">
-        <v>2473.1364074076</v>
+        <v>2504.6364074076</v>
       </c>
       <c r="D8" s="96">
-        <v>3998.4464768564999</v>
+        <v>4165.4464768565003</v>
       </c>
       <c r="E8" s="96">
-        <v>34463405.027844027</v>
+        <v>35141605.525244027</v>
       </c>
       <c r="F8" s="96">
         <v>0</v>
@@ -2722,13 +2722,13 @@
         <v>1</v>
       </c>
       <c r="C9" s="96">
-        <v>576.65056746009998</v>
+        <v>634.52771825369996</v>
       </c>
       <c r="D9" s="96">
-        <v>2650.0165416687</v>
+        <v>2715.0165416691002</v>
       </c>
       <c r="E9" s="96">
-        <v>10717659.288687283</v>
+        <v>11583284.080894364</v>
       </c>
       <c r="F9" s="96">
         <v>0</v>
@@ -2748,13 +2748,13 @@
         <v>1</v>
       </c>
       <c r="C10" s="96">
-        <v>495.37635912669998</v>
+        <v>548.72655753940001</v>
       </c>
       <c r="D10" s="96">
-        <v>1340.3138265031</v>
+        <v>1542.5938265057</v>
       </c>
       <c r="E10" s="96">
-        <v>11631494.832822802</v>
+        <v>12850915.177441016</v>
       </c>
       <c r="F10" s="96">
         <v>0</v>
@@ -2774,13 +2774,13 @@
         <v>1</v>
       </c>
       <c r="C11" s="96">
-        <v>459.1063611093</v>
+        <v>477.53224999819997</v>
       </c>
       <c r="D11" s="96">
-        <v>1150.3370952383</v>
+        <v>1238.3370952383</v>
       </c>
       <c r="E11" s="96">
-        <v>7991786.3456236413</v>
+        <v>8419876.3054508269</v>
       </c>
       <c r="F11" s="96">
         <v>0</v>
@@ -2800,13 +2800,13 @@
         <v>1</v>
       </c>
       <c r="C12" s="96">
-        <v>798.34394047329999</v>
+        <v>828.06636110800002</v>
       </c>
       <c r="D12" s="96">
-        <v>3718.8703690389002</v>
+        <v>3857.8762023697</v>
       </c>
       <c r="E12" s="96">
-        <v>12574415.55208604</v>
+        <v>13449925.580210861</v>
       </c>
       <c r="F12" s="96">
         <v>0</v>
@@ -2826,13 +2826,13 @@
         <v>1</v>
       </c>
       <c r="C13" s="96">
-        <v>968.04365079210004</v>
+        <v>1012.3775793632</v>
       </c>
       <c r="D13" s="96">
-        <v>2262.1718690541002</v>
+        <v>2392.5997261978</v>
       </c>
       <c r="E13" s="96">
-        <v>16359393.288683873</v>
+        <v>17565663.927074969</v>
       </c>
       <c r="F13" s="96">
         <v>0</v>
@@ -2852,13 +2852,13 @@
         <v>1</v>
       </c>
       <c r="C14" s="96">
-        <v>3892.4892857146001</v>
+        <v>3963.072619048</v>
       </c>
       <c r="D14" s="96">
-        <v>35411.129166664898</v>
+        <v>36247.932499996903</v>
       </c>
       <c r="E14" s="96">
-        <v>62611489.816173963</v>
+        <v>64304217.001077607</v>
       </c>
       <c r="F14" s="96">
         <v>0</v>
@@ -2878,13 +2878,13 @@
         <v>1</v>
       </c>
       <c r="C15" s="96">
-        <v>797.04543650590006</v>
+        <v>869.14722222030002</v>
       </c>
       <c r="D15" s="96">
-        <v>3142.0966666586</v>
+        <v>3369.6016666586002</v>
       </c>
       <c r="E15" s="96">
-        <v>14638836.948941169</v>
+        <v>15725839.167291585</v>
       </c>
       <c r="F15" s="96">
         <v>0</v>
@@ -2904,13 +2904,13 @@
         <v>1</v>
       </c>
       <c r="C16" s="96">
-        <v>425.41124999800002</v>
+        <v>464.79805555370001</v>
       </c>
       <c r="D16" s="96">
-        <v>2175.1130357194002</v>
+        <v>2338.1130357237998</v>
       </c>
       <c r="E16" s="96">
-        <v>11260002.931573136</v>
+        <v>12119565.962394305</v>
       </c>
       <c r="F16" s="96">
         <v>0</v>
@@ -2930,13 +2930,13 @@
         <v>1</v>
       </c>
       <c r="C17" s="96">
-        <v>976.82622221960003</v>
+        <v>1029.9283055527001</v>
       </c>
       <c r="D17" s="96">
-        <v>2719.8554523931002</v>
+        <v>2861.6129523987001</v>
       </c>
       <c r="E17" s="96">
-        <v>18892134.412943024</v>
+        <v>20167812.79109044</v>
       </c>
       <c r="F17" s="96">
         <v>0</v>
@@ -2956,13 +2956,13 @@
         <v>1</v>
       </c>
       <c r="C18" s="96">
-        <v>1280.1470714266</v>
+        <v>1412.5037777752</v>
       </c>
       <c r="D18" s="96">
-        <v>6001.0228690393997</v>
+        <v>6177.8516190375003</v>
       </c>
       <c r="E18" s="96">
-        <v>23833343.066456228</v>
+        <v>25816464.992216989</v>
       </c>
       <c r="F18" s="96">
         <v>0</v>
@@ -2982,13 +2982,13 @@
         <v>1</v>
       </c>
       <c r="C19" s="96">
-        <v>1123.4378756589001</v>
+        <v>1194.5462089912</v>
       </c>
       <c r="D19" s="96">
-        <v>3967.9302262039</v>
+        <v>4286.9402262046997</v>
       </c>
       <c r="E19" s="96">
-        <v>22295266.235117078</v>
+        <v>23966157.061793938</v>
       </c>
       <c r="F19" s="96">
         <v>0</v>
@@ -3008,13 +3008,13 @@
         <v>1</v>
       </c>
       <c r="C20" s="96">
-        <v>3363.5946388891002</v>
+        <v>3508.6099166665999</v>
       </c>
       <c r="D20" s="96">
-        <v>14739.0918333273</v>
+        <v>15461.246833323699</v>
       </c>
       <c r="E20" s="96">
-        <v>51657737.149835296</v>
+        <v>55125480.325350739</v>
       </c>
       <c r="F20" s="96">
         <v>0</v>
@@ -3034,13 +3034,13 @@
         <v>1</v>
       </c>
       <c r="C21" s="96">
-        <v>523.02232142529999</v>
+        <v>579.55577380600005</v>
       </c>
       <c r="D21" s="96">
-        <v>1996.3987381019001</v>
+        <v>2214.4087381038999</v>
       </c>
       <c r="E21" s="96">
-        <v>11678597.247224085</v>
+        <v>12810368.916756971</v>
       </c>
       <c r="F21" s="96">
         <v>0</v>
@@ -3060,13 +3060,13 @@
         <v>1</v>
       </c>
       <c r="C22" s="96">
-        <v>389.55977380809998</v>
+        <v>420.12088491920002</v>
       </c>
       <c r="D22" s="96">
-        <v>1391.7165238095999</v>
+        <v>1580.969023808</v>
       </c>
       <c r="E22" s="96">
-        <v>7127555.5584793668</v>
+        <v>7669142.5805392843</v>
       </c>
       <c r="F22" s="96">
         <v>0</v>
@@ -3086,13 +3086,13 @@
         <v>1</v>
       </c>
       <c r="C23" s="96">
-        <v>1903.2949206333999</v>
+        <v>1994.7653571408</v>
       </c>
       <c r="D23" s="96">
-        <v>10893.3035833293</v>
+        <v>11279.0875118984</v>
       </c>
       <c r="E23" s="96">
-        <v>36077557.848657869</v>
+        <v>38129967.134491101</v>
       </c>
       <c r="F23" s="96">
         <v>0</v>
@@ -3112,13 +3112,13 @@
         <v>1</v>
       </c>
       <c r="C24" s="96">
-        <v>1861.3213293652</v>
+        <v>3181.5931547619998</v>
       </c>
       <c r="D24" s="96">
-        <v>15300.7601488083</v>
+        <v>23090.136053568302</v>
       </c>
       <c r="E24" s="96">
-        <v>32490170.4422471</v>
+        <v>53747040.528584458</v>
       </c>
       <c r="F24" s="96">
         <v>0</v>
@@ -3138,13 +3138,13 @@
         <v>1</v>
       </c>
       <c r="C25" s="96">
-        <v>589.45227380790004</v>
+        <v>628.11695634729995</v>
       </c>
       <c r="D25" s="96">
-        <v>2385.2491666783999</v>
+        <v>2590.2491666810001</v>
       </c>
       <c r="E25" s="96">
-        <v>10794067.346588679</v>
+        <v>11588903.613097664</v>
       </c>
       <c r="F25" s="96">
         <v>0</v>
@@ -3164,13 +3164,13 @@
         <v>1</v>
       </c>
       <c r="C26" s="96">
-        <v>498.76428571280002</v>
+        <v>784.00873015690001</v>
       </c>
       <c r="D26" s="96">
-        <v>1206.0319166669001</v>
+        <v>1674.4697738176999</v>
       </c>
       <c r="E26" s="96">
-        <v>7538759.4369671568</v>
+        <v>10653241.374119855</v>
       </c>
       <c r="F26" s="96">
         <v>0</v>
@@ -3190,13 +3190,13 @@
         <v>1</v>
       </c>
       <c r="C27" s="96">
-        <v>5474.0857142857003</v>
+        <v>7615.0857142857003</v>
       </c>
       <c r="D27" s="96">
-        <v>16376.539999999801</v>
+        <v>17396.539999999801</v>
       </c>
       <c r="E27" s="96">
-        <v>54039192.425718747</v>
+        <v>72314066.082918748</v>
       </c>
       <c r="F27" s="96">
         <v>0</v>
@@ -3216,13 +3216,13 @@
         <v>1</v>
       </c>
       <c r="C28" s="96">
-        <v>778.3840244685</v>
+        <v>815.06844907130005</v>
       </c>
       <c r="D28" s="96">
-        <v>3355.8351711417999</v>
+        <v>3472.4468378094002</v>
       </c>
       <c r="E28" s="96">
-        <v>15114947.7812881</v>
+        <v>15729400.126823407</v>
       </c>
       <c r="F28" s="96">
         <v>0</v>
@@ -3242,13 +3242,13 @@
         <v>1</v>
       </c>
       <c r="C29" s="96">
-        <v>2965.9849603173002</v>
+        <v>3269.3926984126001</v>
       </c>
       <c r="D29" s="96">
-        <v>7595.5816666709998</v>
+        <v>8462.8200000057004</v>
       </c>
       <c r="E29" s="96">
-        <v>37484101.183935247</v>
+        <v>43692487.08063937</v>
       </c>
       <c r="F29" s="96">
         <v>0</v>
@@ -3268,13 +3268,13 @@
         <v>1</v>
       </c>
       <c r="C30" s="96">
-        <v>304.95458333319999</v>
+        <v>327.40299603160003</v>
       </c>
       <c r="D30" s="96">
-        <v>1376.8666666718</v>
+        <v>1464.9833333412</v>
       </c>
       <c r="E30" s="96">
-        <v>6541870.7729290416</v>
+        <v>7015916.0627130093</v>
       </c>
       <c r="F30" s="96">
         <v>0</v>
@@ -3294,13 +3294,13 @@
         <v>1</v>
       </c>
       <c r="C31" s="96">
-        <v>428.45109126770001</v>
+        <v>455.2816468231</v>
       </c>
       <c r="D31" s="96">
-        <v>1137.6699999990999</v>
+        <v>1129.6699999987</v>
       </c>
       <c r="E31" s="96">
-        <v>7043117.2210489651</v>
+        <v>7535974.4603506317</v>
       </c>
       <c r="F31" s="96">
         <v>0</v>
@@ -3320,13 +3320,13 @@
         <v>1</v>
       </c>
       <c r="C32" s="96">
-        <v>183.9674603174</v>
+        <v>194.12043650780001</v>
       </c>
       <c r="D32" s="96">
-        <v>707.0404166651</v>
+        <v>747.53541666410001</v>
       </c>
       <c r="E32" s="96">
-        <v>4108217.6743740062</v>
+        <v>4297511.625002631</v>
       </c>
       <c r="F32" s="96">
         <v>0</v>
@@ -3346,13 +3346,13 @@
         <v>1</v>
       </c>
       <c r="C33" s="96">
-        <v>492.08900793570001</v>
+        <v>511.86003968160003</v>
       </c>
       <c r="D33" s="96">
-        <v>1996.6025000049999</v>
+        <v>2133.6025000029999</v>
       </c>
       <c r="E33" s="96">
-        <v>9187869.5284201782</v>
+        <v>9642556.4815232344</v>
       </c>
       <c r="F33" s="96">
         <v>0</v>
@@ -3398,13 +3398,13 @@
         <v>1</v>
       </c>
       <c r="C35" s="96">
-        <v>921.18333333329997</v>
+        <v>920.18333333329997</v>
       </c>
       <c r="D35" s="96">
         <v>6152.3953333332001</v>
       </c>
       <c r="E35" s="96">
-        <v>11858403.056258887</v>
+        <v>11751173.096258886</v>
       </c>
       <c r="F35" s="96">
         <v>0</v>
@@ -3424,13 +3424,13 @@
         <v>1</v>
       </c>
       <c r="C36" s="96">
-        <v>840.67315872849997</v>
+        <v>864.83347618870005</v>
       </c>
       <c r="D36" s="96">
-        <v>2927.6872023914998</v>
+        <v>2988.6367857250998</v>
       </c>
       <c r="E36" s="96">
-        <v>14549220.102775784</v>
+        <v>15219121.752963766</v>
       </c>
       <c r="F36" s="96">
         <v>0</v>
@@ -3450,13 +3450,13 @@
         <v>1</v>
       </c>
       <c r="C37" s="96">
-        <v>644.06299603219998</v>
+        <v>1463.5992658733001</v>
       </c>
       <c r="D37" s="96">
-        <v>3989.6771547639</v>
+        <v>6012.6120714331</v>
       </c>
       <c r="E37" s="96">
-        <v>12726652.901956733</v>
+        <v>23371700.396195162</v>
       </c>
       <c r="F37" s="96">
         <v>0</v>
@@ -3476,13 +3476,13 @@
         <v>1</v>
       </c>
       <c r="C38" s="96">
-        <v>906.70050505009999</v>
+        <v>1030.3671717167999</v>
       </c>
       <c r="D38" s="96">
-        <v>10318.049999995001</v>
+        <v>12545.709999995601</v>
       </c>
       <c r="E38" s="96">
-        <v>20234990.306558445</v>
+        <v>24556777.325660907</v>
       </c>
       <c r="F38" s="96">
         <v>0</v>
@@ -3502,13 +3502,13 @@
         <v>1</v>
       </c>
       <c r="C39" s="96">
-        <v>1252.5833333331</v>
+        <v>1327.2499999997999</v>
       </c>
       <c r="D39" s="96">
-        <v>15232.0899999962</v>
+        <v>15910.4699999969</v>
       </c>
       <c r="E39" s="96">
-        <v>28060601.939276338</v>
+        <v>29449983.687544316</v>
       </c>
       <c r="F39" s="96">
         <v>0</v>
@@ -3528,13 +3528,13 @@
         <v>1</v>
       </c>
       <c r="C40" s="96">
-        <v>1336.1126653440001</v>
+        <v>1518.3182208994999</v>
       </c>
       <c r="D40" s="96">
-        <v>7969.6475939415996</v>
+        <v>8342.6813439440994</v>
       </c>
       <c r="E40" s="96">
-        <v>17261217.954442594</v>
+        <v>19950659.881944489</v>
       </c>
       <c r="F40" s="96">
         <v>0</v>
@@ -3580,13 +3580,13 @@
         <v>1</v>
       </c>
       <c r="C42" s="96">
-        <v>216.06111111109999</v>
+        <v>209.06111111109999</v>
       </c>
       <c r="D42" s="96">
-        <v>2515.5499999999001</v>
+        <v>2389.5499999999001</v>
       </c>
       <c r="E42" s="96">
-        <v>4941053.6803995185</v>
+        <v>4784668.386799518</v>
       </c>
       <c r="F42" s="96">
         <v>0</v>
@@ -3658,13 +3658,13 @@
         <v>1</v>
       </c>
       <c r="C45" s="96">
-        <v>422.06325396929998</v>
+        <v>487.22089285819999</v>
       </c>
       <c r="D45" s="96">
-        <v>3750.5670488104001</v>
+        <v>4715.5670488094001</v>
       </c>
       <c r="E45" s="96">
-        <v>8740812.2586272676</v>
+        <v>10336849.130847456</v>
       </c>
       <c r="F45" s="96">
         <v>0</v>
@@ -3684,13 +3684,13 @@
         <v>1</v>
       </c>
       <c r="C46" s="96">
-        <v>321.87900000000002</v>
+        <v>473.87900000000002</v>
       </c>
       <c r="D46" s="96">
         <v>-24.9999999996</v>
       </c>
       <c r="E46" s="96">
-        <v>1592393.851396092</v>
+        <v>3970024.203796092</v>
       </c>
       <c r="F46" s="96">
         <v>0</v>
@@ -3779,44 +3779,44 @@
       </c>
       <c r="D2" s="59">
         <f>IFERROR(+VLOOKUP(B2,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>25816464.992216989</v>
+      </c>
+      <c r="E2" s="59">
         <v>23833343.066456228</v>
-      </c>
-      <c r="E2" s="59">
-        <v>22534059.612904426</v>
       </c>
       <c r="F2" s="59">
         <f t="shared" ref="F2:F9" si="0">+D2-E2</f>
-        <v>1299283.4535518028</v>
+        <v>1983121.9257607609</v>
       </c>
       <c r="G2" s="60">
         <f t="shared" ref="G2:G41" si="1">+D2/C2</f>
-        <v>0.73835268999651871</v>
+        <v>0.79978945127644818</v>
       </c>
       <c r="H2" s="59">
         <f>+D2/$N$3*$N$4</f>
-        <v>47666686.132912457</v>
+        <v>47661166.139477521</v>
       </c>
       <c r="I2" s="60">
         <f t="shared" ref="I2:I41" si="2">+H2/C2</f>
-        <v>1.4767053799930374</v>
+        <v>1.4765343715872892</v>
       </c>
       <c r="J2" s="59">
         <f>+D2/$N$3</f>
-        <v>1986111.9222046856</v>
+        <v>1985881.92247823</v>
       </c>
       <c r="K2" s="59">
         <f t="shared" ref="K2:K41" si="3">+(C2-D2)/$N$2</f>
-        <v>703811.1309828771</v>
+        <v>587510.14963943313</v>
       </c>
       <c r="L2" s="61" cm="1">
         <f t="array" ref="L2">+_xlfn.IFS(I2&gt;114%,H2*0.02,I2&gt;109%,H2*0.015,I2&gt;104%,H2*0.0125,I2&gt;99%,H2*0.01,I2&lt;99%,H2*0)</f>
-        <v>953333.7226582492</v>
+        <v>953223.32278955041</v>
       </c>
       <c r="M2" s="53" t="s">
         <v>36</v>
       </c>
       <c r="N2">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -3829,45 +3829,45 @@
       </c>
       <c r="D3" s="4">
         <f>IFERROR(+VLOOKUP(B3,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>20167812.79109044</v>
+      </c>
+      <c r="E3" s="4">
         <v>18892134.412943024</v>
-      </c>
-      <c r="E3" s="4">
-        <v>17944639.742629033</v>
       </c>
       <c r="F3" s="4">
         <f t="shared" si="0"/>
-        <v>947494.67031399161</v>
+        <v>1275678.3781474158</v>
       </c>
       <c r="G3" s="5">
         <f t="shared" si="1"/>
-        <v>0.60976342379749637</v>
+        <v>0.65093727946256574</v>
       </c>
       <c r="H3" s="4">
         <f t="shared" ref="H3:H41" si="4">+D3/$N$3*$N$4</f>
-        <v>37784268.825886048</v>
+        <v>37232885.152782351</v>
       </c>
       <c r="I3" s="5">
         <f t="shared" si="2"/>
-        <v>1.2195268475949927</v>
+        <v>1.2017303620847368</v>
       </c>
       <c r="J3" s="4">
         <f t="shared" ref="J3:J41" si="5">+D3/$N$3</f>
-        <v>1574344.5344119186</v>
+        <v>1551370.2146992646</v>
       </c>
       <c r="K3" s="4">
         <f t="shared" si="3"/>
-        <v>1007549.4804950192</v>
+        <v>983174.12616298313</v>
       </c>
       <c r="L3" s="63" cm="1">
         <f t="array" ref="L3">+_xlfn.IFS(I3&gt;114%,H3*0.02,I3&gt;109%,H3*0.015,I3&gt;104%,H3*0.0125,I3&gt;99%,H3*0.01,I3&lt;99%,H3*0)</f>
-        <v>755685.37651772099</v>
+        <v>744657.70305564709</v>
       </c>
       <c r="M3" s="53" t="s">
         <v>40</v>
       </c>
       <c r="N3">
         <f>N4-N2</f>
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -3880,38 +3880,38 @@
       </c>
       <c r="D4" s="4">
         <f>IFERROR(+VLOOKUP(B4,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>15725839.167291585</v>
+      </c>
+      <c r="E4" s="4">
         <v>14638836.948941169</v>
-      </c>
-      <c r="E4" s="4">
-        <v>13843506.900515262</v>
       </c>
       <c r="F4" s="4">
         <f t="shared" si="0"/>
-        <v>795330.04842590727</v>
+        <v>1087002.218350416</v>
       </c>
       <c r="G4" s="5">
         <f t="shared" si="1"/>
-        <v>0.51563299859729439</v>
+        <v>0.5539211641998546</v>
       </c>
       <c r="H4" s="4">
         <f t="shared" si="4"/>
-        <v>29277673.897882339</v>
+        <v>29032318.46269216</v>
       </c>
       <c r="I4" s="5">
         <f t="shared" si="2"/>
-        <v>1.0312659971945888</v>
+        <v>1.0226236877535777</v>
       </c>
       <c r="J4" s="4">
         <f t="shared" si="5"/>
-        <v>1219903.0790784308</v>
+        <v>1209679.9359455067</v>
       </c>
       <c r="K4" s="4">
         <f t="shared" si="3"/>
-        <v>1145932.8592672569</v>
+        <v>1151290.1902596971</v>
       </c>
       <c r="L4" s="63" cm="1">
         <f t="array" ref="L4">+_xlfn.IFS(I4&gt;114%,H4*0.02,I4&gt;109%,H4*0.015,I4&gt;104%,H4*0.0125,I4&gt;99%,H4*0.01,I4&lt;99%,H4*0)</f>
-        <v>292776.73897882341</v>
+        <v>290323.1846269216</v>
       </c>
       <c r="M4" s="53" t="s">
         <v>47</v>
@@ -3930,38 +3930,38 @@
       </c>
       <c r="D5" s="4">
         <f>IFERROR(+VLOOKUP(B5,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>17565663.927074969</v>
+      </c>
+      <c r="E5" s="4">
         <v>16359393.288683873</v>
-      </c>
-      <c r="E5" s="4">
-        <v>15247177.219484905</v>
       </c>
       <c r="F5" s="4">
         <f t="shared" si="0"/>
-        <v>1112216.0691989679</v>
+        <v>1206270.6383910961</v>
       </c>
       <c r="G5" s="5">
         <f t="shared" si="1"/>
-        <v>0.57623724112089769</v>
+        <v>0.61872647360315869</v>
       </c>
       <c r="H5" s="4">
         <f t="shared" si="4"/>
-        <v>32718786.577367745</v>
+        <v>32428918.019215323</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" si="2"/>
-        <v>1.1524744822417954</v>
+        <v>1.1422642589596774</v>
       </c>
       <c r="J5" s="4">
         <f t="shared" si="5"/>
-        <v>1363282.7740569895</v>
+        <v>1351204.9174673052</v>
       </c>
       <c r="K5" s="4">
         <f t="shared" si="3"/>
-        <v>1002553.1642886983</v>
+        <v>984033.39391575311</v>
       </c>
       <c r="L5" s="63" cm="1">
         <f t="array" ref="L5">+_xlfn.IFS(I5&gt;114%,H5*0.02,I5&gt;109%,H5*0.015,I5&gt;104%,H5*0.0125,I5&gt;99%,H5*0.01,I5&lt;99%,H5*0)</f>
-        <v>654375.73154735495</v>
+        <v>648578.36038430652</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
@@ -3974,38 +3974,38 @@
       </c>
       <c r="D6" s="4">
         <f>IFERROR(+VLOOKUP(B6,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>13449925.580210861</v>
+      </c>
+      <c r="E6" s="4">
         <v>12574415.55208604</v>
-      </c>
-      <c r="E6" s="4">
-        <v>11563280.456663784</v>
       </c>
       <c r="F6" s="4">
         <f t="shared" si="0"/>
-        <v>1011135.0954222567</v>
+        <v>875510.02812482044</v>
       </c>
       <c r="G6" s="5">
         <f t="shared" si="1"/>
-        <v>0.53442827009318861</v>
+        <v>0.57163853309442725</v>
       </c>
       <c r="H6" s="4">
         <f t="shared" si="4"/>
-        <v>25148831.104172081</v>
+        <v>24830631.840389282</v>
       </c>
       <c r="I6" s="5">
         <f t="shared" si="2"/>
-        <v>1.0688565401863772</v>
+        <v>1.0553326764820194</v>
       </c>
       <c r="J6" s="4">
         <f t="shared" si="5"/>
-        <v>1047867.9626738367</v>
+        <v>1034609.6600162201</v>
       </c>
       <c r="K6" s="4">
         <f t="shared" si="3"/>
-        <v>912859.08211950713</v>
+        <v>916254.45066447859</v>
       </c>
       <c r="L6" s="63" cm="1">
         <f t="array" ref="L6">+_xlfn.IFS(I6&gt;114%,H6*0.02,I6&gt;109%,H6*0.015,I6&gt;104%,H6*0.0125,I6&gt;99%,H6*0.01,I6&lt;99%,H6*0)</f>
-        <v>314360.38880215102</v>
+        <v>310382.89800486603</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
@@ -4018,34 +4018,34 @@
       </c>
       <c r="D7" s="4">
         <f>IFERROR(+VLOOKUP(B7,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>11583284.080894364</v>
+      </c>
+      <c r="E7" s="4">
         <v>10717659.288687283</v>
-      </c>
-      <c r="E7" s="4">
-        <v>9615921.6737193447</v>
       </c>
       <c r="F7" s="4">
         <f t="shared" ref="F7:F8" si="6">+D7-E7</f>
-        <v>1101737.6149679385</v>
+        <v>865624.79220708087</v>
       </c>
       <c r="G7" s="5">
         <f t="shared" si="1"/>
-        <v>0.38633532271894305</v>
+        <v>0.41753816509739311</v>
       </c>
       <c r="H7" s="4">
         <f t="shared" si="4"/>
-        <v>21435318.577374566</v>
+        <v>21384524.45703575</v>
       </c>
       <c r="I7" s="5">
         <f t="shared" si="2"/>
-        <v>0.77267064543788611</v>
+        <v>0.7708396894105719</v>
       </c>
       <c r="J7" s="4">
         <f t="shared" si="5"/>
-        <v>893138.27405727364</v>
+        <v>891021.85237648955</v>
       </c>
       <c r="K7" s="4">
         <f t="shared" si="3"/>
-        <v>1418683.1451481015</v>
+        <v>1468961.1772336492</v>
       </c>
       <c r="L7" s="63" cm="1">
         <f t="array" ref="L7">+_xlfn.IFS(I7&gt;114%,H7*0.02,I7&gt;109%,H7*0.015,I7&gt;104%,H7*0.0125,I7&gt;99%,H7*0.01,I7&lt;99%,H7*0)</f>
@@ -4062,38 +4062,38 @@
       </c>
       <c r="D8" s="4">
         <f>IFERROR(+VLOOKUP(B8,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>20343953.298605677</v>
+      </c>
+      <c r="E8" s="4">
         <v>19406220.336191598</v>
-      </c>
-      <c r="E8" s="4">
-        <v>16806749.78055869</v>
       </c>
       <c r="F8" s="4">
         <f t="shared" si="6"/>
-        <v>2599470.5556329079</v>
+        <v>937732.96241407841</v>
       </c>
       <c r="G8" s="5">
         <f t="shared" si="1"/>
-        <v>0.54160312736361316</v>
+        <v>0.56777407133296731</v>
       </c>
       <c r="H8" s="4">
         <f t="shared" si="4"/>
-        <v>38812440.672383197</v>
+        <v>37558067.6281951</v>
       </c>
       <c r="I8" s="5">
         <f t="shared" si="2"/>
-        <v>1.0832062547272263</v>
+        <v>1.0481982855377858</v>
       </c>
       <c r="J8" s="4">
         <f t="shared" si="5"/>
-        <v>1617185.0280159665</v>
+        <v>1564919.4845081291</v>
       </c>
       <c r="K8" s="4">
         <f t="shared" si="3"/>
-        <v>1368737.5900605088</v>
+        <v>1407919.8289374569</v>
       </c>
       <c r="L8" s="63" cm="1">
         <f t="array" ref="L8">+_xlfn.IFS(I8&gt;114%,H8*0.02,I8&gt;109%,H8*0.015,I8&gt;104%,H8*0.0125,I8&gt;99%,H8*0.01,I8&lt;99%,H8*0)</f>
-        <v>485155.50840478996</v>
+        <v>469475.84535243874</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
@@ -4106,38 +4106,38 @@
       </c>
       <c r="D9" s="4">
         <f>IFERROR(+VLOOKUP(B9,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>21241812.405432917</v>
+      </c>
+      <c r="E9" s="4">
         <v>20167339.013423331</v>
-      </c>
-      <c r="E9" s="4">
-        <v>18863848.650468376</v>
       </c>
       <c r="F9" s="4">
         <f t="shared" si="0"/>
-        <v>1303490.3629549555</v>
+        <v>1074473.3920095861</v>
       </c>
       <c r="G9" s="5">
         <f t="shared" si="1"/>
-        <v>0.56284498944403005</v>
+        <v>0.59283218629637624</v>
       </c>
       <c r="H9" s="4">
         <f t="shared" si="4"/>
-        <v>40334678.026846662</v>
+        <v>39215653.671568461</v>
       </c>
       <c r="I9" s="5">
         <f t="shared" si="2"/>
-        <v>1.1256899788880601</v>
+        <v>1.0944594208548484</v>
       </c>
       <c r="J9" s="4">
         <f t="shared" si="5"/>
-        <v>1680611.5844519443</v>
+        <v>1633985.5696486859</v>
       </c>
       <c r="K9" s="4">
         <f t="shared" si="3"/>
-        <v>1305311.033624531</v>
+        <v>1326296.2737713442</v>
       </c>
       <c r="L9" s="63" cm="1">
         <f t="array" ref="L9">+_xlfn.IFS(I9&gt;114%,H9*0.02,I9&gt;109%,H9*0.015,I9&gt;104%,H9*0.0125,I9&gt;99%,H9*0.01,I9&lt;99%,H9*0)</f>
-        <v>605020.17040269997</v>
+        <v>588234.80507352692</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4148,34 +4148,34 @@
       </c>
       <c r="D10" s="64">
         <f>+SUM(D2:D9)</f>
+        <v>145894756.24281782</v>
+      </c>
+      <c r="E10" s="65">
         <v>136589341.90741256</v>
-      </c>
-      <c r="E10" s="65">
-        <v>126419184.03694384</v>
       </c>
       <c r="F10" s="64">
         <f>+SUM(F2:F9)</f>
-        <v>10170157.870468728</v>
+        <v>9305414.3354052547</v>
       </c>
       <c r="G10" s="66">
         <f t="shared" si="1"/>
-        <v>0.56215483656000598</v>
+        <v>0.6004527271698662</v>
       </c>
       <c r="H10" s="64">
         <f t="shared" si="4"/>
-        <v>273178683.81482512</v>
+        <v>269344165.37135601</v>
       </c>
       <c r="I10" s="66">
         <f t="shared" si="2"/>
-        <v>1.124309673120012</v>
+        <v>1.1085281116982146</v>
       </c>
       <c r="J10" s="64">
         <f t="shared" si="5"/>
-        <v>11382445.158951046</v>
+        <v>11222673.557139833</v>
       </c>
       <c r="K10" s="67">
         <f t="shared" si="3"/>
-        <v>8865437.4859864954</v>
+        <v>8825439.5905847903</v>
       </c>
       <c r="L10" s="68"/>
     </row>
@@ -4191,38 +4191,38 @@
       </c>
       <c r="D11" s="59">
         <f>IFERROR(+VLOOKUP(B11,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>55125480.325350739</v>
+      </c>
+      <c r="E11" s="59">
         <v>51657737.149835296</v>
-      </c>
-      <c r="E11" s="59">
-        <v>49340595.584204771</v>
       </c>
       <c r="F11" s="59">
         <f t="shared" ref="F11:F16" si="7">+D11-E11</f>
-        <v>2317141.5656305254</v>
+        <v>3467743.1755154431</v>
       </c>
       <c r="G11" s="60">
         <f t="shared" si="1"/>
-        <v>0.53270804556862339</v>
+        <v>0.56846831675906706</v>
       </c>
       <c r="H11" s="59">
         <f t="shared" si="4"/>
-        <v>103315474.29967059</v>
+        <v>101770117.52372445</v>
       </c>
       <c r="I11" s="60">
         <f t="shared" si="2"/>
-        <v>1.0654160911372468</v>
+        <v>1.0494799694013546</v>
       </c>
       <c r="J11" s="59">
         <f t="shared" si="5"/>
-        <v>4304811.4291529413</v>
+        <v>4240421.5634885188</v>
       </c>
       <c r="K11" s="59">
         <f t="shared" si="3"/>
-        <v>3776184.2775251847</v>
+        <v>3804224.3777078884</v>
       </c>
       <c r="L11" s="61" cm="1">
         <f t="array" ref="L11">+_xlfn.IFS(I11&gt;114%,H11*0.0125,I11&gt;109%,H11*0.01,I11&gt;104%,H11*0.0075,I11&gt;99%,H11*0.005,I11&lt;99%,H11*0)</f>
-        <v>774866.05724752939</v>
+        <v>763275.88142793335</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4235,38 +4235,38 @@
       </c>
       <c r="D12" s="4">
         <f>IFERROR(+VLOOKUP(B12,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>12726652.901956733</v>
+        <v>23371700.396195162</v>
       </c>
       <c r="E12" s="4">
         <v>12726652.901956733</v>
       </c>
       <c r="F12" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>10645047.494238429</v>
       </c>
       <c r="G12" s="5">
         <f t="shared" si="1"/>
-        <v>0.40234871384857518</v>
+        <v>0.73888819529426719</v>
       </c>
       <c r="H12" s="4">
         <f t="shared" si="4"/>
-        <v>25453305.803913467</v>
+        <v>43147754.577591069</v>
       </c>
       <c r="I12" s="5">
         <f t="shared" si="2"/>
-        <v>0.80469742769715036</v>
+        <v>1.3641012836201856</v>
       </c>
       <c r="J12" s="4">
         <f t="shared" si="5"/>
-        <v>1060554.4084963945</v>
+        <v>1797823.1073996278</v>
       </c>
       <c r="K12" s="4">
         <f t="shared" si="3"/>
-        <v>1575354.1255508559</v>
+        <v>750836.5465792584</v>
       </c>
       <c r="L12" s="63" cm="1">
         <f t="array" ref="L12">+_xlfn.IFS(I12&gt;114%,H12*0.02,I12&gt;109%,H12*0.015,I12&gt;104%,H12*0.0125,I12&gt;99%,H12*0.01,I12&lt;99%,H12*0)</f>
-        <v>0</v>
+        <v>862955.09155182145</v>
       </c>
       <c r="M12" s="27"/>
     </row>
@@ -4280,34 +4280,34 @@
       </c>
       <c r="D13" s="4">
         <f>IFERROR(+VLOOKUP(B13,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>64304217.001077607</v>
+      </c>
+      <c r="E13" s="4">
         <v>62611489.816173963</v>
-      </c>
-      <c r="E13" s="4">
-        <v>60038357.598558225</v>
       </c>
       <c r="F13" s="4">
         <f t="shared" si="7"/>
-        <v>2573132.2176157385</v>
+        <v>1692727.184903644</v>
       </c>
       <c r="G13" s="5">
         <f t="shared" si="1"/>
-        <v>0.4877655008575344</v>
+        <v>0.50095244027686125</v>
       </c>
       <c r="H13" s="4">
         <f t="shared" si="4"/>
-        <v>125222979.63234791</v>
+        <v>118715477.54045096</v>
       </c>
       <c r="I13" s="5">
         <f t="shared" si="2"/>
-        <v>0.97553100171506857</v>
+        <v>0.9248352743572823</v>
       </c>
       <c r="J13" s="4">
         <f t="shared" si="5"/>
-        <v>5217624.15134783</v>
+        <v>4946478.2308521233</v>
       </c>
       <c r="K13" s="4">
         <f t="shared" si="3"/>
-        <v>5479368.8548709182</v>
+        <v>5823609.006686125</v>
       </c>
       <c r="L13" s="63" cm="1">
         <f t="array" ref="L13">+_xlfn.IFS(I13&gt;114%,H13*0.0125,I13&gt;109%,H13*0.01,I13&gt;104%,H13*0.0075,I13&gt;99%,H13*0.005,I13&lt;99%,H13*0)</f>
@@ -4330,38 +4330,38 @@
       </c>
       <c r="D14" s="4">
         <f>IFERROR(+VLOOKUP(B14,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>24556777.325660907</v>
+      </c>
+      <c r="E14" s="4">
         <v>20234990.306558445</v>
-      </c>
-      <c r="E14" s="4">
-        <v>18735817.540831447</v>
       </c>
       <c r="F14" s="4">
         <f t="shared" si="7"/>
-        <v>1499172.7657269984</v>
+        <v>4321787.0191024616</v>
       </c>
       <c r="G14" s="5">
         <f t="shared" si="1"/>
-        <v>0.47668880178606288</v>
+        <v>0.57849994399564386</v>
       </c>
       <c r="H14" s="4">
         <f t="shared" si="4"/>
-        <v>40469980.61311689</v>
+        <v>45335588.908912443</v>
       </c>
       <c r="I14" s="5">
         <f t="shared" si="2"/>
-        <v>0.95337760357212575</v>
+        <v>1.0679998966073425</v>
       </c>
       <c r="J14" s="4">
         <f t="shared" si="5"/>
-        <v>1686249.1922132038</v>
+        <v>1888982.8712046852</v>
       </c>
       <c r="K14" s="4">
         <f t="shared" si="3"/>
-        <v>1851172.2573680461</v>
+        <v>1626570.9153921902</v>
       </c>
       <c r="L14" s="63" cm="1">
         <f t="array" ref="L14">+_xlfn.IFS(I14&gt;109%,H14*0.015,I14&gt;104%,H14*0.0125,I14&gt;99%,H14*0.01,I14&lt;99%,H14*0)</f>
-        <v>0</v>
+        <v>566694.86136140558</v>
       </c>
       <c r="N14" s="28"/>
     </row>
@@ -4375,38 +4375,38 @@
       </c>
       <c r="D15" s="4">
         <f>IFERROR(+VLOOKUP(B15,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>29449983.687544316</v>
+      </c>
+      <c r="E15" s="4">
         <v>28060601.939276338</v>
-      </c>
-      <c r="E15" s="4">
-        <v>27101787.621247634</v>
       </c>
       <c r="F15" s="4">
         <f t="shared" si="7"/>
-        <v>958814.31802870333</v>
+        <v>1389381.7482679784</v>
       </c>
       <c r="G15" s="5">
         <f t="shared" si="1"/>
-        <v>0.66104181485542413</v>
+        <v>0.69377238258841811</v>
       </c>
       <c r="H15" s="4">
         <f t="shared" si="4"/>
-        <v>56121203.878552675</v>
+        <v>54369200.653927967</v>
       </c>
       <c r="I15" s="5">
         <f t="shared" si="2"/>
-        <v>1.3220836297108483</v>
+        <v>1.2808105524709259</v>
       </c>
       <c r="J15" s="4">
         <f t="shared" si="5"/>
-        <v>2338383.4949396946</v>
+        <v>2265383.3605803321</v>
       </c>
       <c r="K15" s="4">
         <f t="shared" si="3"/>
-        <v>1199037.9546415552</v>
+        <v>1181733.9734027893</v>
       </c>
       <c r="L15" s="63" cm="1">
         <f t="array" ref="L15">+_xlfn.IFS(I15&gt;109%,H15*0.015,I15&gt;104%,H15*0.0125,I15&gt;99%,H15*0.01,I15&lt;99%,H15*0)</f>
-        <v>841818.05817829014</v>
+        <v>815538.00980891951</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4417,34 +4417,34 @@
       </c>
       <c r="D16" s="64">
         <f>+SUM(D11:D15)</f>
+        <v>196808158.73582876</v>
+      </c>
+      <c r="E16" s="65">
         <v>175291472.11380076</v>
-      </c>
-      <c r="E16" s="65">
-        <v>167943211.24679881</v>
       </c>
       <c r="F16" s="64">
         <f t="shared" si="7"/>
-        <v>7348260.8670019507</v>
+        <v>21516686.622027993</v>
       </c>
       <c r="G16" s="66">
         <f t="shared" si="1"/>
-        <v>0.51275074296840728</v>
+        <v>0.57568989750126853</v>
       </c>
       <c r="H16" s="64">
         <f t="shared" si="4"/>
-        <v>350582944.22760153</v>
+        <v>363338139.20460695</v>
       </c>
       <c r="I16" s="66">
         <f t="shared" si="2"/>
-        <v>1.0255014859368146</v>
+        <v>1.0628121184638804</v>
       </c>
       <c r="J16" s="64">
         <f t="shared" si="5"/>
-        <v>14607622.676150063</v>
+        <v>15139089.13352529</v>
       </c>
       <c r="K16" s="67">
         <f t="shared" si="3"/>
-        <v>13881117.469956562</v>
+        <v>13186974.81976825</v>
       </c>
       <c r="L16" s="68"/>
     </row>
@@ -4460,34 +4460,34 @@
       </c>
       <c r="D17" s="59">
         <f>IFERROR(+VLOOKUP(B17,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>10621962.126144474</v>
+      </c>
+      <c r="E17" s="59">
         <v>9577653.6863288712</v>
-      </c>
-      <c r="E17" s="59">
-        <v>8693363.8308905065</v>
       </c>
       <c r="F17" s="59">
         <f t="shared" ref="F17:F40" si="8">+D17-E17</f>
-        <v>884289.85543836467</v>
+        <v>1044308.4398156032</v>
       </c>
       <c r="G17" s="60">
         <f t="shared" si="1"/>
-        <v>0.32645878269871814</v>
+        <v>0.36205452182121672</v>
       </c>
       <c r="H17" s="59">
         <f t="shared" si="4"/>
-        <v>19155307.372657742</v>
+        <v>19609776.232882109</v>
       </c>
       <c r="I17" s="60">
         <f t="shared" si="2"/>
-        <v>0.65291756539743628</v>
+        <v>0.66840834797763093</v>
       </c>
       <c r="J17" s="59">
         <f t="shared" si="5"/>
-        <v>798137.80719407264</v>
+        <v>817074.00970342115</v>
       </c>
       <c r="K17" s="59">
         <f t="shared" si="3"/>
-        <v>1646697.0371809278</v>
+        <v>1701459.636941412</v>
       </c>
       <c r="L17" s="61" cm="1">
         <f t="array" ref="L17">+_xlfn.IFS(I17&gt;114%,H17*0.02,I17&gt;109%,H17*0.015,I17&gt;104%,H17*0.0125,I17&gt;99%,H17*0.01,I17&lt;99%,H17*0)</f>
@@ -4504,34 +4504,34 @@
       </c>
       <c r="D18" s="4">
         <f>IFERROR(+VLOOKUP(B18,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>10967412.891714148</v>
+      </c>
+      <c r="E18" s="4">
         <v>10073320.978867745</v>
-      </c>
-      <c r="E18" s="4">
-        <v>9146279.4433018658</v>
       </c>
       <c r="F18" s="4">
         <f t="shared" si="8"/>
-        <v>927041.5355658792</v>
+        <v>894091.9128464032</v>
       </c>
       <c r="G18" s="5">
         <f t="shared" si="1"/>
-        <v>0.40358655412596706</v>
+        <v>0.43940825333862665</v>
       </c>
       <c r="H18" s="4">
         <f t="shared" si="4"/>
-        <v>20146641.95773549</v>
+        <v>20247531.492395353</v>
       </c>
       <c r="I18" s="5">
         <f t="shared" si="2"/>
-        <v>0.80717310825193411</v>
+        <v>0.81121523693284936</v>
       </c>
       <c r="J18" s="4">
         <f t="shared" si="5"/>
-        <v>839443.41490564542</v>
+        <v>843647.14551647299</v>
       </c>
       <c r="K18" s="4">
         <f t="shared" si="3"/>
-        <v>1240515.4100943548</v>
+        <v>1272008.4552987141</v>
       </c>
       <c r="L18" s="63" cm="1">
         <f t="array" ref="L18">+_xlfn.IFS(I18&gt;114%,H18*0.02,I18&gt;109%,H18*0.015,I18&gt;104%,H18*0.0125,I18&gt;99%,H18*0.01,I18&lt;99%,H18*0)</f>
@@ -4548,34 +4548,34 @@
       </c>
       <c r="D19" s="4">
         <f>IFERROR(+VLOOKUP(B19,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>12119565.962394305</v>
+      </c>
+      <c r="E19" s="4">
         <v>11260002.931573136</v>
-      </c>
-      <c r="E19" s="4">
-        <v>10467417.738483323</v>
       </c>
       <c r="F19" s="4">
         <f t="shared" si="8"/>
-        <v>792585.19308981299</v>
+        <v>859563.0308211688</v>
       </c>
       <c r="G19" s="5">
         <f t="shared" si="1"/>
-        <v>0.435478024396104</v>
+        <v>0.46872142697607416</v>
       </c>
       <c r="H19" s="4">
         <f t="shared" si="4"/>
-        <v>22520005.863146272</v>
+        <v>22374583.315189485</v>
       </c>
       <c r="I19" s="5">
         <f t="shared" si="2"/>
-        <v>0.870956048792208</v>
+        <v>0.86533186518659844</v>
       </c>
       <c r="J19" s="4">
         <f t="shared" si="5"/>
-        <v>938333.57763109461</v>
+        <v>932274.30479956185</v>
       </c>
       <c r="K19" s="4">
         <f t="shared" si="3"/>
-        <v>1216387.2694939054</v>
+        <v>1248825.8366459722</v>
       </c>
       <c r="L19" s="63" cm="1">
         <f t="array" ref="L19">+_xlfn.IFS(I19&gt;114%,H19*0.02,I19&gt;109%,H19*0.015,I19&gt;104%,H19*0.0125,I19&gt;99%,H19*0.01,I19&lt;99%,H19*0)</f>
@@ -4592,38 +4592,38 @@
       </c>
       <c r="D20" s="4">
         <f>IFERROR(+VLOOKUP(B20,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>23966157.061793938</v>
+      </c>
+      <c r="E20" s="4">
         <v>22295266.235117078</v>
-      </c>
-      <c r="E20" s="4">
-        <v>20445334.936737273</v>
       </c>
       <c r="F20" s="4">
         <f t="shared" si="8"/>
-        <v>1849931.2983798049</v>
+        <v>1670890.8266768605</v>
       </c>
       <c r="G20" s="5">
         <f t="shared" si="1"/>
-        <v>0.66457552880345572</v>
+        <v>0.71438131012947481</v>
       </c>
       <c r="H20" s="4">
         <f t="shared" si="4"/>
-        <v>44590532.470234156</v>
+        <v>44245213.037158042</v>
       </c>
       <c r="I20" s="5">
         <f t="shared" si="2"/>
-        <v>1.3291510576069114</v>
+        <v>1.3188578033159537</v>
       </c>
       <c r="J20" s="4">
         <f t="shared" si="5"/>
-        <v>1857938.8529264231</v>
+        <v>1843550.5432149183</v>
       </c>
       <c r="K20" s="4">
         <f t="shared" si="3"/>
-        <v>937738.64707357681</v>
+        <v>871088.4489278238</v>
       </c>
       <c r="L20" s="63" cm="1">
         <f t="array" ref="L20">+_xlfn.IFS(I20&gt;114%,H20*0.02,I20&gt;109%,H20*0.015,I20&gt;104%,H20*0.0125,I20&gt;99%,H20*0.01,I20&lt;99%,H20*0)</f>
-        <v>891810.64940468315</v>
+        <v>884904.26074316085</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4636,34 +4636,34 @@
       </c>
       <c r="D21" s="4">
         <f>IFERROR(+VLOOKUP(B21,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>12810368.916756971</v>
+      </c>
+      <c r="E21" s="4">
         <v>11678597.247224085</v>
-      </c>
-      <c r="E21" s="4">
-        <v>10980183.446752926</v>
       </c>
       <c r="F21" s="4">
         <f t="shared" ref="F21:F23" si="9">+D21-E21</f>
-        <v>698413.8004711587</v>
+        <v>1131771.6695328858</v>
       </c>
       <c r="G21" s="5">
         <f t="shared" si="1"/>
-        <v>0.45873058742338357</v>
+        <v>0.50318612191982059</v>
       </c>
       <c r="H21" s="4">
         <f t="shared" si="4"/>
-        <v>23357194.49444817</v>
+        <v>23649911.846320562</v>
       </c>
       <c r="I21" s="5">
         <f t="shared" si="2"/>
-        <v>0.91746117484676715</v>
+        <v>0.92895899431351492</v>
       </c>
       <c r="J21" s="4">
         <f t="shared" si="5"/>
-        <v>973216.43726867379</v>
+        <v>985412.99359669001</v>
       </c>
       <c r="K21" s="4">
         <f t="shared" si="3"/>
-        <v>1148326.0627313263</v>
+        <v>1149831.0075675482</v>
       </c>
       <c r="L21" s="63" cm="1">
         <f t="array" ref="L21">+_xlfn.IFS(I21&gt;114%,H21*0.02,I21&gt;109%,H21*0.015,I21&gt;104%,H21*0.0125,I21&gt;99%,H21*0.01,I21&lt;99%,H21*0)</f>
@@ -4680,34 +4680,34 @@
       </c>
       <c r="D22" s="4">
         <f>IFERROR(+VLOOKUP(B22,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>15729400.126823407</v>
+      </c>
+      <c r="E22" s="4">
         <v>15114947.7812881</v>
-      </c>
-      <c r="E22" s="4">
-        <v>14579075.923666339</v>
       </c>
       <c r="F22" s="4">
         <f t="shared" si="9"/>
-        <v>535871.85762176104</v>
+        <v>614452.34553530626</v>
       </c>
       <c r="G22" s="5">
         <f t="shared" si="1"/>
-        <v>0.47616797607446909</v>
+        <v>0.49552514051866031</v>
       </c>
       <c r="H22" s="4">
         <f t="shared" si="4"/>
-        <v>30229895.562576201</v>
+        <v>29038892.541827828</v>
       </c>
       <c r="I22" s="5">
         <f t="shared" si="2"/>
-        <v>0.95233595214893818</v>
+        <v>0.91481564403444982</v>
       </c>
       <c r="J22" s="4">
         <f t="shared" si="5"/>
-        <v>1259578.9817740084</v>
+        <v>1209953.8559094928</v>
       </c>
       <c r="K22" s="4">
         <f t="shared" si="3"/>
-        <v>1385661.868225992</v>
+        <v>1455771.8248342359</v>
       </c>
       <c r="L22" s="63" cm="1">
         <f t="array" ref="L22">+_xlfn.IFS(I22&gt;114%,H22*0.02,I22&gt;109%,H22*0.015,I22&gt;104%,H22*0.0125,I22&gt;99%,H22*0.01,I22&lt;99%,H22*0)</f>
@@ -4724,38 +4724,38 @@
       </c>
       <c r="D23" s="4">
         <f>IFERROR(+VLOOKUP(B23,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>15219121.752963766</v>
+      </c>
+      <c r="E23" s="4">
         <v>14549220.102775784</v>
-      </c>
-      <c r="E23" s="4">
-        <v>13476544.027213015</v>
       </c>
       <c r="F23" s="4">
         <f t="shared" si="9"/>
-        <v>1072676.0755627695</v>
+        <v>669901.65018798225</v>
       </c>
       <c r="G23" s="5">
         <f t="shared" si="1"/>
-        <v>0.53029773352110054</v>
+        <v>0.55471466613104536</v>
       </c>
       <c r="H23" s="4">
         <f t="shared" si="4"/>
-        <v>29098440.205551568</v>
+        <v>28096840.159317724</v>
       </c>
       <c r="I23" s="5">
         <f t="shared" si="2"/>
-        <v>1.0605954670422011</v>
+        <v>1.0240886143957761</v>
       </c>
       <c r="J23" s="4">
         <f t="shared" si="5"/>
-        <v>1212435.0085646487</v>
+        <v>1170701.6733049052</v>
       </c>
       <c r="K23" s="4">
         <f t="shared" si="3"/>
-        <v>1073893.8439353516</v>
+        <v>1110620.4070032944</v>
       </c>
       <c r="L23" s="63" cm="1">
         <f t="array" ref="L23">+_xlfn.IFS(I23&gt;114%,H23*0.02,I23&gt;109%,H23*0.015,I23&gt;104%,H23*0.0125,I23&gt;99%,H23*0.01,I23&lt;99%,H23*0)</f>
-        <v>363730.50256939465</v>
+        <v>280968.40159317723</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4768,38 +4768,38 @@
       </c>
       <c r="D24" s="4">
         <f>IFERROR(+VLOOKUP(B24,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>19950659.881944489</v>
+      </c>
+      <c r="E24" s="4">
         <v>17261217.954442594</v>
-      </c>
-      <c r="E24" s="4">
-        <v>12878412.530010875</v>
       </c>
       <c r="F24" s="4">
         <f t="shared" si="8"/>
-        <v>4382805.4244317189</v>
+        <v>2689441.9275018945</v>
       </c>
       <c r="G24" s="5">
         <f t="shared" si="1"/>
-        <v>0.51535169314203955</v>
+        <v>0.59564779128548306</v>
       </c>
       <c r="H24" s="4">
         <f t="shared" si="4"/>
-        <v>34522435.908885188</v>
+        <v>36831987.474359058</v>
       </c>
       <c r="I24" s="5">
         <f t="shared" si="2"/>
-        <v>1.0307033862840791</v>
+        <v>1.099657460834738</v>
       </c>
       <c r="J24" s="4">
         <f t="shared" si="5"/>
-        <v>1438434.8295368829</v>
+        <v>1534666.1447649607</v>
       </c>
       <c r="K24" s="4">
         <f t="shared" si="3"/>
-        <v>1352736.4204631171</v>
+        <v>1231217.7380050465</v>
       </c>
       <c r="L24" s="63" cm="1">
         <f t="array" ref="L24">+_xlfn.IFS(I24&gt;114%,H24*0.02,I24&gt;109%,H24*0.015,I24&gt;104%,H24*0.0125,I24&gt;99%,H24*0.01,I24&lt;99%,H24*0)</f>
-        <v>345224.3590888519</v>
+        <v>552479.8121153859</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -4815,11 +4815,11 @@
         <v>22089067.174868885</v>
       </c>
       <c r="E25" s="4">
-        <v>20675373.952008072</v>
+        <v>22089067.174868885</v>
       </c>
       <c r="F25" s="4">
         <f t="shared" si="8"/>
-        <v>1413693.2228608131</v>
+        <v>0</v>
       </c>
       <c r="G25" s="5">
         <f t="shared" si="1"/>
@@ -4827,19 +4827,19 @@
       </c>
       <c r="H25" s="4">
         <f t="shared" si="4"/>
-        <v>44178134.349737771</v>
+        <v>40779816.322834864</v>
       </c>
       <c r="I25" s="5">
         <f t="shared" si="2"/>
-        <v>0.81713072903347228</v>
+        <v>0.75427451910782051</v>
       </c>
       <c r="J25" s="4">
         <f t="shared" si="5"/>
-        <v>1840755.5979057404</v>
+        <v>1699159.0134514528</v>
       </c>
       <c r="K25" s="4">
         <f t="shared" si="3"/>
-        <v>2664657.1408442603</v>
+        <v>2906898.6991028297</v>
       </c>
       <c r="L25" s="63" cm="1">
         <f t="array" ref="L25">+_xlfn.IFS(I25&gt;109%,H25*0.015,I25&gt;104%,H25*0.0125,I25&gt;99%,H25*0.01,I25&lt;99%,H25*0)</f>
@@ -4854,34 +4854,34 @@
       </c>
       <c r="D26" s="67">
         <f>+SUM(D17:D25)</f>
+        <v>143473715.8954044</v>
+      </c>
+      <c r="E26" s="65">
         <v>133899294.09248626</v>
-      </c>
-      <c r="E26" s="65">
-        <v>121341985.82906419</v>
       </c>
       <c r="F26" s="67">
         <f>+D26-E26</f>
-        <v>12557308.263422072</v>
+        <v>9574421.8029181361</v>
       </c>
       <c r="G26" s="66">
         <f t="shared" si="1"/>
-        <v>0.46834530388593854</v>
+        <v>0.50183416967280814</v>
       </c>
       <c r="H26" s="64">
         <f t="shared" si="4"/>
-        <v>267798588.18497252</v>
+        <v>264874552.42228505</v>
       </c>
       <c r="I26" s="66">
         <f t="shared" si="2"/>
-        <v>0.93669060777187707</v>
+        <v>0.92646308247287656</v>
       </c>
       <c r="J26" s="64">
         <f t="shared" si="5"/>
-        <v>11158274.507707188</v>
+        <v>11036439.684261877</v>
       </c>
       <c r="K26" s="67">
         <f t="shared" si="3"/>
-        <v>12666613.700042814</v>
+        <v>12947722.054326875</v>
       </c>
       <c r="L26" s="68"/>
     </row>
@@ -4897,34 +4897,34 @@
       </c>
       <c r="D27" s="59">
         <f>IFERROR(+VLOOKUP(B27,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>43692487.08063937</v>
+      </c>
+      <c r="E27" s="59">
         <v>37484101.183935247</v>
-      </c>
-      <c r="E27" s="59">
-        <v>34411101.004763618</v>
       </c>
       <c r="F27" s="59">
         <f t="shared" si="8"/>
-        <v>3073000.1791716293</v>
+        <v>6208385.8967041224</v>
       </c>
       <c r="G27" s="60">
         <f t="shared" si="1"/>
-        <v>0.45724753419448516</v>
+        <v>0.53298015290303791</v>
       </c>
       <c r="H27" s="59">
         <f t="shared" si="4"/>
-        <v>74968202.367870495</v>
+        <v>80663053.071949601</v>
       </c>
       <c r="I27" s="60">
         <f t="shared" si="2"/>
-        <v>0.91449506838897032</v>
+        <v>0.9839633592056084</v>
       </c>
       <c r="J27" s="59">
         <f t="shared" si="5"/>
-        <v>3123675.0986612705</v>
+        <v>3360960.5446645669</v>
       </c>
       <c r="K27" s="59">
         <f t="shared" si="3"/>
-        <v>3707799.9013387295</v>
+        <v>3480473.9017600571</v>
       </c>
       <c r="L27" s="61" cm="1">
         <f t="array" ref="L27">+_xlfn.IFS(I27&gt;114%,H27*0.0125,I27&gt;109%,H27*0.01,I27&gt;104%,H27*0.0075,I27&gt;99%,H27*0.005,I27&lt;99%,H27*0)</f>
@@ -4941,34 +4941,34 @@
       </c>
       <c r="D28" s="4">
         <f>IFERROR(+VLOOKUP(B28,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>7535974.4603506317</v>
+      </c>
+      <c r="E28" s="4">
         <v>7043117.2210489651</v>
-      </c>
-      <c r="E28" s="4">
-        <v>6108215.4389794497</v>
       </c>
       <c r="F28" s="4">
         <f t="shared" si="8"/>
-        <v>934901.78206951544</v>
+        <v>492857.23930166662</v>
       </c>
       <c r="G28" s="5">
         <f t="shared" si="1"/>
-        <v>0.33538653433566501</v>
+        <v>0.35885592668336341</v>
       </c>
       <c r="H28" s="4">
         <f t="shared" si="4"/>
-        <v>14086234.44209793</v>
+        <v>13912568.234493474</v>
       </c>
       <c r="I28" s="5">
         <f t="shared" si="2"/>
-        <v>0.67077306867133002</v>
+        <v>0.66250324926159398</v>
       </c>
       <c r="J28" s="4">
         <f t="shared" si="5"/>
-        <v>586926.43508741376</v>
+        <v>579690.34310389473</v>
       </c>
       <c r="K28" s="4">
         <f t="shared" si="3"/>
-        <v>1163073.5649125862</v>
+        <v>1224002.3217863061</v>
       </c>
       <c r="L28" s="63" cm="1">
         <f t="array" ref="L28">+_xlfn.IFS(I28&gt;114%,H28*0.02,I28&gt;109%,H28*0.015,I28&gt;104%,H28*0.0125,I28&gt;99%,H28*0.01,I28&lt;99%,H28*0)</f>
@@ -4985,34 +4985,34 @@
       </c>
       <c r="D29" s="4">
         <f>IFERROR(+VLOOKUP(B29,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>12850915.177441016</v>
+      </c>
+      <c r="E29" s="4">
         <v>11631494.832822802</v>
-      </c>
-      <c r="E29" s="4">
-        <v>11264156.639444824</v>
       </c>
       <c r="F29" s="4">
         <f t="shared" si="8"/>
-        <v>367338.19337797724</v>
+        <v>1219420.3446182143</v>
       </c>
       <c r="G29" s="5">
         <f t="shared" si="1"/>
-        <v>0.45188929291416768</v>
+        <v>0.4992643728342217</v>
       </c>
       <c r="H29" s="4">
         <f t="shared" si="4"/>
-        <v>23262989.665645603</v>
+        <v>23724766.481429566</v>
       </c>
       <c r="I29" s="5">
         <f t="shared" si="2"/>
-        <v>0.90377858582833537</v>
+        <v>0.92171884215548605</v>
       </c>
       <c r="J29" s="4">
         <f t="shared" si="5"/>
-        <v>969291.2360685668</v>
+        <v>988531.93672623194</v>
       </c>
       <c r="K29" s="4">
         <f t="shared" si="3"/>
-        <v>1175683.7639314332</v>
+        <v>1171707.7111417258</v>
       </c>
       <c r="L29" s="63" cm="1">
         <f t="array" ref="L29">+_xlfn.IFS(I29&gt;114%,H29*0.02,I29&gt;109%,H29*0.015,I29&gt;104%,H29*0.0125,I29&gt;99%,H29*0.01,I29&lt;99%,H29*0)</f>
@@ -5030,34 +5030,34 @@
       </c>
       <c r="D30" s="4">
         <f>IFERROR(+VLOOKUP(B30,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>9642556.4815232344</v>
+      </c>
+      <c r="E30" s="4">
         <v>9187869.5284201782</v>
-      </c>
-      <c r="E30" s="4">
-        <v>9010188.8518341817</v>
       </c>
       <c r="F30" s="4">
         <f t="shared" si="8"/>
-        <v>177680.67658599652</v>
+        <v>454686.95310305618</v>
       </c>
       <c r="G30" s="5">
         <f t="shared" si="1"/>
-        <v>0.24031125566049505</v>
+        <v>0.25220371803108643</v>
       </c>
       <c r="H30" s="4">
         <f t="shared" si="4"/>
-        <v>18375739.056840356</v>
+        <v>17801642.73511982</v>
       </c>
       <c r="I30" s="5">
         <f t="shared" si="2"/>
-        <v>0.4806225113209901</v>
+        <v>0.46560686405739032</v>
       </c>
       <c r="J30" s="4">
         <f t="shared" si="5"/>
-        <v>765655.79403501481</v>
+        <v>741735.11396332574</v>
       </c>
       <c r="K30" s="4">
         <f t="shared" si="3"/>
-        <v>2420444.6319754575</v>
+        <v>2599149.8755093124</v>
       </c>
       <c r="L30" s="63" cm="1">
         <f t="array" ref="L30">+_xlfn.IFS(I30&gt;114%,H30*0.02,I30&gt;109%,H30*0.015,I30&gt;104%,H30*0.0125,I30&gt;99%,H30*0.01,I30&lt;99%,H30*0)</f>
@@ -5075,34 +5075,34 @@
       </c>
       <c r="D31" s="4">
         <f>IFERROR(+VLOOKUP(B31,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>11588903.613097664</v>
+      </c>
+      <c r="E31" s="4">
         <v>10794067.346588679</v>
-      </c>
-      <c r="E31" s="4">
-        <v>9777757.9714250863</v>
       </c>
       <c r="F31" s="4">
         <f t="shared" si="8"/>
-        <v>1016309.3751635924</v>
+        <v>794836.26650898531</v>
       </c>
       <c r="G31" s="5">
         <f t="shared" si="1"/>
-        <v>0.42470828918026299</v>
+        <v>0.45598227887184523</v>
       </c>
       <c r="H31" s="4">
         <f t="shared" si="4"/>
-        <v>21588134.693177357</v>
+        <v>21394898.978026457</v>
       </c>
       <c r="I31" s="5">
         <f t="shared" si="2"/>
-        <v>0.84941657836052598</v>
+        <v>0.84181343791725272</v>
       </c>
       <c r="J31" s="4">
         <f t="shared" si="5"/>
-        <v>899505.61221572326</v>
+        <v>891454.12408443564</v>
       </c>
       <c r="K31" s="4">
         <f t="shared" si="3"/>
-        <v>1218431.8877842769</v>
+        <v>1256940.5806274852</v>
       </c>
       <c r="L31" s="63" cm="1">
         <f t="array" ref="L31">+_xlfn.IFS(I31&gt;114%,H31*0.02,I31&gt;109%,H31*0.015,I31&gt;104%,H31*0.0125,I31&gt;99%,H31*0.01,I31&lt;99%,H31*0)</f>
@@ -5120,34 +5120,34 @@
       </c>
       <c r="D32" s="4">
         <f>IFERROR(+VLOOKUP(B32,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>8419876.3054508269</v>
+      </c>
+      <c r="E32" s="4">
         <v>7991786.3456236413</v>
-      </c>
-      <c r="E32" s="4">
-        <v>7333522.0196865257</v>
       </c>
       <c r="F32" s="4">
         <f t="shared" si="8"/>
-        <v>658264.32593711559</v>
+        <v>428089.95982718561</v>
       </c>
       <c r="G32" s="5">
         <f t="shared" si="1"/>
-        <v>0.31713437879458894</v>
+        <v>0.33412207561312807</v>
       </c>
       <c r="H32" s="4">
         <f t="shared" si="4"/>
-        <v>15983572.691247284</v>
+        <v>15544387.025447682</v>
       </c>
       <c r="I32" s="5">
         <f t="shared" si="2"/>
-        <v>0.634268757589178</v>
+        <v>0.61684075497808255</v>
       </c>
       <c r="J32" s="4">
         <f t="shared" si="5"/>
-        <v>665982.19546863681</v>
+        <v>647682.79272698669</v>
       </c>
       <c r="K32" s="4">
         <f t="shared" si="3"/>
-        <v>1434017.8045313631</v>
+        <v>1525465.7904135613</v>
       </c>
       <c r="L32" s="63" cm="1">
         <f t="array" ref="L32">+_xlfn.IFS(I32&gt;114%,H32*0.02,I32&gt;109%,H32*0.015,I32&gt;104%,H32*0.0125,I32&gt;99%,H32*0.01,I32&lt;99%,H32*0)</f>
@@ -5165,34 +5165,34 @@
       </c>
       <c r="D33" s="4">
         <f>IFERROR(+VLOOKUP(B33,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>10653241.374119855</v>
+      </c>
+      <c r="E33" s="4">
         <v>7538759.4369671568</v>
-      </c>
-      <c r="E33" s="4">
-        <v>6945315.7802029736</v>
       </c>
       <c r="F33" s="4">
         <f t="shared" si="8"/>
-        <v>593443.65676418319</v>
+        <v>3114481.9371526986</v>
       </c>
       <c r="G33" s="5">
         <f t="shared" si="1"/>
-        <v>0.284516381705951</v>
+        <v>0.40205841750855692</v>
       </c>
       <c r="H33" s="4">
         <f t="shared" si="4"/>
-        <v>15077518.873934314</v>
+        <v>19667522.536836654</v>
       </c>
       <c r="I33" s="5">
         <f t="shared" si="2"/>
-        <v>0.56903276341190201</v>
+        <v>0.74226169386195118</v>
       </c>
       <c r="J33" s="4">
         <f t="shared" si="5"/>
-        <v>628229.9530805964</v>
+        <v>819480.10570152733</v>
       </c>
       <c r="K33" s="4">
         <f t="shared" si="3"/>
-        <v>1579832.5469194036</v>
+        <v>1440318.965989104</v>
       </c>
       <c r="L33" s="63" cm="1">
         <f t="array" ref="L33">+_xlfn.IFS(I33&gt;114%,H33*0.02,I33&gt;109%,H33*0.015,I33&gt;104%,H33*0.0125,I33&gt;99%,H33*0.01,I33&lt;99%,H33*0)</f>
@@ -5209,34 +5209,34 @@
       </c>
       <c r="D34" s="4">
         <f>IFERROR(+VLOOKUP(B34,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>7015916.0627130093</v>
+      </c>
+      <c r="E34" s="4">
         <v>6541870.7729290416</v>
-      </c>
-      <c r="E34" s="4">
-        <v>6164880.2550763758</v>
       </c>
       <c r="F34" s="4">
         <f t="shared" si="8"/>
-        <v>376990.51785266586</v>
+        <v>474045.28978396766</v>
       </c>
       <c r="G34" s="5">
         <f t="shared" si="1"/>
-        <v>0.3115176558537639</v>
+        <v>0.3340912410815719</v>
       </c>
       <c r="H34" s="4">
         <f t="shared" si="4"/>
-        <v>13083741.545858083</v>
+        <v>12952460.423470173</v>
       </c>
       <c r="I34" s="5">
         <f t="shared" si="2"/>
-        <v>0.62303531170752779</v>
+        <v>0.61678382968905587</v>
       </c>
       <c r="J34" s="4">
         <f t="shared" si="5"/>
-        <v>545155.8977440868</v>
+        <v>539685.85097792384</v>
       </c>
       <c r="K34" s="4">
         <f t="shared" si="3"/>
-        <v>1204844.1022559132</v>
+        <v>1271280.3579351811</v>
       </c>
       <c r="L34" s="63" cm="1">
         <f t="array" ref="L34">+_xlfn.IFS(I34&gt;114%,H34*0.02,I34&gt;109%,H34*0.015,I34&gt;104%,H34*0.0125,I34&gt;99%,H34*0.01,I34&lt;99%,H34*0)</f>
@@ -5253,34 +5253,34 @@
       </c>
       <c r="D35" s="4">
         <f>IFERROR(+VLOOKUP(B35,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>4297511.625002631</v>
+      </c>
+      <c r="E35" s="4">
         <v>4108217.6743740062</v>
-      </c>
-      <c r="E35" s="4">
-        <v>3882737.6125165834</v>
       </c>
       <c r="F35" s="4">
         <f t="shared" si="8"/>
-        <v>225480.06185742281</v>
+        <v>189293.95062862476</v>
       </c>
       <c r="G35" s="5">
         <f t="shared" si="1"/>
-        <v>0.16660655175049299</v>
+        <v>0.17428326581026315</v>
       </c>
       <c r="H35" s="4">
         <f t="shared" si="4"/>
-        <v>8216435.3487480134</v>
+        <v>7933867.6153894728</v>
       </c>
       <c r="I35" s="5">
         <f t="shared" si="2"/>
-        <v>0.33321310350098604</v>
+        <v>0.32175372149587045</v>
       </c>
       <c r="J35" s="4">
         <f t="shared" si="5"/>
-        <v>342351.47286450054</v>
+        <v>330577.8173078947</v>
       </c>
       <c r="K35" s="4">
         <f t="shared" si="3"/>
-        <v>1712498.5271354995</v>
+        <v>1850971.6704543063</v>
       </c>
       <c r="L35" s="63" cm="1">
         <f t="array" ref="L35">+_xlfn.IFS(I35&gt;114%,H35*0.02,I35&gt;109%,H35*0.015,I35&gt;104%,H35*0.0125,I35&gt;99%,H35*0.01,I35&lt;99%,H35*0)</f>
@@ -5297,34 +5297,34 @@
       </c>
       <c r="D36" s="4">
         <f>IFERROR(+VLOOKUP(B36,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>7669142.5805392843</v>
+      </c>
+      <c r="E36" s="4">
         <v>7127555.5584793668</v>
-      </c>
-      <c r="E36" s="4">
-        <v>6557112.931111577</v>
       </c>
       <c r="F36" s="4">
         <f t="shared" si="8"/>
-        <v>570442.62736778986</v>
+        <v>541587.02205991745</v>
       </c>
       <c r="G36" s="5">
         <f t="shared" si="1"/>
-        <v>0.28244721848541182</v>
+        <v>0.30390895900690645</v>
       </c>
       <c r="H36" s="4">
         <f t="shared" si="4"/>
-        <v>14255111.116958734</v>
+        <v>14158417.07176483</v>
       </c>
       <c r="I36" s="5">
         <f t="shared" si="2"/>
-        <v>0.56489443697082364</v>
+        <v>0.56106269355121186</v>
       </c>
       <c r="J36" s="4">
         <f t="shared" si="5"/>
-        <v>593962.9632066139</v>
+        <v>589934.04465686798</v>
       </c>
       <c r="K36" s="4">
         <f t="shared" si="3"/>
-        <v>1508953.7034600526</v>
+        <v>1596896.1290418832</v>
       </c>
       <c r="L36" s="63" cm="1">
         <f t="array" ref="L36">+_xlfn.IFS(I36&gt;114%,H36*0.02,I36&gt;109%,H36*0.015,I36&gt;104%,H36*0.0125,I36&gt;99%,H36*0.01,I36&lt;99%,H36*0)</f>
@@ -5341,34 +5341,34 @@
       </c>
       <c r="D37" s="4">
         <f>IFERROR(+VLOOKUP(B37,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>35141605.525244027</v>
+      </c>
+      <c r="E37" s="4">
         <v>34463405.027844027</v>
-      </c>
-      <c r="E37" s="4">
-        <v>33451176.522885799</v>
       </c>
       <c r="F37" s="4">
         <f t="shared" si="8"/>
-        <v>1012228.5049582273</v>
+        <v>678200.49740000069</v>
       </c>
       <c r="G37" s="5">
         <f t="shared" si="1"/>
-        <v>0.282459722345135</v>
+        <v>0.28801820746972345</v>
       </c>
       <c r="H37" s="4">
         <f t="shared" si="4"/>
-        <v>68926810.055688053</v>
+        <v>64876810.200450517</v>
       </c>
       <c r="I37" s="5">
         <f t="shared" si="2"/>
-        <v>0.56491944469027</v>
+        <v>0.53172592148256637</v>
       </c>
       <c r="J37" s="4">
         <f t="shared" si="5"/>
-        <v>2871950.4189870022</v>
+        <v>2703200.4250187716</v>
       </c>
       <c r="K37" s="4">
         <f t="shared" si="3"/>
-        <v>7295695.4143463308</v>
+        <v>7897285.8613414522</v>
       </c>
       <c r="L37" s="63" cm="1">
         <f t="array" ref="L37">+_xlfn.IFS(I37&gt;114%,H37*0.0125,I37&gt;109%,H37*0.01,I37&gt;104%,H37*0.0075,I37&gt;99%,H37*0.005,I37&lt;99%,H37*0)</f>
@@ -5385,34 +5385,34 @@
       </c>
       <c r="D38" s="4">
         <f>IFERROR(+VLOOKUP(B38,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>4784668.386799518</v>
+      </c>
+      <c r="E38" s="4">
         <v>4941053.6803995185</v>
-      </c>
-      <c r="E38" s="4">
-        <v>4955958.0088995183</v>
       </c>
       <c r="F38" s="4">
         <f t="shared" ref="F38" si="10">+D38-E38</f>
-        <v>-14904.328499999829</v>
+        <v>-156385.29360000044</v>
       </c>
       <c r="G38" s="5">
         <f t="shared" si="1"/>
-        <v>0.13840486499718538</v>
+        <v>0.1340243245602106</v>
       </c>
       <c r="H38" s="4">
         <f t="shared" si="4"/>
-        <v>9882107.3607990369</v>
+        <v>8833233.9448606484</v>
       </c>
       <c r="I38" s="5">
         <f t="shared" si="2"/>
-        <v>0.27680972999437076</v>
+        <v>0.24742952226500414</v>
       </c>
       <c r="J38" s="4">
         <f t="shared" si="5"/>
-        <v>411754.47336662654</v>
+        <v>368051.41436919372</v>
       </c>
       <c r="K38" s="4">
         <f t="shared" si="3"/>
-        <v>2563245.5266333735</v>
+        <v>2810484.6921091345</v>
       </c>
       <c r="L38" s="63" cm="1">
         <f t="array" ref="L38">+_xlfn.IFS(I38&gt;109%,H38*0.015,I38&gt;104%,H38*0.0125,I38&gt;99%,H38*0.01,I38&lt;99%,H38*0)</f>
@@ -5429,34 +5429,34 @@
       </c>
       <c r="D39" s="4">
         <f>IFERROR(+VLOOKUP(B39,COMISIONES!A:E,5,FALSE),"0")*1</f>
+        <v>12792718.437014684</v>
+      </c>
+      <c r="E39" s="4">
         <v>11258463.913889455</v>
-      </c>
-      <c r="E39" s="4">
-        <v>11259066.488129456</v>
       </c>
       <c r="F39" s="4">
         <f t="shared" si="8"/>
-        <v>-602.57424000091851</v>
+        <v>1534254.5231252294</v>
       </c>
       <c r="G39" s="5">
         <f t="shared" si="1"/>
-        <v>0.30962656347550455</v>
+        <v>0.35182112564006007</v>
       </c>
       <c r="H39" s="4">
         <f t="shared" si="4"/>
-        <v>22516927.827778909</v>
+        <v>23617326.345257878</v>
       </c>
       <c r="I39" s="5">
         <f t="shared" si="2"/>
-        <v>0.61925312695100909</v>
+        <v>0.64951592425857241</v>
       </c>
       <c r="J39" s="4">
         <f t="shared" si="5"/>
-        <v>938205.32615745452</v>
+        <v>984055.26438574493</v>
       </c>
       <c r="K39" s="4">
         <f t="shared" si="3"/>
-        <v>2091913.6520925455</v>
+        <v>2142609.9365441198</v>
       </c>
       <c r="L39" s="63" cm="1">
         <f t="array" ref="L39">+_xlfn.IFS(I39&gt;114%,H39*0.02,I39&gt;109%,H39*0.015,I39&gt;104%,H39*0.0125,I39&gt;99%,H39*0.01,I39&lt;99%,H39*0)</f>
@@ -5471,34 +5471,34 @@
       </c>
       <c r="D40" s="67">
         <f>+SUM(D27:D39)</f>
+        <v>176085517.10993576</v>
+      </c>
+      <c r="E40" s="65">
         <v>160111762.52332208</v>
-      </c>
-      <c r="E40" s="65">
-        <v>151121189.52495596</v>
       </c>
       <c r="F40" s="67">
         <f t="shared" si="8"/>
-        <v>8990572.9983661175</v>
+        <v>15973754.586613685</v>
       </c>
       <c r="G40" s="66">
         <f t="shared" si="1"/>
-        <v>0.31454350914660889</v>
+        <v>0.345924344275373</v>
       </c>
       <c r="H40" s="64">
         <f t="shared" si="4"/>
-        <v>320223525.04664415</v>
+        <v>325080954.66449678</v>
       </c>
       <c r="I40" s="66">
         <f t="shared" si="2"/>
-        <v>0.62908701829321778</v>
+        <v>0.63862955866222704</v>
       </c>
       <c r="J40" s="64">
         <f t="shared" si="5"/>
-        <v>13342646.876943506</v>
+        <v>13545039.777687367</v>
       </c>
       <c r="K40" s="67">
         <f t="shared" si="3"/>
-        <v>29076435.027316969</v>
+        <v>30267587.794653632</v>
       </c>
       <c r="L40" s="68"/>
     </row>
@@ -5512,34 +5512,34 @@
       </c>
       <c r="D41" s="81">
         <f>+D40+D26+D10+D16</f>
+        <v>662262147.98398674</v>
+      </c>
+      <c r="E41" s="82">
         <v>605891870.63702166</v>
-      </c>
-      <c r="E41" s="82">
-        <v>566825570.63776278</v>
       </c>
       <c r="F41" s="81">
         <f>+D41-E41</f>
-        <v>39066299.999258876</v>
+        <v>56370277.346965075</v>
       </c>
       <c r="G41" s="83">
         <f t="shared" si="1"/>
-        <v>0.43912617568370266</v>
+        <v>0.47998109636051739</v>
       </c>
       <c r="H41" s="81">
         <f t="shared" si="4"/>
-        <v>1211783741.2740433</v>
+        <v>1222637811.6627448</v>
       </c>
       <c r="I41" s="83">
         <f t="shared" si="2"/>
-        <v>0.87825235136740532</v>
+        <v>0.88611894712710904</v>
       </c>
       <c r="J41" s="81">
         <f t="shared" si="5"/>
-        <v>50490989.219751805</v>
+        <v>50943242.152614363</v>
       </c>
       <c r="K41" s="81">
         <f t="shared" si="3"/>
-        <v>64489606.371342868</v>
+        <v>65227727.191740848</v>
       </c>
       <c r="L41" s="84"/>
     </row>
@@ -5590,11 +5590,11 @@
         <v>11698187.310080834</v>
       </c>
       <c r="E43" s="4">
-        <v>10831277.641265372</v>
+        <v>11698187.310080834</v>
       </c>
       <c r="F43" s="4">
         <f t="shared" ref="F43" si="11">+D43-E43</f>
-        <v>866909.66881546192</v>
+        <v>0</v>
       </c>
       <c r="G43" s="5">
         <f>+D43/C43</f>
@@ -5602,19 +5602,19 @@
       </c>
       <c r="H43" s="4">
         <f t="shared" ref="H43" si="12">+D43/$N$3*$N$4</f>
-        <v>23396374.620161667</v>
+        <v>21596653.495533846</v>
       </c>
       <c r="I43" s="5">
         <f>+H43/C43</f>
-        <v>0.58490936550404171</v>
+        <v>0.53991633738834621</v>
       </c>
       <c r="J43" s="4">
         <f t="shared" ref="J43" si="13">+D43/$N$3</f>
-        <v>974848.94250673614</v>
+        <v>899860.56231391034</v>
       </c>
       <c r="K43" s="4">
         <f>+(C43-D43)/$N$2</f>
-        <v>2358484.3908265973</v>
+        <v>2572892.0627199244</v>
       </c>
       <c r="L43" s="4" cm="1">
         <f t="array" ref="L43">+_xlfn.IFS(I43&gt;114%,H43*0.02,I43&gt;109%,H43*0.015,I43&gt;104%,H43*0.0125,I43&gt;99%,H43*0.01,I43&lt;99%,H43*0)</f>
@@ -5633,11 +5633,11 @@
         <v>18973242.700626545</v>
       </c>
       <c r="E44" s="4">
-        <v>16443269.938349089</v>
+        <v>18973242.700626545</v>
       </c>
       <c r="F44" s="4">
         <f t="shared" ref="F44" si="14">+D44-E44</f>
-        <v>2529972.762277456</v>
+        <v>0</v>
       </c>
       <c r="G44" s="5">
         <f>+D44/C44</f>
@@ -5645,23 +5645,23 @@
       </c>
       <c r="H44" s="4">
         <f t="shared" ref="H44" si="15">+D44/$N$3*$N$4</f>
-        <v>37946485.401253089</v>
+        <v>35027524.985772081</v>
       </c>
       <c r="I44" s="5">
         <f>+H44/C44</f>
-        <v>1.2648828467084363</v>
+        <v>1.1675841661924027</v>
       </c>
       <c r="J44" s="4">
         <f t="shared" ref="J44" si="16">+D44/$N$3</f>
-        <v>1581103.5583855454</v>
+        <v>1459480.2077405034</v>
       </c>
       <c r="K44" s="4">
         <f>+(C44-D44)/$N$2</f>
-        <v>918896.44161445461</v>
+        <v>1002432.4817612232</v>
       </c>
       <c r="L44" s="4" cm="1">
         <f t="array" ref="L44">+_xlfn.IFS(I44&gt;114%,H44*0.02,I44&gt;109%,H44*0.015,I44&gt;104%,H44*0.0125,I44&gt;99%,H44*0.01,I44&lt;99%,H44*0)</f>
-        <v>758929.70802506176</v>
+        <v>700550.49971544161</v>
       </c>
     </row>
   </sheetData>
@@ -5799,26 +5799,26 @@
       </c>
       <c r="D2" s="22">
         <f>H2/G2</f>
-        <v>0.68493150684931503</v>
+        <v>0.72972972972972971</v>
       </c>
       <c r="E2" s="13">
         <v>33</v>
       </c>
       <c r="F2" s="12">
         <f>+H2-E2</f>
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G2" s="13">
         <f>VLOOKUP(B2,'Base Cobertura'!$A:$C,3,FALSE)</f>
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H2" s="13">
         <f>VLOOKUP(B2,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="I2" s="17">
         <f>(+G2*$M$2)-H2</f>
-        <v>12.049999999999997</v>
+        <v>8.8999999999999986</v>
       </c>
       <c r="J2" t="s">
         <v>55</v>
@@ -5902,14 +5902,14 @@
         <v>145 - ALMACEN</v>
       </c>
       <c r="S3" s="12">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="T3" s="12">
         <v>214</v>
       </c>
       <c r="U3" s="41">
         <f>+S3/T3</f>
-        <v>0.2102803738317757</v>
+        <v>0.25233644859813081</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
@@ -5923,14 +5923,14 @@
       </c>
       <c r="D4" s="22">
         <f t="shared" si="0"/>
-        <v>0.78854625550660795</v>
+        <v>0.80616740088105732</v>
       </c>
       <c r="E4" s="13">
         <v>126</v>
       </c>
       <c r="F4" s="12">
         <f t="shared" si="1"/>
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G4" s="13">
         <f>VLOOKUP(B4,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -5938,11 +5938,11 @@
       </c>
       <c r="H4" s="13">
         <f>VLOOKUP(B4,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="I4" s="17">
         <f t="shared" si="2"/>
-        <v>13.949999999999989</v>
+        <v>9.9499999999999886</v>
       </c>
       <c r="J4" t="s">
         <v>57</v>
@@ -5960,14 +5960,14 @@
         <v>145 - Articulos Sin Asociar Agrupacion</v>
       </c>
       <c r="S4" s="13">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="T4" s="13">
         <v>214</v>
       </c>
       <c r="U4" s="5">
         <f t="shared" ref="U4:U11" si="3">+S4/T4</f>
-        <v>0.11682242990654206</v>
+        <v>0.13551401869158877</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
@@ -5981,14 +5981,14 @@
       </c>
       <c r="D5" s="22">
         <f t="shared" si="0"/>
-        <v>0.67692307692307696</v>
+        <v>0.70769230769230773</v>
       </c>
       <c r="E5" s="13">
         <v>21</v>
       </c>
       <c r="F5" s="12">
         <f t="shared" si="1"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G5" s="13">
         <f>VLOOKUP(B5,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -5996,11 +5996,11 @@
       </c>
       <c r="H5" s="13">
         <f>VLOOKUP(B5,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I5" s="17">
         <f t="shared" si="2"/>
-        <v>11.25</v>
+        <v>9.25</v>
       </c>
       <c r="K5" t="s">
         <v>64</v>
@@ -6015,14 +6015,14 @@
         <v>145 - BEBIDAS</v>
       </c>
       <c r="S5" s="13">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="T5" s="13">
         <v>214</v>
       </c>
       <c r="U5" s="5">
         <f t="shared" si="3"/>
-        <v>0.30841121495327101</v>
+        <v>0.35046728971962615</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
@@ -6036,14 +6036,14 @@
       </c>
       <c r="D6" s="22">
         <f t="shared" si="0"/>
-        <v>0.72946859903381644</v>
+        <v>0.7874396135265701</v>
       </c>
       <c r="E6" s="13">
         <v>100</v>
       </c>
       <c r="F6" s="12">
         <f t="shared" si="1"/>
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="G6" s="13">
         <f>VLOOKUP(B6,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6051,11 +6051,11 @@
       </c>
       <c r="H6" s="13">
         <f>VLOOKUP(B6,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="I6" s="17">
         <f t="shared" si="2"/>
-        <v>24.949999999999989</v>
+        <v>12.949999999999989</v>
       </c>
       <c r="J6" t="s">
         <v>58</v>
@@ -6073,14 +6073,14 @@
         <v>145 - CHOCOLATE</v>
       </c>
       <c r="S6" s="13">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="T6" s="13">
         <v>214</v>
       </c>
       <c r="U6" s="5">
         <f t="shared" si="3"/>
-        <v>0.14953271028037382</v>
+        <v>0.17289719626168223</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
@@ -6094,14 +6094,14 @@
       </c>
       <c r="D7" s="22">
         <f t="shared" si="0"/>
-        <v>0.59595959595959591</v>
+        <v>0.64141414141414144</v>
       </c>
       <c r="E7" s="13">
         <v>81</v>
       </c>
       <c r="F7" s="12">
         <f t="shared" si="1"/>
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="G7" s="13">
         <f>VLOOKUP(B7,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6109,11 +6109,11 @@
       </c>
       <c r="H7" s="13">
         <f>VLOOKUP(B7,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="I7" s="17">
         <f t="shared" si="2"/>
-        <v>50.299999999999983</v>
+        <v>41.299999999999983</v>
       </c>
       <c r="J7" t="s">
         <v>58</v>
@@ -6131,14 +6131,14 @@
         <v>145 - GALLETITAS</v>
       </c>
       <c r="S7" s="13">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="T7" s="13">
         <v>214</v>
       </c>
       <c r="U7" s="5">
         <f t="shared" si="3"/>
-        <v>0.31775700934579437</v>
+        <v>0.3364485981308411</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
@@ -6152,14 +6152,14 @@
       </c>
       <c r="D8" s="22">
         <f t="shared" si="0"/>
-        <v>0.7429906542056075</v>
+        <v>0.75233644859813087</v>
       </c>
       <c r="E8" s="13">
         <v>89</v>
       </c>
       <c r="F8" s="12">
         <f t="shared" si="1"/>
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G8" s="13">
         <f>VLOOKUP(B8,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6167,11 +6167,11 @@
       </c>
       <c r="H8" s="13">
         <f>VLOOKUP(B8,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I8" s="17">
         <f t="shared" si="2"/>
-        <v>22.900000000000006</v>
+        <v>20.900000000000006</v>
       </c>
       <c r="J8" t="s">
         <v>55</v>
@@ -6190,14 +6190,14 @@
         <v>145 - GOLOSINAS</v>
       </c>
       <c r="S8" s="13">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="T8" s="13">
         <v>214</v>
       </c>
       <c r="U8" s="5">
         <f t="shared" si="3"/>
-        <v>0.28037383177570091</v>
+        <v>0.30373831775700932</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
@@ -6211,14 +6211,14 @@
       </c>
       <c r="D9" s="22">
         <f>H9/G9</f>
-        <v>0.66867469879518071</v>
+        <v>0.69277108433734935</v>
       </c>
       <c r="E9" s="13">
         <v>92</v>
       </c>
       <c r="F9" s="12">
         <f t="shared" si="1"/>
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G9" s="13">
         <f>VLOOKUP(B9,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6226,11 +6226,11 @@
       </c>
       <c r="H9" s="13">
         <f>VLOOKUP(B9,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="I9" s="17">
         <f t="shared" si="2"/>
-        <v>30.099999999999994</v>
+        <v>26.099999999999994</v>
       </c>
       <c r="J9" t="s">
         <v>55</v>
@@ -6269,14 +6269,14 @@
       </c>
       <c r="D10" s="22">
         <f t="shared" si="0"/>
-        <v>0.57435897435897432</v>
+        <v>0.64102564102564108</v>
       </c>
       <c r="E10" s="13">
         <v>64</v>
       </c>
       <c r="F10" s="12">
         <f t="shared" si="1"/>
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G10" s="13">
         <f>VLOOKUP(B10,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6284,11 +6284,11 @@
       </c>
       <c r="H10" s="13">
         <f>VLOOKUP(B10,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="I10" s="17">
         <f t="shared" si="2"/>
-        <v>53.75</v>
+        <v>40.75</v>
       </c>
       <c r="J10" t="s">
         <v>58</v>
@@ -6306,14 +6306,14 @@
         <v>145 - NO PERECEDEROS</v>
       </c>
       <c r="S10" s="13">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T10" s="13">
         <v>214</v>
       </c>
       <c r="U10" s="5">
         <f t="shared" si="3"/>
-        <v>7.9439252336448593E-2</v>
+        <v>8.4112149532710276E-2</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
@@ -6327,14 +6327,14 @@
       </c>
       <c r="D11" s="32">
         <f t="shared" si="0"/>
-        <v>0.31683168316831684</v>
+        <v>0.37623762376237624</v>
       </c>
       <c r="E11" s="31">
         <v>19</v>
       </c>
       <c r="F11" s="33">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G11" s="13">
         <f>VLOOKUP(B11,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6342,11 +6342,11 @@
       </c>
       <c r="H11" s="13">
         <f>VLOOKUP(B11,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="I11" s="34">
         <f t="shared" si="2"/>
-        <v>53.849999999999994</v>
+        <v>47.849999999999994</v>
       </c>
       <c r="J11" t="s">
         <v>59</v>
@@ -6382,14 +6382,14 @@
       </c>
       <c r="D12" s="32">
         <f t="shared" si="0"/>
-        <v>0.40952380952380951</v>
+        <v>0.44761904761904764</v>
       </c>
       <c r="E12" s="31">
         <v>24</v>
       </c>
       <c r="F12" s="33">
         <f t="shared" si="1"/>
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G12" s="13">
         <f>VLOOKUP(B12,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6397,11 +6397,11 @@
       </c>
       <c r="H12" s="13">
         <f>VLOOKUP(B12,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I12" s="34">
         <f t="shared" si="2"/>
-        <v>46.25</v>
+        <v>42.25</v>
       </c>
       <c r="J12" t="s">
         <v>59</v>
@@ -6418,14 +6418,14 @@
       </c>
       <c r="D13" s="22">
         <f t="shared" si="0"/>
-        <v>0.72796934865900387</v>
+        <v>0.74712643678160917</v>
       </c>
       <c r="E13" s="13">
         <v>144</v>
       </c>
       <c r="F13" s="12">
         <f t="shared" si="1"/>
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="G13" s="13">
         <f>VLOOKUP(B13,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6433,11 +6433,11 @@
       </c>
       <c r="H13" s="13">
         <f>VLOOKUP(B13,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="I13" s="17">
         <f t="shared" si="2"/>
-        <v>31.849999999999994</v>
+        <v>26.849999999999994</v>
       </c>
       <c r="J13" t="s">
         <v>57</v>
@@ -6457,14 +6457,14 @@
       </c>
       <c r="D14" s="22">
         <f t="shared" si="0"/>
-        <v>0.59340659340659341</v>
+        <v>0.63736263736263732</v>
       </c>
       <c r="E14" s="13">
         <v>85</v>
       </c>
       <c r="F14" s="12">
         <f t="shared" si="1"/>
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G14" s="13">
         <f>VLOOKUP(B14,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6472,11 +6472,11 @@
       </c>
       <c r="H14" s="13">
         <f>VLOOKUP(B14,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="I14" s="17">
         <f t="shared" si="2"/>
-        <v>46.699999999999989</v>
+        <v>38.699999999999989</v>
       </c>
       <c r="J14" t="s">
         <v>55</v>
@@ -6492,15 +6492,15 @@
       <c r="E15" s="14"/>
       <c r="F15" s="16">
         <f>+SUM(F2:F14)</f>
-        <v>500</v>
+        <v>573</v>
       </c>
       <c r="G15" s="8">
         <f>+SUM(G2:G14)</f>
-        <v>2235</v>
+        <v>2236</v>
       </c>
       <c r="H15" s="8">
         <f>+SUM(H2:H14)</f>
-        <v>1379</v>
+        <v>1452</v>
       </c>
       <c r="I15" s="8"/>
     </row>
@@ -6517,26 +6517,26 @@
       </c>
       <c r="D16" s="22">
         <f t="shared" si="0"/>
-        <v>0.75</v>
+        <v>0.75776397515527949</v>
       </c>
       <c r="E16" s="13">
         <v>90</v>
       </c>
       <c r="F16" s="12">
         <f t="shared" si="1"/>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G16" s="13">
         <f>VLOOKUP(B16,'Base Cobertura'!$A:$C,3,FALSE)</f>
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H16" s="13">
         <f>VLOOKUP(B16,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="I16" s="17">
         <f t="shared" si="2"/>
-        <v>16</v>
+        <v>14.849999999999994</v>
       </c>
       <c r="J16" t="s">
         <v>55</v>
@@ -6556,14 +6556,14 @@
       </c>
       <c r="D17" s="22">
         <f t="shared" si="0"/>
-        <v>0.43069306930693069</v>
+        <v>0.51485148514851486</v>
       </c>
       <c r="E17" s="13">
         <v>92</v>
       </c>
       <c r="F17" s="12">
         <f t="shared" si="1"/>
-        <v>-5</v>
+        <v>12</v>
       </c>
       <c r="G17" s="13">
         <f>VLOOKUP(B17,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6571,11 +6571,11 @@
       </c>
       <c r="H17" s="13">
         <f>VLOOKUP(B17,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="I17" s="17">
         <f t="shared" si="2"/>
-        <v>84.699999999999989</v>
+        <v>67.699999999999989</v>
       </c>
       <c r="J17" t="s">
         <v>55</v>
@@ -6595,14 +6595,14 @@
       </c>
       <c r="D18" s="22">
         <f t="shared" si="0"/>
-        <v>0.78947368421052633</v>
+        <v>0.82456140350877194</v>
       </c>
       <c r="E18" s="13">
         <v>88</v>
       </c>
       <c r="F18" s="12">
         <f t="shared" si="1"/>
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G18" s="13">
         <f>VLOOKUP(B18,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6610,11 +6610,11 @@
       </c>
       <c r="H18" s="13">
         <f>VLOOKUP(B18,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="I18" s="17">
         <f t="shared" si="2"/>
-        <v>10.349999999999994</v>
+        <v>4.3499999999999943</v>
       </c>
       <c r="J18" t="s">
         <v>58</v>
@@ -6634,14 +6634,14 @@
       </c>
       <c r="D19" s="22">
         <f t="shared" si="0"/>
-        <v>0.74025974025974028</v>
+        <v>0.77272727272727271</v>
       </c>
       <c r="E19" s="13">
         <v>95</v>
       </c>
       <c r="F19" s="12">
         <f t="shared" si="1"/>
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G19" s="13">
         <f>VLOOKUP(B19,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6649,11 +6649,11 @@
       </c>
       <c r="H19" s="13">
         <f>VLOOKUP(B19,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="I19" s="17">
         <f t="shared" si="2"/>
-        <v>16.900000000000006</v>
+        <v>11.900000000000006</v>
       </c>
       <c r="J19" t="s">
         <v>58</v>
@@ -6673,14 +6673,14 @@
       </c>
       <c r="D20" s="22">
         <f t="shared" si="0"/>
-        <v>0.76836158192090398</v>
+        <v>0.78531073446327682</v>
       </c>
       <c r="E20" s="13">
         <v>83</v>
       </c>
       <c r="F20" s="12">
         <f t="shared" si="1"/>
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G20" s="13">
         <f>VLOOKUP(B20,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6688,11 +6688,11 @@
       </c>
       <c r="H20" s="13">
         <f>VLOOKUP(B20,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="I20" s="17">
         <f t="shared" si="2"/>
-        <v>14.449999999999989</v>
+        <v>11.449999999999989</v>
       </c>
       <c r="J20" t="s">
         <v>55</v>
@@ -6712,14 +6712,14 @@
       </c>
       <c r="D21" s="22">
         <f t="shared" si="0"/>
-        <v>0.70414201183431957</v>
+        <v>0.74556213017751483</v>
       </c>
       <c r="E21" s="13">
         <v>64</v>
       </c>
       <c r="F21" s="12">
         <f t="shared" si="1"/>
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="G21" s="13">
         <f>VLOOKUP(B21,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6727,11 +6727,11 @@
       </c>
       <c r="H21" s="13">
         <f>VLOOKUP(B21,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="I21" s="17">
         <f t="shared" si="2"/>
-        <v>24.650000000000006</v>
+        <v>17.650000000000006</v>
       </c>
       <c r="J21" t="s">
         <v>58</v>
@@ -6751,14 +6751,14 @@
       </c>
       <c r="D22" s="22">
         <f t="shared" si="0"/>
-        <v>0.34848484848484851</v>
+        <v>0.35858585858585856</v>
       </c>
       <c r="E22" s="13">
         <v>66</v>
       </c>
       <c r="F22" s="12">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G22" s="13">
         <f>VLOOKUP(B22,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6766,11 +6766,11 @@
       </c>
       <c r="H22" s="13">
         <f>VLOOKUP(B22,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I22" s="17">
         <f t="shared" si="2"/>
-        <v>99.299999999999983</v>
+        <v>97.299999999999983</v>
       </c>
       <c r="J22" t="s">
         <v>58</v>
@@ -6790,14 +6790,14 @@
       </c>
       <c r="D23" s="22">
         <f t="shared" si="0"/>
-        <v>0.63043478260869568</v>
+        <v>0.71014492753623193</v>
       </c>
       <c r="E23" s="13">
         <v>70</v>
       </c>
       <c r="F23" s="12">
         <f t="shared" si="1"/>
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="G23" s="13">
         <f>VLOOKUP(B23,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6805,11 +6805,11 @@
       </c>
       <c r="H23" s="13">
         <f>VLOOKUP(B23,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="I23" s="17">
         <f t="shared" si="2"/>
-        <v>30.299999999999997</v>
+        <v>19.299999999999997</v>
       </c>
       <c r="J23" t="s">
         <v>58</v>
@@ -6829,14 +6829,14 @@
       </c>
       <c r="D24" s="22">
         <f t="shared" si="0"/>
-        <v>0.69411764705882351</v>
+        <v>0.74117647058823533</v>
       </c>
       <c r="E24" s="13">
         <v>79</v>
       </c>
       <c r="F24" s="12">
         <f t="shared" si="1"/>
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="G24" s="13">
         <f>VLOOKUP(B24,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6844,11 +6844,11 @@
       </c>
       <c r="H24" s="13">
         <f>VLOOKUP(B24,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="I24" s="17">
         <f t="shared" si="2"/>
-        <v>26.5</v>
+        <v>18.5</v>
       </c>
       <c r="J24" t="s">
         <v>60</v>
@@ -6864,15 +6864,15 @@
       <c r="E25" s="14"/>
       <c r="F25" s="16">
         <f>+SUM(F16:F24)</f>
-        <v>258</v>
+        <v>319</v>
       </c>
       <c r="G25" s="8">
         <f>+SUM(G16:G24)</f>
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="H25" s="8">
         <f>+SUM(H16:H24)</f>
-        <v>985</v>
+        <v>1046</v>
       </c>
       <c r="I25" s="8"/>
     </row>
@@ -6889,26 +6889,26 @@
       </c>
       <c r="D26" s="22">
         <f t="shared" si="0"/>
-        <v>0.57894736842105265</v>
+        <v>0.67241379310344829</v>
       </c>
       <c r="E26" s="13">
         <v>20</v>
       </c>
       <c r="F26" s="12">
         <f>+H26-E26</f>
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G26" s="13">
         <f>VLOOKUP(B26,'Base Cobertura'!$A:$C,3,FALSE)</f>
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H26" s="13">
         <f>VLOOKUP(B26,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="I26" s="17">
         <f t="shared" si="2"/>
-        <v>15.449999999999996</v>
+        <v>10.299999999999997</v>
       </c>
       <c r="J26" t="s">
         <v>55</v>
@@ -6928,14 +6928,14 @@
       </c>
       <c r="D27" s="22">
         <f t="shared" si="0"/>
-        <v>0.63124999999999998</v>
+        <v>0.65</v>
       </c>
       <c r="E27" s="13">
         <v>68</v>
       </c>
       <c r="F27" s="12">
         <f t="shared" si="1"/>
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G27" s="13">
         <f>VLOOKUP(B27,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6943,11 +6943,11 @@
       </c>
       <c r="H27" s="13">
         <f>VLOOKUP(B27,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="I27" s="17">
         <f t="shared" si="2"/>
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J27" t="s">
         <v>58</v>
@@ -6967,14 +6967,14 @@
       </c>
       <c r="D28" s="22">
         <f t="shared" si="0"/>
-        <v>0.68944099378881984</v>
+        <v>0.70186335403726707</v>
       </c>
       <c r="E28" s="13">
         <v>80</v>
       </c>
       <c r="F28" s="12">
         <f t="shared" si="1"/>
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G28" s="13">
         <f>VLOOKUP(B28,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -6982,11 +6982,11 @@
       </c>
       <c r="H28" s="13">
         <f>VLOOKUP(B28,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="I28" s="17">
         <f t="shared" si="2"/>
-        <v>25.849999999999994</v>
+        <v>23.849999999999994</v>
       </c>
       <c r="J28" t="s">
         <v>58</v>
@@ -7006,14 +7006,14 @@
       </c>
       <c r="D29" s="22">
         <f t="shared" si="0"/>
-        <v>0.34799999999999998</v>
+        <v>0.38</v>
       </c>
       <c r="E29" s="13">
         <v>68</v>
       </c>
       <c r="F29" s="12">
         <f t="shared" si="1"/>
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G29" s="13">
         <f>VLOOKUP(B29,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7021,11 +7021,11 @@
       </c>
       <c r="H29" s="13">
         <f>VLOOKUP(B29,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="I29" s="17">
         <f t="shared" si="2"/>
-        <v>125.5</v>
+        <v>117.5</v>
       </c>
       <c r="J29" t="s">
         <v>58</v>
@@ -7045,14 +7045,14 @@
       </c>
       <c r="D30" s="22">
         <f t="shared" si="0"/>
-        <v>0.83453237410071945</v>
+        <v>0.87050359712230219</v>
       </c>
       <c r="E30" s="13">
         <v>73</v>
       </c>
       <c r="F30" s="12">
         <f t="shared" si="1"/>
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="G30" s="13">
         <f>VLOOKUP(B30,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7060,11 +7060,11 @@
       </c>
       <c r="H30" s="13">
         <f>VLOOKUP(B30,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="I30" s="17">
         <f t="shared" si="2"/>
-        <v>2.1499999999999915</v>
+        <v>-2.8500000000000085</v>
       </c>
       <c r="J30" t="s">
         <v>55</v>
@@ -7084,14 +7084,14 @@
       </c>
       <c r="D31" s="22">
         <f t="shared" si="0"/>
-        <v>0.53591160220994472</v>
+        <v>0.60220994475138123</v>
       </c>
       <c r="E31" s="13">
         <v>40</v>
       </c>
       <c r="F31" s="12">
         <f t="shared" si="1"/>
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="G31" s="13">
         <f>VLOOKUP(B31,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7099,11 +7099,11 @@
       </c>
       <c r="H31" s="13">
         <f>VLOOKUP(B31,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="I31" s="17">
         <f t="shared" si="2"/>
-        <v>56.849999999999994</v>
+        <v>44.849999999999994</v>
       </c>
       <c r="J31" t="s">
         <v>58</v>
@@ -7123,14 +7123,14 @@
       </c>
       <c r="D32" s="22">
         <f t="shared" si="0"/>
-        <v>0.6607142857142857</v>
+        <v>0.72619047619047616</v>
       </c>
       <c r="E32" s="13">
         <v>67</v>
       </c>
       <c r="F32" s="12">
         <f t="shared" si="1"/>
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="G32" s="13">
         <f>VLOOKUP(B32,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7138,11 +7138,11 @@
       </c>
       <c r="H32" s="13">
         <f>VLOOKUP(B32,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="I32" s="17">
         <f t="shared" si="2"/>
-        <v>31.799999999999983</v>
+        <v>20.799999999999983</v>
       </c>
       <c r="J32" t="s">
         <v>58</v>
@@ -7162,14 +7162,14 @@
       </c>
       <c r="D33" s="22">
         <f t="shared" si="0"/>
-        <v>0.67261904761904767</v>
+        <v>0.70238095238095233</v>
       </c>
       <c r="E33" s="13">
         <v>66</v>
       </c>
       <c r="F33" s="12">
         <f t="shared" si="1"/>
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G33" s="13">
         <f>VLOOKUP(B33,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7177,11 +7177,11 @@
       </c>
       <c r="H33" s="13">
         <f>VLOOKUP(B33,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="I33" s="17">
         <f t="shared" si="2"/>
-        <v>29.799999999999983</v>
+        <v>24.799999999999983</v>
       </c>
       <c r="J33" t="s">
         <v>58</v>
@@ -7240,14 +7240,14 @@
       </c>
       <c r="D35" s="22">
         <f t="shared" si="0"/>
-        <v>0.61235955056179781</v>
+        <v>0.6179775280898876</v>
       </c>
       <c r="E35" s="13">
         <v>81</v>
       </c>
       <c r="F35" s="12">
         <f t="shared" si="1"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G35" s="13">
         <f>VLOOKUP(B35,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7255,11 +7255,11 @@
       </c>
       <c r="H35" s="13">
         <f>VLOOKUP(B35,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I35" s="17">
         <f t="shared" si="2"/>
-        <v>42.299999999999983</v>
+        <v>41.299999999999983</v>
       </c>
       <c r="J35" t="s">
         <v>58</v>
@@ -7279,14 +7279,14 @@
       </c>
       <c r="D36" s="22">
         <f t="shared" si="0"/>
-        <v>6.1403508771929821E-2</v>
+        <v>7.8947368421052627E-2</v>
       </c>
       <c r="E36" s="13">
         <v>0</v>
       </c>
       <c r="F36" s="12">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G36" s="13">
         <f>VLOOKUP(B36,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7294,11 +7294,11 @@
       </c>
       <c r="H36" s="13">
         <f>VLOOKUP(B36,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I36" s="17">
         <f t="shared" si="2"/>
-        <v>89.899999999999991</v>
+        <v>87.899999999999991</v>
       </c>
       <c r="J36" t="s">
         <v>58</v>
@@ -7315,14 +7315,14 @@
       </c>
       <c r="D37" s="22">
         <f t="shared" si="0"/>
-        <v>0.20192307692307693</v>
+        <v>0.25</v>
       </c>
       <c r="E37" s="13">
         <v>17</v>
       </c>
       <c r="F37" s="12">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G37" s="13">
         <f>VLOOKUP(B37,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7330,11 +7330,11 @@
       </c>
       <c r="H37" s="13">
         <f>VLOOKUP(B37,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="I37" s="17">
         <f t="shared" si="2"/>
-        <v>67.399999999999991</v>
+        <v>62.399999999999991</v>
       </c>
       <c r="J37" t="s">
         <v>59</v>
@@ -7351,14 +7351,14 @@
       </c>
       <c r="D38" s="22">
         <f t="shared" si="0"/>
-        <v>0.65354330708661412</v>
+        <v>0.64566929133858264</v>
       </c>
       <c r="E38" s="13">
         <v>60</v>
       </c>
       <c r="F38" s="12">
         <f t="shared" si="1"/>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G38" s="13">
         <f>VLOOKUP(B38,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7366,11 +7366,11 @@
       </c>
       <c r="H38" s="13">
         <f>VLOOKUP(B38,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I38" s="17">
         <f t="shared" si="2"/>
-        <v>24.950000000000003</v>
+        <v>25.950000000000003</v>
       </c>
       <c r="J38" t="s">
         <v>55</v>
@@ -7386,15 +7386,15 @@
       <c r="E39" s="14"/>
       <c r="F39" s="8">
         <f>+SUM(F26:F38)</f>
-        <v>336</v>
+        <v>395</v>
       </c>
       <c r="G39" s="8">
         <f>+SUM(G26:G38)</f>
-        <v>1949</v>
+        <v>1950</v>
       </c>
       <c r="H39" s="8">
         <f>+SUM(H26:H38)</f>
-        <v>1058</v>
+        <v>1117</v>
       </c>
       <c r="I39" s="8"/>
       <c r="L39" t="s">
@@ -7410,20 +7410,20 @@
       <c r="E40" s="6"/>
       <c r="F40" s="8">
         <f>+SUM(F39+F25+F15)</f>
-        <v>1094</v>
+        <v>1287</v>
       </c>
       <c r="G40" s="8">
         <f>+G15+G25+G39</f>
-        <v>5723</v>
+        <v>5726</v>
       </c>
       <c r="H40" s="8">
         <f>+H15+H25+H39</f>
-        <v>3422</v>
+        <v>3615</v>
       </c>
       <c r="I40" s="8"/>
       <c r="L40" s="1">
         <f>+H40/G40</f>
-        <v>0.59793814432989689</v>
+        <v>0.63133077191756903</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
@@ -7436,14 +7436,14 @@
       </c>
       <c r="D41" s="22">
         <f t="shared" ref="D41:D42" si="4">H41/G41</f>
-        <v>0.19834710743801653</v>
+        <v>0.28099173553719009</v>
       </c>
       <c r="E41" s="13">
         <v>60</v>
       </c>
       <c r="F41" s="12">
         <f t="shared" ref="F41:F42" si="5">+H41-E41</f>
-        <v>-36</v>
+        <v>-26</v>
       </c>
       <c r="G41" s="13">
         <f>VLOOKUP(B41,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7451,11 +7451,11 @@
       </c>
       <c r="H41" s="13">
         <f>VLOOKUP(B41,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="I41" s="17">
         <f t="shared" ref="I41:I42" si="6">(+G41*$M$2)-H41</f>
-        <v>78.849999999999994</v>
+        <v>68.849999999999994</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
@@ -7468,14 +7468,14 @@
       </c>
       <c r="D42" s="22">
         <f t="shared" si="4"/>
-        <v>0.21311475409836064</v>
+        <v>0.35245901639344263</v>
       </c>
       <c r="E42" s="13">
         <v>60</v>
       </c>
       <c r="F42" s="12">
         <f t="shared" si="5"/>
-        <v>-34</v>
+        <v>-17</v>
       </c>
       <c r="G42" s="13">
         <f>VLOOKUP(B42,'Base Cobertura'!$A:$C,3,FALSE)</f>
@@ -7483,11 +7483,11 @@
       </c>
       <c r="H42" s="13">
         <f>VLOOKUP(B42,'Base Cobertura'!$A:$C,2,FALSE)</f>
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="I42" s="17">
         <f t="shared" si="6"/>
-        <v>77.7</v>
+        <v>60.7</v>
       </c>
     </row>
   </sheetData>
@@ -8081,7 +8081,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="51">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C4" s="51">
         <v>127</v>
@@ -8101,7 +8101,7 @@
         <v>10</v>
       </c>
       <c r="B5" s="51">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="C5" s="51">
         <v>181</v>
@@ -8119,7 +8119,7 @@
         <v>100</v>
       </c>
       <c r="B6" s="51">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C6" s="51">
         <v>2027</v>
@@ -8137,7 +8137,7 @@
         <v>11</v>
       </c>
       <c r="B7" s="51">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C7" s="51">
         <v>166</v>
@@ -8157,7 +8157,7 @@
         <v>12</v>
       </c>
       <c r="B8" s="51">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C8" s="51">
         <v>214</v>
@@ -8197,7 +8197,7 @@
         <v>15</v>
       </c>
       <c r="B10" s="51">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C10" s="51">
         <v>65</v>
@@ -8217,7 +8217,7 @@
         <v>16</v>
       </c>
       <c r="B11" s="51">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="C11" s="51">
         <v>198</v>
@@ -8237,7 +8237,7 @@
         <v>18</v>
       </c>
       <c r="B12" s="51">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C12" s="51">
         <v>177</v>
@@ -8253,7 +8253,7 @@
         <v>222</v>
       </c>
       <c r="H12">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I12" s="51">
         <v>127</v>
@@ -8264,7 +8264,7 @@
         <v>19</v>
       </c>
       <c r="B13" s="51">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="C13" s="51">
         <v>207</v>
@@ -8277,7 +8277,7 @@
         <v>223</v>
       </c>
       <c r="H13" s="51">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I13" s="51">
         <v>127</v>
@@ -8288,7 +8288,7 @@
         <v>2</v>
       </c>
       <c r="B14" s="51">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="C14" s="51">
         <v>138</v>
@@ -8301,7 +8301,7 @@
         <v>224</v>
       </c>
       <c r="H14" s="51">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I14" s="51">
         <v>127</v>
@@ -8312,7 +8312,7 @@
         <v>20</v>
       </c>
       <c r="B15" s="51">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C15" s="51">
         <v>227</v>
@@ -8336,7 +8336,7 @@
         <v>21</v>
       </c>
       <c r="B16" s="51">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C16" s="51">
         <v>171</v>
@@ -8360,10 +8360,10 @@
         <v>22</v>
       </c>
       <c r="B17" s="51">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C17" s="51">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E17">
         <f t="shared" si="0"/>
@@ -8384,7 +8384,7 @@
         <v>23</v>
       </c>
       <c r="B18" s="51">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="C18" s="51">
         <v>154</v>
@@ -8397,7 +8397,7 @@
         <v>228</v>
       </c>
       <c r="H18" s="51">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I18" s="51">
         <v>127</v>
@@ -8408,7 +8408,7 @@
         <v>24</v>
       </c>
       <c r="B19" s="51">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C19" s="51">
         <v>178</v>
@@ -8459,7 +8459,7 @@
         <v>56</v>
       </c>
       <c r="C21" s="51">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E21">
         <f>+$F$21</f>
@@ -8483,7 +8483,7 @@
         <v>27</v>
       </c>
       <c r="B22" s="51">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C22" s="51">
         <v>139</v>
@@ -8496,7 +8496,7 @@
         <v>223</v>
       </c>
       <c r="H22" s="51">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I22" s="51">
         <v>181</v>
@@ -8507,7 +8507,7 @@
         <v>28</v>
       </c>
       <c r="B23" s="51">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="C23" s="51">
         <v>168</v>
@@ -8520,7 +8520,7 @@
         <v>224</v>
       </c>
       <c r="H23" s="51">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="I23" s="51">
         <v>181</v>
@@ -8531,7 +8531,7 @@
         <v>3</v>
       </c>
       <c r="B24" s="51">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="C24" s="51">
         <v>170</v>
@@ -8544,7 +8544,7 @@
         <v>225</v>
       </c>
       <c r="H24" s="51">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I24" s="51">
         <v>181</v>
@@ -8555,7 +8555,7 @@
         <v>30</v>
       </c>
       <c r="B25" s="51">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C25" s="51">
         <v>139</v>
@@ -8568,7 +8568,7 @@
         <v>226</v>
       </c>
       <c r="H25" s="51">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="I25" s="51">
         <v>181</v>
@@ -8579,10 +8579,10 @@
         <v>31</v>
       </c>
       <c r="B26" s="51">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C26" s="51">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E26">
         <f t="shared" si="1"/>
@@ -8592,7 +8592,7 @@
         <v>227</v>
       </c>
       <c r="H26" s="51">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I26" s="51">
         <v>181</v>
@@ -8603,10 +8603,10 @@
         <v>32</v>
       </c>
       <c r="B27" s="51">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C27" s="51">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E27">
         <f t="shared" si="1"/>
@@ -8616,7 +8616,7 @@
         <v>228</v>
       </c>
       <c r="H27" s="51">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I27" s="51">
         <v>181</v>
@@ -8627,7 +8627,7 @@
         <v>33</v>
       </c>
       <c r="B28" s="51">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C28" s="51">
         <v>168</v>
@@ -8640,7 +8640,7 @@
         <v>229</v>
       </c>
       <c r="H28" s="51">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I28" s="51">
         <v>181</v>
@@ -8651,7 +8651,7 @@
         <v>36</v>
       </c>
       <c r="B29" s="51">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C29" s="51">
         <v>160</v>
@@ -8664,7 +8664,7 @@
         <v>230</v>
       </c>
       <c r="H29" s="51">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I29" s="51">
         <v>181</v>
@@ -8691,7 +8691,7 @@
         <v>222</v>
       </c>
       <c r="H30" s="51">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I30" s="51">
         <v>2027</v>
@@ -8702,7 +8702,7 @@
         <v>4</v>
       </c>
       <c r="B31" s="51">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C31" s="51">
         <v>182</v>
@@ -8715,7 +8715,7 @@
         <v>223</v>
       </c>
       <c r="H31" s="51">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I31" s="51">
         <v>2027</v>
@@ -8726,7 +8726,7 @@
         <v>40</v>
       </c>
       <c r="B32" s="51">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="C32" s="51">
         <v>250</v>
@@ -8739,7 +8739,7 @@
         <v>224</v>
       </c>
       <c r="H32" s="51">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I32" s="51">
         <v>2027</v>
@@ -8774,7 +8774,7 @@
         <v>43</v>
       </c>
       <c r="B34" s="51">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C34" s="51">
         <v>93</v>
@@ -8787,7 +8787,7 @@
         <v>226</v>
       </c>
       <c r="H34" s="51">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I34" s="51">
         <v>2027</v>
@@ -8798,7 +8798,7 @@
         <v>44</v>
       </c>
       <c r="B35" s="51">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="C35" s="51">
         <v>169</v>
@@ -8835,7 +8835,7 @@
         <v>228</v>
       </c>
       <c r="H36" s="51">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I36" s="51">
         <v>2027</v>
@@ -8846,7 +8846,7 @@
         <v>5</v>
       </c>
       <c r="B37" s="51">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="C37" s="51">
         <v>261</v>
@@ -8859,7 +8859,7 @@
         <v>229</v>
       </c>
       <c r="H37" s="51">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I37" s="51">
         <v>2027</v>
@@ -8870,7 +8870,7 @@
         <v>52</v>
       </c>
       <c r="B38" s="51">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C38" s="51">
         <v>101</v>
@@ -8894,7 +8894,7 @@
         <v>53</v>
       </c>
       <c r="B39" s="51">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C39" s="51">
         <v>105</v>
@@ -8910,7 +8910,7 @@
         <v>222</v>
       </c>
       <c r="H39" s="51">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I39" s="51">
         <v>166</v>
@@ -8921,7 +8921,7 @@
         <v>54</v>
       </c>
       <c r="B40" s="51">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="C40" s="51">
         <v>202</v>
@@ -8934,7 +8934,7 @@
         <v>223</v>
       </c>
       <c r="H40" s="51">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I40" s="51">
         <v>166</v>
@@ -8945,7 +8945,7 @@
         <v>56</v>
       </c>
       <c r="B41">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C41" s="51">
         <v>198</v>
@@ -8958,7 +8958,7 @@
         <v>224</v>
       </c>
       <c r="H41" s="51">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="I41" s="51">
         <v>166</v>
@@ -8969,7 +8969,7 @@
         <v>57</v>
       </c>
       <c r="B42" s="51">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C42" s="51">
         <v>104</v>
@@ -8982,7 +8982,7 @@
         <v>225</v>
       </c>
       <c r="H42" s="51">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="I42" s="51">
         <v>166</v>
@@ -8993,7 +8993,7 @@
         <v>58</v>
       </c>
       <c r="B43" s="51">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C43" s="51">
         <v>121</v>
@@ -9006,7 +9006,7 @@
         <v>226</v>
       </c>
       <c r="H43" s="51">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I43" s="51">
         <v>166</v>
@@ -9017,7 +9017,7 @@
         <v>59</v>
       </c>
       <c r="B44" s="51">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="C44" s="51">
         <v>122</v>
@@ -9030,7 +9030,7 @@
         <v>227</v>
       </c>
       <c r="H44" s="51">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="I44" s="51">
         <v>166</v>
@@ -9041,7 +9041,7 @@
         <v>7</v>
       </c>
       <c r="B45" s="51">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C45" s="51">
         <v>114</v>
@@ -9054,7 +9054,7 @@
         <v>228</v>
       </c>
       <c r="H45" s="51">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I45" s="51">
         <v>166</v>
@@ -9065,7 +9065,7 @@
         <v>8</v>
       </c>
       <c r="B46" s="51">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="C46" s="51">
         <v>195</v>
@@ -9078,7 +9078,7 @@
         <v>229</v>
       </c>
       <c r="H46" s="51">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I46" s="51">
         <v>166</v>
@@ -9089,7 +9089,7 @@
         <v>9</v>
       </c>
       <c r="B47" s="51">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C47" s="51">
         <v>161</v>
@@ -9102,7 +9102,7 @@
         <v>230</v>
       </c>
       <c r="H47" s="51">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I47" s="51">
         <v>166</v>
@@ -9122,7 +9122,7 @@
         <v>222</v>
       </c>
       <c r="H48" s="51">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="I48" s="51">
         <v>214</v>
@@ -9139,7 +9139,7 @@
         <v>223</v>
       </c>
       <c r="H49" s="51">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I49" s="51">
         <v>214</v>
@@ -9154,7 +9154,7 @@
         <v>224</v>
       </c>
       <c r="H50" s="51">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="I50" s="51">
         <v>214</v>
@@ -9169,7 +9169,7 @@
         <v>225</v>
       </c>
       <c r="H51" s="51">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I51" s="51">
         <v>214</v>
@@ -9184,7 +9184,7 @@
         <v>226</v>
       </c>
       <c r="H52" s="51">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="I52" s="51">
         <v>214</v>
@@ -9199,7 +9199,7 @@
         <v>227</v>
       </c>
       <c r="H53" s="51">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="I53" s="51">
         <v>214</v>
@@ -9229,7 +9229,7 @@
         <v>229</v>
       </c>
       <c r="H55" s="51">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I55" s="51">
         <v>214</v>
@@ -9277,7 +9277,7 @@
         <v>223</v>
       </c>
       <c r="H58" s="51">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I58" s="51">
         <v>489</v>
@@ -9292,7 +9292,7 @@
         <v>224</v>
       </c>
       <c r="H59" s="51">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I59" s="51">
         <v>489</v>
@@ -9322,7 +9322,7 @@
         <v>226</v>
       </c>
       <c r="H61" s="51">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I61" s="51">
         <v>489</v>
@@ -9337,7 +9337,7 @@
         <v>227</v>
       </c>
       <c r="H62" s="51">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I62" s="51">
         <v>489</v>
@@ -9367,7 +9367,7 @@
         <v>229</v>
       </c>
       <c r="H64" s="51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I64" s="51">
         <v>489</v>
@@ -9400,7 +9400,7 @@
         <v>222</v>
       </c>
       <c r="H66" s="51">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I66" s="51">
         <v>65</v>
@@ -9415,7 +9415,7 @@
         <v>223</v>
       </c>
       <c r="H67" s="51">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I67" s="51">
         <v>65</v>
@@ -9430,7 +9430,7 @@
         <v>224</v>
       </c>
       <c r="H68" s="51">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I68" s="51">
         <v>65</v>
@@ -9445,7 +9445,7 @@
         <v>225</v>
       </c>
       <c r="H69" s="51">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I69" s="51">
         <v>65</v>
@@ -9460,7 +9460,7 @@
         <v>226</v>
       </c>
       <c r="H70" s="51">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I70" s="51">
         <v>65</v>
@@ -9475,7 +9475,7 @@
         <v>227</v>
       </c>
       <c r="H71" s="51">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I71" s="51">
         <v>65</v>
@@ -9490,7 +9490,7 @@
         <v>228</v>
       </c>
       <c r="H72" s="51">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I72" s="51">
         <v>65</v>
@@ -9538,7 +9538,7 @@
         <v>222</v>
       </c>
       <c r="H75" s="51">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="I75" s="51">
         <v>198</v>
@@ -9568,7 +9568,7 @@
         <v>224</v>
       </c>
       <c r="H77" s="51">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="I77" s="51">
         <v>198</v>
@@ -9583,7 +9583,7 @@
         <v>225</v>
       </c>
       <c r="H78" s="51">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I78" s="51">
         <v>198</v>
@@ -9598,7 +9598,7 @@
         <v>226</v>
       </c>
       <c r="H79" s="51">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="I79" s="51">
         <v>198</v>
@@ -9613,7 +9613,7 @@
         <v>227</v>
       </c>
       <c r="H80" s="51">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="I80" s="51">
         <v>198</v>
@@ -9643,7 +9643,7 @@
         <v>229</v>
       </c>
       <c r="H82" s="51">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="I82" s="51">
         <v>198</v>
@@ -9658,7 +9658,7 @@
         <v>230</v>
       </c>
       <c r="H83" s="51">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I83" s="51">
         <v>198</v>
@@ -9676,7 +9676,7 @@
         <v>222</v>
       </c>
       <c r="H84" s="51">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I84" s="51">
         <v>177</v>
@@ -9691,7 +9691,7 @@
         <v>223</v>
       </c>
       <c r="H85" s="51">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="I85" s="51">
         <v>177</v>
@@ -9706,7 +9706,7 @@
         <v>224</v>
       </c>
       <c r="H86" s="51">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I86" s="51">
         <v>177</v>
@@ -9721,7 +9721,7 @@
         <v>225</v>
       </c>
       <c r="H87" s="51">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I87" s="51">
         <v>177</v>
@@ -9736,7 +9736,7 @@
         <v>226</v>
       </c>
       <c r="H88" s="51">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="I88" s="51">
         <v>177</v>
@@ -9751,7 +9751,7 @@
         <v>227</v>
       </c>
       <c r="H89" s="51">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="I89" s="51">
         <v>177</v>
@@ -9766,7 +9766,7 @@
         <v>228</v>
       </c>
       <c r="H90" s="51">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I90" s="51">
         <v>177</v>
@@ -9781,7 +9781,7 @@
         <v>229</v>
       </c>
       <c r="H91" s="51">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="I91" s="51">
         <v>177</v>
@@ -9796,7 +9796,7 @@
         <v>230</v>
       </c>
       <c r="H92" s="51">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="I92" s="51">
         <v>177</v>
@@ -9814,7 +9814,7 @@
         <v>222</v>
       </c>
       <c r="H93" s="51">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="I93" s="51">
         <v>207</v>
@@ -9829,7 +9829,7 @@
         <v>223</v>
       </c>
       <c r="H94" s="51">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I94" s="51">
         <v>207</v>
@@ -9844,7 +9844,7 @@
         <v>224</v>
       </c>
       <c r="H95" s="51">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="I95" s="51">
         <v>207</v>
@@ -9859,7 +9859,7 @@
         <v>225</v>
       </c>
       <c r="H96" s="51">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I96" s="51">
         <v>207</v>
@@ -9874,7 +9874,7 @@
         <v>226</v>
       </c>
       <c r="H97" s="51">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="I97" s="51">
         <v>207</v>
@@ -9889,7 +9889,7 @@
         <v>227</v>
       </c>
       <c r="H98" s="51">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="I98" s="51">
         <v>207</v>
@@ -9904,7 +9904,7 @@
         <v>228</v>
       </c>
       <c r="H99" s="51">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I99" s="51">
         <v>207</v>
@@ -9919,7 +9919,7 @@
         <v>229</v>
       </c>
       <c r="H100" s="51">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I100" s="51">
         <v>207</v>
@@ -9934,7 +9934,7 @@
         <v>230</v>
       </c>
       <c r="H101" s="51">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I101" s="51">
         <v>207</v>
@@ -9952,7 +9952,7 @@
         <v>222</v>
       </c>
       <c r="H102" s="51">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I102" s="51">
         <v>138</v>
@@ -9967,7 +9967,7 @@
         <v>223</v>
       </c>
       <c r="H103" s="51">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I103" s="51">
         <v>138</v>
@@ -9982,7 +9982,7 @@
         <v>224</v>
       </c>
       <c r="H104" s="51">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I104" s="51">
         <v>138</v>
@@ -9997,7 +9997,7 @@
         <v>225</v>
       </c>
       <c r="H105" s="51">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="I105" s="51">
         <v>138</v>
@@ -10012,7 +10012,7 @@
         <v>226</v>
       </c>
       <c r="H106" s="51">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="I106" s="51">
         <v>138</v>
@@ -10027,7 +10027,7 @@
         <v>227</v>
       </c>
       <c r="H107" s="51">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="I107" s="51">
         <v>138</v>
@@ -10042,7 +10042,7 @@
         <v>228</v>
       </c>
       <c r="H108" s="51">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I108" s="51">
         <v>138</v>
@@ -10057,7 +10057,7 @@
         <v>229</v>
       </c>
       <c r="H109" s="51">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I109" s="51">
         <v>138</v>
@@ -10072,7 +10072,7 @@
         <v>230</v>
       </c>
       <c r="H110" s="51">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I110" s="51">
         <v>138</v>
@@ -10090,7 +10090,7 @@
         <v>222</v>
       </c>
       <c r="H111" s="51">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="I111" s="51">
         <v>227</v>
@@ -10105,7 +10105,7 @@
         <v>223</v>
       </c>
       <c r="H112" s="51">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="I112" s="51">
         <v>227</v>
@@ -10120,7 +10120,7 @@
         <v>224</v>
       </c>
       <c r="H113" s="51">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I113" s="51">
         <v>227</v>
@@ -10135,7 +10135,7 @@
         <v>225</v>
       </c>
       <c r="H114" s="51">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="I114" s="51">
         <v>227</v>
@@ -10150,7 +10150,7 @@
         <v>226</v>
       </c>
       <c r="H115" s="51">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="I115" s="51">
         <v>227</v>
@@ -10165,7 +10165,7 @@
         <v>227</v>
       </c>
       <c r="H116">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I116" s="51">
         <v>227</v>
@@ -10180,7 +10180,7 @@
         <v>228</v>
       </c>
       <c r="H117" s="51">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I117" s="51">
         <v>227</v>
@@ -10195,7 +10195,7 @@
         <v>229</v>
       </c>
       <c r="H118" s="51">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I118" s="51">
         <v>227</v>
@@ -10210,7 +10210,7 @@
         <v>230</v>
       </c>
       <c r="H119" s="51">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I119" s="51">
         <v>227</v>
@@ -10228,7 +10228,7 @@
         <v>222</v>
       </c>
       <c r="H120" s="51">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="I120" s="51">
         <v>171</v>
@@ -10243,7 +10243,7 @@
         <v>223</v>
       </c>
       <c r="H121" s="51">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="I121" s="51">
         <v>171</v>
@@ -10258,7 +10258,7 @@
         <v>224</v>
       </c>
       <c r="H122" s="51">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="I122" s="51">
         <v>171</v>
@@ -10273,7 +10273,7 @@
         <v>225</v>
       </c>
       <c r="H123" s="51">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="I123" s="51">
         <v>171</v>
@@ -10288,7 +10288,7 @@
         <v>226</v>
       </c>
       <c r="H124">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="I124" s="51">
         <v>171</v>
@@ -10303,7 +10303,7 @@
         <v>227</v>
       </c>
       <c r="H125" s="51">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I125" s="51">
         <v>171</v>
@@ -10318,7 +10318,7 @@
         <v>228</v>
       </c>
       <c r="H126" s="51">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I126" s="51">
         <v>171</v>
@@ -10333,7 +10333,7 @@
         <v>229</v>
       </c>
       <c r="H127" s="51">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I127" s="51">
         <v>171</v>
@@ -10348,7 +10348,7 @@
         <v>230</v>
       </c>
       <c r="H128" s="51">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I128" s="51">
         <v>171</v>
@@ -10366,10 +10366,10 @@
         <v>222</v>
       </c>
       <c r="H129" s="51">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="I129" s="51">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="130" spans="5:9" x14ac:dyDescent="0.25">
@@ -10381,10 +10381,10 @@
         <v>223</v>
       </c>
       <c r="H130" s="51">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I130" s="51">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="131" spans="5:9" x14ac:dyDescent="0.25">
@@ -10396,10 +10396,10 @@
         <v>224</v>
       </c>
       <c r="H131" s="51">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I131" s="51">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="132" spans="5:9" x14ac:dyDescent="0.25">
@@ -10411,10 +10411,10 @@
         <v>225</v>
       </c>
       <c r="H132" s="51">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="I132" s="51">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="133" spans="5:9" x14ac:dyDescent="0.25">
@@ -10426,10 +10426,10 @@
         <v>226</v>
       </c>
       <c r="H133" s="51">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I133" s="51">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="134" spans="5:9" x14ac:dyDescent="0.25">
@@ -10441,10 +10441,10 @@
         <v>227</v>
       </c>
       <c r="H134" s="51">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I134" s="51">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="135" spans="5:9" x14ac:dyDescent="0.25">
@@ -10456,10 +10456,10 @@
         <v>228</v>
       </c>
       <c r="H135" s="51">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I135" s="51">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="136" spans="5:9" x14ac:dyDescent="0.25">
@@ -10471,10 +10471,10 @@
         <v>229</v>
       </c>
       <c r="H136" s="51">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="I136" s="51">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="137" spans="5:9" x14ac:dyDescent="0.25">
@@ -10486,10 +10486,10 @@
         <v>230</v>
       </c>
       <c r="H137" s="51">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I137" s="51">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="138" spans="5:9" x14ac:dyDescent="0.25">
@@ -10504,7 +10504,7 @@
         <v>222</v>
       </c>
       <c r="H138" s="51">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I138" s="51">
         <v>154</v>
@@ -10519,7 +10519,7 @@
         <v>223</v>
       </c>
       <c r="H139" s="51">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="I139" s="51">
         <v>154</v>
@@ -10534,7 +10534,7 @@
         <v>224</v>
       </c>
       <c r="H140">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="I140" s="51">
         <v>154</v>
@@ -10549,7 +10549,7 @@
         <v>225</v>
       </c>
       <c r="H141" s="51">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I141" s="51">
         <v>154</v>
@@ -10564,7 +10564,7 @@
         <v>226</v>
       </c>
       <c r="H142" s="51">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="I142" s="51">
         <v>154</v>
@@ -10579,7 +10579,7 @@
         <v>227</v>
       </c>
       <c r="H143" s="51">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="I143" s="51">
         <v>154</v>
@@ -10594,7 +10594,7 @@
         <v>228</v>
       </c>
       <c r="H144" s="51">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I144" s="51">
         <v>154</v>
@@ -10624,7 +10624,7 @@
         <v>230</v>
       </c>
       <c r="H146" s="51">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I146" s="51">
         <v>154</v>
@@ -10642,7 +10642,7 @@
         <v>222</v>
       </c>
       <c r="H147" s="51">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I147" s="51">
         <v>178</v>
@@ -10657,7 +10657,7 @@
         <v>223</v>
       </c>
       <c r="H148">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I148" s="51">
         <v>178</v>
@@ -10687,7 +10687,7 @@
         <v>225</v>
       </c>
       <c r="H150" s="51">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I150" s="51">
         <v>178</v>
@@ -10702,7 +10702,7 @@
         <v>226</v>
       </c>
       <c r="H151" s="51">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I151" s="51">
         <v>178</v>
@@ -10717,7 +10717,7 @@
         <v>227</v>
       </c>
       <c r="H152" s="51">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I152" s="51">
         <v>178</v>
@@ -10747,7 +10747,7 @@
         <v>229</v>
       </c>
       <c r="H154" s="51">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I154" s="51">
         <v>178</v>
@@ -10762,7 +10762,7 @@
         <v>230</v>
       </c>
       <c r="H155" s="51">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I155" s="51">
         <v>178</v>
@@ -10921,7 +10921,7 @@
         <v>31</v>
       </c>
       <c r="I165" s="51">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="166" spans="5:9" x14ac:dyDescent="0.25">
@@ -10936,7 +10936,7 @@
         <v>7</v>
       </c>
       <c r="I166" s="51">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="167" spans="5:9" x14ac:dyDescent="0.25">
@@ -10951,7 +10951,7 @@
         <v>7</v>
       </c>
       <c r="I167" s="51">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="168" spans="5:9" x14ac:dyDescent="0.25">
@@ -10966,7 +10966,7 @@
         <v>22</v>
       </c>
       <c r="I168" s="51">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="169" spans="5:9" x14ac:dyDescent="0.25">
@@ -10981,7 +10981,7 @@
         <v>21</v>
       </c>
       <c r="I169" s="51">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="170" spans="5:9" x14ac:dyDescent="0.25">
@@ -10996,7 +10996,7 @@
         <v>23</v>
       </c>
       <c r="I170" s="51">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="171" spans="5:9" x14ac:dyDescent="0.25">
@@ -11011,7 +11011,7 @@
         <v>27</v>
       </c>
       <c r="I171" s="51">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="172" spans="5:9" x14ac:dyDescent="0.25">
@@ -11026,7 +11026,7 @@
         <v>13</v>
       </c>
       <c r="I172" s="51">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="173" spans="5:9" x14ac:dyDescent="0.25">
@@ -11041,7 +11041,7 @@
         <v>17</v>
       </c>
       <c r="I173" s="51">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="174" spans="5:9" x14ac:dyDescent="0.25">
@@ -11056,7 +11056,7 @@
         <v>222</v>
       </c>
       <c r="H174" s="51">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="I174" s="51">
         <v>139</v>
@@ -11071,7 +11071,7 @@
         <v>223</v>
       </c>
       <c r="H175" s="51">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I175" s="51">
         <v>139</v>
@@ -11086,7 +11086,7 @@
         <v>224</v>
       </c>
       <c r="H176" s="51">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I176" s="51">
         <v>139</v>
@@ -11101,7 +11101,7 @@
         <v>225</v>
       </c>
       <c r="H177" s="51">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I177" s="51">
         <v>139</v>
@@ -11116,7 +11116,7 @@
         <v>226</v>
       </c>
       <c r="H178" s="51">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="I178" s="51">
         <v>139</v>
@@ -11131,7 +11131,7 @@
         <v>227</v>
       </c>
       <c r="H179" s="51">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="I179" s="51">
         <v>139</v>
@@ -11146,7 +11146,7 @@
         <v>228</v>
       </c>
       <c r="H180">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I180" s="51">
         <v>139</v>
@@ -11161,7 +11161,7 @@
         <v>229</v>
       </c>
       <c r="H181" s="51">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I181" s="51">
         <v>139</v>
@@ -11176,7 +11176,7 @@
         <v>230</v>
       </c>
       <c r="H182" s="51">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I182" s="51">
         <v>139</v>
@@ -11194,7 +11194,7 @@
         <v>222</v>
       </c>
       <c r="H183" s="51">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I183" s="51">
         <v>168</v>
@@ -11224,7 +11224,7 @@
         <v>224</v>
       </c>
       <c r="H185" s="51">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I185" s="51">
         <v>168</v>
@@ -11239,7 +11239,7 @@
         <v>225</v>
       </c>
       <c r="H186">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="I186" s="51">
         <v>168</v>
@@ -11254,7 +11254,7 @@
         <v>226</v>
       </c>
       <c r="H187" s="51">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="I187" s="51">
         <v>168</v>
@@ -11269,7 +11269,7 @@
         <v>227</v>
       </c>
       <c r="H188" s="51">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="I188" s="51">
         <v>168</v>
@@ -11284,7 +11284,7 @@
         <v>228</v>
       </c>
       <c r="H189" s="51">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I189" s="51">
         <v>168</v>
@@ -11299,7 +11299,7 @@
         <v>229</v>
       </c>
       <c r="H190" s="51">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I190" s="51">
         <v>168</v>
@@ -11314,7 +11314,7 @@
         <v>230</v>
       </c>
       <c r="H191" s="51">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I191" s="51">
         <v>168</v>
@@ -11332,7 +11332,7 @@
         <v>222</v>
       </c>
       <c r="H192" s="51">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I192" s="51">
         <v>170</v>
@@ -11347,7 +11347,7 @@
         <v>223</v>
       </c>
       <c r="H193" s="51">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I193" s="51">
         <v>170</v>
@@ -11362,7 +11362,7 @@
         <v>224</v>
       </c>
       <c r="H194" s="51">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="I194" s="51">
         <v>170</v>
@@ -11377,7 +11377,7 @@
         <v>225</v>
       </c>
       <c r="H195" s="51">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I195" s="51">
         <v>170</v>
@@ -11392,7 +11392,7 @@
         <v>226</v>
       </c>
       <c r="H196">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="I196" s="51">
         <v>170</v>
@@ -11407,7 +11407,7 @@
         <v>227</v>
       </c>
       <c r="H197" s="51">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="I197" s="51">
         <v>170</v>
@@ -11422,7 +11422,7 @@
         <v>228</v>
       </c>
       <c r="H198" s="51">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I198" s="51">
         <v>170</v>
@@ -11437,7 +11437,7 @@
         <v>229</v>
       </c>
       <c r="H199" s="51">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I199" s="51">
         <v>170</v>
@@ -11470,7 +11470,7 @@
         <v>222</v>
       </c>
       <c r="H201" s="51">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I201" s="51">
         <v>139</v>
@@ -11485,7 +11485,7 @@
         <v>223</v>
       </c>
       <c r="H202" s="51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I202" s="51">
         <v>139</v>
@@ -11500,7 +11500,7 @@
         <v>224</v>
       </c>
       <c r="H203" s="51">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I203" s="51">
         <v>139</v>
@@ -11528,7 +11528,7 @@
         <v>226</v>
       </c>
       <c r="H205" s="51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I205" s="51">
         <v>139</v>
@@ -11600,10 +11600,10 @@
         <v>222</v>
       </c>
       <c r="H210" s="51">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I210" s="51">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="211" spans="5:9" x14ac:dyDescent="0.25">
@@ -11615,10 +11615,10 @@
         <v>223</v>
       </c>
       <c r="H211" s="51">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I211" s="51">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="212" spans="5:9" x14ac:dyDescent="0.25">
@@ -11630,10 +11630,10 @@
         <v>224</v>
       </c>
       <c r="H212">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="I212" s="51">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="213" spans="5:9" x14ac:dyDescent="0.25">
@@ -11645,10 +11645,10 @@
         <v>225</v>
       </c>
       <c r="H213" s="51">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I213" s="51">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="214" spans="5:9" x14ac:dyDescent="0.25">
@@ -11660,10 +11660,10 @@
         <v>226</v>
       </c>
       <c r="H214" s="51">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I214" s="51">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="215" spans="5:9" x14ac:dyDescent="0.25">
@@ -11675,10 +11675,10 @@
         <v>227</v>
       </c>
       <c r="H215" s="51">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="I215" s="51">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="216" spans="5:9" x14ac:dyDescent="0.25">
@@ -11690,10 +11690,10 @@
         <v>228</v>
       </c>
       <c r="H216" s="51">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I216" s="51">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="217" spans="5:9" x14ac:dyDescent="0.25">
@@ -11705,10 +11705,10 @@
         <v>229</v>
       </c>
       <c r="H217" s="51">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I217" s="51">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="218" spans="5:9" x14ac:dyDescent="0.25">
@@ -11720,10 +11720,10 @@
         <v>230</v>
       </c>
       <c r="H218" s="51">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I218" s="51">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="219" spans="5:9" x14ac:dyDescent="0.25">
@@ -11738,10 +11738,10 @@
         <v>222</v>
       </c>
       <c r="H219" s="51">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I219" s="51">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="220" spans="5:9" x14ac:dyDescent="0.25">
@@ -11753,10 +11753,10 @@
         <v>223</v>
       </c>
       <c r="H220" s="51">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I220" s="51">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="221" spans="5:9" x14ac:dyDescent="0.25">
@@ -11768,10 +11768,10 @@
         <v>224</v>
       </c>
       <c r="H221" s="51">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I221" s="51">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="222" spans="5:9" x14ac:dyDescent="0.25">
@@ -11783,10 +11783,10 @@
         <v>225</v>
       </c>
       <c r="H222" s="51">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I222" s="51">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="223" spans="5:9" x14ac:dyDescent="0.25">
@@ -11798,10 +11798,10 @@
         <v>226</v>
       </c>
       <c r="H223" s="51">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="I223" s="51">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="224" spans="5:9" x14ac:dyDescent="0.25">
@@ -11813,10 +11813,10 @@
         <v>227</v>
       </c>
       <c r="H224" s="51">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I224" s="51">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="225" spans="5:9" x14ac:dyDescent="0.25">
@@ -11828,10 +11828,10 @@
         <v>228</v>
       </c>
       <c r="H225" s="51">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I225" s="51">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="226" spans="5:9" x14ac:dyDescent="0.25">
@@ -11843,10 +11843,10 @@
         <v>229</v>
       </c>
       <c r="H226" s="51">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I226" s="51">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="227" spans="5:9" x14ac:dyDescent="0.25">
@@ -11858,10 +11858,10 @@
         <v>230</v>
       </c>
       <c r="H227" s="51">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I227" s="51">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="228" spans="5:9" x14ac:dyDescent="0.25">
@@ -11876,7 +11876,7 @@
         <v>222</v>
       </c>
       <c r="H228" s="51">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I228" s="51">
         <v>168</v>
@@ -11891,7 +11891,7 @@
         <v>223</v>
       </c>
       <c r="H229" s="51">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I229" s="51">
         <v>168</v>
@@ -11906,7 +11906,7 @@
         <v>224</v>
       </c>
       <c r="H230" s="51">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I230" s="51">
         <v>168</v>
@@ -11921,7 +11921,7 @@
         <v>225</v>
       </c>
       <c r="H231" s="51">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I231" s="51">
         <v>168</v>
@@ -11936,7 +11936,7 @@
         <v>226</v>
       </c>
       <c r="H232" s="51">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I232" s="51">
         <v>168</v>
@@ -11951,7 +11951,7 @@
         <v>227</v>
       </c>
       <c r="H233" s="51">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="I233" s="51">
         <v>168</v>
@@ -11981,7 +11981,7 @@
         <v>229</v>
       </c>
       <c r="H235" s="51">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I235" s="51">
         <v>168</v>
@@ -11996,7 +11996,7 @@
         <v>230</v>
       </c>
       <c r="H236">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I236" s="51">
         <v>168</v>
@@ -12014,7 +12014,7 @@
         <v>222</v>
       </c>
       <c r="H237" s="51">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I237" s="51">
         <v>160</v>
@@ -12029,7 +12029,7 @@
         <v>223</v>
       </c>
       <c r="H238" s="51">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I238" s="51">
         <v>160</v>
@@ -12044,7 +12044,7 @@
         <v>224</v>
       </c>
       <c r="H239" s="51">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I239" s="51">
         <v>160</v>
@@ -12059,7 +12059,7 @@
         <v>225</v>
       </c>
       <c r="H240" s="51">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I240" s="51">
         <v>160</v>
@@ -12074,7 +12074,7 @@
         <v>226</v>
       </c>
       <c r="H241" s="51">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I241" s="51">
         <v>160</v>
@@ -12089,7 +12089,7 @@
         <v>227</v>
       </c>
       <c r="H242" s="51">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="I242" s="51">
         <v>160</v>
@@ -12104,7 +12104,7 @@
         <v>228</v>
       </c>
       <c r="H243" s="51">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I243" s="51">
         <v>160</v>
@@ -12119,7 +12119,7 @@
         <v>229</v>
       </c>
       <c r="H244">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I244" s="51">
         <v>160</v>
@@ -12134,7 +12134,7 @@
         <v>230</v>
       </c>
       <c r="H245" s="51">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I245" s="51">
         <v>160</v>
@@ -12152,7 +12152,7 @@
         <v>222</v>
       </c>
       <c r="H246" s="51">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I246" s="51">
         <v>142</v>
@@ -12182,7 +12182,7 @@
         <v>224</v>
       </c>
       <c r="H248" s="51">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I248" s="51">
         <v>142</v>
@@ -12197,7 +12197,7 @@
         <v>225</v>
       </c>
       <c r="H249" s="51">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I249" s="51">
         <v>142</v>
@@ -12212,7 +12212,7 @@
         <v>226</v>
       </c>
       <c r="H250" s="51">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I250" s="51">
         <v>142</v>
@@ -12242,7 +12242,7 @@
         <v>228</v>
       </c>
       <c r="H252">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I252" s="51">
         <v>142</v>
@@ -12272,7 +12272,7 @@
         <v>230</v>
       </c>
       <c r="H254" s="51">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I254" s="51">
         <v>142</v>
@@ -12290,7 +12290,7 @@
         <v>222</v>
       </c>
       <c r="H255" s="51">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I255" s="51">
         <v>182</v>
@@ -12305,7 +12305,7 @@
         <v>223</v>
       </c>
       <c r="H256" s="51">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I256" s="51">
         <v>182</v>
@@ -12320,7 +12320,7 @@
         <v>224</v>
       </c>
       <c r="H257" s="51">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="I257" s="51">
         <v>182</v>
@@ -12335,7 +12335,7 @@
         <v>225</v>
       </c>
       <c r="H258">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I258" s="51">
         <v>182</v>
@@ -12350,7 +12350,7 @@
         <v>226</v>
       </c>
       <c r="H259" s="51">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="I259" s="51">
         <v>182</v>
@@ -12365,7 +12365,7 @@
         <v>227</v>
       </c>
       <c r="H260">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="I260" s="51">
         <v>182</v>
@@ -12380,7 +12380,7 @@
         <v>228</v>
       </c>
       <c r="H261" s="51">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I261" s="51">
         <v>182</v>
@@ -12395,7 +12395,7 @@
         <v>229</v>
       </c>
       <c r="H262" s="51">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I262" s="51">
         <v>182</v>
@@ -12410,7 +12410,7 @@
         <v>230</v>
       </c>
       <c r="H263" s="51">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="I263" s="51">
         <v>182</v>
@@ -12428,7 +12428,7 @@
         <v>222</v>
       </c>
       <c r="H264" s="51">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I264" s="51">
         <v>250</v>
@@ -12443,7 +12443,7 @@
         <v>223</v>
       </c>
       <c r="H265">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I265" s="51">
         <v>250</v>
@@ -12458,7 +12458,7 @@
         <v>224</v>
       </c>
       <c r="H266" s="51">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I266" s="51">
         <v>250</v>
@@ -12473,7 +12473,7 @@
         <v>225</v>
       </c>
       <c r="H267" s="51">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I267" s="51">
         <v>250</v>
@@ -12488,7 +12488,7 @@
         <v>226</v>
       </c>
       <c r="H268">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="I268" s="51">
         <v>250</v>
@@ -12503,7 +12503,7 @@
         <v>227</v>
       </c>
       <c r="H269" s="51">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="I269" s="51">
         <v>250</v>
@@ -12518,7 +12518,7 @@
         <v>228</v>
       </c>
       <c r="H270" s="51">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I270" s="51">
         <v>250</v>
@@ -12533,7 +12533,7 @@
         <v>229</v>
       </c>
       <c r="H271" s="51">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I271" s="51">
         <v>250</v>
@@ -12548,7 +12548,7 @@
         <v>230</v>
       </c>
       <c r="H272" s="51">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I272" s="51">
         <v>250</v>
@@ -12703,7 +12703,9 @@
       <c r="G282" t="s">
         <v>222</v>
       </c>
-      <c r="H282" s="51"/>
+      <c r="H282" s="51">
+        <v>3</v>
+      </c>
       <c r="I282" s="51">
         <v>93</v>
       </c>
@@ -12730,7 +12732,7 @@
         <v>224</v>
       </c>
       <c r="H284">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I284" s="51">
         <v>93</v>
@@ -12744,6 +12746,9 @@
       <c r="G285" t="s">
         <v>225</v>
       </c>
+      <c r="H285">
+        <v>2</v>
+      </c>
       <c r="I285" s="51">
         <v>93</v>
       </c>
@@ -12757,7 +12762,7 @@
         <v>226</v>
       </c>
       <c r="H286">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I286" s="51">
         <v>93</v>
@@ -12771,6 +12776,9 @@
       <c r="G287" t="s">
         <v>227</v>
       </c>
+      <c r="H287">
+        <v>1</v>
+      </c>
       <c r="I287" s="51">
         <v>93</v>
       </c>
@@ -12784,7 +12792,7 @@
         <v>228</v>
       </c>
       <c r="H288">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I288" s="51">
         <v>93</v>
@@ -12811,6 +12819,9 @@
       <c r="G290" t="s">
         <v>230</v>
       </c>
+      <c r="H290">
+        <v>1</v>
+      </c>
       <c r="I290" s="51">
         <v>93</v>
       </c>
@@ -12827,7 +12838,7 @@
         <v>222</v>
       </c>
       <c r="H291">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I291" s="51">
         <v>169</v>
@@ -12842,7 +12853,7 @@
         <v>223</v>
       </c>
       <c r="H292">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I292" s="51">
         <v>169</v>
@@ -12857,7 +12868,7 @@
         <v>224</v>
       </c>
       <c r="H293">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="I293" s="51">
         <v>169</v>
@@ -12872,7 +12883,7 @@
         <v>225</v>
       </c>
       <c r="H294">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="I294" s="51">
         <v>169</v>
@@ -12887,7 +12898,7 @@
         <v>226</v>
       </c>
       <c r="H295">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="I295" s="51">
         <v>169</v>
@@ -12902,7 +12913,7 @@
         <v>227</v>
       </c>
       <c r="H296">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="I296" s="51">
         <v>169</v>
@@ -12917,7 +12928,7 @@
         <v>228</v>
       </c>
       <c r="H297" s="51">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I297" s="51">
         <v>169</v>
@@ -12932,7 +12943,7 @@
         <v>229</v>
       </c>
       <c r="H298">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I298" s="51">
         <v>169</v>
@@ -12947,7 +12958,7 @@
         <v>230</v>
       </c>
       <c r="H299" s="51">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I299" s="51">
         <v>169</v>
@@ -13103,7 +13114,7 @@
         <v>222</v>
       </c>
       <c r="H309">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="I309" s="51">
         <v>261</v>
@@ -13118,7 +13129,7 @@
         <v>223</v>
       </c>
       <c r="H310">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="I310" s="51">
         <v>261</v>
@@ -13133,7 +13144,7 @@
         <v>224</v>
       </c>
       <c r="H311">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I311" s="51">
         <v>261</v>
@@ -13148,7 +13159,7 @@
         <v>225</v>
       </c>
       <c r="H312">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I312" s="51">
         <v>261</v>
@@ -13163,7 +13174,7 @@
         <v>226</v>
       </c>
       <c r="H313">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="I313" s="51">
         <v>261</v>
@@ -13178,7 +13189,7 @@
         <v>227</v>
       </c>
       <c r="H314">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I314" s="51">
         <v>261</v>
@@ -13193,7 +13204,7 @@
         <v>228</v>
       </c>
       <c r="H315" s="51">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="I315" s="51">
         <v>261</v>
@@ -13223,7 +13234,7 @@
         <v>230</v>
       </c>
       <c r="H317" s="51">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I317" s="51">
         <v>261</v>
@@ -13256,7 +13267,7 @@
         <v>223</v>
       </c>
       <c r="H319" s="51">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I319" s="51">
         <v>101</v>
@@ -13322,7 +13333,7 @@
         <v>228</v>
       </c>
       <c r="H324" s="51">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="I324" s="51">
         <v>101</v>
@@ -13378,7 +13389,7 @@
         <v>223</v>
       </c>
       <c r="H328">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I328" s="51">
         <v>105</v>
@@ -13443,7 +13454,7 @@
         <v>228</v>
       </c>
       <c r="H333" s="51">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="I333" s="51">
         <v>105</v>
@@ -13487,7 +13498,7 @@
         <v>222</v>
       </c>
       <c r="H336" s="51">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I336" s="51">
         <v>202</v>
@@ -13502,7 +13513,7 @@
         <v>223</v>
       </c>
       <c r="H337" s="51">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I337" s="51">
         <v>202</v>
@@ -13517,7 +13528,7 @@
         <v>224</v>
       </c>
       <c r="H338" s="51">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="I338" s="51">
         <v>202</v>
@@ -13532,7 +13543,7 @@
         <v>225</v>
       </c>
       <c r="H339" s="51">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="I339" s="51">
         <v>202</v>
@@ -13547,7 +13558,7 @@
         <v>226</v>
       </c>
       <c r="H340">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="I340" s="51">
         <v>202</v>
@@ -13562,7 +13573,7 @@
         <v>227</v>
       </c>
       <c r="H341" s="51">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="I341" s="51">
         <v>202</v>
@@ -13577,7 +13588,7 @@
         <v>228</v>
       </c>
       <c r="H342" s="51">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="I342" s="51">
         <v>202</v>
@@ -13592,7 +13603,7 @@
         <v>229</v>
       </c>
       <c r="H343" s="51">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="I343" s="51">
         <v>202</v>
@@ -13607,7 +13618,7 @@
         <v>230</v>
       </c>
       <c r="H344" s="51">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I344" s="51">
         <v>202</v>
@@ -13625,7 +13636,7 @@
         <v>222</v>
       </c>
       <c r="H345">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I345" s="51">
         <v>198</v>
@@ -13655,7 +13666,7 @@
         <v>224</v>
       </c>
       <c r="H347" s="51">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I347" s="51">
         <v>198</v>
@@ -13670,7 +13681,7 @@
         <v>225</v>
       </c>
       <c r="H348">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I348" s="51">
         <v>198</v>
@@ -13685,7 +13696,7 @@
         <v>226</v>
       </c>
       <c r="H349" s="51">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I349" s="51">
         <v>198</v>
@@ -13700,7 +13711,7 @@
         <v>227</v>
       </c>
       <c r="H350" s="51">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I350" s="51">
         <v>198</v>
@@ -13715,7 +13726,7 @@
         <v>228</v>
       </c>
       <c r="H351" s="51">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I351" s="51">
         <v>198</v>
@@ -13730,7 +13741,7 @@
         <v>229</v>
       </c>
       <c r="H352">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I352" s="51">
         <v>198</v>
@@ -13843,7 +13854,7 @@
         <v>228</v>
       </c>
       <c r="H360" s="51">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="I360" s="51">
         <v>104</v>
@@ -13887,7 +13898,7 @@
         <v>222</v>
       </c>
       <c r="H363" s="51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I363" s="51">
         <v>121</v>
@@ -13902,7 +13913,7 @@
         <v>223</v>
       </c>
       <c r="H364" s="51">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I364" s="51">
         <v>121</v>
@@ -13917,7 +13928,7 @@
         <v>224</v>
       </c>
       <c r="H365" s="51">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I365" s="51">
         <v>121</v>
@@ -13932,7 +13943,7 @@
         <v>225</v>
       </c>
       <c r="H366" s="51">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="I366" s="51">
         <v>121</v>
@@ -13947,7 +13958,7 @@
         <v>226</v>
       </c>
       <c r="H367" s="51">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I367" s="51">
         <v>121</v>
@@ -13962,7 +13973,7 @@
         <v>227</v>
       </c>
       <c r="H368" s="51">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="I368" s="51">
         <v>121</v>
@@ -13977,7 +13988,7 @@
         <v>228</v>
       </c>
       <c r="H369" s="51">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I369" s="51">
         <v>121</v>
@@ -13992,7 +14003,7 @@
         <v>229</v>
       </c>
       <c r="H370" s="51">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I370" s="51">
         <v>121</v>
@@ -14025,7 +14036,7 @@
         <v>222</v>
       </c>
       <c r="H372">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I372">
         <v>122</v>
@@ -14040,7 +14051,7 @@
         <v>223</v>
       </c>
       <c r="H373">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="I373">
         <v>122</v>
@@ -14055,7 +14066,7 @@
         <v>224</v>
       </c>
       <c r="H374">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I374">
         <v>122</v>
@@ -14070,7 +14081,7 @@
         <v>225</v>
       </c>
       <c r="H375">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="I375">
         <v>122</v>
@@ -14085,7 +14096,7 @@
         <v>226</v>
       </c>
       <c r="H376">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="I376">
         <v>122</v>
@@ -14100,7 +14111,7 @@
         <v>227</v>
       </c>
       <c r="H377">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="I377">
         <v>122</v>
@@ -14115,7 +14126,7 @@
         <v>228</v>
       </c>
       <c r="H378">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I378">
         <v>122</v>
@@ -14130,7 +14141,7 @@
         <v>229</v>
       </c>
       <c r="H379">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I379">
         <v>122</v>
@@ -14145,7 +14156,7 @@
         <v>230</v>
       </c>
       <c r="H380">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I380">
         <v>122</v>
@@ -14163,7 +14174,7 @@
         <v>222</v>
       </c>
       <c r="H381">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I381">
         <v>114</v>
@@ -14178,7 +14189,7 @@
         <v>223</v>
       </c>
       <c r="H382">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I382">
         <v>114</v>
@@ -14193,7 +14204,7 @@
         <v>224</v>
       </c>
       <c r="H383">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I383">
         <v>114</v>
@@ -14223,7 +14234,7 @@
         <v>226</v>
       </c>
       <c r="H385">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I385">
         <v>114</v>
@@ -14238,7 +14249,7 @@
         <v>227</v>
       </c>
       <c r="H386">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I386">
         <v>114</v>
@@ -14268,7 +14279,7 @@
         <v>229</v>
       </c>
       <c r="H388">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I388">
         <v>114</v>
@@ -14283,7 +14294,7 @@
         <v>230</v>
       </c>
       <c r="H389">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I389">
         <v>114</v>
@@ -14301,7 +14312,7 @@
         <v>222</v>
       </c>
       <c r="H390">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I390">
         <v>195</v>
@@ -14316,7 +14327,7 @@
         <v>223</v>
       </c>
       <c r="H391">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I391">
         <v>195</v>
@@ -14331,7 +14342,7 @@
         <v>224</v>
       </c>
       <c r="H392">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="I392">
         <v>195</v>
@@ -14346,7 +14357,7 @@
         <v>225</v>
       </c>
       <c r="H393">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I393">
         <v>195</v>
@@ -14361,7 +14372,7 @@
         <v>226</v>
       </c>
       <c r="H394">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="I394">
         <v>195</v>
@@ -14376,7 +14387,7 @@
         <v>227</v>
       </c>
       <c r="H395">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="I395">
         <v>195</v>
@@ -14391,7 +14402,7 @@
         <v>228</v>
       </c>
       <c r="H396">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I396">
         <v>195</v>
@@ -14406,7 +14417,7 @@
         <v>229</v>
       </c>
       <c r="H397">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I397">
         <v>195</v>
@@ -14421,7 +14432,7 @@
         <v>230</v>
       </c>
       <c r="H398">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="I398">
         <v>195</v>
@@ -14439,7 +14450,7 @@
         <v>222</v>
       </c>
       <c r="H399">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="I399">
         <v>161</v>
@@ -14454,7 +14465,7 @@
         <v>223</v>
       </c>
       <c r="H400">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I400">
         <v>161</v>
@@ -14469,7 +14480,7 @@
         <v>224</v>
       </c>
       <c r="H401">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I401">
         <v>161</v>
@@ -14484,7 +14495,7 @@
         <v>225</v>
       </c>
       <c r="H402">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="I402">
         <v>161</v>
@@ -14499,7 +14510,7 @@
         <v>226</v>
       </c>
       <c r="H403">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I403">
         <v>161</v>
@@ -14514,7 +14525,7 @@
         <v>227</v>
       </c>
       <c r="H404">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I404">
         <v>161</v>
@@ -14529,7 +14540,7 @@
         <v>228</v>
       </c>
       <c r="H405">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I405">
         <v>161</v>
@@ -14544,7 +14555,7 @@
         <v>229</v>
       </c>
       <c r="H406">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I406">
         <v>161</v>
@@ -14559,7 +14570,7 @@
         <v>230</v>
       </c>
       <c r="H407">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I407">
         <v>161</v>

--- a/data/ventas.xlsx
+++ b/data/ventas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cesar\Desktop\Reportes Ventas Rap\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B38A1ECE-0E51-4269-8094-37DB251324AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9CD65A72-776C-4954-B430-B2927854684C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2540,22 +2540,22 @@
         <v>0</v>
       </c>
       <c r="C2" s="96">
-        <v>54563.0283089636</v>
+        <v>58505.265374438502</v>
       </c>
       <c r="D2" s="96">
-        <v>260206.8107035108</v>
+        <v>273974.59280026332</v>
       </c>
       <c r="E2" s="96">
-        <v>885063636.71088195</v>
+        <v>942730778.12102687</v>
       </c>
       <c r="F2" s="96">
         <v>0</v>
       </c>
       <c r="G2" s="96">
-        <v>383781.55311044212</v>
+        <v>422317.67258803378</v>
       </c>
       <c r="H2" s="96">
-        <v>383781.74</v>
+        <v>422317.85</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -2566,22 +2566,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="96">
-        <v>572.62823782090004</v>
+        <v>622.19177948770005</v>
       </c>
       <c r="D3" s="96">
-        <v>935.33198825989996</v>
+        <v>1024.1983945085001</v>
       </c>
       <c r="E3" s="96">
-        <v>12792718.437014684</v>
+        <v>14077255.752934411</v>
       </c>
       <c r="F3" s="96">
         <v>0</v>
       </c>
       <c r="G3" s="96">
-        <v>383781.55311044212</v>
+        <v>422317.67258803378</v>
       </c>
       <c r="H3" s="96">
-        <v>383781.74</v>
+        <v>422317.85</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2592,13 +2592,13 @@
         <v>1</v>
       </c>
       <c r="C4" s="96">
-        <v>380.24508928329999</v>
+        <v>440.13645833089998</v>
       </c>
       <c r="D4" s="96">
-        <v>750.88741071799996</v>
+        <v>818.46919643310002</v>
       </c>
       <c r="E4" s="96">
-        <v>10621962.126144474</v>
+        <v>11896290.267721681</v>
       </c>
       <c r="F4" s="96">
         <v>0</v>
@@ -2618,13 +2618,13 @@
         <v>1</v>
       </c>
       <c r="C5" s="96">
-        <v>507.97551587089998</v>
+        <v>565.20448412489998</v>
       </c>
       <c r="D5" s="96">
-        <v>1706.3107738065</v>
+        <v>2169.8357738070999</v>
       </c>
       <c r="E5" s="96">
-        <v>10967412.891714148</v>
+        <v>12287251.632388951</v>
       </c>
       <c r="F5" s="96">
         <v>0</v>
@@ -2644,13 +2644,13 @@
         <v>1</v>
       </c>
       <c r="C6" s="96">
-        <v>1010.0983928567</v>
+        <v>1081.1318253964</v>
       </c>
       <c r="D6" s="96">
-        <v>2838.9477381194001</v>
+        <v>2961.7110714546002</v>
       </c>
       <c r="E6" s="96">
-        <v>21241812.405432917</v>
+        <v>22371668.480170313</v>
       </c>
       <c r="F6" s="96">
         <v>0</v>
@@ -2670,13 +2670,13 @@
         <v>1</v>
       </c>
       <c r="C7" s="96">
-        <v>1020.4847182516</v>
+        <v>1080.4690436484</v>
       </c>
       <c r="D7" s="96">
-        <v>3984.8321785777998</v>
+        <v>4106.5442619117002</v>
       </c>
       <c r="E7" s="96">
-        <v>20343953.298605677</v>
+        <v>21392847.025956277</v>
       </c>
       <c r="F7" s="96">
         <v>0</v>
@@ -2696,13 +2696,13 @@
         <v>1</v>
       </c>
       <c r="C8" s="96">
-        <v>2504.6364074076</v>
+        <v>2500.4697407408999</v>
       </c>
       <c r="D8" s="96">
-        <v>4165.4464768565003</v>
+        <v>4082.9464768558</v>
       </c>
       <c r="E8" s="96">
-        <v>35141605.525244027</v>
+        <v>34946802.602325797</v>
       </c>
       <c r="F8" s="96">
         <v>0</v>
@@ -2722,13 +2722,13 @@
         <v>1</v>
       </c>
       <c r="C9" s="96">
-        <v>634.52771825369996</v>
+        <v>673.67959920659996</v>
       </c>
       <c r="D9" s="96">
-        <v>2715.0165416691002</v>
+        <v>2908.0165416699001</v>
       </c>
       <c r="E9" s="96">
-        <v>11583284.080894364</v>
+        <v>12584516.890795717</v>
       </c>
       <c r="F9" s="96">
         <v>0</v>
@@ -2748,13 +2748,13 @@
         <v>1</v>
       </c>
       <c r="C10" s="96">
-        <v>548.72655753940001</v>
+        <v>560.69205357119995</v>
       </c>
       <c r="D10" s="96">
-        <v>1542.5938265057</v>
+        <v>1571.6719217456</v>
       </c>
       <c r="E10" s="96">
-        <v>12850915.177441016</v>
+        <v>13277219.730041685</v>
       </c>
       <c r="F10" s="96">
         <v>0</v>
@@ -2774,13 +2774,13 @@
         <v>1</v>
       </c>
       <c r="C11" s="96">
-        <v>477.53224999819997</v>
+        <v>536.77748809349998</v>
       </c>
       <c r="D11" s="96">
-        <v>1238.3370952383</v>
+        <v>1482.3370952391001</v>
       </c>
       <c r="E11" s="96">
-        <v>8419876.3054508269</v>
+        <v>9453417.9587769005</v>
       </c>
       <c r="F11" s="96">
         <v>0</v>
@@ -2800,13 +2800,13 @@
         <v>1</v>
       </c>
       <c r="C12" s="96">
-        <v>828.06636110800002</v>
+        <v>890.29010317129996</v>
       </c>
       <c r="D12" s="96">
-        <v>3857.8762023697</v>
+        <v>4240.1128690380001</v>
       </c>
       <c r="E12" s="96">
-        <v>13449925.580210861</v>
+        <v>15064484.982327275</v>
       </c>
       <c r="F12" s="96">
         <v>0</v>
@@ -2826,13 +2826,13 @@
         <v>1</v>
       </c>
       <c r="C13" s="96">
-        <v>1012.3775793632</v>
+        <v>1062.2566785690999</v>
       </c>
       <c r="D13" s="96">
-        <v>2392.5997261978</v>
+        <v>2589.6907381013002</v>
       </c>
       <c r="E13" s="96">
-        <v>17565663.927074969</v>
+        <v>19347743.856695283</v>
       </c>
       <c r="F13" s="96">
         <v>0</v>
@@ -2852,13 +2852,13 @@
         <v>1</v>
       </c>
       <c r="C14" s="96">
-        <v>3963.072619048</v>
+        <v>4036.6059523814001</v>
       </c>
       <c r="D14" s="96">
-        <v>36247.932499996903</v>
+        <v>36547.9324999979</v>
       </c>
       <c r="E14" s="96">
-        <v>64304217.001077607</v>
+        <v>65596238.911079958</v>
       </c>
       <c r="F14" s="96">
         <v>0</v>
@@ -2878,13 +2878,13 @@
         <v>1</v>
       </c>
       <c r="C15" s="96">
-        <v>869.14722222030002</v>
+        <v>905.74484126790003</v>
       </c>
       <c r="D15" s="96">
-        <v>3369.6016666586002</v>
+        <v>3575.1241666564001</v>
       </c>
       <c r="E15" s="96">
-        <v>15725839.167291585</v>
+        <v>16877139.689307179</v>
       </c>
       <c r="F15" s="96">
         <v>0</v>
@@ -2904,13 +2904,13 @@
         <v>1</v>
       </c>
       <c r="C16" s="96">
-        <v>464.79805555370001</v>
+        <v>508.7474603151</v>
       </c>
       <c r="D16" s="96">
-        <v>2338.1130357237998</v>
+        <v>2464.3705357250001</v>
       </c>
       <c r="E16" s="96">
-        <v>12119565.962394305</v>
+        <v>13261392.359808654</v>
       </c>
       <c r="F16" s="96">
         <v>0</v>
@@ -2930,13 +2930,13 @@
         <v>1</v>
       </c>
       <c r="C17" s="96">
-        <v>1029.9283055527001</v>
+        <v>1088.9443769812999</v>
       </c>
       <c r="D17" s="96">
-        <v>2861.6129523987001</v>
+        <v>2991.6753928728999</v>
       </c>
       <c r="E17" s="96">
-        <v>20167812.79109044</v>
+        <v>21783715.745983802</v>
       </c>
       <c r="F17" s="96">
         <v>0</v>
@@ -2956,13 +2956,13 @@
         <v>1</v>
       </c>
       <c r="C18" s="96">
-        <v>1412.5037777752</v>
+        <v>1474.1537380929999</v>
       </c>
       <c r="D18" s="96">
-        <v>6177.8516190375003</v>
+        <v>6402.1041190419</v>
       </c>
       <c r="E18" s="96">
-        <v>25816464.992216989</v>
+        <v>26937005.080985263</v>
       </c>
       <c r="F18" s="96">
         <v>0</v>
@@ -2982,13 +2982,13 @@
         <v>1</v>
       </c>
       <c r="C19" s="96">
-        <v>1194.5462089912</v>
+        <v>1274.6862883563001</v>
       </c>
       <c r="D19" s="96">
-        <v>4286.9402262046997</v>
+        <v>4655.9612381137003</v>
       </c>
       <c r="E19" s="96">
-        <v>23966157.061793938</v>
+        <v>25788895.62215988</v>
       </c>
       <c r="F19" s="96">
         <v>0</v>
@@ -3008,13 +3008,13 @@
         <v>1</v>
       </c>
       <c r="C20" s="96">
-        <v>3508.6099166665999</v>
+        <v>3786.6001944444001</v>
       </c>
       <c r="D20" s="96">
-        <v>15461.246833323699</v>
+        <v>17533.019333324501</v>
       </c>
       <c r="E20" s="96">
-        <v>55125480.325350739</v>
+        <v>59333161.464760199</v>
       </c>
       <c r="F20" s="96">
         <v>0</v>
@@ -3034,13 +3034,13 @@
         <v>1</v>
       </c>
       <c r="C21" s="96">
-        <v>579.55577380600005</v>
+        <v>615.33484126650001</v>
       </c>
       <c r="D21" s="96">
-        <v>2214.4087381038999</v>
+        <v>2414.6612381065002</v>
       </c>
       <c r="E21" s="96">
-        <v>12810368.916756971</v>
+        <v>13501972.617272178</v>
       </c>
       <c r="F21" s="96">
         <v>0</v>
@@ -3060,13 +3060,13 @@
         <v>1</v>
       </c>
       <c r="C22" s="96">
-        <v>420.12088491920002</v>
+        <v>471.90600396650001</v>
       </c>
       <c r="D22" s="96">
-        <v>1580.969023808</v>
+        <v>1692.1829523797001</v>
       </c>
       <c r="E22" s="96">
-        <v>7669142.5805392843</v>
+        <v>8338730.6322451513</v>
       </c>
       <c r="F22" s="96">
         <v>0</v>
@@ -3112,13 +3112,13 @@
         <v>1</v>
       </c>
       <c r="C24" s="96">
-        <v>3181.5931547619998</v>
+        <v>3181.4264880953001</v>
       </c>
       <c r="D24" s="96">
         <v>23090.136053568302</v>
       </c>
       <c r="E24" s="96">
-        <v>53747040.528584458</v>
+        <v>53743536.921917096</v>
       </c>
       <c r="F24" s="96">
         <v>0</v>
@@ -3138,13 +3138,13 @@
         <v>1</v>
       </c>
       <c r="C25" s="96">
-        <v>628.11695634729995</v>
+        <v>675.41417856889996</v>
       </c>
       <c r="D25" s="96">
-        <v>2590.2491666810001</v>
+        <v>2959.9912500175001</v>
       </c>
       <c r="E25" s="96">
-        <v>11588903.613097664</v>
+        <v>12802627.864902593</v>
       </c>
       <c r="F25" s="96">
         <v>0</v>
@@ -3164,13 +3164,13 @@
         <v>1</v>
       </c>
       <c r="C26" s="96">
-        <v>784.00873015690001</v>
+        <v>840.58888888670003</v>
       </c>
       <c r="D26" s="96">
-        <v>1674.4697738176999</v>
+        <v>1768.1776904830001</v>
       </c>
       <c r="E26" s="96">
-        <v>10653241.374119855</v>
+        <v>11452040.387756737</v>
       </c>
       <c r="F26" s="96">
         <v>0</v>
@@ -3190,13 +3190,13 @@
         <v>1</v>
       </c>
       <c r="C27" s="96">
-        <v>7615.0857142857003</v>
+        <v>8164.9607142857003</v>
       </c>
       <c r="D27" s="96">
-        <v>17396.539999999801</v>
+        <v>17737.549999999799</v>
       </c>
       <c r="E27" s="96">
-        <v>72314066.082918748</v>
+        <v>77097707.321156248</v>
       </c>
       <c r="F27" s="96">
         <v>0</v>
@@ -3216,13 +3216,13 @@
         <v>1</v>
       </c>
       <c r="C28" s="96">
-        <v>815.06844907130005</v>
+        <v>843.38471891239999</v>
       </c>
       <c r="D28" s="96">
-        <v>3472.4468378094002</v>
+        <v>3562.4468378097999</v>
       </c>
       <c r="E28" s="96">
-        <v>15729400.126823407</v>
+        <v>16175526.924235191</v>
       </c>
       <c r="F28" s="96">
         <v>0</v>
@@ -3242,13 +3242,13 @@
         <v>1</v>
       </c>
       <c r="C29" s="96">
-        <v>3269.3926984126001</v>
+        <v>3409.3926984126001</v>
       </c>
       <c r="D29" s="96">
         <v>8462.8200000057004</v>
       </c>
       <c r="E29" s="96">
-        <v>43692487.08063937</v>
+        <v>44876701.927839369</v>
       </c>
       <c r="F29" s="96">
         <v>0</v>
@@ -3268,13 +3268,13 @@
         <v>1</v>
       </c>
       <c r="C30" s="96"